--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ37"/>
+  <dimension ref="A1:AM38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -523,6 +523,9 @@
     <col width="15" customWidth="1" min="34" max="34"/>
     <col width="26" customWidth="1" min="35" max="35"/>
     <col width="14" customWidth="1" min="36" max="36"/>
+    <col width="15" customWidth="1" min="37" max="37"/>
+    <col width="26" customWidth="1" min="38" max="38"/>
+    <col width="20" customWidth="1" min="39" max="39"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -566,6 +569,9 @@
       <c r="AH1" s="1" t="n"/>
       <c r="AI1" s="1" t="n"/>
       <c r="AJ1" s="1" t="n"/>
+      <c r="AK1" s="1" t="n"/>
+      <c r="AL1" s="1" t="n"/>
+      <c r="AM1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -660,6 +666,13 @@
       </c>
       <c r="AI2" s="2" t="n"/>
       <c r="AJ2" s="3" t="n"/>
+      <c r="AK2" s="2" t="inlineStr">
+        <is>
+          <t>December_2025</t>
+        </is>
+      </c>
+      <c r="AL2" s="2" t="n"/>
+      <c r="AM2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n"/>
@@ -830,6 +843,21 @@
           <t>% Net Assets</t>
         </is>
       </c>
+      <c r="AK3" s="4" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="AL3" s="4" t="inlineStr">
+        <is>
+          <t>Market Value (Rs. Lakhs)</t>
+        </is>
+      </c>
+      <c r="AM3" s="5" t="inlineStr">
+        <is>
+          <t>% Net Assets</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -946,6 +974,15 @@
       <c r="AJ4" s="10" t="n">
         <v>0.0803</v>
       </c>
+      <c r="AK4" s="8" t="n">
+        <v>108738215</v>
+      </c>
+      <c r="AL4" s="9" t="n">
+        <v>1077813.19</v>
+      </c>
+      <c r="AM4" s="10" t="n">
+        <v>0.0809</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -1062,6 +1099,15 @@
       <c r="AJ5" s="10" t="n">
         <v>0.0591</v>
       </c>
+      <c r="AK5" s="8" t="n">
+        <v>305419267</v>
+      </c>
+      <c r="AL5" s="9" t="n">
+        <v>808139.38</v>
+      </c>
+      <c r="AM5" s="10" t="n">
+        <v>0.0606</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -1178,6 +1224,15 @@
       <c r="AJ6" s="10" t="n">
         <v>0.0471</v>
       </c>
+      <c r="AK6" s="8" t="n">
+        <v>5318918</v>
+      </c>
+      <c r="AL6" s="9" t="n">
+        <v>602527.03</v>
+      </c>
+      <c r="AM6" s="10" t="n">
+        <v>0.0452</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -1294,6 +1349,15 @@
       <c r="AJ7" s="10" t="n">
         <v>0.047</v>
       </c>
+      <c r="AK7" s="8" t="n">
+        <v>162039558</v>
+      </c>
+      <c r="AL7" s="9" t="n">
+        <v>646537.84</v>
+      </c>
+      <c r="AM7" s="10" t="n">
+        <v>0.0485</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -1410,6 +1474,15 @@
       <c r="AJ8" s="10" t="n">
         <v>0.0451</v>
       </c>
+      <c r="AK8" s="8" t="n">
+        <v>148665711</v>
+      </c>
+      <c r="AL8" s="9" t="n">
+        <v>599122.8199999999</v>
+      </c>
+      <c r="AM8" s="10" t="n">
+        <v>0.0449</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -1526,6 +1599,15 @@
       <c r="AJ9" s="10" t="n">
         <v>0.0485</v>
       </c>
+      <c r="AK9" s="8" t="n">
+        <v>49325234</v>
+      </c>
+      <c r="AL9" s="9" t="n">
+        <v>662388.5699999999</v>
+      </c>
+      <c r="AM9" s="10" t="n">
+        <v>0.0497</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -1642,6 +1724,15 @@
       <c r="AJ10" s="10" t="n">
         <v>0.0398</v>
       </c>
+      <c r="AK10" s="8" t="n">
+        <v>24621592</v>
+      </c>
+      <c r="AL10" s="9" t="n">
+        <v>541945.86</v>
+      </c>
+      <c r="AM10" s="10" t="n">
+        <v>0.0407</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -1757,6 +1848,15 @@
       </c>
       <c r="AJ11" s="10" t="n">
         <v>0.0337</v>
+      </c>
+      <c r="AK11" s="8" t="n">
+        <v>2746670</v>
+      </c>
+      <c r="AL11" s="9" t="n">
+        <v>458611.49</v>
+      </c>
+      <c r="AM11" s="10" t="n">
+        <v>0.0344</v>
       </c>
     </row>
     <row r="12">
@@ -1850,6 +1950,15 @@
       <c r="AJ12" s="10" t="n">
         <v>0.0343</v>
       </c>
+      <c r="AK12" s="8" t="n">
+        <v>21167034</v>
+      </c>
+      <c r="AL12" s="9" t="n">
+        <v>445693.07</v>
+      </c>
+      <c r="AM12" s="10" t="n">
+        <v>0.0334</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -1966,6 +2075,15 @@
       <c r="AJ13" s="10" t="n">
         <v>0.036</v>
       </c>
+      <c r="AK13" s="8" t="n">
+        <v>13033470</v>
+      </c>
+      <c r="AL13" s="9" t="n">
+        <v>483437.47</v>
+      </c>
+      <c r="AM13" s="10" t="n">
+        <v>0.0363</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -2082,6 +2200,15 @@
       <c r="AJ14" s="10" t="n">
         <v>0.0328</v>
       </c>
+      <c r="AK14" s="8" t="n">
+        <v>33244875</v>
+      </c>
+      <c r="AL14" s="9" t="n">
+        <v>422010.44</v>
+      </c>
+      <c r="AM14" s="10" t="n">
+        <v>0.0317</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -2198,6 +2325,15 @@
       <c r="AJ15" s="10" t="n">
         <v>0.0248</v>
       </c>
+      <c r="AK15" s="8" t="n">
+        <v>21315882</v>
+      </c>
+      <c r="AL15" s="9" t="n">
+        <v>346020.71</v>
+      </c>
+      <c r="AM15" s="10" t="n">
+        <v>0.026</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -2314,6 +2450,15 @@
       <c r="AJ16" s="10" t="n">
         <v>0.0126</v>
       </c>
+      <c r="AK16" s="8" t="n">
+        <v>17903094</v>
+      </c>
+      <c r="AL16" s="9" t="n">
+        <v>163696.94</v>
+      </c>
+      <c r="AM16" s="10" t="n">
+        <v>0.0123</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -2430,6 +2575,15 @@
       <c r="AJ17" s="10" t="n">
         <v>0.0127</v>
       </c>
+      <c r="AK17" s="8" t="n">
+        <v>13125545</v>
+      </c>
+      <c r="AL17" s="9" t="n">
+        <v>166878.18</v>
+      </c>
+      <c r="AM17" s="10" t="n">
+        <v>0.0125</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -2546,6 +2700,15 @@
       <c r="AJ18" s="10" t="n">
         <v>0.0127</v>
       </c>
+      <c r="AK18" s="8" t="n">
+        <v>10989584</v>
+      </c>
+      <c r="AL18" s="9" t="n">
+        <v>166085.58</v>
+      </c>
+      <c r="AM18" s="10" t="n">
+        <v>0.0125</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -2662,6 +2825,15 @@
       <c r="AJ19" s="10" t="n">
         <v>0.0212</v>
       </c>
+      <c r="AK19" s="8" t="n">
+        <v>16417936</v>
+      </c>
+      <c r="AL19" s="9" t="n">
+        <v>265215.34</v>
+      </c>
+      <c r="AM19" s="10" t="n">
+        <v>0.0199</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -2777,6 +2949,15 @@
       </c>
       <c r="AJ20" s="10" t="n">
         <v>0.008699999999999999</v>
+      </c>
+      <c r="AK20" s="8" t="n">
+        <v>80755676</v>
+      </c>
+      <c r="AL20" s="9" t="n">
+        <v>108390.27</v>
+      </c>
+      <c r="AM20" s="10" t="n">
+        <v>0.0081</v>
       </c>
     </row>
     <row r="21">
@@ -2846,6 +3027,15 @@
       <c r="AJ21" s="10" t="n">
         <v>0.0073</v>
       </c>
+      <c r="AK21" s="8" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="AL21" s="9" t="n">
+        <v>100012</v>
+      </c>
+      <c r="AM21" s="10" t="n">
+        <v>0.0075</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -2962,6 +3152,15 @@
       <c r="AJ22" s="10" t="n">
         <v>0.0075</v>
       </c>
+      <c r="AK22" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="AL22" s="9" t="n">
+        <v>97173.95</v>
+      </c>
+      <c r="AM22" s="10" t="n">
+        <v>0.0073</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -3078,6 +3277,15 @@
       <c r="AJ23" s="10" t="n">
         <v>0.0062</v>
       </c>
+      <c r="AK23" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AL23" s="9" t="n">
+        <v>88833.99000000001</v>
+      </c>
+      <c r="AM23" s="10" t="n">
+        <v>0.0067</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -3194,6 +3402,15 @@
       <c r="AJ24" s="10" t="n">
         <v>0.0046</v>
       </c>
+      <c r="AK24" s="8" t="n">
+        <v>6180145</v>
+      </c>
+      <c r="AL24" s="9" t="n">
+        <v>63945.96</v>
+      </c>
+      <c r="AM24" s="10" t="n">
+        <v>0.0048</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -3310,6 +3527,15 @@
       <c r="AJ25" s="10" t="n">
         <v>0.0028</v>
       </c>
+      <c r="AK25" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="AL25" s="9" t="n">
+        <v>32691.81</v>
+      </c>
+      <c r="AM25" s="10" t="n">
+        <v>0.0025</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -3426,6 +3652,15 @@
       <c r="AJ26" s="10" t="n">
         <v>0.003</v>
       </c>
+      <c r="AK26" s="8" t="n">
+        <v>1995914</v>
+      </c>
+      <c r="AL26" s="9" t="n">
+        <v>37762.69</v>
+      </c>
+      <c r="AM26" s="10" t="n">
+        <v>0.0028</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -3542,6 +3777,15 @@
       <c r="AJ27" s="10" t="n">
         <v>0.0014</v>
       </c>
+      <c r="AK27" s="8" t="n">
+        <v>287393</v>
+      </c>
+      <c r="AL27" s="9" t="n">
+        <v>17460.56</v>
+      </c>
+      <c r="AM27" s="10" t="n">
+        <v>0.0013</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -3656,6 +3900,15 @@
         <v>11787.38</v>
       </c>
       <c r="AJ28" s="10" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="AK28" s="8" t="n">
+        <v>80159</v>
+      </c>
+      <c r="AL28" s="9" t="n">
+        <v>11401.01</v>
+      </c>
+      <c r="AM28" s="10" t="n">
         <v>0.0009</v>
       </c>
     </row>
@@ -3750,6 +4003,15 @@
       <c r="AJ29" s="10" t="n">
         <v>0.0002</v>
       </c>
+      <c r="AK29" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AL29" s="9" t="n">
+        <v>1858.32</v>
+      </c>
+      <c r="AM29" s="10" t="n">
+        <v>0.0001</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -3864,6 +4126,15 @@
         <v>1764.08</v>
       </c>
       <c r="AJ30" s="10" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AK30" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="AL30" s="9" t="n">
+        <v>1691.91</v>
+      </c>
+      <c r="AM30" s="10" t="n">
         <v>0.0001</v>
       </c>
     </row>
@@ -3934,6 +4205,9 @@
       <c r="AH31" s="8" t="n"/>
       <c r="AI31" s="9" t="n"/>
       <c r="AJ31" s="10" t="n"/>
+      <c r="AK31" s="8" t="n"/>
+      <c r="AL31" s="9" t="n"/>
+      <c r="AM31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -4032,6 +4306,9 @@
       <c r="AH32" s="8" t="n"/>
       <c r="AI32" s="9" t="n"/>
       <c r="AJ32" s="10" t="n"/>
+      <c r="AK32" s="8" t="n"/>
+      <c r="AL32" s="9" t="n"/>
+      <c r="AM32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -4118,6 +4395,9 @@
       <c r="AH33" s="8" t="n"/>
       <c r="AI33" s="9" t="n"/>
       <c r="AJ33" s="10" t="n"/>
+      <c r="AK33" s="8" t="n"/>
+      <c r="AL33" s="9" t="n"/>
+      <c r="AM33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -4186,6 +4466,9 @@
       <c r="AH34" s="8" t="n"/>
       <c r="AI34" s="9" t="n"/>
       <c r="AJ34" s="10" t="n"/>
+      <c r="AK34" s="8" t="n"/>
+      <c r="AL34" s="9" t="n"/>
+      <c r="AM34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -4242,21 +4525,30 @@
       <c r="AJ35" s="10" t="n">
         <v>0.0068</v>
       </c>
+      <c r="AK35" s="8" t="n">
+        <v>4654589</v>
+      </c>
+      <c r="AL35" s="9" t="n">
+        <v>149235.43</v>
+      </c>
+      <c r="AM35" s="10" t="n">
+        <v>0.0112</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Indus Towers Limited</t>
+          <t>The Great Eastern Shipping Company Limited</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>INE121J01017</t>
+          <t>INE017A01032</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Telecom - Services</t>
+          <t>Transport Services</t>
         </is>
       </c>
       <c r="D36" s="8" t="n"/>
@@ -4289,133 +4581,211 @@
       <c r="AE36" s="8" t="n"/>
       <c r="AF36" s="9" t="n"/>
       <c r="AG36" s="10" t="n"/>
-      <c r="AH36" s="8" t="n">
-        <v>710855</v>
-      </c>
-      <c r="AI36" s="9" t="n">
-        <v>2850.8839775</v>
-      </c>
-      <c r="AJ36" s="10" t="n">
-        <v>0.0002</v>
+      <c r="AH36" s="8" t="n"/>
+      <c r="AI36" s="9" t="n"/>
+      <c r="AJ36" s="10" t="n"/>
+      <c r="AK36" s="8" t="n">
+        <v>1657424</v>
+      </c>
+      <c r="AL36" s="9" t="n">
+        <v>18712.32</v>
+      </c>
+      <c r="AM36" s="10" t="n">
+        <v>0.0014</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Indus Towers Limited</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>INE121J01017</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Telecom - Services</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="10" t="n"/>
+      <c r="G37" s="8" t="n"/>
+      <c r="H37" s="9" t="n"/>
+      <c r="I37" s="10" t="n"/>
+      <c r="J37" s="8" t="n"/>
+      <c r="K37" s="9" t="n"/>
+      <c r="L37" s="10" t="n"/>
+      <c r="M37" s="8" t="n"/>
+      <c r="N37" s="9" t="n"/>
+      <c r="O37" s="10" t="n"/>
+      <c r="P37" s="8" t="n"/>
+      <c r="Q37" s="9" t="n"/>
+      <c r="R37" s="10" t="n"/>
+      <c r="S37" s="8" t="n"/>
+      <c r="T37" s="9" t="n"/>
+      <c r="U37" s="10" t="n"/>
+      <c r="V37" s="8" t="n"/>
+      <c r="W37" s="9" t="n"/>
+      <c r="X37" s="10" t="n"/>
+      <c r="Y37" s="8" t="n"/>
+      <c r="Z37" s="9" t="n"/>
+      <c r="AA37" s="10" t="n"/>
+      <c r="AB37" s="8" t="n"/>
+      <c r="AC37" s="9" t="n"/>
+      <c r="AD37" s="10" t="n"/>
+      <c r="AE37" s="8" t="n"/>
+      <c r="AF37" s="9" t="n"/>
+      <c r="AG37" s="10" t="n"/>
+      <c r="AH37" s="8" t="n">
+        <v>710855</v>
+      </c>
+      <c r="AI37" s="9" t="n">
+        <v>2850.8839775</v>
+      </c>
+      <c r="AJ37" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AK37" s="8" t="n">
+        <v>710855</v>
+      </c>
+      <c r="AL37" s="9" t="n">
+        <v>2976.71</v>
+      </c>
+      <c r="AM37" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="12" t="n"/>
-      <c r="D37" s="13" t="n">
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="12" t="n"/>
+      <c r="D38" s="13" t="n">
         <v>697292654</v>
       </c>
-      <c r="E37" s="14" t="n">
+      <c r="E38" s="14" t="n">
         <v>5868142.6</v>
       </c>
-      <c r="F37" s="15" t="n">
+      <c r="F38" s="15" t="n">
         <v>0.6543000000000002</v>
       </c>
-      <c r="G37" s="13" t="n">
+      <c r="G38" s="13" t="n">
         <v>718063829</v>
       </c>
-      <c r="H37" s="14" t="n">
+      <c r="H38" s="14" t="n">
         <v>5662977.75</v>
       </c>
-      <c r="I37" s="15" t="n">
+      <c r="I38" s="15" t="n">
         <v>0.6436999999999999</v>
       </c>
-      <c r="J37" s="13" t="n">
+      <c r="J38" s="13" t="n">
         <v>717176528</v>
       </c>
-      <c r="K37" s="14" t="n">
+      <c r="K38" s="14" t="n">
         <v>6051937.58</v>
       </c>
-      <c r="L37" s="15" t="n">
+      <c r="L38" s="15" t="n">
         <v>0.6476999999999997</v>
       </c>
-      <c r="M37" s="13" t="n">
+      <c r="M38" s="13" t="n">
         <v>719050337</v>
       </c>
-      <c r="N37" s="14" t="n">
+      <c r="N38" s="14" t="n">
         <v>6275568.750000001</v>
       </c>
-      <c r="O37" s="15" t="n">
+      <c r="O38" s="15" t="n">
         <v>0.6370000000000001</v>
       </c>
-      <c r="P37" s="13" t="n">
+      <c r="P38" s="13" t="n">
         <v>756845974</v>
       </c>
-      <c r="Q37" s="14" t="n">
+      <c r="Q38" s="14" t="n">
         <v>6714757.130000002</v>
       </c>
-      <c r="R37" s="15" t="n">
+      <c r="R38" s="15" t="n">
         <v>0.6467999999999998</v>
       </c>
-      <c r="S37" s="13" t="n">
+      <c r="S38" s="13" t="n">
         <v>799425942</v>
       </c>
-      <c r="T37" s="14" t="n">
+      <c r="T38" s="14" t="n">
         <v>7347454.069999999</v>
       </c>
-      <c r="U37" s="15" t="n">
+      <c r="U38" s="15" t="n">
         <v>0.6657999999999999</v>
       </c>
-      <c r="V37" s="13" t="n">
+      <c r="V38" s="13" t="n">
         <v>819556049</v>
       </c>
-      <c r="W37" s="14" t="n">
+      <c r="W38" s="14" t="n">
         <v>7290583.900000001</v>
       </c>
-      <c r="X37" s="15" t="n">
+      <c r="X38" s="15" t="n">
         <v>0.6436999999999998</v>
       </c>
-      <c r="Y37" s="13" t="n">
+      <c r="Y38" s="13" t="n">
         <v>927478800</v>
       </c>
-      <c r="Z37" s="14" t="n">
+      <c r="Z38" s="14" t="n">
         <v>7320811.49</v>
       </c>
-      <c r="AA37" s="15" t="n">
+      <c r="AA38" s="15" t="n">
         <v>0.6363999999999999</v>
       </c>
-      <c r="AB37" s="13" t="n">
+      <c r="AB38" s="13" t="n">
         <v>979359723</v>
       </c>
-      <c r="AC37" s="14" t="n">
+      <c r="AC38" s="14" t="n">
         <v>7559180.720000002</v>
       </c>
-      <c r="AD37" s="15" t="n">
+      <c r="AD38" s="15" t="n">
         <v>0.6313999999999996</v>
       </c>
-      <c r="AE37" s="13" t="n">
+      <c r="AE38" s="13" t="n">
         <v>991416407</v>
       </c>
-      <c r="AF37" s="14" t="n">
+      <c r="AF38" s="14" t="n">
         <v>7865128.239999998</v>
       </c>
-      <c r="AG37" s="15" t="n">
+      <c r="AG38" s="15" t="n">
         <v>0.6254999999999999</v>
       </c>
-      <c r="AH37" s="13" t="n">
+      <c r="AH38" s="13" t="n">
         <v>1039629309</v>
       </c>
-      <c r="AI37" s="14" t="n">
+      <c r="AI38" s="14" t="n">
         <v>8271351.1939775</v>
       </c>
-      <c r="AJ37" s="15" t="n">
+      <c r="AJ38" s="15" t="n">
         <v>0.6374</v>
+      </c>
+      <c r="AK38" s="13" t="n">
+        <v>1079845116</v>
+      </c>
+      <c r="AL38" s="14" t="n">
+        <v>8588270.840000002</v>
+      </c>
+      <c r="AM38" s="15" t="n">
+        <v>0.6443999999999998</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
-    <mergeCell ref="A1:AJ1"/>
+    <mergeCell ref="A1:AM1"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="Y2:AA2"/>
     <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="AE2:AG2"/>
+    <mergeCell ref="AK2:AM2"/>
     <mergeCell ref="P2:R2"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="S2:U2"/>

--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -495,7 +495,7 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
@@ -513,7 +513,7 @@
     <col width="20" customWidth="1" min="24" max="24"/>
     <col width="13" customWidth="1" min="25" max="25"/>
     <col width="26" customWidth="1" min="26" max="26"/>
-    <col width="20" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
     <col width="16" customWidth="1" min="28" max="28"/>
     <col width="26" customWidth="1" min="29" max="29"/>
     <col width="20" customWidth="1" min="30" max="30"/>
@@ -522,7 +522,7 @@
     <col width="14" customWidth="1" min="33" max="33"/>
     <col width="15" customWidth="1" min="34" max="34"/>
     <col width="26" customWidth="1" min="35" max="35"/>
-    <col width="14" customWidth="1" min="36" max="36"/>
+    <col width="20" customWidth="1" min="36" max="36"/>
     <col width="15" customWidth="1" min="37" max="37"/>
     <col width="26" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
@@ -1112,501 +1112,501 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Bajaj Holdings &amp; Investment Limited</t>
+          <t>ICICI Bank Limited</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>INE118A01012</t>
+          <t>INE090A01021</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>5318918</v>
+        <v>34986740</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>614850.96</v>
+        <v>438313.88</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.0489</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>5318918</v>
+        <v>34986740</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>615630.1899999999</v>
+        <v>421275.34</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0479</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>5318918</v>
+        <v>34986740</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>663431.3</v>
+        <v>471743.71</v>
       </c>
       <c r="L6" s="10" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.0505</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>5318918</v>
+        <v>34986740</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>636834.05</v>
+        <v>499260.78</v>
       </c>
       <c r="O6" s="10" t="n">
-        <v>0.0646</v>
+        <v>0.0507</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>5318918</v>
+        <v>34986740</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>713479.66</v>
+        <v>505838.29</v>
       </c>
       <c r="R6" s="10" t="n">
-        <v>0.0687</v>
+        <v>0.0487</v>
       </c>
       <c r="S6" s="8" t="n">
-        <v>5318918</v>
+        <v>36489310</v>
       </c>
       <c r="T6" s="9" t="n">
-        <v>764807.22</v>
+        <v>527562.4399999999</v>
       </c>
       <c r="U6" s="10" t="n">
-        <v>0.0693</v>
+        <v>0.0478</v>
       </c>
       <c r="V6" s="8" t="n">
-        <v>5318918</v>
+        <v>39605543</v>
       </c>
       <c r="W6" s="9" t="n">
-        <v>742680.52</v>
+        <v>586716.51</v>
       </c>
       <c r="X6" s="10" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0518</v>
       </c>
       <c r="Y6" s="8" t="n">
-        <v>5318918</v>
+        <v>40720543</v>
       </c>
       <c r="Z6" s="9" t="n">
-        <v>679225.83</v>
+        <v>569191.75</v>
       </c>
       <c r="AA6" s="10" t="n">
-        <v>0.059</v>
+        <v>0.0495</v>
       </c>
       <c r="AB6" s="8" t="n">
-        <v>5318918</v>
+        <v>42215573</v>
       </c>
       <c r="AC6" s="9" t="n">
-        <v>651407.89</v>
+        <v>569065.92</v>
       </c>
       <c r="AD6" s="10" t="n">
-        <v>0.0544</v>
+        <v>0.0475</v>
       </c>
       <c r="AE6" s="8" t="n">
-        <v>5318918</v>
+        <v>43295573</v>
       </c>
       <c r="AF6" s="9" t="n">
-        <v>654386.48</v>
+        <v>582455.34</v>
       </c>
       <c r="AG6" s="10" t="n">
-        <v>0.052</v>
+        <v>0.0463</v>
       </c>
       <c r="AH6" s="8" t="n">
-        <v>5318918</v>
+        <v>45308598</v>
       </c>
       <c r="AI6" s="9" t="n">
-        <v>611622.38</v>
+        <v>629245.8100000001</v>
       </c>
       <c r="AJ6" s="10" t="n">
-        <v>0.0471</v>
+        <v>0.0485</v>
       </c>
       <c r="AK6" s="8" t="n">
-        <v>5318918</v>
+        <v>49325234</v>
       </c>
       <c r="AL6" s="9" t="n">
-        <v>602527.03</v>
+        <v>662388.5699999999</v>
       </c>
       <c r="AM6" s="10" t="n">
-        <v>0.0452</v>
+        <v>0.0497</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Coal India Limited</t>
+          <t>Bajaj Holdings &amp; Investment Limited</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>INE522F01014</t>
+          <t>INE118A01012</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Consumable Fuels</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>139335199</v>
+        <v>5318918</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>551628.05</v>
+        <v>614850.96</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.0615</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>142636407</v>
+        <v>5318918</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>526827.5699999999</v>
+        <v>615630.1899999999</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>0.0599</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>141074007</v>
+        <v>5318918</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>561756.7</v>
+        <v>663431.3</v>
       </c>
       <c r="L7" s="10" t="n">
-        <v>0.0601</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>148323775</v>
+        <v>5318918</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>571491.51</v>
+        <v>636834.05</v>
       </c>
       <c r="O7" s="10" t="n">
-        <v>0.058</v>
+        <v>0.0646</v>
       </c>
       <c r="P7" s="8" t="n">
-        <v>155681572</v>
+        <v>5318918</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>618522.89</v>
+        <v>713479.66</v>
       </c>
       <c r="R7" s="10" t="n">
-        <v>0.0595</v>
+        <v>0.0687</v>
       </c>
       <c r="S7" s="8" t="n">
-        <v>162039558</v>
+        <v>5318918</v>
       </c>
       <c r="T7" s="9" t="n">
-        <v>635114.05</v>
+        <v>764807.22</v>
       </c>
       <c r="U7" s="10" t="n">
-        <v>0.0575</v>
+        <v>0.0693</v>
       </c>
       <c r="V7" s="8" t="n">
-        <v>162039558</v>
+        <v>5318918</v>
       </c>
       <c r="W7" s="9" t="n">
-        <v>609835.88</v>
+        <v>742680.52</v>
       </c>
       <c r="X7" s="10" t="n">
-        <v>0.0538</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="Y7" s="8" t="n">
-        <v>162039558</v>
+        <v>5318918</v>
       </c>
       <c r="Z7" s="9" t="n">
-        <v>607324.26</v>
+        <v>679225.83</v>
       </c>
       <c r="AA7" s="10" t="n">
-        <v>0.0528</v>
+        <v>0.059</v>
       </c>
       <c r="AB7" s="8" t="n">
-        <v>162039558</v>
+        <v>5318918</v>
       </c>
       <c r="AC7" s="9" t="n">
-        <v>631873.26</v>
+        <v>651407.89</v>
       </c>
       <c r="AD7" s="10" t="n">
-        <v>0.0528</v>
+        <v>0.0544</v>
       </c>
       <c r="AE7" s="8" t="n">
-        <v>162039558</v>
+        <v>5318918</v>
       </c>
       <c r="AF7" s="9" t="n">
-        <v>629766.74</v>
+        <v>654386.48</v>
       </c>
       <c r="AG7" s="10" t="n">
-        <v>0.0501</v>
+        <v>0.052</v>
       </c>
       <c r="AH7" s="8" t="n">
-        <v>162039558</v>
+        <v>5318918</v>
       </c>
       <c r="AI7" s="9" t="n">
-        <v>609511.8</v>
+        <v>611622.38</v>
       </c>
       <c r="AJ7" s="10" t="n">
-        <v>0.047</v>
+        <v>0.0471</v>
       </c>
       <c r="AK7" s="8" t="n">
-        <v>162039558</v>
+        <v>5318918</v>
       </c>
       <c r="AL7" s="9" t="n">
-        <v>646537.84</v>
+        <v>602527.03</v>
       </c>
       <c r="AM7" s="10" t="n">
-        <v>0.0485</v>
+        <v>0.0452</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>ITC Limited</t>
+          <t>Coal India Limited</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>INE154A01025</t>
+          <t>INE522F01014</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Diversified FMCG</t>
+          <t>Consumable Fuels</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>98994120</v>
+        <v>139335199</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>442998.69</v>
+        <v>551628.05</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>0.0494</v>
+        <v>0.0615</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>101194120</v>
+        <v>142636407</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>399716.77</v>
+        <v>526827.5699999999</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>0.0454</v>
+        <v>0.0599</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>101194120</v>
+        <v>141074007</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>414642.91</v>
+        <v>561756.7</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>0.0444</v>
+        <v>0.0601</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>105271096</v>
+        <v>148323775</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>448244.33</v>
+        <v>571491.51</v>
       </c>
       <c r="O8" s="10" t="n">
-        <v>0.0455</v>
+        <v>0.058</v>
       </c>
       <c r="P8" s="8" t="n">
-        <v>109270669</v>
+        <v>155681572</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>456806.03</v>
+        <v>618522.89</v>
       </c>
       <c r="R8" s="10" t="n">
-        <v>0.044</v>
+        <v>0.0595</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>117422359</v>
+        <v>162039558</v>
       </c>
       <c r="T8" s="9" t="n">
-        <v>489005.41</v>
+        <v>635114.05</v>
       </c>
       <c r="U8" s="10" t="n">
-        <v>0.0443</v>
+        <v>0.0575</v>
       </c>
       <c r="V8" s="8" t="n">
-        <v>122172359</v>
+        <v>162039558</v>
       </c>
       <c r="W8" s="9" t="n">
-        <v>503289.03</v>
+        <v>609835.88</v>
       </c>
       <c r="X8" s="10" t="n">
-        <v>0.0444</v>
+        <v>0.0538</v>
       </c>
       <c r="Y8" s="8" t="n">
-        <v>129421024</v>
+        <v>162039558</v>
       </c>
       <c r="Z8" s="9" t="n">
-        <v>530302.65</v>
+        <v>607324.26</v>
       </c>
       <c r="AA8" s="10" t="n">
-        <v>0.0461</v>
+        <v>0.0528</v>
       </c>
       <c r="AB8" s="8" t="n">
-        <v>135721024</v>
+        <v>162039558</v>
       </c>
       <c r="AC8" s="9" t="n">
-        <v>544987.77</v>
+        <v>631873.26</v>
       </c>
       <c r="AD8" s="10" t="n">
-        <v>0.0455</v>
+        <v>0.0528</v>
       </c>
       <c r="AE8" s="8" t="n">
-        <v>138771024</v>
+        <v>162039558</v>
       </c>
       <c r="AF8" s="9" t="n">
-        <v>583324</v>
+        <v>629766.74</v>
       </c>
       <c r="AG8" s="10" t="n">
-        <v>0.0464</v>
+        <v>0.0501</v>
       </c>
       <c r="AH8" s="8" t="n">
-        <v>144737169</v>
+        <v>162039558</v>
       </c>
       <c r="AI8" s="9" t="n">
-        <v>585100.01</v>
+        <v>609511.8</v>
       </c>
       <c r="AJ8" s="10" t="n">
-        <v>0.0451</v>
+        <v>0.047</v>
       </c>
       <c r="AK8" s="8" t="n">
-        <v>148665711</v>
+        <v>162039558</v>
       </c>
       <c r="AL8" s="9" t="n">
-        <v>599122.8199999999</v>
+        <v>646537.84</v>
       </c>
       <c r="AM8" s="10" t="n">
-        <v>0.0449</v>
+        <v>0.0485</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>ICICI Bank Limited</t>
+          <t>ITC Limited</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>INE090A01021</t>
+          <t>INE154A01025</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Diversified FMCG</t>
         </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>34986740</v>
+        <v>98994120</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>438313.88</v>
+        <v>442998.69</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.0489</v>
+        <v>0.0494</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>34986740</v>
+        <v>101194120</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>421275.34</v>
+        <v>399716.77</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>0.0479</v>
+        <v>0.0454</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>34986740</v>
+        <v>101194120</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>471743.71</v>
+        <v>414642.91</v>
       </c>
       <c r="L9" s="10" t="n">
-        <v>0.0505</v>
+        <v>0.0444</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>34986740</v>
+        <v>105271096</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>499260.78</v>
+        <v>448244.33</v>
       </c>
       <c r="O9" s="10" t="n">
-        <v>0.0507</v>
+        <v>0.0455</v>
       </c>
       <c r="P9" s="8" t="n">
-        <v>34986740</v>
+        <v>109270669</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>505838.29</v>
+        <v>456806.03</v>
       </c>
       <c r="R9" s="10" t="n">
-        <v>0.0487</v>
+        <v>0.044</v>
       </c>
       <c r="S9" s="8" t="n">
-        <v>36489310</v>
+        <v>117422359</v>
       </c>
       <c r="T9" s="9" t="n">
-        <v>527562.4399999999</v>
+        <v>489005.41</v>
       </c>
       <c r="U9" s="10" t="n">
-        <v>0.0478</v>
+        <v>0.0443</v>
       </c>
       <c r="V9" s="8" t="n">
-        <v>39605543</v>
+        <v>122172359</v>
       </c>
       <c r="W9" s="9" t="n">
-        <v>586716.51</v>
+        <v>503289.03</v>
       </c>
       <c r="X9" s="10" t="n">
-        <v>0.0518</v>
+        <v>0.0444</v>
       </c>
       <c r="Y9" s="8" t="n">
-        <v>40720543</v>
+        <v>129421024</v>
       </c>
       <c r="Z9" s="9" t="n">
-        <v>569191.75</v>
+        <v>530302.65</v>
       </c>
       <c r="AA9" s="10" t="n">
-        <v>0.0495</v>
+        <v>0.0461</v>
       </c>
       <c r="AB9" s="8" t="n">
-        <v>42215573</v>
+        <v>135721024</v>
       </c>
       <c r="AC9" s="9" t="n">
-        <v>569065.92</v>
+        <v>544987.77</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>0.0475</v>
+        <v>0.0455</v>
       </c>
       <c r="AE9" s="8" t="n">
-        <v>43295573</v>
+        <v>138771024</v>
       </c>
       <c r="AF9" s="9" t="n">
-        <v>582455.34</v>
+        <v>583324</v>
       </c>
       <c r="AG9" s="10" t="n">
-        <v>0.0463</v>
+        <v>0.0464</v>
       </c>
       <c r="AH9" s="8" t="n">
-        <v>45308598</v>
+        <v>144737169</v>
       </c>
       <c r="AI9" s="9" t="n">
-        <v>629245.8100000001</v>
+        <v>585100.01</v>
       </c>
       <c r="AJ9" s="10" t="n">
-        <v>0.0485</v>
+        <v>0.0451</v>
       </c>
       <c r="AK9" s="8" t="n">
-        <v>49325234</v>
+        <v>148665711</v>
       </c>
       <c r="AL9" s="9" t="n">
-        <v>662388.5699999999</v>
+        <v>599122.8199999999</v>
       </c>
       <c r="AM9" s="10" t="n">
-        <v>0.0497</v>
+        <v>0.0449</v>
       </c>
     </row>
     <row r="10">
@@ -1737,12 +1737,12 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Maruti Suzuki India Limited</t>
+          <t>Mahindra &amp; Mahindra Limited</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>INE585B01010</t>
+          <t>INE101A01026</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -1751,112 +1751,112 @@
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>3018078</v>
+        <v>9331737</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>371545.02</v>
+        <v>279004.94</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.0414</v>
+        <v>0.0311</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>3018078</v>
+        <v>10068665</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>360535.07</v>
+        <v>260285.06</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>0.041</v>
+        <v>0.0296</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>3018078</v>
+        <v>10399289</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>347747.47</v>
+        <v>277224.25</v>
       </c>
       <c r="L11" s="10" t="n">
-        <v>0.0372</v>
+        <v>0.0297</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>3021670</v>
+        <v>11040212</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>370366.09</v>
+        <v>323345.73</v>
       </c>
       <c r="O11" s="10" t="n">
-        <v>0.0376</v>
+        <v>0.0328</v>
       </c>
       <c r="P11" s="8" t="n">
-        <v>3021670</v>
+        <v>12231374</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>372239.53</v>
+        <v>364103.54</v>
       </c>
       <c r="R11" s="10" t="n">
-        <v>0.0358</v>
+        <v>0.0351</v>
       </c>
       <c r="S11" s="8" t="n">
-        <v>3021670</v>
+        <v>12335671</v>
       </c>
       <c r="T11" s="9" t="n">
-        <v>374687.08</v>
+        <v>392669.08</v>
       </c>
       <c r="U11" s="10" t="n">
-        <v>0.0339</v>
+        <v>0.0356</v>
       </c>
       <c r="V11" s="8" t="n">
-        <v>3021670</v>
+        <v>12335671</v>
       </c>
       <c r="W11" s="9" t="n">
-        <v>380972.15</v>
+        <v>395123.88</v>
       </c>
       <c r="X11" s="10" t="n">
-        <v>0.0336</v>
+        <v>0.0349</v>
       </c>
       <c r="Y11" s="8" t="n">
-        <v>2746670</v>
+        <v>12335671</v>
       </c>
       <c r="Z11" s="9" t="n">
-        <v>406259.96</v>
+        <v>394679.79</v>
       </c>
       <c r="AA11" s="10" t="n">
+        <v>0.0343</v>
+      </c>
+      <c r="AB11" s="8" t="n">
+        <v>12335671</v>
+      </c>
+      <c r="AC11" s="9" t="n">
+        <v>422743.45</v>
+      </c>
+      <c r="AD11" s="10" t="n">
         <v>0.0353</v>
       </c>
-      <c r="AB11" s="8" t="n">
-        <v>2696670</v>
-      </c>
-      <c r="AC11" s="9" t="n">
-        <v>432249.23</v>
-      </c>
-      <c r="AD11" s="10" t="n">
-        <v>0.0361</v>
-      </c>
       <c r="AE11" s="8" t="n">
-        <v>2696670</v>
+        <v>12435671</v>
       </c>
       <c r="AF11" s="9" t="n">
-        <v>436483.01</v>
+        <v>433656.72</v>
       </c>
       <c r="AG11" s="10" t="n">
-        <v>0.0347</v>
+        <v>0.0345</v>
       </c>
       <c r="AH11" s="8" t="n">
-        <v>2746670</v>
+        <v>12435671</v>
       </c>
       <c r="AI11" s="9" t="n">
-        <v>436720.53</v>
+        <v>467245.47</v>
       </c>
       <c r="AJ11" s="10" t="n">
-        <v>0.0337</v>
+        <v>0.036</v>
       </c>
       <c r="AK11" s="8" t="n">
-        <v>2746670</v>
+        <v>13033470</v>
       </c>
       <c r="AL11" s="9" t="n">
-        <v>458611.49</v>
+        <v>483437.47</v>
       </c>
       <c r="AM11" s="10" t="n">
-        <v>0.0344</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="12">
@@ -1963,12 +1963,12 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Mahindra &amp; Mahindra Limited</t>
+          <t>Maruti Suzuki India Limited</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>INE101A01026</t>
+          <t>INE585B01010</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -1977,112 +1977,112 @@
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>9331737</v>
+        <v>3018078</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>279004.94</v>
+        <v>371545.02</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.0311</v>
+        <v>0.0414</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>10068665</v>
+        <v>3018078</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>260285.06</v>
+        <v>360535.07</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>0.0296</v>
+        <v>0.041</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>10399289</v>
+        <v>3018078</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>277224.25</v>
+        <v>347747.47</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>0.0297</v>
+        <v>0.0372</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>11040212</v>
+        <v>3021670</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>323345.73</v>
+        <v>370366.09</v>
       </c>
       <c r="O13" s="10" t="n">
-        <v>0.0328</v>
+        <v>0.0376</v>
       </c>
       <c r="P13" s="8" t="n">
-        <v>12231374</v>
+        <v>3021670</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>364103.54</v>
+        <v>372239.53</v>
       </c>
       <c r="R13" s="10" t="n">
-        <v>0.0351</v>
+        <v>0.0358</v>
       </c>
       <c r="S13" s="8" t="n">
-        <v>12335671</v>
+        <v>3021670</v>
       </c>
       <c r="T13" s="9" t="n">
-        <v>392669.08</v>
+        <v>374687.08</v>
       </c>
       <c r="U13" s="10" t="n">
-        <v>0.0356</v>
+        <v>0.0339</v>
       </c>
       <c r="V13" s="8" t="n">
-        <v>12335671</v>
+        <v>3021670</v>
       </c>
       <c r="W13" s="9" t="n">
-        <v>395123.88</v>
+        <v>380972.15</v>
       </c>
       <c r="X13" s="10" t="n">
-        <v>0.0349</v>
+        <v>0.0336</v>
       </c>
       <c r="Y13" s="8" t="n">
-        <v>12335671</v>
+        <v>2746670</v>
       </c>
       <c r="Z13" s="9" t="n">
-        <v>394679.79</v>
+        <v>406259.96</v>
       </c>
       <c r="AA13" s="10" t="n">
-        <v>0.0343</v>
+        <v>0.0353</v>
       </c>
       <c r="AB13" s="8" t="n">
-        <v>12335671</v>
+        <v>2696670</v>
       </c>
       <c r="AC13" s="9" t="n">
-        <v>422743.45</v>
+        <v>432249.23</v>
       </c>
       <c r="AD13" s="10" t="n">
-        <v>0.0353</v>
+        <v>0.0361</v>
       </c>
       <c r="AE13" s="8" t="n">
-        <v>12435671</v>
+        <v>2696670</v>
       </c>
       <c r="AF13" s="9" t="n">
-        <v>433656.72</v>
+        <v>436483.01</v>
       </c>
       <c r="AG13" s="10" t="n">
-        <v>0.0345</v>
+        <v>0.0347</v>
       </c>
       <c r="AH13" s="8" t="n">
-        <v>12435671</v>
+        <v>2746670</v>
       </c>
       <c r="AI13" s="9" t="n">
-        <v>467245.47</v>
+        <v>436720.53</v>
       </c>
       <c r="AJ13" s="10" t="n">
-        <v>0.036</v>
+        <v>0.0337</v>
       </c>
       <c r="AK13" s="8" t="n">
-        <v>13033470</v>
+        <v>2746670</v>
       </c>
       <c r="AL13" s="9" t="n">
-        <v>483437.47</v>
+        <v>458611.49</v>
       </c>
       <c r="AM13" s="10" t="n">
-        <v>0.0363</v>
+        <v>0.0344</v>
       </c>
     </row>
     <row r="14">
@@ -2338,126 +2338,126 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences Limited</t>
+          <t>Infosys Limited</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>INE010B01027</t>
+          <t>INE009A01021</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Pharmaceuticals &amp; Biotechnology</t>
+          <t>IT - Software</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>8859127</v>
+        <v>9306473</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>85955.67999999999</v>
+        <v>174943.08</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0195</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>11479604</v>
+        <v>9306473</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>100630.21</v>
+        <v>157065.34</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>0.0114</v>
+        <v>0.0178</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>13003659</v>
+        <v>9306473</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>115264.43</v>
+        <v>146172.12</v>
       </c>
       <c r="L16" s="10" t="n">
-        <v>0.0123</v>
+        <v>0.0156</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>13936283</v>
+        <v>9306473</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>123789.03</v>
+        <v>139606.4</v>
       </c>
       <c r="O16" s="10" t="n">
-        <v>0.0126</v>
+        <v>0.0142</v>
       </c>
       <c r="P16" s="8" t="n">
-        <v>14258435</v>
+        <v>9306473</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>132603.45</v>
+        <v>145432.25</v>
       </c>
       <c r="R16" s="10" t="n">
-        <v>0.0128</v>
+        <v>0.014</v>
       </c>
       <c r="S16" s="8" t="n">
-        <v>14258435</v>
+        <v>9306473</v>
       </c>
       <c r="T16" s="9" t="n">
-        <v>141151.38</v>
+        <v>149071.08</v>
       </c>
       <c r="U16" s="10" t="n">
-        <v>0.0128</v>
+        <v>0.0135</v>
       </c>
       <c r="V16" s="8" t="n">
-        <v>14470385</v>
+        <v>9306473</v>
       </c>
       <c r="W16" s="9" t="n">
-        <v>140333.79</v>
+        <v>140434.68</v>
       </c>
       <c r="X16" s="10" t="n">
         <v>0.0124</v>
       </c>
       <c r="Y16" s="8" t="n">
-        <v>14786344</v>
+        <v>9306473</v>
       </c>
       <c r="Z16" s="9" t="n">
-        <v>145061.43</v>
+        <v>136767.93</v>
       </c>
       <c r="AA16" s="10" t="n">
-        <v>0.0126</v>
+        <v>0.0119</v>
       </c>
       <c r="AB16" s="8" t="n">
-        <v>15148311</v>
+        <v>9306473</v>
       </c>
       <c r="AC16" s="9" t="n">
-        <v>148741.27</v>
+        <v>134180.73</v>
       </c>
       <c r="AD16" s="10" t="n">
-        <v>0.0124</v>
+        <v>0.0112</v>
       </c>
       <c r="AE16" s="8" t="n">
-        <v>15759789</v>
+        <v>9306473</v>
       </c>
       <c r="AF16" s="9" t="n">
-        <v>153571.26</v>
+        <v>137949.85</v>
       </c>
       <c r="AG16" s="10" t="n">
-        <v>0.0122</v>
+        <v>0.011</v>
       </c>
       <c r="AH16" s="8" t="n">
-        <v>17405149</v>
+        <v>17621740</v>
       </c>
       <c r="AI16" s="9" t="n">
-        <v>164043.53</v>
+        <v>274916.77</v>
       </c>
       <c r="AJ16" s="10" t="n">
-        <v>0.0126</v>
+        <v>0.0212</v>
       </c>
       <c r="AK16" s="8" t="n">
-        <v>17903094</v>
+        <v>16417936</v>
       </c>
       <c r="AL16" s="9" t="n">
-        <v>163696.94</v>
+        <v>265215.34</v>
       </c>
       <c r="AM16" s="10" t="n">
-        <v>0.0123</v>
+        <v>0.0199</v>
       </c>
     </row>
     <row r="17">
@@ -2713,126 +2713,126 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Infosys Limited</t>
+          <t>Zydus Lifesciences Limited</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>INE009A01021</t>
+          <t>INE010B01027</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>IT - Software</t>
+          <t>Pharmaceuticals &amp; Biotechnology</t>
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>9306473</v>
+        <v>8859127</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>174943.08</v>
+        <v>85955.67999999999</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>0.0195</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>9306473</v>
+        <v>11479604</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>157065.34</v>
+        <v>100630.21</v>
       </c>
       <c r="I19" s="10" t="n">
-        <v>0.0178</v>
+        <v>0.0114</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>9306473</v>
+        <v>13003659</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>146172.12</v>
+        <v>115264.43</v>
       </c>
       <c r="L19" s="10" t="n">
-        <v>0.0156</v>
+        <v>0.0123</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>9306473</v>
+        <v>13936283</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>139606.4</v>
+        <v>123789.03</v>
       </c>
       <c r="O19" s="10" t="n">
-        <v>0.0142</v>
+        <v>0.0126</v>
       </c>
       <c r="P19" s="8" t="n">
-        <v>9306473</v>
+        <v>14258435</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>145432.25</v>
+        <v>132603.45</v>
       </c>
       <c r="R19" s="10" t="n">
-        <v>0.014</v>
+        <v>0.0128</v>
       </c>
       <c r="S19" s="8" t="n">
-        <v>9306473</v>
+        <v>14258435</v>
       </c>
       <c r="T19" s="9" t="n">
-        <v>149071.08</v>
+        <v>141151.38</v>
       </c>
       <c r="U19" s="10" t="n">
-        <v>0.0135</v>
+        <v>0.0128</v>
       </c>
       <c r="V19" s="8" t="n">
-        <v>9306473</v>
+        <v>14470385</v>
       </c>
       <c r="W19" s="9" t="n">
-        <v>140434.68</v>
+        <v>140333.79</v>
       </c>
       <c r="X19" s="10" t="n">
         <v>0.0124</v>
       </c>
       <c r="Y19" s="8" t="n">
-        <v>9306473</v>
+        <v>14786344</v>
       </c>
       <c r="Z19" s="9" t="n">
-        <v>136767.93</v>
+        <v>145061.43</v>
       </c>
       <c r="AA19" s="10" t="n">
-        <v>0.0119</v>
+        <v>0.0126</v>
       </c>
       <c r="AB19" s="8" t="n">
-        <v>9306473</v>
+        <v>15148311</v>
       </c>
       <c r="AC19" s="9" t="n">
-        <v>134180.73</v>
+        <v>148741.27</v>
       </c>
       <c r="AD19" s="10" t="n">
-        <v>0.0112</v>
+        <v>0.0124</v>
       </c>
       <c r="AE19" s="8" t="n">
-        <v>9306473</v>
+        <v>15759789</v>
       </c>
       <c r="AF19" s="9" t="n">
-        <v>137949.85</v>
+        <v>153571.26</v>
       </c>
       <c r="AG19" s="10" t="n">
-        <v>0.011</v>
+        <v>0.0122</v>
       </c>
       <c r="AH19" s="8" t="n">
-        <v>17621740</v>
+        <v>17405149</v>
       </c>
       <c r="AI19" s="9" t="n">
-        <v>274916.77</v>
+        <v>164043.53</v>
       </c>
       <c r="AJ19" s="10" t="n">
-        <v>0.0212</v>
+        <v>0.0126</v>
       </c>
       <c r="AK19" s="8" t="n">
-        <v>16417936</v>
+        <v>17903094</v>
       </c>
       <c r="AL19" s="9" t="n">
-        <v>265215.34</v>
+        <v>163696.94</v>
       </c>
       <c r="AM19" s="10" t="n">
-        <v>0.0199</v>
+        <v>0.0123</v>
       </c>
     </row>
     <row r="20">
@@ -2963,578 +2963,518 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited</t>
+          <t>Balkrishna Industries Limited</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>INE768C01028</t>
+          <t>INE787D01026</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="10" t="n"/>
-      <c r="G21" s="8" t="n"/>
-      <c r="H21" s="9" t="n"/>
-      <c r="I21" s="10" t="n"/>
-      <c r="J21" s="8" t="n"/>
-      <c r="K21" s="9" t="n"/>
-      <c r="L21" s="10" t="n"/>
-      <c r="M21" s="8" t="n"/>
-      <c r="N21" s="9" t="n"/>
-      <c r="O21" s="10" t="n"/>
-      <c r="P21" s="8" t="n"/>
-      <c r="Q21" s="9" t="n"/>
-      <c r="R21" s="10" t="n"/>
-      <c r="S21" s="8" t="n"/>
-      <c r="T21" s="9" t="n"/>
-      <c r="U21" s="10" t="n"/>
-      <c r="V21" s="8" t="n"/>
-      <c r="W21" s="9" t="n"/>
-      <c r="X21" s="10" t="n"/>
-      <c r="Y21" s="8" t="n"/>
-      <c r="Z21" s="9" t="n"/>
-      <c r="AA21" s="10" t="n"/>
+          <t>Auto Components</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>116089.71</v>
+      </c>
+      <c r="F21" s="10" t="n">
+        <v>0.0129</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>109571.51</v>
+      </c>
+      <c r="I21" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="J21" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="K21" s="9" t="n">
+        <v>107022.46</v>
+      </c>
+      <c r="L21" s="10" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="M21" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="N21" s="9" t="n">
+        <v>112061.92</v>
+      </c>
+      <c r="O21" s="10" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="P21" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="Q21" s="9" t="n">
+        <v>103562.29</v>
+      </c>
+      <c r="R21" s="10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="S21" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="T21" s="9" t="n">
+        <v>102435.43</v>
+      </c>
+      <c r="U21" s="10" t="n">
+        <v>0.009299999999999999</v>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="W21" s="9" t="n">
+        <v>112108</v>
+      </c>
+      <c r="X21" s="10" t="n">
+        <v>0.009900000000000001</v>
+      </c>
+      <c r="Y21" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="Z21" s="9" t="n">
+        <v>95904.66</v>
+      </c>
+      <c r="AA21" s="10" t="n">
+        <v>0.0083</v>
+      </c>
       <c r="AB21" s="8" t="n">
-        <v>22000000</v>
+        <v>4189074</v>
       </c>
       <c r="AC21" s="9" t="n">
-        <v>100584</v>
+        <v>96130.87</v>
       </c>
       <c r="AD21" s="10" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="AE21" s="8" t="n">
-        <v>22000000</v>
+        <v>4189074</v>
       </c>
       <c r="AF21" s="9" t="n">
-        <v>104852</v>
+        <v>95502.50999999999</v>
       </c>
       <c r="AG21" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.0076</v>
       </c>
       <c r="AH21" s="8" t="n">
-        <v>22000000</v>
+        <v>4189074</v>
       </c>
       <c r="AI21" s="9" t="n">
-        <v>94699</v>
+        <v>96721.53</v>
       </c>
       <c r="AJ21" s="10" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="AK21" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="AL21" s="9" t="n">
+        <v>97173.95</v>
+      </c>
+      <c r="AM21" s="10" t="n">
         <v>0.0073</v>
-      </c>
-      <c r="AK21" s="8" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="AL21" s="9" t="n">
-        <v>100012</v>
-      </c>
-      <c r="AM21" s="10" t="n">
-        <v>0.0075</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Balkrishna Industries Limited</t>
+          <t>Zydus Wellness Limited</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>INE787D01026</t>
+          <t>INE768C01028</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Auto Components</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>116089.71</v>
-      </c>
-      <c r="F22" s="10" t="n">
-        <v>0.0129</v>
-      </c>
-      <c r="G22" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="H22" s="9" t="n">
-        <v>109571.51</v>
-      </c>
-      <c r="I22" s="10" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="J22" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="K22" s="9" t="n">
-        <v>107022.46</v>
-      </c>
-      <c r="L22" s="10" t="n">
-        <v>0.0115</v>
-      </c>
-      <c r="M22" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="N22" s="9" t="n">
-        <v>112061.92</v>
-      </c>
-      <c r="O22" s="10" t="n">
-        <v>0.0114</v>
-      </c>
-      <c r="P22" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="Q22" s="9" t="n">
-        <v>103562.29</v>
-      </c>
-      <c r="R22" s="10" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="S22" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="T22" s="9" t="n">
-        <v>102435.43</v>
-      </c>
-      <c r="U22" s="10" t="n">
-        <v>0.009299999999999999</v>
-      </c>
-      <c r="V22" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="W22" s="9" t="n">
-        <v>112108</v>
-      </c>
-      <c r="X22" s="10" t="n">
-        <v>0.009900000000000001</v>
-      </c>
-      <c r="Y22" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="Z22" s="9" t="n">
-        <v>95904.66</v>
-      </c>
-      <c r="AA22" s="10" t="n">
+          <t>Food Products</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="10" t="n"/>
+      <c r="G22" s="8" t="n"/>
+      <c r="H22" s="9" t="n"/>
+      <c r="I22" s="10" t="n"/>
+      <c r="J22" s="8" t="n"/>
+      <c r="K22" s="9" t="n"/>
+      <c r="L22" s="10" t="n"/>
+      <c r="M22" s="8" t="n"/>
+      <c r="N22" s="9" t="n"/>
+      <c r="O22" s="10" t="n"/>
+      <c r="P22" s="8" t="n"/>
+      <c r="Q22" s="9" t="n"/>
+      <c r="R22" s="10" t="n"/>
+      <c r="S22" s="8" t="n"/>
+      <c r="T22" s="9" t="n"/>
+      <c r="U22" s="10" t="n"/>
+      <c r="V22" s="8" t="n"/>
+      <c r="W22" s="9" t="n"/>
+      <c r="X22" s="10" t="n"/>
+      <c r="Y22" s="8" t="n"/>
+      <c r="Z22" s="9" t="n"/>
+      <c r="AA22" s="10" t="n"/>
+      <c r="AB22" s="8" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="AC22" s="9" t="n">
+        <v>100584</v>
+      </c>
+      <c r="AD22" s="10" t="n">
+        <v>0.008399999999999999</v>
+      </c>
+      <c r="AE22" s="8" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="AF22" s="9" t="n">
+        <v>104852</v>
+      </c>
+      <c r="AG22" s="10" t="n">
         <v>0.0083</v>
       </c>
-      <c r="AB22" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="AC22" s="9" t="n">
-        <v>96130.87</v>
-      </c>
-      <c r="AD22" s="10" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="AE22" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="AF22" s="9" t="n">
-        <v>95502.50999999999</v>
-      </c>
-      <c r="AG22" s="10" t="n">
-        <v>0.0076</v>
-      </c>
       <c r="AH22" s="8" t="n">
-        <v>4189074</v>
+        <v>22000000</v>
       </c>
       <c r="AI22" s="9" t="n">
-        <v>96721.53</v>
+        <v>94699</v>
       </c>
       <c r="AJ22" s="10" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="AK22" s="8" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="AL22" s="9" t="n">
+        <v>100012</v>
+      </c>
+      <c r="AM22" s="10" t="n">
         <v>0.0075</v>
-      </c>
-      <c r="AK22" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="AL22" s="9" t="n">
-        <v>97173.95</v>
-      </c>
-      <c r="AM22" s="10" t="n">
-        <v>0.0073</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Multi Commodity Exchange of India Limited</t>
+          <t>Tata Consultancy Services Limited</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>INE745G01035</t>
+          <t>INE467B01029</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="n">
-        <v>882136</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>50572.42</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>0.0056</v>
-      </c>
-      <c r="G23" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="H23" s="9" t="n">
-        <v>39819.34</v>
-      </c>
-      <c r="I23" s="10" t="n">
-        <v>0.0045</v>
-      </c>
-      <c r="J23" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="K23" s="9" t="n">
-        <v>42372.84</v>
-      </c>
-      <c r="L23" s="10" t="n">
-        <v>0.0045</v>
-      </c>
-      <c r="M23" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="N23" s="9" t="n">
-        <v>48884.22</v>
-      </c>
-      <c r="O23" s="10" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="P23" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="Q23" s="9" t="n">
-        <v>52665.41</v>
-      </c>
-      <c r="R23" s="10" t="n">
-        <v>0.0051</v>
-      </c>
-      <c r="S23" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="T23" s="9" t="n">
-        <v>71347.99000000001</v>
-      </c>
-      <c r="U23" s="10" t="n">
-        <v>0.0065</v>
-      </c>
-      <c r="V23" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="W23" s="9" t="n">
-        <v>61368.52</v>
-      </c>
-      <c r="X23" s="10" t="n">
-        <v>0.0054</v>
-      </c>
-      <c r="Y23" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="Z23" s="9" t="n">
-        <v>58951.43</v>
-      </c>
-      <c r="AA23" s="10" t="n">
-        <v>0.0051</v>
-      </c>
-      <c r="AB23" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="AC23" s="9" t="n">
-        <v>62190.17</v>
-      </c>
-      <c r="AD23" s="10" t="n">
-        <v>0.0052</v>
-      </c>
-      <c r="AE23" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="AF23" s="9" t="n">
-        <v>73737.16</v>
-      </c>
-      <c r="AG23" s="10" t="n">
-        <v>0.0059</v>
-      </c>
+          <t>IT - Software</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="10" t="n"/>
+      <c r="G23" s="8" t="n"/>
+      <c r="H23" s="9" t="n"/>
+      <c r="I23" s="10" t="n"/>
+      <c r="J23" s="8" t="n"/>
+      <c r="K23" s="9" t="n"/>
+      <c r="L23" s="10" t="n"/>
+      <c r="M23" s="8" t="n"/>
+      <c r="N23" s="9" t="n"/>
+      <c r="O23" s="10" t="n"/>
+      <c r="P23" s="8" t="n"/>
+      <c r="Q23" s="9" t="n"/>
+      <c r="R23" s="10" t="n"/>
+      <c r="S23" s="8" t="n"/>
+      <c r="T23" s="9" t="n"/>
+      <c r="U23" s="10" t="n"/>
+      <c r="V23" s="8" t="n"/>
+      <c r="W23" s="9" t="n"/>
+      <c r="X23" s="10" t="n"/>
+      <c r="Y23" s="8" t="n"/>
+      <c r="Z23" s="9" t="n"/>
+      <c r="AA23" s="10" t="n"/>
+      <c r="AB23" s="8" t="n"/>
+      <c r="AC23" s="9" t="n"/>
+      <c r="AD23" s="10" t="n"/>
+      <c r="AE23" s="8" t="n"/>
+      <c r="AF23" s="9" t="n"/>
+      <c r="AG23" s="10" t="n"/>
       <c r="AH23" s="8" t="n">
-        <v>797719</v>
+        <v>2811139</v>
       </c>
       <c r="AI23" s="9" t="n">
-        <v>80358.22</v>
+        <v>88199.49000000001</v>
       </c>
       <c r="AJ23" s="10" t="n">
-        <v>0.0062</v>
+        <v>0.0068</v>
       </c>
       <c r="AK23" s="8" t="n">
-        <v>797719</v>
+        <v>4654589</v>
       </c>
       <c r="AL23" s="9" t="n">
-        <v>88833.99000000001</v>
+        <v>149235.43</v>
       </c>
       <c r="AM23" s="10" t="n">
-        <v>0.0067</v>
+        <v>0.0112</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>EID Parry India Limited</t>
+          <t>Multi Commodity Exchange of India Limited</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>INE126A01031</t>
+          <t>INE745G01035</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>2259531</v>
+        <v>882136</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>18525.89</v>
+        <v>50572.42</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>0.0021</v>
+        <v>0.0056</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>2609056</v>
+        <v>797719</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>17326.74</v>
+        <v>39819.34</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>0.002</v>
+        <v>0.0045</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>2843265</v>
+        <v>797719</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>22336.69</v>
+        <v>42372.84</v>
       </c>
       <c r="L24" s="10" t="n">
-        <v>0.0024</v>
+        <v>0.0045</v>
       </c>
       <c r="M24" s="8" t="n">
-        <v>2988209</v>
+        <v>797719</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>24424.13</v>
+        <v>48884.22</v>
       </c>
       <c r="O24" s="10" t="n">
-        <v>0.0025</v>
+        <v>0.005</v>
       </c>
       <c r="P24" s="8" t="n">
-        <v>3243008</v>
+        <v>797719</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>30813.44</v>
+        <v>52665.41</v>
       </c>
       <c r="R24" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0051</v>
       </c>
       <c r="S24" s="8" t="n">
-        <v>3516819</v>
+        <v>797719</v>
       </c>
       <c r="T24" s="9" t="n">
-        <v>39036.69</v>
+        <v>71347.99000000001</v>
       </c>
       <c r="U24" s="10" t="n">
-        <v>0.0035</v>
+        <v>0.0065</v>
       </c>
       <c r="V24" s="8" t="n">
-        <v>3997165</v>
+        <v>797719</v>
       </c>
       <c r="W24" s="9" t="n">
-        <v>49305.03</v>
+        <v>61368.52</v>
       </c>
       <c r="X24" s="10" t="n">
-        <v>0.0044</v>
+        <v>0.0054</v>
       </c>
       <c r="Y24" s="8" t="n">
-        <v>4433570</v>
+        <v>797719</v>
       </c>
       <c r="Z24" s="9" t="n">
-        <v>49913.13</v>
+        <v>58951.43</v>
       </c>
       <c r="AA24" s="10" t="n">
-        <v>0.0043</v>
+        <v>0.0051</v>
       </c>
       <c r="AB24" s="8" t="n">
-        <v>4996218</v>
+        <v>797719</v>
       </c>
       <c r="AC24" s="9" t="n">
-        <v>51236.22</v>
+        <v>62190.17</v>
       </c>
       <c r="AD24" s="10" t="n">
-        <v>0.0043</v>
+        <v>0.0052</v>
       </c>
       <c r="AE24" s="8" t="n">
-        <v>5528341</v>
+        <v>797719</v>
       </c>
       <c r="AF24" s="9" t="n">
-        <v>59285.93</v>
+        <v>73737.16</v>
       </c>
       <c r="AG24" s="10" t="n">
-        <v>0.0047</v>
+        <v>0.0059</v>
       </c>
       <c r="AH24" s="8" t="n">
-        <v>5842830</v>
+        <v>797719</v>
       </c>
       <c r="AI24" s="9" t="n">
-        <v>60233.73</v>
+        <v>80358.22</v>
       </c>
       <c r="AJ24" s="10" t="n">
-        <v>0.0046</v>
+        <v>0.0062</v>
       </c>
       <c r="AK24" s="8" t="n">
-        <v>6180145</v>
+        <v>797719</v>
       </c>
       <c r="AL24" s="9" t="n">
-        <v>63945.96</v>
+        <v>88833.99000000001</v>
       </c>
       <c r="AM24" s="10" t="n">
-        <v>0.0048</v>
+        <v>0.0067</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Central Depository Services (India) Limited</t>
+          <t>EID Parry India Limited</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>INE736A01011</t>
+          <t>INE126A01031</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>2264603</v>
+        <v>2259531</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>29659.51</v>
+        <v>18525.89</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>0.0033</v>
+        <v>0.0021</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>2264603</v>
+        <v>2609056</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>25089.54</v>
+        <v>17326.74</v>
       </c>
       <c r="I25" s="10" t="n">
-        <v>0.0029</v>
+        <v>0.002</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>2264603</v>
+        <v>2843265</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>27629.29</v>
+        <v>22336.69</v>
       </c>
       <c r="L25" s="10" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="M25" s="8" t="n">
+        <v>2988209</v>
+      </c>
+      <c r="N25" s="9" t="n">
+        <v>24424.13</v>
+      </c>
+      <c r="O25" s="10" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="P25" s="8" t="n">
+        <v>3243008</v>
+      </c>
+      <c r="Q25" s="9" t="n">
+        <v>30813.44</v>
+      </c>
+      <c r="R25" s="10" t="n">
         <v>0.003</v>
       </c>
-      <c r="M25" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="N25" s="9" t="n">
-        <v>29892.76</v>
-      </c>
-      <c r="O25" s="10" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="P25" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="Q25" s="9" t="n">
-        <v>34641.63</v>
-      </c>
-      <c r="R25" s="10" t="n">
-        <v>0.0033</v>
-      </c>
       <c r="S25" s="8" t="n">
-        <v>2264603</v>
+        <v>3516819</v>
       </c>
       <c r="T25" s="9" t="n">
-        <v>40626.98</v>
+        <v>39036.69</v>
       </c>
       <c r="U25" s="10" t="n">
-        <v>0.0037</v>
+        <v>0.0035</v>
       </c>
       <c r="V25" s="8" t="n">
-        <v>2264603</v>
+        <v>3997165</v>
       </c>
       <c r="W25" s="9" t="n">
-        <v>33534.24</v>
+        <v>49305.03</v>
       </c>
       <c r="X25" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0044</v>
       </c>
       <c r="Y25" s="8" t="n">
-        <v>2264603</v>
+        <v>4433570</v>
       </c>
       <c r="Z25" s="9" t="n">
-        <v>32257.01</v>
+        <v>49913.13</v>
       </c>
       <c r="AA25" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.0043</v>
       </c>
       <c r="AB25" s="8" t="n">
-        <v>2264603</v>
+        <v>4996218</v>
       </c>
       <c r="AC25" s="9" t="n">
-        <v>33031.5</v>
+        <v>51236.22</v>
       </c>
       <c r="AD25" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.0043</v>
       </c>
       <c r="AE25" s="8" t="n">
-        <v>2264603</v>
+        <v>5528341</v>
       </c>
       <c r="AF25" s="9" t="n">
-        <v>35943.78</v>
+        <v>59285.93</v>
       </c>
       <c r="AG25" s="10" t="n">
-        <v>0.0029</v>
+        <v>0.0047</v>
       </c>
       <c r="AH25" s="8" t="n">
-        <v>2264603</v>
+        <v>5842830</v>
       </c>
       <c r="AI25" s="9" t="n">
-        <v>36623.16</v>
+        <v>60233.73</v>
       </c>
       <c r="AJ25" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.0046</v>
       </c>
       <c r="AK25" s="8" t="n">
-        <v>2264603</v>
+        <v>6180145</v>
       </c>
       <c r="AL25" s="9" t="n">
-        <v>32691.81</v>
+        <v>63945.96</v>
       </c>
       <c r="AM25" s="10" t="n">
-        <v>0.0025</v>
+        <v>0.0048</v>
       </c>
     </row>
     <row r="26">
@@ -3665,12 +3605,12 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>ICRA Limited</t>
+          <t>Central Depository Services (India) Limited</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>INE725G01011</t>
+          <t>INE736A01011</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -3679,479 +3619,443 @@
         </is>
       </c>
       <c r="D27" s="8" t="n">
-        <v>297835</v>
+        <v>2264603</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>18529.51</v>
+        <v>29659.51</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>0.0021</v>
+        <v>0.0033</v>
       </c>
       <c r="G27" s="8" t="n">
-        <v>287393</v>
+        <v>2264603</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>15273.64</v>
+        <v>25089.54</v>
       </c>
       <c r="I27" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.0029</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>287393</v>
+        <v>2264603</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>15821.13</v>
+        <v>27629.29</v>
       </c>
       <c r="L27" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.003</v>
       </c>
       <c r="M27" s="8" t="n">
-        <v>287393</v>
+        <v>2264603</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>15976.18</v>
+        <v>29892.76</v>
       </c>
       <c r="O27" s="10" t="n">
-        <v>0.0016</v>
+        <v>0.003</v>
       </c>
       <c r="P27" s="8" t="n">
-        <v>287393</v>
+        <v>2264603</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>19370.29</v>
+        <v>34641.63</v>
       </c>
       <c r="R27" s="10" t="n">
-        <v>0.0019</v>
+        <v>0.0033</v>
       </c>
       <c r="S27" s="8" t="n">
-        <v>287393</v>
+        <v>2264603</v>
       </c>
       <c r="T27" s="9" t="n">
-        <v>19453.63</v>
+        <v>40626.98</v>
       </c>
       <c r="U27" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.0037</v>
       </c>
       <c r="V27" s="8" t="n">
-        <v>287393</v>
+        <v>2264603</v>
       </c>
       <c r="W27" s="9" t="n">
-        <v>19048.41</v>
+        <v>33534.24</v>
       </c>
       <c r="X27" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.003</v>
       </c>
       <c r="Y27" s="8" t="n">
-        <v>287393</v>
+        <v>2264603</v>
       </c>
       <c r="Z27" s="9" t="n">
-        <v>17962.06</v>
+        <v>32257.01</v>
       </c>
       <c r="AA27" s="10" t="n">
-        <v>0.0016</v>
+        <v>0.0028</v>
       </c>
       <c r="AB27" s="8" t="n">
-        <v>287393</v>
+        <v>2264603</v>
       </c>
       <c r="AC27" s="9" t="n">
-        <v>18243.71</v>
+        <v>33031.5</v>
       </c>
       <c r="AD27" s="10" t="n">
-        <v>0.0015</v>
+        <v>0.0028</v>
       </c>
       <c r="AE27" s="8" t="n">
-        <v>287393</v>
+        <v>2264603</v>
       </c>
       <c r="AF27" s="9" t="n">
-        <v>18463.56</v>
+        <v>35943.78</v>
       </c>
       <c r="AG27" s="10" t="n">
-        <v>0.0015</v>
+        <v>0.0029</v>
       </c>
       <c r="AH27" s="8" t="n">
-        <v>287393</v>
+        <v>2264603</v>
       </c>
       <c r="AI27" s="9" t="n">
-        <v>17812.62</v>
+        <v>36623.16</v>
       </c>
       <c r="AJ27" s="10" t="n">
-        <v>0.0014</v>
+        <v>0.0028</v>
       </c>
       <c r="AK27" s="8" t="n">
-        <v>287393</v>
+        <v>2264603</v>
       </c>
       <c r="AL27" s="9" t="n">
-        <v>17460.56</v>
+        <v>32691.81</v>
       </c>
       <c r="AM27" s="10" t="n">
-        <v>0.0013</v>
+        <v>0.0025</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Maharashtra Scooters Limited</t>
+          <t>ICRA Limited</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>INE288A01013</t>
+          <t>INE725G01011</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>80159</v>
+        <v>297835</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>7463.48</v>
+        <v>18529.51</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>0.0008</v>
+        <v>0.0021</v>
       </c>
       <c r="G28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>7401.52</v>
+        <v>15273.64</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>0.0008</v>
+        <v>0.0017</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>8997.450000000001</v>
+        <v>15821.13</v>
       </c>
       <c r="L28" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0017</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>9198.25</v>
+        <v>15976.18</v>
       </c>
       <c r="O28" s="10" t="n">
-        <v>0.0009</v>
+        <v>0.0016</v>
       </c>
       <c r="P28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>10722.07</v>
+        <v>19370.29</v>
       </c>
       <c r="R28" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0019</v>
       </c>
       <c r="S28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="T28" s="9" t="n">
-        <v>11621.45</v>
+        <v>19453.63</v>
       </c>
       <c r="U28" s="10" t="n">
-        <v>0.0011</v>
+        <v>0.0018</v>
       </c>
       <c r="V28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="W28" s="9" t="n">
-        <v>12868.73</v>
+        <v>19048.41</v>
       </c>
       <c r="X28" s="10" t="n">
-        <v>0.0011</v>
+        <v>0.0017</v>
       </c>
       <c r="Y28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="Z28" s="9" t="n">
-        <v>12726.04</v>
+        <v>17962.06</v>
       </c>
       <c r="AA28" s="10" t="n">
-        <v>0.0011</v>
+        <v>0.0016</v>
       </c>
       <c r="AB28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="AC28" s="9" t="n">
-        <v>13825.82</v>
+        <v>18243.71</v>
       </c>
       <c r="AD28" s="10" t="n">
-        <v>0.0012</v>
+        <v>0.0015</v>
       </c>
       <c r="AE28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="AF28" s="9" t="n">
-        <v>12110.42</v>
+        <v>18463.56</v>
       </c>
       <c r="AG28" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0015</v>
       </c>
       <c r="AH28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="AI28" s="9" t="n">
-        <v>11787.38</v>
+        <v>17812.62</v>
       </c>
       <c r="AJ28" s="10" t="n">
-        <v>0.0009</v>
+        <v>0.0014</v>
       </c>
       <c r="AK28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="AL28" s="9" t="n">
-        <v>11401.01</v>
+        <v>17460.56</v>
       </c>
       <c r="AM28" s="10" t="n">
-        <v>0.0009</v>
+        <v>0.0013</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Nesco Limited</t>
+          <t>Maharashtra Scooters Limited</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>INE317F01035</t>
+          <t>INE288A01013</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Commercial Services &amp; Supplies</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="n"/>
-      <c r="E29" s="9" t="n"/>
-      <c r="F29" s="10" t="n"/>
-      <c r="G29" s="8" t="n"/>
-      <c r="H29" s="9" t="n"/>
-      <c r="I29" s="10" t="n"/>
-      <c r="J29" s="8" t="n"/>
-      <c r="K29" s="9" t="n"/>
-      <c r="L29" s="10" t="n"/>
-      <c r="M29" s="8" t="n"/>
-      <c r="N29" s="9" t="n"/>
-      <c r="O29" s="10" t="n"/>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>80159</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>7463.48</v>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="G29" s="8" t="n">
+        <v>80159</v>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>7401.52</v>
+      </c>
+      <c r="I29" s="10" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="J29" s="8" t="n">
+        <v>80159</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <v>8997.450000000001</v>
+      </c>
+      <c r="L29" s="10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="M29" s="8" t="n">
+        <v>80159</v>
+      </c>
+      <c r="N29" s="9" t="n">
+        <v>9198.25</v>
+      </c>
+      <c r="O29" s="10" t="n">
+        <v>0.0009</v>
+      </c>
       <c r="P29" s="8" t="n">
-        <v>89469</v>
+        <v>80159</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>828.48</v>
+        <v>10722.07</v>
       </c>
       <c r="R29" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.001</v>
       </c>
       <c r="S29" s="8" t="n">
-        <v>151687</v>
+        <v>80159</v>
       </c>
       <c r="T29" s="9" t="n">
-        <v>1766.62</v>
+        <v>11621.45</v>
       </c>
       <c r="U29" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0011</v>
       </c>
       <c r="V29" s="8" t="n">
-        <v>151687</v>
+        <v>80159</v>
       </c>
       <c r="W29" s="9" t="n">
-        <v>2091.16</v>
+        <v>12868.73</v>
       </c>
       <c r="X29" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0011</v>
       </c>
       <c r="Y29" s="8" t="n">
-        <v>151687</v>
+        <v>80159</v>
       </c>
       <c r="Z29" s="9" t="n">
-        <v>2130.6</v>
+        <v>12726.04</v>
       </c>
       <c r="AA29" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0011</v>
       </c>
       <c r="AB29" s="8" t="n">
-        <v>151687</v>
+        <v>80159</v>
       </c>
       <c r="AC29" s="9" t="n">
-        <v>1987.1</v>
+        <v>13825.82</v>
       </c>
       <c r="AD29" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0012</v>
       </c>
       <c r="AE29" s="8" t="n">
-        <v>151687</v>
+        <v>80159</v>
       </c>
       <c r="AF29" s="9" t="n">
-        <v>2076.6</v>
+        <v>12110.42</v>
       </c>
       <c r="AG29" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.001</v>
       </c>
       <c r="AH29" s="8" t="n">
-        <v>151687</v>
+        <v>80159</v>
       </c>
       <c r="AI29" s="9" t="n">
-        <v>1947.66</v>
+        <v>11787.38</v>
       </c>
       <c r="AJ29" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0009</v>
       </c>
       <c r="AK29" s="8" t="n">
-        <v>151687</v>
+        <v>80159</v>
       </c>
       <c r="AL29" s="9" t="n">
-        <v>1858.32</v>
+        <v>11401.01</v>
       </c>
       <c r="AM29" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0009</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Swaraj Engines Limited</t>
+          <t>Indus Towers Limited</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>INE277A01016</t>
+          <t>INE121J01017</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Industrial Products</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="E30" s="9" t="n">
-        <v>1612.64</v>
-      </c>
-      <c r="F30" s="10" t="n">
+          <t>Telecom - Services</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="10" t="n"/>
+      <c r="G30" s="8" t="n"/>
+      <c r="H30" s="9" t="n"/>
+      <c r="I30" s="10" t="n"/>
+      <c r="J30" s="8" t="n"/>
+      <c r="K30" s="9" t="n"/>
+      <c r="L30" s="10" t="n"/>
+      <c r="M30" s="8" t="n"/>
+      <c r="N30" s="9" t="n"/>
+      <c r="O30" s="10" t="n"/>
+      <c r="P30" s="8" t="n"/>
+      <c r="Q30" s="9" t="n"/>
+      <c r="R30" s="10" t="n"/>
+      <c r="S30" s="8" t="n"/>
+      <c r="T30" s="9" t="n"/>
+      <c r="U30" s="10" t="n"/>
+      <c r="V30" s="8" t="n"/>
+      <c r="W30" s="9" t="n"/>
+      <c r="X30" s="10" t="n"/>
+      <c r="Y30" s="8" t="n"/>
+      <c r="Z30" s="9" t="n"/>
+      <c r="AA30" s="10" t="n"/>
+      <c r="AB30" s="8" t="n"/>
+      <c r="AC30" s="9" t="n"/>
+      <c r="AD30" s="10" t="n"/>
+      <c r="AE30" s="8" t="n"/>
+      <c r="AF30" s="9" t="n"/>
+      <c r="AG30" s="10" t="n"/>
+      <c r="AH30" s="8" t="n">
+        <v>710855</v>
+      </c>
+      <c r="AI30" s="9" t="n">
+        <v>2850.8839775</v>
+      </c>
+      <c r="AJ30" s="10" t="n">
         <v>0.0002</v>
       </c>
-      <c r="G30" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="H30" s="9" t="n">
-        <v>1236.83</v>
-      </c>
-      <c r="I30" s="10" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="J30" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="K30" s="9" t="n">
-        <v>1844.17</v>
-      </c>
-      <c r="L30" s="10" t="n">
+      <c r="AK30" s="8" t="n">
+        <v>710855</v>
+      </c>
+      <c r="AL30" s="9" t="n">
+        <v>2976.71</v>
+      </c>
+      <c r="AM30" s="10" t="n">
         <v>0.0002</v>
-      </c>
-      <c r="M30" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="N30" s="9" t="n">
-        <v>1925.39</v>
-      </c>
-      <c r="O30" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="P30" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="Q30" s="9" t="n">
-        <v>1857.76</v>
-      </c>
-      <c r="R30" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="S30" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="T30" s="9" t="n">
-        <v>1867.41</v>
-      </c>
-      <c r="U30" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="V30" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="W30" s="9" t="n">
-        <v>1983.66</v>
-      </c>
-      <c r="X30" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="Y30" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="Z30" s="9" t="n">
-        <v>1897.21</v>
-      </c>
-      <c r="AA30" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AB30" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="AC30" s="9" t="n">
-        <v>1955.38</v>
-      </c>
-      <c r="AD30" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AE30" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="AF30" s="9" t="n">
-        <v>1892.15</v>
-      </c>
-      <c r="AG30" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AH30" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="AI30" s="9" t="n">
-        <v>1764.08</v>
-      </c>
-      <c r="AJ30" s="10" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="AK30" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="AL30" s="9" t="n">
-        <v>1691.91</v>
-      </c>
-      <c r="AM30" s="10" t="n">
-        <v>0.0001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited</t>
+          <t>Nesco Limited</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>INE768C01010</t>
+          <t>INE317F01035</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Commercial Services &amp; Supplies</t>
         </is>
       </c>
       <c r="D31" s="8" t="n"/>
@@ -4166,149 +4070,203 @@
       <c r="M31" s="8" t="n"/>
       <c r="N31" s="9" t="n"/>
       <c r="O31" s="10" t="n"/>
-      <c r="P31" s="8" t="n"/>
-      <c r="Q31" s="9" t="n"/>
-      <c r="R31" s="10" t="n"/>
+      <c r="P31" s="8" t="n">
+        <v>89469</v>
+      </c>
+      <c r="Q31" s="9" t="n">
+        <v>828.48</v>
+      </c>
+      <c r="R31" s="10" t="n">
+        <v>0.0001</v>
+      </c>
       <c r="S31" s="8" t="n">
-        <v>4400000</v>
+        <v>151687</v>
       </c>
       <c r="T31" s="9" t="n">
-        <v>89020.8</v>
+        <v>1766.62</v>
       </c>
       <c r="U31" s="10" t="n">
-        <v>0.0081</v>
+        <v>0.0002</v>
       </c>
       <c r="V31" s="8" t="n">
-        <v>4400000</v>
+        <v>151687</v>
       </c>
       <c r="W31" s="9" t="n">
-        <v>89280.39999999999</v>
+        <v>2091.16</v>
       </c>
       <c r="X31" s="10" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0002</v>
       </c>
       <c r="Y31" s="8" t="n">
-        <v>4400000</v>
+        <v>151687</v>
       </c>
       <c r="Z31" s="9" t="n">
-        <v>88822.8</v>
+        <v>2130.6</v>
       </c>
       <c r="AA31" s="10" t="n">
-        <v>0.0077</v>
-      </c>
-      <c r="AB31" s="8" t="n"/>
-      <c r="AC31" s="9" t="n"/>
-      <c r="AD31" s="10" t="n"/>
-      <c r="AE31" s="8" t="n"/>
-      <c r="AF31" s="9" t="n"/>
-      <c r="AG31" s="10" t="n"/>
-      <c r="AH31" s="8" t="n"/>
-      <c r="AI31" s="9" t="n"/>
-      <c r="AJ31" s="10" t="n"/>
-      <c r="AK31" s="8" t="n"/>
-      <c r="AL31" s="9" t="n"/>
-      <c r="AM31" s="10" t="n"/>
+        <v>0.0002</v>
+      </c>
+      <c r="AB31" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AC31" s="9" t="n">
+        <v>1987.1</v>
+      </c>
+      <c r="AD31" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AE31" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AF31" s="9" t="n">
+        <v>2076.6</v>
+      </c>
+      <c r="AG31" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AH31" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AI31" s="9" t="n">
+        <v>1947.66</v>
+      </c>
+      <c r="AJ31" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AK31" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AL31" s="9" t="n">
+        <v>1858.32</v>
+      </c>
+      <c r="AM31" s="10" t="n">
+        <v>0.0001</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>IPCA Laboratories Limited</t>
+          <t>Swaraj Engines Limited</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>INE571A01038</t>
+          <t>INE277A01016</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Pharmaceuticals &amp; Biotechnology</t>
+          <t>Industrial Products</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>2246361</v>
+        <v>47293</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>32421.73</v>
+        <v>1612.64</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>0.0036</v>
+        <v>0.0002</v>
       </c>
       <c r="G32" s="8" t="n">
-        <v>1926988</v>
+        <v>47293</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>26117.43</v>
+        <v>1236.83</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0001</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>1926988</v>
+        <v>47293</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>28941.43</v>
+        <v>1844.17</v>
       </c>
       <c r="L32" s="10" t="n">
-        <v>0.0031</v>
+        <v>0.0002</v>
       </c>
       <c r="M32" s="8" t="n">
-        <v>1857217</v>
+        <v>47293</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>26023.32</v>
+        <v>1925.39</v>
       </c>
       <c r="O32" s="10" t="n">
-        <v>0.0026</v>
+        <v>0.0002</v>
       </c>
       <c r="P32" s="8" t="n">
-        <v>1641095</v>
+        <v>47293</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>23382.32</v>
+        <v>1857.76</v>
       </c>
       <c r="R32" s="10" t="n">
-        <v>0.0023</v>
+        <v>0.0002</v>
       </c>
       <c r="S32" s="8" t="n">
-        <v>1311557</v>
+        <v>47293</v>
       </c>
       <c r="T32" s="9" t="n">
-        <v>18228.02</v>
+        <v>1867.41</v>
       </c>
       <c r="U32" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.0002</v>
       </c>
       <c r="V32" s="8" t="n">
-        <v>566216</v>
+        <v>47293</v>
       </c>
       <c r="W32" s="9" t="n">
-        <v>8345.459999999999</v>
+        <v>1983.66</v>
       </c>
       <c r="X32" s="10" t="n">
-        <v>0.0007</v>
+        <v>0.0002</v>
       </c>
       <c r="Y32" s="8" t="n">
-        <v>218075</v>
+        <v>47293</v>
       </c>
       <c r="Z32" s="9" t="n">
-        <v>3019.03</v>
+        <v>1897.21</v>
       </c>
       <c r="AA32" s="10" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="AB32" s="8" t="n"/>
-      <c r="AC32" s="9" t="n"/>
-      <c r="AD32" s="10" t="n"/>
-      <c r="AE32" s="8" t="n"/>
-      <c r="AF32" s="9" t="n"/>
-      <c r="AG32" s="10" t="n"/>
-      <c r="AH32" s="8" t="n"/>
-      <c r="AI32" s="9" t="n"/>
-      <c r="AJ32" s="10" t="n"/>
-      <c r="AK32" s="8" t="n"/>
-      <c r="AL32" s="9" t="n"/>
-      <c r="AM32" s="10" t="n"/>
+        <v>0.0002</v>
+      </c>
+      <c r="AB32" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="AC32" s="9" t="n">
+        <v>1955.38</v>
+      </c>
+      <c r="AD32" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AE32" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="AF32" s="9" t="n">
+        <v>1892.15</v>
+      </c>
+      <c r="AG32" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AH32" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="AI32" s="9" t="n">
+        <v>1764.08</v>
+      </c>
+      <c r="AJ32" s="10" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AK32" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="AL32" s="9" t="n">
+        <v>1691.91</v>
+      </c>
+      <c r="AM32" s="10" t="n">
+        <v>0.0001</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -4402,61 +4360,91 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>ITC Hotels Limited</t>
+          <t>IPCA Laboratories Limited</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>INE379A01028</t>
+          <t>INE571A01038</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Leisure Services</t>
+          <t>Pharmaceuticals &amp; Biotechnology</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>9899412</v>
+        <v>2246361</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>16131.09</v>
+        <v>32421.73</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.0036</v>
       </c>
       <c r="G34" s="8" t="n">
-        <v>9899412</v>
+        <v>1926988</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>16216.23</v>
+        <v>26117.43</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.003</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>9899412</v>
+        <v>1926988</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>19552.33</v>
+        <v>28941.43</v>
       </c>
       <c r="L34" s="10" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="M34" s="8" t="n"/>
-      <c r="N34" s="9" t="n"/>
-      <c r="O34" s="10" t="n"/>
-      <c r="P34" s="8" t="n"/>
-      <c r="Q34" s="9" t="n"/>
-      <c r="R34" s="10" t="n"/>
-      <c r="S34" s="8" t="n"/>
-      <c r="T34" s="9" t="n"/>
-      <c r="U34" s="10" t="n"/>
-      <c r="V34" s="8" t="n"/>
-      <c r="W34" s="9" t="n"/>
-      <c r="X34" s="10" t="n"/>
-      <c r="Y34" s="8" t="n"/>
-      <c r="Z34" s="9" t="n"/>
-      <c r="AA34" s="10" t="n"/>
+        <v>0.0031</v>
+      </c>
+      <c r="M34" s="8" t="n">
+        <v>1857217</v>
+      </c>
+      <c r="N34" s="9" t="n">
+        <v>26023.32</v>
+      </c>
+      <c r="O34" s="10" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="P34" s="8" t="n">
+        <v>1641095</v>
+      </c>
+      <c r="Q34" s="9" t="n">
+        <v>23382.32</v>
+      </c>
+      <c r="R34" s="10" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="S34" s="8" t="n">
+        <v>1311557</v>
+      </c>
+      <c r="T34" s="9" t="n">
+        <v>18228.02</v>
+      </c>
+      <c r="U34" s="10" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v>566216</v>
+      </c>
+      <c r="W34" s="9" t="n">
+        <v>8345.459999999999</v>
+      </c>
+      <c r="X34" s="10" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="Y34" s="8" t="n">
+        <v>218075</v>
+      </c>
+      <c r="Z34" s="9" t="n">
+        <v>3019.03</v>
+      </c>
+      <c r="AA34" s="10" t="n">
+        <v>0.0003</v>
+      </c>
       <c r="AB34" s="8" t="n"/>
       <c r="AC34" s="9" t="n"/>
       <c r="AD34" s="10" t="n"/>
@@ -4473,28 +4461,46 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services Limited</t>
+          <t>ITC Hotels Limited</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>INE467B01029</t>
+          <t>INE379A01028</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>IT - Software</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="n"/>
-      <c r="E35" s="9" t="n"/>
-      <c r="F35" s="10" t="n"/>
-      <c r="G35" s="8" t="n"/>
-      <c r="H35" s="9" t="n"/>
-      <c r="I35" s="10" t="n"/>
-      <c r="J35" s="8" t="n"/>
-      <c r="K35" s="9" t="n"/>
-      <c r="L35" s="10" t="n"/>
+          <t>Leisure Services</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>16131.09</v>
+      </c>
+      <c r="F35" s="10" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="G35" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="H35" s="9" t="n">
+        <v>16216.23</v>
+      </c>
+      <c r="I35" s="10" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="J35" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="K35" s="9" t="n">
+        <v>19552.33</v>
+      </c>
+      <c r="L35" s="10" t="n">
+        <v>0.0021</v>
+      </c>
       <c r="M35" s="8" t="n"/>
       <c r="N35" s="9" t="n"/>
       <c r="O35" s="10" t="n"/>
@@ -4516,39 +4522,27 @@
       <c r="AE35" s="8" t="n"/>
       <c r="AF35" s="9" t="n"/>
       <c r="AG35" s="10" t="n"/>
-      <c r="AH35" s="8" t="n">
-        <v>2811139</v>
-      </c>
-      <c r="AI35" s="9" t="n">
-        <v>88199.49000000001</v>
-      </c>
-      <c r="AJ35" s="10" t="n">
-        <v>0.0068</v>
-      </c>
-      <c r="AK35" s="8" t="n">
-        <v>4654589</v>
-      </c>
-      <c r="AL35" s="9" t="n">
-        <v>149235.43</v>
-      </c>
-      <c r="AM35" s="10" t="n">
-        <v>0.0112</v>
-      </c>
+      <c r="AH35" s="8" t="n"/>
+      <c r="AI35" s="9" t="n"/>
+      <c r="AJ35" s="10" t="n"/>
+      <c r="AK35" s="8" t="n"/>
+      <c r="AL35" s="9" t="n"/>
+      <c r="AM35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>The Great Eastern Shipping Company Limited</t>
+          <t>Zydus Wellness Limited</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>INE017A01032</t>
+          <t>INE768C01010</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Transport Services</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D36" s="8" t="n"/>
@@ -4566,15 +4560,33 @@
       <c r="P36" s="8" t="n"/>
       <c r="Q36" s="9" t="n"/>
       <c r="R36" s="10" t="n"/>
-      <c r="S36" s="8" t="n"/>
-      <c r="T36" s="9" t="n"/>
-      <c r="U36" s="10" t="n"/>
-      <c r="V36" s="8" t="n"/>
-      <c r="W36" s="9" t="n"/>
-      <c r="X36" s="10" t="n"/>
-      <c r="Y36" s="8" t="n"/>
-      <c r="Z36" s="9" t="n"/>
-      <c r="AA36" s="10" t="n"/>
+      <c r="S36" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="T36" s="9" t="n">
+        <v>89020.8</v>
+      </c>
+      <c r="U36" s="10" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="W36" s="9" t="n">
+        <v>89280.39999999999</v>
+      </c>
+      <c r="X36" s="10" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="Y36" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="Z36" s="9" t="n">
+        <v>88822.8</v>
+      </c>
+      <c r="AA36" s="10" t="n">
+        <v>0.0077</v>
+      </c>
       <c r="AB36" s="8" t="n"/>
       <c r="AC36" s="9" t="n"/>
       <c r="AD36" s="10" t="n"/>
@@ -4584,30 +4596,24 @@
       <c r="AH36" s="8" t="n"/>
       <c r="AI36" s="9" t="n"/>
       <c r="AJ36" s="10" t="n"/>
-      <c r="AK36" s="8" t="n">
-        <v>1657424</v>
-      </c>
-      <c r="AL36" s="9" t="n">
-        <v>18712.32</v>
-      </c>
-      <c r="AM36" s="10" t="n">
-        <v>0.0014</v>
-      </c>
+      <c r="AK36" s="8" t="n"/>
+      <c r="AL36" s="9" t="n"/>
+      <c r="AM36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Indus Towers Limited</t>
+          <t>The Great Eastern Shipping Company Limited</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>INE121J01017</t>
+          <t>INE017A01032</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Telecom - Services</t>
+          <t>Transport Services</t>
         </is>
       </c>
       <c r="D37" s="8" t="n"/>
@@ -4640,23 +4646,17 @@
       <c r="AE37" s="8" t="n"/>
       <c r="AF37" s="9" t="n"/>
       <c r="AG37" s="10" t="n"/>
-      <c r="AH37" s="8" t="n">
-        <v>710855</v>
-      </c>
-      <c r="AI37" s="9" t="n">
-        <v>2850.8839775</v>
-      </c>
-      <c r="AJ37" s="10" t="n">
-        <v>0.0002</v>
-      </c>
+      <c r="AH37" s="8" t="n"/>
+      <c r="AI37" s="9" t="n"/>
+      <c r="AJ37" s="10" t="n"/>
       <c r="AK37" s="8" t="n">
-        <v>710855</v>
+        <v>1657424</v>
       </c>
       <c r="AL37" s="9" t="n">
-        <v>2976.71</v>
+        <v>18712.32</v>
       </c>
       <c r="AM37" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0014</v>
       </c>
     </row>
     <row r="38">
@@ -4671,7 +4671,7 @@
         <v>697292654</v>
       </c>
       <c r="E38" s="14" t="n">
-        <v>5868142.6</v>
+        <v>5868142.600000001</v>
       </c>
       <c r="F38" s="15" t="n">
         <v>0.6543000000000002</v>
@@ -4683,7 +4683,7 @@
         <v>5662977.75</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>0.6436999999999999</v>
+        <v>0.6437</v>
       </c>
       <c r="J38" s="13" t="n">
         <v>717176528</v>
@@ -4701,7 +4701,7 @@
         <v>6275568.750000001</v>
       </c>
       <c r="O38" s="15" t="n">
-        <v>0.6370000000000001</v>
+        <v>0.6369999999999999</v>
       </c>
       <c r="P38" s="13" t="n">
         <v>756845974</v>
@@ -4716,7 +4716,7 @@
         <v>799425942</v>
       </c>
       <c r="T38" s="14" t="n">
-        <v>7347454.069999999</v>
+        <v>7347454.07</v>
       </c>
       <c r="U38" s="15" t="n">
         <v>0.6657999999999999</v>
@@ -4737,13 +4737,13 @@
         <v>7320811.49</v>
       </c>
       <c r="AA38" s="15" t="n">
-        <v>0.6363999999999999</v>
+        <v>0.6364</v>
       </c>
       <c r="AB38" s="13" t="n">
         <v>979359723</v>
       </c>
       <c r="AC38" s="14" t="n">
-        <v>7559180.720000002</v>
+        <v>7559180.720000001</v>
       </c>
       <c r="AD38" s="15" t="n">
         <v>0.6313999999999996</v>
@@ -4761,16 +4761,16 @@
         <v>1039629309</v>
       </c>
       <c r="AI38" s="14" t="n">
-        <v>8271351.1939775</v>
+        <v>8271351.193977501</v>
       </c>
       <c r="AJ38" s="15" t="n">
-        <v>0.6374</v>
+        <v>0.6374000000000001</v>
       </c>
       <c r="AK38" s="13" t="n">
         <v>1079845116</v>
       </c>
       <c r="AL38" s="14" t="n">
-        <v>8588270.840000002</v>
+        <v>8588270.840000004</v>
       </c>
       <c r="AM38" s="15" t="n">
         <v>0.6443999999999998</v>

--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -495,7 +495,7 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
@@ -513,7 +513,7 @@
     <col width="20" customWidth="1" min="24" max="24"/>
     <col width="13" customWidth="1" min="25" max="25"/>
     <col width="26" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="20" customWidth="1" min="27" max="27"/>
     <col width="16" customWidth="1" min="28" max="28"/>
     <col width="26" customWidth="1" min="29" max="29"/>
     <col width="20" customWidth="1" min="30" max="30"/>
@@ -522,7 +522,7 @@
     <col width="14" customWidth="1" min="33" max="33"/>
     <col width="15" customWidth="1" min="34" max="34"/>
     <col width="26" customWidth="1" min="35" max="35"/>
-    <col width="20" customWidth="1" min="36" max="36"/>
+    <col width="14" customWidth="1" min="36" max="36"/>
     <col width="15" customWidth="1" min="37" max="37"/>
     <col width="26" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
@@ -1112,501 +1112,501 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>ICICI Bank Limited</t>
+          <t>Bajaj Holdings &amp; Investment Limited</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>INE090A01021</t>
+          <t>INE118A01012</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>34986740</v>
+        <v>5318918</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>438313.88</v>
+        <v>614850.96</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.0489</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>34986740</v>
+        <v>5318918</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>421275.34</v>
+        <v>615630.1899999999</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>0.0479</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>34986740</v>
+        <v>5318918</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>471743.71</v>
+        <v>663431.3</v>
       </c>
       <c r="L6" s="10" t="n">
-        <v>0.0505</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>34986740</v>
+        <v>5318918</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>499260.78</v>
+        <v>636834.05</v>
       </c>
       <c r="O6" s="10" t="n">
-        <v>0.0507</v>
+        <v>0.0646</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>34986740</v>
+        <v>5318918</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>505838.29</v>
+        <v>713479.66</v>
       </c>
       <c r="R6" s="10" t="n">
-        <v>0.0487</v>
+        <v>0.0687</v>
       </c>
       <c r="S6" s="8" t="n">
-        <v>36489310</v>
+        <v>5318918</v>
       </c>
       <c r="T6" s="9" t="n">
-        <v>527562.4399999999</v>
+        <v>764807.22</v>
       </c>
       <c r="U6" s="10" t="n">
-        <v>0.0478</v>
+        <v>0.0693</v>
       </c>
       <c r="V6" s="8" t="n">
-        <v>39605543</v>
+        <v>5318918</v>
       </c>
       <c r="W6" s="9" t="n">
-        <v>586716.51</v>
+        <v>742680.52</v>
       </c>
       <c r="X6" s="10" t="n">
-        <v>0.0518</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="Y6" s="8" t="n">
-        <v>40720543</v>
+        <v>5318918</v>
       </c>
       <c r="Z6" s="9" t="n">
-        <v>569191.75</v>
+        <v>679225.83</v>
       </c>
       <c r="AA6" s="10" t="n">
-        <v>0.0495</v>
+        <v>0.059</v>
       </c>
       <c r="AB6" s="8" t="n">
-        <v>42215573</v>
+        <v>5318918</v>
       </c>
       <c r="AC6" s="9" t="n">
-        <v>569065.92</v>
+        <v>651407.89</v>
       </c>
       <c r="AD6" s="10" t="n">
-        <v>0.0475</v>
+        <v>0.0544</v>
       </c>
       <c r="AE6" s="8" t="n">
-        <v>43295573</v>
+        <v>5318918</v>
       </c>
       <c r="AF6" s="9" t="n">
-        <v>582455.34</v>
+        <v>654386.48</v>
       </c>
       <c r="AG6" s="10" t="n">
-        <v>0.0463</v>
+        <v>0.052</v>
       </c>
       <c r="AH6" s="8" t="n">
-        <v>45308598</v>
+        <v>5318918</v>
       </c>
       <c r="AI6" s="9" t="n">
-        <v>629245.8100000001</v>
+        <v>611622.38</v>
       </c>
       <c r="AJ6" s="10" t="n">
-        <v>0.0485</v>
+        <v>0.0471</v>
       </c>
       <c r="AK6" s="8" t="n">
-        <v>49325234</v>
+        <v>5318918</v>
       </c>
       <c r="AL6" s="9" t="n">
-        <v>662388.5699999999</v>
+        <v>602527.03</v>
       </c>
       <c r="AM6" s="10" t="n">
-        <v>0.0497</v>
+        <v>0.0452</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Bajaj Holdings &amp; Investment Limited</t>
+          <t>Coal India Limited</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>INE118A01012</t>
+          <t>INE522F01014</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Consumable Fuels</t>
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>5318918</v>
+        <v>139335199</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>614850.96</v>
+        <v>551628.05</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.0615</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>5318918</v>
+        <v>142636407</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>615630.1899999999</v>
+        <v>526827.5699999999</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0599</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>5318918</v>
+        <v>141074007</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>663431.3</v>
+        <v>561756.7</v>
       </c>
       <c r="L7" s="10" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.0601</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>5318918</v>
+        <v>148323775</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>636834.05</v>
+        <v>571491.51</v>
       </c>
       <c r="O7" s="10" t="n">
-        <v>0.0646</v>
+        <v>0.058</v>
       </c>
       <c r="P7" s="8" t="n">
-        <v>5318918</v>
+        <v>155681572</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>713479.66</v>
+        <v>618522.89</v>
       </c>
       <c r="R7" s="10" t="n">
-        <v>0.0687</v>
+        <v>0.0595</v>
       </c>
       <c r="S7" s="8" t="n">
-        <v>5318918</v>
+        <v>162039558</v>
       </c>
       <c r="T7" s="9" t="n">
-        <v>764807.22</v>
+        <v>635114.05</v>
       </c>
       <c r="U7" s="10" t="n">
-        <v>0.0693</v>
+        <v>0.0575</v>
       </c>
       <c r="V7" s="8" t="n">
-        <v>5318918</v>
+        <v>162039558</v>
       </c>
       <c r="W7" s="9" t="n">
-        <v>742680.52</v>
+        <v>609835.88</v>
       </c>
       <c r="X7" s="10" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0538</v>
       </c>
       <c r="Y7" s="8" t="n">
-        <v>5318918</v>
+        <v>162039558</v>
       </c>
       <c r="Z7" s="9" t="n">
-        <v>679225.83</v>
+        <v>607324.26</v>
       </c>
       <c r="AA7" s="10" t="n">
-        <v>0.059</v>
+        <v>0.0528</v>
       </c>
       <c r="AB7" s="8" t="n">
-        <v>5318918</v>
+        <v>162039558</v>
       </c>
       <c r="AC7" s="9" t="n">
-        <v>651407.89</v>
+        <v>631873.26</v>
       </c>
       <c r="AD7" s="10" t="n">
-        <v>0.0544</v>
+        <v>0.0528</v>
       </c>
       <c r="AE7" s="8" t="n">
-        <v>5318918</v>
+        <v>162039558</v>
       </c>
       <c r="AF7" s="9" t="n">
-        <v>654386.48</v>
+        <v>629766.74</v>
       </c>
       <c r="AG7" s="10" t="n">
-        <v>0.052</v>
+        <v>0.0501</v>
       </c>
       <c r="AH7" s="8" t="n">
-        <v>5318918</v>
+        <v>162039558</v>
       </c>
       <c r="AI7" s="9" t="n">
-        <v>611622.38</v>
+        <v>609511.8</v>
       </c>
       <c r="AJ7" s="10" t="n">
-        <v>0.0471</v>
+        <v>0.047</v>
       </c>
       <c r="AK7" s="8" t="n">
-        <v>5318918</v>
+        <v>162039558</v>
       </c>
       <c r="AL7" s="9" t="n">
-        <v>602527.03</v>
+        <v>646537.84</v>
       </c>
       <c r="AM7" s="10" t="n">
-        <v>0.0452</v>
+        <v>0.0485</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Coal India Limited</t>
+          <t>ITC Limited</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>INE522F01014</t>
+          <t>INE154A01025</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Consumable Fuels</t>
+          <t>Diversified FMCG</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>139335199</v>
+        <v>98994120</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>551628.05</v>
+        <v>442998.69</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>0.0615</v>
+        <v>0.0494</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>142636407</v>
+        <v>101194120</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>526827.5699999999</v>
+        <v>399716.77</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>0.0599</v>
+        <v>0.0454</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>141074007</v>
+        <v>101194120</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>561756.7</v>
+        <v>414642.91</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>0.0601</v>
+        <v>0.0444</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>148323775</v>
+        <v>105271096</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>571491.51</v>
+        <v>448244.33</v>
       </c>
       <c r="O8" s="10" t="n">
-        <v>0.058</v>
+        <v>0.0455</v>
       </c>
       <c r="P8" s="8" t="n">
-        <v>155681572</v>
+        <v>109270669</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>618522.89</v>
+        <v>456806.03</v>
       </c>
       <c r="R8" s="10" t="n">
-        <v>0.0595</v>
+        <v>0.044</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>162039558</v>
+        <v>117422359</v>
       </c>
       <c r="T8" s="9" t="n">
-        <v>635114.05</v>
+        <v>489005.41</v>
       </c>
       <c r="U8" s="10" t="n">
-        <v>0.0575</v>
+        <v>0.0443</v>
       </c>
       <c r="V8" s="8" t="n">
-        <v>162039558</v>
+        <v>122172359</v>
       </c>
       <c r="W8" s="9" t="n">
-        <v>609835.88</v>
+        <v>503289.03</v>
       </c>
       <c r="X8" s="10" t="n">
-        <v>0.0538</v>
+        <v>0.0444</v>
       </c>
       <c r="Y8" s="8" t="n">
-        <v>162039558</v>
+        <v>129421024</v>
       </c>
       <c r="Z8" s="9" t="n">
-        <v>607324.26</v>
+        <v>530302.65</v>
       </c>
       <c r="AA8" s="10" t="n">
-        <v>0.0528</v>
+        <v>0.0461</v>
       </c>
       <c r="AB8" s="8" t="n">
-        <v>162039558</v>
+        <v>135721024</v>
       </c>
       <c r="AC8" s="9" t="n">
-        <v>631873.26</v>
+        <v>544987.77</v>
       </c>
       <c r="AD8" s="10" t="n">
-        <v>0.0528</v>
+        <v>0.0455</v>
       </c>
       <c r="AE8" s="8" t="n">
-        <v>162039558</v>
+        <v>138771024</v>
       </c>
       <c r="AF8" s="9" t="n">
-        <v>629766.74</v>
+        <v>583324</v>
       </c>
       <c r="AG8" s="10" t="n">
-        <v>0.0501</v>
+        <v>0.0464</v>
       </c>
       <c r="AH8" s="8" t="n">
-        <v>162039558</v>
+        <v>144737169</v>
       </c>
       <c r="AI8" s="9" t="n">
-        <v>609511.8</v>
+        <v>585100.01</v>
       </c>
       <c r="AJ8" s="10" t="n">
-        <v>0.047</v>
+        <v>0.0451</v>
       </c>
       <c r="AK8" s="8" t="n">
-        <v>162039558</v>
+        <v>148665711</v>
       </c>
       <c r="AL8" s="9" t="n">
-        <v>646537.84</v>
+        <v>599122.8199999999</v>
       </c>
       <c r="AM8" s="10" t="n">
-        <v>0.0485</v>
+        <v>0.0449</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>ITC Limited</t>
+          <t>ICICI Bank Limited</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>INE154A01025</t>
+          <t>INE090A01021</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Diversified FMCG</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>98994120</v>
+        <v>34986740</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>442998.69</v>
+        <v>438313.88</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.0494</v>
+        <v>0.0489</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>101194120</v>
+        <v>34986740</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>399716.77</v>
+        <v>421275.34</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>0.0454</v>
+        <v>0.0479</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>101194120</v>
+        <v>34986740</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>414642.91</v>
+        <v>471743.71</v>
       </c>
       <c r="L9" s="10" t="n">
-        <v>0.0444</v>
+        <v>0.0505</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>105271096</v>
+        <v>34986740</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>448244.33</v>
+        <v>499260.78</v>
       </c>
       <c r="O9" s="10" t="n">
-        <v>0.0455</v>
+        <v>0.0507</v>
       </c>
       <c r="P9" s="8" t="n">
-        <v>109270669</v>
+        <v>34986740</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>456806.03</v>
+        <v>505838.29</v>
       </c>
       <c r="R9" s="10" t="n">
-        <v>0.044</v>
+        <v>0.0487</v>
       </c>
       <c r="S9" s="8" t="n">
-        <v>117422359</v>
+        <v>36489310</v>
       </c>
       <c r="T9" s="9" t="n">
-        <v>489005.41</v>
+        <v>527562.4399999999</v>
       </c>
       <c r="U9" s="10" t="n">
-        <v>0.0443</v>
+        <v>0.0478</v>
       </c>
       <c r="V9" s="8" t="n">
-        <v>122172359</v>
+        <v>39605543</v>
       </c>
       <c r="W9" s="9" t="n">
-        <v>503289.03</v>
+        <v>586716.51</v>
       </c>
       <c r="X9" s="10" t="n">
-        <v>0.0444</v>
+        <v>0.0518</v>
       </c>
       <c r="Y9" s="8" t="n">
-        <v>129421024</v>
+        <v>40720543</v>
       </c>
       <c r="Z9" s="9" t="n">
-        <v>530302.65</v>
+        <v>569191.75</v>
       </c>
       <c r="AA9" s="10" t="n">
-        <v>0.0461</v>
+        <v>0.0495</v>
       </c>
       <c r="AB9" s="8" t="n">
-        <v>135721024</v>
+        <v>42215573</v>
       </c>
       <c r="AC9" s="9" t="n">
-        <v>544987.77</v>
+        <v>569065.92</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>0.0455</v>
+        <v>0.0475</v>
       </c>
       <c r="AE9" s="8" t="n">
-        <v>138771024</v>
+        <v>43295573</v>
       </c>
       <c r="AF9" s="9" t="n">
-        <v>583324</v>
+        <v>582455.34</v>
       </c>
       <c r="AG9" s="10" t="n">
-        <v>0.0464</v>
+        <v>0.0463</v>
       </c>
       <c r="AH9" s="8" t="n">
-        <v>144737169</v>
+        <v>45308598</v>
       </c>
       <c r="AI9" s="9" t="n">
-        <v>585100.01</v>
+        <v>629245.8100000001</v>
       </c>
       <c r="AJ9" s="10" t="n">
-        <v>0.0451</v>
+        <v>0.0485</v>
       </c>
       <c r="AK9" s="8" t="n">
-        <v>148665711</v>
+        <v>49325234</v>
       </c>
       <c r="AL9" s="9" t="n">
-        <v>599122.8199999999</v>
+        <v>662388.5699999999</v>
       </c>
       <c r="AM9" s="10" t="n">
-        <v>0.0449</v>
+        <v>0.0497</v>
       </c>
     </row>
     <row r="10">
@@ -1737,12 +1737,12 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Mahindra &amp; Mahindra Limited</t>
+          <t>Maruti Suzuki India Limited</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>INE101A01026</t>
+          <t>INE585B01010</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -1751,112 +1751,112 @@
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>9331737</v>
+        <v>3018078</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>279004.94</v>
+        <v>371545.02</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.0311</v>
+        <v>0.0414</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>10068665</v>
+        <v>3018078</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>260285.06</v>
+        <v>360535.07</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>0.0296</v>
+        <v>0.041</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>10399289</v>
+        <v>3018078</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>277224.25</v>
+        <v>347747.47</v>
       </c>
       <c r="L11" s="10" t="n">
-        <v>0.0297</v>
+        <v>0.0372</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>11040212</v>
+        <v>3021670</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>323345.73</v>
+        <v>370366.09</v>
       </c>
       <c r="O11" s="10" t="n">
-        <v>0.0328</v>
+        <v>0.0376</v>
       </c>
       <c r="P11" s="8" t="n">
-        <v>12231374</v>
+        <v>3021670</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>364103.54</v>
+        <v>372239.53</v>
       </c>
       <c r="R11" s="10" t="n">
-        <v>0.0351</v>
+        <v>0.0358</v>
       </c>
       <c r="S11" s="8" t="n">
-        <v>12335671</v>
+        <v>3021670</v>
       </c>
       <c r="T11" s="9" t="n">
-        <v>392669.08</v>
+        <v>374687.08</v>
       </c>
       <c r="U11" s="10" t="n">
-        <v>0.0356</v>
+        <v>0.0339</v>
       </c>
       <c r="V11" s="8" t="n">
-        <v>12335671</v>
+        <v>3021670</v>
       </c>
       <c r="W11" s="9" t="n">
-        <v>395123.88</v>
+        <v>380972.15</v>
       </c>
       <c r="X11" s="10" t="n">
-        <v>0.0349</v>
+        <v>0.0336</v>
       </c>
       <c r="Y11" s="8" t="n">
-        <v>12335671</v>
+        <v>2746670</v>
       </c>
       <c r="Z11" s="9" t="n">
-        <v>394679.79</v>
+        <v>406259.96</v>
       </c>
       <c r="AA11" s="10" t="n">
-        <v>0.0343</v>
+        <v>0.0353</v>
       </c>
       <c r="AB11" s="8" t="n">
-        <v>12335671</v>
+        <v>2696670</v>
       </c>
       <c r="AC11" s="9" t="n">
-        <v>422743.45</v>
+        <v>432249.23</v>
       </c>
       <c r="AD11" s="10" t="n">
-        <v>0.0353</v>
+        <v>0.0361</v>
       </c>
       <c r="AE11" s="8" t="n">
-        <v>12435671</v>
+        <v>2696670</v>
       </c>
       <c r="AF11" s="9" t="n">
-        <v>433656.72</v>
+        <v>436483.01</v>
       </c>
       <c r="AG11" s="10" t="n">
-        <v>0.0345</v>
+        <v>0.0347</v>
       </c>
       <c r="AH11" s="8" t="n">
-        <v>12435671</v>
+        <v>2746670</v>
       </c>
       <c r="AI11" s="9" t="n">
-        <v>467245.47</v>
+        <v>436720.53</v>
       </c>
       <c r="AJ11" s="10" t="n">
-        <v>0.036</v>
+        <v>0.0337</v>
       </c>
       <c r="AK11" s="8" t="n">
-        <v>13033470</v>
+        <v>2746670</v>
       </c>
       <c r="AL11" s="9" t="n">
-        <v>483437.47</v>
+        <v>458611.49</v>
       </c>
       <c r="AM11" s="10" t="n">
-        <v>0.0363</v>
+        <v>0.0344</v>
       </c>
     </row>
     <row r="12">
@@ -1963,12 +1963,12 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Maruti Suzuki India Limited</t>
+          <t>Mahindra &amp; Mahindra Limited</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>INE585B01010</t>
+          <t>INE101A01026</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -1977,112 +1977,112 @@
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>3018078</v>
+        <v>9331737</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>371545.02</v>
+        <v>279004.94</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.0414</v>
+        <v>0.0311</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>3018078</v>
+        <v>10068665</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>360535.07</v>
+        <v>260285.06</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>0.041</v>
+        <v>0.0296</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>3018078</v>
+        <v>10399289</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>347747.47</v>
+        <v>277224.25</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>0.0372</v>
+        <v>0.0297</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>3021670</v>
+        <v>11040212</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>370366.09</v>
+        <v>323345.73</v>
       </c>
       <c r="O13" s="10" t="n">
-        <v>0.0376</v>
+        <v>0.0328</v>
       </c>
       <c r="P13" s="8" t="n">
-        <v>3021670</v>
+        <v>12231374</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>372239.53</v>
+        <v>364103.54</v>
       </c>
       <c r="R13" s="10" t="n">
-        <v>0.0358</v>
+        <v>0.0351</v>
       </c>
       <c r="S13" s="8" t="n">
-        <v>3021670</v>
+        <v>12335671</v>
       </c>
       <c r="T13" s="9" t="n">
-        <v>374687.08</v>
+        <v>392669.08</v>
       </c>
       <c r="U13" s="10" t="n">
-        <v>0.0339</v>
+        <v>0.0356</v>
       </c>
       <c r="V13" s="8" t="n">
-        <v>3021670</v>
+        <v>12335671</v>
       </c>
       <c r="W13" s="9" t="n">
-        <v>380972.15</v>
+        <v>395123.88</v>
       </c>
       <c r="X13" s="10" t="n">
-        <v>0.0336</v>
+        <v>0.0349</v>
       </c>
       <c r="Y13" s="8" t="n">
-        <v>2746670</v>
+        <v>12335671</v>
       </c>
       <c r="Z13" s="9" t="n">
-        <v>406259.96</v>
+        <v>394679.79</v>
       </c>
       <c r="AA13" s="10" t="n">
+        <v>0.0343</v>
+      </c>
+      <c r="AB13" s="8" t="n">
+        <v>12335671</v>
+      </c>
+      <c r="AC13" s="9" t="n">
+        <v>422743.45</v>
+      </c>
+      <c r="AD13" s="10" t="n">
         <v>0.0353</v>
       </c>
-      <c r="AB13" s="8" t="n">
-        <v>2696670</v>
-      </c>
-      <c r="AC13" s="9" t="n">
-        <v>432249.23</v>
-      </c>
-      <c r="AD13" s="10" t="n">
-        <v>0.0361</v>
-      </c>
       <c r="AE13" s="8" t="n">
-        <v>2696670</v>
+        <v>12435671</v>
       </c>
       <c r="AF13" s="9" t="n">
-        <v>436483.01</v>
+        <v>433656.72</v>
       </c>
       <c r="AG13" s="10" t="n">
-        <v>0.0347</v>
+        <v>0.0345</v>
       </c>
       <c r="AH13" s="8" t="n">
-        <v>2746670</v>
+        <v>12435671</v>
       </c>
       <c r="AI13" s="9" t="n">
-        <v>436720.53</v>
+        <v>467245.47</v>
       </c>
       <c r="AJ13" s="10" t="n">
-        <v>0.0337</v>
+        <v>0.036</v>
       </c>
       <c r="AK13" s="8" t="n">
-        <v>2746670</v>
+        <v>13033470</v>
       </c>
       <c r="AL13" s="9" t="n">
-        <v>458611.49</v>
+        <v>483437.47</v>
       </c>
       <c r="AM13" s="10" t="n">
-        <v>0.0344</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="14">
@@ -2338,126 +2338,126 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Infosys Limited</t>
+          <t>Zydus Lifesciences Limited</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>INE009A01021</t>
+          <t>INE010B01027</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>IT - Software</t>
+          <t>Pharmaceuticals &amp; Biotechnology</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>9306473</v>
+        <v>8859127</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>174943.08</v>
+        <v>85955.67999999999</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>0.0195</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>9306473</v>
+        <v>11479604</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>157065.34</v>
+        <v>100630.21</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>0.0178</v>
+        <v>0.0114</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>9306473</v>
+        <v>13003659</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>146172.12</v>
+        <v>115264.43</v>
       </c>
       <c r="L16" s="10" t="n">
-        <v>0.0156</v>
+        <v>0.0123</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>9306473</v>
+        <v>13936283</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>139606.4</v>
+        <v>123789.03</v>
       </c>
       <c r="O16" s="10" t="n">
-        <v>0.0142</v>
+        <v>0.0126</v>
       </c>
       <c r="P16" s="8" t="n">
-        <v>9306473</v>
+        <v>14258435</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>145432.25</v>
+        <v>132603.45</v>
       </c>
       <c r="R16" s="10" t="n">
-        <v>0.014</v>
+        <v>0.0128</v>
       </c>
       <c r="S16" s="8" t="n">
-        <v>9306473</v>
+        <v>14258435</v>
       </c>
       <c r="T16" s="9" t="n">
-        <v>149071.08</v>
+        <v>141151.38</v>
       </c>
       <c r="U16" s="10" t="n">
-        <v>0.0135</v>
+        <v>0.0128</v>
       </c>
       <c r="V16" s="8" t="n">
-        <v>9306473</v>
+        <v>14470385</v>
       </c>
       <c r="W16" s="9" t="n">
-        <v>140434.68</v>
+        <v>140333.79</v>
       </c>
       <c r="X16" s="10" t="n">
         <v>0.0124</v>
       </c>
       <c r="Y16" s="8" t="n">
-        <v>9306473</v>
+        <v>14786344</v>
       </c>
       <c r="Z16" s="9" t="n">
-        <v>136767.93</v>
+        <v>145061.43</v>
       </c>
       <c r="AA16" s="10" t="n">
-        <v>0.0119</v>
+        <v>0.0126</v>
       </c>
       <c r="AB16" s="8" t="n">
-        <v>9306473</v>
+        <v>15148311</v>
       </c>
       <c r="AC16" s="9" t="n">
-        <v>134180.73</v>
+        <v>148741.27</v>
       </c>
       <c r="AD16" s="10" t="n">
-        <v>0.0112</v>
+        <v>0.0124</v>
       </c>
       <c r="AE16" s="8" t="n">
-        <v>9306473</v>
+        <v>15759789</v>
       </c>
       <c r="AF16" s="9" t="n">
-        <v>137949.85</v>
+        <v>153571.26</v>
       </c>
       <c r="AG16" s="10" t="n">
-        <v>0.011</v>
+        <v>0.0122</v>
       </c>
       <c r="AH16" s="8" t="n">
-        <v>17621740</v>
+        <v>17405149</v>
       </c>
       <c r="AI16" s="9" t="n">
-        <v>274916.77</v>
+        <v>164043.53</v>
       </c>
       <c r="AJ16" s="10" t="n">
-        <v>0.0212</v>
+        <v>0.0126</v>
       </c>
       <c r="AK16" s="8" t="n">
-        <v>16417936</v>
+        <v>17903094</v>
       </c>
       <c r="AL16" s="9" t="n">
-        <v>265215.34</v>
+        <v>163696.94</v>
       </c>
       <c r="AM16" s="10" t="n">
-        <v>0.0199</v>
+        <v>0.0123</v>
       </c>
     </row>
     <row r="17">
@@ -2713,126 +2713,126 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences Limited</t>
+          <t>Infosys Limited</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>INE010B01027</t>
+          <t>INE009A01021</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Pharmaceuticals &amp; Biotechnology</t>
+          <t>IT - Software</t>
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>8859127</v>
+        <v>9306473</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>85955.67999999999</v>
+        <v>174943.08</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0195</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>11479604</v>
+        <v>9306473</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>100630.21</v>
+        <v>157065.34</v>
       </c>
       <c r="I19" s="10" t="n">
-        <v>0.0114</v>
+        <v>0.0178</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>13003659</v>
+        <v>9306473</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>115264.43</v>
+        <v>146172.12</v>
       </c>
       <c r="L19" s="10" t="n">
-        <v>0.0123</v>
+        <v>0.0156</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>13936283</v>
+        <v>9306473</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>123789.03</v>
+        <v>139606.4</v>
       </c>
       <c r="O19" s="10" t="n">
-        <v>0.0126</v>
+        <v>0.0142</v>
       </c>
       <c r="P19" s="8" t="n">
-        <v>14258435</v>
+        <v>9306473</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>132603.45</v>
+        <v>145432.25</v>
       </c>
       <c r="R19" s="10" t="n">
-        <v>0.0128</v>
+        <v>0.014</v>
       </c>
       <c r="S19" s="8" t="n">
-        <v>14258435</v>
+        <v>9306473</v>
       </c>
       <c r="T19" s="9" t="n">
-        <v>141151.38</v>
+        <v>149071.08</v>
       </c>
       <c r="U19" s="10" t="n">
-        <v>0.0128</v>
+        <v>0.0135</v>
       </c>
       <c r="V19" s="8" t="n">
-        <v>14470385</v>
+        <v>9306473</v>
       </c>
       <c r="W19" s="9" t="n">
-        <v>140333.79</v>
+        <v>140434.68</v>
       </c>
       <c r="X19" s="10" t="n">
         <v>0.0124</v>
       </c>
       <c r="Y19" s="8" t="n">
-        <v>14786344</v>
+        <v>9306473</v>
       </c>
       <c r="Z19" s="9" t="n">
-        <v>145061.43</v>
+        <v>136767.93</v>
       </c>
       <c r="AA19" s="10" t="n">
-        <v>0.0126</v>
+        <v>0.0119</v>
       </c>
       <c r="AB19" s="8" t="n">
-        <v>15148311</v>
+        <v>9306473</v>
       </c>
       <c r="AC19" s="9" t="n">
-        <v>148741.27</v>
+        <v>134180.73</v>
       </c>
       <c r="AD19" s="10" t="n">
-        <v>0.0124</v>
+        <v>0.0112</v>
       </c>
       <c r="AE19" s="8" t="n">
-        <v>15759789</v>
+        <v>9306473</v>
       </c>
       <c r="AF19" s="9" t="n">
-        <v>153571.26</v>
+        <v>137949.85</v>
       </c>
       <c r="AG19" s="10" t="n">
-        <v>0.0122</v>
+        <v>0.011</v>
       </c>
       <c r="AH19" s="8" t="n">
-        <v>17405149</v>
+        <v>17621740</v>
       </c>
       <c r="AI19" s="9" t="n">
-        <v>164043.53</v>
+        <v>274916.77</v>
       </c>
       <c r="AJ19" s="10" t="n">
-        <v>0.0126</v>
+        <v>0.0212</v>
       </c>
       <c r="AK19" s="8" t="n">
-        <v>17903094</v>
+        <v>16417936</v>
       </c>
       <c r="AL19" s="9" t="n">
-        <v>163696.94</v>
+        <v>265215.34</v>
       </c>
       <c r="AM19" s="10" t="n">
-        <v>0.0123</v>
+        <v>0.0199</v>
       </c>
     </row>
     <row r="20">
@@ -2963,518 +2963,578 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Balkrishna Industries Limited</t>
+          <t>Zydus Wellness Limited</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>INE787D01026</t>
+          <t>INE768C01028</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Auto Components</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>116089.71</v>
-      </c>
-      <c r="F21" s="10" t="n">
-        <v>0.0129</v>
-      </c>
-      <c r="G21" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="H21" s="9" t="n">
-        <v>109571.51</v>
-      </c>
-      <c r="I21" s="10" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="J21" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="K21" s="9" t="n">
-        <v>107022.46</v>
-      </c>
-      <c r="L21" s="10" t="n">
-        <v>0.0115</v>
-      </c>
-      <c r="M21" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="N21" s="9" t="n">
-        <v>112061.92</v>
-      </c>
-      <c r="O21" s="10" t="n">
-        <v>0.0114</v>
-      </c>
-      <c r="P21" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="Q21" s="9" t="n">
-        <v>103562.29</v>
-      </c>
-      <c r="R21" s="10" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="S21" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="T21" s="9" t="n">
-        <v>102435.43</v>
-      </c>
-      <c r="U21" s="10" t="n">
-        <v>0.009299999999999999</v>
-      </c>
-      <c r="V21" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="W21" s="9" t="n">
-        <v>112108</v>
-      </c>
-      <c r="X21" s="10" t="n">
-        <v>0.009900000000000001</v>
-      </c>
-      <c r="Y21" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="Z21" s="9" t="n">
-        <v>95904.66</v>
-      </c>
-      <c r="AA21" s="10" t="n">
+          <t>Food Products</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="8" t="n"/>
+      <c r="H21" s="9" t="n"/>
+      <c r="I21" s="10" t="n"/>
+      <c r="J21" s="8" t="n"/>
+      <c r="K21" s="9" t="n"/>
+      <c r="L21" s="10" t="n"/>
+      <c r="M21" s="8" t="n"/>
+      <c r="N21" s="9" t="n"/>
+      <c r="O21" s="10" t="n"/>
+      <c r="P21" s="8" t="n"/>
+      <c r="Q21" s="9" t="n"/>
+      <c r="R21" s="10" t="n"/>
+      <c r="S21" s="8" t="n"/>
+      <c r="T21" s="9" t="n"/>
+      <c r="U21" s="10" t="n"/>
+      <c r="V21" s="8" t="n"/>
+      <c r="W21" s="9" t="n"/>
+      <c r="X21" s="10" t="n"/>
+      <c r="Y21" s="8" t="n"/>
+      <c r="Z21" s="9" t="n"/>
+      <c r="AA21" s="10" t="n"/>
+      <c r="AB21" s="8" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="AC21" s="9" t="n">
+        <v>100584</v>
+      </c>
+      <c r="AD21" s="10" t="n">
+        <v>0.008399999999999999</v>
+      </c>
+      <c r="AE21" s="8" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="AF21" s="9" t="n">
+        <v>104852</v>
+      </c>
+      <c r="AG21" s="10" t="n">
         <v>0.0083</v>
       </c>
-      <c r="AB21" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="AC21" s="9" t="n">
-        <v>96130.87</v>
-      </c>
-      <c r="AD21" s="10" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="AE21" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="AF21" s="9" t="n">
-        <v>95502.50999999999</v>
-      </c>
-      <c r="AG21" s="10" t="n">
-        <v>0.0076</v>
-      </c>
       <c r="AH21" s="8" t="n">
-        <v>4189074</v>
+        <v>22000000</v>
       </c>
       <c r="AI21" s="9" t="n">
-        <v>96721.53</v>
+        <v>94699</v>
       </c>
       <c r="AJ21" s="10" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="AK21" s="8" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="AL21" s="9" t="n">
+        <v>100012</v>
+      </c>
+      <c r="AM21" s="10" t="n">
         <v>0.0075</v>
-      </c>
-      <c r="AK21" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="AL21" s="9" t="n">
-        <v>97173.95</v>
-      </c>
-      <c r="AM21" s="10" t="n">
-        <v>0.0073</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited</t>
+          <t>Balkrishna Industries Limited</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>INE768C01028</t>
+          <t>INE787D01026</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="8" t="n"/>
-      <c r="H22" s="9" t="n"/>
-      <c r="I22" s="10" t="n"/>
-      <c r="J22" s="8" t="n"/>
-      <c r="K22" s="9" t="n"/>
-      <c r="L22" s="10" t="n"/>
-      <c r="M22" s="8" t="n"/>
-      <c r="N22" s="9" t="n"/>
-      <c r="O22" s="10" t="n"/>
-      <c r="P22" s="8" t="n"/>
-      <c r="Q22" s="9" t="n"/>
-      <c r="R22" s="10" t="n"/>
-      <c r="S22" s="8" t="n"/>
-      <c r="T22" s="9" t="n"/>
-      <c r="U22" s="10" t="n"/>
-      <c r="V22" s="8" t="n"/>
-      <c r="W22" s="9" t="n"/>
-      <c r="X22" s="10" t="n"/>
-      <c r="Y22" s="8" t="n"/>
-      <c r="Z22" s="9" t="n"/>
-      <c r="AA22" s="10" t="n"/>
+          <t>Auto Components</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>116089.71</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>0.0129</v>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>109571.51</v>
+      </c>
+      <c r="I22" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="J22" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>107022.46</v>
+      </c>
+      <c r="L22" s="10" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="M22" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="N22" s="9" t="n">
+        <v>112061.92</v>
+      </c>
+      <c r="O22" s="10" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="P22" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="Q22" s="9" t="n">
+        <v>103562.29</v>
+      </c>
+      <c r="R22" s="10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="S22" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="T22" s="9" t="n">
+        <v>102435.43</v>
+      </c>
+      <c r="U22" s="10" t="n">
+        <v>0.009299999999999999</v>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="W22" s="9" t="n">
+        <v>112108</v>
+      </c>
+      <c r="X22" s="10" t="n">
+        <v>0.009900000000000001</v>
+      </c>
+      <c r="Y22" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="Z22" s="9" t="n">
+        <v>95904.66</v>
+      </c>
+      <c r="AA22" s="10" t="n">
+        <v>0.0083</v>
+      </c>
       <c r="AB22" s="8" t="n">
-        <v>22000000</v>
+        <v>4189074</v>
       </c>
       <c r="AC22" s="9" t="n">
-        <v>100584</v>
+        <v>96130.87</v>
       </c>
       <c r="AD22" s="10" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="AE22" s="8" t="n">
-        <v>22000000</v>
+        <v>4189074</v>
       </c>
       <c r="AF22" s="9" t="n">
-        <v>104852</v>
+        <v>95502.50999999999</v>
       </c>
       <c r="AG22" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.0076</v>
       </c>
       <c r="AH22" s="8" t="n">
-        <v>22000000</v>
+        <v>4189074</v>
       </c>
       <c r="AI22" s="9" t="n">
-        <v>94699</v>
+        <v>96721.53</v>
       </c>
       <c r="AJ22" s="10" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="AK22" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="AL22" s="9" t="n">
+        <v>97173.95</v>
+      </c>
+      <c r="AM22" s="10" t="n">
         <v>0.0073</v>
-      </c>
-      <c r="AK22" s="8" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="AL22" s="9" t="n">
-        <v>100012</v>
-      </c>
-      <c r="AM22" s="10" t="n">
-        <v>0.0075</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services Limited</t>
+          <t>Multi Commodity Exchange of India Limited</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>INE467B01029</t>
+          <t>INE745G01035</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>IT - Software</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="10" t="n"/>
-      <c r="G23" s="8" t="n"/>
-      <c r="H23" s="9" t="n"/>
-      <c r="I23" s="10" t="n"/>
-      <c r="J23" s="8" t="n"/>
-      <c r="K23" s="9" t="n"/>
-      <c r="L23" s="10" t="n"/>
-      <c r="M23" s="8" t="n"/>
-      <c r="N23" s="9" t="n"/>
-      <c r="O23" s="10" t="n"/>
-      <c r="P23" s="8" t="n"/>
-      <c r="Q23" s="9" t="n"/>
-      <c r="R23" s="10" t="n"/>
-      <c r="S23" s="8" t="n"/>
-      <c r="T23" s="9" t="n"/>
-      <c r="U23" s="10" t="n"/>
-      <c r="V23" s="8" t="n"/>
-      <c r="W23" s="9" t="n"/>
-      <c r="X23" s="10" t="n"/>
-      <c r="Y23" s="8" t="n"/>
-      <c r="Z23" s="9" t="n"/>
-      <c r="AA23" s="10" t="n"/>
-      <c r="AB23" s="8" t="n"/>
-      <c r="AC23" s="9" t="n"/>
-      <c r="AD23" s="10" t="n"/>
-      <c r="AE23" s="8" t="n"/>
-      <c r="AF23" s="9" t="n"/>
-      <c r="AG23" s="10" t="n"/>
+          <t>Capital Markets</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>882136</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>50572.42</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="G23" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>39819.34</v>
+      </c>
+      <c r="I23" s="10" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="J23" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="K23" s="9" t="n">
+        <v>42372.84</v>
+      </c>
+      <c r="L23" s="10" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="M23" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="N23" s="9" t="n">
+        <v>48884.22</v>
+      </c>
+      <c r="O23" s="10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="P23" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="Q23" s="9" t="n">
+        <v>52665.41</v>
+      </c>
+      <c r="R23" s="10" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="S23" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="T23" s="9" t="n">
+        <v>71347.99000000001</v>
+      </c>
+      <c r="U23" s="10" t="n">
+        <v>0.0065</v>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="W23" s="9" t="n">
+        <v>61368.52</v>
+      </c>
+      <c r="X23" s="10" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="Y23" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="Z23" s="9" t="n">
+        <v>58951.43</v>
+      </c>
+      <c r="AA23" s="10" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="AB23" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AC23" s="9" t="n">
+        <v>62190.17</v>
+      </c>
+      <c r="AD23" s="10" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="AE23" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AF23" s="9" t="n">
+        <v>73737.16</v>
+      </c>
+      <c r="AG23" s="10" t="n">
+        <v>0.0059</v>
+      </c>
       <c r="AH23" s="8" t="n">
-        <v>2811139</v>
+        <v>797719</v>
       </c>
       <c r="AI23" s="9" t="n">
-        <v>88199.49000000001</v>
+        <v>80358.22</v>
       </c>
       <c r="AJ23" s="10" t="n">
-        <v>0.0068</v>
+        <v>0.0062</v>
       </c>
       <c r="AK23" s="8" t="n">
-        <v>4654589</v>
+        <v>797719</v>
       </c>
       <c r="AL23" s="9" t="n">
-        <v>149235.43</v>
+        <v>88833.99000000001</v>
       </c>
       <c r="AM23" s="10" t="n">
-        <v>0.0112</v>
+        <v>0.0067</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Multi Commodity Exchange of India Limited</t>
+          <t>EID Parry India Limited</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>INE745G01035</t>
+          <t>INE126A01031</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>882136</v>
+        <v>2259531</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>50572.42</v>
+        <v>18525.89</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>0.0056</v>
+        <v>0.0021</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>797719</v>
+        <v>2609056</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>39819.34</v>
+        <v>17326.74</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>0.0045</v>
+        <v>0.002</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>797719</v>
+        <v>2843265</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>42372.84</v>
+        <v>22336.69</v>
       </c>
       <c r="L24" s="10" t="n">
-        <v>0.0045</v>
+        <v>0.0024</v>
       </c>
       <c r="M24" s="8" t="n">
-        <v>797719</v>
+        <v>2988209</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>48884.22</v>
+        <v>24424.13</v>
       </c>
       <c r="O24" s="10" t="n">
-        <v>0.005</v>
+        <v>0.0025</v>
       </c>
       <c r="P24" s="8" t="n">
-        <v>797719</v>
+        <v>3243008</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>52665.41</v>
+        <v>30813.44</v>
       </c>
       <c r="R24" s="10" t="n">
-        <v>0.0051</v>
+        <v>0.003</v>
       </c>
       <c r="S24" s="8" t="n">
-        <v>797719</v>
+        <v>3516819</v>
       </c>
       <c r="T24" s="9" t="n">
-        <v>71347.99000000001</v>
+        <v>39036.69</v>
       </c>
       <c r="U24" s="10" t="n">
-        <v>0.0065</v>
+        <v>0.0035</v>
       </c>
       <c r="V24" s="8" t="n">
-        <v>797719</v>
+        <v>3997165</v>
       </c>
       <c r="W24" s="9" t="n">
-        <v>61368.52</v>
+        <v>49305.03</v>
       </c>
       <c r="X24" s="10" t="n">
-        <v>0.0054</v>
+        <v>0.0044</v>
       </c>
       <c r="Y24" s="8" t="n">
-        <v>797719</v>
+        <v>4433570</v>
       </c>
       <c r="Z24" s="9" t="n">
-        <v>58951.43</v>
+        <v>49913.13</v>
       </c>
       <c r="AA24" s="10" t="n">
-        <v>0.0051</v>
+        <v>0.0043</v>
       </c>
       <c r="AB24" s="8" t="n">
-        <v>797719</v>
+        <v>4996218</v>
       </c>
       <c r="AC24" s="9" t="n">
-        <v>62190.17</v>
+        <v>51236.22</v>
       </c>
       <c r="AD24" s="10" t="n">
-        <v>0.0052</v>
+        <v>0.0043</v>
       </c>
       <c r="AE24" s="8" t="n">
-        <v>797719</v>
+        <v>5528341</v>
       </c>
       <c r="AF24" s="9" t="n">
-        <v>73737.16</v>
+        <v>59285.93</v>
       </c>
       <c r="AG24" s="10" t="n">
-        <v>0.0059</v>
+        <v>0.0047</v>
       </c>
       <c r="AH24" s="8" t="n">
-        <v>797719</v>
+        <v>5842830</v>
       </c>
       <c r="AI24" s="9" t="n">
-        <v>80358.22</v>
+        <v>60233.73</v>
       </c>
       <c r="AJ24" s="10" t="n">
-        <v>0.0062</v>
+        <v>0.0046</v>
       </c>
       <c r="AK24" s="8" t="n">
-        <v>797719</v>
+        <v>6180145</v>
       </c>
       <c r="AL24" s="9" t="n">
-        <v>88833.99000000001</v>
+        <v>63945.96</v>
       </c>
       <c r="AM24" s="10" t="n">
-        <v>0.0067</v>
+        <v>0.0048</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>EID Parry India Limited</t>
+          <t>Central Depository Services (India) Limited</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>INE126A01031</t>
+          <t>INE736A01011</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>2259531</v>
+        <v>2264603</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>18525.89</v>
+        <v>29659.51</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>0.0021</v>
+        <v>0.0033</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>2609056</v>
+        <v>2264603</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>17326.74</v>
+        <v>25089.54</v>
       </c>
       <c r="I25" s="10" t="n">
-        <v>0.002</v>
+        <v>0.0029</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>2843265</v>
+        <v>2264603</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>22336.69</v>
+        <v>27629.29</v>
       </c>
       <c r="L25" s="10" t="n">
-        <v>0.0024</v>
+        <v>0.003</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>2988209</v>
+        <v>2264603</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>24424.13</v>
+        <v>29892.76</v>
       </c>
       <c r="O25" s="10" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="P25" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="Q25" s="9" t="n">
+        <v>34641.63</v>
+      </c>
+      <c r="R25" s="10" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="S25" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="T25" s="9" t="n">
+        <v>40626.98</v>
+      </c>
+      <c r="U25" s="10" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="W25" s="9" t="n">
+        <v>33534.24</v>
+      </c>
+      <c r="X25" s="10" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="Y25" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="Z25" s="9" t="n">
+        <v>32257.01</v>
+      </c>
+      <c r="AA25" s="10" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="AB25" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="AC25" s="9" t="n">
+        <v>33031.5</v>
+      </c>
+      <c r="AD25" s="10" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="AE25" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="AF25" s="9" t="n">
+        <v>35943.78</v>
+      </c>
+      <c r="AG25" s="10" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="AH25" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="AI25" s="9" t="n">
+        <v>36623.16</v>
+      </c>
+      <c r="AJ25" s="10" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="AK25" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="AL25" s="9" t="n">
+        <v>32691.81</v>
+      </c>
+      <c r="AM25" s="10" t="n">
         <v>0.0025</v>
-      </c>
-      <c r="P25" s="8" t="n">
-        <v>3243008</v>
-      </c>
-      <c r="Q25" s="9" t="n">
-        <v>30813.44</v>
-      </c>
-      <c r="R25" s="10" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="S25" s="8" t="n">
-        <v>3516819</v>
-      </c>
-      <c r="T25" s="9" t="n">
-        <v>39036.69</v>
-      </c>
-      <c r="U25" s="10" t="n">
-        <v>0.0035</v>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v>3997165</v>
-      </c>
-      <c r="W25" s="9" t="n">
-        <v>49305.03</v>
-      </c>
-      <c r="X25" s="10" t="n">
-        <v>0.0044</v>
-      </c>
-      <c r="Y25" s="8" t="n">
-        <v>4433570</v>
-      </c>
-      <c r="Z25" s="9" t="n">
-        <v>49913.13</v>
-      </c>
-      <c r="AA25" s="10" t="n">
-        <v>0.0043</v>
-      </c>
-      <c r="AB25" s="8" t="n">
-        <v>4996218</v>
-      </c>
-      <c r="AC25" s="9" t="n">
-        <v>51236.22</v>
-      </c>
-      <c r="AD25" s="10" t="n">
-        <v>0.0043</v>
-      </c>
-      <c r="AE25" s="8" t="n">
-        <v>5528341</v>
-      </c>
-      <c r="AF25" s="9" t="n">
-        <v>59285.93</v>
-      </c>
-      <c r="AG25" s="10" t="n">
-        <v>0.0047</v>
-      </c>
-      <c r="AH25" s="8" t="n">
-        <v>5842830</v>
-      </c>
-      <c r="AI25" s="9" t="n">
-        <v>60233.73</v>
-      </c>
-      <c r="AJ25" s="10" t="n">
-        <v>0.0046</v>
-      </c>
-      <c r="AK25" s="8" t="n">
-        <v>6180145</v>
-      </c>
-      <c r="AL25" s="9" t="n">
-        <v>63945.96</v>
-      </c>
-      <c r="AM25" s="10" t="n">
-        <v>0.0048</v>
       </c>
     </row>
     <row r="26">
@@ -3605,12 +3665,12 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Central Depository Services (India) Limited</t>
+          <t>ICRA Limited</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>INE736A01011</t>
+          <t>INE725G01011</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -3619,443 +3679,479 @@
         </is>
       </c>
       <c r="D27" s="8" t="n">
-        <v>2264603</v>
+        <v>297835</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>29659.51</v>
+        <v>18529.51</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>0.0033</v>
+        <v>0.0021</v>
       </c>
       <c r="G27" s="8" t="n">
-        <v>2264603</v>
+        <v>287393</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>25089.54</v>
+        <v>15273.64</v>
       </c>
       <c r="I27" s="10" t="n">
-        <v>0.0029</v>
+        <v>0.0017</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>2264603</v>
+        <v>287393</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>27629.29</v>
+        <v>15821.13</v>
       </c>
       <c r="L27" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0017</v>
       </c>
       <c r="M27" s="8" t="n">
-        <v>2264603</v>
+        <v>287393</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>29892.76</v>
+        <v>15976.18</v>
       </c>
       <c r="O27" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0016</v>
       </c>
       <c r="P27" s="8" t="n">
-        <v>2264603</v>
+        <v>287393</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>34641.63</v>
+        <v>19370.29</v>
       </c>
       <c r="R27" s="10" t="n">
-        <v>0.0033</v>
+        <v>0.0019</v>
       </c>
       <c r="S27" s="8" t="n">
-        <v>2264603</v>
+        <v>287393</v>
       </c>
       <c r="T27" s="9" t="n">
-        <v>40626.98</v>
+        <v>19453.63</v>
       </c>
       <c r="U27" s="10" t="n">
-        <v>0.0037</v>
+        <v>0.0018</v>
       </c>
       <c r="V27" s="8" t="n">
-        <v>2264603</v>
+        <v>287393</v>
       </c>
       <c r="W27" s="9" t="n">
-        <v>33534.24</v>
+        <v>19048.41</v>
       </c>
       <c r="X27" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0017</v>
       </c>
       <c r="Y27" s="8" t="n">
-        <v>2264603</v>
+        <v>287393</v>
       </c>
       <c r="Z27" s="9" t="n">
-        <v>32257.01</v>
+        <v>17962.06</v>
       </c>
       <c r="AA27" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.0016</v>
       </c>
       <c r="AB27" s="8" t="n">
-        <v>2264603</v>
+        <v>287393</v>
       </c>
       <c r="AC27" s="9" t="n">
-        <v>33031.5</v>
+        <v>18243.71</v>
       </c>
       <c r="AD27" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.0015</v>
       </c>
       <c r="AE27" s="8" t="n">
-        <v>2264603</v>
+        <v>287393</v>
       </c>
       <c r="AF27" s="9" t="n">
-        <v>35943.78</v>
+        <v>18463.56</v>
       </c>
       <c r="AG27" s="10" t="n">
-        <v>0.0029</v>
+        <v>0.0015</v>
       </c>
       <c r="AH27" s="8" t="n">
-        <v>2264603</v>
+        <v>287393</v>
       </c>
       <c r="AI27" s="9" t="n">
-        <v>36623.16</v>
+        <v>17812.62</v>
       </c>
       <c r="AJ27" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.0014</v>
       </c>
       <c r="AK27" s="8" t="n">
-        <v>2264603</v>
+        <v>287393</v>
       </c>
       <c r="AL27" s="9" t="n">
-        <v>32691.81</v>
+        <v>17460.56</v>
       </c>
       <c r="AM27" s="10" t="n">
-        <v>0.0025</v>
+        <v>0.0013</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>ICRA Limited</t>
+          <t>Maharashtra Scooters Limited</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>INE725G01011</t>
+          <t>INE288A01013</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>297835</v>
+        <v>80159</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>18529.51</v>
+        <v>7463.48</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>0.0021</v>
+        <v>0.0008</v>
       </c>
       <c r="G28" s="8" t="n">
-        <v>287393</v>
+        <v>80159</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>15273.64</v>
+        <v>7401.52</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.0008</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>287393</v>
+        <v>80159</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>15821.13</v>
+        <v>8997.450000000001</v>
       </c>
       <c r="L28" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.001</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>287393</v>
+        <v>80159</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>15976.18</v>
+        <v>9198.25</v>
       </c>
       <c r="O28" s="10" t="n">
-        <v>0.0016</v>
+        <v>0.0009</v>
       </c>
       <c r="P28" s="8" t="n">
-        <v>287393</v>
+        <v>80159</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>19370.29</v>
+        <v>10722.07</v>
       </c>
       <c r="R28" s="10" t="n">
-        <v>0.0019</v>
+        <v>0.001</v>
       </c>
       <c r="S28" s="8" t="n">
-        <v>287393</v>
+        <v>80159</v>
       </c>
       <c r="T28" s="9" t="n">
-        <v>19453.63</v>
+        <v>11621.45</v>
       </c>
       <c r="U28" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.0011</v>
       </c>
       <c r="V28" s="8" t="n">
-        <v>287393</v>
+        <v>80159</v>
       </c>
       <c r="W28" s="9" t="n">
-        <v>19048.41</v>
+        <v>12868.73</v>
       </c>
       <c r="X28" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.0011</v>
       </c>
       <c r="Y28" s="8" t="n">
-        <v>287393</v>
+        <v>80159</v>
       </c>
       <c r="Z28" s="9" t="n">
-        <v>17962.06</v>
+        <v>12726.04</v>
       </c>
       <c r="AA28" s="10" t="n">
-        <v>0.0016</v>
+        <v>0.0011</v>
       </c>
       <c r="AB28" s="8" t="n">
-        <v>287393</v>
+        <v>80159</v>
       </c>
       <c r="AC28" s="9" t="n">
-        <v>18243.71</v>
+        <v>13825.82</v>
       </c>
       <c r="AD28" s="10" t="n">
-        <v>0.0015</v>
+        <v>0.0012</v>
       </c>
       <c r="AE28" s="8" t="n">
-        <v>287393</v>
+        <v>80159</v>
       </c>
       <c r="AF28" s="9" t="n">
-        <v>18463.56</v>
+        <v>12110.42</v>
       </c>
       <c r="AG28" s="10" t="n">
-        <v>0.0015</v>
+        <v>0.001</v>
       </c>
       <c r="AH28" s="8" t="n">
-        <v>287393</v>
+        <v>80159</v>
       </c>
       <c r="AI28" s="9" t="n">
-        <v>17812.62</v>
+        <v>11787.38</v>
       </c>
       <c r="AJ28" s="10" t="n">
-        <v>0.0014</v>
+        <v>0.0009</v>
       </c>
       <c r="AK28" s="8" t="n">
-        <v>287393</v>
+        <v>80159</v>
       </c>
       <c r="AL28" s="9" t="n">
-        <v>17460.56</v>
+        <v>11401.01</v>
       </c>
       <c r="AM28" s="10" t="n">
-        <v>0.0013</v>
+        <v>0.0009</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Maharashtra Scooters Limited</t>
+          <t>Nesco Limited</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>INE288A01013</t>
+          <t>INE317F01035</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="n">
-        <v>80159</v>
-      </c>
-      <c r="E29" s="9" t="n">
-        <v>7463.48</v>
-      </c>
-      <c r="F29" s="10" t="n">
-        <v>0.0008</v>
-      </c>
-      <c r="G29" s="8" t="n">
-        <v>80159</v>
-      </c>
-      <c r="H29" s="9" t="n">
-        <v>7401.52</v>
-      </c>
-      <c r="I29" s="10" t="n">
-        <v>0.0008</v>
-      </c>
-      <c r="J29" s="8" t="n">
-        <v>80159</v>
-      </c>
-      <c r="K29" s="9" t="n">
-        <v>8997.450000000001</v>
-      </c>
-      <c r="L29" s="10" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="M29" s="8" t="n">
-        <v>80159</v>
-      </c>
-      <c r="N29" s="9" t="n">
-        <v>9198.25</v>
-      </c>
-      <c r="O29" s="10" t="n">
-        <v>0.0009</v>
-      </c>
+          <t>Commercial Services &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="10" t="n"/>
+      <c r="G29" s="8" t="n"/>
+      <c r="H29" s="9" t="n"/>
+      <c r="I29" s="10" t="n"/>
+      <c r="J29" s="8" t="n"/>
+      <c r="K29" s="9" t="n"/>
+      <c r="L29" s="10" t="n"/>
+      <c r="M29" s="8" t="n"/>
+      <c r="N29" s="9" t="n"/>
+      <c r="O29" s="10" t="n"/>
       <c r="P29" s="8" t="n">
-        <v>80159</v>
+        <v>89469</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>10722.07</v>
+        <v>828.48</v>
       </c>
       <c r="R29" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0001</v>
       </c>
       <c r="S29" s="8" t="n">
-        <v>80159</v>
+        <v>151687</v>
       </c>
       <c r="T29" s="9" t="n">
-        <v>11621.45</v>
+        <v>1766.62</v>
       </c>
       <c r="U29" s="10" t="n">
-        <v>0.0011</v>
+        <v>0.0002</v>
       </c>
       <c r="V29" s="8" t="n">
-        <v>80159</v>
+        <v>151687</v>
       </c>
       <c r="W29" s="9" t="n">
-        <v>12868.73</v>
+        <v>2091.16</v>
       </c>
       <c r="X29" s="10" t="n">
-        <v>0.0011</v>
+        <v>0.0002</v>
       </c>
       <c r="Y29" s="8" t="n">
-        <v>80159</v>
+        <v>151687</v>
       </c>
       <c r="Z29" s="9" t="n">
-        <v>12726.04</v>
+        <v>2130.6</v>
       </c>
       <c r="AA29" s="10" t="n">
-        <v>0.0011</v>
+        <v>0.0002</v>
       </c>
       <c r="AB29" s="8" t="n">
-        <v>80159</v>
+        <v>151687</v>
       </c>
       <c r="AC29" s="9" t="n">
-        <v>13825.82</v>
+        <v>1987.1</v>
       </c>
       <c r="AD29" s="10" t="n">
-        <v>0.0012</v>
+        <v>0.0002</v>
       </c>
       <c r="AE29" s="8" t="n">
-        <v>80159</v>
+        <v>151687</v>
       </c>
       <c r="AF29" s="9" t="n">
-        <v>12110.42</v>
+        <v>2076.6</v>
       </c>
       <c r="AG29" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0002</v>
       </c>
       <c r="AH29" s="8" t="n">
-        <v>80159</v>
+        <v>151687</v>
       </c>
       <c r="AI29" s="9" t="n">
-        <v>11787.38</v>
+        <v>1947.66</v>
       </c>
       <c r="AJ29" s="10" t="n">
-        <v>0.0009</v>
+        <v>0.0002</v>
       </c>
       <c r="AK29" s="8" t="n">
-        <v>80159</v>
+        <v>151687</v>
       </c>
       <c r="AL29" s="9" t="n">
-        <v>11401.01</v>
+        <v>1858.32</v>
       </c>
       <c r="AM29" s="10" t="n">
-        <v>0.0009</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Indus Towers Limited</t>
+          <t>Swaraj Engines Limited</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>INE121J01017</t>
+          <t>INE277A01016</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Telecom - Services</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="n"/>
-      <c r="E30" s="9" t="n"/>
-      <c r="F30" s="10" t="n"/>
-      <c r="G30" s="8" t="n"/>
-      <c r="H30" s="9" t="n"/>
-      <c r="I30" s="10" t="n"/>
-      <c r="J30" s="8" t="n"/>
-      <c r="K30" s="9" t="n"/>
-      <c r="L30" s="10" t="n"/>
-      <c r="M30" s="8" t="n"/>
-      <c r="N30" s="9" t="n"/>
-      <c r="O30" s="10" t="n"/>
-      <c r="P30" s="8" t="n"/>
-      <c r="Q30" s="9" t="n"/>
-      <c r="R30" s="10" t="n"/>
-      <c r="S30" s="8" t="n"/>
-      <c r="T30" s="9" t="n"/>
-      <c r="U30" s="10" t="n"/>
-      <c r="V30" s="8" t="n"/>
-      <c r="W30" s="9" t="n"/>
-      <c r="X30" s="10" t="n"/>
-      <c r="Y30" s="8" t="n"/>
-      <c r="Z30" s="9" t="n"/>
-      <c r="AA30" s="10" t="n"/>
-      <c r="AB30" s="8" t="n"/>
-      <c r="AC30" s="9" t="n"/>
-      <c r="AD30" s="10" t="n"/>
-      <c r="AE30" s="8" t="n"/>
-      <c r="AF30" s="9" t="n"/>
-      <c r="AG30" s="10" t="n"/>
+          <t>Industrial Products</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>1612.64</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="G30" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="H30" s="9" t="n">
+        <v>1236.83</v>
+      </c>
+      <c r="I30" s="10" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="J30" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <v>1844.17</v>
+      </c>
+      <c r="L30" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="M30" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="N30" s="9" t="n">
+        <v>1925.39</v>
+      </c>
+      <c r="O30" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P30" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="Q30" s="9" t="n">
+        <v>1857.76</v>
+      </c>
+      <c r="R30" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="S30" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="T30" s="9" t="n">
+        <v>1867.41</v>
+      </c>
+      <c r="U30" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="V30" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="W30" s="9" t="n">
+        <v>1983.66</v>
+      </c>
+      <c r="X30" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="Y30" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="Z30" s="9" t="n">
+        <v>1897.21</v>
+      </c>
+      <c r="AA30" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AB30" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="AC30" s="9" t="n">
+        <v>1955.38</v>
+      </c>
+      <c r="AD30" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AE30" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="AF30" s="9" t="n">
+        <v>1892.15</v>
+      </c>
+      <c r="AG30" s="10" t="n">
+        <v>0.0002</v>
+      </c>
       <c r="AH30" s="8" t="n">
-        <v>710855</v>
+        <v>47293</v>
       </c>
       <c r="AI30" s="9" t="n">
-        <v>2850.8839775</v>
+        <v>1764.08</v>
       </c>
       <c r="AJ30" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="AK30" s="8" t="n">
-        <v>710855</v>
+        <v>47293</v>
       </c>
       <c r="AL30" s="9" t="n">
-        <v>2976.71</v>
+        <v>1691.91</v>
       </c>
       <c r="AM30" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Nesco Limited</t>
+          <t>Zydus Wellness Limited</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>INE317F01035</t>
+          <t>INE768C01010</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Commercial Services &amp; Supplies</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D31" s="8" t="n"/>
@@ -4070,203 +4166,149 @@
       <c r="M31" s="8" t="n"/>
       <c r="N31" s="9" t="n"/>
       <c r="O31" s="10" t="n"/>
-      <c r="P31" s="8" t="n">
-        <v>89469</v>
-      </c>
-      <c r="Q31" s="9" t="n">
-        <v>828.48</v>
-      </c>
-      <c r="R31" s="10" t="n">
-        <v>0.0001</v>
-      </c>
+      <c r="P31" s="8" t="n"/>
+      <c r="Q31" s="9" t="n"/>
+      <c r="R31" s="10" t="n"/>
       <c r="S31" s="8" t="n">
-        <v>151687</v>
+        <v>4400000</v>
       </c>
       <c r="T31" s="9" t="n">
-        <v>1766.62</v>
+        <v>89020.8</v>
       </c>
       <c r="U31" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0081</v>
       </c>
       <c r="V31" s="8" t="n">
-        <v>151687</v>
+        <v>4400000</v>
       </c>
       <c r="W31" s="9" t="n">
-        <v>2091.16</v>
+        <v>89280.39999999999</v>
       </c>
       <c r="X31" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="Y31" s="8" t="n">
-        <v>151687</v>
+        <v>4400000</v>
       </c>
       <c r="Z31" s="9" t="n">
-        <v>2130.6</v>
+        <v>88822.8</v>
       </c>
       <c r="AA31" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AB31" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AC31" s="9" t="n">
-        <v>1987.1</v>
-      </c>
-      <c r="AD31" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AE31" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AF31" s="9" t="n">
-        <v>2076.6</v>
-      </c>
-      <c r="AG31" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AH31" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AI31" s="9" t="n">
-        <v>1947.66</v>
-      </c>
-      <c r="AJ31" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AK31" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AL31" s="9" t="n">
-        <v>1858.32</v>
-      </c>
-      <c r="AM31" s="10" t="n">
-        <v>0.0001</v>
-      </c>
+        <v>0.0077</v>
+      </c>
+      <c r="AB31" s="8" t="n"/>
+      <c r="AC31" s="9" t="n"/>
+      <c r="AD31" s="10" t="n"/>
+      <c r="AE31" s="8" t="n"/>
+      <c r="AF31" s="9" t="n"/>
+      <c r="AG31" s="10" t="n"/>
+      <c r="AH31" s="8" t="n"/>
+      <c r="AI31" s="9" t="n"/>
+      <c r="AJ31" s="10" t="n"/>
+      <c r="AK31" s="8" t="n"/>
+      <c r="AL31" s="9" t="n"/>
+      <c r="AM31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Swaraj Engines Limited</t>
+          <t>IPCA Laboratories Limited</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>INE277A01016</t>
+          <t>INE571A01038</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Industrial Products</t>
+          <t>Pharmaceuticals &amp; Biotechnology</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>47293</v>
+        <v>2246361</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>1612.64</v>
+        <v>32421.73</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0036</v>
       </c>
       <c r="G32" s="8" t="n">
-        <v>47293</v>
+        <v>1926988</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>1236.83</v>
+        <v>26117.43</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.003</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>47293</v>
+        <v>1926988</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>1844.17</v>
+        <v>28941.43</v>
       </c>
       <c r="L32" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0031</v>
       </c>
       <c r="M32" s="8" t="n">
-        <v>47293</v>
+        <v>1857217</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>1925.39</v>
+        <v>26023.32</v>
       </c>
       <c r="O32" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0026</v>
       </c>
       <c r="P32" s="8" t="n">
-        <v>47293</v>
+        <v>1641095</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>1857.76</v>
+        <v>23382.32</v>
       </c>
       <c r="R32" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0023</v>
       </c>
       <c r="S32" s="8" t="n">
-        <v>47293</v>
+        <v>1311557</v>
       </c>
       <c r="T32" s="9" t="n">
-        <v>1867.41</v>
+        <v>18228.02</v>
       </c>
       <c r="U32" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0017</v>
       </c>
       <c r="V32" s="8" t="n">
-        <v>47293</v>
+        <v>566216</v>
       </c>
       <c r="W32" s="9" t="n">
-        <v>1983.66</v>
+        <v>8345.459999999999</v>
       </c>
       <c r="X32" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0007</v>
       </c>
       <c r="Y32" s="8" t="n">
-        <v>47293</v>
+        <v>218075</v>
       </c>
       <c r="Z32" s="9" t="n">
-        <v>1897.21</v>
+        <v>3019.03</v>
       </c>
       <c r="AA32" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AB32" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="AC32" s="9" t="n">
-        <v>1955.38</v>
-      </c>
-      <c r="AD32" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AE32" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="AF32" s="9" t="n">
-        <v>1892.15</v>
-      </c>
-      <c r="AG32" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AH32" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="AI32" s="9" t="n">
-        <v>1764.08</v>
-      </c>
-      <c r="AJ32" s="10" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="AK32" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="AL32" s="9" t="n">
-        <v>1691.91</v>
-      </c>
-      <c r="AM32" s="10" t="n">
-        <v>0.0001</v>
-      </c>
+        <v>0.0003</v>
+      </c>
+      <c r="AB32" s="8" t="n"/>
+      <c r="AC32" s="9" t="n"/>
+      <c r="AD32" s="10" t="n"/>
+      <c r="AE32" s="8" t="n"/>
+      <c r="AF32" s="9" t="n"/>
+      <c r="AG32" s="10" t="n"/>
+      <c r="AH32" s="8" t="n"/>
+      <c r="AI32" s="9" t="n"/>
+      <c r="AJ32" s="10" t="n"/>
+      <c r="AK32" s="8" t="n"/>
+      <c r="AL32" s="9" t="n"/>
+      <c r="AM32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -4360,147 +4402,93 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>IPCA Laboratories Limited</t>
+          <t>Tata Consultancy Services Limited</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>INE571A01038</t>
+          <t>INE467B01029</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Pharmaceuticals &amp; Biotechnology</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="n">
-        <v>2246361</v>
-      </c>
-      <c r="E34" s="9" t="n">
-        <v>32421.73</v>
-      </c>
-      <c r="F34" s="10" t="n">
-        <v>0.0036</v>
-      </c>
-      <c r="G34" s="8" t="n">
-        <v>1926988</v>
-      </c>
-      <c r="H34" s="9" t="n">
-        <v>26117.43</v>
-      </c>
-      <c r="I34" s="10" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="J34" s="8" t="n">
-        <v>1926988</v>
-      </c>
-      <c r="K34" s="9" t="n">
-        <v>28941.43</v>
-      </c>
-      <c r="L34" s="10" t="n">
-        <v>0.0031</v>
-      </c>
-      <c r="M34" s="8" t="n">
-        <v>1857217</v>
-      </c>
-      <c r="N34" s="9" t="n">
-        <v>26023.32</v>
-      </c>
-      <c r="O34" s="10" t="n">
-        <v>0.0026</v>
-      </c>
-      <c r="P34" s="8" t="n">
-        <v>1641095</v>
-      </c>
-      <c r="Q34" s="9" t="n">
-        <v>23382.32</v>
-      </c>
-      <c r="R34" s="10" t="n">
-        <v>0.0023</v>
-      </c>
-      <c r="S34" s="8" t="n">
-        <v>1311557</v>
-      </c>
-      <c r="T34" s="9" t="n">
-        <v>18228.02</v>
-      </c>
-      <c r="U34" s="10" t="n">
-        <v>0.0017</v>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v>566216</v>
-      </c>
-      <c r="W34" s="9" t="n">
-        <v>8345.459999999999</v>
-      </c>
-      <c r="X34" s="10" t="n">
-        <v>0.0007</v>
-      </c>
-      <c r="Y34" s="8" t="n">
-        <v>218075</v>
-      </c>
-      <c r="Z34" s="9" t="n">
-        <v>3019.03</v>
-      </c>
-      <c r="AA34" s="10" t="n">
-        <v>0.0003</v>
-      </c>
+          <t>IT - Software</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="10" t="n"/>
+      <c r="G34" s="8" t="n"/>
+      <c r="H34" s="9" t="n"/>
+      <c r="I34" s="10" t="n"/>
+      <c r="J34" s="8" t="n"/>
+      <c r="K34" s="9" t="n"/>
+      <c r="L34" s="10" t="n"/>
+      <c r="M34" s="8" t="n"/>
+      <c r="N34" s="9" t="n"/>
+      <c r="O34" s="10" t="n"/>
+      <c r="P34" s="8" t="n"/>
+      <c r="Q34" s="9" t="n"/>
+      <c r="R34" s="10" t="n"/>
+      <c r="S34" s="8" t="n"/>
+      <c r="T34" s="9" t="n"/>
+      <c r="U34" s="10" t="n"/>
+      <c r="V34" s="8" t="n"/>
+      <c r="W34" s="9" t="n"/>
+      <c r="X34" s="10" t="n"/>
+      <c r="Y34" s="8" t="n"/>
+      <c r="Z34" s="9" t="n"/>
+      <c r="AA34" s="10" t="n"/>
       <c r="AB34" s="8" t="n"/>
       <c r="AC34" s="9" t="n"/>
       <c r="AD34" s="10" t="n"/>
       <c r="AE34" s="8" t="n"/>
       <c r="AF34" s="9" t="n"/>
       <c r="AG34" s="10" t="n"/>
-      <c r="AH34" s="8" t="n"/>
-      <c r="AI34" s="9" t="n"/>
-      <c r="AJ34" s="10" t="n"/>
-      <c r="AK34" s="8" t="n"/>
-      <c r="AL34" s="9" t="n"/>
-      <c r="AM34" s="10" t="n"/>
+      <c r="AH34" s="8" t="n">
+        <v>2811139</v>
+      </c>
+      <c r="AI34" s="9" t="n">
+        <v>88199.49000000001</v>
+      </c>
+      <c r="AJ34" s="10" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="AK34" s="8" t="n">
+        <v>4654589</v>
+      </c>
+      <c r="AL34" s="9" t="n">
+        <v>149235.43</v>
+      </c>
+      <c r="AM34" s="10" t="n">
+        <v>0.0112</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>ITC Hotels Limited</t>
+          <t>Indus Towers Limited</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>INE379A01028</t>
+          <t>INE121J01017</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Leisure Services</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="E35" s="9" t="n">
-        <v>16131.09</v>
-      </c>
-      <c r="F35" s="10" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="G35" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="H35" s="9" t="n">
-        <v>16216.23</v>
-      </c>
-      <c r="I35" s="10" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="J35" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="K35" s="9" t="n">
-        <v>19552.33</v>
-      </c>
-      <c r="L35" s="10" t="n">
-        <v>0.0021</v>
-      </c>
+          <t>Telecom - Services</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="10" t="n"/>
+      <c r="G35" s="8" t="n"/>
+      <c r="H35" s="9" t="n"/>
+      <c r="I35" s="10" t="n"/>
+      <c r="J35" s="8" t="n"/>
+      <c r="K35" s="9" t="n"/>
+      <c r="L35" s="10" t="n"/>
       <c r="M35" s="8" t="n"/>
       <c r="N35" s="9" t="n"/>
       <c r="O35" s="10" t="n"/>
@@ -4522,71 +4510,83 @@
       <c r="AE35" s="8" t="n"/>
       <c r="AF35" s="9" t="n"/>
       <c r="AG35" s="10" t="n"/>
-      <c r="AH35" s="8" t="n"/>
-      <c r="AI35" s="9" t="n"/>
-      <c r="AJ35" s="10" t="n"/>
-      <c r="AK35" s="8" t="n"/>
-      <c r="AL35" s="9" t="n"/>
-      <c r="AM35" s="10" t="n"/>
+      <c r="AH35" s="8" t="n">
+        <v>710855</v>
+      </c>
+      <c r="AI35" s="9" t="n">
+        <v>2850.8839775</v>
+      </c>
+      <c r="AJ35" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AK35" s="8" t="n">
+        <v>710855</v>
+      </c>
+      <c r="AL35" s="9" t="n">
+        <v>2976.71</v>
+      </c>
+      <c r="AM35" s="10" t="n">
+        <v>0.0002</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited</t>
+          <t>ITC Hotels Limited</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>INE768C01010</t>
+          <t>INE379A01028</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="n"/>
-      <c r="E36" s="9" t="n"/>
-      <c r="F36" s="10" t="n"/>
-      <c r="G36" s="8" t="n"/>
-      <c r="H36" s="9" t="n"/>
-      <c r="I36" s="10" t="n"/>
-      <c r="J36" s="8" t="n"/>
-      <c r="K36" s="9" t="n"/>
-      <c r="L36" s="10" t="n"/>
+          <t>Leisure Services</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>16131.09</v>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="G36" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="H36" s="9" t="n">
+        <v>16216.23</v>
+      </c>
+      <c r="I36" s="10" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="J36" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="K36" s="9" t="n">
+        <v>19552.33</v>
+      </c>
+      <c r="L36" s="10" t="n">
+        <v>0.0021</v>
+      </c>
       <c r="M36" s="8" t="n"/>
       <c r="N36" s="9" t="n"/>
       <c r="O36" s="10" t="n"/>
       <c r="P36" s="8" t="n"/>
       <c r="Q36" s="9" t="n"/>
       <c r="R36" s="10" t="n"/>
-      <c r="S36" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="T36" s="9" t="n">
-        <v>89020.8</v>
-      </c>
-      <c r="U36" s="10" t="n">
-        <v>0.0081</v>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="W36" s="9" t="n">
-        <v>89280.39999999999</v>
-      </c>
-      <c r="X36" s="10" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-      <c r="Y36" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="Z36" s="9" t="n">
-        <v>88822.8</v>
-      </c>
-      <c r="AA36" s="10" t="n">
-        <v>0.0077</v>
-      </c>
+      <c r="S36" s="8" t="n"/>
+      <c r="T36" s="9" t="n"/>
+      <c r="U36" s="10" t="n"/>
+      <c r="V36" s="8" t="n"/>
+      <c r="W36" s="9" t="n"/>
+      <c r="X36" s="10" t="n"/>
+      <c r="Y36" s="8" t="n"/>
+      <c r="Z36" s="9" t="n"/>
+      <c r="AA36" s="10" t="n"/>
       <c r="AB36" s="8" t="n"/>
       <c r="AC36" s="9" t="n"/>
       <c r="AD36" s="10" t="n"/>
@@ -4671,7 +4671,7 @@
         <v>697292654</v>
       </c>
       <c r="E38" s="14" t="n">
-        <v>5868142.600000001</v>
+        <v>5868142.6</v>
       </c>
       <c r="F38" s="15" t="n">
         <v>0.6543000000000002</v>
@@ -4683,7 +4683,7 @@
         <v>5662977.75</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>0.6437</v>
+        <v>0.6436999999999999</v>
       </c>
       <c r="J38" s="13" t="n">
         <v>717176528</v>
@@ -4701,7 +4701,7 @@
         <v>6275568.750000001</v>
       </c>
       <c r="O38" s="15" t="n">
-        <v>0.6369999999999999</v>
+        <v>0.6370000000000001</v>
       </c>
       <c r="P38" s="13" t="n">
         <v>756845974</v>
@@ -4716,7 +4716,7 @@
         <v>799425942</v>
       </c>
       <c r="T38" s="14" t="n">
-        <v>7347454.07</v>
+        <v>7347454.069999999</v>
       </c>
       <c r="U38" s="15" t="n">
         <v>0.6657999999999999</v>
@@ -4737,13 +4737,13 @@
         <v>7320811.49</v>
       </c>
       <c r="AA38" s="15" t="n">
-        <v>0.6364</v>
+        <v>0.6363999999999999</v>
       </c>
       <c r="AB38" s="13" t="n">
         <v>979359723</v>
       </c>
       <c r="AC38" s="14" t="n">
-        <v>7559180.720000001</v>
+        <v>7559180.720000002</v>
       </c>
       <c r="AD38" s="15" t="n">
         <v>0.6313999999999996</v>
@@ -4761,16 +4761,16 @@
         <v>1039629309</v>
       </c>
       <c r="AI38" s="14" t="n">
-        <v>8271351.193977501</v>
+        <v>8271351.1939775</v>
       </c>
       <c r="AJ38" s="15" t="n">
-        <v>0.6374000000000001</v>
+        <v>0.6374</v>
       </c>
       <c r="AK38" s="13" t="n">
         <v>1079845116</v>
       </c>
       <c r="AL38" s="14" t="n">
-        <v>8588270.840000004</v>
+        <v>8588270.840000002</v>
       </c>
       <c r="AM38" s="15" t="n">
         <v>0.6443999999999998</v>

--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM38"/>
+  <dimension ref="A1:AV44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -496,36 +496,45 @@
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
     <col width="26" customWidth="1" min="14" max="14"/>
     <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
     <col width="26" customWidth="1" min="17" max="17"/>
     <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
     <col width="26" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="20" customWidth="1" min="24" max="24"/>
     <col width="13" customWidth="1" min="25" max="25"/>
     <col width="26" customWidth="1" min="26" max="26"/>
     <col width="20" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
     <col width="26" customWidth="1" min="29" max="29"/>
     <col width="20" customWidth="1" min="30" max="30"/>
-    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
     <col width="26" customWidth="1" min="32" max="32"/>
-    <col width="14" customWidth="1" min="33" max="33"/>
-    <col width="15" customWidth="1" min="34" max="34"/>
+    <col width="20" customWidth="1" min="33" max="33"/>
+    <col width="13" customWidth="1" min="34" max="34"/>
     <col width="26" customWidth="1" min="35" max="35"/>
-    <col width="14" customWidth="1" min="36" max="36"/>
-    <col width="15" customWidth="1" min="37" max="37"/>
+    <col width="20" customWidth="1" min="36" max="36"/>
+    <col width="13" customWidth="1" min="37" max="37"/>
     <col width="26" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
+    <col width="13" customWidth="1" min="40" max="40"/>
+    <col width="26" customWidth="1" min="41" max="41"/>
+    <col width="20" customWidth="1" min="42" max="42"/>
+    <col width="15" customWidth="1" min="43" max="43"/>
+    <col width="26" customWidth="1" min="44" max="44"/>
+    <col width="20" customWidth="1" min="45" max="45"/>
+    <col width="14" customWidth="1" min="46" max="46"/>
+    <col width="26" customWidth="1" min="47" max="47"/>
+    <col width="20" customWidth="1" min="48" max="48"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -572,6 +581,15 @@
       <c r="AK1" s="1" t="n"/>
       <c r="AL1" s="1" t="n"/>
       <c r="AM1" s="1" t="n"/>
+      <c r="AN1" s="1" t="n"/>
+      <c r="AO1" s="1" t="n"/>
+      <c r="AP1" s="1" t="n"/>
+      <c r="AQ1" s="1" t="n"/>
+      <c r="AR1" s="1" t="n"/>
+      <c r="AS1" s="1" t="n"/>
+      <c r="AT1" s="1" t="n"/>
+      <c r="AU1" s="1" t="n"/>
+      <c r="AV1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -591,49 +609,49 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>January_2025</t>
+          <t>March_2026</t>
         </is>
       </c>
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="3" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>February_2025</t>
+          <t>February_2026</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="3" t="n"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>March_2025</t>
+          <t>January_2026</t>
         </is>
       </c>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="3" t="n"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>April_2025</t>
+          <t>December_2025</t>
         </is>
       </c>
       <c r="N2" s="2" t="n"/>
       <c r="O2" s="3" t="n"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>May_2025</t>
+          <t>November_2025</t>
         </is>
       </c>
       <c r="Q2" s="2" t="n"/>
       <c r="R2" s="3" t="n"/>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>June_2025</t>
+          <t>October_2025</t>
         </is>
       </c>
       <c r="T2" s="2" t="n"/>
       <c r="U2" s="3" t="n"/>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>July_2025</t>
+          <t>September_2025</t>
         </is>
       </c>
       <c r="W2" s="2" t="n"/>
@@ -647,32 +665,53 @@
       <c r="AA2" s="3" t="n"/>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>September_2025</t>
+          <t>July_2025</t>
         </is>
       </c>
       <c r="AC2" s="2" t="n"/>
       <c r="AD2" s="3" t="n"/>
       <c r="AE2" s="2" t="inlineStr">
         <is>
-          <t>October_2025</t>
+          <t>June_2025</t>
         </is>
       </c>
       <c r="AF2" s="2" t="n"/>
       <c r="AG2" s="3" t="n"/>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>November_2025</t>
+          <t>May_2025</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n"/>
       <c r="AJ2" s="3" t="n"/>
       <c r="AK2" s="2" t="inlineStr">
         <is>
-          <t>December_2025</t>
+          <t>April_2025</t>
         </is>
       </c>
       <c r="AL2" s="2" t="n"/>
       <c r="AM2" s="3" t="n"/>
+      <c r="AN2" s="2" t="inlineStr">
+        <is>
+          <t>March_2025</t>
+        </is>
+      </c>
+      <c r="AO2" s="2" t="n"/>
+      <c r="AP2" s="3" t="n"/>
+      <c r="AQ2" s="2" t="inlineStr">
+        <is>
+          <t>February_2025</t>
+        </is>
+      </c>
+      <c r="AR2" s="2" t="n"/>
+      <c r="AS2" s="3" t="n"/>
+      <c r="AT2" s="2" t="inlineStr">
+        <is>
+          <t>January_2025</t>
+        </is>
+      </c>
+      <c r="AU2" s="2" t="n"/>
+      <c r="AV2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n"/>
@@ -858,6 +897,51 @@
           <t>% Net Assets</t>
         </is>
       </c>
+      <c r="AN3" s="4" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="AO3" s="4" t="inlineStr">
+        <is>
+          <t>Market Value (Rs. Lakhs)</t>
+        </is>
+      </c>
+      <c r="AP3" s="5" t="inlineStr">
+        <is>
+          <t>% Net Assets</t>
+        </is>
+      </c>
+      <c r="AQ3" s="4" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="AR3" s="4" t="inlineStr">
+        <is>
+          <t>Market Value (Rs. Lakhs)</t>
+        </is>
+      </c>
+      <c r="AS3" s="5" t="inlineStr">
+        <is>
+          <t>% Net Assets</t>
+        </is>
+      </c>
+      <c r="AT3" s="4" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="AU3" s="4" t="inlineStr">
+        <is>
+          <t>Market Value (Rs. Lakhs)</t>
+        </is>
+      </c>
+      <c r="AV3" s="5" t="inlineStr">
+        <is>
+          <t>% Net Assets</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -876,67 +960,67 @@
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>42813069</v>
+        <v>140247203</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>727287.01</v>
+        <v>1025978.41</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.0796</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>42813069</v>
+        <v>116915576</v>
       </c>
       <c r="H4" s="9" t="n">
-        <v>741693.61</v>
+        <v>1037918.03</v>
       </c>
       <c r="I4" s="10" t="n">
-        <v>0.0843</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>42813069</v>
+        <v>115915576</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>782708.53</v>
+        <v>1077145.49</v>
       </c>
       <c r="L4" s="10" t="n">
-        <v>0.0838</v>
+        <v>0.0804</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>42813069</v>
+        <v>108738215</v>
       </c>
       <c r="N4" s="9" t="n">
-        <v>824151.58</v>
+        <v>1077813.19</v>
       </c>
       <c r="O4" s="10" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.0809</v>
       </c>
       <c r="P4" s="8" t="n">
-        <v>43293069</v>
+        <v>103486016</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>842006.9</v>
+        <v>1042725.1</v>
       </c>
       <c r="R4" s="10" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.0803</v>
       </c>
       <c r="S4" s="8" t="n">
-        <v>44461271</v>
+        <v>102203321</v>
       </c>
       <c r="T4" s="9" t="n">
-        <v>889892.34</v>
+        <v>1009053.39</v>
       </c>
       <c r="U4" s="10" t="n">
-        <v>0.0806</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="V4" s="8" t="n">
-        <v>44870461</v>
+        <v>101668321</v>
       </c>
       <c r="W4" s="9" t="n">
-        <v>905575.64</v>
+        <v>966865.73</v>
       </c>
       <c r="X4" s="10" t="n">
-        <v>0.0799</v>
+        <v>0.0808</v>
       </c>
       <c r="Y4" s="8" t="n">
         <v>95825482</v>
@@ -948,551 +1032,686 @@
         <v>0.0793</v>
       </c>
       <c r="AB4" s="8" t="n">
-        <v>101668321</v>
+        <v>44870461</v>
       </c>
       <c r="AC4" s="9" t="n">
-        <v>966865.73</v>
+        <v>905575.64</v>
       </c>
       <c r="AD4" s="10" t="n">
-        <v>0.0808</v>
+        <v>0.0799</v>
       </c>
       <c r="AE4" s="8" t="n">
-        <v>102203321</v>
+        <v>44461271</v>
       </c>
       <c r="AF4" s="9" t="n">
-        <v>1009053.39</v>
+        <v>889892.34</v>
       </c>
       <c r="AG4" s="10" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.0806</v>
       </c>
       <c r="AH4" s="8" t="n">
-        <v>103486016</v>
+        <v>43293069</v>
       </c>
       <c r="AI4" s="9" t="n">
-        <v>1042725.1</v>
+        <v>842006.9</v>
       </c>
       <c r="AJ4" s="10" t="n">
-        <v>0.0803</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="AK4" s="8" t="n">
-        <v>108738215</v>
+        <v>42813069</v>
       </c>
       <c r="AL4" s="9" t="n">
-        <v>1077813.19</v>
+        <v>824151.58</v>
       </c>
       <c r="AM4" s="10" t="n">
-        <v>0.0809</v>
+        <v>0.08359999999999999</v>
+      </c>
+      <c r="AN4" s="8" t="n">
+        <v>42813069</v>
+      </c>
+      <c r="AO4" s="9" t="n">
+        <v>782708.53</v>
+      </c>
+      <c r="AP4" s="10" t="n">
+        <v>0.0838</v>
+      </c>
+      <c r="AQ4" s="8" t="n">
+        <v>42813069</v>
+      </c>
+      <c r="AR4" s="9" t="n">
+        <v>741693.61</v>
+      </c>
+      <c r="AS4" s="10" t="n">
+        <v>0.0843</v>
+      </c>
+      <c r="AT4" s="8" t="n">
+        <v>42813069</v>
+      </c>
+      <c r="AU4" s="9" t="n">
+        <v>727287.01</v>
+      </c>
+      <c r="AV4" s="10" t="n">
+        <v>0.08110000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Power Grid Corporation of India Limited</t>
+          <t>Bajaj Holdings &amp; Investment Limited</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>INE752E01010</t>
+          <t>INE118A01012</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>185577147</v>
+        <v>6026828</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>559793.46</v>
+        <v>527106.38</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.0624</v>
+        <v>0.0409</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>193498810</v>
+        <v>6026828</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>485391.76</v>
+        <v>651138.5</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>0.0552</v>
+        <v>0.0485</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>192765312</v>
+        <v>5979253</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>559694.08</v>
+        <v>645759.3199999999</v>
       </c>
       <c r="L5" s="10" t="n">
-        <v>0.0599</v>
+        <v>0.0482</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>193616648</v>
+        <v>5318918</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>595274.38</v>
+        <v>602527.03</v>
       </c>
       <c r="O5" s="10" t="n">
-        <v>0.0604</v>
+        <v>0.0452</v>
       </c>
       <c r="P5" s="8" t="n">
-        <v>208867542</v>
+        <v>5318918</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>605193.7</v>
+        <v>611622.38</v>
       </c>
       <c r="R5" s="10" t="n">
-        <v>0.0583</v>
+        <v>0.0471</v>
       </c>
       <c r="S5" s="8" t="n">
-        <v>224216515</v>
+        <v>5318918</v>
       </c>
       <c r="T5" s="9" t="n">
-        <v>672425.33</v>
+        <v>654386.48</v>
       </c>
       <c r="U5" s="10" t="n">
-        <v>0.0609</v>
+        <v>0.052</v>
       </c>
       <c r="V5" s="8" t="n">
-        <v>230787510</v>
+        <v>5318918</v>
       </c>
       <c r="W5" s="9" t="n">
-        <v>671591.65</v>
+        <v>651407.89</v>
       </c>
       <c r="X5" s="10" t="n">
-        <v>0.0593</v>
+        <v>0.0544</v>
       </c>
       <c r="Y5" s="8" t="n">
-        <v>246049993</v>
+        <v>5318918</v>
       </c>
       <c r="Z5" s="9" t="n">
-        <v>677252.61</v>
+        <v>679225.83</v>
       </c>
       <c r="AA5" s="10" t="n">
-        <v>0.0589</v>
+        <v>0.059</v>
       </c>
       <c r="AB5" s="8" t="n">
-        <v>255922726</v>
+        <v>5318918</v>
       </c>
       <c r="AC5" s="9" t="n">
-        <v>717223.4399999999</v>
+        <v>742680.52</v>
       </c>
       <c r="AD5" s="10" t="n">
-        <v>0.0599</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="AE5" s="8" t="n">
-        <v>261786637</v>
+        <v>5318918</v>
       </c>
       <c r="AF5" s="9" t="n">
-        <v>754338.1899999999</v>
+        <v>764807.22</v>
       </c>
       <c r="AG5" s="10" t="n">
-        <v>0.06</v>
+        <v>0.0693</v>
       </c>
       <c r="AH5" s="8" t="n">
-        <v>284154236</v>
+        <v>5318918</v>
       </c>
       <c r="AI5" s="9" t="n">
-        <v>767074.36</v>
+        <v>713479.66</v>
       </c>
       <c r="AJ5" s="10" t="n">
-        <v>0.0591</v>
+        <v>0.0687</v>
       </c>
       <c r="AK5" s="8" t="n">
-        <v>305419267</v>
+        <v>5318918</v>
       </c>
       <c r="AL5" s="9" t="n">
-        <v>808139.38</v>
+        <v>636834.05</v>
       </c>
       <c r="AM5" s="10" t="n">
-        <v>0.0606</v>
+        <v>0.0646</v>
+      </c>
+      <c r="AN5" s="8" t="n">
+        <v>5318918</v>
+      </c>
+      <c r="AO5" s="9" t="n">
+        <v>663431.3</v>
+      </c>
+      <c r="AP5" s="10" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="AQ5" s="8" t="n">
+        <v>5318918</v>
+      </c>
+      <c r="AR5" s="9" t="n">
+        <v>615630.1899999999</v>
+      </c>
+      <c r="AS5" s="10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AT5" s="8" t="n">
+        <v>5318918</v>
+      </c>
+      <c r="AU5" s="9" t="n">
+        <v>614850.96</v>
+      </c>
+      <c r="AV5" s="10" t="n">
+        <v>0.06850000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Bajaj Holdings &amp; Investment Limited</t>
+          <t>Coal India Limited</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>INE118A01012</t>
+          <t>INE522F01014</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Consumable Fuels</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>5318918</v>
+        <v>174817417</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>614850.96</v>
+        <v>787465.05</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.0611</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>5318918</v>
+        <v>161423761</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>615630.1899999999</v>
+        <v>695171.4300000001</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0518</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>5318918</v>
+        <v>159832308</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>663431.3</v>
+        <v>704460.9</v>
       </c>
       <c r="L6" s="10" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.0526</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>5318918</v>
+        <v>162039558</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>636834.05</v>
+        <v>646537.84</v>
       </c>
       <c r="O6" s="10" t="n">
-        <v>0.0646</v>
+        <v>0.0485</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>5318918</v>
+        <v>162039558</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>713479.66</v>
+        <v>609511.8</v>
       </c>
       <c r="R6" s="10" t="n">
-        <v>0.0687</v>
+        <v>0.047</v>
       </c>
       <c r="S6" s="8" t="n">
-        <v>5318918</v>
+        <v>162039558</v>
       </c>
       <c r="T6" s="9" t="n">
-        <v>764807.22</v>
+        <v>629766.74</v>
       </c>
       <c r="U6" s="10" t="n">
-        <v>0.0693</v>
+        <v>0.0501</v>
       </c>
       <c r="V6" s="8" t="n">
-        <v>5318918</v>
+        <v>162039558</v>
       </c>
       <c r="W6" s="9" t="n">
-        <v>742680.52</v>
+        <v>631873.26</v>
       </c>
       <c r="X6" s="10" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0528</v>
       </c>
       <c r="Y6" s="8" t="n">
-        <v>5318918</v>
+        <v>162039558</v>
       </c>
       <c r="Z6" s="9" t="n">
-        <v>679225.83</v>
+        <v>607324.26</v>
       </c>
       <c r="AA6" s="10" t="n">
-        <v>0.059</v>
+        <v>0.0528</v>
       </c>
       <c r="AB6" s="8" t="n">
-        <v>5318918</v>
+        <v>162039558</v>
       </c>
       <c r="AC6" s="9" t="n">
-        <v>651407.89</v>
+        <v>609835.88</v>
       </c>
       <c r="AD6" s="10" t="n">
-        <v>0.0544</v>
+        <v>0.0538</v>
       </c>
       <c r="AE6" s="8" t="n">
-        <v>5318918</v>
+        <v>162039558</v>
       </c>
       <c r="AF6" s="9" t="n">
-        <v>654386.48</v>
+        <v>635114.05</v>
       </c>
       <c r="AG6" s="10" t="n">
-        <v>0.052</v>
+        <v>0.0575</v>
       </c>
       <c r="AH6" s="8" t="n">
-        <v>5318918</v>
+        <v>155681572</v>
       </c>
       <c r="AI6" s="9" t="n">
-        <v>611622.38</v>
+        <v>618522.89</v>
       </c>
       <c r="AJ6" s="10" t="n">
-        <v>0.0471</v>
+        <v>0.0595</v>
       </c>
       <c r="AK6" s="8" t="n">
-        <v>5318918</v>
+        <v>148323775</v>
       </c>
       <c r="AL6" s="9" t="n">
-        <v>602527.03</v>
+        <v>571491.51</v>
       </c>
       <c r="AM6" s="10" t="n">
-        <v>0.0452</v>
+        <v>0.058</v>
+      </c>
+      <c r="AN6" s="8" t="n">
+        <v>141074007</v>
+      </c>
+      <c r="AO6" s="9" t="n">
+        <v>561756.7</v>
+      </c>
+      <c r="AP6" s="10" t="n">
+        <v>0.0601</v>
+      </c>
+      <c r="AQ6" s="8" t="n">
+        <v>142636407</v>
+      </c>
+      <c r="AR6" s="9" t="n">
+        <v>526827.5699999999</v>
+      </c>
+      <c r="AS6" s="10" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="AT6" s="8" t="n">
+        <v>139335199</v>
+      </c>
+      <c r="AU6" s="9" t="n">
+        <v>551628.05</v>
+      </c>
+      <c r="AV6" s="10" t="n">
+        <v>0.0615</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Coal India Limited</t>
+          <t>Power Grid Corporation of India Limited</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>INE522F01014</t>
+          <t>INE752E01010</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Consumable Fuels</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>139335199</v>
+        <v>312063864</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>551628.05</v>
+        <v>924021.1</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.0615</v>
+        <v>0.0716</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>142636407</v>
+        <v>311113864</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>526827.5699999999</v>
+        <v>929141.55</v>
       </c>
       <c r="I7" s="10" t="n">
+        <v>0.0692</v>
+      </c>
+      <c r="J7" s="8" t="n">
+        <v>313365617</v>
+      </c>
+      <c r="K7" s="9" t="n">
+        <v>803782.8100000001</v>
+      </c>
+      <c r="L7" s="10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>305419267</v>
+      </c>
+      <c r="N7" s="9" t="n">
+        <v>808139.38</v>
+      </c>
+      <c r="O7" s="10" t="n">
+        <v>0.0606</v>
+      </c>
+      <c r="P7" s="8" t="n">
+        <v>284154236</v>
+      </c>
+      <c r="Q7" s="9" t="n">
+        <v>767074.36</v>
+      </c>
+      <c r="R7" s="10" t="n">
+        <v>0.0591</v>
+      </c>
+      <c r="S7" s="8" t="n">
+        <v>261786637</v>
+      </c>
+      <c r="T7" s="9" t="n">
+        <v>754338.1899999999</v>
+      </c>
+      <c r="U7" s="10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v>255922726</v>
+      </c>
+      <c r="W7" s="9" t="n">
+        <v>717223.4399999999</v>
+      </c>
+      <c r="X7" s="10" t="n">
         <v>0.0599</v>
       </c>
-      <c r="J7" s="8" t="n">
-        <v>141074007</v>
-      </c>
-      <c r="K7" s="9" t="n">
-        <v>561756.7</v>
-      </c>
-      <c r="L7" s="10" t="n">
-        <v>0.0601</v>
-      </c>
-      <c r="M7" s="8" t="n">
-        <v>148323775</v>
-      </c>
-      <c r="N7" s="9" t="n">
-        <v>571491.51</v>
-      </c>
-      <c r="O7" s="10" t="n">
-        <v>0.058</v>
-      </c>
-      <c r="P7" s="8" t="n">
-        <v>155681572</v>
-      </c>
-      <c r="Q7" s="9" t="n">
-        <v>618522.89</v>
-      </c>
-      <c r="R7" s="10" t="n">
-        <v>0.0595</v>
-      </c>
-      <c r="S7" s="8" t="n">
-        <v>162039558</v>
-      </c>
-      <c r="T7" s="9" t="n">
-        <v>635114.05</v>
-      </c>
-      <c r="U7" s="10" t="n">
-        <v>0.0575</v>
-      </c>
-      <c r="V7" s="8" t="n">
-        <v>162039558</v>
-      </c>
-      <c r="W7" s="9" t="n">
-        <v>609835.88</v>
-      </c>
-      <c r="X7" s="10" t="n">
-        <v>0.0538</v>
-      </c>
       <c r="Y7" s="8" t="n">
-        <v>162039558</v>
+        <v>246049993</v>
       </c>
       <c r="Z7" s="9" t="n">
-        <v>607324.26</v>
+        <v>677252.61</v>
       </c>
       <c r="AA7" s="10" t="n">
-        <v>0.0528</v>
+        <v>0.0589</v>
       </c>
       <c r="AB7" s="8" t="n">
-        <v>162039558</v>
+        <v>230787510</v>
       </c>
       <c r="AC7" s="9" t="n">
-        <v>631873.26</v>
+        <v>671591.65</v>
       </c>
       <c r="AD7" s="10" t="n">
-        <v>0.0528</v>
+        <v>0.0593</v>
       </c>
       <c r="AE7" s="8" t="n">
-        <v>162039558</v>
+        <v>224216515</v>
       </c>
       <c r="AF7" s="9" t="n">
-        <v>629766.74</v>
+        <v>672425.33</v>
       </c>
       <c r="AG7" s="10" t="n">
-        <v>0.0501</v>
+        <v>0.0609</v>
       </c>
       <c r="AH7" s="8" t="n">
-        <v>162039558</v>
+        <v>208867542</v>
       </c>
       <c r="AI7" s="9" t="n">
-        <v>609511.8</v>
+        <v>605193.7</v>
       </c>
       <c r="AJ7" s="10" t="n">
-        <v>0.047</v>
+        <v>0.0583</v>
       </c>
       <c r="AK7" s="8" t="n">
-        <v>162039558</v>
+        <v>193616648</v>
       </c>
       <c r="AL7" s="9" t="n">
-        <v>646537.84</v>
+        <v>595274.38</v>
       </c>
       <c r="AM7" s="10" t="n">
-        <v>0.0485</v>
+        <v>0.0604</v>
+      </c>
+      <c r="AN7" s="8" t="n">
+        <v>192765312</v>
+      </c>
+      <c r="AO7" s="9" t="n">
+        <v>559694.08</v>
+      </c>
+      <c r="AP7" s="10" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="AQ7" s="8" t="n">
+        <v>193498810</v>
+      </c>
+      <c r="AR7" s="9" t="n">
+        <v>485391.76</v>
+      </c>
+      <c r="AS7" s="10" t="n">
+        <v>0.0552</v>
+      </c>
+      <c r="AT7" s="8" t="n">
+        <v>185577147</v>
+      </c>
+      <c r="AU7" s="9" t="n">
+        <v>559793.46</v>
+      </c>
+      <c r="AV7" s="10" t="n">
+        <v>0.0624</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>ITC Limited</t>
+          <t>ICICI Bank Limited</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>INE154A01025</t>
+          <t>INE090A01021</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Diversified FMCG</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>98994120</v>
+        <v>53846183</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>442998.69</v>
+        <v>649331.12</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>0.0494</v>
+        <v>0.0503</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>101194120</v>
+        <v>49325234</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>399716.77</v>
+        <v>680145.65</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>0.0454</v>
+        <v>0.0507</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>101194120</v>
+        <v>49325234</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>414642.91</v>
+        <v>668356.92</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>0.0444</v>
+        <v>0.0499</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>105271096</v>
+        <v>49325234</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>448244.33</v>
+        <v>662388.5699999999</v>
       </c>
       <c r="O8" s="10" t="n">
-        <v>0.0455</v>
+        <v>0.0497</v>
       </c>
       <c r="P8" s="8" t="n">
-        <v>109270669</v>
+        <v>45308598</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>456806.03</v>
+        <v>629245.8100000001</v>
       </c>
       <c r="R8" s="10" t="n">
-        <v>0.044</v>
+        <v>0.0485</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>117422359</v>
+        <v>43295573</v>
       </c>
       <c r="T8" s="9" t="n">
-        <v>489005.41</v>
+        <v>582455.34</v>
       </c>
       <c r="U8" s="10" t="n">
-        <v>0.0443</v>
+        <v>0.0463</v>
       </c>
       <c r="V8" s="8" t="n">
-        <v>122172359</v>
+        <v>42215573</v>
       </c>
       <c r="W8" s="9" t="n">
-        <v>503289.03</v>
+        <v>569065.92</v>
       </c>
       <c r="X8" s="10" t="n">
-        <v>0.0444</v>
+        <v>0.0475</v>
       </c>
       <c r="Y8" s="8" t="n">
-        <v>129421024</v>
+        <v>40720543</v>
       </c>
       <c r="Z8" s="9" t="n">
-        <v>530302.65</v>
+        <v>569191.75</v>
       </c>
       <c r="AA8" s="10" t="n">
-        <v>0.0461</v>
+        <v>0.0495</v>
       </c>
       <c r="AB8" s="8" t="n">
-        <v>135721024</v>
+        <v>39605543</v>
       </c>
       <c r="AC8" s="9" t="n">
-        <v>544987.77</v>
+        <v>586716.51</v>
       </c>
       <c r="AD8" s="10" t="n">
-        <v>0.0455</v>
+        <v>0.0518</v>
       </c>
       <c r="AE8" s="8" t="n">
-        <v>138771024</v>
+        <v>36489310</v>
       </c>
       <c r="AF8" s="9" t="n">
-        <v>583324</v>
+        <v>527562.4399999999</v>
       </c>
       <c r="AG8" s="10" t="n">
-        <v>0.0464</v>
+        <v>0.0478</v>
       </c>
       <c r="AH8" s="8" t="n">
-        <v>144737169</v>
+        <v>34986740</v>
       </c>
       <c r="AI8" s="9" t="n">
-        <v>585100.01</v>
+        <v>505838.29</v>
       </c>
       <c r="AJ8" s="10" t="n">
-        <v>0.0451</v>
+        <v>0.0487</v>
       </c>
       <c r="AK8" s="8" t="n">
-        <v>148665711</v>
+        <v>34986740</v>
       </c>
       <c r="AL8" s="9" t="n">
-        <v>599122.8199999999</v>
+        <v>499260.78</v>
       </c>
       <c r="AM8" s="10" t="n">
-        <v>0.0449</v>
+        <v>0.0507</v>
+      </c>
+      <c r="AN8" s="8" t="n">
+        <v>34986740</v>
+      </c>
+      <c r="AO8" s="9" t="n">
+        <v>471743.71</v>
+      </c>
+      <c r="AP8" s="10" t="n">
+        <v>0.0505</v>
+      </c>
+      <c r="AQ8" s="8" t="n">
+        <v>34986740</v>
+      </c>
+      <c r="AR8" s="9" t="n">
+        <v>421275.34</v>
+      </c>
+      <c r="AS8" s="10" t="n">
+        <v>0.0479</v>
+      </c>
+      <c r="AT8" s="8" t="n">
+        <v>34986740</v>
+      </c>
+      <c r="AU8" s="9" t="n">
+        <v>438313.88</v>
+      </c>
+      <c r="AV8" s="10" t="n">
+        <v>0.0489</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>ICICI Bank Limited</t>
+          <t>Kotak Mahindra Bank Limited</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>INE090A01021</t>
+          <t>INE237A01028</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -1500,238 +1719,274 @@
           <t>Banks</t>
         </is>
       </c>
-      <c r="D9" s="8" t="n">
-        <v>34986740</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>438313.88</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>0.0489</v>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>34986740</v>
-      </c>
-      <c r="H9" s="9" t="n">
-        <v>421275.34</v>
-      </c>
-      <c r="I9" s="10" t="n">
-        <v>0.0479</v>
-      </c>
-      <c r="J9" s="8" t="n">
-        <v>34986740</v>
-      </c>
-      <c r="K9" s="9" t="n">
-        <v>471743.71</v>
-      </c>
-      <c r="L9" s="10" t="n">
-        <v>0.0505</v>
-      </c>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="8" t="n"/>
+      <c r="H9" s="9" t="n"/>
+      <c r="I9" s="10" t="n"/>
+      <c r="J9" s="8" t="n"/>
+      <c r="K9" s="9" t="n"/>
+      <c r="L9" s="10" t="n"/>
       <c r="M9" s="8" t="n">
-        <v>34986740</v>
+        <v>24621592</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>499260.78</v>
+        <v>541945.86</v>
       </c>
       <c r="O9" s="10" t="n">
-        <v>0.0507</v>
+        <v>0.0407</v>
       </c>
       <c r="P9" s="8" t="n">
-        <v>34986740</v>
+        <v>24306544</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>505838.29</v>
+        <v>516368.22</v>
       </c>
       <c r="R9" s="10" t="n">
-        <v>0.0487</v>
+        <v>0.0398</v>
       </c>
       <c r="S9" s="8" t="n">
-        <v>36489310</v>
+        <v>24205055</v>
       </c>
       <c r="T9" s="9" t="n">
-        <v>527562.4399999999</v>
+        <v>508838.67</v>
       </c>
       <c r="U9" s="10" t="n">
-        <v>0.0478</v>
+        <v>0.0404</v>
       </c>
       <c r="V9" s="8" t="n">
-        <v>39605543</v>
+        <v>24205055</v>
       </c>
       <c r="W9" s="9" t="n">
-        <v>586716.51</v>
+        <v>482334.13</v>
       </c>
       <c r="X9" s="10" t="n">
-        <v>0.0518</v>
+        <v>0.0403</v>
       </c>
       <c r="Y9" s="8" t="n">
-        <v>40720543</v>
+        <v>23407381</v>
       </c>
       <c r="Z9" s="9" t="n">
-        <v>569191.75</v>
+        <v>458854.89</v>
       </c>
       <c r="AA9" s="10" t="n">
-        <v>0.0495</v>
+        <v>0.0399</v>
       </c>
       <c r="AB9" s="8" t="n">
-        <v>42215573</v>
+        <v>21994066</v>
       </c>
       <c r="AC9" s="9" t="n">
-        <v>569065.92</v>
+        <v>435174.59</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>0.0475</v>
+        <v>0.0384</v>
       </c>
       <c r="AE9" s="8" t="n">
-        <v>43295573</v>
+        <v>20473232</v>
       </c>
       <c r="AF9" s="9" t="n">
-        <v>582455.34</v>
+        <v>442938.37</v>
       </c>
       <c r="AG9" s="10" t="n">
-        <v>0.0463</v>
+        <v>0.0401</v>
       </c>
       <c r="AH9" s="8" t="n">
-        <v>45308598</v>
+        <v>19753232</v>
       </c>
       <c r="AI9" s="9" t="n">
-        <v>629245.8100000001</v>
+        <v>409820.3</v>
       </c>
       <c r="AJ9" s="10" t="n">
-        <v>0.0485</v>
+        <v>0.0395</v>
       </c>
       <c r="AK9" s="8" t="n">
-        <v>49325234</v>
+        <v>19753232</v>
       </c>
       <c r="AL9" s="9" t="n">
-        <v>662388.5699999999</v>
+        <v>436171.12</v>
       </c>
       <c r="AM9" s="10" t="n">
-        <v>0.0497</v>
+        <v>0.0443</v>
+      </c>
+      <c r="AN9" s="8" t="n">
+        <v>19753232</v>
+      </c>
+      <c r="AO9" s="9" t="n">
+        <v>428882.17</v>
+      </c>
+      <c r="AP9" s="10" t="n">
+        <v>0.0459</v>
+      </c>
+      <c r="AQ9" s="8" t="n">
+        <v>19753232</v>
+      </c>
+      <c r="AR9" s="9" t="n">
+        <v>375894.13</v>
+      </c>
+      <c r="AS9" s="10" t="n">
+        <v>0.0427</v>
+      </c>
+      <c r="AT9" s="8" t="n">
+        <v>19753232</v>
+      </c>
+      <c r="AU9" s="9" t="n">
+        <v>375568.2</v>
+      </c>
+      <c r="AV9" s="10" t="n">
+        <v>0.0419</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Kotak Mahindra Bank Limited</t>
+          <t>ITC Limited</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>INE237A01028</t>
+          <t>INE154A01025</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Diversified FMCG</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>19753232</v>
+        <v>224093958</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>375568.2</v>
+        <v>644718.3199999999</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>0.0419</v>
+        <v>0.05</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>19753232</v>
+        <v>215593958</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>375894.13</v>
+        <v>676102.65</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>0.0427</v>
+        <v>0.0504</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>19753232</v>
+        <v>209900994</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>428882.17</v>
+        <v>676196.05</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>0.0459</v>
+        <v>0.0505</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>19753232</v>
+        <v>148665711</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>436171.12</v>
+        <v>599122.8199999999</v>
       </c>
       <c r="O10" s="10" t="n">
+        <v>0.0449</v>
+      </c>
+      <c r="P10" s="8" t="n">
+        <v>144737169</v>
+      </c>
+      <c r="Q10" s="9" t="n">
+        <v>585100.01</v>
+      </c>
+      <c r="R10" s="10" t="n">
+        <v>0.0451</v>
+      </c>
+      <c r="S10" s="8" t="n">
+        <v>138771024</v>
+      </c>
+      <c r="T10" s="9" t="n">
+        <v>583324</v>
+      </c>
+      <c r="U10" s="10" t="n">
+        <v>0.0464</v>
+      </c>
+      <c r="V10" s="8" t="n">
+        <v>135721024</v>
+      </c>
+      <c r="W10" s="9" t="n">
+        <v>544987.77</v>
+      </c>
+      <c r="X10" s="10" t="n">
+        <v>0.0455</v>
+      </c>
+      <c r="Y10" s="8" t="n">
+        <v>129421024</v>
+      </c>
+      <c r="Z10" s="9" t="n">
+        <v>530302.65</v>
+      </c>
+      <c r="AA10" s="10" t="n">
+        <v>0.0461</v>
+      </c>
+      <c r="AB10" s="8" t="n">
+        <v>122172359</v>
+      </c>
+      <c r="AC10" s="9" t="n">
+        <v>503289.03</v>
+      </c>
+      <c r="AD10" s="10" t="n">
+        <v>0.0444</v>
+      </c>
+      <c r="AE10" s="8" t="n">
+        <v>117422359</v>
+      </c>
+      <c r="AF10" s="9" t="n">
+        <v>489005.41</v>
+      </c>
+      <c r="AG10" s="10" t="n">
         <v>0.0443</v>
       </c>
-      <c r="P10" s="8" t="n">
-        <v>19753232</v>
-      </c>
-      <c r="Q10" s="9" t="n">
-        <v>409820.3</v>
-      </c>
-      <c r="R10" s="10" t="n">
-        <v>0.0395</v>
-      </c>
-      <c r="S10" s="8" t="n">
-        <v>20473232</v>
-      </c>
-      <c r="T10" s="9" t="n">
-        <v>442938.37</v>
-      </c>
-      <c r="U10" s="10" t="n">
-        <v>0.0401</v>
-      </c>
-      <c r="V10" s="8" t="n">
-        <v>21994066</v>
-      </c>
-      <c r="W10" s="9" t="n">
-        <v>435174.59</v>
-      </c>
-      <c r="X10" s="10" t="n">
-        <v>0.0384</v>
-      </c>
-      <c r="Y10" s="8" t="n">
-        <v>23407381</v>
-      </c>
-      <c r="Z10" s="9" t="n">
-        <v>458854.89</v>
-      </c>
-      <c r="AA10" s="10" t="n">
-        <v>0.0399</v>
-      </c>
-      <c r="AB10" s="8" t="n">
-        <v>24205055</v>
-      </c>
-      <c r="AC10" s="9" t="n">
-        <v>482334.13</v>
-      </c>
-      <c r="AD10" s="10" t="n">
-        <v>0.0403</v>
-      </c>
-      <c r="AE10" s="8" t="n">
-        <v>24205055</v>
-      </c>
-      <c r="AF10" s="9" t="n">
-        <v>508838.67</v>
-      </c>
-      <c r="AG10" s="10" t="n">
-        <v>0.0404</v>
-      </c>
       <c r="AH10" s="8" t="n">
-        <v>24306544</v>
+        <v>109270669</v>
       </c>
       <c r="AI10" s="9" t="n">
-        <v>516368.22</v>
+        <v>456806.03</v>
       </c>
       <c r="AJ10" s="10" t="n">
-        <v>0.0398</v>
+        <v>0.044</v>
       </c>
       <c r="AK10" s="8" t="n">
-        <v>24621592</v>
+        <v>105271096</v>
       </c>
       <c r="AL10" s="9" t="n">
-        <v>541945.86</v>
+        <v>448244.33</v>
       </c>
       <c r="AM10" s="10" t="n">
-        <v>0.0407</v>
+        <v>0.0455</v>
+      </c>
+      <c r="AN10" s="8" t="n">
+        <v>101194120</v>
+      </c>
+      <c r="AO10" s="9" t="n">
+        <v>414642.91</v>
+      </c>
+      <c r="AP10" s="10" t="n">
+        <v>0.0444</v>
+      </c>
+      <c r="AQ10" s="8" t="n">
+        <v>101194120</v>
+      </c>
+      <c r="AR10" s="9" t="n">
+        <v>399716.77</v>
+      </c>
+      <c r="AS10" s="10" t="n">
+        <v>0.0454</v>
+      </c>
+      <c r="AT10" s="8" t="n">
+        <v>98994120</v>
+      </c>
+      <c r="AU10" s="9" t="n">
+        <v>442998.69</v>
+      </c>
+      <c r="AV10" s="10" t="n">
+        <v>0.0494</v>
       </c>
     </row>
     <row r="11">
@@ -1751,67 +2006,67 @@
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>3018078</v>
+        <v>3039945</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>371545.02</v>
+        <v>374095.63</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.0414</v>
+        <v>0.029</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>3018078</v>
+        <v>2861040</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>360535.07</v>
+        <v>425064.71</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>0.041</v>
+        <v>0.0317</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>3018078</v>
+        <v>2780478</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>347747.47</v>
+        <v>405921.98</v>
       </c>
       <c r="L11" s="10" t="n">
-        <v>0.0372</v>
+        <v>0.0303</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>3021670</v>
+        <v>2746670</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>370366.09</v>
+        <v>458611.49</v>
       </c>
       <c r="O11" s="10" t="n">
-        <v>0.0376</v>
+        <v>0.0344</v>
       </c>
       <c r="P11" s="8" t="n">
-        <v>3021670</v>
+        <v>2746670</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>372239.53</v>
+        <v>436720.53</v>
       </c>
       <c r="R11" s="10" t="n">
-        <v>0.0358</v>
+        <v>0.0337</v>
       </c>
       <c r="S11" s="8" t="n">
-        <v>3021670</v>
+        <v>2696670</v>
       </c>
       <c r="T11" s="9" t="n">
-        <v>374687.08</v>
+        <v>436483.01</v>
       </c>
       <c r="U11" s="10" t="n">
-        <v>0.0339</v>
+        <v>0.0347</v>
       </c>
       <c r="V11" s="8" t="n">
-        <v>3021670</v>
+        <v>2696670</v>
       </c>
       <c r="W11" s="9" t="n">
-        <v>380972.15</v>
+        <v>432249.23</v>
       </c>
       <c r="X11" s="10" t="n">
-        <v>0.0336</v>
+        <v>0.0361</v>
       </c>
       <c r="Y11" s="8" t="n">
         <v>2746670</v>
@@ -1823,402 +2078,534 @@
         <v>0.0353</v>
       </c>
       <c r="AB11" s="8" t="n">
-        <v>2696670</v>
+        <v>3021670</v>
       </c>
       <c r="AC11" s="9" t="n">
-        <v>432249.23</v>
+        <v>380972.15</v>
       </c>
       <c r="AD11" s="10" t="n">
-        <v>0.0361</v>
+        <v>0.0336</v>
       </c>
       <c r="AE11" s="8" t="n">
-        <v>2696670</v>
+        <v>3021670</v>
       </c>
       <c r="AF11" s="9" t="n">
-        <v>436483.01</v>
+        <v>374687.08</v>
       </c>
       <c r="AG11" s="10" t="n">
-        <v>0.0347</v>
+        <v>0.0339</v>
       </c>
       <c r="AH11" s="8" t="n">
-        <v>2746670</v>
+        <v>3021670</v>
       </c>
       <c r="AI11" s="9" t="n">
-        <v>436720.53</v>
+        <v>372239.53</v>
       </c>
       <c r="AJ11" s="10" t="n">
-        <v>0.0337</v>
+        <v>0.0358</v>
       </c>
       <c r="AK11" s="8" t="n">
-        <v>2746670</v>
+        <v>3021670</v>
       </c>
       <c r="AL11" s="9" t="n">
-        <v>458611.49</v>
+        <v>370366.09</v>
       </c>
       <c r="AM11" s="10" t="n">
-        <v>0.0344</v>
+        <v>0.0376</v>
+      </c>
+      <c r="AN11" s="8" t="n">
+        <v>3018078</v>
+      </c>
+      <c r="AO11" s="9" t="n">
+        <v>347747.47</v>
+      </c>
+      <c r="AP11" s="10" t="n">
+        <v>0.0372</v>
+      </c>
+      <c r="AQ11" s="8" t="n">
+        <v>3018078</v>
+      </c>
+      <c r="AR11" s="9" t="n">
+        <v>360535.07</v>
+      </c>
+      <c r="AS11" s="10" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="AT11" s="8" t="n">
+        <v>3018078</v>
+      </c>
+      <c r="AU11" s="9" t="n">
+        <v>371545.02</v>
+      </c>
+      <c r="AV11" s="10" t="n">
+        <v>0.0414</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Bharti Airtel Limited</t>
+          <t>Axis Bank Limited</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>INE397D01024</t>
+          <t>INE238A01034</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Telecom - Services</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="9" t="n"/>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="8" t="n"/>
-      <c r="H12" s="9" t="n"/>
-      <c r="I12" s="10" t="n"/>
-      <c r="J12" s="8" t="n"/>
-      <c r="K12" s="9" t="n"/>
-      <c r="L12" s="10" t="n"/>
-      <c r="M12" s="8" t="n"/>
-      <c r="N12" s="9" t="n"/>
-      <c r="O12" s="10" t="n"/>
+          <t>Banks</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>33244875</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>386072.73</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>0.0299</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>33244875</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>460075.83</v>
+      </c>
+      <c r="I12" s="10" t="n">
+        <v>0.0343</v>
+      </c>
+      <c r="J12" s="8" t="n">
+        <v>33244875</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>455587.77</v>
+      </c>
+      <c r="L12" s="10" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>33244875</v>
+      </c>
+      <c r="N12" s="9" t="n">
+        <v>422010.44</v>
+      </c>
+      <c r="O12" s="10" t="n">
+        <v>0.0317</v>
+      </c>
       <c r="P12" s="8" t="n">
-        <v>11799076</v>
+        <v>33244875</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>219014.45</v>
+        <v>425434.67</v>
       </c>
       <c r="R12" s="10" t="n">
-        <v>0.0211</v>
+        <v>0.0328</v>
       </c>
       <c r="S12" s="8" t="n">
-        <v>20937034</v>
+        <v>33244875</v>
       </c>
       <c r="T12" s="9" t="n">
-        <v>420750.64</v>
+        <v>409842.82</v>
       </c>
       <c r="U12" s="10" t="n">
-        <v>0.0381</v>
+        <v>0.0326</v>
       </c>
       <c r="V12" s="8" t="n">
-        <v>21167034</v>
+        <v>33244875</v>
       </c>
       <c r="W12" s="9" t="n">
-        <v>405200.53</v>
+        <v>376199.01</v>
       </c>
       <c r="X12" s="10" t="n">
-        <v>0.0358</v>
+        <v>0.0314</v>
       </c>
       <c r="Y12" s="8" t="n">
-        <v>21167034</v>
+        <v>32644875</v>
       </c>
       <c r="Z12" s="9" t="n">
-        <v>399802.94</v>
+        <v>341204.23</v>
       </c>
       <c r="AA12" s="10" t="n">
-        <v>0.0348</v>
+        <v>0.0297</v>
       </c>
       <c r="AB12" s="8" t="n">
-        <v>21167034</v>
+        <v>30107270</v>
       </c>
       <c r="AC12" s="9" t="n">
-        <v>397601.57</v>
+        <v>321666.07</v>
       </c>
       <c r="AD12" s="10" t="n">
-        <v>0.0332</v>
+        <v>0.0284</v>
       </c>
       <c r="AE12" s="8" t="n">
-        <v>21167034</v>
+        <v>27257270</v>
       </c>
       <c r="AF12" s="9" t="n">
-        <v>434876.71</v>
+        <v>326869.18</v>
       </c>
       <c r="AG12" s="10" t="n">
-        <v>0.0346</v>
+        <v>0.0296</v>
       </c>
       <c r="AH12" s="8" t="n">
-        <v>21167034</v>
+        <v>27257270</v>
       </c>
       <c r="AI12" s="9" t="n">
-        <v>444846.39</v>
+        <v>324961.17</v>
       </c>
       <c r="AJ12" s="10" t="n">
-        <v>0.0343</v>
+        <v>0.0313</v>
       </c>
       <c r="AK12" s="8" t="n">
-        <v>21167034</v>
+        <v>27257270</v>
       </c>
       <c r="AL12" s="9" t="n">
-        <v>445693.07</v>
+        <v>322998.65</v>
       </c>
       <c r="AM12" s="10" t="n">
-        <v>0.0334</v>
+        <v>0.0328</v>
+      </c>
+      <c r="AN12" s="8" t="n">
+        <v>27257270</v>
+      </c>
+      <c r="AO12" s="9" t="n">
+        <v>300375.12</v>
+      </c>
+      <c r="AP12" s="10" t="n">
+        <v>0.0321</v>
+      </c>
+      <c r="AQ12" s="8" t="n">
+        <v>27257270</v>
+      </c>
+      <c r="AR12" s="9" t="n">
+        <v>276811.21</v>
+      </c>
+      <c r="AS12" s="10" t="n">
+        <v>0.0315</v>
+      </c>
+      <c r="AT12" s="8" t="n">
+        <v>27257270</v>
+      </c>
+      <c r="AU12" s="9" t="n">
+        <v>268783.94</v>
+      </c>
+      <c r="AV12" s="10" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Mahindra &amp; Mahindra Limited</t>
+          <t>HCL Technologies Limited</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>INE101A01026</t>
+          <t>INE860A01027</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Automobiles</t>
+          <t>IT - Software</t>
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>9331737</v>
+        <v>29868916</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>279004.94</v>
+        <v>400721.38</v>
       </c>
       <c r="F13" s="10" t="n">
         <v>0.0311</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>10068665</v>
+        <v>27771661</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>260285.06</v>
+        <v>385776.14</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>0.0296</v>
+        <v>0.0287</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>10399289</v>
+        <v>23460156</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>277224.25</v>
+        <v>397790.41</v>
       </c>
       <c r="L13" s="10" t="n">
         <v>0.0297</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>11040212</v>
+        <v>21315882</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>323345.73</v>
+        <v>346020.71</v>
       </c>
       <c r="O13" s="10" t="n">
-        <v>0.0328</v>
+        <v>0.026</v>
       </c>
       <c r="P13" s="8" t="n">
-        <v>12231374</v>
+        <v>19831378</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>364103.54</v>
+        <v>322101.24</v>
       </c>
       <c r="R13" s="10" t="n">
-        <v>0.0351</v>
+        <v>0.0248</v>
       </c>
       <c r="S13" s="8" t="n">
-        <v>12335671</v>
+        <v>18138945</v>
       </c>
       <c r="T13" s="9" t="n">
-        <v>392669.08</v>
+        <v>279611.84</v>
       </c>
       <c r="U13" s="10" t="n">
-        <v>0.0356</v>
+        <v>0.0222</v>
       </c>
       <c r="V13" s="8" t="n">
-        <v>12335671</v>
+        <v>18706995</v>
       </c>
       <c r="W13" s="9" t="n">
-        <v>395123.88</v>
+        <v>259110.59</v>
       </c>
       <c r="X13" s="10" t="n">
-        <v>0.0349</v>
+        <v>0.0216</v>
       </c>
       <c r="Y13" s="8" t="n">
-        <v>12335671</v>
+        <v>18706995</v>
       </c>
       <c r="Z13" s="9" t="n">
-        <v>394679.79</v>
+        <v>272149.36</v>
       </c>
       <c r="AA13" s="10" t="n">
-        <v>0.0343</v>
+        <v>0.0237</v>
       </c>
       <c r="AB13" s="8" t="n">
-        <v>12335671</v>
+        <v>18706995</v>
       </c>
       <c r="AC13" s="9" t="n">
-        <v>422743.45</v>
+        <v>274599.98</v>
       </c>
       <c r="AD13" s="10" t="n">
-        <v>0.0353</v>
+        <v>0.0242</v>
       </c>
       <c r="AE13" s="8" t="n">
-        <v>12435671</v>
+        <v>18558995</v>
       </c>
       <c r="AF13" s="9" t="n">
-        <v>433656.72</v>
+        <v>320810.79</v>
       </c>
       <c r="AG13" s="10" t="n">
-        <v>0.0345</v>
+        <v>0.0291</v>
       </c>
       <c r="AH13" s="8" t="n">
-        <v>12435671</v>
+        <v>18341573</v>
       </c>
       <c r="AI13" s="9" t="n">
-        <v>467245.47</v>
+        <v>300178.18</v>
       </c>
       <c r="AJ13" s="10" t="n">
+        <v>0.0289</v>
+      </c>
+      <c r="AK13" s="8" t="n">
+        <v>18706973</v>
+      </c>
+      <c r="AL13" s="9" t="n">
+        <v>293231.8</v>
+      </c>
+      <c r="AM13" s="10" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="AN13" s="8" t="n">
+        <v>18706973</v>
+      </c>
+      <c r="AO13" s="9" t="n">
+        <v>297908.55</v>
+      </c>
+      <c r="AP13" s="10" t="n">
+        <v>0.0319</v>
+      </c>
+      <c r="AQ13" s="8" t="n">
+        <v>18706973</v>
+      </c>
+      <c r="AR13" s="9" t="n">
+        <v>294644.18</v>
+      </c>
+      <c r="AS13" s="10" t="n">
+        <v>0.0335</v>
+      </c>
+      <c r="AT13" s="8" t="n">
+        <v>18706973</v>
+      </c>
+      <c r="AU13" s="9" t="n">
+        <v>322779.47</v>
+      </c>
+      <c r="AV13" s="10" t="n">
         <v>0.036</v>
-      </c>
-      <c r="AK13" s="8" t="n">
-        <v>13033470</v>
-      </c>
-      <c r="AL13" s="9" t="n">
-        <v>483437.47</v>
-      </c>
-      <c r="AM13" s="10" t="n">
-        <v>0.0363</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Axis Bank Limited</t>
+          <t>Mahindra &amp; Mahindra Limited</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>INE238A01034</t>
+          <t>INE101A01026</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Automobiles</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>27257270</v>
+        <v>14645626</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>268783.94</v>
+        <v>432734.31</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>0.03</v>
+        <v>0.0336</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>27257270</v>
+        <v>13974725</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>276811.21</v>
+        <v>474777.31</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>0.0315</v>
+        <v>0.0354</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>27257270</v>
+        <v>13974725</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>300375.12</v>
+        <v>479584.61</v>
       </c>
       <c r="L14" s="10" t="n">
-        <v>0.0321</v>
+        <v>0.0358</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>27257270</v>
+        <v>13033470</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>322998.65</v>
+        <v>483437.47</v>
       </c>
       <c r="O14" s="10" t="n">
+        <v>0.0363</v>
+      </c>
+      <c r="P14" s="8" t="n">
+        <v>12435671</v>
+      </c>
+      <c r="Q14" s="9" t="n">
+        <v>467245.47</v>
+      </c>
+      <c r="R14" s="10" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="S14" s="8" t="n">
+        <v>12435671</v>
+      </c>
+      <c r="T14" s="9" t="n">
+        <v>433656.72</v>
+      </c>
+      <c r="U14" s="10" t="n">
+        <v>0.0345</v>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v>12335671</v>
+      </c>
+      <c r="W14" s="9" t="n">
+        <v>422743.45</v>
+      </c>
+      <c r="X14" s="10" t="n">
+        <v>0.0353</v>
+      </c>
+      <c r="Y14" s="8" t="n">
+        <v>12335671</v>
+      </c>
+      <c r="Z14" s="9" t="n">
+        <v>394679.79</v>
+      </c>
+      <c r="AA14" s="10" t="n">
+        <v>0.0343</v>
+      </c>
+      <c r="AB14" s="8" t="n">
+        <v>12335671</v>
+      </c>
+      <c r="AC14" s="9" t="n">
+        <v>395123.88</v>
+      </c>
+      <c r="AD14" s="10" t="n">
+        <v>0.0349</v>
+      </c>
+      <c r="AE14" s="8" t="n">
+        <v>12335671</v>
+      </c>
+      <c r="AF14" s="9" t="n">
+        <v>392669.08</v>
+      </c>
+      <c r="AG14" s="10" t="n">
+        <v>0.0356</v>
+      </c>
+      <c r="AH14" s="8" t="n">
+        <v>12231374</v>
+      </c>
+      <c r="AI14" s="9" t="n">
+        <v>364103.54</v>
+      </c>
+      <c r="AJ14" s="10" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="AK14" s="8" t="n">
+        <v>11040212</v>
+      </c>
+      <c r="AL14" s="9" t="n">
+        <v>323345.73</v>
+      </c>
+      <c r="AM14" s="10" t="n">
         <v>0.0328</v>
       </c>
-      <c r="P14" s="8" t="n">
-        <v>27257270</v>
-      </c>
-      <c r="Q14" s="9" t="n">
-        <v>324961.17</v>
-      </c>
-      <c r="R14" s="10" t="n">
-        <v>0.0313</v>
-      </c>
-      <c r="S14" s="8" t="n">
-        <v>27257270</v>
-      </c>
-      <c r="T14" s="9" t="n">
-        <v>326869.18</v>
-      </c>
-      <c r="U14" s="10" t="n">
+      <c r="AN14" s="8" t="n">
+        <v>10399289</v>
+      </c>
+      <c r="AO14" s="9" t="n">
+        <v>277224.25</v>
+      </c>
+      <c r="AP14" s="10" t="n">
+        <v>0.0297</v>
+      </c>
+      <c r="AQ14" s="8" t="n">
+        <v>10068665</v>
+      </c>
+      <c r="AR14" s="9" t="n">
+        <v>260285.06</v>
+      </c>
+      <c r="AS14" s="10" t="n">
         <v>0.0296</v>
       </c>
-      <c r="V14" s="8" t="n">
-        <v>30107270</v>
-      </c>
-      <c r="W14" s="9" t="n">
-        <v>321666.07</v>
-      </c>
-      <c r="X14" s="10" t="n">
-        <v>0.0284</v>
-      </c>
-      <c r="Y14" s="8" t="n">
-        <v>32644875</v>
-      </c>
-      <c r="Z14" s="9" t="n">
-        <v>341204.23</v>
-      </c>
-      <c r="AA14" s="10" t="n">
-        <v>0.0297</v>
-      </c>
-      <c r="AB14" s="8" t="n">
-        <v>33244875</v>
-      </c>
-      <c r="AC14" s="9" t="n">
-        <v>376199.01</v>
-      </c>
-      <c r="AD14" s="10" t="n">
-        <v>0.0314</v>
-      </c>
-      <c r="AE14" s="8" t="n">
-        <v>33244875</v>
-      </c>
-      <c r="AF14" s="9" t="n">
-        <v>409842.82</v>
-      </c>
-      <c r="AG14" s="10" t="n">
-        <v>0.0326</v>
-      </c>
-      <c r="AH14" s="8" t="n">
-        <v>33244875</v>
-      </c>
-      <c r="AI14" s="9" t="n">
-        <v>425434.67</v>
-      </c>
-      <c r="AJ14" s="10" t="n">
-        <v>0.0328</v>
-      </c>
-      <c r="AK14" s="8" t="n">
-        <v>33244875</v>
-      </c>
-      <c r="AL14" s="9" t="n">
-        <v>422010.44</v>
-      </c>
-      <c r="AM14" s="10" t="n">
-        <v>0.0317</v>
+      <c r="AT14" s="8" t="n">
+        <v>9331737</v>
+      </c>
+      <c r="AU14" s="9" t="n">
+        <v>279004.94</v>
+      </c>
+      <c r="AV14" s="10" t="n">
+        <v>0.0311</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>HCL Technologies Limited</t>
+          <t>Infosys Limited</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>INE860A01027</t>
+          <t>INE009A01021</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -2227,123 +2614,150 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>18706973</v>
+        <v>26944033</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>322779.47</v>
+        <v>336962.08</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.036</v>
+        <v>0.0261</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>18706973</v>
+        <v>20693682</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>294644.18</v>
+        <v>269038.56</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>0.0335</v>
+        <v>0.02</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>18706973</v>
+        <v>16509541</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>297908.55</v>
+        <v>270921.57</v>
       </c>
       <c r="L15" s="10" t="n">
-        <v>0.0319</v>
+        <v>0.0202</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>18706973</v>
+        <v>16417936</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>293231.8</v>
+        <v>265215.34</v>
       </c>
       <c r="O15" s="10" t="n">
-        <v>0.0298</v>
+        <v>0.0199</v>
       </c>
       <c r="P15" s="8" t="n">
-        <v>18341573</v>
+        <v>17621740</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>300178.18</v>
+        <v>274916.77</v>
       </c>
       <c r="R15" s="10" t="n">
-        <v>0.0289</v>
+        <v>0.0212</v>
       </c>
       <c r="S15" s="8" t="n">
-        <v>18558995</v>
+        <v>9306473</v>
       </c>
       <c r="T15" s="9" t="n">
-        <v>320810.79</v>
+        <v>137949.85</v>
       </c>
       <c r="U15" s="10" t="n">
-        <v>0.0291</v>
+        <v>0.011</v>
       </c>
       <c r="V15" s="8" t="n">
-        <v>18706995</v>
+        <v>9306473</v>
       </c>
       <c r="W15" s="9" t="n">
-        <v>274599.98</v>
+        <v>134180.73</v>
       </c>
       <c r="X15" s="10" t="n">
-        <v>0.0242</v>
+        <v>0.0112</v>
       </c>
       <c r="Y15" s="8" t="n">
-        <v>18706995</v>
+        <v>9306473</v>
       </c>
       <c r="Z15" s="9" t="n">
-        <v>272149.36</v>
+        <v>136767.93</v>
       </c>
       <c r="AA15" s="10" t="n">
-        <v>0.0237</v>
+        <v>0.0119</v>
       </c>
       <c r="AB15" s="8" t="n">
-        <v>18706995</v>
+        <v>9306473</v>
       </c>
       <c r="AC15" s="9" t="n">
-        <v>259110.59</v>
+        <v>140434.68</v>
       </c>
       <c r="AD15" s="10" t="n">
-        <v>0.0216</v>
+        <v>0.0124</v>
       </c>
       <c r="AE15" s="8" t="n">
-        <v>18138945</v>
+        <v>9306473</v>
       </c>
       <c r="AF15" s="9" t="n">
-        <v>279611.84</v>
+        <v>149071.08</v>
       </c>
       <c r="AG15" s="10" t="n">
-        <v>0.0222</v>
+        <v>0.0135</v>
       </c>
       <c r="AH15" s="8" t="n">
-        <v>19831378</v>
+        <v>9306473</v>
       </c>
       <c r="AI15" s="9" t="n">
-        <v>322101.24</v>
+        <v>145432.25</v>
       </c>
       <c r="AJ15" s="10" t="n">
-        <v>0.0248</v>
+        <v>0.014</v>
       </c>
       <c r="AK15" s="8" t="n">
-        <v>21315882</v>
+        <v>9306473</v>
       </c>
       <c r="AL15" s="9" t="n">
-        <v>346020.71</v>
+        <v>139606.4</v>
       </c>
       <c r="AM15" s="10" t="n">
-        <v>0.026</v>
+        <v>0.0142</v>
+      </c>
+      <c r="AN15" s="8" t="n">
+        <v>9306473</v>
+      </c>
+      <c r="AO15" s="9" t="n">
+        <v>146172.12</v>
+      </c>
+      <c r="AP15" s="10" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="AQ15" s="8" t="n">
+        <v>9306473</v>
+      </c>
+      <c r="AR15" s="9" t="n">
+        <v>157065.34</v>
+      </c>
+      <c r="AS15" s="10" t="n">
+        <v>0.0178</v>
+      </c>
+      <c r="AT15" s="8" t="n">
+        <v>9306473</v>
+      </c>
+      <c r="AU15" s="9" t="n">
+        <v>174943.08</v>
+      </c>
+      <c r="AV15" s="10" t="n">
+        <v>0.0195</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences Limited</t>
+          <t>Dr. Reddy's Laboratories Limited</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>INE010B01027</t>
+          <t>INE089A01031</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -2352,123 +2766,150 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>8859127</v>
+        <v>13769904</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>85955.67999999999</v>
+        <v>172798.53</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0134</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>11479604</v>
+        <v>13769904</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>100630.21</v>
+        <v>177122.28</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>0.0114</v>
+        <v>0.0132</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>13003659</v>
+        <v>14083029</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>115264.43</v>
+        <v>171545.38</v>
       </c>
       <c r="L16" s="10" t="n">
-        <v>0.0123</v>
+        <v>0.0128</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>13936283</v>
+        <v>13125545</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>123789.03</v>
+        <v>166878.18</v>
       </c>
       <c r="O16" s="10" t="n">
-        <v>0.0126</v>
+        <v>0.0125</v>
       </c>
       <c r="P16" s="8" t="n">
-        <v>14258435</v>
+        <v>13125545</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>132603.45</v>
+        <v>165224.36</v>
       </c>
       <c r="R16" s="10" t="n">
-        <v>0.0128</v>
+        <v>0.0127</v>
       </c>
       <c r="S16" s="8" t="n">
-        <v>14258435</v>
+        <v>12775545</v>
       </c>
       <c r="T16" s="9" t="n">
-        <v>141151.38</v>
+        <v>152999.93</v>
       </c>
       <c r="U16" s="10" t="n">
-        <v>0.0128</v>
+        <v>0.0122</v>
       </c>
       <c r="V16" s="8" t="n">
-        <v>14470385</v>
+        <v>12107943</v>
       </c>
       <c r="W16" s="9" t="n">
-        <v>140333.79</v>
+        <v>148164.9</v>
       </c>
       <c r="X16" s="10" t="n">
         <v>0.0124</v>
       </c>
       <c r="Y16" s="8" t="n">
-        <v>14786344</v>
+        <v>11632943</v>
       </c>
       <c r="Z16" s="9" t="n">
-        <v>145061.43</v>
+        <v>146586.71</v>
       </c>
       <c r="AA16" s="10" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="AB16" s="8" t="n">
+        <v>11217622</v>
+      </c>
+      <c r="AC16" s="9" t="n">
+        <v>142497.45</v>
+      </c>
+      <c r="AD16" s="10" t="n">
         <v>0.0126</v>
       </c>
-      <c r="AB16" s="8" t="n">
-        <v>15148311</v>
-      </c>
-      <c r="AC16" s="9" t="n">
-        <v>148741.27</v>
-      </c>
-      <c r="AD16" s="10" t="n">
+      <c r="AE16" s="8" t="n">
+        <v>10341500</v>
+      </c>
+      <c r="AF16" s="9" t="n">
+        <v>132712.47</v>
+      </c>
+      <c r="AG16" s="10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AH16" s="8" t="n">
+        <v>10341500</v>
+      </c>
+      <c r="AI16" s="9" t="n">
+        <v>129392.85</v>
+      </c>
+      <c r="AJ16" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AK16" s="8" t="n">
+        <v>10403670</v>
+      </c>
+      <c r="AL16" s="9" t="n">
+        <v>123169.05</v>
+      </c>
+      <c r="AM16" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AN16" s="8" t="n">
+        <v>10133496</v>
+      </c>
+      <c r="AO16" s="9" t="n">
+        <v>115947.46</v>
+      </c>
+      <c r="AP16" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="AE16" s="8" t="n">
-        <v>15759789</v>
-      </c>
-      <c r="AF16" s="9" t="n">
-        <v>153571.26</v>
-      </c>
-      <c r="AG16" s="10" t="n">
-        <v>0.0122</v>
-      </c>
-      <c r="AH16" s="8" t="n">
-        <v>17405149</v>
-      </c>
-      <c r="AI16" s="9" t="n">
-        <v>164043.53</v>
-      </c>
-      <c r="AJ16" s="10" t="n">
+      <c r="AQ16" s="8" t="n">
+        <v>9911843</v>
+      </c>
+      <c r="AR16" s="9" t="n">
+        <v>110665.73</v>
+      </c>
+      <c r="AS16" s="10" t="n">
         <v>0.0126</v>
       </c>
-      <c r="AK16" s="8" t="n">
-        <v>17903094</v>
-      </c>
-      <c r="AL16" s="9" t="n">
-        <v>163696.94</v>
-      </c>
-      <c r="AM16" s="10" t="n">
-        <v>0.0123</v>
+      <c r="AT16" s="8" t="n">
+        <v>7388241</v>
+      </c>
+      <c r="AU16" s="9" t="n">
+        <v>89940.75</v>
+      </c>
+      <c r="AV16" s="10" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Laboratories Limited</t>
+          <t>Cipla Limited</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>INE089A01031</t>
+          <t>INE059A01026</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -2477,123 +2918,150 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>7388241</v>
+        <v>13271296</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>89940.75</v>
+        <v>162467.21</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0.01</v>
+        <v>0.0126</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>9911843</v>
+        <v>12881359</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>110665.73</v>
+        <v>173666.48</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>0.0126</v>
+        <v>0.0129</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>10133496</v>
+        <v>12623339</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>115947.46</v>
+        <v>167133.01</v>
       </c>
       <c r="L17" s="10" t="n">
-        <v>0.0124</v>
+        <v>0.0125</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>10403670</v>
+        <v>10989584</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>123169.05</v>
+        <v>166085.58</v>
       </c>
       <c r="O17" s="10" t="n">
         <v>0.0125</v>
       </c>
       <c r="P17" s="8" t="n">
-        <v>10341500</v>
+        <v>10765866</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>129392.85</v>
+        <v>164857.71</v>
       </c>
       <c r="R17" s="10" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="S17" s="8" t="n">
+        <v>10173460</v>
+      </c>
+      <c r="T17" s="9" t="n">
+        <v>152734.15</v>
+      </c>
+      <c r="U17" s="10" t="n">
+        <v>0.0121</v>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v>9988840</v>
+      </c>
+      <c r="W17" s="9" t="n">
+        <v>150162.23</v>
+      </c>
+      <c r="X17" s="10" t="n">
         <v>0.0125</v>
       </c>
-      <c r="S17" s="8" t="n">
-        <v>10341500</v>
-      </c>
-      <c r="T17" s="9" t="n">
-        <v>132712.47</v>
-      </c>
-      <c r="U17" s="10" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v>11217622</v>
-      </c>
-      <c r="W17" s="9" t="n">
-        <v>142497.45</v>
-      </c>
-      <c r="X17" s="10" t="n">
+      <c r="Y17" s="8" t="n">
+        <v>8991707</v>
+      </c>
+      <c r="Z17" s="9" t="n">
+        <v>142914.19</v>
+      </c>
+      <c r="AA17" s="10" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="AB17" s="8" t="n">
+        <v>9450707</v>
+      </c>
+      <c r="AC17" s="9" t="n">
+        <v>146920.69</v>
+      </c>
+      <c r="AD17" s="10" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="AE17" s="8" t="n">
+        <v>9147124</v>
+      </c>
+      <c r="AF17" s="9" t="n">
+        <v>137746.54</v>
+      </c>
+      <c r="AG17" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AH17" s="8" t="n">
+        <v>8881919</v>
+      </c>
+      <c r="AI17" s="9" t="n">
+        <v>130182.29</v>
+      </c>
+      <c r="AJ17" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AK17" s="8" t="n">
+        <v>7994194</v>
+      </c>
+      <c r="AL17" s="9" t="n">
+        <v>123918</v>
+      </c>
+      <c r="AM17" s="10" t="n">
         <v>0.0126</v>
       </c>
-      <c r="Y17" s="8" t="n">
-        <v>11632943</v>
-      </c>
-      <c r="Z17" s="9" t="n">
-        <v>146586.71</v>
-      </c>
-      <c r="AA17" s="10" t="n">
-        <v>0.0127</v>
-      </c>
-      <c r="AB17" s="8" t="n">
-        <v>12107943</v>
-      </c>
-      <c r="AC17" s="9" t="n">
-        <v>148164.9</v>
-      </c>
-      <c r="AD17" s="10" t="n">
+      <c r="AN17" s="8" t="n">
+        <v>7994194</v>
+      </c>
+      <c r="AO17" s="9" t="n">
+        <v>115292.27</v>
+      </c>
+      <c r="AP17" s="10" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="AQ17" s="8" t="n">
+        <v>7755553</v>
+      </c>
+      <c r="AR17" s="9" t="n">
+        <v>109159.41</v>
+      </c>
+      <c r="AS17" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="AE17" s="8" t="n">
-        <v>12775545</v>
-      </c>
-      <c r="AF17" s="9" t="n">
-        <v>152999.93</v>
-      </c>
-      <c r="AG17" s="10" t="n">
-        <v>0.0122</v>
-      </c>
-      <c r="AH17" s="8" t="n">
-        <v>13125545</v>
-      </c>
-      <c r="AI17" s="9" t="n">
-        <v>165224.36</v>
-      </c>
-      <c r="AJ17" s="10" t="n">
-        <v>0.0127</v>
-      </c>
-      <c r="AK17" s="8" t="n">
-        <v>13125545</v>
-      </c>
-      <c r="AL17" s="9" t="n">
-        <v>166878.18</v>
-      </c>
-      <c r="AM17" s="10" t="n">
-        <v>0.0125</v>
+      <c r="AT17" s="8" t="n">
+        <v>6223549</v>
+      </c>
+      <c r="AU17" s="9" t="n">
+        <v>92071.17999999999</v>
+      </c>
+      <c r="AV17" s="10" t="n">
+        <v>0.0103</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Cipla Limited</t>
+          <t>Zydus Lifesciences Limited</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>INE059A01026</t>
+          <t>INE010B01027</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -2602,237 +3070,291 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>6223549</v>
+        <v>18853686</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>92071.17999999999</v>
+        <v>164253.31</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>0.0103</v>
+        <v>0.0127</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>7755553</v>
+        <v>18853686</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>109159.41</v>
+        <v>173774.42</v>
       </c>
       <c r="I18" s="10" t="n">
+        <v>0.0129</v>
+      </c>
+      <c r="J18" s="8" t="n">
+        <v>18750502</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <v>165998.19</v>
+      </c>
+      <c r="L18" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="J18" s="8" t="n">
-        <v>7994194</v>
-      </c>
-      <c r="K18" s="9" t="n">
-        <v>115292.27</v>
-      </c>
-      <c r="L18" s="10" t="n">
+      <c r="M18" s="8" t="n">
+        <v>17903094</v>
+      </c>
+      <c r="N18" s="9" t="n">
+        <v>163696.94</v>
+      </c>
+      <c r="O18" s="10" t="n">
         <v>0.0123</v>
       </c>
-      <c r="M18" s="8" t="n">
-        <v>7994194</v>
-      </c>
-      <c r="N18" s="9" t="n">
-        <v>123918</v>
-      </c>
-      <c r="O18" s="10" t="n">
+      <c r="P18" s="8" t="n">
+        <v>17405149</v>
+      </c>
+      <c r="Q18" s="9" t="n">
+        <v>164043.53</v>
+      </c>
+      <c r="R18" s="10" t="n">
         <v>0.0126</v>
       </c>
-      <c r="P18" s="8" t="n">
-        <v>8881919</v>
-      </c>
-      <c r="Q18" s="9" t="n">
-        <v>130182.29</v>
-      </c>
-      <c r="R18" s="10" t="n">
-        <v>0.0125</v>
-      </c>
       <c r="S18" s="8" t="n">
-        <v>9147124</v>
+        <v>15759789</v>
       </c>
       <c r="T18" s="9" t="n">
-        <v>137746.54</v>
+        <v>153571.26</v>
       </c>
       <c r="U18" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.0122</v>
       </c>
       <c r="V18" s="8" t="n">
-        <v>9450707</v>
+        <v>15148311</v>
       </c>
       <c r="W18" s="9" t="n">
-        <v>146920.69</v>
+        <v>148741.27</v>
       </c>
       <c r="X18" s="10" t="n">
-        <v>0.013</v>
+        <v>0.0124</v>
       </c>
       <c r="Y18" s="8" t="n">
-        <v>8991707</v>
+        <v>14786344</v>
       </c>
       <c r="Z18" s="9" t="n">
-        <v>142914.19</v>
+        <v>145061.43</v>
       </c>
       <c r="AA18" s="10" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="AB18" s="8" t="n">
+        <v>14470385</v>
+      </c>
+      <c r="AC18" s="9" t="n">
+        <v>140333.79</v>
+      </c>
+      <c r="AD18" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="AB18" s="8" t="n">
-        <v>9988840</v>
-      </c>
-      <c r="AC18" s="9" t="n">
-        <v>150162.23</v>
-      </c>
-      <c r="AD18" s="10" t="n">
-        <v>0.0125</v>
-      </c>
       <c r="AE18" s="8" t="n">
-        <v>10173460</v>
+        <v>14258435</v>
       </c>
       <c r="AF18" s="9" t="n">
-        <v>152734.15</v>
+        <v>141151.38</v>
       </c>
       <c r="AG18" s="10" t="n">
-        <v>0.0121</v>
+        <v>0.0128</v>
       </c>
       <c r="AH18" s="8" t="n">
-        <v>10765866</v>
+        <v>14258435</v>
       </c>
       <c r="AI18" s="9" t="n">
-        <v>164857.71</v>
+        <v>132603.45</v>
       </c>
       <c r="AJ18" s="10" t="n">
-        <v>0.0127</v>
+        <v>0.0128</v>
       </c>
       <c r="AK18" s="8" t="n">
-        <v>10989584</v>
+        <v>13936283</v>
       </c>
       <c r="AL18" s="9" t="n">
-        <v>166085.58</v>
+        <v>123789.03</v>
       </c>
       <c r="AM18" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.0126</v>
+      </c>
+      <c r="AN18" s="8" t="n">
+        <v>13003659</v>
+      </c>
+      <c r="AO18" s="9" t="n">
+        <v>115264.43</v>
+      </c>
+      <c r="AP18" s="10" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="AQ18" s="8" t="n">
+        <v>11479604</v>
+      </c>
+      <c r="AR18" s="9" t="n">
+        <v>100630.21</v>
+      </c>
+      <c r="AS18" s="10" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="AT18" s="8" t="n">
+        <v>8859127</v>
+      </c>
+      <c r="AU18" s="9" t="n">
+        <v>85955.67999999999</v>
+      </c>
+      <c r="AV18" s="10" t="n">
+        <v>0.009599999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Infosys Limited</t>
+          <t>Balkrishna Industries Limited</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>INE009A01021</t>
+          <t>INE787D01026</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>IT - Software</t>
+          <t>Auto Components</t>
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>9306473</v>
+        <v>2274074</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>174943.08</v>
+        <v>47368.96</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>0.0195</v>
+        <v>0.0037</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>9306473</v>
+        <v>2906065</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>157065.34</v>
+        <v>69277.67999999999</v>
       </c>
       <c r="I19" s="10" t="n">
-        <v>0.0178</v>
+        <v>0.0052</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>9306473</v>
+        <v>4189074</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>146172.12</v>
+        <v>96591.67</v>
       </c>
       <c r="L19" s="10" t="n">
-        <v>0.0156</v>
+        <v>0.0072</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>9306473</v>
+        <v>4189074</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>139606.4</v>
+        <v>97173.95</v>
       </c>
       <c r="O19" s="10" t="n">
-        <v>0.0142</v>
+        <v>0.0073</v>
       </c>
       <c r="P19" s="8" t="n">
-        <v>9306473</v>
+        <v>4189074</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>145432.25</v>
+        <v>96721.53</v>
       </c>
       <c r="R19" s="10" t="n">
-        <v>0.014</v>
+        <v>0.0075</v>
       </c>
       <c r="S19" s="8" t="n">
-        <v>9306473</v>
+        <v>4189074</v>
       </c>
       <c r="T19" s="9" t="n">
-        <v>149071.08</v>
+        <v>95502.50999999999</v>
       </c>
       <c r="U19" s="10" t="n">
-        <v>0.0135</v>
+        <v>0.0076</v>
       </c>
       <c r="V19" s="8" t="n">
-        <v>9306473</v>
+        <v>4189074</v>
       </c>
       <c r="W19" s="9" t="n">
-        <v>140434.68</v>
+        <v>96130.87</v>
       </c>
       <c r="X19" s="10" t="n">
-        <v>0.0124</v>
+        <v>0.008</v>
       </c>
       <c r="Y19" s="8" t="n">
-        <v>9306473</v>
+        <v>4189074</v>
       </c>
       <c r="Z19" s="9" t="n">
-        <v>136767.93</v>
+        <v>95904.66</v>
       </c>
       <c r="AA19" s="10" t="n">
-        <v>0.0119</v>
+        <v>0.0083</v>
       </c>
       <c r="AB19" s="8" t="n">
-        <v>9306473</v>
+        <v>4189074</v>
       </c>
       <c r="AC19" s="9" t="n">
-        <v>134180.73</v>
+        <v>112108</v>
       </c>
       <c r="AD19" s="10" t="n">
-        <v>0.0112</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="AE19" s="8" t="n">
-        <v>9306473</v>
+        <v>4189074</v>
       </c>
       <c r="AF19" s="9" t="n">
-        <v>137949.85</v>
+        <v>102435.43</v>
       </c>
       <c r="AG19" s="10" t="n">
-        <v>0.011</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="AH19" s="8" t="n">
-        <v>17621740</v>
+        <v>4189074</v>
       </c>
       <c r="AI19" s="9" t="n">
-        <v>274916.77</v>
+        <v>103562.29</v>
       </c>
       <c r="AJ19" s="10" t="n">
-        <v>0.0212</v>
+        <v>0.01</v>
       </c>
       <c r="AK19" s="8" t="n">
-        <v>16417936</v>
+        <v>4189074</v>
       </c>
       <c r="AL19" s="9" t="n">
-        <v>265215.34</v>
+        <v>112061.92</v>
       </c>
       <c r="AM19" s="10" t="n">
-        <v>0.0199</v>
+        <v>0.0114</v>
+      </c>
+      <c r="AN19" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="AO19" s="9" t="n">
+        <v>107022.46</v>
+      </c>
+      <c r="AP19" s="10" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="AQ19" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="AR19" s="9" t="n">
+        <v>109571.51</v>
+      </c>
+      <c r="AS19" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AT19" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="AU19" s="9" t="n">
+        <v>116089.71</v>
+      </c>
+      <c r="AV19" s="10" t="n">
+        <v>0.0129</v>
       </c>
     </row>
     <row r="20">
@@ -2852,67 +3374,67 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>44206584</v>
+        <v>80755676</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>77184.7</v>
+        <v>92667.14</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>0.0086</v>
+        <v>0.0072</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>44206584</v>
+        <v>80755676</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>68931.33</v>
+        <v>101461.43</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>0.0078</v>
+        <v>0.0076</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>44206584</v>
+        <v>80755676</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>77701.91</v>
+        <v>102390.12</v>
       </c>
       <c r="L20" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.0076</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>44206584</v>
+        <v>80755676</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>84147.23</v>
+        <v>108390.27</v>
       </c>
       <c r="O20" s="10" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0081</v>
       </c>
       <c r="P20" s="8" t="n">
-        <v>44206584</v>
+        <v>80755676</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>88656.3</v>
+        <v>112484.58</v>
       </c>
       <c r="R20" s="10" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="S20" s="8" t="n">
-        <v>44206584</v>
+        <v>80755676</v>
       </c>
       <c r="T20" s="9" t="n">
-        <v>85367.33</v>
+        <v>112298.84</v>
       </c>
       <c r="U20" s="10" t="n">
-        <v>0.0077</v>
+        <v>0.0089</v>
       </c>
       <c r="V20" s="8" t="n">
-        <v>44206584</v>
+        <v>80755676</v>
       </c>
       <c r="W20" s="9" t="n">
-        <v>59811.51</v>
+        <v>112403.83</v>
       </c>
       <c r="X20" s="10" t="n">
-        <v>0.0053</v>
+        <v>0.0094</v>
       </c>
       <c r="Y20" s="8" t="n">
         <v>73511702</v>
@@ -2924,56 +3446,83 @@
         <v>0.0089</v>
       </c>
       <c r="AB20" s="8" t="n">
-        <v>80755676</v>
+        <v>44206584</v>
       </c>
       <c r="AC20" s="9" t="n">
-        <v>112403.83</v>
+        <v>59811.51</v>
       </c>
       <c r="AD20" s="10" t="n">
-        <v>0.0094</v>
+        <v>0.0053</v>
       </c>
       <c r="AE20" s="8" t="n">
-        <v>80755676</v>
+        <v>44206584</v>
       </c>
       <c r="AF20" s="9" t="n">
-        <v>112298.84</v>
+        <v>85367.33</v>
       </c>
       <c r="AG20" s="10" t="n">
-        <v>0.0089</v>
+        <v>0.0077</v>
       </c>
       <c r="AH20" s="8" t="n">
-        <v>80755676</v>
+        <v>44206584</v>
       </c>
       <c r="AI20" s="9" t="n">
-        <v>112484.58</v>
+        <v>88656.3</v>
       </c>
       <c r="AJ20" s="10" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="AK20" s="8" t="n">
-        <v>80755676</v>
+        <v>44206584</v>
       </c>
       <c r="AL20" s="9" t="n">
-        <v>108390.27</v>
+        <v>84147.23</v>
       </c>
       <c r="AM20" s="10" t="n">
-        <v>0.0081</v>
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="AN20" s="8" t="n">
+        <v>44206584</v>
+      </c>
+      <c r="AO20" s="9" t="n">
+        <v>77701.91</v>
+      </c>
+      <c r="AP20" s="10" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="AQ20" s="8" t="n">
+        <v>44206584</v>
+      </c>
+      <c r="AR20" s="9" t="n">
+        <v>68931.33</v>
+      </c>
+      <c r="AS20" s="10" t="n">
+        <v>0.0078</v>
+      </c>
+      <c r="AT20" s="8" t="n">
+        <v>44206584</v>
+      </c>
+      <c r="AU20" s="9" t="n">
+        <v>77184.7</v>
+      </c>
+      <c r="AV20" s="10" t="n">
+        <v>0.0086</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited</t>
+          <t>Motilal Oswal Financial Services Limited</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>INE768C01028</t>
+          <t>INE338I01027</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D21" s="8" t="n"/>
@@ -3000,416 +3549,458 @@
       <c r="Y21" s="8" t="n"/>
       <c r="Z21" s="9" t="n"/>
       <c r="AA21" s="10" t="n"/>
-      <c r="AB21" s="8" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="AC21" s="9" t="n">
-        <v>100584</v>
-      </c>
-      <c r="AD21" s="10" t="n">
-        <v>0.008399999999999999</v>
-      </c>
+      <c r="AB21" s="8" t="n"/>
+      <c r="AC21" s="9" t="n"/>
+      <c r="AD21" s="10" t="n"/>
       <c r="AE21" s="8" t="n">
-        <v>22000000</v>
+        <v>591805</v>
       </c>
       <c r="AF21" s="9" t="n">
-        <v>104852</v>
+        <v>5149</v>
       </c>
       <c r="AG21" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.0005</v>
       </c>
       <c r="AH21" s="8" t="n">
-        <v>22000000</v>
+        <v>5392631</v>
       </c>
       <c r="AI21" s="9" t="n">
-        <v>94699</v>
+        <v>43674.92</v>
       </c>
       <c r="AJ21" s="10" t="n">
-        <v>0.0073</v>
+        <v>0.0042</v>
       </c>
       <c r="AK21" s="8" t="n">
-        <v>22000000</v>
+        <v>8585949</v>
       </c>
       <c r="AL21" s="9" t="n">
-        <v>100012</v>
+        <v>56044.78</v>
       </c>
       <c r="AM21" s="10" t="n">
-        <v>0.0075</v>
+        <v>0.0057</v>
+      </c>
+      <c r="AN21" s="8" t="n">
+        <v>10913294</v>
+      </c>
+      <c r="AO21" s="9" t="n">
+        <v>67154.95</v>
+      </c>
+      <c r="AP21" s="10" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="AQ21" s="8" t="n">
+        <v>12053879</v>
+      </c>
+      <c r="AR21" s="9" t="n">
+        <v>70937.08</v>
+      </c>
+      <c r="AS21" s="10" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="AT21" s="8" t="n">
+        <v>12053879</v>
+      </c>
+      <c r="AU21" s="9" t="n">
+        <v>76801.28999999999</v>
+      </c>
+      <c r="AV21" s="10" t="n">
+        <v>0.0086</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Balkrishna Industries Limited</t>
+          <t>Multi Commodity Exchange of India Limited</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>INE787D01026</t>
+          <t>INE745G01035</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Auto Components</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>116089.71</v>
-      </c>
-      <c r="F22" s="10" t="n">
-        <v>0.0129</v>
-      </c>
-      <c r="G22" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="H22" s="9" t="n">
-        <v>109571.51</v>
-      </c>
-      <c r="I22" s="10" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="J22" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="K22" s="9" t="n">
-        <v>107022.46</v>
-      </c>
-      <c r="L22" s="10" t="n">
-        <v>0.0115</v>
-      </c>
+          <t>Capital Markets</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="10" t="n"/>
+      <c r="G22" s="8" t="n"/>
+      <c r="H22" s="9" t="n"/>
+      <c r="I22" s="10" t="n"/>
+      <c r="J22" s="8" t="n"/>
+      <c r="K22" s="9" t="n"/>
+      <c r="L22" s="10" t="n"/>
       <c r="M22" s="8" t="n">
-        <v>4189074</v>
+        <v>797719</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>112061.92</v>
+        <v>88833.99000000001</v>
       </c>
       <c r="O22" s="10" t="n">
-        <v>0.0114</v>
+        <v>0.0067</v>
       </c>
       <c r="P22" s="8" t="n">
-        <v>4189074</v>
+        <v>797719</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>103562.29</v>
+        <v>80358.22</v>
       </c>
       <c r="R22" s="10" t="n">
-        <v>0.01</v>
+        <v>0.0062</v>
       </c>
       <c r="S22" s="8" t="n">
-        <v>4189074</v>
+        <v>797719</v>
       </c>
       <c r="T22" s="9" t="n">
-        <v>102435.43</v>
+        <v>73737.16</v>
       </c>
       <c r="U22" s="10" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0059</v>
       </c>
       <c r="V22" s="8" t="n">
-        <v>4189074</v>
+        <v>797719</v>
       </c>
       <c r="W22" s="9" t="n">
-        <v>112108</v>
+        <v>62190.17</v>
       </c>
       <c r="X22" s="10" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0052</v>
       </c>
       <c r="Y22" s="8" t="n">
-        <v>4189074</v>
+        <v>797719</v>
       </c>
       <c r="Z22" s="9" t="n">
-        <v>95904.66</v>
+        <v>58951.43</v>
       </c>
       <c r="AA22" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.0051</v>
       </c>
       <c r="AB22" s="8" t="n">
-        <v>4189074</v>
+        <v>797719</v>
       </c>
       <c r="AC22" s="9" t="n">
-        <v>96130.87</v>
+        <v>61368.52</v>
       </c>
       <c r="AD22" s="10" t="n">
-        <v>0.008</v>
+        <v>0.0054</v>
       </c>
       <c r="AE22" s="8" t="n">
-        <v>4189074</v>
+        <v>797719</v>
       </c>
       <c r="AF22" s="9" t="n">
-        <v>95502.50999999999</v>
+        <v>71347.99000000001</v>
       </c>
       <c r="AG22" s="10" t="n">
-        <v>0.0076</v>
+        <v>0.0065</v>
       </c>
       <c r="AH22" s="8" t="n">
-        <v>4189074</v>
+        <v>797719</v>
       </c>
       <c r="AI22" s="9" t="n">
-        <v>96721.53</v>
+        <v>52665.41</v>
       </c>
       <c r="AJ22" s="10" t="n">
-        <v>0.0075</v>
+        <v>0.0051</v>
       </c>
       <c r="AK22" s="8" t="n">
-        <v>4189074</v>
+        <v>797719</v>
       </c>
       <c r="AL22" s="9" t="n">
-        <v>97173.95</v>
+        <v>48884.22</v>
       </c>
       <c r="AM22" s="10" t="n">
-        <v>0.0073</v>
+        <v>0.005</v>
+      </c>
+      <c r="AN22" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AO22" s="9" t="n">
+        <v>42372.84</v>
+      </c>
+      <c r="AP22" s="10" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="AQ22" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AR22" s="9" t="n">
+        <v>39819.34</v>
+      </c>
+      <c r="AS22" s="10" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="AT22" s="8" t="n">
+        <v>882136</v>
+      </c>
+      <c r="AU22" s="9" t="n">
+        <v>50572.42</v>
+      </c>
+      <c r="AV22" s="10" t="n">
+        <v>0.0056</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Multi Commodity Exchange of India Limited</t>
+          <t>Narayana Hrudayalaya Limited</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>INE745G01035</t>
+          <t>INE410P01011</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Healthcare Services</t>
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>882136</v>
+        <v>1995914</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>50572.42</v>
+        <v>32040.41</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>0.0056</v>
+        <v>0.0025</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>797719</v>
+        <v>1995914</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>39819.34</v>
+        <v>36543.19</v>
       </c>
       <c r="I23" s="10" t="n">
-        <v>0.0045</v>
+        <v>0.0027</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>797719</v>
+        <v>1995914</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>42372.84</v>
+        <v>35285.76</v>
       </c>
       <c r="L23" s="10" t="n">
-        <v>0.0045</v>
+        <v>0.0026</v>
       </c>
       <c r="M23" s="8" t="n">
-        <v>797719</v>
+        <v>1995914</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>48884.22</v>
+        <v>37762.69</v>
       </c>
       <c r="O23" s="10" t="n">
-        <v>0.005</v>
+        <v>0.0028</v>
       </c>
       <c r="P23" s="8" t="n">
-        <v>797719</v>
+        <v>1995914</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>52665.41</v>
+        <v>38830.51</v>
       </c>
       <c r="R23" s="10" t="n">
-        <v>0.0051</v>
+        <v>0.003</v>
       </c>
       <c r="S23" s="8" t="n">
-        <v>797719</v>
+        <v>1995914</v>
       </c>
       <c r="T23" s="9" t="n">
-        <v>71347.99000000001</v>
+        <v>35076.19</v>
       </c>
       <c r="U23" s="10" t="n">
-        <v>0.0065</v>
+        <v>0.0028</v>
       </c>
       <c r="V23" s="8" t="n">
-        <v>797719</v>
+        <v>1995914</v>
       </c>
       <c r="W23" s="9" t="n">
-        <v>61368.52</v>
+        <v>34681</v>
       </c>
       <c r="X23" s="10" t="n">
-        <v>0.0054</v>
+        <v>0.0029</v>
       </c>
       <c r="Y23" s="8" t="n">
-        <v>797719</v>
+        <v>1995914</v>
       </c>
       <c r="Z23" s="9" t="n">
-        <v>58951.43</v>
+        <v>35004.34</v>
       </c>
       <c r="AA23" s="10" t="n">
-        <v>0.0051</v>
+        <v>0.003</v>
       </c>
       <c r="AB23" s="8" t="n">
-        <v>797719</v>
+        <v>1995914</v>
       </c>
       <c r="AC23" s="9" t="n">
-        <v>62190.17</v>
+        <v>38225.74</v>
       </c>
       <c r="AD23" s="10" t="n">
-        <v>0.0052</v>
+        <v>0.0034</v>
       </c>
       <c r="AE23" s="8" t="n">
-        <v>797719</v>
+        <v>1995914</v>
       </c>
       <c r="AF23" s="9" t="n">
-        <v>73737.16</v>
+        <v>43319.32</v>
       </c>
       <c r="AG23" s="10" t="n">
-        <v>0.0059</v>
+        <v>0.0039</v>
       </c>
       <c r="AH23" s="8" t="n">
-        <v>797719</v>
+        <v>1995914</v>
       </c>
       <c r="AI23" s="9" t="n">
-        <v>80358.22</v>
+        <v>34806.74</v>
       </c>
       <c r="AJ23" s="10" t="n">
-        <v>0.0062</v>
+        <v>0.0034</v>
       </c>
       <c r="AK23" s="8" t="n">
-        <v>797719</v>
+        <v>1995914</v>
       </c>
       <c r="AL23" s="9" t="n">
-        <v>88833.99000000001</v>
+        <v>35138.07</v>
       </c>
       <c r="AM23" s="10" t="n">
-        <v>0.0067</v>
+        <v>0.0036</v>
+      </c>
+      <c r="AN23" s="8" t="n">
+        <v>1995914</v>
+      </c>
+      <c r="AO23" s="9" t="n">
+        <v>33771.86</v>
+      </c>
+      <c r="AP23" s="10" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="AQ23" s="8" t="n">
+        <v>1995914</v>
+      </c>
+      <c r="AR23" s="9" t="n">
+        <v>28830.98</v>
+      </c>
+      <c r="AS23" s="10" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="AT23" s="8" t="n">
+        <v>1995914</v>
+      </c>
+      <c r="AU23" s="9" t="n">
+        <v>27686.32</v>
+      </c>
+      <c r="AV23" s="10" t="n">
+        <v>0.0031</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>EID Parry India Limited</t>
+          <t>IPCA Laboratories Limited</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>INE126A01031</t>
+          <t>INE571A01038</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="n">
-        <v>2259531</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>18525.89</v>
-      </c>
-      <c r="F24" s="10" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="G24" s="8" t="n">
-        <v>2609056</v>
-      </c>
-      <c r="H24" s="9" t="n">
-        <v>17326.74</v>
-      </c>
-      <c r="I24" s="10" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="J24" s="8" t="n">
-        <v>2843265</v>
-      </c>
-      <c r="K24" s="9" t="n">
-        <v>22336.69</v>
-      </c>
-      <c r="L24" s="10" t="n">
-        <v>0.0024</v>
-      </c>
-      <c r="M24" s="8" t="n">
-        <v>2988209</v>
-      </c>
-      <c r="N24" s="9" t="n">
-        <v>24424.13</v>
-      </c>
-      <c r="O24" s="10" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="P24" s="8" t="n">
-        <v>3243008</v>
-      </c>
-      <c r="Q24" s="9" t="n">
-        <v>30813.44</v>
-      </c>
-      <c r="R24" s="10" t="n">
+          <t>Pharmaceuticals &amp; Biotechnology</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="10" t="n"/>
+      <c r="G24" s="8" t="n"/>
+      <c r="H24" s="9" t="n"/>
+      <c r="I24" s="10" t="n"/>
+      <c r="J24" s="8" t="n"/>
+      <c r="K24" s="9" t="n"/>
+      <c r="L24" s="10" t="n"/>
+      <c r="M24" s="8" t="n"/>
+      <c r="N24" s="9" t="n"/>
+      <c r="O24" s="10" t="n"/>
+      <c r="P24" s="8" t="n"/>
+      <c r="Q24" s="9" t="n"/>
+      <c r="R24" s="10" t="n"/>
+      <c r="S24" s="8" t="n"/>
+      <c r="T24" s="9" t="n"/>
+      <c r="U24" s="10" t="n"/>
+      <c r="V24" s="8" t="n"/>
+      <c r="W24" s="9" t="n"/>
+      <c r="X24" s="10" t="n"/>
+      <c r="Y24" s="8" t="n">
+        <v>218075</v>
+      </c>
+      <c r="Z24" s="9" t="n">
+        <v>3019.03</v>
+      </c>
+      <c r="AA24" s="10" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="AB24" s="8" t="n">
+        <v>566216</v>
+      </c>
+      <c r="AC24" s="9" t="n">
+        <v>8345.459999999999</v>
+      </c>
+      <c r="AD24" s="10" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="AE24" s="8" t="n">
+        <v>1311557</v>
+      </c>
+      <c r="AF24" s="9" t="n">
+        <v>18228.02</v>
+      </c>
+      <c r="AG24" s="10" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="AH24" s="8" t="n">
+        <v>1641095</v>
+      </c>
+      <c r="AI24" s="9" t="n">
+        <v>23382.32</v>
+      </c>
+      <c r="AJ24" s="10" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="AK24" s="8" t="n">
+        <v>1857217</v>
+      </c>
+      <c r="AL24" s="9" t="n">
+        <v>26023.32</v>
+      </c>
+      <c r="AM24" s="10" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="AN24" s="8" t="n">
+        <v>1926988</v>
+      </c>
+      <c r="AO24" s="9" t="n">
+        <v>28941.43</v>
+      </c>
+      <c r="AP24" s="10" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="AQ24" s="8" t="n">
+        <v>1926988</v>
+      </c>
+      <c r="AR24" s="9" t="n">
+        <v>26117.43</v>
+      </c>
+      <c r="AS24" s="10" t="n">
         <v>0.003</v>
       </c>
-      <c r="S24" s="8" t="n">
-        <v>3516819</v>
-      </c>
-      <c r="T24" s="9" t="n">
-        <v>39036.69</v>
-      </c>
-      <c r="U24" s="10" t="n">
-        <v>0.0035</v>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v>3997165</v>
-      </c>
-      <c r="W24" s="9" t="n">
-        <v>49305.03</v>
-      </c>
-      <c r="X24" s="10" t="n">
-        <v>0.0044</v>
-      </c>
-      <c r="Y24" s="8" t="n">
-        <v>4433570</v>
-      </c>
-      <c r="Z24" s="9" t="n">
-        <v>49913.13</v>
-      </c>
-      <c r="AA24" s="10" t="n">
-        <v>0.0043</v>
-      </c>
-      <c r="AB24" s="8" t="n">
-        <v>4996218</v>
-      </c>
-      <c r="AC24" s="9" t="n">
-        <v>51236.22</v>
-      </c>
-      <c r="AD24" s="10" t="n">
-        <v>0.0043</v>
-      </c>
-      <c r="AE24" s="8" t="n">
-        <v>5528341</v>
-      </c>
-      <c r="AF24" s="9" t="n">
-        <v>59285.93</v>
-      </c>
-      <c r="AG24" s="10" t="n">
-        <v>0.0047</v>
-      </c>
-      <c r="AH24" s="8" t="n">
-        <v>5842830</v>
-      </c>
-      <c r="AI24" s="9" t="n">
-        <v>60233.73</v>
-      </c>
-      <c r="AJ24" s="10" t="n">
-        <v>0.0046</v>
-      </c>
-      <c r="AK24" s="8" t="n">
-        <v>6180145</v>
-      </c>
-      <c r="AL24" s="9" t="n">
-        <v>63945.96</v>
-      </c>
-      <c r="AM24" s="10" t="n">
-        <v>0.0048</v>
+      <c r="AT24" s="8" t="n">
+        <v>2246361</v>
+      </c>
+      <c r="AU24" s="9" t="n">
+        <v>32421.73</v>
+      </c>
+      <c r="AV24" s="10" t="n">
+        <v>0.0036</v>
       </c>
     </row>
     <row r="25">
@@ -3432,64 +4023,64 @@
         <v>2264603</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>29659.51</v>
+        <v>25349.97</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>0.0033</v>
+        <v>0.002</v>
       </c>
       <c r="G25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>25089.54</v>
+        <v>28810.28</v>
       </c>
       <c r="I25" s="10" t="n">
-        <v>0.0029</v>
+        <v>0.0021</v>
       </c>
       <c r="J25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>27629.29</v>
+        <v>29897.29</v>
       </c>
       <c r="L25" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0022</v>
       </c>
       <c r="M25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>29892.76</v>
+        <v>32691.81</v>
       </c>
       <c r="O25" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0025</v>
       </c>
       <c r="P25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>34641.63</v>
+        <v>36623.16</v>
       </c>
       <c r="R25" s="10" t="n">
-        <v>0.0033</v>
+        <v>0.0028</v>
       </c>
       <c r="S25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="T25" s="9" t="n">
-        <v>40626.98</v>
+        <v>35943.78</v>
       </c>
       <c r="U25" s="10" t="n">
-        <v>0.0037</v>
+        <v>0.0029</v>
       </c>
       <c r="V25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="W25" s="9" t="n">
-        <v>33534.24</v>
+        <v>33031.5</v>
       </c>
       <c r="X25" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0028</v>
       </c>
       <c r="Y25" s="8" t="n">
         <v>2264603</v>
@@ -3504,513 +4095,600 @@
         <v>2264603</v>
       </c>
       <c r="AC25" s="9" t="n">
-        <v>33031.5</v>
+        <v>33534.24</v>
       </c>
       <c r="AD25" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.003</v>
       </c>
       <c r="AE25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="AF25" s="9" t="n">
-        <v>35943.78</v>
+        <v>40626.98</v>
       </c>
       <c r="AG25" s="10" t="n">
-        <v>0.0029</v>
+        <v>0.0037</v>
       </c>
       <c r="AH25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="AI25" s="9" t="n">
-        <v>36623.16</v>
+        <v>34641.63</v>
       </c>
       <c r="AJ25" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.0033</v>
       </c>
       <c r="AK25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="AL25" s="9" t="n">
-        <v>32691.81</v>
+        <v>29892.76</v>
       </c>
       <c r="AM25" s="10" t="n">
-        <v>0.0025</v>
+        <v>0.003</v>
+      </c>
+      <c r="AN25" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="AO25" s="9" t="n">
+        <v>27629.29</v>
+      </c>
+      <c r="AP25" s="10" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="AQ25" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="AR25" s="9" t="n">
+        <v>25089.54</v>
+      </c>
+      <c r="AS25" s="10" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="AT25" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="AU25" s="9" t="n">
+        <v>29659.51</v>
+      </c>
+      <c r="AV25" s="10" t="n">
+        <v>0.0033</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Narayana Hrudayalaya Limited</t>
+          <t>EID Parry India Limited</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>INE410P01011</t>
+          <t>INE126A01031</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Healthcare Services</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>1995914</v>
+        <v>7394472</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>27686.32</v>
+        <v>57344.13</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>0.0031</v>
+        <v>0.0044</v>
       </c>
       <c r="G26" s="8" t="n">
-        <v>1995914</v>
+        <v>7394472</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>28830.98</v>
+        <v>63976.97</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>0.0033</v>
+        <v>0.0048</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>1995914</v>
+        <v>7362903</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>33771.86</v>
+        <v>67966.96000000001</v>
       </c>
       <c r="L26" s="10" t="n">
-        <v>0.0036</v>
+        <v>0.0051</v>
       </c>
       <c r="M26" s="8" t="n">
-        <v>1995914</v>
+        <v>6180145</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>35138.07</v>
+        <v>63945.96</v>
       </c>
       <c r="O26" s="10" t="n">
-        <v>0.0036</v>
+        <v>0.0048</v>
       </c>
       <c r="P26" s="8" t="n">
-        <v>1995914</v>
+        <v>5842830</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>34806.74</v>
+        <v>60233.73</v>
       </c>
       <c r="R26" s="10" t="n">
-        <v>0.0034</v>
+        <v>0.0046</v>
       </c>
       <c r="S26" s="8" t="n">
-        <v>1995914</v>
+        <v>5528341</v>
       </c>
       <c r="T26" s="9" t="n">
-        <v>43319.32</v>
+        <v>59285.93</v>
       </c>
       <c r="U26" s="10" t="n">
-        <v>0.0039</v>
+        <v>0.0047</v>
       </c>
       <c r="V26" s="8" t="n">
-        <v>1995914</v>
+        <v>4996218</v>
       </c>
       <c r="W26" s="9" t="n">
-        <v>38225.74</v>
+        <v>51236.22</v>
       </c>
       <c r="X26" s="10" t="n">
-        <v>0.0034</v>
+        <v>0.0043</v>
       </c>
       <c r="Y26" s="8" t="n">
-        <v>1995914</v>
+        <v>4433570</v>
       </c>
       <c r="Z26" s="9" t="n">
-        <v>35004.34</v>
+        <v>49913.13</v>
       </c>
       <c r="AA26" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0043</v>
       </c>
       <c r="AB26" s="8" t="n">
-        <v>1995914</v>
+        <v>3997165</v>
       </c>
       <c r="AC26" s="9" t="n">
-        <v>34681</v>
+        <v>49305.03</v>
       </c>
       <c r="AD26" s="10" t="n">
-        <v>0.0029</v>
+        <v>0.0044</v>
       </c>
       <c r="AE26" s="8" t="n">
-        <v>1995914</v>
+        <v>3516819</v>
       </c>
       <c r="AF26" s="9" t="n">
-        <v>35076.19</v>
+        <v>39036.69</v>
       </c>
       <c r="AG26" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.0035</v>
       </c>
       <c r="AH26" s="8" t="n">
-        <v>1995914</v>
+        <v>3243008</v>
       </c>
       <c r="AI26" s="9" t="n">
-        <v>38830.51</v>
+        <v>30813.44</v>
       </c>
       <c r="AJ26" s="10" t="n">
         <v>0.003</v>
       </c>
       <c r="AK26" s="8" t="n">
-        <v>1995914</v>
+        <v>2988209</v>
       </c>
       <c r="AL26" s="9" t="n">
-        <v>37762.69</v>
+        <v>24424.13</v>
       </c>
       <c r="AM26" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.0025</v>
+      </c>
+      <c r="AN26" s="8" t="n">
+        <v>2843265</v>
+      </c>
+      <c r="AO26" s="9" t="n">
+        <v>22336.69</v>
+      </c>
+      <c r="AP26" s="10" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="AQ26" s="8" t="n">
+        <v>2609056</v>
+      </c>
+      <c r="AR26" s="9" t="n">
+        <v>17326.74</v>
+      </c>
+      <c r="AS26" s="10" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="AT26" s="8" t="n">
+        <v>2259531</v>
+      </c>
+      <c r="AU26" s="9" t="n">
+        <v>18525.89</v>
+      </c>
+      <c r="AV26" s="10" t="n">
+        <v>0.0021</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>ICRA Limited</t>
+          <t>ITC Hotels Limited</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>INE725G01011</t>
+          <t>INE379A01028</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="n">
-        <v>297835</v>
-      </c>
-      <c r="E27" s="9" t="n">
-        <v>18529.51</v>
-      </c>
-      <c r="F27" s="10" t="n">
+          <t>Leisure Services</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="10" t="n"/>
+      <c r="G27" s="8" t="n"/>
+      <c r="H27" s="9" t="n"/>
+      <c r="I27" s="10" t="n"/>
+      <c r="J27" s="8" t="n"/>
+      <c r="K27" s="9" t="n"/>
+      <c r="L27" s="10" t="n"/>
+      <c r="M27" s="8" t="n"/>
+      <c r="N27" s="9" t="n"/>
+      <c r="O27" s="10" t="n"/>
+      <c r="P27" s="8" t="n"/>
+      <c r="Q27" s="9" t="n"/>
+      <c r="R27" s="10" t="n"/>
+      <c r="S27" s="8" t="n"/>
+      <c r="T27" s="9" t="n"/>
+      <c r="U27" s="10" t="n"/>
+      <c r="V27" s="8" t="n"/>
+      <c r="W27" s="9" t="n"/>
+      <c r="X27" s="10" t="n"/>
+      <c r="Y27" s="8" t="n"/>
+      <c r="Z27" s="9" t="n"/>
+      <c r="AA27" s="10" t="n"/>
+      <c r="AB27" s="8" t="n"/>
+      <c r="AC27" s="9" t="n"/>
+      <c r="AD27" s="10" t="n"/>
+      <c r="AE27" s="8" t="n"/>
+      <c r="AF27" s="9" t="n"/>
+      <c r="AG27" s="10" t="n"/>
+      <c r="AH27" s="8" t="n"/>
+      <c r="AI27" s="9" t="n"/>
+      <c r="AJ27" s="10" t="n"/>
+      <c r="AK27" s="8" t="n"/>
+      <c r="AL27" s="9" t="n"/>
+      <c r="AM27" s="10" t="n"/>
+      <c r="AN27" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="AO27" s="9" t="n">
+        <v>19552.33</v>
+      </c>
+      <c r="AP27" s="10" t="n">
         <v>0.0021</v>
       </c>
-      <c r="G27" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="H27" s="9" t="n">
-        <v>15273.64</v>
-      </c>
-      <c r="I27" s="10" t="n">
-        <v>0.0017</v>
-      </c>
-      <c r="J27" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="K27" s="9" t="n">
-        <v>15821.13</v>
-      </c>
-      <c r="L27" s="10" t="n">
-        <v>0.0017</v>
-      </c>
-      <c r="M27" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="N27" s="9" t="n">
-        <v>15976.18</v>
-      </c>
-      <c r="O27" s="10" t="n">
-        <v>0.0016</v>
-      </c>
-      <c r="P27" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="Q27" s="9" t="n">
-        <v>19370.29</v>
-      </c>
-      <c r="R27" s="10" t="n">
-        <v>0.0019</v>
-      </c>
-      <c r="S27" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="T27" s="9" t="n">
-        <v>19453.63</v>
-      </c>
-      <c r="U27" s="10" t="n">
+      <c r="AQ27" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="AR27" s="9" t="n">
+        <v>16216.23</v>
+      </c>
+      <c r="AS27" s="10" t="n">
         <v>0.0018</v>
       </c>
-      <c r="V27" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="W27" s="9" t="n">
-        <v>19048.41</v>
-      </c>
-      <c r="X27" s="10" t="n">
-        <v>0.0017</v>
-      </c>
-      <c r="Y27" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="Z27" s="9" t="n">
-        <v>17962.06</v>
-      </c>
-      <c r="AA27" s="10" t="n">
-        <v>0.0016</v>
-      </c>
-      <c r="AB27" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="AC27" s="9" t="n">
-        <v>18243.71</v>
-      </c>
-      <c r="AD27" s="10" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="AE27" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="AF27" s="9" t="n">
-        <v>18463.56</v>
-      </c>
-      <c r="AG27" s="10" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="AH27" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="AI27" s="9" t="n">
-        <v>17812.62</v>
-      </c>
-      <c r="AJ27" s="10" t="n">
-        <v>0.0014</v>
-      </c>
-      <c r="AK27" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="AL27" s="9" t="n">
-        <v>17460.56</v>
-      </c>
-      <c r="AM27" s="10" t="n">
-        <v>0.0013</v>
+      <c r="AT27" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="AU27" s="9" t="n">
+        <v>16131.09</v>
+      </c>
+      <c r="AV27" s="10" t="n">
+        <v>0.0018</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Maharashtra Scooters Limited</t>
+          <t>ICRA Limited</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>INE288A01013</t>
+          <t>INE725G01011</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>7463.48</v>
+        <v>14378.27</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>0.0008</v>
+        <v>0.0011</v>
       </c>
       <c r="G28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>7401.52</v>
+        <v>15895.71</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>0.0008</v>
+        <v>0.0012</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>8997.450000000001</v>
+        <v>18124.44</v>
       </c>
       <c r="L28" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0014</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>9198.25</v>
+        <v>17460.56</v>
       </c>
       <c r="O28" s="10" t="n">
-        <v>0.0009</v>
+        <v>0.0013</v>
       </c>
       <c r="P28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>10722.07</v>
+        <v>17812.62</v>
       </c>
       <c r="R28" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0014</v>
       </c>
       <c r="S28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="T28" s="9" t="n">
-        <v>11621.45</v>
+        <v>18463.56</v>
       </c>
       <c r="U28" s="10" t="n">
-        <v>0.0011</v>
+        <v>0.0015</v>
       </c>
       <c r="V28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="W28" s="9" t="n">
-        <v>12868.73</v>
+        <v>18243.71</v>
       </c>
       <c r="X28" s="10" t="n">
-        <v>0.0011</v>
+        <v>0.0015</v>
       </c>
       <c r="Y28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="Z28" s="9" t="n">
-        <v>12726.04</v>
+        <v>17962.06</v>
       </c>
       <c r="AA28" s="10" t="n">
-        <v>0.0011</v>
+        <v>0.0016</v>
       </c>
       <c r="AB28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="AC28" s="9" t="n">
-        <v>13825.82</v>
+        <v>19048.41</v>
       </c>
       <c r="AD28" s="10" t="n">
-        <v>0.0012</v>
+        <v>0.0017</v>
       </c>
       <c r="AE28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="AF28" s="9" t="n">
-        <v>12110.42</v>
+        <v>19453.63</v>
       </c>
       <c r="AG28" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0018</v>
       </c>
       <c r="AH28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="AI28" s="9" t="n">
-        <v>11787.38</v>
+        <v>19370.29</v>
       </c>
       <c r="AJ28" s="10" t="n">
-        <v>0.0009</v>
+        <v>0.0019</v>
       </c>
       <c r="AK28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="AL28" s="9" t="n">
-        <v>11401.01</v>
+        <v>15976.18</v>
       </c>
       <c r="AM28" s="10" t="n">
-        <v>0.0009</v>
+        <v>0.0016</v>
+      </c>
+      <c r="AN28" s="8" t="n">
+        <v>287393</v>
+      </c>
+      <c r="AO28" s="9" t="n">
+        <v>15821.13</v>
+      </c>
+      <c r="AP28" s="10" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="AQ28" s="8" t="n">
+        <v>287393</v>
+      </c>
+      <c r="AR28" s="9" t="n">
+        <v>15273.64</v>
+      </c>
+      <c r="AS28" s="10" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="AT28" s="8" t="n">
+        <v>297835</v>
+      </c>
+      <c r="AU28" s="9" t="n">
+        <v>18529.51</v>
+      </c>
+      <c r="AV28" s="10" t="n">
+        <v>0.0021</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Nesco Limited</t>
+          <t>Maharashtra Scooters Limited</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>INE317F01035</t>
+          <t>INE288A01013</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Commercial Services &amp; Supplies</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="n"/>
-      <c r="E29" s="9" t="n"/>
-      <c r="F29" s="10" t="n"/>
-      <c r="G29" s="8" t="n"/>
-      <c r="H29" s="9" t="n"/>
-      <c r="I29" s="10" t="n"/>
-      <c r="J29" s="8" t="n"/>
-      <c r="K29" s="9" t="n"/>
-      <c r="L29" s="10" t="n"/>
-      <c r="M29" s="8" t="n"/>
-      <c r="N29" s="9" t="n"/>
-      <c r="O29" s="10" t="n"/>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>80565</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>8949.969999999999</v>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="G29" s="8" t="n">
+        <v>80565</v>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>10682.11</v>
+      </c>
+      <c r="I29" s="10" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="J29" s="8" t="n">
+        <v>80552</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <v>10825.38</v>
+      </c>
+      <c r="L29" s="10" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="M29" s="8" t="n">
+        <v>80159</v>
+      </c>
+      <c r="N29" s="9" t="n">
+        <v>11401.01</v>
+      </c>
+      <c r="O29" s="10" t="n">
+        <v>0.0009</v>
+      </c>
       <c r="P29" s="8" t="n">
-        <v>89469</v>
+        <v>80159</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>828.48</v>
+        <v>11787.38</v>
       </c>
       <c r="R29" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0009</v>
       </c>
       <c r="S29" s="8" t="n">
-        <v>151687</v>
+        <v>80159</v>
       </c>
       <c r="T29" s="9" t="n">
-        <v>1766.62</v>
+        <v>12110.42</v>
       </c>
       <c r="U29" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.001</v>
       </c>
       <c r="V29" s="8" t="n">
-        <v>151687</v>
+        <v>80159</v>
       </c>
       <c r="W29" s="9" t="n">
-        <v>2091.16</v>
+        <v>13825.82</v>
       </c>
       <c r="X29" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0012</v>
       </c>
       <c r="Y29" s="8" t="n">
-        <v>151687</v>
+        <v>80159</v>
       </c>
       <c r="Z29" s="9" t="n">
-        <v>2130.6</v>
+        <v>12726.04</v>
       </c>
       <c r="AA29" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0011</v>
       </c>
       <c r="AB29" s="8" t="n">
-        <v>151687</v>
+        <v>80159</v>
       </c>
       <c r="AC29" s="9" t="n">
-        <v>1987.1</v>
+        <v>12868.73</v>
       </c>
       <c r="AD29" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0011</v>
       </c>
       <c r="AE29" s="8" t="n">
-        <v>151687</v>
+        <v>80159</v>
       </c>
       <c r="AF29" s="9" t="n">
-        <v>2076.6</v>
+        <v>11621.45</v>
       </c>
       <c r="AG29" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0011</v>
       </c>
       <c r="AH29" s="8" t="n">
-        <v>151687</v>
+        <v>80159</v>
       </c>
       <c r="AI29" s="9" t="n">
-        <v>1947.66</v>
+        <v>10722.07</v>
       </c>
       <c r="AJ29" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.001</v>
       </c>
       <c r="AK29" s="8" t="n">
-        <v>151687</v>
+        <v>80159</v>
       </c>
       <c r="AL29" s="9" t="n">
-        <v>1858.32</v>
+        <v>9198.25</v>
       </c>
       <c r="AM29" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0009</v>
+      </c>
+      <c r="AN29" s="8" t="n">
+        <v>80159</v>
+      </c>
+      <c r="AO29" s="9" t="n">
+        <v>8997.450000000001</v>
+      </c>
+      <c r="AP29" s="10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AQ29" s="8" t="n">
+        <v>80159</v>
+      </c>
+      <c r="AR29" s="9" t="n">
+        <v>7401.52</v>
+      </c>
+      <c r="AS29" s="10" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="AT29" s="8" t="n">
+        <v>80159</v>
+      </c>
+      <c r="AU29" s="9" t="n">
+        <v>7463.48</v>
+      </c>
+      <c r="AV29" s="10" t="n">
+        <v>0.0008</v>
       </c>
     </row>
     <row r="30">
@@ -4033,16 +4711,16 @@
         <v>47293</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>1612.64</v>
+        <v>1564.88</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="G30" s="8" t="n">
         <v>47293</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>1236.83</v>
+        <v>1700.33</v>
       </c>
       <c r="I30" s="10" t="n">
         <v>0.0001</v>
@@ -4051,34 +4729,34 @@
         <v>47293</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>1844.17</v>
+        <v>1637.61</v>
       </c>
       <c r="L30" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="M30" s="8" t="n">
         <v>47293</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>1925.39</v>
+        <v>1691.91</v>
       </c>
       <c r="O30" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="P30" s="8" t="n">
         <v>47293</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>1857.76</v>
+        <v>1764.08</v>
       </c>
       <c r="R30" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="S30" s="8" t="n">
         <v>47293</v>
       </c>
       <c r="T30" s="9" t="n">
-        <v>1867.41</v>
+        <v>1892.15</v>
       </c>
       <c r="U30" s="10" t="n">
         <v>0.0002</v>
@@ -4087,7 +4765,7 @@
         <v>47293</v>
       </c>
       <c r="W30" s="9" t="n">
-        <v>1983.66</v>
+        <v>1955.38</v>
       </c>
       <c r="X30" s="10" t="n">
         <v>0.0002</v>
@@ -4105,7 +4783,7 @@
         <v>47293</v>
       </c>
       <c r="AC30" s="9" t="n">
-        <v>1955.38</v>
+        <v>1983.66</v>
       </c>
       <c r="AD30" s="10" t="n">
         <v>0.0002</v>
@@ -4114,7 +4792,7 @@
         <v>47293</v>
       </c>
       <c r="AF30" s="9" t="n">
-        <v>1892.15</v>
+        <v>1867.41</v>
       </c>
       <c r="AG30" s="10" t="n">
         <v>0.0002</v>
@@ -4123,281 +4801,383 @@
         <v>47293</v>
       </c>
       <c r="AI30" s="9" t="n">
-        <v>1764.08</v>
+        <v>1857.76</v>
       </c>
       <c r="AJ30" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="AK30" s="8" t="n">
         <v>47293</v>
       </c>
       <c r="AL30" s="9" t="n">
-        <v>1691.91</v>
+        <v>1925.39</v>
       </c>
       <c r="AM30" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AN30" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="AO30" s="9" t="n">
+        <v>1844.17</v>
+      </c>
+      <c r="AP30" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AQ30" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="AR30" s="9" t="n">
+        <v>1236.83</v>
+      </c>
+      <c r="AS30" s="10" t="n">
         <v>0.0001</v>
+      </c>
+      <c r="AT30" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="AU30" s="9" t="n">
+        <v>1612.64</v>
+      </c>
+      <c r="AV30" s="10" t="n">
+        <v>0.0002</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited</t>
+          <t>Nesco Limited</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>INE768C01010</t>
+          <t>INE317F01035</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="n"/>
-      <c r="E31" s="9" t="n"/>
-      <c r="F31" s="10" t="n"/>
-      <c r="G31" s="8" t="n"/>
-      <c r="H31" s="9" t="n"/>
-      <c r="I31" s="10" t="n"/>
-      <c r="J31" s="8" t="n"/>
-      <c r="K31" s="9" t="n"/>
-      <c r="L31" s="10" t="n"/>
-      <c r="M31" s="8" t="n"/>
-      <c r="N31" s="9" t="n"/>
-      <c r="O31" s="10" t="n"/>
-      <c r="P31" s="8" t="n"/>
-      <c r="Q31" s="9" t="n"/>
-      <c r="R31" s="10" t="n"/>
+          <t>Commercial Services &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>1538.11</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="H31" s="9" t="n">
+        <v>1704.36</v>
+      </c>
+      <c r="I31" s="10" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="J31" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="K31" s="9" t="n">
+        <v>1728.63</v>
+      </c>
+      <c r="L31" s="10" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M31" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="N31" s="9" t="n">
+        <v>1858.32</v>
+      </c>
+      <c r="O31" s="10" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P31" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="Q31" s="9" t="n">
+        <v>1947.66</v>
+      </c>
+      <c r="R31" s="10" t="n">
+        <v>0.0002</v>
+      </c>
       <c r="S31" s="8" t="n">
-        <v>4400000</v>
+        <v>151687</v>
       </c>
       <c r="T31" s="9" t="n">
-        <v>89020.8</v>
+        <v>2076.6</v>
       </c>
       <c r="U31" s="10" t="n">
-        <v>0.0081</v>
+        <v>0.0002</v>
       </c>
       <c r="V31" s="8" t="n">
-        <v>4400000</v>
+        <v>151687</v>
       </c>
       <c r="W31" s="9" t="n">
-        <v>89280.39999999999</v>
+        <v>1987.1</v>
       </c>
       <c r="X31" s="10" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0002</v>
       </c>
       <c r="Y31" s="8" t="n">
-        <v>4400000</v>
+        <v>151687</v>
       </c>
       <c r="Z31" s="9" t="n">
-        <v>88822.8</v>
+        <v>2130.6</v>
       </c>
       <c r="AA31" s="10" t="n">
-        <v>0.0077</v>
-      </c>
-      <c r="AB31" s="8" t="n"/>
-      <c r="AC31" s="9" t="n"/>
-      <c r="AD31" s="10" t="n"/>
-      <c r="AE31" s="8" t="n"/>
-      <c r="AF31" s="9" t="n"/>
-      <c r="AG31" s="10" t="n"/>
-      <c r="AH31" s="8" t="n"/>
-      <c r="AI31" s="9" t="n"/>
-      <c r="AJ31" s="10" t="n"/>
+        <v>0.0002</v>
+      </c>
+      <c r="AB31" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AC31" s="9" t="n">
+        <v>2091.16</v>
+      </c>
+      <c r="AD31" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AE31" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AF31" s="9" t="n">
+        <v>1766.62</v>
+      </c>
+      <c r="AG31" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AH31" s="8" t="n">
+        <v>89469</v>
+      </c>
+      <c r="AI31" s="9" t="n">
+        <v>828.48</v>
+      </c>
+      <c r="AJ31" s="10" t="n">
+        <v>0.0001</v>
+      </c>
       <c r="AK31" s="8" t="n"/>
       <c r="AL31" s="9" t="n"/>
       <c r="AM31" s="10" t="n"/>
+      <c r="AN31" s="8" t="n"/>
+      <c r="AO31" s="9" t="n"/>
+      <c r="AP31" s="10" t="n"/>
+      <c r="AQ31" s="8" t="n"/>
+      <c r="AR31" s="9" t="n"/>
+      <c r="AS31" s="10" t="n"/>
+      <c r="AT31" s="8" t="n"/>
+      <c r="AU31" s="9" t="n"/>
+      <c r="AV31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>IPCA Laboratories Limited</t>
+          <t>Bharti Airtel Limited</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>INE571A01038</t>
+          <t>INE397D01024</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Pharmaceuticals &amp; Biotechnology</t>
+          <t>Telecom - Services</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>2246361</v>
+        <v>21167034</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>32421.73</v>
+        <v>377281.21</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>0.0036</v>
+        <v>0.0293</v>
       </c>
       <c r="G32" s="8" t="n">
-        <v>1926988</v>
+        <v>21167034</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>26117.43</v>
+        <v>397792.07</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0296</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>1926988</v>
+        <v>21167034</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>28941.43</v>
+        <v>416715.398358</v>
       </c>
       <c r="L32" s="10" t="n">
-        <v>0.0031</v>
+        <v>0.0311051731198606</v>
       </c>
       <c r="M32" s="8" t="n">
-        <v>1857217</v>
+        <v>21167034</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>26023.32</v>
+        <v>445693.07</v>
       </c>
       <c r="O32" s="10" t="n">
-        <v>0.0026</v>
+        <v>0.0334</v>
       </c>
       <c r="P32" s="8" t="n">
-        <v>1641095</v>
+        <v>21167034</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>23382.32</v>
+        <v>444846.39</v>
       </c>
       <c r="R32" s="10" t="n">
-        <v>0.0023</v>
+        <v>0.0343</v>
       </c>
       <c r="S32" s="8" t="n">
-        <v>1311557</v>
+        <v>21167034</v>
       </c>
       <c r="T32" s="9" t="n">
-        <v>18228.02</v>
+        <v>434876.71</v>
       </c>
       <c r="U32" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.0346</v>
       </c>
       <c r="V32" s="8" t="n">
-        <v>566216</v>
+        <v>21167034</v>
       </c>
       <c r="W32" s="9" t="n">
-        <v>8345.459999999999</v>
+        <v>397601.57</v>
       </c>
       <c r="X32" s="10" t="n">
-        <v>0.0007</v>
+        <v>0.0332</v>
       </c>
       <c r="Y32" s="8" t="n">
-        <v>218075</v>
+        <v>21167034</v>
       </c>
       <c r="Z32" s="9" t="n">
-        <v>3019.03</v>
+        <v>399802.94</v>
       </c>
       <c r="AA32" s="10" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="AB32" s="8" t="n"/>
-      <c r="AC32" s="9" t="n"/>
-      <c r="AD32" s="10" t="n"/>
-      <c r="AE32" s="8" t="n"/>
-      <c r="AF32" s="9" t="n"/>
-      <c r="AG32" s="10" t="n"/>
-      <c r="AH32" s="8" t="n"/>
-      <c r="AI32" s="9" t="n"/>
-      <c r="AJ32" s="10" t="n"/>
+        <v>0.0348</v>
+      </c>
+      <c r="AB32" s="8" t="n">
+        <v>21167034</v>
+      </c>
+      <c r="AC32" s="9" t="n">
+        <v>405200.53</v>
+      </c>
+      <c r="AD32" s="10" t="n">
+        <v>0.0358</v>
+      </c>
+      <c r="AE32" s="8" t="n">
+        <v>20937034</v>
+      </c>
+      <c r="AF32" s="9" t="n">
+        <v>420750.64</v>
+      </c>
+      <c r="AG32" s="10" t="n">
+        <v>0.0381</v>
+      </c>
+      <c r="AH32" s="8" t="n">
+        <v>11799076</v>
+      </c>
+      <c r="AI32" s="9" t="n">
+        <v>219014.45</v>
+      </c>
+      <c r="AJ32" s="10" t="n">
+        <v>0.0211</v>
+      </c>
       <c r="AK32" s="8" t="n"/>
       <c r="AL32" s="9" t="n"/>
       <c r="AM32" s="10" t="n"/>
+      <c r="AN32" s="8" t="n"/>
+      <c r="AO32" s="9" t="n"/>
+      <c r="AP32" s="10" t="n"/>
+      <c r="AQ32" s="8" t="n"/>
+      <c r="AR32" s="9" t="n"/>
+      <c r="AS32" s="10" t="n"/>
+      <c r="AT32" s="8" t="n"/>
+      <c r="AU32" s="9" t="n"/>
+      <c r="AV32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Motilal Oswal Financial Services Limited</t>
+          <t>Zydus Wellness Limited</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>INE338I01027</t>
+          <t>INE768C01010</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="n">
-        <v>12053879</v>
-      </c>
-      <c r="E33" s="9" t="n">
-        <v>76801.28999999999</v>
-      </c>
-      <c r="F33" s="10" t="n">
-        <v>0.0086</v>
-      </c>
-      <c r="G33" s="8" t="n">
-        <v>12053879</v>
-      </c>
-      <c r="H33" s="9" t="n">
-        <v>70937.08</v>
-      </c>
-      <c r="I33" s="10" t="n">
-        <v>0.0081</v>
-      </c>
-      <c r="J33" s="8" t="n">
-        <v>10913294</v>
-      </c>
-      <c r="K33" s="9" t="n">
-        <v>67154.95</v>
-      </c>
-      <c r="L33" s="10" t="n">
-        <v>0.0072</v>
-      </c>
-      <c r="M33" s="8" t="n">
-        <v>8585949</v>
-      </c>
-      <c r="N33" s="9" t="n">
-        <v>56044.78</v>
-      </c>
-      <c r="O33" s="10" t="n">
-        <v>0.0057</v>
-      </c>
-      <c r="P33" s="8" t="n">
-        <v>5392631</v>
-      </c>
-      <c r="Q33" s="9" t="n">
-        <v>43674.92</v>
-      </c>
-      <c r="R33" s="10" t="n">
-        <v>0.0042</v>
-      </c>
-      <c r="S33" s="8" t="n">
-        <v>591805</v>
-      </c>
-      <c r="T33" s="9" t="n">
-        <v>5149</v>
-      </c>
-      <c r="U33" s="10" t="n">
-        <v>0.0005</v>
-      </c>
+          <t>Food Products</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="10" t="n"/>
+      <c r="G33" s="8" t="n"/>
+      <c r="H33" s="9" t="n"/>
+      <c r="I33" s="10" t="n"/>
+      <c r="J33" s="8" t="n"/>
+      <c r="K33" s="9" t="n"/>
+      <c r="L33" s="10" t="n"/>
+      <c r="M33" s="8" t="n"/>
+      <c r="N33" s="9" t="n"/>
+      <c r="O33" s="10" t="n"/>
+      <c r="P33" s="8" t="n"/>
+      <c r="Q33" s="9" t="n"/>
+      <c r="R33" s="10" t="n"/>
+      <c r="S33" s="8" t="n"/>
+      <c r="T33" s="9" t="n"/>
+      <c r="U33" s="10" t="n"/>
       <c r="V33" s="8" t="n"/>
       <c r="W33" s="9" t="n"/>
       <c r="X33" s="10" t="n"/>
-      <c r="Y33" s="8" t="n"/>
-      <c r="Z33" s="9" t="n"/>
-      <c r="AA33" s="10" t="n"/>
-      <c r="AB33" s="8" t="n"/>
-      <c r="AC33" s="9" t="n"/>
-      <c r="AD33" s="10" t="n"/>
-      <c r="AE33" s="8" t="n"/>
-      <c r="AF33" s="9" t="n"/>
-      <c r="AG33" s="10" t="n"/>
+      <c r="Y33" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="Z33" s="9" t="n">
+        <v>88822.8</v>
+      </c>
+      <c r="AA33" s="10" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="AB33" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AC33" s="9" t="n">
+        <v>89280.39999999999</v>
+      </c>
+      <c r="AD33" s="10" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="AE33" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AF33" s="9" t="n">
+        <v>89020.8</v>
+      </c>
+      <c r="AG33" s="10" t="n">
+        <v>0.0081</v>
+      </c>
       <c r="AH33" s="8" t="n"/>
       <c r="AI33" s="9" t="n"/>
       <c r="AJ33" s="10" t="n"/>
       <c r="AK33" s="8" t="n"/>
       <c r="AL33" s="9" t="n"/>
       <c r="AM33" s="10" t="n"/>
+      <c r="AN33" s="8" t="n"/>
+      <c r="AO33" s="9" t="n"/>
+      <c r="AP33" s="10" t="n"/>
+      <c r="AQ33" s="8" t="n"/>
+      <c r="AR33" s="9" t="n"/>
+      <c r="AS33" s="10" t="n"/>
+      <c r="AT33" s="8" t="n"/>
+      <c r="AU33" s="9" t="n"/>
+      <c r="AV33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -4415,21 +5195,51 @@
           <t>IT - Software</t>
         </is>
       </c>
-      <c r="D34" s="8" t="n"/>
-      <c r="E34" s="9" t="n"/>
-      <c r="F34" s="10" t="n"/>
-      <c r="G34" s="8" t="n"/>
-      <c r="H34" s="9" t="n"/>
-      <c r="I34" s="10" t="n"/>
-      <c r="J34" s="8" t="n"/>
-      <c r="K34" s="9" t="n"/>
-      <c r="L34" s="10" t="n"/>
-      <c r="M34" s="8" t="n"/>
-      <c r="N34" s="9" t="n"/>
-      <c r="O34" s="10" t="n"/>
-      <c r="P34" s="8" t="n"/>
-      <c r="Q34" s="9" t="n"/>
-      <c r="R34" s="10" t="n"/>
+      <c r="D34" s="8" t="n">
+        <v>12412184</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>292791.01</v>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="G34" s="8" t="n">
+        <v>10378056</v>
+      </c>
+      <c r="H34" s="9" t="n">
+        <v>273710.85</v>
+      </c>
+      <c r="I34" s="10" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="J34" s="8" t="n">
+        <v>8465650</v>
+      </c>
+      <c r="K34" s="9" t="n">
+        <v>264458.44</v>
+      </c>
+      <c r="L34" s="10" t="n">
+        <v>0.0197</v>
+      </c>
+      <c r="M34" s="8" t="n">
+        <v>4654589</v>
+      </c>
+      <c r="N34" s="9" t="n">
+        <v>149235.43</v>
+      </c>
+      <c r="O34" s="10" t="n">
+        <v>0.0112</v>
+      </c>
+      <c r="P34" s="8" t="n">
+        <v>2811139</v>
+      </c>
+      <c r="Q34" s="9" t="n">
+        <v>88199.49000000001</v>
+      </c>
+      <c r="R34" s="10" t="n">
+        <v>0.0068</v>
+      </c>
       <c r="S34" s="8" t="n"/>
       <c r="T34" s="9" t="n"/>
       <c r="U34" s="10" t="n"/>
@@ -4445,62 +5255,101 @@
       <c r="AE34" s="8" t="n"/>
       <c r="AF34" s="9" t="n"/>
       <c r="AG34" s="10" t="n"/>
-      <c r="AH34" s="8" t="n">
-        <v>2811139</v>
-      </c>
-      <c r="AI34" s="9" t="n">
-        <v>88199.49000000001</v>
-      </c>
-      <c r="AJ34" s="10" t="n">
-        <v>0.0068</v>
-      </c>
-      <c r="AK34" s="8" t="n">
-        <v>4654589</v>
-      </c>
-      <c r="AL34" s="9" t="n">
-        <v>149235.43</v>
-      </c>
-      <c r="AM34" s="10" t="n">
-        <v>0.0112</v>
-      </c>
+      <c r="AH34" s="8" t="n"/>
+      <c r="AI34" s="9" t="n"/>
+      <c r="AJ34" s="10" t="n"/>
+      <c r="AK34" s="8" t="n"/>
+      <c r="AL34" s="9" t="n"/>
+      <c r="AM34" s="10" t="n"/>
+      <c r="AN34" s="8" t="n"/>
+      <c r="AO34" s="9" t="n"/>
+      <c r="AP34" s="10" t="n"/>
+      <c r="AQ34" s="8" t="n"/>
+      <c r="AR34" s="9" t="n"/>
+      <c r="AS34" s="10" t="n"/>
+      <c r="AT34" s="8" t="n"/>
+      <c r="AU34" s="9" t="n"/>
+      <c r="AV34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Indus Towers Limited</t>
+          <t>Zydus Wellness Limited</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>INE121J01017</t>
+          <t>INE768C01028</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Telecom - Services</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="n"/>
-      <c r="E35" s="9" t="n"/>
-      <c r="F35" s="10" t="n"/>
-      <c r="G35" s="8" t="n"/>
-      <c r="H35" s="9" t="n"/>
-      <c r="I35" s="10" t="n"/>
-      <c r="J35" s="8" t="n"/>
-      <c r="K35" s="9" t="n"/>
-      <c r="L35" s="10" t="n"/>
-      <c r="M35" s="8" t="n"/>
-      <c r="N35" s="9" t="n"/>
-      <c r="O35" s="10" t="n"/>
-      <c r="P35" s="8" t="n"/>
-      <c r="Q35" s="9" t="n"/>
-      <c r="R35" s="10" t="n"/>
-      <c r="S35" s="8" t="n"/>
-      <c r="T35" s="9" t="n"/>
-      <c r="U35" s="10" t="n"/>
-      <c r="V35" s="8" t="n"/>
-      <c r="W35" s="9" t="n"/>
-      <c r="X35" s="10" t="n"/>
+          <t>Food Products</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>22157154</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>94467.03</v>
+      </c>
+      <c r="F35" s="10" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="G35" s="8" t="n">
+        <v>22075063</v>
+      </c>
+      <c r="H35" s="9" t="n">
+        <v>84966.92</v>
+      </c>
+      <c r="I35" s="10" t="n">
+        <v>0.0063</v>
+      </c>
+      <c r="J35" s="8" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="K35" s="9" t="n">
+        <v>98626</v>
+      </c>
+      <c r="L35" s="10" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="M35" s="8" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="N35" s="9" t="n">
+        <v>100012</v>
+      </c>
+      <c r="O35" s="10" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="P35" s="8" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="Q35" s="9" t="n">
+        <v>94699</v>
+      </c>
+      <c r="R35" s="10" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="S35" s="8" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="T35" s="9" t="n">
+        <v>104852</v>
+      </c>
+      <c r="U35" s="10" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="W35" s="9" t="n">
+        <v>100584</v>
+      </c>
+      <c r="X35" s="10" t="n">
+        <v>0.008399999999999999</v>
+      </c>
       <c r="Y35" s="8" t="n"/>
       <c r="Z35" s="9" t="n"/>
       <c r="AA35" s="10" t="n"/>
@@ -4510,71 +5359,74 @@
       <c r="AE35" s="8" t="n"/>
       <c r="AF35" s="9" t="n"/>
       <c r="AG35" s="10" t="n"/>
-      <c r="AH35" s="8" t="n">
-        <v>710855</v>
-      </c>
-      <c r="AI35" s="9" t="n">
-        <v>2850.8839775</v>
-      </c>
-      <c r="AJ35" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AK35" s="8" t="n">
-        <v>710855</v>
-      </c>
-      <c r="AL35" s="9" t="n">
-        <v>2976.71</v>
-      </c>
-      <c r="AM35" s="10" t="n">
-        <v>0.0002</v>
-      </c>
+      <c r="AH35" s="8" t="n"/>
+      <c r="AI35" s="9" t="n"/>
+      <c r="AJ35" s="10" t="n"/>
+      <c r="AK35" s="8" t="n"/>
+      <c r="AL35" s="9" t="n"/>
+      <c r="AM35" s="10" t="n"/>
+      <c r="AN35" s="8" t="n"/>
+      <c r="AO35" s="9" t="n"/>
+      <c r="AP35" s="10" t="n"/>
+      <c r="AQ35" s="8" t="n"/>
+      <c r="AR35" s="9" t="n"/>
+      <c r="AS35" s="10" t="n"/>
+      <c r="AT35" s="8" t="n"/>
+      <c r="AU35" s="9" t="n"/>
+      <c r="AV35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>ITC Hotels Limited</t>
+          <t>The Great Eastern Shipping Company Limited</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>INE379A01028</t>
+          <t>INE017A01032</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Leisure Services</t>
+          <t>Transport Services</t>
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>9899412</v>
+        <v>2205298</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>16131.09</v>
+        <v>31198.35</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.0024</v>
       </c>
       <c r="G36" s="8" t="n">
-        <v>9899412</v>
+        <v>2205298</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>16216.23</v>
+        <v>29526.73</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.0022</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>9899412</v>
+        <v>2205298</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>19552.33</v>
+        <v>26516.5</v>
       </c>
       <c r="L36" s="10" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="M36" s="8" t="n"/>
-      <c r="N36" s="9" t="n"/>
-      <c r="O36" s="10" t="n"/>
+        <v>0.002</v>
+      </c>
+      <c r="M36" s="8" t="n">
+        <v>1657424</v>
+      </c>
+      <c r="N36" s="9" t="n">
+        <v>18712.32</v>
+      </c>
+      <c r="O36" s="10" t="n">
+        <v>0.0014</v>
+      </c>
       <c r="P36" s="8" t="n"/>
       <c r="Q36" s="9" t="n"/>
       <c r="R36" s="10" t="n"/>
@@ -4599,38 +5451,77 @@
       <c r="AK36" s="8" t="n"/>
       <c r="AL36" s="9" t="n"/>
       <c r="AM36" s="10" t="n"/>
+      <c r="AN36" s="8" t="n"/>
+      <c r="AO36" s="9" t="n"/>
+      <c r="AP36" s="10" t="n"/>
+      <c r="AQ36" s="8" t="n"/>
+      <c r="AR36" s="9" t="n"/>
+      <c r="AS36" s="10" t="n"/>
+      <c r="AT36" s="8" t="n"/>
+      <c r="AU36" s="9" t="n"/>
+      <c r="AV36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>The Great Eastern Shipping Company Limited</t>
+          <t>Indus Towers Limited</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>INE017A01032</t>
+          <t>INE121J01017</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Transport Services</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="n"/>
-      <c r="E37" s="9" t="n"/>
-      <c r="F37" s="10" t="n"/>
-      <c r="G37" s="8" t="n"/>
-      <c r="H37" s="9" t="n"/>
-      <c r="I37" s="10" t="n"/>
-      <c r="J37" s="8" t="n"/>
-      <c r="K37" s="9" t="n"/>
-      <c r="L37" s="10" t="n"/>
-      <c r="M37" s="8" t="n"/>
-      <c r="N37" s="9" t="n"/>
-      <c r="O37" s="10" t="n"/>
-      <c r="P37" s="8" t="n"/>
-      <c r="Q37" s="9" t="n"/>
-      <c r="R37" s="10" t="n"/>
+          <t>Telecom - Services</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>710855</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>2972.44</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="G37" s="8" t="n">
+        <v>710855</v>
+      </c>
+      <c r="H37" s="9" t="n">
+        <v>3234.03</v>
+      </c>
+      <c r="I37" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="J37" s="8" t="n">
+        <v>710855</v>
+      </c>
+      <c r="K37" s="9" t="n">
+        <v>3158.33</v>
+      </c>
+      <c r="L37" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="M37" s="8" t="n">
+        <v>710855</v>
+      </c>
+      <c r="N37" s="9" t="n">
+        <v>2976.71</v>
+      </c>
+      <c r="O37" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P37" s="8" t="n">
+        <v>710855</v>
+      </c>
+      <c r="Q37" s="9" t="n">
+        <v>2850.8839775</v>
+      </c>
+      <c r="R37" s="10" t="n">
+        <v>0.0002</v>
+      </c>
       <c r="S37" s="8" t="n"/>
       <c r="T37" s="9" t="n"/>
       <c r="U37" s="10" t="n"/>
@@ -4649,144 +5540,633 @@
       <c r="AH37" s="8" t="n"/>
       <c r="AI37" s="9" t="n"/>
       <c r="AJ37" s="10" t="n"/>
-      <c r="AK37" s="8" t="n">
-        <v>1657424</v>
-      </c>
-      <c r="AL37" s="9" t="n">
-        <v>18712.32</v>
-      </c>
-      <c r="AM37" s="10" t="n">
-        <v>0.0014</v>
-      </c>
+      <c r="AK37" s="8" t="n"/>
+      <c r="AL37" s="9" t="n"/>
+      <c r="AM37" s="10" t="n"/>
+      <c r="AN37" s="8" t="n"/>
+      <c r="AO37" s="9" t="n"/>
+      <c r="AP37" s="10" t="n"/>
+      <c r="AQ37" s="8" t="n"/>
+      <c r="AR37" s="9" t="n"/>
+      <c r="AS37" s="10" t="n"/>
+      <c r="AT37" s="8" t="n"/>
+      <c r="AU37" s="9" t="n"/>
+      <c r="AV37" s="10" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Kotak Mahindra Bank Limited</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>INE237A01036</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Banks</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>146607960</v>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>518112.53</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>0.0402</v>
+      </c>
+      <c r="G38" s="8" t="n">
+        <v>123107960</v>
+      </c>
+      <c r="H38" s="9" t="n">
+        <v>511144.25</v>
+      </c>
+      <c r="I38" s="10" t="n">
+        <v>0.0381</v>
+      </c>
+      <c r="J38" s="8" t="n">
+        <v>123107960</v>
+      </c>
+      <c r="K38" s="9" t="n">
+        <v>502280.48</v>
+      </c>
+      <c r="L38" s="10" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="M38" s="8" t="n"/>
+      <c r="N38" s="9" t="n"/>
+      <c r="O38" s="10" t="n"/>
+      <c r="P38" s="8" t="n"/>
+      <c r="Q38" s="9" t="n"/>
+      <c r="R38" s="10" t="n"/>
+      <c r="S38" s="8" t="n"/>
+      <c r="T38" s="9" t="n"/>
+      <c r="U38" s="10" t="n"/>
+      <c r="V38" s="8" t="n"/>
+      <c r="W38" s="9" t="n"/>
+      <c r="X38" s="10" t="n"/>
+      <c r="Y38" s="8" t="n"/>
+      <c r="Z38" s="9" t="n"/>
+      <c r="AA38" s="10" t="n"/>
+      <c r="AB38" s="8" t="n"/>
+      <c r="AC38" s="9" t="n"/>
+      <c r="AD38" s="10" t="n"/>
+      <c r="AE38" s="8" t="n"/>
+      <c r="AF38" s="9" t="n"/>
+      <c r="AG38" s="10" t="n"/>
+      <c r="AH38" s="8" t="n"/>
+      <c r="AI38" s="9" t="n"/>
+      <c r="AJ38" s="10" t="n"/>
+      <c r="AK38" s="8" t="n"/>
+      <c r="AL38" s="9" t="n"/>
+      <c r="AM38" s="10" t="n"/>
+      <c r="AN38" s="8" t="n"/>
+      <c r="AO38" s="9" t="n"/>
+      <c r="AP38" s="10" t="n"/>
+      <c r="AQ38" s="8" t="n"/>
+      <c r="AR38" s="9" t="n"/>
+      <c r="AS38" s="10" t="n"/>
+      <c r="AT38" s="8" t="n"/>
+      <c r="AU38" s="9" t="n"/>
+      <c r="AV38" s="10" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>CMS Info System Limited</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>INE925R01014</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Commercial Services &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>6957544</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>18479.24</v>
+      </c>
+      <c r="F39" s="10" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>5086596</v>
+      </c>
+      <c r="H39" s="9" t="n">
+        <v>15442.91</v>
+      </c>
+      <c r="I39" s="10" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="J39" s="8" t="n">
+        <v>199758</v>
+      </c>
+      <c r="K39" s="9" t="n">
+        <v>629.9400000000001</v>
+      </c>
+      <c r="L39" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="8" t="n"/>
+      <c r="N39" s="9" t="n"/>
+      <c r="O39" s="10" t="n"/>
+      <c r="P39" s="8" t="n"/>
+      <c r="Q39" s="9" t="n"/>
+      <c r="R39" s="10" t="n"/>
+      <c r="S39" s="8" t="n"/>
+      <c r="T39" s="9" t="n"/>
+      <c r="U39" s="10" t="n"/>
+      <c r="V39" s="8" t="n"/>
+      <c r="W39" s="9" t="n"/>
+      <c r="X39" s="10" t="n"/>
+      <c r="Y39" s="8" t="n"/>
+      <c r="Z39" s="9" t="n"/>
+      <c r="AA39" s="10" t="n"/>
+      <c r="AB39" s="8" t="n"/>
+      <c r="AC39" s="9" t="n"/>
+      <c r="AD39" s="10" t="n"/>
+      <c r="AE39" s="8" t="n"/>
+      <c r="AF39" s="9" t="n"/>
+      <c r="AG39" s="10" t="n"/>
+      <c r="AH39" s="8" t="n"/>
+      <c r="AI39" s="9" t="n"/>
+      <c r="AJ39" s="10" t="n"/>
+      <c r="AK39" s="8" t="n"/>
+      <c r="AL39" s="9" t="n"/>
+      <c r="AM39" s="10" t="n"/>
+      <c r="AN39" s="8" t="n"/>
+      <c r="AO39" s="9" t="n"/>
+      <c r="AP39" s="10" t="n"/>
+      <c r="AQ39" s="8" t="n"/>
+      <c r="AR39" s="9" t="n"/>
+      <c r="AS39" s="10" t="n"/>
+      <c r="AT39" s="8" t="n"/>
+      <c r="AU39" s="9" t="n"/>
+      <c r="AV39" s="10" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>CIE Automotive India Limited</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>INE536H01010</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Auto Components</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>464063</v>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>2065.08</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="G40" s="8" t="n">
+        <v>464063</v>
+      </c>
+      <c r="H40" s="9" t="n">
+        <v>2188.75</v>
+      </c>
+      <c r="I40" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="J40" s="8" t="n">
+        <v>462075</v>
+      </c>
+      <c r="K40" s="9" t="n">
+        <v>1932.4</v>
+      </c>
+      <c r="L40" s="10" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M40" s="8" t="n"/>
+      <c r="N40" s="9" t="n"/>
+      <c r="O40" s="10" t="n"/>
+      <c r="P40" s="8" t="n"/>
+      <c r="Q40" s="9" t="n"/>
+      <c r="R40" s="10" t="n"/>
+      <c r="S40" s="8" t="n"/>
+      <c r="T40" s="9" t="n"/>
+      <c r="U40" s="10" t="n"/>
+      <c r="V40" s="8" t="n"/>
+      <c r="W40" s="9" t="n"/>
+      <c r="X40" s="10" t="n"/>
+      <c r="Y40" s="8" t="n"/>
+      <c r="Z40" s="9" t="n"/>
+      <c r="AA40" s="10" t="n"/>
+      <c r="AB40" s="8" t="n"/>
+      <c r="AC40" s="9" t="n"/>
+      <c r="AD40" s="10" t="n"/>
+      <c r="AE40" s="8" t="n"/>
+      <c r="AF40" s="9" t="n"/>
+      <c r="AG40" s="10" t="n"/>
+      <c r="AH40" s="8" t="n"/>
+      <c r="AI40" s="9" t="n"/>
+      <c r="AJ40" s="10" t="n"/>
+      <c r="AK40" s="8" t="n"/>
+      <c r="AL40" s="9" t="n"/>
+      <c r="AM40" s="10" t="n"/>
+      <c r="AN40" s="8" t="n"/>
+      <c r="AO40" s="9" t="n"/>
+      <c r="AP40" s="10" t="n"/>
+      <c r="AQ40" s="8" t="n"/>
+      <c r="AR40" s="9" t="n"/>
+      <c r="AS40" s="10" t="n"/>
+      <c r="AT40" s="8" t="n"/>
+      <c r="AU40" s="9" t="n"/>
+      <c r="AV40" s="10" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Indraprastha Gas Limited</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>INE203G01027</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>481152</v>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>700.65</v>
+      </c>
+      <c r="F41" s="10" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="G41" s="8" t="n">
+        <v>286134</v>
+      </c>
+      <c r="H41" s="9" t="n">
+        <v>488.89</v>
+      </c>
+      <c r="I41" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="8" t="n"/>
+      <c r="K41" s="9" t="n"/>
+      <c r="L41" s="10" t="n"/>
+      <c r="M41" s="8" t="n"/>
+      <c r="N41" s="9" t="n"/>
+      <c r="O41" s="10" t="n"/>
+      <c r="P41" s="8" t="n"/>
+      <c r="Q41" s="9" t="n"/>
+      <c r="R41" s="10" t="n"/>
+      <c r="S41" s="8" t="n"/>
+      <c r="T41" s="9" t="n"/>
+      <c r="U41" s="10" t="n"/>
+      <c r="V41" s="8" t="n"/>
+      <c r="W41" s="9" t="n"/>
+      <c r="X41" s="10" t="n"/>
+      <c r="Y41" s="8" t="n"/>
+      <c r="Z41" s="9" t="n"/>
+      <c r="AA41" s="10" t="n"/>
+      <c r="AB41" s="8" t="n"/>
+      <c r="AC41" s="9" t="n"/>
+      <c r="AD41" s="10" t="n"/>
+      <c r="AE41" s="8" t="n"/>
+      <c r="AF41" s="9" t="n"/>
+      <c r="AG41" s="10" t="n"/>
+      <c r="AH41" s="8" t="n"/>
+      <c r="AI41" s="9" t="n"/>
+      <c r="AJ41" s="10" t="n"/>
+      <c r="AK41" s="8" t="n"/>
+      <c r="AL41" s="9" t="n"/>
+      <c r="AM41" s="10" t="n"/>
+      <c r="AN41" s="8" t="n"/>
+      <c r="AO41" s="9" t="n"/>
+      <c r="AP41" s="10" t="n"/>
+      <c r="AQ41" s="8" t="n"/>
+      <c r="AR41" s="9" t="n"/>
+      <c r="AS41" s="10" t="n"/>
+      <c r="AT41" s="8" t="n"/>
+      <c r="AU41" s="9" t="n"/>
+      <c r="AV41" s="10" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Mahanagar Gas Limited</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>INE002S01010</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>53045</v>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>492.1</v>
+      </c>
+      <c r="F42" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="8" t="n">
+        <v>3045</v>
+      </c>
+      <c r="H42" s="9" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="I42" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="8" t="n"/>
+      <c r="K42" s="9" t="n"/>
+      <c r="L42" s="10" t="n"/>
+      <c r="M42" s="8" t="n"/>
+      <c r="N42" s="9" t="n"/>
+      <c r="O42" s="10" t="n"/>
+      <c r="P42" s="8" t="n"/>
+      <c r="Q42" s="9" t="n"/>
+      <c r="R42" s="10" t="n"/>
+      <c r="S42" s="8" t="n"/>
+      <c r="T42" s="9" t="n"/>
+      <c r="U42" s="10" t="n"/>
+      <c r="V42" s="8" t="n"/>
+      <c r="W42" s="9" t="n"/>
+      <c r="X42" s="10" t="n"/>
+      <c r="Y42" s="8" t="n"/>
+      <c r="Z42" s="9" t="n"/>
+      <c r="AA42" s="10" t="n"/>
+      <c r="AB42" s="8" t="n"/>
+      <c r="AC42" s="9" t="n"/>
+      <c r="AD42" s="10" t="n"/>
+      <c r="AE42" s="8" t="n"/>
+      <c r="AF42" s="9" t="n"/>
+      <c r="AG42" s="10" t="n"/>
+      <c r="AH42" s="8" t="n"/>
+      <c r="AI42" s="9" t="n"/>
+      <c r="AJ42" s="10" t="n"/>
+      <c r="AK42" s="8" t="n"/>
+      <c r="AL42" s="9" t="n"/>
+      <c r="AM42" s="10" t="n"/>
+      <c r="AN42" s="8" t="n"/>
+      <c r="AO42" s="9" t="n"/>
+      <c r="AP42" s="10" t="n"/>
+      <c r="AQ42" s="8" t="n"/>
+      <c r="AR42" s="9" t="n"/>
+      <c r="AS42" s="10" t="n"/>
+      <c r="AT42" s="8" t="n"/>
+      <c r="AU42" s="9" t="n"/>
+      <c r="AV42" s="10" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Multi Commodity Exchange of India Limited</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>INE745G01043</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Capital Markets</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="n"/>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="10" t="n"/>
+      <c r="G43" s="8" t="n"/>
+      <c r="H43" s="9" t="n"/>
+      <c r="I43" s="10" t="n"/>
+      <c r="J43" s="8" t="n">
+        <v>795472</v>
+      </c>
+      <c r="K43" s="9" t="n">
+        <v>20109.53</v>
+      </c>
+      <c r="L43" s="10" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="M43" s="8" t="n"/>
+      <c r="N43" s="9" t="n"/>
+      <c r="O43" s="10" t="n"/>
+      <c r="P43" s="8" t="n"/>
+      <c r="Q43" s="9" t="n"/>
+      <c r="R43" s="10" t="n"/>
+      <c r="S43" s="8" t="n"/>
+      <c r="T43" s="9" t="n"/>
+      <c r="U43" s="10" t="n"/>
+      <c r="V43" s="8" t="n"/>
+      <c r="W43" s="9" t="n"/>
+      <c r="X43" s="10" t="n"/>
+      <c r="Y43" s="8" t="n"/>
+      <c r="Z43" s="9" t="n"/>
+      <c r="AA43" s="10" t="n"/>
+      <c r="AB43" s="8" t="n"/>
+      <c r="AC43" s="9" t="n"/>
+      <c r="AD43" s="10" t="n"/>
+      <c r="AE43" s="8" t="n"/>
+      <c r="AF43" s="9" t="n"/>
+      <c r="AG43" s="10" t="n"/>
+      <c r="AH43" s="8" t="n"/>
+      <c r="AI43" s="9" t="n"/>
+      <c r="AJ43" s="10" t="n"/>
+      <c r="AK43" s="8" t="n"/>
+      <c r="AL43" s="9" t="n"/>
+      <c r="AM43" s="10" t="n"/>
+      <c r="AN43" s="8" t="n"/>
+      <c r="AO43" s="9" t="n"/>
+      <c r="AP43" s="10" t="n"/>
+      <c r="AQ43" s="8" t="n"/>
+      <c r="AR43" s="9" t="n"/>
+      <c r="AS43" s="10" t="n"/>
+      <c r="AT43" s="8" t="n"/>
+      <c r="AU43" s="9" t="n"/>
+      <c r="AV43" s="10" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B38" s="11" t="n"/>
-      <c r="C38" s="12" t="n"/>
-      <c r="D38" s="13" t="n">
+      <c r="B44" s="11" t="n"/>
+      <c r="C44" s="12" t="n"/>
+      <c r="D44" s="13" t="n">
+        <v>1373201700</v>
+      </c>
+      <c r="E44" s="14" t="n">
+        <v>8608487.039999999</v>
+      </c>
+      <c r="F44" s="15" t="n">
+        <v>0.6674999999999998</v>
+      </c>
+      <c r="G44" s="13" t="n">
+        <v>1285817925</v>
+      </c>
+      <c r="H44" s="14" t="n">
+        <v>8857498.140000001</v>
+      </c>
+      <c r="I44" s="15" t="n">
+        <v>0.6597999999999999</v>
+      </c>
+      <c r="J44" s="13" t="n">
+        <v>1265994824</v>
+      </c>
+      <c r="K44" s="14" t="n">
+        <v>8789059.288358001</v>
+      </c>
+      <c r="L44" s="15" t="n">
+        <v>0.6559051731198605</v>
+      </c>
+      <c r="M44" s="13" t="n">
+        <v>1079845116</v>
+      </c>
+      <c r="N44" s="14" t="n">
+        <v>8588270.840000002</v>
+      </c>
+      <c r="O44" s="15" t="n">
+        <v>0.6443999999999998</v>
+      </c>
+      <c r="P44" s="13" t="n">
+        <v>1039629309</v>
+      </c>
+      <c r="Q44" s="14" t="n">
+        <v>8271351.1939775</v>
+      </c>
+      <c r="R44" s="15" t="n">
+        <v>0.6374000000000001</v>
+      </c>
+      <c r="S44" s="13" t="n">
+        <v>991416407</v>
+      </c>
+      <c r="T44" s="14" t="n">
+        <v>7865128.239999999</v>
+      </c>
+      <c r="U44" s="15" t="n">
+        <v>0.6254999999999999</v>
+      </c>
+      <c r="V44" s="13" t="n">
+        <v>979359723</v>
+      </c>
+      <c r="W44" s="14" t="n">
+        <v>7559180.72</v>
+      </c>
+      <c r="X44" s="15" t="n">
+        <v>0.6313999999999997</v>
+      </c>
+      <c r="Y44" s="13" t="n">
+        <v>927478800</v>
+      </c>
+      <c r="Z44" s="14" t="n">
+        <v>7320811.49</v>
+      </c>
+      <c r="AA44" s="15" t="n">
+        <v>0.6364000000000001</v>
+      </c>
+      <c r="AB44" s="13" t="n">
+        <v>819556049</v>
+      </c>
+      <c r="AC44" s="14" t="n">
+        <v>7290583.900000003</v>
+      </c>
+      <c r="AD44" s="15" t="n">
+        <v>0.6436999999999999</v>
+      </c>
+      <c r="AE44" s="13" t="n">
+        <v>799425942</v>
+      </c>
+      <c r="AF44" s="14" t="n">
+        <v>7347454.07</v>
+      </c>
+      <c r="AG44" s="15" t="n">
+        <v>0.6657999999999998</v>
+      </c>
+      <c r="AH44" s="13" t="n">
+        <v>756845974</v>
+      </c>
+      <c r="AI44" s="14" t="n">
+        <v>6714757.130000002</v>
+      </c>
+      <c r="AJ44" s="15" t="n">
+        <v>0.6467999999999997</v>
+      </c>
+      <c r="AK44" s="13" t="n">
+        <v>719050337</v>
+      </c>
+      <c r="AL44" s="14" t="n">
+        <v>6275568.75</v>
+      </c>
+      <c r="AM44" s="15" t="n">
+        <v>0.6370000000000001</v>
+      </c>
+      <c r="AN44" s="13" t="n">
+        <v>717176528</v>
+      </c>
+      <c r="AO44" s="14" t="n">
+        <v>6051937.58</v>
+      </c>
+      <c r="AP44" s="15" t="n">
+        <v>0.6476999999999997</v>
+      </c>
+      <c r="AQ44" s="13" t="n">
+        <v>718063829</v>
+      </c>
+      <c r="AR44" s="14" t="n">
+        <v>5662977.749999999</v>
+      </c>
+      <c r="AS44" s="15" t="n">
+        <v>0.6436999999999998</v>
+      </c>
+      <c r="AT44" s="13" t="n">
         <v>697292654</v>
       </c>
-      <c r="E38" s="14" t="n">
+      <c r="AU44" s="14" t="n">
         <v>5868142.6</v>
       </c>
-      <c r="F38" s="15" t="n">
+      <c r="AV44" s="15" t="n">
         <v>0.6543000000000002</v>
-      </c>
-      <c r="G38" s="13" t="n">
-        <v>718063829</v>
-      </c>
-      <c r="H38" s="14" t="n">
-        <v>5662977.75</v>
-      </c>
-      <c r="I38" s="15" t="n">
-        <v>0.6436999999999999</v>
-      </c>
-      <c r="J38" s="13" t="n">
-        <v>717176528</v>
-      </c>
-      <c r="K38" s="14" t="n">
-        <v>6051937.58</v>
-      </c>
-      <c r="L38" s="15" t="n">
-        <v>0.6476999999999997</v>
-      </c>
-      <c r="M38" s="13" t="n">
-        <v>719050337</v>
-      </c>
-      <c r="N38" s="14" t="n">
-        <v>6275568.750000001</v>
-      </c>
-      <c r="O38" s="15" t="n">
-        <v>0.6370000000000001</v>
-      </c>
-      <c r="P38" s="13" t="n">
-        <v>756845974</v>
-      </c>
-      <c r="Q38" s="14" t="n">
-        <v>6714757.130000002</v>
-      </c>
-      <c r="R38" s="15" t="n">
-        <v>0.6467999999999998</v>
-      </c>
-      <c r="S38" s="13" t="n">
-        <v>799425942</v>
-      </c>
-      <c r="T38" s="14" t="n">
-        <v>7347454.069999999</v>
-      </c>
-      <c r="U38" s="15" t="n">
-        <v>0.6657999999999999</v>
-      </c>
-      <c r="V38" s="13" t="n">
-        <v>819556049</v>
-      </c>
-      <c r="W38" s="14" t="n">
-        <v>7290583.900000001</v>
-      </c>
-      <c r="X38" s="15" t="n">
-        <v>0.6436999999999998</v>
-      </c>
-      <c r="Y38" s="13" t="n">
-        <v>927478800</v>
-      </c>
-      <c r="Z38" s="14" t="n">
-        <v>7320811.49</v>
-      </c>
-      <c r="AA38" s="15" t="n">
-        <v>0.6363999999999999</v>
-      </c>
-      <c r="AB38" s="13" t="n">
-        <v>979359723</v>
-      </c>
-      <c r="AC38" s="14" t="n">
-        <v>7559180.720000002</v>
-      </c>
-      <c r="AD38" s="15" t="n">
-        <v>0.6313999999999996</v>
-      </c>
-      <c r="AE38" s="13" t="n">
-        <v>991416407</v>
-      </c>
-      <c r="AF38" s="14" t="n">
-        <v>7865128.239999998</v>
-      </c>
-      <c r="AG38" s="15" t="n">
-        <v>0.6254999999999999</v>
-      </c>
-      <c r="AH38" s="13" t="n">
-        <v>1039629309</v>
-      </c>
-      <c r="AI38" s="14" t="n">
-        <v>8271351.1939775</v>
-      </c>
-      <c r="AJ38" s="15" t="n">
-        <v>0.6374</v>
-      </c>
-      <c r="AK38" s="13" t="n">
-        <v>1079845116</v>
-      </c>
-      <c r="AL38" s="14" t="n">
-        <v>8588270.840000002</v>
-      </c>
-      <c r="AM38" s="15" t="n">
-        <v>0.6443999999999998</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="16">
     <mergeCell ref="D2:F2"/>
+    <mergeCell ref="AT2:AV2"/>
     <mergeCell ref="G2:I2"/>
-    <mergeCell ref="A1:AM1"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="Y2:AA2"/>
     <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="AE2:AG2"/>
     <mergeCell ref="AK2:AM2"/>
     <mergeCell ref="P2:R2"/>
+    <mergeCell ref="AN2:AP2"/>
+    <mergeCell ref="A1:AV1"/>
+    <mergeCell ref="AQ2:AS2"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="S2:U2"/>
     <mergeCell ref="AH2:AJ2"/>

--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -487,7 +487,7 @@
   <dimension ref="A1:AV44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -495,7 +495,7 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
@@ -513,13 +513,13 @@
     <col width="20" customWidth="1" min="24" max="24"/>
     <col width="13" customWidth="1" min="25" max="25"/>
     <col width="26" customWidth="1" min="26" max="26"/>
-    <col width="20" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="26" customWidth="1" min="29" max="29"/>
     <col width="20" customWidth="1" min="30" max="30"/>
     <col width="13" customWidth="1" min="31" max="31"/>
     <col width="26" customWidth="1" min="32" max="32"/>
-    <col width="20" customWidth="1" min="33" max="33"/>
+    <col width="14" customWidth="1" min="33" max="33"/>
     <col width="13" customWidth="1" min="34" max="34"/>
     <col width="26" customWidth="1" min="35" max="35"/>
     <col width="20" customWidth="1" min="36" max="36"/>
@@ -1250,305 +1250,305 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Coal India Limited</t>
+          <t>Power Grid Corporation of India Limited</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>INE522F01014</t>
+          <t>INE752E01010</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Consumable Fuels</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>174817417</v>
+        <v>312063864</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>787465.05</v>
+        <v>924021.1</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.0611</v>
+        <v>0.0716</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>161423761</v>
+        <v>311113864</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>695171.4300000001</v>
+        <v>929141.55</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>0.0518</v>
+        <v>0.0692</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>159832308</v>
+        <v>313365617</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>704460.9</v>
+        <v>803782.8100000001</v>
       </c>
       <c r="L6" s="10" t="n">
-        <v>0.0526</v>
+        <v>0.06</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>162039558</v>
+        <v>305419267</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>646537.84</v>
+        <v>808139.38</v>
       </c>
       <c r="O6" s="10" t="n">
-        <v>0.0485</v>
+        <v>0.0606</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>162039558</v>
+        <v>284154236</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>609511.8</v>
+        <v>767074.36</v>
       </c>
       <c r="R6" s="10" t="n">
-        <v>0.047</v>
+        <v>0.0591</v>
       </c>
       <c r="S6" s="8" t="n">
-        <v>162039558</v>
+        <v>261786637</v>
       </c>
       <c r="T6" s="9" t="n">
-        <v>629766.74</v>
+        <v>754338.1899999999</v>
       </c>
       <c r="U6" s="10" t="n">
-        <v>0.0501</v>
+        <v>0.06</v>
       </c>
       <c r="V6" s="8" t="n">
-        <v>162039558</v>
+        <v>255922726</v>
       </c>
       <c r="W6" s="9" t="n">
-        <v>631873.26</v>
+        <v>717223.4399999999</v>
       </c>
       <c r="X6" s="10" t="n">
-        <v>0.0528</v>
+        <v>0.0599</v>
       </c>
       <c r="Y6" s="8" t="n">
-        <v>162039558</v>
+        <v>246049993</v>
       </c>
       <c r="Z6" s="9" t="n">
-        <v>607324.26</v>
+        <v>677252.61</v>
       </c>
       <c r="AA6" s="10" t="n">
-        <v>0.0528</v>
+        <v>0.0589</v>
       </c>
       <c r="AB6" s="8" t="n">
-        <v>162039558</v>
+        <v>230787510</v>
       </c>
       <c r="AC6" s="9" t="n">
-        <v>609835.88</v>
+        <v>671591.65</v>
       </c>
       <c r="AD6" s="10" t="n">
-        <v>0.0538</v>
+        <v>0.0593</v>
       </c>
       <c r="AE6" s="8" t="n">
-        <v>162039558</v>
+        <v>224216515</v>
       </c>
       <c r="AF6" s="9" t="n">
-        <v>635114.05</v>
+        <v>672425.33</v>
       </c>
       <c r="AG6" s="10" t="n">
-        <v>0.0575</v>
+        <v>0.0609</v>
       </c>
       <c r="AH6" s="8" t="n">
-        <v>155681572</v>
+        <v>208867542</v>
       </c>
       <c r="AI6" s="9" t="n">
-        <v>618522.89</v>
+        <v>605193.7</v>
       </c>
       <c r="AJ6" s="10" t="n">
-        <v>0.0595</v>
+        <v>0.0583</v>
       </c>
       <c r="AK6" s="8" t="n">
-        <v>148323775</v>
+        <v>193616648</v>
       </c>
       <c r="AL6" s="9" t="n">
-        <v>571491.51</v>
+        <v>595274.38</v>
       </c>
       <c r="AM6" s="10" t="n">
-        <v>0.058</v>
+        <v>0.0604</v>
       </c>
       <c r="AN6" s="8" t="n">
-        <v>141074007</v>
+        <v>192765312</v>
       </c>
       <c r="AO6" s="9" t="n">
-        <v>561756.7</v>
+        <v>559694.08</v>
       </c>
       <c r="AP6" s="10" t="n">
-        <v>0.0601</v>
+        <v>0.0599</v>
       </c>
       <c r="AQ6" s="8" t="n">
-        <v>142636407</v>
+        <v>193498810</v>
       </c>
       <c r="AR6" s="9" t="n">
-        <v>526827.5699999999</v>
+        <v>485391.76</v>
       </c>
       <c r="AS6" s="10" t="n">
-        <v>0.0599</v>
+        <v>0.0552</v>
       </c>
       <c r="AT6" s="8" t="n">
-        <v>139335199</v>
+        <v>185577147</v>
       </c>
       <c r="AU6" s="9" t="n">
-        <v>551628.05</v>
+        <v>559793.46</v>
       </c>
       <c r="AV6" s="10" t="n">
-        <v>0.0615</v>
+        <v>0.0624</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Power Grid Corporation of India Limited</t>
+          <t>Coal India Limited</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>INE752E01010</t>
+          <t>INE522F01014</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Consumable Fuels</t>
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>312063864</v>
+        <v>174817417</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>924021.1</v>
+        <v>787465.05</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.0716</v>
+        <v>0.0611</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>311113864</v>
+        <v>161423761</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>929141.55</v>
+        <v>695171.4300000001</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>0.0692</v>
+        <v>0.0518</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>313365617</v>
+        <v>159832308</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>803782.8100000001</v>
+        <v>704460.9</v>
       </c>
       <c r="L7" s="10" t="n">
-        <v>0.06</v>
+        <v>0.0526</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>305419267</v>
+        <v>162039558</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>808139.38</v>
+        <v>646537.84</v>
       </c>
       <c r="O7" s="10" t="n">
-        <v>0.0606</v>
+        <v>0.0485</v>
       </c>
       <c r="P7" s="8" t="n">
-        <v>284154236</v>
+        <v>162039558</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>767074.36</v>
+        <v>609511.8</v>
       </c>
       <c r="R7" s="10" t="n">
-        <v>0.0591</v>
+        <v>0.047</v>
       </c>
       <c r="S7" s="8" t="n">
-        <v>261786637</v>
+        <v>162039558</v>
       </c>
       <c r="T7" s="9" t="n">
-        <v>754338.1899999999</v>
+        <v>629766.74</v>
       </c>
       <c r="U7" s="10" t="n">
-        <v>0.06</v>
+        <v>0.0501</v>
       </c>
       <c r="V7" s="8" t="n">
-        <v>255922726</v>
+        <v>162039558</v>
       </c>
       <c r="W7" s="9" t="n">
-        <v>717223.4399999999</v>
+        <v>631873.26</v>
       </c>
       <c r="X7" s="10" t="n">
+        <v>0.0528</v>
+      </c>
+      <c r="Y7" s="8" t="n">
+        <v>162039558</v>
+      </c>
+      <c r="Z7" s="9" t="n">
+        <v>607324.26</v>
+      </c>
+      <c r="AA7" s="10" t="n">
+        <v>0.0528</v>
+      </c>
+      <c r="AB7" s="8" t="n">
+        <v>162039558</v>
+      </c>
+      <c r="AC7" s="9" t="n">
+        <v>609835.88</v>
+      </c>
+      <c r="AD7" s="10" t="n">
+        <v>0.0538</v>
+      </c>
+      <c r="AE7" s="8" t="n">
+        <v>162039558</v>
+      </c>
+      <c r="AF7" s="9" t="n">
+        <v>635114.05</v>
+      </c>
+      <c r="AG7" s="10" t="n">
+        <v>0.0575</v>
+      </c>
+      <c r="AH7" s="8" t="n">
+        <v>155681572</v>
+      </c>
+      <c r="AI7" s="9" t="n">
+        <v>618522.89</v>
+      </c>
+      <c r="AJ7" s="10" t="n">
+        <v>0.0595</v>
+      </c>
+      <c r="AK7" s="8" t="n">
+        <v>148323775</v>
+      </c>
+      <c r="AL7" s="9" t="n">
+        <v>571491.51</v>
+      </c>
+      <c r="AM7" s="10" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="AN7" s="8" t="n">
+        <v>141074007</v>
+      </c>
+      <c r="AO7" s="9" t="n">
+        <v>561756.7</v>
+      </c>
+      <c r="AP7" s="10" t="n">
+        <v>0.0601</v>
+      </c>
+      <c r="AQ7" s="8" t="n">
+        <v>142636407</v>
+      </c>
+      <c r="AR7" s="9" t="n">
+        <v>526827.5699999999</v>
+      </c>
+      <c r="AS7" s="10" t="n">
         <v>0.0599</v>
       </c>
-      <c r="Y7" s="8" t="n">
-        <v>246049993</v>
-      </c>
-      <c r="Z7" s="9" t="n">
-        <v>677252.61</v>
-      </c>
-      <c r="AA7" s="10" t="n">
-        <v>0.0589</v>
-      </c>
-      <c r="AB7" s="8" t="n">
-        <v>230787510</v>
-      </c>
-      <c r="AC7" s="9" t="n">
-        <v>671591.65</v>
-      </c>
-      <c r="AD7" s="10" t="n">
-        <v>0.0593</v>
-      </c>
-      <c r="AE7" s="8" t="n">
-        <v>224216515</v>
-      </c>
-      <c r="AF7" s="9" t="n">
-        <v>672425.33</v>
-      </c>
-      <c r="AG7" s="10" t="n">
-        <v>0.0609</v>
-      </c>
-      <c r="AH7" s="8" t="n">
-        <v>208867542</v>
-      </c>
-      <c r="AI7" s="9" t="n">
-        <v>605193.7</v>
-      </c>
-      <c r="AJ7" s="10" t="n">
-        <v>0.0583</v>
-      </c>
-      <c r="AK7" s="8" t="n">
-        <v>193616648</v>
-      </c>
-      <c r="AL7" s="9" t="n">
-        <v>595274.38</v>
-      </c>
-      <c r="AM7" s="10" t="n">
-        <v>0.0604</v>
-      </c>
-      <c r="AN7" s="8" t="n">
-        <v>192765312</v>
-      </c>
-      <c r="AO7" s="9" t="n">
-        <v>559694.08</v>
-      </c>
-      <c r="AP7" s="10" t="n">
-        <v>0.0599</v>
-      </c>
-      <c r="AQ7" s="8" t="n">
-        <v>193498810</v>
-      </c>
-      <c r="AR7" s="9" t="n">
-        <v>485391.76</v>
-      </c>
-      <c r="AS7" s="10" t="n">
-        <v>0.0552</v>
-      </c>
       <c r="AT7" s="8" t="n">
-        <v>185577147</v>
+        <v>139335199</v>
       </c>
       <c r="AU7" s="9" t="n">
-        <v>559793.46</v>
+        <v>551628.05</v>
       </c>
       <c r="AV7" s="10" t="n">
-        <v>0.0624</v>
+        <v>0.0615</v>
       </c>
     </row>
     <row r="8">
@@ -1706,287 +1706,287 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Kotak Mahindra Bank Limited</t>
+          <t>ITC Limited</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>INE237A01028</t>
+          <t>INE154A01025</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Banks</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="10" t="n"/>
-      <c r="G9" s="8" t="n"/>
-      <c r="H9" s="9" t="n"/>
-      <c r="I9" s="10" t="n"/>
-      <c r="J9" s="8" t="n"/>
-      <c r="K9" s="9" t="n"/>
-      <c r="L9" s="10" t="n"/>
+          <t>Diversified FMCG</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>224093958</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>644718.3199999999</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>215593958</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>676102.65</v>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>0.0504</v>
+      </c>
+      <c r="J9" s="8" t="n">
+        <v>209900994</v>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>676196.05</v>
+      </c>
+      <c r="L9" s="10" t="n">
+        <v>0.0505</v>
+      </c>
       <c r="M9" s="8" t="n">
-        <v>24621592</v>
+        <v>148665711</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>541945.86</v>
+        <v>599122.8199999999</v>
       </c>
       <c r="O9" s="10" t="n">
-        <v>0.0407</v>
+        <v>0.0449</v>
       </c>
       <c r="P9" s="8" t="n">
-        <v>24306544</v>
+        <v>144737169</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>516368.22</v>
+        <v>585100.01</v>
       </c>
       <c r="R9" s="10" t="n">
-        <v>0.0398</v>
+        <v>0.0451</v>
       </c>
       <c r="S9" s="8" t="n">
-        <v>24205055</v>
+        <v>138771024</v>
       </c>
       <c r="T9" s="9" t="n">
-        <v>508838.67</v>
+        <v>583324</v>
       </c>
       <c r="U9" s="10" t="n">
-        <v>0.0404</v>
+        <v>0.0464</v>
       </c>
       <c r="V9" s="8" t="n">
-        <v>24205055</v>
+        <v>135721024</v>
       </c>
       <c r="W9" s="9" t="n">
-        <v>482334.13</v>
+        <v>544987.77</v>
       </c>
       <c r="X9" s="10" t="n">
-        <v>0.0403</v>
+        <v>0.0455</v>
       </c>
       <c r="Y9" s="8" t="n">
-        <v>23407381</v>
+        <v>129421024</v>
       </c>
       <c r="Z9" s="9" t="n">
-        <v>458854.89</v>
+        <v>530302.65</v>
       </c>
       <c r="AA9" s="10" t="n">
-        <v>0.0399</v>
+        <v>0.0461</v>
       </c>
       <c r="AB9" s="8" t="n">
-        <v>21994066</v>
+        <v>122172359</v>
       </c>
       <c r="AC9" s="9" t="n">
-        <v>435174.59</v>
+        <v>503289.03</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>0.0384</v>
+        <v>0.0444</v>
       </c>
       <c r="AE9" s="8" t="n">
-        <v>20473232</v>
+        <v>117422359</v>
       </c>
       <c r="AF9" s="9" t="n">
-        <v>442938.37</v>
+        <v>489005.41</v>
       </c>
       <c r="AG9" s="10" t="n">
-        <v>0.0401</v>
+        <v>0.0443</v>
       </c>
       <c r="AH9" s="8" t="n">
-        <v>19753232</v>
+        <v>109270669</v>
       </c>
       <c r="AI9" s="9" t="n">
-        <v>409820.3</v>
+        <v>456806.03</v>
       </c>
       <c r="AJ9" s="10" t="n">
-        <v>0.0395</v>
+        <v>0.044</v>
       </c>
       <c r="AK9" s="8" t="n">
-        <v>19753232</v>
+        <v>105271096</v>
       </c>
       <c r="AL9" s="9" t="n">
-        <v>436171.12</v>
+        <v>448244.33</v>
       </c>
       <c r="AM9" s="10" t="n">
-        <v>0.0443</v>
+        <v>0.0455</v>
       </c>
       <c r="AN9" s="8" t="n">
-        <v>19753232</v>
+        <v>101194120</v>
       </c>
       <c r="AO9" s="9" t="n">
-        <v>428882.17</v>
+        <v>414642.91</v>
       </c>
       <c r="AP9" s="10" t="n">
-        <v>0.0459</v>
+        <v>0.0444</v>
       </c>
       <c r="AQ9" s="8" t="n">
-        <v>19753232</v>
+        <v>101194120</v>
       </c>
       <c r="AR9" s="9" t="n">
-        <v>375894.13</v>
+        <v>399716.77</v>
       </c>
       <c r="AS9" s="10" t="n">
-        <v>0.0427</v>
+        <v>0.0454</v>
       </c>
       <c r="AT9" s="8" t="n">
-        <v>19753232</v>
+        <v>98994120</v>
       </c>
       <c r="AU9" s="9" t="n">
-        <v>375568.2</v>
+        <v>442998.69</v>
       </c>
       <c r="AV9" s="10" t="n">
-        <v>0.0419</v>
+        <v>0.0494</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>ITC Limited</t>
+          <t>Kotak Mahindra Bank Limited</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>INE154A01025</t>
+          <t>INE237A01028</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Diversified FMCG</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>224093958</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>644718.3199999999</v>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>215593958</v>
-      </c>
-      <c r="H10" s="9" t="n">
-        <v>676102.65</v>
-      </c>
-      <c r="I10" s="10" t="n">
-        <v>0.0504</v>
-      </c>
-      <c r="J10" s="8" t="n">
-        <v>209900994</v>
-      </c>
-      <c r="K10" s="9" t="n">
-        <v>676196.05</v>
-      </c>
-      <c r="L10" s="10" t="n">
-        <v>0.0505</v>
-      </c>
+          <t>Banks</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="9" t="n"/>
+      <c r="I10" s="10" t="n"/>
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="9" t="n"/>
+      <c r="L10" s="10" t="n"/>
       <c r="M10" s="8" t="n">
-        <v>148665711</v>
+        <v>24621592</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>599122.8199999999</v>
+        <v>541945.86</v>
       </c>
       <c r="O10" s="10" t="n">
-        <v>0.0449</v>
+        <v>0.0407</v>
       </c>
       <c r="P10" s="8" t="n">
-        <v>144737169</v>
+        <v>24306544</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>585100.01</v>
+        <v>516368.22</v>
       </c>
       <c r="R10" s="10" t="n">
-        <v>0.0451</v>
+        <v>0.0398</v>
       </c>
       <c r="S10" s="8" t="n">
-        <v>138771024</v>
+        <v>24205055</v>
       </c>
       <c r="T10" s="9" t="n">
-        <v>583324</v>
+        <v>508838.67</v>
       </c>
       <c r="U10" s="10" t="n">
-        <v>0.0464</v>
+        <v>0.0404</v>
       </c>
       <c r="V10" s="8" t="n">
-        <v>135721024</v>
+        <v>24205055</v>
       </c>
       <c r="W10" s="9" t="n">
-        <v>544987.77</v>
+        <v>482334.13</v>
       </c>
       <c r="X10" s="10" t="n">
-        <v>0.0455</v>
+        <v>0.0403</v>
       </c>
       <c r="Y10" s="8" t="n">
-        <v>129421024</v>
+        <v>23407381</v>
       </c>
       <c r="Z10" s="9" t="n">
-        <v>530302.65</v>
+        <v>458854.89</v>
       </c>
       <c r="AA10" s="10" t="n">
-        <v>0.0461</v>
+        <v>0.0399</v>
       </c>
       <c r="AB10" s="8" t="n">
-        <v>122172359</v>
+        <v>21994066</v>
       </c>
       <c r="AC10" s="9" t="n">
-        <v>503289.03</v>
+        <v>435174.59</v>
       </c>
       <c r="AD10" s="10" t="n">
-        <v>0.0444</v>
+        <v>0.0384</v>
       </c>
       <c r="AE10" s="8" t="n">
-        <v>117422359</v>
+        <v>20473232</v>
       </c>
       <c r="AF10" s="9" t="n">
-        <v>489005.41</v>
+        <v>442938.37</v>
       </c>
       <c r="AG10" s="10" t="n">
+        <v>0.0401</v>
+      </c>
+      <c r="AH10" s="8" t="n">
+        <v>19753232</v>
+      </c>
+      <c r="AI10" s="9" t="n">
+        <v>409820.3</v>
+      </c>
+      <c r="AJ10" s="10" t="n">
+        <v>0.0395</v>
+      </c>
+      <c r="AK10" s="8" t="n">
+        <v>19753232</v>
+      </c>
+      <c r="AL10" s="9" t="n">
+        <v>436171.12</v>
+      </c>
+      <c r="AM10" s="10" t="n">
         <v>0.0443</v>
       </c>
-      <c r="AH10" s="8" t="n">
-        <v>109270669</v>
-      </c>
-      <c r="AI10" s="9" t="n">
-        <v>456806.03</v>
-      </c>
-      <c r="AJ10" s="10" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="AK10" s="8" t="n">
-        <v>105271096</v>
-      </c>
-      <c r="AL10" s="9" t="n">
-        <v>448244.33</v>
-      </c>
-      <c r="AM10" s="10" t="n">
-        <v>0.0455</v>
-      </c>
       <c r="AN10" s="8" t="n">
-        <v>101194120</v>
+        <v>19753232</v>
       </c>
       <c r="AO10" s="9" t="n">
-        <v>414642.91</v>
+        <v>428882.17</v>
       </c>
       <c r="AP10" s="10" t="n">
-        <v>0.0444</v>
+        <v>0.0459</v>
       </c>
       <c r="AQ10" s="8" t="n">
-        <v>101194120</v>
+        <v>19753232</v>
       </c>
       <c r="AR10" s="9" t="n">
-        <v>399716.77</v>
+        <v>375894.13</v>
       </c>
       <c r="AS10" s="10" t="n">
-        <v>0.0454</v>
+        <v>0.0427</v>
       </c>
       <c r="AT10" s="8" t="n">
-        <v>98994120</v>
+        <v>19753232</v>
       </c>
       <c r="AU10" s="9" t="n">
-        <v>442998.69</v>
+        <v>375568.2</v>
       </c>
       <c r="AV10" s="10" t="n">
-        <v>0.0494</v>
+        <v>0.0419</v>
       </c>
     </row>
     <row r="11">
@@ -2144,468 +2144,444 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Axis Bank Limited</t>
+          <t>Bharti Airtel Limited</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>INE238A01034</t>
+          <t>INE397D01024</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Telecom - Services</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>33244875</v>
+        <v>21167034</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>386072.73</v>
+        <v>377281.21</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>0.0299</v>
+        <v>0.0293</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>33244875</v>
+        <v>21167034</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>460075.83</v>
+        <v>397792.07</v>
       </c>
       <c r="I12" s="10" t="n">
+        <v>0.0296</v>
+      </c>
+      <c r="J12" s="8" t="n">
+        <v>21167034</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>416715.398358</v>
+      </c>
+      <c r="L12" s="10" t="n">
+        <v>0.0311051731198606</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>21167034</v>
+      </c>
+      <c r="N12" s="9" t="n">
+        <v>445693.07</v>
+      </c>
+      <c r="O12" s="10" t="n">
+        <v>0.0334</v>
+      </c>
+      <c r="P12" s="8" t="n">
+        <v>21167034</v>
+      </c>
+      <c r="Q12" s="9" t="n">
+        <v>444846.39</v>
+      </c>
+      <c r="R12" s="10" t="n">
         <v>0.0343</v>
       </c>
-      <c r="J12" s="8" t="n">
-        <v>33244875</v>
-      </c>
-      <c r="K12" s="9" t="n">
-        <v>455587.77</v>
-      </c>
-      <c r="L12" s="10" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="M12" s="8" t="n">
-        <v>33244875</v>
-      </c>
-      <c r="N12" s="9" t="n">
-        <v>422010.44</v>
-      </c>
-      <c r="O12" s="10" t="n">
-        <v>0.0317</v>
-      </c>
-      <c r="P12" s="8" t="n">
-        <v>33244875</v>
-      </c>
-      <c r="Q12" s="9" t="n">
-        <v>425434.67</v>
-      </c>
-      <c r="R12" s="10" t="n">
-        <v>0.0328</v>
-      </c>
       <c r="S12" s="8" t="n">
-        <v>33244875</v>
+        <v>21167034</v>
       </c>
       <c r="T12" s="9" t="n">
-        <v>409842.82</v>
+        <v>434876.71</v>
       </c>
       <c r="U12" s="10" t="n">
-        <v>0.0326</v>
+        <v>0.0346</v>
       </c>
       <c r="V12" s="8" t="n">
-        <v>33244875</v>
+        <v>21167034</v>
       </c>
       <c r="W12" s="9" t="n">
-        <v>376199.01</v>
+        <v>397601.57</v>
       </c>
       <c r="X12" s="10" t="n">
-        <v>0.0314</v>
+        <v>0.0332</v>
       </c>
       <c r="Y12" s="8" t="n">
-        <v>32644875</v>
+        <v>21167034</v>
       </c>
       <c r="Z12" s="9" t="n">
-        <v>341204.23</v>
+        <v>399802.94</v>
       </c>
       <c r="AA12" s="10" t="n">
-        <v>0.0297</v>
+        <v>0.0348</v>
       </c>
       <c r="AB12" s="8" t="n">
-        <v>30107270</v>
+        <v>21167034</v>
       </c>
       <c r="AC12" s="9" t="n">
-        <v>321666.07</v>
+        <v>405200.53</v>
       </c>
       <c r="AD12" s="10" t="n">
-        <v>0.0284</v>
+        <v>0.0358</v>
       </c>
       <c r="AE12" s="8" t="n">
-        <v>27257270</v>
+        <v>20937034</v>
       </c>
       <c r="AF12" s="9" t="n">
-        <v>326869.18</v>
+        <v>420750.64</v>
       </c>
       <c r="AG12" s="10" t="n">
-        <v>0.0296</v>
+        <v>0.0381</v>
       </c>
       <c r="AH12" s="8" t="n">
-        <v>27257270</v>
+        <v>11799076</v>
       </c>
       <c r="AI12" s="9" t="n">
-        <v>324961.17</v>
+        <v>219014.45</v>
       </c>
       <c r="AJ12" s="10" t="n">
-        <v>0.0313</v>
-      </c>
-      <c r="AK12" s="8" t="n">
-        <v>27257270</v>
-      </c>
-      <c r="AL12" s="9" t="n">
-        <v>322998.65</v>
-      </c>
-      <c r="AM12" s="10" t="n">
-        <v>0.0328</v>
-      </c>
-      <c r="AN12" s="8" t="n">
-        <v>27257270</v>
-      </c>
-      <c r="AO12" s="9" t="n">
-        <v>300375.12</v>
-      </c>
-      <c r="AP12" s="10" t="n">
-        <v>0.0321</v>
-      </c>
-      <c r="AQ12" s="8" t="n">
-        <v>27257270</v>
-      </c>
-      <c r="AR12" s="9" t="n">
-        <v>276811.21</v>
-      </c>
-      <c r="AS12" s="10" t="n">
-        <v>0.0315</v>
-      </c>
-      <c r="AT12" s="8" t="n">
-        <v>27257270</v>
-      </c>
-      <c r="AU12" s="9" t="n">
-        <v>268783.94</v>
-      </c>
-      <c r="AV12" s="10" t="n">
-        <v>0.03</v>
-      </c>
+        <v>0.0211</v>
+      </c>
+      <c r="AK12" s="8" t="n"/>
+      <c r="AL12" s="9" t="n"/>
+      <c r="AM12" s="10" t="n"/>
+      <c r="AN12" s="8" t="n"/>
+      <c r="AO12" s="9" t="n"/>
+      <c r="AP12" s="10" t="n"/>
+      <c r="AQ12" s="8" t="n"/>
+      <c r="AR12" s="9" t="n"/>
+      <c r="AS12" s="10" t="n"/>
+      <c r="AT12" s="8" t="n"/>
+      <c r="AU12" s="9" t="n"/>
+      <c r="AV12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>HCL Technologies Limited</t>
+          <t>Mahindra &amp; Mahindra Limited</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>INE860A01027</t>
+          <t>INE101A01026</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>IT - Software</t>
+          <t>Automobiles</t>
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>29868916</v>
+        <v>14645626</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>400721.38</v>
+        <v>432734.31</v>
       </c>
       <c r="F13" s="10" t="n">
+        <v>0.0336</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>13974725</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>474777.31</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>0.0354</v>
+      </c>
+      <c r="J13" s="8" t="n">
+        <v>13974725</v>
+      </c>
+      <c r="K13" s="9" t="n">
+        <v>479584.61</v>
+      </c>
+      <c r="L13" s="10" t="n">
+        <v>0.0358</v>
+      </c>
+      <c r="M13" s="8" t="n">
+        <v>13033470</v>
+      </c>
+      <c r="N13" s="9" t="n">
+        <v>483437.47</v>
+      </c>
+      <c r="O13" s="10" t="n">
+        <v>0.0363</v>
+      </c>
+      <c r="P13" s="8" t="n">
+        <v>12435671</v>
+      </c>
+      <c r="Q13" s="9" t="n">
+        <v>467245.47</v>
+      </c>
+      <c r="R13" s="10" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="S13" s="8" t="n">
+        <v>12435671</v>
+      </c>
+      <c r="T13" s="9" t="n">
+        <v>433656.72</v>
+      </c>
+      <c r="U13" s="10" t="n">
+        <v>0.0345</v>
+      </c>
+      <c r="V13" s="8" t="n">
+        <v>12335671</v>
+      </c>
+      <c r="W13" s="9" t="n">
+        <v>422743.45</v>
+      </c>
+      <c r="X13" s="10" t="n">
+        <v>0.0353</v>
+      </c>
+      <c r="Y13" s="8" t="n">
+        <v>12335671</v>
+      </c>
+      <c r="Z13" s="9" t="n">
+        <v>394679.79</v>
+      </c>
+      <c r="AA13" s="10" t="n">
+        <v>0.0343</v>
+      </c>
+      <c r="AB13" s="8" t="n">
+        <v>12335671</v>
+      </c>
+      <c r="AC13" s="9" t="n">
+        <v>395123.88</v>
+      </c>
+      <c r="AD13" s="10" t="n">
+        <v>0.0349</v>
+      </c>
+      <c r="AE13" s="8" t="n">
+        <v>12335671</v>
+      </c>
+      <c r="AF13" s="9" t="n">
+        <v>392669.08</v>
+      </c>
+      <c r="AG13" s="10" t="n">
+        <v>0.0356</v>
+      </c>
+      <c r="AH13" s="8" t="n">
+        <v>12231374</v>
+      </c>
+      <c r="AI13" s="9" t="n">
+        <v>364103.54</v>
+      </c>
+      <c r="AJ13" s="10" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="AK13" s="8" t="n">
+        <v>11040212</v>
+      </c>
+      <c r="AL13" s="9" t="n">
+        <v>323345.73</v>
+      </c>
+      <c r="AM13" s="10" t="n">
+        <v>0.0328</v>
+      </c>
+      <c r="AN13" s="8" t="n">
+        <v>10399289</v>
+      </c>
+      <c r="AO13" s="9" t="n">
+        <v>277224.25</v>
+      </c>
+      <c r="AP13" s="10" t="n">
+        <v>0.0297</v>
+      </c>
+      <c r="AQ13" s="8" t="n">
+        <v>10068665</v>
+      </c>
+      <c r="AR13" s="9" t="n">
+        <v>260285.06</v>
+      </c>
+      <c r="AS13" s="10" t="n">
+        <v>0.0296</v>
+      </c>
+      <c r="AT13" s="8" t="n">
+        <v>9331737</v>
+      </c>
+      <c r="AU13" s="9" t="n">
+        <v>279004.94</v>
+      </c>
+      <c r="AV13" s="10" t="n">
         <v>0.0311</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <v>27771661</v>
-      </c>
-      <c r="H13" s="9" t="n">
-        <v>385776.14</v>
-      </c>
-      <c r="I13" s="10" t="n">
-        <v>0.0287</v>
-      </c>
-      <c r="J13" s="8" t="n">
-        <v>23460156</v>
-      </c>
-      <c r="K13" s="9" t="n">
-        <v>397790.41</v>
-      </c>
-      <c r="L13" s="10" t="n">
-        <v>0.0297</v>
-      </c>
-      <c r="M13" s="8" t="n">
-        <v>21315882</v>
-      </c>
-      <c r="N13" s="9" t="n">
-        <v>346020.71</v>
-      </c>
-      <c r="O13" s="10" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="P13" s="8" t="n">
-        <v>19831378</v>
-      </c>
-      <c r="Q13" s="9" t="n">
-        <v>322101.24</v>
-      </c>
-      <c r="R13" s="10" t="n">
-        <v>0.0248</v>
-      </c>
-      <c r="S13" s="8" t="n">
-        <v>18138945</v>
-      </c>
-      <c r="T13" s="9" t="n">
-        <v>279611.84</v>
-      </c>
-      <c r="U13" s="10" t="n">
-        <v>0.0222</v>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v>18706995</v>
-      </c>
-      <c r="W13" s="9" t="n">
-        <v>259110.59</v>
-      </c>
-      <c r="X13" s="10" t="n">
-        <v>0.0216</v>
-      </c>
-      <c r="Y13" s="8" t="n">
-        <v>18706995</v>
-      </c>
-      <c r="Z13" s="9" t="n">
-        <v>272149.36</v>
-      </c>
-      <c r="AA13" s="10" t="n">
-        <v>0.0237</v>
-      </c>
-      <c r="AB13" s="8" t="n">
-        <v>18706995</v>
-      </c>
-      <c r="AC13" s="9" t="n">
-        <v>274599.98</v>
-      </c>
-      <c r="AD13" s="10" t="n">
-        <v>0.0242</v>
-      </c>
-      <c r="AE13" s="8" t="n">
-        <v>18558995</v>
-      </c>
-      <c r="AF13" s="9" t="n">
-        <v>320810.79</v>
-      </c>
-      <c r="AG13" s="10" t="n">
-        <v>0.0291</v>
-      </c>
-      <c r="AH13" s="8" t="n">
-        <v>18341573</v>
-      </c>
-      <c r="AI13" s="9" t="n">
-        <v>300178.18</v>
-      </c>
-      <c r="AJ13" s="10" t="n">
-        <v>0.0289</v>
-      </c>
-      <c r="AK13" s="8" t="n">
-        <v>18706973</v>
-      </c>
-      <c r="AL13" s="9" t="n">
-        <v>293231.8</v>
-      </c>
-      <c r="AM13" s="10" t="n">
-        <v>0.0298</v>
-      </c>
-      <c r="AN13" s="8" t="n">
-        <v>18706973</v>
-      </c>
-      <c r="AO13" s="9" t="n">
-        <v>297908.55</v>
-      </c>
-      <c r="AP13" s="10" t="n">
-        <v>0.0319</v>
-      </c>
-      <c r="AQ13" s="8" t="n">
-        <v>18706973</v>
-      </c>
-      <c r="AR13" s="9" t="n">
-        <v>294644.18</v>
-      </c>
-      <c r="AS13" s="10" t="n">
-        <v>0.0335</v>
-      </c>
-      <c r="AT13" s="8" t="n">
-        <v>18706973</v>
-      </c>
-      <c r="AU13" s="9" t="n">
-        <v>322779.47</v>
-      </c>
-      <c r="AV13" s="10" t="n">
-        <v>0.036</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Mahindra &amp; Mahindra Limited</t>
+          <t>Axis Bank Limited</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>INE101A01026</t>
+          <t>INE238A01034</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Automobiles</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>14645626</v>
+        <v>33244875</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>432734.31</v>
+        <v>386072.73</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>0.0336</v>
+        <v>0.0299</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>13974725</v>
+        <v>33244875</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>474777.31</v>
+        <v>460075.83</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>0.0354</v>
+        <v>0.0343</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>13974725</v>
+        <v>33244875</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>479584.61</v>
+        <v>455587.77</v>
       </c>
       <c r="L14" s="10" t="n">
-        <v>0.0358</v>
+        <v>0.034</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>13033470</v>
+        <v>33244875</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>483437.47</v>
+        <v>422010.44</v>
       </c>
       <c r="O14" s="10" t="n">
-        <v>0.0363</v>
+        <v>0.0317</v>
       </c>
       <c r="P14" s="8" t="n">
-        <v>12435671</v>
+        <v>33244875</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>467245.47</v>
+        <v>425434.67</v>
       </c>
       <c r="R14" s="10" t="n">
-        <v>0.036</v>
+        <v>0.0328</v>
       </c>
       <c r="S14" s="8" t="n">
-        <v>12435671</v>
+        <v>33244875</v>
       </c>
       <c r="T14" s="9" t="n">
-        <v>433656.72</v>
+        <v>409842.82</v>
       </c>
       <c r="U14" s="10" t="n">
-        <v>0.0345</v>
+        <v>0.0326</v>
       </c>
       <c r="V14" s="8" t="n">
-        <v>12335671</v>
+        <v>33244875</v>
       </c>
       <c r="W14" s="9" t="n">
-        <v>422743.45</v>
+        <v>376199.01</v>
       </c>
       <c r="X14" s="10" t="n">
-        <v>0.0353</v>
+        <v>0.0314</v>
       </c>
       <c r="Y14" s="8" t="n">
-        <v>12335671</v>
+        <v>32644875</v>
       </c>
       <c r="Z14" s="9" t="n">
-        <v>394679.79</v>
+        <v>341204.23</v>
       </c>
       <c r="AA14" s="10" t="n">
-        <v>0.0343</v>
+        <v>0.0297</v>
       </c>
       <c r="AB14" s="8" t="n">
-        <v>12335671</v>
+        <v>30107270</v>
       </c>
       <c r="AC14" s="9" t="n">
-        <v>395123.88</v>
+        <v>321666.07</v>
       </c>
       <c r="AD14" s="10" t="n">
-        <v>0.0349</v>
+        <v>0.0284</v>
       </c>
       <c r="AE14" s="8" t="n">
-        <v>12335671</v>
+        <v>27257270</v>
       </c>
       <c r="AF14" s="9" t="n">
-        <v>392669.08</v>
+        <v>326869.18</v>
       </c>
       <c r="AG14" s="10" t="n">
-        <v>0.0356</v>
+        <v>0.0296</v>
       </c>
       <c r="AH14" s="8" t="n">
-        <v>12231374</v>
+        <v>27257270</v>
       </c>
       <c r="AI14" s="9" t="n">
-        <v>364103.54</v>
+        <v>324961.17</v>
       </c>
       <c r="AJ14" s="10" t="n">
-        <v>0.0351</v>
+        <v>0.0313</v>
       </c>
       <c r="AK14" s="8" t="n">
-        <v>11040212</v>
+        <v>27257270</v>
       </c>
       <c r="AL14" s="9" t="n">
-        <v>323345.73</v>
+        <v>322998.65</v>
       </c>
       <c r="AM14" s="10" t="n">
         <v>0.0328</v>
       </c>
       <c r="AN14" s="8" t="n">
-        <v>10399289</v>
+        <v>27257270</v>
       </c>
       <c r="AO14" s="9" t="n">
-        <v>277224.25</v>
+        <v>300375.12</v>
       </c>
       <c r="AP14" s="10" t="n">
-        <v>0.0297</v>
+        <v>0.0321</v>
       </c>
       <c r="AQ14" s="8" t="n">
-        <v>10068665</v>
+        <v>27257270</v>
       </c>
       <c r="AR14" s="9" t="n">
-        <v>260285.06</v>
+        <v>276811.21</v>
       </c>
       <c r="AS14" s="10" t="n">
-        <v>0.0296</v>
+        <v>0.0315</v>
       </c>
       <c r="AT14" s="8" t="n">
-        <v>9331737</v>
+        <v>27257270</v>
       </c>
       <c r="AU14" s="9" t="n">
-        <v>279004.94</v>
+        <v>268783.94</v>
       </c>
       <c r="AV14" s="10" t="n">
-        <v>0.0311</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Infosys Limited</t>
+          <t>HCL Technologies Limited</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>INE009A01021</t>
+          <t>INE860A01027</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -2614,139 +2590,139 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>26944033</v>
+        <v>29868916</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>336962.08</v>
+        <v>400721.38</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.0261</v>
+        <v>0.0311</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>20693682</v>
+        <v>27771661</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>269038.56</v>
+        <v>385776.14</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>0.02</v>
+        <v>0.0287</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>16509541</v>
+        <v>23460156</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>270921.57</v>
+        <v>397790.41</v>
       </c>
       <c r="L15" s="10" t="n">
-        <v>0.0202</v>
+        <v>0.0297</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>16417936</v>
+        <v>21315882</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>265215.34</v>
+        <v>346020.71</v>
       </c>
       <c r="O15" s="10" t="n">
-        <v>0.0199</v>
+        <v>0.026</v>
       </c>
       <c r="P15" s="8" t="n">
-        <v>17621740</v>
+        <v>19831378</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>274916.77</v>
+        <v>322101.24</v>
       </c>
       <c r="R15" s="10" t="n">
-        <v>0.0212</v>
+        <v>0.0248</v>
       </c>
       <c r="S15" s="8" t="n">
-        <v>9306473</v>
+        <v>18138945</v>
       </c>
       <c r="T15" s="9" t="n">
-        <v>137949.85</v>
+        <v>279611.84</v>
       </c>
       <c r="U15" s="10" t="n">
-        <v>0.011</v>
+        <v>0.0222</v>
       </c>
       <c r="V15" s="8" t="n">
-        <v>9306473</v>
+        <v>18706995</v>
       </c>
       <c r="W15" s="9" t="n">
-        <v>134180.73</v>
+        <v>259110.59</v>
       </c>
       <c r="X15" s="10" t="n">
-        <v>0.0112</v>
+        <v>0.0216</v>
       </c>
       <c r="Y15" s="8" t="n">
-        <v>9306473</v>
+        <v>18706995</v>
       </c>
       <c r="Z15" s="9" t="n">
-        <v>136767.93</v>
+        <v>272149.36</v>
       </c>
       <c r="AA15" s="10" t="n">
-        <v>0.0119</v>
+        <v>0.0237</v>
       </c>
       <c r="AB15" s="8" t="n">
-        <v>9306473</v>
+        <v>18706995</v>
       </c>
       <c r="AC15" s="9" t="n">
-        <v>140434.68</v>
+        <v>274599.98</v>
       </c>
       <c r="AD15" s="10" t="n">
-        <v>0.0124</v>
+        <v>0.0242</v>
       </c>
       <c r="AE15" s="8" t="n">
-        <v>9306473</v>
+        <v>18558995</v>
       </c>
       <c r="AF15" s="9" t="n">
-        <v>149071.08</v>
+        <v>320810.79</v>
       </c>
       <c r="AG15" s="10" t="n">
-        <v>0.0135</v>
+        <v>0.0291</v>
       </c>
       <c r="AH15" s="8" t="n">
-        <v>9306473</v>
+        <v>18341573</v>
       </c>
       <c r="AI15" s="9" t="n">
-        <v>145432.25</v>
+        <v>300178.18</v>
       </c>
       <c r="AJ15" s="10" t="n">
-        <v>0.014</v>
+        <v>0.0289</v>
       </c>
       <c r="AK15" s="8" t="n">
-        <v>9306473</v>
+        <v>18706973</v>
       </c>
       <c r="AL15" s="9" t="n">
-        <v>139606.4</v>
+        <v>293231.8</v>
       </c>
       <c r="AM15" s="10" t="n">
-        <v>0.0142</v>
+        <v>0.0298</v>
       </c>
       <c r="AN15" s="8" t="n">
-        <v>9306473</v>
+        <v>18706973</v>
       </c>
       <c r="AO15" s="9" t="n">
-        <v>146172.12</v>
+        <v>297908.55</v>
       </c>
       <c r="AP15" s="10" t="n">
-        <v>0.0156</v>
+        <v>0.0319</v>
       </c>
       <c r="AQ15" s="8" t="n">
-        <v>9306473</v>
+        <v>18706973</v>
       </c>
       <c r="AR15" s="9" t="n">
-        <v>157065.34</v>
+        <v>294644.18</v>
       </c>
       <c r="AS15" s="10" t="n">
-        <v>0.0178</v>
+        <v>0.0335</v>
       </c>
       <c r="AT15" s="8" t="n">
-        <v>9306473</v>
+        <v>18706973</v>
       </c>
       <c r="AU15" s="9" t="n">
-        <v>174943.08</v>
+        <v>322779.47</v>
       </c>
       <c r="AV15" s="10" t="n">
-        <v>0.0195</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="16">
@@ -2904,12 +2880,12 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Cipla Limited</t>
+          <t>Zydus Lifesciences Limited</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>INE059A01026</t>
+          <t>INE010B01027</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -2918,150 +2894,150 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>13271296</v>
+        <v>18853686</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>162467.21</v>
+        <v>164253.31</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0.0126</v>
+        <v>0.0127</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>12881359</v>
+        <v>18853686</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>173666.48</v>
+        <v>173774.42</v>
       </c>
       <c r="I17" s="10" t="n">
         <v>0.0129</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>12623339</v>
+        <v>18750502</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>167133.01</v>
+        <v>165998.19</v>
       </c>
       <c r="L17" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.0124</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>10989584</v>
+        <v>17903094</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>166085.58</v>
+        <v>163696.94</v>
       </c>
       <c r="O17" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.0123</v>
       </c>
       <c r="P17" s="8" t="n">
-        <v>10765866</v>
+        <v>17405149</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>164857.71</v>
+        <v>164043.53</v>
       </c>
       <c r="R17" s="10" t="n">
-        <v>0.0127</v>
+        <v>0.0126</v>
       </c>
       <c r="S17" s="8" t="n">
-        <v>10173460</v>
+        <v>15759789</v>
       </c>
       <c r="T17" s="9" t="n">
-        <v>152734.15</v>
+        <v>153571.26</v>
       </c>
       <c r="U17" s="10" t="n">
-        <v>0.0121</v>
+        <v>0.0122</v>
       </c>
       <c r="V17" s="8" t="n">
-        <v>9988840</v>
+        <v>15148311</v>
       </c>
       <c r="W17" s="9" t="n">
-        <v>150162.23</v>
+        <v>148741.27</v>
       </c>
       <c r="X17" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.0124</v>
       </c>
       <c r="Y17" s="8" t="n">
-        <v>8991707</v>
+        <v>14786344</v>
       </c>
       <c r="Z17" s="9" t="n">
-        <v>142914.19</v>
+        <v>145061.43</v>
       </c>
       <c r="AA17" s="10" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="AB17" s="8" t="n">
+        <v>14470385</v>
+      </c>
+      <c r="AC17" s="9" t="n">
+        <v>140333.79</v>
+      </c>
+      <c r="AD17" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="AB17" s="8" t="n">
-        <v>9450707</v>
-      </c>
-      <c r="AC17" s="9" t="n">
-        <v>146920.69</v>
-      </c>
-      <c r="AD17" s="10" t="n">
-        <v>0.013</v>
-      </c>
       <c r="AE17" s="8" t="n">
-        <v>9147124</v>
+        <v>14258435</v>
       </c>
       <c r="AF17" s="9" t="n">
-        <v>137746.54</v>
+        <v>141151.38</v>
       </c>
       <c r="AG17" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.0128</v>
       </c>
       <c r="AH17" s="8" t="n">
-        <v>8881919</v>
+        <v>14258435</v>
       </c>
       <c r="AI17" s="9" t="n">
-        <v>130182.29</v>
+        <v>132603.45</v>
       </c>
       <c r="AJ17" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.0128</v>
       </c>
       <c r="AK17" s="8" t="n">
-        <v>7994194</v>
+        <v>13936283</v>
       </c>
       <c r="AL17" s="9" t="n">
-        <v>123918</v>
+        <v>123789.03</v>
       </c>
       <c r="AM17" s="10" t="n">
         <v>0.0126</v>
       </c>
       <c r="AN17" s="8" t="n">
-        <v>7994194</v>
+        <v>13003659</v>
       </c>
       <c r="AO17" s="9" t="n">
-        <v>115292.27</v>
+        <v>115264.43</v>
       </c>
       <c r="AP17" s="10" t="n">
         <v>0.0123</v>
       </c>
       <c r="AQ17" s="8" t="n">
-        <v>7755553</v>
+        <v>11479604</v>
       </c>
       <c r="AR17" s="9" t="n">
-        <v>109159.41</v>
+        <v>100630.21</v>
       </c>
       <c r="AS17" s="10" t="n">
-        <v>0.0124</v>
+        <v>0.0114</v>
       </c>
       <c r="AT17" s="8" t="n">
-        <v>6223549</v>
+        <v>8859127</v>
       </c>
       <c r="AU17" s="9" t="n">
-        <v>92071.17999999999</v>
+        <v>85955.67999999999</v>
       </c>
       <c r="AV17" s="10" t="n">
-        <v>0.0103</v>
+        <v>0.009599999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences Limited</t>
+          <t>Cipla Limited</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>INE010B01027</t>
+          <t>INE059A01026</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -3070,291 +3046,291 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>18853686</v>
+        <v>13271296</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>164253.31</v>
+        <v>162467.21</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>0.0127</v>
+        <v>0.0126</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>18853686</v>
+        <v>12881359</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>173774.42</v>
+        <v>173666.48</v>
       </c>
       <c r="I18" s="10" t="n">
         <v>0.0129</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>18750502</v>
+        <v>12623339</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>165998.19</v>
+        <v>167133.01</v>
       </c>
       <c r="L18" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="M18" s="8" t="n">
+        <v>10989584</v>
+      </c>
+      <c r="N18" s="9" t="n">
+        <v>166085.58</v>
+      </c>
+      <c r="O18" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="P18" s="8" t="n">
+        <v>10765866</v>
+      </c>
+      <c r="Q18" s="9" t="n">
+        <v>164857.71</v>
+      </c>
+      <c r="R18" s="10" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="S18" s="8" t="n">
+        <v>10173460</v>
+      </c>
+      <c r="T18" s="9" t="n">
+        <v>152734.15</v>
+      </c>
+      <c r="U18" s="10" t="n">
+        <v>0.0121</v>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v>9988840</v>
+      </c>
+      <c r="W18" s="9" t="n">
+        <v>150162.23</v>
+      </c>
+      <c r="X18" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="Y18" s="8" t="n">
+        <v>8991707</v>
+      </c>
+      <c r="Z18" s="9" t="n">
+        <v>142914.19</v>
+      </c>
+      <c r="AA18" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="M18" s="8" t="n">
-        <v>17903094</v>
-      </c>
-      <c r="N18" s="9" t="n">
-        <v>163696.94</v>
-      </c>
-      <c r="O18" s="10" t="n">
-        <v>0.0123</v>
-      </c>
-      <c r="P18" s="8" t="n">
-        <v>17405149</v>
-      </c>
-      <c r="Q18" s="9" t="n">
-        <v>164043.53</v>
-      </c>
-      <c r="R18" s="10" t="n">
-        <v>0.0126</v>
-      </c>
-      <c r="S18" s="8" t="n">
-        <v>15759789</v>
-      </c>
-      <c r="T18" s="9" t="n">
-        <v>153571.26</v>
-      </c>
-      <c r="U18" s="10" t="n">
-        <v>0.0122</v>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v>15148311</v>
-      </c>
-      <c r="W18" s="9" t="n">
-        <v>148741.27</v>
-      </c>
-      <c r="X18" s="10" t="n">
-        <v>0.0124</v>
-      </c>
-      <c r="Y18" s="8" t="n">
-        <v>14786344</v>
-      </c>
-      <c r="Z18" s="9" t="n">
-        <v>145061.43</v>
-      </c>
-      <c r="AA18" s="10" t="n">
-        <v>0.0126</v>
-      </c>
       <c r="AB18" s="8" t="n">
-        <v>14470385</v>
+        <v>9450707</v>
       </c>
       <c r="AC18" s="9" t="n">
-        <v>140333.79</v>
+        <v>146920.69</v>
       </c>
       <c r="AD18" s="10" t="n">
-        <v>0.0124</v>
+        <v>0.013</v>
       </c>
       <c r="AE18" s="8" t="n">
-        <v>14258435</v>
+        <v>9147124</v>
       </c>
       <c r="AF18" s="9" t="n">
-        <v>141151.38</v>
+        <v>137746.54</v>
       </c>
       <c r="AG18" s="10" t="n">
-        <v>0.0128</v>
+        <v>0.0125</v>
       </c>
       <c r="AH18" s="8" t="n">
-        <v>14258435</v>
+        <v>8881919</v>
       </c>
       <c r="AI18" s="9" t="n">
-        <v>132603.45</v>
+        <v>130182.29</v>
       </c>
       <c r="AJ18" s="10" t="n">
-        <v>0.0128</v>
+        <v>0.0125</v>
       </c>
       <c r="AK18" s="8" t="n">
-        <v>13936283</v>
+        <v>7994194</v>
       </c>
       <c r="AL18" s="9" t="n">
-        <v>123789.03</v>
+        <v>123918</v>
       </c>
       <c r="AM18" s="10" t="n">
         <v>0.0126</v>
       </c>
       <c r="AN18" s="8" t="n">
-        <v>13003659</v>
+        <v>7994194</v>
       </c>
       <c r="AO18" s="9" t="n">
-        <v>115264.43</v>
+        <v>115292.27</v>
       </c>
       <c r="AP18" s="10" t="n">
         <v>0.0123</v>
       </c>
       <c r="AQ18" s="8" t="n">
-        <v>11479604</v>
+        <v>7755553</v>
       </c>
       <c r="AR18" s="9" t="n">
-        <v>100630.21</v>
+        <v>109159.41</v>
       </c>
       <c r="AS18" s="10" t="n">
-        <v>0.0114</v>
+        <v>0.0124</v>
       </c>
       <c r="AT18" s="8" t="n">
-        <v>8859127</v>
+        <v>6223549</v>
       </c>
       <c r="AU18" s="9" t="n">
-        <v>85955.67999999999</v>
+        <v>92071.17999999999</v>
       </c>
       <c r="AV18" s="10" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0103</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Balkrishna Industries Limited</t>
+          <t>Infosys Limited</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>INE787D01026</t>
+          <t>INE009A01021</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Auto Components</t>
+          <t>IT - Software</t>
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>2274074</v>
+        <v>26944033</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>47368.96</v>
+        <v>336962.08</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>0.0037</v>
+        <v>0.0261</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>2906065</v>
+        <v>20693682</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>69277.67999999999</v>
+        <v>269038.56</v>
       </c>
       <c r="I19" s="10" t="n">
-        <v>0.0052</v>
+        <v>0.02</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>4189074</v>
+        <v>16509541</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>96591.67</v>
+        <v>270921.57</v>
       </c>
       <c r="L19" s="10" t="n">
-        <v>0.0072</v>
+        <v>0.0202</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>4189074</v>
+        <v>16417936</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>97173.95</v>
+        <v>265215.34</v>
       </c>
       <c r="O19" s="10" t="n">
-        <v>0.0073</v>
+        <v>0.0199</v>
       </c>
       <c r="P19" s="8" t="n">
-        <v>4189074</v>
+        <v>17621740</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>96721.53</v>
+        <v>274916.77</v>
       </c>
       <c r="R19" s="10" t="n">
-        <v>0.0075</v>
+        <v>0.0212</v>
       </c>
       <c r="S19" s="8" t="n">
-        <v>4189074</v>
+        <v>9306473</v>
       </c>
       <c r="T19" s="9" t="n">
-        <v>95502.50999999999</v>
+        <v>137949.85</v>
       </c>
       <c r="U19" s="10" t="n">
-        <v>0.0076</v>
+        <v>0.011</v>
       </c>
       <c r="V19" s="8" t="n">
-        <v>4189074</v>
+        <v>9306473</v>
       </c>
       <c r="W19" s="9" t="n">
-        <v>96130.87</v>
+        <v>134180.73</v>
       </c>
       <c r="X19" s="10" t="n">
-        <v>0.008</v>
+        <v>0.0112</v>
       </c>
       <c r="Y19" s="8" t="n">
-        <v>4189074</v>
+        <v>9306473</v>
       </c>
       <c r="Z19" s="9" t="n">
-        <v>95904.66</v>
+        <v>136767.93</v>
       </c>
       <c r="AA19" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.0119</v>
       </c>
       <c r="AB19" s="8" t="n">
-        <v>4189074</v>
+        <v>9306473</v>
       </c>
       <c r="AC19" s="9" t="n">
-        <v>112108</v>
+        <v>140434.68</v>
       </c>
       <c r="AD19" s="10" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0124</v>
       </c>
       <c r="AE19" s="8" t="n">
-        <v>4189074</v>
+        <v>9306473</v>
       </c>
       <c r="AF19" s="9" t="n">
-        <v>102435.43</v>
+        <v>149071.08</v>
       </c>
       <c r="AG19" s="10" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0135</v>
       </c>
       <c r="AH19" s="8" t="n">
-        <v>4189074</v>
+        <v>9306473</v>
       </c>
       <c r="AI19" s="9" t="n">
-        <v>103562.29</v>
+        <v>145432.25</v>
       </c>
       <c r="AJ19" s="10" t="n">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
       <c r="AK19" s="8" t="n">
-        <v>4189074</v>
+        <v>9306473</v>
       </c>
       <c r="AL19" s="9" t="n">
-        <v>112061.92</v>
+        <v>139606.4</v>
       </c>
       <c r="AM19" s="10" t="n">
-        <v>0.0114</v>
+        <v>0.0142</v>
       </c>
       <c r="AN19" s="8" t="n">
-        <v>4189074</v>
+        <v>9306473</v>
       </c>
       <c r="AO19" s="9" t="n">
-        <v>107022.46</v>
+        <v>146172.12</v>
       </c>
       <c r="AP19" s="10" t="n">
-        <v>0.0115</v>
+        <v>0.0156</v>
       </c>
       <c r="AQ19" s="8" t="n">
-        <v>4189074</v>
+        <v>9306473</v>
       </c>
       <c r="AR19" s="9" t="n">
-        <v>109571.51</v>
+        <v>157065.34</v>
       </c>
       <c r="AS19" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.0178</v>
       </c>
       <c r="AT19" s="8" t="n">
-        <v>4189074</v>
+        <v>9306473</v>
       </c>
       <c r="AU19" s="9" t="n">
-        <v>116089.71</v>
+        <v>174943.08</v>
       </c>
       <c r="AV19" s="10" t="n">
-        <v>0.0129</v>
+        <v>0.0195</v>
       </c>
     </row>
     <row r="20">
@@ -3512,115 +3488,169 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Motilal Oswal Financial Services Limited</t>
+          <t>Balkrishna Industries Limited</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>INE338I01027</t>
+          <t>INE787D01026</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="10" t="n"/>
-      <c r="G21" s="8" t="n"/>
-      <c r="H21" s="9" t="n"/>
-      <c r="I21" s="10" t="n"/>
-      <c r="J21" s="8" t="n"/>
-      <c r="K21" s="9" t="n"/>
-      <c r="L21" s="10" t="n"/>
-      <c r="M21" s="8" t="n"/>
-      <c r="N21" s="9" t="n"/>
-      <c r="O21" s="10" t="n"/>
-      <c r="P21" s="8" t="n"/>
-      <c r="Q21" s="9" t="n"/>
-      <c r="R21" s="10" t="n"/>
-      <c r="S21" s="8" t="n"/>
-      <c r="T21" s="9" t="n"/>
-      <c r="U21" s="10" t="n"/>
-      <c r="V21" s="8" t="n"/>
-      <c r="W21" s="9" t="n"/>
-      <c r="X21" s="10" t="n"/>
-      <c r="Y21" s="8" t="n"/>
-      <c r="Z21" s="9" t="n"/>
-      <c r="AA21" s="10" t="n"/>
-      <c r="AB21" s="8" t="n"/>
-      <c r="AC21" s="9" t="n"/>
-      <c r="AD21" s="10" t="n"/>
+          <t>Auto Components</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>2274074</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>47368.96</v>
+      </c>
+      <c r="F21" s="10" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>2906065</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>69277.67999999999</v>
+      </c>
+      <c r="I21" s="10" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="J21" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="K21" s="9" t="n">
+        <v>96591.67</v>
+      </c>
+      <c r="L21" s="10" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="M21" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="N21" s="9" t="n">
+        <v>97173.95</v>
+      </c>
+      <c r="O21" s="10" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="P21" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="Q21" s="9" t="n">
+        <v>96721.53</v>
+      </c>
+      <c r="R21" s="10" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="S21" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="T21" s="9" t="n">
+        <v>95502.50999999999</v>
+      </c>
+      <c r="U21" s="10" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="W21" s="9" t="n">
+        <v>96130.87</v>
+      </c>
+      <c r="X21" s="10" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="Y21" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="Z21" s="9" t="n">
+        <v>95904.66</v>
+      </c>
+      <c r="AA21" s="10" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="AB21" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="AC21" s="9" t="n">
+        <v>112108</v>
+      </c>
+      <c r="AD21" s="10" t="n">
+        <v>0.009900000000000001</v>
+      </c>
       <c r="AE21" s="8" t="n">
-        <v>591805</v>
+        <v>4189074</v>
       </c>
       <c r="AF21" s="9" t="n">
-        <v>5149</v>
+        <v>102435.43</v>
       </c>
       <c r="AG21" s="10" t="n">
-        <v>0.0005</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="AH21" s="8" t="n">
-        <v>5392631</v>
+        <v>4189074</v>
       </c>
       <c r="AI21" s="9" t="n">
-        <v>43674.92</v>
+        <v>103562.29</v>
       </c>
       <c r="AJ21" s="10" t="n">
-        <v>0.0042</v>
+        <v>0.01</v>
       </c>
       <c r="AK21" s="8" t="n">
-        <v>8585949</v>
+        <v>4189074</v>
       </c>
       <c r="AL21" s="9" t="n">
-        <v>56044.78</v>
+        <v>112061.92</v>
       </c>
       <c r="AM21" s="10" t="n">
-        <v>0.0057</v>
+        <v>0.0114</v>
       </c>
       <c r="AN21" s="8" t="n">
-        <v>10913294</v>
+        <v>4189074</v>
       </c>
       <c r="AO21" s="9" t="n">
-        <v>67154.95</v>
+        <v>107022.46</v>
       </c>
       <c r="AP21" s="10" t="n">
-        <v>0.0072</v>
+        <v>0.0115</v>
       </c>
       <c r="AQ21" s="8" t="n">
-        <v>12053879</v>
+        <v>4189074</v>
       </c>
       <c r="AR21" s="9" t="n">
-        <v>70937.08</v>
+        <v>109571.51</v>
       </c>
       <c r="AS21" s="10" t="n">
-        <v>0.0081</v>
+        <v>0.0125</v>
       </c>
       <c r="AT21" s="8" t="n">
-        <v>12053879</v>
+        <v>4189074</v>
       </c>
       <c r="AU21" s="9" t="n">
-        <v>76801.28999999999</v>
+        <v>116089.71</v>
       </c>
       <c r="AV21" s="10" t="n">
-        <v>0.0086</v>
+        <v>0.0129</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Multi Commodity Exchange of India Limited</t>
+          <t>Zydus Wellness Limited</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>INE745G01035</t>
+          <t>INE768C01010</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D22" s="8" t="n"/>
@@ -3632,1487 +3662,1457 @@
       <c r="J22" s="8" t="n"/>
       <c r="K22" s="9" t="n"/>
       <c r="L22" s="10" t="n"/>
-      <c r="M22" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="N22" s="9" t="n">
-        <v>88833.99000000001</v>
-      </c>
-      <c r="O22" s="10" t="n">
-        <v>0.0067</v>
-      </c>
-      <c r="P22" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="Q22" s="9" t="n">
-        <v>80358.22</v>
-      </c>
-      <c r="R22" s="10" t="n">
-        <v>0.0062</v>
-      </c>
-      <c r="S22" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="T22" s="9" t="n">
-        <v>73737.16</v>
-      </c>
-      <c r="U22" s="10" t="n">
-        <v>0.0059</v>
-      </c>
-      <c r="V22" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="W22" s="9" t="n">
-        <v>62190.17</v>
-      </c>
-      <c r="X22" s="10" t="n">
-        <v>0.0052</v>
-      </c>
+      <c r="M22" s="8" t="n"/>
+      <c r="N22" s="9" t="n"/>
+      <c r="O22" s="10" t="n"/>
+      <c r="P22" s="8" t="n"/>
+      <c r="Q22" s="9" t="n"/>
+      <c r="R22" s="10" t="n"/>
+      <c r="S22" s="8" t="n"/>
+      <c r="T22" s="9" t="n"/>
+      <c r="U22" s="10" t="n"/>
+      <c r="V22" s="8" t="n"/>
+      <c r="W22" s="9" t="n"/>
+      <c r="X22" s="10" t="n"/>
       <c r="Y22" s="8" t="n">
-        <v>797719</v>
+        <v>4400000</v>
       </c>
       <c r="Z22" s="9" t="n">
-        <v>58951.43</v>
+        <v>88822.8</v>
       </c>
       <c r="AA22" s="10" t="n">
-        <v>0.0051</v>
+        <v>0.0077</v>
       </c>
       <c r="AB22" s="8" t="n">
-        <v>797719</v>
+        <v>4400000</v>
       </c>
       <c r="AC22" s="9" t="n">
-        <v>61368.52</v>
+        <v>89280.39999999999</v>
       </c>
       <c r="AD22" s="10" t="n">
-        <v>0.0054</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="AE22" s="8" t="n">
-        <v>797719</v>
+        <v>4400000</v>
       </c>
       <c r="AF22" s="9" t="n">
-        <v>71347.99000000001</v>
+        <v>89020.8</v>
       </c>
       <c r="AG22" s="10" t="n">
-        <v>0.0065</v>
-      </c>
-      <c r="AH22" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="AI22" s="9" t="n">
-        <v>52665.41</v>
-      </c>
-      <c r="AJ22" s="10" t="n">
-        <v>0.0051</v>
-      </c>
-      <c r="AK22" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="AL22" s="9" t="n">
-        <v>48884.22</v>
-      </c>
-      <c r="AM22" s="10" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="AN22" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="AO22" s="9" t="n">
-        <v>42372.84</v>
-      </c>
-      <c r="AP22" s="10" t="n">
-        <v>0.0045</v>
-      </c>
-      <c r="AQ22" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="AR22" s="9" t="n">
-        <v>39819.34</v>
-      </c>
-      <c r="AS22" s="10" t="n">
-        <v>0.0045</v>
-      </c>
-      <c r="AT22" s="8" t="n">
-        <v>882136</v>
-      </c>
-      <c r="AU22" s="9" t="n">
-        <v>50572.42</v>
-      </c>
-      <c r="AV22" s="10" t="n">
-        <v>0.0056</v>
-      </c>
+        <v>0.0081</v>
+      </c>
+      <c r="AH22" s="8" t="n"/>
+      <c r="AI22" s="9" t="n"/>
+      <c r="AJ22" s="10" t="n"/>
+      <c r="AK22" s="8" t="n"/>
+      <c r="AL22" s="9" t="n"/>
+      <c r="AM22" s="10" t="n"/>
+      <c r="AN22" s="8" t="n"/>
+      <c r="AO22" s="9" t="n"/>
+      <c r="AP22" s="10" t="n"/>
+      <c r="AQ22" s="8" t="n"/>
+      <c r="AR22" s="9" t="n"/>
+      <c r="AS22" s="10" t="n"/>
+      <c r="AT22" s="8" t="n"/>
+      <c r="AU22" s="9" t="n"/>
+      <c r="AV22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Narayana Hrudayalaya Limited</t>
+          <t>Multi Commodity Exchange of India Limited</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>INE410P01011</t>
+          <t>INE745G01035</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Healthcare Services</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="n">
-        <v>1995914</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>32040.41</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="G23" s="8" t="n">
-        <v>1995914</v>
-      </c>
-      <c r="H23" s="9" t="n">
-        <v>36543.19</v>
-      </c>
-      <c r="I23" s="10" t="n">
-        <v>0.0027</v>
-      </c>
-      <c r="J23" s="8" t="n">
-        <v>1995914</v>
-      </c>
-      <c r="K23" s="9" t="n">
-        <v>35285.76</v>
-      </c>
-      <c r="L23" s="10" t="n">
-        <v>0.0026</v>
-      </c>
+          <t>Capital Markets</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="10" t="n"/>
+      <c r="G23" s="8" t="n"/>
+      <c r="H23" s="9" t="n"/>
+      <c r="I23" s="10" t="n"/>
+      <c r="J23" s="8" t="n"/>
+      <c r="K23" s="9" t="n"/>
+      <c r="L23" s="10" t="n"/>
       <c r="M23" s="8" t="n">
-        <v>1995914</v>
+        <v>797719</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>37762.69</v>
+        <v>88833.99000000001</v>
       </c>
       <c r="O23" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.0067</v>
       </c>
       <c r="P23" s="8" t="n">
-        <v>1995914</v>
+        <v>797719</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>38830.51</v>
+        <v>80358.22</v>
       </c>
       <c r="R23" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0062</v>
       </c>
       <c r="S23" s="8" t="n">
-        <v>1995914</v>
+        <v>797719</v>
       </c>
       <c r="T23" s="9" t="n">
-        <v>35076.19</v>
+        <v>73737.16</v>
       </c>
       <c r="U23" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.0059</v>
       </c>
       <c r="V23" s="8" t="n">
-        <v>1995914</v>
+        <v>797719</v>
       </c>
       <c r="W23" s="9" t="n">
-        <v>34681</v>
+        <v>62190.17</v>
       </c>
       <c r="X23" s="10" t="n">
-        <v>0.0029</v>
+        <v>0.0052</v>
       </c>
       <c r="Y23" s="8" t="n">
-        <v>1995914</v>
+        <v>797719</v>
       </c>
       <c r="Z23" s="9" t="n">
-        <v>35004.34</v>
+        <v>58951.43</v>
       </c>
       <c r="AA23" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0051</v>
       </c>
       <c r="AB23" s="8" t="n">
-        <v>1995914</v>
+        <v>797719</v>
       </c>
       <c r="AC23" s="9" t="n">
-        <v>38225.74</v>
+        <v>61368.52</v>
       </c>
       <c r="AD23" s="10" t="n">
-        <v>0.0034</v>
+        <v>0.0054</v>
       </c>
       <c r="AE23" s="8" t="n">
-        <v>1995914</v>
+        <v>797719</v>
       </c>
       <c r="AF23" s="9" t="n">
-        <v>43319.32</v>
+        <v>71347.99000000001</v>
       </c>
       <c r="AG23" s="10" t="n">
-        <v>0.0039</v>
+        <v>0.0065</v>
       </c>
       <c r="AH23" s="8" t="n">
-        <v>1995914</v>
+        <v>797719</v>
       </c>
       <c r="AI23" s="9" t="n">
-        <v>34806.74</v>
+        <v>52665.41</v>
       </c>
       <c r="AJ23" s="10" t="n">
-        <v>0.0034</v>
+        <v>0.0051</v>
       </c>
       <c r="AK23" s="8" t="n">
-        <v>1995914</v>
+        <v>797719</v>
       </c>
       <c r="AL23" s="9" t="n">
-        <v>35138.07</v>
+        <v>48884.22</v>
       </c>
       <c r="AM23" s="10" t="n">
-        <v>0.0036</v>
+        <v>0.005</v>
       </c>
       <c r="AN23" s="8" t="n">
-        <v>1995914</v>
+        <v>797719</v>
       </c>
       <c r="AO23" s="9" t="n">
-        <v>33771.86</v>
+        <v>42372.84</v>
       </c>
       <c r="AP23" s="10" t="n">
-        <v>0.0036</v>
+        <v>0.0045</v>
       </c>
       <c r="AQ23" s="8" t="n">
-        <v>1995914</v>
+        <v>797719</v>
       </c>
       <c r="AR23" s="9" t="n">
-        <v>28830.98</v>
+        <v>39819.34</v>
       </c>
       <c r="AS23" s="10" t="n">
-        <v>0.0033</v>
+        <v>0.0045</v>
       </c>
       <c r="AT23" s="8" t="n">
-        <v>1995914</v>
+        <v>882136</v>
       </c>
       <c r="AU23" s="9" t="n">
-        <v>27686.32</v>
+        <v>50572.42</v>
       </c>
       <c r="AV23" s="10" t="n">
-        <v>0.0031</v>
+        <v>0.0056</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>IPCA Laboratories Limited</t>
+          <t>EID Parry India Limited</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>INE571A01038</t>
+          <t>INE126A01031</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Pharmaceuticals &amp; Biotechnology</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="10" t="n"/>
-      <c r="G24" s="8" t="n"/>
-      <c r="H24" s="9" t="n"/>
-      <c r="I24" s="10" t="n"/>
-      <c r="J24" s="8" t="n"/>
-      <c r="K24" s="9" t="n"/>
-      <c r="L24" s="10" t="n"/>
-      <c r="M24" s="8" t="n"/>
-      <c r="N24" s="9" t="n"/>
-      <c r="O24" s="10" t="n"/>
-      <c r="P24" s="8" t="n"/>
-      <c r="Q24" s="9" t="n"/>
-      <c r="R24" s="10" t="n"/>
-      <c r="S24" s="8" t="n"/>
-      <c r="T24" s="9" t="n"/>
-      <c r="U24" s="10" t="n"/>
-      <c r="V24" s="8" t="n"/>
-      <c r="W24" s="9" t="n"/>
-      <c r="X24" s="10" t="n"/>
+          <t>Food Products</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>7394472</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>57344.13</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>7394472</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>63976.97</v>
+      </c>
+      <c r="I24" s="10" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="J24" s="8" t="n">
+        <v>7362903</v>
+      </c>
+      <c r="K24" s="9" t="n">
+        <v>67966.96000000001</v>
+      </c>
+      <c r="L24" s="10" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="M24" s="8" t="n">
+        <v>6180145</v>
+      </c>
+      <c r="N24" s="9" t="n">
+        <v>63945.96</v>
+      </c>
+      <c r="O24" s="10" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="P24" s="8" t="n">
+        <v>5842830</v>
+      </c>
+      <c r="Q24" s="9" t="n">
+        <v>60233.73</v>
+      </c>
+      <c r="R24" s="10" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="S24" s="8" t="n">
+        <v>5528341</v>
+      </c>
+      <c r="T24" s="9" t="n">
+        <v>59285.93</v>
+      </c>
+      <c r="U24" s="10" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v>4996218</v>
+      </c>
+      <c r="W24" s="9" t="n">
+        <v>51236.22</v>
+      </c>
+      <c r="X24" s="10" t="n">
+        <v>0.0043</v>
+      </c>
       <c r="Y24" s="8" t="n">
-        <v>218075</v>
+        <v>4433570</v>
       </c>
       <c r="Z24" s="9" t="n">
-        <v>3019.03</v>
+        <v>49913.13</v>
       </c>
       <c r="AA24" s="10" t="n">
-        <v>0.0003</v>
+        <v>0.0043</v>
       </c>
       <c r="AB24" s="8" t="n">
-        <v>566216</v>
+        <v>3997165</v>
       </c>
       <c r="AC24" s="9" t="n">
-        <v>8345.459999999999</v>
+        <v>49305.03</v>
       </c>
       <c r="AD24" s="10" t="n">
-        <v>0.0007</v>
+        <v>0.0044</v>
       </c>
       <c r="AE24" s="8" t="n">
-        <v>1311557</v>
+        <v>3516819</v>
       </c>
       <c r="AF24" s="9" t="n">
-        <v>18228.02</v>
+        <v>39036.69</v>
       </c>
       <c r="AG24" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.0035</v>
       </c>
       <c r="AH24" s="8" t="n">
-        <v>1641095</v>
+        <v>3243008</v>
       </c>
       <c r="AI24" s="9" t="n">
-        <v>23382.32</v>
+        <v>30813.44</v>
       </c>
       <c r="AJ24" s="10" t="n">
-        <v>0.0023</v>
+        <v>0.003</v>
       </c>
       <c r="AK24" s="8" t="n">
-        <v>1857217</v>
+        <v>2988209</v>
       </c>
       <c r="AL24" s="9" t="n">
-        <v>26023.32</v>
+        <v>24424.13</v>
       </c>
       <c r="AM24" s="10" t="n">
-        <v>0.0026</v>
+        <v>0.0025</v>
       </c>
       <c r="AN24" s="8" t="n">
-        <v>1926988</v>
+        <v>2843265</v>
       </c>
       <c r="AO24" s="9" t="n">
-        <v>28941.43</v>
+        <v>22336.69</v>
       </c>
       <c r="AP24" s="10" t="n">
-        <v>0.0031</v>
+        <v>0.0024</v>
       </c>
       <c r="AQ24" s="8" t="n">
-        <v>1926988</v>
+        <v>2609056</v>
       </c>
       <c r="AR24" s="9" t="n">
-        <v>26117.43</v>
+        <v>17326.74</v>
       </c>
       <c r="AS24" s="10" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="AT24" s="8" t="n">
-        <v>2246361</v>
+        <v>2259531</v>
       </c>
       <c r="AU24" s="9" t="n">
-        <v>32421.73</v>
+        <v>18525.89</v>
       </c>
       <c r="AV24" s="10" t="n">
-        <v>0.0036</v>
+        <v>0.0021</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Central Depository Services (India) Limited</t>
+          <t>Narayana Hrudayalaya Limited</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>INE736A01011</t>
+          <t>INE410P01011</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Healthcare Services</t>
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>2264603</v>
+        <v>1995914</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>25349.97</v>
+        <v>32040.41</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>0.002</v>
+        <v>0.0025</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>2264603</v>
+        <v>1995914</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>28810.28</v>
+        <v>36543.19</v>
       </c>
       <c r="I25" s="10" t="n">
-        <v>0.0021</v>
+        <v>0.0027</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>2264603</v>
+        <v>1995914</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>29897.29</v>
+        <v>35285.76</v>
       </c>
       <c r="L25" s="10" t="n">
-        <v>0.0022</v>
+        <v>0.0026</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>2264603</v>
+        <v>1995914</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>32691.81</v>
+        <v>37762.69</v>
       </c>
       <c r="O25" s="10" t="n">
-        <v>0.0025</v>
+        <v>0.0028</v>
       </c>
       <c r="P25" s="8" t="n">
-        <v>2264603</v>
+        <v>1995914</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>36623.16</v>
+        <v>38830.51</v>
       </c>
       <c r="R25" s="10" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S25" s="8" t="n">
+        <v>1995914</v>
+      </c>
+      <c r="T25" s="9" t="n">
+        <v>35076.19</v>
+      </c>
+      <c r="U25" s="10" t="n">
         <v>0.0028</v>
       </c>
-      <c r="S25" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="T25" s="9" t="n">
-        <v>35943.78</v>
-      </c>
-      <c r="U25" s="10" t="n">
+      <c r="V25" s="8" t="n">
+        <v>1995914</v>
+      </c>
+      <c r="W25" s="9" t="n">
+        <v>34681</v>
+      </c>
+      <c r="X25" s="10" t="n">
         <v>0.0029</v>
       </c>
-      <c r="V25" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="W25" s="9" t="n">
-        <v>33031.5</v>
-      </c>
-      <c r="X25" s="10" t="n">
-        <v>0.0028</v>
-      </c>
       <c r="Y25" s="8" t="n">
-        <v>2264603</v>
+        <v>1995914</v>
       </c>
       <c r="Z25" s="9" t="n">
-        <v>32257.01</v>
+        <v>35004.34</v>
       </c>
       <c r="AA25" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.003</v>
       </c>
       <c r="AB25" s="8" t="n">
-        <v>2264603</v>
+        <v>1995914</v>
       </c>
       <c r="AC25" s="9" t="n">
-        <v>33534.24</v>
+        <v>38225.74</v>
       </c>
       <c r="AD25" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0034</v>
       </c>
       <c r="AE25" s="8" t="n">
-        <v>2264603</v>
+        <v>1995914</v>
       </c>
       <c r="AF25" s="9" t="n">
-        <v>40626.98</v>
+        <v>43319.32</v>
       </c>
       <c r="AG25" s="10" t="n">
-        <v>0.0037</v>
+        <v>0.0039</v>
       </c>
       <c r="AH25" s="8" t="n">
-        <v>2264603</v>
+        <v>1995914</v>
       </c>
       <c r="AI25" s="9" t="n">
-        <v>34641.63</v>
+        <v>34806.74</v>
       </c>
       <c r="AJ25" s="10" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="AK25" s="8" t="n">
+        <v>1995914</v>
+      </c>
+      <c r="AL25" s="9" t="n">
+        <v>35138.07</v>
+      </c>
+      <c r="AM25" s="10" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="AN25" s="8" t="n">
+        <v>1995914</v>
+      </c>
+      <c r="AO25" s="9" t="n">
+        <v>33771.86</v>
+      </c>
+      <c r="AP25" s="10" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="AQ25" s="8" t="n">
+        <v>1995914</v>
+      </c>
+      <c r="AR25" s="9" t="n">
+        <v>28830.98</v>
+      </c>
+      <c r="AS25" s="10" t="n">
         <v>0.0033</v>
       </c>
-      <c r="AK25" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="AL25" s="9" t="n">
-        <v>29892.76</v>
-      </c>
-      <c r="AM25" s="10" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="AN25" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="AO25" s="9" t="n">
-        <v>27629.29</v>
-      </c>
-      <c r="AP25" s="10" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="AQ25" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="AR25" s="9" t="n">
-        <v>25089.54</v>
-      </c>
-      <c r="AS25" s="10" t="n">
-        <v>0.0029</v>
-      </c>
       <c r="AT25" s="8" t="n">
-        <v>2264603</v>
+        <v>1995914</v>
       </c>
       <c r="AU25" s="9" t="n">
-        <v>29659.51</v>
+        <v>27686.32</v>
       </c>
       <c r="AV25" s="10" t="n">
-        <v>0.0033</v>
+        <v>0.0031</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>EID Parry India Limited</t>
+          <t>Central Depository Services (India)</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>INE126A01031</t>
+          <t>INE736A01011</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>7394472</v>
+        <v>2264603</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>57344.13</v>
+        <v>25349.97</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>0.0044</v>
+        <v>0.002</v>
       </c>
       <c r="G26" s="8" t="n">
-        <v>7394472</v>
+        <v>2264603</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>63976.97</v>
+        <v>28810.28</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>0.0048</v>
+        <v>0.0021</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>7362903</v>
+        <v>2264603</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>67966.96000000001</v>
+        <v>29897.29</v>
       </c>
       <c r="L26" s="10" t="n">
-        <v>0.0051</v>
+        <v>0.0022</v>
       </c>
       <c r="M26" s="8" t="n">
-        <v>6180145</v>
+        <v>2264603</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>63945.96</v>
+        <v>32691.81</v>
       </c>
       <c r="O26" s="10" t="n">
-        <v>0.0048</v>
+        <v>0.0025</v>
       </c>
       <c r="P26" s="8" t="n">
-        <v>5842830</v>
+        <v>2264603</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>60233.73</v>
+        <v>36623.16</v>
       </c>
       <c r="R26" s="10" t="n">
-        <v>0.0046</v>
+        <v>0.0028</v>
       </c>
       <c r="S26" s="8" t="n">
-        <v>5528341</v>
+        <v>2264603</v>
       </c>
       <c r="T26" s="9" t="n">
-        <v>59285.93</v>
+        <v>35943.78</v>
       </c>
       <c r="U26" s="10" t="n">
-        <v>0.0047</v>
+        <v>0.0029</v>
       </c>
       <c r="V26" s="8" t="n">
-        <v>4996218</v>
+        <v>2264603</v>
       </c>
       <c r="W26" s="9" t="n">
-        <v>51236.22</v>
+        <v>33031.5</v>
       </c>
       <c r="X26" s="10" t="n">
-        <v>0.0043</v>
+        <v>0.0028</v>
       </c>
       <c r="Y26" s="8" t="n">
-        <v>4433570</v>
+        <v>2264603</v>
       </c>
       <c r="Z26" s="9" t="n">
-        <v>49913.13</v>
+        <v>32257.01</v>
       </c>
       <c r="AA26" s="10" t="n">
-        <v>0.0043</v>
+        <v>0.0028</v>
       </c>
       <c r="AB26" s="8" t="n">
-        <v>3997165</v>
+        <v>2264603</v>
       </c>
       <c r="AC26" s="9" t="n">
-        <v>49305.03</v>
+        <v>33534.24</v>
       </c>
       <c r="AD26" s="10" t="n">
-        <v>0.0044</v>
+        <v>0.003</v>
       </c>
       <c r="AE26" s="8" t="n">
-        <v>3516819</v>
+        <v>2264603</v>
       </c>
       <c r="AF26" s="9" t="n">
-        <v>39036.69</v>
+        <v>40626.98</v>
       </c>
       <c r="AG26" s="10" t="n">
-        <v>0.0035</v>
+        <v>0.0037</v>
       </c>
       <c r="AH26" s="8" t="n">
-        <v>3243008</v>
+        <v>2264603</v>
       </c>
       <c r="AI26" s="9" t="n">
-        <v>30813.44</v>
+        <v>34641.63</v>
       </c>
       <c r="AJ26" s="10" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="AK26" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="AL26" s="9" t="n">
+        <v>29892.76</v>
+      </c>
+      <c r="AM26" s="10" t="n">
         <v>0.003</v>
       </c>
-      <c r="AK26" s="8" t="n">
-        <v>2988209</v>
-      </c>
-      <c r="AL26" s="9" t="n">
-        <v>24424.13</v>
-      </c>
-      <c r="AM26" s="10" t="n">
-        <v>0.0025</v>
-      </c>
       <c r="AN26" s="8" t="n">
-        <v>2843265</v>
+        <v>2264603</v>
       </c>
       <c r="AO26" s="9" t="n">
-        <v>22336.69</v>
+        <v>27629.29</v>
       </c>
       <c r="AP26" s="10" t="n">
-        <v>0.0024</v>
+        <v>0.003</v>
       </c>
       <c r="AQ26" s="8" t="n">
-        <v>2609056</v>
+        <v>2264603</v>
       </c>
       <c r="AR26" s="9" t="n">
-        <v>17326.74</v>
+        <v>25089.54</v>
       </c>
       <c r="AS26" s="10" t="n">
-        <v>0.002</v>
+        <v>0.0029</v>
       </c>
       <c r="AT26" s="8" t="n">
-        <v>2259531</v>
+        <v>2264603</v>
       </c>
       <c r="AU26" s="9" t="n">
-        <v>18525.89</v>
+        <v>29659.51</v>
       </c>
       <c r="AV26" s="10" t="n">
-        <v>0.0021</v>
+        <v>0.0033</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>ITC Hotels Limited</t>
+          <t>ICRA Limited</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>INE379A01028</t>
+          <t>INE725G01011</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Leisure Services</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="9" t="n"/>
-      <c r="F27" s="10" t="n"/>
-      <c r="G27" s="8" t="n"/>
-      <c r="H27" s="9" t="n"/>
-      <c r="I27" s="10" t="n"/>
-      <c r="J27" s="8" t="n"/>
-      <c r="K27" s="9" t="n"/>
-      <c r="L27" s="10" t="n"/>
-      <c r="M27" s="8" t="n"/>
-      <c r="N27" s="9" t="n"/>
-      <c r="O27" s="10" t="n"/>
-      <c r="P27" s="8" t="n"/>
-      <c r="Q27" s="9" t="n"/>
-      <c r="R27" s="10" t="n"/>
-      <c r="S27" s="8" t="n"/>
-      <c r="T27" s="9" t="n"/>
-      <c r="U27" s="10" t="n"/>
-      <c r="V27" s="8" t="n"/>
-      <c r="W27" s="9" t="n"/>
-      <c r="X27" s="10" t="n"/>
-      <c r="Y27" s="8" t="n"/>
-      <c r="Z27" s="9" t="n"/>
-      <c r="AA27" s="10" t="n"/>
-      <c r="AB27" s="8" t="n"/>
-      <c r="AC27" s="9" t="n"/>
-      <c r="AD27" s="10" t="n"/>
-      <c r="AE27" s="8" t="n"/>
-      <c r="AF27" s="9" t="n"/>
-      <c r="AG27" s="10" t="n"/>
-      <c r="AH27" s="8" t="n"/>
-      <c r="AI27" s="9" t="n"/>
-      <c r="AJ27" s="10" t="n"/>
-      <c r="AK27" s="8" t="n"/>
-      <c r="AL27" s="9" t="n"/>
-      <c r="AM27" s="10" t="n"/>
+          <t>Capital Markets</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>287393</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>14378.27</v>
+      </c>
+      <c r="F27" s="10" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>287393</v>
+      </c>
+      <c r="H27" s="9" t="n">
+        <v>15895.71</v>
+      </c>
+      <c r="I27" s="10" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="J27" s="8" t="n">
+        <v>287393</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <v>18124.44</v>
+      </c>
+      <c r="L27" s="10" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="M27" s="8" t="n">
+        <v>287393</v>
+      </c>
+      <c r="N27" s="9" t="n">
+        <v>17460.56</v>
+      </c>
+      <c r="O27" s="10" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="P27" s="8" t="n">
+        <v>287393</v>
+      </c>
+      <c r="Q27" s="9" t="n">
+        <v>17812.62</v>
+      </c>
+      <c r="R27" s="10" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="S27" s="8" t="n">
+        <v>287393</v>
+      </c>
+      <c r="T27" s="9" t="n">
+        <v>18463.56</v>
+      </c>
+      <c r="U27" s="10" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v>287393</v>
+      </c>
+      <c r="W27" s="9" t="n">
+        <v>18243.71</v>
+      </c>
+      <c r="X27" s="10" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="Y27" s="8" t="n">
+        <v>287393</v>
+      </c>
+      <c r="Z27" s="9" t="n">
+        <v>17962.06</v>
+      </c>
+      <c r="AA27" s="10" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="AB27" s="8" t="n">
+        <v>287393</v>
+      </c>
+      <c r="AC27" s="9" t="n">
+        <v>19048.41</v>
+      </c>
+      <c r="AD27" s="10" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="AE27" s="8" t="n">
+        <v>287393</v>
+      </c>
+      <c r="AF27" s="9" t="n">
+        <v>19453.63</v>
+      </c>
+      <c r="AG27" s="10" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="AH27" s="8" t="n">
+        <v>287393</v>
+      </c>
+      <c r="AI27" s="9" t="n">
+        <v>19370.29</v>
+      </c>
+      <c r="AJ27" s="10" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="AK27" s="8" t="n">
+        <v>287393</v>
+      </c>
+      <c r="AL27" s="9" t="n">
+        <v>15976.18</v>
+      </c>
+      <c r="AM27" s="10" t="n">
+        <v>0.0016</v>
+      </c>
       <c r="AN27" s="8" t="n">
-        <v>9899412</v>
+        <v>287393</v>
       </c>
       <c r="AO27" s="9" t="n">
-        <v>19552.33</v>
+        <v>15821.13</v>
       </c>
       <c r="AP27" s="10" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="AQ27" s="8" t="n">
+        <v>287393</v>
+      </c>
+      <c r="AR27" s="9" t="n">
+        <v>15273.64</v>
+      </c>
+      <c r="AS27" s="10" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="AT27" s="8" t="n">
+        <v>297835</v>
+      </c>
+      <c r="AU27" s="9" t="n">
+        <v>18529.51</v>
+      </c>
+      <c r="AV27" s="10" t="n">
         <v>0.0021</v>
-      </c>
-      <c r="AQ27" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="AR27" s="9" t="n">
-        <v>16216.23</v>
-      </c>
-      <c r="AS27" s="10" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="AT27" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="AU27" s="9" t="n">
-        <v>16131.09</v>
-      </c>
-      <c r="AV27" s="10" t="n">
-        <v>0.0018</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>ICRA Limited</t>
+          <t>Maharashtra Scooters Limited</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>INE725G01011</t>
+          <t>INE288A01013</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>287393</v>
+        <v>80565</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>14378.27</v>
+        <v>8949.969999999999</v>
       </c>
       <c r="F28" s="10" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="G28" s="8" t="n">
+        <v>80565</v>
+      </c>
+      <c r="H28" s="9" t="n">
+        <v>10682.11</v>
+      </c>
+      <c r="I28" s="10" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="J28" s="8" t="n">
+        <v>80552</v>
+      </c>
+      <c r="K28" s="9" t="n">
+        <v>10825.38</v>
+      </c>
+      <c r="L28" s="10" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="M28" s="8" t="n">
+        <v>80159</v>
+      </c>
+      <c r="N28" s="9" t="n">
+        <v>11401.01</v>
+      </c>
+      <c r="O28" s="10" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="P28" s="8" t="n">
+        <v>80159</v>
+      </c>
+      <c r="Q28" s="9" t="n">
+        <v>11787.38</v>
+      </c>
+      <c r="R28" s="10" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="S28" s="8" t="n">
+        <v>80159</v>
+      </c>
+      <c r="T28" s="9" t="n">
+        <v>12110.42</v>
+      </c>
+      <c r="U28" s="10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v>80159</v>
+      </c>
+      <c r="W28" s="9" t="n">
+        <v>13825.82</v>
+      </c>
+      <c r="X28" s="10" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="Y28" s="8" t="n">
+        <v>80159</v>
+      </c>
+      <c r="Z28" s="9" t="n">
+        <v>12726.04</v>
+      </c>
+      <c r="AA28" s="10" t="n">
         <v>0.0011</v>
       </c>
-      <c r="G28" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="H28" s="9" t="n">
-        <v>15895.71</v>
-      </c>
-      <c r="I28" s="10" t="n">
-        <v>0.0012</v>
-      </c>
-      <c r="J28" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="K28" s="9" t="n">
-        <v>18124.44</v>
-      </c>
-      <c r="L28" s="10" t="n">
-        <v>0.0014</v>
-      </c>
-      <c r="M28" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="N28" s="9" t="n">
-        <v>17460.56</v>
-      </c>
-      <c r="O28" s="10" t="n">
-        <v>0.0013</v>
-      </c>
-      <c r="P28" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="Q28" s="9" t="n">
-        <v>17812.62</v>
-      </c>
-      <c r="R28" s="10" t="n">
-        <v>0.0014</v>
-      </c>
-      <c r="S28" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="T28" s="9" t="n">
-        <v>18463.56</v>
-      </c>
-      <c r="U28" s="10" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="W28" s="9" t="n">
-        <v>18243.71</v>
-      </c>
-      <c r="X28" s="10" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="Y28" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="Z28" s="9" t="n">
-        <v>17962.06</v>
-      </c>
-      <c r="AA28" s="10" t="n">
-        <v>0.0016</v>
-      </c>
       <c r="AB28" s="8" t="n">
-        <v>287393</v>
+        <v>80159</v>
       </c>
       <c r="AC28" s="9" t="n">
-        <v>19048.41</v>
+        <v>12868.73</v>
       </c>
       <c r="AD28" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.0011</v>
       </c>
       <c r="AE28" s="8" t="n">
-        <v>287393</v>
+        <v>80159</v>
       </c>
       <c r="AF28" s="9" t="n">
-        <v>19453.63</v>
+        <v>11621.45</v>
       </c>
       <c r="AG28" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.0011</v>
       </c>
       <c r="AH28" s="8" t="n">
-        <v>287393</v>
+        <v>80159</v>
       </c>
       <c r="AI28" s="9" t="n">
-        <v>19370.29</v>
+        <v>10722.07</v>
       </c>
       <c r="AJ28" s="10" t="n">
-        <v>0.0019</v>
+        <v>0.001</v>
       </c>
       <c r="AK28" s="8" t="n">
-        <v>287393</v>
+        <v>80159</v>
       </c>
       <c r="AL28" s="9" t="n">
-        <v>15976.18</v>
+        <v>9198.25</v>
       </c>
       <c r="AM28" s="10" t="n">
-        <v>0.0016</v>
+        <v>0.0009</v>
       </c>
       <c r="AN28" s="8" t="n">
-        <v>287393</v>
+        <v>80159</v>
       </c>
       <c r="AO28" s="9" t="n">
-        <v>15821.13</v>
+        <v>8997.450000000001</v>
       </c>
       <c r="AP28" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.001</v>
       </c>
       <c r="AQ28" s="8" t="n">
-        <v>287393</v>
+        <v>80159</v>
       </c>
       <c r="AR28" s="9" t="n">
-        <v>15273.64</v>
+        <v>7401.52</v>
       </c>
       <c r="AS28" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.0008</v>
       </c>
       <c r="AT28" s="8" t="n">
-        <v>297835</v>
+        <v>80159</v>
       </c>
       <c r="AU28" s="9" t="n">
-        <v>18529.51</v>
+        <v>7463.48</v>
       </c>
       <c r="AV28" s="10" t="n">
-        <v>0.0021</v>
+        <v>0.0008</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Maharashtra Scooters Limited</t>
+          <t>IPCA Laboratories Limited</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>INE288A01013</t>
+          <t>INE571A01038</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="n">
-        <v>80565</v>
-      </c>
-      <c r="E29" s="9" t="n">
-        <v>8949.969999999999</v>
-      </c>
-      <c r="F29" s="10" t="n">
+          <t>Pharmaceuticals &amp; Biotechnology</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="10" t="n"/>
+      <c r="G29" s="8" t="n"/>
+      <c r="H29" s="9" t="n"/>
+      <c r="I29" s="10" t="n"/>
+      <c r="J29" s="8" t="n"/>
+      <c r="K29" s="9" t="n"/>
+      <c r="L29" s="10" t="n"/>
+      <c r="M29" s="8" t="n"/>
+      <c r="N29" s="9" t="n"/>
+      <c r="O29" s="10" t="n"/>
+      <c r="P29" s="8" t="n"/>
+      <c r="Q29" s="9" t="n"/>
+      <c r="R29" s="10" t="n"/>
+      <c r="S29" s="8" t="n"/>
+      <c r="T29" s="9" t="n"/>
+      <c r="U29" s="10" t="n"/>
+      <c r="V29" s="8" t="n"/>
+      <c r="W29" s="9" t="n"/>
+      <c r="X29" s="10" t="n"/>
+      <c r="Y29" s="8" t="n">
+        <v>218075</v>
+      </c>
+      <c r="Z29" s="9" t="n">
+        <v>3019.03</v>
+      </c>
+      <c r="AA29" s="10" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="AB29" s="8" t="n">
+        <v>566216</v>
+      </c>
+      <c r="AC29" s="9" t="n">
+        <v>8345.459999999999</v>
+      </c>
+      <c r="AD29" s="10" t="n">
         <v>0.0007</v>
       </c>
-      <c r="G29" s="8" t="n">
-        <v>80565</v>
-      </c>
-      <c r="H29" s="9" t="n">
-        <v>10682.11</v>
-      </c>
-      <c r="I29" s="10" t="n">
-        <v>0.0008</v>
-      </c>
-      <c r="J29" s="8" t="n">
-        <v>80552</v>
-      </c>
-      <c r="K29" s="9" t="n">
-        <v>10825.38</v>
-      </c>
-      <c r="L29" s="10" t="n">
-        <v>0.0008</v>
-      </c>
-      <c r="M29" s="8" t="n">
-        <v>80159</v>
-      </c>
-      <c r="N29" s="9" t="n">
-        <v>11401.01</v>
-      </c>
-      <c r="O29" s="10" t="n">
-        <v>0.0009</v>
-      </c>
-      <c r="P29" s="8" t="n">
-        <v>80159</v>
-      </c>
-      <c r="Q29" s="9" t="n">
-        <v>11787.38</v>
-      </c>
-      <c r="R29" s="10" t="n">
-        <v>0.0009</v>
-      </c>
-      <c r="S29" s="8" t="n">
-        <v>80159</v>
-      </c>
-      <c r="T29" s="9" t="n">
-        <v>12110.42</v>
-      </c>
-      <c r="U29" s="10" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v>80159</v>
-      </c>
-      <c r="W29" s="9" t="n">
-        <v>13825.82</v>
-      </c>
-      <c r="X29" s="10" t="n">
-        <v>0.0012</v>
-      </c>
-      <c r="Y29" s="8" t="n">
-        <v>80159</v>
-      </c>
-      <c r="Z29" s="9" t="n">
-        <v>12726.04</v>
-      </c>
-      <c r="AA29" s="10" t="n">
-        <v>0.0011</v>
-      </c>
-      <c r="AB29" s="8" t="n">
-        <v>80159</v>
-      </c>
-      <c r="AC29" s="9" t="n">
-        <v>12868.73</v>
-      </c>
-      <c r="AD29" s="10" t="n">
-        <v>0.0011</v>
-      </c>
       <c r="AE29" s="8" t="n">
-        <v>80159</v>
+        <v>1311557</v>
       </c>
       <c r="AF29" s="9" t="n">
-        <v>11621.45</v>
+        <v>18228.02</v>
       </c>
       <c r="AG29" s="10" t="n">
-        <v>0.0011</v>
+        <v>0.0017</v>
       </c>
       <c r="AH29" s="8" t="n">
-        <v>80159</v>
+        <v>1641095</v>
       </c>
       <c r="AI29" s="9" t="n">
-        <v>10722.07</v>
+        <v>23382.32</v>
       </c>
       <c r="AJ29" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0023</v>
       </c>
       <c r="AK29" s="8" t="n">
-        <v>80159</v>
+        <v>1857217</v>
       </c>
       <c r="AL29" s="9" t="n">
-        <v>9198.25</v>
+        <v>26023.32</v>
       </c>
       <c r="AM29" s="10" t="n">
-        <v>0.0009</v>
+        <v>0.0026</v>
       </c>
       <c r="AN29" s="8" t="n">
-        <v>80159</v>
+        <v>1926988</v>
       </c>
       <c r="AO29" s="9" t="n">
-        <v>8997.450000000001</v>
+        <v>28941.43</v>
       </c>
       <c r="AP29" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0031</v>
       </c>
       <c r="AQ29" s="8" t="n">
-        <v>80159</v>
+        <v>1926988</v>
       </c>
       <c r="AR29" s="9" t="n">
-        <v>7401.52</v>
+        <v>26117.43</v>
       </c>
       <c r="AS29" s="10" t="n">
-        <v>0.0008</v>
+        <v>0.003</v>
       </c>
       <c r="AT29" s="8" t="n">
-        <v>80159</v>
+        <v>2246361</v>
       </c>
       <c r="AU29" s="9" t="n">
-        <v>7463.48</v>
+        <v>32421.73</v>
       </c>
       <c r="AV29" s="10" t="n">
-        <v>0.0008</v>
+        <v>0.0036</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Swaraj Engines Limited</t>
+          <t>Nesco Limited</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>INE277A01016</t>
+          <t>INE317F01035</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Industrial Products</t>
+          <t>Commercial Services &amp; Supplies</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>1564.88</v>
+        <v>1538.11</v>
       </c>
       <c r="F30" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="G30" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>1700.33</v>
+        <v>1704.36</v>
       </c>
       <c r="I30" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>1637.61</v>
+        <v>1728.63</v>
       </c>
       <c r="L30" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="M30" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>1691.91</v>
+        <v>1858.32</v>
       </c>
       <c r="O30" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="P30" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>1764.08</v>
+        <v>1947.66</v>
       </c>
       <c r="R30" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="S30" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="T30" s="9" t="n">
-        <v>1892.15</v>
+        <v>2076.6</v>
       </c>
       <c r="U30" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="V30" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="W30" s="9" t="n">
-        <v>1955.38</v>
+        <v>1987.1</v>
       </c>
       <c r="X30" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="Y30" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="Z30" s="9" t="n">
-        <v>1897.21</v>
+        <v>2130.6</v>
       </c>
       <c r="AA30" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="AB30" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AC30" s="9" t="n">
-        <v>1983.66</v>
+        <v>2091.16</v>
       </c>
       <c r="AD30" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="AE30" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AF30" s="9" t="n">
-        <v>1867.41</v>
+        <v>1766.62</v>
       </c>
       <c r="AG30" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="AH30" s="8" t="n">
-        <v>47293</v>
+        <v>89469</v>
       </c>
       <c r="AI30" s="9" t="n">
-        <v>1857.76</v>
+        <v>828.48</v>
       </c>
       <c r="AJ30" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AK30" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="AL30" s="9" t="n">
-        <v>1925.39</v>
-      </c>
-      <c r="AM30" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AN30" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="AO30" s="9" t="n">
-        <v>1844.17</v>
-      </c>
-      <c r="AP30" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AQ30" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="AR30" s="9" t="n">
-        <v>1236.83</v>
-      </c>
-      <c r="AS30" s="10" t="n">
         <v>0.0001</v>
       </c>
-      <c r="AT30" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="AU30" s="9" t="n">
-        <v>1612.64</v>
-      </c>
-      <c r="AV30" s="10" t="n">
-        <v>0.0002</v>
-      </c>
+      <c r="AK30" s="8" t="n"/>
+      <c r="AL30" s="9" t="n"/>
+      <c r="AM30" s="10" t="n"/>
+      <c r="AN30" s="8" t="n"/>
+      <c r="AO30" s="9" t="n"/>
+      <c r="AP30" s="10" t="n"/>
+      <c r="AQ30" s="8" t="n"/>
+      <c r="AR30" s="9" t="n"/>
+      <c r="AS30" s="10" t="n"/>
+      <c r="AT30" s="8" t="n"/>
+      <c r="AU30" s="9" t="n"/>
+      <c r="AV30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Nesco Limited</t>
+          <t>Swaraj Engines Limited</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>INE317F01035</t>
+          <t>INE277A01016</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Commercial Services &amp; Supplies</t>
+          <t>Industrial Products</t>
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>1538.11</v>
+        <v>1564.88</v>
       </c>
       <c r="F31" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="G31" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>1704.36</v>
+        <v>1700.33</v>
       </c>
       <c r="I31" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>1728.63</v>
+        <v>1637.61</v>
       </c>
       <c r="L31" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="M31" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>1858.32</v>
+        <v>1691.91</v>
       </c>
       <c r="O31" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="P31" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>1947.66</v>
+        <v>1764.08</v>
       </c>
       <c r="R31" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="S31" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="T31" s="9" t="n">
-        <v>2076.6</v>
+        <v>1892.15</v>
       </c>
       <c r="U31" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="V31" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="W31" s="9" t="n">
-        <v>1987.1</v>
+        <v>1955.38</v>
       </c>
       <c r="X31" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="Y31" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="Z31" s="9" t="n">
-        <v>2130.6</v>
+        <v>1897.21</v>
       </c>
       <c r="AA31" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="AB31" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AC31" s="9" t="n">
-        <v>2091.16</v>
+        <v>1983.66</v>
       </c>
       <c r="AD31" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="AE31" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AF31" s="9" t="n">
-        <v>1766.62</v>
+        <v>1867.41</v>
       </c>
       <c r="AG31" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="AH31" s="8" t="n">
-        <v>89469</v>
+        <v>47293</v>
       </c>
       <c r="AI31" s="9" t="n">
-        <v>828.48</v>
+        <v>1857.76</v>
       </c>
       <c r="AJ31" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AK31" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="AL31" s="9" t="n">
+        <v>1925.39</v>
+      </c>
+      <c r="AM31" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AN31" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="AO31" s="9" t="n">
+        <v>1844.17</v>
+      </c>
+      <c r="AP31" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AQ31" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="AR31" s="9" t="n">
+        <v>1236.83</v>
+      </c>
+      <c r="AS31" s="10" t="n">
         <v>0.0001</v>
       </c>
-      <c r="AK31" s="8" t="n"/>
-      <c r="AL31" s="9" t="n"/>
-      <c r="AM31" s="10" t="n"/>
-      <c r="AN31" s="8" t="n"/>
-      <c r="AO31" s="9" t="n"/>
-      <c r="AP31" s="10" t="n"/>
-      <c r="AQ31" s="8" t="n"/>
-      <c r="AR31" s="9" t="n"/>
-      <c r="AS31" s="10" t="n"/>
-      <c r="AT31" s="8" t="n"/>
-      <c r="AU31" s="9" t="n"/>
-      <c r="AV31" s="10" t="n"/>
+      <c r="AT31" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="AU31" s="9" t="n">
+        <v>1612.64</v>
+      </c>
+      <c r="AV31" s="10" t="n">
+        <v>0.0002</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Bharti Airtel Limited</t>
+          <t>Motilal Oswal Financial Services Limited</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>INE397D01024</t>
+          <t>INE338I01027</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Telecom - Services</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="n">
-        <v>21167034</v>
-      </c>
-      <c r="E32" s="9" t="n">
-        <v>377281.21</v>
-      </c>
-      <c r="F32" s="10" t="n">
-        <v>0.0293</v>
-      </c>
-      <c r="G32" s="8" t="n">
-        <v>21167034</v>
-      </c>
-      <c r="H32" s="9" t="n">
-        <v>397792.07</v>
-      </c>
-      <c r="I32" s="10" t="n">
-        <v>0.0296</v>
-      </c>
-      <c r="J32" s="8" t="n">
-        <v>21167034</v>
-      </c>
-      <c r="K32" s="9" t="n">
-        <v>416715.398358</v>
-      </c>
-      <c r="L32" s="10" t="n">
-        <v>0.0311051731198606</v>
-      </c>
-      <c r="M32" s="8" t="n">
-        <v>21167034</v>
-      </c>
-      <c r="N32" s="9" t="n">
-        <v>445693.07</v>
-      </c>
-      <c r="O32" s="10" t="n">
-        <v>0.0334</v>
-      </c>
-      <c r="P32" s="8" t="n">
-        <v>21167034</v>
-      </c>
-      <c r="Q32" s="9" t="n">
-        <v>444846.39</v>
-      </c>
-      <c r="R32" s="10" t="n">
-        <v>0.0343</v>
-      </c>
-      <c r="S32" s="8" t="n">
-        <v>21167034</v>
-      </c>
-      <c r="T32" s="9" t="n">
-        <v>434876.71</v>
-      </c>
-      <c r="U32" s="10" t="n">
-        <v>0.0346</v>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v>21167034</v>
-      </c>
-      <c r="W32" s="9" t="n">
-        <v>397601.57</v>
-      </c>
-      <c r="X32" s="10" t="n">
-        <v>0.0332</v>
-      </c>
-      <c r="Y32" s="8" t="n">
-        <v>21167034</v>
-      </c>
-      <c r="Z32" s="9" t="n">
-        <v>399802.94</v>
-      </c>
-      <c r="AA32" s="10" t="n">
-        <v>0.0348</v>
-      </c>
-      <c r="AB32" s="8" t="n">
-        <v>21167034</v>
-      </c>
-      <c r="AC32" s="9" t="n">
-        <v>405200.53</v>
-      </c>
-      <c r="AD32" s="10" t="n">
-        <v>0.0358</v>
-      </c>
+          <t>Capital Markets</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="8" t="n"/>
+      <c r="H32" s="9" t="n"/>
+      <c r="I32" s="10" t="n"/>
+      <c r="J32" s="8" t="n"/>
+      <c r="K32" s="9" t="n"/>
+      <c r="L32" s="10" t="n"/>
+      <c r="M32" s="8" t="n"/>
+      <c r="N32" s="9" t="n"/>
+      <c r="O32" s="10" t="n"/>
+      <c r="P32" s="8" t="n"/>
+      <c r="Q32" s="9" t="n"/>
+      <c r="R32" s="10" t="n"/>
+      <c r="S32" s="8" t="n"/>
+      <c r="T32" s="9" t="n"/>
+      <c r="U32" s="10" t="n"/>
+      <c r="V32" s="8" t="n"/>
+      <c r="W32" s="9" t="n"/>
+      <c r="X32" s="10" t="n"/>
+      <c r="Y32" s="8" t="n"/>
+      <c r="Z32" s="9" t="n"/>
+      <c r="AA32" s="10" t="n"/>
+      <c r="AB32" s="8" t="n"/>
+      <c r="AC32" s="9" t="n"/>
+      <c r="AD32" s="10" t="n"/>
       <c r="AE32" s="8" t="n">
-        <v>20937034</v>
+        <v>591805</v>
       </c>
       <c r="AF32" s="9" t="n">
-        <v>420750.64</v>
+        <v>5149</v>
       </c>
       <c r="AG32" s="10" t="n">
-        <v>0.0381</v>
+        <v>0.0005</v>
       </c>
       <c r="AH32" s="8" t="n">
-        <v>11799076</v>
+        <v>5392631</v>
       </c>
       <c r="AI32" s="9" t="n">
-        <v>219014.45</v>
+        <v>43674.92</v>
       </c>
       <c r="AJ32" s="10" t="n">
-        <v>0.0211</v>
-      </c>
-      <c r="AK32" s="8" t="n"/>
-      <c r="AL32" s="9" t="n"/>
-      <c r="AM32" s="10" t="n"/>
-      <c r="AN32" s="8" t="n"/>
-      <c r="AO32" s="9" t="n"/>
-      <c r="AP32" s="10" t="n"/>
-      <c r="AQ32" s="8" t="n"/>
-      <c r="AR32" s="9" t="n"/>
-      <c r="AS32" s="10" t="n"/>
-      <c r="AT32" s="8" t="n"/>
-      <c r="AU32" s="9" t="n"/>
-      <c r="AV32" s="10" t="n"/>
+        <v>0.0042</v>
+      </c>
+      <c r="AK32" s="8" t="n">
+        <v>8585949</v>
+      </c>
+      <c r="AL32" s="9" t="n">
+        <v>56044.78</v>
+      </c>
+      <c r="AM32" s="10" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="AN32" s="8" t="n">
+        <v>10913294</v>
+      </c>
+      <c r="AO32" s="9" t="n">
+        <v>67154.95</v>
+      </c>
+      <c r="AP32" s="10" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="AQ32" s="8" t="n">
+        <v>12053879</v>
+      </c>
+      <c r="AR32" s="9" t="n">
+        <v>70937.08</v>
+      </c>
+      <c r="AS32" s="10" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="AT32" s="8" t="n">
+        <v>12053879</v>
+      </c>
+      <c r="AU32" s="9" t="n">
+        <v>76801.28999999999</v>
+      </c>
+      <c r="AV32" s="10" t="n">
+        <v>0.0086</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited</t>
+          <t>ITC Hotels Limited</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>INE768C01010</t>
+          <t>INE379A01028</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Leisure Services</t>
         </is>
       </c>
       <c r="D33" s="8" t="n"/>
@@ -5136,116 +5136,128 @@
       <c r="V33" s="8" t="n"/>
       <c r="W33" s="9" t="n"/>
       <c r="X33" s="10" t="n"/>
-      <c r="Y33" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="Z33" s="9" t="n">
-        <v>88822.8</v>
-      </c>
-      <c r="AA33" s="10" t="n">
-        <v>0.0077</v>
-      </c>
-      <c r="AB33" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="AC33" s="9" t="n">
-        <v>89280.39999999999</v>
-      </c>
-      <c r="AD33" s="10" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-      <c r="AE33" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="AF33" s="9" t="n">
-        <v>89020.8</v>
-      </c>
-      <c r="AG33" s="10" t="n">
-        <v>0.0081</v>
-      </c>
+      <c r="Y33" s="8" t="n"/>
+      <c r="Z33" s="9" t="n"/>
+      <c r="AA33" s="10" t="n"/>
+      <c r="AB33" s="8" t="n"/>
+      <c r="AC33" s="9" t="n"/>
+      <c r="AD33" s="10" t="n"/>
+      <c r="AE33" s="8" t="n"/>
+      <c r="AF33" s="9" t="n"/>
+      <c r="AG33" s="10" t="n"/>
       <c r="AH33" s="8" t="n"/>
       <c r="AI33" s="9" t="n"/>
       <c r="AJ33" s="10" t="n"/>
       <c r="AK33" s="8" t="n"/>
       <c r="AL33" s="9" t="n"/>
       <c r="AM33" s="10" t="n"/>
-      <c r="AN33" s="8" t="n"/>
-      <c r="AO33" s="9" t="n"/>
-      <c r="AP33" s="10" t="n"/>
-      <c r="AQ33" s="8" t="n"/>
-      <c r="AR33" s="9" t="n"/>
-      <c r="AS33" s="10" t="n"/>
-      <c r="AT33" s="8" t="n"/>
-      <c r="AU33" s="9" t="n"/>
-      <c r="AV33" s="10" t="n"/>
+      <c r="AN33" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="AO33" s="9" t="n">
+        <v>19552.33</v>
+      </c>
+      <c r="AP33" s="10" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="AQ33" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="AR33" s="9" t="n">
+        <v>16216.23</v>
+      </c>
+      <c r="AS33" s="10" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="AT33" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="AU33" s="9" t="n">
+        <v>16131.09</v>
+      </c>
+      <c r="AV33" s="10" t="n">
+        <v>0.0018</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services Limited</t>
+          <t>Zydus Wellness Limited</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>INE467B01029</t>
+          <t>INE768C01028</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>IT - Software</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>12412184</v>
+        <v>22157154</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>292791.01</v>
+        <v>94467.03</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>0.0227</v>
+        <v>0.0073</v>
       </c>
       <c r="G34" s="8" t="n">
-        <v>10378056</v>
+        <v>22075063</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>273710.85</v>
+        <v>84966.92</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>0.0204</v>
+        <v>0.0063</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>8465650</v>
+        <v>22000000</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>264458.44</v>
+        <v>98626</v>
       </c>
       <c r="L34" s="10" t="n">
-        <v>0.0197</v>
+        <v>0.0074</v>
       </c>
       <c r="M34" s="8" t="n">
-        <v>4654589</v>
+        <v>22000000</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>149235.43</v>
+        <v>100012</v>
       </c>
       <c r="O34" s="10" t="n">
-        <v>0.0112</v>
+        <v>0.0075</v>
       </c>
       <c r="P34" s="8" t="n">
-        <v>2811139</v>
+        <v>22000000</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>88199.49000000001</v>
+        <v>94699</v>
       </c>
       <c r="R34" s="10" t="n">
-        <v>0.0068</v>
-      </c>
-      <c r="S34" s="8" t="n"/>
-      <c r="T34" s="9" t="n"/>
-      <c r="U34" s="10" t="n"/>
-      <c r="V34" s="8" t="n"/>
-      <c r="W34" s="9" t="n"/>
-      <c r="X34" s="10" t="n"/>
+        <v>0.0073</v>
+      </c>
+      <c r="S34" s="8" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="T34" s="9" t="n">
+        <v>104852</v>
+      </c>
+      <c r="U34" s="10" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="W34" s="9" t="n">
+        <v>100584</v>
+      </c>
+      <c r="X34" s="10" t="n">
+        <v>0.008399999999999999</v>
+      </c>
       <c r="Y34" s="8" t="n"/>
       <c r="Z34" s="9" t="n"/>
       <c r="AA34" s="10" t="n"/>
@@ -5274,82 +5286,70 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited</t>
+          <t>Tata Consultancy Services Limited</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>INE768C01028</t>
+          <t>INE467B01029</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>IT - Software</t>
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>22157154</v>
+        <v>12412184</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>94467.03</v>
+        <v>292791.01</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>0.0073</v>
+        <v>0.0227</v>
       </c>
       <c r="G35" s="8" t="n">
-        <v>22075063</v>
+        <v>10378056</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>84966.92</v>
+        <v>273710.85</v>
       </c>
       <c r="I35" s="10" t="n">
-        <v>0.0063</v>
+        <v>0.0204</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>22000000</v>
+        <v>8465650</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>98626</v>
+        <v>264458.44</v>
       </c>
       <c r="L35" s="10" t="n">
-        <v>0.0074</v>
+        <v>0.0197</v>
       </c>
       <c r="M35" s="8" t="n">
-        <v>22000000</v>
+        <v>4654589</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>100012</v>
+        <v>149235.43</v>
       </c>
       <c r="O35" s="10" t="n">
-        <v>0.0075</v>
+        <v>0.0112</v>
       </c>
       <c r="P35" s="8" t="n">
-        <v>22000000</v>
+        <v>2811139</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>94699</v>
+        <v>88199.49000000001</v>
       </c>
       <c r="R35" s="10" t="n">
-        <v>0.0073</v>
-      </c>
-      <c r="S35" s="8" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="T35" s="9" t="n">
-        <v>104852</v>
-      </c>
-      <c r="U35" s="10" t="n">
-        <v>0.0083</v>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="W35" s="9" t="n">
-        <v>100584</v>
-      </c>
-      <c r="X35" s="10" t="n">
-        <v>0.008399999999999999</v>
-      </c>
+        <v>0.0068</v>
+      </c>
+      <c r="S35" s="8" t="n"/>
+      <c r="T35" s="9" t="n"/>
+      <c r="U35" s="10" t="n"/>
+      <c r="V35" s="8" t="n"/>
+      <c r="W35" s="9" t="n"/>
+      <c r="X35" s="10" t="n"/>
       <c r="Y35" s="8" t="n"/>
       <c r="Z35" s="9" t="n"/>
       <c r="AA35" s="10" t="n"/>
@@ -5378,58 +5378,64 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>The Great Eastern Shipping Company Limited</t>
+          <t>Indus Towers Limited</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>INE017A01032</t>
+          <t>INE121J01017</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Transport Services</t>
+          <t>Telecom - Services</t>
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>2205298</v>
+        <v>710855</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>31198.35</v>
+        <v>2972.44</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>0.0024</v>
+        <v>0.0002</v>
       </c>
       <c r="G36" s="8" t="n">
-        <v>2205298</v>
+        <v>710855</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>29526.73</v>
+        <v>3234.03</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>0.0022</v>
+        <v>0.0002</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>2205298</v>
+        <v>710855</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>26516.5</v>
+        <v>3158.33</v>
       </c>
       <c r="L36" s="10" t="n">
-        <v>0.002</v>
+        <v>0.0002</v>
       </c>
       <c r="M36" s="8" t="n">
-        <v>1657424</v>
+        <v>710855</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>18712.32</v>
+        <v>2976.71</v>
       </c>
       <c r="O36" s="10" t="n">
-        <v>0.0014</v>
-      </c>
-      <c r="P36" s="8" t="n"/>
-      <c r="Q36" s="9" t="n"/>
-      <c r="R36" s="10" t="n"/>
+        <v>0.0002</v>
+      </c>
+      <c r="P36" s="8" t="n">
+        <v>710855</v>
+      </c>
+      <c r="Q36" s="9" t="n">
+        <v>2850.8839775</v>
+      </c>
+      <c r="R36" s="10" t="n">
+        <v>0.0002</v>
+      </c>
       <c r="S36" s="8" t="n"/>
       <c r="T36" s="9" t="n"/>
       <c r="U36" s="10" t="n"/>
@@ -5464,64 +5470,52 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Indus Towers Limited</t>
+          <t>Kotak Mahindra Bank Limited</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>INE121J01017</t>
+          <t>INE237A01036</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Telecom - Services</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="D37" s="8" t="n">
-        <v>710855</v>
+        <v>146607960</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>2972.44</v>
+        <v>518112.53</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0402</v>
       </c>
       <c r="G37" s="8" t="n">
-        <v>710855</v>
+        <v>123107960</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>3234.03</v>
+        <v>511144.25</v>
       </c>
       <c r="I37" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0381</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>710855</v>
+        <v>123107960</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>3158.33</v>
+        <v>502280.48</v>
       </c>
       <c r="L37" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="M37" s="8" t="n">
-        <v>710855</v>
-      </c>
-      <c r="N37" s="9" t="n">
-        <v>2976.71</v>
-      </c>
-      <c r="O37" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="P37" s="8" t="n">
-        <v>710855</v>
-      </c>
-      <c r="Q37" s="9" t="n">
-        <v>2850.8839775</v>
-      </c>
-      <c r="R37" s="10" t="n">
-        <v>0.0002</v>
-      </c>
+        <v>0.0375</v>
+      </c>
+      <c r="M37" s="8" t="n"/>
+      <c r="N37" s="9" t="n"/>
+      <c r="O37" s="10" t="n"/>
+      <c r="P37" s="8" t="n"/>
+      <c r="Q37" s="9" t="n"/>
+      <c r="R37" s="10" t="n"/>
       <c r="S37" s="8" t="n"/>
       <c r="T37" s="9" t="n"/>
       <c r="U37" s="10" t="n"/>
@@ -5556,49 +5550,55 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Kotak Mahindra Bank Limited</t>
+          <t>The Great Eastern Shipping Company Limited</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>INE237A01036</t>
+          <t>INE017A01032</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Transport Services</t>
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>146607960</v>
+        <v>2205298</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>518112.53</v>
+        <v>31198.35</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>0.0402</v>
+        <v>0.0024</v>
       </c>
       <c r="G38" s="8" t="n">
-        <v>123107960</v>
+        <v>2205298</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>511144.25</v>
+        <v>29526.73</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>0.0381</v>
+        <v>0.0022</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>123107960</v>
+        <v>2205298</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>502280.48</v>
+        <v>26516.5</v>
       </c>
       <c r="L38" s="10" t="n">
-        <v>0.0375</v>
-      </c>
-      <c r="M38" s="8" t="n"/>
-      <c r="N38" s="9" t="n"/>
-      <c r="O38" s="10" t="n"/>
+        <v>0.002</v>
+      </c>
+      <c r="M38" s="8" t="n">
+        <v>1657424</v>
+      </c>
+      <c r="N38" s="9" t="n">
+        <v>18712.32</v>
+      </c>
+      <c r="O38" s="10" t="n">
+        <v>0.0014</v>
+      </c>
       <c r="P38" s="8" t="n"/>
       <c r="Q38" s="9" t="n"/>
       <c r="R38" s="10" t="n"/>
@@ -6030,19 +6030,19 @@
         <v>1285817925</v>
       </c>
       <c r="H44" s="14" t="n">
-        <v>8857498.140000001</v>
+        <v>8857498.140000002</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>0.6597999999999999</v>
+        <v>0.6598000000000001</v>
       </c>
       <c r="J44" s="13" t="n">
         <v>1265994824</v>
       </c>
       <c r="K44" s="14" t="n">
-        <v>8789059.288358001</v>
+        <v>8789059.288358003</v>
       </c>
       <c r="L44" s="15" t="n">
-        <v>0.6559051731198605</v>
+        <v>0.6559051731198604</v>
       </c>
       <c r="M44" s="13" t="n">
         <v>1079845116</v>
@@ -6066,7 +6066,7 @@
         <v>991416407</v>
       </c>
       <c r="T44" s="14" t="n">
-        <v>7865128.239999999</v>
+        <v>7865128.239999998</v>
       </c>
       <c r="U44" s="15" t="n">
         <v>0.6254999999999999</v>
@@ -6075,10 +6075,10 @@
         <v>979359723</v>
       </c>
       <c r="W44" s="14" t="n">
-        <v>7559180.72</v>
+        <v>7559180.720000002</v>
       </c>
       <c r="X44" s="15" t="n">
-        <v>0.6313999999999997</v>
+        <v>0.6313999999999996</v>
       </c>
       <c r="Y44" s="13" t="n">
         <v>927478800</v>
@@ -6087,7 +6087,7 @@
         <v>7320811.49</v>
       </c>
       <c r="AA44" s="15" t="n">
-        <v>0.6364000000000001</v>
+        <v>0.6364</v>
       </c>
       <c r="AB44" s="13" t="n">
         <v>819556049</v>
@@ -6096,7 +6096,7 @@
         <v>7290583.900000003</v>
       </c>
       <c r="AD44" s="15" t="n">
-        <v>0.6436999999999999</v>
+        <v>0.6436999999999998</v>
       </c>
       <c r="AE44" s="13" t="n">
         <v>799425942</v>
@@ -6105,22 +6105,22 @@
         <v>7347454.07</v>
       </c>
       <c r="AG44" s="15" t="n">
-        <v>0.6657999999999998</v>
+        <v>0.6657999999999999</v>
       </c>
       <c r="AH44" s="13" t="n">
         <v>756845974</v>
       </c>
       <c r="AI44" s="14" t="n">
-        <v>6714757.130000002</v>
+        <v>6714757.130000001</v>
       </c>
       <c r="AJ44" s="15" t="n">
-        <v>0.6467999999999997</v>
+        <v>0.6467999999999998</v>
       </c>
       <c r="AK44" s="13" t="n">
         <v>719050337</v>
       </c>
       <c r="AL44" s="14" t="n">
-        <v>6275568.75</v>
+        <v>6275568.750000001</v>
       </c>
       <c r="AM44" s="15" t="n">
         <v>0.6370000000000001</v>
@@ -6138,7 +6138,7 @@
         <v>718063829</v>
       </c>
       <c r="AR44" s="14" t="n">
-        <v>5662977.749999999</v>
+        <v>5662977.75</v>
       </c>
       <c r="AS44" s="15" t="n">
         <v>0.6436999999999998</v>

--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -487,7 +487,7 @@
   <dimension ref="A1:AV44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -495,7 +495,7 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
@@ -513,13 +513,13 @@
     <col width="20" customWidth="1" min="24" max="24"/>
     <col width="13" customWidth="1" min="25" max="25"/>
     <col width="26" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="20" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="26" customWidth="1" min="29" max="29"/>
     <col width="20" customWidth="1" min="30" max="30"/>
     <col width="13" customWidth="1" min="31" max="31"/>
     <col width="26" customWidth="1" min="32" max="32"/>
-    <col width="14" customWidth="1" min="33" max="33"/>
+    <col width="20" customWidth="1" min="33" max="33"/>
     <col width="13" customWidth="1" min="34" max="34"/>
     <col width="26" customWidth="1" min="35" max="35"/>
     <col width="20" customWidth="1" min="36" max="36"/>
@@ -1250,305 +1250,305 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Power Grid Corporation of India Limited</t>
+          <t>Coal India Limited</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>INE752E01010</t>
+          <t>INE522F01014</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Consumable Fuels</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>312063864</v>
+        <v>174817417</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>924021.1</v>
+        <v>787465.05</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.0716</v>
+        <v>0.0611</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>311113864</v>
+        <v>161423761</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>929141.55</v>
+        <v>695171.4300000001</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>0.0692</v>
+        <v>0.0518</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>313365617</v>
+        <v>159832308</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>803782.8100000001</v>
+        <v>704460.9</v>
       </c>
       <c r="L6" s="10" t="n">
-        <v>0.06</v>
+        <v>0.0526</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>305419267</v>
+        <v>162039558</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>808139.38</v>
+        <v>646537.84</v>
       </c>
       <c r="O6" s="10" t="n">
-        <v>0.0606</v>
+        <v>0.0485</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>284154236</v>
+        <v>162039558</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>767074.36</v>
+        <v>609511.8</v>
       </c>
       <c r="R6" s="10" t="n">
-        <v>0.0591</v>
+        <v>0.047</v>
       </c>
       <c r="S6" s="8" t="n">
-        <v>261786637</v>
+        <v>162039558</v>
       </c>
       <c r="T6" s="9" t="n">
-        <v>754338.1899999999</v>
+        <v>629766.74</v>
       </c>
       <c r="U6" s="10" t="n">
-        <v>0.06</v>
+        <v>0.0501</v>
       </c>
       <c r="V6" s="8" t="n">
-        <v>255922726</v>
+        <v>162039558</v>
       </c>
       <c r="W6" s="9" t="n">
-        <v>717223.4399999999</v>
+        <v>631873.26</v>
       </c>
       <c r="X6" s="10" t="n">
+        <v>0.0528</v>
+      </c>
+      <c r="Y6" s="8" t="n">
+        <v>162039558</v>
+      </c>
+      <c r="Z6" s="9" t="n">
+        <v>607324.26</v>
+      </c>
+      <c r="AA6" s="10" t="n">
+        <v>0.0528</v>
+      </c>
+      <c r="AB6" s="8" t="n">
+        <v>162039558</v>
+      </c>
+      <c r="AC6" s="9" t="n">
+        <v>609835.88</v>
+      </c>
+      <c r="AD6" s="10" t="n">
+        <v>0.0538</v>
+      </c>
+      <c r="AE6" s="8" t="n">
+        <v>162039558</v>
+      </c>
+      <c r="AF6" s="9" t="n">
+        <v>635114.05</v>
+      </c>
+      <c r="AG6" s="10" t="n">
+        <v>0.0575</v>
+      </c>
+      <c r="AH6" s="8" t="n">
+        <v>155681572</v>
+      </c>
+      <c r="AI6" s="9" t="n">
+        <v>618522.89</v>
+      </c>
+      <c r="AJ6" s="10" t="n">
+        <v>0.0595</v>
+      </c>
+      <c r="AK6" s="8" t="n">
+        <v>148323775</v>
+      </c>
+      <c r="AL6" s="9" t="n">
+        <v>571491.51</v>
+      </c>
+      <c r="AM6" s="10" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="AN6" s="8" t="n">
+        <v>141074007</v>
+      </c>
+      <c r="AO6" s="9" t="n">
+        <v>561756.7</v>
+      </c>
+      <c r="AP6" s="10" t="n">
+        <v>0.0601</v>
+      </c>
+      <c r="AQ6" s="8" t="n">
+        <v>142636407</v>
+      </c>
+      <c r="AR6" s="9" t="n">
+        <v>526827.5699999999</v>
+      </c>
+      <c r="AS6" s="10" t="n">
         <v>0.0599</v>
       </c>
-      <c r="Y6" s="8" t="n">
-        <v>246049993</v>
-      </c>
-      <c r="Z6" s="9" t="n">
-        <v>677252.61</v>
-      </c>
-      <c r="AA6" s="10" t="n">
-        <v>0.0589</v>
-      </c>
-      <c r="AB6" s="8" t="n">
-        <v>230787510</v>
-      </c>
-      <c r="AC6" s="9" t="n">
-        <v>671591.65</v>
-      </c>
-      <c r="AD6" s="10" t="n">
-        <v>0.0593</v>
-      </c>
-      <c r="AE6" s="8" t="n">
-        <v>224216515</v>
-      </c>
-      <c r="AF6" s="9" t="n">
-        <v>672425.33</v>
-      </c>
-      <c r="AG6" s="10" t="n">
-        <v>0.0609</v>
-      </c>
-      <c r="AH6" s="8" t="n">
-        <v>208867542</v>
-      </c>
-      <c r="AI6" s="9" t="n">
-        <v>605193.7</v>
-      </c>
-      <c r="AJ6" s="10" t="n">
-        <v>0.0583</v>
-      </c>
-      <c r="AK6" s="8" t="n">
-        <v>193616648</v>
-      </c>
-      <c r="AL6" s="9" t="n">
-        <v>595274.38</v>
-      </c>
-      <c r="AM6" s="10" t="n">
-        <v>0.0604</v>
-      </c>
-      <c r="AN6" s="8" t="n">
-        <v>192765312</v>
-      </c>
-      <c r="AO6" s="9" t="n">
-        <v>559694.08</v>
-      </c>
-      <c r="AP6" s="10" t="n">
-        <v>0.0599</v>
-      </c>
-      <c r="AQ6" s="8" t="n">
-        <v>193498810</v>
-      </c>
-      <c r="AR6" s="9" t="n">
-        <v>485391.76</v>
-      </c>
-      <c r="AS6" s="10" t="n">
-        <v>0.0552</v>
-      </c>
       <c r="AT6" s="8" t="n">
-        <v>185577147</v>
+        <v>139335199</v>
       </c>
       <c r="AU6" s="9" t="n">
-        <v>559793.46</v>
+        <v>551628.05</v>
       </c>
       <c r="AV6" s="10" t="n">
-        <v>0.0624</v>
+        <v>0.0615</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Coal India Limited</t>
+          <t>Power Grid Corporation of India Limited</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>INE522F01014</t>
+          <t>INE752E01010</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Consumable Fuels</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>174817417</v>
+        <v>312063864</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>787465.05</v>
+        <v>924021.1</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.0611</v>
+        <v>0.0716</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>161423761</v>
+        <v>311113864</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>695171.4300000001</v>
+        <v>929141.55</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>0.0518</v>
+        <v>0.0692</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>159832308</v>
+        <v>313365617</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>704460.9</v>
+        <v>803782.8100000001</v>
       </c>
       <c r="L7" s="10" t="n">
-        <v>0.0526</v>
+        <v>0.06</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>162039558</v>
+        <v>305419267</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>646537.84</v>
+        <v>808139.38</v>
       </c>
       <c r="O7" s="10" t="n">
-        <v>0.0485</v>
+        <v>0.0606</v>
       </c>
       <c r="P7" s="8" t="n">
-        <v>162039558</v>
+        <v>284154236</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>609511.8</v>
+        <v>767074.36</v>
       </c>
       <c r="R7" s="10" t="n">
-        <v>0.047</v>
+        <v>0.0591</v>
       </c>
       <c r="S7" s="8" t="n">
-        <v>162039558</v>
+        <v>261786637</v>
       </c>
       <c r="T7" s="9" t="n">
-        <v>629766.74</v>
+        <v>754338.1899999999</v>
       </c>
       <c r="U7" s="10" t="n">
-        <v>0.0501</v>
+        <v>0.06</v>
       </c>
       <c r="V7" s="8" t="n">
-        <v>162039558</v>
+        <v>255922726</v>
       </c>
       <c r="W7" s="9" t="n">
-        <v>631873.26</v>
+        <v>717223.4399999999</v>
       </c>
       <c r="X7" s="10" t="n">
-        <v>0.0528</v>
+        <v>0.0599</v>
       </c>
       <c r="Y7" s="8" t="n">
-        <v>162039558</v>
+        <v>246049993</v>
       </c>
       <c r="Z7" s="9" t="n">
-        <v>607324.26</v>
+        <v>677252.61</v>
       </c>
       <c r="AA7" s="10" t="n">
-        <v>0.0528</v>
+        <v>0.0589</v>
       </c>
       <c r="AB7" s="8" t="n">
-        <v>162039558</v>
+        <v>230787510</v>
       </c>
       <c r="AC7" s="9" t="n">
-        <v>609835.88</v>
+        <v>671591.65</v>
       </c>
       <c r="AD7" s="10" t="n">
-        <v>0.0538</v>
+        <v>0.0593</v>
       </c>
       <c r="AE7" s="8" t="n">
-        <v>162039558</v>
+        <v>224216515</v>
       </c>
       <c r="AF7" s="9" t="n">
-        <v>635114.05</v>
+        <v>672425.33</v>
       </c>
       <c r="AG7" s="10" t="n">
-        <v>0.0575</v>
+        <v>0.0609</v>
       </c>
       <c r="AH7" s="8" t="n">
-        <v>155681572</v>
+        <v>208867542</v>
       </c>
       <c r="AI7" s="9" t="n">
-        <v>618522.89</v>
+        <v>605193.7</v>
       </c>
       <c r="AJ7" s="10" t="n">
-        <v>0.0595</v>
+        <v>0.0583</v>
       </c>
       <c r="AK7" s="8" t="n">
-        <v>148323775</v>
+        <v>193616648</v>
       </c>
       <c r="AL7" s="9" t="n">
-        <v>571491.51</v>
+        <v>595274.38</v>
       </c>
       <c r="AM7" s="10" t="n">
-        <v>0.058</v>
+        <v>0.0604</v>
       </c>
       <c r="AN7" s="8" t="n">
-        <v>141074007</v>
+        <v>192765312</v>
       </c>
       <c r="AO7" s="9" t="n">
-        <v>561756.7</v>
+        <v>559694.08</v>
       </c>
       <c r="AP7" s="10" t="n">
-        <v>0.0601</v>
+        <v>0.0599</v>
       </c>
       <c r="AQ7" s="8" t="n">
-        <v>142636407</v>
+        <v>193498810</v>
       </c>
       <c r="AR7" s="9" t="n">
-        <v>526827.5699999999</v>
+        <v>485391.76</v>
       </c>
       <c r="AS7" s="10" t="n">
-        <v>0.0599</v>
+        <v>0.0552</v>
       </c>
       <c r="AT7" s="8" t="n">
-        <v>139335199</v>
+        <v>185577147</v>
       </c>
       <c r="AU7" s="9" t="n">
-        <v>551628.05</v>
+        <v>559793.46</v>
       </c>
       <c r="AV7" s="10" t="n">
-        <v>0.0615</v>
+        <v>0.0624</v>
       </c>
     </row>
     <row r="8">
@@ -1706,287 +1706,287 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>ITC Limited</t>
+          <t>Kotak Mahindra Bank Limited</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>INE154A01025</t>
+          <t>INE237A01028</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Diversified FMCG</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>224093958</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>644718.3199999999</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>215593958</v>
-      </c>
-      <c r="H9" s="9" t="n">
-        <v>676102.65</v>
-      </c>
-      <c r="I9" s="10" t="n">
-        <v>0.0504</v>
-      </c>
-      <c r="J9" s="8" t="n">
-        <v>209900994</v>
-      </c>
-      <c r="K9" s="9" t="n">
-        <v>676196.05</v>
-      </c>
-      <c r="L9" s="10" t="n">
-        <v>0.0505</v>
-      </c>
+          <t>Banks</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="8" t="n"/>
+      <c r="H9" s="9" t="n"/>
+      <c r="I9" s="10" t="n"/>
+      <c r="J9" s="8" t="n"/>
+      <c r="K9" s="9" t="n"/>
+      <c r="L9" s="10" t="n"/>
       <c r="M9" s="8" t="n">
-        <v>148665711</v>
+        <v>24621592</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>599122.8199999999</v>
+        <v>541945.86</v>
       </c>
       <c r="O9" s="10" t="n">
-        <v>0.0449</v>
+        <v>0.0407</v>
       </c>
       <c r="P9" s="8" t="n">
-        <v>144737169</v>
+        <v>24306544</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>585100.01</v>
+        <v>516368.22</v>
       </c>
       <c r="R9" s="10" t="n">
-        <v>0.0451</v>
+        <v>0.0398</v>
       </c>
       <c r="S9" s="8" t="n">
-        <v>138771024</v>
+        <v>24205055</v>
       </c>
       <c r="T9" s="9" t="n">
-        <v>583324</v>
+        <v>508838.67</v>
       </c>
       <c r="U9" s="10" t="n">
-        <v>0.0464</v>
+        <v>0.0404</v>
       </c>
       <c r="V9" s="8" t="n">
-        <v>135721024</v>
+        <v>24205055</v>
       </c>
       <c r="W9" s="9" t="n">
-        <v>544987.77</v>
+        <v>482334.13</v>
       </c>
       <c r="X9" s="10" t="n">
-        <v>0.0455</v>
+        <v>0.0403</v>
       </c>
       <c r="Y9" s="8" t="n">
-        <v>129421024</v>
+        <v>23407381</v>
       </c>
       <c r="Z9" s="9" t="n">
-        <v>530302.65</v>
+        <v>458854.89</v>
       </c>
       <c r="AA9" s="10" t="n">
-        <v>0.0461</v>
+        <v>0.0399</v>
       </c>
       <c r="AB9" s="8" t="n">
-        <v>122172359</v>
+        <v>21994066</v>
       </c>
       <c r="AC9" s="9" t="n">
-        <v>503289.03</v>
+        <v>435174.59</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>0.0444</v>
+        <v>0.0384</v>
       </c>
       <c r="AE9" s="8" t="n">
-        <v>117422359</v>
+        <v>20473232</v>
       </c>
       <c r="AF9" s="9" t="n">
-        <v>489005.41</v>
+        <v>442938.37</v>
       </c>
       <c r="AG9" s="10" t="n">
+        <v>0.0401</v>
+      </c>
+      <c r="AH9" s="8" t="n">
+        <v>19753232</v>
+      </c>
+      <c r="AI9" s="9" t="n">
+        <v>409820.3</v>
+      </c>
+      <c r="AJ9" s="10" t="n">
+        <v>0.0395</v>
+      </c>
+      <c r="AK9" s="8" t="n">
+        <v>19753232</v>
+      </c>
+      <c r="AL9" s="9" t="n">
+        <v>436171.12</v>
+      </c>
+      <c r="AM9" s="10" t="n">
         <v>0.0443</v>
       </c>
-      <c r="AH9" s="8" t="n">
-        <v>109270669</v>
-      </c>
-      <c r="AI9" s="9" t="n">
-        <v>456806.03</v>
-      </c>
-      <c r="AJ9" s="10" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="AK9" s="8" t="n">
-        <v>105271096</v>
-      </c>
-      <c r="AL9" s="9" t="n">
-        <v>448244.33</v>
-      </c>
-      <c r="AM9" s="10" t="n">
-        <v>0.0455</v>
-      </c>
       <c r="AN9" s="8" t="n">
-        <v>101194120</v>
+        <v>19753232</v>
       </c>
       <c r="AO9" s="9" t="n">
-        <v>414642.91</v>
+        <v>428882.17</v>
       </c>
       <c r="AP9" s="10" t="n">
-        <v>0.0444</v>
+        <v>0.0459</v>
       </c>
       <c r="AQ9" s="8" t="n">
-        <v>101194120</v>
+        <v>19753232</v>
       </c>
       <c r="AR9" s="9" t="n">
-        <v>399716.77</v>
+        <v>375894.13</v>
       </c>
       <c r="AS9" s="10" t="n">
-        <v>0.0454</v>
+        <v>0.0427</v>
       </c>
       <c r="AT9" s="8" t="n">
-        <v>98994120</v>
+        <v>19753232</v>
       </c>
       <c r="AU9" s="9" t="n">
-        <v>442998.69</v>
+        <v>375568.2</v>
       </c>
       <c r="AV9" s="10" t="n">
-        <v>0.0494</v>
+        <v>0.0419</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Kotak Mahindra Bank Limited</t>
+          <t>ITC Limited</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>INE237A01028</t>
+          <t>INE154A01025</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Banks</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="9" t="n"/>
-      <c r="I10" s="10" t="n"/>
-      <c r="J10" s="8" t="n"/>
-      <c r="K10" s="9" t="n"/>
-      <c r="L10" s="10" t="n"/>
+          <t>Diversified FMCG</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>224093958</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>644718.3199999999</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>215593958</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>676102.65</v>
+      </c>
+      <c r="I10" s="10" t="n">
+        <v>0.0504</v>
+      </c>
+      <c r="J10" s="8" t="n">
+        <v>209900994</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>676196.05</v>
+      </c>
+      <c r="L10" s="10" t="n">
+        <v>0.0505</v>
+      </c>
       <c r="M10" s="8" t="n">
-        <v>24621592</v>
+        <v>148665711</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>541945.86</v>
+        <v>599122.8199999999</v>
       </c>
       <c r="O10" s="10" t="n">
-        <v>0.0407</v>
+        <v>0.0449</v>
       </c>
       <c r="P10" s="8" t="n">
-        <v>24306544</v>
+        <v>144737169</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>516368.22</v>
+        <v>585100.01</v>
       </c>
       <c r="R10" s="10" t="n">
-        <v>0.0398</v>
+        <v>0.0451</v>
       </c>
       <c r="S10" s="8" t="n">
-        <v>24205055</v>
+        <v>138771024</v>
       </c>
       <c r="T10" s="9" t="n">
-        <v>508838.67</v>
+        <v>583324</v>
       </c>
       <c r="U10" s="10" t="n">
-        <v>0.0404</v>
+        <v>0.0464</v>
       </c>
       <c r="V10" s="8" t="n">
-        <v>24205055</v>
+        <v>135721024</v>
       </c>
       <c r="W10" s="9" t="n">
-        <v>482334.13</v>
+        <v>544987.77</v>
       </c>
       <c r="X10" s="10" t="n">
-        <v>0.0403</v>
+        <v>0.0455</v>
       </c>
       <c r="Y10" s="8" t="n">
-        <v>23407381</v>
+        <v>129421024</v>
       </c>
       <c r="Z10" s="9" t="n">
-        <v>458854.89</v>
+        <v>530302.65</v>
       </c>
       <c r="AA10" s="10" t="n">
-        <v>0.0399</v>
+        <v>0.0461</v>
       </c>
       <c r="AB10" s="8" t="n">
-        <v>21994066</v>
+        <v>122172359</v>
       </c>
       <c r="AC10" s="9" t="n">
-        <v>435174.59</v>
+        <v>503289.03</v>
       </c>
       <c r="AD10" s="10" t="n">
-        <v>0.0384</v>
+        <v>0.0444</v>
       </c>
       <c r="AE10" s="8" t="n">
-        <v>20473232</v>
+        <v>117422359</v>
       </c>
       <c r="AF10" s="9" t="n">
-        <v>442938.37</v>
+        <v>489005.41</v>
       </c>
       <c r="AG10" s="10" t="n">
-        <v>0.0401</v>
+        <v>0.0443</v>
       </c>
       <c r="AH10" s="8" t="n">
-        <v>19753232</v>
+        <v>109270669</v>
       </c>
       <c r="AI10" s="9" t="n">
-        <v>409820.3</v>
+        <v>456806.03</v>
       </c>
       <c r="AJ10" s="10" t="n">
-        <v>0.0395</v>
+        <v>0.044</v>
       </c>
       <c r="AK10" s="8" t="n">
-        <v>19753232</v>
+        <v>105271096</v>
       </c>
       <c r="AL10" s="9" t="n">
-        <v>436171.12</v>
+        <v>448244.33</v>
       </c>
       <c r="AM10" s="10" t="n">
-        <v>0.0443</v>
+        <v>0.0455</v>
       </c>
       <c r="AN10" s="8" t="n">
-        <v>19753232</v>
+        <v>101194120</v>
       </c>
       <c r="AO10" s="9" t="n">
-        <v>428882.17</v>
+        <v>414642.91</v>
       </c>
       <c r="AP10" s="10" t="n">
-        <v>0.0459</v>
+        <v>0.0444</v>
       </c>
       <c r="AQ10" s="8" t="n">
-        <v>19753232</v>
+        <v>101194120</v>
       </c>
       <c r="AR10" s="9" t="n">
-        <v>375894.13</v>
+        <v>399716.77</v>
       </c>
       <c r="AS10" s="10" t="n">
-        <v>0.0427</v>
+        <v>0.0454</v>
       </c>
       <c r="AT10" s="8" t="n">
-        <v>19753232</v>
+        <v>98994120</v>
       </c>
       <c r="AU10" s="9" t="n">
-        <v>375568.2</v>
+        <v>442998.69</v>
       </c>
       <c r="AV10" s="10" t="n">
-        <v>0.0419</v>
+        <v>0.0494</v>
       </c>
     </row>
     <row r="11">
@@ -2144,444 +2144,468 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Bharti Airtel Limited</t>
+          <t>Axis Bank Limited</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>INE397D01024</t>
+          <t>INE238A01034</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Telecom - Services</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>21167034</v>
+        <v>33244875</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>377281.21</v>
+        <v>386072.73</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>0.0293</v>
+        <v>0.0299</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>21167034</v>
+        <v>33244875</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>397792.07</v>
+        <v>460075.83</v>
       </c>
       <c r="I12" s="10" t="n">
+        <v>0.0343</v>
+      </c>
+      <c r="J12" s="8" t="n">
+        <v>33244875</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>455587.77</v>
+      </c>
+      <c r="L12" s="10" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>33244875</v>
+      </c>
+      <c r="N12" s="9" t="n">
+        <v>422010.44</v>
+      </c>
+      <c r="O12" s="10" t="n">
+        <v>0.0317</v>
+      </c>
+      <c r="P12" s="8" t="n">
+        <v>33244875</v>
+      </c>
+      <c r="Q12" s="9" t="n">
+        <v>425434.67</v>
+      </c>
+      <c r="R12" s="10" t="n">
+        <v>0.0328</v>
+      </c>
+      <c r="S12" s="8" t="n">
+        <v>33244875</v>
+      </c>
+      <c r="T12" s="9" t="n">
+        <v>409842.82</v>
+      </c>
+      <c r="U12" s="10" t="n">
+        <v>0.0326</v>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v>33244875</v>
+      </c>
+      <c r="W12" s="9" t="n">
+        <v>376199.01</v>
+      </c>
+      <c r="X12" s="10" t="n">
+        <v>0.0314</v>
+      </c>
+      <c r="Y12" s="8" t="n">
+        <v>32644875</v>
+      </c>
+      <c r="Z12" s="9" t="n">
+        <v>341204.23</v>
+      </c>
+      <c r="AA12" s="10" t="n">
+        <v>0.0297</v>
+      </c>
+      <c r="AB12" s="8" t="n">
+        <v>30107270</v>
+      </c>
+      <c r="AC12" s="9" t="n">
+        <v>321666.07</v>
+      </c>
+      <c r="AD12" s="10" t="n">
+        <v>0.0284</v>
+      </c>
+      <c r="AE12" s="8" t="n">
+        <v>27257270</v>
+      </c>
+      <c r="AF12" s="9" t="n">
+        <v>326869.18</v>
+      </c>
+      <c r="AG12" s="10" t="n">
         <v>0.0296</v>
       </c>
-      <c r="J12" s="8" t="n">
-        <v>21167034</v>
-      </c>
-      <c r="K12" s="9" t="n">
-        <v>416715.398358</v>
-      </c>
-      <c r="L12" s="10" t="n">
-        <v>0.0311051731198606</v>
-      </c>
-      <c r="M12" s="8" t="n">
-        <v>21167034</v>
-      </c>
-      <c r="N12" s="9" t="n">
-        <v>445693.07</v>
-      </c>
-      <c r="O12" s="10" t="n">
-        <v>0.0334</v>
-      </c>
-      <c r="P12" s="8" t="n">
-        <v>21167034</v>
-      </c>
-      <c r="Q12" s="9" t="n">
-        <v>444846.39</v>
-      </c>
-      <c r="R12" s="10" t="n">
-        <v>0.0343</v>
-      </c>
-      <c r="S12" s="8" t="n">
-        <v>21167034</v>
-      </c>
-      <c r="T12" s="9" t="n">
-        <v>434876.71</v>
-      </c>
-      <c r="U12" s="10" t="n">
-        <v>0.0346</v>
-      </c>
-      <c r="V12" s="8" t="n">
-        <v>21167034</v>
-      </c>
-      <c r="W12" s="9" t="n">
-        <v>397601.57</v>
-      </c>
-      <c r="X12" s="10" t="n">
-        <v>0.0332</v>
-      </c>
-      <c r="Y12" s="8" t="n">
-        <v>21167034</v>
-      </c>
-      <c r="Z12" s="9" t="n">
-        <v>399802.94</v>
-      </c>
-      <c r="AA12" s="10" t="n">
-        <v>0.0348</v>
-      </c>
-      <c r="AB12" s="8" t="n">
-        <v>21167034</v>
-      </c>
-      <c r="AC12" s="9" t="n">
-        <v>405200.53</v>
-      </c>
-      <c r="AD12" s="10" t="n">
-        <v>0.0358</v>
-      </c>
-      <c r="AE12" s="8" t="n">
-        <v>20937034</v>
-      </c>
-      <c r="AF12" s="9" t="n">
-        <v>420750.64</v>
-      </c>
-      <c r="AG12" s="10" t="n">
-        <v>0.0381</v>
-      </c>
       <c r="AH12" s="8" t="n">
-        <v>11799076</v>
+        <v>27257270</v>
       </c>
       <c r="AI12" s="9" t="n">
-        <v>219014.45</v>
+        <v>324961.17</v>
       </c>
       <c r="AJ12" s="10" t="n">
-        <v>0.0211</v>
-      </c>
-      <c r="AK12" s="8" t="n"/>
-      <c r="AL12" s="9" t="n"/>
-      <c r="AM12" s="10" t="n"/>
-      <c r="AN12" s="8" t="n"/>
-      <c r="AO12" s="9" t="n"/>
-      <c r="AP12" s="10" t="n"/>
-      <c r="AQ12" s="8" t="n"/>
-      <c r="AR12" s="9" t="n"/>
-      <c r="AS12" s="10" t="n"/>
-      <c r="AT12" s="8" t="n"/>
-      <c r="AU12" s="9" t="n"/>
-      <c r="AV12" s="10" t="n"/>
+        <v>0.0313</v>
+      </c>
+      <c r="AK12" s="8" t="n">
+        <v>27257270</v>
+      </c>
+      <c r="AL12" s="9" t="n">
+        <v>322998.65</v>
+      </c>
+      <c r="AM12" s="10" t="n">
+        <v>0.0328</v>
+      </c>
+      <c r="AN12" s="8" t="n">
+        <v>27257270</v>
+      </c>
+      <c r="AO12" s="9" t="n">
+        <v>300375.12</v>
+      </c>
+      <c r="AP12" s="10" t="n">
+        <v>0.0321</v>
+      </c>
+      <c r="AQ12" s="8" t="n">
+        <v>27257270</v>
+      </c>
+      <c r="AR12" s="9" t="n">
+        <v>276811.21</v>
+      </c>
+      <c r="AS12" s="10" t="n">
+        <v>0.0315</v>
+      </c>
+      <c r="AT12" s="8" t="n">
+        <v>27257270</v>
+      </c>
+      <c r="AU12" s="9" t="n">
+        <v>268783.94</v>
+      </c>
+      <c r="AV12" s="10" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Mahindra &amp; Mahindra Limited</t>
+          <t>HCL Technologies Limited</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>INE101A01026</t>
+          <t>INE860A01027</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Automobiles</t>
+          <t>IT - Software</t>
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>14645626</v>
+        <v>29868916</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>432734.31</v>
+        <v>400721.38</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.0336</v>
+        <v>0.0311</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>13974725</v>
+        <v>27771661</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>474777.31</v>
+        <v>385776.14</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>0.0354</v>
+        <v>0.0287</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>13974725</v>
+        <v>23460156</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>479584.61</v>
+        <v>397790.41</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>0.0358</v>
+        <v>0.0297</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>13033470</v>
+        <v>21315882</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>483437.47</v>
+        <v>346020.71</v>
       </c>
       <c r="O13" s="10" t="n">
-        <v>0.0363</v>
+        <v>0.026</v>
       </c>
       <c r="P13" s="8" t="n">
-        <v>12435671</v>
+        <v>19831378</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>467245.47</v>
+        <v>322101.24</v>
       </c>
       <c r="R13" s="10" t="n">
+        <v>0.0248</v>
+      </c>
+      <c r="S13" s="8" t="n">
+        <v>18138945</v>
+      </c>
+      <c r="T13" s="9" t="n">
+        <v>279611.84</v>
+      </c>
+      <c r="U13" s="10" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="V13" s="8" t="n">
+        <v>18706995</v>
+      </c>
+      <c r="W13" s="9" t="n">
+        <v>259110.59</v>
+      </c>
+      <c r="X13" s="10" t="n">
+        <v>0.0216</v>
+      </c>
+      <c r="Y13" s="8" t="n">
+        <v>18706995</v>
+      </c>
+      <c r="Z13" s="9" t="n">
+        <v>272149.36</v>
+      </c>
+      <c r="AA13" s="10" t="n">
+        <v>0.0237</v>
+      </c>
+      <c r="AB13" s="8" t="n">
+        <v>18706995</v>
+      </c>
+      <c r="AC13" s="9" t="n">
+        <v>274599.98</v>
+      </c>
+      <c r="AD13" s="10" t="n">
+        <v>0.0242</v>
+      </c>
+      <c r="AE13" s="8" t="n">
+        <v>18558995</v>
+      </c>
+      <c r="AF13" s="9" t="n">
+        <v>320810.79</v>
+      </c>
+      <c r="AG13" s="10" t="n">
+        <v>0.0291</v>
+      </c>
+      <c r="AH13" s="8" t="n">
+        <v>18341573</v>
+      </c>
+      <c r="AI13" s="9" t="n">
+        <v>300178.18</v>
+      </c>
+      <c r="AJ13" s="10" t="n">
+        <v>0.0289</v>
+      </c>
+      <c r="AK13" s="8" t="n">
+        <v>18706973</v>
+      </c>
+      <c r="AL13" s="9" t="n">
+        <v>293231.8</v>
+      </c>
+      <c r="AM13" s="10" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="AN13" s="8" t="n">
+        <v>18706973</v>
+      </c>
+      <c r="AO13" s="9" t="n">
+        <v>297908.55</v>
+      </c>
+      <c r="AP13" s="10" t="n">
+        <v>0.0319</v>
+      </c>
+      <c r="AQ13" s="8" t="n">
+        <v>18706973</v>
+      </c>
+      <c r="AR13" s="9" t="n">
+        <v>294644.18</v>
+      </c>
+      <c r="AS13" s="10" t="n">
+        <v>0.0335</v>
+      </c>
+      <c r="AT13" s="8" t="n">
+        <v>18706973</v>
+      </c>
+      <c r="AU13" s="9" t="n">
+        <v>322779.47</v>
+      </c>
+      <c r="AV13" s="10" t="n">
         <v>0.036</v>
-      </c>
-      <c r="S13" s="8" t="n">
-        <v>12435671</v>
-      </c>
-      <c r="T13" s="9" t="n">
-        <v>433656.72</v>
-      </c>
-      <c r="U13" s="10" t="n">
-        <v>0.0345</v>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v>12335671</v>
-      </c>
-      <c r="W13" s="9" t="n">
-        <v>422743.45</v>
-      </c>
-      <c r="X13" s="10" t="n">
-        <v>0.0353</v>
-      </c>
-      <c r="Y13" s="8" t="n">
-        <v>12335671</v>
-      </c>
-      <c r="Z13" s="9" t="n">
-        <v>394679.79</v>
-      </c>
-      <c r="AA13" s="10" t="n">
-        <v>0.0343</v>
-      </c>
-      <c r="AB13" s="8" t="n">
-        <v>12335671</v>
-      </c>
-      <c r="AC13" s="9" t="n">
-        <v>395123.88</v>
-      </c>
-      <c r="AD13" s="10" t="n">
-        <v>0.0349</v>
-      </c>
-      <c r="AE13" s="8" t="n">
-        <v>12335671</v>
-      </c>
-      <c r="AF13" s="9" t="n">
-        <v>392669.08</v>
-      </c>
-      <c r="AG13" s="10" t="n">
-        <v>0.0356</v>
-      </c>
-      <c r="AH13" s="8" t="n">
-        <v>12231374</v>
-      </c>
-      <c r="AI13" s="9" t="n">
-        <v>364103.54</v>
-      </c>
-      <c r="AJ13" s="10" t="n">
-        <v>0.0351</v>
-      </c>
-      <c r="AK13" s="8" t="n">
-        <v>11040212</v>
-      </c>
-      <c r="AL13" s="9" t="n">
-        <v>323345.73</v>
-      </c>
-      <c r="AM13" s="10" t="n">
-        <v>0.0328</v>
-      </c>
-      <c r="AN13" s="8" t="n">
-        <v>10399289</v>
-      </c>
-      <c r="AO13" s="9" t="n">
-        <v>277224.25</v>
-      </c>
-      <c r="AP13" s="10" t="n">
-        <v>0.0297</v>
-      </c>
-      <c r="AQ13" s="8" t="n">
-        <v>10068665</v>
-      </c>
-      <c r="AR13" s="9" t="n">
-        <v>260285.06</v>
-      </c>
-      <c r="AS13" s="10" t="n">
-        <v>0.0296</v>
-      </c>
-      <c r="AT13" s="8" t="n">
-        <v>9331737</v>
-      </c>
-      <c r="AU13" s="9" t="n">
-        <v>279004.94</v>
-      </c>
-      <c r="AV13" s="10" t="n">
-        <v>0.0311</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Axis Bank Limited</t>
+          <t>Mahindra &amp; Mahindra Limited</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>INE238A01034</t>
+          <t>INE101A01026</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Automobiles</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>33244875</v>
+        <v>14645626</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>386072.73</v>
+        <v>432734.31</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>0.0299</v>
+        <v>0.0336</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>33244875</v>
+        <v>13974725</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>460075.83</v>
+        <v>474777.31</v>
       </c>
       <c r="I14" s="10" t="n">
+        <v>0.0354</v>
+      </c>
+      <c r="J14" s="8" t="n">
+        <v>13974725</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>479584.61</v>
+      </c>
+      <c r="L14" s="10" t="n">
+        <v>0.0358</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>13033470</v>
+      </c>
+      <c r="N14" s="9" t="n">
+        <v>483437.47</v>
+      </c>
+      <c r="O14" s="10" t="n">
+        <v>0.0363</v>
+      </c>
+      <c r="P14" s="8" t="n">
+        <v>12435671</v>
+      </c>
+      <c r="Q14" s="9" t="n">
+        <v>467245.47</v>
+      </c>
+      <c r="R14" s="10" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="S14" s="8" t="n">
+        <v>12435671</v>
+      </c>
+      <c r="T14" s="9" t="n">
+        <v>433656.72</v>
+      </c>
+      <c r="U14" s="10" t="n">
+        <v>0.0345</v>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v>12335671</v>
+      </c>
+      <c r="W14" s="9" t="n">
+        <v>422743.45</v>
+      </c>
+      <c r="X14" s="10" t="n">
+        <v>0.0353</v>
+      </c>
+      <c r="Y14" s="8" t="n">
+        <v>12335671</v>
+      </c>
+      <c r="Z14" s="9" t="n">
+        <v>394679.79</v>
+      </c>
+      <c r="AA14" s="10" t="n">
         <v>0.0343</v>
       </c>
-      <c r="J14" s="8" t="n">
-        <v>33244875</v>
-      </c>
-      <c r="K14" s="9" t="n">
-        <v>455587.77</v>
-      </c>
-      <c r="L14" s="10" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="M14" s="8" t="n">
-        <v>33244875</v>
-      </c>
-      <c r="N14" s="9" t="n">
-        <v>422010.44</v>
-      </c>
-      <c r="O14" s="10" t="n">
-        <v>0.0317</v>
-      </c>
-      <c r="P14" s="8" t="n">
-        <v>33244875</v>
-      </c>
-      <c r="Q14" s="9" t="n">
-        <v>425434.67</v>
-      </c>
-      <c r="R14" s="10" t="n">
-        <v>0.0328</v>
-      </c>
-      <c r="S14" s="8" t="n">
-        <v>33244875</v>
-      </c>
-      <c r="T14" s="9" t="n">
-        <v>409842.82</v>
-      </c>
-      <c r="U14" s="10" t="n">
-        <v>0.0326</v>
-      </c>
-      <c r="V14" s="8" t="n">
-        <v>33244875</v>
-      </c>
-      <c r="W14" s="9" t="n">
-        <v>376199.01</v>
-      </c>
-      <c r="X14" s="10" t="n">
-        <v>0.0314</v>
-      </c>
-      <c r="Y14" s="8" t="n">
-        <v>32644875</v>
-      </c>
-      <c r="Z14" s="9" t="n">
-        <v>341204.23</v>
-      </c>
-      <c r="AA14" s="10" t="n">
-        <v>0.0297</v>
-      </c>
       <c r="AB14" s="8" t="n">
-        <v>30107270</v>
+        <v>12335671</v>
       </c>
       <c r="AC14" s="9" t="n">
-        <v>321666.07</v>
+        <v>395123.88</v>
       </c>
       <c r="AD14" s="10" t="n">
-        <v>0.0284</v>
+        <v>0.0349</v>
       </c>
       <c r="AE14" s="8" t="n">
-        <v>27257270</v>
+        <v>12335671</v>
       </c>
       <c r="AF14" s="9" t="n">
-        <v>326869.18</v>
+        <v>392669.08</v>
       </c>
       <c r="AG14" s="10" t="n">
-        <v>0.0296</v>
+        <v>0.0356</v>
       </c>
       <c r="AH14" s="8" t="n">
-        <v>27257270</v>
+        <v>12231374</v>
       </c>
       <c r="AI14" s="9" t="n">
-        <v>324961.17</v>
+        <v>364103.54</v>
       </c>
       <c r="AJ14" s="10" t="n">
-        <v>0.0313</v>
+        <v>0.0351</v>
       </c>
       <c r="AK14" s="8" t="n">
-        <v>27257270</v>
+        <v>11040212</v>
       </c>
       <c r="AL14" s="9" t="n">
-        <v>322998.65</v>
+        <v>323345.73</v>
       </c>
       <c r="AM14" s="10" t="n">
         <v>0.0328</v>
       </c>
       <c r="AN14" s="8" t="n">
-        <v>27257270</v>
+        <v>10399289</v>
       </c>
       <c r="AO14" s="9" t="n">
-        <v>300375.12</v>
+        <v>277224.25</v>
       </c>
       <c r="AP14" s="10" t="n">
-        <v>0.0321</v>
+        <v>0.0297</v>
       </c>
       <c r="AQ14" s="8" t="n">
-        <v>27257270</v>
+        <v>10068665</v>
       </c>
       <c r="AR14" s="9" t="n">
-        <v>276811.21</v>
+        <v>260285.06</v>
       </c>
       <c r="AS14" s="10" t="n">
-        <v>0.0315</v>
+        <v>0.0296</v>
       </c>
       <c r="AT14" s="8" t="n">
-        <v>27257270</v>
+        <v>9331737</v>
       </c>
       <c r="AU14" s="9" t="n">
-        <v>268783.94</v>
+        <v>279004.94</v>
       </c>
       <c r="AV14" s="10" t="n">
-        <v>0.03</v>
+        <v>0.0311</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>HCL Technologies Limited</t>
+          <t>Infosys Limited</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>INE860A01027</t>
+          <t>INE009A01021</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -2590,139 +2614,139 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>29868916</v>
+        <v>26944033</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>400721.38</v>
+        <v>336962.08</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.0311</v>
+        <v>0.0261</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>27771661</v>
+        <v>20693682</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>385776.14</v>
+        <v>269038.56</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>0.0287</v>
+        <v>0.02</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>23460156</v>
+        <v>16509541</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>397790.41</v>
+        <v>270921.57</v>
       </c>
       <c r="L15" s="10" t="n">
-        <v>0.0297</v>
+        <v>0.0202</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>21315882</v>
+        <v>16417936</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>346020.71</v>
+        <v>265215.34</v>
       </c>
       <c r="O15" s="10" t="n">
-        <v>0.026</v>
+        <v>0.0199</v>
       </c>
       <c r="P15" s="8" t="n">
-        <v>19831378</v>
+        <v>17621740</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>322101.24</v>
+        <v>274916.77</v>
       </c>
       <c r="R15" s="10" t="n">
-        <v>0.0248</v>
+        <v>0.0212</v>
       </c>
       <c r="S15" s="8" t="n">
-        <v>18138945</v>
+        <v>9306473</v>
       </c>
       <c r="T15" s="9" t="n">
-        <v>279611.84</v>
+        <v>137949.85</v>
       </c>
       <c r="U15" s="10" t="n">
-        <v>0.0222</v>
+        <v>0.011</v>
       </c>
       <c r="V15" s="8" t="n">
-        <v>18706995</v>
+        <v>9306473</v>
       </c>
       <c r="W15" s="9" t="n">
-        <v>259110.59</v>
+        <v>134180.73</v>
       </c>
       <c r="X15" s="10" t="n">
-        <v>0.0216</v>
+        <v>0.0112</v>
       </c>
       <c r="Y15" s="8" t="n">
-        <v>18706995</v>
+        <v>9306473</v>
       </c>
       <c r="Z15" s="9" t="n">
-        <v>272149.36</v>
+        <v>136767.93</v>
       </c>
       <c r="AA15" s="10" t="n">
-        <v>0.0237</v>
+        <v>0.0119</v>
       </c>
       <c r="AB15" s="8" t="n">
-        <v>18706995</v>
+        <v>9306473</v>
       </c>
       <c r="AC15" s="9" t="n">
-        <v>274599.98</v>
+        <v>140434.68</v>
       </c>
       <c r="AD15" s="10" t="n">
-        <v>0.0242</v>
+        <v>0.0124</v>
       </c>
       <c r="AE15" s="8" t="n">
-        <v>18558995</v>
+        <v>9306473</v>
       </c>
       <c r="AF15" s="9" t="n">
-        <v>320810.79</v>
+        <v>149071.08</v>
       </c>
       <c r="AG15" s="10" t="n">
-        <v>0.0291</v>
+        <v>0.0135</v>
       </c>
       <c r="AH15" s="8" t="n">
-        <v>18341573</v>
+        <v>9306473</v>
       </c>
       <c r="AI15" s="9" t="n">
-        <v>300178.18</v>
+        <v>145432.25</v>
       </c>
       <c r="AJ15" s="10" t="n">
-        <v>0.0289</v>
+        <v>0.014</v>
       </c>
       <c r="AK15" s="8" t="n">
-        <v>18706973</v>
+        <v>9306473</v>
       </c>
       <c r="AL15" s="9" t="n">
-        <v>293231.8</v>
+        <v>139606.4</v>
       </c>
       <c r="AM15" s="10" t="n">
-        <v>0.0298</v>
+        <v>0.0142</v>
       </c>
       <c r="AN15" s="8" t="n">
-        <v>18706973</v>
+        <v>9306473</v>
       </c>
       <c r="AO15" s="9" t="n">
-        <v>297908.55</v>
+        <v>146172.12</v>
       </c>
       <c r="AP15" s="10" t="n">
-        <v>0.0319</v>
+        <v>0.0156</v>
       </c>
       <c r="AQ15" s="8" t="n">
-        <v>18706973</v>
+        <v>9306473</v>
       </c>
       <c r="AR15" s="9" t="n">
-        <v>294644.18</v>
+        <v>157065.34</v>
       </c>
       <c r="AS15" s="10" t="n">
-        <v>0.0335</v>
+        <v>0.0178</v>
       </c>
       <c r="AT15" s="8" t="n">
-        <v>18706973</v>
+        <v>9306473</v>
       </c>
       <c r="AU15" s="9" t="n">
-        <v>322779.47</v>
+        <v>174943.08</v>
       </c>
       <c r="AV15" s="10" t="n">
-        <v>0.036</v>
+        <v>0.0195</v>
       </c>
     </row>
     <row r="16">
@@ -2880,12 +2904,12 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences Limited</t>
+          <t>Cipla Limited</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>INE010B01027</t>
+          <t>INE059A01026</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -2894,150 +2918,150 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>18853686</v>
+        <v>13271296</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>164253.31</v>
+        <v>162467.21</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0.0127</v>
+        <v>0.0126</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>18853686</v>
+        <v>12881359</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>173774.42</v>
+        <v>173666.48</v>
       </c>
       <c r="I17" s="10" t="n">
         <v>0.0129</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>18750502</v>
+        <v>12623339</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>165998.19</v>
+        <v>167133.01</v>
       </c>
       <c r="L17" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="M17" s="8" t="n">
+        <v>10989584</v>
+      </c>
+      <c r="N17" s="9" t="n">
+        <v>166085.58</v>
+      </c>
+      <c r="O17" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="P17" s="8" t="n">
+        <v>10765866</v>
+      </c>
+      <c r="Q17" s="9" t="n">
+        <v>164857.71</v>
+      </c>
+      <c r="R17" s="10" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="S17" s="8" t="n">
+        <v>10173460</v>
+      </c>
+      <c r="T17" s="9" t="n">
+        <v>152734.15</v>
+      </c>
+      <c r="U17" s="10" t="n">
+        <v>0.0121</v>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v>9988840</v>
+      </c>
+      <c r="W17" s="9" t="n">
+        <v>150162.23</v>
+      </c>
+      <c r="X17" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="Y17" s="8" t="n">
+        <v>8991707</v>
+      </c>
+      <c r="Z17" s="9" t="n">
+        <v>142914.19</v>
+      </c>
+      <c r="AA17" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="M17" s="8" t="n">
-        <v>17903094</v>
-      </c>
-      <c r="N17" s="9" t="n">
-        <v>163696.94</v>
-      </c>
-      <c r="O17" s="10" t="n">
-        <v>0.0123</v>
-      </c>
-      <c r="P17" s="8" t="n">
-        <v>17405149</v>
-      </c>
-      <c r="Q17" s="9" t="n">
-        <v>164043.53</v>
-      </c>
-      <c r="R17" s="10" t="n">
-        <v>0.0126</v>
-      </c>
-      <c r="S17" s="8" t="n">
-        <v>15759789</v>
-      </c>
-      <c r="T17" s="9" t="n">
-        <v>153571.26</v>
-      </c>
-      <c r="U17" s="10" t="n">
-        <v>0.0122</v>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v>15148311</v>
-      </c>
-      <c r="W17" s="9" t="n">
-        <v>148741.27</v>
-      </c>
-      <c r="X17" s="10" t="n">
-        <v>0.0124</v>
-      </c>
-      <c r="Y17" s="8" t="n">
-        <v>14786344</v>
-      </c>
-      <c r="Z17" s="9" t="n">
-        <v>145061.43</v>
-      </c>
-      <c r="AA17" s="10" t="n">
-        <v>0.0126</v>
-      </c>
       <c r="AB17" s="8" t="n">
-        <v>14470385</v>
+        <v>9450707</v>
       </c>
       <c r="AC17" s="9" t="n">
-        <v>140333.79</v>
+        <v>146920.69</v>
       </c>
       <c r="AD17" s="10" t="n">
-        <v>0.0124</v>
+        <v>0.013</v>
       </c>
       <c r="AE17" s="8" t="n">
-        <v>14258435</v>
+        <v>9147124</v>
       </c>
       <c r="AF17" s="9" t="n">
-        <v>141151.38</v>
+        <v>137746.54</v>
       </c>
       <c r="AG17" s="10" t="n">
-        <v>0.0128</v>
+        <v>0.0125</v>
       </c>
       <c r="AH17" s="8" t="n">
-        <v>14258435</v>
+        <v>8881919</v>
       </c>
       <c r="AI17" s="9" t="n">
-        <v>132603.45</v>
+        <v>130182.29</v>
       </c>
       <c r="AJ17" s="10" t="n">
-        <v>0.0128</v>
+        <v>0.0125</v>
       </c>
       <c r="AK17" s="8" t="n">
-        <v>13936283</v>
+        <v>7994194</v>
       </c>
       <c r="AL17" s="9" t="n">
-        <v>123789.03</v>
+        <v>123918</v>
       </c>
       <c r="AM17" s="10" t="n">
         <v>0.0126</v>
       </c>
       <c r="AN17" s="8" t="n">
-        <v>13003659</v>
+        <v>7994194</v>
       </c>
       <c r="AO17" s="9" t="n">
-        <v>115264.43</v>
+        <v>115292.27</v>
       </c>
       <c r="AP17" s="10" t="n">
         <v>0.0123</v>
       </c>
       <c r="AQ17" s="8" t="n">
-        <v>11479604</v>
+        <v>7755553</v>
       </c>
       <c r="AR17" s="9" t="n">
-        <v>100630.21</v>
+        <v>109159.41</v>
       </c>
       <c r="AS17" s="10" t="n">
-        <v>0.0114</v>
+        <v>0.0124</v>
       </c>
       <c r="AT17" s="8" t="n">
-        <v>8859127</v>
+        <v>6223549</v>
       </c>
       <c r="AU17" s="9" t="n">
-        <v>85955.67999999999</v>
+        <v>92071.17999999999</v>
       </c>
       <c r="AV17" s="10" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0103</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Cipla Limited</t>
+          <t>Zydus Lifesciences Limited</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>INE059A01026</t>
+          <t>INE010B01027</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -3046,291 +3070,291 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>13271296</v>
+        <v>18853686</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>162467.21</v>
+        <v>164253.31</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>0.0126</v>
+        <v>0.0127</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>12881359</v>
+        <v>18853686</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>173666.48</v>
+        <v>173774.42</v>
       </c>
       <c r="I18" s="10" t="n">
         <v>0.0129</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>12623339</v>
+        <v>18750502</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>167133.01</v>
+        <v>165998.19</v>
       </c>
       <c r="L18" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.0124</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>10989584</v>
+        <v>17903094</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>166085.58</v>
+        <v>163696.94</v>
       </c>
       <c r="O18" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.0123</v>
       </c>
       <c r="P18" s="8" t="n">
-        <v>10765866</v>
+        <v>17405149</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>164857.71</v>
+        <v>164043.53</v>
       </c>
       <c r="R18" s="10" t="n">
-        <v>0.0127</v>
+        <v>0.0126</v>
       </c>
       <c r="S18" s="8" t="n">
-        <v>10173460</v>
+        <v>15759789</v>
       </c>
       <c r="T18" s="9" t="n">
-        <v>152734.15</v>
+        <v>153571.26</v>
       </c>
       <c r="U18" s="10" t="n">
-        <v>0.0121</v>
+        <v>0.0122</v>
       </c>
       <c r="V18" s="8" t="n">
-        <v>9988840</v>
+        <v>15148311</v>
       </c>
       <c r="W18" s="9" t="n">
-        <v>150162.23</v>
+        <v>148741.27</v>
       </c>
       <c r="X18" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.0124</v>
       </c>
       <c r="Y18" s="8" t="n">
-        <v>8991707</v>
+        <v>14786344</v>
       </c>
       <c r="Z18" s="9" t="n">
-        <v>142914.19</v>
+        <v>145061.43</v>
       </c>
       <c r="AA18" s="10" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="AB18" s="8" t="n">
+        <v>14470385</v>
+      </c>
+      <c r="AC18" s="9" t="n">
+        <v>140333.79</v>
+      </c>
+      <c r="AD18" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="AB18" s="8" t="n">
-        <v>9450707</v>
-      </c>
-      <c r="AC18" s="9" t="n">
-        <v>146920.69</v>
-      </c>
-      <c r="AD18" s="10" t="n">
-        <v>0.013</v>
-      </c>
       <c r="AE18" s="8" t="n">
-        <v>9147124</v>
+        <v>14258435</v>
       </c>
       <c r="AF18" s="9" t="n">
-        <v>137746.54</v>
+        <v>141151.38</v>
       </c>
       <c r="AG18" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.0128</v>
       </c>
       <c r="AH18" s="8" t="n">
-        <v>8881919</v>
+        <v>14258435</v>
       </c>
       <c r="AI18" s="9" t="n">
-        <v>130182.29</v>
+        <v>132603.45</v>
       </c>
       <c r="AJ18" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.0128</v>
       </c>
       <c r="AK18" s="8" t="n">
-        <v>7994194</v>
+        <v>13936283</v>
       </c>
       <c r="AL18" s="9" t="n">
-        <v>123918</v>
+        <v>123789.03</v>
       </c>
       <c r="AM18" s="10" t="n">
         <v>0.0126</v>
       </c>
       <c r="AN18" s="8" t="n">
-        <v>7994194</v>
+        <v>13003659</v>
       </c>
       <c r="AO18" s="9" t="n">
-        <v>115292.27</v>
+        <v>115264.43</v>
       </c>
       <c r="AP18" s="10" t="n">
         <v>0.0123</v>
       </c>
       <c r="AQ18" s="8" t="n">
-        <v>7755553</v>
+        <v>11479604</v>
       </c>
       <c r="AR18" s="9" t="n">
-        <v>109159.41</v>
+        <v>100630.21</v>
       </c>
       <c r="AS18" s="10" t="n">
-        <v>0.0124</v>
+        <v>0.0114</v>
       </c>
       <c r="AT18" s="8" t="n">
-        <v>6223549</v>
+        <v>8859127</v>
       </c>
       <c r="AU18" s="9" t="n">
-        <v>92071.17999999999</v>
+        <v>85955.67999999999</v>
       </c>
       <c r="AV18" s="10" t="n">
-        <v>0.0103</v>
+        <v>0.009599999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Infosys Limited</t>
+          <t>Balkrishna Industries Limited</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>INE009A01021</t>
+          <t>INE787D01026</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>IT - Software</t>
+          <t>Auto Components</t>
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>26944033</v>
+        <v>2274074</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>336962.08</v>
+        <v>47368.96</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>0.0261</v>
+        <v>0.0037</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>20693682</v>
+        <v>2906065</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>269038.56</v>
+        <v>69277.67999999999</v>
       </c>
       <c r="I19" s="10" t="n">
-        <v>0.02</v>
+        <v>0.0052</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>16509541</v>
+        <v>4189074</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>270921.57</v>
+        <v>96591.67</v>
       </c>
       <c r="L19" s="10" t="n">
-        <v>0.0202</v>
+        <v>0.0072</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>16417936</v>
+        <v>4189074</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>265215.34</v>
+        <v>97173.95</v>
       </c>
       <c r="O19" s="10" t="n">
-        <v>0.0199</v>
+        <v>0.0073</v>
       </c>
       <c r="P19" s="8" t="n">
-        <v>17621740</v>
+        <v>4189074</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>274916.77</v>
+        <v>96721.53</v>
       </c>
       <c r="R19" s="10" t="n">
-        <v>0.0212</v>
+        <v>0.0075</v>
       </c>
       <c r="S19" s="8" t="n">
-        <v>9306473</v>
+        <v>4189074</v>
       </c>
       <c r="T19" s="9" t="n">
-        <v>137949.85</v>
+        <v>95502.50999999999</v>
       </c>
       <c r="U19" s="10" t="n">
-        <v>0.011</v>
+        <v>0.0076</v>
       </c>
       <c r="V19" s="8" t="n">
-        <v>9306473</v>
+        <v>4189074</v>
       </c>
       <c r="W19" s="9" t="n">
-        <v>134180.73</v>
+        <v>96130.87</v>
       </c>
       <c r="X19" s="10" t="n">
-        <v>0.0112</v>
+        <v>0.008</v>
       </c>
       <c r="Y19" s="8" t="n">
-        <v>9306473</v>
+        <v>4189074</v>
       </c>
       <c r="Z19" s="9" t="n">
-        <v>136767.93</v>
+        <v>95904.66</v>
       </c>
       <c r="AA19" s="10" t="n">
-        <v>0.0119</v>
+        <v>0.0083</v>
       </c>
       <c r="AB19" s="8" t="n">
-        <v>9306473</v>
+        <v>4189074</v>
       </c>
       <c r="AC19" s="9" t="n">
-        <v>140434.68</v>
+        <v>112108</v>
       </c>
       <c r="AD19" s="10" t="n">
-        <v>0.0124</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="AE19" s="8" t="n">
-        <v>9306473</v>
+        <v>4189074</v>
       </c>
       <c r="AF19" s="9" t="n">
-        <v>149071.08</v>
+        <v>102435.43</v>
       </c>
       <c r="AG19" s="10" t="n">
-        <v>0.0135</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="AH19" s="8" t="n">
-        <v>9306473</v>
+        <v>4189074</v>
       </c>
       <c r="AI19" s="9" t="n">
-        <v>145432.25</v>
+        <v>103562.29</v>
       </c>
       <c r="AJ19" s="10" t="n">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
       <c r="AK19" s="8" t="n">
-        <v>9306473</v>
+        <v>4189074</v>
       </c>
       <c r="AL19" s="9" t="n">
-        <v>139606.4</v>
+        <v>112061.92</v>
       </c>
       <c r="AM19" s="10" t="n">
-        <v>0.0142</v>
+        <v>0.0114</v>
       </c>
       <c r="AN19" s="8" t="n">
-        <v>9306473</v>
+        <v>4189074</v>
       </c>
       <c r="AO19" s="9" t="n">
-        <v>146172.12</v>
+        <v>107022.46</v>
       </c>
       <c r="AP19" s="10" t="n">
-        <v>0.0156</v>
+        <v>0.0115</v>
       </c>
       <c r="AQ19" s="8" t="n">
-        <v>9306473</v>
+        <v>4189074</v>
       </c>
       <c r="AR19" s="9" t="n">
-        <v>157065.34</v>
+        <v>109571.51</v>
       </c>
       <c r="AS19" s="10" t="n">
-        <v>0.0178</v>
+        <v>0.0125</v>
       </c>
       <c r="AT19" s="8" t="n">
-        <v>9306473</v>
+        <v>4189074</v>
       </c>
       <c r="AU19" s="9" t="n">
-        <v>174943.08</v>
+        <v>116089.71</v>
       </c>
       <c r="AV19" s="10" t="n">
-        <v>0.0195</v>
+        <v>0.0129</v>
       </c>
     </row>
     <row r="20">
@@ -3488,169 +3512,115 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Balkrishna Industries Limited</t>
+          <t>Motilal Oswal Financial Services Limited</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>INE787D01026</t>
+          <t>INE338I01027</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Auto Components</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="n">
-        <v>2274074</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>47368.96</v>
-      </c>
-      <c r="F21" s="10" t="n">
-        <v>0.0037</v>
-      </c>
-      <c r="G21" s="8" t="n">
-        <v>2906065</v>
-      </c>
-      <c r="H21" s="9" t="n">
-        <v>69277.67999999999</v>
-      </c>
-      <c r="I21" s="10" t="n">
-        <v>0.0052</v>
-      </c>
-      <c r="J21" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="K21" s="9" t="n">
-        <v>96591.67</v>
-      </c>
-      <c r="L21" s="10" t="n">
+          <t>Capital Markets</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="8" t="n"/>
+      <c r="H21" s="9" t="n"/>
+      <c r="I21" s="10" t="n"/>
+      <c r="J21" s="8" t="n"/>
+      <c r="K21" s="9" t="n"/>
+      <c r="L21" s="10" t="n"/>
+      <c r="M21" s="8" t="n"/>
+      <c r="N21" s="9" t="n"/>
+      <c r="O21" s="10" t="n"/>
+      <c r="P21" s="8" t="n"/>
+      <c r="Q21" s="9" t="n"/>
+      <c r="R21" s="10" t="n"/>
+      <c r="S21" s="8" t="n"/>
+      <c r="T21" s="9" t="n"/>
+      <c r="U21" s="10" t="n"/>
+      <c r="V21" s="8" t="n"/>
+      <c r="W21" s="9" t="n"/>
+      <c r="X21" s="10" t="n"/>
+      <c r="Y21" s="8" t="n"/>
+      <c r="Z21" s="9" t="n"/>
+      <c r="AA21" s="10" t="n"/>
+      <c r="AB21" s="8" t="n"/>
+      <c r="AC21" s="9" t="n"/>
+      <c r="AD21" s="10" t="n"/>
+      <c r="AE21" s="8" t="n">
+        <v>591805</v>
+      </c>
+      <c r="AF21" s="9" t="n">
+        <v>5149</v>
+      </c>
+      <c r="AG21" s="10" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="AH21" s="8" t="n">
+        <v>5392631</v>
+      </c>
+      <c r="AI21" s="9" t="n">
+        <v>43674.92</v>
+      </c>
+      <c r="AJ21" s="10" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="AK21" s="8" t="n">
+        <v>8585949</v>
+      </c>
+      <c r="AL21" s="9" t="n">
+        <v>56044.78</v>
+      </c>
+      <c r="AM21" s="10" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="AN21" s="8" t="n">
+        <v>10913294</v>
+      </c>
+      <c r="AO21" s="9" t="n">
+        <v>67154.95</v>
+      </c>
+      <c r="AP21" s="10" t="n">
         <v>0.0072</v>
       </c>
-      <c r="M21" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="N21" s="9" t="n">
-        <v>97173.95</v>
-      </c>
-      <c r="O21" s="10" t="n">
-        <v>0.0073</v>
-      </c>
-      <c r="P21" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="Q21" s="9" t="n">
-        <v>96721.53</v>
-      </c>
-      <c r="R21" s="10" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="S21" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="T21" s="9" t="n">
-        <v>95502.50999999999</v>
-      </c>
-      <c r="U21" s="10" t="n">
-        <v>0.0076</v>
-      </c>
-      <c r="V21" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="W21" s="9" t="n">
-        <v>96130.87</v>
-      </c>
-      <c r="X21" s="10" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="Y21" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="Z21" s="9" t="n">
-        <v>95904.66</v>
-      </c>
-      <c r="AA21" s="10" t="n">
-        <v>0.0083</v>
-      </c>
-      <c r="AB21" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="AC21" s="9" t="n">
-        <v>112108</v>
-      </c>
-      <c r="AD21" s="10" t="n">
-        <v>0.009900000000000001</v>
-      </c>
-      <c r="AE21" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="AF21" s="9" t="n">
-        <v>102435.43</v>
-      </c>
-      <c r="AG21" s="10" t="n">
-        <v>0.009299999999999999</v>
-      </c>
-      <c r="AH21" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="AI21" s="9" t="n">
-        <v>103562.29</v>
-      </c>
-      <c r="AJ21" s="10" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AK21" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="AL21" s="9" t="n">
-        <v>112061.92</v>
-      </c>
-      <c r="AM21" s="10" t="n">
-        <v>0.0114</v>
-      </c>
-      <c r="AN21" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="AO21" s="9" t="n">
-        <v>107022.46</v>
-      </c>
-      <c r="AP21" s="10" t="n">
-        <v>0.0115</v>
-      </c>
       <c r="AQ21" s="8" t="n">
-        <v>4189074</v>
+        <v>12053879</v>
       </c>
       <c r="AR21" s="9" t="n">
-        <v>109571.51</v>
+        <v>70937.08</v>
       </c>
       <c r="AS21" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.0081</v>
       </c>
       <c r="AT21" s="8" t="n">
-        <v>4189074</v>
+        <v>12053879</v>
       </c>
       <c r="AU21" s="9" t="n">
-        <v>116089.71</v>
+        <v>76801.28999999999</v>
       </c>
       <c r="AV21" s="10" t="n">
-        <v>0.0129</v>
+        <v>0.0086</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited</t>
+          <t>Multi Commodity Exchange of India Limited</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>INE768C01010</t>
+          <t>INE745G01035</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D22" s="8" t="n"/>
@@ -3662,1457 +3632,1487 @@
       <c r="J22" s="8" t="n"/>
       <c r="K22" s="9" t="n"/>
       <c r="L22" s="10" t="n"/>
-      <c r="M22" s="8" t="n"/>
-      <c r="N22" s="9" t="n"/>
-      <c r="O22" s="10" t="n"/>
-      <c r="P22" s="8" t="n"/>
-      <c r="Q22" s="9" t="n"/>
-      <c r="R22" s="10" t="n"/>
-      <c r="S22" s="8" t="n"/>
-      <c r="T22" s="9" t="n"/>
-      <c r="U22" s="10" t="n"/>
-      <c r="V22" s="8" t="n"/>
-      <c r="W22" s="9" t="n"/>
-      <c r="X22" s="10" t="n"/>
+      <c r="M22" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="N22" s="9" t="n">
+        <v>88833.99000000001</v>
+      </c>
+      <c r="O22" s="10" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="P22" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="Q22" s="9" t="n">
+        <v>80358.22</v>
+      </c>
+      <c r="R22" s="10" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="S22" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="T22" s="9" t="n">
+        <v>73737.16</v>
+      </c>
+      <c r="U22" s="10" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="W22" s="9" t="n">
+        <v>62190.17</v>
+      </c>
+      <c r="X22" s="10" t="n">
+        <v>0.0052</v>
+      </c>
       <c r="Y22" s="8" t="n">
-        <v>4400000</v>
+        <v>797719</v>
       </c>
       <c r="Z22" s="9" t="n">
-        <v>88822.8</v>
+        <v>58951.43</v>
       </c>
       <c r="AA22" s="10" t="n">
-        <v>0.0077</v>
+        <v>0.0051</v>
       </c>
       <c r="AB22" s="8" t="n">
-        <v>4400000</v>
+        <v>797719</v>
       </c>
       <c r="AC22" s="9" t="n">
-        <v>89280.39999999999</v>
+        <v>61368.52</v>
       </c>
       <c r="AD22" s="10" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0054</v>
       </c>
       <c r="AE22" s="8" t="n">
-        <v>4400000</v>
+        <v>797719</v>
       </c>
       <c r="AF22" s="9" t="n">
-        <v>89020.8</v>
+        <v>71347.99000000001</v>
       </c>
       <c r="AG22" s="10" t="n">
-        <v>0.0081</v>
-      </c>
-      <c r="AH22" s="8" t="n"/>
-      <c r="AI22" s="9" t="n"/>
-      <c r="AJ22" s="10" t="n"/>
-      <c r="AK22" s="8" t="n"/>
-      <c r="AL22" s="9" t="n"/>
-      <c r="AM22" s="10" t="n"/>
-      <c r="AN22" s="8" t="n"/>
-      <c r="AO22" s="9" t="n"/>
-      <c r="AP22" s="10" t="n"/>
-      <c r="AQ22" s="8" t="n"/>
-      <c r="AR22" s="9" t="n"/>
-      <c r="AS22" s="10" t="n"/>
-      <c r="AT22" s="8" t="n"/>
-      <c r="AU22" s="9" t="n"/>
-      <c r="AV22" s="10" t="n"/>
+        <v>0.0065</v>
+      </c>
+      <c r="AH22" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AI22" s="9" t="n">
+        <v>52665.41</v>
+      </c>
+      <c r="AJ22" s="10" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="AK22" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AL22" s="9" t="n">
+        <v>48884.22</v>
+      </c>
+      <c r="AM22" s="10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="AN22" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AO22" s="9" t="n">
+        <v>42372.84</v>
+      </c>
+      <c r="AP22" s="10" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="AQ22" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AR22" s="9" t="n">
+        <v>39819.34</v>
+      </c>
+      <c r="AS22" s="10" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="AT22" s="8" t="n">
+        <v>882136</v>
+      </c>
+      <c r="AU22" s="9" t="n">
+        <v>50572.42</v>
+      </c>
+      <c r="AV22" s="10" t="n">
+        <v>0.0056</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Multi Commodity Exchange of India Limited</t>
+          <t>Narayana Hrudayalaya Limited</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>INE745G01035</t>
+          <t>INE410P01011</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="10" t="n"/>
-      <c r="G23" s="8" t="n"/>
-      <c r="H23" s="9" t="n"/>
-      <c r="I23" s="10" t="n"/>
-      <c r="J23" s="8" t="n"/>
-      <c r="K23" s="9" t="n"/>
-      <c r="L23" s="10" t="n"/>
+          <t>Healthcare Services</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>1995914</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>32040.41</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="G23" s="8" t="n">
+        <v>1995914</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>36543.19</v>
+      </c>
+      <c r="I23" s="10" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="J23" s="8" t="n">
+        <v>1995914</v>
+      </c>
+      <c r="K23" s="9" t="n">
+        <v>35285.76</v>
+      </c>
+      <c r="L23" s="10" t="n">
+        <v>0.0026</v>
+      </c>
       <c r="M23" s="8" t="n">
-        <v>797719</v>
+        <v>1995914</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>88833.99000000001</v>
+        <v>37762.69</v>
       </c>
       <c r="O23" s="10" t="n">
-        <v>0.0067</v>
+        <v>0.0028</v>
       </c>
       <c r="P23" s="8" t="n">
-        <v>797719</v>
+        <v>1995914</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>80358.22</v>
+        <v>38830.51</v>
       </c>
       <c r="R23" s="10" t="n">
-        <v>0.0062</v>
+        <v>0.003</v>
       </c>
       <c r="S23" s="8" t="n">
-        <v>797719</v>
+        <v>1995914</v>
       </c>
       <c r="T23" s="9" t="n">
-        <v>73737.16</v>
+        <v>35076.19</v>
       </c>
       <c r="U23" s="10" t="n">
-        <v>0.0059</v>
+        <v>0.0028</v>
       </c>
       <c r="V23" s="8" t="n">
-        <v>797719</v>
+        <v>1995914</v>
       </c>
       <c r="W23" s="9" t="n">
-        <v>62190.17</v>
+        <v>34681</v>
       </c>
       <c r="X23" s="10" t="n">
-        <v>0.0052</v>
+        <v>0.0029</v>
       </c>
       <c r="Y23" s="8" t="n">
-        <v>797719</v>
+        <v>1995914</v>
       </c>
       <c r="Z23" s="9" t="n">
-        <v>58951.43</v>
+        <v>35004.34</v>
       </c>
       <c r="AA23" s="10" t="n">
-        <v>0.0051</v>
+        <v>0.003</v>
       </c>
       <c r="AB23" s="8" t="n">
-        <v>797719</v>
+        <v>1995914</v>
       </c>
       <c r="AC23" s="9" t="n">
-        <v>61368.52</v>
+        <v>38225.74</v>
       </c>
       <c r="AD23" s="10" t="n">
-        <v>0.0054</v>
+        <v>0.0034</v>
       </c>
       <c r="AE23" s="8" t="n">
-        <v>797719</v>
+        <v>1995914</v>
       </c>
       <c r="AF23" s="9" t="n">
-        <v>71347.99000000001</v>
+        <v>43319.32</v>
       </c>
       <c r="AG23" s="10" t="n">
-        <v>0.0065</v>
+        <v>0.0039</v>
       </c>
       <c r="AH23" s="8" t="n">
-        <v>797719</v>
+        <v>1995914</v>
       </c>
       <c r="AI23" s="9" t="n">
-        <v>52665.41</v>
+        <v>34806.74</v>
       </c>
       <c r="AJ23" s="10" t="n">
-        <v>0.0051</v>
+        <v>0.0034</v>
       </c>
       <c r="AK23" s="8" t="n">
-        <v>797719</v>
+        <v>1995914</v>
       </c>
       <c r="AL23" s="9" t="n">
-        <v>48884.22</v>
+        <v>35138.07</v>
       </c>
       <c r="AM23" s="10" t="n">
-        <v>0.005</v>
+        <v>0.0036</v>
       </c>
       <c r="AN23" s="8" t="n">
-        <v>797719</v>
+        <v>1995914</v>
       </c>
       <c r="AO23" s="9" t="n">
-        <v>42372.84</v>
+        <v>33771.86</v>
       </c>
       <c r="AP23" s="10" t="n">
-        <v>0.0045</v>
+        <v>0.0036</v>
       </c>
       <c r="AQ23" s="8" t="n">
-        <v>797719</v>
+        <v>1995914</v>
       </c>
       <c r="AR23" s="9" t="n">
-        <v>39819.34</v>
+        <v>28830.98</v>
       </c>
       <c r="AS23" s="10" t="n">
-        <v>0.0045</v>
+        <v>0.0033</v>
       </c>
       <c r="AT23" s="8" t="n">
-        <v>882136</v>
+        <v>1995914</v>
       </c>
       <c r="AU23" s="9" t="n">
-        <v>50572.42</v>
+        <v>27686.32</v>
       </c>
       <c r="AV23" s="10" t="n">
-        <v>0.0056</v>
+        <v>0.0031</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>EID Parry India Limited</t>
+          <t>IPCA Laboratories Limited</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>INE126A01031</t>
+          <t>INE571A01038</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="n">
-        <v>7394472</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>57344.13</v>
-      </c>
-      <c r="F24" s="10" t="n">
-        <v>0.0044</v>
-      </c>
-      <c r="G24" s="8" t="n">
-        <v>7394472</v>
-      </c>
-      <c r="H24" s="9" t="n">
-        <v>63976.97</v>
-      </c>
-      <c r="I24" s="10" t="n">
-        <v>0.0048</v>
-      </c>
-      <c r="J24" s="8" t="n">
-        <v>7362903</v>
-      </c>
-      <c r="K24" s="9" t="n">
-        <v>67966.96000000001</v>
-      </c>
-      <c r="L24" s="10" t="n">
-        <v>0.0051</v>
-      </c>
-      <c r="M24" s="8" t="n">
-        <v>6180145</v>
-      </c>
-      <c r="N24" s="9" t="n">
-        <v>63945.96</v>
-      </c>
-      <c r="O24" s="10" t="n">
-        <v>0.0048</v>
-      </c>
-      <c r="P24" s="8" t="n">
-        <v>5842830</v>
-      </c>
-      <c r="Q24" s="9" t="n">
-        <v>60233.73</v>
-      </c>
-      <c r="R24" s="10" t="n">
-        <v>0.0046</v>
-      </c>
-      <c r="S24" s="8" t="n">
-        <v>5528341</v>
-      </c>
-      <c r="T24" s="9" t="n">
-        <v>59285.93</v>
-      </c>
-      <c r="U24" s="10" t="n">
-        <v>0.0047</v>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v>4996218</v>
-      </c>
-      <c r="W24" s="9" t="n">
-        <v>51236.22</v>
-      </c>
-      <c r="X24" s="10" t="n">
-        <v>0.0043</v>
-      </c>
+          <t>Pharmaceuticals &amp; Biotechnology</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="10" t="n"/>
+      <c r="G24" s="8" t="n"/>
+      <c r="H24" s="9" t="n"/>
+      <c r="I24" s="10" t="n"/>
+      <c r="J24" s="8" t="n"/>
+      <c r="K24" s="9" t="n"/>
+      <c r="L24" s="10" t="n"/>
+      <c r="M24" s="8" t="n"/>
+      <c r="N24" s="9" t="n"/>
+      <c r="O24" s="10" t="n"/>
+      <c r="P24" s="8" t="n"/>
+      <c r="Q24" s="9" t="n"/>
+      <c r="R24" s="10" t="n"/>
+      <c r="S24" s="8" t="n"/>
+      <c r="T24" s="9" t="n"/>
+      <c r="U24" s="10" t="n"/>
+      <c r="V24" s="8" t="n"/>
+      <c r="W24" s="9" t="n"/>
+      <c r="X24" s="10" t="n"/>
       <c r="Y24" s="8" t="n">
-        <v>4433570</v>
+        <v>218075</v>
       </c>
       <c r="Z24" s="9" t="n">
-        <v>49913.13</v>
+        <v>3019.03</v>
       </c>
       <c r="AA24" s="10" t="n">
-        <v>0.0043</v>
+        <v>0.0003</v>
       </c>
       <c r="AB24" s="8" t="n">
-        <v>3997165</v>
+        <v>566216</v>
       </c>
       <c r="AC24" s="9" t="n">
-        <v>49305.03</v>
+        <v>8345.459999999999</v>
       </c>
       <c r="AD24" s="10" t="n">
-        <v>0.0044</v>
+        <v>0.0007</v>
       </c>
       <c r="AE24" s="8" t="n">
-        <v>3516819</v>
+        <v>1311557</v>
       </c>
       <c r="AF24" s="9" t="n">
-        <v>39036.69</v>
+        <v>18228.02</v>
       </c>
       <c r="AG24" s="10" t="n">
-        <v>0.0035</v>
+        <v>0.0017</v>
       </c>
       <c r="AH24" s="8" t="n">
-        <v>3243008</v>
+        <v>1641095</v>
       </c>
       <c r="AI24" s="9" t="n">
-        <v>30813.44</v>
+        <v>23382.32</v>
       </c>
       <c r="AJ24" s="10" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="AK24" s="8" t="n">
+        <v>1857217</v>
+      </c>
+      <c r="AL24" s="9" t="n">
+        <v>26023.32</v>
+      </c>
+      <c r="AM24" s="10" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="AN24" s="8" t="n">
+        <v>1926988</v>
+      </c>
+      <c r="AO24" s="9" t="n">
+        <v>28941.43</v>
+      </c>
+      <c r="AP24" s="10" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="AQ24" s="8" t="n">
+        <v>1926988</v>
+      </c>
+      <c r="AR24" s="9" t="n">
+        <v>26117.43</v>
+      </c>
+      <c r="AS24" s="10" t="n">
         <v>0.003</v>
       </c>
-      <c r="AK24" s="8" t="n">
-        <v>2988209</v>
-      </c>
-      <c r="AL24" s="9" t="n">
-        <v>24424.13</v>
-      </c>
-      <c r="AM24" s="10" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="AN24" s="8" t="n">
-        <v>2843265</v>
-      </c>
-      <c r="AO24" s="9" t="n">
-        <v>22336.69</v>
-      </c>
-      <c r="AP24" s="10" t="n">
-        <v>0.0024</v>
-      </c>
-      <c r="AQ24" s="8" t="n">
-        <v>2609056</v>
-      </c>
-      <c r="AR24" s="9" t="n">
-        <v>17326.74</v>
-      </c>
-      <c r="AS24" s="10" t="n">
-        <v>0.002</v>
-      </c>
       <c r="AT24" s="8" t="n">
-        <v>2259531</v>
+        <v>2246361</v>
       </c>
       <c r="AU24" s="9" t="n">
-        <v>18525.89</v>
+        <v>32421.73</v>
       </c>
       <c r="AV24" s="10" t="n">
-        <v>0.0021</v>
+        <v>0.0036</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Narayana Hrudayalaya Limited</t>
+          <t>Central Depository Services (India) Limited</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>INE410P01011</t>
+          <t>INE736A01011</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Healthcare Services</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>1995914</v>
+        <v>2264603</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>32040.41</v>
+        <v>25349.97</v>
       </c>
       <c r="F25" s="10" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="G25" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="H25" s="9" t="n">
+        <v>28810.28</v>
+      </c>
+      <c r="I25" s="10" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="J25" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="K25" s="9" t="n">
+        <v>29897.29</v>
+      </c>
+      <c r="L25" s="10" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="M25" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="N25" s="9" t="n">
+        <v>32691.81</v>
+      </c>
+      <c r="O25" s="10" t="n">
         <v>0.0025</v>
       </c>
-      <c r="G25" s="8" t="n">
-        <v>1995914</v>
-      </c>
-      <c r="H25" s="9" t="n">
-        <v>36543.19</v>
-      </c>
-      <c r="I25" s="10" t="n">
-        <v>0.0027</v>
-      </c>
-      <c r="J25" s="8" t="n">
-        <v>1995914</v>
-      </c>
-      <c r="K25" s="9" t="n">
-        <v>35285.76</v>
-      </c>
-      <c r="L25" s="10" t="n">
-        <v>0.0026</v>
-      </c>
-      <c r="M25" s="8" t="n">
-        <v>1995914</v>
-      </c>
-      <c r="N25" s="9" t="n">
-        <v>37762.69</v>
-      </c>
-      <c r="O25" s="10" t="n">
+      <c r="P25" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="Q25" s="9" t="n">
+        <v>36623.16</v>
+      </c>
+      <c r="R25" s="10" t="n">
         <v>0.0028</v>
       </c>
-      <c r="P25" s="8" t="n">
-        <v>1995914</v>
-      </c>
-      <c r="Q25" s="9" t="n">
-        <v>38830.51</v>
-      </c>
-      <c r="R25" s="10" t="n">
+      <c r="S25" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="T25" s="9" t="n">
+        <v>35943.78</v>
+      </c>
+      <c r="U25" s="10" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="W25" s="9" t="n">
+        <v>33031.5</v>
+      </c>
+      <c r="X25" s="10" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="Y25" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="Z25" s="9" t="n">
+        <v>32257.01</v>
+      </c>
+      <c r="AA25" s="10" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="AB25" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="AC25" s="9" t="n">
+        <v>33534.24</v>
+      </c>
+      <c r="AD25" s="10" t="n">
         <v>0.003</v>
       </c>
-      <c r="S25" s="8" t="n">
-        <v>1995914</v>
-      </c>
-      <c r="T25" s="9" t="n">
-        <v>35076.19</v>
-      </c>
-      <c r="U25" s="10" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v>1995914</v>
-      </c>
-      <c r="W25" s="9" t="n">
-        <v>34681</v>
-      </c>
-      <c r="X25" s="10" t="n">
+      <c r="AE25" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="AF25" s="9" t="n">
+        <v>40626.98</v>
+      </c>
+      <c r="AG25" s="10" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="AH25" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="AI25" s="9" t="n">
+        <v>34641.63</v>
+      </c>
+      <c r="AJ25" s="10" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="AK25" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="AL25" s="9" t="n">
+        <v>29892.76</v>
+      </c>
+      <c r="AM25" s="10" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="AN25" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="AO25" s="9" t="n">
+        <v>27629.29</v>
+      </c>
+      <c r="AP25" s="10" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="AQ25" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="AR25" s="9" t="n">
+        <v>25089.54</v>
+      </c>
+      <c r="AS25" s="10" t="n">
         <v>0.0029</v>
       </c>
-      <c r="Y25" s="8" t="n">
-        <v>1995914</v>
-      </c>
-      <c r="Z25" s="9" t="n">
-        <v>35004.34</v>
-      </c>
-      <c r="AA25" s="10" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="AB25" s="8" t="n">
-        <v>1995914</v>
-      </c>
-      <c r="AC25" s="9" t="n">
-        <v>38225.74</v>
-      </c>
-      <c r="AD25" s="10" t="n">
-        <v>0.0034</v>
-      </c>
-      <c r="AE25" s="8" t="n">
-        <v>1995914</v>
-      </c>
-      <c r="AF25" s="9" t="n">
-        <v>43319.32</v>
-      </c>
-      <c r="AG25" s="10" t="n">
-        <v>0.0039</v>
-      </c>
-      <c r="AH25" s="8" t="n">
-        <v>1995914</v>
-      </c>
-      <c r="AI25" s="9" t="n">
-        <v>34806.74</v>
-      </c>
-      <c r="AJ25" s="10" t="n">
-        <v>0.0034</v>
-      </c>
-      <c r="AK25" s="8" t="n">
-        <v>1995914</v>
-      </c>
-      <c r="AL25" s="9" t="n">
-        <v>35138.07</v>
-      </c>
-      <c r="AM25" s="10" t="n">
-        <v>0.0036</v>
-      </c>
-      <c r="AN25" s="8" t="n">
-        <v>1995914</v>
-      </c>
-      <c r="AO25" s="9" t="n">
-        <v>33771.86</v>
-      </c>
-      <c r="AP25" s="10" t="n">
-        <v>0.0036</v>
-      </c>
-      <c r="AQ25" s="8" t="n">
-        <v>1995914</v>
-      </c>
-      <c r="AR25" s="9" t="n">
-        <v>28830.98</v>
-      </c>
-      <c r="AS25" s="10" t="n">
+      <c r="AT25" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="AU25" s="9" t="n">
+        <v>29659.51</v>
+      </c>
+      <c r="AV25" s="10" t="n">
         <v>0.0033</v>
-      </c>
-      <c r="AT25" s="8" t="n">
-        <v>1995914</v>
-      </c>
-      <c r="AU25" s="9" t="n">
-        <v>27686.32</v>
-      </c>
-      <c r="AV25" s="10" t="n">
-        <v>0.0031</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Central Depository Services (India)</t>
+          <t>EID Parry India Limited</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>INE736A01011</t>
+          <t>INE126A01031</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>2264603</v>
+        <v>7394472</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>25349.97</v>
+        <v>57344.13</v>
       </c>
       <c r="F26" s="10" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="G26" s="8" t="n">
+        <v>7394472</v>
+      </c>
+      <c r="H26" s="9" t="n">
+        <v>63976.97</v>
+      </c>
+      <c r="I26" s="10" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="J26" s="8" t="n">
+        <v>7362903</v>
+      </c>
+      <c r="K26" s="9" t="n">
+        <v>67966.96000000001</v>
+      </c>
+      <c r="L26" s="10" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="M26" s="8" t="n">
+        <v>6180145</v>
+      </c>
+      <c r="N26" s="9" t="n">
+        <v>63945.96</v>
+      </c>
+      <c r="O26" s="10" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="P26" s="8" t="n">
+        <v>5842830</v>
+      </c>
+      <c r="Q26" s="9" t="n">
+        <v>60233.73</v>
+      </c>
+      <c r="R26" s="10" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="S26" s="8" t="n">
+        <v>5528341</v>
+      </c>
+      <c r="T26" s="9" t="n">
+        <v>59285.93</v>
+      </c>
+      <c r="U26" s="10" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v>4996218</v>
+      </c>
+      <c r="W26" s="9" t="n">
+        <v>51236.22</v>
+      </c>
+      <c r="X26" s="10" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="Y26" s="8" t="n">
+        <v>4433570</v>
+      </c>
+      <c r="Z26" s="9" t="n">
+        <v>49913.13</v>
+      </c>
+      <c r="AA26" s="10" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="AB26" s="8" t="n">
+        <v>3997165</v>
+      </c>
+      <c r="AC26" s="9" t="n">
+        <v>49305.03</v>
+      </c>
+      <c r="AD26" s="10" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="AE26" s="8" t="n">
+        <v>3516819</v>
+      </c>
+      <c r="AF26" s="9" t="n">
+        <v>39036.69</v>
+      </c>
+      <c r="AG26" s="10" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="AH26" s="8" t="n">
+        <v>3243008</v>
+      </c>
+      <c r="AI26" s="9" t="n">
+        <v>30813.44</v>
+      </c>
+      <c r="AJ26" s="10" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="AK26" s="8" t="n">
+        <v>2988209</v>
+      </c>
+      <c r="AL26" s="9" t="n">
+        <v>24424.13</v>
+      </c>
+      <c r="AM26" s="10" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="AN26" s="8" t="n">
+        <v>2843265</v>
+      </c>
+      <c r="AO26" s="9" t="n">
+        <v>22336.69</v>
+      </c>
+      <c r="AP26" s="10" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="AQ26" s="8" t="n">
+        <v>2609056</v>
+      </c>
+      <c r="AR26" s="9" t="n">
+        <v>17326.74</v>
+      </c>
+      <c r="AS26" s="10" t="n">
         <v>0.002</v>
       </c>
-      <c r="G26" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="H26" s="9" t="n">
-        <v>28810.28</v>
-      </c>
-      <c r="I26" s="10" t="n">
+      <c r="AT26" s="8" t="n">
+        <v>2259531</v>
+      </c>
+      <c r="AU26" s="9" t="n">
+        <v>18525.89</v>
+      </c>
+      <c r="AV26" s="10" t="n">
         <v>0.0021</v>
-      </c>
-      <c r="J26" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="K26" s="9" t="n">
-        <v>29897.29</v>
-      </c>
-      <c r="L26" s="10" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="M26" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="N26" s="9" t="n">
-        <v>32691.81</v>
-      </c>
-      <c r="O26" s="10" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="P26" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="Q26" s="9" t="n">
-        <v>36623.16</v>
-      </c>
-      <c r="R26" s="10" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="S26" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="T26" s="9" t="n">
-        <v>35943.78</v>
-      </c>
-      <c r="U26" s="10" t="n">
-        <v>0.0029</v>
-      </c>
-      <c r="V26" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="W26" s="9" t="n">
-        <v>33031.5</v>
-      </c>
-      <c r="X26" s="10" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="Y26" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="Z26" s="9" t="n">
-        <v>32257.01</v>
-      </c>
-      <c r="AA26" s="10" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="AB26" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="AC26" s="9" t="n">
-        <v>33534.24</v>
-      </c>
-      <c r="AD26" s="10" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="AE26" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="AF26" s="9" t="n">
-        <v>40626.98</v>
-      </c>
-      <c r="AG26" s="10" t="n">
-        <v>0.0037</v>
-      </c>
-      <c r="AH26" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="AI26" s="9" t="n">
-        <v>34641.63</v>
-      </c>
-      <c r="AJ26" s="10" t="n">
-        <v>0.0033</v>
-      </c>
-      <c r="AK26" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="AL26" s="9" t="n">
-        <v>29892.76</v>
-      </c>
-      <c r="AM26" s="10" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="AN26" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="AO26" s="9" t="n">
-        <v>27629.29</v>
-      </c>
-      <c r="AP26" s="10" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="AQ26" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="AR26" s="9" t="n">
-        <v>25089.54</v>
-      </c>
-      <c r="AS26" s="10" t="n">
-        <v>0.0029</v>
-      </c>
-      <c r="AT26" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="AU26" s="9" t="n">
-        <v>29659.51</v>
-      </c>
-      <c r="AV26" s="10" t="n">
-        <v>0.0033</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>ICRA Limited</t>
+          <t>ITC Hotels Limited</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>INE725G01011</t>
+          <t>INE379A01028</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="E27" s="9" t="n">
-        <v>14378.27</v>
-      </c>
-      <c r="F27" s="10" t="n">
-        <v>0.0011</v>
-      </c>
-      <c r="G27" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="H27" s="9" t="n">
-        <v>15895.71</v>
-      </c>
-      <c r="I27" s="10" t="n">
-        <v>0.0012</v>
-      </c>
-      <c r="J27" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="K27" s="9" t="n">
-        <v>18124.44</v>
-      </c>
-      <c r="L27" s="10" t="n">
-        <v>0.0014</v>
-      </c>
-      <c r="M27" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="N27" s="9" t="n">
-        <v>17460.56</v>
-      </c>
-      <c r="O27" s="10" t="n">
-        <v>0.0013</v>
-      </c>
-      <c r="P27" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="Q27" s="9" t="n">
-        <v>17812.62</v>
-      </c>
-      <c r="R27" s="10" t="n">
-        <v>0.0014</v>
-      </c>
-      <c r="S27" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="T27" s="9" t="n">
-        <v>18463.56</v>
-      </c>
-      <c r="U27" s="10" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="W27" s="9" t="n">
-        <v>18243.71</v>
-      </c>
-      <c r="X27" s="10" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="Y27" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="Z27" s="9" t="n">
-        <v>17962.06</v>
-      </c>
-      <c r="AA27" s="10" t="n">
-        <v>0.0016</v>
-      </c>
-      <c r="AB27" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="AC27" s="9" t="n">
-        <v>19048.41</v>
-      </c>
-      <c r="AD27" s="10" t="n">
-        <v>0.0017</v>
-      </c>
-      <c r="AE27" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="AF27" s="9" t="n">
-        <v>19453.63</v>
-      </c>
-      <c r="AG27" s="10" t="n">
+          <t>Leisure Services</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="10" t="n"/>
+      <c r="G27" s="8" t="n"/>
+      <c r="H27" s="9" t="n"/>
+      <c r="I27" s="10" t="n"/>
+      <c r="J27" s="8" t="n"/>
+      <c r="K27" s="9" t="n"/>
+      <c r="L27" s="10" t="n"/>
+      <c r="M27" s="8" t="n"/>
+      <c r="N27" s="9" t="n"/>
+      <c r="O27" s="10" t="n"/>
+      <c r="P27" s="8" t="n"/>
+      <c r="Q27" s="9" t="n"/>
+      <c r="R27" s="10" t="n"/>
+      <c r="S27" s="8" t="n"/>
+      <c r="T27" s="9" t="n"/>
+      <c r="U27" s="10" t="n"/>
+      <c r="V27" s="8" t="n"/>
+      <c r="W27" s="9" t="n"/>
+      <c r="X27" s="10" t="n"/>
+      <c r="Y27" s="8" t="n"/>
+      <c r="Z27" s="9" t="n"/>
+      <c r="AA27" s="10" t="n"/>
+      <c r="AB27" s="8" t="n"/>
+      <c r="AC27" s="9" t="n"/>
+      <c r="AD27" s="10" t="n"/>
+      <c r="AE27" s="8" t="n"/>
+      <c r="AF27" s="9" t="n"/>
+      <c r="AG27" s="10" t="n"/>
+      <c r="AH27" s="8" t="n"/>
+      <c r="AI27" s="9" t="n"/>
+      <c r="AJ27" s="10" t="n"/>
+      <c r="AK27" s="8" t="n"/>
+      <c r="AL27" s="9" t="n"/>
+      <c r="AM27" s="10" t="n"/>
+      <c r="AN27" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="AO27" s="9" t="n">
+        <v>19552.33</v>
+      </c>
+      <c r="AP27" s="10" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="AQ27" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="AR27" s="9" t="n">
+        <v>16216.23</v>
+      </c>
+      <c r="AS27" s="10" t="n">
         <v>0.0018</v>
       </c>
-      <c r="AH27" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="AI27" s="9" t="n">
-        <v>19370.29</v>
-      </c>
-      <c r="AJ27" s="10" t="n">
-        <v>0.0019</v>
-      </c>
-      <c r="AK27" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="AL27" s="9" t="n">
-        <v>15976.18</v>
-      </c>
-      <c r="AM27" s="10" t="n">
-        <v>0.0016</v>
-      </c>
-      <c r="AN27" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="AO27" s="9" t="n">
-        <v>15821.13</v>
-      </c>
-      <c r="AP27" s="10" t="n">
-        <v>0.0017</v>
-      </c>
-      <c r="AQ27" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="AR27" s="9" t="n">
-        <v>15273.64</v>
-      </c>
-      <c r="AS27" s="10" t="n">
-        <v>0.0017</v>
-      </c>
       <c r="AT27" s="8" t="n">
-        <v>297835</v>
+        <v>9899412</v>
       </c>
       <c r="AU27" s="9" t="n">
-        <v>18529.51</v>
+        <v>16131.09</v>
       </c>
       <c r="AV27" s="10" t="n">
-        <v>0.0021</v>
+        <v>0.0018</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Maharashtra Scooters Limited</t>
+          <t>ICRA Limited</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>INE288A01013</t>
+          <t>INE725G01011</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>80565</v>
+        <v>287393</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>8949.969999999999</v>
+        <v>14378.27</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>0.0007</v>
+        <v>0.0011</v>
       </c>
       <c r="G28" s="8" t="n">
-        <v>80565</v>
+        <v>287393</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>10682.11</v>
+        <v>15895.71</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>0.0008</v>
+        <v>0.0012</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>80552</v>
+        <v>287393</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>10825.38</v>
+        <v>18124.44</v>
       </c>
       <c r="L28" s="10" t="n">
-        <v>0.0008</v>
+        <v>0.0014</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>11401.01</v>
+        <v>17460.56</v>
       </c>
       <c r="O28" s="10" t="n">
-        <v>0.0009</v>
+        <v>0.0013</v>
       </c>
       <c r="P28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>11787.38</v>
+        <v>17812.62</v>
       </c>
       <c r="R28" s="10" t="n">
-        <v>0.0009</v>
+        <v>0.0014</v>
       </c>
       <c r="S28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="T28" s="9" t="n">
-        <v>12110.42</v>
+        <v>18463.56</v>
       </c>
       <c r="U28" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0015</v>
       </c>
       <c r="V28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="W28" s="9" t="n">
-        <v>13825.82</v>
+        <v>18243.71</v>
       </c>
       <c r="X28" s="10" t="n">
-        <v>0.0012</v>
+        <v>0.0015</v>
       </c>
       <c r="Y28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="Z28" s="9" t="n">
-        <v>12726.04</v>
+        <v>17962.06</v>
       </c>
       <c r="AA28" s="10" t="n">
-        <v>0.0011</v>
+        <v>0.0016</v>
       </c>
       <c r="AB28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="AC28" s="9" t="n">
-        <v>12868.73</v>
+        <v>19048.41</v>
       </c>
       <c r="AD28" s="10" t="n">
-        <v>0.0011</v>
+        <v>0.0017</v>
       </c>
       <c r="AE28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="AF28" s="9" t="n">
-        <v>11621.45</v>
+        <v>19453.63</v>
       </c>
       <c r="AG28" s="10" t="n">
-        <v>0.0011</v>
+        <v>0.0018</v>
       </c>
       <c r="AH28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="AI28" s="9" t="n">
-        <v>10722.07</v>
+        <v>19370.29</v>
       </c>
       <c r="AJ28" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0019</v>
       </c>
       <c r="AK28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="AL28" s="9" t="n">
-        <v>9198.25</v>
+        <v>15976.18</v>
       </c>
       <c r="AM28" s="10" t="n">
-        <v>0.0009</v>
+        <v>0.0016</v>
       </c>
       <c r="AN28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="AO28" s="9" t="n">
-        <v>8997.450000000001</v>
+        <v>15821.13</v>
       </c>
       <c r="AP28" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0017</v>
       </c>
       <c r="AQ28" s="8" t="n">
-        <v>80159</v>
+        <v>287393</v>
       </c>
       <c r="AR28" s="9" t="n">
-        <v>7401.52</v>
+        <v>15273.64</v>
       </c>
       <c r="AS28" s="10" t="n">
-        <v>0.0008</v>
+        <v>0.0017</v>
       </c>
       <c r="AT28" s="8" t="n">
-        <v>80159</v>
+        <v>297835</v>
       </c>
       <c r="AU28" s="9" t="n">
-        <v>7463.48</v>
+        <v>18529.51</v>
       </c>
       <c r="AV28" s="10" t="n">
-        <v>0.0008</v>
+        <v>0.0021</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>IPCA Laboratories Limited</t>
+          <t>Maharashtra Scooters Limited</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>INE571A01038</t>
+          <t>INE288A01013</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Pharmaceuticals &amp; Biotechnology</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="n"/>
-      <c r="E29" s="9" t="n"/>
-      <c r="F29" s="10" t="n"/>
-      <c r="G29" s="8" t="n"/>
-      <c r="H29" s="9" t="n"/>
-      <c r="I29" s="10" t="n"/>
-      <c r="J29" s="8" t="n"/>
-      <c r="K29" s="9" t="n"/>
-      <c r="L29" s="10" t="n"/>
-      <c r="M29" s="8" t="n"/>
-      <c r="N29" s="9" t="n"/>
-      <c r="O29" s="10" t="n"/>
-      <c r="P29" s="8" t="n"/>
-      <c r="Q29" s="9" t="n"/>
-      <c r="R29" s="10" t="n"/>
-      <c r="S29" s="8" t="n"/>
-      <c r="T29" s="9" t="n"/>
-      <c r="U29" s="10" t="n"/>
-      <c r="V29" s="8" t="n"/>
-      <c r="W29" s="9" t="n"/>
-      <c r="X29" s="10" t="n"/>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>80565</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>8949.969999999999</v>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="G29" s="8" t="n">
+        <v>80565</v>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>10682.11</v>
+      </c>
+      <c r="I29" s="10" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="J29" s="8" t="n">
+        <v>80552</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <v>10825.38</v>
+      </c>
+      <c r="L29" s="10" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="M29" s="8" t="n">
+        <v>80159</v>
+      </c>
+      <c r="N29" s="9" t="n">
+        <v>11401.01</v>
+      </c>
+      <c r="O29" s="10" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="P29" s="8" t="n">
+        <v>80159</v>
+      </c>
+      <c r="Q29" s="9" t="n">
+        <v>11787.38</v>
+      </c>
+      <c r="R29" s="10" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="S29" s="8" t="n">
+        <v>80159</v>
+      </c>
+      <c r="T29" s="9" t="n">
+        <v>12110.42</v>
+      </c>
+      <c r="U29" s="10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v>80159</v>
+      </c>
+      <c r="W29" s="9" t="n">
+        <v>13825.82</v>
+      </c>
+      <c r="X29" s="10" t="n">
+        <v>0.0012</v>
+      </c>
       <c r="Y29" s="8" t="n">
-        <v>218075</v>
+        <v>80159</v>
       </c>
       <c r="Z29" s="9" t="n">
-        <v>3019.03</v>
+        <v>12726.04</v>
       </c>
       <c r="AA29" s="10" t="n">
-        <v>0.0003</v>
+        <v>0.0011</v>
       </c>
       <c r="AB29" s="8" t="n">
-        <v>566216</v>
+        <v>80159</v>
       </c>
       <c r="AC29" s="9" t="n">
-        <v>8345.459999999999</v>
+        <v>12868.73</v>
       </c>
       <c r="AD29" s="10" t="n">
-        <v>0.0007</v>
+        <v>0.0011</v>
       </c>
       <c r="AE29" s="8" t="n">
-        <v>1311557</v>
+        <v>80159</v>
       </c>
       <c r="AF29" s="9" t="n">
-        <v>18228.02</v>
+        <v>11621.45</v>
       </c>
       <c r="AG29" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.0011</v>
       </c>
       <c r="AH29" s="8" t="n">
-        <v>1641095</v>
+        <v>80159</v>
       </c>
       <c r="AI29" s="9" t="n">
-        <v>23382.32</v>
+        <v>10722.07</v>
       </c>
       <c r="AJ29" s="10" t="n">
-        <v>0.0023</v>
+        <v>0.001</v>
       </c>
       <c r="AK29" s="8" t="n">
-        <v>1857217</v>
+        <v>80159</v>
       </c>
       <c r="AL29" s="9" t="n">
-        <v>26023.32</v>
+        <v>9198.25</v>
       </c>
       <c r="AM29" s="10" t="n">
-        <v>0.0026</v>
+        <v>0.0009</v>
       </c>
       <c r="AN29" s="8" t="n">
-        <v>1926988</v>
+        <v>80159</v>
       </c>
       <c r="AO29" s="9" t="n">
-        <v>28941.43</v>
+        <v>8997.450000000001</v>
       </c>
       <c r="AP29" s="10" t="n">
-        <v>0.0031</v>
+        <v>0.001</v>
       </c>
       <c r="AQ29" s="8" t="n">
-        <v>1926988</v>
+        <v>80159</v>
       </c>
       <c r="AR29" s="9" t="n">
-        <v>26117.43</v>
+        <v>7401.52</v>
       </c>
       <c r="AS29" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0008</v>
       </c>
       <c r="AT29" s="8" t="n">
-        <v>2246361</v>
+        <v>80159</v>
       </c>
       <c r="AU29" s="9" t="n">
-        <v>32421.73</v>
+        <v>7463.48</v>
       </c>
       <c r="AV29" s="10" t="n">
-        <v>0.0036</v>
+        <v>0.0008</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Nesco Limited</t>
+          <t>Swaraj Engines Limited</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>INE317F01035</t>
+          <t>INE277A01016</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Commercial Services &amp; Supplies</t>
+          <t>Industrial Products</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>1538.11</v>
+        <v>1564.88</v>
       </c>
       <c r="F30" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="G30" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>1704.36</v>
+        <v>1700.33</v>
       </c>
       <c r="I30" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>1728.63</v>
+        <v>1637.61</v>
       </c>
       <c r="L30" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="M30" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>1858.32</v>
+        <v>1691.91</v>
       </c>
       <c r="O30" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="P30" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>1947.66</v>
+        <v>1764.08</v>
       </c>
       <c r="R30" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="S30" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="T30" s="9" t="n">
-        <v>2076.6</v>
+        <v>1892.15</v>
       </c>
       <c r="U30" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="V30" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="W30" s="9" t="n">
-        <v>1987.1</v>
+        <v>1955.38</v>
       </c>
       <c r="X30" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="Y30" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="Z30" s="9" t="n">
-        <v>2130.6</v>
+        <v>1897.21</v>
       </c>
       <c r="AA30" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="AB30" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AC30" s="9" t="n">
-        <v>2091.16</v>
+        <v>1983.66</v>
       </c>
       <c r="AD30" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="AE30" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AF30" s="9" t="n">
-        <v>1766.62</v>
+        <v>1867.41</v>
       </c>
       <c r="AG30" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="AH30" s="8" t="n">
-        <v>89469</v>
+        <v>47293</v>
       </c>
       <c r="AI30" s="9" t="n">
-        <v>828.48</v>
+        <v>1857.76</v>
       </c>
       <c r="AJ30" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AK30" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="AL30" s="9" t="n">
+        <v>1925.39</v>
+      </c>
+      <c r="AM30" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AN30" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="AO30" s="9" t="n">
+        <v>1844.17</v>
+      </c>
+      <c r="AP30" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AQ30" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="AR30" s="9" t="n">
+        <v>1236.83</v>
+      </c>
+      <c r="AS30" s="10" t="n">
         <v>0.0001</v>
       </c>
-      <c r="AK30" s="8" t="n"/>
-      <c r="AL30" s="9" t="n"/>
-      <c r="AM30" s="10" t="n"/>
-      <c r="AN30" s="8" t="n"/>
-      <c r="AO30" s="9" t="n"/>
-      <c r="AP30" s="10" t="n"/>
-      <c r="AQ30" s="8" t="n"/>
-      <c r="AR30" s="9" t="n"/>
-      <c r="AS30" s="10" t="n"/>
-      <c r="AT30" s="8" t="n"/>
-      <c r="AU30" s="9" t="n"/>
-      <c r="AV30" s="10" t="n"/>
+      <c r="AT30" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="AU30" s="9" t="n">
+        <v>1612.64</v>
+      </c>
+      <c r="AV30" s="10" t="n">
+        <v>0.0002</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Swaraj Engines Limited</t>
+          <t>Nesco Limited</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>INE277A01016</t>
+          <t>INE317F01035</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Industrial Products</t>
+          <t>Commercial Services &amp; Supplies</t>
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>1564.88</v>
+        <v>1538.11</v>
       </c>
       <c r="F31" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="G31" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>1700.33</v>
+        <v>1704.36</v>
       </c>
       <c r="I31" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>1637.61</v>
+        <v>1728.63</v>
       </c>
       <c r="L31" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="M31" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>1691.91</v>
+        <v>1858.32</v>
       </c>
       <c r="O31" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="P31" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>1764.08</v>
+        <v>1947.66</v>
       </c>
       <c r="R31" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="S31" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="T31" s="9" t="n">
-        <v>1892.15</v>
+        <v>2076.6</v>
       </c>
       <c r="U31" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="V31" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="W31" s="9" t="n">
-        <v>1955.38</v>
+        <v>1987.1</v>
       </c>
       <c r="X31" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="Y31" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="Z31" s="9" t="n">
-        <v>1897.21</v>
+        <v>2130.6</v>
       </c>
       <c r="AA31" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="AB31" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AC31" s="9" t="n">
-        <v>1983.66</v>
+        <v>2091.16</v>
       </c>
       <c r="AD31" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="AE31" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AF31" s="9" t="n">
-        <v>1867.41</v>
+        <v>1766.62</v>
       </c>
       <c r="AG31" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="AH31" s="8" t="n">
-        <v>47293</v>
+        <v>89469</v>
       </c>
       <c r="AI31" s="9" t="n">
-        <v>1857.76</v>
+        <v>828.48</v>
       </c>
       <c r="AJ31" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AK31" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="AL31" s="9" t="n">
-        <v>1925.39</v>
-      </c>
-      <c r="AM31" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AN31" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="AO31" s="9" t="n">
-        <v>1844.17</v>
-      </c>
-      <c r="AP31" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AQ31" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="AR31" s="9" t="n">
-        <v>1236.83</v>
-      </c>
-      <c r="AS31" s="10" t="n">
         <v>0.0001</v>
       </c>
-      <c r="AT31" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="AU31" s="9" t="n">
-        <v>1612.64</v>
-      </c>
-      <c r="AV31" s="10" t="n">
-        <v>0.0002</v>
-      </c>
+      <c r="AK31" s="8" t="n"/>
+      <c r="AL31" s="9" t="n"/>
+      <c r="AM31" s="10" t="n"/>
+      <c r="AN31" s="8" t="n"/>
+      <c r="AO31" s="9" t="n"/>
+      <c r="AP31" s="10" t="n"/>
+      <c r="AQ31" s="8" t="n"/>
+      <c r="AR31" s="9" t="n"/>
+      <c r="AS31" s="10" t="n"/>
+      <c r="AT31" s="8" t="n"/>
+      <c r="AU31" s="9" t="n"/>
+      <c r="AV31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Motilal Oswal Financial Services Limited</t>
+          <t>Bharti Airtel Limited</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>INE338I01027</t>
+          <t>INE397D01024</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="n"/>
-      <c r="E32" s="9" t="n"/>
-      <c r="F32" s="10" t="n"/>
-      <c r="G32" s="8" t="n"/>
-      <c r="H32" s="9" t="n"/>
-      <c r="I32" s="10" t="n"/>
-      <c r="J32" s="8" t="n"/>
-      <c r="K32" s="9" t="n"/>
-      <c r="L32" s="10" t="n"/>
-      <c r="M32" s="8" t="n"/>
-      <c r="N32" s="9" t="n"/>
-      <c r="O32" s="10" t="n"/>
-      <c r="P32" s="8" t="n"/>
-      <c r="Q32" s="9" t="n"/>
-      <c r="R32" s="10" t="n"/>
-      <c r="S32" s="8" t="n"/>
-      <c r="T32" s="9" t="n"/>
-      <c r="U32" s="10" t="n"/>
-      <c r="V32" s="8" t="n"/>
-      <c r="W32" s="9" t="n"/>
-      <c r="X32" s="10" t="n"/>
-      <c r="Y32" s="8" t="n"/>
-      <c r="Z32" s="9" t="n"/>
-      <c r="AA32" s="10" t="n"/>
-      <c r="AB32" s="8" t="n"/>
-      <c r="AC32" s="9" t="n"/>
-      <c r="AD32" s="10" t="n"/>
+          <t>Telecom - Services</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>21167034</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>377281.21</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>0.0293</v>
+      </c>
+      <c r="G32" s="8" t="n">
+        <v>21167034</v>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>397792.07</v>
+      </c>
+      <c r="I32" s="10" t="n">
+        <v>0.0296</v>
+      </c>
+      <c r="J32" s="8" t="n">
+        <v>21167034</v>
+      </c>
+      <c r="K32" s="9" t="n">
+        <v>416715.398358</v>
+      </c>
+      <c r="L32" s="10" t="n">
+        <v>0.0311051731198606</v>
+      </c>
+      <c r="M32" s="8" t="n">
+        <v>21167034</v>
+      </c>
+      <c r="N32" s="9" t="n">
+        <v>445693.07</v>
+      </c>
+      <c r="O32" s="10" t="n">
+        <v>0.0334</v>
+      </c>
+      <c r="P32" s="8" t="n">
+        <v>21167034</v>
+      </c>
+      <c r="Q32" s="9" t="n">
+        <v>444846.39</v>
+      </c>
+      <c r="R32" s="10" t="n">
+        <v>0.0343</v>
+      </c>
+      <c r="S32" s="8" t="n">
+        <v>21167034</v>
+      </c>
+      <c r="T32" s="9" t="n">
+        <v>434876.71</v>
+      </c>
+      <c r="U32" s="10" t="n">
+        <v>0.0346</v>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v>21167034</v>
+      </c>
+      <c r="W32" s="9" t="n">
+        <v>397601.57</v>
+      </c>
+      <c r="X32" s="10" t="n">
+        <v>0.0332</v>
+      </c>
+      <c r="Y32" s="8" t="n">
+        <v>21167034</v>
+      </c>
+      <c r="Z32" s="9" t="n">
+        <v>399802.94</v>
+      </c>
+      <c r="AA32" s="10" t="n">
+        <v>0.0348</v>
+      </c>
+      <c r="AB32" s="8" t="n">
+        <v>21167034</v>
+      </c>
+      <c r="AC32" s="9" t="n">
+        <v>405200.53</v>
+      </c>
+      <c r="AD32" s="10" t="n">
+        <v>0.0358</v>
+      </c>
       <c r="AE32" s="8" t="n">
-        <v>591805</v>
+        <v>20937034</v>
       </c>
       <c r="AF32" s="9" t="n">
-        <v>5149</v>
+        <v>420750.64</v>
       </c>
       <c r="AG32" s="10" t="n">
-        <v>0.0005</v>
+        <v>0.0381</v>
       </c>
       <c r="AH32" s="8" t="n">
-        <v>5392631</v>
+        <v>11799076</v>
       </c>
       <c r="AI32" s="9" t="n">
-        <v>43674.92</v>
+        <v>219014.45</v>
       </c>
       <c r="AJ32" s="10" t="n">
-        <v>0.0042</v>
-      </c>
-      <c r="AK32" s="8" t="n">
-        <v>8585949</v>
-      </c>
-      <c r="AL32" s="9" t="n">
-        <v>56044.78</v>
-      </c>
-      <c r="AM32" s="10" t="n">
-        <v>0.0057</v>
-      </c>
-      <c r="AN32" s="8" t="n">
-        <v>10913294</v>
-      </c>
-      <c r="AO32" s="9" t="n">
-        <v>67154.95</v>
-      </c>
-      <c r="AP32" s="10" t="n">
-        <v>0.0072</v>
-      </c>
-      <c r="AQ32" s="8" t="n">
-        <v>12053879</v>
-      </c>
-      <c r="AR32" s="9" t="n">
-        <v>70937.08</v>
-      </c>
-      <c r="AS32" s="10" t="n">
-        <v>0.0081</v>
-      </c>
-      <c r="AT32" s="8" t="n">
-        <v>12053879</v>
-      </c>
-      <c r="AU32" s="9" t="n">
-        <v>76801.28999999999</v>
-      </c>
-      <c r="AV32" s="10" t="n">
-        <v>0.0086</v>
-      </c>
+        <v>0.0211</v>
+      </c>
+      <c r="AK32" s="8" t="n"/>
+      <c r="AL32" s="9" t="n"/>
+      <c r="AM32" s="10" t="n"/>
+      <c r="AN32" s="8" t="n"/>
+      <c r="AO32" s="9" t="n"/>
+      <c r="AP32" s="10" t="n"/>
+      <c r="AQ32" s="8" t="n"/>
+      <c r="AR32" s="9" t="n"/>
+      <c r="AS32" s="10" t="n"/>
+      <c r="AT32" s="8" t="n"/>
+      <c r="AU32" s="9" t="n"/>
+      <c r="AV32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>ITC Hotels Limited</t>
+          <t>Zydus Wellness Limited</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>INE379A01028</t>
+          <t>INE768C01010</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Leisure Services</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D33" s="8" t="n"/>
@@ -5136,128 +5136,116 @@
       <c r="V33" s="8" t="n"/>
       <c r="W33" s="9" t="n"/>
       <c r="X33" s="10" t="n"/>
-      <c r="Y33" s="8" t="n"/>
-      <c r="Z33" s="9" t="n"/>
-      <c r="AA33" s="10" t="n"/>
-      <c r="AB33" s="8" t="n"/>
-      <c r="AC33" s="9" t="n"/>
-      <c r="AD33" s="10" t="n"/>
-      <c r="AE33" s="8" t="n"/>
-      <c r="AF33" s="9" t="n"/>
-      <c r="AG33" s="10" t="n"/>
+      <c r="Y33" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="Z33" s="9" t="n">
+        <v>88822.8</v>
+      </c>
+      <c r="AA33" s="10" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="AB33" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AC33" s="9" t="n">
+        <v>89280.39999999999</v>
+      </c>
+      <c r="AD33" s="10" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="AE33" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AF33" s="9" t="n">
+        <v>89020.8</v>
+      </c>
+      <c r="AG33" s="10" t="n">
+        <v>0.0081</v>
+      </c>
       <c r="AH33" s="8" t="n"/>
       <c r="AI33" s="9" t="n"/>
       <c r="AJ33" s="10" t="n"/>
       <c r="AK33" s="8" t="n"/>
       <c r="AL33" s="9" t="n"/>
       <c r="AM33" s="10" t="n"/>
-      <c r="AN33" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="AO33" s="9" t="n">
-        <v>19552.33</v>
-      </c>
-      <c r="AP33" s="10" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="AQ33" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="AR33" s="9" t="n">
-        <v>16216.23</v>
-      </c>
-      <c r="AS33" s="10" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="AT33" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="AU33" s="9" t="n">
-        <v>16131.09</v>
-      </c>
-      <c r="AV33" s="10" t="n">
-        <v>0.0018</v>
-      </c>
+      <c r="AN33" s="8" t="n"/>
+      <c r="AO33" s="9" t="n"/>
+      <c r="AP33" s="10" t="n"/>
+      <c r="AQ33" s="8" t="n"/>
+      <c r="AR33" s="9" t="n"/>
+      <c r="AS33" s="10" t="n"/>
+      <c r="AT33" s="8" t="n"/>
+      <c r="AU33" s="9" t="n"/>
+      <c r="AV33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited</t>
+          <t>Tata Consultancy Services Limited</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>INE768C01028</t>
+          <t>INE467B01029</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>IT - Software</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>22157154</v>
+        <v>12412184</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>94467.03</v>
+        <v>292791.01</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>0.0073</v>
+        <v>0.0227</v>
       </c>
       <c r="G34" s="8" t="n">
-        <v>22075063</v>
+        <v>10378056</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>84966.92</v>
+        <v>273710.85</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>0.0063</v>
+        <v>0.0204</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>22000000</v>
+        <v>8465650</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>98626</v>
+        <v>264458.44</v>
       </c>
       <c r="L34" s="10" t="n">
-        <v>0.0074</v>
+        <v>0.0197</v>
       </c>
       <c r="M34" s="8" t="n">
-        <v>22000000</v>
+        <v>4654589</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>100012</v>
+        <v>149235.43</v>
       </c>
       <c r="O34" s="10" t="n">
-        <v>0.0075</v>
+        <v>0.0112</v>
       </c>
       <c r="P34" s="8" t="n">
-        <v>22000000</v>
+        <v>2811139</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>94699</v>
+        <v>88199.49000000001</v>
       </c>
       <c r="R34" s="10" t="n">
-        <v>0.0073</v>
-      </c>
-      <c r="S34" s="8" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="T34" s="9" t="n">
-        <v>104852</v>
-      </c>
-      <c r="U34" s="10" t="n">
-        <v>0.0083</v>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="W34" s="9" t="n">
-        <v>100584</v>
-      </c>
-      <c r="X34" s="10" t="n">
-        <v>0.008399999999999999</v>
-      </c>
+        <v>0.0068</v>
+      </c>
+      <c r="S34" s="8" t="n"/>
+      <c r="T34" s="9" t="n"/>
+      <c r="U34" s="10" t="n"/>
+      <c r="V34" s="8" t="n"/>
+      <c r="W34" s="9" t="n"/>
+      <c r="X34" s="10" t="n"/>
       <c r="Y34" s="8" t="n"/>
       <c r="Z34" s="9" t="n"/>
       <c r="AA34" s="10" t="n"/>
@@ -5286,70 +5274,82 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services Limited</t>
+          <t>Zydus Wellness Limited</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>INE467B01029</t>
+          <t>INE768C01028</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>IT - Software</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>12412184</v>
+        <v>22157154</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>292791.01</v>
+        <v>94467.03</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>0.0227</v>
+        <v>0.0073</v>
       </c>
       <c r="G35" s="8" t="n">
-        <v>10378056</v>
+        <v>22075063</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>273710.85</v>
+        <v>84966.92</v>
       </c>
       <c r="I35" s="10" t="n">
-        <v>0.0204</v>
+        <v>0.0063</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>8465650</v>
+        <v>22000000</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>264458.44</v>
+        <v>98626</v>
       </c>
       <c r="L35" s="10" t="n">
-        <v>0.0197</v>
+        <v>0.0074</v>
       </c>
       <c r="M35" s="8" t="n">
-        <v>4654589</v>
+        <v>22000000</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>149235.43</v>
+        <v>100012</v>
       </c>
       <c r="O35" s="10" t="n">
-        <v>0.0112</v>
+        <v>0.0075</v>
       </c>
       <c r="P35" s="8" t="n">
-        <v>2811139</v>
+        <v>22000000</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>88199.49000000001</v>
+        <v>94699</v>
       </c>
       <c r="R35" s="10" t="n">
-        <v>0.0068</v>
-      </c>
-      <c r="S35" s="8" t="n"/>
-      <c r="T35" s="9" t="n"/>
-      <c r="U35" s="10" t="n"/>
-      <c r="V35" s="8" t="n"/>
-      <c r="W35" s="9" t="n"/>
-      <c r="X35" s="10" t="n"/>
+        <v>0.0073</v>
+      </c>
+      <c r="S35" s="8" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="T35" s="9" t="n">
+        <v>104852</v>
+      </c>
+      <c r="U35" s="10" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="W35" s="9" t="n">
+        <v>100584</v>
+      </c>
+      <c r="X35" s="10" t="n">
+        <v>0.008399999999999999</v>
+      </c>
       <c r="Y35" s="8" t="n"/>
       <c r="Z35" s="9" t="n"/>
       <c r="AA35" s="10" t="n"/>
@@ -5378,64 +5378,58 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Indus Towers Limited</t>
+          <t>The Great Eastern Shipping Company Limited</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>INE121J01017</t>
+          <t>INE017A01032</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Telecom - Services</t>
+          <t>Transport Services</t>
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>710855</v>
+        <v>2205298</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>2972.44</v>
+        <v>31198.35</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0024</v>
       </c>
       <c r="G36" s="8" t="n">
-        <v>710855</v>
+        <v>2205298</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>3234.03</v>
+        <v>29526.73</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0022</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>710855</v>
+        <v>2205298</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>3158.33</v>
+        <v>26516.5</v>
       </c>
       <c r="L36" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.002</v>
       </c>
       <c r="M36" s="8" t="n">
-        <v>710855</v>
+        <v>1657424</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>2976.71</v>
+        <v>18712.32</v>
       </c>
       <c r="O36" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="P36" s="8" t="n">
-        <v>710855</v>
-      </c>
-      <c r="Q36" s="9" t="n">
-        <v>2850.8839775</v>
-      </c>
-      <c r="R36" s="10" t="n">
-        <v>0.0002</v>
-      </c>
+        <v>0.0014</v>
+      </c>
+      <c r="P36" s="8" t="n"/>
+      <c r="Q36" s="9" t="n"/>
+      <c r="R36" s="10" t="n"/>
       <c r="S36" s="8" t="n"/>
       <c r="T36" s="9" t="n"/>
       <c r="U36" s="10" t="n"/>
@@ -5470,52 +5464,64 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Kotak Mahindra Bank Limited</t>
+          <t>Indus Towers Limited</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>INE237A01036</t>
+          <t>INE121J01017</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Telecom - Services</t>
         </is>
       </c>
       <c r="D37" s="8" t="n">
-        <v>146607960</v>
+        <v>710855</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>518112.53</v>
+        <v>2972.44</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>0.0402</v>
+        <v>0.0002</v>
       </c>
       <c r="G37" s="8" t="n">
-        <v>123107960</v>
+        <v>710855</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>511144.25</v>
+        <v>3234.03</v>
       </c>
       <c r="I37" s="10" t="n">
-        <v>0.0381</v>
+        <v>0.0002</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>123107960</v>
+        <v>710855</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>502280.48</v>
+        <v>3158.33</v>
       </c>
       <c r="L37" s="10" t="n">
-        <v>0.0375</v>
-      </c>
-      <c r="M37" s="8" t="n"/>
-      <c r="N37" s="9" t="n"/>
-      <c r="O37" s="10" t="n"/>
-      <c r="P37" s="8" t="n"/>
-      <c r="Q37" s="9" t="n"/>
-      <c r="R37" s="10" t="n"/>
+        <v>0.0002</v>
+      </c>
+      <c r="M37" s="8" t="n">
+        <v>710855</v>
+      </c>
+      <c r="N37" s="9" t="n">
+        <v>2976.71</v>
+      </c>
+      <c r="O37" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P37" s="8" t="n">
+        <v>710855</v>
+      </c>
+      <c r="Q37" s="9" t="n">
+        <v>2850.8839775</v>
+      </c>
+      <c r="R37" s="10" t="n">
+        <v>0.0002</v>
+      </c>
       <c r="S37" s="8" t="n"/>
       <c r="T37" s="9" t="n"/>
       <c r="U37" s="10" t="n"/>
@@ -5550,55 +5556,49 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>The Great Eastern Shipping Company Limited</t>
+          <t>Kotak Mahindra Bank Limited</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>INE017A01032</t>
+          <t>INE237A01036</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Transport Services</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>2205298</v>
+        <v>146607960</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>31198.35</v>
+        <v>518112.53</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>0.0024</v>
+        <v>0.0402</v>
       </c>
       <c r="G38" s="8" t="n">
-        <v>2205298</v>
+        <v>123107960</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>29526.73</v>
+        <v>511144.25</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>0.0022</v>
+        <v>0.0381</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>2205298</v>
+        <v>123107960</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>26516.5</v>
+        <v>502280.48</v>
       </c>
       <c r="L38" s="10" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="M38" s="8" t="n">
-        <v>1657424</v>
-      </c>
-      <c r="N38" s="9" t="n">
-        <v>18712.32</v>
-      </c>
-      <c r="O38" s="10" t="n">
-        <v>0.0014</v>
-      </c>
+        <v>0.0375</v>
+      </c>
+      <c r="M38" s="8" t="n"/>
+      <c r="N38" s="9" t="n"/>
+      <c r="O38" s="10" t="n"/>
       <c r="P38" s="8" t="n"/>
       <c r="Q38" s="9" t="n"/>
       <c r="R38" s="10" t="n"/>
@@ -6030,19 +6030,19 @@
         <v>1285817925</v>
       </c>
       <c r="H44" s="14" t="n">
-        <v>8857498.140000002</v>
+        <v>8857498.140000001</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>0.6598000000000001</v>
+        <v>0.6597999999999999</v>
       </c>
       <c r="J44" s="13" t="n">
         <v>1265994824</v>
       </c>
       <c r="K44" s="14" t="n">
-        <v>8789059.288358003</v>
+        <v>8789059.288358001</v>
       </c>
       <c r="L44" s="15" t="n">
-        <v>0.6559051731198604</v>
+        <v>0.6559051731198605</v>
       </c>
       <c r="M44" s="13" t="n">
         <v>1079845116</v>
@@ -6066,7 +6066,7 @@
         <v>991416407</v>
       </c>
       <c r="T44" s="14" t="n">
-        <v>7865128.239999998</v>
+        <v>7865128.239999999</v>
       </c>
       <c r="U44" s="15" t="n">
         <v>0.6254999999999999</v>
@@ -6075,10 +6075,10 @@
         <v>979359723</v>
       </c>
       <c r="W44" s="14" t="n">
-        <v>7559180.720000002</v>
+        <v>7559180.72</v>
       </c>
       <c r="X44" s="15" t="n">
-        <v>0.6313999999999996</v>
+        <v>0.6313999999999997</v>
       </c>
       <c r="Y44" s="13" t="n">
         <v>927478800</v>
@@ -6087,7 +6087,7 @@
         <v>7320811.49</v>
       </c>
       <c r="AA44" s="15" t="n">
-        <v>0.6364</v>
+        <v>0.6364000000000001</v>
       </c>
       <c r="AB44" s="13" t="n">
         <v>819556049</v>
@@ -6096,7 +6096,7 @@
         <v>7290583.900000003</v>
       </c>
       <c r="AD44" s="15" t="n">
-        <v>0.6436999999999998</v>
+        <v>0.6436999999999999</v>
       </c>
       <c r="AE44" s="13" t="n">
         <v>799425942</v>
@@ -6105,22 +6105,22 @@
         <v>7347454.07</v>
       </c>
       <c r="AG44" s="15" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.6657999999999998</v>
       </c>
       <c r="AH44" s="13" t="n">
         <v>756845974</v>
       </c>
       <c r="AI44" s="14" t="n">
-        <v>6714757.130000001</v>
+        <v>6714757.130000002</v>
       </c>
       <c r="AJ44" s="15" t="n">
-        <v>0.6467999999999998</v>
+        <v>0.6467999999999997</v>
       </c>
       <c r="AK44" s="13" t="n">
         <v>719050337</v>
       </c>
       <c r="AL44" s="14" t="n">
-        <v>6275568.750000001</v>
+        <v>6275568.75</v>
       </c>
       <c r="AM44" s="15" t="n">
         <v>0.6370000000000001</v>
@@ -6138,7 +6138,7 @@
         <v>718063829</v>
       </c>
       <c r="AR44" s="14" t="n">
-        <v>5662977.75</v>
+        <v>5662977.749999999</v>
       </c>
       <c r="AS44" s="15" t="n">
         <v>0.6436999999999998</v>

--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -484,13 +484,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV44"/>
+  <dimension ref="A1:AM38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
@@ -498,17 +498,17 @@
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
     <col width="26" customWidth="1" min="14" max="14"/>
     <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
     <col width="26" customWidth="1" min="17" max="17"/>
     <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
     <col width="26" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="20" customWidth="1" min="24" max="24"/>
     <col width="13" customWidth="1" min="25" max="25"/>
@@ -520,21 +520,12 @@
     <col width="13" customWidth="1" min="31" max="31"/>
     <col width="26" customWidth="1" min="32" max="32"/>
     <col width="20" customWidth="1" min="33" max="33"/>
-    <col width="13" customWidth="1" min="34" max="34"/>
+    <col width="15" customWidth="1" min="34" max="34"/>
     <col width="26" customWidth="1" min="35" max="35"/>
     <col width="20" customWidth="1" min="36" max="36"/>
-    <col width="13" customWidth="1" min="37" max="37"/>
+    <col width="14" customWidth="1" min="37" max="37"/>
     <col width="26" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
-    <col width="13" customWidth="1" min="40" max="40"/>
-    <col width="26" customWidth="1" min="41" max="41"/>
-    <col width="20" customWidth="1" min="42" max="42"/>
-    <col width="15" customWidth="1" min="43" max="43"/>
-    <col width="26" customWidth="1" min="44" max="44"/>
-    <col width="20" customWidth="1" min="45" max="45"/>
-    <col width="14" customWidth="1" min="46" max="46"/>
-    <col width="26" customWidth="1" min="47" max="47"/>
-    <col width="20" customWidth="1" min="48" max="48"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -581,15 +572,6 @@
       <c r="AK1" s="1" t="n"/>
       <c r="AL1" s="1" t="n"/>
       <c r="AM1" s="1" t="n"/>
-      <c r="AN1" s="1" t="n"/>
-      <c r="AO1" s="1" t="n"/>
-      <c r="AP1" s="1" t="n"/>
-      <c r="AQ1" s="1" t="n"/>
-      <c r="AR1" s="1" t="n"/>
-      <c r="AS1" s="1" t="n"/>
-      <c r="AT1" s="1" t="n"/>
-      <c r="AU1" s="1" t="n"/>
-      <c r="AV1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -609,109 +591,88 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>March_2026</t>
+          <t>December_2025</t>
         </is>
       </c>
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="3" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>February_2026</t>
+          <t>November_2025</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="3" t="n"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>January_2026</t>
+          <t>October_2025</t>
         </is>
       </c>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="3" t="n"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>December_2025</t>
+          <t>September_2025</t>
         </is>
       </c>
       <c r="N2" s="2" t="n"/>
       <c r="O2" s="3" t="n"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>November_2025</t>
+          <t>August_2025</t>
         </is>
       </c>
       <c r="Q2" s="2" t="n"/>
       <c r="R2" s="3" t="n"/>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>October_2025</t>
+          <t>July_2025</t>
         </is>
       </c>
       <c r="T2" s="2" t="n"/>
       <c r="U2" s="3" t="n"/>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>September_2025</t>
+          <t>June_2025</t>
         </is>
       </c>
       <c r="W2" s="2" t="n"/>
       <c r="X2" s="3" t="n"/>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>August_2025</t>
+          <t>May_2025</t>
         </is>
       </c>
       <c r="Z2" s="2" t="n"/>
       <c r="AA2" s="3" t="n"/>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>July_2025</t>
+          <t>April_2025</t>
         </is>
       </c>
       <c r="AC2" s="2" t="n"/>
       <c r="AD2" s="3" t="n"/>
       <c r="AE2" s="2" t="inlineStr">
         <is>
-          <t>June_2025</t>
+          <t>March_2025</t>
         </is>
       </c>
       <c r="AF2" s="2" t="n"/>
       <c r="AG2" s="3" t="n"/>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>May_2025</t>
+          <t>February_2025</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n"/>
       <c r="AJ2" s="3" t="n"/>
       <c r="AK2" s="2" t="inlineStr">
         <is>
-          <t>April_2025</t>
+          <t>January_2025</t>
         </is>
       </c>
       <c r="AL2" s="2" t="n"/>
       <c r="AM2" s="3" t="n"/>
-      <c r="AN2" s="2" t="inlineStr">
-        <is>
-          <t>March_2025</t>
-        </is>
-      </c>
-      <c r="AO2" s="2" t="n"/>
-      <c r="AP2" s="3" t="n"/>
-      <c r="AQ2" s="2" t="inlineStr">
-        <is>
-          <t>February_2025</t>
-        </is>
-      </c>
-      <c r="AR2" s="2" t="n"/>
-      <c r="AS2" s="3" t="n"/>
-      <c r="AT2" s="2" t="inlineStr">
-        <is>
-          <t>January_2025</t>
-        </is>
-      </c>
-      <c r="AU2" s="2" t="n"/>
-      <c r="AV2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n"/>
@@ -897,51 +858,6 @@
           <t>% Net Assets</t>
         </is>
       </c>
-      <c r="AN3" s="4" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="AO3" s="4" t="inlineStr">
-        <is>
-          <t>Market Value (Rs. Lakhs)</t>
-        </is>
-      </c>
-      <c r="AP3" s="5" t="inlineStr">
-        <is>
-          <t>% Net Assets</t>
-        </is>
-      </c>
-      <c r="AQ3" s="4" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="AR3" s="4" t="inlineStr">
-        <is>
-          <t>Market Value (Rs. Lakhs)</t>
-        </is>
-      </c>
-      <c r="AS3" s="5" t="inlineStr">
-        <is>
-          <t>% Net Assets</t>
-        </is>
-      </c>
-      <c r="AT3" s="4" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="AU3" s="4" t="inlineStr">
-        <is>
-          <t>Market Value (Rs. Lakhs)</t>
-        </is>
-      </c>
-      <c r="AV3" s="5" t="inlineStr">
-        <is>
-          <t>% Net Assets</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -960,138 +876,111 @@
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>140247203</v>
+        <v>108738215</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>1025978.41</v>
+        <v>1077813.19</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>0.0796</v>
+        <v>0.0809</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>116915576</v>
+        <v>103486016</v>
       </c>
       <c r="H4" s="9" t="n">
-        <v>1037918.03</v>
+        <v>1042725.1</v>
       </c>
       <c r="I4" s="10" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0803</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>115915576</v>
+        <v>102203321</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>1077145.49</v>
+        <v>1009053.39</v>
       </c>
       <c r="L4" s="10" t="n">
-        <v>0.0804</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>108738215</v>
+        <v>101668321</v>
       </c>
       <c r="N4" s="9" t="n">
-        <v>1077813.19</v>
+        <v>966865.73</v>
       </c>
       <c r="O4" s="10" t="n">
-        <v>0.0809</v>
+        <v>0.0808</v>
       </c>
       <c r="P4" s="8" t="n">
-        <v>103486016</v>
+        <v>95825482</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>1042725.1</v>
+        <v>911875.29</v>
       </c>
       <c r="R4" s="10" t="n">
-        <v>0.0803</v>
+        <v>0.0793</v>
       </c>
       <c r="S4" s="8" t="n">
-        <v>102203321</v>
+        <v>44870461</v>
       </c>
       <c r="T4" s="9" t="n">
-        <v>1009053.39</v>
+        <v>905575.64</v>
       </c>
       <c r="U4" s="10" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.0799</v>
       </c>
       <c r="V4" s="8" t="n">
-        <v>101668321</v>
+        <v>44461271</v>
       </c>
       <c r="W4" s="9" t="n">
-        <v>966865.73</v>
+        <v>889892.34</v>
       </c>
       <c r="X4" s="10" t="n">
-        <v>0.0808</v>
+        <v>0.0806</v>
       </c>
       <c r="Y4" s="8" t="n">
-        <v>95825482</v>
+        <v>43293069</v>
       </c>
       <c r="Z4" s="9" t="n">
-        <v>911875.29</v>
+        <v>842006.9</v>
       </c>
       <c r="AA4" s="10" t="n">
-        <v>0.0793</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="AB4" s="8" t="n">
-        <v>44870461</v>
+        <v>42813069</v>
       </c>
       <c r="AC4" s="9" t="n">
-        <v>905575.64</v>
+        <v>824151.58</v>
       </c>
       <c r="AD4" s="10" t="n">
-        <v>0.0799</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="AE4" s="8" t="n">
-        <v>44461271</v>
+        <v>42813069</v>
       </c>
       <c r="AF4" s="9" t="n">
-        <v>889892.34</v>
+        <v>782708.53</v>
       </c>
       <c r="AG4" s="10" t="n">
-        <v>0.0806</v>
+        <v>0.0838</v>
       </c>
       <c r="AH4" s="8" t="n">
-        <v>43293069</v>
+        <v>42813069</v>
       </c>
       <c r="AI4" s="9" t="n">
-        <v>842006.9</v>
+        <v>741693.61</v>
       </c>
       <c r="AJ4" s="10" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.0843</v>
       </c>
       <c r="AK4" s="8" t="n">
         <v>42813069</v>
       </c>
       <c r="AL4" s="9" t="n">
-        <v>824151.58</v>
+        <v>727287.01</v>
       </c>
       <c r="AM4" s="10" t="n">
-        <v>0.08359999999999999</v>
-      </c>
-      <c r="AN4" s="8" t="n">
-        <v>42813069</v>
-      </c>
-      <c r="AO4" s="9" t="n">
-        <v>782708.53</v>
-      </c>
-      <c r="AP4" s="10" t="n">
-        <v>0.0838</v>
-      </c>
-      <c r="AQ4" s="8" t="n">
-        <v>42813069</v>
-      </c>
-      <c r="AR4" s="9" t="n">
-        <v>741693.61</v>
-      </c>
-      <c r="AS4" s="10" t="n">
-        <v>0.0843</v>
-      </c>
-      <c r="AT4" s="8" t="n">
-        <v>42813069</v>
-      </c>
-      <c r="AU4" s="9" t="n">
-        <v>727287.01</v>
-      </c>
-      <c r="AV4" s="10" t="n">
         <v>0.08110000000000001</v>
       </c>
     </row>
@@ -1112,138 +1001,111 @@
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>6026828</v>
+        <v>5318918</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>527106.38</v>
+        <v>602527.03</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.0409</v>
+        <v>0.0452</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>6026828</v>
+        <v>5318918</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>651138.5</v>
+        <v>611622.38</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>0.0485</v>
+        <v>0.0471</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>5979253</v>
+        <v>5318918</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>645759.3199999999</v>
+        <v>654386.48</v>
       </c>
       <c r="L5" s="10" t="n">
-        <v>0.0482</v>
+        <v>0.052</v>
       </c>
       <c r="M5" s="8" t="n">
         <v>5318918</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>602527.03</v>
+        <v>651407.89</v>
       </c>
       <c r="O5" s="10" t="n">
-        <v>0.0452</v>
+        <v>0.0544</v>
       </c>
       <c r="P5" s="8" t="n">
         <v>5318918</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>611622.38</v>
+        <v>679225.83</v>
       </c>
       <c r="R5" s="10" t="n">
-        <v>0.0471</v>
+        <v>0.059</v>
       </c>
       <c r="S5" s="8" t="n">
         <v>5318918</v>
       </c>
       <c r="T5" s="9" t="n">
-        <v>654386.48</v>
+        <v>742680.52</v>
       </c>
       <c r="U5" s="10" t="n">
-        <v>0.052</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="V5" s="8" t="n">
         <v>5318918</v>
       </c>
       <c r="W5" s="9" t="n">
-        <v>651407.89</v>
+        <v>764807.22</v>
       </c>
       <c r="X5" s="10" t="n">
-        <v>0.0544</v>
+        <v>0.0693</v>
       </c>
       <c r="Y5" s="8" t="n">
         <v>5318918</v>
       </c>
       <c r="Z5" s="9" t="n">
-        <v>679225.83</v>
+        <v>713479.66</v>
       </c>
       <c r="AA5" s="10" t="n">
-        <v>0.059</v>
+        <v>0.0687</v>
       </c>
       <c r="AB5" s="8" t="n">
         <v>5318918</v>
       </c>
       <c r="AC5" s="9" t="n">
-        <v>742680.52</v>
+        <v>636834.05</v>
       </c>
       <c r="AD5" s="10" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0646</v>
       </c>
       <c r="AE5" s="8" t="n">
         <v>5318918</v>
       </c>
       <c r="AF5" s="9" t="n">
-        <v>764807.22</v>
+        <v>663431.3</v>
       </c>
       <c r="AG5" s="10" t="n">
-        <v>0.0693</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AH5" s="8" t="n">
         <v>5318918</v>
       </c>
       <c r="AI5" s="9" t="n">
-        <v>713479.66</v>
+        <v>615630.1899999999</v>
       </c>
       <c r="AJ5" s="10" t="n">
-        <v>0.0687</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AK5" s="8" t="n">
         <v>5318918</v>
       </c>
       <c r="AL5" s="9" t="n">
-        <v>636834.05</v>
+        <v>614850.96</v>
       </c>
       <c r="AM5" s="10" t="n">
-        <v>0.0646</v>
-      </c>
-      <c r="AN5" s="8" t="n">
-        <v>5318918</v>
-      </c>
-      <c r="AO5" s="9" t="n">
-        <v>663431.3</v>
-      </c>
-      <c r="AP5" s="10" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="AQ5" s="8" t="n">
-        <v>5318918</v>
-      </c>
-      <c r="AR5" s="9" t="n">
-        <v>615630.1899999999</v>
-      </c>
-      <c r="AS5" s="10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AT5" s="8" t="n">
-        <v>5318918</v>
-      </c>
-      <c r="AU5" s="9" t="n">
-        <v>614850.96</v>
-      </c>
-      <c r="AV5" s="10" t="n">
         <v>0.06850000000000001</v>
       </c>
     </row>
@@ -1264,138 +1126,111 @@
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>174817417</v>
+        <v>162039558</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>787465.05</v>
+        <v>646537.84</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.0611</v>
+        <v>0.0485</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>161423761</v>
+        <v>162039558</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>695171.4300000001</v>
+        <v>609511.8</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>0.0518</v>
+        <v>0.047</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>159832308</v>
+        <v>162039558</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>704460.9</v>
+        <v>629766.74</v>
       </c>
       <c r="L6" s="10" t="n">
-        <v>0.0526</v>
+        <v>0.0501</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>162039558</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>646537.84</v>
+        <v>631873.26</v>
       </c>
       <c r="O6" s="10" t="n">
-        <v>0.0485</v>
+        <v>0.0528</v>
       </c>
       <c r="P6" s="8" t="n">
         <v>162039558</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>609511.8</v>
+        <v>607324.26</v>
       </c>
       <c r="R6" s="10" t="n">
-        <v>0.047</v>
+        <v>0.0528</v>
       </c>
       <c r="S6" s="8" t="n">
         <v>162039558</v>
       </c>
       <c r="T6" s="9" t="n">
-        <v>629766.74</v>
+        <v>609835.88</v>
       </c>
       <c r="U6" s="10" t="n">
-        <v>0.0501</v>
+        <v>0.0538</v>
       </c>
       <c r="V6" s="8" t="n">
         <v>162039558</v>
       </c>
       <c r="W6" s="9" t="n">
-        <v>631873.26</v>
+        <v>635114.05</v>
       </c>
       <c r="X6" s="10" t="n">
-        <v>0.0528</v>
+        <v>0.0575</v>
       </c>
       <c r="Y6" s="8" t="n">
-        <v>162039558</v>
+        <v>155681572</v>
       </c>
       <c r="Z6" s="9" t="n">
-        <v>607324.26</v>
+        <v>618522.89</v>
       </c>
       <c r="AA6" s="10" t="n">
-        <v>0.0528</v>
+        <v>0.0595</v>
       </c>
       <c r="AB6" s="8" t="n">
-        <v>162039558</v>
+        <v>148323775</v>
       </c>
       <c r="AC6" s="9" t="n">
-        <v>609835.88</v>
+        <v>571491.51</v>
       </c>
       <c r="AD6" s="10" t="n">
-        <v>0.0538</v>
+        <v>0.058</v>
       </c>
       <c r="AE6" s="8" t="n">
-        <v>162039558</v>
+        <v>141074007</v>
       </c>
       <c r="AF6" s="9" t="n">
-        <v>635114.05</v>
+        <v>561756.7</v>
       </c>
       <c r="AG6" s="10" t="n">
-        <v>0.0575</v>
+        <v>0.0601</v>
       </c>
       <c r="AH6" s="8" t="n">
-        <v>155681572</v>
+        <v>142636407</v>
       </c>
       <c r="AI6" s="9" t="n">
-        <v>618522.89</v>
+        <v>526827.5699999999</v>
       </c>
       <c r="AJ6" s="10" t="n">
-        <v>0.0595</v>
+        <v>0.0599</v>
       </c>
       <c r="AK6" s="8" t="n">
-        <v>148323775</v>
+        <v>139335199</v>
       </c>
       <c r="AL6" s="9" t="n">
-        <v>571491.51</v>
+        <v>551628.05</v>
       </c>
       <c r="AM6" s="10" t="n">
-        <v>0.058</v>
-      </c>
-      <c r="AN6" s="8" t="n">
-        <v>141074007</v>
-      </c>
-      <c r="AO6" s="9" t="n">
-        <v>561756.7</v>
-      </c>
-      <c r="AP6" s="10" t="n">
-        <v>0.0601</v>
-      </c>
-      <c r="AQ6" s="8" t="n">
-        <v>142636407</v>
-      </c>
-      <c r="AR6" s="9" t="n">
-        <v>526827.5699999999</v>
-      </c>
-      <c r="AS6" s="10" t="n">
-        <v>0.0599</v>
-      </c>
-      <c r="AT6" s="8" t="n">
-        <v>139335199</v>
-      </c>
-      <c r="AU6" s="9" t="n">
-        <v>551628.05</v>
-      </c>
-      <c r="AV6" s="10" t="n">
         <v>0.0615</v>
       </c>
     </row>
@@ -1416,138 +1251,111 @@
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>312063864</v>
+        <v>305419267</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>924021.1</v>
+        <v>808139.38</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.0716</v>
+        <v>0.0606</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>311113864</v>
+        <v>284154236</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>929141.55</v>
+        <v>767074.36</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>0.0692</v>
+        <v>0.0591</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>313365617</v>
+        <v>261786637</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>803782.8100000001</v>
+        <v>754338.1899999999</v>
       </c>
       <c r="L7" s="10" t="n">
         <v>0.06</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>305419267</v>
+        <v>255922726</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>808139.38</v>
+        <v>717223.4399999999</v>
       </c>
       <c r="O7" s="10" t="n">
-        <v>0.0606</v>
+        <v>0.0599</v>
       </c>
       <c r="P7" s="8" t="n">
-        <v>284154236</v>
+        <v>246049993</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>767074.36</v>
+        <v>677252.61</v>
       </c>
       <c r="R7" s="10" t="n">
-        <v>0.0591</v>
+        <v>0.0589</v>
       </c>
       <c r="S7" s="8" t="n">
-        <v>261786637</v>
+        <v>230787510</v>
       </c>
       <c r="T7" s="9" t="n">
-        <v>754338.1899999999</v>
+        <v>671591.65</v>
       </c>
       <c r="U7" s="10" t="n">
-        <v>0.06</v>
+        <v>0.0593</v>
       </c>
       <c r="V7" s="8" t="n">
-        <v>255922726</v>
+        <v>224216515</v>
       </c>
       <c r="W7" s="9" t="n">
-        <v>717223.4399999999</v>
+        <v>672425.33</v>
       </c>
       <c r="X7" s="10" t="n">
+        <v>0.0609</v>
+      </c>
+      <c r="Y7" s="8" t="n">
+        <v>208867542</v>
+      </c>
+      <c r="Z7" s="9" t="n">
+        <v>605193.7</v>
+      </c>
+      <c r="AA7" s="10" t="n">
+        <v>0.0583</v>
+      </c>
+      <c r="AB7" s="8" t="n">
+        <v>193616648</v>
+      </c>
+      <c r="AC7" s="9" t="n">
+        <v>595274.38</v>
+      </c>
+      <c r="AD7" s="10" t="n">
+        <v>0.0604</v>
+      </c>
+      <c r="AE7" s="8" t="n">
+        <v>192765312</v>
+      </c>
+      <c r="AF7" s="9" t="n">
+        <v>559694.08</v>
+      </c>
+      <c r="AG7" s="10" t="n">
         <v>0.0599</v>
       </c>
-      <c r="Y7" s="8" t="n">
-        <v>246049993</v>
-      </c>
-      <c r="Z7" s="9" t="n">
-        <v>677252.61</v>
-      </c>
-      <c r="AA7" s="10" t="n">
-        <v>0.0589</v>
-      </c>
-      <c r="AB7" s="8" t="n">
-        <v>230787510</v>
-      </c>
-      <c r="AC7" s="9" t="n">
-        <v>671591.65</v>
-      </c>
-      <c r="AD7" s="10" t="n">
-        <v>0.0593</v>
-      </c>
-      <c r="AE7" s="8" t="n">
-        <v>224216515</v>
-      </c>
-      <c r="AF7" s="9" t="n">
-        <v>672425.33</v>
-      </c>
-      <c r="AG7" s="10" t="n">
-        <v>0.0609</v>
-      </c>
       <c r="AH7" s="8" t="n">
-        <v>208867542</v>
+        <v>193498810</v>
       </c>
       <c r="AI7" s="9" t="n">
-        <v>605193.7</v>
+        <v>485391.76</v>
       </c>
       <c r="AJ7" s="10" t="n">
-        <v>0.0583</v>
+        <v>0.0552</v>
       </c>
       <c r="AK7" s="8" t="n">
-        <v>193616648</v>
+        <v>185577147</v>
       </c>
       <c r="AL7" s="9" t="n">
-        <v>595274.38</v>
+        <v>559793.46</v>
       </c>
       <c r="AM7" s="10" t="n">
-        <v>0.0604</v>
-      </c>
-      <c r="AN7" s="8" t="n">
-        <v>192765312</v>
-      </c>
-      <c r="AO7" s="9" t="n">
-        <v>559694.08</v>
-      </c>
-      <c r="AP7" s="10" t="n">
-        <v>0.0599</v>
-      </c>
-      <c r="AQ7" s="8" t="n">
-        <v>193498810</v>
-      </c>
-      <c r="AR7" s="9" t="n">
-        <v>485391.76</v>
-      </c>
-      <c r="AS7" s="10" t="n">
-        <v>0.0552</v>
-      </c>
-      <c r="AT7" s="8" t="n">
-        <v>185577147</v>
-      </c>
-      <c r="AU7" s="9" t="n">
-        <v>559793.46</v>
-      </c>
-      <c r="AV7" s="10" t="n">
         <v>0.0624</v>
       </c>
     </row>
@@ -1568,138 +1376,111 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>53846183</v>
+        <v>49325234</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>649331.12</v>
+        <v>662388.5699999999</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>0.0503</v>
+        <v>0.0497</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>49325234</v>
+        <v>45308598</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>680145.65</v>
+        <v>629245.8100000001</v>
       </c>
       <c r="I8" s="10" t="n">
+        <v>0.0485</v>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>43295573</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>582455.34</v>
+      </c>
+      <c r="L8" s="10" t="n">
+        <v>0.0463</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>42215573</v>
+      </c>
+      <c r="N8" s="9" t="n">
+        <v>569065.92</v>
+      </c>
+      <c r="O8" s="10" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="P8" s="8" t="n">
+        <v>40720543</v>
+      </c>
+      <c r="Q8" s="9" t="n">
+        <v>569191.75</v>
+      </c>
+      <c r="R8" s="10" t="n">
+        <v>0.0495</v>
+      </c>
+      <c r="S8" s="8" t="n">
+        <v>39605543</v>
+      </c>
+      <c r="T8" s="9" t="n">
+        <v>586716.51</v>
+      </c>
+      <c r="U8" s="10" t="n">
+        <v>0.0518</v>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v>36489310</v>
+      </c>
+      <c r="W8" s="9" t="n">
+        <v>527562.4399999999</v>
+      </c>
+      <c r="X8" s="10" t="n">
+        <v>0.0478</v>
+      </c>
+      <c r="Y8" s="8" t="n">
+        <v>34986740</v>
+      </c>
+      <c r="Z8" s="9" t="n">
+        <v>505838.29</v>
+      </c>
+      <c r="AA8" s="10" t="n">
+        <v>0.0487</v>
+      </c>
+      <c r="AB8" s="8" t="n">
+        <v>34986740</v>
+      </c>
+      <c r="AC8" s="9" t="n">
+        <v>499260.78</v>
+      </c>
+      <c r="AD8" s="10" t="n">
         <v>0.0507</v>
       </c>
-      <c r="J8" s="8" t="n">
-        <v>49325234</v>
-      </c>
-      <c r="K8" s="9" t="n">
-        <v>668356.92</v>
-      </c>
-      <c r="L8" s="10" t="n">
-        <v>0.0499</v>
-      </c>
-      <c r="M8" s="8" t="n">
-        <v>49325234</v>
-      </c>
-      <c r="N8" s="9" t="n">
-        <v>662388.5699999999</v>
-      </c>
-      <c r="O8" s="10" t="n">
-        <v>0.0497</v>
-      </c>
-      <c r="P8" s="8" t="n">
-        <v>45308598</v>
-      </c>
-      <c r="Q8" s="9" t="n">
-        <v>629245.8100000001</v>
-      </c>
-      <c r="R8" s="10" t="n">
-        <v>0.0485</v>
-      </c>
-      <c r="S8" s="8" t="n">
-        <v>43295573</v>
-      </c>
-      <c r="T8" s="9" t="n">
-        <v>582455.34</v>
-      </c>
-      <c r="U8" s="10" t="n">
-        <v>0.0463</v>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v>42215573</v>
-      </c>
-      <c r="W8" s="9" t="n">
-        <v>569065.92</v>
-      </c>
-      <c r="X8" s="10" t="n">
-        <v>0.0475</v>
-      </c>
-      <c r="Y8" s="8" t="n">
-        <v>40720543</v>
-      </c>
-      <c r="Z8" s="9" t="n">
-        <v>569191.75</v>
-      </c>
-      <c r="AA8" s="10" t="n">
-        <v>0.0495</v>
-      </c>
-      <c r="AB8" s="8" t="n">
-        <v>39605543</v>
-      </c>
-      <c r="AC8" s="9" t="n">
-        <v>586716.51</v>
-      </c>
-      <c r="AD8" s="10" t="n">
-        <v>0.0518</v>
-      </c>
       <c r="AE8" s="8" t="n">
-        <v>36489310</v>
+        <v>34986740</v>
       </c>
       <c r="AF8" s="9" t="n">
-        <v>527562.4399999999</v>
+        <v>471743.71</v>
       </c>
       <c r="AG8" s="10" t="n">
-        <v>0.0478</v>
+        <v>0.0505</v>
       </c>
       <c r="AH8" s="8" t="n">
         <v>34986740</v>
       </c>
       <c r="AI8" s="9" t="n">
-        <v>505838.29</v>
+        <v>421275.34</v>
       </c>
       <c r="AJ8" s="10" t="n">
-        <v>0.0487</v>
+        <v>0.0479</v>
       </c>
       <c r="AK8" s="8" t="n">
         <v>34986740</v>
       </c>
       <c r="AL8" s="9" t="n">
-        <v>499260.78</v>
+        <v>438313.88</v>
       </c>
       <c r="AM8" s="10" t="n">
-        <v>0.0507</v>
-      </c>
-      <c r="AN8" s="8" t="n">
-        <v>34986740</v>
-      </c>
-      <c r="AO8" s="9" t="n">
-        <v>471743.71</v>
-      </c>
-      <c r="AP8" s="10" t="n">
-        <v>0.0505</v>
-      </c>
-      <c r="AQ8" s="8" t="n">
-        <v>34986740</v>
-      </c>
-      <c r="AR8" s="9" t="n">
-        <v>421275.34</v>
-      </c>
-      <c r="AS8" s="10" t="n">
-        <v>0.0479</v>
-      </c>
-      <c r="AT8" s="8" t="n">
-        <v>34986740</v>
-      </c>
-      <c r="AU8" s="9" t="n">
-        <v>438313.88</v>
-      </c>
-      <c r="AV8" s="10" t="n">
         <v>0.0489</v>
       </c>
     </row>
@@ -1719,121 +1500,112 @@
           <t>Banks</t>
         </is>
       </c>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="10" t="n"/>
-      <c r="G9" s="8" t="n"/>
-      <c r="H9" s="9" t="n"/>
-      <c r="I9" s="10" t="n"/>
-      <c r="J9" s="8" t="n"/>
-      <c r="K9" s="9" t="n"/>
-      <c r="L9" s="10" t="n"/>
+      <c r="D9" s="8" t="n">
+        <v>24621592</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>541945.86</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>0.0407</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>24306544</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>516368.22</v>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>0.0398</v>
+      </c>
+      <c r="J9" s="8" t="n">
+        <v>24205055</v>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>508838.67</v>
+      </c>
+      <c r="L9" s="10" t="n">
+        <v>0.0404</v>
+      </c>
       <c r="M9" s="8" t="n">
-        <v>24621592</v>
+        <v>24205055</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>541945.86</v>
+        <v>482334.13</v>
       </c>
       <c r="O9" s="10" t="n">
-        <v>0.0407</v>
+        <v>0.0403</v>
       </c>
       <c r="P9" s="8" t="n">
-        <v>24306544</v>
+        <v>23407381</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>516368.22</v>
+        <v>458854.89</v>
       </c>
       <c r="R9" s="10" t="n">
-        <v>0.0398</v>
+        <v>0.0399</v>
       </c>
       <c r="S9" s="8" t="n">
-        <v>24205055</v>
+        <v>21994066</v>
       </c>
       <c r="T9" s="9" t="n">
-        <v>508838.67</v>
+        <v>435174.59</v>
       </c>
       <c r="U9" s="10" t="n">
-        <v>0.0404</v>
+        <v>0.0384</v>
       </c>
       <c r="V9" s="8" t="n">
-        <v>24205055</v>
+        <v>20473232</v>
       </c>
       <c r="W9" s="9" t="n">
-        <v>482334.13</v>
+        <v>442938.37</v>
       </c>
       <c r="X9" s="10" t="n">
-        <v>0.0403</v>
+        <v>0.0401</v>
       </c>
       <c r="Y9" s="8" t="n">
-        <v>23407381</v>
+        <v>19753232</v>
       </c>
       <c r="Z9" s="9" t="n">
-        <v>458854.89</v>
+        <v>409820.3</v>
       </c>
       <c r="AA9" s="10" t="n">
-        <v>0.0399</v>
+        <v>0.0395</v>
       </c>
       <c r="AB9" s="8" t="n">
-        <v>21994066</v>
+        <v>19753232</v>
       </c>
       <c r="AC9" s="9" t="n">
-        <v>435174.59</v>
+        <v>436171.12</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>0.0384</v>
+        <v>0.0443</v>
       </c>
       <c r="AE9" s="8" t="n">
-        <v>20473232</v>
+        <v>19753232</v>
       </c>
       <c r="AF9" s="9" t="n">
-        <v>442938.37</v>
+        <v>428882.17</v>
       </c>
       <c r="AG9" s="10" t="n">
-        <v>0.0401</v>
+        <v>0.0459</v>
       </c>
       <c r="AH9" s="8" t="n">
         <v>19753232</v>
       </c>
       <c r="AI9" s="9" t="n">
-        <v>409820.3</v>
+        <v>375894.13</v>
       </c>
       <c r="AJ9" s="10" t="n">
-        <v>0.0395</v>
+        <v>0.0427</v>
       </c>
       <c r="AK9" s="8" t="n">
         <v>19753232</v>
       </c>
       <c r="AL9" s="9" t="n">
-        <v>436171.12</v>
+        <v>375568.2</v>
       </c>
       <c r="AM9" s="10" t="n">
-        <v>0.0443</v>
-      </c>
-      <c r="AN9" s="8" t="n">
-        <v>19753232</v>
-      </c>
-      <c r="AO9" s="9" t="n">
-        <v>428882.17</v>
-      </c>
-      <c r="AP9" s="10" t="n">
-        <v>0.0459</v>
-      </c>
-      <c r="AQ9" s="8" t="n">
-        <v>19753232</v>
-      </c>
-      <c r="AR9" s="9" t="n">
-        <v>375894.13</v>
-      </c>
-      <c r="AS9" s="10" t="n">
-        <v>0.0427</v>
-      </c>
-      <c r="AT9" s="8" t="n">
-        <v>19753232</v>
-      </c>
-      <c r="AU9" s="9" t="n">
-        <v>375568.2</v>
-      </c>
-      <c r="AV9" s="10" t="n">
         <v>0.0419</v>
       </c>
     </row>
@@ -1854,138 +1626,111 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>224093958</v>
+        <v>148665711</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>644718.3199999999</v>
+        <v>599122.8199999999</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>0.05</v>
+        <v>0.0449</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>215593958</v>
+        <v>144737169</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>676102.65</v>
+        <v>585100.01</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>0.0504</v>
+        <v>0.0451</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>209900994</v>
+        <v>138771024</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>676196.05</v>
+        <v>583324</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>0.0505</v>
+        <v>0.0464</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>148665711</v>
+        <v>135721024</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>599122.8199999999</v>
+        <v>544987.77</v>
       </c>
       <c r="O10" s="10" t="n">
-        <v>0.0449</v>
+        <v>0.0455</v>
       </c>
       <c r="P10" s="8" t="n">
-        <v>144737169</v>
+        <v>129421024</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>585100.01</v>
+        <v>530302.65</v>
       </c>
       <c r="R10" s="10" t="n">
-        <v>0.0451</v>
+        <v>0.0461</v>
       </c>
       <c r="S10" s="8" t="n">
-        <v>138771024</v>
+        <v>122172359</v>
       </c>
       <c r="T10" s="9" t="n">
-        <v>583324</v>
+        <v>503289.03</v>
       </c>
       <c r="U10" s="10" t="n">
-        <v>0.0464</v>
+        <v>0.0444</v>
       </c>
       <c r="V10" s="8" t="n">
-        <v>135721024</v>
+        <v>117422359</v>
       </c>
       <c r="W10" s="9" t="n">
-        <v>544987.77</v>
+        <v>489005.41</v>
       </c>
       <c r="X10" s="10" t="n">
+        <v>0.0443</v>
+      </c>
+      <c r="Y10" s="8" t="n">
+        <v>109270669</v>
+      </c>
+      <c r="Z10" s="9" t="n">
+        <v>456806.03</v>
+      </c>
+      <c r="AA10" s="10" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="AB10" s="8" t="n">
+        <v>105271096</v>
+      </c>
+      <c r="AC10" s="9" t="n">
+        <v>448244.33</v>
+      </c>
+      <c r="AD10" s="10" t="n">
         <v>0.0455</v>
       </c>
-      <c r="Y10" s="8" t="n">
-        <v>129421024</v>
-      </c>
-      <c r="Z10" s="9" t="n">
-        <v>530302.65</v>
-      </c>
-      <c r="AA10" s="10" t="n">
-        <v>0.0461</v>
-      </c>
-      <c r="AB10" s="8" t="n">
-        <v>122172359</v>
-      </c>
-      <c r="AC10" s="9" t="n">
-        <v>503289.03</v>
-      </c>
-      <c r="AD10" s="10" t="n">
+      <c r="AE10" s="8" t="n">
+        <v>101194120</v>
+      </c>
+      <c r="AF10" s="9" t="n">
+        <v>414642.91</v>
+      </c>
+      <c r="AG10" s="10" t="n">
         <v>0.0444</v>
       </c>
-      <c r="AE10" s="8" t="n">
-        <v>117422359</v>
-      </c>
-      <c r="AF10" s="9" t="n">
-        <v>489005.41</v>
-      </c>
-      <c r="AG10" s="10" t="n">
-        <v>0.0443</v>
-      </c>
       <c r="AH10" s="8" t="n">
-        <v>109270669</v>
+        <v>101194120</v>
       </c>
       <c r="AI10" s="9" t="n">
-        <v>456806.03</v>
+        <v>399716.77</v>
       </c>
       <c r="AJ10" s="10" t="n">
-        <v>0.044</v>
+        <v>0.0454</v>
       </c>
       <c r="AK10" s="8" t="n">
-        <v>105271096</v>
+        <v>98994120</v>
       </c>
       <c r="AL10" s="9" t="n">
-        <v>448244.33</v>
+        <v>442998.69</v>
       </c>
       <c r="AM10" s="10" t="n">
-        <v>0.0455</v>
-      </c>
-      <c r="AN10" s="8" t="n">
-        <v>101194120</v>
-      </c>
-      <c r="AO10" s="9" t="n">
-        <v>414642.91</v>
-      </c>
-      <c r="AP10" s="10" t="n">
-        <v>0.0444</v>
-      </c>
-      <c r="AQ10" s="8" t="n">
-        <v>101194120</v>
-      </c>
-      <c r="AR10" s="9" t="n">
-        <v>399716.77</v>
-      </c>
-      <c r="AS10" s="10" t="n">
-        <v>0.0454</v>
-      </c>
-      <c r="AT10" s="8" t="n">
-        <v>98994120</v>
-      </c>
-      <c r="AU10" s="9" t="n">
-        <v>442998.69</v>
-      </c>
-      <c r="AV10" s="10" t="n">
         <v>0.0494</v>
       </c>
     </row>
@@ -2006,138 +1751,111 @@
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>3039945</v>
+        <v>2746670</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>374095.63</v>
+        <v>458611.49</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.029</v>
+        <v>0.0344</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>2861040</v>
+        <v>2746670</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>425064.71</v>
+        <v>436720.53</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>0.0317</v>
+        <v>0.0337</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>2780478</v>
+        <v>2696670</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>405921.98</v>
+        <v>436483.01</v>
       </c>
       <c r="L11" s="10" t="n">
-        <v>0.0303</v>
+        <v>0.0347</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>2746670</v>
+        <v>2696670</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>458611.49</v>
+        <v>432249.23</v>
       </c>
       <c r="O11" s="10" t="n">
-        <v>0.0344</v>
+        <v>0.0361</v>
       </c>
       <c r="P11" s="8" t="n">
         <v>2746670</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>436720.53</v>
+        <v>406259.96</v>
       </c>
       <c r="R11" s="10" t="n">
-        <v>0.0337</v>
+        <v>0.0353</v>
       </c>
       <c r="S11" s="8" t="n">
-        <v>2696670</v>
+        <v>3021670</v>
       </c>
       <c r="T11" s="9" t="n">
-        <v>436483.01</v>
+        <v>380972.15</v>
       </c>
       <c r="U11" s="10" t="n">
-        <v>0.0347</v>
+        <v>0.0336</v>
       </c>
       <c r="V11" s="8" t="n">
-        <v>2696670</v>
+        <v>3021670</v>
       </c>
       <c r="W11" s="9" t="n">
-        <v>432249.23</v>
+        <v>374687.08</v>
       </c>
       <c r="X11" s="10" t="n">
-        <v>0.0361</v>
+        <v>0.0339</v>
       </c>
       <c r="Y11" s="8" t="n">
-        <v>2746670</v>
+        <v>3021670</v>
       </c>
       <c r="Z11" s="9" t="n">
-        <v>406259.96</v>
+        <v>372239.53</v>
       </c>
       <c r="AA11" s="10" t="n">
-        <v>0.0353</v>
+        <v>0.0358</v>
       </c>
       <c r="AB11" s="8" t="n">
         <v>3021670</v>
       </c>
       <c r="AC11" s="9" t="n">
-        <v>380972.15</v>
+        <v>370366.09</v>
       </c>
       <c r="AD11" s="10" t="n">
-        <v>0.0336</v>
+        <v>0.0376</v>
       </c>
       <c r="AE11" s="8" t="n">
-        <v>3021670</v>
+        <v>3018078</v>
       </c>
       <c r="AF11" s="9" t="n">
-        <v>374687.08</v>
+        <v>347747.47</v>
       </c>
       <c r="AG11" s="10" t="n">
-        <v>0.0339</v>
+        <v>0.0372</v>
       </c>
       <c r="AH11" s="8" t="n">
-        <v>3021670</v>
+        <v>3018078</v>
       </c>
       <c r="AI11" s="9" t="n">
-        <v>372239.53</v>
+        <v>360535.07</v>
       </c>
       <c r="AJ11" s="10" t="n">
-        <v>0.0358</v>
+        <v>0.041</v>
       </c>
       <c r="AK11" s="8" t="n">
-        <v>3021670</v>
+        <v>3018078</v>
       </c>
       <c r="AL11" s="9" t="n">
-        <v>370366.09</v>
+        <v>371545.02</v>
       </c>
       <c r="AM11" s="10" t="n">
-        <v>0.0376</v>
-      </c>
-      <c r="AN11" s="8" t="n">
-        <v>3018078</v>
-      </c>
-      <c r="AO11" s="9" t="n">
-        <v>347747.47</v>
-      </c>
-      <c r="AP11" s="10" t="n">
-        <v>0.0372</v>
-      </c>
-      <c r="AQ11" s="8" t="n">
-        <v>3018078</v>
-      </c>
-      <c r="AR11" s="9" t="n">
-        <v>360535.07</v>
-      </c>
-      <c r="AS11" s="10" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="AT11" s="8" t="n">
-        <v>3018078</v>
-      </c>
-      <c r="AU11" s="9" t="n">
-        <v>371545.02</v>
-      </c>
-      <c r="AV11" s="10" t="n">
         <v>0.0414</v>
       </c>
     </row>
@@ -2161,135 +1879,108 @@
         <v>33244875</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>386072.73</v>
+        <v>422010.44</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>0.0299</v>
+        <v>0.0317</v>
       </c>
       <c r="G12" s="8" t="n">
         <v>33244875</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>460075.83</v>
+        <v>425434.67</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>0.0343</v>
+        <v>0.0328</v>
       </c>
       <c r="J12" s="8" t="n">
         <v>33244875</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>455587.77</v>
+        <v>409842.82</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>0.034</v>
+        <v>0.0326</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>33244875</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>422010.44</v>
+        <v>376199.01</v>
       </c>
       <c r="O12" s="10" t="n">
-        <v>0.0317</v>
+        <v>0.0314</v>
       </c>
       <c r="P12" s="8" t="n">
-        <v>33244875</v>
+        <v>32644875</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>425434.67</v>
+        <v>341204.23</v>
       </c>
       <c r="R12" s="10" t="n">
+        <v>0.0297</v>
+      </c>
+      <c r="S12" s="8" t="n">
+        <v>30107270</v>
+      </c>
+      <c r="T12" s="9" t="n">
+        <v>321666.07</v>
+      </c>
+      <c r="U12" s="10" t="n">
+        <v>0.0284</v>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v>27257270</v>
+      </c>
+      <c r="W12" s="9" t="n">
+        <v>326869.18</v>
+      </c>
+      <c r="X12" s="10" t="n">
+        <v>0.0296</v>
+      </c>
+      <c r="Y12" s="8" t="n">
+        <v>27257270</v>
+      </c>
+      <c r="Z12" s="9" t="n">
+        <v>324961.17</v>
+      </c>
+      <c r="AA12" s="10" t="n">
+        <v>0.0313</v>
+      </c>
+      <c r="AB12" s="8" t="n">
+        <v>27257270</v>
+      </c>
+      <c r="AC12" s="9" t="n">
+        <v>322998.65</v>
+      </c>
+      <c r="AD12" s="10" t="n">
         <v>0.0328</v>
-      </c>
-      <c r="S12" s="8" t="n">
-        <v>33244875</v>
-      </c>
-      <c r="T12" s="9" t="n">
-        <v>409842.82</v>
-      </c>
-      <c r="U12" s="10" t="n">
-        <v>0.0326</v>
-      </c>
-      <c r="V12" s="8" t="n">
-        <v>33244875</v>
-      </c>
-      <c r="W12" s="9" t="n">
-        <v>376199.01</v>
-      </c>
-      <c r="X12" s="10" t="n">
-        <v>0.0314</v>
-      </c>
-      <c r="Y12" s="8" t="n">
-        <v>32644875</v>
-      </c>
-      <c r="Z12" s="9" t="n">
-        <v>341204.23</v>
-      </c>
-      <c r="AA12" s="10" t="n">
-        <v>0.0297</v>
-      </c>
-      <c r="AB12" s="8" t="n">
-        <v>30107270</v>
-      </c>
-      <c r="AC12" s="9" t="n">
-        <v>321666.07</v>
-      </c>
-      <c r="AD12" s="10" t="n">
-        <v>0.0284</v>
       </c>
       <c r="AE12" s="8" t="n">
         <v>27257270</v>
       </c>
       <c r="AF12" s="9" t="n">
-        <v>326869.18</v>
+        <v>300375.12</v>
       </c>
       <c r="AG12" s="10" t="n">
-        <v>0.0296</v>
+        <v>0.0321</v>
       </c>
       <c r="AH12" s="8" t="n">
         <v>27257270</v>
       </c>
       <c r="AI12" s="9" t="n">
-        <v>324961.17</v>
+        <v>276811.21</v>
       </c>
       <c r="AJ12" s="10" t="n">
-        <v>0.0313</v>
+        <v>0.0315</v>
       </c>
       <c r="AK12" s="8" t="n">
         <v>27257270</v>
       </c>
       <c r="AL12" s="9" t="n">
-        <v>322998.65</v>
+        <v>268783.94</v>
       </c>
       <c r="AM12" s="10" t="n">
-        <v>0.0328</v>
-      </c>
-      <c r="AN12" s="8" t="n">
-        <v>27257270</v>
-      </c>
-      <c r="AO12" s="9" t="n">
-        <v>300375.12</v>
-      </c>
-      <c r="AP12" s="10" t="n">
-        <v>0.0321</v>
-      </c>
-      <c r="AQ12" s="8" t="n">
-        <v>27257270</v>
-      </c>
-      <c r="AR12" s="9" t="n">
-        <v>276811.21</v>
-      </c>
-      <c r="AS12" s="10" t="n">
-        <v>0.0315</v>
-      </c>
-      <c r="AT12" s="8" t="n">
-        <v>27257270</v>
-      </c>
-      <c r="AU12" s="9" t="n">
-        <v>268783.94</v>
-      </c>
-      <c r="AV12" s="10" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -2310,138 +2001,111 @@
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>29868916</v>
+        <v>21315882</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>400721.38</v>
+        <v>346020.71</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.0311</v>
+        <v>0.026</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>27771661</v>
+        <v>19831378</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>385776.14</v>
+        <v>322101.24</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>0.0287</v>
+        <v>0.0248</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>23460156</v>
+        <v>18138945</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>397790.41</v>
+        <v>279611.84</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>0.0297</v>
+        <v>0.0222</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>21315882</v>
+        <v>18706995</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>346020.71</v>
+        <v>259110.59</v>
       </c>
       <c r="O13" s="10" t="n">
-        <v>0.026</v>
+        <v>0.0216</v>
       </c>
       <c r="P13" s="8" t="n">
-        <v>19831378</v>
+        <v>18706995</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>322101.24</v>
+        <v>272149.36</v>
       </c>
       <c r="R13" s="10" t="n">
-        <v>0.0248</v>
+        <v>0.0237</v>
       </c>
       <c r="S13" s="8" t="n">
-        <v>18138945</v>
+        <v>18706995</v>
       </c>
       <c r="T13" s="9" t="n">
-        <v>279611.84</v>
+        <v>274599.98</v>
       </c>
       <c r="U13" s="10" t="n">
-        <v>0.0222</v>
+        <v>0.0242</v>
       </c>
       <c r="V13" s="8" t="n">
-        <v>18706995</v>
+        <v>18558995</v>
       </c>
       <c r="W13" s="9" t="n">
-        <v>259110.59</v>
+        <v>320810.79</v>
       </c>
       <c r="X13" s="10" t="n">
-        <v>0.0216</v>
+        <v>0.0291</v>
       </c>
       <c r="Y13" s="8" t="n">
-        <v>18706995</v>
+        <v>18341573</v>
       </c>
       <c r="Z13" s="9" t="n">
-        <v>272149.36</v>
+        <v>300178.18</v>
       </c>
       <c r="AA13" s="10" t="n">
-        <v>0.0237</v>
+        <v>0.0289</v>
       </c>
       <c r="AB13" s="8" t="n">
-        <v>18706995</v>
+        <v>18706973</v>
       </c>
       <c r="AC13" s="9" t="n">
-        <v>274599.98</v>
+        <v>293231.8</v>
       </c>
       <c r="AD13" s="10" t="n">
-        <v>0.0242</v>
+        <v>0.0298</v>
       </c>
       <c r="AE13" s="8" t="n">
-        <v>18558995</v>
+        <v>18706973</v>
       </c>
       <c r="AF13" s="9" t="n">
-        <v>320810.79</v>
+        <v>297908.55</v>
       </c>
       <c r="AG13" s="10" t="n">
-        <v>0.0291</v>
+        <v>0.0319</v>
       </c>
       <c r="AH13" s="8" t="n">
-        <v>18341573</v>
+        <v>18706973</v>
       </c>
       <c r="AI13" s="9" t="n">
-        <v>300178.18</v>
+        <v>294644.18</v>
       </c>
       <c r="AJ13" s="10" t="n">
-        <v>0.0289</v>
+        <v>0.0335</v>
       </c>
       <c r="AK13" s="8" t="n">
         <v>18706973</v>
       </c>
       <c r="AL13" s="9" t="n">
-        <v>293231.8</v>
+        <v>322779.47</v>
       </c>
       <c r="AM13" s="10" t="n">
-        <v>0.0298</v>
-      </c>
-      <c r="AN13" s="8" t="n">
-        <v>18706973</v>
-      </c>
-      <c r="AO13" s="9" t="n">
-        <v>297908.55</v>
-      </c>
-      <c r="AP13" s="10" t="n">
-        <v>0.0319</v>
-      </c>
-      <c r="AQ13" s="8" t="n">
-        <v>18706973</v>
-      </c>
-      <c r="AR13" s="9" t="n">
-        <v>294644.18</v>
-      </c>
-      <c r="AS13" s="10" t="n">
-        <v>0.0335</v>
-      </c>
-      <c r="AT13" s="8" t="n">
-        <v>18706973</v>
-      </c>
-      <c r="AU13" s="9" t="n">
-        <v>322779.47</v>
-      </c>
-      <c r="AV13" s="10" t="n">
         <v>0.036</v>
       </c>
     </row>
@@ -2462,138 +2126,111 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>14645626</v>
+        <v>13033470</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>432734.31</v>
+        <v>483437.47</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>0.0336</v>
+        <v>0.0363</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>13974725</v>
+        <v>12435671</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>474777.31</v>
+        <v>467245.47</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>0.0354</v>
+        <v>0.036</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>13974725</v>
+        <v>12435671</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>479584.61</v>
+        <v>433656.72</v>
       </c>
       <c r="L14" s="10" t="n">
-        <v>0.0358</v>
+        <v>0.0345</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>13033470</v>
+        <v>12335671</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>483437.47</v>
+        <v>422743.45</v>
       </c>
       <c r="O14" s="10" t="n">
-        <v>0.0363</v>
+        <v>0.0353</v>
       </c>
       <c r="P14" s="8" t="n">
-        <v>12435671</v>
+        <v>12335671</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>467245.47</v>
+        <v>394679.79</v>
       </c>
       <c r="R14" s="10" t="n">
-        <v>0.036</v>
+        <v>0.0343</v>
       </c>
       <c r="S14" s="8" t="n">
-        <v>12435671</v>
+        <v>12335671</v>
       </c>
       <c r="T14" s="9" t="n">
-        <v>433656.72</v>
+        <v>395123.88</v>
       </c>
       <c r="U14" s="10" t="n">
-        <v>0.0345</v>
+        <v>0.0349</v>
       </c>
       <c r="V14" s="8" t="n">
         <v>12335671</v>
       </c>
       <c r="W14" s="9" t="n">
-        <v>422743.45</v>
+        <v>392669.08</v>
       </c>
       <c r="X14" s="10" t="n">
-        <v>0.0353</v>
+        <v>0.0356</v>
       </c>
       <c r="Y14" s="8" t="n">
-        <v>12335671</v>
+        <v>12231374</v>
       </c>
       <c r="Z14" s="9" t="n">
-        <v>394679.79</v>
+        <v>364103.54</v>
       </c>
       <c r="AA14" s="10" t="n">
-        <v>0.0343</v>
+        <v>0.0351</v>
       </c>
       <c r="AB14" s="8" t="n">
-        <v>12335671</v>
+        <v>11040212</v>
       </c>
       <c r="AC14" s="9" t="n">
-        <v>395123.88</v>
+        <v>323345.73</v>
       </c>
       <c r="AD14" s="10" t="n">
-        <v>0.0349</v>
+        <v>0.0328</v>
       </c>
       <c r="AE14" s="8" t="n">
-        <v>12335671</v>
+        <v>10399289</v>
       </c>
       <c r="AF14" s="9" t="n">
-        <v>392669.08</v>
+        <v>277224.25</v>
       </c>
       <c r="AG14" s="10" t="n">
-        <v>0.0356</v>
+        <v>0.0297</v>
       </c>
       <c r="AH14" s="8" t="n">
-        <v>12231374</v>
+        <v>10068665</v>
       </c>
       <c r="AI14" s="9" t="n">
-        <v>364103.54</v>
+        <v>260285.06</v>
       </c>
       <c r="AJ14" s="10" t="n">
-        <v>0.0351</v>
+        <v>0.0296</v>
       </c>
       <c r="AK14" s="8" t="n">
-        <v>11040212</v>
+        <v>9331737</v>
       </c>
       <c r="AL14" s="9" t="n">
-        <v>323345.73</v>
+        <v>279004.94</v>
       </c>
       <c r="AM14" s="10" t="n">
-        <v>0.0328</v>
-      </c>
-      <c r="AN14" s="8" t="n">
-        <v>10399289</v>
-      </c>
-      <c r="AO14" s="9" t="n">
-        <v>277224.25</v>
-      </c>
-      <c r="AP14" s="10" t="n">
-        <v>0.0297</v>
-      </c>
-      <c r="AQ14" s="8" t="n">
-        <v>10068665</v>
-      </c>
-      <c r="AR14" s="9" t="n">
-        <v>260285.06</v>
-      </c>
-      <c r="AS14" s="10" t="n">
-        <v>0.0296</v>
-      </c>
-      <c r="AT14" s="8" t="n">
-        <v>9331737</v>
-      </c>
-      <c r="AU14" s="9" t="n">
-        <v>279004.94</v>
-      </c>
-      <c r="AV14" s="10" t="n">
         <v>0.0311</v>
       </c>
     </row>
@@ -2614,138 +2251,111 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>26944033</v>
+        <v>16417936</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>336962.08</v>
+        <v>265215.34</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.0261</v>
+        <v>0.0199</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>20693682</v>
+        <v>17621740</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>269038.56</v>
+        <v>274916.77</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>0.02</v>
+        <v>0.0212</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>16509541</v>
+        <v>9306473</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>270921.57</v>
+        <v>137949.85</v>
       </c>
       <c r="L15" s="10" t="n">
-        <v>0.0202</v>
+        <v>0.011</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>16417936</v>
+        <v>9306473</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>265215.34</v>
+        <v>134180.73</v>
       </c>
       <c r="O15" s="10" t="n">
-        <v>0.0199</v>
+        <v>0.0112</v>
       </c>
       <c r="P15" s="8" t="n">
-        <v>17621740</v>
+        <v>9306473</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>274916.77</v>
+        <v>136767.93</v>
       </c>
       <c r="R15" s="10" t="n">
-        <v>0.0212</v>
+        <v>0.0119</v>
       </c>
       <c r="S15" s="8" t="n">
         <v>9306473</v>
       </c>
       <c r="T15" s="9" t="n">
-        <v>137949.85</v>
+        <v>140434.68</v>
       </c>
       <c r="U15" s="10" t="n">
-        <v>0.011</v>
+        <v>0.0124</v>
       </c>
       <c r="V15" s="8" t="n">
         <v>9306473</v>
       </c>
       <c r="W15" s="9" t="n">
-        <v>134180.73</v>
+        <v>149071.08</v>
       </c>
       <c r="X15" s="10" t="n">
-        <v>0.0112</v>
+        <v>0.0135</v>
       </c>
       <c r="Y15" s="8" t="n">
         <v>9306473</v>
       </c>
       <c r="Z15" s="9" t="n">
-        <v>136767.93</v>
+        <v>145432.25</v>
       </c>
       <c r="AA15" s="10" t="n">
-        <v>0.0119</v>
+        <v>0.014</v>
       </c>
       <c r="AB15" s="8" t="n">
         <v>9306473</v>
       </c>
       <c r="AC15" s="9" t="n">
-        <v>140434.68</v>
+        <v>139606.4</v>
       </c>
       <c r="AD15" s="10" t="n">
-        <v>0.0124</v>
+        <v>0.0142</v>
       </c>
       <c r="AE15" s="8" t="n">
         <v>9306473</v>
       </c>
       <c r="AF15" s="9" t="n">
-        <v>149071.08</v>
+        <v>146172.12</v>
       </c>
       <c r="AG15" s="10" t="n">
-        <v>0.0135</v>
+        <v>0.0156</v>
       </c>
       <c r="AH15" s="8" t="n">
         <v>9306473</v>
       </c>
       <c r="AI15" s="9" t="n">
-        <v>145432.25</v>
+        <v>157065.34</v>
       </c>
       <c r="AJ15" s="10" t="n">
-        <v>0.014</v>
+        <v>0.0178</v>
       </c>
       <c r="AK15" s="8" t="n">
         <v>9306473</v>
       </c>
       <c r="AL15" s="9" t="n">
-        <v>139606.4</v>
+        <v>174943.08</v>
       </c>
       <c r="AM15" s="10" t="n">
-        <v>0.0142</v>
-      </c>
-      <c r="AN15" s="8" t="n">
-        <v>9306473</v>
-      </c>
-      <c r="AO15" s="9" t="n">
-        <v>146172.12</v>
-      </c>
-      <c r="AP15" s="10" t="n">
-        <v>0.0156</v>
-      </c>
-      <c r="AQ15" s="8" t="n">
-        <v>9306473</v>
-      </c>
-      <c r="AR15" s="9" t="n">
-        <v>157065.34</v>
-      </c>
-      <c r="AS15" s="10" t="n">
-        <v>0.0178</v>
-      </c>
-      <c r="AT15" s="8" t="n">
-        <v>9306473</v>
-      </c>
-      <c r="AU15" s="9" t="n">
-        <v>174943.08</v>
-      </c>
-      <c r="AV15" s="10" t="n">
         <v>0.0195</v>
       </c>
     </row>
@@ -2766,138 +2376,111 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>13769904</v>
+        <v>13125545</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>172798.53</v>
+        <v>166878.18</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>0.0134</v>
+        <v>0.0125</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>13769904</v>
+        <v>13125545</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>177122.28</v>
+        <v>165224.36</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>0.0132</v>
+        <v>0.0127</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>14083029</v>
+        <v>12775545</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>171545.38</v>
+        <v>152999.93</v>
       </c>
       <c r="L16" s="10" t="n">
-        <v>0.0128</v>
+        <v>0.0122</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>13125545</v>
+        <v>12107943</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>166878.18</v>
+        <v>148164.9</v>
       </c>
       <c r="O16" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.0124</v>
       </c>
       <c r="P16" s="8" t="n">
-        <v>13125545</v>
+        <v>11632943</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>165224.36</v>
+        <v>146586.71</v>
       </c>
       <c r="R16" s="10" t="n">
         <v>0.0127</v>
       </c>
       <c r="S16" s="8" t="n">
-        <v>12775545</v>
+        <v>11217622</v>
       </c>
       <c r="T16" s="9" t="n">
-        <v>152999.93</v>
+        <v>142497.45</v>
       </c>
       <c r="U16" s="10" t="n">
-        <v>0.0122</v>
+        <v>0.0126</v>
       </c>
       <c r="V16" s="8" t="n">
-        <v>12107943</v>
+        <v>10341500</v>
       </c>
       <c r="W16" s="9" t="n">
-        <v>148164.9</v>
+        <v>132712.47</v>
       </c>
       <c r="X16" s="10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="Y16" s="8" t="n">
+        <v>10341500</v>
+      </c>
+      <c r="Z16" s="9" t="n">
+        <v>129392.85</v>
+      </c>
+      <c r="AA16" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AB16" s="8" t="n">
+        <v>10403670</v>
+      </c>
+      <c r="AC16" s="9" t="n">
+        <v>123169.05</v>
+      </c>
+      <c r="AD16" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AE16" s="8" t="n">
+        <v>10133496</v>
+      </c>
+      <c r="AF16" s="9" t="n">
+        <v>115947.46</v>
+      </c>
+      <c r="AG16" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="Y16" s="8" t="n">
-        <v>11632943</v>
-      </c>
-      <c r="Z16" s="9" t="n">
-        <v>146586.71</v>
-      </c>
-      <c r="AA16" s="10" t="n">
-        <v>0.0127</v>
-      </c>
-      <c r="AB16" s="8" t="n">
-        <v>11217622</v>
-      </c>
-      <c r="AC16" s="9" t="n">
-        <v>142497.45</v>
-      </c>
-      <c r="AD16" s="10" t="n">
+      <c r="AH16" s="8" t="n">
+        <v>9911843</v>
+      </c>
+      <c r="AI16" s="9" t="n">
+        <v>110665.73</v>
+      </c>
+      <c r="AJ16" s="10" t="n">
         <v>0.0126</v>
       </c>
-      <c r="AE16" s="8" t="n">
-        <v>10341500</v>
-      </c>
-      <c r="AF16" s="9" t="n">
-        <v>132712.47</v>
-      </c>
-      <c r="AG16" s="10" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="AH16" s="8" t="n">
-        <v>10341500</v>
-      </c>
-      <c r="AI16" s="9" t="n">
-        <v>129392.85</v>
-      </c>
-      <c r="AJ16" s="10" t="n">
-        <v>0.0125</v>
-      </c>
       <c r="AK16" s="8" t="n">
-        <v>10403670</v>
+        <v>7388241</v>
       </c>
       <c r="AL16" s="9" t="n">
-        <v>123169.05</v>
+        <v>89940.75</v>
       </c>
       <c r="AM16" s="10" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="AN16" s="8" t="n">
-        <v>10133496</v>
-      </c>
-      <c r="AO16" s="9" t="n">
-        <v>115947.46</v>
-      </c>
-      <c r="AP16" s="10" t="n">
-        <v>0.0124</v>
-      </c>
-      <c r="AQ16" s="8" t="n">
-        <v>9911843</v>
-      </c>
-      <c r="AR16" s="9" t="n">
-        <v>110665.73</v>
-      </c>
-      <c r="AS16" s="10" t="n">
-        <v>0.0126</v>
-      </c>
-      <c r="AT16" s="8" t="n">
-        <v>7388241</v>
-      </c>
-      <c r="AU16" s="9" t="n">
-        <v>89940.75</v>
-      </c>
-      <c r="AV16" s="10" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -2918,138 +2501,111 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>13271296</v>
+        <v>10989584</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>162467.21</v>
+        <v>166085.58</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0.0126</v>
+        <v>0.0125</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>12881359</v>
+        <v>10765866</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>173666.48</v>
+        <v>164857.71</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>0.0129</v>
+        <v>0.0127</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>12623339</v>
+        <v>10173460</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>167133.01</v>
+        <v>152734.15</v>
       </c>
       <c r="L17" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.0121</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>10989584</v>
+        <v>9988840</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>166085.58</v>
+        <v>150162.23</v>
       </c>
       <c r="O17" s="10" t="n">
         <v>0.0125</v>
       </c>
       <c r="P17" s="8" t="n">
-        <v>10765866</v>
+        <v>8991707</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>164857.71</v>
+        <v>142914.19</v>
       </c>
       <c r="R17" s="10" t="n">
-        <v>0.0127</v>
+        <v>0.0124</v>
       </c>
       <c r="S17" s="8" t="n">
-        <v>10173460</v>
+        <v>9450707</v>
       </c>
       <c r="T17" s="9" t="n">
-        <v>152734.15</v>
+        <v>146920.69</v>
       </c>
       <c r="U17" s="10" t="n">
-        <v>0.0121</v>
+        <v>0.013</v>
       </c>
       <c r="V17" s="8" t="n">
-        <v>9988840</v>
+        <v>9147124</v>
       </c>
       <c r="W17" s="9" t="n">
-        <v>150162.23</v>
+        <v>137746.54</v>
       </c>
       <c r="X17" s="10" t="n">
         <v>0.0125</v>
       </c>
       <c r="Y17" s="8" t="n">
-        <v>8991707</v>
+        <v>8881919</v>
       </c>
       <c r="Z17" s="9" t="n">
-        <v>142914.19</v>
+        <v>130182.29</v>
       </c>
       <c r="AA17" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AB17" s="8" t="n">
+        <v>7994194</v>
+      </c>
+      <c r="AC17" s="9" t="n">
+        <v>123918</v>
+      </c>
+      <c r="AD17" s="10" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="AE17" s="8" t="n">
+        <v>7994194</v>
+      </c>
+      <c r="AF17" s="9" t="n">
+        <v>115292.27</v>
+      </c>
+      <c r="AG17" s="10" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="AH17" s="8" t="n">
+        <v>7755553</v>
+      </c>
+      <c r="AI17" s="9" t="n">
+        <v>109159.41</v>
+      </c>
+      <c r="AJ17" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="AB17" s="8" t="n">
-        <v>9450707</v>
-      </c>
-      <c r="AC17" s="9" t="n">
-        <v>146920.69</v>
-      </c>
-      <c r="AD17" s="10" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="AE17" s="8" t="n">
-        <v>9147124</v>
-      </c>
-      <c r="AF17" s="9" t="n">
-        <v>137746.54</v>
-      </c>
-      <c r="AG17" s="10" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="AH17" s="8" t="n">
-        <v>8881919</v>
-      </c>
-      <c r="AI17" s="9" t="n">
-        <v>130182.29</v>
-      </c>
-      <c r="AJ17" s="10" t="n">
-        <v>0.0125</v>
-      </c>
       <c r="AK17" s="8" t="n">
-        <v>7994194</v>
+        <v>6223549</v>
       </c>
       <c r="AL17" s="9" t="n">
-        <v>123918</v>
+        <v>92071.17999999999</v>
       </c>
       <c r="AM17" s="10" t="n">
-        <v>0.0126</v>
-      </c>
-      <c r="AN17" s="8" t="n">
-        <v>7994194</v>
-      </c>
-      <c r="AO17" s="9" t="n">
-        <v>115292.27</v>
-      </c>
-      <c r="AP17" s="10" t="n">
-        <v>0.0123</v>
-      </c>
-      <c r="AQ17" s="8" t="n">
-        <v>7755553</v>
-      </c>
-      <c r="AR17" s="9" t="n">
-        <v>109159.41</v>
-      </c>
-      <c r="AS17" s="10" t="n">
-        <v>0.0124</v>
-      </c>
-      <c r="AT17" s="8" t="n">
-        <v>6223549</v>
-      </c>
-      <c r="AU17" s="9" t="n">
-        <v>92071.17999999999</v>
-      </c>
-      <c r="AV17" s="10" t="n">
         <v>0.0103</v>
       </c>
     </row>
@@ -3070,138 +2626,111 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>18853686</v>
+        <v>17903094</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>164253.31</v>
+        <v>163696.94</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>0.0127</v>
+        <v>0.0123</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>18853686</v>
+        <v>17405149</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>173774.42</v>
+        <v>164043.53</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>0.0129</v>
+        <v>0.0126</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>18750502</v>
+        <v>15759789</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>165998.19</v>
+        <v>153571.26</v>
       </c>
       <c r="L18" s="10" t="n">
+        <v>0.0122</v>
+      </c>
+      <c r="M18" s="8" t="n">
+        <v>15148311</v>
+      </c>
+      <c r="N18" s="9" t="n">
+        <v>148741.27</v>
+      </c>
+      <c r="O18" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="M18" s="8" t="n">
-        <v>17903094</v>
-      </c>
-      <c r="N18" s="9" t="n">
-        <v>163696.94</v>
-      </c>
-      <c r="O18" s="10" t="n">
-        <v>0.0123</v>
-      </c>
       <c r="P18" s="8" t="n">
-        <v>17405149</v>
+        <v>14786344</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>164043.53</v>
+        <v>145061.43</v>
       </c>
       <c r="R18" s="10" t="n">
         <v>0.0126</v>
       </c>
       <c r="S18" s="8" t="n">
-        <v>15759789</v>
+        <v>14470385</v>
       </c>
       <c r="T18" s="9" t="n">
-        <v>153571.26</v>
+        <v>140333.79</v>
       </c>
       <c r="U18" s="10" t="n">
-        <v>0.0122</v>
+        <v>0.0124</v>
       </c>
       <c r="V18" s="8" t="n">
-        <v>15148311</v>
+        <v>14258435</v>
       </c>
       <c r="W18" s="9" t="n">
-        <v>148741.27</v>
+        <v>141151.38</v>
       </c>
       <c r="X18" s="10" t="n">
-        <v>0.0124</v>
+        <v>0.0128</v>
       </c>
       <c r="Y18" s="8" t="n">
-        <v>14786344</v>
+        <v>14258435</v>
       </c>
       <c r="Z18" s="9" t="n">
-        <v>145061.43</v>
+        <v>132603.45</v>
       </c>
       <c r="AA18" s="10" t="n">
+        <v>0.0128</v>
+      </c>
+      <c r="AB18" s="8" t="n">
+        <v>13936283</v>
+      </c>
+      <c r="AC18" s="9" t="n">
+        <v>123789.03</v>
+      </c>
+      <c r="AD18" s="10" t="n">
         <v>0.0126</v>
       </c>
-      <c r="AB18" s="8" t="n">
-        <v>14470385</v>
-      </c>
-      <c r="AC18" s="9" t="n">
-        <v>140333.79</v>
-      </c>
-      <c r="AD18" s="10" t="n">
-        <v>0.0124</v>
-      </c>
       <c r="AE18" s="8" t="n">
-        <v>14258435</v>
+        <v>13003659</v>
       </c>
       <c r="AF18" s="9" t="n">
-        <v>141151.38</v>
+        <v>115264.43</v>
       </c>
       <c r="AG18" s="10" t="n">
-        <v>0.0128</v>
+        <v>0.0123</v>
       </c>
       <c r="AH18" s="8" t="n">
-        <v>14258435</v>
+        <v>11479604</v>
       </c>
       <c r="AI18" s="9" t="n">
-        <v>132603.45</v>
+        <v>100630.21</v>
       </c>
       <c r="AJ18" s="10" t="n">
-        <v>0.0128</v>
+        <v>0.0114</v>
       </c>
       <c r="AK18" s="8" t="n">
-        <v>13936283</v>
+        <v>8859127</v>
       </c>
       <c r="AL18" s="9" t="n">
-        <v>123789.03</v>
+        <v>85955.67999999999</v>
       </c>
       <c r="AM18" s="10" t="n">
-        <v>0.0126</v>
-      </c>
-      <c r="AN18" s="8" t="n">
-        <v>13003659</v>
-      </c>
-      <c r="AO18" s="9" t="n">
-        <v>115264.43</v>
-      </c>
-      <c r="AP18" s="10" t="n">
-        <v>0.0123</v>
-      </c>
-      <c r="AQ18" s="8" t="n">
-        <v>11479604</v>
-      </c>
-      <c r="AR18" s="9" t="n">
-        <v>100630.21</v>
-      </c>
-      <c r="AS18" s="10" t="n">
-        <v>0.0114</v>
-      </c>
-      <c r="AT18" s="8" t="n">
-        <v>8859127</v>
-      </c>
-      <c r="AU18" s="9" t="n">
-        <v>85955.67999999999</v>
-      </c>
-      <c r="AV18" s="10" t="n">
         <v>0.009599999999999999</v>
       </c>
     </row>
@@ -3222,138 +2751,111 @@
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>2274074</v>
+        <v>4189074</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>47368.96</v>
+        <v>97173.95</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>0.0037</v>
+        <v>0.0073</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>2906065</v>
+        <v>4189074</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>69277.67999999999</v>
+        <v>96721.53</v>
       </c>
       <c r="I19" s="10" t="n">
-        <v>0.0052</v>
+        <v>0.0075</v>
       </c>
       <c r="J19" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>96591.67</v>
+        <v>95502.50999999999</v>
       </c>
       <c r="L19" s="10" t="n">
-        <v>0.0072</v>
+        <v>0.0076</v>
       </c>
       <c r="M19" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>97173.95</v>
+        <v>96130.87</v>
       </c>
       <c r="O19" s="10" t="n">
-        <v>0.0073</v>
+        <v>0.008</v>
       </c>
       <c r="P19" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>96721.53</v>
+        <v>95904.66</v>
       </c>
       <c r="R19" s="10" t="n">
-        <v>0.0075</v>
+        <v>0.0083</v>
       </c>
       <c r="S19" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="T19" s="9" t="n">
-        <v>95502.50999999999</v>
+        <v>112108</v>
       </c>
       <c r="U19" s="10" t="n">
-        <v>0.0076</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="V19" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="W19" s="9" t="n">
-        <v>96130.87</v>
+        <v>102435.43</v>
       </c>
       <c r="X19" s="10" t="n">
-        <v>0.008</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="Y19" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="Z19" s="9" t="n">
-        <v>95904.66</v>
+        <v>103562.29</v>
       </c>
       <c r="AA19" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.01</v>
       </c>
       <c r="AB19" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="AC19" s="9" t="n">
-        <v>112108</v>
+        <v>112061.92</v>
       </c>
       <c r="AD19" s="10" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0114</v>
       </c>
       <c r="AE19" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="AF19" s="9" t="n">
-        <v>102435.43</v>
+        <v>107022.46</v>
       </c>
       <c r="AG19" s="10" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0115</v>
       </c>
       <c r="AH19" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="AI19" s="9" t="n">
-        <v>103562.29</v>
+        <v>109571.51</v>
       </c>
       <c r="AJ19" s="10" t="n">
-        <v>0.01</v>
+        <v>0.0125</v>
       </c>
       <c r="AK19" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="AL19" s="9" t="n">
-        <v>112061.92</v>
+        <v>116089.71</v>
       </c>
       <c r="AM19" s="10" t="n">
-        <v>0.0114</v>
-      </c>
-      <c r="AN19" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="AO19" s="9" t="n">
-        <v>107022.46</v>
-      </c>
-      <c r="AP19" s="10" t="n">
-        <v>0.0115</v>
-      </c>
-      <c r="AQ19" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="AR19" s="9" t="n">
-        <v>109571.51</v>
-      </c>
-      <c r="AS19" s="10" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="AT19" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="AU19" s="9" t="n">
-        <v>116089.71</v>
-      </c>
-      <c r="AV19" s="10" t="n">
         <v>0.0129</v>
       </c>
     </row>
@@ -3377,135 +2879,108 @@
         <v>80755676</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>92667.14</v>
+        <v>108390.27</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>0.0072</v>
+        <v>0.0081</v>
       </c>
       <c r="G20" s="8" t="n">
         <v>80755676</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>101461.43</v>
+        <v>112484.58</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>0.0076</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="J20" s="8" t="n">
         <v>80755676</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>102390.12</v>
+        <v>112298.84</v>
       </c>
       <c r="L20" s="10" t="n">
-        <v>0.0076</v>
+        <v>0.0089</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>80755676</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>108390.27</v>
+        <v>112403.83</v>
       </c>
       <c r="O20" s="10" t="n">
-        <v>0.0081</v>
+        <v>0.0094</v>
       </c>
       <c r="P20" s="8" t="n">
-        <v>80755676</v>
+        <v>73511702</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>112484.58</v>
+        <v>102769.36</v>
       </c>
       <c r="R20" s="10" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0089</v>
       </c>
       <c r="S20" s="8" t="n">
-        <v>80755676</v>
+        <v>44206584</v>
       </c>
       <c r="T20" s="9" t="n">
-        <v>112298.84</v>
+        <v>59811.51</v>
       </c>
       <c r="U20" s="10" t="n">
-        <v>0.0089</v>
+        <v>0.0053</v>
       </c>
       <c r="V20" s="8" t="n">
-        <v>80755676</v>
+        <v>44206584</v>
       </c>
       <c r="W20" s="9" t="n">
-        <v>112403.83</v>
+        <v>85367.33</v>
       </c>
       <c r="X20" s="10" t="n">
-        <v>0.0094</v>
+        <v>0.0077</v>
       </c>
       <c r="Y20" s="8" t="n">
-        <v>73511702</v>
+        <v>44206584</v>
       </c>
       <c r="Z20" s="9" t="n">
-        <v>102769.36</v>
+        <v>88656.3</v>
       </c>
       <c r="AA20" s="10" t="n">
-        <v>0.0089</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="AB20" s="8" t="n">
         <v>44206584</v>
       </c>
       <c r="AC20" s="9" t="n">
-        <v>59811.51</v>
+        <v>84147.23</v>
       </c>
       <c r="AD20" s="10" t="n">
-        <v>0.0053</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="AE20" s="8" t="n">
         <v>44206584</v>
       </c>
       <c r="AF20" s="9" t="n">
-        <v>85367.33</v>
+        <v>77701.91</v>
       </c>
       <c r="AG20" s="10" t="n">
-        <v>0.0077</v>
+        <v>0.0083</v>
       </c>
       <c r="AH20" s="8" t="n">
         <v>44206584</v>
       </c>
       <c r="AI20" s="9" t="n">
-        <v>88656.3</v>
+        <v>68931.33</v>
       </c>
       <c r="AJ20" s="10" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0078</v>
       </c>
       <c r="AK20" s="8" t="n">
         <v>44206584</v>
       </c>
       <c r="AL20" s="9" t="n">
-        <v>84147.23</v>
+        <v>77184.7</v>
       </c>
       <c r="AM20" s="10" t="n">
-        <v>0.008500000000000001</v>
-      </c>
-      <c r="AN20" s="8" t="n">
-        <v>44206584</v>
-      </c>
-      <c r="AO20" s="9" t="n">
-        <v>77701.91</v>
-      </c>
-      <c r="AP20" s="10" t="n">
-        <v>0.0083</v>
-      </c>
-      <c r="AQ20" s="8" t="n">
-        <v>44206584</v>
-      </c>
-      <c r="AR20" s="9" t="n">
-        <v>68931.33</v>
-      </c>
-      <c r="AS20" s="10" t="n">
-        <v>0.0078</v>
-      </c>
-      <c r="AT20" s="8" t="n">
-        <v>44206584</v>
-      </c>
-      <c r="AU20" s="9" t="n">
-        <v>77184.7</v>
-      </c>
-      <c r="AV20" s="10" t="n">
         <v>0.0086</v>
       </c>
     </row>
@@ -3543,67 +3018,58 @@
       <c r="S21" s="8" t="n"/>
       <c r="T21" s="9" t="n"/>
       <c r="U21" s="10" t="n"/>
-      <c r="V21" s="8" t="n"/>
-      <c r="W21" s="9" t="n"/>
-      <c r="X21" s="10" t="n"/>
-      <c r="Y21" s="8" t="n"/>
-      <c r="Z21" s="9" t="n"/>
-      <c r="AA21" s="10" t="n"/>
-      <c r="AB21" s="8" t="n"/>
-      <c r="AC21" s="9" t="n"/>
-      <c r="AD21" s="10" t="n"/>
+      <c r="V21" s="8" t="n">
+        <v>591805</v>
+      </c>
+      <c r="W21" s="9" t="n">
+        <v>5149</v>
+      </c>
+      <c r="X21" s="10" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="Y21" s="8" t="n">
+        <v>5392631</v>
+      </c>
+      <c r="Z21" s="9" t="n">
+        <v>43674.92</v>
+      </c>
+      <c r="AA21" s="10" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="AB21" s="8" t="n">
+        <v>8585949</v>
+      </c>
+      <c r="AC21" s="9" t="n">
+        <v>56044.78</v>
+      </c>
+      <c r="AD21" s="10" t="n">
+        <v>0.0057</v>
+      </c>
       <c r="AE21" s="8" t="n">
-        <v>591805</v>
+        <v>10913294</v>
       </c>
       <c r="AF21" s="9" t="n">
-        <v>5149</v>
+        <v>67154.95</v>
       </c>
       <c r="AG21" s="10" t="n">
-        <v>0.0005</v>
+        <v>0.0072</v>
       </c>
       <c r="AH21" s="8" t="n">
-        <v>5392631</v>
+        <v>12053879</v>
       </c>
       <c r="AI21" s="9" t="n">
-        <v>43674.92</v>
+        <v>70937.08</v>
       </c>
       <c r="AJ21" s="10" t="n">
-        <v>0.0042</v>
+        <v>0.0081</v>
       </c>
       <c r="AK21" s="8" t="n">
-        <v>8585949</v>
+        <v>12053879</v>
       </c>
       <c r="AL21" s="9" t="n">
-        <v>56044.78</v>
+        <v>76801.28999999999</v>
       </c>
       <c r="AM21" s="10" t="n">
-        <v>0.0057</v>
-      </c>
-      <c r="AN21" s="8" t="n">
-        <v>10913294</v>
-      </c>
-      <c r="AO21" s="9" t="n">
-        <v>67154.95</v>
-      </c>
-      <c r="AP21" s="10" t="n">
-        <v>0.0072</v>
-      </c>
-      <c r="AQ21" s="8" t="n">
-        <v>12053879</v>
-      </c>
-      <c r="AR21" s="9" t="n">
-        <v>70937.08</v>
-      </c>
-      <c r="AS21" s="10" t="n">
-        <v>0.0081</v>
-      </c>
-      <c r="AT21" s="8" t="n">
-        <v>12053879</v>
-      </c>
-      <c r="AU21" s="9" t="n">
-        <v>76801.28999999999</v>
-      </c>
-      <c r="AV21" s="10" t="n">
         <v>0.0086</v>
       </c>
     </row>
@@ -3623,56 +3089,74 @@
           <t>Capital Markets</t>
         </is>
       </c>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="8" t="n"/>
-      <c r="H22" s="9" t="n"/>
-      <c r="I22" s="10" t="n"/>
-      <c r="J22" s="8" t="n"/>
-      <c r="K22" s="9" t="n"/>
-      <c r="L22" s="10" t="n"/>
+      <c r="D22" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>88833.99000000001</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>80358.22</v>
+      </c>
+      <c r="I22" s="10" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="J22" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>73737.16</v>
+      </c>
+      <c r="L22" s="10" t="n">
+        <v>0.0059</v>
+      </c>
       <c r="M22" s="8" t="n">
         <v>797719</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>88833.99000000001</v>
+        <v>62190.17</v>
       </c>
       <c r="O22" s="10" t="n">
-        <v>0.0067</v>
+        <v>0.0052</v>
       </c>
       <c r="P22" s="8" t="n">
         <v>797719</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>80358.22</v>
+        <v>58951.43</v>
       </c>
       <c r="R22" s="10" t="n">
-        <v>0.0062</v>
+        <v>0.0051</v>
       </c>
       <c r="S22" s="8" t="n">
         <v>797719</v>
       </c>
       <c r="T22" s="9" t="n">
-        <v>73737.16</v>
+        <v>61368.52</v>
       </c>
       <c r="U22" s="10" t="n">
-        <v>0.0059</v>
+        <v>0.0054</v>
       </c>
       <c r="V22" s="8" t="n">
         <v>797719</v>
       </c>
       <c r="W22" s="9" t="n">
-        <v>62190.17</v>
+        <v>71347.99000000001</v>
       </c>
       <c r="X22" s="10" t="n">
-        <v>0.0052</v>
+        <v>0.0065</v>
       </c>
       <c r="Y22" s="8" t="n">
         <v>797719</v>
       </c>
       <c r="Z22" s="9" t="n">
-        <v>58951.43</v>
+        <v>52665.41</v>
       </c>
       <c r="AA22" s="10" t="n">
         <v>0.0051</v>
@@ -3681,63 +3165,36 @@
         <v>797719</v>
       </c>
       <c r="AC22" s="9" t="n">
-        <v>61368.52</v>
+        <v>48884.22</v>
       </c>
       <c r="AD22" s="10" t="n">
-        <v>0.0054</v>
+        <v>0.005</v>
       </c>
       <c r="AE22" s="8" t="n">
         <v>797719</v>
       </c>
       <c r="AF22" s="9" t="n">
-        <v>71347.99000000001</v>
+        <v>42372.84</v>
       </c>
       <c r="AG22" s="10" t="n">
-        <v>0.0065</v>
+        <v>0.0045</v>
       </c>
       <c r="AH22" s="8" t="n">
         <v>797719</v>
       </c>
       <c r="AI22" s="9" t="n">
-        <v>52665.41</v>
+        <v>39819.34</v>
       </c>
       <c r="AJ22" s="10" t="n">
-        <v>0.0051</v>
+        <v>0.0045</v>
       </c>
       <c r="AK22" s="8" t="n">
-        <v>797719</v>
+        <v>882136</v>
       </c>
       <c r="AL22" s="9" t="n">
-        <v>48884.22</v>
+        <v>50572.42</v>
       </c>
       <c r="AM22" s="10" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="AN22" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="AO22" s="9" t="n">
-        <v>42372.84</v>
-      </c>
-      <c r="AP22" s="10" t="n">
-        <v>0.0045</v>
-      </c>
-      <c r="AQ22" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="AR22" s="9" t="n">
-        <v>39819.34</v>
-      </c>
-      <c r="AS22" s="10" t="n">
-        <v>0.0045</v>
-      </c>
-      <c r="AT22" s="8" t="n">
-        <v>882136</v>
-      </c>
-      <c r="AU22" s="9" t="n">
-        <v>50572.42</v>
-      </c>
-      <c r="AV22" s="10" t="n">
         <v>0.0056</v>
       </c>
     </row>
@@ -3761,43 +3218,43 @@
         <v>1995914</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>32040.41</v>
+        <v>37762.69</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>0.0025</v>
+        <v>0.0028</v>
       </c>
       <c r="G23" s="8" t="n">
         <v>1995914</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>36543.19</v>
+        <v>38830.51</v>
       </c>
       <c r="I23" s="10" t="n">
-        <v>0.0027</v>
+        <v>0.003</v>
       </c>
       <c r="J23" s="8" t="n">
         <v>1995914</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>35285.76</v>
+        <v>35076.19</v>
       </c>
       <c r="L23" s="10" t="n">
-        <v>0.0026</v>
+        <v>0.0028</v>
       </c>
       <c r="M23" s="8" t="n">
         <v>1995914</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>37762.69</v>
+        <v>34681</v>
       </c>
       <c r="O23" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.0029</v>
       </c>
       <c r="P23" s="8" t="n">
         <v>1995914</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>38830.51</v>
+        <v>35004.34</v>
       </c>
       <c r="R23" s="10" t="n">
         <v>0.003</v>
@@ -3806,90 +3263,63 @@
         <v>1995914</v>
       </c>
       <c r="T23" s="9" t="n">
-        <v>35076.19</v>
+        <v>38225.74</v>
       </c>
       <c r="U23" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.0034</v>
       </c>
       <c r="V23" s="8" t="n">
         <v>1995914</v>
       </c>
       <c r="W23" s="9" t="n">
-        <v>34681</v>
+        <v>43319.32</v>
       </c>
       <c r="X23" s="10" t="n">
-        <v>0.0029</v>
+        <v>0.0039</v>
       </c>
       <c r="Y23" s="8" t="n">
         <v>1995914</v>
       </c>
       <c r="Z23" s="9" t="n">
-        <v>35004.34</v>
+        <v>34806.74</v>
       </c>
       <c r="AA23" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0034</v>
       </c>
       <c r="AB23" s="8" t="n">
         <v>1995914</v>
       </c>
       <c r="AC23" s="9" t="n">
-        <v>38225.74</v>
+        <v>35138.07</v>
       </c>
       <c r="AD23" s="10" t="n">
-        <v>0.0034</v>
+        <v>0.0036</v>
       </c>
       <c r="AE23" s="8" t="n">
         <v>1995914</v>
       </c>
       <c r="AF23" s="9" t="n">
-        <v>43319.32</v>
+        <v>33771.86</v>
       </c>
       <c r="AG23" s="10" t="n">
-        <v>0.0039</v>
+        <v>0.0036</v>
       </c>
       <c r="AH23" s="8" t="n">
         <v>1995914</v>
       </c>
       <c r="AI23" s="9" t="n">
-        <v>34806.74</v>
+        <v>28830.98</v>
       </c>
       <c r="AJ23" s="10" t="n">
-        <v>0.0034</v>
+        <v>0.0033</v>
       </c>
       <c r="AK23" s="8" t="n">
         <v>1995914</v>
       </c>
       <c r="AL23" s="9" t="n">
-        <v>35138.07</v>
+        <v>27686.32</v>
       </c>
       <c r="AM23" s="10" t="n">
-        <v>0.0036</v>
-      </c>
-      <c r="AN23" s="8" t="n">
-        <v>1995914</v>
-      </c>
-      <c r="AO23" s="9" t="n">
-        <v>33771.86</v>
-      </c>
-      <c r="AP23" s="10" t="n">
-        <v>0.0036</v>
-      </c>
-      <c r="AQ23" s="8" t="n">
-        <v>1995914</v>
-      </c>
-      <c r="AR23" s="9" t="n">
-        <v>28830.98</v>
-      </c>
-      <c r="AS23" s="10" t="n">
-        <v>0.0033</v>
-      </c>
-      <c r="AT23" s="8" t="n">
-        <v>1995914</v>
-      </c>
-      <c r="AU23" s="9" t="n">
-        <v>27686.32</v>
-      </c>
-      <c r="AV23" s="10" t="n">
         <v>0.0031</v>
       </c>
     </row>
@@ -3921,85 +3351,76 @@
       <c r="M24" s="8" t="n"/>
       <c r="N24" s="9" t="n"/>
       <c r="O24" s="10" t="n"/>
-      <c r="P24" s="8" t="n"/>
-      <c r="Q24" s="9" t="n"/>
-      <c r="R24" s="10" t="n"/>
-      <c r="S24" s="8" t="n"/>
-      <c r="T24" s="9" t="n"/>
-      <c r="U24" s="10" t="n"/>
-      <c r="V24" s="8" t="n"/>
-      <c r="W24" s="9" t="n"/>
-      <c r="X24" s="10" t="n"/>
+      <c r="P24" s="8" t="n">
+        <v>218075</v>
+      </c>
+      <c r="Q24" s="9" t="n">
+        <v>3019.03</v>
+      </c>
+      <c r="R24" s="10" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="S24" s="8" t="n">
+        <v>566216</v>
+      </c>
+      <c r="T24" s="9" t="n">
+        <v>8345.459999999999</v>
+      </c>
+      <c r="U24" s="10" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v>1311557</v>
+      </c>
+      <c r="W24" s="9" t="n">
+        <v>18228.02</v>
+      </c>
+      <c r="X24" s="10" t="n">
+        <v>0.0017</v>
+      </c>
       <c r="Y24" s="8" t="n">
-        <v>218075</v>
+        <v>1641095</v>
       </c>
       <c r="Z24" s="9" t="n">
-        <v>3019.03</v>
+        <v>23382.32</v>
       </c>
       <c r="AA24" s="10" t="n">
-        <v>0.0003</v>
+        <v>0.0023</v>
       </c>
       <c r="AB24" s="8" t="n">
-        <v>566216</v>
+        <v>1857217</v>
       </c>
       <c r="AC24" s="9" t="n">
-        <v>8345.459999999999</v>
+        <v>26023.32</v>
       </c>
       <c r="AD24" s="10" t="n">
-        <v>0.0007</v>
+        <v>0.0026</v>
       </c>
       <c r="AE24" s="8" t="n">
-        <v>1311557</v>
+        <v>1926988</v>
       </c>
       <c r="AF24" s="9" t="n">
-        <v>18228.02</v>
+        <v>28941.43</v>
       </c>
       <c r="AG24" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.0031</v>
       </c>
       <c r="AH24" s="8" t="n">
-        <v>1641095</v>
+        <v>1926988</v>
       </c>
       <c r="AI24" s="9" t="n">
-        <v>23382.32</v>
+        <v>26117.43</v>
       </c>
       <c r="AJ24" s="10" t="n">
-        <v>0.0023</v>
+        <v>0.003</v>
       </c>
       <c r="AK24" s="8" t="n">
-        <v>1857217</v>
+        <v>2246361</v>
       </c>
       <c r="AL24" s="9" t="n">
-        <v>26023.32</v>
+        <v>32421.73</v>
       </c>
       <c r="AM24" s="10" t="n">
-        <v>0.0026</v>
-      </c>
-      <c r="AN24" s="8" t="n">
-        <v>1926988</v>
-      </c>
-      <c r="AO24" s="9" t="n">
-        <v>28941.43</v>
-      </c>
-      <c r="AP24" s="10" t="n">
-        <v>0.0031</v>
-      </c>
-      <c r="AQ24" s="8" t="n">
-        <v>1926988</v>
-      </c>
-      <c r="AR24" s="9" t="n">
-        <v>26117.43</v>
-      </c>
-      <c r="AS24" s="10" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="AT24" s="8" t="n">
-        <v>2246361</v>
-      </c>
-      <c r="AU24" s="9" t="n">
-        <v>32421.73</v>
-      </c>
-      <c r="AV24" s="10" t="n">
         <v>0.0036</v>
       </c>
     </row>
@@ -4023,43 +3444,43 @@
         <v>2264603</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>25349.97</v>
+        <v>32691.81</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>0.002</v>
+        <v>0.0025</v>
       </c>
       <c r="G25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>28810.28</v>
+        <v>36623.16</v>
       </c>
       <c r="I25" s="10" t="n">
-        <v>0.0021</v>
+        <v>0.0028</v>
       </c>
       <c r="J25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>29897.29</v>
+        <v>35943.78</v>
       </c>
       <c r="L25" s="10" t="n">
-        <v>0.0022</v>
+        <v>0.0029</v>
       </c>
       <c r="M25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>32691.81</v>
+        <v>33031.5</v>
       </c>
       <c r="O25" s="10" t="n">
-        <v>0.0025</v>
+        <v>0.0028</v>
       </c>
       <c r="P25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>36623.16</v>
+        <v>32257.01</v>
       </c>
       <c r="R25" s="10" t="n">
         <v>0.0028</v>
@@ -4068,34 +3489,34 @@
         <v>2264603</v>
       </c>
       <c r="T25" s="9" t="n">
-        <v>35943.78</v>
+        <v>33534.24</v>
       </c>
       <c r="U25" s="10" t="n">
-        <v>0.0029</v>
+        <v>0.003</v>
       </c>
       <c r="V25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="W25" s="9" t="n">
-        <v>33031.5</v>
+        <v>40626.98</v>
       </c>
       <c r="X25" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.0037</v>
       </c>
       <c r="Y25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="Z25" s="9" t="n">
-        <v>32257.01</v>
+        <v>34641.63</v>
       </c>
       <c r="AA25" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.0033</v>
       </c>
       <c r="AB25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="AC25" s="9" t="n">
-        <v>33534.24</v>
+        <v>29892.76</v>
       </c>
       <c r="AD25" s="10" t="n">
         <v>0.003</v>
@@ -4104,54 +3525,27 @@
         <v>2264603</v>
       </c>
       <c r="AF25" s="9" t="n">
-        <v>40626.98</v>
+        <v>27629.29</v>
       </c>
       <c r="AG25" s="10" t="n">
-        <v>0.0037</v>
+        <v>0.003</v>
       </c>
       <c r="AH25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="AI25" s="9" t="n">
-        <v>34641.63</v>
+        <v>25089.54</v>
       </c>
       <c r="AJ25" s="10" t="n">
-        <v>0.0033</v>
+        <v>0.0029</v>
       </c>
       <c r="AK25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="AL25" s="9" t="n">
-        <v>29892.76</v>
+        <v>29659.51</v>
       </c>
       <c r="AM25" s="10" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="AN25" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="AO25" s="9" t="n">
-        <v>27629.29</v>
-      </c>
-      <c r="AP25" s="10" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="AQ25" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="AR25" s="9" t="n">
-        <v>25089.54</v>
-      </c>
-      <c r="AS25" s="10" t="n">
-        <v>0.0029</v>
-      </c>
-      <c r="AT25" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="AU25" s="9" t="n">
-        <v>29659.51</v>
-      </c>
-      <c r="AV25" s="10" t="n">
         <v>0.0033</v>
       </c>
     </row>
@@ -4172,138 +3566,111 @@
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>7394472</v>
+        <v>6180145</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>57344.13</v>
+        <v>63945.96</v>
       </c>
       <c r="F26" s="10" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="G26" s="8" t="n">
+        <v>5842830</v>
+      </c>
+      <c r="H26" s="9" t="n">
+        <v>60233.73</v>
+      </c>
+      <c r="I26" s="10" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="J26" s="8" t="n">
+        <v>5528341</v>
+      </c>
+      <c r="K26" s="9" t="n">
+        <v>59285.93</v>
+      </c>
+      <c r="L26" s="10" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="M26" s="8" t="n">
+        <v>4996218</v>
+      </c>
+      <c r="N26" s="9" t="n">
+        <v>51236.22</v>
+      </c>
+      <c r="O26" s="10" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="P26" s="8" t="n">
+        <v>4433570</v>
+      </c>
+      <c r="Q26" s="9" t="n">
+        <v>49913.13</v>
+      </c>
+      <c r="R26" s="10" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="S26" s="8" t="n">
+        <v>3997165</v>
+      </c>
+      <c r="T26" s="9" t="n">
+        <v>49305.03</v>
+      </c>
+      <c r="U26" s="10" t="n">
         <v>0.0044</v>
       </c>
-      <c r="G26" s="8" t="n">
-        <v>7394472</v>
-      </c>
-      <c r="H26" s="9" t="n">
-        <v>63976.97</v>
-      </c>
-      <c r="I26" s="10" t="n">
-        <v>0.0048</v>
-      </c>
-      <c r="J26" s="8" t="n">
-        <v>7362903</v>
-      </c>
-      <c r="K26" s="9" t="n">
-        <v>67966.96000000001</v>
-      </c>
-      <c r="L26" s="10" t="n">
-        <v>0.0051</v>
-      </c>
-      <c r="M26" s="8" t="n">
-        <v>6180145</v>
-      </c>
-      <c r="N26" s="9" t="n">
-        <v>63945.96</v>
-      </c>
-      <c r="O26" s="10" t="n">
-        <v>0.0048</v>
-      </c>
-      <c r="P26" s="8" t="n">
-        <v>5842830</v>
-      </c>
-      <c r="Q26" s="9" t="n">
-        <v>60233.73</v>
-      </c>
-      <c r="R26" s="10" t="n">
-        <v>0.0046</v>
-      </c>
-      <c r="S26" s="8" t="n">
-        <v>5528341</v>
-      </c>
-      <c r="T26" s="9" t="n">
-        <v>59285.93</v>
-      </c>
-      <c r="U26" s="10" t="n">
-        <v>0.0047</v>
-      </c>
       <c r="V26" s="8" t="n">
-        <v>4996218</v>
+        <v>3516819</v>
       </c>
       <c r="W26" s="9" t="n">
-        <v>51236.22</v>
+        <v>39036.69</v>
       </c>
       <c r="X26" s="10" t="n">
-        <v>0.0043</v>
+        <v>0.0035</v>
       </c>
       <c r="Y26" s="8" t="n">
-        <v>4433570</v>
+        <v>3243008</v>
       </c>
       <c r="Z26" s="9" t="n">
-        <v>49913.13</v>
+        <v>30813.44</v>
       </c>
       <c r="AA26" s="10" t="n">
-        <v>0.0043</v>
+        <v>0.003</v>
       </c>
       <c r="AB26" s="8" t="n">
-        <v>3997165</v>
+        <v>2988209</v>
       </c>
       <c r="AC26" s="9" t="n">
-        <v>49305.03</v>
+        <v>24424.13</v>
       </c>
       <c r="AD26" s="10" t="n">
-        <v>0.0044</v>
+        <v>0.0025</v>
       </c>
       <c r="AE26" s="8" t="n">
-        <v>3516819</v>
+        <v>2843265</v>
       </c>
       <c r="AF26" s="9" t="n">
-        <v>39036.69</v>
+        <v>22336.69</v>
       </c>
       <c r="AG26" s="10" t="n">
-        <v>0.0035</v>
+        <v>0.0024</v>
       </c>
       <c r="AH26" s="8" t="n">
-        <v>3243008</v>
+        <v>2609056</v>
       </c>
       <c r="AI26" s="9" t="n">
-        <v>30813.44</v>
+        <v>17326.74</v>
       </c>
       <c r="AJ26" s="10" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="AK26" s="8" t="n">
-        <v>2988209</v>
+        <v>2259531</v>
       </c>
       <c r="AL26" s="9" t="n">
-        <v>24424.13</v>
+        <v>18525.89</v>
       </c>
       <c r="AM26" s="10" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="AN26" s="8" t="n">
-        <v>2843265</v>
-      </c>
-      <c r="AO26" s="9" t="n">
-        <v>22336.69</v>
-      </c>
-      <c r="AP26" s="10" t="n">
-        <v>0.0024</v>
-      </c>
-      <c r="AQ26" s="8" t="n">
-        <v>2609056</v>
-      </c>
-      <c r="AR26" s="9" t="n">
-        <v>17326.74</v>
-      </c>
-      <c r="AS26" s="10" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="AT26" s="8" t="n">
-        <v>2259531</v>
-      </c>
-      <c r="AU26" s="9" t="n">
-        <v>18525.89</v>
-      </c>
-      <c r="AV26" s="10" t="n">
         <v>0.0021</v>
       </c>
     </row>
@@ -4350,40 +3717,31 @@
       <c r="AB27" s="8" t="n"/>
       <c r="AC27" s="9" t="n"/>
       <c r="AD27" s="10" t="n"/>
-      <c r="AE27" s="8" t="n"/>
-      <c r="AF27" s="9" t="n"/>
-      <c r="AG27" s="10" t="n"/>
-      <c r="AH27" s="8" t="n"/>
-      <c r="AI27" s="9" t="n"/>
-      <c r="AJ27" s="10" t="n"/>
-      <c r="AK27" s="8" t="n"/>
-      <c r="AL27" s="9" t="n"/>
-      <c r="AM27" s="10" t="n"/>
-      <c r="AN27" s="8" t="n">
+      <c r="AE27" s="8" t="n">
         <v>9899412</v>
       </c>
-      <c r="AO27" s="9" t="n">
+      <c r="AF27" s="9" t="n">
         <v>19552.33</v>
       </c>
-      <c r="AP27" s="10" t="n">
+      <c r="AG27" s="10" t="n">
         <v>0.0021</v>
       </c>
-      <c r="AQ27" s="8" t="n">
+      <c r="AH27" s="8" t="n">
         <v>9899412</v>
       </c>
-      <c r="AR27" s="9" t="n">
+      <c r="AI27" s="9" t="n">
         <v>16216.23</v>
       </c>
-      <c r="AS27" s="10" t="n">
+      <c r="AJ27" s="10" t="n">
         <v>0.0018</v>
       </c>
-      <c r="AT27" s="8" t="n">
+      <c r="AK27" s="8" t="n">
         <v>9899412</v>
       </c>
-      <c r="AU27" s="9" t="n">
+      <c r="AL27" s="9" t="n">
         <v>16131.09</v>
       </c>
-      <c r="AV27" s="10" t="n">
+      <c r="AM27" s="10" t="n">
         <v>0.0018</v>
       </c>
     </row>
@@ -4407,135 +3765,108 @@
         <v>287393</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>14378.27</v>
+        <v>17460.56</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>0.0011</v>
+        <v>0.0013</v>
       </c>
       <c r="G28" s="8" t="n">
         <v>287393</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>15895.71</v>
+        <v>17812.62</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>0.0012</v>
+        <v>0.0014</v>
       </c>
       <c r="J28" s="8" t="n">
         <v>287393</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>18124.44</v>
+        <v>18463.56</v>
       </c>
       <c r="L28" s="10" t="n">
-        <v>0.0014</v>
+        <v>0.0015</v>
       </c>
       <c r="M28" s="8" t="n">
         <v>287393</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>17460.56</v>
+        <v>18243.71</v>
       </c>
       <c r="O28" s="10" t="n">
-        <v>0.0013</v>
+        <v>0.0015</v>
       </c>
       <c r="P28" s="8" t="n">
         <v>287393</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>17812.62</v>
+        <v>17962.06</v>
       </c>
       <c r="R28" s="10" t="n">
-        <v>0.0014</v>
+        <v>0.0016</v>
       </c>
       <c r="S28" s="8" t="n">
         <v>287393</v>
       </c>
       <c r="T28" s="9" t="n">
-        <v>18463.56</v>
+        <v>19048.41</v>
       </c>
       <c r="U28" s="10" t="n">
-        <v>0.0015</v>
+        <v>0.0017</v>
       </c>
       <c r="V28" s="8" t="n">
         <v>287393</v>
       </c>
       <c r="W28" s="9" t="n">
-        <v>18243.71</v>
+        <v>19453.63</v>
       </c>
       <c r="X28" s="10" t="n">
-        <v>0.0015</v>
+        <v>0.0018</v>
       </c>
       <c r="Y28" s="8" t="n">
         <v>287393</v>
       </c>
       <c r="Z28" s="9" t="n">
-        <v>17962.06</v>
+        <v>19370.29</v>
       </c>
       <c r="AA28" s="10" t="n">
-        <v>0.0016</v>
+        <v>0.0019</v>
       </c>
       <c r="AB28" s="8" t="n">
         <v>287393</v>
       </c>
       <c r="AC28" s="9" t="n">
-        <v>19048.41</v>
+        <v>15976.18</v>
       </c>
       <c r="AD28" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.0016</v>
       </c>
       <c r="AE28" s="8" t="n">
         <v>287393</v>
       </c>
       <c r="AF28" s="9" t="n">
-        <v>19453.63</v>
+        <v>15821.13</v>
       </c>
       <c r="AG28" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.0017</v>
       </c>
       <c r="AH28" s="8" t="n">
         <v>287393</v>
       </c>
       <c r="AI28" s="9" t="n">
-        <v>19370.29</v>
+        <v>15273.64</v>
       </c>
       <c r="AJ28" s="10" t="n">
-        <v>0.0019</v>
+        <v>0.0017</v>
       </c>
       <c r="AK28" s="8" t="n">
-        <v>287393</v>
+        <v>297835</v>
       </c>
       <c r="AL28" s="9" t="n">
-        <v>15976.18</v>
+        <v>18529.51</v>
       </c>
       <c r="AM28" s="10" t="n">
-        <v>0.0016</v>
-      </c>
-      <c r="AN28" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="AO28" s="9" t="n">
-        <v>15821.13</v>
-      </c>
-      <c r="AP28" s="10" t="n">
-        <v>0.0017</v>
-      </c>
-      <c r="AQ28" s="8" t="n">
-        <v>287393</v>
-      </c>
-      <c r="AR28" s="9" t="n">
-        <v>15273.64</v>
-      </c>
-      <c r="AS28" s="10" t="n">
-        <v>0.0017</v>
-      </c>
-      <c r="AT28" s="8" t="n">
-        <v>297835</v>
-      </c>
-      <c r="AU28" s="9" t="n">
-        <v>18529.51</v>
-      </c>
-      <c r="AV28" s="10" t="n">
         <v>0.0021</v>
       </c>
     </row>
@@ -4556,138 +3887,111 @@
         </is>
       </c>
       <c r="D29" s="8" t="n">
-        <v>80565</v>
+        <v>80159</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>8949.969999999999</v>
+        <v>11401.01</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>0.0007</v>
+        <v>0.0009</v>
       </c>
       <c r="G29" s="8" t="n">
-        <v>80565</v>
+        <v>80159</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>10682.11</v>
+        <v>11787.38</v>
       </c>
       <c r="I29" s="10" t="n">
-        <v>0.0008</v>
+        <v>0.0009</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>80552</v>
+        <v>80159</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>10825.38</v>
+        <v>12110.42</v>
       </c>
       <c r="L29" s="10" t="n">
-        <v>0.0008</v>
+        <v>0.001</v>
       </c>
       <c r="M29" s="8" t="n">
         <v>80159</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>11401.01</v>
+        <v>13825.82</v>
       </c>
       <c r="O29" s="10" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="P29" s="8" t="n">
         <v>80159</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>11787.38</v>
+        <v>12726.04</v>
       </c>
       <c r="R29" s="10" t="n">
-        <v>0.0009</v>
+        <v>0.0011</v>
       </c>
       <c r="S29" s="8" t="n">
         <v>80159</v>
       </c>
       <c r="T29" s="9" t="n">
-        <v>12110.42</v>
+        <v>12868.73</v>
       </c>
       <c r="U29" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0011</v>
       </c>
       <c r="V29" s="8" t="n">
         <v>80159</v>
       </c>
       <c r="W29" s="9" t="n">
-        <v>13825.82</v>
+        <v>11621.45</v>
       </c>
       <c r="X29" s="10" t="n">
-        <v>0.0012</v>
+        <v>0.0011</v>
       </c>
       <c r="Y29" s="8" t="n">
         <v>80159</v>
       </c>
       <c r="Z29" s="9" t="n">
-        <v>12726.04</v>
+        <v>10722.07</v>
       </c>
       <c r="AA29" s="10" t="n">
-        <v>0.0011</v>
+        <v>0.001</v>
       </c>
       <c r="AB29" s="8" t="n">
         <v>80159</v>
       </c>
       <c r="AC29" s="9" t="n">
-        <v>12868.73</v>
+        <v>9198.25</v>
       </c>
       <c r="AD29" s="10" t="n">
-        <v>0.0011</v>
+        <v>0.0009</v>
       </c>
       <c r="AE29" s="8" t="n">
         <v>80159</v>
       </c>
       <c r="AF29" s="9" t="n">
-        <v>11621.45</v>
+        <v>8997.450000000001</v>
       </c>
       <c r="AG29" s="10" t="n">
-        <v>0.0011</v>
+        <v>0.001</v>
       </c>
       <c r="AH29" s="8" t="n">
         <v>80159</v>
       </c>
       <c r="AI29" s="9" t="n">
-        <v>10722.07</v>
+        <v>7401.52</v>
       </c>
       <c r="AJ29" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0008</v>
       </c>
       <c r="AK29" s="8" t="n">
         <v>80159</v>
       </c>
       <c r="AL29" s="9" t="n">
-        <v>9198.25</v>
+        <v>7463.48</v>
       </c>
       <c r="AM29" s="10" t="n">
-        <v>0.0009</v>
-      </c>
-      <c r="AN29" s="8" t="n">
-        <v>80159</v>
-      </c>
-      <c r="AO29" s="9" t="n">
-        <v>8997.450000000001</v>
-      </c>
-      <c r="AP29" s="10" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="AQ29" s="8" t="n">
-        <v>80159</v>
-      </c>
-      <c r="AR29" s="9" t="n">
-        <v>7401.52</v>
-      </c>
-      <c r="AS29" s="10" t="n">
-        <v>0.0008</v>
-      </c>
-      <c r="AT29" s="8" t="n">
-        <v>80159</v>
-      </c>
-      <c r="AU29" s="9" t="n">
-        <v>7463.48</v>
-      </c>
-      <c r="AV29" s="10" t="n">
         <v>0.0008</v>
       </c>
     </row>
@@ -4711,7 +4015,7 @@
         <v>47293</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>1564.88</v>
+        <v>1691.91</v>
       </c>
       <c r="F30" s="10" t="n">
         <v>0.0001</v>
@@ -4720,7 +4024,7 @@
         <v>47293</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>1700.33</v>
+        <v>1764.08</v>
       </c>
       <c r="I30" s="10" t="n">
         <v>0.0001</v>
@@ -4729,34 +4033,34 @@
         <v>47293</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>1637.61</v>
+        <v>1892.15</v>
       </c>
       <c r="L30" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="M30" s="8" t="n">
         <v>47293</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>1691.91</v>
+        <v>1955.38</v>
       </c>
       <c r="O30" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="P30" s="8" t="n">
         <v>47293</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>1764.08</v>
+        <v>1897.21</v>
       </c>
       <c r="R30" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="S30" s="8" t="n">
         <v>47293</v>
       </c>
       <c r="T30" s="9" t="n">
-        <v>1892.15</v>
+        <v>1983.66</v>
       </c>
       <c r="U30" s="10" t="n">
         <v>0.0002</v>
@@ -4765,7 +4069,7 @@
         <v>47293</v>
       </c>
       <c r="W30" s="9" t="n">
-        <v>1955.38</v>
+        <v>1867.41</v>
       </c>
       <c r="X30" s="10" t="n">
         <v>0.0002</v>
@@ -4774,7 +4078,7 @@
         <v>47293</v>
       </c>
       <c r="Z30" s="9" t="n">
-        <v>1897.21</v>
+        <v>1857.76</v>
       </c>
       <c r="AA30" s="10" t="n">
         <v>0.0002</v>
@@ -4783,7 +4087,7 @@
         <v>47293</v>
       </c>
       <c r="AC30" s="9" t="n">
-        <v>1983.66</v>
+        <v>1925.39</v>
       </c>
       <c r="AD30" s="10" t="n">
         <v>0.0002</v>
@@ -4792,7 +4096,7 @@
         <v>47293</v>
       </c>
       <c r="AF30" s="9" t="n">
-        <v>1867.41</v>
+        <v>1844.17</v>
       </c>
       <c r="AG30" s="10" t="n">
         <v>0.0002</v>
@@ -4801,45 +4105,18 @@
         <v>47293</v>
       </c>
       <c r="AI30" s="9" t="n">
-        <v>1857.76</v>
+        <v>1236.83</v>
       </c>
       <c r="AJ30" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="AK30" s="8" t="n">
         <v>47293</v>
       </c>
       <c r="AL30" s="9" t="n">
-        <v>1925.39</v>
+        <v>1612.64</v>
       </c>
       <c r="AM30" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AN30" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="AO30" s="9" t="n">
-        <v>1844.17</v>
-      </c>
-      <c r="AP30" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AQ30" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="AR30" s="9" t="n">
-        <v>1236.83</v>
-      </c>
-      <c r="AS30" s="10" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="AT30" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="AU30" s="9" t="n">
-        <v>1612.64</v>
-      </c>
-      <c r="AV30" s="10" t="n">
         <v>0.0002</v>
       </c>
     </row>
@@ -4863,7 +4140,7 @@
         <v>151687</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>1538.11</v>
+        <v>1858.32</v>
       </c>
       <c r="F31" s="10" t="n">
         <v>0.0001</v>
@@ -4872,34 +4149,34 @@
         <v>151687</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>1704.36</v>
+        <v>1947.66</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="J31" s="8" t="n">
         <v>151687</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>1728.63</v>
+        <v>2076.6</v>
       </c>
       <c r="L31" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="M31" s="8" t="n">
         <v>151687</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>1858.32</v>
+        <v>1987.1</v>
       </c>
       <c r="O31" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="P31" s="8" t="n">
         <v>151687</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>1947.66</v>
+        <v>2130.6</v>
       </c>
       <c r="R31" s="10" t="n">
         <v>0.0002</v>
@@ -4908,7 +4185,7 @@
         <v>151687</v>
       </c>
       <c r="T31" s="9" t="n">
-        <v>2076.6</v>
+        <v>2091.16</v>
       </c>
       <c r="U31" s="10" t="n">
         <v>0.0002</v>
@@ -4917,59 +4194,32 @@
         <v>151687</v>
       </c>
       <c r="W31" s="9" t="n">
-        <v>1987.1</v>
+        <v>1766.62</v>
       </c>
       <c r="X31" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="Y31" s="8" t="n">
-        <v>151687</v>
+        <v>89469</v>
       </c>
       <c r="Z31" s="9" t="n">
-        <v>2130.6</v>
+        <v>828.48</v>
       </c>
       <c r="AA31" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AB31" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AC31" s="9" t="n">
-        <v>2091.16</v>
-      </c>
-      <c r="AD31" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AE31" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AF31" s="9" t="n">
-        <v>1766.62</v>
-      </c>
-      <c r="AG31" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AH31" s="8" t="n">
-        <v>89469</v>
-      </c>
-      <c r="AI31" s="9" t="n">
-        <v>828.48</v>
-      </c>
-      <c r="AJ31" s="10" t="n">
         <v>0.0001</v>
       </c>
+      <c r="AB31" s="8" t="n"/>
+      <c r="AC31" s="9" t="n"/>
+      <c r="AD31" s="10" t="n"/>
+      <c r="AE31" s="8" t="n"/>
+      <c r="AF31" s="9" t="n"/>
+      <c r="AG31" s="10" t="n"/>
+      <c r="AH31" s="8" t="n"/>
+      <c r="AI31" s="9" t="n"/>
+      <c r="AJ31" s="10" t="n"/>
       <c r="AK31" s="8" t="n"/>
       <c r="AL31" s="9" t="n"/>
       <c r="AM31" s="10" t="n"/>
-      <c r="AN31" s="8" t="n"/>
-      <c r="AO31" s="9" t="n"/>
-      <c r="AP31" s="10" t="n"/>
-      <c r="AQ31" s="8" t="n"/>
-      <c r="AR31" s="9" t="n"/>
-      <c r="AS31" s="10" t="n"/>
-      <c r="AT31" s="8" t="n"/>
-      <c r="AU31" s="9" t="n"/>
-      <c r="AV31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -4991,113 +4241,86 @@
         <v>21167034</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>377281.21</v>
+        <v>445693.07</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>0.0293</v>
+        <v>0.0334</v>
       </c>
       <c r="G32" s="8" t="n">
         <v>21167034</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>397792.07</v>
+        <v>444846.39</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>0.0296</v>
+        <v>0.0343</v>
       </c>
       <c r="J32" s="8" t="n">
         <v>21167034</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>416715.398358</v>
+        <v>434876.71</v>
       </c>
       <c r="L32" s="10" t="n">
-        <v>0.0311051731198606</v>
+        <v>0.0346</v>
       </c>
       <c r="M32" s="8" t="n">
         <v>21167034</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>445693.07</v>
+        <v>397601.57</v>
       </c>
       <c r="O32" s="10" t="n">
-        <v>0.0334</v>
+        <v>0.0332</v>
       </c>
       <c r="P32" s="8" t="n">
         <v>21167034</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>444846.39</v>
+        <v>399802.94</v>
       </c>
       <c r="R32" s="10" t="n">
-        <v>0.0343</v>
+        <v>0.0348</v>
       </c>
       <c r="S32" s="8" t="n">
         <v>21167034</v>
       </c>
       <c r="T32" s="9" t="n">
-        <v>434876.71</v>
+        <v>405200.53</v>
       </c>
       <c r="U32" s="10" t="n">
-        <v>0.0346</v>
+        <v>0.0358</v>
       </c>
       <c r="V32" s="8" t="n">
-        <v>21167034</v>
+        <v>20937034</v>
       </c>
       <c r="W32" s="9" t="n">
-        <v>397601.57</v>
+        <v>420750.64</v>
       </c>
       <c r="X32" s="10" t="n">
-        <v>0.0332</v>
+        <v>0.0381</v>
       </c>
       <c r="Y32" s="8" t="n">
-        <v>21167034</v>
+        <v>11799076</v>
       </c>
       <c r="Z32" s="9" t="n">
-        <v>399802.94</v>
+        <v>219014.45</v>
       </c>
       <c r="AA32" s="10" t="n">
-        <v>0.0348</v>
-      </c>
-      <c r="AB32" s="8" t="n">
-        <v>21167034</v>
-      </c>
-      <c r="AC32" s="9" t="n">
-        <v>405200.53</v>
-      </c>
-      <c r="AD32" s="10" t="n">
-        <v>0.0358</v>
-      </c>
-      <c r="AE32" s="8" t="n">
-        <v>20937034</v>
-      </c>
-      <c r="AF32" s="9" t="n">
-        <v>420750.64</v>
-      </c>
-      <c r="AG32" s="10" t="n">
-        <v>0.0381</v>
-      </c>
-      <c r="AH32" s="8" t="n">
-        <v>11799076</v>
-      </c>
-      <c r="AI32" s="9" t="n">
-        <v>219014.45</v>
-      </c>
-      <c r="AJ32" s="10" t="n">
         <v>0.0211</v>
       </c>
+      <c r="AB32" s="8" t="n"/>
+      <c r="AC32" s="9" t="n"/>
+      <c r="AD32" s="10" t="n"/>
+      <c r="AE32" s="8" t="n"/>
+      <c r="AF32" s="9" t="n"/>
+      <c r="AG32" s="10" t="n"/>
+      <c r="AH32" s="8" t="n"/>
+      <c r="AI32" s="9" t="n"/>
+      <c r="AJ32" s="10" t="n"/>
       <c r="AK32" s="8" t="n"/>
       <c r="AL32" s="9" t="n"/>
       <c r="AM32" s="10" t="n"/>
-      <c r="AN32" s="8" t="n"/>
-      <c r="AO32" s="9" t="n"/>
-      <c r="AP32" s="10" t="n"/>
-      <c r="AQ32" s="8" t="n"/>
-      <c r="AR32" s="9" t="n"/>
-      <c r="AS32" s="10" t="n"/>
-      <c r="AT32" s="8" t="n"/>
-      <c r="AU32" s="9" t="n"/>
-      <c r="AV32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -5127,57 +4350,48 @@
       <c r="M33" s="8" t="n"/>
       <c r="N33" s="9" t="n"/>
       <c r="O33" s="10" t="n"/>
-      <c r="P33" s="8" t="n"/>
-      <c r="Q33" s="9" t="n"/>
-      <c r="R33" s="10" t="n"/>
-      <c r="S33" s="8" t="n"/>
-      <c r="T33" s="9" t="n"/>
-      <c r="U33" s="10" t="n"/>
-      <c r="V33" s="8" t="n"/>
-      <c r="W33" s="9" t="n"/>
-      <c r="X33" s="10" t="n"/>
-      <c r="Y33" s="8" t="n">
+      <c r="P33" s="8" t="n">
         <v>4400000</v>
       </c>
-      <c r="Z33" s="9" t="n">
+      <c r="Q33" s="9" t="n">
         <v>88822.8</v>
       </c>
-      <c r="AA33" s="10" t="n">
+      <c r="R33" s="10" t="n">
         <v>0.0077</v>
       </c>
-      <c r="AB33" s="8" t="n">
+      <c r="S33" s="8" t="n">
         <v>4400000</v>
       </c>
-      <c r="AC33" s="9" t="n">
+      <c r="T33" s="9" t="n">
         <v>89280.39999999999</v>
       </c>
-      <c r="AD33" s="10" t="n">
+      <c r="U33" s="10" t="n">
         <v>0.007900000000000001</v>
       </c>
-      <c r="AE33" s="8" t="n">
+      <c r="V33" s="8" t="n">
         <v>4400000</v>
       </c>
-      <c r="AF33" s="9" t="n">
+      <c r="W33" s="9" t="n">
         <v>89020.8</v>
       </c>
-      <c r="AG33" s="10" t="n">
+      <c r="X33" s="10" t="n">
         <v>0.0081</v>
       </c>
+      <c r="Y33" s="8" t="n"/>
+      <c r="Z33" s="9" t="n"/>
+      <c r="AA33" s="10" t="n"/>
+      <c r="AB33" s="8" t="n"/>
+      <c r="AC33" s="9" t="n"/>
+      <c r="AD33" s="10" t="n"/>
+      <c r="AE33" s="8" t="n"/>
+      <c r="AF33" s="9" t="n"/>
+      <c r="AG33" s="10" t="n"/>
       <c r="AH33" s="8" t="n"/>
       <c r="AI33" s="9" t="n"/>
       <c r="AJ33" s="10" t="n"/>
       <c r="AK33" s="8" t="n"/>
       <c r="AL33" s="9" t="n"/>
       <c r="AM33" s="10" t="n"/>
-      <c r="AN33" s="8" t="n"/>
-      <c r="AO33" s="9" t="n"/>
-      <c r="AP33" s="10" t="n"/>
-      <c r="AQ33" s="8" t="n"/>
-      <c r="AR33" s="9" t="n"/>
-      <c r="AS33" s="10" t="n"/>
-      <c r="AT33" s="8" t="n"/>
-      <c r="AU33" s="9" t="n"/>
-      <c r="AV33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -5196,50 +4410,32 @@
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>12412184</v>
+        <v>4654589</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>292791.01</v>
+        <v>149235.43</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>0.0227</v>
+        <v>0.0112</v>
       </c>
       <c r="G34" s="8" t="n">
-        <v>10378056</v>
+        <v>2811139</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>273710.85</v>
+        <v>88199.49000000001</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>0.0204</v>
-      </c>
-      <c r="J34" s="8" t="n">
-        <v>8465650</v>
-      </c>
-      <c r="K34" s="9" t="n">
-        <v>264458.44</v>
-      </c>
-      <c r="L34" s="10" t="n">
-        <v>0.0197</v>
-      </c>
-      <c r="M34" s="8" t="n">
-        <v>4654589</v>
-      </c>
-      <c r="N34" s="9" t="n">
-        <v>149235.43</v>
-      </c>
-      <c r="O34" s="10" t="n">
-        <v>0.0112</v>
-      </c>
-      <c r="P34" s="8" t="n">
-        <v>2811139</v>
-      </c>
-      <c r="Q34" s="9" t="n">
-        <v>88199.49000000001</v>
-      </c>
-      <c r="R34" s="10" t="n">
         <v>0.0068</v>
       </c>
+      <c r="J34" s="8" t="n"/>
+      <c r="K34" s="9" t="n"/>
+      <c r="L34" s="10" t="n"/>
+      <c r="M34" s="8" t="n"/>
+      <c r="N34" s="9" t="n"/>
+      <c r="O34" s="10" t="n"/>
+      <c r="P34" s="8" t="n"/>
+      <c r="Q34" s="9" t="n"/>
+      <c r="R34" s="10" t="n"/>
       <c r="S34" s="8" t="n"/>
       <c r="T34" s="9" t="n"/>
       <c r="U34" s="10" t="n"/>
@@ -5261,15 +4457,6 @@
       <c r="AK34" s="8" t="n"/>
       <c r="AL34" s="9" t="n"/>
       <c r="AM34" s="10" t="n"/>
-      <c r="AN34" s="8" t="n"/>
-      <c r="AO34" s="9" t="n"/>
-      <c r="AP34" s="10" t="n"/>
-      <c r="AQ34" s="8" t="n"/>
-      <c r="AR34" s="9" t="n"/>
-      <c r="AS34" s="10" t="n"/>
-      <c r="AT34" s="8" t="n"/>
-      <c r="AU34" s="9" t="n"/>
-      <c r="AV34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -5288,68 +4475,50 @@
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>22157154</v>
+        <v>22000000</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>94467.03</v>
+        <v>100012</v>
       </c>
       <c r="F35" s="10" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="G35" s="8" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="H35" s="9" t="n">
+        <v>94699</v>
+      </c>
+      <c r="I35" s="10" t="n">
         <v>0.0073</v>
-      </c>
-      <c r="G35" s="8" t="n">
-        <v>22075063</v>
-      </c>
-      <c r="H35" s="9" t="n">
-        <v>84966.92</v>
-      </c>
-      <c r="I35" s="10" t="n">
-        <v>0.0063</v>
       </c>
       <c r="J35" s="8" t="n">
         <v>22000000</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>98626</v>
+        <v>104852</v>
       </c>
       <c r="L35" s="10" t="n">
-        <v>0.0074</v>
+        <v>0.0083</v>
       </c>
       <c r="M35" s="8" t="n">
         <v>22000000</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>100012</v>
+        <v>100584</v>
       </c>
       <c r="O35" s="10" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="P35" s="8" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="Q35" s="9" t="n">
-        <v>94699</v>
-      </c>
-      <c r="R35" s="10" t="n">
-        <v>0.0073</v>
-      </c>
-      <c r="S35" s="8" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="T35" s="9" t="n">
-        <v>104852</v>
-      </c>
-      <c r="U35" s="10" t="n">
-        <v>0.0083</v>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="W35" s="9" t="n">
-        <v>100584</v>
-      </c>
-      <c r="X35" s="10" t="n">
         <v>0.008399999999999999</v>
       </c>
+      <c r="P35" s="8" t="n"/>
+      <c r="Q35" s="9" t="n"/>
+      <c r="R35" s="10" t="n"/>
+      <c r="S35" s="8" t="n"/>
+      <c r="T35" s="9" t="n"/>
+      <c r="U35" s="10" t="n"/>
+      <c r="V35" s="8" t="n"/>
+      <c r="W35" s="9" t="n"/>
+      <c r="X35" s="10" t="n"/>
       <c r="Y35" s="8" t="n"/>
       <c r="Z35" s="9" t="n"/>
       <c r="AA35" s="10" t="n"/>
@@ -5365,15 +4534,6 @@
       <c r="AK35" s="8" t="n"/>
       <c r="AL35" s="9" t="n"/>
       <c r="AM35" s="10" t="n"/>
-      <c r="AN35" s="8" t="n"/>
-      <c r="AO35" s="9" t="n"/>
-      <c r="AP35" s="10" t="n"/>
-      <c r="AQ35" s="8" t="n"/>
-      <c r="AR35" s="9" t="n"/>
-      <c r="AS35" s="10" t="n"/>
-      <c r="AT35" s="8" t="n"/>
-      <c r="AU35" s="9" t="n"/>
-      <c r="AV35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -5392,41 +4552,23 @@
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>2205298</v>
+        <v>1657424</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>31198.35</v>
+        <v>18712.32</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>0.0024</v>
-      </c>
-      <c r="G36" s="8" t="n">
-        <v>2205298</v>
-      </c>
-      <c r="H36" s="9" t="n">
-        <v>29526.73</v>
-      </c>
-      <c r="I36" s="10" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="J36" s="8" t="n">
-        <v>2205298</v>
-      </c>
-      <c r="K36" s="9" t="n">
-        <v>26516.5</v>
-      </c>
-      <c r="L36" s="10" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="M36" s="8" t="n">
-        <v>1657424</v>
-      </c>
-      <c r="N36" s="9" t="n">
-        <v>18712.32</v>
-      </c>
-      <c r="O36" s="10" t="n">
         <v>0.0014</v>
       </c>
+      <c r="G36" s="8" t="n"/>
+      <c r="H36" s="9" t="n"/>
+      <c r="I36" s="10" t="n"/>
+      <c r="J36" s="8" t="n"/>
+      <c r="K36" s="9" t="n"/>
+      <c r="L36" s="10" t="n"/>
+      <c r="M36" s="8" t="n"/>
+      <c r="N36" s="9" t="n"/>
+      <c r="O36" s="10" t="n"/>
       <c r="P36" s="8" t="n"/>
       <c r="Q36" s="9" t="n"/>
       <c r="R36" s="10" t="n"/>
@@ -5451,15 +4593,6 @@
       <c r="AK36" s="8" t="n"/>
       <c r="AL36" s="9" t="n"/>
       <c r="AM36" s="10" t="n"/>
-      <c r="AN36" s="8" t="n"/>
-      <c r="AO36" s="9" t="n"/>
-      <c r="AP36" s="10" t="n"/>
-      <c r="AQ36" s="8" t="n"/>
-      <c r="AR36" s="9" t="n"/>
-      <c r="AS36" s="10" t="n"/>
-      <c r="AT36" s="8" t="n"/>
-      <c r="AU36" s="9" t="n"/>
-      <c r="AV36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -5481,7 +4614,7 @@
         <v>710855</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>2972.44</v>
+        <v>2976.71</v>
       </c>
       <c r="F37" s="10" t="n">
         <v>0.0002</v>
@@ -5490,38 +4623,20 @@
         <v>710855</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>3234.03</v>
+        <v>2850.8839775</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>0.0002</v>
       </c>
-      <c r="J37" s="8" t="n">
-        <v>710855</v>
-      </c>
-      <c r="K37" s="9" t="n">
-        <v>3158.33</v>
-      </c>
-      <c r="L37" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="M37" s="8" t="n">
-        <v>710855</v>
-      </c>
-      <c r="N37" s="9" t="n">
-        <v>2976.71</v>
-      </c>
-      <c r="O37" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="P37" s="8" t="n">
-        <v>710855</v>
-      </c>
-      <c r="Q37" s="9" t="n">
-        <v>2850.8839775</v>
-      </c>
-      <c r="R37" s="10" t="n">
-        <v>0.0002</v>
-      </c>
+      <c r="J37" s="8" t="n"/>
+      <c r="K37" s="9" t="n"/>
+      <c r="L37" s="10" t="n"/>
+      <c r="M37" s="8" t="n"/>
+      <c r="N37" s="9" t="n"/>
+      <c r="O37" s="10" t="n"/>
+      <c r="P37" s="8" t="n"/>
+      <c r="Q37" s="9" t="n"/>
+      <c r="R37" s="10" t="n"/>
       <c r="S37" s="8" t="n"/>
       <c r="T37" s="9" t="n"/>
       <c r="U37" s="10" t="n"/>
@@ -5543,630 +4658,135 @@
       <c r="AK37" s="8" t="n"/>
       <c r="AL37" s="9" t="n"/>
       <c r="AM37" s="10" t="n"/>
-      <c r="AN37" s="8" t="n"/>
-      <c r="AO37" s="9" t="n"/>
-      <c r="AP37" s="10" t="n"/>
-      <c r="AQ37" s="8" t="n"/>
-      <c r="AR37" s="9" t="n"/>
-      <c r="AS37" s="10" t="n"/>
-      <c r="AT37" s="8" t="n"/>
-      <c r="AU37" s="9" t="n"/>
-      <c r="AV37" s="10" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>Kotak Mahindra Bank Limited</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>INE237A01036</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>Banks</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="n">
-        <v>146607960</v>
-      </c>
-      <c r="E38" s="9" t="n">
-        <v>518112.53</v>
-      </c>
-      <c r="F38" s="10" t="n">
-        <v>0.0402</v>
-      </c>
-      <c r="G38" s="8" t="n">
-        <v>123107960</v>
-      </c>
-      <c r="H38" s="9" t="n">
-        <v>511144.25</v>
-      </c>
-      <c r="I38" s="10" t="n">
-        <v>0.0381</v>
-      </c>
-      <c r="J38" s="8" t="n">
-        <v>123107960</v>
-      </c>
-      <c r="K38" s="9" t="n">
-        <v>502280.48</v>
-      </c>
-      <c r="L38" s="10" t="n">
-        <v>0.0375</v>
-      </c>
-      <c r="M38" s="8" t="n"/>
-      <c r="N38" s="9" t="n"/>
-      <c r="O38" s="10" t="n"/>
-      <c r="P38" s="8" t="n"/>
-      <c r="Q38" s="9" t="n"/>
-      <c r="R38" s="10" t="n"/>
-      <c r="S38" s="8" t="n"/>
-      <c r="T38" s="9" t="n"/>
-      <c r="U38" s="10" t="n"/>
-      <c r="V38" s="8" t="n"/>
-      <c r="W38" s="9" t="n"/>
-      <c r="X38" s="10" t="n"/>
-      <c r="Y38" s="8" t="n"/>
-      <c r="Z38" s="9" t="n"/>
-      <c r="AA38" s="10" t="n"/>
-      <c r="AB38" s="8" t="n"/>
-      <c r="AC38" s="9" t="n"/>
-      <c r="AD38" s="10" t="n"/>
-      <c r="AE38" s="8" t="n"/>
-      <c r="AF38" s="9" t="n"/>
-      <c r="AG38" s="10" t="n"/>
-      <c r="AH38" s="8" t="n"/>
-      <c r="AI38" s="9" t="n"/>
-      <c r="AJ38" s="10" t="n"/>
-      <c r="AK38" s="8" t="n"/>
-      <c r="AL38" s="9" t="n"/>
-      <c r="AM38" s="10" t="n"/>
-      <c r="AN38" s="8" t="n"/>
-      <c r="AO38" s="9" t="n"/>
-      <c r="AP38" s="10" t="n"/>
-      <c r="AQ38" s="8" t="n"/>
-      <c r="AR38" s="9" t="n"/>
-      <c r="AS38" s="10" t="n"/>
-      <c r="AT38" s="8" t="n"/>
-      <c r="AU38" s="9" t="n"/>
-      <c r="AV38" s="10" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>CMS Info System Limited</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>INE925R01014</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>Commercial Services &amp; Supplies</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="n">
-        <v>6957544</v>
-      </c>
-      <c r="E39" s="9" t="n">
-        <v>18479.24</v>
-      </c>
-      <c r="F39" s="10" t="n">
-        <v>0.0014</v>
-      </c>
-      <c r="G39" s="8" t="n">
-        <v>5086596</v>
-      </c>
-      <c r="H39" s="9" t="n">
-        <v>15442.91</v>
-      </c>
-      <c r="I39" s="10" t="n">
-        <v>0.0012</v>
-      </c>
-      <c r="J39" s="8" t="n">
-        <v>199758</v>
-      </c>
-      <c r="K39" s="9" t="n">
-        <v>629.9400000000001</v>
-      </c>
-      <c r="L39" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="8" t="n"/>
-      <c r="N39" s="9" t="n"/>
-      <c r="O39" s="10" t="n"/>
-      <c r="P39" s="8" t="n"/>
-      <c r="Q39" s="9" t="n"/>
-      <c r="R39" s="10" t="n"/>
-      <c r="S39" s="8" t="n"/>
-      <c r="T39" s="9" t="n"/>
-      <c r="U39" s="10" t="n"/>
-      <c r="V39" s="8" t="n"/>
-      <c r="W39" s="9" t="n"/>
-      <c r="X39" s="10" t="n"/>
-      <c r="Y39" s="8" t="n"/>
-      <c r="Z39" s="9" t="n"/>
-      <c r="AA39" s="10" t="n"/>
-      <c r="AB39" s="8" t="n"/>
-      <c r="AC39" s="9" t="n"/>
-      <c r="AD39" s="10" t="n"/>
-      <c r="AE39" s="8" t="n"/>
-      <c r="AF39" s="9" t="n"/>
-      <c r="AG39" s="10" t="n"/>
-      <c r="AH39" s="8" t="n"/>
-      <c r="AI39" s="9" t="n"/>
-      <c r="AJ39" s="10" t="n"/>
-      <c r="AK39" s="8" t="n"/>
-      <c r="AL39" s="9" t="n"/>
-      <c r="AM39" s="10" t="n"/>
-      <c r="AN39" s="8" t="n"/>
-      <c r="AO39" s="9" t="n"/>
-      <c r="AP39" s="10" t="n"/>
-      <c r="AQ39" s="8" t="n"/>
-      <c r="AR39" s="9" t="n"/>
-      <c r="AS39" s="10" t="n"/>
-      <c r="AT39" s="8" t="n"/>
-      <c r="AU39" s="9" t="n"/>
-      <c r="AV39" s="10" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>CIE Automotive India Limited</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>INE536H01010</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>Auto Components</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="n">
-        <v>464063</v>
-      </c>
-      <c r="E40" s="9" t="n">
-        <v>2065.08</v>
-      </c>
-      <c r="F40" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="G40" s="8" t="n">
-        <v>464063</v>
-      </c>
-      <c r="H40" s="9" t="n">
-        <v>2188.75</v>
-      </c>
-      <c r="I40" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="J40" s="8" t="n">
-        <v>462075</v>
-      </c>
-      <c r="K40" s="9" t="n">
-        <v>1932.4</v>
-      </c>
-      <c r="L40" s="10" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="M40" s="8" t="n"/>
-      <c r="N40" s="9" t="n"/>
-      <c r="O40" s="10" t="n"/>
-      <c r="P40" s="8" t="n"/>
-      <c r="Q40" s="9" t="n"/>
-      <c r="R40" s="10" t="n"/>
-      <c r="S40" s="8" t="n"/>
-      <c r="T40" s="9" t="n"/>
-      <c r="U40" s="10" t="n"/>
-      <c r="V40" s="8" t="n"/>
-      <c r="W40" s="9" t="n"/>
-      <c r="X40" s="10" t="n"/>
-      <c r="Y40" s="8" t="n"/>
-      <c r="Z40" s="9" t="n"/>
-      <c r="AA40" s="10" t="n"/>
-      <c r="AB40" s="8" t="n"/>
-      <c r="AC40" s="9" t="n"/>
-      <c r="AD40" s="10" t="n"/>
-      <c r="AE40" s="8" t="n"/>
-      <c r="AF40" s="9" t="n"/>
-      <c r="AG40" s="10" t="n"/>
-      <c r="AH40" s="8" t="n"/>
-      <c r="AI40" s="9" t="n"/>
-      <c r="AJ40" s="10" t="n"/>
-      <c r="AK40" s="8" t="n"/>
-      <c r="AL40" s="9" t="n"/>
-      <c r="AM40" s="10" t="n"/>
-      <c r="AN40" s="8" t="n"/>
-      <c r="AO40" s="9" t="n"/>
-      <c r="AP40" s="10" t="n"/>
-      <c r="AQ40" s="8" t="n"/>
-      <c r="AR40" s="9" t="n"/>
-      <c r="AS40" s="10" t="n"/>
-      <c r="AT40" s="8" t="n"/>
-      <c r="AU40" s="9" t="n"/>
-      <c r="AV40" s="10" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>Indraprastha Gas Limited</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>INE203G01027</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>Gas</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="n">
-        <v>481152</v>
-      </c>
-      <c r="E41" s="9" t="n">
-        <v>700.65</v>
-      </c>
-      <c r="F41" s="10" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="G41" s="8" t="n">
-        <v>286134</v>
-      </c>
-      <c r="H41" s="9" t="n">
-        <v>488.89</v>
-      </c>
-      <c r="I41" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="8" t="n"/>
-      <c r="K41" s="9" t="n"/>
-      <c r="L41" s="10" t="n"/>
-      <c r="M41" s="8" t="n"/>
-      <c r="N41" s="9" t="n"/>
-      <c r="O41" s="10" t="n"/>
-      <c r="P41" s="8" t="n"/>
-      <c r="Q41" s="9" t="n"/>
-      <c r="R41" s="10" t="n"/>
-      <c r="S41" s="8" t="n"/>
-      <c r="T41" s="9" t="n"/>
-      <c r="U41" s="10" t="n"/>
-      <c r="V41" s="8" t="n"/>
-      <c r="W41" s="9" t="n"/>
-      <c r="X41" s="10" t="n"/>
-      <c r="Y41" s="8" t="n"/>
-      <c r="Z41" s="9" t="n"/>
-      <c r="AA41" s="10" t="n"/>
-      <c r="AB41" s="8" t="n"/>
-      <c r="AC41" s="9" t="n"/>
-      <c r="AD41" s="10" t="n"/>
-      <c r="AE41" s="8" t="n"/>
-      <c r="AF41" s="9" t="n"/>
-      <c r="AG41" s="10" t="n"/>
-      <c r="AH41" s="8" t="n"/>
-      <c r="AI41" s="9" t="n"/>
-      <c r="AJ41" s="10" t="n"/>
-      <c r="AK41" s="8" t="n"/>
-      <c r="AL41" s="9" t="n"/>
-      <c r="AM41" s="10" t="n"/>
-      <c r="AN41" s="8" t="n"/>
-      <c r="AO41" s="9" t="n"/>
-      <c r="AP41" s="10" t="n"/>
-      <c r="AQ41" s="8" t="n"/>
-      <c r="AR41" s="9" t="n"/>
-      <c r="AS41" s="10" t="n"/>
-      <c r="AT41" s="8" t="n"/>
-      <c r="AU41" s="9" t="n"/>
-      <c r="AV41" s="10" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>Mahanagar Gas Limited</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>INE002S01010</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>Gas</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="n">
-        <v>53045</v>
-      </c>
-      <c r="E42" s="9" t="n">
-        <v>492.1</v>
-      </c>
-      <c r="F42" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="8" t="n">
-        <v>3045</v>
-      </c>
-      <c r="H42" s="9" t="n">
-        <v>37.14</v>
-      </c>
-      <c r="I42" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="8" t="n"/>
-      <c r="K42" s="9" t="n"/>
-      <c r="L42" s="10" t="n"/>
-      <c r="M42" s="8" t="n"/>
-      <c r="N42" s="9" t="n"/>
-      <c r="O42" s="10" t="n"/>
-      <c r="P42" s="8" t="n"/>
-      <c r="Q42" s="9" t="n"/>
-      <c r="R42" s="10" t="n"/>
-      <c r="S42" s="8" t="n"/>
-      <c r="T42" s="9" t="n"/>
-      <c r="U42" s="10" t="n"/>
-      <c r="V42" s="8" t="n"/>
-      <c r="W42" s="9" t="n"/>
-      <c r="X42" s="10" t="n"/>
-      <c r="Y42" s="8" t="n"/>
-      <c r="Z42" s="9" t="n"/>
-      <c r="AA42" s="10" t="n"/>
-      <c r="AB42" s="8" t="n"/>
-      <c r="AC42" s="9" t="n"/>
-      <c r="AD42" s="10" t="n"/>
-      <c r="AE42" s="8" t="n"/>
-      <c r="AF42" s="9" t="n"/>
-      <c r="AG42" s="10" t="n"/>
-      <c r="AH42" s="8" t="n"/>
-      <c r="AI42" s="9" t="n"/>
-      <c r="AJ42" s="10" t="n"/>
-      <c r="AK42" s="8" t="n"/>
-      <c r="AL42" s="9" t="n"/>
-      <c r="AM42" s="10" t="n"/>
-      <c r="AN42" s="8" t="n"/>
-      <c r="AO42" s="9" t="n"/>
-      <c r="AP42" s="10" t="n"/>
-      <c r="AQ42" s="8" t="n"/>
-      <c r="AR42" s="9" t="n"/>
-      <c r="AS42" s="10" t="n"/>
-      <c r="AT42" s="8" t="n"/>
-      <c r="AU42" s="9" t="n"/>
-      <c r="AV42" s="10" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>Multi Commodity Exchange of India Limited</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>INE745G01043</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>Capital Markets</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="n"/>
-      <c r="E43" s="9" t="n"/>
-      <c r="F43" s="10" t="n"/>
-      <c r="G43" s="8" t="n"/>
-      <c r="H43" s="9" t="n"/>
-      <c r="I43" s="10" t="n"/>
-      <c r="J43" s="8" t="n">
-        <v>795472</v>
-      </c>
-      <c r="K43" s="9" t="n">
-        <v>20109.53</v>
-      </c>
-      <c r="L43" s="10" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="M43" s="8" t="n"/>
-      <c r="N43" s="9" t="n"/>
-      <c r="O43" s="10" t="n"/>
-      <c r="P43" s="8" t="n"/>
-      <c r="Q43" s="9" t="n"/>
-      <c r="R43" s="10" t="n"/>
-      <c r="S43" s="8" t="n"/>
-      <c r="T43" s="9" t="n"/>
-      <c r="U43" s="10" t="n"/>
-      <c r="V43" s="8" t="n"/>
-      <c r="W43" s="9" t="n"/>
-      <c r="X43" s="10" t="n"/>
-      <c r="Y43" s="8" t="n"/>
-      <c r="Z43" s="9" t="n"/>
-      <c r="AA43" s="10" t="n"/>
-      <c r="AB43" s="8" t="n"/>
-      <c r="AC43" s="9" t="n"/>
-      <c r="AD43" s="10" t="n"/>
-      <c r="AE43" s="8" t="n"/>
-      <c r="AF43" s="9" t="n"/>
-      <c r="AG43" s="10" t="n"/>
-      <c r="AH43" s="8" t="n"/>
-      <c r="AI43" s="9" t="n"/>
-      <c r="AJ43" s="10" t="n"/>
-      <c r="AK43" s="8" t="n"/>
-      <c r="AL43" s="9" t="n"/>
-      <c r="AM43" s="10" t="n"/>
-      <c r="AN43" s="8" t="n"/>
-      <c r="AO43" s="9" t="n"/>
-      <c r="AP43" s="10" t="n"/>
-      <c r="AQ43" s="8" t="n"/>
-      <c r="AR43" s="9" t="n"/>
-      <c r="AS43" s="10" t="n"/>
-      <c r="AT43" s="8" t="n"/>
-      <c r="AU43" s="9" t="n"/>
-      <c r="AV43" s="10" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="11" t="inlineStr">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B44" s="11" t="n"/>
-      <c r="C44" s="12" t="n"/>
-      <c r="D44" s="13" t="n">
-        <v>1373201700</v>
-      </c>
-      <c r="E44" s="14" t="n">
-        <v>8608487.039999999</v>
-      </c>
-      <c r="F44" s="15" t="n">
-        <v>0.6674999999999998</v>
-      </c>
-      <c r="G44" s="13" t="n">
-        <v>1285817925</v>
-      </c>
-      <c r="H44" s="14" t="n">
-        <v>8857498.140000001</v>
-      </c>
-      <c r="I44" s="15" t="n">
-        <v>0.6597999999999999</v>
-      </c>
-      <c r="J44" s="13" t="n">
-        <v>1265994824</v>
-      </c>
-      <c r="K44" s="14" t="n">
-        <v>8789059.288358001</v>
-      </c>
-      <c r="L44" s="15" t="n">
-        <v>0.6559051731198605</v>
-      </c>
-      <c r="M44" s="13" t="n">
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="12" t="n"/>
+      <c r="D38" s="13" t="n">
         <v>1079845116</v>
       </c>
-      <c r="N44" s="14" t="n">
+      <c r="E38" s="14" t="n">
         <v>8588270.840000002</v>
       </c>
-      <c r="O44" s="15" t="n">
+      <c r="F38" s="15" t="n">
         <v>0.6443999999999998</v>
       </c>
-      <c r="P44" s="13" t="n">
+      <c r="G38" s="13" t="n">
         <v>1039629309</v>
       </c>
-      <c r="Q44" s="14" t="n">
+      <c r="H38" s="14" t="n">
         <v>8271351.1939775</v>
       </c>
-      <c r="R44" s="15" t="n">
+      <c r="I38" s="15" t="n">
         <v>0.6374000000000001</v>
       </c>
-      <c r="S44" s="13" t="n">
+      <c r="J38" s="13" t="n">
         <v>991416407</v>
       </c>
-      <c r="T44" s="14" t="n">
+      <c r="K38" s="14" t="n">
         <v>7865128.239999999</v>
       </c>
-      <c r="U44" s="15" t="n">
+      <c r="L38" s="15" t="n">
         <v>0.6254999999999999</v>
       </c>
-      <c r="V44" s="13" t="n">
+      <c r="M38" s="13" t="n">
         <v>979359723</v>
       </c>
-      <c r="W44" s="14" t="n">
+      <c r="N38" s="14" t="n">
         <v>7559180.72</v>
       </c>
-      <c r="X44" s="15" t="n">
+      <c r="O38" s="15" t="n">
         <v>0.6313999999999997</v>
       </c>
-      <c r="Y44" s="13" t="n">
+      <c r="P38" s="13" t="n">
         <v>927478800</v>
       </c>
-      <c r="Z44" s="14" t="n">
+      <c r="Q38" s="14" t="n">
         <v>7320811.49</v>
       </c>
-      <c r="AA44" s="15" t="n">
+      <c r="R38" s="15" t="n">
         <v>0.6364000000000001</v>
       </c>
-      <c r="AB44" s="13" t="n">
+      <c r="S38" s="13" t="n">
         <v>819556049</v>
       </c>
-      <c r="AC44" s="14" t="n">
+      <c r="T38" s="14" t="n">
         <v>7290583.900000003</v>
       </c>
-      <c r="AD44" s="15" t="n">
+      <c r="U38" s="15" t="n">
         <v>0.6436999999999999</v>
       </c>
-      <c r="AE44" s="13" t="n">
+      <c r="V38" s="13" t="n">
         <v>799425942</v>
       </c>
-      <c r="AF44" s="14" t="n">
+      <c r="W38" s="14" t="n">
         <v>7347454.07</v>
       </c>
-      <c r="AG44" s="15" t="n">
+      <c r="X38" s="15" t="n">
         <v>0.6657999999999998</v>
       </c>
-      <c r="AH44" s="13" t="n">
+      <c r="Y38" s="13" t="n">
         <v>756845974</v>
       </c>
-      <c r="AI44" s="14" t="n">
+      <c r="Z38" s="14" t="n">
         <v>6714757.130000002</v>
       </c>
-      <c r="AJ44" s="15" t="n">
+      <c r="AA38" s="15" t="n">
         <v>0.6467999999999997</v>
       </c>
-      <c r="AK44" s="13" t="n">
+      <c r="AB38" s="13" t="n">
         <v>719050337</v>
       </c>
-      <c r="AL44" s="14" t="n">
+      <c r="AC38" s="14" t="n">
         <v>6275568.75</v>
       </c>
-      <c r="AM44" s="15" t="n">
+      <c r="AD38" s="15" t="n">
         <v>0.6370000000000001</v>
       </c>
-      <c r="AN44" s="13" t="n">
+      <c r="AE38" s="13" t="n">
         <v>717176528</v>
       </c>
-      <c r="AO44" s="14" t="n">
+      <c r="AF38" s="14" t="n">
         <v>6051937.58</v>
       </c>
-      <c r="AP44" s="15" t="n">
+      <c r="AG38" s="15" t="n">
         <v>0.6476999999999997</v>
       </c>
-      <c r="AQ44" s="13" t="n">
+      <c r="AH38" s="13" t="n">
         <v>718063829</v>
       </c>
-      <c r="AR44" s="14" t="n">
+      <c r="AI38" s="14" t="n">
         <v>5662977.749999999</v>
       </c>
-      <c r="AS44" s="15" t="n">
+      <c r="AJ38" s="15" t="n">
         <v>0.6436999999999998</v>
       </c>
-      <c r="AT44" s="13" t="n">
+      <c r="AK38" s="13" t="n">
         <v>697292654</v>
       </c>
-      <c r="AU44" s="14" t="n">
+      <c r="AL38" s="14" t="n">
         <v>5868142.6</v>
       </c>
-      <c r="AV44" s="15" t="n">
+      <c r="AM38" s="15" t="n">
         <v>0.6543000000000002</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="13">
     <mergeCell ref="D2:F2"/>
-    <mergeCell ref="AT2:AV2"/>
     <mergeCell ref="G2:I2"/>
+    <mergeCell ref="A1:AM1"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="Y2:AA2"/>
     <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="AE2:AG2"/>
     <mergeCell ref="AK2:AM2"/>
     <mergeCell ref="P2:R2"/>
-    <mergeCell ref="AN2:AP2"/>
-    <mergeCell ref="A1:AV1"/>
-    <mergeCell ref="AQ2:AS2"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="S2:U2"/>
     <mergeCell ref="AH2:AJ2"/>

--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -484,13 +484,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM38"/>
+  <dimension ref="A1:AV44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
@@ -498,17 +498,17 @@
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
     <col width="26" customWidth="1" min="14" max="14"/>
     <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
     <col width="26" customWidth="1" min="17" max="17"/>
     <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
     <col width="26" customWidth="1" min="20" max="20"/>
-    <col width="20" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="20" customWidth="1" min="24" max="24"/>
     <col width="13" customWidth="1" min="25" max="25"/>
@@ -520,12 +520,21 @@
     <col width="13" customWidth="1" min="31" max="31"/>
     <col width="26" customWidth="1" min="32" max="32"/>
     <col width="20" customWidth="1" min="33" max="33"/>
-    <col width="15" customWidth="1" min="34" max="34"/>
+    <col width="13" customWidth="1" min="34" max="34"/>
     <col width="26" customWidth="1" min="35" max="35"/>
     <col width="20" customWidth="1" min="36" max="36"/>
-    <col width="14" customWidth="1" min="37" max="37"/>
+    <col width="13" customWidth="1" min="37" max="37"/>
     <col width="26" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
+    <col width="13" customWidth="1" min="40" max="40"/>
+    <col width="26" customWidth="1" min="41" max="41"/>
+    <col width="20" customWidth="1" min="42" max="42"/>
+    <col width="15" customWidth="1" min="43" max="43"/>
+    <col width="26" customWidth="1" min="44" max="44"/>
+    <col width="20" customWidth="1" min="45" max="45"/>
+    <col width="14" customWidth="1" min="46" max="46"/>
+    <col width="26" customWidth="1" min="47" max="47"/>
+    <col width="20" customWidth="1" min="48" max="48"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -572,6 +581,15 @@
       <c r="AK1" s="1" t="n"/>
       <c r="AL1" s="1" t="n"/>
       <c r="AM1" s="1" t="n"/>
+      <c r="AN1" s="1" t="n"/>
+      <c r="AO1" s="1" t="n"/>
+      <c r="AP1" s="1" t="n"/>
+      <c r="AQ1" s="1" t="n"/>
+      <c r="AR1" s="1" t="n"/>
+      <c r="AS1" s="1" t="n"/>
+      <c r="AT1" s="1" t="n"/>
+      <c r="AU1" s="1" t="n"/>
+      <c r="AV1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -591,88 +609,109 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>December_2025</t>
+          <t>March_2026</t>
         </is>
       </c>
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="3" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>November_2025</t>
+          <t>February_2026</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="3" t="n"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>October_2025</t>
+          <t>January_2026</t>
         </is>
       </c>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="3" t="n"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>September_2025</t>
+          <t>December_2025</t>
         </is>
       </c>
       <c r="N2" s="2" t="n"/>
       <c r="O2" s="3" t="n"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>August_2025</t>
+          <t>November_2025</t>
         </is>
       </c>
       <c r="Q2" s="2" t="n"/>
       <c r="R2" s="3" t="n"/>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>July_2025</t>
+          <t>October_2025</t>
         </is>
       </c>
       <c r="T2" s="2" t="n"/>
       <c r="U2" s="3" t="n"/>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>June_2025</t>
+          <t>September_2025</t>
         </is>
       </c>
       <c r="W2" s="2" t="n"/>
       <c r="X2" s="3" t="n"/>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>May_2025</t>
+          <t>August_2025</t>
         </is>
       </c>
       <c r="Z2" s="2" t="n"/>
       <c r="AA2" s="3" t="n"/>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>April_2025</t>
+          <t>July_2025</t>
         </is>
       </c>
       <c r="AC2" s="2" t="n"/>
       <c r="AD2" s="3" t="n"/>
       <c r="AE2" s="2" t="inlineStr">
         <is>
-          <t>March_2025</t>
+          <t>June_2025</t>
         </is>
       </c>
       <c r="AF2" s="2" t="n"/>
       <c r="AG2" s="3" t="n"/>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>February_2025</t>
+          <t>May_2025</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n"/>
       <c r="AJ2" s="3" t="n"/>
       <c r="AK2" s="2" t="inlineStr">
         <is>
-          <t>January_2025</t>
+          <t>April_2025</t>
         </is>
       </c>
       <c r="AL2" s="2" t="n"/>
       <c r="AM2" s="3" t="n"/>
+      <c r="AN2" s="2" t="inlineStr">
+        <is>
+          <t>March_2025</t>
+        </is>
+      </c>
+      <c r="AO2" s="2" t="n"/>
+      <c r="AP2" s="3" t="n"/>
+      <c r="AQ2" s="2" t="inlineStr">
+        <is>
+          <t>February_2025</t>
+        </is>
+      </c>
+      <c r="AR2" s="2" t="n"/>
+      <c r="AS2" s="3" t="n"/>
+      <c r="AT2" s="2" t="inlineStr">
+        <is>
+          <t>January_2025</t>
+        </is>
+      </c>
+      <c r="AU2" s="2" t="n"/>
+      <c r="AV2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n"/>
@@ -858,6 +897,51 @@
           <t>% Net Assets</t>
         </is>
       </c>
+      <c r="AN3" s="4" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="AO3" s="4" t="inlineStr">
+        <is>
+          <t>Market Value (Rs. Lakhs)</t>
+        </is>
+      </c>
+      <c r="AP3" s="5" t="inlineStr">
+        <is>
+          <t>% Net Assets</t>
+        </is>
+      </c>
+      <c r="AQ3" s="4" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="AR3" s="4" t="inlineStr">
+        <is>
+          <t>Market Value (Rs. Lakhs)</t>
+        </is>
+      </c>
+      <c r="AS3" s="5" t="inlineStr">
+        <is>
+          <t>% Net Assets</t>
+        </is>
+      </c>
+      <c r="AT3" s="4" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="AU3" s="4" t="inlineStr">
+        <is>
+          <t>Market Value (Rs. Lakhs)</t>
+        </is>
+      </c>
+      <c r="AV3" s="5" t="inlineStr">
+        <is>
+          <t>% Net Assets</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -876,111 +960,138 @@
         </is>
       </c>
       <c r="D4" s="8" t="n">
+        <v>140247203</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>1025978.41</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>0.0796</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>116915576</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>1037918.03</v>
+      </c>
+      <c r="I4" s="10" t="n">
+        <v>0.07729999999999999</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>115915576</v>
+      </c>
+      <c r="K4" s="9" t="n">
+        <v>1077145.49</v>
+      </c>
+      <c r="L4" s="10" t="n">
+        <v>0.0804</v>
+      </c>
+      <c r="M4" s="8" t="n">
         <v>108738215</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="N4" s="9" t="n">
         <v>1077813.19</v>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="O4" s="10" t="n">
         <v>0.0809</v>
       </c>
-      <c r="G4" s="8" t="n">
+      <c r="P4" s="8" t="n">
         <v>103486016</v>
       </c>
-      <c r="H4" s="9" t="n">
+      <c r="Q4" s="9" t="n">
         <v>1042725.1</v>
       </c>
-      <c r="I4" s="10" t="n">
+      <c r="R4" s="10" t="n">
         <v>0.0803</v>
       </c>
-      <c r="J4" s="8" t="n">
+      <c r="S4" s="8" t="n">
         <v>102203321</v>
       </c>
-      <c r="K4" s="9" t="n">
+      <c r="T4" s="9" t="n">
         <v>1009053.39</v>
       </c>
-      <c r="L4" s="10" t="n">
+      <c r="U4" s="10" t="n">
         <v>0.08019999999999999</v>
       </c>
-      <c r="M4" s="8" t="n">
+      <c r="V4" s="8" t="n">
         <v>101668321</v>
       </c>
-      <c r="N4" s="9" t="n">
+      <c r="W4" s="9" t="n">
         <v>966865.73</v>
       </c>
-      <c r="O4" s="10" t="n">
+      <c r="X4" s="10" t="n">
         <v>0.0808</v>
       </c>
-      <c r="P4" s="8" t="n">
+      <c r="Y4" s="8" t="n">
         <v>95825482</v>
       </c>
-      <c r="Q4" s="9" t="n">
+      <c r="Z4" s="9" t="n">
         <v>911875.29</v>
       </c>
-      <c r="R4" s="10" t="n">
+      <c r="AA4" s="10" t="n">
         <v>0.0793</v>
       </c>
-      <c r="S4" s="8" t="n">
+      <c r="AB4" s="8" t="n">
         <v>44870461</v>
       </c>
-      <c r="T4" s="9" t="n">
+      <c r="AC4" s="9" t="n">
         <v>905575.64</v>
       </c>
-      <c r="U4" s="10" t="n">
+      <c r="AD4" s="10" t="n">
         <v>0.0799</v>
       </c>
-      <c r="V4" s="8" t="n">
+      <c r="AE4" s="8" t="n">
         <v>44461271</v>
       </c>
-      <c r="W4" s="9" t="n">
+      <c r="AF4" s="9" t="n">
         <v>889892.34</v>
       </c>
-      <c r="X4" s="10" t="n">
+      <c r="AG4" s="10" t="n">
         <v>0.0806</v>
       </c>
-      <c r="Y4" s="8" t="n">
+      <c r="AH4" s="8" t="n">
         <v>43293069</v>
       </c>
-      <c r="Z4" s="9" t="n">
+      <c r="AI4" s="9" t="n">
         <v>842006.9</v>
       </c>
-      <c r="AA4" s="10" t="n">
+      <c r="AJ4" s="10" t="n">
         <v>0.08110000000000001</v>
-      </c>
-      <c r="AB4" s="8" t="n">
-        <v>42813069</v>
-      </c>
-      <c r="AC4" s="9" t="n">
-        <v>824151.58</v>
-      </c>
-      <c r="AD4" s="10" t="n">
-        <v>0.08359999999999999</v>
-      </c>
-      <c r="AE4" s="8" t="n">
-        <v>42813069</v>
-      </c>
-      <c r="AF4" s="9" t="n">
-        <v>782708.53</v>
-      </c>
-      <c r="AG4" s="10" t="n">
-        <v>0.0838</v>
-      </c>
-      <c r="AH4" s="8" t="n">
-        <v>42813069</v>
-      </c>
-      <c r="AI4" s="9" t="n">
-        <v>741693.61</v>
-      </c>
-      <c r="AJ4" s="10" t="n">
-        <v>0.0843</v>
       </c>
       <c r="AK4" s="8" t="n">
         <v>42813069</v>
       </c>
       <c r="AL4" s="9" t="n">
+        <v>824151.58</v>
+      </c>
+      <c r="AM4" s="10" t="n">
+        <v>0.08359999999999999</v>
+      </c>
+      <c r="AN4" s="8" t="n">
+        <v>42813069</v>
+      </c>
+      <c r="AO4" s="9" t="n">
+        <v>782708.53</v>
+      </c>
+      <c r="AP4" s="10" t="n">
+        <v>0.0838</v>
+      </c>
+      <c r="AQ4" s="8" t="n">
+        <v>42813069</v>
+      </c>
+      <c r="AR4" s="9" t="n">
+        <v>741693.61</v>
+      </c>
+      <c r="AS4" s="10" t="n">
+        <v>0.0843</v>
+      </c>
+      <c r="AT4" s="8" t="n">
+        <v>42813069</v>
+      </c>
+      <c r="AU4" s="9" t="n">
         <v>727287.01</v>
       </c>
-      <c r="AM4" s="10" t="n">
+      <c r="AV4" s="10" t="n">
         <v>0.08110000000000001</v>
       </c>
     </row>
@@ -1001,111 +1112,138 @@
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>5318918</v>
+        <v>6026828</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>602527.03</v>
+        <v>527106.38</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.0452</v>
+        <v>0.0409</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>5318918</v>
+        <v>6026828</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>611622.38</v>
+        <v>651138.5</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>0.0471</v>
+        <v>0.0485</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>5318918</v>
+        <v>5979253</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>654386.48</v>
+        <v>645759.3199999999</v>
       </c>
       <c r="L5" s="10" t="n">
-        <v>0.052</v>
+        <v>0.0482</v>
       </c>
       <c r="M5" s="8" t="n">
         <v>5318918</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>651407.89</v>
+        <v>602527.03</v>
       </c>
       <c r="O5" s="10" t="n">
-        <v>0.0544</v>
+        <v>0.0452</v>
       </c>
       <c r="P5" s="8" t="n">
         <v>5318918</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>679225.83</v>
+        <v>611622.38</v>
       </c>
       <c r="R5" s="10" t="n">
-        <v>0.059</v>
+        <v>0.0471</v>
       </c>
       <c r="S5" s="8" t="n">
         <v>5318918</v>
       </c>
       <c r="T5" s="9" t="n">
-        <v>742680.52</v>
+        <v>654386.48</v>
       </c>
       <c r="U5" s="10" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.052</v>
       </c>
       <c r="V5" s="8" t="n">
         <v>5318918</v>
       </c>
       <c r="W5" s="9" t="n">
-        <v>764807.22</v>
+        <v>651407.89</v>
       </c>
       <c r="X5" s="10" t="n">
-        <v>0.0693</v>
+        <v>0.0544</v>
       </c>
       <c r="Y5" s="8" t="n">
         <v>5318918</v>
       </c>
       <c r="Z5" s="9" t="n">
-        <v>713479.66</v>
+        <v>679225.83</v>
       </c>
       <c r="AA5" s="10" t="n">
-        <v>0.0687</v>
+        <v>0.059</v>
       </c>
       <c r="AB5" s="8" t="n">
         <v>5318918</v>
       </c>
       <c r="AC5" s="9" t="n">
-        <v>636834.05</v>
+        <v>742680.52</v>
       </c>
       <c r="AD5" s="10" t="n">
-        <v>0.0646</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="AE5" s="8" t="n">
         <v>5318918</v>
       </c>
       <c r="AF5" s="9" t="n">
-        <v>663431.3</v>
+        <v>764807.22</v>
       </c>
       <c r="AG5" s="10" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.0693</v>
       </c>
       <c r="AH5" s="8" t="n">
         <v>5318918</v>
       </c>
       <c r="AI5" s="9" t="n">
-        <v>615630.1899999999</v>
+        <v>713479.66</v>
       </c>
       <c r="AJ5" s="10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0687</v>
       </c>
       <c r="AK5" s="8" t="n">
         <v>5318918</v>
       </c>
       <c r="AL5" s="9" t="n">
+        <v>636834.05</v>
+      </c>
+      <c r="AM5" s="10" t="n">
+        <v>0.0646</v>
+      </c>
+      <c r="AN5" s="8" t="n">
+        <v>5318918</v>
+      </c>
+      <c r="AO5" s="9" t="n">
+        <v>663431.3</v>
+      </c>
+      <c r="AP5" s="10" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="AQ5" s="8" t="n">
+        <v>5318918</v>
+      </c>
+      <c r="AR5" s="9" t="n">
+        <v>615630.1899999999</v>
+      </c>
+      <c r="AS5" s="10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AT5" s="8" t="n">
+        <v>5318918</v>
+      </c>
+      <c r="AU5" s="9" t="n">
         <v>614850.96</v>
       </c>
-      <c r="AM5" s="10" t="n">
+      <c r="AV5" s="10" t="n">
         <v>0.06850000000000001</v>
       </c>
     </row>
@@ -1126,111 +1264,138 @@
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>162039558</v>
+        <v>174817417</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>646537.84</v>
+        <v>787465.05</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.0485</v>
+        <v>0.0611</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>162039558</v>
+        <v>161423761</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>609511.8</v>
+        <v>695171.4300000001</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>0.047</v>
+        <v>0.0518</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>162039558</v>
+        <v>159832308</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>629766.74</v>
+        <v>704460.9</v>
       </c>
       <c r="L6" s="10" t="n">
-        <v>0.0501</v>
+        <v>0.0526</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>162039558</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>631873.26</v>
+        <v>646537.84</v>
       </c>
       <c r="O6" s="10" t="n">
-        <v>0.0528</v>
+        <v>0.0485</v>
       </c>
       <c r="P6" s="8" t="n">
         <v>162039558</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>607324.26</v>
+        <v>609511.8</v>
       </c>
       <c r="R6" s="10" t="n">
-        <v>0.0528</v>
+        <v>0.047</v>
       </c>
       <c r="S6" s="8" t="n">
         <v>162039558</v>
       </c>
       <c r="T6" s="9" t="n">
-        <v>609835.88</v>
+        <v>629766.74</v>
       </c>
       <c r="U6" s="10" t="n">
-        <v>0.0538</v>
+        <v>0.0501</v>
       </c>
       <c r="V6" s="8" t="n">
         <v>162039558</v>
       </c>
       <c r="W6" s="9" t="n">
+        <v>631873.26</v>
+      </c>
+      <c r="X6" s="10" t="n">
+        <v>0.0528</v>
+      </c>
+      <c r="Y6" s="8" t="n">
+        <v>162039558</v>
+      </c>
+      <c r="Z6" s="9" t="n">
+        <v>607324.26</v>
+      </c>
+      <c r="AA6" s="10" t="n">
+        <v>0.0528</v>
+      </c>
+      <c r="AB6" s="8" t="n">
+        <v>162039558</v>
+      </c>
+      <c r="AC6" s="9" t="n">
+        <v>609835.88</v>
+      </c>
+      <c r="AD6" s="10" t="n">
+        <v>0.0538</v>
+      </c>
+      <c r="AE6" s="8" t="n">
+        <v>162039558</v>
+      </c>
+      <c r="AF6" s="9" t="n">
         <v>635114.05</v>
       </c>
-      <c r="X6" s="10" t="n">
+      <c r="AG6" s="10" t="n">
         <v>0.0575</v>
       </c>
-      <c r="Y6" s="8" t="n">
+      <c r="AH6" s="8" t="n">
         <v>155681572</v>
       </c>
-      <c r="Z6" s="9" t="n">
+      <c r="AI6" s="9" t="n">
         <v>618522.89</v>
       </c>
-      <c r="AA6" s="10" t="n">
+      <c r="AJ6" s="10" t="n">
         <v>0.0595</v>
       </c>
-      <c r="AB6" s="8" t="n">
+      <c r="AK6" s="8" t="n">
         <v>148323775</v>
       </c>
-      <c r="AC6" s="9" t="n">
+      <c r="AL6" s="9" t="n">
         <v>571491.51</v>
       </c>
-      <c r="AD6" s="10" t="n">
+      <c r="AM6" s="10" t="n">
         <v>0.058</v>
       </c>
-      <c r="AE6" s="8" t="n">
+      <c r="AN6" s="8" t="n">
         <v>141074007</v>
       </c>
-      <c r="AF6" s="9" t="n">
+      <c r="AO6" s="9" t="n">
         <v>561756.7</v>
       </c>
-      <c r="AG6" s="10" t="n">
+      <c r="AP6" s="10" t="n">
         <v>0.0601</v>
       </c>
-      <c r="AH6" s="8" t="n">
+      <c r="AQ6" s="8" t="n">
         <v>142636407</v>
       </c>
-      <c r="AI6" s="9" t="n">
+      <c r="AR6" s="9" t="n">
         <v>526827.5699999999</v>
       </c>
-      <c r="AJ6" s="10" t="n">
+      <c r="AS6" s="10" t="n">
         <v>0.0599</v>
       </c>
-      <c r="AK6" s="8" t="n">
+      <c r="AT6" s="8" t="n">
         <v>139335199</v>
       </c>
-      <c r="AL6" s="9" t="n">
+      <c r="AU6" s="9" t="n">
         <v>551628.05</v>
       </c>
-      <c r="AM6" s="10" t="n">
+      <c r="AV6" s="10" t="n">
         <v>0.0615</v>
       </c>
     </row>
@@ -1251,111 +1416,138 @@
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>305419267</v>
+        <v>312063864</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>808139.38</v>
+        <v>924021.1</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.0606</v>
+        <v>0.0716</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>284154236</v>
+        <v>311113864</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>767074.36</v>
+        <v>929141.55</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>0.0591</v>
+        <v>0.0692</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>261786637</v>
+        <v>313365617</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>754338.1899999999</v>
+        <v>803782.8100000001</v>
       </c>
       <c r="L7" s="10" t="n">
         <v>0.06</v>
       </c>
       <c r="M7" s="8" t="n">
+        <v>305419267</v>
+      </c>
+      <c r="N7" s="9" t="n">
+        <v>808139.38</v>
+      </c>
+      <c r="O7" s="10" t="n">
+        <v>0.0606</v>
+      </c>
+      <c r="P7" s="8" t="n">
+        <v>284154236</v>
+      </c>
+      <c r="Q7" s="9" t="n">
+        <v>767074.36</v>
+      </c>
+      <c r="R7" s="10" t="n">
+        <v>0.0591</v>
+      </c>
+      <c r="S7" s="8" t="n">
+        <v>261786637</v>
+      </c>
+      <c r="T7" s="9" t="n">
+        <v>754338.1899999999</v>
+      </c>
+      <c r="U7" s="10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="V7" s="8" t="n">
         <v>255922726</v>
       </c>
-      <c r="N7" s="9" t="n">
+      <c r="W7" s="9" t="n">
         <v>717223.4399999999</v>
       </c>
-      <c r="O7" s="10" t="n">
+      <c r="X7" s="10" t="n">
         <v>0.0599</v>
       </c>
-      <c r="P7" s="8" t="n">
+      <c r="Y7" s="8" t="n">
         <v>246049993</v>
       </c>
-      <c r="Q7" s="9" t="n">
+      <c r="Z7" s="9" t="n">
         <v>677252.61</v>
       </c>
-      <c r="R7" s="10" t="n">
+      <c r="AA7" s="10" t="n">
         <v>0.0589</v>
       </c>
-      <c r="S7" s="8" t="n">
+      <c r="AB7" s="8" t="n">
         <v>230787510</v>
       </c>
-      <c r="T7" s="9" t="n">
+      <c r="AC7" s="9" t="n">
         <v>671591.65</v>
       </c>
-      <c r="U7" s="10" t="n">
+      <c r="AD7" s="10" t="n">
         <v>0.0593</v>
       </c>
-      <c r="V7" s="8" t="n">
+      <c r="AE7" s="8" t="n">
         <v>224216515</v>
       </c>
-      <c r="W7" s="9" t="n">
+      <c r="AF7" s="9" t="n">
         <v>672425.33</v>
       </c>
-      <c r="X7" s="10" t="n">
+      <c r="AG7" s="10" t="n">
         <v>0.0609</v>
       </c>
-      <c r="Y7" s="8" t="n">
+      <c r="AH7" s="8" t="n">
         <v>208867542</v>
       </c>
-      <c r="Z7" s="9" t="n">
+      <c r="AI7" s="9" t="n">
         <v>605193.7</v>
       </c>
-      <c r="AA7" s="10" t="n">
+      <c r="AJ7" s="10" t="n">
         <v>0.0583</v>
       </c>
-      <c r="AB7" s="8" t="n">
+      <c r="AK7" s="8" t="n">
         <v>193616648</v>
       </c>
-      <c r="AC7" s="9" t="n">
+      <c r="AL7" s="9" t="n">
         <v>595274.38</v>
       </c>
-      <c r="AD7" s="10" t="n">
+      <c r="AM7" s="10" t="n">
         <v>0.0604</v>
       </c>
-      <c r="AE7" s="8" t="n">
+      <c r="AN7" s="8" t="n">
         <v>192765312</v>
       </c>
-      <c r="AF7" s="9" t="n">
+      <c r="AO7" s="9" t="n">
         <v>559694.08</v>
       </c>
-      <c r="AG7" s="10" t="n">
+      <c r="AP7" s="10" t="n">
         <v>0.0599</v>
       </c>
-      <c r="AH7" s="8" t="n">
+      <c r="AQ7" s="8" t="n">
         <v>193498810</v>
       </c>
-      <c r="AI7" s="9" t="n">
+      <c r="AR7" s="9" t="n">
         <v>485391.76</v>
       </c>
-      <c r="AJ7" s="10" t="n">
+      <c r="AS7" s="10" t="n">
         <v>0.0552</v>
       </c>
-      <c r="AK7" s="8" t="n">
+      <c r="AT7" s="8" t="n">
         <v>185577147</v>
       </c>
-      <c r="AL7" s="9" t="n">
+      <c r="AU7" s="9" t="n">
         <v>559793.46</v>
       </c>
-      <c r="AM7" s="10" t="n">
+      <c r="AV7" s="10" t="n">
         <v>0.0624</v>
       </c>
     </row>
@@ -1376,111 +1568,138 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
+        <v>53846183</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>649331.12</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="G8" s="8" t="n">
         <v>49325234</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="H8" s="9" t="n">
+        <v>680145.65</v>
+      </c>
+      <c r="I8" s="10" t="n">
+        <v>0.0507</v>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>49325234</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>668356.92</v>
+      </c>
+      <c r="L8" s="10" t="n">
+        <v>0.0499</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>49325234</v>
+      </c>
+      <c r="N8" s="9" t="n">
         <v>662388.5699999999</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="O8" s="10" t="n">
         <v>0.0497</v>
       </c>
-      <c r="G8" s="8" t="n">
+      <c r="P8" s="8" t="n">
         <v>45308598</v>
       </c>
-      <c r="H8" s="9" t="n">
+      <c r="Q8" s="9" t="n">
         <v>629245.8100000001</v>
       </c>
-      <c r="I8" s="10" t="n">
+      <c r="R8" s="10" t="n">
         <v>0.0485</v>
       </c>
-      <c r="J8" s="8" t="n">
+      <c r="S8" s="8" t="n">
         <v>43295573</v>
       </c>
-      <c r="K8" s="9" t="n">
+      <c r="T8" s="9" t="n">
         <v>582455.34</v>
       </c>
-      <c r="L8" s="10" t="n">
+      <c r="U8" s="10" t="n">
         <v>0.0463</v>
       </c>
-      <c r="M8" s="8" t="n">
+      <c r="V8" s="8" t="n">
         <v>42215573</v>
       </c>
-      <c r="N8" s="9" t="n">
+      <c r="W8" s="9" t="n">
         <v>569065.92</v>
       </c>
-      <c r="O8" s="10" t="n">
+      <c r="X8" s="10" t="n">
         <v>0.0475</v>
       </c>
-      <c r="P8" s="8" t="n">
+      <c r="Y8" s="8" t="n">
         <v>40720543</v>
       </c>
-      <c r="Q8" s="9" t="n">
+      <c r="Z8" s="9" t="n">
         <v>569191.75</v>
       </c>
-      <c r="R8" s="10" t="n">
+      <c r="AA8" s="10" t="n">
         <v>0.0495</v>
       </c>
-      <c r="S8" s="8" t="n">
+      <c r="AB8" s="8" t="n">
         <v>39605543</v>
       </c>
-      <c r="T8" s="9" t="n">
+      <c r="AC8" s="9" t="n">
         <v>586716.51</v>
       </c>
-      <c r="U8" s="10" t="n">
+      <c r="AD8" s="10" t="n">
         <v>0.0518</v>
       </c>
-      <c r="V8" s="8" t="n">
+      <c r="AE8" s="8" t="n">
         <v>36489310</v>
       </c>
-      <c r="W8" s="9" t="n">
+      <c r="AF8" s="9" t="n">
         <v>527562.4399999999</v>
       </c>
-      <c r="X8" s="10" t="n">
+      <c r="AG8" s="10" t="n">
         <v>0.0478</v>
-      </c>
-      <c r="Y8" s="8" t="n">
-        <v>34986740</v>
-      </c>
-      <c r="Z8" s="9" t="n">
-        <v>505838.29</v>
-      </c>
-      <c r="AA8" s="10" t="n">
-        <v>0.0487</v>
-      </c>
-      <c r="AB8" s="8" t="n">
-        <v>34986740</v>
-      </c>
-      <c r="AC8" s="9" t="n">
-        <v>499260.78</v>
-      </c>
-      <c r="AD8" s="10" t="n">
-        <v>0.0507</v>
-      </c>
-      <c r="AE8" s="8" t="n">
-        <v>34986740</v>
-      </c>
-      <c r="AF8" s="9" t="n">
-        <v>471743.71</v>
-      </c>
-      <c r="AG8" s="10" t="n">
-        <v>0.0505</v>
       </c>
       <c r="AH8" s="8" t="n">
         <v>34986740</v>
       </c>
       <c r="AI8" s="9" t="n">
-        <v>421275.34</v>
+        <v>505838.29</v>
       </c>
       <c r="AJ8" s="10" t="n">
-        <v>0.0479</v>
+        <v>0.0487</v>
       </c>
       <c r="AK8" s="8" t="n">
         <v>34986740</v>
       </c>
       <c r="AL8" s="9" t="n">
+        <v>499260.78</v>
+      </c>
+      <c r="AM8" s="10" t="n">
+        <v>0.0507</v>
+      </c>
+      <c r="AN8" s="8" t="n">
+        <v>34986740</v>
+      </c>
+      <c r="AO8" s="9" t="n">
+        <v>471743.71</v>
+      </c>
+      <c r="AP8" s="10" t="n">
+        <v>0.0505</v>
+      </c>
+      <c r="AQ8" s="8" t="n">
+        <v>34986740</v>
+      </c>
+      <c r="AR8" s="9" t="n">
+        <v>421275.34</v>
+      </c>
+      <c r="AS8" s="10" t="n">
+        <v>0.0479</v>
+      </c>
+      <c r="AT8" s="8" t="n">
+        <v>34986740</v>
+      </c>
+      <c r="AU8" s="9" t="n">
         <v>438313.88</v>
       </c>
-      <c r="AM8" s="10" t="n">
+      <c r="AV8" s="10" t="n">
         <v>0.0489</v>
       </c>
     </row>
@@ -1500,112 +1719,121 @@
           <t>Banks</t>
         </is>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="8" t="n"/>
+      <c r="H9" s="9" t="n"/>
+      <c r="I9" s="10" t="n"/>
+      <c r="J9" s="8" t="n"/>
+      <c r="K9" s="9" t="n"/>
+      <c r="L9" s="10" t="n"/>
+      <c r="M9" s="8" t="n">
         <v>24621592</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="N9" s="9" t="n">
         <v>541945.86</v>
       </c>
-      <c r="F9" s="10" t="n">
+      <c r="O9" s="10" t="n">
         <v>0.0407</v>
       </c>
-      <c r="G9" s="8" t="n">
+      <c r="P9" s="8" t="n">
         <v>24306544</v>
       </c>
-      <c r="H9" s="9" t="n">
+      <c r="Q9" s="9" t="n">
         <v>516368.22</v>
       </c>
-      <c r="I9" s="10" t="n">
+      <c r="R9" s="10" t="n">
         <v>0.0398</v>
       </c>
-      <c r="J9" s="8" t="n">
+      <c r="S9" s="8" t="n">
         <v>24205055</v>
       </c>
-      <c r="K9" s="9" t="n">
+      <c r="T9" s="9" t="n">
         <v>508838.67</v>
       </c>
-      <c r="L9" s="10" t="n">
+      <c r="U9" s="10" t="n">
         <v>0.0404</v>
       </c>
-      <c r="M9" s="8" t="n">
+      <c r="V9" s="8" t="n">
         <v>24205055</v>
       </c>
-      <c r="N9" s="9" t="n">
+      <c r="W9" s="9" t="n">
         <v>482334.13</v>
       </c>
-      <c r="O9" s="10" t="n">
+      <c r="X9" s="10" t="n">
         <v>0.0403</v>
       </c>
-      <c r="P9" s="8" t="n">
+      <c r="Y9" s="8" t="n">
         <v>23407381</v>
       </c>
-      <c r="Q9" s="9" t="n">
+      <c r="Z9" s="9" t="n">
         <v>458854.89</v>
       </c>
-      <c r="R9" s="10" t="n">
+      <c r="AA9" s="10" t="n">
         <v>0.0399</v>
       </c>
-      <c r="S9" s="8" t="n">
+      <c r="AB9" s="8" t="n">
         <v>21994066</v>
       </c>
-      <c r="T9" s="9" t="n">
+      <c r="AC9" s="9" t="n">
         <v>435174.59</v>
       </c>
-      <c r="U9" s="10" t="n">
+      <c r="AD9" s="10" t="n">
         <v>0.0384</v>
       </c>
-      <c r="V9" s="8" t="n">
+      <c r="AE9" s="8" t="n">
         <v>20473232</v>
       </c>
-      <c r="W9" s="9" t="n">
+      <c r="AF9" s="9" t="n">
         <v>442938.37</v>
       </c>
-      <c r="X9" s="10" t="n">
+      <c r="AG9" s="10" t="n">
         <v>0.0401</v>
-      </c>
-      <c r="Y9" s="8" t="n">
-        <v>19753232</v>
-      </c>
-      <c r="Z9" s="9" t="n">
-        <v>409820.3</v>
-      </c>
-      <c r="AA9" s="10" t="n">
-        <v>0.0395</v>
-      </c>
-      <c r="AB9" s="8" t="n">
-        <v>19753232</v>
-      </c>
-      <c r="AC9" s="9" t="n">
-        <v>436171.12</v>
-      </c>
-      <c r="AD9" s="10" t="n">
-        <v>0.0443</v>
-      </c>
-      <c r="AE9" s="8" t="n">
-        <v>19753232</v>
-      </c>
-      <c r="AF9" s="9" t="n">
-        <v>428882.17</v>
-      </c>
-      <c r="AG9" s="10" t="n">
-        <v>0.0459</v>
       </c>
       <c r="AH9" s="8" t="n">
         <v>19753232</v>
       </c>
       <c r="AI9" s="9" t="n">
-        <v>375894.13</v>
+        <v>409820.3</v>
       </c>
       <c r="AJ9" s="10" t="n">
-        <v>0.0427</v>
+        <v>0.0395</v>
       </c>
       <c r="AK9" s="8" t="n">
         <v>19753232</v>
       </c>
       <c r="AL9" s="9" t="n">
+        <v>436171.12</v>
+      </c>
+      <c r="AM9" s="10" t="n">
+        <v>0.0443</v>
+      </c>
+      <c r="AN9" s="8" t="n">
+        <v>19753232</v>
+      </c>
+      <c r="AO9" s="9" t="n">
+        <v>428882.17</v>
+      </c>
+      <c r="AP9" s="10" t="n">
+        <v>0.0459</v>
+      </c>
+      <c r="AQ9" s="8" t="n">
+        <v>19753232</v>
+      </c>
+      <c r="AR9" s="9" t="n">
+        <v>375894.13</v>
+      </c>
+      <c r="AS9" s="10" t="n">
+        <v>0.0427</v>
+      </c>
+      <c r="AT9" s="8" t="n">
+        <v>19753232</v>
+      </c>
+      <c r="AU9" s="9" t="n">
         <v>375568.2</v>
       </c>
-      <c r="AM9" s="10" t="n">
+      <c r="AV9" s="10" t="n">
         <v>0.0419</v>
       </c>
     </row>
@@ -1626,111 +1854,138 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
+        <v>224093958</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>644718.3199999999</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>215593958</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>676102.65</v>
+      </c>
+      <c r="I10" s="10" t="n">
+        <v>0.0504</v>
+      </c>
+      <c r="J10" s="8" t="n">
+        <v>209900994</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>676196.05</v>
+      </c>
+      <c r="L10" s="10" t="n">
+        <v>0.0505</v>
+      </c>
+      <c r="M10" s="8" t="n">
         <v>148665711</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="N10" s="9" t="n">
         <v>599122.8199999999</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="O10" s="10" t="n">
         <v>0.0449</v>
       </c>
-      <c r="G10" s="8" t="n">
+      <c r="P10" s="8" t="n">
         <v>144737169</v>
       </c>
-      <c r="H10" s="9" t="n">
+      <c r="Q10" s="9" t="n">
         <v>585100.01</v>
       </c>
-      <c r="I10" s="10" t="n">
+      <c r="R10" s="10" t="n">
         <v>0.0451</v>
       </c>
-      <c r="J10" s="8" t="n">
+      <c r="S10" s="8" t="n">
         <v>138771024</v>
       </c>
-      <c r="K10" s="9" t="n">
+      <c r="T10" s="9" t="n">
         <v>583324</v>
       </c>
-      <c r="L10" s="10" t="n">
+      <c r="U10" s="10" t="n">
         <v>0.0464</v>
       </c>
-      <c r="M10" s="8" t="n">
+      <c r="V10" s="8" t="n">
         <v>135721024</v>
       </c>
-      <c r="N10" s="9" t="n">
+      <c r="W10" s="9" t="n">
         <v>544987.77</v>
       </c>
-      <c r="O10" s="10" t="n">
+      <c r="X10" s="10" t="n">
         <v>0.0455</v>
       </c>
-      <c r="P10" s="8" t="n">
+      <c r="Y10" s="8" t="n">
         <v>129421024</v>
       </c>
-      <c r="Q10" s="9" t="n">
+      <c r="Z10" s="9" t="n">
         <v>530302.65</v>
       </c>
-      <c r="R10" s="10" t="n">
+      <c r="AA10" s="10" t="n">
         <v>0.0461</v>
       </c>
-      <c r="S10" s="8" t="n">
+      <c r="AB10" s="8" t="n">
         <v>122172359</v>
       </c>
-      <c r="T10" s="9" t="n">
+      <c r="AC10" s="9" t="n">
         <v>503289.03</v>
       </c>
-      <c r="U10" s="10" t="n">
+      <c r="AD10" s="10" t="n">
         <v>0.0444</v>
       </c>
-      <c r="V10" s="8" t="n">
+      <c r="AE10" s="8" t="n">
         <v>117422359</v>
       </c>
-      <c r="W10" s="9" t="n">
+      <c r="AF10" s="9" t="n">
         <v>489005.41</v>
       </c>
-      <c r="X10" s="10" t="n">
+      <c r="AG10" s="10" t="n">
         <v>0.0443</v>
       </c>
-      <c r="Y10" s="8" t="n">
+      <c r="AH10" s="8" t="n">
         <v>109270669</v>
       </c>
-      <c r="Z10" s="9" t="n">
+      <c r="AI10" s="9" t="n">
         <v>456806.03</v>
       </c>
-      <c r="AA10" s="10" t="n">
+      <c r="AJ10" s="10" t="n">
         <v>0.044</v>
       </c>
-      <c r="AB10" s="8" t="n">
+      <c r="AK10" s="8" t="n">
         <v>105271096</v>
       </c>
-      <c r="AC10" s="9" t="n">
+      <c r="AL10" s="9" t="n">
         <v>448244.33</v>
       </c>
-      <c r="AD10" s="10" t="n">
+      <c r="AM10" s="10" t="n">
         <v>0.0455</v>
       </c>
-      <c r="AE10" s="8" t="n">
+      <c r="AN10" s="8" t="n">
         <v>101194120</v>
       </c>
-      <c r="AF10" s="9" t="n">
+      <c r="AO10" s="9" t="n">
         <v>414642.91</v>
       </c>
-      <c r="AG10" s="10" t="n">
+      <c r="AP10" s="10" t="n">
         <v>0.0444</v>
       </c>
-      <c r="AH10" s="8" t="n">
+      <c r="AQ10" s="8" t="n">
         <v>101194120</v>
       </c>
-      <c r="AI10" s="9" t="n">
+      <c r="AR10" s="9" t="n">
         <v>399716.77</v>
       </c>
-      <c r="AJ10" s="10" t="n">
+      <c r="AS10" s="10" t="n">
         <v>0.0454</v>
       </c>
-      <c r="AK10" s="8" t="n">
+      <c r="AT10" s="8" t="n">
         <v>98994120</v>
       </c>
-      <c r="AL10" s="9" t="n">
+      <c r="AU10" s="9" t="n">
         <v>442998.69</v>
       </c>
-      <c r="AM10" s="10" t="n">
+      <c r="AV10" s="10" t="n">
         <v>0.0494</v>
       </c>
     </row>
@@ -1751,111 +2006,138 @@
         </is>
       </c>
       <c r="D11" s="8" t="n">
+        <v>3039945</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>374095.63</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>2861040</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>425064.71</v>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>0.0317</v>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>2780478</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>405921.98</v>
+      </c>
+      <c r="L11" s="10" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="M11" s="8" t="n">
         <v>2746670</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="N11" s="9" t="n">
         <v>458611.49</v>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="O11" s="10" t="n">
         <v>0.0344</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>2746670</v>
-      </c>
-      <c r="H11" s="9" t="n">
-        <v>436720.53</v>
-      </c>
-      <c r="I11" s="10" t="n">
-        <v>0.0337</v>
-      </c>
-      <c r="J11" s="8" t="n">
-        <v>2696670</v>
-      </c>
-      <c r="K11" s="9" t="n">
-        <v>436483.01</v>
-      </c>
-      <c r="L11" s="10" t="n">
-        <v>0.0347</v>
-      </c>
-      <c r="M11" s="8" t="n">
-        <v>2696670</v>
-      </c>
-      <c r="N11" s="9" t="n">
-        <v>432249.23</v>
-      </c>
-      <c r="O11" s="10" t="n">
-        <v>0.0361</v>
       </c>
       <c r="P11" s="8" t="n">
         <v>2746670</v>
       </c>
       <c r="Q11" s="9" t="n">
+        <v>436720.53</v>
+      </c>
+      <c r="R11" s="10" t="n">
+        <v>0.0337</v>
+      </c>
+      <c r="S11" s="8" t="n">
+        <v>2696670</v>
+      </c>
+      <c r="T11" s="9" t="n">
+        <v>436483.01</v>
+      </c>
+      <c r="U11" s="10" t="n">
+        <v>0.0347</v>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v>2696670</v>
+      </c>
+      <c r="W11" s="9" t="n">
+        <v>432249.23</v>
+      </c>
+      <c r="X11" s="10" t="n">
+        <v>0.0361</v>
+      </c>
+      <c r="Y11" s="8" t="n">
+        <v>2746670</v>
+      </c>
+      <c r="Z11" s="9" t="n">
         <v>406259.96</v>
       </c>
-      <c r="R11" s="10" t="n">
+      <c r="AA11" s="10" t="n">
         <v>0.0353</v>
-      </c>
-      <c r="S11" s="8" t="n">
-        <v>3021670</v>
-      </c>
-      <c r="T11" s="9" t="n">
-        <v>380972.15</v>
-      </c>
-      <c r="U11" s="10" t="n">
-        <v>0.0336</v>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v>3021670</v>
-      </c>
-      <c r="W11" s="9" t="n">
-        <v>374687.08</v>
-      </c>
-      <c r="X11" s="10" t="n">
-        <v>0.0339</v>
-      </c>
-      <c r="Y11" s="8" t="n">
-        <v>3021670</v>
-      </c>
-      <c r="Z11" s="9" t="n">
-        <v>372239.53</v>
-      </c>
-      <c r="AA11" s="10" t="n">
-        <v>0.0358</v>
       </c>
       <c r="AB11" s="8" t="n">
         <v>3021670</v>
       </c>
       <c r="AC11" s="9" t="n">
+        <v>380972.15</v>
+      </c>
+      <c r="AD11" s="10" t="n">
+        <v>0.0336</v>
+      </c>
+      <c r="AE11" s="8" t="n">
+        <v>3021670</v>
+      </c>
+      <c r="AF11" s="9" t="n">
+        <v>374687.08</v>
+      </c>
+      <c r="AG11" s="10" t="n">
+        <v>0.0339</v>
+      </c>
+      <c r="AH11" s="8" t="n">
+        <v>3021670</v>
+      </c>
+      <c r="AI11" s="9" t="n">
+        <v>372239.53</v>
+      </c>
+      <c r="AJ11" s="10" t="n">
+        <v>0.0358</v>
+      </c>
+      <c r="AK11" s="8" t="n">
+        <v>3021670</v>
+      </c>
+      <c r="AL11" s="9" t="n">
         <v>370366.09</v>
       </c>
-      <c r="AD11" s="10" t="n">
+      <c r="AM11" s="10" t="n">
         <v>0.0376</v>
       </c>
-      <c r="AE11" s="8" t="n">
+      <c r="AN11" s="8" t="n">
         <v>3018078</v>
       </c>
-      <c r="AF11" s="9" t="n">
+      <c r="AO11" s="9" t="n">
         <v>347747.47</v>
       </c>
-      <c r="AG11" s="10" t="n">
+      <c r="AP11" s="10" t="n">
         <v>0.0372</v>
       </c>
-      <c r="AH11" s="8" t="n">
+      <c r="AQ11" s="8" t="n">
         <v>3018078</v>
       </c>
-      <c r="AI11" s="9" t="n">
+      <c r="AR11" s="9" t="n">
         <v>360535.07</v>
       </c>
-      <c r="AJ11" s="10" t="n">
+      <c r="AS11" s="10" t="n">
         <v>0.041</v>
       </c>
-      <c r="AK11" s="8" t="n">
+      <c r="AT11" s="8" t="n">
         <v>3018078</v>
       </c>
-      <c r="AL11" s="9" t="n">
+      <c r="AU11" s="9" t="n">
         <v>371545.02</v>
       </c>
-      <c r="AM11" s="10" t="n">
+      <c r="AV11" s="10" t="n">
         <v>0.0414</v>
       </c>
     </row>
@@ -1879,108 +2161,135 @@
         <v>33244875</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>422010.44</v>
+        <v>386072.73</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>0.0317</v>
+        <v>0.0299</v>
       </c>
       <c r="G12" s="8" t="n">
         <v>33244875</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>425434.67</v>
+        <v>460075.83</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>0.0328</v>
+        <v>0.0343</v>
       </c>
       <c r="J12" s="8" t="n">
         <v>33244875</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>409842.82</v>
+        <v>455587.77</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>0.0326</v>
+        <v>0.034</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>33244875</v>
       </c>
       <c r="N12" s="9" t="n">
+        <v>422010.44</v>
+      </c>
+      <c r="O12" s="10" t="n">
+        <v>0.0317</v>
+      </c>
+      <c r="P12" s="8" t="n">
+        <v>33244875</v>
+      </c>
+      <c r="Q12" s="9" t="n">
+        <v>425434.67</v>
+      </c>
+      <c r="R12" s="10" t="n">
+        <v>0.0328</v>
+      </c>
+      <c r="S12" s="8" t="n">
+        <v>33244875</v>
+      </c>
+      <c r="T12" s="9" t="n">
+        <v>409842.82</v>
+      </c>
+      <c r="U12" s="10" t="n">
+        <v>0.0326</v>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v>33244875</v>
+      </c>
+      <c r="W12" s="9" t="n">
         <v>376199.01</v>
       </c>
-      <c r="O12" s="10" t="n">
+      <c r="X12" s="10" t="n">
         <v>0.0314</v>
       </c>
-      <c r="P12" s="8" t="n">
+      <c r="Y12" s="8" t="n">
         <v>32644875</v>
       </c>
-      <c r="Q12" s="9" t="n">
+      <c r="Z12" s="9" t="n">
         <v>341204.23</v>
       </c>
-      <c r="R12" s="10" t="n">
+      <c r="AA12" s="10" t="n">
         <v>0.0297</v>
       </c>
-      <c r="S12" s="8" t="n">
+      <c r="AB12" s="8" t="n">
         <v>30107270</v>
       </c>
-      <c r="T12" s="9" t="n">
+      <c r="AC12" s="9" t="n">
         <v>321666.07</v>
       </c>
-      <c r="U12" s="10" t="n">
+      <c r="AD12" s="10" t="n">
         <v>0.0284</v>
-      </c>
-      <c r="V12" s="8" t="n">
-        <v>27257270</v>
-      </c>
-      <c r="W12" s="9" t="n">
-        <v>326869.18</v>
-      </c>
-      <c r="X12" s="10" t="n">
-        <v>0.0296</v>
-      </c>
-      <c r="Y12" s="8" t="n">
-        <v>27257270</v>
-      </c>
-      <c r="Z12" s="9" t="n">
-        <v>324961.17</v>
-      </c>
-      <c r="AA12" s="10" t="n">
-        <v>0.0313</v>
-      </c>
-      <c r="AB12" s="8" t="n">
-        <v>27257270</v>
-      </c>
-      <c r="AC12" s="9" t="n">
-        <v>322998.65</v>
-      </c>
-      <c r="AD12" s="10" t="n">
-        <v>0.0328</v>
       </c>
       <c r="AE12" s="8" t="n">
         <v>27257270</v>
       </c>
       <c r="AF12" s="9" t="n">
-        <v>300375.12</v>
+        <v>326869.18</v>
       </c>
       <c r="AG12" s="10" t="n">
-        <v>0.0321</v>
+        <v>0.0296</v>
       </c>
       <c r="AH12" s="8" t="n">
         <v>27257270</v>
       </c>
       <c r="AI12" s="9" t="n">
-        <v>276811.21</v>
+        <v>324961.17</v>
       </c>
       <c r="AJ12" s="10" t="n">
-        <v>0.0315</v>
+        <v>0.0313</v>
       </c>
       <c r="AK12" s="8" t="n">
         <v>27257270</v>
       </c>
       <c r="AL12" s="9" t="n">
+        <v>322998.65</v>
+      </c>
+      <c r="AM12" s="10" t="n">
+        <v>0.0328</v>
+      </c>
+      <c r="AN12" s="8" t="n">
+        <v>27257270</v>
+      </c>
+      <c r="AO12" s="9" t="n">
+        <v>300375.12</v>
+      </c>
+      <c r="AP12" s="10" t="n">
+        <v>0.0321</v>
+      </c>
+      <c r="AQ12" s="8" t="n">
+        <v>27257270</v>
+      </c>
+      <c r="AR12" s="9" t="n">
+        <v>276811.21</v>
+      </c>
+      <c r="AS12" s="10" t="n">
+        <v>0.0315</v>
+      </c>
+      <c r="AT12" s="8" t="n">
+        <v>27257270</v>
+      </c>
+      <c r="AU12" s="9" t="n">
         <v>268783.94</v>
       </c>
-      <c r="AM12" s="10" t="n">
+      <c r="AV12" s="10" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -2001,111 +2310,138 @@
         </is>
       </c>
       <c r="D13" s="8" t="n">
+        <v>29868916</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>400721.38</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>0.0311</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>27771661</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>385776.14</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>0.0287</v>
+      </c>
+      <c r="J13" s="8" t="n">
+        <v>23460156</v>
+      </c>
+      <c r="K13" s="9" t="n">
+        <v>397790.41</v>
+      </c>
+      <c r="L13" s="10" t="n">
+        <v>0.0297</v>
+      </c>
+      <c r="M13" s="8" t="n">
         <v>21315882</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="N13" s="9" t="n">
         <v>346020.71</v>
       </c>
-      <c r="F13" s="10" t="n">
+      <c r="O13" s="10" t="n">
         <v>0.026</v>
       </c>
-      <c r="G13" s="8" t="n">
+      <c r="P13" s="8" t="n">
         <v>19831378</v>
       </c>
-      <c r="H13" s="9" t="n">
+      <c r="Q13" s="9" t="n">
         <v>322101.24</v>
       </c>
-      <c r="I13" s="10" t="n">
+      <c r="R13" s="10" t="n">
         <v>0.0248</v>
       </c>
-      <c r="J13" s="8" t="n">
+      <c r="S13" s="8" t="n">
         <v>18138945</v>
       </c>
-      <c r="K13" s="9" t="n">
+      <c r="T13" s="9" t="n">
         <v>279611.84</v>
       </c>
-      <c r="L13" s="10" t="n">
+      <c r="U13" s="10" t="n">
         <v>0.0222</v>
       </c>
-      <c r="M13" s="8" t="n">
+      <c r="V13" s="8" t="n">
         <v>18706995</v>
       </c>
-      <c r="N13" s="9" t="n">
+      <c r="W13" s="9" t="n">
         <v>259110.59</v>
       </c>
-      <c r="O13" s="10" t="n">
+      <c r="X13" s="10" t="n">
         <v>0.0216</v>
       </c>
-      <c r="P13" s="8" t="n">
+      <c r="Y13" s="8" t="n">
         <v>18706995</v>
       </c>
-      <c r="Q13" s="9" t="n">
+      <c r="Z13" s="9" t="n">
         <v>272149.36</v>
       </c>
-      <c r="R13" s="10" t="n">
+      <c r="AA13" s="10" t="n">
         <v>0.0237</v>
       </c>
-      <c r="S13" s="8" t="n">
+      <c r="AB13" s="8" t="n">
         <v>18706995</v>
       </c>
-      <c r="T13" s="9" t="n">
+      <c r="AC13" s="9" t="n">
         <v>274599.98</v>
       </c>
-      <c r="U13" s="10" t="n">
+      <c r="AD13" s="10" t="n">
         <v>0.0242</v>
       </c>
-      <c r="V13" s="8" t="n">
+      <c r="AE13" s="8" t="n">
         <v>18558995</v>
       </c>
-      <c r="W13" s="9" t="n">
+      <c r="AF13" s="9" t="n">
         <v>320810.79</v>
       </c>
-      <c r="X13" s="10" t="n">
+      <c r="AG13" s="10" t="n">
         <v>0.0291</v>
       </c>
-      <c r="Y13" s="8" t="n">
+      <c r="AH13" s="8" t="n">
         <v>18341573</v>
       </c>
-      <c r="Z13" s="9" t="n">
+      <c r="AI13" s="9" t="n">
         <v>300178.18</v>
       </c>
-      <c r="AA13" s="10" t="n">
+      <c r="AJ13" s="10" t="n">
         <v>0.0289</v>
-      </c>
-      <c r="AB13" s="8" t="n">
-        <v>18706973</v>
-      </c>
-      <c r="AC13" s="9" t="n">
-        <v>293231.8</v>
-      </c>
-      <c r="AD13" s="10" t="n">
-        <v>0.0298</v>
-      </c>
-      <c r="AE13" s="8" t="n">
-        <v>18706973</v>
-      </c>
-      <c r="AF13" s="9" t="n">
-        <v>297908.55</v>
-      </c>
-      <c r="AG13" s="10" t="n">
-        <v>0.0319</v>
-      </c>
-      <c r="AH13" s="8" t="n">
-        <v>18706973</v>
-      </c>
-      <c r="AI13" s="9" t="n">
-        <v>294644.18</v>
-      </c>
-      <c r="AJ13" s="10" t="n">
-        <v>0.0335</v>
       </c>
       <c r="AK13" s="8" t="n">
         <v>18706973</v>
       </c>
       <c r="AL13" s="9" t="n">
+        <v>293231.8</v>
+      </c>
+      <c r="AM13" s="10" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="AN13" s="8" t="n">
+        <v>18706973</v>
+      </c>
+      <c r="AO13" s="9" t="n">
+        <v>297908.55</v>
+      </c>
+      <c r="AP13" s="10" t="n">
+        <v>0.0319</v>
+      </c>
+      <c r="AQ13" s="8" t="n">
+        <v>18706973</v>
+      </c>
+      <c r="AR13" s="9" t="n">
+        <v>294644.18</v>
+      </c>
+      <c r="AS13" s="10" t="n">
+        <v>0.0335</v>
+      </c>
+      <c r="AT13" s="8" t="n">
+        <v>18706973</v>
+      </c>
+      <c r="AU13" s="9" t="n">
         <v>322779.47</v>
       </c>
-      <c r="AM13" s="10" t="n">
+      <c r="AV13" s="10" t="n">
         <v>0.036</v>
       </c>
     </row>
@@ -2126,111 +2462,138 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
+        <v>14645626</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>432734.31</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>0.0336</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>13974725</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>474777.31</v>
+      </c>
+      <c r="I14" s="10" t="n">
+        <v>0.0354</v>
+      </c>
+      <c r="J14" s="8" t="n">
+        <v>13974725</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>479584.61</v>
+      </c>
+      <c r="L14" s="10" t="n">
+        <v>0.0358</v>
+      </c>
+      <c r="M14" s="8" t="n">
         <v>13033470</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="N14" s="9" t="n">
         <v>483437.47</v>
       </c>
-      <c r="F14" s="10" t="n">
+      <c r="O14" s="10" t="n">
         <v>0.0363</v>
       </c>
-      <c r="G14" s="8" t="n">
+      <c r="P14" s="8" t="n">
         <v>12435671</v>
       </c>
-      <c r="H14" s="9" t="n">
+      <c r="Q14" s="9" t="n">
         <v>467245.47</v>
       </c>
-      <c r="I14" s="10" t="n">
+      <c r="R14" s="10" t="n">
         <v>0.036</v>
       </c>
-      <c r="J14" s="8" t="n">
+      <c r="S14" s="8" t="n">
         <v>12435671</v>
       </c>
-      <c r="K14" s="9" t="n">
+      <c r="T14" s="9" t="n">
         <v>433656.72</v>
       </c>
-      <c r="L14" s="10" t="n">
+      <c r="U14" s="10" t="n">
         <v>0.0345</v>
-      </c>
-      <c r="M14" s="8" t="n">
-        <v>12335671</v>
-      </c>
-      <c r="N14" s="9" t="n">
-        <v>422743.45</v>
-      </c>
-      <c r="O14" s="10" t="n">
-        <v>0.0353</v>
-      </c>
-      <c r="P14" s="8" t="n">
-        <v>12335671</v>
-      </c>
-      <c r="Q14" s="9" t="n">
-        <v>394679.79</v>
-      </c>
-      <c r="R14" s="10" t="n">
-        <v>0.0343</v>
-      </c>
-      <c r="S14" s="8" t="n">
-        <v>12335671</v>
-      </c>
-      <c r="T14" s="9" t="n">
-        <v>395123.88</v>
-      </c>
-      <c r="U14" s="10" t="n">
-        <v>0.0349</v>
       </c>
       <c r="V14" s="8" t="n">
         <v>12335671</v>
       </c>
       <c r="W14" s="9" t="n">
+        <v>422743.45</v>
+      </c>
+      <c r="X14" s="10" t="n">
+        <v>0.0353</v>
+      </c>
+      <c r="Y14" s="8" t="n">
+        <v>12335671</v>
+      </c>
+      <c r="Z14" s="9" t="n">
+        <v>394679.79</v>
+      </c>
+      <c r="AA14" s="10" t="n">
+        <v>0.0343</v>
+      </c>
+      <c r="AB14" s="8" t="n">
+        <v>12335671</v>
+      </c>
+      <c r="AC14" s="9" t="n">
+        <v>395123.88</v>
+      </c>
+      <c r="AD14" s="10" t="n">
+        <v>0.0349</v>
+      </c>
+      <c r="AE14" s="8" t="n">
+        <v>12335671</v>
+      </c>
+      <c r="AF14" s="9" t="n">
         <v>392669.08</v>
       </c>
-      <c r="X14" s="10" t="n">
+      <c r="AG14" s="10" t="n">
         <v>0.0356</v>
       </c>
-      <c r="Y14" s="8" t="n">
+      <c r="AH14" s="8" t="n">
         <v>12231374</v>
       </c>
-      <c r="Z14" s="9" t="n">
+      <c r="AI14" s="9" t="n">
         <v>364103.54</v>
       </c>
-      <c r="AA14" s="10" t="n">
+      <c r="AJ14" s="10" t="n">
         <v>0.0351</v>
       </c>
-      <c r="AB14" s="8" t="n">
+      <c r="AK14" s="8" t="n">
         <v>11040212</v>
       </c>
-      <c r="AC14" s="9" t="n">
+      <c r="AL14" s="9" t="n">
         <v>323345.73</v>
       </c>
-      <c r="AD14" s="10" t="n">
+      <c r="AM14" s="10" t="n">
         <v>0.0328</v>
       </c>
-      <c r="AE14" s="8" t="n">
+      <c r="AN14" s="8" t="n">
         <v>10399289</v>
       </c>
-      <c r="AF14" s="9" t="n">
+      <c r="AO14" s="9" t="n">
         <v>277224.25</v>
       </c>
-      <c r="AG14" s="10" t="n">
+      <c r="AP14" s="10" t="n">
         <v>0.0297</v>
       </c>
-      <c r="AH14" s="8" t="n">
+      <c r="AQ14" s="8" t="n">
         <v>10068665</v>
       </c>
-      <c r="AI14" s="9" t="n">
+      <c r="AR14" s="9" t="n">
         <v>260285.06</v>
       </c>
-      <c r="AJ14" s="10" t="n">
+      <c r="AS14" s="10" t="n">
         <v>0.0296</v>
       </c>
-      <c r="AK14" s="8" t="n">
+      <c r="AT14" s="8" t="n">
         <v>9331737</v>
       </c>
-      <c r="AL14" s="9" t="n">
+      <c r="AU14" s="9" t="n">
         <v>279004.94</v>
       </c>
-      <c r="AM14" s="10" t="n">
+      <c r="AV14" s="10" t="n">
         <v>0.0311</v>
       </c>
     </row>
@@ -2251,111 +2614,138 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
+        <v>26944033</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>336962.08</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>0.0261</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>20693682</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>269038.56</v>
+      </c>
+      <c r="I15" s="10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J15" s="8" t="n">
+        <v>16509541</v>
+      </c>
+      <c r="K15" s="9" t="n">
+        <v>270921.57</v>
+      </c>
+      <c r="L15" s="10" t="n">
+        <v>0.0202</v>
+      </c>
+      <c r="M15" s="8" t="n">
         <v>16417936</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="N15" s="9" t="n">
         <v>265215.34</v>
       </c>
-      <c r="F15" s="10" t="n">
+      <c r="O15" s="10" t="n">
         <v>0.0199</v>
       </c>
-      <c r="G15" s="8" t="n">
+      <c r="P15" s="8" t="n">
         <v>17621740</v>
       </c>
-      <c r="H15" s="9" t="n">
+      <c r="Q15" s="9" t="n">
         <v>274916.77</v>
       </c>
-      <c r="I15" s="10" t="n">
+      <c r="R15" s="10" t="n">
         <v>0.0212</v>
-      </c>
-      <c r="J15" s="8" t="n">
-        <v>9306473</v>
-      </c>
-      <c r="K15" s="9" t="n">
-        <v>137949.85</v>
-      </c>
-      <c r="L15" s="10" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="M15" s="8" t="n">
-        <v>9306473</v>
-      </c>
-      <c r="N15" s="9" t="n">
-        <v>134180.73</v>
-      </c>
-      <c r="O15" s="10" t="n">
-        <v>0.0112</v>
-      </c>
-      <c r="P15" s="8" t="n">
-        <v>9306473</v>
-      </c>
-      <c r="Q15" s="9" t="n">
-        <v>136767.93</v>
-      </c>
-      <c r="R15" s="10" t="n">
-        <v>0.0119</v>
       </c>
       <c r="S15" s="8" t="n">
         <v>9306473</v>
       </c>
       <c r="T15" s="9" t="n">
-        <v>140434.68</v>
+        <v>137949.85</v>
       </c>
       <c r="U15" s="10" t="n">
-        <v>0.0124</v>
+        <v>0.011</v>
       </c>
       <c r="V15" s="8" t="n">
         <v>9306473</v>
       </c>
       <c r="W15" s="9" t="n">
-        <v>149071.08</v>
+        <v>134180.73</v>
       </c>
       <c r="X15" s="10" t="n">
-        <v>0.0135</v>
+        <v>0.0112</v>
       </c>
       <c r="Y15" s="8" t="n">
         <v>9306473</v>
       </c>
       <c r="Z15" s="9" t="n">
-        <v>145432.25</v>
+        <v>136767.93</v>
       </c>
       <c r="AA15" s="10" t="n">
-        <v>0.014</v>
+        <v>0.0119</v>
       </c>
       <c r="AB15" s="8" t="n">
         <v>9306473</v>
       </c>
       <c r="AC15" s="9" t="n">
-        <v>139606.4</v>
+        <v>140434.68</v>
       </c>
       <c r="AD15" s="10" t="n">
-        <v>0.0142</v>
+        <v>0.0124</v>
       </c>
       <c r="AE15" s="8" t="n">
         <v>9306473</v>
       </c>
       <c r="AF15" s="9" t="n">
-        <v>146172.12</v>
+        <v>149071.08</v>
       </c>
       <c r="AG15" s="10" t="n">
-        <v>0.0156</v>
+        <v>0.0135</v>
       </c>
       <c r="AH15" s="8" t="n">
         <v>9306473</v>
       </c>
       <c r="AI15" s="9" t="n">
-        <v>157065.34</v>
+        <v>145432.25</v>
       </c>
       <c r="AJ15" s="10" t="n">
-        <v>0.0178</v>
+        <v>0.014</v>
       </c>
       <c r="AK15" s="8" t="n">
         <v>9306473</v>
       </c>
       <c r="AL15" s="9" t="n">
+        <v>139606.4</v>
+      </c>
+      <c r="AM15" s="10" t="n">
+        <v>0.0142</v>
+      </c>
+      <c r="AN15" s="8" t="n">
+        <v>9306473</v>
+      </c>
+      <c r="AO15" s="9" t="n">
+        <v>146172.12</v>
+      </c>
+      <c r="AP15" s="10" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="AQ15" s="8" t="n">
+        <v>9306473</v>
+      </c>
+      <c r="AR15" s="9" t="n">
+        <v>157065.34</v>
+      </c>
+      <c r="AS15" s="10" t="n">
+        <v>0.0178</v>
+      </c>
+      <c r="AT15" s="8" t="n">
+        <v>9306473</v>
+      </c>
+      <c r="AU15" s="9" t="n">
         <v>174943.08</v>
       </c>
-      <c r="AM15" s="10" t="n">
+      <c r="AV15" s="10" t="n">
         <v>0.0195</v>
       </c>
     </row>
@@ -2376,111 +2766,138 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
+        <v>13769904</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>172798.53</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>0.0134</v>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>13769904</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>177122.28</v>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="J16" s="8" t="n">
+        <v>14083029</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>171545.38</v>
+      </c>
+      <c r="L16" s="10" t="n">
+        <v>0.0128</v>
+      </c>
+      <c r="M16" s="8" t="n">
         <v>13125545</v>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="N16" s="9" t="n">
         <v>166878.18</v>
       </c>
-      <c r="F16" s="10" t="n">
+      <c r="O16" s="10" t="n">
         <v>0.0125</v>
       </c>
-      <c r="G16" s="8" t="n">
+      <c r="P16" s="8" t="n">
         <v>13125545</v>
       </c>
-      <c r="H16" s="9" t="n">
+      <c r="Q16" s="9" t="n">
         <v>165224.36</v>
-      </c>
-      <c r="I16" s="10" t="n">
-        <v>0.0127</v>
-      </c>
-      <c r="J16" s="8" t="n">
-        <v>12775545</v>
-      </c>
-      <c r="K16" s="9" t="n">
-        <v>152999.93</v>
-      </c>
-      <c r="L16" s="10" t="n">
-        <v>0.0122</v>
-      </c>
-      <c r="M16" s="8" t="n">
-        <v>12107943</v>
-      </c>
-      <c r="N16" s="9" t="n">
-        <v>148164.9</v>
-      </c>
-      <c r="O16" s="10" t="n">
-        <v>0.0124</v>
-      </c>
-      <c r="P16" s="8" t="n">
-        <v>11632943</v>
-      </c>
-      <c r="Q16" s="9" t="n">
-        <v>146586.71</v>
       </c>
       <c r="R16" s="10" t="n">
         <v>0.0127</v>
       </c>
       <c r="S16" s="8" t="n">
+        <v>12775545</v>
+      </c>
+      <c r="T16" s="9" t="n">
+        <v>152999.93</v>
+      </c>
+      <c r="U16" s="10" t="n">
+        <v>0.0122</v>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v>12107943</v>
+      </c>
+      <c r="W16" s="9" t="n">
+        <v>148164.9</v>
+      </c>
+      <c r="X16" s="10" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="Y16" s="8" t="n">
+        <v>11632943</v>
+      </c>
+      <c r="Z16" s="9" t="n">
+        <v>146586.71</v>
+      </c>
+      <c r="AA16" s="10" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="AB16" s="8" t="n">
         <v>11217622</v>
       </c>
-      <c r="T16" s="9" t="n">
+      <c r="AC16" s="9" t="n">
         <v>142497.45</v>
       </c>
-      <c r="U16" s="10" t="n">
+      <c r="AD16" s="10" t="n">
         <v>0.0126</v>
       </c>
-      <c r="V16" s="8" t="n">
+      <c r="AE16" s="8" t="n">
         <v>10341500</v>
       </c>
-      <c r="W16" s="9" t="n">
+      <c r="AF16" s="9" t="n">
         <v>132712.47</v>
       </c>
-      <c r="X16" s="10" t="n">
+      <c r="AG16" s="10" t="n">
         <v>0.012</v>
       </c>
-      <c r="Y16" s="8" t="n">
+      <c r="AH16" s="8" t="n">
         <v>10341500</v>
       </c>
-      <c r="Z16" s="9" t="n">
+      <c r="AI16" s="9" t="n">
         <v>129392.85</v>
       </c>
-      <c r="AA16" s="10" t="n">
+      <c r="AJ16" s="10" t="n">
         <v>0.0125</v>
       </c>
-      <c r="AB16" s="8" t="n">
+      <c r="AK16" s="8" t="n">
         <v>10403670</v>
       </c>
-      <c r="AC16" s="9" t="n">
+      <c r="AL16" s="9" t="n">
         <v>123169.05</v>
       </c>
-      <c r="AD16" s="10" t="n">
+      <c r="AM16" s="10" t="n">
         <v>0.0125</v>
       </c>
-      <c r="AE16" s="8" t="n">
+      <c r="AN16" s="8" t="n">
         <v>10133496</v>
       </c>
-      <c r="AF16" s="9" t="n">
+      <c r="AO16" s="9" t="n">
         <v>115947.46</v>
       </c>
-      <c r="AG16" s="10" t="n">
+      <c r="AP16" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="AH16" s="8" t="n">
+      <c r="AQ16" s="8" t="n">
         <v>9911843</v>
       </c>
-      <c r="AI16" s="9" t="n">
+      <c r="AR16" s="9" t="n">
         <v>110665.73</v>
       </c>
-      <c r="AJ16" s="10" t="n">
+      <c r="AS16" s="10" t="n">
         <v>0.0126</v>
       </c>
-      <c r="AK16" s="8" t="n">
+      <c r="AT16" s="8" t="n">
         <v>7388241</v>
       </c>
-      <c r="AL16" s="9" t="n">
+      <c r="AU16" s="9" t="n">
         <v>89940.75</v>
       </c>
-      <c r="AM16" s="10" t="n">
+      <c r="AV16" s="10" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -2501,111 +2918,138 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
+        <v>13271296</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>162467.21</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>12881359</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>173666.48</v>
+      </c>
+      <c r="I17" s="10" t="n">
+        <v>0.0129</v>
+      </c>
+      <c r="J17" s="8" t="n">
+        <v>12623339</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <v>167133.01</v>
+      </c>
+      <c r="L17" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="M17" s="8" t="n">
         <v>10989584</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="N17" s="9" t="n">
         <v>166085.58</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="G17" s="8" t="n">
-        <v>10765866</v>
-      </c>
-      <c r="H17" s="9" t="n">
-        <v>164857.71</v>
-      </c>
-      <c r="I17" s="10" t="n">
-        <v>0.0127</v>
-      </c>
-      <c r="J17" s="8" t="n">
-        <v>10173460</v>
-      </c>
-      <c r="K17" s="9" t="n">
-        <v>152734.15</v>
-      </c>
-      <c r="L17" s="10" t="n">
-        <v>0.0121</v>
-      </c>
-      <c r="M17" s="8" t="n">
-        <v>9988840</v>
-      </c>
-      <c r="N17" s="9" t="n">
-        <v>150162.23</v>
       </c>
       <c r="O17" s="10" t="n">
         <v>0.0125</v>
       </c>
       <c r="P17" s="8" t="n">
-        <v>8991707</v>
+        <v>10765866</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>142914.19</v>
+        <v>164857.71</v>
       </c>
       <c r="R17" s="10" t="n">
-        <v>0.0124</v>
+        <v>0.0127</v>
       </c>
       <c r="S17" s="8" t="n">
-        <v>9450707</v>
+        <v>10173460</v>
       </c>
       <c r="T17" s="9" t="n">
-        <v>146920.69</v>
+        <v>152734.15</v>
       </c>
       <c r="U17" s="10" t="n">
-        <v>0.013</v>
+        <v>0.0121</v>
       </c>
       <c r="V17" s="8" t="n">
-        <v>9147124</v>
+        <v>9988840</v>
       </c>
       <c r="W17" s="9" t="n">
-        <v>137746.54</v>
+        <v>150162.23</v>
       </c>
       <c r="X17" s="10" t="n">
         <v>0.0125</v>
       </c>
       <c r="Y17" s="8" t="n">
+        <v>8991707</v>
+      </c>
+      <c r="Z17" s="9" t="n">
+        <v>142914.19</v>
+      </c>
+      <c r="AA17" s="10" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="AB17" s="8" t="n">
+        <v>9450707</v>
+      </c>
+      <c r="AC17" s="9" t="n">
+        <v>146920.69</v>
+      </c>
+      <c r="AD17" s="10" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="AE17" s="8" t="n">
+        <v>9147124</v>
+      </c>
+      <c r="AF17" s="9" t="n">
+        <v>137746.54</v>
+      </c>
+      <c r="AG17" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AH17" s="8" t="n">
         <v>8881919</v>
       </c>
-      <c r="Z17" s="9" t="n">
+      <c r="AI17" s="9" t="n">
         <v>130182.29</v>
       </c>
-      <c r="AA17" s="10" t="n">
+      <c r="AJ17" s="10" t="n">
         <v>0.0125</v>
       </c>
-      <c r="AB17" s="8" t="n">
+      <c r="AK17" s="8" t="n">
         <v>7994194</v>
       </c>
-      <c r="AC17" s="9" t="n">
+      <c r="AL17" s="9" t="n">
         <v>123918</v>
       </c>
-      <c r="AD17" s="10" t="n">
+      <c r="AM17" s="10" t="n">
         <v>0.0126</v>
       </c>
-      <c r="AE17" s="8" t="n">
+      <c r="AN17" s="8" t="n">
         <v>7994194</v>
       </c>
-      <c r="AF17" s="9" t="n">
+      <c r="AO17" s="9" t="n">
         <v>115292.27</v>
       </c>
-      <c r="AG17" s="10" t="n">
+      <c r="AP17" s="10" t="n">
         <v>0.0123</v>
       </c>
-      <c r="AH17" s="8" t="n">
+      <c r="AQ17" s="8" t="n">
         <v>7755553</v>
       </c>
-      <c r="AI17" s="9" t="n">
+      <c r="AR17" s="9" t="n">
         <v>109159.41</v>
       </c>
-      <c r="AJ17" s="10" t="n">
+      <c r="AS17" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="AK17" s="8" t="n">
+      <c r="AT17" s="8" t="n">
         <v>6223549</v>
       </c>
-      <c r="AL17" s="9" t="n">
+      <c r="AU17" s="9" t="n">
         <v>92071.17999999999</v>
       </c>
-      <c r="AM17" s="10" t="n">
+      <c r="AV17" s="10" t="n">
         <v>0.0103</v>
       </c>
     </row>
@@ -2626,111 +3070,138 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
+        <v>18853686</v>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>164253.31</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>18853686</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>173774.42</v>
+      </c>
+      <c r="I18" s="10" t="n">
+        <v>0.0129</v>
+      </c>
+      <c r="J18" s="8" t="n">
+        <v>18750502</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <v>165998.19</v>
+      </c>
+      <c r="L18" s="10" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="M18" s="8" t="n">
         <v>17903094</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="N18" s="9" t="n">
         <v>163696.94</v>
       </c>
-      <c r="F18" s="10" t="n">
+      <c r="O18" s="10" t="n">
         <v>0.0123</v>
       </c>
-      <c r="G18" s="8" t="n">
+      <c r="P18" s="8" t="n">
         <v>17405149</v>
       </c>
-      <c r="H18" s="9" t="n">
+      <c r="Q18" s="9" t="n">
         <v>164043.53</v>
-      </c>
-      <c r="I18" s="10" t="n">
-        <v>0.0126</v>
-      </c>
-      <c r="J18" s="8" t="n">
-        <v>15759789</v>
-      </c>
-      <c r="K18" s="9" t="n">
-        <v>153571.26</v>
-      </c>
-      <c r="L18" s="10" t="n">
-        <v>0.0122</v>
-      </c>
-      <c r="M18" s="8" t="n">
-        <v>15148311</v>
-      </c>
-      <c r="N18" s="9" t="n">
-        <v>148741.27</v>
-      </c>
-      <c r="O18" s="10" t="n">
-        <v>0.0124</v>
-      </c>
-      <c r="P18" s="8" t="n">
-        <v>14786344</v>
-      </c>
-      <c r="Q18" s="9" t="n">
-        <v>145061.43</v>
       </c>
       <c r="R18" s="10" t="n">
         <v>0.0126</v>
       </c>
       <c r="S18" s="8" t="n">
+        <v>15759789</v>
+      </c>
+      <c r="T18" s="9" t="n">
+        <v>153571.26</v>
+      </c>
+      <c r="U18" s="10" t="n">
+        <v>0.0122</v>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v>15148311</v>
+      </c>
+      <c r="W18" s="9" t="n">
+        <v>148741.27</v>
+      </c>
+      <c r="X18" s="10" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="Y18" s="8" t="n">
+        <v>14786344</v>
+      </c>
+      <c r="Z18" s="9" t="n">
+        <v>145061.43</v>
+      </c>
+      <c r="AA18" s="10" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="AB18" s="8" t="n">
         <v>14470385</v>
       </c>
-      <c r="T18" s="9" t="n">
+      <c r="AC18" s="9" t="n">
         <v>140333.79</v>
       </c>
-      <c r="U18" s="10" t="n">
+      <c r="AD18" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="V18" s="8" t="n">
+      <c r="AE18" s="8" t="n">
         <v>14258435</v>
       </c>
-      <c r="W18" s="9" t="n">
+      <c r="AF18" s="9" t="n">
         <v>141151.38</v>
       </c>
-      <c r="X18" s="10" t="n">
+      <c r="AG18" s="10" t="n">
         <v>0.0128</v>
       </c>
-      <c r="Y18" s="8" t="n">
+      <c r="AH18" s="8" t="n">
         <v>14258435</v>
       </c>
-      <c r="Z18" s="9" t="n">
+      <c r="AI18" s="9" t="n">
         <v>132603.45</v>
       </c>
-      <c r="AA18" s="10" t="n">
+      <c r="AJ18" s="10" t="n">
         <v>0.0128</v>
       </c>
-      <c r="AB18" s="8" t="n">
+      <c r="AK18" s="8" t="n">
         <v>13936283</v>
       </c>
-      <c r="AC18" s="9" t="n">
+      <c r="AL18" s="9" t="n">
         <v>123789.03</v>
       </c>
-      <c r="AD18" s="10" t="n">
+      <c r="AM18" s="10" t="n">
         <v>0.0126</v>
       </c>
-      <c r="AE18" s="8" t="n">
+      <c r="AN18" s="8" t="n">
         <v>13003659</v>
       </c>
-      <c r="AF18" s="9" t="n">
+      <c r="AO18" s="9" t="n">
         <v>115264.43</v>
       </c>
-      <c r="AG18" s="10" t="n">
+      <c r="AP18" s="10" t="n">
         <v>0.0123</v>
       </c>
-      <c r="AH18" s="8" t="n">
+      <c r="AQ18" s="8" t="n">
         <v>11479604</v>
       </c>
-      <c r="AI18" s="9" t="n">
+      <c r="AR18" s="9" t="n">
         <v>100630.21</v>
       </c>
-      <c r="AJ18" s="10" t="n">
+      <c r="AS18" s="10" t="n">
         <v>0.0114</v>
       </c>
-      <c r="AK18" s="8" t="n">
+      <c r="AT18" s="8" t="n">
         <v>8859127</v>
       </c>
-      <c r="AL18" s="9" t="n">
+      <c r="AU18" s="9" t="n">
         <v>85955.67999999999</v>
       </c>
-      <c r="AM18" s="10" t="n">
+      <c r="AV18" s="10" t="n">
         <v>0.009599999999999999</v>
       </c>
     </row>
@@ -2751,111 +3222,138 @@
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>4189074</v>
+        <v>2274074</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>97173.95</v>
+        <v>47368.96</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>0.0073</v>
+        <v>0.0037</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>4189074</v>
+        <v>2906065</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>96721.53</v>
+        <v>69277.67999999999</v>
       </c>
       <c r="I19" s="10" t="n">
-        <v>0.0075</v>
+        <v>0.0052</v>
       </c>
       <c r="J19" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>95502.50999999999</v>
+        <v>96591.67</v>
       </c>
       <c r="L19" s="10" t="n">
-        <v>0.0076</v>
+        <v>0.0072</v>
       </c>
       <c r="M19" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>96130.87</v>
+        <v>97173.95</v>
       </c>
       <c r="O19" s="10" t="n">
-        <v>0.008</v>
+        <v>0.0073</v>
       </c>
       <c r="P19" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>95904.66</v>
+        <v>96721.53</v>
       </c>
       <c r="R19" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.0075</v>
       </c>
       <c r="S19" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="T19" s="9" t="n">
-        <v>112108</v>
+        <v>95502.50999999999</v>
       </c>
       <c r="U19" s="10" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0076</v>
       </c>
       <c r="V19" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="W19" s="9" t="n">
-        <v>102435.43</v>
+        <v>96130.87</v>
       </c>
       <c r="X19" s="10" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="Y19" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="Z19" s="9" t="n">
-        <v>103562.29</v>
+        <v>95904.66</v>
       </c>
       <c r="AA19" s="10" t="n">
-        <v>0.01</v>
+        <v>0.0083</v>
       </c>
       <c r="AB19" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="AC19" s="9" t="n">
-        <v>112061.92</v>
+        <v>112108</v>
       </c>
       <c r="AD19" s="10" t="n">
-        <v>0.0114</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="AE19" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="AF19" s="9" t="n">
-        <v>107022.46</v>
+        <v>102435.43</v>
       </c>
       <c r="AG19" s="10" t="n">
-        <v>0.0115</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="AH19" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="AI19" s="9" t="n">
-        <v>109571.51</v>
+        <v>103562.29</v>
       </c>
       <c r="AJ19" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.01</v>
       </c>
       <c r="AK19" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="AL19" s="9" t="n">
+        <v>112061.92</v>
+      </c>
+      <c r="AM19" s="10" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="AN19" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="AO19" s="9" t="n">
+        <v>107022.46</v>
+      </c>
+      <c r="AP19" s="10" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="AQ19" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="AR19" s="9" t="n">
+        <v>109571.51</v>
+      </c>
+      <c r="AS19" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AT19" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="AU19" s="9" t="n">
         <v>116089.71</v>
       </c>
-      <c r="AM19" s="10" t="n">
+      <c r="AV19" s="10" t="n">
         <v>0.0129</v>
       </c>
     </row>
@@ -2879,108 +3377,135 @@
         <v>80755676</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>108390.27</v>
+        <v>92667.14</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>0.0081</v>
+        <v>0.0072</v>
       </c>
       <c r="G20" s="8" t="n">
         <v>80755676</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>112484.58</v>
+        <v>101461.43</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0076</v>
       </c>
       <c r="J20" s="8" t="n">
         <v>80755676</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>112298.84</v>
+        <v>102390.12</v>
       </c>
       <c r="L20" s="10" t="n">
-        <v>0.0089</v>
+        <v>0.0076</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>80755676</v>
       </c>
       <c r="N20" s="9" t="n">
+        <v>108390.27</v>
+      </c>
+      <c r="O20" s="10" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="P20" s="8" t="n">
+        <v>80755676</v>
+      </c>
+      <c r="Q20" s="9" t="n">
+        <v>112484.58</v>
+      </c>
+      <c r="R20" s="10" t="n">
+        <v>0.008699999999999999</v>
+      </c>
+      <c r="S20" s="8" t="n">
+        <v>80755676</v>
+      </c>
+      <c r="T20" s="9" t="n">
+        <v>112298.84</v>
+      </c>
+      <c r="U20" s="10" t="n">
+        <v>0.0089</v>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v>80755676</v>
+      </c>
+      <c r="W20" s="9" t="n">
         <v>112403.83</v>
       </c>
-      <c r="O20" s="10" t="n">
+      <c r="X20" s="10" t="n">
         <v>0.0094</v>
       </c>
-      <c r="P20" s="8" t="n">
+      <c r="Y20" s="8" t="n">
         <v>73511702</v>
       </c>
-      <c r="Q20" s="9" t="n">
+      <c r="Z20" s="9" t="n">
         <v>102769.36</v>
       </c>
-      <c r="R20" s="10" t="n">
+      <c r="AA20" s="10" t="n">
         <v>0.0089</v>
-      </c>
-      <c r="S20" s="8" t="n">
-        <v>44206584</v>
-      </c>
-      <c r="T20" s="9" t="n">
-        <v>59811.51</v>
-      </c>
-      <c r="U20" s="10" t="n">
-        <v>0.0053</v>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v>44206584</v>
-      </c>
-      <c r="W20" s="9" t="n">
-        <v>85367.33</v>
-      </c>
-      <c r="X20" s="10" t="n">
-        <v>0.0077</v>
-      </c>
-      <c r="Y20" s="8" t="n">
-        <v>44206584</v>
-      </c>
-      <c r="Z20" s="9" t="n">
-        <v>88656.3</v>
-      </c>
-      <c r="AA20" s="10" t="n">
-        <v>0.008500000000000001</v>
       </c>
       <c r="AB20" s="8" t="n">
         <v>44206584</v>
       </c>
       <c r="AC20" s="9" t="n">
-        <v>84147.23</v>
+        <v>59811.51</v>
       </c>
       <c r="AD20" s="10" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0053</v>
       </c>
       <c r="AE20" s="8" t="n">
         <v>44206584</v>
       </c>
       <c r="AF20" s="9" t="n">
-        <v>77701.91</v>
+        <v>85367.33</v>
       </c>
       <c r="AG20" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.0077</v>
       </c>
       <c r="AH20" s="8" t="n">
         <v>44206584</v>
       </c>
       <c r="AI20" s="9" t="n">
-        <v>68931.33</v>
+        <v>88656.3</v>
       </c>
       <c r="AJ20" s="10" t="n">
-        <v>0.0078</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="AK20" s="8" t="n">
         <v>44206584</v>
       </c>
       <c r="AL20" s="9" t="n">
+        <v>84147.23</v>
+      </c>
+      <c r="AM20" s="10" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="AN20" s="8" t="n">
+        <v>44206584</v>
+      </c>
+      <c r="AO20" s="9" t="n">
+        <v>77701.91</v>
+      </c>
+      <c r="AP20" s="10" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="AQ20" s="8" t="n">
+        <v>44206584</v>
+      </c>
+      <c r="AR20" s="9" t="n">
+        <v>68931.33</v>
+      </c>
+      <c r="AS20" s="10" t="n">
+        <v>0.0078</v>
+      </c>
+      <c r="AT20" s="8" t="n">
+        <v>44206584</v>
+      </c>
+      <c r="AU20" s="9" t="n">
         <v>77184.7</v>
       </c>
-      <c r="AM20" s="10" t="n">
+      <c r="AV20" s="10" t="n">
         <v>0.0086</v>
       </c>
     </row>
@@ -3018,58 +3543,67 @@
       <c r="S21" s="8" t="n"/>
       <c r="T21" s="9" t="n"/>
       <c r="U21" s="10" t="n"/>
-      <c r="V21" s="8" t="n">
+      <c r="V21" s="8" t="n"/>
+      <c r="W21" s="9" t="n"/>
+      <c r="X21" s="10" t="n"/>
+      <c r="Y21" s="8" t="n"/>
+      <c r="Z21" s="9" t="n"/>
+      <c r="AA21" s="10" t="n"/>
+      <c r="AB21" s="8" t="n"/>
+      <c r="AC21" s="9" t="n"/>
+      <c r="AD21" s="10" t="n"/>
+      <c r="AE21" s="8" t="n">
         <v>591805</v>
       </c>
-      <c r="W21" s="9" t="n">
+      <c r="AF21" s="9" t="n">
         <v>5149</v>
       </c>
-      <c r="X21" s="10" t="n">
+      <c r="AG21" s="10" t="n">
         <v>0.0005</v>
       </c>
-      <c r="Y21" s="8" t="n">
+      <c r="AH21" s="8" t="n">
         <v>5392631</v>
       </c>
-      <c r="Z21" s="9" t="n">
+      <c r="AI21" s="9" t="n">
         <v>43674.92</v>
       </c>
-      <c r="AA21" s="10" t="n">
+      <c r="AJ21" s="10" t="n">
         <v>0.0042</v>
       </c>
-      <c r="AB21" s="8" t="n">
+      <c r="AK21" s="8" t="n">
         <v>8585949</v>
       </c>
-      <c r="AC21" s="9" t="n">
+      <c r="AL21" s="9" t="n">
         <v>56044.78</v>
       </c>
-      <c r="AD21" s="10" t="n">
+      <c r="AM21" s="10" t="n">
         <v>0.0057</v>
       </c>
-      <c r="AE21" s="8" t="n">
+      <c r="AN21" s="8" t="n">
         <v>10913294</v>
       </c>
-      <c r="AF21" s="9" t="n">
+      <c r="AO21" s="9" t="n">
         <v>67154.95</v>
       </c>
-      <c r="AG21" s="10" t="n">
+      <c r="AP21" s="10" t="n">
         <v>0.0072</v>
       </c>
-      <c r="AH21" s="8" t="n">
+      <c r="AQ21" s="8" t="n">
         <v>12053879</v>
       </c>
-      <c r="AI21" s="9" t="n">
+      <c r="AR21" s="9" t="n">
         <v>70937.08</v>
       </c>
-      <c r="AJ21" s="10" t="n">
+      <c r="AS21" s="10" t="n">
         <v>0.0081</v>
       </c>
-      <c r="AK21" s="8" t="n">
+      <c r="AT21" s="8" t="n">
         <v>12053879</v>
       </c>
-      <c r="AL21" s="9" t="n">
+      <c r="AU21" s="9" t="n">
         <v>76801.28999999999</v>
       </c>
-      <c r="AM21" s="10" t="n">
+      <c r="AV21" s="10" t="n">
         <v>0.0086</v>
       </c>
     </row>
@@ -3089,74 +3623,56 @@
           <t>Capital Markets</t>
         </is>
       </c>
-      <c r="D22" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>88833.99000000001</v>
-      </c>
-      <c r="F22" s="10" t="n">
-        <v>0.0067</v>
-      </c>
-      <c r="G22" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="H22" s="9" t="n">
-        <v>80358.22</v>
-      </c>
-      <c r="I22" s="10" t="n">
-        <v>0.0062</v>
-      </c>
-      <c r="J22" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="K22" s="9" t="n">
-        <v>73737.16</v>
-      </c>
-      <c r="L22" s="10" t="n">
-        <v>0.0059</v>
-      </c>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="10" t="n"/>
+      <c r="G22" s="8" t="n"/>
+      <c r="H22" s="9" t="n"/>
+      <c r="I22" s="10" t="n"/>
+      <c r="J22" s="8" t="n"/>
+      <c r="K22" s="9" t="n"/>
+      <c r="L22" s="10" t="n"/>
       <c r="M22" s="8" t="n">
         <v>797719</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>62190.17</v>
+        <v>88833.99000000001</v>
       </c>
       <c r="O22" s="10" t="n">
-        <v>0.0052</v>
+        <v>0.0067</v>
       </c>
       <c r="P22" s="8" t="n">
         <v>797719</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>58951.43</v>
+        <v>80358.22</v>
       </c>
       <c r="R22" s="10" t="n">
-        <v>0.0051</v>
+        <v>0.0062</v>
       </c>
       <c r="S22" s="8" t="n">
         <v>797719</v>
       </c>
       <c r="T22" s="9" t="n">
-        <v>61368.52</v>
+        <v>73737.16</v>
       </c>
       <c r="U22" s="10" t="n">
-        <v>0.0054</v>
+        <v>0.0059</v>
       </c>
       <c r="V22" s="8" t="n">
         <v>797719</v>
       </c>
       <c r="W22" s="9" t="n">
-        <v>71347.99000000001</v>
+        <v>62190.17</v>
       </c>
       <c r="X22" s="10" t="n">
-        <v>0.0065</v>
+        <v>0.0052</v>
       </c>
       <c r="Y22" s="8" t="n">
         <v>797719</v>
       </c>
       <c r="Z22" s="9" t="n">
-        <v>52665.41</v>
+        <v>58951.43</v>
       </c>
       <c r="AA22" s="10" t="n">
         <v>0.0051</v>
@@ -3165,36 +3681,63 @@
         <v>797719</v>
       </c>
       <c r="AC22" s="9" t="n">
-        <v>48884.22</v>
+        <v>61368.52</v>
       </c>
       <c r="AD22" s="10" t="n">
-        <v>0.005</v>
+        <v>0.0054</v>
       </c>
       <c r="AE22" s="8" t="n">
         <v>797719</v>
       </c>
       <c r="AF22" s="9" t="n">
-        <v>42372.84</v>
+        <v>71347.99000000001</v>
       </c>
       <c r="AG22" s="10" t="n">
-        <v>0.0045</v>
+        <v>0.0065</v>
       </c>
       <c r="AH22" s="8" t="n">
         <v>797719</v>
       </c>
       <c r="AI22" s="9" t="n">
+        <v>52665.41</v>
+      </c>
+      <c r="AJ22" s="10" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="AK22" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AL22" s="9" t="n">
+        <v>48884.22</v>
+      </c>
+      <c r="AM22" s="10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="AN22" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AO22" s="9" t="n">
+        <v>42372.84</v>
+      </c>
+      <c r="AP22" s="10" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="AQ22" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AR22" s="9" t="n">
         <v>39819.34</v>
       </c>
-      <c r="AJ22" s="10" t="n">
+      <c r="AS22" s="10" t="n">
         <v>0.0045</v>
       </c>
-      <c r="AK22" s="8" t="n">
+      <c r="AT22" s="8" t="n">
         <v>882136</v>
       </c>
-      <c r="AL22" s="9" t="n">
+      <c r="AU22" s="9" t="n">
         <v>50572.42</v>
       </c>
-      <c r="AM22" s="10" t="n">
+      <c r="AV22" s="10" t="n">
         <v>0.0056</v>
       </c>
     </row>
@@ -3218,43 +3761,43 @@
         <v>1995914</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>37762.69</v>
+        <v>32040.41</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.0025</v>
       </c>
       <c r="G23" s="8" t="n">
         <v>1995914</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>38830.51</v>
+        <v>36543.19</v>
       </c>
       <c r="I23" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0027</v>
       </c>
       <c r="J23" s="8" t="n">
         <v>1995914</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>35076.19</v>
+        <v>35285.76</v>
       </c>
       <c r="L23" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.0026</v>
       </c>
       <c r="M23" s="8" t="n">
         <v>1995914</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>34681</v>
+        <v>37762.69</v>
       </c>
       <c r="O23" s="10" t="n">
-        <v>0.0029</v>
+        <v>0.0028</v>
       </c>
       <c r="P23" s="8" t="n">
         <v>1995914</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>35004.34</v>
+        <v>38830.51</v>
       </c>
       <c r="R23" s="10" t="n">
         <v>0.003</v>
@@ -3263,63 +3806,90 @@
         <v>1995914</v>
       </c>
       <c r="T23" s="9" t="n">
-        <v>38225.74</v>
+        <v>35076.19</v>
       </c>
       <c r="U23" s="10" t="n">
-        <v>0.0034</v>
+        <v>0.0028</v>
       </c>
       <c r="V23" s="8" t="n">
         <v>1995914</v>
       </c>
       <c r="W23" s="9" t="n">
-        <v>43319.32</v>
+        <v>34681</v>
       </c>
       <c r="X23" s="10" t="n">
-        <v>0.0039</v>
+        <v>0.0029</v>
       </c>
       <c r="Y23" s="8" t="n">
         <v>1995914</v>
       </c>
       <c r="Z23" s="9" t="n">
-        <v>34806.74</v>
+        <v>35004.34</v>
       </c>
       <c r="AA23" s="10" t="n">
-        <v>0.0034</v>
+        <v>0.003</v>
       </c>
       <c r="AB23" s="8" t="n">
         <v>1995914</v>
       </c>
       <c r="AC23" s="9" t="n">
-        <v>35138.07</v>
+        <v>38225.74</v>
       </c>
       <c r="AD23" s="10" t="n">
-        <v>0.0036</v>
+        <v>0.0034</v>
       </c>
       <c r="AE23" s="8" t="n">
         <v>1995914</v>
       </c>
       <c r="AF23" s="9" t="n">
-        <v>33771.86</v>
+        <v>43319.32</v>
       </c>
       <c r="AG23" s="10" t="n">
-        <v>0.0036</v>
+        <v>0.0039</v>
       </c>
       <c r="AH23" s="8" t="n">
         <v>1995914</v>
       </c>
       <c r="AI23" s="9" t="n">
-        <v>28830.98</v>
+        <v>34806.74</v>
       </c>
       <c r="AJ23" s="10" t="n">
-        <v>0.0033</v>
+        <v>0.0034</v>
       </c>
       <c r="AK23" s="8" t="n">
         <v>1995914</v>
       </c>
       <c r="AL23" s="9" t="n">
+        <v>35138.07</v>
+      </c>
+      <c r="AM23" s="10" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="AN23" s="8" t="n">
+        <v>1995914</v>
+      </c>
+      <c r="AO23" s="9" t="n">
+        <v>33771.86</v>
+      </c>
+      <c r="AP23" s="10" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="AQ23" s="8" t="n">
+        <v>1995914</v>
+      </c>
+      <c r="AR23" s="9" t="n">
+        <v>28830.98</v>
+      </c>
+      <c r="AS23" s="10" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="AT23" s="8" t="n">
+        <v>1995914</v>
+      </c>
+      <c r="AU23" s="9" t="n">
         <v>27686.32</v>
       </c>
-      <c r="AM23" s="10" t="n">
+      <c r="AV23" s="10" t="n">
         <v>0.0031</v>
       </c>
     </row>
@@ -3351,76 +3921,85 @@
       <c r="M24" s="8" t="n"/>
       <c r="N24" s="9" t="n"/>
       <c r="O24" s="10" t="n"/>
-      <c r="P24" s="8" t="n">
+      <c r="P24" s="8" t="n"/>
+      <c r="Q24" s="9" t="n"/>
+      <c r="R24" s="10" t="n"/>
+      <c r="S24" s="8" t="n"/>
+      <c r="T24" s="9" t="n"/>
+      <c r="U24" s="10" t="n"/>
+      <c r="V24" s="8" t="n"/>
+      <c r="W24" s="9" t="n"/>
+      <c r="X24" s="10" t="n"/>
+      <c r="Y24" s="8" t="n">
         <v>218075</v>
       </c>
-      <c r="Q24" s="9" t="n">
+      <c r="Z24" s="9" t="n">
         <v>3019.03</v>
       </c>
-      <c r="R24" s="10" t="n">
+      <c r="AA24" s="10" t="n">
         <v>0.0003</v>
       </c>
-      <c r="S24" s="8" t="n">
+      <c r="AB24" s="8" t="n">
         <v>566216</v>
       </c>
-      <c r="T24" s="9" t="n">
+      <c r="AC24" s="9" t="n">
         <v>8345.459999999999</v>
       </c>
-      <c r="U24" s="10" t="n">
+      <c r="AD24" s="10" t="n">
         <v>0.0007</v>
       </c>
-      <c r="V24" s="8" t="n">
+      <c r="AE24" s="8" t="n">
         <v>1311557</v>
       </c>
-      <c r="W24" s="9" t="n">
+      <c r="AF24" s="9" t="n">
         <v>18228.02</v>
       </c>
-      <c r="X24" s="10" t="n">
+      <c r="AG24" s="10" t="n">
         <v>0.0017</v>
       </c>
-      <c r="Y24" s="8" t="n">
+      <c r="AH24" s="8" t="n">
         <v>1641095</v>
       </c>
-      <c r="Z24" s="9" t="n">
+      <c r="AI24" s="9" t="n">
         <v>23382.32</v>
       </c>
-      <c r="AA24" s="10" t="n">
+      <c r="AJ24" s="10" t="n">
         <v>0.0023</v>
       </c>
-      <c r="AB24" s="8" t="n">
+      <c r="AK24" s="8" t="n">
         <v>1857217</v>
       </c>
-      <c r="AC24" s="9" t="n">
+      <c r="AL24" s="9" t="n">
         <v>26023.32</v>
       </c>
-      <c r="AD24" s="10" t="n">
+      <c r="AM24" s="10" t="n">
         <v>0.0026</v>
       </c>
-      <c r="AE24" s="8" t="n">
+      <c r="AN24" s="8" t="n">
         <v>1926988</v>
       </c>
-      <c r="AF24" s="9" t="n">
+      <c r="AO24" s="9" t="n">
         <v>28941.43</v>
       </c>
-      <c r="AG24" s="10" t="n">
+      <c r="AP24" s="10" t="n">
         <v>0.0031</v>
       </c>
-      <c r="AH24" s="8" t="n">
+      <c r="AQ24" s="8" t="n">
         <v>1926988</v>
       </c>
-      <c r="AI24" s="9" t="n">
+      <c r="AR24" s="9" t="n">
         <v>26117.43</v>
       </c>
-      <c r="AJ24" s="10" t="n">
+      <c r="AS24" s="10" t="n">
         <v>0.003</v>
       </c>
-      <c r="AK24" s="8" t="n">
+      <c r="AT24" s="8" t="n">
         <v>2246361</v>
       </c>
-      <c r="AL24" s="9" t="n">
+      <c r="AU24" s="9" t="n">
         <v>32421.73</v>
       </c>
-      <c r="AM24" s="10" t="n">
+      <c r="AV24" s="10" t="n">
         <v>0.0036</v>
       </c>
     </row>
@@ -3444,43 +4023,43 @@
         <v>2264603</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>32691.81</v>
+        <v>25349.97</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>0.0025</v>
+        <v>0.002</v>
       </c>
       <c r="G25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>36623.16</v>
+        <v>28810.28</v>
       </c>
       <c r="I25" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.0021</v>
       </c>
       <c r="J25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>35943.78</v>
+        <v>29897.29</v>
       </c>
       <c r="L25" s="10" t="n">
-        <v>0.0029</v>
+        <v>0.0022</v>
       </c>
       <c r="M25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>33031.5</v>
+        <v>32691.81</v>
       </c>
       <c r="O25" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.0025</v>
       </c>
       <c r="P25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>32257.01</v>
+        <v>36623.16</v>
       </c>
       <c r="R25" s="10" t="n">
         <v>0.0028</v>
@@ -3489,34 +4068,34 @@
         <v>2264603</v>
       </c>
       <c r="T25" s="9" t="n">
-        <v>33534.24</v>
+        <v>35943.78</v>
       </c>
       <c r="U25" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0029</v>
       </c>
       <c r="V25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="W25" s="9" t="n">
-        <v>40626.98</v>
+        <v>33031.5</v>
       </c>
       <c r="X25" s="10" t="n">
-        <v>0.0037</v>
+        <v>0.0028</v>
       </c>
       <c r="Y25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="Z25" s="9" t="n">
-        <v>34641.63</v>
+        <v>32257.01</v>
       </c>
       <c r="AA25" s="10" t="n">
-        <v>0.0033</v>
+        <v>0.0028</v>
       </c>
       <c r="AB25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="AC25" s="9" t="n">
-        <v>29892.76</v>
+        <v>33534.24</v>
       </c>
       <c r="AD25" s="10" t="n">
         <v>0.003</v>
@@ -3525,27 +4104,54 @@
         <v>2264603</v>
       </c>
       <c r="AF25" s="9" t="n">
-        <v>27629.29</v>
+        <v>40626.98</v>
       </c>
       <c r="AG25" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0037</v>
       </c>
       <c r="AH25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="AI25" s="9" t="n">
-        <v>25089.54</v>
+        <v>34641.63</v>
       </c>
       <c r="AJ25" s="10" t="n">
-        <v>0.0029</v>
+        <v>0.0033</v>
       </c>
       <c r="AK25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="AL25" s="9" t="n">
+        <v>29892.76</v>
+      </c>
+      <c r="AM25" s="10" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="AN25" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="AO25" s="9" t="n">
+        <v>27629.29</v>
+      </c>
+      <c r="AP25" s="10" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="AQ25" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="AR25" s="9" t="n">
+        <v>25089.54</v>
+      </c>
+      <c r="AS25" s="10" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="AT25" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="AU25" s="9" t="n">
         <v>29659.51</v>
       </c>
-      <c r="AM25" s="10" t="n">
+      <c r="AV25" s="10" t="n">
         <v>0.0033</v>
       </c>
     </row>
@@ -3566,111 +4172,138 @@
         </is>
       </c>
       <c r="D26" s="8" t="n">
+        <v>7394472</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>57344.13</v>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="G26" s="8" t="n">
+        <v>7394472</v>
+      </c>
+      <c r="H26" s="9" t="n">
+        <v>63976.97</v>
+      </c>
+      <c r="I26" s="10" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="J26" s="8" t="n">
+        <v>7362903</v>
+      </c>
+      <c r="K26" s="9" t="n">
+        <v>67966.96000000001</v>
+      </c>
+      <c r="L26" s="10" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="M26" s="8" t="n">
         <v>6180145</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="N26" s="9" t="n">
         <v>63945.96</v>
       </c>
-      <c r="F26" s="10" t="n">
+      <c r="O26" s="10" t="n">
         <v>0.0048</v>
       </c>
-      <c r="G26" s="8" t="n">
+      <c r="P26" s="8" t="n">
         <v>5842830</v>
       </c>
-      <c r="H26" s="9" t="n">
+      <c r="Q26" s="9" t="n">
         <v>60233.73</v>
       </c>
-      <c r="I26" s="10" t="n">
+      <c r="R26" s="10" t="n">
         <v>0.0046</v>
       </c>
-      <c r="J26" s="8" t="n">
+      <c r="S26" s="8" t="n">
         <v>5528341</v>
       </c>
-      <c r="K26" s="9" t="n">
+      <c r="T26" s="9" t="n">
         <v>59285.93</v>
       </c>
-      <c r="L26" s="10" t="n">
+      <c r="U26" s="10" t="n">
         <v>0.0047</v>
       </c>
-      <c r="M26" s="8" t="n">
+      <c r="V26" s="8" t="n">
         <v>4996218</v>
       </c>
-      <c r="N26" s="9" t="n">
+      <c r="W26" s="9" t="n">
         <v>51236.22</v>
       </c>
-      <c r="O26" s="10" t="n">
+      <c r="X26" s="10" t="n">
         <v>0.0043</v>
       </c>
-      <c r="P26" s="8" t="n">
+      <c r="Y26" s="8" t="n">
         <v>4433570</v>
       </c>
-      <c r="Q26" s="9" t="n">
+      <c r="Z26" s="9" t="n">
         <v>49913.13</v>
       </c>
-      <c r="R26" s="10" t="n">
+      <c r="AA26" s="10" t="n">
         <v>0.0043</v>
       </c>
-      <c r="S26" s="8" t="n">
+      <c r="AB26" s="8" t="n">
         <v>3997165</v>
       </c>
-      <c r="T26" s="9" t="n">
+      <c r="AC26" s="9" t="n">
         <v>49305.03</v>
       </c>
-      <c r="U26" s="10" t="n">
+      <c r="AD26" s="10" t="n">
         <v>0.0044</v>
       </c>
-      <c r="V26" s="8" t="n">
+      <c r="AE26" s="8" t="n">
         <v>3516819</v>
       </c>
-      <c r="W26" s="9" t="n">
+      <c r="AF26" s="9" t="n">
         <v>39036.69</v>
       </c>
-      <c r="X26" s="10" t="n">
+      <c r="AG26" s="10" t="n">
         <v>0.0035</v>
       </c>
-      <c r="Y26" s="8" t="n">
+      <c r="AH26" s="8" t="n">
         <v>3243008</v>
       </c>
-      <c r="Z26" s="9" t="n">
+      <c r="AI26" s="9" t="n">
         <v>30813.44</v>
       </c>
-      <c r="AA26" s="10" t="n">
+      <c r="AJ26" s="10" t="n">
         <v>0.003</v>
       </c>
-      <c r="AB26" s="8" t="n">
+      <c r="AK26" s="8" t="n">
         <v>2988209</v>
       </c>
-      <c r="AC26" s="9" t="n">
+      <c r="AL26" s="9" t="n">
         <v>24424.13</v>
       </c>
-      <c r="AD26" s="10" t="n">
+      <c r="AM26" s="10" t="n">
         <v>0.0025</v>
       </c>
-      <c r="AE26" s="8" t="n">
+      <c r="AN26" s="8" t="n">
         <v>2843265</v>
       </c>
-      <c r="AF26" s="9" t="n">
+      <c r="AO26" s="9" t="n">
         <v>22336.69</v>
       </c>
-      <c r="AG26" s="10" t="n">
+      <c r="AP26" s="10" t="n">
         <v>0.0024</v>
       </c>
-      <c r="AH26" s="8" t="n">
+      <c r="AQ26" s="8" t="n">
         <v>2609056</v>
       </c>
-      <c r="AI26" s="9" t="n">
+      <c r="AR26" s="9" t="n">
         <v>17326.74</v>
       </c>
-      <c r="AJ26" s="10" t="n">
+      <c r="AS26" s="10" t="n">
         <v>0.002</v>
       </c>
-      <c r="AK26" s="8" t="n">
+      <c r="AT26" s="8" t="n">
         <v>2259531</v>
       </c>
-      <c r="AL26" s="9" t="n">
+      <c r="AU26" s="9" t="n">
         <v>18525.89</v>
       </c>
-      <c r="AM26" s="10" t="n">
+      <c r="AV26" s="10" t="n">
         <v>0.0021</v>
       </c>
     </row>
@@ -3717,31 +4350,40 @@
       <c r="AB27" s="8" t="n"/>
       <c r="AC27" s="9" t="n"/>
       <c r="AD27" s="10" t="n"/>
-      <c r="AE27" s="8" t="n">
+      <c r="AE27" s="8" t="n"/>
+      <c r="AF27" s="9" t="n"/>
+      <c r="AG27" s="10" t="n"/>
+      <c r="AH27" s="8" t="n"/>
+      <c r="AI27" s="9" t="n"/>
+      <c r="AJ27" s="10" t="n"/>
+      <c r="AK27" s="8" t="n"/>
+      <c r="AL27" s="9" t="n"/>
+      <c r="AM27" s="10" t="n"/>
+      <c r="AN27" s="8" t="n">
         <v>9899412</v>
       </c>
-      <c r="AF27" s="9" t="n">
+      <c r="AO27" s="9" t="n">
         <v>19552.33</v>
       </c>
-      <c r="AG27" s="10" t="n">
+      <c r="AP27" s="10" t="n">
         <v>0.0021</v>
       </c>
-      <c r="AH27" s="8" t="n">
+      <c r="AQ27" s="8" t="n">
         <v>9899412</v>
       </c>
-      <c r="AI27" s="9" t="n">
+      <c r="AR27" s="9" t="n">
         <v>16216.23</v>
       </c>
-      <c r="AJ27" s="10" t="n">
+      <c r="AS27" s="10" t="n">
         <v>0.0018</v>
       </c>
-      <c r="AK27" s="8" t="n">
+      <c r="AT27" s="8" t="n">
         <v>9899412</v>
       </c>
-      <c r="AL27" s="9" t="n">
+      <c r="AU27" s="9" t="n">
         <v>16131.09</v>
       </c>
-      <c r="AM27" s="10" t="n">
+      <c r="AV27" s="10" t="n">
         <v>0.0018</v>
       </c>
     </row>
@@ -3765,108 +4407,135 @@
         <v>287393</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>17460.56</v>
+        <v>14378.27</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>0.0013</v>
+        <v>0.0011</v>
       </c>
       <c r="G28" s="8" t="n">
         <v>287393</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>17812.62</v>
+        <v>15895.71</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>0.0014</v>
+        <v>0.0012</v>
       </c>
       <c r="J28" s="8" t="n">
         <v>287393</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>18463.56</v>
+        <v>18124.44</v>
       </c>
       <c r="L28" s="10" t="n">
-        <v>0.0015</v>
+        <v>0.0014</v>
       </c>
       <c r="M28" s="8" t="n">
         <v>287393</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>18243.71</v>
+        <v>17460.56</v>
       </c>
       <c r="O28" s="10" t="n">
-        <v>0.0015</v>
+        <v>0.0013</v>
       </c>
       <c r="P28" s="8" t="n">
         <v>287393</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>17962.06</v>
+        <v>17812.62</v>
       </c>
       <c r="R28" s="10" t="n">
-        <v>0.0016</v>
+        <v>0.0014</v>
       </c>
       <c r="S28" s="8" t="n">
         <v>287393</v>
       </c>
       <c r="T28" s="9" t="n">
-        <v>19048.41</v>
+        <v>18463.56</v>
       </c>
       <c r="U28" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.0015</v>
       </c>
       <c r="V28" s="8" t="n">
         <v>287393</v>
       </c>
       <c r="W28" s="9" t="n">
-        <v>19453.63</v>
+        <v>18243.71</v>
       </c>
       <c r="X28" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.0015</v>
       </c>
       <c r="Y28" s="8" t="n">
         <v>287393</v>
       </c>
       <c r="Z28" s="9" t="n">
-        <v>19370.29</v>
+        <v>17962.06</v>
       </c>
       <c r="AA28" s="10" t="n">
-        <v>0.0019</v>
+        <v>0.0016</v>
       </c>
       <c r="AB28" s="8" t="n">
         <v>287393</v>
       </c>
       <c r="AC28" s="9" t="n">
-        <v>15976.18</v>
+        <v>19048.41</v>
       </c>
       <c r="AD28" s="10" t="n">
-        <v>0.0016</v>
+        <v>0.0017</v>
       </c>
       <c r="AE28" s="8" t="n">
         <v>287393</v>
       </c>
       <c r="AF28" s="9" t="n">
-        <v>15821.13</v>
+        <v>19453.63</v>
       </c>
       <c r="AG28" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.0018</v>
       </c>
       <c r="AH28" s="8" t="n">
         <v>287393</v>
       </c>
       <c r="AI28" s="9" t="n">
+        <v>19370.29</v>
+      </c>
+      <c r="AJ28" s="10" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="AK28" s="8" t="n">
+        <v>287393</v>
+      </c>
+      <c r="AL28" s="9" t="n">
+        <v>15976.18</v>
+      </c>
+      <c r="AM28" s="10" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="AN28" s="8" t="n">
+        <v>287393</v>
+      </c>
+      <c r="AO28" s="9" t="n">
+        <v>15821.13</v>
+      </c>
+      <c r="AP28" s="10" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="AQ28" s="8" t="n">
+        <v>287393</v>
+      </c>
+      <c r="AR28" s="9" t="n">
         <v>15273.64</v>
       </c>
-      <c r="AJ28" s="10" t="n">
+      <c r="AS28" s="10" t="n">
         <v>0.0017</v>
       </c>
-      <c r="AK28" s="8" t="n">
+      <c r="AT28" s="8" t="n">
         <v>297835</v>
       </c>
-      <c r="AL28" s="9" t="n">
+      <c r="AU28" s="9" t="n">
         <v>18529.51</v>
       </c>
-      <c r="AM28" s="10" t="n">
+      <c r="AV28" s="10" t="n">
         <v>0.0021</v>
       </c>
     </row>
@@ -3887,111 +4556,138 @@
         </is>
       </c>
       <c r="D29" s="8" t="n">
-        <v>80159</v>
+        <v>80565</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>11401.01</v>
+        <v>8949.969999999999</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>0.0009</v>
+        <v>0.0007</v>
       </c>
       <c r="G29" s="8" t="n">
-        <v>80159</v>
+        <v>80565</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>11787.38</v>
+        <v>10682.11</v>
       </c>
       <c r="I29" s="10" t="n">
-        <v>0.0009</v>
+        <v>0.0008</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>80159</v>
+        <v>80552</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>12110.42</v>
+        <v>10825.38</v>
       </c>
       <c r="L29" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0008</v>
       </c>
       <c r="M29" s="8" t="n">
         <v>80159</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>13825.82</v>
+        <v>11401.01</v>
       </c>
       <c r="O29" s="10" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="P29" s="8" t="n">
         <v>80159</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>12726.04</v>
+        <v>11787.38</v>
       </c>
       <c r="R29" s="10" t="n">
-        <v>0.0011</v>
+        <v>0.0009</v>
       </c>
       <c r="S29" s="8" t="n">
         <v>80159</v>
       </c>
       <c r="T29" s="9" t="n">
-        <v>12868.73</v>
+        <v>12110.42</v>
       </c>
       <c r="U29" s="10" t="n">
-        <v>0.0011</v>
+        <v>0.001</v>
       </c>
       <c r="V29" s="8" t="n">
         <v>80159</v>
       </c>
       <c r="W29" s="9" t="n">
-        <v>11621.45</v>
+        <v>13825.82</v>
       </c>
       <c r="X29" s="10" t="n">
-        <v>0.0011</v>
+        <v>0.0012</v>
       </c>
       <c r="Y29" s="8" t="n">
         <v>80159</v>
       </c>
       <c r="Z29" s="9" t="n">
-        <v>10722.07</v>
+        <v>12726.04</v>
       </c>
       <c r="AA29" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0011</v>
       </c>
       <c r="AB29" s="8" t="n">
         <v>80159</v>
       </c>
       <c r="AC29" s="9" t="n">
-        <v>9198.25</v>
+        <v>12868.73</v>
       </c>
       <c r="AD29" s="10" t="n">
-        <v>0.0009</v>
+        <v>0.0011</v>
       </c>
       <c r="AE29" s="8" t="n">
         <v>80159</v>
       </c>
       <c r="AF29" s="9" t="n">
-        <v>8997.450000000001</v>
+        <v>11621.45</v>
       </c>
       <c r="AG29" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0011</v>
       </c>
       <c r="AH29" s="8" t="n">
         <v>80159</v>
       </c>
       <c r="AI29" s="9" t="n">
-        <v>7401.52</v>
+        <v>10722.07</v>
       </c>
       <c r="AJ29" s="10" t="n">
-        <v>0.0008</v>
+        <v>0.001</v>
       </c>
       <c r="AK29" s="8" t="n">
         <v>80159</v>
       </c>
       <c r="AL29" s="9" t="n">
+        <v>9198.25</v>
+      </c>
+      <c r="AM29" s="10" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="AN29" s="8" t="n">
+        <v>80159</v>
+      </c>
+      <c r="AO29" s="9" t="n">
+        <v>8997.450000000001</v>
+      </c>
+      <c r="AP29" s="10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AQ29" s="8" t="n">
+        <v>80159</v>
+      </c>
+      <c r="AR29" s="9" t="n">
+        <v>7401.52</v>
+      </c>
+      <c r="AS29" s="10" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="AT29" s="8" t="n">
+        <v>80159</v>
+      </c>
+      <c r="AU29" s="9" t="n">
         <v>7463.48</v>
       </c>
-      <c r="AM29" s="10" t="n">
+      <c r="AV29" s="10" t="n">
         <v>0.0008</v>
       </c>
     </row>
@@ -4015,7 +4711,7 @@
         <v>47293</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>1691.91</v>
+        <v>1564.88</v>
       </c>
       <c r="F30" s="10" t="n">
         <v>0.0001</v>
@@ -4024,7 +4720,7 @@
         <v>47293</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>1764.08</v>
+        <v>1700.33</v>
       </c>
       <c r="I30" s="10" t="n">
         <v>0.0001</v>
@@ -4033,34 +4729,34 @@
         <v>47293</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>1892.15</v>
+        <v>1637.61</v>
       </c>
       <c r="L30" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="M30" s="8" t="n">
         <v>47293</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>1955.38</v>
+        <v>1691.91</v>
       </c>
       <c r="O30" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="P30" s="8" t="n">
         <v>47293</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>1897.21</v>
+        <v>1764.08</v>
       </c>
       <c r="R30" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="S30" s="8" t="n">
         <v>47293</v>
       </c>
       <c r="T30" s="9" t="n">
-        <v>1983.66</v>
+        <v>1892.15</v>
       </c>
       <c r="U30" s="10" t="n">
         <v>0.0002</v>
@@ -4069,7 +4765,7 @@
         <v>47293</v>
       </c>
       <c r="W30" s="9" t="n">
-        <v>1867.41</v>
+        <v>1955.38</v>
       </c>
       <c r="X30" s="10" t="n">
         <v>0.0002</v>
@@ -4078,7 +4774,7 @@
         <v>47293</v>
       </c>
       <c r="Z30" s="9" t="n">
-        <v>1857.76</v>
+        <v>1897.21</v>
       </c>
       <c r="AA30" s="10" t="n">
         <v>0.0002</v>
@@ -4087,7 +4783,7 @@
         <v>47293</v>
       </c>
       <c r="AC30" s="9" t="n">
-        <v>1925.39</v>
+        <v>1983.66</v>
       </c>
       <c r="AD30" s="10" t="n">
         <v>0.0002</v>
@@ -4096,7 +4792,7 @@
         <v>47293</v>
       </c>
       <c r="AF30" s="9" t="n">
-        <v>1844.17</v>
+        <v>1867.41</v>
       </c>
       <c r="AG30" s="10" t="n">
         <v>0.0002</v>
@@ -4105,18 +4801,45 @@
         <v>47293</v>
       </c>
       <c r="AI30" s="9" t="n">
-        <v>1236.83</v>
+        <v>1857.76</v>
       </c>
       <c r="AJ30" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="AK30" s="8" t="n">
         <v>47293</v>
       </c>
       <c r="AL30" s="9" t="n">
+        <v>1925.39</v>
+      </c>
+      <c r="AM30" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AN30" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="AO30" s="9" t="n">
+        <v>1844.17</v>
+      </c>
+      <c r="AP30" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AQ30" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="AR30" s="9" t="n">
+        <v>1236.83</v>
+      </c>
+      <c r="AS30" s="10" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AT30" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="AU30" s="9" t="n">
         <v>1612.64</v>
       </c>
-      <c r="AM30" s="10" t="n">
+      <c r="AV30" s="10" t="n">
         <v>0.0002</v>
       </c>
     </row>
@@ -4140,7 +4863,7 @@
         <v>151687</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>1858.32</v>
+        <v>1538.11</v>
       </c>
       <c r="F31" s="10" t="n">
         <v>0.0001</v>
@@ -4149,34 +4872,34 @@
         <v>151687</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>1947.66</v>
+        <v>1704.36</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="J31" s="8" t="n">
         <v>151687</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>2076.6</v>
+        <v>1728.63</v>
       </c>
       <c r="L31" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="M31" s="8" t="n">
         <v>151687</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>1987.1</v>
+        <v>1858.32</v>
       </c>
       <c r="O31" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="P31" s="8" t="n">
         <v>151687</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>2130.6</v>
+        <v>1947.66</v>
       </c>
       <c r="R31" s="10" t="n">
         <v>0.0002</v>
@@ -4185,7 +4908,7 @@
         <v>151687</v>
       </c>
       <c r="T31" s="9" t="n">
-        <v>2091.16</v>
+        <v>2076.6</v>
       </c>
       <c r="U31" s="10" t="n">
         <v>0.0002</v>
@@ -4194,32 +4917,59 @@
         <v>151687</v>
       </c>
       <c r="W31" s="9" t="n">
-        <v>1766.62</v>
+        <v>1987.1</v>
       </c>
       <c r="X31" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="Y31" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="Z31" s="9" t="n">
+        <v>2130.6</v>
+      </c>
+      <c r="AA31" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AB31" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AC31" s="9" t="n">
+        <v>2091.16</v>
+      </c>
+      <c r="AD31" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AE31" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AF31" s="9" t="n">
+        <v>1766.62</v>
+      </c>
+      <c r="AG31" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AH31" s="8" t="n">
         <v>89469</v>
       </c>
-      <c r="Z31" s="9" t="n">
+      <c r="AI31" s="9" t="n">
         <v>828.48</v>
       </c>
-      <c r="AA31" s="10" t="n">
+      <c r="AJ31" s="10" t="n">
         <v>0.0001</v>
       </c>
-      <c r="AB31" s="8" t="n"/>
-      <c r="AC31" s="9" t="n"/>
-      <c r="AD31" s="10" t="n"/>
-      <c r="AE31" s="8" t="n"/>
-      <c r="AF31" s="9" t="n"/>
-      <c r="AG31" s="10" t="n"/>
-      <c r="AH31" s="8" t="n"/>
-      <c r="AI31" s="9" t="n"/>
-      <c r="AJ31" s="10" t="n"/>
       <c r="AK31" s="8" t="n"/>
       <c r="AL31" s="9" t="n"/>
       <c r="AM31" s="10" t="n"/>
+      <c r="AN31" s="8" t="n"/>
+      <c r="AO31" s="9" t="n"/>
+      <c r="AP31" s="10" t="n"/>
+      <c r="AQ31" s="8" t="n"/>
+      <c r="AR31" s="9" t="n"/>
+      <c r="AS31" s="10" t="n"/>
+      <c r="AT31" s="8" t="n"/>
+      <c r="AU31" s="9" t="n"/>
+      <c r="AV31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -4241,86 +4991,113 @@
         <v>21167034</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>445693.07</v>
+        <v>377281.21</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>0.0334</v>
+        <v>0.0293</v>
       </c>
       <c r="G32" s="8" t="n">
         <v>21167034</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>444846.39</v>
+        <v>397792.07</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>0.0343</v>
+        <v>0.0296</v>
       </c>
       <c r="J32" s="8" t="n">
         <v>21167034</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>434876.71</v>
+        <v>416715.398358</v>
       </c>
       <c r="L32" s="10" t="n">
-        <v>0.0346</v>
+        <v>0.0311051731198606</v>
       </c>
       <c r="M32" s="8" t="n">
         <v>21167034</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>397601.57</v>
+        <v>445693.07</v>
       </c>
       <c r="O32" s="10" t="n">
-        <v>0.0332</v>
+        <v>0.0334</v>
       </c>
       <c r="P32" s="8" t="n">
         <v>21167034</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>399802.94</v>
+        <v>444846.39</v>
       </c>
       <c r="R32" s="10" t="n">
-        <v>0.0348</v>
+        <v>0.0343</v>
       </c>
       <c r="S32" s="8" t="n">
         <v>21167034</v>
       </c>
       <c r="T32" s="9" t="n">
+        <v>434876.71</v>
+      </c>
+      <c r="U32" s="10" t="n">
+        <v>0.0346</v>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v>21167034</v>
+      </c>
+      <c r="W32" s="9" t="n">
+        <v>397601.57</v>
+      </c>
+      <c r="X32" s="10" t="n">
+        <v>0.0332</v>
+      </c>
+      <c r="Y32" s="8" t="n">
+        <v>21167034</v>
+      </c>
+      <c r="Z32" s="9" t="n">
+        <v>399802.94</v>
+      </c>
+      <c r="AA32" s="10" t="n">
+        <v>0.0348</v>
+      </c>
+      <c r="AB32" s="8" t="n">
+        <v>21167034</v>
+      </c>
+      <c r="AC32" s="9" t="n">
         <v>405200.53</v>
       </c>
-      <c r="U32" s="10" t="n">
+      <c r="AD32" s="10" t="n">
         <v>0.0358</v>
       </c>
-      <c r="V32" s="8" t="n">
+      <c r="AE32" s="8" t="n">
         <v>20937034</v>
       </c>
-      <c r="W32" s="9" t="n">
+      <c r="AF32" s="9" t="n">
         <v>420750.64</v>
       </c>
-      <c r="X32" s="10" t="n">
+      <c r="AG32" s="10" t="n">
         <v>0.0381</v>
       </c>
-      <c r="Y32" s="8" t="n">
+      <c r="AH32" s="8" t="n">
         <v>11799076</v>
       </c>
-      <c r="Z32" s="9" t="n">
+      <c r="AI32" s="9" t="n">
         <v>219014.45</v>
       </c>
-      <c r="AA32" s="10" t="n">
+      <c r="AJ32" s="10" t="n">
         <v>0.0211</v>
       </c>
-      <c r="AB32" s="8" t="n"/>
-      <c r="AC32" s="9" t="n"/>
-      <c r="AD32" s="10" t="n"/>
-      <c r="AE32" s="8" t="n"/>
-      <c r="AF32" s="9" t="n"/>
-      <c r="AG32" s="10" t="n"/>
-      <c r="AH32" s="8" t="n"/>
-      <c r="AI32" s="9" t="n"/>
-      <c r="AJ32" s="10" t="n"/>
       <c r="AK32" s="8" t="n"/>
       <c r="AL32" s="9" t="n"/>
       <c r="AM32" s="10" t="n"/>
+      <c r="AN32" s="8" t="n"/>
+      <c r="AO32" s="9" t="n"/>
+      <c r="AP32" s="10" t="n"/>
+      <c r="AQ32" s="8" t="n"/>
+      <c r="AR32" s="9" t="n"/>
+      <c r="AS32" s="10" t="n"/>
+      <c r="AT32" s="8" t="n"/>
+      <c r="AU32" s="9" t="n"/>
+      <c r="AV32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -4350,48 +5127,57 @@
       <c r="M33" s="8" t="n"/>
       <c r="N33" s="9" t="n"/>
       <c r="O33" s="10" t="n"/>
-      <c r="P33" s="8" t="n">
+      <c r="P33" s="8" t="n"/>
+      <c r="Q33" s="9" t="n"/>
+      <c r="R33" s="10" t="n"/>
+      <c r="S33" s="8" t="n"/>
+      <c r="T33" s="9" t="n"/>
+      <c r="U33" s="10" t="n"/>
+      <c r="V33" s="8" t="n"/>
+      <c r="W33" s="9" t="n"/>
+      <c r="X33" s="10" t="n"/>
+      <c r="Y33" s="8" t="n">
         <v>4400000</v>
       </c>
-      <c r="Q33" s="9" t="n">
+      <c r="Z33" s="9" t="n">
         <v>88822.8</v>
       </c>
-      <c r="R33" s="10" t="n">
+      <c r="AA33" s="10" t="n">
         <v>0.0077</v>
       </c>
-      <c r="S33" s="8" t="n">
+      <c r="AB33" s="8" t="n">
         <v>4400000</v>
       </c>
-      <c r="T33" s="9" t="n">
+      <c r="AC33" s="9" t="n">
         <v>89280.39999999999</v>
       </c>
-      <c r="U33" s="10" t="n">
+      <c r="AD33" s="10" t="n">
         <v>0.007900000000000001</v>
       </c>
-      <c r="V33" s="8" t="n">
+      <c r="AE33" s="8" t="n">
         <v>4400000</v>
       </c>
-      <c r="W33" s="9" t="n">
+      <c r="AF33" s="9" t="n">
         <v>89020.8</v>
       </c>
-      <c r="X33" s="10" t="n">
+      <c r="AG33" s="10" t="n">
         <v>0.0081</v>
       </c>
-      <c r="Y33" s="8" t="n"/>
-      <c r="Z33" s="9" t="n"/>
-      <c r="AA33" s="10" t="n"/>
-      <c r="AB33" s="8" t="n"/>
-      <c r="AC33" s="9" t="n"/>
-      <c r="AD33" s="10" t="n"/>
-      <c r="AE33" s="8" t="n"/>
-      <c r="AF33" s="9" t="n"/>
-      <c r="AG33" s="10" t="n"/>
       <c r="AH33" s="8" t="n"/>
       <c r="AI33" s="9" t="n"/>
       <c r="AJ33" s="10" t="n"/>
       <c r="AK33" s="8" t="n"/>
       <c r="AL33" s="9" t="n"/>
       <c r="AM33" s="10" t="n"/>
+      <c r="AN33" s="8" t="n"/>
+      <c r="AO33" s="9" t="n"/>
+      <c r="AP33" s="10" t="n"/>
+      <c r="AQ33" s="8" t="n"/>
+      <c r="AR33" s="9" t="n"/>
+      <c r="AS33" s="10" t="n"/>
+      <c r="AT33" s="8" t="n"/>
+      <c r="AU33" s="9" t="n"/>
+      <c r="AV33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -4410,32 +5196,50 @@
         </is>
       </c>
       <c r="D34" s="8" t="n">
+        <v>12412184</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>292791.01</v>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="G34" s="8" t="n">
+        <v>10378056</v>
+      </c>
+      <c r="H34" s="9" t="n">
+        <v>273710.85</v>
+      </c>
+      <c r="I34" s="10" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="J34" s="8" t="n">
+        <v>8465650</v>
+      </c>
+      <c r="K34" s="9" t="n">
+        <v>264458.44</v>
+      </c>
+      <c r="L34" s="10" t="n">
+        <v>0.0197</v>
+      </c>
+      <c r="M34" s="8" t="n">
         <v>4654589</v>
       </c>
-      <c r="E34" s="9" t="n">
+      <c r="N34" s="9" t="n">
         <v>149235.43</v>
       </c>
-      <c r="F34" s="10" t="n">
+      <c r="O34" s="10" t="n">
         <v>0.0112</v>
       </c>
-      <c r="G34" s="8" t="n">
+      <c r="P34" s="8" t="n">
         <v>2811139</v>
       </c>
-      <c r="H34" s="9" t="n">
+      <c r="Q34" s="9" t="n">
         <v>88199.49000000001</v>
       </c>
-      <c r="I34" s="10" t="n">
+      <c r="R34" s="10" t="n">
         <v>0.0068</v>
       </c>
-      <c r="J34" s="8" t="n"/>
-      <c r="K34" s="9" t="n"/>
-      <c r="L34" s="10" t="n"/>
-      <c r="M34" s="8" t="n"/>
-      <c r="N34" s="9" t="n"/>
-      <c r="O34" s="10" t="n"/>
-      <c r="P34" s="8" t="n"/>
-      <c r="Q34" s="9" t="n"/>
-      <c r="R34" s="10" t="n"/>
       <c r="S34" s="8" t="n"/>
       <c r="T34" s="9" t="n"/>
       <c r="U34" s="10" t="n"/>
@@ -4457,6 +5261,15 @@
       <c r="AK34" s="8" t="n"/>
       <c r="AL34" s="9" t="n"/>
       <c r="AM34" s="10" t="n"/>
+      <c r="AN34" s="8" t="n"/>
+      <c r="AO34" s="9" t="n"/>
+      <c r="AP34" s="10" t="n"/>
+      <c r="AQ34" s="8" t="n"/>
+      <c r="AR34" s="9" t="n"/>
+      <c r="AS34" s="10" t="n"/>
+      <c r="AT34" s="8" t="n"/>
+      <c r="AU34" s="9" t="n"/>
+      <c r="AV34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -4475,50 +5288,68 @@
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>22000000</v>
+        <v>22157154</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>100012</v>
+        <v>94467.03</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>0.0075</v>
+        <v>0.0073</v>
       </c>
       <c r="G35" s="8" t="n">
-        <v>22000000</v>
+        <v>22075063</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>94699</v>
+        <v>84966.92</v>
       </c>
       <c r="I35" s="10" t="n">
-        <v>0.0073</v>
+        <v>0.0063</v>
       </c>
       <c r="J35" s="8" t="n">
         <v>22000000</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>104852</v>
+        <v>98626</v>
       </c>
       <c r="L35" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.0074</v>
       </c>
       <c r="M35" s="8" t="n">
         <v>22000000</v>
       </c>
       <c r="N35" s="9" t="n">
+        <v>100012</v>
+      </c>
+      <c r="O35" s="10" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="P35" s="8" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="Q35" s="9" t="n">
+        <v>94699</v>
+      </c>
+      <c r="R35" s="10" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="S35" s="8" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="T35" s="9" t="n">
+        <v>104852</v>
+      </c>
+      <c r="U35" s="10" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="W35" s="9" t="n">
         <v>100584</v>
       </c>
-      <c r="O35" s="10" t="n">
+      <c r="X35" s="10" t="n">
         <v>0.008399999999999999</v>
       </c>
-      <c r="P35" s="8" t="n"/>
-      <c r="Q35" s="9" t="n"/>
-      <c r="R35" s="10" t="n"/>
-      <c r="S35" s="8" t="n"/>
-      <c r="T35" s="9" t="n"/>
-      <c r="U35" s="10" t="n"/>
-      <c r="V35" s="8" t="n"/>
-      <c r="W35" s="9" t="n"/>
-      <c r="X35" s="10" t="n"/>
       <c r="Y35" s="8" t="n"/>
       <c r="Z35" s="9" t="n"/>
       <c r="AA35" s="10" t="n"/>
@@ -4534,6 +5365,15 @@
       <c r="AK35" s="8" t="n"/>
       <c r="AL35" s="9" t="n"/>
       <c r="AM35" s="10" t="n"/>
+      <c r="AN35" s="8" t="n"/>
+      <c r="AO35" s="9" t="n"/>
+      <c r="AP35" s="10" t="n"/>
+      <c r="AQ35" s="8" t="n"/>
+      <c r="AR35" s="9" t="n"/>
+      <c r="AS35" s="10" t="n"/>
+      <c r="AT35" s="8" t="n"/>
+      <c r="AU35" s="9" t="n"/>
+      <c r="AV35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -4552,23 +5392,41 @@
         </is>
       </c>
       <c r="D36" s="8" t="n">
+        <v>2205298</v>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>31198.35</v>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="G36" s="8" t="n">
+        <v>2205298</v>
+      </c>
+      <c r="H36" s="9" t="n">
+        <v>29526.73</v>
+      </c>
+      <c r="I36" s="10" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="J36" s="8" t="n">
+        <v>2205298</v>
+      </c>
+      <c r="K36" s="9" t="n">
+        <v>26516.5</v>
+      </c>
+      <c r="L36" s="10" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="M36" s="8" t="n">
         <v>1657424</v>
       </c>
-      <c r="E36" s="9" t="n">
+      <c r="N36" s="9" t="n">
         <v>18712.32</v>
       </c>
-      <c r="F36" s="10" t="n">
+      <c r="O36" s="10" t="n">
         <v>0.0014</v>
       </c>
-      <c r="G36" s="8" t="n"/>
-      <c r="H36" s="9" t="n"/>
-      <c r="I36" s="10" t="n"/>
-      <c r="J36" s="8" t="n"/>
-      <c r="K36" s="9" t="n"/>
-      <c r="L36" s="10" t="n"/>
-      <c r="M36" s="8" t="n"/>
-      <c r="N36" s="9" t="n"/>
-      <c r="O36" s="10" t="n"/>
       <c r="P36" s="8" t="n"/>
       <c r="Q36" s="9" t="n"/>
       <c r="R36" s="10" t="n"/>
@@ -4593,6 +5451,15 @@
       <c r="AK36" s="8" t="n"/>
       <c r="AL36" s="9" t="n"/>
       <c r="AM36" s="10" t="n"/>
+      <c r="AN36" s="8" t="n"/>
+      <c r="AO36" s="9" t="n"/>
+      <c r="AP36" s="10" t="n"/>
+      <c r="AQ36" s="8" t="n"/>
+      <c r="AR36" s="9" t="n"/>
+      <c r="AS36" s="10" t="n"/>
+      <c r="AT36" s="8" t="n"/>
+      <c r="AU36" s="9" t="n"/>
+      <c r="AV36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -4614,7 +5481,7 @@
         <v>710855</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>2976.71</v>
+        <v>2972.44</v>
       </c>
       <c r="F37" s="10" t="n">
         <v>0.0002</v>
@@ -4623,20 +5490,38 @@
         <v>710855</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>2850.8839775</v>
+        <v>3234.03</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>0.0002</v>
       </c>
-      <c r="J37" s="8" t="n"/>
-      <c r="K37" s="9" t="n"/>
-      <c r="L37" s="10" t="n"/>
-      <c r="M37" s="8" t="n"/>
-      <c r="N37" s="9" t="n"/>
-      <c r="O37" s="10" t="n"/>
-      <c r="P37" s="8" t="n"/>
-      <c r="Q37" s="9" t="n"/>
-      <c r="R37" s="10" t="n"/>
+      <c r="J37" s="8" t="n">
+        <v>710855</v>
+      </c>
+      <c r="K37" s="9" t="n">
+        <v>3158.33</v>
+      </c>
+      <c r="L37" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="M37" s="8" t="n">
+        <v>710855</v>
+      </c>
+      <c r="N37" s="9" t="n">
+        <v>2976.71</v>
+      </c>
+      <c r="O37" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P37" s="8" t="n">
+        <v>710855</v>
+      </c>
+      <c r="Q37" s="9" t="n">
+        <v>2850.8839775</v>
+      </c>
+      <c r="R37" s="10" t="n">
+        <v>0.0002</v>
+      </c>
       <c r="S37" s="8" t="n"/>
       <c r="T37" s="9" t="n"/>
       <c r="U37" s="10" t="n"/>
@@ -4658,135 +5543,630 @@
       <c r="AK37" s="8" t="n"/>
       <c r="AL37" s="9" t="n"/>
       <c r="AM37" s="10" t="n"/>
+      <c r="AN37" s="8" t="n"/>
+      <c r="AO37" s="9" t="n"/>
+      <c r="AP37" s="10" t="n"/>
+      <c r="AQ37" s="8" t="n"/>
+      <c r="AR37" s="9" t="n"/>
+      <c r="AS37" s="10" t="n"/>
+      <c r="AT37" s="8" t="n"/>
+      <c r="AU37" s="9" t="n"/>
+      <c r="AV37" s="10" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Kotak Mahindra Bank Limited</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>INE237A01036</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Banks</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>146607960</v>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>518112.53</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>0.0402</v>
+      </c>
+      <c r="G38" s="8" t="n">
+        <v>123107960</v>
+      </c>
+      <c r="H38" s="9" t="n">
+        <v>511144.25</v>
+      </c>
+      <c r="I38" s="10" t="n">
+        <v>0.0381</v>
+      </c>
+      <c r="J38" s="8" t="n">
+        <v>123107960</v>
+      </c>
+      <c r="K38" s="9" t="n">
+        <v>502280.48</v>
+      </c>
+      <c r="L38" s="10" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="M38" s="8" t="n"/>
+      <c r="N38" s="9" t="n"/>
+      <c r="O38" s="10" t="n"/>
+      <c r="P38" s="8" t="n"/>
+      <c r="Q38" s="9" t="n"/>
+      <c r="R38" s="10" t="n"/>
+      <c r="S38" s="8" t="n"/>
+      <c r="T38" s="9" t="n"/>
+      <c r="U38" s="10" t="n"/>
+      <c r="V38" s="8" t="n"/>
+      <c r="W38" s="9" t="n"/>
+      <c r="X38" s="10" t="n"/>
+      <c r="Y38" s="8" t="n"/>
+      <c r="Z38" s="9" t="n"/>
+      <c r="AA38" s="10" t="n"/>
+      <c r="AB38" s="8" t="n"/>
+      <c r="AC38" s="9" t="n"/>
+      <c r="AD38" s="10" t="n"/>
+      <c r="AE38" s="8" t="n"/>
+      <c r="AF38" s="9" t="n"/>
+      <c r="AG38" s="10" t="n"/>
+      <c r="AH38" s="8" t="n"/>
+      <c r="AI38" s="9" t="n"/>
+      <c r="AJ38" s="10" t="n"/>
+      <c r="AK38" s="8" t="n"/>
+      <c r="AL38" s="9" t="n"/>
+      <c r="AM38" s="10" t="n"/>
+      <c r="AN38" s="8" t="n"/>
+      <c r="AO38" s="9" t="n"/>
+      <c r="AP38" s="10" t="n"/>
+      <c r="AQ38" s="8" t="n"/>
+      <c r="AR38" s="9" t="n"/>
+      <c r="AS38" s="10" t="n"/>
+      <c r="AT38" s="8" t="n"/>
+      <c r="AU38" s="9" t="n"/>
+      <c r="AV38" s="10" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>CMS Info System Limited</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>INE925R01014</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Commercial Services &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>6957544</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>18479.24</v>
+      </c>
+      <c r="F39" s="10" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>5086596</v>
+      </c>
+      <c r="H39" s="9" t="n">
+        <v>15442.91</v>
+      </c>
+      <c r="I39" s="10" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="J39" s="8" t="n">
+        <v>199758</v>
+      </c>
+      <c r="K39" s="9" t="n">
+        <v>629.9400000000001</v>
+      </c>
+      <c r="L39" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="8" t="n"/>
+      <c r="N39" s="9" t="n"/>
+      <c r="O39" s="10" t="n"/>
+      <c r="P39" s="8" t="n"/>
+      <c r="Q39" s="9" t="n"/>
+      <c r="R39" s="10" t="n"/>
+      <c r="S39" s="8" t="n"/>
+      <c r="T39" s="9" t="n"/>
+      <c r="U39" s="10" t="n"/>
+      <c r="V39" s="8" t="n"/>
+      <c r="W39" s="9" t="n"/>
+      <c r="X39" s="10" t="n"/>
+      <c r="Y39" s="8" t="n"/>
+      <c r="Z39" s="9" t="n"/>
+      <c r="AA39" s="10" t="n"/>
+      <c r="AB39" s="8" t="n"/>
+      <c r="AC39" s="9" t="n"/>
+      <c r="AD39" s="10" t="n"/>
+      <c r="AE39" s="8" t="n"/>
+      <c r="AF39" s="9" t="n"/>
+      <c r="AG39" s="10" t="n"/>
+      <c r="AH39" s="8" t="n"/>
+      <c r="AI39" s="9" t="n"/>
+      <c r="AJ39" s="10" t="n"/>
+      <c r="AK39" s="8" t="n"/>
+      <c r="AL39" s="9" t="n"/>
+      <c r="AM39" s="10" t="n"/>
+      <c r="AN39" s="8" t="n"/>
+      <c r="AO39" s="9" t="n"/>
+      <c r="AP39" s="10" t="n"/>
+      <c r="AQ39" s="8" t="n"/>
+      <c r="AR39" s="9" t="n"/>
+      <c r="AS39" s="10" t="n"/>
+      <c r="AT39" s="8" t="n"/>
+      <c r="AU39" s="9" t="n"/>
+      <c r="AV39" s="10" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>CIE Automotive India Limited</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>INE536H01010</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Auto Components</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>464063</v>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>2065.08</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="G40" s="8" t="n">
+        <v>464063</v>
+      </c>
+      <c r="H40" s="9" t="n">
+        <v>2188.75</v>
+      </c>
+      <c r="I40" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="J40" s="8" t="n">
+        <v>462075</v>
+      </c>
+      <c r="K40" s="9" t="n">
+        <v>1932.4</v>
+      </c>
+      <c r="L40" s="10" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M40" s="8" t="n"/>
+      <c r="N40" s="9" t="n"/>
+      <c r="O40" s="10" t="n"/>
+      <c r="P40" s="8" t="n"/>
+      <c r="Q40" s="9" t="n"/>
+      <c r="R40" s="10" t="n"/>
+      <c r="S40" s="8" t="n"/>
+      <c r="T40" s="9" t="n"/>
+      <c r="U40" s="10" t="n"/>
+      <c r="V40" s="8" t="n"/>
+      <c r="W40" s="9" t="n"/>
+      <c r="X40" s="10" t="n"/>
+      <c r="Y40" s="8" t="n"/>
+      <c r="Z40" s="9" t="n"/>
+      <c r="AA40" s="10" t="n"/>
+      <c r="AB40" s="8" t="n"/>
+      <c r="AC40" s="9" t="n"/>
+      <c r="AD40" s="10" t="n"/>
+      <c r="AE40" s="8" t="n"/>
+      <c r="AF40" s="9" t="n"/>
+      <c r="AG40" s="10" t="n"/>
+      <c r="AH40" s="8" t="n"/>
+      <c r="AI40" s="9" t="n"/>
+      <c r="AJ40" s="10" t="n"/>
+      <c r="AK40" s="8" t="n"/>
+      <c r="AL40" s="9" t="n"/>
+      <c r="AM40" s="10" t="n"/>
+      <c r="AN40" s="8" t="n"/>
+      <c r="AO40" s="9" t="n"/>
+      <c r="AP40" s="10" t="n"/>
+      <c r="AQ40" s="8" t="n"/>
+      <c r="AR40" s="9" t="n"/>
+      <c r="AS40" s="10" t="n"/>
+      <c r="AT40" s="8" t="n"/>
+      <c r="AU40" s="9" t="n"/>
+      <c r="AV40" s="10" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Indraprastha Gas Limited</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>INE203G01027</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>481152</v>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>700.65</v>
+      </c>
+      <c r="F41" s="10" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="G41" s="8" t="n">
+        <v>286134</v>
+      </c>
+      <c r="H41" s="9" t="n">
+        <v>488.89</v>
+      </c>
+      <c r="I41" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="8" t="n"/>
+      <c r="K41" s="9" t="n"/>
+      <c r="L41" s="10" t="n"/>
+      <c r="M41" s="8" t="n"/>
+      <c r="N41" s="9" t="n"/>
+      <c r="O41" s="10" t="n"/>
+      <c r="P41" s="8" t="n"/>
+      <c r="Q41" s="9" t="n"/>
+      <c r="R41" s="10" t="n"/>
+      <c r="S41" s="8" t="n"/>
+      <c r="T41" s="9" t="n"/>
+      <c r="U41" s="10" t="n"/>
+      <c r="V41" s="8" t="n"/>
+      <c r="W41" s="9" t="n"/>
+      <c r="X41" s="10" t="n"/>
+      <c r="Y41" s="8" t="n"/>
+      <c r="Z41" s="9" t="n"/>
+      <c r="AA41" s="10" t="n"/>
+      <c r="AB41" s="8" t="n"/>
+      <c r="AC41" s="9" t="n"/>
+      <c r="AD41" s="10" t="n"/>
+      <c r="AE41" s="8" t="n"/>
+      <c r="AF41" s="9" t="n"/>
+      <c r="AG41" s="10" t="n"/>
+      <c r="AH41" s="8" t="n"/>
+      <c r="AI41" s="9" t="n"/>
+      <c r="AJ41" s="10" t="n"/>
+      <c r="AK41" s="8" t="n"/>
+      <c r="AL41" s="9" t="n"/>
+      <c r="AM41" s="10" t="n"/>
+      <c r="AN41" s="8" t="n"/>
+      <c r="AO41" s="9" t="n"/>
+      <c r="AP41" s="10" t="n"/>
+      <c r="AQ41" s="8" t="n"/>
+      <c r="AR41" s="9" t="n"/>
+      <c r="AS41" s="10" t="n"/>
+      <c r="AT41" s="8" t="n"/>
+      <c r="AU41" s="9" t="n"/>
+      <c r="AV41" s="10" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Mahanagar Gas Limited</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>INE002S01010</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>53045</v>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>492.1</v>
+      </c>
+      <c r="F42" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="8" t="n">
+        <v>3045</v>
+      </c>
+      <c r="H42" s="9" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="I42" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="8" t="n"/>
+      <c r="K42" s="9" t="n"/>
+      <c r="L42" s="10" t="n"/>
+      <c r="M42" s="8" t="n"/>
+      <c r="N42" s="9" t="n"/>
+      <c r="O42" s="10" t="n"/>
+      <c r="P42" s="8" t="n"/>
+      <c r="Q42" s="9" t="n"/>
+      <c r="R42" s="10" t="n"/>
+      <c r="S42" s="8" t="n"/>
+      <c r="T42" s="9" t="n"/>
+      <c r="U42" s="10" t="n"/>
+      <c r="V42" s="8" t="n"/>
+      <c r="W42" s="9" t="n"/>
+      <c r="X42" s="10" t="n"/>
+      <c r="Y42" s="8" t="n"/>
+      <c r="Z42" s="9" t="n"/>
+      <c r="AA42" s="10" t="n"/>
+      <c r="AB42" s="8" t="n"/>
+      <c r="AC42" s="9" t="n"/>
+      <c r="AD42" s="10" t="n"/>
+      <c r="AE42" s="8" t="n"/>
+      <c r="AF42" s="9" t="n"/>
+      <c r="AG42" s="10" t="n"/>
+      <c r="AH42" s="8" t="n"/>
+      <c r="AI42" s="9" t="n"/>
+      <c r="AJ42" s="10" t="n"/>
+      <c r="AK42" s="8" t="n"/>
+      <c r="AL42" s="9" t="n"/>
+      <c r="AM42" s="10" t="n"/>
+      <c r="AN42" s="8" t="n"/>
+      <c r="AO42" s="9" t="n"/>
+      <c r="AP42" s="10" t="n"/>
+      <c r="AQ42" s="8" t="n"/>
+      <c r="AR42" s="9" t="n"/>
+      <c r="AS42" s="10" t="n"/>
+      <c r="AT42" s="8" t="n"/>
+      <c r="AU42" s="9" t="n"/>
+      <c r="AV42" s="10" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Multi Commodity Exchange of India Limited</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>INE745G01043</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Capital Markets</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="n"/>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="10" t="n"/>
+      <c r="G43" s="8" t="n"/>
+      <c r="H43" s="9" t="n"/>
+      <c r="I43" s="10" t="n"/>
+      <c r="J43" s="8" t="n">
+        <v>795472</v>
+      </c>
+      <c r="K43" s="9" t="n">
+        <v>20109.53</v>
+      </c>
+      <c r="L43" s="10" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="M43" s="8" t="n"/>
+      <c r="N43" s="9" t="n"/>
+      <c r="O43" s="10" t="n"/>
+      <c r="P43" s="8" t="n"/>
+      <c r="Q43" s="9" t="n"/>
+      <c r="R43" s="10" t="n"/>
+      <c r="S43" s="8" t="n"/>
+      <c r="T43" s="9" t="n"/>
+      <c r="U43" s="10" t="n"/>
+      <c r="V43" s="8" t="n"/>
+      <c r="W43" s="9" t="n"/>
+      <c r="X43" s="10" t="n"/>
+      <c r="Y43" s="8" t="n"/>
+      <c r="Z43" s="9" t="n"/>
+      <c r="AA43" s="10" t="n"/>
+      <c r="AB43" s="8" t="n"/>
+      <c r="AC43" s="9" t="n"/>
+      <c r="AD43" s="10" t="n"/>
+      <c r="AE43" s="8" t="n"/>
+      <c r="AF43" s="9" t="n"/>
+      <c r="AG43" s="10" t="n"/>
+      <c r="AH43" s="8" t="n"/>
+      <c r="AI43" s="9" t="n"/>
+      <c r="AJ43" s="10" t="n"/>
+      <c r="AK43" s="8" t="n"/>
+      <c r="AL43" s="9" t="n"/>
+      <c r="AM43" s="10" t="n"/>
+      <c r="AN43" s="8" t="n"/>
+      <c r="AO43" s="9" t="n"/>
+      <c r="AP43" s="10" t="n"/>
+      <c r="AQ43" s="8" t="n"/>
+      <c r="AR43" s="9" t="n"/>
+      <c r="AS43" s="10" t="n"/>
+      <c r="AT43" s="8" t="n"/>
+      <c r="AU43" s="9" t="n"/>
+      <c r="AV43" s="10" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B38" s="11" t="n"/>
-      <c r="C38" s="12" t="n"/>
-      <c r="D38" s="13" t="n">
+      <c r="B44" s="11" t="n"/>
+      <c r="C44" s="12" t="n"/>
+      <c r="D44" s="13" t="n">
+        <v>1373201700</v>
+      </c>
+      <c r="E44" s="14" t="n">
+        <v>8608487.039999999</v>
+      </c>
+      <c r="F44" s="15" t="n">
+        <v>0.6674999999999998</v>
+      </c>
+      <c r="G44" s="13" t="n">
+        <v>1285817925</v>
+      </c>
+      <c r="H44" s="14" t="n">
+        <v>8857498.140000001</v>
+      </c>
+      <c r="I44" s="15" t="n">
+        <v>0.6597999999999999</v>
+      </c>
+      <c r="J44" s="13" t="n">
+        <v>1265994824</v>
+      </c>
+      <c r="K44" s="14" t="n">
+        <v>8789059.288358001</v>
+      </c>
+      <c r="L44" s="15" t="n">
+        <v>0.6559051731198605</v>
+      </c>
+      <c r="M44" s="13" t="n">
         <v>1079845116</v>
       </c>
-      <c r="E38" s="14" t="n">
+      <c r="N44" s="14" t="n">
         <v>8588270.840000002</v>
       </c>
-      <c r="F38" s="15" t="n">
+      <c r="O44" s="15" t="n">
         <v>0.6443999999999998</v>
       </c>
-      <c r="G38" s="13" t="n">
+      <c r="P44" s="13" t="n">
         <v>1039629309</v>
       </c>
-      <c r="H38" s="14" t="n">
+      <c r="Q44" s="14" t="n">
         <v>8271351.1939775</v>
       </c>
-      <c r="I38" s="15" t="n">
+      <c r="R44" s="15" t="n">
         <v>0.6374000000000001</v>
       </c>
-      <c r="J38" s="13" t="n">
+      <c r="S44" s="13" t="n">
         <v>991416407</v>
       </c>
-      <c r="K38" s="14" t="n">
+      <c r="T44" s="14" t="n">
         <v>7865128.239999999</v>
       </c>
-      <c r="L38" s="15" t="n">
+      <c r="U44" s="15" t="n">
         <v>0.6254999999999999</v>
       </c>
-      <c r="M38" s="13" t="n">
+      <c r="V44" s="13" t="n">
         <v>979359723</v>
       </c>
-      <c r="N38" s="14" t="n">
+      <c r="W44" s="14" t="n">
         <v>7559180.72</v>
       </c>
-      <c r="O38" s="15" t="n">
+      <c r="X44" s="15" t="n">
         <v>0.6313999999999997</v>
       </c>
-      <c r="P38" s="13" t="n">
+      <c r="Y44" s="13" t="n">
         <v>927478800</v>
       </c>
-      <c r="Q38" s="14" t="n">
+      <c r="Z44" s="14" t="n">
         <v>7320811.49</v>
       </c>
-      <c r="R38" s="15" t="n">
+      <c r="AA44" s="15" t="n">
         <v>0.6364000000000001</v>
       </c>
-      <c r="S38" s="13" t="n">
+      <c r="AB44" s="13" t="n">
         <v>819556049</v>
       </c>
-      <c r="T38" s="14" t="n">
+      <c r="AC44" s="14" t="n">
         <v>7290583.900000003</v>
       </c>
-      <c r="U38" s="15" t="n">
+      <c r="AD44" s="15" t="n">
         <v>0.6436999999999999</v>
       </c>
-      <c r="V38" s="13" t="n">
+      <c r="AE44" s="13" t="n">
         <v>799425942</v>
       </c>
-      <c r="W38" s="14" t="n">
+      <c r="AF44" s="14" t="n">
         <v>7347454.07</v>
       </c>
-      <c r="X38" s="15" t="n">
+      <c r="AG44" s="15" t="n">
         <v>0.6657999999999998</v>
       </c>
-      <c r="Y38" s="13" t="n">
+      <c r="AH44" s="13" t="n">
         <v>756845974</v>
       </c>
-      <c r="Z38" s="14" t="n">
+      <c r="AI44" s="14" t="n">
         <v>6714757.130000002</v>
       </c>
-      <c r="AA38" s="15" t="n">
+      <c r="AJ44" s="15" t="n">
         <v>0.6467999999999997</v>
       </c>
-      <c r="AB38" s="13" t="n">
+      <c r="AK44" s="13" t="n">
         <v>719050337</v>
       </c>
-      <c r="AC38" s="14" t="n">
+      <c r="AL44" s="14" t="n">
         <v>6275568.75</v>
       </c>
-      <c r="AD38" s="15" t="n">
+      <c r="AM44" s="15" t="n">
         <v>0.6370000000000001</v>
       </c>
-      <c r="AE38" s="13" t="n">
+      <c r="AN44" s="13" t="n">
         <v>717176528</v>
       </c>
-      <c r="AF38" s="14" t="n">
+      <c r="AO44" s="14" t="n">
         <v>6051937.58</v>
       </c>
-      <c r="AG38" s="15" t="n">
+      <c r="AP44" s="15" t="n">
         <v>0.6476999999999997</v>
       </c>
-      <c r="AH38" s="13" t="n">
+      <c r="AQ44" s="13" t="n">
         <v>718063829</v>
       </c>
-      <c r="AI38" s="14" t="n">
+      <c r="AR44" s="14" t="n">
         <v>5662977.749999999</v>
       </c>
-      <c r="AJ38" s="15" t="n">
+      <c r="AS44" s="15" t="n">
         <v>0.6436999999999998</v>
       </c>
-      <c r="AK38" s="13" t="n">
+      <c r="AT44" s="13" t="n">
         <v>697292654</v>
       </c>
-      <c r="AL38" s="14" t="n">
+      <c r="AU44" s="14" t="n">
         <v>5868142.6</v>
       </c>
-      <c r="AM38" s="15" t="n">
+      <c r="AV44" s="15" t="n">
         <v>0.6543000000000002</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="16">
     <mergeCell ref="D2:F2"/>
+    <mergeCell ref="AT2:AV2"/>
     <mergeCell ref="G2:I2"/>
-    <mergeCell ref="A1:AM1"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="Y2:AA2"/>
     <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="AE2:AG2"/>
     <mergeCell ref="AK2:AM2"/>
     <mergeCell ref="P2:R2"/>
+    <mergeCell ref="AN2:AP2"/>
+    <mergeCell ref="A1:AV1"/>
+    <mergeCell ref="AQ2:AS2"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="S2:U2"/>
     <mergeCell ref="AH2:AJ2"/>

--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV44"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -493,25 +493,25 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="26" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
     <col width="15" customWidth="1" min="16" max="16"/>
     <col width="26" customWidth="1" min="17" max="17"/>
     <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
     <col width="26" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
-    <col width="20" customWidth="1" min="24" max="24"/>
-    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
     <col width="26" customWidth="1" min="26" max="26"/>
     <col width="20" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
@@ -529,12 +529,15 @@
     <col width="13" customWidth="1" min="40" max="40"/>
     <col width="26" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
-    <col width="15" customWidth="1" min="43" max="43"/>
+    <col width="13" customWidth="1" min="43" max="43"/>
     <col width="26" customWidth="1" min="44" max="44"/>
     <col width="20" customWidth="1" min="45" max="45"/>
-    <col width="14" customWidth="1" min="46" max="46"/>
+    <col width="15" customWidth="1" min="46" max="46"/>
     <col width="26" customWidth="1" min="47" max="47"/>
     <col width="20" customWidth="1" min="48" max="48"/>
+    <col width="14" customWidth="1" min="49" max="49"/>
+    <col width="26" customWidth="1" min="50" max="50"/>
+    <col width="20" customWidth="1" min="51" max="51"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -590,6 +593,9 @@
       <c r="AT1" s="1" t="n"/>
       <c r="AU1" s="1" t="n"/>
       <c r="AV1" s="1" t="n"/>
+      <c r="AW1" s="1" t="n"/>
+      <c r="AX1" s="1" t="n"/>
+      <c r="AY1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -609,109 +615,116 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>March_2026</t>
+          <t>April_2026</t>
         </is>
       </c>
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="3" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>February_2026</t>
+          <t>March_2026</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="3" t="n"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>January_2026</t>
+          <t>February_2026</t>
         </is>
       </c>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="3" t="n"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>December_2025</t>
+          <t>January_2026</t>
         </is>
       </c>
       <c r="N2" s="2" t="n"/>
       <c r="O2" s="3" t="n"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>November_2025</t>
+          <t>December_2025</t>
         </is>
       </c>
       <c r="Q2" s="2" t="n"/>
       <c r="R2" s="3" t="n"/>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>October_2025</t>
+          <t>November_2025</t>
         </is>
       </c>
       <c r="T2" s="2" t="n"/>
       <c r="U2" s="3" t="n"/>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>September_2025</t>
+          <t>October_2025</t>
         </is>
       </c>
       <c r="W2" s="2" t="n"/>
       <c r="X2" s="3" t="n"/>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>August_2025</t>
+          <t>September_2025</t>
         </is>
       </c>
       <c r="Z2" s="2" t="n"/>
       <c r="AA2" s="3" t="n"/>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>July_2025</t>
+          <t>August_2025</t>
         </is>
       </c>
       <c r="AC2" s="2" t="n"/>
       <c r="AD2" s="3" t="n"/>
       <c r="AE2" s="2" t="inlineStr">
         <is>
-          <t>June_2025</t>
+          <t>July_2025</t>
         </is>
       </c>
       <c r="AF2" s="2" t="n"/>
       <c r="AG2" s="3" t="n"/>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>May_2025</t>
+          <t>June_2025</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n"/>
       <c r="AJ2" s="3" t="n"/>
       <c r="AK2" s="2" t="inlineStr">
         <is>
-          <t>April_2025</t>
+          <t>May_2025</t>
         </is>
       </c>
       <c r="AL2" s="2" t="n"/>
       <c r="AM2" s="3" t="n"/>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>March_2025</t>
+          <t>April_2025</t>
         </is>
       </c>
       <c r="AO2" s="2" t="n"/>
       <c r="AP2" s="3" t="n"/>
       <c r="AQ2" s="2" t="inlineStr">
         <is>
-          <t>February_2025</t>
+          <t>March_2025</t>
         </is>
       </c>
       <c r="AR2" s="2" t="n"/>
       <c r="AS2" s="3" t="n"/>
       <c r="AT2" s="2" t="inlineStr">
         <is>
-          <t>January_2025</t>
+          <t>February_2025</t>
         </is>
       </c>
       <c r="AU2" s="2" t="n"/>
       <c r="AV2" s="3" t="n"/>
+      <c r="AW2" s="2" t="inlineStr">
+        <is>
+          <t>January_2025</t>
+        </is>
+      </c>
+      <c r="AX2" s="2" t="n"/>
+      <c r="AY2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n"/>
@@ -942,6 +955,21 @@
           <t>% Net Assets</t>
         </is>
       </c>
+      <c r="AW3" s="4" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="AX3" s="4" t="inlineStr">
+        <is>
+          <t>Market Value (Rs. Lakhs)</t>
+        </is>
+      </c>
+      <c r="AY3" s="5" t="inlineStr">
+        <is>
+          <t>% Net Assets</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -960,138 +988,147 @@
         </is>
       </c>
       <c r="D4" s="8" t="n">
+        <v>145007203</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>1119020.59</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>0.0794</v>
+      </c>
+      <c r="G4" s="8" t="n">
         <v>140247203</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="H4" s="9" t="n">
         <v>1025978.41</v>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="I4" s="10" t="n">
         <v>0.0796</v>
       </c>
-      <c r="G4" s="8" t="n">
+      <c r="J4" s="8" t="n">
         <v>116915576</v>
       </c>
-      <c r="H4" s="9" t="n">
+      <c r="K4" s="9" t="n">
         <v>1037918.03</v>
       </c>
-      <c r="I4" s="10" t="n">
+      <c r="L4" s="10" t="n">
         <v>0.07729999999999999</v>
       </c>
-      <c r="J4" s="8" t="n">
+      <c r="M4" s="8" t="n">
         <v>115915576</v>
       </c>
-      <c r="K4" s="9" t="n">
+      <c r="N4" s="9" t="n">
         <v>1077145.49</v>
       </c>
-      <c r="L4" s="10" t="n">
+      <c r="O4" s="10" t="n">
         <v>0.0804</v>
       </c>
-      <c r="M4" s="8" t="n">
+      <c r="P4" s="8" t="n">
         <v>108738215</v>
       </c>
-      <c r="N4" s="9" t="n">
+      <c r="Q4" s="9" t="n">
         <v>1077813.19</v>
       </c>
-      <c r="O4" s="10" t="n">
+      <c r="R4" s="10" t="n">
         <v>0.0809</v>
       </c>
-      <c r="P4" s="8" t="n">
+      <c r="S4" s="8" t="n">
         <v>103486016</v>
       </c>
-      <c r="Q4" s="9" t="n">
+      <c r="T4" s="9" t="n">
         <v>1042725.1</v>
       </c>
-      <c r="R4" s="10" t="n">
+      <c r="U4" s="10" t="n">
         <v>0.0803</v>
       </c>
-      <c r="S4" s="8" t="n">
+      <c r="V4" s="8" t="n">
         <v>102203321</v>
       </c>
-      <c r="T4" s="9" t="n">
+      <c r="W4" s="9" t="n">
         <v>1009053.39</v>
       </c>
-      <c r="U4" s="10" t="n">
+      <c r="X4" s="10" t="n">
         <v>0.08019999999999999</v>
       </c>
-      <c r="V4" s="8" t="n">
+      <c r="Y4" s="8" t="n">
         <v>101668321</v>
       </c>
-      <c r="W4" s="9" t="n">
+      <c r="Z4" s="9" t="n">
         <v>966865.73</v>
       </c>
-      <c r="X4" s="10" t="n">
+      <c r="AA4" s="10" t="n">
         <v>0.0808</v>
       </c>
-      <c r="Y4" s="8" t="n">
+      <c r="AB4" s="8" t="n">
         <v>95825482</v>
       </c>
-      <c r="Z4" s="9" t="n">
+      <c r="AC4" s="9" t="n">
         <v>911875.29</v>
       </c>
-      <c r="AA4" s="10" t="n">
+      <c r="AD4" s="10" t="n">
         <v>0.0793</v>
       </c>
-      <c r="AB4" s="8" t="n">
+      <c r="AE4" s="8" t="n">
         <v>44870461</v>
       </c>
-      <c r="AC4" s="9" t="n">
+      <c r="AF4" s="9" t="n">
         <v>905575.64</v>
       </c>
-      <c r="AD4" s="10" t="n">
+      <c r="AG4" s="10" t="n">
         <v>0.0799</v>
       </c>
-      <c r="AE4" s="8" t="n">
+      <c r="AH4" s="8" t="n">
         <v>44461271</v>
       </c>
-      <c r="AF4" s="9" t="n">
+      <c r="AI4" s="9" t="n">
         <v>889892.34</v>
       </c>
-      <c r="AG4" s="10" t="n">
+      <c r="AJ4" s="10" t="n">
         <v>0.0806</v>
       </c>
-      <c r="AH4" s="8" t="n">
+      <c r="AK4" s="8" t="n">
         <v>43293069</v>
       </c>
-      <c r="AI4" s="9" t="n">
+      <c r="AL4" s="9" t="n">
         <v>842006.9</v>
       </c>
-      <c r="AJ4" s="10" t="n">
+      <c r="AM4" s="10" t="n">
         <v>0.08110000000000001</v>
-      </c>
-      <c r="AK4" s="8" t="n">
-        <v>42813069</v>
-      </c>
-      <c r="AL4" s="9" t="n">
-        <v>824151.58</v>
-      </c>
-      <c r="AM4" s="10" t="n">
-        <v>0.08359999999999999</v>
       </c>
       <c r="AN4" s="8" t="n">
         <v>42813069</v>
       </c>
       <c r="AO4" s="9" t="n">
-        <v>782708.53</v>
+        <v>824151.58</v>
       </c>
       <c r="AP4" s="10" t="n">
-        <v>0.0838</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="AQ4" s="8" t="n">
         <v>42813069</v>
       </c>
       <c r="AR4" s="9" t="n">
-        <v>741693.61</v>
+        <v>782708.53</v>
       </c>
       <c r="AS4" s="10" t="n">
-        <v>0.0843</v>
+        <v>0.0838</v>
       </c>
       <c r="AT4" s="8" t="n">
         <v>42813069</v>
       </c>
       <c r="AU4" s="9" t="n">
+        <v>741693.61</v>
+      </c>
+      <c r="AV4" s="10" t="n">
+        <v>0.0843</v>
+      </c>
+      <c r="AW4" s="8" t="n">
+        <v>42813069</v>
+      </c>
+      <c r="AX4" s="9" t="n">
         <v>727287.01</v>
       </c>
-      <c r="AV4" s="10" t="n">
+      <c r="AY4" s="10" t="n">
         <v>0.08110000000000001</v>
       </c>
     </row>
@@ -1112,138 +1149,147 @@
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>6026828</v>
+        <v>6054746</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>527106.38</v>
+        <v>621640.77</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.0409</v>
+        <v>0.0441</v>
       </c>
       <c r="G5" s="8" t="n">
         <v>6026828</v>
       </c>
       <c r="H5" s="9" t="n">
+        <v>527106.38</v>
+      </c>
+      <c r="I5" s="10" t="n">
+        <v>0.0409</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>6026828</v>
+      </c>
+      <c r="K5" s="9" t="n">
         <v>651138.5</v>
       </c>
-      <c r="I5" s="10" t="n">
+      <c r="L5" s="10" t="n">
         <v>0.0485</v>
       </c>
-      <c r="J5" s="8" t="n">
+      <c r="M5" s="8" t="n">
         <v>5979253</v>
       </c>
-      <c r="K5" s="9" t="n">
+      <c r="N5" s="9" t="n">
         <v>645759.3199999999</v>
       </c>
-      <c r="L5" s="10" t="n">
+      <c r="O5" s="10" t="n">
         <v>0.0482</v>
-      </c>
-      <c r="M5" s="8" t="n">
-        <v>5318918</v>
-      </c>
-      <c r="N5" s="9" t="n">
-        <v>602527.03</v>
-      </c>
-      <c r="O5" s="10" t="n">
-        <v>0.0452</v>
       </c>
       <c r="P5" s="8" t="n">
         <v>5318918</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>611622.38</v>
+        <v>602527.03</v>
       </c>
       <c r="R5" s="10" t="n">
-        <v>0.0471</v>
+        <v>0.0452</v>
       </c>
       <c r="S5" s="8" t="n">
         <v>5318918</v>
       </c>
       <c r="T5" s="9" t="n">
-        <v>654386.48</v>
+        <v>611622.38</v>
       </c>
       <c r="U5" s="10" t="n">
-        <v>0.052</v>
+        <v>0.0471</v>
       </c>
       <c r="V5" s="8" t="n">
         <v>5318918</v>
       </c>
       <c r="W5" s="9" t="n">
-        <v>651407.89</v>
+        <v>654386.48</v>
       </c>
       <c r="X5" s="10" t="n">
-        <v>0.0544</v>
+        <v>0.052</v>
       </c>
       <c r="Y5" s="8" t="n">
         <v>5318918</v>
       </c>
       <c r="Z5" s="9" t="n">
-        <v>679225.83</v>
+        <v>651407.89</v>
       </c>
       <c r="AA5" s="10" t="n">
-        <v>0.059</v>
+        <v>0.0544</v>
       </c>
       <c r="AB5" s="8" t="n">
         <v>5318918</v>
       </c>
       <c r="AC5" s="9" t="n">
-        <v>742680.52</v>
+        <v>679225.83</v>
       </c>
       <c r="AD5" s="10" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.059</v>
       </c>
       <c r="AE5" s="8" t="n">
         <v>5318918</v>
       </c>
       <c r="AF5" s="9" t="n">
-        <v>764807.22</v>
+        <v>742680.52</v>
       </c>
       <c r="AG5" s="10" t="n">
-        <v>0.0693</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="AH5" s="8" t="n">
         <v>5318918</v>
       </c>
       <c r="AI5" s="9" t="n">
-        <v>713479.66</v>
+        <v>764807.22</v>
       </c>
       <c r="AJ5" s="10" t="n">
-        <v>0.0687</v>
+        <v>0.0693</v>
       </c>
       <c r="AK5" s="8" t="n">
         <v>5318918</v>
       </c>
       <c r="AL5" s="9" t="n">
-        <v>636834.05</v>
+        <v>713479.66</v>
       </c>
       <c r="AM5" s="10" t="n">
-        <v>0.0646</v>
+        <v>0.0687</v>
       </c>
       <c r="AN5" s="8" t="n">
         <v>5318918</v>
       </c>
       <c r="AO5" s="9" t="n">
-        <v>663431.3</v>
+        <v>636834.05</v>
       </c>
       <c r="AP5" s="10" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.0646</v>
       </c>
       <c r="AQ5" s="8" t="n">
         <v>5318918</v>
       </c>
       <c r="AR5" s="9" t="n">
-        <v>615630.1899999999</v>
+        <v>663431.3</v>
       </c>
       <c r="AS5" s="10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AT5" s="8" t="n">
         <v>5318918</v>
       </c>
       <c r="AU5" s="9" t="n">
+        <v>615630.1899999999</v>
+      </c>
+      <c r="AV5" s="10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AW5" s="8" t="n">
+        <v>5318918</v>
+      </c>
+      <c r="AX5" s="9" t="n">
         <v>614850.96</v>
       </c>
-      <c r="AV5" s="10" t="n">
+      <c r="AY5" s="10" t="n">
         <v>0.06850000000000001</v>
       </c>
     </row>
@@ -1264,73 +1310,73 @@
         </is>
       </c>
       <c r="D6" s="8" t="n">
+        <v>174142417</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>838408.67</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>0.0595</v>
+      </c>
+      <c r="G6" s="8" t="n">
         <v>174817417</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="H6" s="9" t="n">
         <v>787465.05</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="I6" s="10" t="n">
         <v>0.0611</v>
       </c>
-      <c r="G6" s="8" t="n">
+      <c r="J6" s="8" t="n">
         <v>161423761</v>
       </c>
-      <c r="H6" s="9" t="n">
+      <c r="K6" s="9" t="n">
         <v>695171.4300000001</v>
       </c>
-      <c r="I6" s="10" t="n">
+      <c r="L6" s="10" t="n">
         <v>0.0518</v>
       </c>
-      <c r="J6" s="8" t="n">
+      <c r="M6" s="8" t="n">
         <v>159832308</v>
       </c>
-      <c r="K6" s="9" t="n">
+      <c r="N6" s="9" t="n">
         <v>704460.9</v>
       </c>
-      <c r="L6" s="10" t="n">
+      <c r="O6" s="10" t="n">
         <v>0.0526</v>
-      </c>
-      <c r="M6" s="8" t="n">
-        <v>162039558</v>
-      </c>
-      <c r="N6" s="9" t="n">
-        <v>646537.84</v>
-      </c>
-      <c r="O6" s="10" t="n">
-        <v>0.0485</v>
       </c>
       <c r="P6" s="8" t="n">
         <v>162039558</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>609511.8</v>
+        <v>646537.84</v>
       </c>
       <c r="R6" s="10" t="n">
-        <v>0.047</v>
+        <v>0.0485</v>
       </c>
       <c r="S6" s="8" t="n">
         <v>162039558</v>
       </c>
       <c r="T6" s="9" t="n">
-        <v>629766.74</v>
+        <v>609511.8</v>
       </c>
       <c r="U6" s="10" t="n">
-        <v>0.0501</v>
+        <v>0.047</v>
       </c>
       <c r="V6" s="8" t="n">
         <v>162039558</v>
       </c>
       <c r="W6" s="9" t="n">
-        <v>631873.26</v>
+        <v>629766.74</v>
       </c>
       <c r="X6" s="10" t="n">
-        <v>0.0528</v>
+        <v>0.0501</v>
       </c>
       <c r="Y6" s="8" t="n">
         <v>162039558</v>
       </c>
       <c r="Z6" s="9" t="n">
-        <v>607324.26</v>
+        <v>631873.26</v>
       </c>
       <c r="AA6" s="10" t="n">
         <v>0.0528</v>
@@ -1339,63 +1385,72 @@
         <v>162039558</v>
       </c>
       <c r="AC6" s="9" t="n">
-        <v>609835.88</v>
+        <v>607324.26</v>
       </c>
       <c r="AD6" s="10" t="n">
-        <v>0.0538</v>
+        <v>0.0528</v>
       </c>
       <c r="AE6" s="8" t="n">
         <v>162039558</v>
       </c>
       <c r="AF6" s="9" t="n">
+        <v>609835.88</v>
+      </c>
+      <c r="AG6" s="10" t="n">
+        <v>0.0538</v>
+      </c>
+      <c r="AH6" s="8" t="n">
+        <v>162039558</v>
+      </c>
+      <c r="AI6" s="9" t="n">
         <v>635114.05</v>
       </c>
-      <c r="AG6" s="10" t="n">
+      <c r="AJ6" s="10" t="n">
         <v>0.0575</v>
       </c>
-      <c r="AH6" s="8" t="n">
+      <c r="AK6" s="8" t="n">
         <v>155681572</v>
       </c>
-      <c r="AI6" s="9" t="n">
+      <c r="AL6" s="9" t="n">
         <v>618522.89</v>
       </c>
-      <c r="AJ6" s="10" t="n">
+      <c r="AM6" s="10" t="n">
         <v>0.0595</v>
       </c>
-      <c r="AK6" s="8" t="n">
+      <c r="AN6" s="8" t="n">
         <v>148323775</v>
       </c>
-      <c r="AL6" s="9" t="n">
+      <c r="AO6" s="9" t="n">
         <v>571491.51</v>
       </c>
-      <c r="AM6" s="10" t="n">
+      <c r="AP6" s="10" t="n">
         <v>0.058</v>
       </c>
-      <c r="AN6" s="8" t="n">
+      <c r="AQ6" s="8" t="n">
         <v>141074007</v>
       </c>
-      <c r="AO6" s="9" t="n">
+      <c r="AR6" s="9" t="n">
         <v>561756.7</v>
       </c>
-      <c r="AP6" s="10" t="n">
+      <c r="AS6" s="10" t="n">
         <v>0.0601</v>
       </c>
-      <c r="AQ6" s="8" t="n">
+      <c r="AT6" s="8" t="n">
         <v>142636407</v>
       </c>
-      <c r="AR6" s="9" t="n">
+      <c r="AU6" s="9" t="n">
         <v>526827.5699999999</v>
       </c>
-      <c r="AS6" s="10" t="n">
+      <c r="AV6" s="10" t="n">
         <v>0.0599</v>
       </c>
-      <c r="AT6" s="8" t="n">
+      <c r="AW6" s="8" t="n">
         <v>139335199</v>
       </c>
-      <c r="AU6" s="9" t="n">
+      <c r="AX6" s="9" t="n">
         <v>551628.05</v>
       </c>
-      <c r="AV6" s="10" t="n">
+      <c r="AY6" s="10" t="n">
         <v>0.0615</v>
       </c>
     </row>
@@ -1416,138 +1471,147 @@
         </is>
       </c>
       <c r="D7" s="8" t="n">
+        <v>309434264</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>985083.98</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>0.0699</v>
+      </c>
+      <c r="G7" s="8" t="n">
         <v>312063864</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="H7" s="9" t="n">
         <v>924021.1</v>
       </c>
-      <c r="F7" s="10" t="n">
+      <c r="I7" s="10" t="n">
         <v>0.0716</v>
       </c>
-      <c r="G7" s="8" t="n">
+      <c r="J7" s="8" t="n">
         <v>311113864</v>
       </c>
-      <c r="H7" s="9" t="n">
+      <c r="K7" s="9" t="n">
         <v>929141.55</v>
       </c>
-      <c r="I7" s="10" t="n">
+      <c r="L7" s="10" t="n">
         <v>0.0692</v>
       </c>
-      <c r="J7" s="8" t="n">
+      <c r="M7" s="8" t="n">
         <v>313365617</v>
       </c>
-      <c r="K7" s="9" t="n">
+      <c r="N7" s="9" t="n">
         <v>803782.8100000001</v>
       </c>
-      <c r="L7" s="10" t="n">
+      <c r="O7" s="10" t="n">
         <v>0.06</v>
       </c>
-      <c r="M7" s="8" t="n">
+      <c r="P7" s="8" t="n">
         <v>305419267</v>
       </c>
-      <c r="N7" s="9" t="n">
+      <c r="Q7" s="9" t="n">
         <v>808139.38</v>
       </c>
-      <c r="O7" s="10" t="n">
+      <c r="R7" s="10" t="n">
         <v>0.0606</v>
       </c>
-      <c r="P7" s="8" t="n">
+      <c r="S7" s="8" t="n">
         <v>284154236</v>
       </c>
-      <c r="Q7" s="9" t="n">
+      <c r="T7" s="9" t="n">
         <v>767074.36</v>
       </c>
-      <c r="R7" s="10" t="n">
+      <c r="U7" s="10" t="n">
         <v>0.0591</v>
       </c>
-      <c r="S7" s="8" t="n">
+      <c r="V7" s="8" t="n">
         <v>261786637</v>
       </c>
-      <c r="T7" s="9" t="n">
+      <c r="W7" s="9" t="n">
         <v>754338.1899999999</v>
       </c>
-      <c r="U7" s="10" t="n">
+      <c r="X7" s="10" t="n">
         <v>0.06</v>
       </c>
-      <c r="V7" s="8" t="n">
+      <c r="Y7" s="8" t="n">
         <v>255922726</v>
       </c>
-      <c r="W7" s="9" t="n">
+      <c r="Z7" s="9" t="n">
         <v>717223.4399999999</v>
       </c>
-      <c r="X7" s="10" t="n">
+      <c r="AA7" s="10" t="n">
         <v>0.0599</v>
       </c>
-      <c r="Y7" s="8" t="n">
+      <c r="AB7" s="8" t="n">
         <v>246049993</v>
       </c>
-      <c r="Z7" s="9" t="n">
+      <c r="AC7" s="9" t="n">
         <v>677252.61</v>
       </c>
-      <c r="AA7" s="10" t="n">
+      <c r="AD7" s="10" t="n">
         <v>0.0589</v>
       </c>
-      <c r="AB7" s="8" t="n">
+      <c r="AE7" s="8" t="n">
         <v>230787510</v>
       </c>
-      <c r="AC7" s="9" t="n">
+      <c r="AF7" s="9" t="n">
         <v>671591.65</v>
       </c>
-      <c r="AD7" s="10" t="n">
+      <c r="AG7" s="10" t="n">
         <v>0.0593</v>
       </c>
-      <c r="AE7" s="8" t="n">
+      <c r="AH7" s="8" t="n">
         <v>224216515</v>
       </c>
-      <c r="AF7" s="9" t="n">
+      <c r="AI7" s="9" t="n">
         <v>672425.33</v>
       </c>
-      <c r="AG7" s="10" t="n">
+      <c r="AJ7" s="10" t="n">
         <v>0.0609</v>
       </c>
-      <c r="AH7" s="8" t="n">
+      <c r="AK7" s="8" t="n">
         <v>208867542</v>
       </c>
-      <c r="AI7" s="9" t="n">
+      <c r="AL7" s="9" t="n">
         <v>605193.7</v>
       </c>
-      <c r="AJ7" s="10" t="n">
+      <c r="AM7" s="10" t="n">
         <v>0.0583</v>
       </c>
-      <c r="AK7" s="8" t="n">
+      <c r="AN7" s="8" t="n">
         <v>193616648</v>
       </c>
-      <c r="AL7" s="9" t="n">
+      <c r="AO7" s="9" t="n">
         <v>595274.38</v>
       </c>
-      <c r="AM7" s="10" t="n">
+      <c r="AP7" s="10" t="n">
         <v>0.0604</v>
       </c>
-      <c r="AN7" s="8" t="n">
+      <c r="AQ7" s="8" t="n">
         <v>192765312</v>
       </c>
-      <c r="AO7" s="9" t="n">
+      <c r="AR7" s="9" t="n">
         <v>559694.08</v>
       </c>
-      <c r="AP7" s="10" t="n">
+      <c r="AS7" s="10" t="n">
         <v>0.0599</v>
       </c>
-      <c r="AQ7" s="8" t="n">
+      <c r="AT7" s="8" t="n">
         <v>193498810</v>
       </c>
-      <c r="AR7" s="9" t="n">
+      <c r="AU7" s="9" t="n">
         <v>485391.76</v>
       </c>
-      <c r="AS7" s="10" t="n">
+      <c r="AV7" s="10" t="n">
         <v>0.0552</v>
       </c>
-      <c r="AT7" s="8" t="n">
+      <c r="AW7" s="8" t="n">
         <v>185577147</v>
       </c>
-      <c r="AU7" s="9" t="n">
+      <c r="AX7" s="9" t="n">
         <v>559793.46</v>
       </c>
-      <c r="AV7" s="10" t="n">
+      <c r="AY7" s="10" t="n">
         <v>0.0624</v>
       </c>
     </row>
@@ -1568,138 +1632,147 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
+        <v>54846183</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>692926.6800000001</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>0.0492</v>
+      </c>
+      <c r="G8" s="8" t="n">
         <v>53846183</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="H8" s="9" t="n">
         <v>649331.12</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="I8" s="10" t="n">
         <v>0.0503</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>49325234</v>
-      </c>
-      <c r="H8" s="9" t="n">
-        <v>680145.65</v>
-      </c>
-      <c r="I8" s="10" t="n">
-        <v>0.0507</v>
       </c>
       <c r="J8" s="8" t="n">
         <v>49325234</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>668356.92</v>
+        <v>680145.65</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>0.0499</v>
+        <v>0.0507</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>49325234</v>
       </c>
       <c r="N8" s="9" t="n">
+        <v>668356.92</v>
+      </c>
+      <c r="O8" s="10" t="n">
+        <v>0.0499</v>
+      </c>
+      <c r="P8" s="8" t="n">
+        <v>49325234</v>
+      </c>
+      <c r="Q8" s="9" t="n">
         <v>662388.5699999999</v>
       </c>
-      <c r="O8" s="10" t="n">
+      <c r="R8" s="10" t="n">
         <v>0.0497</v>
       </c>
-      <c r="P8" s="8" t="n">
+      <c r="S8" s="8" t="n">
         <v>45308598</v>
       </c>
-      <c r="Q8" s="9" t="n">
+      <c r="T8" s="9" t="n">
         <v>629245.8100000001</v>
       </c>
-      <c r="R8" s="10" t="n">
+      <c r="U8" s="10" t="n">
         <v>0.0485</v>
       </c>
-      <c r="S8" s="8" t="n">
+      <c r="V8" s="8" t="n">
         <v>43295573</v>
       </c>
-      <c r="T8" s="9" t="n">
+      <c r="W8" s="9" t="n">
         <v>582455.34</v>
       </c>
-      <c r="U8" s="10" t="n">
+      <c r="X8" s="10" t="n">
         <v>0.0463</v>
       </c>
-      <c r="V8" s="8" t="n">
+      <c r="Y8" s="8" t="n">
         <v>42215573</v>
       </c>
-      <c r="W8" s="9" t="n">
+      <c r="Z8" s="9" t="n">
         <v>569065.92</v>
       </c>
-      <c r="X8" s="10" t="n">
+      <c r="AA8" s="10" t="n">
         <v>0.0475</v>
       </c>
-      <c r="Y8" s="8" t="n">
+      <c r="AB8" s="8" t="n">
         <v>40720543</v>
       </c>
-      <c r="Z8" s="9" t="n">
+      <c r="AC8" s="9" t="n">
         <v>569191.75</v>
       </c>
-      <c r="AA8" s="10" t="n">
+      <c r="AD8" s="10" t="n">
         <v>0.0495</v>
       </c>
-      <c r="AB8" s="8" t="n">
+      <c r="AE8" s="8" t="n">
         <v>39605543</v>
       </c>
-      <c r="AC8" s="9" t="n">
+      <c r="AF8" s="9" t="n">
         <v>586716.51</v>
       </c>
-      <c r="AD8" s="10" t="n">
+      <c r="AG8" s="10" t="n">
         <v>0.0518</v>
       </c>
-      <c r="AE8" s="8" t="n">
+      <c r="AH8" s="8" t="n">
         <v>36489310</v>
       </c>
-      <c r="AF8" s="9" t="n">
+      <c r="AI8" s="9" t="n">
         <v>527562.4399999999</v>
       </c>
-      <c r="AG8" s="10" t="n">
+      <c r="AJ8" s="10" t="n">
         <v>0.0478</v>
-      </c>
-      <c r="AH8" s="8" t="n">
-        <v>34986740</v>
-      </c>
-      <c r="AI8" s="9" t="n">
-        <v>505838.29</v>
-      </c>
-      <c r="AJ8" s="10" t="n">
-        <v>0.0487</v>
       </c>
       <c r="AK8" s="8" t="n">
         <v>34986740</v>
       </c>
       <c r="AL8" s="9" t="n">
-        <v>499260.78</v>
+        <v>505838.29</v>
       </c>
       <c r="AM8" s="10" t="n">
-        <v>0.0507</v>
+        <v>0.0487</v>
       </c>
       <c r="AN8" s="8" t="n">
         <v>34986740</v>
       </c>
       <c r="AO8" s="9" t="n">
-        <v>471743.71</v>
+        <v>499260.78</v>
       </c>
       <c r="AP8" s="10" t="n">
-        <v>0.0505</v>
+        <v>0.0507</v>
       </c>
       <c r="AQ8" s="8" t="n">
         <v>34986740</v>
       </c>
       <c r="AR8" s="9" t="n">
-        <v>421275.34</v>
+        <v>471743.71</v>
       </c>
       <c r="AS8" s="10" t="n">
-        <v>0.0479</v>
+        <v>0.0505</v>
       </c>
       <c r="AT8" s="8" t="n">
         <v>34986740</v>
       </c>
       <c r="AU8" s="9" t="n">
+        <v>421275.34</v>
+      </c>
+      <c r="AV8" s="10" t="n">
+        <v>0.0479</v>
+      </c>
+      <c r="AW8" s="8" t="n">
+        <v>34986740</v>
+      </c>
+      <c r="AX8" s="9" t="n">
         <v>438313.88</v>
       </c>
-      <c r="AV8" s="10" t="n">
+      <c r="AY8" s="10" t="n">
         <v>0.0489</v>
       </c>
     </row>
@@ -1728,112 +1801,115 @@
       <c r="J9" s="8" t="n"/>
       <c r="K9" s="9" t="n"/>
       <c r="L9" s="10" t="n"/>
-      <c r="M9" s="8" t="n">
+      <c r="M9" s="8" t="n"/>
+      <c r="N9" s="9" t="n"/>
+      <c r="O9" s="10" t="n"/>
+      <c r="P9" s="8" t="n">
         <v>24621592</v>
       </c>
-      <c r="N9" s="9" t="n">
+      <c r="Q9" s="9" t="n">
         <v>541945.86</v>
       </c>
-      <c r="O9" s="10" t="n">
+      <c r="R9" s="10" t="n">
         <v>0.0407</v>
       </c>
-      <c r="P9" s="8" t="n">
+      <c r="S9" s="8" t="n">
         <v>24306544</v>
       </c>
-      <c r="Q9" s="9" t="n">
+      <c r="T9" s="9" t="n">
         <v>516368.22</v>
       </c>
-      <c r="R9" s="10" t="n">
+      <c r="U9" s="10" t="n">
         <v>0.0398</v>
-      </c>
-      <c r="S9" s="8" t="n">
-        <v>24205055</v>
-      </c>
-      <c r="T9" s="9" t="n">
-        <v>508838.67</v>
-      </c>
-      <c r="U9" s="10" t="n">
-        <v>0.0404</v>
       </c>
       <c r="V9" s="8" t="n">
         <v>24205055</v>
       </c>
       <c r="W9" s="9" t="n">
+        <v>508838.67</v>
+      </c>
+      <c r="X9" s="10" t="n">
+        <v>0.0404</v>
+      </c>
+      <c r="Y9" s="8" t="n">
+        <v>24205055</v>
+      </c>
+      <c r="Z9" s="9" t="n">
         <v>482334.13</v>
       </c>
-      <c r="X9" s="10" t="n">
+      <c r="AA9" s="10" t="n">
         <v>0.0403</v>
       </c>
-      <c r="Y9" s="8" t="n">
+      <c r="AB9" s="8" t="n">
         <v>23407381</v>
       </c>
-      <c r="Z9" s="9" t="n">
+      <c r="AC9" s="9" t="n">
         <v>458854.89</v>
       </c>
-      <c r="AA9" s="10" t="n">
+      <c r="AD9" s="10" t="n">
         <v>0.0399</v>
       </c>
-      <c r="AB9" s="8" t="n">
+      <c r="AE9" s="8" t="n">
         <v>21994066</v>
       </c>
-      <c r="AC9" s="9" t="n">
+      <c r="AF9" s="9" t="n">
         <v>435174.59</v>
       </c>
-      <c r="AD9" s="10" t="n">
+      <c r="AG9" s="10" t="n">
         <v>0.0384</v>
       </c>
-      <c r="AE9" s="8" t="n">
+      <c r="AH9" s="8" t="n">
         <v>20473232</v>
       </c>
-      <c r="AF9" s="9" t="n">
+      <c r="AI9" s="9" t="n">
         <v>442938.37</v>
       </c>
-      <c r="AG9" s="10" t="n">
+      <c r="AJ9" s="10" t="n">
         <v>0.0401</v>
-      </c>
-      <c r="AH9" s="8" t="n">
-        <v>19753232</v>
-      </c>
-      <c r="AI9" s="9" t="n">
-        <v>409820.3</v>
-      </c>
-      <c r="AJ9" s="10" t="n">
-        <v>0.0395</v>
       </c>
       <c r="AK9" s="8" t="n">
         <v>19753232</v>
       </c>
       <c r="AL9" s="9" t="n">
-        <v>436171.12</v>
+        <v>409820.3</v>
       </c>
       <c r="AM9" s="10" t="n">
-        <v>0.0443</v>
+        <v>0.0395</v>
       </c>
       <c r="AN9" s="8" t="n">
         <v>19753232</v>
       </c>
       <c r="AO9" s="9" t="n">
-        <v>428882.17</v>
+        <v>436171.12</v>
       </c>
       <c r="AP9" s="10" t="n">
-        <v>0.0459</v>
+        <v>0.0443</v>
       </c>
       <c r="AQ9" s="8" t="n">
         <v>19753232</v>
       </c>
       <c r="AR9" s="9" t="n">
-        <v>375894.13</v>
+        <v>428882.17</v>
       </c>
       <c r="AS9" s="10" t="n">
-        <v>0.0427</v>
+        <v>0.0459</v>
       </c>
       <c r="AT9" s="8" t="n">
         <v>19753232</v>
       </c>
       <c r="AU9" s="9" t="n">
+        <v>375894.13</v>
+      </c>
+      <c r="AV9" s="10" t="n">
+        <v>0.0427</v>
+      </c>
+      <c r="AW9" s="8" t="n">
+        <v>19753232</v>
+      </c>
+      <c r="AX9" s="9" t="n">
         <v>375568.2</v>
       </c>
-      <c r="AV9" s="10" t="n">
+      <c r="AY9" s="10" t="n">
         <v>0.0419</v>
       </c>
     </row>
@@ -1854,138 +1930,147 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
+        <v>243200889</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>765839.6</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>0.0543</v>
+      </c>
+      <c r="G10" s="8" t="n">
         <v>224093958</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="H10" s="9" t="n">
         <v>644718.3199999999</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="I10" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="G10" s="8" t="n">
+      <c r="J10" s="8" t="n">
         <v>215593958</v>
       </c>
-      <c r="H10" s="9" t="n">
+      <c r="K10" s="9" t="n">
         <v>676102.65</v>
       </c>
-      <c r="I10" s="10" t="n">
+      <c r="L10" s="10" t="n">
         <v>0.0504</v>
       </c>
-      <c r="J10" s="8" t="n">
+      <c r="M10" s="8" t="n">
         <v>209900994</v>
       </c>
-      <c r="K10" s="9" t="n">
+      <c r="N10" s="9" t="n">
         <v>676196.05</v>
       </c>
-      <c r="L10" s="10" t="n">
+      <c r="O10" s="10" t="n">
         <v>0.0505</v>
       </c>
-      <c r="M10" s="8" t="n">
+      <c r="P10" s="8" t="n">
         <v>148665711</v>
       </c>
-      <c r="N10" s="9" t="n">
+      <c r="Q10" s="9" t="n">
         <v>599122.8199999999</v>
       </c>
-      <c r="O10" s="10" t="n">
+      <c r="R10" s="10" t="n">
         <v>0.0449</v>
       </c>
-      <c r="P10" s="8" t="n">
+      <c r="S10" s="8" t="n">
         <v>144737169</v>
       </c>
-      <c r="Q10" s="9" t="n">
+      <c r="T10" s="9" t="n">
         <v>585100.01</v>
       </c>
-      <c r="R10" s="10" t="n">
+      <c r="U10" s="10" t="n">
         <v>0.0451</v>
       </c>
-      <c r="S10" s="8" t="n">
+      <c r="V10" s="8" t="n">
         <v>138771024</v>
       </c>
-      <c r="T10" s="9" t="n">
+      <c r="W10" s="9" t="n">
         <v>583324</v>
       </c>
-      <c r="U10" s="10" t="n">
+      <c r="X10" s="10" t="n">
         <v>0.0464</v>
       </c>
-      <c r="V10" s="8" t="n">
+      <c r="Y10" s="8" t="n">
         <v>135721024</v>
       </c>
-      <c r="W10" s="9" t="n">
+      <c r="Z10" s="9" t="n">
         <v>544987.77</v>
       </c>
-      <c r="X10" s="10" t="n">
+      <c r="AA10" s="10" t="n">
         <v>0.0455</v>
       </c>
-      <c r="Y10" s="8" t="n">
+      <c r="AB10" s="8" t="n">
         <v>129421024</v>
       </c>
-      <c r="Z10" s="9" t="n">
+      <c r="AC10" s="9" t="n">
         <v>530302.65</v>
       </c>
-      <c r="AA10" s="10" t="n">
+      <c r="AD10" s="10" t="n">
         <v>0.0461</v>
       </c>
-      <c r="AB10" s="8" t="n">
+      <c r="AE10" s="8" t="n">
         <v>122172359</v>
       </c>
-      <c r="AC10" s="9" t="n">
+      <c r="AF10" s="9" t="n">
         <v>503289.03</v>
       </c>
-      <c r="AD10" s="10" t="n">
+      <c r="AG10" s="10" t="n">
         <v>0.0444</v>
       </c>
-      <c r="AE10" s="8" t="n">
+      <c r="AH10" s="8" t="n">
         <v>117422359</v>
       </c>
-      <c r="AF10" s="9" t="n">
+      <c r="AI10" s="9" t="n">
         <v>489005.41</v>
       </c>
-      <c r="AG10" s="10" t="n">
+      <c r="AJ10" s="10" t="n">
         <v>0.0443</v>
       </c>
-      <c r="AH10" s="8" t="n">
+      <c r="AK10" s="8" t="n">
         <v>109270669</v>
       </c>
-      <c r="AI10" s="9" t="n">
+      <c r="AL10" s="9" t="n">
         <v>456806.03</v>
       </c>
-      <c r="AJ10" s="10" t="n">
+      <c r="AM10" s="10" t="n">
         <v>0.044</v>
       </c>
-      <c r="AK10" s="8" t="n">
+      <c r="AN10" s="8" t="n">
         <v>105271096</v>
       </c>
-      <c r="AL10" s="9" t="n">
+      <c r="AO10" s="9" t="n">
         <v>448244.33</v>
       </c>
-      <c r="AM10" s="10" t="n">
+      <c r="AP10" s="10" t="n">
         <v>0.0455</v>
-      </c>
-      <c r="AN10" s="8" t="n">
-        <v>101194120</v>
-      </c>
-      <c r="AO10" s="9" t="n">
-        <v>414642.91</v>
-      </c>
-      <c r="AP10" s="10" t="n">
-        <v>0.0444</v>
       </c>
       <c r="AQ10" s="8" t="n">
         <v>101194120</v>
       </c>
       <c r="AR10" s="9" t="n">
+        <v>414642.91</v>
+      </c>
+      <c r="AS10" s="10" t="n">
+        <v>0.0444</v>
+      </c>
+      <c r="AT10" s="8" t="n">
+        <v>101194120</v>
+      </c>
+      <c r="AU10" s="9" t="n">
         <v>399716.77</v>
       </c>
-      <c r="AS10" s="10" t="n">
+      <c r="AV10" s="10" t="n">
         <v>0.0454</v>
       </c>
-      <c r="AT10" s="8" t="n">
+      <c r="AW10" s="8" t="n">
         <v>98994120</v>
       </c>
-      <c r="AU10" s="9" t="n">
+      <c r="AX10" s="9" t="n">
         <v>442998.69</v>
       </c>
-      <c r="AV10" s="10" t="n">
+      <c r="AY10" s="10" t="n">
         <v>0.0494</v>
       </c>
     </row>
@@ -2009,135 +2094,144 @@
         <v>3039945</v>
       </c>
       <c r="E11" s="9" t="n">
+        <v>404738.28</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>0.0287</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>3039945</v>
+      </c>
+      <c r="H11" s="9" t="n">
         <v>374095.63</v>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="I11" s="10" t="n">
         <v>0.029</v>
       </c>
-      <c r="G11" s="8" t="n">
+      <c r="J11" s="8" t="n">
         <v>2861040</v>
       </c>
-      <c r="H11" s="9" t="n">
+      <c r="K11" s="9" t="n">
         <v>425064.71</v>
       </c>
-      <c r="I11" s="10" t="n">
+      <c r="L11" s="10" t="n">
         <v>0.0317</v>
       </c>
-      <c r="J11" s="8" t="n">
+      <c r="M11" s="8" t="n">
         <v>2780478</v>
       </c>
-      <c r="K11" s="9" t="n">
+      <c r="N11" s="9" t="n">
         <v>405921.98</v>
       </c>
-      <c r="L11" s="10" t="n">
+      <c r="O11" s="10" t="n">
         <v>0.0303</v>
-      </c>
-      <c r="M11" s="8" t="n">
-        <v>2746670</v>
-      </c>
-      <c r="N11" s="9" t="n">
-        <v>458611.49</v>
-      </c>
-      <c r="O11" s="10" t="n">
-        <v>0.0344</v>
       </c>
       <c r="P11" s="8" t="n">
         <v>2746670</v>
       </c>
       <c r="Q11" s="9" t="n">
+        <v>458611.49</v>
+      </c>
+      <c r="R11" s="10" t="n">
+        <v>0.0344</v>
+      </c>
+      <c r="S11" s="8" t="n">
+        <v>2746670</v>
+      </c>
+      <c r="T11" s="9" t="n">
         <v>436720.53</v>
       </c>
-      <c r="R11" s="10" t="n">
+      <c r="U11" s="10" t="n">
         <v>0.0337</v>
-      </c>
-      <c r="S11" s="8" t="n">
-        <v>2696670</v>
-      </c>
-      <c r="T11" s="9" t="n">
-        <v>436483.01</v>
-      </c>
-      <c r="U11" s="10" t="n">
-        <v>0.0347</v>
       </c>
       <c r="V11" s="8" t="n">
         <v>2696670</v>
       </c>
       <c r="W11" s="9" t="n">
+        <v>436483.01</v>
+      </c>
+      <c r="X11" s="10" t="n">
+        <v>0.0347</v>
+      </c>
+      <c r="Y11" s="8" t="n">
+        <v>2696670</v>
+      </c>
+      <c r="Z11" s="9" t="n">
         <v>432249.23</v>
       </c>
-      <c r="X11" s="10" t="n">
+      <c r="AA11" s="10" t="n">
         <v>0.0361</v>
       </c>
-      <c r="Y11" s="8" t="n">
+      <c r="AB11" s="8" t="n">
         <v>2746670</v>
       </c>
-      <c r="Z11" s="9" t="n">
+      <c r="AC11" s="9" t="n">
         <v>406259.96</v>
       </c>
-      <c r="AA11" s="10" t="n">
+      <c r="AD11" s="10" t="n">
         <v>0.0353</v>
-      </c>
-      <c r="AB11" s="8" t="n">
-        <v>3021670</v>
-      </c>
-      <c r="AC11" s="9" t="n">
-        <v>380972.15</v>
-      </c>
-      <c r="AD11" s="10" t="n">
-        <v>0.0336</v>
       </c>
       <c r="AE11" s="8" t="n">
         <v>3021670</v>
       </c>
       <c r="AF11" s="9" t="n">
-        <v>374687.08</v>
+        <v>380972.15</v>
       </c>
       <c r="AG11" s="10" t="n">
-        <v>0.0339</v>
+        <v>0.0336</v>
       </c>
       <c r="AH11" s="8" t="n">
         <v>3021670</v>
       </c>
       <c r="AI11" s="9" t="n">
-        <v>372239.53</v>
+        <v>374687.08</v>
       </c>
       <c r="AJ11" s="10" t="n">
-        <v>0.0358</v>
+        <v>0.0339</v>
       </c>
       <c r="AK11" s="8" t="n">
         <v>3021670</v>
       </c>
       <c r="AL11" s="9" t="n">
+        <v>372239.53</v>
+      </c>
+      <c r="AM11" s="10" t="n">
+        <v>0.0358</v>
+      </c>
+      <c r="AN11" s="8" t="n">
+        <v>3021670</v>
+      </c>
+      <c r="AO11" s="9" t="n">
         <v>370366.09</v>
       </c>
-      <c r="AM11" s="10" t="n">
+      <c r="AP11" s="10" t="n">
         <v>0.0376</v>
-      </c>
-      <c r="AN11" s="8" t="n">
-        <v>3018078</v>
-      </c>
-      <c r="AO11" s="9" t="n">
-        <v>347747.47</v>
-      </c>
-      <c r="AP11" s="10" t="n">
-        <v>0.0372</v>
       </c>
       <c r="AQ11" s="8" t="n">
         <v>3018078</v>
       </c>
       <c r="AR11" s="9" t="n">
-        <v>360535.07</v>
+        <v>347747.47</v>
       </c>
       <c r="AS11" s="10" t="n">
-        <v>0.041</v>
+        <v>0.0372</v>
       </c>
       <c r="AT11" s="8" t="n">
         <v>3018078</v>
       </c>
       <c r="AU11" s="9" t="n">
+        <v>360535.07</v>
+      </c>
+      <c r="AV11" s="10" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="AW11" s="8" t="n">
+        <v>3018078</v>
+      </c>
+      <c r="AX11" s="9" t="n">
         <v>371545.02</v>
       </c>
-      <c r="AV11" s="10" t="n">
+      <c r="AY11" s="10" t="n">
         <v>0.0414</v>
       </c>
     </row>
@@ -2161,7 +2255,7 @@
         <v>33244875</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>386072.73</v>
+        <v>421644.75</v>
       </c>
       <c r="F12" s="10" t="n">
         <v>0.0299</v>
@@ -2170,126 +2264,135 @@
         <v>33244875</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>460075.83</v>
+        <v>386072.73</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>0.0343</v>
+        <v>0.0299</v>
       </c>
       <c r="J12" s="8" t="n">
         <v>33244875</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>455587.77</v>
+        <v>460075.83</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>0.034</v>
+        <v>0.0343</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>33244875</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>422010.44</v>
+        <v>455587.77</v>
       </c>
       <c r="O12" s="10" t="n">
-        <v>0.0317</v>
+        <v>0.034</v>
       </c>
       <c r="P12" s="8" t="n">
         <v>33244875</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>425434.67</v>
+        <v>422010.44</v>
       </c>
       <c r="R12" s="10" t="n">
-        <v>0.0328</v>
+        <v>0.0317</v>
       </c>
       <c r="S12" s="8" t="n">
         <v>33244875</v>
       </c>
       <c r="T12" s="9" t="n">
-        <v>409842.82</v>
+        <v>425434.67</v>
       </c>
       <c r="U12" s="10" t="n">
-        <v>0.0326</v>
+        <v>0.0328</v>
       </c>
       <c r="V12" s="8" t="n">
         <v>33244875</v>
       </c>
       <c r="W12" s="9" t="n">
+        <v>409842.82</v>
+      </c>
+      <c r="X12" s="10" t="n">
+        <v>0.0326</v>
+      </c>
+      <c r="Y12" s="8" t="n">
+        <v>33244875</v>
+      </c>
+      <c r="Z12" s="9" t="n">
         <v>376199.01</v>
       </c>
-      <c r="X12" s="10" t="n">
+      <c r="AA12" s="10" t="n">
         <v>0.0314</v>
       </c>
-      <c r="Y12" s="8" t="n">
+      <c r="AB12" s="8" t="n">
         <v>32644875</v>
       </c>
-      <c r="Z12" s="9" t="n">
+      <c r="AC12" s="9" t="n">
         <v>341204.23</v>
       </c>
-      <c r="AA12" s="10" t="n">
+      <c r="AD12" s="10" t="n">
         <v>0.0297</v>
       </c>
-      <c r="AB12" s="8" t="n">
+      <c r="AE12" s="8" t="n">
         <v>30107270</v>
       </c>
-      <c r="AC12" s="9" t="n">
+      <c r="AF12" s="9" t="n">
         <v>321666.07</v>
       </c>
-      <c r="AD12" s="10" t="n">
+      <c r="AG12" s="10" t="n">
         <v>0.0284</v>
-      </c>
-      <c r="AE12" s="8" t="n">
-        <v>27257270</v>
-      </c>
-      <c r="AF12" s="9" t="n">
-        <v>326869.18</v>
-      </c>
-      <c r="AG12" s="10" t="n">
-        <v>0.0296</v>
       </c>
       <c r="AH12" s="8" t="n">
         <v>27257270</v>
       </c>
       <c r="AI12" s="9" t="n">
-        <v>324961.17</v>
+        <v>326869.18</v>
       </c>
       <c r="AJ12" s="10" t="n">
-        <v>0.0313</v>
+        <v>0.0296</v>
       </c>
       <c r="AK12" s="8" t="n">
         <v>27257270</v>
       </c>
       <c r="AL12" s="9" t="n">
-        <v>322998.65</v>
+        <v>324961.17</v>
       </c>
       <c r="AM12" s="10" t="n">
-        <v>0.0328</v>
+        <v>0.0313</v>
       </c>
       <c r="AN12" s="8" t="n">
         <v>27257270</v>
       </c>
       <c r="AO12" s="9" t="n">
-        <v>300375.12</v>
+        <v>322998.65</v>
       </c>
       <c r="AP12" s="10" t="n">
-        <v>0.0321</v>
+        <v>0.0328</v>
       </c>
       <c r="AQ12" s="8" t="n">
         <v>27257270</v>
       </c>
       <c r="AR12" s="9" t="n">
-        <v>276811.21</v>
+        <v>300375.12</v>
       </c>
       <c r="AS12" s="10" t="n">
-        <v>0.0315</v>
+        <v>0.0321</v>
       </c>
       <c r="AT12" s="8" t="n">
         <v>27257270</v>
       </c>
       <c r="AU12" s="9" t="n">
+        <v>276811.21</v>
+      </c>
+      <c r="AV12" s="10" t="n">
+        <v>0.0315</v>
+      </c>
+      <c r="AW12" s="8" t="n">
+        <v>27257270</v>
+      </c>
+      <c r="AX12" s="9" t="n">
         <v>268783.94</v>
       </c>
-      <c r="AV12" s="10" t="n">
+      <c r="AY12" s="10" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -2310,138 +2413,147 @@
         </is>
       </c>
       <c r="D13" s="8" t="n">
+        <v>40299975</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>483237</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>0.0343</v>
+      </c>
+      <c r="G13" s="8" t="n">
         <v>29868916</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="H13" s="9" t="n">
         <v>400721.38</v>
       </c>
-      <c r="F13" s="10" t="n">
+      <c r="I13" s="10" t="n">
         <v>0.0311</v>
       </c>
-      <c r="G13" s="8" t="n">
+      <c r="J13" s="8" t="n">
         <v>27771661</v>
       </c>
-      <c r="H13" s="9" t="n">
+      <c r="K13" s="9" t="n">
         <v>385776.14</v>
       </c>
-      <c r="I13" s="10" t="n">
+      <c r="L13" s="10" t="n">
         <v>0.0287</v>
       </c>
-      <c r="J13" s="8" t="n">
+      <c r="M13" s="8" t="n">
         <v>23460156</v>
       </c>
-      <c r="K13" s="9" t="n">
+      <c r="N13" s="9" t="n">
         <v>397790.41</v>
       </c>
-      <c r="L13" s="10" t="n">
+      <c r="O13" s="10" t="n">
         <v>0.0297</v>
       </c>
-      <c r="M13" s="8" t="n">
+      <c r="P13" s="8" t="n">
         <v>21315882</v>
       </c>
-      <c r="N13" s="9" t="n">
+      <c r="Q13" s="9" t="n">
         <v>346020.71</v>
       </c>
-      <c r="O13" s="10" t="n">
+      <c r="R13" s="10" t="n">
         <v>0.026</v>
       </c>
-      <c r="P13" s="8" t="n">
+      <c r="S13" s="8" t="n">
         <v>19831378</v>
       </c>
-      <c r="Q13" s="9" t="n">
+      <c r="T13" s="9" t="n">
         <v>322101.24</v>
       </c>
-      <c r="R13" s="10" t="n">
+      <c r="U13" s="10" t="n">
         <v>0.0248</v>
       </c>
-      <c r="S13" s="8" t="n">
+      <c r="V13" s="8" t="n">
         <v>18138945</v>
       </c>
-      <c r="T13" s="9" t="n">
+      <c r="W13" s="9" t="n">
         <v>279611.84</v>
       </c>
-      <c r="U13" s="10" t="n">
+      <c r="X13" s="10" t="n">
         <v>0.0222</v>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v>18706995</v>
-      </c>
-      <c r="W13" s="9" t="n">
-        <v>259110.59</v>
-      </c>
-      <c r="X13" s="10" t="n">
-        <v>0.0216</v>
       </c>
       <c r="Y13" s="8" t="n">
         <v>18706995</v>
       </c>
       <c r="Z13" s="9" t="n">
-        <v>272149.36</v>
+        <v>259110.59</v>
       </c>
       <c r="AA13" s="10" t="n">
-        <v>0.0237</v>
+        <v>0.0216</v>
       </c>
       <c r="AB13" s="8" t="n">
         <v>18706995</v>
       </c>
       <c r="AC13" s="9" t="n">
+        <v>272149.36</v>
+      </c>
+      <c r="AD13" s="10" t="n">
+        <v>0.0237</v>
+      </c>
+      <c r="AE13" s="8" t="n">
+        <v>18706995</v>
+      </c>
+      <c r="AF13" s="9" t="n">
         <v>274599.98</v>
       </c>
-      <c r="AD13" s="10" t="n">
+      <c r="AG13" s="10" t="n">
         <v>0.0242</v>
       </c>
-      <c r="AE13" s="8" t="n">
+      <c r="AH13" s="8" t="n">
         <v>18558995</v>
       </c>
-      <c r="AF13" s="9" t="n">
+      <c r="AI13" s="9" t="n">
         <v>320810.79</v>
       </c>
-      <c r="AG13" s="10" t="n">
+      <c r="AJ13" s="10" t="n">
         <v>0.0291</v>
       </c>
-      <c r="AH13" s="8" t="n">
+      <c r="AK13" s="8" t="n">
         <v>18341573</v>
       </c>
-      <c r="AI13" s="9" t="n">
+      <c r="AL13" s="9" t="n">
         <v>300178.18</v>
       </c>
-      <c r="AJ13" s="10" t="n">
+      <c r="AM13" s="10" t="n">
         <v>0.0289</v>
-      </c>
-      <c r="AK13" s="8" t="n">
-        <v>18706973</v>
-      </c>
-      <c r="AL13" s="9" t="n">
-        <v>293231.8</v>
-      </c>
-      <c r="AM13" s="10" t="n">
-        <v>0.0298</v>
       </c>
       <c r="AN13" s="8" t="n">
         <v>18706973</v>
       </c>
       <c r="AO13" s="9" t="n">
-        <v>297908.55</v>
+        <v>293231.8</v>
       </c>
       <c r="AP13" s="10" t="n">
-        <v>0.0319</v>
+        <v>0.0298</v>
       </c>
       <c r="AQ13" s="8" t="n">
         <v>18706973</v>
       </c>
       <c r="AR13" s="9" t="n">
-        <v>294644.18</v>
+        <v>297908.55</v>
       </c>
       <c r="AS13" s="10" t="n">
-        <v>0.0335</v>
+        <v>0.0319</v>
       </c>
       <c r="AT13" s="8" t="n">
         <v>18706973</v>
       </c>
       <c r="AU13" s="9" t="n">
+        <v>294644.18</v>
+      </c>
+      <c r="AV13" s="10" t="n">
+        <v>0.0335</v>
+      </c>
+      <c r="AW13" s="8" t="n">
+        <v>18706973</v>
+      </c>
+      <c r="AX13" s="9" t="n">
         <v>322779.47</v>
       </c>
-      <c r="AV13" s="10" t="n">
+      <c r="AY13" s="10" t="n">
         <v>0.036</v>
       </c>
     </row>
@@ -2462,138 +2574,147 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
+        <v>16026000</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>496405.35</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>0.0352</v>
+      </c>
+      <c r="G14" s="8" t="n">
         <v>14645626</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="H14" s="9" t="n">
         <v>432734.31</v>
       </c>
-      <c r="F14" s="10" t="n">
+      <c r="I14" s="10" t="n">
         <v>0.0336</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>13974725</v>
-      </c>
-      <c r="H14" s="9" t="n">
-        <v>474777.31</v>
-      </c>
-      <c r="I14" s="10" t="n">
-        <v>0.0354</v>
       </c>
       <c r="J14" s="8" t="n">
         <v>13974725</v>
       </c>
       <c r="K14" s="9" t="n">
+        <v>474777.31</v>
+      </c>
+      <c r="L14" s="10" t="n">
+        <v>0.0354</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>13974725</v>
+      </c>
+      <c r="N14" s="9" t="n">
         <v>479584.61</v>
       </c>
-      <c r="L14" s="10" t="n">
+      <c r="O14" s="10" t="n">
         <v>0.0358</v>
       </c>
-      <c r="M14" s="8" t="n">
+      <c r="P14" s="8" t="n">
         <v>13033470</v>
       </c>
-      <c r="N14" s="9" t="n">
+      <c r="Q14" s="9" t="n">
         <v>483437.47</v>
       </c>
-      <c r="O14" s="10" t="n">
+      <c r="R14" s="10" t="n">
         <v>0.0363</v>
-      </c>
-      <c r="P14" s="8" t="n">
-        <v>12435671</v>
-      </c>
-      <c r="Q14" s="9" t="n">
-        <v>467245.47</v>
-      </c>
-      <c r="R14" s="10" t="n">
-        <v>0.036</v>
       </c>
       <c r="S14" s="8" t="n">
         <v>12435671</v>
       </c>
       <c r="T14" s="9" t="n">
+        <v>467245.47</v>
+      </c>
+      <c r="U14" s="10" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v>12435671</v>
+      </c>
+      <c r="W14" s="9" t="n">
         <v>433656.72</v>
       </c>
-      <c r="U14" s="10" t="n">
+      <c r="X14" s="10" t="n">
         <v>0.0345</v>
-      </c>
-      <c r="V14" s="8" t="n">
-        <v>12335671</v>
-      </c>
-      <c r="W14" s="9" t="n">
-        <v>422743.45</v>
-      </c>
-      <c r="X14" s="10" t="n">
-        <v>0.0353</v>
       </c>
       <c r="Y14" s="8" t="n">
         <v>12335671</v>
       </c>
       <c r="Z14" s="9" t="n">
-        <v>394679.79</v>
+        <v>422743.45</v>
       </c>
       <c r="AA14" s="10" t="n">
-        <v>0.0343</v>
+        <v>0.0353</v>
       </c>
       <c r="AB14" s="8" t="n">
         <v>12335671</v>
       </c>
       <c r="AC14" s="9" t="n">
-        <v>395123.88</v>
+        <v>394679.79</v>
       </c>
       <c r="AD14" s="10" t="n">
-        <v>0.0349</v>
+        <v>0.0343</v>
       </c>
       <c r="AE14" s="8" t="n">
         <v>12335671</v>
       </c>
       <c r="AF14" s="9" t="n">
+        <v>395123.88</v>
+      </c>
+      <c r="AG14" s="10" t="n">
+        <v>0.0349</v>
+      </c>
+      <c r="AH14" s="8" t="n">
+        <v>12335671</v>
+      </c>
+      <c r="AI14" s="9" t="n">
         <v>392669.08</v>
       </c>
-      <c r="AG14" s="10" t="n">
+      <c r="AJ14" s="10" t="n">
         <v>0.0356</v>
       </c>
-      <c r="AH14" s="8" t="n">
+      <c r="AK14" s="8" t="n">
         <v>12231374</v>
       </c>
-      <c r="AI14" s="9" t="n">
+      <c r="AL14" s="9" t="n">
         <v>364103.54</v>
       </c>
-      <c r="AJ14" s="10" t="n">
+      <c r="AM14" s="10" t="n">
         <v>0.0351</v>
       </c>
-      <c r="AK14" s="8" t="n">
+      <c r="AN14" s="8" t="n">
         <v>11040212</v>
       </c>
-      <c r="AL14" s="9" t="n">
+      <c r="AO14" s="9" t="n">
         <v>323345.73</v>
       </c>
-      <c r="AM14" s="10" t="n">
+      <c r="AP14" s="10" t="n">
         <v>0.0328</v>
       </c>
-      <c r="AN14" s="8" t="n">
+      <c r="AQ14" s="8" t="n">
         <v>10399289</v>
       </c>
-      <c r="AO14" s="9" t="n">
+      <c r="AR14" s="9" t="n">
         <v>277224.25</v>
       </c>
-      <c r="AP14" s="10" t="n">
+      <c r="AS14" s="10" t="n">
         <v>0.0297</v>
       </c>
-      <c r="AQ14" s="8" t="n">
+      <c r="AT14" s="8" t="n">
         <v>10068665</v>
       </c>
-      <c r="AR14" s="9" t="n">
+      <c r="AU14" s="9" t="n">
         <v>260285.06</v>
       </c>
-      <c r="AS14" s="10" t="n">
+      <c r="AV14" s="10" t="n">
         <v>0.0296</v>
       </c>
-      <c r="AT14" s="8" t="n">
+      <c r="AW14" s="8" t="n">
         <v>9331737</v>
       </c>
-      <c r="AU14" s="9" t="n">
+      <c r="AX14" s="9" t="n">
         <v>279004.94</v>
       </c>
-      <c r="AV14" s="10" t="n">
+      <c r="AY14" s="10" t="n">
         <v>0.0311</v>
       </c>
     </row>
@@ -2614,138 +2735,147 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
+        <v>36169670</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>427453.16</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="G15" s="8" t="n">
         <v>26944033</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="H15" s="9" t="n">
         <v>336962.08</v>
       </c>
-      <c r="F15" s="10" t="n">
+      <c r="I15" s="10" t="n">
         <v>0.0261</v>
       </c>
-      <c r="G15" s="8" t="n">
+      <c r="J15" s="8" t="n">
         <v>20693682</v>
       </c>
-      <c r="H15" s="9" t="n">
+      <c r="K15" s="9" t="n">
         <v>269038.56</v>
       </c>
-      <c r="I15" s="10" t="n">
+      <c r="L15" s="10" t="n">
         <v>0.02</v>
       </c>
-      <c r="J15" s="8" t="n">
+      <c r="M15" s="8" t="n">
         <v>16509541</v>
       </c>
-      <c r="K15" s="9" t="n">
+      <c r="N15" s="9" t="n">
         <v>270921.57</v>
       </c>
-      <c r="L15" s="10" t="n">
+      <c r="O15" s="10" t="n">
         <v>0.0202</v>
       </c>
-      <c r="M15" s="8" t="n">
+      <c r="P15" s="8" t="n">
         <v>16417936</v>
       </c>
-      <c r="N15" s="9" t="n">
+      <c r="Q15" s="9" t="n">
         <v>265215.34</v>
       </c>
-      <c r="O15" s="10" t="n">
+      <c r="R15" s="10" t="n">
         <v>0.0199</v>
       </c>
-      <c r="P15" s="8" t="n">
+      <c r="S15" s="8" t="n">
         <v>17621740</v>
       </c>
-      <c r="Q15" s="9" t="n">
+      <c r="T15" s="9" t="n">
         <v>274916.77</v>
       </c>
-      <c r="R15" s="10" t="n">
+      <c r="U15" s="10" t="n">
         <v>0.0212</v>
-      </c>
-      <c r="S15" s="8" t="n">
-        <v>9306473</v>
-      </c>
-      <c r="T15" s="9" t="n">
-        <v>137949.85</v>
-      </c>
-      <c r="U15" s="10" t="n">
-        <v>0.011</v>
       </c>
       <c r="V15" s="8" t="n">
         <v>9306473</v>
       </c>
       <c r="W15" s="9" t="n">
-        <v>134180.73</v>
+        <v>137949.85</v>
       </c>
       <c r="X15" s="10" t="n">
-        <v>0.0112</v>
+        <v>0.011</v>
       </c>
       <c r="Y15" s="8" t="n">
         <v>9306473</v>
       </c>
       <c r="Z15" s="9" t="n">
-        <v>136767.93</v>
+        <v>134180.73</v>
       </c>
       <c r="AA15" s="10" t="n">
-        <v>0.0119</v>
+        <v>0.0112</v>
       </c>
       <c r="AB15" s="8" t="n">
         <v>9306473</v>
       </c>
       <c r="AC15" s="9" t="n">
-        <v>140434.68</v>
+        <v>136767.93</v>
       </c>
       <c r="AD15" s="10" t="n">
-        <v>0.0124</v>
+        <v>0.0119</v>
       </c>
       <c r="AE15" s="8" t="n">
         <v>9306473</v>
       </c>
       <c r="AF15" s="9" t="n">
-        <v>149071.08</v>
+        <v>140434.68</v>
       </c>
       <c r="AG15" s="10" t="n">
-        <v>0.0135</v>
+        <v>0.0124</v>
       </c>
       <c r="AH15" s="8" t="n">
         <v>9306473</v>
       </c>
       <c r="AI15" s="9" t="n">
-        <v>145432.25</v>
+        <v>149071.08</v>
       </c>
       <c r="AJ15" s="10" t="n">
-        <v>0.014</v>
+        <v>0.0135</v>
       </c>
       <c r="AK15" s="8" t="n">
         <v>9306473</v>
       </c>
       <c r="AL15" s="9" t="n">
-        <v>139606.4</v>
+        <v>145432.25</v>
       </c>
       <c r="AM15" s="10" t="n">
-        <v>0.0142</v>
+        <v>0.014</v>
       </c>
       <c r="AN15" s="8" t="n">
         <v>9306473</v>
       </c>
       <c r="AO15" s="9" t="n">
-        <v>146172.12</v>
+        <v>139606.4</v>
       </c>
       <c r="AP15" s="10" t="n">
-        <v>0.0156</v>
+        <v>0.0142</v>
       </c>
       <c r="AQ15" s="8" t="n">
         <v>9306473</v>
       </c>
       <c r="AR15" s="9" t="n">
-        <v>157065.34</v>
+        <v>146172.12</v>
       </c>
       <c r="AS15" s="10" t="n">
-        <v>0.0178</v>
+        <v>0.0156</v>
       </c>
       <c r="AT15" s="8" t="n">
         <v>9306473</v>
       </c>
       <c r="AU15" s="9" t="n">
+        <v>157065.34</v>
+      </c>
+      <c r="AV15" s="10" t="n">
+        <v>0.0178</v>
+      </c>
+      <c r="AW15" s="8" t="n">
+        <v>9306473</v>
+      </c>
+      <c r="AX15" s="9" t="n">
         <v>174943.08</v>
       </c>
-      <c r="AV15" s="10" t="n">
+      <c r="AY15" s="10" t="n">
         <v>0.0195</v>
       </c>
     </row>
@@ -2766,10 +2896,10 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>13769904</v>
+        <v>14298956</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>172798.53</v>
+        <v>189160.89</v>
       </c>
       <c r="F16" s="10" t="n">
         <v>0.0134</v>
@@ -2778,126 +2908,135 @@
         <v>13769904</v>
       </c>
       <c r="H16" s="9" t="n">
+        <v>172798.53</v>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>0.0134</v>
+      </c>
+      <c r="J16" s="8" t="n">
+        <v>13769904</v>
+      </c>
+      <c r="K16" s="9" t="n">
         <v>177122.28</v>
       </c>
-      <c r="I16" s="10" t="n">
+      <c r="L16" s="10" t="n">
         <v>0.0132</v>
       </c>
-      <c r="J16" s="8" t="n">
+      <c r="M16" s="8" t="n">
         <v>14083029</v>
       </c>
-      <c r="K16" s="9" t="n">
+      <c r="N16" s="9" t="n">
         <v>171545.38</v>
       </c>
-      <c r="L16" s="10" t="n">
+      <c r="O16" s="10" t="n">
         <v>0.0128</v>
-      </c>
-      <c r="M16" s="8" t="n">
-        <v>13125545</v>
-      </c>
-      <c r="N16" s="9" t="n">
-        <v>166878.18</v>
-      </c>
-      <c r="O16" s="10" t="n">
-        <v>0.0125</v>
       </c>
       <c r="P16" s="8" t="n">
         <v>13125545</v>
       </c>
       <c r="Q16" s="9" t="n">
+        <v>166878.18</v>
+      </c>
+      <c r="R16" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="S16" s="8" t="n">
+        <v>13125545</v>
+      </c>
+      <c r="T16" s="9" t="n">
         <v>165224.36</v>
       </c>
-      <c r="R16" s="10" t="n">
+      <c r="U16" s="10" t="n">
         <v>0.0127</v>
       </c>
-      <c r="S16" s="8" t="n">
+      <c r="V16" s="8" t="n">
         <v>12775545</v>
       </c>
-      <c r="T16" s="9" t="n">
+      <c r="W16" s="9" t="n">
         <v>152999.93</v>
       </c>
-      <c r="U16" s="10" t="n">
+      <c r="X16" s="10" t="n">
         <v>0.0122</v>
       </c>
-      <c r="V16" s="8" t="n">
+      <c r="Y16" s="8" t="n">
         <v>12107943</v>
       </c>
-      <c r="W16" s="9" t="n">
+      <c r="Z16" s="9" t="n">
         <v>148164.9</v>
       </c>
-      <c r="X16" s="10" t="n">
+      <c r="AA16" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="Y16" s="8" t="n">
+      <c r="AB16" s="8" t="n">
         <v>11632943</v>
       </c>
-      <c r="Z16" s="9" t="n">
+      <c r="AC16" s="9" t="n">
         <v>146586.71</v>
       </c>
-      <c r="AA16" s="10" t="n">
+      <c r="AD16" s="10" t="n">
         <v>0.0127</v>
       </c>
-      <c r="AB16" s="8" t="n">
+      <c r="AE16" s="8" t="n">
         <v>11217622</v>
       </c>
-      <c r="AC16" s="9" t="n">
+      <c r="AF16" s="9" t="n">
         <v>142497.45</v>
       </c>
-      <c r="AD16" s="10" t="n">
+      <c r="AG16" s="10" t="n">
         <v>0.0126</v>
-      </c>
-      <c r="AE16" s="8" t="n">
-        <v>10341500</v>
-      </c>
-      <c r="AF16" s="9" t="n">
-        <v>132712.47</v>
-      </c>
-      <c r="AG16" s="10" t="n">
-        <v>0.012</v>
       </c>
       <c r="AH16" s="8" t="n">
         <v>10341500</v>
       </c>
       <c r="AI16" s="9" t="n">
+        <v>132712.47</v>
+      </c>
+      <c r="AJ16" s="10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AK16" s="8" t="n">
+        <v>10341500</v>
+      </c>
+      <c r="AL16" s="9" t="n">
         <v>129392.85</v>
-      </c>
-      <c r="AJ16" s="10" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="AK16" s="8" t="n">
-        <v>10403670</v>
-      </c>
-      <c r="AL16" s="9" t="n">
-        <v>123169.05</v>
       </c>
       <c r="AM16" s="10" t="n">
         <v>0.0125</v>
       </c>
       <c r="AN16" s="8" t="n">
+        <v>10403670</v>
+      </c>
+      <c r="AO16" s="9" t="n">
+        <v>123169.05</v>
+      </c>
+      <c r="AP16" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AQ16" s="8" t="n">
         <v>10133496</v>
       </c>
-      <c r="AO16" s="9" t="n">
+      <c r="AR16" s="9" t="n">
         <v>115947.46</v>
       </c>
-      <c r="AP16" s="10" t="n">
+      <c r="AS16" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="AQ16" s="8" t="n">
+      <c r="AT16" s="8" t="n">
         <v>9911843</v>
       </c>
-      <c r="AR16" s="9" t="n">
+      <c r="AU16" s="9" t="n">
         <v>110665.73</v>
       </c>
-      <c r="AS16" s="10" t="n">
+      <c r="AV16" s="10" t="n">
         <v>0.0126</v>
       </c>
-      <c r="AT16" s="8" t="n">
+      <c r="AW16" s="8" t="n">
         <v>7388241</v>
       </c>
-      <c r="AU16" s="9" t="n">
+      <c r="AX16" s="9" t="n">
         <v>89940.75</v>
       </c>
-      <c r="AV16" s="10" t="n">
+      <c r="AY16" s="10" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -2918,138 +3057,147 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
+        <v>14344551</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>187856.24</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="G17" s="8" t="n">
         <v>13271296</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="H17" s="9" t="n">
         <v>162467.21</v>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="I17" s="10" t="n">
         <v>0.0126</v>
       </c>
-      <c r="G17" s="8" t="n">
+      <c r="J17" s="8" t="n">
         <v>12881359</v>
       </c>
-      <c r="H17" s="9" t="n">
+      <c r="K17" s="9" t="n">
         <v>173666.48</v>
       </c>
-      <c r="I17" s="10" t="n">
+      <c r="L17" s="10" t="n">
         <v>0.0129</v>
       </c>
-      <c r="J17" s="8" t="n">
+      <c r="M17" s="8" t="n">
         <v>12623339</v>
       </c>
-      <c r="K17" s="9" t="n">
+      <c r="N17" s="9" t="n">
         <v>167133.01</v>
-      </c>
-      <c r="L17" s="10" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="M17" s="8" t="n">
-        <v>10989584</v>
-      </c>
-      <c r="N17" s="9" t="n">
-        <v>166085.58</v>
       </c>
       <c r="O17" s="10" t="n">
         <v>0.0125</v>
       </c>
       <c r="P17" s="8" t="n">
+        <v>10989584</v>
+      </c>
+      <c r="Q17" s="9" t="n">
+        <v>166085.58</v>
+      </c>
+      <c r="R17" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="S17" s="8" t="n">
         <v>10765866</v>
       </c>
-      <c r="Q17" s="9" t="n">
+      <c r="T17" s="9" t="n">
         <v>164857.71</v>
       </c>
-      <c r="R17" s="10" t="n">
+      <c r="U17" s="10" t="n">
         <v>0.0127</v>
       </c>
-      <c r="S17" s="8" t="n">
+      <c r="V17" s="8" t="n">
         <v>10173460</v>
       </c>
-      <c r="T17" s="9" t="n">
+      <c r="W17" s="9" t="n">
         <v>152734.15</v>
       </c>
-      <c r="U17" s="10" t="n">
+      <c r="X17" s="10" t="n">
         <v>0.0121</v>
       </c>
-      <c r="V17" s="8" t="n">
+      <c r="Y17" s="8" t="n">
         <v>9988840</v>
       </c>
-      <c r="W17" s="9" t="n">
+      <c r="Z17" s="9" t="n">
         <v>150162.23</v>
       </c>
-      <c r="X17" s="10" t="n">
+      <c r="AA17" s="10" t="n">
         <v>0.0125</v>
       </c>
-      <c r="Y17" s="8" t="n">
+      <c r="AB17" s="8" t="n">
         <v>8991707</v>
       </c>
-      <c r="Z17" s="9" t="n">
+      <c r="AC17" s="9" t="n">
         <v>142914.19</v>
       </c>
-      <c r="AA17" s="10" t="n">
+      <c r="AD17" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="AB17" s="8" t="n">
+      <c r="AE17" s="8" t="n">
         <v>9450707</v>
       </c>
-      <c r="AC17" s="9" t="n">
+      <c r="AF17" s="9" t="n">
         <v>146920.69</v>
       </c>
-      <c r="AD17" s="10" t="n">
+      <c r="AG17" s="10" t="n">
         <v>0.013</v>
       </c>
-      <c r="AE17" s="8" t="n">
+      <c r="AH17" s="8" t="n">
         <v>9147124</v>
       </c>
-      <c r="AF17" s="9" t="n">
+      <c r="AI17" s="9" t="n">
         <v>137746.54</v>
-      </c>
-      <c r="AG17" s="10" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="AH17" s="8" t="n">
-        <v>8881919</v>
-      </c>
-      <c r="AI17" s="9" t="n">
-        <v>130182.29</v>
       </c>
       <c r="AJ17" s="10" t="n">
         <v>0.0125</v>
       </c>
       <c r="AK17" s="8" t="n">
-        <v>7994194</v>
+        <v>8881919</v>
       </c>
       <c r="AL17" s="9" t="n">
-        <v>123918</v>
+        <v>130182.29</v>
       </c>
       <c r="AM17" s="10" t="n">
-        <v>0.0126</v>
+        <v>0.0125</v>
       </c>
       <c r="AN17" s="8" t="n">
         <v>7994194</v>
       </c>
       <c r="AO17" s="9" t="n">
+        <v>123918</v>
+      </c>
+      <c r="AP17" s="10" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="AQ17" s="8" t="n">
+        <v>7994194</v>
+      </c>
+      <c r="AR17" s="9" t="n">
         <v>115292.27</v>
       </c>
-      <c r="AP17" s="10" t="n">
+      <c r="AS17" s="10" t="n">
         <v>0.0123</v>
       </c>
-      <c r="AQ17" s="8" t="n">
+      <c r="AT17" s="8" t="n">
         <v>7755553</v>
       </c>
-      <c r="AR17" s="9" t="n">
+      <c r="AU17" s="9" t="n">
         <v>109159.41</v>
       </c>
-      <c r="AS17" s="10" t="n">
+      <c r="AV17" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="AT17" s="8" t="n">
+      <c r="AW17" s="8" t="n">
         <v>6223549</v>
       </c>
-      <c r="AU17" s="9" t="n">
+      <c r="AX17" s="9" t="n">
         <v>92071.17999999999</v>
       </c>
-      <c r="AV17" s="10" t="n">
+      <c r="AY17" s="10" t="n">
         <v>0.0103</v>
       </c>
     </row>
@@ -3070,138 +3218,147 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>18853686</v>
+        <v>19200553</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>164253.31</v>
+        <v>171249.73</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>0.0127</v>
+        <v>0.0121</v>
       </c>
       <c r="G18" s="8" t="n">
         <v>18853686</v>
       </c>
       <c r="H18" s="9" t="n">
+        <v>164253.31</v>
+      </c>
+      <c r="I18" s="10" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="J18" s="8" t="n">
+        <v>18853686</v>
+      </c>
+      <c r="K18" s="9" t="n">
         <v>173774.42</v>
       </c>
-      <c r="I18" s="10" t="n">
+      <c r="L18" s="10" t="n">
         <v>0.0129</v>
       </c>
-      <c r="J18" s="8" t="n">
+      <c r="M18" s="8" t="n">
         <v>18750502</v>
       </c>
-      <c r="K18" s="9" t="n">
+      <c r="N18" s="9" t="n">
         <v>165998.19</v>
       </c>
-      <c r="L18" s="10" t="n">
+      <c r="O18" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="M18" s="8" t="n">
+      <c r="P18" s="8" t="n">
         <v>17903094</v>
       </c>
-      <c r="N18" s="9" t="n">
+      <c r="Q18" s="9" t="n">
         <v>163696.94</v>
       </c>
-      <c r="O18" s="10" t="n">
+      <c r="R18" s="10" t="n">
         <v>0.0123</v>
       </c>
-      <c r="P18" s="8" t="n">
+      <c r="S18" s="8" t="n">
         <v>17405149</v>
       </c>
-      <c r="Q18" s="9" t="n">
+      <c r="T18" s="9" t="n">
         <v>164043.53</v>
       </c>
-      <c r="R18" s="10" t="n">
+      <c r="U18" s="10" t="n">
         <v>0.0126</v>
       </c>
-      <c r="S18" s="8" t="n">
+      <c r="V18" s="8" t="n">
         <v>15759789</v>
       </c>
-      <c r="T18" s="9" t="n">
+      <c r="W18" s="9" t="n">
         <v>153571.26</v>
       </c>
-      <c r="U18" s="10" t="n">
+      <c r="X18" s="10" t="n">
         <v>0.0122</v>
       </c>
-      <c r="V18" s="8" t="n">
+      <c r="Y18" s="8" t="n">
         <v>15148311</v>
       </c>
-      <c r="W18" s="9" t="n">
+      <c r="Z18" s="9" t="n">
         <v>148741.27</v>
       </c>
-      <c r="X18" s="10" t="n">
+      <c r="AA18" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="Y18" s="8" t="n">
+      <c r="AB18" s="8" t="n">
         <v>14786344</v>
       </c>
-      <c r="Z18" s="9" t="n">
+      <c r="AC18" s="9" t="n">
         <v>145061.43</v>
       </c>
-      <c r="AA18" s="10" t="n">
+      <c r="AD18" s="10" t="n">
         <v>0.0126</v>
       </c>
-      <c r="AB18" s="8" t="n">
+      <c r="AE18" s="8" t="n">
         <v>14470385</v>
       </c>
-      <c r="AC18" s="9" t="n">
+      <c r="AF18" s="9" t="n">
         <v>140333.79</v>
       </c>
-      <c r="AD18" s="10" t="n">
+      <c r="AG18" s="10" t="n">
         <v>0.0124</v>
-      </c>
-      <c r="AE18" s="8" t="n">
-        <v>14258435</v>
-      </c>
-      <c r="AF18" s="9" t="n">
-        <v>141151.38</v>
-      </c>
-      <c r="AG18" s="10" t="n">
-        <v>0.0128</v>
       </c>
       <c r="AH18" s="8" t="n">
         <v>14258435</v>
       </c>
       <c r="AI18" s="9" t="n">
-        <v>132603.45</v>
+        <v>141151.38</v>
       </c>
       <c r="AJ18" s="10" t="n">
         <v>0.0128</v>
       </c>
       <c r="AK18" s="8" t="n">
+        <v>14258435</v>
+      </c>
+      <c r="AL18" s="9" t="n">
+        <v>132603.45</v>
+      </c>
+      <c r="AM18" s="10" t="n">
+        <v>0.0128</v>
+      </c>
+      <c r="AN18" s="8" t="n">
         <v>13936283</v>
       </c>
-      <c r="AL18" s="9" t="n">
+      <c r="AO18" s="9" t="n">
         <v>123789.03</v>
       </c>
-      <c r="AM18" s="10" t="n">
+      <c r="AP18" s="10" t="n">
         <v>0.0126</v>
       </c>
-      <c r="AN18" s="8" t="n">
+      <c r="AQ18" s="8" t="n">
         <v>13003659</v>
       </c>
-      <c r="AO18" s="9" t="n">
+      <c r="AR18" s="9" t="n">
         <v>115264.43</v>
       </c>
-      <c r="AP18" s="10" t="n">
+      <c r="AS18" s="10" t="n">
         <v>0.0123</v>
       </c>
-      <c r="AQ18" s="8" t="n">
+      <c r="AT18" s="8" t="n">
         <v>11479604</v>
       </c>
-      <c r="AR18" s="9" t="n">
+      <c r="AU18" s="9" t="n">
         <v>100630.21</v>
       </c>
-      <c r="AS18" s="10" t="n">
+      <c r="AV18" s="10" t="n">
         <v>0.0114</v>
       </c>
-      <c r="AT18" s="8" t="n">
+      <c r="AW18" s="8" t="n">
         <v>8859127</v>
       </c>
-      <c r="AU18" s="9" t="n">
+      <c r="AX18" s="9" t="n">
         <v>85955.67999999999</v>
       </c>
-      <c r="AV18" s="10" t="n">
+      <c r="AY18" s="10" t="n">
         <v>0.009599999999999999</v>
       </c>
     </row>
@@ -3221,139 +3378,142 @@
           <t>Auto Components</t>
         </is>
       </c>
-      <c r="D19" s="8" t="n">
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="8" t="n">
         <v>2274074</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="H19" s="9" t="n">
         <v>47368.96</v>
       </c>
-      <c r="F19" s="10" t="n">
+      <c r="I19" s="10" t="n">
         <v>0.0037</v>
       </c>
-      <c r="G19" s="8" t="n">
+      <c r="J19" s="8" t="n">
         <v>2906065</v>
       </c>
-      <c r="H19" s="9" t="n">
+      <c r="K19" s="9" t="n">
         <v>69277.67999999999</v>
       </c>
-      <c r="I19" s="10" t="n">
+      <c r="L19" s="10" t="n">
         <v>0.0052</v>
-      </c>
-      <c r="J19" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="K19" s="9" t="n">
-        <v>96591.67</v>
-      </c>
-      <c r="L19" s="10" t="n">
-        <v>0.0072</v>
       </c>
       <c r="M19" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>97173.95</v>
+        <v>96591.67</v>
       </c>
       <c r="O19" s="10" t="n">
-        <v>0.0073</v>
+        <v>0.0072</v>
       </c>
       <c r="P19" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>96721.53</v>
+        <v>97173.95</v>
       </c>
       <c r="R19" s="10" t="n">
-        <v>0.0075</v>
+        <v>0.0073</v>
       </c>
       <c r="S19" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="T19" s="9" t="n">
-        <v>95502.50999999999</v>
+        <v>96721.53</v>
       </c>
       <c r="U19" s="10" t="n">
-        <v>0.0076</v>
+        <v>0.0075</v>
       </c>
       <c r="V19" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="W19" s="9" t="n">
-        <v>96130.87</v>
+        <v>95502.50999999999</v>
       </c>
       <c r="X19" s="10" t="n">
-        <v>0.008</v>
+        <v>0.0076</v>
       </c>
       <c r="Y19" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="Z19" s="9" t="n">
-        <v>95904.66</v>
+        <v>96130.87</v>
       </c>
       <c r="AA19" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.008</v>
       </c>
       <c r="AB19" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="AC19" s="9" t="n">
-        <v>112108</v>
+        <v>95904.66</v>
       </c>
       <c r="AD19" s="10" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0083</v>
       </c>
       <c r="AE19" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="AF19" s="9" t="n">
-        <v>102435.43</v>
+        <v>112108</v>
       </c>
       <c r="AG19" s="10" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="AH19" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="AI19" s="9" t="n">
-        <v>103562.29</v>
+        <v>102435.43</v>
       </c>
       <c r="AJ19" s="10" t="n">
-        <v>0.01</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="AK19" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="AL19" s="9" t="n">
-        <v>112061.92</v>
+        <v>103562.29</v>
       </c>
       <c r="AM19" s="10" t="n">
-        <v>0.0114</v>
+        <v>0.01</v>
       </c>
       <c r="AN19" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="AO19" s="9" t="n">
-        <v>107022.46</v>
+        <v>112061.92</v>
       </c>
       <c r="AP19" s="10" t="n">
-        <v>0.0115</v>
+        <v>0.0114</v>
       </c>
       <c r="AQ19" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="AR19" s="9" t="n">
-        <v>109571.51</v>
+        <v>107022.46</v>
       </c>
       <c r="AS19" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.0115</v>
       </c>
       <c r="AT19" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="AU19" s="9" t="n">
+        <v>109571.51</v>
+      </c>
+      <c r="AV19" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AW19" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="AX19" s="9" t="n">
         <v>116089.71</v>
       </c>
-      <c r="AV19" s="10" t="n">
+      <c r="AY19" s="10" t="n">
         <v>0.0129</v>
       </c>
     </row>
@@ -3377,7 +3537,7 @@
         <v>80755676</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>92667.14</v>
+        <v>101098.03</v>
       </c>
       <c r="F20" s="10" t="n">
         <v>0.0072</v>
@@ -3386,16 +3546,16 @@
         <v>80755676</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>101461.43</v>
+        <v>92667.14</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>0.0076</v>
+        <v>0.0072</v>
       </c>
       <c r="J20" s="8" t="n">
         <v>80755676</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>102390.12</v>
+        <v>101461.43</v>
       </c>
       <c r="L20" s="10" t="n">
         <v>0.0076</v>
@@ -3404,79 +3564,79 @@
         <v>80755676</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>108390.27</v>
+        <v>102390.12</v>
       </c>
       <c r="O20" s="10" t="n">
-        <v>0.0081</v>
+        <v>0.0076</v>
       </c>
       <c r="P20" s="8" t="n">
         <v>80755676</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>112484.58</v>
+        <v>108390.27</v>
       </c>
       <c r="R20" s="10" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0081</v>
       </c>
       <c r="S20" s="8" t="n">
         <v>80755676</v>
       </c>
       <c r="T20" s="9" t="n">
-        <v>112298.84</v>
+        <v>112484.58</v>
       </c>
       <c r="U20" s="10" t="n">
-        <v>0.0089</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="V20" s="8" t="n">
         <v>80755676</v>
       </c>
       <c r="W20" s="9" t="n">
+        <v>112298.84</v>
+      </c>
+      <c r="X20" s="10" t="n">
+        <v>0.0089</v>
+      </c>
+      <c r="Y20" s="8" t="n">
+        <v>80755676</v>
+      </c>
+      <c r="Z20" s="9" t="n">
         <v>112403.83</v>
       </c>
-      <c r="X20" s="10" t="n">
+      <c r="AA20" s="10" t="n">
         <v>0.0094</v>
       </c>
-      <c r="Y20" s="8" t="n">
+      <c r="AB20" s="8" t="n">
         <v>73511702</v>
       </c>
-      <c r="Z20" s="9" t="n">
+      <c r="AC20" s="9" t="n">
         <v>102769.36</v>
       </c>
-      <c r="AA20" s="10" t="n">
+      <c r="AD20" s="10" t="n">
         <v>0.0089</v>
-      </c>
-      <c r="AB20" s="8" t="n">
-        <v>44206584</v>
-      </c>
-      <c r="AC20" s="9" t="n">
-        <v>59811.51</v>
-      </c>
-      <c r="AD20" s="10" t="n">
-        <v>0.0053</v>
       </c>
       <c r="AE20" s="8" t="n">
         <v>44206584</v>
       </c>
       <c r="AF20" s="9" t="n">
-        <v>85367.33</v>
+        <v>59811.51</v>
       </c>
       <c r="AG20" s="10" t="n">
-        <v>0.0077</v>
+        <v>0.0053</v>
       </c>
       <c r="AH20" s="8" t="n">
         <v>44206584</v>
       </c>
       <c r="AI20" s="9" t="n">
-        <v>88656.3</v>
+        <v>85367.33</v>
       </c>
       <c r="AJ20" s="10" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0077</v>
       </c>
       <c r="AK20" s="8" t="n">
         <v>44206584</v>
       </c>
       <c r="AL20" s="9" t="n">
-        <v>84147.23</v>
+        <v>88656.3</v>
       </c>
       <c r="AM20" s="10" t="n">
         <v>0.008500000000000001</v>
@@ -3485,27 +3645,36 @@
         <v>44206584</v>
       </c>
       <c r="AO20" s="9" t="n">
-        <v>77701.91</v>
+        <v>84147.23</v>
       </c>
       <c r="AP20" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="AQ20" s="8" t="n">
         <v>44206584</v>
       </c>
       <c r="AR20" s="9" t="n">
-        <v>68931.33</v>
+        <v>77701.91</v>
       </c>
       <c r="AS20" s="10" t="n">
-        <v>0.0078</v>
+        <v>0.0083</v>
       </c>
       <c r="AT20" s="8" t="n">
         <v>44206584</v>
       </c>
       <c r="AU20" s="9" t="n">
+        <v>68931.33</v>
+      </c>
+      <c r="AV20" s="10" t="n">
+        <v>0.0078</v>
+      </c>
+      <c r="AW20" s="8" t="n">
+        <v>44206584</v>
+      </c>
+      <c r="AX20" s="9" t="n">
         <v>77184.7</v>
       </c>
-      <c r="AV20" s="10" t="n">
+      <c r="AY20" s="10" t="n">
         <v>0.0086</v>
       </c>
     </row>
@@ -3552,58 +3721,61 @@
       <c r="AB21" s="8" t="n"/>
       <c r="AC21" s="9" t="n"/>
       <c r="AD21" s="10" t="n"/>
-      <c r="AE21" s="8" t="n">
+      <c r="AE21" s="8" t="n"/>
+      <c r="AF21" s="9" t="n"/>
+      <c r="AG21" s="10" t="n"/>
+      <c r="AH21" s="8" t="n">
         <v>591805</v>
       </c>
-      <c r="AF21" s="9" t="n">
+      <c r="AI21" s="9" t="n">
         <v>5149</v>
       </c>
-      <c r="AG21" s="10" t="n">
+      <c r="AJ21" s="10" t="n">
         <v>0.0005</v>
       </c>
-      <c r="AH21" s="8" t="n">
+      <c r="AK21" s="8" t="n">
         <v>5392631</v>
       </c>
-      <c r="AI21" s="9" t="n">
+      <c r="AL21" s="9" t="n">
         <v>43674.92</v>
       </c>
-      <c r="AJ21" s="10" t="n">
+      <c r="AM21" s="10" t="n">
         <v>0.0042</v>
       </c>
-      <c r="AK21" s="8" t="n">
+      <c r="AN21" s="8" t="n">
         <v>8585949</v>
       </c>
-      <c r="AL21" s="9" t="n">
+      <c r="AO21" s="9" t="n">
         <v>56044.78</v>
       </c>
-      <c r="AM21" s="10" t="n">
+      <c r="AP21" s="10" t="n">
         <v>0.0057</v>
       </c>
-      <c r="AN21" s="8" t="n">
+      <c r="AQ21" s="8" t="n">
         <v>10913294</v>
       </c>
-      <c r="AO21" s="9" t="n">
+      <c r="AR21" s="9" t="n">
         <v>67154.95</v>
       </c>
-      <c r="AP21" s="10" t="n">
+      <c r="AS21" s="10" t="n">
         <v>0.0072</v>
-      </c>
-      <c r="AQ21" s="8" t="n">
-        <v>12053879</v>
-      </c>
-      <c r="AR21" s="9" t="n">
-        <v>70937.08</v>
-      </c>
-      <c r="AS21" s="10" t="n">
-        <v>0.0081</v>
       </c>
       <c r="AT21" s="8" t="n">
         <v>12053879</v>
       </c>
       <c r="AU21" s="9" t="n">
+        <v>70937.08</v>
+      </c>
+      <c r="AV21" s="10" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="AW21" s="8" t="n">
+        <v>12053879</v>
+      </c>
+      <c r="AX21" s="9" t="n">
         <v>76801.28999999999</v>
       </c>
-      <c r="AV21" s="10" t="n">
+      <c r="AY21" s="10" t="n">
         <v>0.0086</v>
       </c>
     </row>
@@ -3632,112 +3804,115 @@
       <c r="J22" s="8" t="n"/>
       <c r="K22" s="9" t="n"/>
       <c r="L22" s="10" t="n"/>
-      <c r="M22" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="N22" s="9" t="n">
-        <v>88833.99000000001</v>
-      </c>
-      <c r="O22" s="10" t="n">
-        <v>0.0067</v>
-      </c>
+      <c r="M22" s="8" t="n"/>
+      <c r="N22" s="9" t="n"/>
+      <c r="O22" s="10" t="n"/>
       <c r="P22" s="8" t="n">
         <v>797719</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>80358.22</v>
+        <v>88833.99000000001</v>
       </c>
       <c r="R22" s="10" t="n">
-        <v>0.0062</v>
+        <v>0.0067</v>
       </c>
       <c r="S22" s="8" t="n">
         <v>797719</v>
       </c>
       <c r="T22" s="9" t="n">
-        <v>73737.16</v>
+        <v>80358.22</v>
       </c>
       <c r="U22" s="10" t="n">
-        <v>0.0059</v>
+        <v>0.0062</v>
       </c>
       <c r="V22" s="8" t="n">
         <v>797719</v>
       </c>
       <c r="W22" s="9" t="n">
-        <v>62190.17</v>
+        <v>73737.16</v>
       </c>
       <c r="X22" s="10" t="n">
-        <v>0.0052</v>
+        <v>0.0059</v>
       </c>
       <c r="Y22" s="8" t="n">
         <v>797719</v>
       </c>
       <c r="Z22" s="9" t="n">
-        <v>58951.43</v>
+        <v>62190.17</v>
       </c>
       <c r="AA22" s="10" t="n">
-        <v>0.0051</v>
+        <v>0.0052</v>
       </c>
       <c r="AB22" s="8" t="n">
         <v>797719</v>
       </c>
       <c r="AC22" s="9" t="n">
-        <v>61368.52</v>
+        <v>58951.43</v>
       </c>
       <c r="AD22" s="10" t="n">
-        <v>0.0054</v>
+        <v>0.0051</v>
       </c>
       <c r="AE22" s="8" t="n">
         <v>797719</v>
       </c>
       <c r="AF22" s="9" t="n">
-        <v>71347.99000000001</v>
+        <v>61368.52</v>
       </c>
       <c r="AG22" s="10" t="n">
-        <v>0.0065</v>
+        <v>0.0054</v>
       </c>
       <c r="AH22" s="8" t="n">
         <v>797719</v>
       </c>
       <c r="AI22" s="9" t="n">
-        <v>52665.41</v>
+        <v>71347.99000000001</v>
       </c>
       <c r="AJ22" s="10" t="n">
-        <v>0.0051</v>
+        <v>0.0065</v>
       </c>
       <c r="AK22" s="8" t="n">
         <v>797719</v>
       </c>
       <c r="AL22" s="9" t="n">
-        <v>48884.22</v>
+        <v>52665.41</v>
       </c>
       <c r="AM22" s="10" t="n">
-        <v>0.005</v>
+        <v>0.0051</v>
       </c>
       <c r="AN22" s="8" t="n">
         <v>797719</v>
       </c>
       <c r="AO22" s="9" t="n">
-        <v>42372.84</v>
+        <v>48884.22</v>
       </c>
       <c r="AP22" s="10" t="n">
-        <v>0.0045</v>
+        <v>0.005</v>
       </c>
       <c r="AQ22" s="8" t="n">
         <v>797719</v>
       </c>
       <c r="AR22" s="9" t="n">
-        <v>39819.34</v>
+        <v>42372.84</v>
       </c>
       <c r="AS22" s="10" t="n">
         <v>0.0045</v>
       </c>
       <c r="AT22" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AU22" s="9" t="n">
+        <v>39819.34</v>
+      </c>
+      <c r="AV22" s="10" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="AW22" s="8" t="n">
         <v>882136</v>
       </c>
-      <c r="AU22" s="9" t="n">
+      <c r="AX22" s="9" t="n">
         <v>50572.42</v>
       </c>
-      <c r="AV22" s="10" t="n">
+      <c r="AY22" s="10" t="n">
         <v>0.0056</v>
       </c>
     </row>
@@ -3761,7 +3936,7 @@
         <v>1995914</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>32040.41</v>
+        <v>35259.82</v>
       </c>
       <c r="F23" s="10" t="n">
         <v>0.0025</v>
@@ -3770,106 +3945,106 @@
         <v>1995914</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>36543.19</v>
+        <v>32040.41</v>
       </c>
       <c r="I23" s="10" t="n">
-        <v>0.0027</v>
+        <v>0.0025</v>
       </c>
       <c r="J23" s="8" t="n">
         <v>1995914</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>35285.76</v>
+        <v>36543.19</v>
       </c>
       <c r="L23" s="10" t="n">
-        <v>0.0026</v>
+        <v>0.0027</v>
       </c>
       <c r="M23" s="8" t="n">
         <v>1995914</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>37762.69</v>
+        <v>35285.76</v>
       </c>
       <c r="O23" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.0026</v>
       </c>
       <c r="P23" s="8" t="n">
         <v>1995914</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>38830.51</v>
+        <v>37762.69</v>
       </c>
       <c r="R23" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0028</v>
       </c>
       <c r="S23" s="8" t="n">
         <v>1995914</v>
       </c>
       <c r="T23" s="9" t="n">
-        <v>35076.19</v>
+        <v>38830.51</v>
       </c>
       <c r="U23" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.003</v>
       </c>
       <c r="V23" s="8" t="n">
         <v>1995914</v>
       </c>
       <c r="W23" s="9" t="n">
-        <v>34681</v>
+        <v>35076.19</v>
       </c>
       <c r="X23" s="10" t="n">
-        <v>0.0029</v>
+        <v>0.0028</v>
       </c>
       <c r="Y23" s="8" t="n">
         <v>1995914</v>
       </c>
       <c r="Z23" s="9" t="n">
-        <v>35004.34</v>
+        <v>34681</v>
       </c>
       <c r="AA23" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0029</v>
       </c>
       <c r="AB23" s="8" t="n">
         <v>1995914</v>
       </c>
       <c r="AC23" s="9" t="n">
-        <v>38225.74</v>
+        <v>35004.34</v>
       </c>
       <c r="AD23" s="10" t="n">
-        <v>0.0034</v>
+        <v>0.003</v>
       </c>
       <c r="AE23" s="8" t="n">
         <v>1995914</v>
       </c>
       <c r="AF23" s="9" t="n">
-        <v>43319.32</v>
+        <v>38225.74</v>
       </c>
       <c r="AG23" s="10" t="n">
-        <v>0.0039</v>
+        <v>0.0034</v>
       </c>
       <c r="AH23" s="8" t="n">
         <v>1995914</v>
       </c>
       <c r="AI23" s="9" t="n">
-        <v>34806.74</v>
+        <v>43319.32</v>
       </c>
       <c r="AJ23" s="10" t="n">
-        <v>0.0034</v>
+        <v>0.0039</v>
       </c>
       <c r="AK23" s="8" t="n">
         <v>1995914</v>
       </c>
       <c r="AL23" s="9" t="n">
-        <v>35138.07</v>
+        <v>34806.74</v>
       </c>
       <c r="AM23" s="10" t="n">
-        <v>0.0036</v>
+        <v>0.0034</v>
       </c>
       <c r="AN23" s="8" t="n">
         <v>1995914</v>
       </c>
       <c r="AO23" s="9" t="n">
-        <v>33771.86</v>
+        <v>35138.07</v>
       </c>
       <c r="AP23" s="10" t="n">
         <v>0.0036</v>
@@ -3878,18 +4053,27 @@
         <v>1995914</v>
       </c>
       <c r="AR23" s="9" t="n">
-        <v>28830.98</v>
+        <v>33771.86</v>
       </c>
       <c r="AS23" s="10" t="n">
-        <v>0.0033</v>
+        <v>0.0036</v>
       </c>
       <c r="AT23" s="8" t="n">
         <v>1995914</v>
       </c>
       <c r="AU23" s="9" t="n">
+        <v>28830.98</v>
+      </c>
+      <c r="AV23" s="10" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="AW23" s="8" t="n">
+        <v>1995914</v>
+      </c>
+      <c r="AX23" s="9" t="n">
         <v>27686.32</v>
       </c>
-      <c r="AV23" s="10" t="n">
+      <c r="AY23" s="10" t="n">
         <v>0.0031</v>
       </c>
     </row>
@@ -3930,76 +4114,79 @@
       <c r="V24" s="8" t="n"/>
       <c r="W24" s="9" t="n"/>
       <c r="X24" s="10" t="n"/>
-      <c r="Y24" s="8" t="n">
+      <c r="Y24" s="8" t="n"/>
+      <c r="Z24" s="9" t="n"/>
+      <c r="AA24" s="10" t="n"/>
+      <c r="AB24" s="8" t="n">
         <v>218075</v>
       </c>
-      <c r="Z24" s="9" t="n">
+      <c r="AC24" s="9" t="n">
         <v>3019.03</v>
       </c>
-      <c r="AA24" s="10" t="n">
+      <c r="AD24" s="10" t="n">
         <v>0.0003</v>
       </c>
-      <c r="AB24" s="8" t="n">
+      <c r="AE24" s="8" t="n">
         <v>566216</v>
       </c>
-      <c r="AC24" s="9" t="n">
+      <c r="AF24" s="9" t="n">
         <v>8345.459999999999</v>
       </c>
-      <c r="AD24" s="10" t="n">
+      <c r="AG24" s="10" t="n">
         <v>0.0007</v>
       </c>
-      <c r="AE24" s="8" t="n">
+      <c r="AH24" s="8" t="n">
         <v>1311557</v>
       </c>
-      <c r="AF24" s="9" t="n">
+      <c r="AI24" s="9" t="n">
         <v>18228.02</v>
       </c>
-      <c r="AG24" s="10" t="n">
+      <c r="AJ24" s="10" t="n">
         <v>0.0017</v>
       </c>
-      <c r="AH24" s="8" t="n">
+      <c r="AK24" s="8" t="n">
         <v>1641095</v>
       </c>
-      <c r="AI24" s="9" t="n">
+      <c r="AL24" s="9" t="n">
         <v>23382.32</v>
       </c>
-      <c r="AJ24" s="10" t="n">
+      <c r="AM24" s="10" t="n">
         <v>0.0023</v>
       </c>
-      <c r="AK24" s="8" t="n">
+      <c r="AN24" s="8" t="n">
         <v>1857217</v>
       </c>
-      <c r="AL24" s="9" t="n">
+      <c r="AO24" s="9" t="n">
         <v>26023.32</v>
       </c>
-      <c r="AM24" s="10" t="n">
+      <c r="AP24" s="10" t="n">
         <v>0.0026</v>
-      </c>
-      <c r="AN24" s="8" t="n">
-        <v>1926988</v>
-      </c>
-      <c r="AO24" s="9" t="n">
-        <v>28941.43</v>
-      </c>
-      <c r="AP24" s="10" t="n">
-        <v>0.0031</v>
       </c>
       <c r="AQ24" s="8" t="n">
         <v>1926988</v>
       </c>
       <c r="AR24" s="9" t="n">
+        <v>28941.43</v>
+      </c>
+      <c r="AS24" s="10" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="AT24" s="8" t="n">
+        <v>1926988</v>
+      </c>
+      <c r="AU24" s="9" t="n">
         <v>26117.43</v>
       </c>
-      <c r="AS24" s="10" t="n">
+      <c r="AV24" s="10" t="n">
         <v>0.003</v>
       </c>
-      <c r="AT24" s="8" t="n">
+      <c r="AW24" s="8" t="n">
         <v>2246361</v>
       </c>
-      <c r="AU24" s="9" t="n">
+      <c r="AX24" s="9" t="n">
         <v>32421.73</v>
       </c>
-      <c r="AV24" s="10" t="n">
+      <c r="AY24" s="10" t="n">
         <v>0.0036</v>
       </c>
     </row>
@@ -4023,7 +4210,7 @@
         <v>2264603</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>25349.97</v>
+        <v>28805.75</v>
       </c>
       <c r="F25" s="10" t="n">
         <v>0.002</v>
@@ -4032,61 +4219,61 @@
         <v>2264603</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>28810.28</v>
+        <v>25349.97</v>
       </c>
       <c r="I25" s="10" t="n">
-        <v>0.0021</v>
+        <v>0.002</v>
       </c>
       <c r="J25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>29897.29</v>
+        <v>28810.28</v>
       </c>
       <c r="L25" s="10" t="n">
-        <v>0.0022</v>
+        <v>0.0021</v>
       </c>
       <c r="M25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>32691.81</v>
+        <v>29897.29</v>
       </c>
       <c r="O25" s="10" t="n">
-        <v>0.0025</v>
+        <v>0.0022</v>
       </c>
       <c r="P25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>36623.16</v>
+        <v>32691.81</v>
       </c>
       <c r="R25" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.0025</v>
       </c>
       <c r="S25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="T25" s="9" t="n">
-        <v>35943.78</v>
+        <v>36623.16</v>
       </c>
       <c r="U25" s="10" t="n">
-        <v>0.0029</v>
+        <v>0.0028</v>
       </c>
       <c r="V25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="W25" s="9" t="n">
-        <v>33031.5</v>
+        <v>35943.78</v>
       </c>
       <c r="X25" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.0029</v>
       </c>
       <c r="Y25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="Z25" s="9" t="n">
-        <v>32257.01</v>
+        <v>33031.5</v>
       </c>
       <c r="AA25" s="10" t="n">
         <v>0.0028</v>
@@ -4095,43 +4282,43 @@
         <v>2264603</v>
       </c>
       <c r="AC25" s="9" t="n">
-        <v>33534.24</v>
+        <v>32257.01</v>
       </c>
       <c r="AD25" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0028</v>
       </c>
       <c r="AE25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="AF25" s="9" t="n">
-        <v>40626.98</v>
+        <v>33534.24</v>
       </c>
       <c r="AG25" s="10" t="n">
-        <v>0.0037</v>
+        <v>0.003</v>
       </c>
       <c r="AH25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="AI25" s="9" t="n">
-        <v>34641.63</v>
+        <v>40626.98</v>
       </c>
       <c r="AJ25" s="10" t="n">
-        <v>0.0033</v>
+        <v>0.0037</v>
       </c>
       <c r="AK25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="AL25" s="9" t="n">
-        <v>29892.76</v>
+        <v>34641.63</v>
       </c>
       <c r="AM25" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0033</v>
       </c>
       <c r="AN25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="AO25" s="9" t="n">
-        <v>27629.29</v>
+        <v>29892.76</v>
       </c>
       <c r="AP25" s="10" t="n">
         <v>0.003</v>
@@ -4140,18 +4327,27 @@
         <v>2264603</v>
       </c>
       <c r="AR25" s="9" t="n">
-        <v>25089.54</v>
+        <v>27629.29</v>
       </c>
       <c r="AS25" s="10" t="n">
-        <v>0.0029</v>
+        <v>0.003</v>
       </c>
       <c r="AT25" s="8" t="n">
         <v>2264603</v>
       </c>
       <c r="AU25" s="9" t="n">
+        <v>25089.54</v>
+      </c>
+      <c r="AV25" s="10" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="AW25" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="AX25" s="9" t="n">
         <v>29659.51</v>
       </c>
-      <c r="AV25" s="10" t="n">
+      <c r="AY25" s="10" t="n">
         <v>0.0033</v>
       </c>
     </row>
@@ -4172,138 +4368,147 @@
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>7394472</v>
+        <v>8256209</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>57344.13</v>
+        <v>69682.39999999999</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>0.0044</v>
+        <v>0.0049</v>
       </c>
       <c r="G26" s="8" t="n">
         <v>7394472</v>
       </c>
       <c r="H26" s="9" t="n">
+        <v>57344.13</v>
+      </c>
+      <c r="I26" s="10" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="J26" s="8" t="n">
+        <v>7394472</v>
+      </c>
+      <c r="K26" s="9" t="n">
         <v>63976.97</v>
       </c>
-      <c r="I26" s="10" t="n">
+      <c r="L26" s="10" t="n">
         <v>0.0048</v>
       </c>
-      <c r="J26" s="8" t="n">
+      <c r="M26" s="8" t="n">
         <v>7362903</v>
       </c>
-      <c r="K26" s="9" t="n">
+      <c r="N26" s="9" t="n">
         <v>67966.96000000001</v>
       </c>
-      <c r="L26" s="10" t="n">
+      <c r="O26" s="10" t="n">
         <v>0.0051</v>
       </c>
-      <c r="M26" s="8" t="n">
+      <c r="P26" s="8" t="n">
         <v>6180145</v>
       </c>
-      <c r="N26" s="9" t="n">
+      <c r="Q26" s="9" t="n">
         <v>63945.96</v>
       </c>
-      <c r="O26" s="10" t="n">
+      <c r="R26" s="10" t="n">
         <v>0.0048</v>
       </c>
-      <c r="P26" s="8" t="n">
+      <c r="S26" s="8" t="n">
         <v>5842830</v>
       </c>
-      <c r="Q26" s="9" t="n">
+      <c r="T26" s="9" t="n">
         <v>60233.73</v>
       </c>
-      <c r="R26" s="10" t="n">
+      <c r="U26" s="10" t="n">
         <v>0.0046</v>
       </c>
-      <c r="S26" s="8" t="n">
+      <c r="V26" s="8" t="n">
         <v>5528341</v>
       </c>
-      <c r="T26" s="9" t="n">
+      <c r="W26" s="9" t="n">
         <v>59285.93</v>
       </c>
-      <c r="U26" s="10" t="n">
+      <c r="X26" s="10" t="n">
         <v>0.0047</v>
       </c>
-      <c r="V26" s="8" t="n">
+      <c r="Y26" s="8" t="n">
         <v>4996218</v>
       </c>
-      <c r="W26" s="9" t="n">
+      <c r="Z26" s="9" t="n">
         <v>51236.22</v>
-      </c>
-      <c r="X26" s="10" t="n">
-        <v>0.0043</v>
-      </c>
-      <c r="Y26" s="8" t="n">
-        <v>4433570</v>
-      </c>
-      <c r="Z26" s="9" t="n">
-        <v>49913.13</v>
       </c>
       <c r="AA26" s="10" t="n">
         <v>0.0043</v>
       </c>
       <c r="AB26" s="8" t="n">
+        <v>4433570</v>
+      </c>
+      <c r="AC26" s="9" t="n">
+        <v>49913.13</v>
+      </c>
+      <c r="AD26" s="10" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="AE26" s="8" t="n">
         <v>3997165</v>
       </c>
-      <c r="AC26" s="9" t="n">
+      <c r="AF26" s="9" t="n">
         <v>49305.03</v>
       </c>
-      <c r="AD26" s="10" t="n">
+      <c r="AG26" s="10" t="n">
         <v>0.0044</v>
       </c>
-      <c r="AE26" s="8" t="n">
+      <c r="AH26" s="8" t="n">
         <v>3516819</v>
       </c>
-      <c r="AF26" s="9" t="n">
+      <c r="AI26" s="9" t="n">
         <v>39036.69</v>
       </c>
-      <c r="AG26" s="10" t="n">
+      <c r="AJ26" s="10" t="n">
         <v>0.0035</v>
       </c>
-      <c r="AH26" s="8" t="n">
+      <c r="AK26" s="8" t="n">
         <v>3243008</v>
       </c>
-      <c r="AI26" s="9" t="n">
+      <c r="AL26" s="9" t="n">
         <v>30813.44</v>
       </c>
-      <c r="AJ26" s="10" t="n">
+      <c r="AM26" s="10" t="n">
         <v>0.003</v>
       </c>
-      <c r="AK26" s="8" t="n">
+      <c r="AN26" s="8" t="n">
         <v>2988209</v>
       </c>
-      <c r="AL26" s="9" t="n">
+      <c r="AO26" s="9" t="n">
         <v>24424.13</v>
       </c>
-      <c r="AM26" s="10" t="n">
+      <c r="AP26" s="10" t="n">
         <v>0.0025</v>
       </c>
-      <c r="AN26" s="8" t="n">
+      <c r="AQ26" s="8" t="n">
         <v>2843265</v>
       </c>
-      <c r="AO26" s="9" t="n">
+      <c r="AR26" s="9" t="n">
         <v>22336.69</v>
       </c>
-      <c r="AP26" s="10" t="n">
+      <c r="AS26" s="10" t="n">
         <v>0.0024</v>
       </c>
-      <c r="AQ26" s="8" t="n">
+      <c r="AT26" s="8" t="n">
         <v>2609056</v>
       </c>
-      <c r="AR26" s="9" t="n">
+      <c r="AU26" s="9" t="n">
         <v>17326.74</v>
       </c>
-      <c r="AS26" s="10" t="n">
+      <c r="AV26" s="10" t="n">
         <v>0.002</v>
       </c>
-      <c r="AT26" s="8" t="n">
+      <c r="AW26" s="8" t="n">
         <v>2259531</v>
       </c>
-      <c r="AU26" s="9" t="n">
+      <c r="AX26" s="9" t="n">
         <v>18525.89</v>
       </c>
-      <c r="AV26" s="10" t="n">
+      <c r="AY26" s="10" t="n">
         <v>0.0021</v>
       </c>
     </row>
@@ -4359,31 +4564,34 @@
       <c r="AK27" s="8" t="n"/>
       <c r="AL27" s="9" t="n"/>
       <c r="AM27" s="10" t="n"/>
-      <c r="AN27" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="AO27" s="9" t="n">
-        <v>19552.33</v>
-      </c>
-      <c r="AP27" s="10" t="n">
-        <v>0.0021</v>
-      </c>
+      <c r="AN27" s="8" t="n"/>
+      <c r="AO27" s="9" t="n"/>
+      <c r="AP27" s="10" t="n"/>
       <c r="AQ27" s="8" t="n">
         <v>9899412</v>
       </c>
       <c r="AR27" s="9" t="n">
-        <v>16216.23</v>
+        <v>19552.33</v>
       </c>
       <c r="AS27" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.0021</v>
       </c>
       <c r="AT27" s="8" t="n">
         <v>9899412</v>
       </c>
       <c r="AU27" s="9" t="n">
+        <v>16216.23</v>
+      </c>
+      <c r="AV27" s="10" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="AW27" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="AX27" s="9" t="n">
         <v>16131.09</v>
       </c>
-      <c r="AV27" s="10" t="n">
+      <c r="AY27" s="10" t="n">
         <v>0.0018</v>
       </c>
     </row>
@@ -4407,7 +4615,7 @@
         <v>287393</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>14378.27</v>
+        <v>15582.45</v>
       </c>
       <c r="F28" s="10" t="n">
         <v>0.0011</v>
@@ -4416,52 +4624,52 @@
         <v>287393</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>15895.71</v>
+        <v>14378.27</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>0.0012</v>
+        <v>0.0011</v>
       </c>
       <c r="J28" s="8" t="n">
         <v>287393</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>18124.44</v>
+        <v>15895.71</v>
       </c>
       <c r="L28" s="10" t="n">
-        <v>0.0014</v>
+        <v>0.0012</v>
       </c>
       <c r="M28" s="8" t="n">
         <v>287393</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>17460.56</v>
+        <v>18124.44</v>
       </c>
       <c r="O28" s="10" t="n">
-        <v>0.0013</v>
+        <v>0.0014</v>
       </c>
       <c r="P28" s="8" t="n">
         <v>287393</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>17812.62</v>
+        <v>17460.56</v>
       </c>
       <c r="R28" s="10" t="n">
-        <v>0.0014</v>
+        <v>0.0013</v>
       </c>
       <c r="S28" s="8" t="n">
         <v>287393</v>
       </c>
       <c r="T28" s="9" t="n">
-        <v>18463.56</v>
+        <v>17812.62</v>
       </c>
       <c r="U28" s="10" t="n">
-        <v>0.0015</v>
+        <v>0.0014</v>
       </c>
       <c r="V28" s="8" t="n">
         <v>287393</v>
       </c>
       <c r="W28" s="9" t="n">
-        <v>18243.71</v>
+        <v>18463.56</v>
       </c>
       <c r="X28" s="10" t="n">
         <v>0.0015</v>
@@ -4470,72 +4678,81 @@
         <v>287393</v>
       </c>
       <c r="Z28" s="9" t="n">
-        <v>17962.06</v>
+        <v>18243.71</v>
       </c>
       <c r="AA28" s="10" t="n">
-        <v>0.0016</v>
+        <v>0.0015</v>
       </c>
       <c r="AB28" s="8" t="n">
         <v>287393</v>
       </c>
       <c r="AC28" s="9" t="n">
-        <v>19048.41</v>
+        <v>17962.06</v>
       </c>
       <c r="AD28" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.0016</v>
       </c>
       <c r="AE28" s="8" t="n">
         <v>287393</v>
       </c>
       <c r="AF28" s="9" t="n">
-        <v>19453.63</v>
+        <v>19048.41</v>
       </c>
       <c r="AG28" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.0017</v>
       </c>
       <c r="AH28" s="8" t="n">
         <v>287393</v>
       </c>
       <c r="AI28" s="9" t="n">
-        <v>19370.29</v>
+        <v>19453.63</v>
       </c>
       <c r="AJ28" s="10" t="n">
-        <v>0.0019</v>
+        <v>0.0018</v>
       </c>
       <c r="AK28" s="8" t="n">
         <v>287393</v>
       </c>
       <c r="AL28" s="9" t="n">
-        <v>15976.18</v>
+        <v>19370.29</v>
       </c>
       <c r="AM28" s="10" t="n">
-        <v>0.0016</v>
+        <v>0.0019</v>
       </c>
       <c r="AN28" s="8" t="n">
         <v>287393</v>
       </c>
       <c r="AO28" s="9" t="n">
-        <v>15821.13</v>
+        <v>15976.18</v>
       </c>
       <c r="AP28" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.0016</v>
       </c>
       <c r="AQ28" s="8" t="n">
         <v>287393</v>
       </c>
       <c r="AR28" s="9" t="n">
-        <v>15273.64</v>
+        <v>15821.13</v>
       </c>
       <c r="AS28" s="10" t="n">
         <v>0.0017</v>
       </c>
       <c r="AT28" s="8" t="n">
+        <v>287393</v>
+      </c>
+      <c r="AU28" s="9" t="n">
+        <v>15273.64</v>
+      </c>
+      <c r="AV28" s="10" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="AW28" s="8" t="n">
         <v>297835</v>
       </c>
-      <c r="AU28" s="9" t="n">
+      <c r="AX28" s="9" t="n">
         <v>18529.51</v>
       </c>
-      <c r="AV28" s="10" t="n">
+      <c r="AY28" s="10" t="n">
         <v>0.0021</v>
       </c>
     </row>
@@ -4556,10 +4773,10 @@
         </is>
       </c>
       <c r="D29" s="8" t="n">
-        <v>80565</v>
+        <v>80662</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>8949.969999999999</v>
+        <v>9876.26</v>
       </c>
       <c r="F29" s="10" t="n">
         <v>0.0007</v>
@@ -4568,34 +4785,34 @@
         <v>80565</v>
       </c>
       <c r="H29" s="9" t="n">
+        <v>8949.969999999999</v>
+      </c>
+      <c r="I29" s="10" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="J29" s="8" t="n">
+        <v>80565</v>
+      </c>
+      <c r="K29" s="9" t="n">
         <v>10682.11</v>
-      </c>
-      <c r="I29" s="10" t="n">
-        <v>0.0008</v>
-      </c>
-      <c r="J29" s="8" t="n">
-        <v>80552</v>
-      </c>
-      <c r="K29" s="9" t="n">
-        <v>10825.38</v>
       </c>
       <c r="L29" s="10" t="n">
         <v>0.0008</v>
       </c>
       <c r="M29" s="8" t="n">
-        <v>80159</v>
+        <v>80552</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>11401.01</v>
+        <v>10825.38</v>
       </c>
       <c r="O29" s="10" t="n">
-        <v>0.0009</v>
+        <v>0.0008</v>
       </c>
       <c r="P29" s="8" t="n">
         <v>80159</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>11787.38</v>
+        <v>11401.01</v>
       </c>
       <c r="R29" s="10" t="n">
         <v>0.0009</v>
@@ -4604,34 +4821,34 @@
         <v>80159</v>
       </c>
       <c r="T29" s="9" t="n">
-        <v>12110.42</v>
+        <v>11787.38</v>
       </c>
       <c r="U29" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="V29" s="8" t="n">
         <v>80159</v>
       </c>
       <c r="W29" s="9" t="n">
-        <v>13825.82</v>
+        <v>12110.42</v>
       </c>
       <c r="X29" s="10" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="Y29" s="8" t="n">
         <v>80159</v>
       </c>
       <c r="Z29" s="9" t="n">
-        <v>12726.04</v>
+        <v>13825.82</v>
       </c>
       <c r="AA29" s="10" t="n">
-        <v>0.0011</v>
+        <v>0.0012</v>
       </c>
       <c r="AB29" s="8" t="n">
         <v>80159</v>
       </c>
       <c r="AC29" s="9" t="n">
-        <v>12868.73</v>
+        <v>12726.04</v>
       </c>
       <c r="AD29" s="10" t="n">
         <v>0.0011</v>
@@ -4640,7 +4857,7 @@
         <v>80159</v>
       </c>
       <c r="AF29" s="9" t="n">
-        <v>11621.45</v>
+        <v>12868.73</v>
       </c>
       <c r="AG29" s="10" t="n">
         <v>0.0011</v>
@@ -4649,45 +4866,54 @@
         <v>80159</v>
       </c>
       <c r="AI29" s="9" t="n">
-        <v>10722.07</v>
+        <v>11621.45</v>
       </c>
       <c r="AJ29" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0011</v>
       </c>
       <c r="AK29" s="8" t="n">
         <v>80159</v>
       </c>
       <c r="AL29" s="9" t="n">
-        <v>9198.25</v>
+        <v>10722.07</v>
       </c>
       <c r="AM29" s="10" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="AN29" s="8" t="n">
         <v>80159</v>
       </c>
       <c r="AO29" s="9" t="n">
-        <v>8997.450000000001</v>
+        <v>9198.25</v>
       </c>
       <c r="AP29" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="AQ29" s="8" t="n">
         <v>80159</v>
       </c>
       <c r="AR29" s="9" t="n">
-        <v>7401.52</v>
+        <v>8997.450000000001</v>
       </c>
       <c r="AS29" s="10" t="n">
-        <v>0.0008</v>
+        <v>0.001</v>
       </c>
       <c r="AT29" s="8" t="n">
         <v>80159</v>
       </c>
       <c r="AU29" s="9" t="n">
+        <v>7401.52</v>
+      </c>
+      <c r="AV29" s="10" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="AW29" s="8" t="n">
+        <v>80159</v>
+      </c>
+      <c r="AX29" s="9" t="n">
         <v>7463.48</v>
       </c>
-      <c r="AV29" s="10" t="n">
+      <c r="AY29" s="10" t="n">
         <v>0.0008</v>
       </c>
     </row>
@@ -4711,7 +4937,7 @@
         <v>47293</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>1564.88</v>
+        <v>1871.38</v>
       </c>
       <c r="F30" s="10" t="n">
         <v>0.0001</v>
@@ -4720,7 +4946,7 @@
         <v>47293</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>1700.33</v>
+        <v>1564.88</v>
       </c>
       <c r="I30" s="10" t="n">
         <v>0.0001</v>
@@ -4729,7 +4955,7 @@
         <v>47293</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>1637.61</v>
+        <v>1700.33</v>
       </c>
       <c r="L30" s="10" t="n">
         <v>0.0001</v>
@@ -4738,7 +4964,7 @@
         <v>47293</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>1691.91</v>
+        <v>1637.61</v>
       </c>
       <c r="O30" s="10" t="n">
         <v>0.0001</v>
@@ -4747,7 +4973,7 @@
         <v>47293</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>1764.08</v>
+        <v>1691.91</v>
       </c>
       <c r="R30" s="10" t="n">
         <v>0.0001</v>
@@ -4756,16 +4982,16 @@
         <v>47293</v>
       </c>
       <c r="T30" s="9" t="n">
-        <v>1892.15</v>
+        <v>1764.08</v>
       </c>
       <c r="U30" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="V30" s="8" t="n">
         <v>47293</v>
       </c>
       <c r="W30" s="9" t="n">
-        <v>1955.38</v>
+        <v>1892.15</v>
       </c>
       <c r="X30" s="10" t="n">
         <v>0.0002</v>
@@ -4774,7 +5000,7 @@
         <v>47293</v>
       </c>
       <c r="Z30" s="9" t="n">
-        <v>1897.21</v>
+        <v>1955.38</v>
       </c>
       <c r="AA30" s="10" t="n">
         <v>0.0002</v>
@@ -4783,7 +5009,7 @@
         <v>47293</v>
       </c>
       <c r="AC30" s="9" t="n">
-        <v>1983.66</v>
+        <v>1897.21</v>
       </c>
       <c r="AD30" s="10" t="n">
         <v>0.0002</v>
@@ -4792,7 +5018,7 @@
         <v>47293</v>
       </c>
       <c r="AF30" s="9" t="n">
-        <v>1867.41</v>
+        <v>1983.66</v>
       </c>
       <c r="AG30" s="10" t="n">
         <v>0.0002</v>
@@ -4801,7 +5027,7 @@
         <v>47293</v>
       </c>
       <c r="AI30" s="9" t="n">
-        <v>1857.76</v>
+        <v>1867.41</v>
       </c>
       <c r="AJ30" s="10" t="n">
         <v>0.0002</v>
@@ -4810,7 +5036,7 @@
         <v>47293</v>
       </c>
       <c r="AL30" s="9" t="n">
-        <v>1925.39</v>
+        <v>1857.76</v>
       </c>
       <c r="AM30" s="10" t="n">
         <v>0.0002</v>
@@ -4819,7 +5045,7 @@
         <v>47293</v>
       </c>
       <c r="AO30" s="9" t="n">
-        <v>1844.17</v>
+        <v>1925.39</v>
       </c>
       <c r="AP30" s="10" t="n">
         <v>0.0002</v>
@@ -4828,18 +5054,27 @@
         <v>47293</v>
       </c>
       <c r="AR30" s="9" t="n">
-        <v>1236.83</v>
+        <v>1844.17</v>
       </c>
       <c r="AS30" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="AT30" s="8" t="n">
         <v>47293</v>
       </c>
       <c r="AU30" s="9" t="n">
+        <v>1236.83</v>
+      </c>
+      <c r="AV30" s="10" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AW30" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="AX30" s="9" t="n">
         <v>1612.64</v>
       </c>
-      <c r="AV30" s="10" t="n">
+      <c r="AY30" s="10" t="n">
         <v>0.0002</v>
       </c>
     </row>
@@ -4863,7 +5098,7 @@
         <v>151687</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>1538.11</v>
+        <v>1862.26</v>
       </c>
       <c r="F31" s="10" t="n">
         <v>0.0001</v>
@@ -4872,7 +5107,7 @@
         <v>151687</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>1704.36</v>
+        <v>1538.11</v>
       </c>
       <c r="I31" s="10" t="n">
         <v>0.0001</v>
@@ -4881,7 +5116,7 @@
         <v>151687</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>1728.63</v>
+        <v>1704.36</v>
       </c>
       <c r="L31" s="10" t="n">
         <v>0.0001</v>
@@ -4890,7 +5125,7 @@
         <v>151687</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>1858.32</v>
+        <v>1728.63</v>
       </c>
       <c r="O31" s="10" t="n">
         <v>0.0001</v>
@@ -4899,16 +5134,16 @@
         <v>151687</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>1947.66</v>
+        <v>1858.32</v>
       </c>
       <c r="R31" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="S31" s="8" t="n">
         <v>151687</v>
       </c>
       <c r="T31" s="9" t="n">
-        <v>2076.6</v>
+        <v>1947.66</v>
       </c>
       <c r="U31" s="10" t="n">
         <v>0.0002</v>
@@ -4917,7 +5152,7 @@
         <v>151687</v>
       </c>
       <c r="W31" s="9" t="n">
-        <v>1987.1</v>
+        <v>2076.6</v>
       </c>
       <c r="X31" s="10" t="n">
         <v>0.0002</v>
@@ -4926,7 +5161,7 @@
         <v>151687</v>
       </c>
       <c r="Z31" s="9" t="n">
-        <v>2130.6</v>
+        <v>1987.1</v>
       </c>
       <c r="AA31" s="10" t="n">
         <v>0.0002</v>
@@ -4935,7 +5170,7 @@
         <v>151687</v>
       </c>
       <c r="AC31" s="9" t="n">
-        <v>2091.16</v>
+        <v>2130.6</v>
       </c>
       <c r="AD31" s="10" t="n">
         <v>0.0002</v>
@@ -4944,23 +5179,29 @@
         <v>151687</v>
       </c>
       <c r="AF31" s="9" t="n">
-        <v>1766.62</v>
+        <v>2091.16</v>
       </c>
       <c r="AG31" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="AH31" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AI31" s="9" t="n">
+        <v>1766.62</v>
+      </c>
+      <c r="AJ31" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AK31" s="8" t="n">
         <v>89469</v>
       </c>
-      <c r="AI31" s="9" t="n">
+      <c r="AL31" s="9" t="n">
         <v>828.48</v>
       </c>
-      <c r="AJ31" s="10" t="n">
+      <c r="AM31" s="10" t="n">
         <v>0.0001</v>
       </c>
-      <c r="AK31" s="8" t="n"/>
-      <c r="AL31" s="9" t="n"/>
-      <c r="AM31" s="10" t="n"/>
       <c r="AN31" s="8" t="n"/>
       <c r="AO31" s="9" t="n"/>
       <c r="AP31" s="10" t="n"/>
@@ -4970,6 +5211,9 @@
       <c r="AT31" s="8" t="n"/>
       <c r="AU31" s="9" t="n"/>
       <c r="AV31" s="10" t="n"/>
+      <c r="AW31" s="8" t="n"/>
+      <c r="AX31" s="9" t="n"/>
+      <c r="AY31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -4991,104 +5235,110 @@
         <v>21167034</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>377281.21</v>
+        <v>399379.6</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>0.0293</v>
+        <v>0.0283</v>
       </c>
       <c r="G32" s="8" t="n">
         <v>21167034</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>397792.07</v>
+        <v>377281.21</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>0.0296</v>
+        <v>0.0293</v>
       </c>
       <c r="J32" s="8" t="n">
         <v>21167034</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>416715.398358</v>
+        <v>397792.07</v>
       </c>
       <c r="L32" s="10" t="n">
-        <v>0.0311051731198606</v>
+        <v>0.0296</v>
       </c>
       <c r="M32" s="8" t="n">
         <v>21167034</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>445693.07</v>
+        <v>416715.398358</v>
       </c>
       <c r="O32" s="10" t="n">
-        <v>0.0334</v>
+        <v>0.0311051731198606</v>
       </c>
       <c r="P32" s="8" t="n">
         <v>21167034</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>444846.39</v>
+        <v>445693.07</v>
       </c>
       <c r="R32" s="10" t="n">
-        <v>0.0343</v>
+        <v>0.0334</v>
       </c>
       <c r="S32" s="8" t="n">
         <v>21167034</v>
       </c>
       <c r="T32" s="9" t="n">
-        <v>434876.71</v>
+        <v>444846.39</v>
       </c>
       <c r="U32" s="10" t="n">
-        <v>0.0346</v>
+        <v>0.0343</v>
       </c>
       <c r="V32" s="8" t="n">
         <v>21167034</v>
       </c>
       <c r="W32" s="9" t="n">
-        <v>397601.57</v>
+        <v>434876.71</v>
       </c>
       <c r="X32" s="10" t="n">
-        <v>0.0332</v>
+        <v>0.0346</v>
       </c>
       <c r="Y32" s="8" t="n">
         <v>21167034</v>
       </c>
       <c r="Z32" s="9" t="n">
-        <v>399802.94</v>
+        <v>397601.57</v>
       </c>
       <c r="AA32" s="10" t="n">
-        <v>0.0348</v>
+        <v>0.0332</v>
       </c>
       <c r="AB32" s="8" t="n">
         <v>21167034</v>
       </c>
       <c r="AC32" s="9" t="n">
+        <v>399802.94</v>
+      </c>
+      <c r="AD32" s="10" t="n">
+        <v>0.0348</v>
+      </c>
+      <c r="AE32" s="8" t="n">
+        <v>21167034</v>
+      </c>
+      <c r="AF32" s="9" t="n">
         <v>405200.53</v>
       </c>
-      <c r="AD32" s="10" t="n">
+      <c r="AG32" s="10" t="n">
         <v>0.0358</v>
       </c>
-      <c r="AE32" s="8" t="n">
+      <c r="AH32" s="8" t="n">
         <v>20937034</v>
       </c>
-      <c r="AF32" s="9" t="n">
+      <c r="AI32" s="9" t="n">
         <v>420750.64</v>
       </c>
-      <c r="AG32" s="10" t="n">
+      <c r="AJ32" s="10" t="n">
         <v>0.0381</v>
       </c>
-      <c r="AH32" s="8" t="n">
+      <c r="AK32" s="8" t="n">
         <v>11799076</v>
       </c>
-      <c r="AI32" s="9" t="n">
+      <c r="AL32" s="9" t="n">
         <v>219014.45</v>
       </c>
-      <c r="AJ32" s="10" t="n">
+      <c r="AM32" s="10" t="n">
         <v>0.0211</v>
       </c>
-      <c r="AK32" s="8" t="n"/>
-      <c r="AL32" s="9" t="n"/>
-      <c r="AM32" s="10" t="n"/>
       <c r="AN32" s="8" t="n"/>
       <c r="AO32" s="9" t="n"/>
       <c r="AP32" s="10" t="n"/>
@@ -5098,6 +5348,9 @@
       <c r="AT32" s="8" t="n"/>
       <c r="AU32" s="9" t="n"/>
       <c r="AV32" s="10" t="n"/>
+      <c r="AW32" s="8" t="n"/>
+      <c r="AX32" s="9" t="n"/>
+      <c r="AY32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -5136,36 +5389,36 @@
       <c r="V33" s="8" t="n"/>
       <c r="W33" s="9" t="n"/>
       <c r="X33" s="10" t="n"/>
-      <c r="Y33" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="Z33" s="9" t="n">
-        <v>88822.8</v>
-      </c>
-      <c r="AA33" s="10" t="n">
-        <v>0.0077</v>
-      </c>
+      <c r="Y33" s="8" t="n"/>
+      <c r="Z33" s="9" t="n"/>
+      <c r="AA33" s="10" t="n"/>
       <c r="AB33" s="8" t="n">
         <v>4400000</v>
       </c>
       <c r="AC33" s="9" t="n">
-        <v>89280.39999999999</v>
+        <v>88822.8</v>
       </c>
       <c r="AD33" s="10" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0077</v>
       </c>
       <c r="AE33" s="8" t="n">
         <v>4400000</v>
       </c>
       <c r="AF33" s="9" t="n">
+        <v>89280.39999999999</v>
+      </c>
+      <c r="AG33" s="10" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="AH33" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AI33" s="9" t="n">
         <v>89020.8</v>
       </c>
-      <c r="AG33" s="10" t="n">
+      <c r="AJ33" s="10" t="n">
         <v>0.0081</v>
       </c>
-      <c r="AH33" s="8" t="n"/>
-      <c r="AI33" s="9" t="n"/>
-      <c r="AJ33" s="10" t="n"/>
       <c r="AK33" s="8" t="n"/>
       <c r="AL33" s="9" t="n"/>
       <c r="AM33" s="10" t="n"/>
@@ -5178,6 +5431,9 @@
       <c r="AT33" s="8" t="n"/>
       <c r="AU33" s="9" t="n"/>
       <c r="AV33" s="10" t="n"/>
+      <c r="AW33" s="8" t="n"/>
+      <c r="AX33" s="9" t="n"/>
+      <c r="AY33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -5196,53 +5452,59 @@
         </is>
       </c>
       <c r="D34" s="8" t="n">
+        <v>15874545</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>392720.37</v>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>0.0279</v>
+      </c>
+      <c r="G34" s="8" t="n">
         <v>12412184</v>
       </c>
-      <c r="E34" s="9" t="n">
+      <c r="H34" s="9" t="n">
         <v>292791.01</v>
       </c>
-      <c r="F34" s="10" t="n">
+      <c r="I34" s="10" t="n">
         <v>0.0227</v>
       </c>
-      <c r="G34" s="8" t="n">
+      <c r="J34" s="8" t="n">
         <v>10378056</v>
       </c>
-      <c r="H34" s="9" t="n">
+      <c r="K34" s="9" t="n">
         <v>273710.85</v>
       </c>
-      <c r="I34" s="10" t="n">
+      <c r="L34" s="10" t="n">
         <v>0.0204</v>
       </c>
-      <c r="J34" s="8" t="n">
+      <c r="M34" s="8" t="n">
         <v>8465650</v>
       </c>
-      <c r="K34" s="9" t="n">
+      <c r="N34" s="9" t="n">
         <v>264458.44</v>
       </c>
-      <c r="L34" s="10" t="n">
+      <c r="O34" s="10" t="n">
         <v>0.0197</v>
       </c>
-      <c r="M34" s="8" t="n">
+      <c r="P34" s="8" t="n">
         <v>4654589</v>
       </c>
-      <c r="N34" s="9" t="n">
+      <c r="Q34" s="9" t="n">
         <v>149235.43</v>
       </c>
-      <c r="O34" s="10" t="n">
+      <c r="R34" s="10" t="n">
         <v>0.0112</v>
       </c>
-      <c r="P34" s="8" t="n">
+      <c r="S34" s="8" t="n">
         <v>2811139</v>
       </c>
-      <c r="Q34" s="9" t="n">
+      <c r="T34" s="9" t="n">
         <v>88199.49000000001</v>
       </c>
-      <c r="R34" s="10" t="n">
+      <c r="U34" s="10" t="n">
         <v>0.0068</v>
       </c>
-      <c r="S34" s="8" t="n"/>
-      <c r="T34" s="9" t="n"/>
-      <c r="U34" s="10" t="n"/>
       <c r="V34" s="8" t="n"/>
       <c r="W34" s="9" t="n"/>
       <c r="X34" s="10" t="n"/>
@@ -5270,6 +5532,9 @@
       <c r="AT34" s="8" t="n"/>
       <c r="AU34" s="9" t="n"/>
       <c r="AV34" s="10" t="n"/>
+      <c r="AW34" s="8" t="n"/>
+      <c r="AX34" s="9" t="n"/>
+      <c r="AY34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -5291,68 +5556,74 @@
         <v>22157154</v>
       </c>
       <c r="E35" s="9" t="n">
+        <v>112680.21</v>
+      </c>
+      <c r="F35" s="10" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="G35" s="8" t="n">
+        <v>22157154</v>
+      </c>
+      <c r="H35" s="9" t="n">
         <v>94467.03</v>
       </c>
-      <c r="F35" s="10" t="n">
+      <c r="I35" s="10" t="n">
         <v>0.0073</v>
       </c>
-      <c r="G35" s="8" t="n">
+      <c r="J35" s="8" t="n">
         <v>22075063</v>
       </c>
-      <c r="H35" s="9" t="n">
+      <c r="K35" s="9" t="n">
         <v>84966.92</v>
       </c>
-      <c r="I35" s="10" t="n">
+      <c r="L35" s="10" t="n">
         <v>0.0063</v>
-      </c>
-      <c r="J35" s="8" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="K35" s="9" t="n">
-        <v>98626</v>
-      </c>
-      <c r="L35" s="10" t="n">
-        <v>0.0074</v>
       </c>
       <c r="M35" s="8" t="n">
         <v>22000000</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>100012</v>
+        <v>98626</v>
       </c>
       <c r="O35" s="10" t="n">
-        <v>0.0075</v>
+        <v>0.0074</v>
       </c>
       <c r="P35" s="8" t="n">
         <v>22000000</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>94699</v>
+        <v>100012</v>
       </c>
       <c r="R35" s="10" t="n">
-        <v>0.0073</v>
+        <v>0.0075</v>
       </c>
       <c r="S35" s="8" t="n">
         <v>22000000</v>
       </c>
       <c r="T35" s="9" t="n">
-        <v>104852</v>
+        <v>94699</v>
       </c>
       <c r="U35" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.0073</v>
       </c>
       <c r="V35" s="8" t="n">
         <v>22000000</v>
       </c>
       <c r="W35" s="9" t="n">
+        <v>104852</v>
+      </c>
+      <c r="X35" s="10" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="Y35" s="8" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="Z35" s="9" t="n">
         <v>100584</v>
       </c>
-      <c r="X35" s="10" t="n">
+      <c r="AA35" s="10" t="n">
         <v>0.008399999999999999</v>
       </c>
-      <c r="Y35" s="8" t="n"/>
-      <c r="Z35" s="9" t="n"/>
-      <c r="AA35" s="10" t="n"/>
       <c r="AB35" s="8" t="n"/>
       <c r="AC35" s="9" t="n"/>
       <c r="AD35" s="10" t="n"/>
@@ -5374,6 +5645,9 @@
       <c r="AT35" s="8" t="n"/>
       <c r="AU35" s="9" t="n"/>
       <c r="AV35" s="10" t="n"/>
+      <c r="AW35" s="8" t="n"/>
+      <c r="AX35" s="9" t="n"/>
+      <c r="AY35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -5395,41 +5669,47 @@
         <v>2205298</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>31198.35</v>
+        <v>34773.14</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>0.0024</v>
+        <v>0.0025</v>
       </c>
       <c r="G36" s="8" t="n">
         <v>2205298</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>29526.73</v>
+        <v>31198.35</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>0.0022</v>
+        <v>0.0024</v>
       </c>
       <c r="J36" s="8" t="n">
         <v>2205298</v>
       </c>
       <c r="K36" s="9" t="n">
+        <v>29526.73</v>
+      </c>
+      <c r="L36" s="10" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="M36" s="8" t="n">
+        <v>2205298</v>
+      </c>
+      <c r="N36" s="9" t="n">
         <v>26516.5</v>
       </c>
-      <c r="L36" s="10" t="n">
+      <c r="O36" s="10" t="n">
         <v>0.002</v>
       </c>
-      <c r="M36" s="8" t="n">
+      <c r="P36" s="8" t="n">
         <v>1657424</v>
       </c>
-      <c r="N36" s="9" t="n">
+      <c r="Q36" s="9" t="n">
         <v>18712.32</v>
       </c>
-      <c r="O36" s="10" t="n">
+      <c r="R36" s="10" t="n">
         <v>0.0014</v>
       </c>
-      <c r="P36" s="8" t="n"/>
-      <c r="Q36" s="9" t="n"/>
-      <c r="R36" s="10" t="n"/>
       <c r="S36" s="8" t="n"/>
       <c r="T36" s="9" t="n"/>
       <c r="U36" s="10" t="n"/>
@@ -5460,6 +5740,9 @@
       <c r="AT36" s="8" t="n"/>
       <c r="AU36" s="9" t="n"/>
       <c r="AV36" s="10" t="n"/>
+      <c r="AW36" s="8" t="n"/>
+      <c r="AX36" s="9" t="n"/>
+      <c r="AY36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -5478,19 +5761,19 @@
         </is>
       </c>
       <c r="D37" s="8" t="n">
-        <v>710855</v>
+        <v>865823</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>2972.44</v>
+        <v>3549.44</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0003</v>
       </c>
       <c r="G37" s="8" t="n">
         <v>710855</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>3234.03</v>
+        <v>2972.44</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>0.0002</v>
@@ -5499,7 +5782,7 @@
         <v>710855</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>3158.33</v>
+        <v>3234.03</v>
       </c>
       <c r="L37" s="10" t="n">
         <v>0.0002</v>
@@ -5508,7 +5791,7 @@
         <v>710855</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2976.71</v>
+        <v>3158.33</v>
       </c>
       <c r="O37" s="10" t="n">
         <v>0.0002</v>
@@ -5517,14 +5800,20 @@
         <v>710855</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>2850.8839775</v>
+        <v>2976.71</v>
       </c>
       <c r="R37" s="10" t="n">
         <v>0.0002</v>
       </c>
-      <c r="S37" s="8" t="n"/>
-      <c r="T37" s="9" t="n"/>
-      <c r="U37" s="10" t="n"/>
+      <c r="S37" s="8" t="n">
+        <v>710855</v>
+      </c>
+      <c r="T37" s="9" t="n">
+        <v>2850.8839775</v>
+      </c>
+      <c r="U37" s="10" t="n">
+        <v>0.0002</v>
+      </c>
       <c r="V37" s="8" t="n"/>
       <c r="W37" s="9" t="n"/>
       <c r="X37" s="10" t="n"/>
@@ -5552,6 +5841,9 @@
       <c r="AT37" s="8" t="n"/>
       <c r="AU37" s="9" t="n"/>
       <c r="AV37" s="10" t="n"/>
+      <c r="AW37" s="8" t="n"/>
+      <c r="AX37" s="9" t="n"/>
+      <c r="AY37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -5570,35 +5862,41 @@
         </is>
       </c>
       <c r="D38" s="8" t="n">
+        <v>148339325</v>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>568584.63</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>0.0403</v>
+      </c>
+      <c r="G38" s="8" t="n">
         <v>146607960</v>
       </c>
-      <c r="E38" s="9" t="n">
+      <c r="H38" s="9" t="n">
         <v>518112.53</v>
       </c>
-      <c r="F38" s="10" t="n">
+      <c r="I38" s="10" t="n">
         <v>0.0402</v>
-      </c>
-      <c r="G38" s="8" t="n">
-        <v>123107960</v>
-      </c>
-      <c r="H38" s="9" t="n">
-        <v>511144.25</v>
-      </c>
-      <c r="I38" s="10" t="n">
-        <v>0.0381</v>
       </c>
       <c r="J38" s="8" t="n">
         <v>123107960</v>
       </c>
       <c r="K38" s="9" t="n">
+        <v>511144.25</v>
+      </c>
+      <c r="L38" s="10" t="n">
+        <v>0.0381</v>
+      </c>
+      <c r="M38" s="8" t="n">
+        <v>123107960</v>
+      </c>
+      <c r="N38" s="9" t="n">
         <v>502280.48</v>
       </c>
-      <c r="L38" s="10" t="n">
+      <c r="O38" s="10" t="n">
         <v>0.0375</v>
       </c>
-      <c r="M38" s="8" t="n"/>
-      <c r="N38" s="9" t="n"/>
-      <c r="O38" s="10" t="n"/>
       <c r="P38" s="8" t="n"/>
       <c r="Q38" s="9" t="n"/>
       <c r="R38" s="10" t="n"/>
@@ -5632,6 +5930,9 @@
       <c r="AT38" s="8" t="n"/>
       <c r="AU38" s="9" t="n"/>
       <c r="AV38" s="10" t="n"/>
+      <c r="AW38" s="8" t="n"/>
+      <c r="AX38" s="9" t="n"/>
+      <c r="AY38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -5653,32 +5954,38 @@
         <v>6957544</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>18479.24</v>
+        <v>20201.23</v>
       </c>
       <c r="F39" s="10" t="n">
         <v>0.0014</v>
       </c>
       <c r="G39" s="8" t="n">
+        <v>6957544</v>
+      </c>
+      <c r="H39" s="9" t="n">
+        <v>18479.24</v>
+      </c>
+      <c r="I39" s="10" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="J39" s="8" t="n">
         <v>5086596</v>
       </c>
-      <c r="H39" s="9" t="n">
+      <c r="K39" s="9" t="n">
         <v>15442.91</v>
       </c>
-      <c r="I39" s="10" t="n">
+      <c r="L39" s="10" t="n">
         <v>0.0012</v>
       </c>
-      <c r="J39" s="8" t="n">
+      <c r="M39" s="8" t="n">
         <v>199758</v>
       </c>
-      <c r="K39" s="9" t="n">
+      <c r="N39" s="9" t="n">
         <v>629.9400000000001</v>
       </c>
-      <c r="L39" s="10" t="n">
+      <c r="O39" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="M39" s="8" t="n"/>
-      <c r="N39" s="9" t="n"/>
-      <c r="O39" s="10" t="n"/>
       <c r="P39" s="8" t="n"/>
       <c r="Q39" s="9" t="n"/>
       <c r="R39" s="10" t="n"/>
@@ -5712,6 +6019,9 @@
       <c r="AT39" s="8" t="n"/>
       <c r="AU39" s="9" t="n"/>
       <c r="AV39" s="10" t="n"/>
+      <c r="AW39" s="8" t="n"/>
+      <c r="AX39" s="9" t="n"/>
+      <c r="AY39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -5733,7 +6043,7 @@
         <v>464063</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>2065.08</v>
+        <v>2198.5</v>
       </c>
       <c r="F40" s="10" t="n">
         <v>0.0002</v>
@@ -5742,23 +6052,29 @@
         <v>464063</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>2188.75</v>
+        <v>2065.08</v>
       </c>
       <c r="I40" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="J40" s="8" t="n">
+        <v>464063</v>
+      </c>
+      <c r="K40" s="9" t="n">
+        <v>2188.75</v>
+      </c>
+      <c r="L40" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="M40" s="8" t="n">
         <v>462075</v>
       </c>
-      <c r="K40" s="9" t="n">
+      <c r="N40" s="9" t="n">
         <v>1932.4</v>
       </c>
-      <c r="L40" s="10" t="n">
+      <c r="O40" s="10" t="n">
         <v>0.0001</v>
       </c>
-      <c r="M40" s="8" t="n"/>
-      <c r="N40" s="9" t="n"/>
-      <c r="O40" s="10" t="n"/>
       <c r="P40" s="8" t="n"/>
       <c r="Q40" s="9" t="n"/>
       <c r="R40" s="10" t="n"/>
@@ -5792,6 +6108,9 @@
       <c r="AT40" s="8" t="n"/>
       <c r="AU40" s="9" t="n"/>
       <c r="AV40" s="10" t="n"/>
+      <c r="AW40" s="8" t="n"/>
+      <c r="AX40" s="9" t="n"/>
+      <c r="AY40" s="10" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -5810,26 +6129,32 @@
         </is>
       </c>
       <c r="D41" s="8" t="n">
+        <v>37868936</v>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>62870.01</v>
+      </c>
+      <c r="F41" s="10" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="G41" s="8" t="n">
         <v>481152</v>
       </c>
-      <c r="E41" s="9" t="n">
+      <c r="H41" s="9" t="n">
         <v>700.65</v>
       </c>
-      <c r="F41" s="10" t="n">
+      <c r="I41" s="10" t="n">
         <v>0.0001</v>
       </c>
-      <c r="G41" s="8" t="n">
+      <c r="J41" s="8" t="n">
         <v>286134</v>
       </c>
-      <c r="H41" s="9" t="n">
+      <c r="K41" s="9" t="n">
         <v>488.89</v>
       </c>
-      <c r="I41" s="10" t="n">
+      <c r="L41" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="J41" s="8" t="n"/>
-      <c r="K41" s="9" t="n"/>
-      <c r="L41" s="10" t="n"/>
       <c r="M41" s="8" t="n"/>
       <c r="N41" s="9" t="n"/>
       <c r="O41" s="10" t="n"/>
@@ -5866,6 +6191,9 @@
       <c r="AT41" s="8" t="n"/>
       <c r="AU41" s="9" t="n"/>
       <c r="AV41" s="10" t="n"/>
+      <c r="AW41" s="8" t="n"/>
+      <c r="AX41" s="9" t="n"/>
+      <c r="AY41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -5884,26 +6212,32 @@
         </is>
       </c>
       <c r="D42" s="8" t="n">
+        <v>375782</v>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>4267.57</v>
+      </c>
+      <c r="F42" s="10" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="G42" s="8" t="n">
         <v>53045</v>
       </c>
-      <c r="E42" s="9" t="n">
+      <c r="H42" s="9" t="n">
         <v>492.1</v>
-      </c>
-      <c r="F42" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="8" t="n">
-        <v>3045</v>
-      </c>
-      <c r="H42" s="9" t="n">
-        <v>37.14</v>
       </c>
       <c r="I42" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="J42" s="8" t="n"/>
-      <c r="K42" s="9" t="n"/>
-      <c r="L42" s="10" t="n"/>
+      <c r="J42" s="8" t="n">
+        <v>3045</v>
+      </c>
+      <c r="K42" s="9" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="L42" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="M42" s="8" t="n"/>
       <c r="N42" s="9" t="n"/>
       <c r="O42" s="10" t="n"/>
@@ -5940,6 +6274,9 @@
       <c r="AT42" s="8" t="n"/>
       <c r="AU42" s="9" t="n"/>
       <c r="AV42" s="10" t="n"/>
+      <c r="AW42" s="8" t="n"/>
+      <c r="AX42" s="9" t="n"/>
+      <c r="AY42" s="10" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -5963,18 +6300,18 @@
       <c r="G43" s="8" t="n"/>
       <c r="H43" s="9" t="n"/>
       <c r="I43" s="10" t="n"/>
-      <c r="J43" s="8" t="n">
+      <c r="J43" s="8" t="n"/>
+      <c r="K43" s="9" t="n"/>
+      <c r="L43" s="10" t="n"/>
+      <c r="M43" s="8" t="n">
         <v>795472</v>
       </c>
-      <c r="K43" s="9" t="n">
+      <c r="N43" s="9" t="n">
         <v>20109.53</v>
       </c>
-      <c r="L43" s="10" t="n">
+      <c r="O43" s="10" t="n">
         <v>0.0015</v>
       </c>
-      <c r="M43" s="8" t="n"/>
-      <c r="N43" s="9" t="n"/>
-      <c r="O43" s="10" t="n"/>
       <c r="P43" s="8" t="n"/>
       <c r="Q43" s="9" t="n"/>
       <c r="R43" s="10" t="n"/>
@@ -6008,6 +6345,9 @@
       <c r="AT43" s="8" t="n"/>
       <c r="AU43" s="9" t="n"/>
       <c r="AV43" s="10" t="n"/>
+      <c r="AW43" s="8" t="n"/>
+      <c r="AX43" s="9" t="n"/>
+      <c r="AY43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
@@ -6018,143 +6358,152 @@
       <c r="B44" s="11" t="n"/>
       <c r="C44" s="12" t="n"/>
       <c r="D44" s="13" t="n">
+        <v>1459425168</v>
+      </c>
+      <c r="E44" s="14" t="n">
+        <v>9669928.740000002</v>
+      </c>
+      <c r="F44" s="15" t="n">
+        <v>0.6858999999999997</v>
+      </c>
+      <c r="G44" s="13" t="n">
         <v>1373201700</v>
       </c>
-      <c r="E44" s="14" t="n">
+      <c r="H44" s="14" t="n">
         <v>8608487.039999999</v>
       </c>
-      <c r="F44" s="15" t="n">
+      <c r="I44" s="15" t="n">
         <v>0.6674999999999998</v>
       </c>
-      <c r="G44" s="13" t="n">
+      <c r="J44" s="13" t="n">
         <v>1285817925</v>
       </c>
-      <c r="H44" s="14" t="n">
+      <c r="K44" s="14" t="n">
         <v>8857498.140000001</v>
       </c>
-      <c r="I44" s="15" t="n">
+      <c r="L44" s="15" t="n">
         <v>0.6597999999999999</v>
       </c>
-      <c r="J44" s="13" t="n">
+      <c r="M44" s="13" t="n">
         <v>1265994824</v>
       </c>
-      <c r="K44" s="14" t="n">
+      <c r="N44" s="14" t="n">
         <v>8789059.288358001</v>
       </c>
-      <c r="L44" s="15" t="n">
+      <c r="O44" s="15" t="n">
         <v>0.6559051731198605</v>
       </c>
-      <c r="M44" s="13" t="n">
+      <c r="P44" s="13" t="n">
         <v>1079845116</v>
       </c>
-      <c r="N44" s="14" t="n">
+      <c r="Q44" s="14" t="n">
         <v>8588270.840000002</v>
       </c>
-      <c r="O44" s="15" t="n">
+      <c r="R44" s="15" t="n">
         <v>0.6443999999999998</v>
       </c>
-      <c r="P44" s="13" t="n">
+      <c r="S44" s="13" t="n">
         <v>1039629309</v>
       </c>
-      <c r="Q44" s="14" t="n">
+      <c r="T44" s="14" t="n">
         <v>8271351.1939775</v>
       </c>
-      <c r="R44" s="15" t="n">
+      <c r="U44" s="15" t="n">
         <v>0.6374000000000001</v>
       </c>
-      <c r="S44" s="13" t="n">
+      <c r="V44" s="13" t="n">
         <v>991416407</v>
       </c>
-      <c r="T44" s="14" t="n">
+      <c r="W44" s="14" t="n">
         <v>7865128.239999999</v>
       </c>
-      <c r="U44" s="15" t="n">
+      <c r="X44" s="15" t="n">
         <v>0.6254999999999999</v>
       </c>
-      <c r="V44" s="13" t="n">
+      <c r="Y44" s="13" t="n">
         <v>979359723</v>
       </c>
-      <c r="W44" s="14" t="n">
+      <c r="Z44" s="14" t="n">
         <v>7559180.72</v>
       </c>
-      <c r="X44" s="15" t="n">
+      <c r="AA44" s="15" t="n">
         <v>0.6313999999999997</v>
       </c>
-      <c r="Y44" s="13" t="n">
+      <c r="AB44" s="13" t="n">
         <v>927478800</v>
       </c>
-      <c r="Z44" s="14" t="n">
+      <c r="AC44" s="14" t="n">
         <v>7320811.49</v>
       </c>
-      <c r="AA44" s="15" t="n">
+      <c r="AD44" s="15" t="n">
         <v>0.6364000000000001</v>
       </c>
-      <c r="AB44" s="13" t="n">
+      <c r="AE44" s="13" t="n">
         <v>819556049</v>
       </c>
-      <c r="AC44" s="14" t="n">
+      <c r="AF44" s="14" t="n">
         <v>7290583.900000003</v>
       </c>
-      <c r="AD44" s="15" t="n">
+      <c r="AG44" s="15" t="n">
         <v>0.6436999999999999</v>
       </c>
-      <c r="AE44" s="13" t="n">
+      <c r="AH44" s="13" t="n">
         <v>799425942</v>
       </c>
-      <c r="AF44" s="14" t="n">
+      <c r="AI44" s="14" t="n">
         <v>7347454.07</v>
       </c>
-      <c r="AG44" s="15" t="n">
+      <c r="AJ44" s="15" t="n">
         <v>0.6657999999999998</v>
       </c>
-      <c r="AH44" s="13" t="n">
+      <c r="AK44" s="13" t="n">
         <v>756845974</v>
       </c>
-      <c r="AI44" s="14" t="n">
+      <c r="AL44" s="14" t="n">
         <v>6714757.130000002</v>
       </c>
-      <c r="AJ44" s="15" t="n">
+      <c r="AM44" s="15" t="n">
         <v>0.6467999999999997</v>
       </c>
-      <c r="AK44" s="13" t="n">
+      <c r="AN44" s="13" t="n">
         <v>719050337</v>
       </c>
-      <c r="AL44" s="14" t="n">
+      <c r="AO44" s="14" t="n">
         <v>6275568.75</v>
       </c>
-      <c r="AM44" s="15" t="n">
+      <c r="AP44" s="15" t="n">
         <v>0.6370000000000001</v>
       </c>
-      <c r="AN44" s="13" t="n">
+      <c r="AQ44" s="13" t="n">
         <v>717176528</v>
       </c>
-      <c r="AO44" s="14" t="n">
+      <c r="AR44" s="14" t="n">
         <v>6051937.58</v>
       </c>
-      <c r="AP44" s="15" t="n">
+      <c r="AS44" s="15" t="n">
         <v>0.6476999999999997</v>
       </c>
-      <c r="AQ44" s="13" t="n">
+      <c r="AT44" s="13" t="n">
         <v>718063829</v>
       </c>
-      <c r="AR44" s="14" t="n">
+      <c r="AU44" s="14" t="n">
         <v>5662977.749999999</v>
       </c>
-      <c r="AS44" s="15" t="n">
+      <c r="AV44" s="15" t="n">
         <v>0.6436999999999998</v>
       </c>
-      <c r="AT44" s="13" t="n">
+      <c r="AW44" s="13" t="n">
         <v>697292654</v>
       </c>
-      <c r="AU44" s="14" t="n">
+      <c r="AX44" s="14" t="n">
         <v>5868142.6</v>
       </c>
-      <c r="AV44" s="15" t="n">
+      <c r="AY44" s="15" t="n">
         <v>0.6543000000000002</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="AT2:AV2"/>
     <mergeCell ref="G2:I2"/>
@@ -6165,7 +6514,8 @@
     <mergeCell ref="AK2:AM2"/>
     <mergeCell ref="P2:R2"/>
     <mergeCell ref="AN2:AP2"/>
-    <mergeCell ref="A1:AV1"/>
+    <mergeCell ref="A1:AY1"/>
+    <mergeCell ref="AW2:AY2"/>
     <mergeCell ref="AQ2:AS2"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="S2:U2"/>

--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -493,7 +493,7 @@
   <dimension ref="A1:BO44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -5417,7 +5417,7 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Central Depository Services (India) Limited</t>
+          <t>Central Depository Services (India)</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -6498,24 +6498,24 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Swaraj Engines Limited</t>
+          <t>Nesco Limited</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>INE277A01016</t>
+          <t>INE317F01035</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Industrial Products</t>
+          <t>Commercial Services &amp; Supplies</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>1871.38</v>
+        <v>1862.26</v>
       </c>
       <c r="F34" s="10" t="n">
         <v>0.0001</v>
@@ -6524,10 +6524,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>1564.88</v>
+        <v>1538.11</v>
       </c>
       <c r="J34" s="10" t="n">
         <v>0.0001</v>
@@ -6536,10 +6536,10 @@
         <v>0</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="M34" s="9" t="n">
-        <v>1700.33</v>
+        <v>1704.36</v>
       </c>
       <c r="N34" s="10" t="n">
         <v>0.0001</v>
@@ -6548,10 +6548,10 @@
         <v>0</v>
       </c>
       <c r="P34" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>1637.61</v>
+        <v>1728.63</v>
       </c>
       <c r="R34" s="10" t="n">
         <v>0.0001</v>
@@ -6560,10 +6560,10 @@
         <v>0</v>
       </c>
       <c r="T34" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="U34" s="9" t="n">
-        <v>1691.91</v>
+        <v>1858.32</v>
       </c>
       <c r="V34" s="10" t="n">
         <v>0.0001</v>
@@ -6572,22 +6572,22 @@
         <v>0</v>
       </c>
       <c r="X34" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="Y34" s="9" t="n">
-        <v>1764.08</v>
+        <v>1947.66</v>
       </c>
       <c r="Z34" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="AA34" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AB34" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AC34" s="9" t="n">
-        <v>1892.15</v>
+        <v>2076.6</v>
       </c>
       <c r="AD34" s="10" t="n">
         <v>0.0002</v>
@@ -6596,10 +6596,10 @@
         <v>0</v>
       </c>
       <c r="AF34" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AG34" s="9" t="n">
-        <v>1955.38</v>
+        <v>1987.1</v>
       </c>
       <c r="AH34" s="10" t="n">
         <v>0.0002</v>
@@ -6608,10 +6608,10 @@
         <v>0</v>
       </c>
       <c r="AJ34" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AK34" s="9" t="n">
-        <v>1897.21</v>
+        <v>2130.6</v>
       </c>
       <c r="AL34" s="10" t="n">
         <v>0.0002</v>
@@ -6620,10 +6620,10 @@
         <v>0</v>
       </c>
       <c r="AN34" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AO34" s="9" t="n">
-        <v>1983.66</v>
+        <v>2091.16</v>
       </c>
       <c r="AP34" s="10" t="n">
         <v>0.0002</v>
@@ -6632,97 +6632,67 @@
         <v>0</v>
       </c>
       <c r="AR34" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AS34" s="9" t="n">
-        <v>1867.41</v>
+        <v>1766.62</v>
       </c>
       <c r="AT34" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="AU34" s="11" t="n">
-        <v>0</v>
+        <v>0.6954140540298874</v>
       </c>
       <c r="AV34" s="8" t="n">
-        <v>47293</v>
+        <v>89469</v>
       </c>
       <c r="AW34" s="9" t="n">
-        <v>1857.76</v>
+        <v>828.48</v>
       </c>
       <c r="AX34" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ34" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="BA34" s="9" t="n">
-        <v>1925.39</v>
-      </c>
-      <c r="BB34" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="BC34" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD34" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="BE34" s="9" t="n">
-        <v>1844.17</v>
-      </c>
-      <c r="BF34" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="BG34" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH34" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="BI34" s="9" t="n">
-        <v>1236.83</v>
-      </c>
-      <c r="BJ34" s="10" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="BK34" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL34" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="BM34" s="9" t="n">
-        <v>1612.64</v>
-      </c>
-      <c r="BN34" s="10" t="n">
-        <v>0.0002</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AZ34" s="8" t="n"/>
+      <c r="BA34" s="9" t="n"/>
+      <c r="BB34" s="10" t="n"/>
+      <c r="BC34" s="11" t="n"/>
+      <c r="BD34" s="8" t="n"/>
+      <c r="BE34" s="9" t="n"/>
+      <c r="BF34" s="10" t="n"/>
+      <c r="BG34" s="11" t="n"/>
+      <c r="BH34" s="8" t="n"/>
+      <c r="BI34" s="9" t="n"/>
+      <c r="BJ34" s="10" t="n"/>
+      <c r="BK34" s="11" t="n"/>
+      <c r="BL34" s="8" t="n"/>
+      <c r="BM34" s="9" t="n"/>
+      <c r="BN34" s="10" t="n"/>
       <c r="BO34" s="11" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Nesco Limited</t>
+          <t>Swaraj Engines Limited</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>INE317F01035</t>
+          <t>INE277A01016</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Commercial Services &amp; Supplies</t>
+          <t>Industrial Products</t>
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>1862.26</v>
+        <v>1871.38</v>
       </c>
       <c r="F35" s="10" t="n">
         <v>0.0001</v>
@@ -6731,10 +6701,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>1538.11</v>
+        <v>1564.88</v>
       </c>
       <c r="J35" s="10" t="n">
         <v>0.0001</v>
@@ -6743,10 +6713,10 @@
         <v>0</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>1704.36</v>
+        <v>1700.33</v>
       </c>
       <c r="N35" s="10" t="n">
         <v>0.0001</v>
@@ -6755,10 +6725,10 @@
         <v>0</v>
       </c>
       <c r="P35" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>1728.63</v>
+        <v>1637.61</v>
       </c>
       <c r="R35" s="10" t="n">
         <v>0.0001</v>
@@ -6767,10 +6737,10 @@
         <v>0</v>
       </c>
       <c r="T35" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="U35" s="9" t="n">
-        <v>1858.32</v>
+        <v>1691.91</v>
       </c>
       <c r="V35" s="10" t="n">
         <v>0.0001</v>
@@ -6779,22 +6749,22 @@
         <v>0</v>
       </c>
       <c r="X35" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="Y35" s="9" t="n">
-        <v>1947.66</v>
+        <v>1764.08</v>
       </c>
       <c r="Z35" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="AA35" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AB35" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AC35" s="9" t="n">
-        <v>2076.6</v>
+        <v>1892.15</v>
       </c>
       <c r="AD35" s="10" t="n">
         <v>0.0002</v>
@@ -6803,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AF35" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AG35" s="9" t="n">
-        <v>1987.1</v>
+        <v>1955.38</v>
       </c>
       <c r="AH35" s="10" t="n">
         <v>0.0002</v>
@@ -6815,10 +6785,10 @@
         <v>0</v>
       </c>
       <c r="AJ35" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AK35" s="9" t="n">
-        <v>2130.6</v>
+        <v>1897.21</v>
       </c>
       <c r="AL35" s="10" t="n">
         <v>0.0002</v>
@@ -6827,10 +6797,10 @@
         <v>0</v>
       </c>
       <c r="AN35" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AO35" s="9" t="n">
-        <v>2091.16</v>
+        <v>1983.66</v>
       </c>
       <c r="AP35" s="10" t="n">
         <v>0.0002</v>
@@ -6839,438 +6809,382 @@
         <v>0</v>
       </c>
       <c r="AR35" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AS35" s="9" t="n">
-        <v>1766.62</v>
+        <v>1867.41</v>
       </c>
       <c r="AT35" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="AU35" s="11" t="n">
-        <v>0.6954140540298874</v>
+        <v>0</v>
       </c>
       <c r="AV35" s="8" t="n">
-        <v>89469</v>
+        <v>47293</v>
       </c>
       <c r="AW35" s="9" t="n">
-        <v>828.48</v>
+        <v>1857.76</v>
       </c>
       <c r="AX35" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AY35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="BA35" s="9" t="n">
+        <v>1925.39</v>
+      </c>
+      <c r="BB35" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="BC35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD35" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="BE35" s="9" t="n">
+        <v>1844.17</v>
+      </c>
+      <c r="BF35" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="BG35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH35" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="BI35" s="9" t="n">
+        <v>1236.83</v>
+      </c>
+      <c r="BJ35" s="10" t="n">
         <v>0.0001</v>
       </c>
-      <c r="AY35" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ35" s="8" t="n"/>
-      <c r="BA35" s="9" t="n"/>
-      <c r="BB35" s="10" t="n"/>
-      <c r="BC35" s="11" t="n"/>
-      <c r="BD35" s="8" t="n"/>
-      <c r="BE35" s="9" t="n"/>
-      <c r="BF35" s="10" t="n"/>
-      <c r="BG35" s="11" t="n"/>
-      <c r="BH35" s="8" t="n"/>
-      <c r="BI35" s="9" t="n"/>
-      <c r="BJ35" s="10" t="n"/>
-      <c r="BK35" s="11" t="n"/>
-      <c r="BL35" s="8" t="n"/>
-      <c r="BM35" s="9" t="n"/>
-      <c r="BN35" s="10" t="n"/>
+      <c r="BK35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL35" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="BM35" s="9" t="n">
+        <v>1612.64</v>
+      </c>
+      <c r="BN35" s="10" t="n">
+        <v>0.0002</v>
+      </c>
       <c r="BO35" s="11" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Kotak Mahindra Bank Limited</t>
+          <t>Balkrishna Industries Limited</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>INE237A01028</t>
+          <t>INE787D01026</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Auto Components</t>
         </is>
       </c>
       <c r="D36" s="8" t="n"/>
       <c r="E36" s="9" t="n"/>
       <c r="F36" s="10" t="n"/>
-      <c r="G36" s="11" t="n"/>
-      <c r="H36" s="8" t="n"/>
-      <c r="I36" s="9" t="n"/>
-      <c r="J36" s="10" t="n"/>
-      <c r="K36" s="11" t="n"/>
-      <c r="L36" s="8" t="n"/>
-      <c r="M36" s="9" t="n"/>
-      <c r="N36" s="10" t="n"/>
-      <c r="O36" s="11" t="n"/>
-      <c r="P36" s="8" t="n"/>
-      <c r="Q36" s="9" t="n"/>
-      <c r="R36" s="10" t="n"/>
+      <c r="G36" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>2274074</v>
+      </c>
+      <c r="I36" s="9" t="n">
+        <v>47368.96</v>
+      </c>
+      <c r="J36" s="10" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="K36" s="11" t="n">
+        <v>-0.2174731122669314</v>
+      </c>
+      <c r="L36" s="8" t="n">
+        <v>2906065</v>
+      </c>
+      <c r="M36" s="9" t="n">
+        <v>69277.67999999999</v>
+      </c>
+      <c r="N36" s="10" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="O36" s="11" t="n">
+        <v>-0.3062750860930125</v>
+      </c>
+      <c r="P36" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="Q36" s="9" t="n">
+        <v>96591.67</v>
+      </c>
+      <c r="R36" s="10" t="n">
+        <v>0.0072</v>
+      </c>
       <c r="S36" s="11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T36" s="8" t="n">
-        <v>24621592</v>
+        <v>4189074</v>
       </c>
       <c r="U36" s="9" t="n">
-        <v>541945.86</v>
+        <v>97173.95</v>
       </c>
       <c r="V36" s="10" t="n">
-        <v>0.0407</v>
+        <v>0.0073</v>
       </c>
       <c r="W36" s="11" t="n">
-        <v>0.01296144774839237</v>
+        <v>0</v>
       </c>
       <c r="X36" s="8" t="n">
-        <v>24306544</v>
+        <v>4189074</v>
       </c>
       <c r="Y36" s="9" t="n">
-        <v>516368.22</v>
+        <v>96721.53</v>
       </c>
       <c r="Z36" s="10" t="n">
-        <v>0.0398</v>
+        <v>0.0075</v>
       </c>
       <c r="AA36" s="11" t="n">
-        <v>0.004192884502844551</v>
+        <v>0</v>
       </c>
       <c r="AB36" s="8" t="n">
-        <v>24205055</v>
+        <v>4189074</v>
       </c>
       <c r="AC36" s="9" t="n">
-        <v>508838.67</v>
+        <v>95502.50999999999</v>
       </c>
       <c r="AD36" s="10" t="n">
-        <v>0.0404</v>
+        <v>0.0076</v>
       </c>
       <c r="AE36" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AF36" s="8" t="n">
-        <v>24205055</v>
+        <v>4189074</v>
       </c>
       <c r="AG36" s="9" t="n">
-        <v>482334.13</v>
+        <v>96130.87</v>
       </c>
       <c r="AH36" s="10" t="n">
-        <v>0.0403</v>
+        <v>0.008</v>
       </c>
       <c r="AI36" s="11" t="n">
-        <v>0.03407788338216907</v>
+        <v>0</v>
       </c>
       <c r="AJ36" s="8" t="n">
-        <v>23407381</v>
+        <v>4189074</v>
       </c>
       <c r="AK36" s="9" t="n">
-        <v>458854.89</v>
+        <v>95904.66</v>
       </c>
       <c r="AL36" s="10" t="n">
-        <v>0.0399</v>
+        <v>0.0083</v>
       </c>
       <c r="AM36" s="11" t="n">
-        <v>0.06425892329321918</v>
+        <v>0</v>
       </c>
       <c r="AN36" s="8" t="n">
-        <v>21994066</v>
+        <v>4189074</v>
       </c>
       <c r="AO36" s="9" t="n">
-        <v>435174.59</v>
+        <v>112108</v>
       </c>
       <c r="AP36" s="10" t="n">
-        <v>0.0384</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="AQ36" s="11" t="n">
-        <v>0.07428402120388222</v>
+        <v>0</v>
       </c>
       <c r="AR36" s="8" t="n">
-        <v>20473232</v>
+        <v>4189074</v>
       </c>
       <c r="AS36" s="9" t="n">
-        <v>442938.37</v>
+        <v>102435.43</v>
       </c>
       <c r="AT36" s="10" t="n">
-        <v>0.0401</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="AU36" s="11" t="n">
-        <v>0.03644973136547983</v>
+        <v>0</v>
       </c>
       <c r="AV36" s="8" t="n">
-        <v>19753232</v>
+        <v>4189074</v>
       </c>
       <c r="AW36" s="9" t="n">
-        <v>409820.3</v>
+        <v>103562.29</v>
       </c>
       <c r="AX36" s="10" t="n">
-        <v>0.0395</v>
+        <v>0.01</v>
       </c>
       <c r="AY36" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AZ36" s="8" t="n">
-        <v>19753232</v>
+        <v>4189074</v>
       </c>
       <c r="BA36" s="9" t="n">
-        <v>436171.12</v>
+        <v>112061.92</v>
       </c>
       <c r="BB36" s="10" t="n">
-        <v>0.0443</v>
+        <v>0.0114</v>
       </c>
       <c r="BC36" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BD36" s="8" t="n">
-        <v>19753232</v>
+        <v>4189074</v>
       </c>
       <c r="BE36" s="9" t="n">
-        <v>428882.17</v>
+        <v>107022.46</v>
       </c>
       <c r="BF36" s="10" t="n">
-        <v>0.0459</v>
+        <v>0.0115</v>
       </c>
       <c r="BG36" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BH36" s="8" t="n">
-        <v>19753232</v>
+        <v>4189074</v>
       </c>
       <c r="BI36" s="9" t="n">
-        <v>375894.13</v>
+        <v>109571.51</v>
       </c>
       <c r="BJ36" s="10" t="n">
-        <v>0.0427</v>
+        <v>0.0125</v>
       </c>
       <c r="BK36" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BL36" s="8" t="n">
-        <v>19753232</v>
+        <v>4189074</v>
       </c>
       <c r="BM36" s="9" t="n">
-        <v>375568.2</v>
+        <v>116089.71</v>
       </c>
       <c r="BN36" s="10" t="n">
-        <v>0.0419</v>
+        <v>0.0129</v>
       </c>
       <c r="BO36" s="11" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Balkrishna Industries Limited</t>
+          <t>Multi Commodity Exchange of India Limited</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>INE787D01026</t>
+          <t>INE745G01043</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Auto Components</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D37" s="8" t="n"/>
       <c r="E37" s="9" t="n"/>
       <c r="F37" s="10" t="n"/>
-      <c r="G37" s="11" t="n">
+      <c r="G37" s="11" t="n"/>
+      <c r="H37" s="8" t="n"/>
+      <c r="I37" s="9" t="n"/>
+      <c r="J37" s="10" t="n"/>
+      <c r="K37" s="11" t="n"/>
+      <c r="L37" s="8" t="n"/>
+      <c r="M37" s="9" t="n"/>
+      <c r="N37" s="10" t="n"/>
+      <c r="O37" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="H37" s="8" t="n">
-        <v>2274074</v>
-      </c>
-      <c r="I37" s="9" t="n">
-        <v>47368.96</v>
-      </c>
-      <c r="J37" s="10" t="n">
-        <v>0.0037</v>
-      </c>
-      <c r="K37" s="11" t="n">
-        <v>-0.2174731122669314</v>
-      </c>
-      <c r="L37" s="8" t="n">
-        <v>2906065</v>
-      </c>
-      <c r="M37" s="9" t="n">
-        <v>69277.67999999999</v>
-      </c>
-      <c r="N37" s="10" t="n">
-        <v>0.0052</v>
-      </c>
-      <c r="O37" s="11" t="n">
-        <v>-0.3062750860930125</v>
-      </c>
       <c r="P37" s="8" t="n">
-        <v>4189074</v>
+        <v>795472</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>96591.67</v>
+        <v>20109.53</v>
       </c>
       <c r="R37" s="10" t="n">
-        <v>0.0072</v>
+        <v>0.0015</v>
       </c>
       <c r="S37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="U37" s="9" t="n">
-        <v>97173.95</v>
-      </c>
-      <c r="V37" s="10" t="n">
-        <v>0.0073</v>
-      </c>
-      <c r="W37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="Y37" s="9" t="n">
-        <v>96721.53</v>
-      </c>
-      <c r="Z37" s="10" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="AA37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="AC37" s="9" t="n">
-        <v>95502.50999999999</v>
-      </c>
-      <c r="AD37" s="10" t="n">
-        <v>0.0076</v>
-      </c>
-      <c r="AE37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF37" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="AG37" s="9" t="n">
-        <v>96130.87</v>
-      </c>
-      <c r="AH37" s="10" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="AI37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ37" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="AK37" s="9" t="n">
-        <v>95904.66</v>
-      </c>
-      <c r="AL37" s="10" t="n">
-        <v>0.0083</v>
-      </c>
-      <c r="AM37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN37" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="AO37" s="9" t="n">
-        <v>112108</v>
-      </c>
-      <c r="AP37" s="10" t="n">
-        <v>0.009900000000000001</v>
-      </c>
-      <c r="AQ37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR37" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="AS37" s="9" t="n">
-        <v>102435.43</v>
-      </c>
-      <c r="AT37" s="10" t="n">
-        <v>0.009299999999999999</v>
-      </c>
-      <c r="AU37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV37" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="AW37" s="9" t="n">
-        <v>103562.29</v>
-      </c>
-      <c r="AX37" s="10" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AY37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ37" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="BA37" s="9" t="n">
-        <v>112061.92</v>
-      </c>
-      <c r="BB37" s="10" t="n">
-        <v>0.0114</v>
-      </c>
-      <c r="BC37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD37" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="BE37" s="9" t="n">
-        <v>107022.46</v>
-      </c>
-      <c r="BF37" s="10" t="n">
-        <v>0.0115</v>
-      </c>
-      <c r="BG37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH37" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="BI37" s="9" t="n">
-        <v>109571.51</v>
-      </c>
-      <c r="BJ37" s="10" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="BK37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL37" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="BM37" s="9" t="n">
-        <v>116089.71</v>
-      </c>
-      <c r="BN37" s="10" t="n">
-        <v>0.0129</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="T37" s="8" t="n"/>
+      <c r="U37" s="9" t="n"/>
+      <c r="V37" s="10" t="n"/>
+      <c r="W37" s="11" t="n"/>
+      <c r="X37" s="8" t="n"/>
+      <c r="Y37" s="9" t="n"/>
+      <c r="Z37" s="10" t="n"/>
+      <c r="AA37" s="11" t="n"/>
+      <c r="AB37" s="8" t="n"/>
+      <c r="AC37" s="9" t="n"/>
+      <c r="AD37" s="10" t="n"/>
+      <c r="AE37" s="11" t="n"/>
+      <c r="AF37" s="8" t="n"/>
+      <c r="AG37" s="9" t="n"/>
+      <c r="AH37" s="10" t="n"/>
+      <c r="AI37" s="11" t="n"/>
+      <c r="AJ37" s="8" t="n"/>
+      <c r="AK37" s="9" t="n"/>
+      <c r="AL37" s="10" t="n"/>
+      <c r="AM37" s="11" t="n"/>
+      <c r="AN37" s="8" t="n"/>
+      <c r="AO37" s="9" t="n"/>
+      <c r="AP37" s="10" t="n"/>
+      <c r="AQ37" s="11" t="n"/>
+      <c r="AR37" s="8" t="n"/>
+      <c r="AS37" s="9" t="n"/>
+      <c r="AT37" s="10" t="n"/>
+      <c r="AU37" s="11" t="n"/>
+      <c r="AV37" s="8" t="n"/>
+      <c r="AW37" s="9" t="n"/>
+      <c r="AX37" s="10" t="n"/>
+      <c r="AY37" s="11" t="n"/>
+      <c r="AZ37" s="8" t="n"/>
+      <c r="BA37" s="9" t="n"/>
+      <c r="BB37" s="10" t="n"/>
+      <c r="BC37" s="11" t="n"/>
+      <c r="BD37" s="8" t="n"/>
+      <c r="BE37" s="9" t="n"/>
+      <c r="BF37" s="10" t="n"/>
+      <c r="BG37" s="11" t="n"/>
+      <c r="BH37" s="8" t="n"/>
+      <c r="BI37" s="9" t="n"/>
+      <c r="BJ37" s="10" t="n"/>
+      <c r="BK37" s="11" t="n"/>
+      <c r="BL37" s="8" t="n"/>
+      <c r="BM37" s="9" t="n"/>
+      <c r="BN37" s="10" t="n"/>
       <c r="BO37" s="11" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Motilal Oswal Financial Services Limited</t>
+          <t>Kotak Mahindra Bank Limited</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>INE338I01027</t>
+          <t>INE237A01028</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="D38" s="8" t="n"/>
@@ -7288,118 +7202,166 @@
       <c r="P38" s="8" t="n"/>
       <c r="Q38" s="9" t="n"/>
       <c r="R38" s="10" t="n"/>
-      <c r="S38" s="11" t="n"/>
-      <c r="T38" s="8" t="n"/>
-      <c r="U38" s="9" t="n"/>
-      <c r="V38" s="10" t="n"/>
-      <c r="W38" s="11" t="n"/>
-      <c r="X38" s="8" t="n"/>
-      <c r="Y38" s="9" t="n"/>
-      <c r="Z38" s="10" t="n"/>
-      <c r="AA38" s="11" t="n"/>
-      <c r="AB38" s="8" t="n"/>
-      <c r="AC38" s="9" t="n"/>
-      <c r="AD38" s="10" t="n"/>
-      <c r="AE38" s="11" t="n"/>
-      <c r="AF38" s="8" t="n"/>
-      <c r="AG38" s="9" t="n"/>
-      <c r="AH38" s="10" t="n"/>
-      <c r="AI38" s="11" t="n"/>
-      <c r="AJ38" s="8" t="n"/>
-      <c r="AK38" s="9" t="n"/>
-      <c r="AL38" s="10" t="n"/>
-      <c r="AM38" s="11" t="n"/>
-      <c r="AN38" s="8" t="n"/>
-      <c r="AO38" s="9" t="n"/>
-      <c r="AP38" s="10" t="n"/>
+      <c r="S38" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v>24621592</v>
+      </c>
+      <c r="U38" s="9" t="n">
+        <v>541945.86</v>
+      </c>
+      <c r="V38" s="10" t="n">
+        <v>0.0407</v>
+      </c>
+      <c r="W38" s="11" t="n">
+        <v>0.01296144774839237</v>
+      </c>
+      <c r="X38" s="8" t="n">
+        <v>24306544</v>
+      </c>
+      <c r="Y38" s="9" t="n">
+        <v>516368.22</v>
+      </c>
+      <c r="Z38" s="10" t="n">
+        <v>0.0398</v>
+      </c>
+      <c r="AA38" s="11" t="n">
+        <v>0.004192884502844551</v>
+      </c>
+      <c r="AB38" s="8" t="n">
+        <v>24205055</v>
+      </c>
+      <c r="AC38" s="9" t="n">
+        <v>508838.67</v>
+      </c>
+      <c r="AD38" s="10" t="n">
+        <v>0.0404</v>
+      </c>
+      <c r="AE38" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" s="8" t="n">
+        <v>24205055</v>
+      </c>
+      <c r="AG38" s="9" t="n">
+        <v>482334.13</v>
+      </c>
+      <c r="AH38" s="10" t="n">
+        <v>0.0403</v>
+      </c>
+      <c r="AI38" s="11" t="n">
+        <v>0.03407788338216907</v>
+      </c>
+      <c r="AJ38" s="8" t="n">
+        <v>23407381</v>
+      </c>
+      <c r="AK38" s="9" t="n">
+        <v>458854.89</v>
+      </c>
+      <c r="AL38" s="10" t="n">
+        <v>0.0399</v>
+      </c>
+      <c r="AM38" s="11" t="n">
+        <v>0.06425892329321918</v>
+      </c>
+      <c r="AN38" s="8" t="n">
+        <v>21994066</v>
+      </c>
+      <c r="AO38" s="9" t="n">
+        <v>435174.59</v>
+      </c>
+      <c r="AP38" s="10" t="n">
+        <v>0.0384</v>
+      </c>
       <c r="AQ38" s="11" t="n">
-        <v>-1</v>
+        <v>0.07428402120388222</v>
       </c>
       <c r="AR38" s="8" t="n">
-        <v>591805</v>
+        <v>20473232</v>
       </c>
       <c r="AS38" s="9" t="n">
-        <v>5149</v>
+        <v>442938.37</v>
       </c>
       <c r="AT38" s="10" t="n">
-        <v>0.0005</v>
+        <v>0.0401</v>
       </c>
       <c r="AU38" s="11" t="n">
-        <v>-0.8902567225534253</v>
+        <v>0.03644973136547983</v>
       </c>
       <c r="AV38" s="8" t="n">
-        <v>5392631</v>
+        <v>19753232</v>
       </c>
       <c r="AW38" s="9" t="n">
-        <v>43674.92</v>
+        <v>409820.3</v>
       </c>
       <c r="AX38" s="10" t="n">
-        <v>0.0042</v>
+        <v>0.0395</v>
       </c>
       <c r="AY38" s="11" t="n">
-        <v>-0.3719237093069153</v>
+        <v>0</v>
       </c>
       <c r="AZ38" s="8" t="n">
-        <v>8585949</v>
+        <v>19753232</v>
       </c>
       <c r="BA38" s="9" t="n">
-        <v>56044.78</v>
+        <v>436171.12</v>
       </c>
       <c r="BB38" s="10" t="n">
-        <v>0.0057</v>
+        <v>0.0443</v>
       </c>
       <c r="BC38" s="11" t="n">
-        <v>-0.2132577936597328</v>
+        <v>0</v>
       </c>
       <c r="BD38" s="8" t="n">
-        <v>10913294</v>
+        <v>19753232</v>
       </c>
       <c r="BE38" s="9" t="n">
-        <v>67154.95</v>
+        <v>428882.17</v>
       </c>
       <c r="BF38" s="10" t="n">
-        <v>0.0072</v>
+        <v>0.0459</v>
       </c>
       <c r="BG38" s="11" t="n">
-        <v>-0.09462389658963724</v>
+        <v>0</v>
       </c>
       <c r="BH38" s="8" t="n">
-        <v>12053879</v>
+        <v>19753232</v>
       </c>
       <c r="BI38" s="9" t="n">
-        <v>70937.08</v>
+        <v>375894.13</v>
       </c>
       <c r="BJ38" s="10" t="n">
-        <v>0.0081</v>
+        <v>0.0427</v>
       </c>
       <c r="BK38" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BL38" s="8" t="n">
-        <v>12053879</v>
+        <v>19753232</v>
       </c>
       <c r="BM38" s="9" t="n">
-        <v>76801.28999999999</v>
+        <v>375568.2</v>
       </c>
       <c r="BN38" s="10" t="n">
-        <v>0.0086</v>
+        <v>0.0419</v>
       </c>
       <c r="BO38" s="11" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Multi Commodity Exchange of India Limited</t>
+          <t>Zydus Wellness Limited</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>INE745G01035</t>
+          <t>INE768C01010</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D39" s="8" t="n"/>
@@ -7417,166 +7379,96 @@
       <c r="P39" s="8" t="n"/>
       <c r="Q39" s="9" t="n"/>
       <c r="R39" s="10" t="n"/>
-      <c r="S39" s="11" t="n">
+      <c r="S39" s="11" t="n"/>
+      <c r="T39" s="8" t="n"/>
+      <c r="U39" s="9" t="n"/>
+      <c r="V39" s="10" t="n"/>
+      <c r="W39" s="11" t="n"/>
+      <c r="X39" s="8" t="n"/>
+      <c r="Y39" s="9" t="n"/>
+      <c r="Z39" s="10" t="n"/>
+      <c r="AA39" s="11" t="n"/>
+      <c r="AB39" s="8" t="n"/>
+      <c r="AC39" s="9" t="n"/>
+      <c r="AD39" s="10" t="n"/>
+      <c r="AE39" s="11" t="n"/>
+      <c r="AF39" s="8" t="n"/>
+      <c r="AG39" s="9" t="n"/>
+      <c r="AH39" s="10" t="n"/>
+      <c r="AI39" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="T39" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="U39" s="9" t="n">
-        <v>88833.99000000001</v>
-      </c>
-      <c r="V39" s="10" t="n">
-        <v>0.0067</v>
-      </c>
-      <c r="W39" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="Y39" s="9" t="n">
-        <v>80358.22</v>
-      </c>
-      <c r="Z39" s="10" t="n">
-        <v>0.0062</v>
-      </c>
-      <c r="AA39" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB39" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="AC39" s="9" t="n">
-        <v>73737.16</v>
-      </c>
-      <c r="AD39" s="10" t="n">
-        <v>0.0059</v>
-      </c>
-      <c r="AE39" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="AG39" s="9" t="n">
-        <v>62190.17</v>
-      </c>
-      <c r="AH39" s="10" t="n">
-        <v>0.0052</v>
-      </c>
-      <c r="AI39" s="11" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ39" s="8" t="n">
-        <v>797719</v>
+        <v>4400000</v>
       </c>
       <c r="AK39" s="9" t="n">
-        <v>58951.43</v>
+        <v>88822.8</v>
       </c>
       <c r="AL39" s="10" t="n">
-        <v>0.0051</v>
+        <v>0.0077</v>
       </c>
       <c r="AM39" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AN39" s="8" t="n">
-        <v>797719</v>
+        <v>4400000</v>
       </c>
       <c r="AO39" s="9" t="n">
-        <v>61368.52</v>
+        <v>89280.39999999999</v>
       </c>
       <c r="AP39" s="10" t="n">
-        <v>0.0054</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="AQ39" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AR39" s="8" t="n">
-        <v>797719</v>
+        <v>4400000</v>
       </c>
       <c r="AS39" s="9" t="n">
-        <v>71347.99000000001</v>
+        <v>89020.8</v>
       </c>
       <c r="AT39" s="10" t="n">
-        <v>0.0065</v>
+        <v>0.0081</v>
       </c>
       <c r="AU39" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV39" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="AW39" s="9" t="n">
-        <v>52665.41</v>
-      </c>
-      <c r="AX39" s="10" t="n">
-        <v>0.0051</v>
-      </c>
-      <c r="AY39" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ39" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="BA39" s="9" t="n">
-        <v>48884.22</v>
-      </c>
-      <c r="BB39" s="10" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="BC39" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD39" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="BE39" s="9" t="n">
-        <v>42372.84</v>
-      </c>
-      <c r="BF39" s="10" t="n">
-        <v>0.0045</v>
-      </c>
-      <c r="BG39" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH39" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="BI39" s="9" t="n">
-        <v>39819.34</v>
-      </c>
-      <c r="BJ39" s="10" t="n">
-        <v>0.0045</v>
-      </c>
-      <c r="BK39" s="11" t="n">
-        <v>-0.09569612848812428</v>
-      </c>
-      <c r="BL39" s="8" t="n">
-        <v>882136</v>
-      </c>
-      <c r="BM39" s="9" t="n">
-        <v>50572.42</v>
-      </c>
-      <c r="BN39" s="10" t="n">
-        <v>0.0056</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AV39" s="8" t="n"/>
+      <c r="AW39" s="9" t="n"/>
+      <c r="AX39" s="10" t="n"/>
+      <c r="AY39" s="11" t="n"/>
+      <c r="AZ39" s="8" t="n"/>
+      <c r="BA39" s="9" t="n"/>
+      <c r="BB39" s="10" t="n"/>
+      <c r="BC39" s="11" t="n"/>
+      <c r="BD39" s="8" t="n"/>
+      <c r="BE39" s="9" t="n"/>
+      <c r="BF39" s="10" t="n"/>
+      <c r="BG39" s="11" t="n"/>
+      <c r="BH39" s="8" t="n"/>
+      <c r="BI39" s="9" t="n"/>
+      <c r="BJ39" s="10" t="n"/>
+      <c r="BK39" s="11" t="n"/>
+      <c r="BL39" s="8" t="n"/>
+      <c r="BM39" s="9" t="n"/>
+      <c r="BN39" s="10" t="n"/>
       <c r="BO39" s="11" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>IPCA Laboratories Limited</t>
+          <t>Multi Commodity Exchange of India Limited</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>INE571A01038</t>
+          <t>INE745G01035</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Pharmaceuticals &amp; Biotechnology</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D40" s="8" t="n"/>
@@ -7594,134 +7486,166 @@
       <c r="P40" s="8" t="n"/>
       <c r="Q40" s="9" t="n"/>
       <c r="R40" s="10" t="n"/>
-      <c r="S40" s="11" t="n"/>
-      <c r="T40" s="8" t="n"/>
-      <c r="U40" s="9" t="n"/>
-      <c r="V40" s="10" t="n"/>
-      <c r="W40" s="11" t="n"/>
-      <c r="X40" s="8" t="n"/>
-      <c r="Y40" s="9" t="n"/>
-      <c r="Z40" s="10" t="n"/>
-      <c r="AA40" s="11" t="n"/>
-      <c r="AB40" s="8" t="n"/>
-      <c r="AC40" s="9" t="n"/>
-      <c r="AD40" s="10" t="n"/>
-      <c r="AE40" s="11" t="n"/>
-      <c r="AF40" s="8" t="n"/>
-      <c r="AG40" s="9" t="n"/>
-      <c r="AH40" s="10" t="n"/>
+      <c r="S40" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="U40" s="9" t="n">
+        <v>88833.99000000001</v>
+      </c>
+      <c r="V40" s="10" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="W40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="Y40" s="9" t="n">
+        <v>80358.22</v>
+      </c>
+      <c r="Z40" s="10" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="AA40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AC40" s="9" t="n">
+        <v>73737.16</v>
+      </c>
+      <c r="AD40" s="10" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="AE40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AG40" s="9" t="n">
+        <v>62190.17</v>
+      </c>
+      <c r="AH40" s="10" t="n">
+        <v>0.0052</v>
+      </c>
       <c r="AI40" s="11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AJ40" s="8" t="n">
-        <v>218075</v>
+        <v>797719</v>
       </c>
       <c r="AK40" s="9" t="n">
-        <v>3019.03</v>
+        <v>58951.43</v>
       </c>
       <c r="AL40" s="10" t="n">
-        <v>0.0003</v>
+        <v>0.0051</v>
       </c>
       <c r="AM40" s="11" t="n">
-        <v>-0.6148554615199853</v>
+        <v>0</v>
       </c>
       <c r="AN40" s="8" t="n">
-        <v>566216</v>
+        <v>797719</v>
       </c>
       <c r="AO40" s="9" t="n">
-        <v>8345.459999999999</v>
+        <v>61368.52</v>
       </c>
       <c r="AP40" s="10" t="n">
-        <v>0.0007</v>
+        <v>0.0054</v>
       </c>
       <c r="AQ40" s="11" t="n">
-        <v>-0.5682871579351869</v>
+        <v>0</v>
       </c>
       <c r="AR40" s="8" t="n">
-        <v>1311557</v>
+        <v>797719</v>
       </c>
       <c r="AS40" s="9" t="n">
-        <v>18228.02</v>
+        <v>71347.99000000001</v>
       </c>
       <c r="AT40" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.0065</v>
       </c>
       <c r="AU40" s="11" t="n">
-        <v>-0.2008037316547793</v>
+        <v>0</v>
       </c>
       <c r="AV40" s="8" t="n">
-        <v>1641095</v>
+        <v>797719</v>
       </c>
       <c r="AW40" s="9" t="n">
-        <v>23382.32</v>
+        <v>52665.41</v>
       </c>
       <c r="AX40" s="10" t="n">
-        <v>0.0023</v>
+        <v>0.0051</v>
       </c>
       <c r="AY40" s="11" t="n">
-        <v>-0.1163687388172734</v>
+        <v>0</v>
       </c>
       <c r="AZ40" s="8" t="n">
-        <v>1857217</v>
+        <v>797719</v>
       </c>
       <c r="BA40" s="9" t="n">
-        <v>26023.32</v>
+        <v>48884.22</v>
       </c>
       <c r="BB40" s="10" t="n">
-        <v>0.0026</v>
+        <v>0.005</v>
       </c>
       <c r="BC40" s="11" t="n">
-        <v>-0.03620728307597141</v>
+        <v>0</v>
       </c>
       <c r="BD40" s="8" t="n">
-        <v>1926988</v>
+        <v>797719</v>
       </c>
       <c r="BE40" s="9" t="n">
-        <v>28941.43</v>
+        <v>42372.84</v>
       </c>
       <c r="BF40" s="10" t="n">
-        <v>0.0031</v>
+        <v>0.0045</v>
       </c>
       <c r="BG40" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BH40" s="8" t="n">
-        <v>1926988</v>
+        <v>797719</v>
       </c>
       <c r="BI40" s="9" t="n">
-        <v>26117.43</v>
+        <v>39819.34</v>
       </c>
       <c r="BJ40" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0045</v>
       </c>
       <c r="BK40" s="11" t="n">
-        <v>-0.1421734974921662</v>
+        <v>-0.09569612848812428</v>
       </c>
       <c r="BL40" s="8" t="n">
-        <v>2246361</v>
+        <v>882136</v>
       </c>
       <c r="BM40" s="9" t="n">
-        <v>32421.73</v>
+        <v>50572.42</v>
       </c>
       <c r="BN40" s="10" t="n">
-        <v>0.0036</v>
+        <v>0.0056</v>
       </c>
       <c r="BO40" s="11" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>ITC Hotels Limited</t>
+          <t>IPCA Laboratories Limited</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>INE379A01028</t>
+          <t>INE571A01038</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Leisure Services</t>
+          <t>Pharmaceuticals &amp; Biotechnology</t>
         </is>
       </c>
       <c r="D41" s="8" t="n"/>
@@ -7755,78 +7679,118 @@
       <c r="AF41" s="8" t="n"/>
       <c r="AG41" s="9" t="n"/>
       <c r="AH41" s="10" t="n"/>
-      <c r="AI41" s="11" t="n"/>
-      <c r="AJ41" s="8" t="n"/>
-      <c r="AK41" s="9" t="n"/>
-      <c r="AL41" s="10" t="n"/>
-      <c r="AM41" s="11" t="n"/>
-      <c r="AN41" s="8" t="n"/>
-      <c r="AO41" s="9" t="n"/>
-      <c r="AP41" s="10" t="n"/>
-      <c r="AQ41" s="11" t="n"/>
-      <c r="AR41" s="8" t="n"/>
-      <c r="AS41" s="9" t="n"/>
-      <c r="AT41" s="10" t="n"/>
-      <c r="AU41" s="11" t="n"/>
-      <c r="AV41" s="8" t="n"/>
-      <c r="AW41" s="9" t="n"/>
-      <c r="AX41" s="10" t="n"/>
-      <c r="AY41" s="11" t="n"/>
-      <c r="AZ41" s="8" t="n"/>
-      <c r="BA41" s="9" t="n"/>
-      <c r="BB41" s="10" t="n"/>
+      <c r="AI41" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AJ41" s="8" t="n">
+        <v>218075</v>
+      </c>
+      <c r="AK41" s="9" t="n">
+        <v>3019.03</v>
+      </c>
+      <c r="AL41" s="10" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="AM41" s="11" t="n">
+        <v>-0.6148554615199853</v>
+      </c>
+      <c r="AN41" s="8" t="n">
+        <v>566216</v>
+      </c>
+      <c r="AO41" s="9" t="n">
+        <v>8345.459999999999</v>
+      </c>
+      <c r="AP41" s="10" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="AQ41" s="11" t="n">
+        <v>-0.5682871579351869</v>
+      </c>
+      <c r="AR41" s="8" t="n">
+        <v>1311557</v>
+      </c>
+      <c r="AS41" s="9" t="n">
+        <v>18228.02</v>
+      </c>
+      <c r="AT41" s="10" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="AU41" s="11" t="n">
+        <v>-0.2008037316547793</v>
+      </c>
+      <c r="AV41" s="8" t="n">
+        <v>1641095</v>
+      </c>
+      <c r="AW41" s="9" t="n">
+        <v>23382.32</v>
+      </c>
+      <c r="AX41" s="10" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="AY41" s="11" t="n">
+        <v>-0.1163687388172734</v>
+      </c>
+      <c r="AZ41" s="8" t="n">
+        <v>1857217</v>
+      </c>
+      <c r="BA41" s="9" t="n">
+        <v>26023.32</v>
+      </c>
+      <c r="BB41" s="10" t="n">
+        <v>0.0026</v>
+      </c>
       <c r="BC41" s="11" t="n">
-        <v>-1</v>
+        <v>-0.03620728307597141</v>
       </c>
       <c r="BD41" s="8" t="n">
-        <v>9899412</v>
+        <v>1926988</v>
       </c>
       <c r="BE41" s="9" t="n">
-        <v>19552.33</v>
+        <v>28941.43</v>
       </c>
       <c r="BF41" s="10" t="n">
-        <v>0.0021</v>
+        <v>0.0031</v>
       </c>
       <c r="BG41" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BH41" s="8" t="n">
-        <v>9899412</v>
+        <v>1926988</v>
       </c>
       <c r="BI41" s="9" t="n">
-        <v>16216.23</v>
+        <v>26117.43</v>
       </c>
       <c r="BJ41" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.003</v>
       </c>
       <c r="BK41" s="11" t="n">
-        <v>0</v>
+        <v>-0.1421734974921662</v>
       </c>
       <c r="BL41" s="8" t="n">
-        <v>9899412</v>
+        <v>2246361</v>
       </c>
       <c r="BM41" s="9" t="n">
-        <v>16131.09</v>
+        <v>32421.73</v>
       </c>
       <c r="BN41" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.0036</v>
       </c>
       <c r="BO41" s="11" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited</t>
+          <t>Motilal Oswal Financial Services Limited</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>INE768C01010</t>
+          <t>INE338I01027</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D42" s="8" t="n"/>
@@ -7860,80 +7824,102 @@
       <c r="AF42" s="8" t="n"/>
       <c r="AG42" s="9" t="n"/>
       <c r="AH42" s="10" t="n"/>
-      <c r="AI42" s="11" t="n">
+      <c r="AI42" s="11" t="n"/>
+      <c r="AJ42" s="8" t="n"/>
+      <c r="AK42" s="9" t="n"/>
+      <c r="AL42" s="10" t="n"/>
+      <c r="AM42" s="11" t="n"/>
+      <c r="AN42" s="8" t="n"/>
+      <c r="AO42" s="9" t="n"/>
+      <c r="AP42" s="10" t="n"/>
+      <c r="AQ42" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="AJ42" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="AK42" s="9" t="n">
-        <v>88822.8</v>
-      </c>
-      <c r="AL42" s="10" t="n">
-        <v>0.0077</v>
-      </c>
-      <c r="AM42" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN42" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="AO42" s="9" t="n">
-        <v>89280.39999999999</v>
-      </c>
-      <c r="AP42" s="10" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-      <c r="AQ42" s="11" t="n">
-        <v>0</v>
-      </c>
       <c r="AR42" s="8" t="n">
-        <v>4400000</v>
+        <v>591805</v>
       </c>
       <c r="AS42" s="9" t="n">
-        <v>89020.8</v>
+        <v>5149</v>
       </c>
       <c r="AT42" s="10" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="AU42" s="11" t="n">
+        <v>-0.8902567225534253</v>
+      </c>
+      <c r="AV42" s="8" t="n">
+        <v>5392631</v>
+      </c>
+      <c r="AW42" s="9" t="n">
+        <v>43674.92</v>
+      </c>
+      <c r="AX42" s="10" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="AY42" s="11" t="n">
+        <v>-0.3719237093069153</v>
+      </c>
+      <c r="AZ42" s="8" t="n">
+        <v>8585949</v>
+      </c>
+      <c r="BA42" s="9" t="n">
+        <v>56044.78</v>
+      </c>
+      <c r="BB42" s="10" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="BC42" s="11" t="n">
+        <v>-0.2132577936597328</v>
+      </c>
+      <c r="BD42" s="8" t="n">
+        <v>10913294</v>
+      </c>
+      <c r="BE42" s="9" t="n">
+        <v>67154.95</v>
+      </c>
+      <c r="BF42" s="10" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="BG42" s="11" t="n">
+        <v>-0.09462389658963724</v>
+      </c>
+      <c r="BH42" s="8" t="n">
+        <v>12053879</v>
+      </c>
+      <c r="BI42" s="9" t="n">
+        <v>70937.08</v>
+      </c>
+      <c r="BJ42" s="10" t="n">
         <v>0.0081</v>
       </c>
-      <c r="AU42" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV42" s="8" t="n"/>
-      <c r="AW42" s="9" t="n"/>
-      <c r="AX42" s="10" t="n"/>
-      <c r="AY42" s="11" t="n"/>
-      <c r="AZ42" s="8" t="n"/>
-      <c r="BA42" s="9" t="n"/>
-      <c r="BB42" s="10" t="n"/>
-      <c r="BC42" s="11" t="n"/>
-      <c r="BD42" s="8" t="n"/>
-      <c r="BE42" s="9" t="n"/>
-      <c r="BF42" s="10" t="n"/>
-      <c r="BG42" s="11" t="n"/>
-      <c r="BH42" s="8" t="n"/>
-      <c r="BI42" s="9" t="n"/>
-      <c r="BJ42" s="10" t="n"/>
-      <c r="BK42" s="11" t="n"/>
-      <c r="BL42" s="8" t="n"/>
-      <c r="BM42" s="9" t="n"/>
-      <c r="BN42" s="10" t="n"/>
+      <c r="BK42" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL42" s="8" t="n">
+        <v>12053879</v>
+      </c>
+      <c r="BM42" s="9" t="n">
+        <v>76801.28999999999</v>
+      </c>
+      <c r="BN42" s="10" t="n">
+        <v>0.0086</v>
+      </c>
       <c r="BO42" s="11" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Multi Commodity Exchange of India Limited</t>
+          <t>ITC Hotels Limited</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>INE745G01043</t>
+          <t>INE379A01028</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Leisure Services</t>
         </is>
       </c>
       <c r="D43" s="8" t="n"/>
@@ -7947,21 +7933,11 @@
       <c r="L43" s="8" t="n"/>
       <c r="M43" s="9" t="n"/>
       <c r="N43" s="10" t="n"/>
-      <c r="O43" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P43" s="8" t="n">
-        <v>795472</v>
-      </c>
-      <c r="Q43" s="9" t="n">
-        <v>20109.53</v>
-      </c>
-      <c r="R43" s="10" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="S43" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="O43" s="11" t="n"/>
+      <c r="P43" s="8" t="n"/>
+      <c r="Q43" s="9" t="n"/>
+      <c r="R43" s="10" t="n"/>
+      <c r="S43" s="11" t="n"/>
       <c r="T43" s="8" t="n"/>
       <c r="U43" s="9" t="n"/>
       <c r="V43" s="10" t="n"/>
@@ -7997,18 +7973,42 @@
       <c r="AZ43" s="8" t="n"/>
       <c r="BA43" s="9" t="n"/>
       <c r="BB43" s="10" t="n"/>
-      <c r="BC43" s="11" t="n"/>
-      <c r="BD43" s="8" t="n"/>
-      <c r="BE43" s="9" t="n"/>
-      <c r="BF43" s="10" t="n"/>
-      <c r="BG43" s="11" t="n"/>
-      <c r="BH43" s="8" t="n"/>
-      <c r="BI43" s="9" t="n"/>
-      <c r="BJ43" s="10" t="n"/>
-      <c r="BK43" s="11" t="n"/>
-      <c r="BL43" s="8" t="n"/>
-      <c r="BM43" s="9" t="n"/>
-      <c r="BN43" s="10" t="n"/>
+      <c r="BC43" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BD43" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BE43" s="9" t="n">
+        <v>19552.33</v>
+      </c>
+      <c r="BF43" s="10" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="BG43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH43" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BI43" s="9" t="n">
+        <v>16216.23</v>
+      </c>
+      <c r="BJ43" s="10" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="BK43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL43" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BM43" s="9" t="n">
+        <v>16131.09</v>
+      </c>
+      <c r="BN43" s="10" t="n">
+        <v>0.0018</v>
+      </c>
       <c r="BO43" s="11" t="n"/>
     </row>
     <row r="44">
@@ -8063,7 +8063,7 @@
         <v>1079845116</v>
       </c>
       <c r="U44" s="15" t="n">
-        <v>8588270.839999998</v>
+        <v>8588270.84</v>
       </c>
       <c r="V44" s="16" t="n">
         <v>0.6443999999999998</v>
@@ -8076,7 +8076,7 @@
         <v>8271351.1939775</v>
       </c>
       <c r="Z44" s="16" t="n">
-        <v>0.6374000000000001</v>
+        <v>0.6374000000000002</v>
       </c>
       <c r="AA44" s="17" t="n"/>
       <c r="AB44" s="14" t="n">

--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -493,7 +493,7 @@
   <dimension ref="A1:BO44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -5417,7 +5417,7 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Central Depository Services (India)</t>
+          <t>Central Depository Services (India) Limited</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -6498,24 +6498,24 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Nesco Limited</t>
+          <t>Swaraj Engines Limited</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>INE317F01035</t>
+          <t>INE277A01016</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Commercial Services &amp; Supplies</t>
+          <t>Industrial Products</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>1862.26</v>
+        <v>1871.38</v>
       </c>
       <c r="F34" s="10" t="n">
         <v>0.0001</v>
@@ -6524,10 +6524,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>1538.11</v>
+        <v>1564.88</v>
       </c>
       <c r="J34" s="10" t="n">
         <v>0.0001</v>
@@ -6536,10 +6536,10 @@
         <v>0</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="M34" s="9" t="n">
-        <v>1704.36</v>
+        <v>1700.33</v>
       </c>
       <c r="N34" s="10" t="n">
         <v>0.0001</v>
@@ -6548,10 +6548,10 @@
         <v>0</v>
       </c>
       <c r="P34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>1728.63</v>
+        <v>1637.61</v>
       </c>
       <c r="R34" s="10" t="n">
         <v>0.0001</v>
@@ -6560,10 +6560,10 @@
         <v>0</v>
       </c>
       <c r="T34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="U34" s="9" t="n">
-        <v>1858.32</v>
+        <v>1691.91</v>
       </c>
       <c r="V34" s="10" t="n">
         <v>0.0001</v>
@@ -6572,22 +6572,22 @@
         <v>0</v>
       </c>
       <c r="X34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="Y34" s="9" t="n">
-        <v>1947.66</v>
+        <v>1764.08</v>
       </c>
       <c r="Z34" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="AA34" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AB34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AC34" s="9" t="n">
-        <v>2076.6</v>
+        <v>1892.15</v>
       </c>
       <c r="AD34" s="10" t="n">
         <v>0.0002</v>
@@ -6596,10 +6596,10 @@
         <v>0</v>
       </c>
       <c r="AF34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AG34" s="9" t="n">
-        <v>1987.1</v>
+        <v>1955.38</v>
       </c>
       <c r="AH34" s="10" t="n">
         <v>0.0002</v>
@@ -6608,10 +6608,10 @@
         <v>0</v>
       </c>
       <c r="AJ34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AK34" s="9" t="n">
-        <v>2130.6</v>
+        <v>1897.21</v>
       </c>
       <c r="AL34" s="10" t="n">
         <v>0.0002</v>
@@ -6620,10 +6620,10 @@
         <v>0</v>
       </c>
       <c r="AN34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AO34" s="9" t="n">
-        <v>2091.16</v>
+        <v>1983.66</v>
       </c>
       <c r="AP34" s="10" t="n">
         <v>0.0002</v>
@@ -6632,67 +6632,97 @@
         <v>0</v>
       </c>
       <c r="AR34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AS34" s="9" t="n">
-        <v>1766.62</v>
+        <v>1867.41</v>
       </c>
       <c r="AT34" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="AU34" s="11" t="n">
-        <v>0.6954140540298874</v>
+        <v>0</v>
       </c>
       <c r="AV34" s="8" t="n">
-        <v>89469</v>
+        <v>47293</v>
       </c>
       <c r="AW34" s="9" t="n">
-        <v>828.48</v>
+        <v>1857.76</v>
       </c>
       <c r="AX34" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AY34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="BA34" s="9" t="n">
+        <v>1925.39</v>
+      </c>
+      <c r="BB34" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="BC34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD34" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="BE34" s="9" t="n">
+        <v>1844.17</v>
+      </c>
+      <c r="BF34" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="BG34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH34" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="BI34" s="9" t="n">
+        <v>1236.83</v>
+      </c>
+      <c r="BJ34" s="10" t="n">
         <v>0.0001</v>
       </c>
-      <c r="AY34" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ34" s="8" t="n"/>
-      <c r="BA34" s="9" t="n"/>
-      <c r="BB34" s="10" t="n"/>
-      <c r="BC34" s="11" t="n"/>
-      <c r="BD34" s="8" t="n"/>
-      <c r="BE34" s="9" t="n"/>
-      <c r="BF34" s="10" t="n"/>
-      <c r="BG34" s="11" t="n"/>
-      <c r="BH34" s="8" t="n"/>
-      <c r="BI34" s="9" t="n"/>
-      <c r="BJ34" s="10" t="n"/>
-      <c r="BK34" s="11" t="n"/>
-      <c r="BL34" s="8" t="n"/>
-      <c r="BM34" s="9" t="n"/>
-      <c r="BN34" s="10" t="n"/>
+      <c r="BK34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL34" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="BM34" s="9" t="n">
+        <v>1612.64</v>
+      </c>
+      <c r="BN34" s="10" t="n">
+        <v>0.0002</v>
+      </c>
       <c r="BO34" s="11" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Swaraj Engines Limited</t>
+          <t>Nesco Limited</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>INE277A01016</t>
+          <t>INE317F01035</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Industrial Products</t>
+          <t>Commercial Services &amp; Supplies</t>
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>1871.38</v>
+        <v>1862.26</v>
       </c>
       <c r="F35" s="10" t="n">
         <v>0.0001</v>
@@ -6701,10 +6731,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>1564.88</v>
+        <v>1538.11</v>
       </c>
       <c r="J35" s="10" t="n">
         <v>0.0001</v>
@@ -6713,10 +6743,10 @@
         <v>0</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>1700.33</v>
+        <v>1704.36</v>
       </c>
       <c r="N35" s="10" t="n">
         <v>0.0001</v>
@@ -6725,10 +6755,10 @@
         <v>0</v>
       </c>
       <c r="P35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>1637.61</v>
+        <v>1728.63</v>
       </c>
       <c r="R35" s="10" t="n">
         <v>0.0001</v>
@@ -6737,10 +6767,10 @@
         <v>0</v>
       </c>
       <c r="T35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="U35" s="9" t="n">
-        <v>1691.91</v>
+        <v>1858.32</v>
       </c>
       <c r="V35" s="10" t="n">
         <v>0.0001</v>
@@ -6749,22 +6779,22 @@
         <v>0</v>
       </c>
       <c r="X35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="Y35" s="9" t="n">
-        <v>1764.08</v>
+        <v>1947.66</v>
       </c>
       <c r="Z35" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="AA35" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AB35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AC35" s="9" t="n">
-        <v>1892.15</v>
+        <v>2076.6</v>
       </c>
       <c r="AD35" s="10" t="n">
         <v>0.0002</v>
@@ -6773,10 +6803,10 @@
         <v>0</v>
       </c>
       <c r="AF35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AG35" s="9" t="n">
-        <v>1955.38</v>
+        <v>1987.1</v>
       </c>
       <c r="AH35" s="10" t="n">
         <v>0.0002</v>
@@ -6785,10 +6815,10 @@
         <v>0</v>
       </c>
       <c r="AJ35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AK35" s="9" t="n">
-        <v>1897.21</v>
+        <v>2130.6</v>
       </c>
       <c r="AL35" s="10" t="n">
         <v>0.0002</v>
@@ -6797,10 +6827,10 @@
         <v>0</v>
       </c>
       <c r="AN35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AO35" s="9" t="n">
-        <v>1983.66</v>
+        <v>2091.16</v>
       </c>
       <c r="AP35" s="10" t="n">
         <v>0.0002</v>
@@ -6809,382 +6839,438 @@
         <v>0</v>
       </c>
       <c r="AR35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AS35" s="9" t="n">
-        <v>1867.41</v>
+        <v>1766.62</v>
       </c>
       <c r="AT35" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="AU35" s="11" t="n">
-        <v>0</v>
+        <v>0.6954140540298874</v>
       </c>
       <c r="AV35" s="8" t="n">
-        <v>47293</v>
+        <v>89469</v>
       </c>
       <c r="AW35" s="9" t="n">
-        <v>1857.76</v>
+        <v>828.48</v>
       </c>
       <c r="AX35" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="AY35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ35" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="BA35" s="9" t="n">
-        <v>1925.39</v>
-      </c>
-      <c r="BB35" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="BC35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD35" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="BE35" s="9" t="n">
-        <v>1844.17</v>
-      </c>
-      <c r="BF35" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="BG35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH35" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="BI35" s="9" t="n">
-        <v>1236.83</v>
-      </c>
-      <c r="BJ35" s="10" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="BK35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL35" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="BM35" s="9" t="n">
-        <v>1612.64</v>
-      </c>
-      <c r="BN35" s="10" t="n">
-        <v>0.0002</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AZ35" s="8" t="n"/>
+      <c r="BA35" s="9" t="n"/>
+      <c r="BB35" s="10" t="n"/>
+      <c r="BC35" s="11" t="n"/>
+      <c r="BD35" s="8" t="n"/>
+      <c r="BE35" s="9" t="n"/>
+      <c r="BF35" s="10" t="n"/>
+      <c r="BG35" s="11" t="n"/>
+      <c r="BH35" s="8" t="n"/>
+      <c r="BI35" s="9" t="n"/>
+      <c r="BJ35" s="10" t="n"/>
+      <c r="BK35" s="11" t="n"/>
+      <c r="BL35" s="8" t="n"/>
+      <c r="BM35" s="9" t="n"/>
+      <c r="BN35" s="10" t="n"/>
       <c r="BO35" s="11" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Balkrishna Industries Limited</t>
+          <t>Kotak Mahindra Bank Limited</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>INE787D01026</t>
+          <t>INE237A01028</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Auto Components</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="D36" s="8" t="n"/>
       <c r="E36" s="9" t="n"/>
       <c r="F36" s="10" t="n"/>
-      <c r="G36" s="11" t="n">
+      <c r="G36" s="11" t="n"/>
+      <c r="H36" s="8" t="n"/>
+      <c r="I36" s="9" t="n"/>
+      <c r="J36" s="10" t="n"/>
+      <c r="K36" s="11" t="n"/>
+      <c r="L36" s="8" t="n"/>
+      <c r="M36" s="9" t="n"/>
+      <c r="N36" s="10" t="n"/>
+      <c r="O36" s="11" t="n"/>
+      <c r="P36" s="8" t="n"/>
+      <c r="Q36" s="9" t="n"/>
+      <c r="R36" s="10" t="n"/>
+      <c r="S36" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="H36" s="8" t="n">
-        <v>2274074</v>
-      </c>
-      <c r="I36" s="9" t="n">
-        <v>47368.96</v>
-      </c>
-      <c r="J36" s="10" t="n">
-        <v>0.0037</v>
-      </c>
-      <c r="K36" s="11" t="n">
-        <v>-0.2174731122669314</v>
-      </c>
-      <c r="L36" s="8" t="n">
-        <v>2906065</v>
-      </c>
-      <c r="M36" s="9" t="n">
-        <v>69277.67999999999</v>
-      </c>
-      <c r="N36" s="10" t="n">
-        <v>0.0052</v>
-      </c>
-      <c r="O36" s="11" t="n">
-        <v>-0.3062750860930125</v>
-      </c>
-      <c r="P36" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="Q36" s="9" t="n">
-        <v>96591.67</v>
-      </c>
-      <c r="R36" s="10" t="n">
-        <v>0.0072</v>
-      </c>
-      <c r="S36" s="11" t="n">
-        <v>0</v>
-      </c>
       <c r="T36" s="8" t="n">
-        <v>4189074</v>
+        <v>24621592</v>
       </c>
       <c r="U36" s="9" t="n">
-        <v>97173.95</v>
+        <v>541945.86</v>
       </c>
       <c r="V36" s="10" t="n">
-        <v>0.0073</v>
+        <v>0.0407</v>
       </c>
       <c r="W36" s="11" t="n">
-        <v>0</v>
+        <v>0.01296144774839237</v>
       </c>
       <c r="X36" s="8" t="n">
-        <v>4189074</v>
+        <v>24306544</v>
       </c>
       <c r="Y36" s="9" t="n">
-        <v>96721.53</v>
+        <v>516368.22</v>
       </c>
       <c r="Z36" s="10" t="n">
-        <v>0.0075</v>
+        <v>0.0398</v>
       </c>
       <c r="AA36" s="11" t="n">
-        <v>0</v>
+        <v>0.004192884502844551</v>
       </c>
       <c r="AB36" s="8" t="n">
-        <v>4189074</v>
+        <v>24205055</v>
       </c>
       <c r="AC36" s="9" t="n">
-        <v>95502.50999999999</v>
+        <v>508838.67</v>
       </c>
       <c r="AD36" s="10" t="n">
-        <v>0.0076</v>
+        <v>0.0404</v>
       </c>
       <c r="AE36" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AF36" s="8" t="n">
-        <v>4189074</v>
+        <v>24205055</v>
       </c>
       <c r="AG36" s="9" t="n">
-        <v>96130.87</v>
+        <v>482334.13</v>
       </c>
       <c r="AH36" s="10" t="n">
-        <v>0.008</v>
+        <v>0.0403</v>
       </c>
       <c r="AI36" s="11" t="n">
-        <v>0</v>
+        <v>0.03407788338216907</v>
       </c>
       <c r="AJ36" s="8" t="n">
-        <v>4189074</v>
+        <v>23407381</v>
       </c>
       <c r="AK36" s="9" t="n">
-        <v>95904.66</v>
+        <v>458854.89</v>
       </c>
       <c r="AL36" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.0399</v>
       </c>
       <c r="AM36" s="11" t="n">
-        <v>0</v>
+        <v>0.06425892329321918</v>
       </c>
       <c r="AN36" s="8" t="n">
-        <v>4189074</v>
+        <v>21994066</v>
       </c>
       <c r="AO36" s="9" t="n">
-        <v>112108</v>
+        <v>435174.59</v>
       </c>
       <c r="AP36" s="10" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0384</v>
       </c>
       <c r="AQ36" s="11" t="n">
-        <v>0</v>
+        <v>0.07428402120388222</v>
       </c>
       <c r="AR36" s="8" t="n">
-        <v>4189074</v>
+        <v>20473232</v>
       </c>
       <c r="AS36" s="9" t="n">
-        <v>102435.43</v>
+        <v>442938.37</v>
       </c>
       <c r="AT36" s="10" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0401</v>
       </c>
       <c r="AU36" s="11" t="n">
-        <v>0</v>
+        <v>0.03644973136547983</v>
       </c>
       <c r="AV36" s="8" t="n">
-        <v>4189074</v>
+        <v>19753232</v>
       </c>
       <c r="AW36" s="9" t="n">
-        <v>103562.29</v>
+        <v>409820.3</v>
       </c>
       <c r="AX36" s="10" t="n">
-        <v>0.01</v>
+        <v>0.0395</v>
       </c>
       <c r="AY36" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AZ36" s="8" t="n">
-        <v>4189074</v>
+        <v>19753232</v>
       </c>
       <c r="BA36" s="9" t="n">
-        <v>112061.92</v>
+        <v>436171.12</v>
       </c>
       <c r="BB36" s="10" t="n">
-        <v>0.0114</v>
+        <v>0.0443</v>
       </c>
       <c r="BC36" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BD36" s="8" t="n">
-        <v>4189074</v>
+        <v>19753232</v>
       </c>
       <c r="BE36" s="9" t="n">
-        <v>107022.46</v>
+        <v>428882.17</v>
       </c>
       <c r="BF36" s="10" t="n">
-        <v>0.0115</v>
+        <v>0.0459</v>
       </c>
       <c r="BG36" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BH36" s="8" t="n">
-        <v>4189074</v>
+        <v>19753232</v>
       </c>
       <c r="BI36" s="9" t="n">
-        <v>109571.51</v>
+        <v>375894.13</v>
       </c>
       <c r="BJ36" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.0427</v>
       </c>
       <c r="BK36" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BL36" s="8" t="n">
-        <v>4189074</v>
+        <v>19753232</v>
       </c>
       <c r="BM36" s="9" t="n">
-        <v>116089.71</v>
+        <v>375568.2</v>
       </c>
       <c r="BN36" s="10" t="n">
-        <v>0.0129</v>
+        <v>0.0419</v>
       </c>
       <c r="BO36" s="11" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Multi Commodity Exchange of India Limited</t>
+          <t>Balkrishna Industries Limited</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>INE745G01043</t>
+          <t>INE787D01026</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Auto Components</t>
         </is>
       </c>
       <c r="D37" s="8" t="n"/>
       <c r="E37" s="9" t="n"/>
       <c r="F37" s="10" t="n"/>
-      <c r="G37" s="11" t="n"/>
-      <c r="H37" s="8" t="n"/>
-      <c r="I37" s="9" t="n"/>
-      <c r="J37" s="10" t="n"/>
-      <c r="K37" s="11" t="n"/>
-      <c r="L37" s="8" t="n"/>
-      <c r="M37" s="9" t="n"/>
-      <c r="N37" s="10" t="n"/>
+      <c r="G37" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>2274074</v>
+      </c>
+      <c r="I37" s="9" t="n">
+        <v>47368.96</v>
+      </c>
+      <c r="J37" s="10" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="K37" s="11" t="n">
+        <v>-0.2174731122669314</v>
+      </c>
+      <c r="L37" s="8" t="n">
+        <v>2906065</v>
+      </c>
+      <c r="M37" s="9" t="n">
+        <v>69277.67999999999</v>
+      </c>
+      <c r="N37" s="10" t="n">
+        <v>0.0052</v>
+      </c>
       <c r="O37" s="11" t="n">
-        <v>-1</v>
+        <v>-0.3062750860930125</v>
       </c>
       <c r="P37" s="8" t="n">
-        <v>795472</v>
+        <v>4189074</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>20109.53</v>
+        <v>96591.67</v>
       </c>
       <c r="R37" s="10" t="n">
-        <v>0.0015</v>
+        <v>0.0072</v>
       </c>
       <c r="S37" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T37" s="8" t="n"/>
-      <c r="U37" s="9" t="n"/>
-      <c r="V37" s="10" t="n"/>
-      <c r="W37" s="11" t="n"/>
-      <c r="X37" s="8" t="n"/>
-      <c r="Y37" s="9" t="n"/>
-      <c r="Z37" s="10" t="n"/>
-      <c r="AA37" s="11" t="n"/>
-      <c r="AB37" s="8" t="n"/>
-      <c r="AC37" s="9" t="n"/>
-      <c r="AD37" s="10" t="n"/>
-      <c r="AE37" s="11" t="n"/>
-      <c r="AF37" s="8" t="n"/>
-      <c r="AG37" s="9" t="n"/>
-      <c r="AH37" s="10" t="n"/>
-      <c r="AI37" s="11" t="n"/>
-      <c r="AJ37" s="8" t="n"/>
-      <c r="AK37" s="9" t="n"/>
-      <c r="AL37" s="10" t="n"/>
-      <c r="AM37" s="11" t="n"/>
-      <c r="AN37" s="8" t="n"/>
-      <c r="AO37" s="9" t="n"/>
-      <c r="AP37" s="10" t="n"/>
-      <c r="AQ37" s="11" t="n"/>
-      <c r="AR37" s="8" t="n"/>
-      <c r="AS37" s="9" t="n"/>
-      <c r="AT37" s="10" t="n"/>
-      <c r="AU37" s="11" t="n"/>
-      <c r="AV37" s="8" t="n"/>
-      <c r="AW37" s="9" t="n"/>
-      <c r="AX37" s="10" t="n"/>
-      <c r="AY37" s="11" t="n"/>
-      <c r="AZ37" s="8" t="n"/>
-      <c r="BA37" s="9" t="n"/>
-      <c r="BB37" s="10" t="n"/>
-      <c r="BC37" s="11" t="n"/>
-      <c r="BD37" s="8" t="n"/>
-      <c r="BE37" s="9" t="n"/>
-      <c r="BF37" s="10" t="n"/>
-      <c r="BG37" s="11" t="n"/>
-      <c r="BH37" s="8" t="n"/>
-      <c r="BI37" s="9" t="n"/>
-      <c r="BJ37" s="10" t="n"/>
-      <c r="BK37" s="11" t="n"/>
-      <c r="BL37" s="8" t="n"/>
-      <c r="BM37" s="9" t="n"/>
-      <c r="BN37" s="10" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="U37" s="9" t="n">
+        <v>97173.95</v>
+      </c>
+      <c r="V37" s="10" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="W37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="Y37" s="9" t="n">
+        <v>96721.53</v>
+      </c>
+      <c r="Z37" s="10" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="AA37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="AC37" s="9" t="n">
+        <v>95502.50999999999</v>
+      </c>
+      <c r="AD37" s="10" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="AE37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="AG37" s="9" t="n">
+        <v>96130.87</v>
+      </c>
+      <c r="AH37" s="10" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="AI37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="AK37" s="9" t="n">
+        <v>95904.66</v>
+      </c>
+      <c r="AL37" s="10" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="AM37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="AO37" s="9" t="n">
+        <v>112108</v>
+      </c>
+      <c r="AP37" s="10" t="n">
+        <v>0.009900000000000001</v>
+      </c>
+      <c r="AQ37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="AS37" s="9" t="n">
+        <v>102435.43</v>
+      </c>
+      <c r="AT37" s="10" t="n">
+        <v>0.009299999999999999</v>
+      </c>
+      <c r="AU37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="AW37" s="9" t="n">
+        <v>103562.29</v>
+      </c>
+      <c r="AX37" s="10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AY37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ37" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="BA37" s="9" t="n">
+        <v>112061.92</v>
+      </c>
+      <c r="BB37" s="10" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="BC37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD37" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="BE37" s="9" t="n">
+        <v>107022.46</v>
+      </c>
+      <c r="BF37" s="10" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="BG37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH37" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="BI37" s="9" t="n">
+        <v>109571.51</v>
+      </c>
+      <c r="BJ37" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="BK37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL37" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="BM37" s="9" t="n">
+        <v>116089.71</v>
+      </c>
+      <c r="BN37" s="10" t="n">
+        <v>0.0129</v>
+      </c>
       <c r="BO37" s="11" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Kotak Mahindra Bank Limited</t>
+          <t>Motilal Oswal Financial Services Limited</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>INE237A01028</t>
+          <t>INE338I01027</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D38" s="8" t="n"/>
@@ -7202,166 +7288,118 @@
       <c r="P38" s="8" t="n"/>
       <c r="Q38" s="9" t="n"/>
       <c r="R38" s="10" t="n"/>
-      <c r="S38" s="11" t="n">
+      <c r="S38" s="11" t="n"/>
+      <c r="T38" s="8" t="n"/>
+      <c r="U38" s="9" t="n"/>
+      <c r="V38" s="10" t="n"/>
+      <c r="W38" s="11" t="n"/>
+      <c r="X38" s="8" t="n"/>
+      <c r="Y38" s="9" t="n"/>
+      <c r="Z38" s="10" t="n"/>
+      <c r="AA38" s="11" t="n"/>
+      <c r="AB38" s="8" t="n"/>
+      <c r="AC38" s="9" t="n"/>
+      <c r="AD38" s="10" t="n"/>
+      <c r="AE38" s="11" t="n"/>
+      <c r="AF38" s="8" t="n"/>
+      <c r="AG38" s="9" t="n"/>
+      <c r="AH38" s="10" t="n"/>
+      <c r="AI38" s="11" t="n"/>
+      <c r="AJ38" s="8" t="n"/>
+      <c r="AK38" s="9" t="n"/>
+      <c r="AL38" s="10" t="n"/>
+      <c r="AM38" s="11" t="n"/>
+      <c r="AN38" s="8" t="n"/>
+      <c r="AO38" s="9" t="n"/>
+      <c r="AP38" s="10" t="n"/>
+      <c r="AQ38" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="T38" s="8" t="n">
-        <v>24621592</v>
-      </c>
-      <c r="U38" s="9" t="n">
-        <v>541945.86</v>
-      </c>
-      <c r="V38" s="10" t="n">
-        <v>0.0407</v>
-      </c>
-      <c r="W38" s="11" t="n">
-        <v>0.01296144774839237</v>
-      </c>
-      <c r="X38" s="8" t="n">
-        <v>24306544</v>
-      </c>
-      <c r="Y38" s="9" t="n">
-        <v>516368.22</v>
-      </c>
-      <c r="Z38" s="10" t="n">
-        <v>0.0398</v>
-      </c>
-      <c r="AA38" s="11" t="n">
-        <v>0.004192884502844551</v>
-      </c>
-      <c r="AB38" s="8" t="n">
-        <v>24205055</v>
-      </c>
-      <c r="AC38" s="9" t="n">
-        <v>508838.67</v>
-      </c>
-      <c r="AD38" s="10" t="n">
-        <v>0.0404</v>
-      </c>
-      <c r="AE38" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" s="8" t="n">
-        <v>24205055</v>
-      </c>
-      <c r="AG38" s="9" t="n">
-        <v>482334.13</v>
-      </c>
-      <c r="AH38" s="10" t="n">
-        <v>0.0403</v>
-      </c>
-      <c r="AI38" s="11" t="n">
-        <v>0.03407788338216907</v>
-      </c>
-      <c r="AJ38" s="8" t="n">
-        <v>23407381</v>
-      </c>
-      <c r="AK38" s="9" t="n">
-        <v>458854.89</v>
-      </c>
-      <c r="AL38" s="10" t="n">
-        <v>0.0399</v>
-      </c>
-      <c r="AM38" s="11" t="n">
-        <v>0.06425892329321918</v>
-      </c>
-      <c r="AN38" s="8" t="n">
-        <v>21994066</v>
-      </c>
-      <c r="AO38" s="9" t="n">
-        <v>435174.59</v>
-      </c>
-      <c r="AP38" s="10" t="n">
-        <v>0.0384</v>
-      </c>
-      <c r="AQ38" s="11" t="n">
-        <v>0.07428402120388222</v>
-      </c>
       <c r="AR38" s="8" t="n">
-        <v>20473232</v>
+        <v>591805</v>
       </c>
       <c r="AS38" s="9" t="n">
-        <v>442938.37</v>
+        <v>5149</v>
       </c>
       <c r="AT38" s="10" t="n">
-        <v>0.0401</v>
+        <v>0.0005</v>
       </c>
       <c r="AU38" s="11" t="n">
-        <v>0.03644973136547983</v>
+        <v>-0.8902567225534253</v>
       </c>
       <c r="AV38" s="8" t="n">
-        <v>19753232</v>
+        <v>5392631</v>
       </c>
       <c r="AW38" s="9" t="n">
-        <v>409820.3</v>
+        <v>43674.92</v>
       </c>
       <c r="AX38" s="10" t="n">
-        <v>0.0395</v>
+        <v>0.0042</v>
       </c>
       <c r="AY38" s="11" t="n">
-        <v>0</v>
+        <v>-0.3719237093069153</v>
       </c>
       <c r="AZ38" s="8" t="n">
-        <v>19753232</v>
+        <v>8585949</v>
       </c>
       <c r="BA38" s="9" t="n">
-        <v>436171.12</v>
+        <v>56044.78</v>
       </c>
       <c r="BB38" s="10" t="n">
-        <v>0.0443</v>
+        <v>0.0057</v>
       </c>
       <c r="BC38" s="11" t="n">
-        <v>0</v>
+        <v>-0.2132577936597328</v>
       </c>
       <c r="BD38" s="8" t="n">
-        <v>19753232</v>
+        <v>10913294</v>
       </c>
       <c r="BE38" s="9" t="n">
-        <v>428882.17</v>
+        <v>67154.95</v>
       </c>
       <c r="BF38" s="10" t="n">
-        <v>0.0459</v>
+        <v>0.0072</v>
       </c>
       <c r="BG38" s="11" t="n">
-        <v>0</v>
+        <v>-0.09462389658963724</v>
       </c>
       <c r="BH38" s="8" t="n">
-        <v>19753232</v>
+        <v>12053879</v>
       </c>
       <c r="BI38" s="9" t="n">
-        <v>375894.13</v>
+        <v>70937.08</v>
       </c>
       <c r="BJ38" s="10" t="n">
-        <v>0.0427</v>
+        <v>0.0081</v>
       </c>
       <c r="BK38" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BL38" s="8" t="n">
-        <v>19753232</v>
+        <v>12053879</v>
       </c>
       <c r="BM38" s="9" t="n">
-        <v>375568.2</v>
+        <v>76801.28999999999</v>
       </c>
       <c r="BN38" s="10" t="n">
-        <v>0.0419</v>
+        <v>0.0086</v>
       </c>
       <c r="BO38" s="11" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited</t>
+          <t>Multi Commodity Exchange of India Limited</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>INE768C01010</t>
+          <t>INE745G01035</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D39" s="8" t="n"/>
@@ -7379,96 +7417,166 @@
       <c r="P39" s="8" t="n"/>
       <c r="Q39" s="9" t="n"/>
       <c r="R39" s="10" t="n"/>
-      <c r="S39" s="11" t="n"/>
-      <c r="T39" s="8" t="n"/>
-      <c r="U39" s="9" t="n"/>
-      <c r="V39" s="10" t="n"/>
-      <c r="W39" s="11" t="n"/>
-      <c r="X39" s="8" t="n"/>
-      <c r="Y39" s="9" t="n"/>
-      <c r="Z39" s="10" t="n"/>
-      <c r="AA39" s="11" t="n"/>
-      <c r="AB39" s="8" t="n"/>
-      <c r="AC39" s="9" t="n"/>
-      <c r="AD39" s="10" t="n"/>
-      <c r="AE39" s="11" t="n"/>
-      <c r="AF39" s="8" t="n"/>
-      <c r="AG39" s="9" t="n"/>
-      <c r="AH39" s="10" t="n"/>
+      <c r="S39" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="U39" s="9" t="n">
+        <v>88833.99000000001</v>
+      </c>
+      <c r="V39" s="10" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="W39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="Y39" s="9" t="n">
+        <v>80358.22</v>
+      </c>
+      <c r="Z39" s="10" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="AA39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AC39" s="9" t="n">
+        <v>73737.16</v>
+      </c>
+      <c r="AD39" s="10" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="AE39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AG39" s="9" t="n">
+        <v>62190.17</v>
+      </c>
+      <c r="AH39" s="10" t="n">
+        <v>0.0052</v>
+      </c>
       <c r="AI39" s="11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AJ39" s="8" t="n">
-        <v>4400000</v>
+        <v>797719</v>
       </c>
       <c r="AK39" s="9" t="n">
-        <v>88822.8</v>
+        <v>58951.43</v>
       </c>
       <c r="AL39" s="10" t="n">
-        <v>0.0077</v>
+        <v>0.0051</v>
       </c>
       <c r="AM39" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AN39" s="8" t="n">
-        <v>4400000</v>
+        <v>797719</v>
       </c>
       <c r="AO39" s="9" t="n">
-        <v>89280.39999999999</v>
+        <v>61368.52</v>
       </c>
       <c r="AP39" s="10" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0054</v>
       </c>
       <c r="AQ39" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AR39" s="8" t="n">
-        <v>4400000</v>
+        <v>797719</v>
       </c>
       <c r="AS39" s="9" t="n">
-        <v>89020.8</v>
+        <v>71347.99000000001</v>
       </c>
       <c r="AT39" s="10" t="n">
-        <v>0.0081</v>
+        <v>0.0065</v>
       </c>
       <c r="AU39" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV39" s="8" t="n"/>
-      <c r="AW39" s="9" t="n"/>
-      <c r="AX39" s="10" t="n"/>
-      <c r="AY39" s="11" t="n"/>
-      <c r="AZ39" s="8" t="n"/>
-      <c r="BA39" s="9" t="n"/>
-      <c r="BB39" s="10" t="n"/>
-      <c r="BC39" s="11" t="n"/>
-      <c r="BD39" s="8" t="n"/>
-      <c r="BE39" s="9" t="n"/>
-      <c r="BF39" s="10" t="n"/>
-      <c r="BG39" s="11" t="n"/>
-      <c r="BH39" s="8" t="n"/>
-      <c r="BI39" s="9" t="n"/>
-      <c r="BJ39" s="10" t="n"/>
-      <c r="BK39" s="11" t="n"/>
-      <c r="BL39" s="8" t="n"/>
-      <c r="BM39" s="9" t="n"/>
-      <c r="BN39" s="10" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AV39" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AW39" s="9" t="n">
+        <v>52665.41</v>
+      </c>
+      <c r="AX39" s="10" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="AY39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ39" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="BA39" s="9" t="n">
+        <v>48884.22</v>
+      </c>
+      <c r="BB39" s="10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="BC39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD39" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="BE39" s="9" t="n">
+        <v>42372.84</v>
+      </c>
+      <c r="BF39" s="10" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="BG39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH39" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="BI39" s="9" t="n">
+        <v>39819.34</v>
+      </c>
+      <c r="BJ39" s="10" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="BK39" s="11" t="n">
+        <v>-0.09569612848812428</v>
+      </c>
+      <c r="BL39" s="8" t="n">
+        <v>882136</v>
+      </c>
+      <c r="BM39" s="9" t="n">
+        <v>50572.42</v>
+      </c>
+      <c r="BN39" s="10" t="n">
+        <v>0.0056</v>
+      </c>
       <c r="BO39" s="11" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Multi Commodity Exchange of India Limited</t>
+          <t>IPCA Laboratories Limited</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>INE745G01035</t>
+          <t>INE571A01038</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Pharmaceuticals &amp; Biotechnology</t>
         </is>
       </c>
       <c r="D40" s="8" t="n"/>
@@ -7486,166 +7594,134 @@
       <c r="P40" s="8" t="n"/>
       <c r="Q40" s="9" t="n"/>
       <c r="R40" s="10" t="n"/>
-      <c r="S40" s="11" t="n">
+      <c r="S40" s="11" t="n"/>
+      <c r="T40" s="8" t="n"/>
+      <c r="U40" s="9" t="n"/>
+      <c r="V40" s="10" t="n"/>
+      <c r="W40" s="11" t="n"/>
+      <c r="X40" s="8" t="n"/>
+      <c r="Y40" s="9" t="n"/>
+      <c r="Z40" s="10" t="n"/>
+      <c r="AA40" s="11" t="n"/>
+      <c r="AB40" s="8" t="n"/>
+      <c r="AC40" s="9" t="n"/>
+      <c r="AD40" s="10" t="n"/>
+      <c r="AE40" s="11" t="n"/>
+      <c r="AF40" s="8" t="n"/>
+      <c r="AG40" s="9" t="n"/>
+      <c r="AH40" s="10" t="n"/>
+      <c r="AI40" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="T40" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="U40" s="9" t="n">
-        <v>88833.99000000001</v>
-      </c>
-      <c r="V40" s="10" t="n">
-        <v>0.0067</v>
-      </c>
-      <c r="W40" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="Y40" s="9" t="n">
-        <v>80358.22</v>
-      </c>
-      <c r="Z40" s="10" t="n">
-        <v>0.0062</v>
-      </c>
-      <c r="AA40" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB40" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="AC40" s="9" t="n">
-        <v>73737.16</v>
-      </c>
-      <c r="AD40" s="10" t="n">
-        <v>0.0059</v>
-      </c>
-      <c r="AE40" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF40" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="AG40" s="9" t="n">
-        <v>62190.17</v>
-      </c>
-      <c r="AH40" s="10" t="n">
-        <v>0.0052</v>
-      </c>
-      <c r="AI40" s="11" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ40" s="8" t="n">
-        <v>797719</v>
+        <v>218075</v>
       </c>
       <c r="AK40" s="9" t="n">
-        <v>58951.43</v>
+        <v>3019.03</v>
       </c>
       <c r="AL40" s="10" t="n">
-        <v>0.0051</v>
+        <v>0.0003</v>
       </c>
       <c r="AM40" s="11" t="n">
-        <v>0</v>
+        <v>-0.6148554615199853</v>
       </c>
       <c r="AN40" s="8" t="n">
-        <v>797719</v>
+        <v>566216</v>
       </c>
       <c r="AO40" s="9" t="n">
-        <v>61368.52</v>
+        <v>8345.459999999999</v>
       </c>
       <c r="AP40" s="10" t="n">
-        <v>0.0054</v>
+        <v>0.0007</v>
       </c>
       <c r="AQ40" s="11" t="n">
-        <v>0</v>
+        <v>-0.5682871579351869</v>
       </c>
       <c r="AR40" s="8" t="n">
-        <v>797719</v>
+        <v>1311557</v>
       </c>
       <c r="AS40" s="9" t="n">
-        <v>71347.99000000001</v>
+        <v>18228.02</v>
       </c>
       <c r="AT40" s="10" t="n">
-        <v>0.0065</v>
+        <v>0.0017</v>
       </c>
       <c r="AU40" s="11" t="n">
-        <v>0</v>
+        <v>-0.2008037316547793</v>
       </c>
       <c r="AV40" s="8" t="n">
-        <v>797719</v>
+        <v>1641095</v>
       </c>
       <c r="AW40" s="9" t="n">
-        <v>52665.41</v>
+        <v>23382.32</v>
       </c>
       <c r="AX40" s="10" t="n">
-        <v>0.0051</v>
+        <v>0.0023</v>
       </c>
       <c r="AY40" s="11" t="n">
-        <v>0</v>
+        <v>-0.1163687388172734</v>
       </c>
       <c r="AZ40" s="8" t="n">
-        <v>797719</v>
+        <v>1857217</v>
       </c>
       <c r="BA40" s="9" t="n">
-        <v>48884.22</v>
+        <v>26023.32</v>
       </c>
       <c r="BB40" s="10" t="n">
-        <v>0.005</v>
+        <v>0.0026</v>
       </c>
       <c r="BC40" s="11" t="n">
-        <v>0</v>
+        <v>-0.03620728307597141</v>
       </c>
       <c r="BD40" s="8" t="n">
-        <v>797719</v>
+        <v>1926988</v>
       </c>
       <c r="BE40" s="9" t="n">
-        <v>42372.84</v>
+        <v>28941.43</v>
       </c>
       <c r="BF40" s="10" t="n">
-        <v>0.0045</v>
+        <v>0.0031</v>
       </c>
       <c r="BG40" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BH40" s="8" t="n">
-        <v>797719</v>
+        <v>1926988</v>
       </c>
       <c r="BI40" s="9" t="n">
-        <v>39819.34</v>
+        <v>26117.43</v>
       </c>
       <c r="BJ40" s="10" t="n">
-        <v>0.0045</v>
+        <v>0.003</v>
       </c>
       <c r="BK40" s="11" t="n">
-        <v>-0.09569612848812428</v>
+        <v>-0.1421734974921662</v>
       </c>
       <c r="BL40" s="8" t="n">
-        <v>882136</v>
+        <v>2246361</v>
       </c>
       <c r="BM40" s="9" t="n">
-        <v>50572.42</v>
+        <v>32421.73</v>
       </c>
       <c r="BN40" s="10" t="n">
-        <v>0.0056</v>
+        <v>0.0036</v>
       </c>
       <c r="BO40" s="11" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>IPCA Laboratories Limited</t>
+          <t>ITC Hotels Limited</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>INE571A01038</t>
+          <t>INE379A01028</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Pharmaceuticals &amp; Biotechnology</t>
+          <t>Leisure Services</t>
         </is>
       </c>
       <c r="D41" s="8" t="n"/>
@@ -7679,118 +7755,78 @@
       <c r="AF41" s="8" t="n"/>
       <c r="AG41" s="9" t="n"/>
       <c r="AH41" s="10" t="n"/>
-      <c r="AI41" s="11" t="n">
+      <c r="AI41" s="11" t="n"/>
+      <c r="AJ41" s="8" t="n"/>
+      <c r="AK41" s="9" t="n"/>
+      <c r="AL41" s="10" t="n"/>
+      <c r="AM41" s="11" t="n"/>
+      <c r="AN41" s="8" t="n"/>
+      <c r="AO41" s="9" t="n"/>
+      <c r="AP41" s="10" t="n"/>
+      <c r="AQ41" s="11" t="n"/>
+      <c r="AR41" s="8" t="n"/>
+      <c r="AS41" s="9" t="n"/>
+      <c r="AT41" s="10" t="n"/>
+      <c r="AU41" s="11" t="n"/>
+      <c r="AV41" s="8" t="n"/>
+      <c r="AW41" s="9" t="n"/>
+      <c r="AX41" s="10" t="n"/>
+      <c r="AY41" s="11" t="n"/>
+      <c r="AZ41" s="8" t="n"/>
+      <c r="BA41" s="9" t="n"/>
+      <c r="BB41" s="10" t="n"/>
+      <c r="BC41" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="AJ41" s="8" t="n">
-        <v>218075</v>
-      </c>
-      <c r="AK41" s="9" t="n">
-        <v>3019.03</v>
-      </c>
-      <c r="AL41" s="10" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="AM41" s="11" t="n">
-        <v>-0.6148554615199853</v>
-      </c>
-      <c r="AN41" s="8" t="n">
-        <v>566216</v>
-      </c>
-      <c r="AO41" s="9" t="n">
-        <v>8345.459999999999</v>
-      </c>
-      <c r="AP41" s="10" t="n">
-        <v>0.0007</v>
-      </c>
-      <c r="AQ41" s="11" t="n">
-        <v>-0.5682871579351869</v>
-      </c>
-      <c r="AR41" s="8" t="n">
-        <v>1311557</v>
-      </c>
-      <c r="AS41" s="9" t="n">
-        <v>18228.02</v>
-      </c>
-      <c r="AT41" s="10" t="n">
-        <v>0.0017</v>
-      </c>
-      <c r="AU41" s="11" t="n">
-        <v>-0.2008037316547793</v>
-      </c>
-      <c r="AV41" s="8" t="n">
-        <v>1641095</v>
-      </c>
-      <c r="AW41" s="9" t="n">
-        <v>23382.32</v>
-      </c>
-      <c r="AX41" s="10" t="n">
-        <v>0.0023</v>
-      </c>
-      <c r="AY41" s="11" t="n">
-        <v>-0.1163687388172734</v>
-      </c>
-      <c r="AZ41" s="8" t="n">
-        <v>1857217</v>
-      </c>
-      <c r="BA41" s="9" t="n">
-        <v>26023.32</v>
-      </c>
-      <c r="BB41" s="10" t="n">
-        <v>0.0026</v>
-      </c>
-      <c r="BC41" s="11" t="n">
-        <v>-0.03620728307597141</v>
-      </c>
       <c r="BD41" s="8" t="n">
-        <v>1926988</v>
+        <v>9899412</v>
       </c>
       <c r="BE41" s="9" t="n">
-        <v>28941.43</v>
+        <v>19552.33</v>
       </c>
       <c r="BF41" s="10" t="n">
-        <v>0.0031</v>
+        <v>0.0021</v>
       </c>
       <c r="BG41" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BH41" s="8" t="n">
-        <v>1926988</v>
+        <v>9899412</v>
       </c>
       <c r="BI41" s="9" t="n">
-        <v>26117.43</v>
+        <v>16216.23</v>
       </c>
       <c r="BJ41" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0018</v>
       </c>
       <c r="BK41" s="11" t="n">
-        <v>-0.1421734974921662</v>
+        <v>0</v>
       </c>
       <c r="BL41" s="8" t="n">
-        <v>2246361</v>
+        <v>9899412</v>
       </c>
       <c r="BM41" s="9" t="n">
-        <v>32421.73</v>
+        <v>16131.09</v>
       </c>
       <c r="BN41" s="10" t="n">
-        <v>0.0036</v>
+        <v>0.0018</v>
       </c>
       <c r="BO41" s="11" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Motilal Oswal Financial Services Limited</t>
+          <t>Zydus Wellness Limited</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>INE338I01027</t>
+          <t>INE768C01010</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D42" s="8" t="n"/>
@@ -7824,102 +7860,80 @@
       <c r="AF42" s="8" t="n"/>
       <c r="AG42" s="9" t="n"/>
       <c r="AH42" s="10" t="n"/>
-      <c r="AI42" s="11" t="n"/>
-      <c r="AJ42" s="8" t="n"/>
-      <c r="AK42" s="9" t="n"/>
-      <c r="AL42" s="10" t="n"/>
-      <c r="AM42" s="11" t="n"/>
-      <c r="AN42" s="8" t="n"/>
-      <c r="AO42" s="9" t="n"/>
-      <c r="AP42" s="10" t="n"/>
+      <c r="AI42" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AJ42" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AK42" s="9" t="n">
+        <v>88822.8</v>
+      </c>
+      <c r="AL42" s="10" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="AM42" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AO42" s="9" t="n">
+        <v>89280.39999999999</v>
+      </c>
+      <c r="AP42" s="10" t="n">
+        <v>0.007900000000000001</v>
+      </c>
       <c r="AQ42" s="11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AR42" s="8" t="n">
-        <v>591805</v>
+        <v>4400000</v>
       </c>
       <c r="AS42" s="9" t="n">
-        <v>5149</v>
+        <v>89020.8</v>
       </c>
       <c r="AT42" s="10" t="n">
-        <v>0.0005</v>
+        <v>0.0081</v>
       </c>
       <c r="AU42" s="11" t="n">
-        <v>-0.8902567225534253</v>
-      </c>
-      <c r="AV42" s="8" t="n">
-        <v>5392631</v>
-      </c>
-      <c r="AW42" s="9" t="n">
-        <v>43674.92</v>
-      </c>
-      <c r="AX42" s="10" t="n">
-        <v>0.0042</v>
-      </c>
-      <c r="AY42" s="11" t="n">
-        <v>-0.3719237093069153</v>
-      </c>
-      <c r="AZ42" s="8" t="n">
-        <v>8585949</v>
-      </c>
-      <c r="BA42" s="9" t="n">
-        <v>56044.78</v>
-      </c>
-      <c r="BB42" s="10" t="n">
-        <v>0.0057</v>
-      </c>
-      <c r="BC42" s="11" t="n">
-        <v>-0.2132577936597328</v>
-      </c>
-      <c r="BD42" s="8" t="n">
-        <v>10913294</v>
-      </c>
-      <c r="BE42" s="9" t="n">
-        <v>67154.95</v>
-      </c>
-      <c r="BF42" s="10" t="n">
-        <v>0.0072</v>
-      </c>
-      <c r="BG42" s="11" t="n">
-        <v>-0.09462389658963724</v>
-      </c>
-      <c r="BH42" s="8" t="n">
-        <v>12053879</v>
-      </c>
-      <c r="BI42" s="9" t="n">
-        <v>70937.08</v>
-      </c>
-      <c r="BJ42" s="10" t="n">
-        <v>0.0081</v>
-      </c>
-      <c r="BK42" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL42" s="8" t="n">
-        <v>12053879</v>
-      </c>
-      <c r="BM42" s="9" t="n">
-        <v>76801.28999999999</v>
-      </c>
-      <c r="BN42" s="10" t="n">
-        <v>0.0086</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AV42" s="8" t="n"/>
+      <c r="AW42" s="9" t="n"/>
+      <c r="AX42" s="10" t="n"/>
+      <c r="AY42" s="11" t="n"/>
+      <c r="AZ42" s="8" t="n"/>
+      <c r="BA42" s="9" t="n"/>
+      <c r="BB42" s="10" t="n"/>
+      <c r="BC42" s="11" t="n"/>
+      <c r="BD42" s="8" t="n"/>
+      <c r="BE42" s="9" t="n"/>
+      <c r="BF42" s="10" t="n"/>
+      <c r="BG42" s="11" t="n"/>
+      <c r="BH42" s="8" t="n"/>
+      <c r="BI42" s="9" t="n"/>
+      <c r="BJ42" s="10" t="n"/>
+      <c r="BK42" s="11" t="n"/>
+      <c r="BL42" s="8" t="n"/>
+      <c r="BM42" s="9" t="n"/>
+      <c r="BN42" s="10" t="n"/>
       <c r="BO42" s="11" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>ITC Hotels Limited</t>
+          <t>Multi Commodity Exchange of India Limited</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>INE379A01028</t>
+          <t>INE745G01043</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Leisure Services</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D43" s="8" t="n"/>
@@ -7933,11 +7947,21 @@
       <c r="L43" s="8" t="n"/>
       <c r="M43" s="9" t="n"/>
       <c r="N43" s="10" t="n"/>
-      <c r="O43" s="11" t="n"/>
-      <c r="P43" s="8" t="n"/>
-      <c r="Q43" s="9" t="n"/>
-      <c r="R43" s="10" t="n"/>
-      <c r="S43" s="11" t="n"/>
+      <c r="O43" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P43" s="8" t="n">
+        <v>795472</v>
+      </c>
+      <c r="Q43" s="9" t="n">
+        <v>20109.53</v>
+      </c>
+      <c r="R43" s="10" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="S43" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="T43" s="8" t="n"/>
       <c r="U43" s="9" t="n"/>
       <c r="V43" s="10" t="n"/>
@@ -7973,42 +7997,18 @@
       <c r="AZ43" s="8" t="n"/>
       <c r="BA43" s="9" t="n"/>
       <c r="BB43" s="10" t="n"/>
-      <c r="BC43" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BD43" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BE43" s="9" t="n">
-        <v>19552.33</v>
-      </c>
-      <c r="BF43" s="10" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="BG43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH43" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BI43" s="9" t="n">
-        <v>16216.23</v>
-      </c>
-      <c r="BJ43" s="10" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="BK43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL43" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BM43" s="9" t="n">
-        <v>16131.09</v>
-      </c>
-      <c r="BN43" s="10" t="n">
-        <v>0.0018</v>
-      </c>
+      <c r="BC43" s="11" t="n"/>
+      <c r="BD43" s="8" t="n"/>
+      <c r="BE43" s="9" t="n"/>
+      <c r="BF43" s="10" t="n"/>
+      <c r="BG43" s="11" t="n"/>
+      <c r="BH43" s="8" t="n"/>
+      <c r="BI43" s="9" t="n"/>
+      <c r="BJ43" s="10" t="n"/>
+      <c r="BK43" s="11" t="n"/>
+      <c r="BL43" s="8" t="n"/>
+      <c r="BM43" s="9" t="n"/>
+      <c r="BN43" s="10" t="n"/>
       <c r="BO43" s="11" t="n"/>
     </row>
     <row r="44">
@@ -8063,7 +8063,7 @@
         <v>1079845116</v>
       </c>
       <c r="U44" s="15" t="n">
-        <v>8588270.84</v>
+        <v>8588270.839999998</v>
       </c>
       <c r="V44" s="16" t="n">
         <v>0.6443999999999998</v>
@@ -8076,7 +8076,7 @@
         <v>8271351.1939775</v>
       </c>
       <c r="Z44" s="16" t="n">
-        <v>0.6374000000000002</v>
+        <v>0.6374000000000001</v>
       </c>
       <c r="AA44" s="17" t="n"/>
       <c r="AB44" s="14" t="n">

--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -7351,17 +7351,17 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited</t>
+          <t>Motilal Oswal Financial Services Limited</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>INE768C01010</t>
+          <t>INE338I01027</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D39" s="8" t="n"/>
@@ -7395,64 +7395,86 @@
       <c r="AF39" s="8" t="n"/>
       <c r="AG39" s="9" t="n"/>
       <c r="AH39" s="10" t="n"/>
-      <c r="AI39" s="11" t="n">
+      <c r="AI39" s="11" t="n"/>
+      <c r="AJ39" s="8" t="n"/>
+      <c r="AK39" s="9" t="n"/>
+      <c r="AL39" s="10" t="n"/>
+      <c r="AM39" s="11" t="n"/>
+      <c r="AN39" s="8" t="n"/>
+      <c r="AO39" s="9" t="n"/>
+      <c r="AP39" s="10" t="n"/>
+      <c r="AQ39" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="AJ39" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="AK39" s="9" t="n">
-        <v>88822.8</v>
-      </c>
-      <c r="AL39" s="10" t="n">
-        <v>0.0077</v>
-      </c>
-      <c r="AM39" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN39" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="AO39" s="9" t="n">
-        <v>89280.39999999999</v>
-      </c>
-      <c r="AP39" s="10" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-      <c r="AQ39" s="11" t="n">
-        <v>0</v>
-      </c>
       <c r="AR39" s="8" t="n">
-        <v>4400000</v>
+        <v>591805</v>
       </c>
       <c r="AS39" s="9" t="n">
-        <v>89020.8</v>
+        <v>5149</v>
       </c>
       <c r="AT39" s="10" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="AU39" s="11" t="n">
+        <v>-0.8902567225534253</v>
+      </c>
+      <c r="AV39" s="8" t="n">
+        <v>5392631</v>
+      </c>
+      <c r="AW39" s="9" t="n">
+        <v>43674.92</v>
+      </c>
+      <c r="AX39" s="10" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="AY39" s="11" t="n">
+        <v>-0.3719237093069153</v>
+      </c>
+      <c r="AZ39" s="8" t="n">
+        <v>8585949</v>
+      </c>
+      <c r="BA39" s="9" t="n">
+        <v>56044.78</v>
+      </c>
+      <c r="BB39" s="10" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="BC39" s="11" t="n">
+        <v>-0.2132577936597328</v>
+      </c>
+      <c r="BD39" s="8" t="n">
+        <v>10913294</v>
+      </c>
+      <c r="BE39" s="9" t="n">
+        <v>67154.95</v>
+      </c>
+      <c r="BF39" s="10" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="BG39" s="11" t="n">
+        <v>-0.09462389658963724</v>
+      </c>
+      <c r="BH39" s="8" t="n">
+        <v>12053879</v>
+      </c>
+      <c r="BI39" s="9" t="n">
+        <v>70937.08</v>
+      </c>
+      <c r="BJ39" s="10" t="n">
         <v>0.0081</v>
       </c>
-      <c r="AU39" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV39" s="8" t="n"/>
-      <c r="AW39" s="9" t="n"/>
-      <c r="AX39" s="10" t="n"/>
-      <c r="AY39" s="11" t="n"/>
-      <c r="AZ39" s="8" t="n"/>
-      <c r="BA39" s="9" t="n"/>
-      <c r="BB39" s="10" t="n"/>
-      <c r="BC39" s="11" t="n"/>
-      <c r="BD39" s="8" t="n"/>
-      <c r="BE39" s="9" t="n"/>
-      <c r="BF39" s="10" t="n"/>
-      <c r="BG39" s="11" t="n"/>
-      <c r="BH39" s="8" t="n"/>
-      <c r="BI39" s="9" t="n"/>
-      <c r="BJ39" s="10" t="n"/>
-      <c r="BK39" s="11" t="n"/>
-      <c r="BL39" s="8" t="n"/>
-      <c r="BM39" s="9" t="n"/>
-      <c r="BN39" s="10" t="n"/>
+      <c r="BK39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL39" s="8" t="n">
+        <v>12053879</v>
+      </c>
+      <c r="BM39" s="9" t="n">
+        <v>76801.28999999999</v>
+      </c>
+      <c r="BN39" s="10" t="n">
+        <v>0.0086</v>
+      </c>
       <c r="BO39" s="11" t="n"/>
     </row>
     <row r="40">
@@ -7780,17 +7802,17 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Motilal Oswal Financial Services Limited</t>
+          <t>ITC Hotels Limited</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>INE338I01027</t>
+          <t>INE379A01028</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Leisure Services</t>
         </is>
       </c>
       <c r="D42" s="8" t="n"/>
@@ -7832,94 +7854,70 @@
       <c r="AN42" s="8" t="n"/>
       <c r="AO42" s="9" t="n"/>
       <c r="AP42" s="10" t="n"/>
-      <c r="AQ42" s="11" t="n">
+      <c r="AQ42" s="11" t="n"/>
+      <c r="AR42" s="8" t="n"/>
+      <c r="AS42" s="9" t="n"/>
+      <c r="AT42" s="10" t="n"/>
+      <c r="AU42" s="11" t="n"/>
+      <c r="AV42" s="8" t="n"/>
+      <c r="AW42" s="9" t="n"/>
+      <c r="AX42" s="10" t="n"/>
+      <c r="AY42" s="11" t="n"/>
+      <c r="AZ42" s="8" t="n"/>
+      <c r="BA42" s="9" t="n"/>
+      <c r="BB42" s="10" t="n"/>
+      <c r="BC42" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="AR42" s="8" t="n">
-        <v>591805</v>
-      </c>
-      <c r="AS42" s="9" t="n">
-        <v>5149</v>
-      </c>
-      <c r="AT42" s="10" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="AU42" s="11" t="n">
-        <v>-0.8902567225534253</v>
-      </c>
-      <c r="AV42" s="8" t="n">
-        <v>5392631</v>
-      </c>
-      <c r="AW42" s="9" t="n">
-        <v>43674.92</v>
-      </c>
-      <c r="AX42" s="10" t="n">
-        <v>0.0042</v>
-      </c>
-      <c r="AY42" s="11" t="n">
-        <v>-0.3719237093069153</v>
-      </c>
-      <c r="AZ42" s="8" t="n">
-        <v>8585949</v>
-      </c>
-      <c r="BA42" s="9" t="n">
-        <v>56044.78</v>
-      </c>
-      <c r="BB42" s="10" t="n">
-        <v>0.0057</v>
-      </c>
-      <c r="BC42" s="11" t="n">
-        <v>-0.2132577936597328</v>
-      </c>
       <c r="BD42" s="8" t="n">
-        <v>10913294</v>
+        <v>9899412</v>
       </c>
       <c r="BE42" s="9" t="n">
-        <v>67154.95</v>
+        <v>19552.33</v>
       </c>
       <c r="BF42" s="10" t="n">
-        <v>0.0072</v>
+        <v>0.0021</v>
       </c>
       <c r="BG42" s="11" t="n">
-        <v>-0.09462389658963724</v>
+        <v>0</v>
       </c>
       <c r="BH42" s="8" t="n">
-        <v>12053879</v>
+        <v>9899412</v>
       </c>
       <c r="BI42" s="9" t="n">
-        <v>70937.08</v>
+        <v>16216.23</v>
       </c>
       <c r="BJ42" s="10" t="n">
-        <v>0.0081</v>
+        <v>0.0018</v>
       </c>
       <c r="BK42" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BL42" s="8" t="n">
-        <v>12053879</v>
+        <v>9899412</v>
       </c>
       <c r="BM42" s="9" t="n">
-        <v>76801.28999999999</v>
+        <v>16131.09</v>
       </c>
       <c r="BN42" s="10" t="n">
-        <v>0.0086</v>
+        <v>0.0018</v>
       </c>
       <c r="BO42" s="11" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>ITC Hotels Limited</t>
+          <t>Zydus Wellness Limited</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>INE379A01028</t>
+          <t>INE768C01010</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Leisure Services</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D43" s="8" t="n"/>
@@ -7953,19 +7951,45 @@
       <c r="AF43" s="8" t="n"/>
       <c r="AG43" s="9" t="n"/>
       <c r="AH43" s="10" t="n"/>
-      <c r="AI43" s="11" t="n"/>
-      <c r="AJ43" s="8" t="n"/>
-      <c r="AK43" s="9" t="n"/>
-      <c r="AL43" s="10" t="n"/>
-      <c r="AM43" s="11" t="n"/>
-      <c r="AN43" s="8" t="n"/>
-      <c r="AO43" s="9" t="n"/>
-      <c r="AP43" s="10" t="n"/>
-      <c r="AQ43" s="11" t="n"/>
-      <c r="AR43" s="8" t="n"/>
-      <c r="AS43" s="9" t="n"/>
-      <c r="AT43" s="10" t="n"/>
-      <c r="AU43" s="11" t="n"/>
+      <c r="AI43" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AJ43" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AK43" s="9" t="n">
+        <v>88822.8</v>
+      </c>
+      <c r="AL43" s="10" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="AM43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN43" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AO43" s="9" t="n">
+        <v>89280.39999999999</v>
+      </c>
+      <c r="AP43" s="10" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="AQ43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR43" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AS43" s="9" t="n">
+        <v>89020.8</v>
+      </c>
+      <c r="AT43" s="10" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="AU43" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="AV43" s="8" t="n"/>
       <c r="AW43" s="9" t="n"/>
       <c r="AX43" s="10" t="n"/>
@@ -7973,42 +7997,18 @@
       <c r="AZ43" s="8" t="n"/>
       <c r="BA43" s="9" t="n"/>
       <c r="BB43" s="10" t="n"/>
-      <c r="BC43" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BD43" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BE43" s="9" t="n">
-        <v>19552.33</v>
-      </c>
-      <c r="BF43" s="10" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="BG43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH43" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BI43" s="9" t="n">
-        <v>16216.23</v>
-      </c>
-      <c r="BJ43" s="10" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="BK43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL43" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BM43" s="9" t="n">
-        <v>16131.09</v>
-      </c>
-      <c r="BN43" s="10" t="n">
-        <v>0.0018</v>
-      </c>
+      <c r="BC43" s="11" t="n"/>
+      <c r="BD43" s="8" t="n"/>
+      <c r="BE43" s="9" t="n"/>
+      <c r="BF43" s="10" t="n"/>
+      <c r="BG43" s="11" t="n"/>
+      <c r="BH43" s="8" t="n"/>
+      <c r="BI43" s="9" t="n"/>
+      <c r="BJ43" s="10" t="n"/>
+      <c r="BK43" s="11" t="n"/>
+      <c r="BL43" s="8" t="n"/>
+      <c r="BM43" s="9" t="n"/>
+      <c r="BN43" s="10" t="n"/>
       <c r="BO43" s="11" t="n"/>
     </row>
     <row r="44">

--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -7351,17 +7351,17 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Motilal Oswal Financial Services Limited</t>
+          <t>Zydus Wellness Limited</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>INE338I01027</t>
+          <t>INE768C01010</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D39" s="8" t="n"/>
@@ -7395,86 +7395,64 @@
       <c r="AF39" s="8" t="n"/>
       <c r="AG39" s="9" t="n"/>
       <c r="AH39" s="10" t="n"/>
-      <c r="AI39" s="11" t="n"/>
-      <c r="AJ39" s="8" t="n"/>
-      <c r="AK39" s="9" t="n"/>
-      <c r="AL39" s="10" t="n"/>
-      <c r="AM39" s="11" t="n"/>
-      <c r="AN39" s="8" t="n"/>
-      <c r="AO39" s="9" t="n"/>
-      <c r="AP39" s="10" t="n"/>
+      <c r="AI39" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AJ39" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AK39" s="9" t="n">
+        <v>88822.8</v>
+      </c>
+      <c r="AL39" s="10" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="AM39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AO39" s="9" t="n">
+        <v>89280.39999999999</v>
+      </c>
+      <c r="AP39" s="10" t="n">
+        <v>0.007900000000000001</v>
+      </c>
       <c r="AQ39" s="11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AR39" s="8" t="n">
-        <v>591805</v>
+        <v>4400000</v>
       </c>
       <c r="AS39" s="9" t="n">
-        <v>5149</v>
+        <v>89020.8</v>
       </c>
       <c r="AT39" s="10" t="n">
-        <v>0.0005</v>
+        <v>0.0081</v>
       </c>
       <c r="AU39" s="11" t="n">
-        <v>-0.8902567225534253</v>
-      </c>
-      <c r="AV39" s="8" t="n">
-        <v>5392631</v>
-      </c>
-      <c r="AW39" s="9" t="n">
-        <v>43674.92</v>
-      </c>
-      <c r="AX39" s="10" t="n">
-        <v>0.0042</v>
-      </c>
-      <c r="AY39" s="11" t="n">
-        <v>-0.3719237093069153</v>
-      </c>
-      <c r="AZ39" s="8" t="n">
-        <v>8585949</v>
-      </c>
-      <c r="BA39" s="9" t="n">
-        <v>56044.78</v>
-      </c>
-      <c r="BB39" s="10" t="n">
-        <v>0.0057</v>
-      </c>
-      <c r="BC39" s="11" t="n">
-        <v>-0.2132577936597328</v>
-      </c>
-      <c r="BD39" s="8" t="n">
-        <v>10913294</v>
-      </c>
-      <c r="BE39" s="9" t="n">
-        <v>67154.95</v>
-      </c>
-      <c r="BF39" s="10" t="n">
-        <v>0.0072</v>
-      </c>
-      <c r="BG39" s="11" t="n">
-        <v>-0.09462389658963724</v>
-      </c>
-      <c r="BH39" s="8" t="n">
-        <v>12053879</v>
-      </c>
-      <c r="BI39" s="9" t="n">
-        <v>70937.08</v>
-      </c>
-      <c r="BJ39" s="10" t="n">
-        <v>0.0081</v>
-      </c>
-      <c r="BK39" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL39" s="8" t="n">
-        <v>12053879</v>
-      </c>
-      <c r="BM39" s="9" t="n">
-        <v>76801.28999999999</v>
-      </c>
-      <c r="BN39" s="10" t="n">
-        <v>0.0086</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AV39" s="8" t="n"/>
+      <c r="AW39" s="9" t="n"/>
+      <c r="AX39" s="10" t="n"/>
+      <c r="AY39" s="11" t="n"/>
+      <c r="AZ39" s="8" t="n"/>
+      <c r="BA39" s="9" t="n"/>
+      <c r="BB39" s="10" t="n"/>
+      <c r="BC39" s="11" t="n"/>
+      <c r="BD39" s="8" t="n"/>
+      <c r="BE39" s="9" t="n"/>
+      <c r="BF39" s="10" t="n"/>
+      <c r="BG39" s="11" t="n"/>
+      <c r="BH39" s="8" t="n"/>
+      <c r="BI39" s="9" t="n"/>
+      <c r="BJ39" s="10" t="n"/>
+      <c r="BK39" s="11" t="n"/>
+      <c r="BL39" s="8" t="n"/>
+      <c r="BM39" s="9" t="n"/>
+      <c r="BN39" s="10" t="n"/>
       <c r="BO39" s="11" t="n"/>
     </row>
     <row r="40">
@@ -7802,17 +7780,17 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>ITC Hotels Limited</t>
+          <t>Motilal Oswal Financial Services Limited</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>INE379A01028</t>
+          <t>INE338I01027</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Leisure Services</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D42" s="8" t="n"/>
@@ -7854,70 +7832,94 @@
       <c r="AN42" s="8" t="n"/>
       <c r="AO42" s="9" t="n"/>
       <c r="AP42" s="10" t="n"/>
-      <c r="AQ42" s="11" t="n"/>
-      <c r="AR42" s="8" t="n"/>
-      <c r="AS42" s="9" t="n"/>
-      <c r="AT42" s="10" t="n"/>
-      <c r="AU42" s="11" t="n"/>
-      <c r="AV42" s="8" t="n"/>
-      <c r="AW42" s="9" t="n"/>
-      <c r="AX42" s="10" t="n"/>
-      <c r="AY42" s="11" t="n"/>
-      <c r="AZ42" s="8" t="n"/>
-      <c r="BA42" s="9" t="n"/>
-      <c r="BB42" s="10" t="n"/>
+      <c r="AQ42" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AR42" s="8" t="n">
+        <v>591805</v>
+      </c>
+      <c r="AS42" s="9" t="n">
+        <v>5149</v>
+      </c>
+      <c r="AT42" s="10" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="AU42" s="11" t="n">
+        <v>-0.8902567225534253</v>
+      </c>
+      <c r="AV42" s="8" t="n">
+        <v>5392631</v>
+      </c>
+      <c r="AW42" s="9" t="n">
+        <v>43674.92</v>
+      </c>
+      <c r="AX42" s="10" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="AY42" s="11" t="n">
+        <v>-0.3719237093069153</v>
+      </c>
+      <c r="AZ42" s="8" t="n">
+        <v>8585949</v>
+      </c>
+      <c r="BA42" s="9" t="n">
+        <v>56044.78</v>
+      </c>
+      <c r="BB42" s="10" t="n">
+        <v>0.0057</v>
+      </c>
       <c r="BC42" s="11" t="n">
-        <v>-1</v>
+        <v>-0.2132577936597328</v>
       </c>
       <c r="BD42" s="8" t="n">
-        <v>9899412</v>
+        <v>10913294</v>
       </c>
       <c r="BE42" s="9" t="n">
-        <v>19552.33</v>
+        <v>67154.95</v>
       </c>
       <c r="BF42" s="10" t="n">
-        <v>0.0021</v>
+        <v>0.0072</v>
       </c>
       <c r="BG42" s="11" t="n">
-        <v>0</v>
+        <v>-0.09462389658963724</v>
       </c>
       <c r="BH42" s="8" t="n">
-        <v>9899412</v>
+        <v>12053879</v>
       </c>
       <c r="BI42" s="9" t="n">
-        <v>16216.23</v>
+        <v>70937.08</v>
       </c>
       <c r="BJ42" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.0081</v>
       </c>
       <c r="BK42" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BL42" s="8" t="n">
-        <v>9899412</v>
+        <v>12053879</v>
       </c>
       <c r="BM42" s="9" t="n">
-        <v>16131.09</v>
+        <v>76801.28999999999</v>
       </c>
       <c r="BN42" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.0086</v>
       </c>
       <c r="BO42" s="11" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited</t>
+          <t>ITC Hotels Limited</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>INE768C01010</t>
+          <t>INE379A01028</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Leisure Services</t>
         </is>
       </c>
       <c r="D43" s="8" t="n"/>
@@ -7951,45 +7953,19 @@
       <c r="AF43" s="8" t="n"/>
       <c r="AG43" s="9" t="n"/>
       <c r="AH43" s="10" t="n"/>
-      <c r="AI43" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AJ43" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="AK43" s="9" t="n">
-        <v>88822.8</v>
-      </c>
-      <c r="AL43" s="10" t="n">
-        <v>0.0077</v>
-      </c>
-      <c r="AM43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN43" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="AO43" s="9" t="n">
-        <v>89280.39999999999</v>
-      </c>
-      <c r="AP43" s="10" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-      <c r="AQ43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR43" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="AS43" s="9" t="n">
-        <v>89020.8</v>
-      </c>
-      <c r="AT43" s="10" t="n">
-        <v>0.0081</v>
-      </c>
-      <c r="AU43" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="AI43" s="11" t="n"/>
+      <c r="AJ43" s="8" t="n"/>
+      <c r="AK43" s="9" t="n"/>
+      <c r="AL43" s="10" t="n"/>
+      <c r="AM43" s="11" t="n"/>
+      <c r="AN43" s="8" t="n"/>
+      <c r="AO43" s="9" t="n"/>
+      <c r="AP43" s="10" t="n"/>
+      <c r="AQ43" s="11" t="n"/>
+      <c r="AR43" s="8" t="n"/>
+      <c r="AS43" s="9" t="n"/>
+      <c r="AT43" s="10" t="n"/>
+      <c r="AU43" s="11" t="n"/>
       <c r="AV43" s="8" t="n"/>
       <c r="AW43" s="9" t="n"/>
       <c r="AX43" s="10" t="n"/>
@@ -7997,18 +7973,42 @@
       <c r="AZ43" s="8" t="n"/>
       <c r="BA43" s="9" t="n"/>
       <c r="BB43" s="10" t="n"/>
-      <c r="BC43" s="11" t="n"/>
-      <c r="BD43" s="8" t="n"/>
-      <c r="BE43" s="9" t="n"/>
-      <c r="BF43" s="10" t="n"/>
-      <c r="BG43" s="11" t="n"/>
-      <c r="BH43" s="8" t="n"/>
-      <c r="BI43" s="9" t="n"/>
-      <c r="BJ43" s="10" t="n"/>
-      <c r="BK43" s="11" t="n"/>
-      <c r="BL43" s="8" t="n"/>
-      <c r="BM43" s="9" t="n"/>
-      <c r="BN43" s="10" t="n"/>
+      <c r="BC43" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BD43" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BE43" s="9" t="n">
+        <v>19552.33</v>
+      </c>
+      <c r="BF43" s="10" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="BG43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH43" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BI43" s="9" t="n">
+        <v>16216.23</v>
+      </c>
+      <c r="BJ43" s="10" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="BK43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL43" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BM43" s="9" t="n">
+        <v>16131.09</v>
+      </c>
+      <c r="BN43" s="10" t="n">
+        <v>0.0018</v>
+      </c>
       <c r="BO43" s="11" t="n"/>
     </row>
     <row r="44">

--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -490,52 +490,52 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO44"/>
+  <dimension ref="A1:BS44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
     <col width="26" customWidth="1" min="17" max="17"/>
-    <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="23" customWidth="1" min="19" max="19"/>
-    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
     <col width="26" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
-    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="23" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
     <col width="26" customWidth="1" min="25" max="25"/>
     <col width="20" customWidth="1" min="26" max="26"/>
     <col width="22" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
     <col width="26" customWidth="1" min="29" max="29"/>
     <col width="14" customWidth="1" min="30" max="30"/>
-    <col width="23" customWidth="1" min="31" max="31"/>
-    <col width="16" customWidth="1" min="32" max="32"/>
+    <col width="22" customWidth="1" min="31" max="31"/>
+    <col width="14" customWidth="1" min="32" max="32"/>
     <col width="26" customWidth="1" min="33" max="33"/>
-    <col width="20" customWidth="1" min="34" max="34"/>
-    <col width="22" customWidth="1" min="35" max="35"/>
-    <col width="13" customWidth="1" min="36" max="36"/>
+    <col width="14" customWidth="1" min="34" max="34"/>
+    <col width="23" customWidth="1" min="35" max="35"/>
+    <col width="16" customWidth="1" min="36" max="36"/>
     <col width="26" customWidth="1" min="37" max="37"/>
     <col width="20" customWidth="1" min="38" max="38"/>
-    <col width="23" customWidth="1" min="39" max="39"/>
+    <col width="22" customWidth="1" min="39" max="39"/>
     <col width="13" customWidth="1" min="40" max="40"/>
     <col width="26" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
-    <col width="22" customWidth="1" min="43" max="43"/>
+    <col width="23" customWidth="1" min="43" max="43"/>
     <col width="13" customWidth="1" min="44" max="44"/>
     <col width="26" customWidth="1" min="45" max="45"/>
     <col width="20" customWidth="1" min="46" max="46"/>
@@ -543,23 +543,27 @@
     <col width="13" customWidth="1" min="48" max="48"/>
     <col width="26" customWidth="1" min="49" max="49"/>
     <col width="20" customWidth="1" min="50" max="50"/>
-    <col width="23" customWidth="1" min="51" max="51"/>
+    <col width="22" customWidth="1" min="51" max="51"/>
     <col width="13" customWidth="1" min="52" max="52"/>
     <col width="26" customWidth="1" min="53" max="53"/>
     <col width="20" customWidth="1" min="54" max="54"/>
-    <col width="22" customWidth="1" min="55" max="55"/>
+    <col width="23" customWidth="1" min="55" max="55"/>
     <col width="13" customWidth="1" min="56" max="56"/>
     <col width="26" customWidth="1" min="57" max="57"/>
     <col width="20" customWidth="1" min="58" max="58"/>
-    <col width="23" customWidth="1" min="59" max="59"/>
-    <col width="15" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="59" max="59"/>
+    <col width="13" customWidth="1" min="60" max="60"/>
     <col width="26" customWidth="1" min="61" max="61"/>
-    <col width="14" customWidth="1" min="62" max="62"/>
-    <col width="22" customWidth="1" min="63" max="63"/>
-    <col width="14" customWidth="1" min="64" max="64"/>
+    <col width="20" customWidth="1" min="62" max="62"/>
+    <col width="23" customWidth="1" min="63" max="63"/>
+    <col width="15" customWidth="1" min="64" max="64"/>
     <col width="26" customWidth="1" min="65" max="65"/>
     <col width="20" customWidth="1" min="66" max="66"/>
-    <col width="17" customWidth="1" min="67" max="67"/>
+    <col width="22" customWidth="1" min="67" max="67"/>
+    <col width="14" customWidth="1" min="68" max="68"/>
+    <col width="26" customWidth="1" min="69" max="69"/>
+    <col width="20" customWidth="1" min="70" max="70"/>
+    <col width="17" customWidth="1" min="71" max="71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -634,6 +638,10 @@
       <c r="BM1" s="1" t="n"/>
       <c r="BN1" s="1" t="n"/>
       <c r="BO1" s="1" t="n"/>
+      <c r="BP1" s="1" t="n"/>
+      <c r="BQ1" s="1" t="n"/>
+      <c r="BR1" s="1" t="n"/>
+      <c r="BS1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -653,7 +661,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>April_2026</t>
+          <t>May_2026</t>
         </is>
       </c>
       <c r="E2" s="2" t="n"/>
@@ -661,7 +669,7 @@
       <c r="G2" s="3" t="n"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>March_2026</t>
+          <t>April_2026</t>
         </is>
       </c>
       <c r="I2" s="2" t="n"/>
@@ -669,7 +677,7 @@
       <c r="K2" s="3" t="n"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>February_2026</t>
+          <t>March_2026</t>
         </is>
       </c>
       <c r="M2" s="2" t="n"/>
@@ -677,7 +685,7 @@
       <c r="O2" s="3" t="n"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>January_2026</t>
+          <t>February_2026</t>
         </is>
       </c>
       <c r="Q2" s="2" t="n"/>
@@ -685,7 +693,7 @@
       <c r="S2" s="3" t="n"/>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>December_2025</t>
+          <t>January_2026</t>
         </is>
       </c>
       <c r="U2" s="2" t="n"/>
@@ -693,7 +701,7 @@
       <c r="W2" s="3" t="n"/>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>November_2025</t>
+          <t>December_2025</t>
         </is>
       </c>
       <c r="Y2" s="2" t="n"/>
@@ -701,7 +709,7 @@
       <c r="AA2" s="3" t="n"/>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>October_2025</t>
+          <t>November_2025</t>
         </is>
       </c>
       <c r="AC2" s="2" t="n"/>
@@ -709,7 +717,7 @@
       <c r="AE2" s="3" t="n"/>
       <c r="AF2" s="2" t="inlineStr">
         <is>
-          <t>September_2025</t>
+          <t>October_2025</t>
         </is>
       </c>
       <c r="AG2" s="2" t="n"/>
@@ -717,7 +725,7 @@
       <c r="AI2" s="3" t="n"/>
       <c r="AJ2" s="2" t="inlineStr">
         <is>
-          <t>August_2025</t>
+          <t>September_2025</t>
         </is>
       </c>
       <c r="AK2" s="2" t="n"/>
@@ -725,7 +733,7 @@
       <c r="AM2" s="3" t="n"/>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>July_2025</t>
+          <t>August_2025</t>
         </is>
       </c>
       <c r="AO2" s="2" t="n"/>
@@ -733,7 +741,7 @@
       <c r="AQ2" s="3" t="n"/>
       <c r="AR2" s="2" t="inlineStr">
         <is>
-          <t>June_2025</t>
+          <t>July_2025</t>
         </is>
       </c>
       <c r="AS2" s="2" t="n"/>
@@ -741,7 +749,7 @@
       <c r="AU2" s="3" t="n"/>
       <c r="AV2" s="2" t="inlineStr">
         <is>
-          <t>May_2025</t>
+          <t>June_2025</t>
         </is>
       </c>
       <c r="AW2" s="2" t="n"/>
@@ -749,7 +757,7 @@
       <c r="AY2" s="3" t="n"/>
       <c r="AZ2" s="2" t="inlineStr">
         <is>
-          <t>April_2025</t>
+          <t>May_2025</t>
         </is>
       </c>
       <c r="BA2" s="2" t="n"/>
@@ -757,7 +765,7 @@
       <c r="BC2" s="3" t="n"/>
       <c r="BD2" s="2" t="inlineStr">
         <is>
-          <t>March_2025</t>
+          <t>April_2025</t>
         </is>
       </c>
       <c r="BE2" s="2" t="n"/>
@@ -765,7 +773,7 @@
       <c r="BG2" s="3" t="n"/>
       <c r="BH2" s="2" t="inlineStr">
         <is>
-          <t>February_2025</t>
+          <t>March_2025</t>
         </is>
       </c>
       <c r="BI2" s="2" t="n"/>
@@ -773,12 +781,20 @@
       <c r="BK2" s="3" t="n"/>
       <c r="BL2" s="2" t="inlineStr">
         <is>
-          <t>January_2025</t>
+          <t>February_2025</t>
         </is>
       </c>
       <c r="BM2" s="2" t="n"/>
       <c r="BN2" s="2" t="n"/>
       <c r="BO2" s="3" t="n"/>
+      <c r="BP2" s="2" t="inlineStr">
+        <is>
+          <t>January_2025</t>
+        </is>
+      </c>
+      <c r="BQ2" s="2" t="n"/>
+      <c r="BR2" s="2" t="n"/>
+      <c r="BS2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n"/>
@@ -1104,6 +1120,26 @@
           <t>% Change in Qty</t>
         </is>
       </c>
+      <c r="BP3" s="4" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="BQ3" s="4" t="inlineStr">
+        <is>
+          <t>Market Value (Rs. Lakhs)</t>
+        </is>
+      </c>
+      <c r="BR3" s="4" t="inlineStr">
+        <is>
+          <t>% Net Assets</t>
+        </is>
+      </c>
+      <c r="BS3" s="5" t="inlineStr">
+        <is>
+          <t>% Change in Qty</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -1122,169 +1158,169 @@
         </is>
       </c>
       <c r="D4" s="8" t="n">
+        <v>149727224</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>1114794.05</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>0.0788</v>
+      </c>
+      <c r="G4" s="11" t="n">
+        <v>0.0325502520036884</v>
+      </c>
+      <c r="H4" s="8" t="n">
         <v>145007203</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="I4" s="9" t="n">
         <v>1119020.59</v>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="J4" s="10" t="n">
         <v>0.0794</v>
       </c>
-      <c r="G4" s="11" t="n">
+      <c r="K4" s="11" t="n">
         <v>0.03394007080483452</v>
       </c>
-      <c r="H4" s="8" t="n">
+      <c r="L4" s="8" t="n">
         <v>140247203</v>
       </c>
-      <c r="I4" s="9" t="n">
+      <c r="M4" s="9" t="n">
         <v>1025978.41</v>
       </c>
-      <c r="J4" s="10" t="n">
+      <c r="N4" s="10" t="n">
         <v>0.0796</v>
       </c>
-      <c r="K4" s="11" t="n">
+      <c r="O4" s="11" t="n">
         <v>0.1995596121426969</v>
       </c>
-      <c r="L4" s="8" t="n">
+      <c r="P4" s="8" t="n">
         <v>116915576</v>
       </c>
-      <c r="M4" s="9" t="n">
+      <c r="Q4" s="9" t="n">
         <v>1037918.03</v>
       </c>
-      <c r="N4" s="10" t="n">
+      <c r="R4" s="10" t="n">
         <v>0.07729999999999999</v>
       </c>
-      <c r="O4" s="11" t="n">
+      <c r="S4" s="11" t="n">
         <v>0.008626968303207154</v>
       </c>
-      <c r="P4" s="8" t="n">
+      <c r="T4" s="8" t="n">
         <v>115915576</v>
       </c>
-      <c r="Q4" s="9" t="n">
+      <c r="U4" s="9" t="n">
         <v>1077145.49</v>
       </c>
-      <c r="R4" s="10" t="n">
+      <c r="V4" s="10" t="n">
         <v>0.0804</v>
       </c>
-      <c r="S4" s="11" t="n">
+      <c r="W4" s="11" t="n">
         <v>0.06600587475157653</v>
       </c>
-      <c r="T4" s="8" t="n">
+      <c r="X4" s="8" t="n">
         <v>108738215</v>
       </c>
-      <c r="U4" s="9" t="n">
+      <c r="Y4" s="9" t="n">
         <v>1077813.19</v>
       </c>
-      <c r="V4" s="10" t="n">
+      <c r="Z4" s="10" t="n">
         <v>0.0809</v>
       </c>
-      <c r="W4" s="11" t="n">
+      <c r="AA4" s="11" t="n">
         <v>0.05075274131724232</v>
       </c>
-      <c r="X4" s="8" t="n">
+      <c r="AB4" s="8" t="n">
         <v>103486016</v>
       </c>
-      <c r="Y4" s="9" t="n">
+      <c r="AC4" s="9" t="n">
         <v>1042725.1</v>
       </c>
-      <c r="Z4" s="10" t="n">
+      <c r="AD4" s="10" t="n">
         <v>0.0803</v>
       </c>
-      <c r="AA4" s="11" t="n">
+      <c r="AE4" s="11" t="n">
         <v>0.01255042387516938</v>
       </c>
-      <c r="AB4" s="8" t="n">
+      <c r="AF4" s="8" t="n">
         <v>102203321</v>
       </c>
-      <c r="AC4" s="9" t="n">
+      <c r="AG4" s="9" t="n">
         <v>1009053.39</v>
       </c>
-      <c r="AD4" s="10" t="n">
+      <c r="AH4" s="10" t="n">
         <v>0.08019999999999999</v>
       </c>
-      <c r="AE4" s="11" t="n">
+      <c r="AI4" s="11" t="n">
         <v>0.005262209454604842</v>
       </c>
-      <c r="AF4" s="8" t="n">
+      <c r="AJ4" s="8" t="n">
         <v>101668321</v>
       </c>
-      <c r="AG4" s="9" t="n">
+      <c r="AK4" s="9" t="n">
         <v>966865.73</v>
       </c>
-      <c r="AH4" s="10" t="n">
+      <c r="AL4" s="10" t="n">
         <v>0.0808</v>
       </c>
-      <c r="AI4" s="11" t="n">
+      <c r="AM4" s="11" t="n">
         <v>0.06097375017638836</v>
       </c>
-      <c r="AJ4" s="8" t="n">
+      <c r="AN4" s="8" t="n">
         <v>95825482</v>
       </c>
-      <c r="AK4" s="9" t="n">
+      <c r="AO4" s="9" t="n">
         <v>911875.29</v>
       </c>
-      <c r="AL4" s="10" t="n">
+      <c r="AP4" s="10" t="n">
         <v>0.0793</v>
       </c>
-      <c r="AM4" s="11" t="n">
+      <c r="AQ4" s="11" t="n">
         <v>1.135602796681763</v>
       </c>
-      <c r="AN4" s="8" t="n">
+      <c r="AR4" s="8" t="n">
         <v>44870461</v>
       </c>
-      <c r="AO4" s="9" t="n">
+      <c r="AS4" s="9" t="n">
         <v>905575.64</v>
       </c>
-      <c r="AP4" s="10" t="n">
+      <c r="AT4" s="10" t="n">
         <v>0.0799</v>
       </c>
-      <c r="AQ4" s="11" t="n">
+      <c r="AU4" s="11" t="n">
         <v>0.009203290657165424</v>
       </c>
-      <c r="AR4" s="8" t="n">
+      <c r="AV4" s="8" t="n">
         <v>44461271</v>
       </c>
-      <c r="AS4" s="9" t="n">
+      <c r="AW4" s="9" t="n">
         <v>889892.34</v>
       </c>
-      <c r="AT4" s="10" t="n">
+      <c r="AX4" s="10" t="n">
         <v>0.0806</v>
       </c>
-      <c r="AU4" s="11" t="n">
+      <c r="AY4" s="11" t="n">
         <v>0.026983580212343</v>
       </c>
-      <c r="AV4" s="8" t="n">
+      <c r="AZ4" s="8" t="n">
         <v>43293069</v>
       </c>
-      <c r="AW4" s="9" t="n">
+      <c r="BA4" s="9" t="n">
         <v>842006.9</v>
       </c>
-      <c r="AX4" s="10" t="n">
+      <c r="BB4" s="10" t="n">
         <v>0.08110000000000001</v>
       </c>
-      <c r="AY4" s="11" t="n">
+      <c r="BC4" s="11" t="n">
         <v>0.01121152982515689</v>
-      </c>
-      <c r="AZ4" s="8" t="n">
-        <v>42813069</v>
-      </c>
-      <c r="BA4" s="9" t="n">
-        <v>824151.58</v>
-      </c>
-      <c r="BB4" s="10" t="n">
-        <v>0.08359999999999999</v>
-      </c>
-      <c r="BC4" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="BD4" s="8" t="n">
         <v>42813069</v>
       </c>
       <c r="BE4" s="9" t="n">
-        <v>782708.53</v>
+        <v>824151.58</v>
       </c>
       <c r="BF4" s="10" t="n">
-        <v>0.0838</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="BG4" s="11" t="n">
         <v>0</v>
@@ -1293,10 +1329,10 @@
         <v>42813069</v>
       </c>
       <c r="BI4" s="9" t="n">
-        <v>741693.61</v>
+        <v>782708.53</v>
       </c>
       <c r="BJ4" s="10" t="n">
-        <v>0.0843</v>
+        <v>0.0838</v>
       </c>
       <c r="BK4" s="11" t="n">
         <v>0</v>
@@ -1305,12 +1341,24 @@
         <v>42813069</v>
       </c>
       <c r="BM4" s="9" t="n">
+        <v>741693.61</v>
+      </c>
+      <c r="BN4" s="10" t="n">
+        <v>0.0843</v>
+      </c>
+      <c r="BO4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP4" s="8" t="n">
+        <v>42813069</v>
+      </c>
+      <c r="BQ4" s="9" t="n">
         <v>727287.01</v>
       </c>
-      <c r="BN4" s="10" t="n">
+      <c r="BR4" s="10" t="n">
         <v>0.08110000000000001</v>
       </c>
-      <c r="BO4" s="11" t="n"/>
+      <c r="BS4" s="11" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -1329,609 +1377,645 @@
         </is>
       </c>
       <c r="D5" s="8" t="n">
+        <v>312022782</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>906582.1899999999</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>0.0641</v>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>0.008365324403764154</v>
+      </c>
+      <c r="H5" s="8" t="n">
         <v>309434264</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="I5" s="9" t="n">
         <v>985083.98</v>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="J5" s="10" t="n">
         <v>0.0699</v>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="K5" s="11" t="n">
         <v>-0.00842648029250833</v>
       </c>
-      <c r="H5" s="8" t="n">
+      <c r="L5" s="8" t="n">
         <v>312063864</v>
       </c>
-      <c r="I5" s="9" t="n">
+      <c r="M5" s="9" t="n">
         <v>924021.1</v>
       </c>
-      <c r="J5" s="10" t="n">
+      <c r="N5" s="10" t="n">
         <v>0.0716</v>
       </c>
-      <c r="K5" s="11" t="n">
+      <c r="O5" s="11" t="n">
         <v>0.003053544409065615</v>
       </c>
-      <c r="L5" s="8" t="n">
+      <c r="P5" s="8" t="n">
         <v>311113864</v>
       </c>
-      <c r="M5" s="9" t="n">
+      <c r="Q5" s="9" t="n">
         <v>929141.55</v>
       </c>
-      <c r="N5" s="10" t="n">
+      <c r="R5" s="10" t="n">
         <v>0.0692</v>
       </c>
-      <c r="O5" s="11" t="n">
+      <c r="S5" s="11" t="n">
         <v>-0.007185705380051316</v>
       </c>
-      <c r="P5" s="8" t="n">
+      <c r="T5" s="8" t="n">
         <v>313365617</v>
       </c>
-      <c r="Q5" s="9" t="n">
+      <c r="U5" s="9" t="n">
         <v>803782.8100000001</v>
       </c>
-      <c r="R5" s="10" t="n">
+      <c r="V5" s="10" t="n">
         <v>0.06</v>
       </c>
-      <c r="S5" s="11" t="n">
+      <c r="W5" s="11" t="n">
         <v>0.02601784123854898</v>
       </c>
-      <c r="T5" s="8" t="n">
+      <c r="X5" s="8" t="n">
         <v>305419267</v>
       </c>
-      <c r="U5" s="9" t="n">
+      <c r="Y5" s="9" t="n">
         <v>808139.38</v>
       </c>
-      <c r="V5" s="10" t="n">
+      <c r="Z5" s="10" t="n">
         <v>0.0606</v>
       </c>
-      <c r="W5" s="11" t="n">
+      <c r="AA5" s="11" t="n">
         <v>0.07483622732268541</v>
       </c>
-      <c r="X5" s="8" t="n">
+      <c r="AB5" s="8" t="n">
         <v>284154236</v>
       </c>
-      <c r="Y5" s="9" t="n">
+      <c r="AC5" s="9" t="n">
         <v>767074.36</v>
       </c>
-      <c r="Z5" s="10" t="n">
+      <c r="AD5" s="10" t="n">
         <v>0.0591</v>
       </c>
-      <c r="AA5" s="11" t="n">
+      <c r="AE5" s="11" t="n">
         <v>0.08544209611432535</v>
       </c>
-      <c r="AB5" s="8" t="n">
+      <c r="AF5" s="8" t="n">
         <v>261786637</v>
       </c>
-      <c r="AC5" s="9" t="n">
+      <c r="AG5" s="9" t="n">
         <v>754338.1899999999</v>
       </c>
-      <c r="AD5" s="10" t="n">
+      <c r="AH5" s="10" t="n">
         <v>0.06</v>
       </c>
-      <c r="AE5" s="11" t="n">
+      <c r="AI5" s="11" t="n">
         <v>0.02291281861384987</v>
       </c>
-      <c r="AF5" s="8" t="n">
+      <c r="AJ5" s="8" t="n">
         <v>255922726</v>
       </c>
-      <c r="AG5" s="9" t="n">
+      <c r="AK5" s="9" t="n">
         <v>717223.4399999999</v>
       </c>
-      <c r="AH5" s="10" t="n">
+      <c r="AL5" s="10" t="n">
         <v>0.0599</v>
       </c>
-      <c r="AI5" s="11" t="n">
+      <c r="AM5" s="11" t="n">
         <v>0.04012490664854439</v>
       </c>
-      <c r="AJ5" s="8" t="n">
+      <c r="AN5" s="8" t="n">
         <v>246049993</v>
       </c>
-      <c r="AK5" s="9" t="n">
+      <c r="AO5" s="9" t="n">
         <v>677252.61</v>
       </c>
-      <c r="AL5" s="10" t="n">
+      <c r="AP5" s="10" t="n">
         <v>0.0589</v>
       </c>
-      <c r="AM5" s="11" t="n">
+      <c r="AQ5" s="11" t="n">
         <v>0.06613218800272164</v>
       </c>
-      <c r="AN5" s="8" t="n">
+      <c r="AR5" s="8" t="n">
         <v>230787510</v>
       </c>
-      <c r="AO5" s="9" t="n">
+      <c r="AS5" s="9" t="n">
         <v>671591.65</v>
       </c>
-      <c r="AP5" s="10" t="n">
+      <c r="AT5" s="10" t="n">
         <v>0.0593</v>
       </c>
-      <c r="AQ5" s="11" t="n">
+      <c r="AU5" s="11" t="n">
         <v>0.02930647191621902</v>
       </c>
-      <c r="AR5" s="8" t="n">
+      <c r="AV5" s="8" t="n">
         <v>224216515</v>
       </c>
-      <c r="AS5" s="9" t="n">
+      <c r="AW5" s="9" t="n">
         <v>672425.33</v>
       </c>
-      <c r="AT5" s="10" t="n">
+      <c r="AX5" s="10" t="n">
         <v>0.0609</v>
       </c>
-      <c r="AU5" s="11" t="n">
+      <c r="AY5" s="11" t="n">
         <v>0.07348663585077284</v>
       </c>
-      <c r="AV5" s="8" t="n">
+      <c r="AZ5" s="8" t="n">
         <v>208867542</v>
       </c>
-      <c r="AW5" s="9" t="n">
+      <c r="BA5" s="9" t="n">
         <v>605193.7</v>
       </c>
-      <c r="AX5" s="10" t="n">
+      <c r="BB5" s="10" t="n">
         <v>0.0583</v>
       </c>
-      <c r="AY5" s="11" t="n">
+      <c r="BC5" s="11" t="n">
         <v>0.0787685054851275</v>
       </c>
-      <c r="AZ5" s="8" t="n">
+      <c r="BD5" s="8" t="n">
         <v>193616648</v>
       </c>
-      <c r="BA5" s="9" t="n">
+      <c r="BE5" s="9" t="n">
         <v>595274.38</v>
       </c>
-      <c r="BB5" s="10" t="n">
+      <c r="BF5" s="10" t="n">
         <v>0.0604</v>
       </c>
-      <c r="BC5" s="11" t="n">
+      <c r="BG5" s="11" t="n">
         <v>0.004416437745811861</v>
       </c>
-      <c r="BD5" s="8" t="n">
+      <c r="BH5" s="8" t="n">
         <v>192765312</v>
       </c>
-      <c r="BE5" s="9" t="n">
+      <c r="BI5" s="9" t="n">
         <v>559694.08</v>
       </c>
-      <c r="BF5" s="10" t="n">
+      <c r="BJ5" s="10" t="n">
         <v>0.0599</v>
       </c>
-      <c r="BG5" s="11" t="n">
+      <c r="BK5" s="11" t="n">
         <v>-0.003790710650882039</v>
       </c>
-      <c r="BH5" s="8" t="n">
+      <c r="BL5" s="8" t="n">
         <v>193498810</v>
       </c>
-      <c r="BI5" s="9" t="n">
+      <c r="BM5" s="9" t="n">
         <v>485391.76</v>
       </c>
-      <c r="BJ5" s="10" t="n">
+      <c r="BN5" s="10" t="n">
         <v>0.0552</v>
       </c>
-      <c r="BK5" s="11" t="n">
+      <c r="BO5" s="11" t="n">
         <v>0.04268662994371823</v>
       </c>
-      <c r="BL5" s="8" t="n">
+      <c r="BP5" s="8" t="n">
         <v>185577147</v>
       </c>
-      <c r="BM5" s="9" t="n">
+      <c r="BQ5" s="9" t="n">
         <v>559793.46</v>
       </c>
-      <c r="BN5" s="10" t="n">
+      <c r="BR5" s="10" t="n">
         <v>0.0624</v>
       </c>
-      <c r="BO5" s="11" t="n"/>
+      <c r="BS5" s="11" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Coal India Limited</t>
+          <t>ITC Limited</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>INE522F01014</t>
+          <t>INE154A01025</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Consumable Fuels</t>
+          <t>Diversified FMCG</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>174142417</v>
+        <v>287864469</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>838408.67</v>
+        <v>825883.16</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.0595</v>
+        <v>0.0584</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>-0.003861171338551467</v>
+        <v>0.1836489175004619</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>174817417</v>
+        <v>243200889</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>787465.05</v>
+        <v>765839.6</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>0.0611</v>
+        <v>0.0543</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>0.08297202293533477</v>
+        <v>0.08526303507031635</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>161423761</v>
+        <v>224093958</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>695171.4300000001</v>
+        <v>644718.3199999999</v>
       </c>
       <c r="N6" s="10" t="n">
-        <v>0.0518</v>
+        <v>0.05</v>
       </c>
       <c r="O6" s="11" t="n">
-        <v>0.009957016950540437</v>
+        <v>0.03942596573137731</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>159832308</v>
+        <v>215593958</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>704460.9</v>
+        <v>676102.65</v>
       </c>
       <c r="R6" s="10" t="n">
-        <v>0.0526</v>
+        <v>0.0504</v>
       </c>
       <c r="S6" s="11" t="n">
-        <v>-0.01362167378906329</v>
+        <v>0.02712213930725835</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>162039558</v>
+        <v>209900994</v>
       </c>
       <c r="U6" s="9" t="n">
-        <v>646537.84</v>
+        <v>676196.05</v>
       </c>
       <c r="V6" s="10" t="n">
-        <v>0.0485</v>
+        <v>0.0505</v>
       </c>
       <c r="W6" s="11" t="n">
-        <v>0</v>
+        <v>0.4118991702128273</v>
       </c>
       <c r="X6" s="8" t="n">
-        <v>162039558</v>
+        <v>148665711</v>
       </c>
       <c r="Y6" s="9" t="n">
-        <v>609511.8</v>
+        <v>599122.8199999999</v>
       </c>
       <c r="Z6" s="10" t="n">
-        <v>0.047</v>
+        <v>0.0449</v>
       </c>
       <c r="AA6" s="11" t="n">
-        <v>0</v>
+        <v>0.02714259251540287</v>
       </c>
       <c r="AB6" s="8" t="n">
-        <v>162039558</v>
+        <v>144737169</v>
       </c>
       <c r="AC6" s="9" t="n">
-        <v>629766.74</v>
+        <v>585100.01</v>
       </c>
       <c r="AD6" s="10" t="n">
-        <v>0.0501</v>
+        <v>0.0451</v>
       </c>
       <c r="AE6" s="11" t="n">
-        <v>0</v>
+        <v>0.04299272879906111</v>
       </c>
       <c r="AF6" s="8" t="n">
-        <v>162039558</v>
+        <v>138771024</v>
       </c>
       <c r="AG6" s="9" t="n">
-        <v>631873.26</v>
+        <v>583324</v>
       </c>
       <c r="AH6" s="10" t="n">
-        <v>0.0528</v>
+        <v>0.0464</v>
       </c>
       <c r="AI6" s="11" t="n">
-        <v>0</v>
+        <v>0.02247256843567582</v>
       </c>
       <c r="AJ6" s="8" t="n">
-        <v>162039558</v>
+        <v>135721024</v>
       </c>
       <c r="AK6" s="9" t="n">
-        <v>607324.26</v>
+        <v>544987.77</v>
       </c>
       <c r="AL6" s="10" t="n">
-        <v>0.0528</v>
+        <v>0.0455</v>
       </c>
       <c r="AM6" s="11" t="n">
-        <v>0</v>
+        <v>0.04867833529118113</v>
       </c>
       <c r="AN6" s="8" t="n">
-        <v>162039558</v>
+        <v>129421024</v>
       </c>
       <c r="AO6" s="9" t="n">
-        <v>609835.88</v>
+        <v>530302.65</v>
       </c>
       <c r="AP6" s="10" t="n">
-        <v>0.0538</v>
+        <v>0.0461</v>
       </c>
       <c r="AQ6" s="11" t="n">
-        <v>0</v>
+        <v>0.05933146465642036</v>
       </c>
       <c r="AR6" s="8" t="n">
-        <v>162039558</v>
+        <v>122172359</v>
       </c>
       <c r="AS6" s="9" t="n">
-        <v>635114.05</v>
+        <v>503289.03</v>
       </c>
       <c r="AT6" s="10" t="n">
-        <v>0.0575</v>
+        <v>0.0444</v>
       </c>
       <c r="AU6" s="11" t="n">
-        <v>0.0408396826825464</v>
+        <v>0.04045226173662547</v>
       </c>
       <c r="AV6" s="8" t="n">
-        <v>155681572</v>
+        <v>117422359</v>
       </c>
       <c r="AW6" s="9" t="n">
-        <v>618522.89</v>
+        <v>489005.41</v>
       </c>
       <c r="AX6" s="10" t="n">
-        <v>0.0595</v>
+        <v>0.0443</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>0.04960632238493121</v>
+        <v>0.07460089770293252</v>
       </c>
       <c r="AZ6" s="8" t="n">
-        <v>148323775</v>
+        <v>109270669</v>
       </c>
       <c r="BA6" s="9" t="n">
-        <v>571491.51</v>
+        <v>456806.03</v>
       </c>
       <c r="BB6" s="10" t="n">
-        <v>0.058</v>
+        <v>0.044</v>
       </c>
       <c r="BC6" s="11" t="n">
-        <v>0.05138982123049783</v>
+        <v>0.03799307836597426</v>
       </c>
       <c r="BD6" s="8" t="n">
-        <v>141074007</v>
+        <v>105271096</v>
       </c>
       <c r="BE6" s="9" t="n">
-        <v>561756.7</v>
+        <v>448244.33</v>
       </c>
       <c r="BF6" s="10" t="n">
-        <v>0.0601</v>
+        <v>0.0455</v>
       </c>
       <c r="BG6" s="11" t="n">
-        <v>-0.01095372515938375</v>
+        <v>0.04028866499357868</v>
       </c>
       <c r="BH6" s="8" t="n">
-        <v>142636407</v>
+        <v>101194120</v>
       </c>
       <c r="BI6" s="9" t="n">
-        <v>526827.5699999999</v>
+        <v>414642.91</v>
       </c>
       <c r="BJ6" s="10" t="n">
-        <v>0.0599</v>
+        <v>0.0444</v>
       </c>
       <c r="BK6" s="11" t="n">
-        <v>0.02369256314048828</v>
+        <v>0</v>
       </c>
       <c r="BL6" s="8" t="n">
-        <v>139335199</v>
+        <v>101194120</v>
       </c>
       <c r="BM6" s="9" t="n">
-        <v>551628.05</v>
+        <v>399716.77</v>
       </c>
       <c r="BN6" s="10" t="n">
-        <v>0.0615</v>
-      </c>
-      <c r="BO6" s="11" t="n"/>
+        <v>0.0454</v>
+      </c>
+      <c r="BO6" s="11" t="n">
+        <v>0.02222354216593874</v>
+      </c>
+      <c r="BP6" s="8" t="n">
+        <v>98994120</v>
+      </c>
+      <c r="BQ6" s="9" t="n">
+        <v>442998.69</v>
+      </c>
+      <c r="BR6" s="10" t="n">
+        <v>0.0494</v>
+      </c>
+      <c r="BS6" s="11" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>ITC Limited</t>
+          <t>Coal India Limited</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>INE154A01025</t>
+          <t>INE522F01014</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Diversified FMCG</t>
+          <t>Consumable Fuels</t>
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>243200889</v>
+        <v>174816417</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>765839.6</v>
+        <v>800484.37</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.0543</v>
+        <v>0.0566</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>0.08526303507031635</v>
+        <v>0.003870395344288807</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>224093958</v>
+        <v>174142417</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>644718.3199999999</v>
+        <v>838408.67</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.05</v>
+        <v>0.0595</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>0.03942596573137731</v>
+        <v>-0.003861171338551467</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>215593958</v>
+        <v>174817417</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>676102.65</v>
+        <v>787465.05</v>
       </c>
       <c r="N7" s="10" t="n">
-        <v>0.0504</v>
+        <v>0.0611</v>
       </c>
       <c r="O7" s="11" t="n">
-        <v>0.02712213930725835</v>
+        <v>0.08297202293533477</v>
       </c>
       <c r="P7" s="8" t="n">
-        <v>209900994</v>
+        <v>161423761</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>676196.05</v>
+        <v>695171.4300000001</v>
       </c>
       <c r="R7" s="10" t="n">
-        <v>0.0505</v>
+        <v>0.0518</v>
       </c>
       <c r="S7" s="11" t="n">
-        <v>0.4118991702128273</v>
+        <v>0.009957016950540437</v>
       </c>
       <c r="T7" s="8" t="n">
-        <v>148665711</v>
+        <v>159832308</v>
       </c>
       <c r="U7" s="9" t="n">
-        <v>599122.8199999999</v>
+        <v>704460.9</v>
       </c>
       <c r="V7" s="10" t="n">
-        <v>0.0449</v>
+        <v>0.0526</v>
       </c>
       <c r="W7" s="11" t="n">
-        <v>0.02714259251540287</v>
+        <v>-0.01362167378906329</v>
       </c>
       <c r="X7" s="8" t="n">
-        <v>144737169</v>
+        <v>162039558</v>
       </c>
       <c r="Y7" s="9" t="n">
-        <v>585100.01</v>
+        <v>646537.84</v>
       </c>
       <c r="Z7" s="10" t="n">
-        <v>0.0451</v>
+        <v>0.0485</v>
       </c>
       <c r="AA7" s="11" t="n">
-        <v>0.04299272879906111</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="8" t="n">
-        <v>138771024</v>
+        <v>162039558</v>
       </c>
       <c r="AC7" s="9" t="n">
-        <v>583324</v>
+        <v>609511.8</v>
       </c>
       <c r="AD7" s="10" t="n">
-        <v>0.0464</v>
+        <v>0.047</v>
       </c>
       <c r="AE7" s="11" t="n">
-        <v>0.02247256843567582</v>
+        <v>0</v>
       </c>
       <c r="AF7" s="8" t="n">
-        <v>135721024</v>
+        <v>162039558</v>
       </c>
       <c r="AG7" s="9" t="n">
-        <v>544987.77</v>
+        <v>629766.74</v>
       </c>
       <c r="AH7" s="10" t="n">
-        <v>0.0455</v>
+        <v>0.0501</v>
       </c>
       <c r="AI7" s="11" t="n">
-        <v>0.04867833529118113</v>
+        <v>0</v>
       </c>
       <c r="AJ7" s="8" t="n">
-        <v>129421024</v>
+        <v>162039558</v>
       </c>
       <c r="AK7" s="9" t="n">
-        <v>530302.65</v>
+        <v>631873.26</v>
       </c>
       <c r="AL7" s="10" t="n">
-        <v>0.0461</v>
+        <v>0.0528</v>
       </c>
       <c r="AM7" s="11" t="n">
-        <v>0.05933146465642036</v>
+        <v>0</v>
       </c>
       <c r="AN7" s="8" t="n">
-        <v>122172359</v>
+        <v>162039558</v>
       </c>
       <c r="AO7" s="9" t="n">
-        <v>503289.03</v>
+        <v>607324.26</v>
       </c>
       <c r="AP7" s="10" t="n">
-        <v>0.0444</v>
+        <v>0.0528</v>
       </c>
       <c r="AQ7" s="11" t="n">
-        <v>0.04045226173662547</v>
+        <v>0</v>
       </c>
       <c r="AR7" s="8" t="n">
-        <v>117422359</v>
+        <v>162039558</v>
       </c>
       <c r="AS7" s="9" t="n">
-        <v>489005.41</v>
+        <v>609835.88</v>
       </c>
       <c r="AT7" s="10" t="n">
-        <v>0.0443</v>
+        <v>0.0538</v>
       </c>
       <c r="AU7" s="11" t="n">
-        <v>0.07460089770293252</v>
+        <v>0</v>
       </c>
       <c r="AV7" s="8" t="n">
-        <v>109270669</v>
+        <v>162039558</v>
       </c>
       <c r="AW7" s="9" t="n">
-        <v>456806.03</v>
+        <v>635114.05</v>
       </c>
       <c r="AX7" s="10" t="n">
-        <v>0.044</v>
+        <v>0.0575</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>0.03799307836597426</v>
+        <v>0.0408396826825464</v>
       </c>
       <c r="AZ7" s="8" t="n">
-        <v>105271096</v>
+        <v>155681572</v>
       </c>
       <c r="BA7" s="9" t="n">
-        <v>448244.33</v>
+        <v>618522.89</v>
       </c>
       <c r="BB7" s="10" t="n">
-        <v>0.0455</v>
+        <v>0.0595</v>
       </c>
       <c r="BC7" s="11" t="n">
-        <v>0.04028866499357868</v>
+        <v>0.04960632238493121</v>
       </c>
       <c r="BD7" s="8" t="n">
-        <v>101194120</v>
+        <v>148323775</v>
       </c>
       <c r="BE7" s="9" t="n">
-        <v>414642.91</v>
+        <v>571491.51</v>
       </c>
       <c r="BF7" s="10" t="n">
-        <v>0.0444</v>
+        <v>0.058</v>
       </c>
       <c r="BG7" s="11" t="n">
-        <v>0</v>
+        <v>0.05138982123049783</v>
       </c>
       <c r="BH7" s="8" t="n">
-        <v>101194120</v>
+        <v>141074007</v>
       </c>
       <c r="BI7" s="9" t="n">
-        <v>399716.77</v>
+        <v>561756.7</v>
       </c>
       <c r="BJ7" s="10" t="n">
-        <v>0.0454</v>
+        <v>0.0601</v>
       </c>
       <c r="BK7" s="11" t="n">
-        <v>0.02222354216593874</v>
+        <v>-0.01095372515938375</v>
       </c>
       <c r="BL7" s="8" t="n">
-        <v>98994120</v>
+        <v>142636407</v>
       </c>
       <c r="BM7" s="9" t="n">
-        <v>442998.69</v>
+        <v>526827.5699999999</v>
       </c>
       <c r="BN7" s="10" t="n">
-        <v>0.0494</v>
-      </c>
-      <c r="BO7" s="11" t="n"/>
+        <v>0.0599</v>
+      </c>
+      <c r="BO7" s="11" t="n">
+        <v>0.02369256314048828</v>
+      </c>
+      <c r="BP7" s="8" t="n">
+        <v>139335199</v>
+      </c>
+      <c r="BQ7" s="9" t="n">
+        <v>551628.05</v>
+      </c>
+      <c r="BR7" s="10" t="n">
+        <v>0.0615</v>
+      </c>
+      <c r="BS7" s="11" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -1950,49 +2034,49 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
+        <v>57517280</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>722647.11</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>0.0511</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>0.04870160244332773</v>
+      </c>
+      <c r="H8" s="8" t="n">
         <v>54846183</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="I8" s="9" t="n">
         <v>692926.6800000001</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="J8" s="10" t="n">
         <v>0.0492</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="K8" s="11" t="n">
         <v>0.01857141851633198</v>
       </c>
-      <c r="H8" s="8" t="n">
+      <c r="L8" s="8" t="n">
         <v>53846183</v>
       </c>
-      <c r="I8" s="9" t="n">
+      <c r="M8" s="9" t="n">
         <v>649331.12</v>
       </c>
-      <c r="J8" s="10" t="n">
+      <c r="N8" s="10" t="n">
         <v>0.0503</v>
       </c>
-      <c r="K8" s="11" t="n">
+      <c r="O8" s="11" t="n">
         <v>0.09165590577836893</v>
-      </c>
-      <c r="L8" s="8" t="n">
-        <v>49325234</v>
-      </c>
-      <c r="M8" s="9" t="n">
-        <v>680145.65</v>
-      </c>
-      <c r="N8" s="10" t="n">
-        <v>0.0507</v>
-      </c>
-      <c r="O8" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="P8" s="8" t="n">
         <v>49325234</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>668356.92</v>
+        <v>680145.65</v>
       </c>
       <c r="R8" s="10" t="n">
-        <v>0.0499</v>
+        <v>0.0507</v>
       </c>
       <c r="S8" s="11" t="n">
         <v>0</v>
@@ -2001,106 +2085,106 @@
         <v>49325234</v>
       </c>
       <c r="U8" s="9" t="n">
+        <v>668356.92</v>
+      </c>
+      <c r="V8" s="10" t="n">
+        <v>0.0499</v>
+      </c>
+      <c r="W8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="8" t="n">
+        <v>49325234</v>
+      </c>
+      <c r="Y8" s="9" t="n">
         <v>662388.5699999999</v>
       </c>
-      <c r="V8" s="10" t="n">
+      <c r="Z8" s="10" t="n">
         <v>0.0497</v>
       </c>
-      <c r="W8" s="11" t="n">
+      <c r="AA8" s="11" t="n">
         <v>0.08865063536064391</v>
       </c>
-      <c r="X8" s="8" t="n">
+      <c r="AB8" s="8" t="n">
         <v>45308598</v>
       </c>
-      <c r="Y8" s="9" t="n">
+      <c r="AC8" s="9" t="n">
         <v>629245.8100000001</v>
       </c>
-      <c r="Z8" s="10" t="n">
+      <c r="AD8" s="10" t="n">
         <v>0.0485</v>
       </c>
-      <c r="AA8" s="11" t="n">
+      <c r="AE8" s="11" t="n">
         <v>0.04649493840859896</v>
       </c>
-      <c r="AB8" s="8" t="n">
+      <c r="AF8" s="8" t="n">
         <v>43295573</v>
       </c>
-      <c r="AC8" s="9" t="n">
+      <c r="AG8" s="9" t="n">
         <v>582455.34</v>
       </c>
-      <c r="AD8" s="10" t="n">
+      <c r="AH8" s="10" t="n">
         <v>0.0463</v>
       </c>
-      <c r="AE8" s="11" t="n">
+      <c r="AI8" s="11" t="n">
         <v>0.02558297621590971</v>
       </c>
-      <c r="AF8" s="8" t="n">
+      <c r="AJ8" s="8" t="n">
         <v>42215573</v>
       </c>
-      <c r="AG8" s="9" t="n">
+      <c r="AK8" s="9" t="n">
         <v>569065.92</v>
       </c>
-      <c r="AH8" s="10" t="n">
+      <c r="AL8" s="10" t="n">
         <v>0.0475</v>
       </c>
-      <c r="AI8" s="11" t="n">
+      <c r="AM8" s="11" t="n">
         <v>0.03671439253646495</v>
       </c>
-      <c r="AJ8" s="8" t="n">
+      <c r="AN8" s="8" t="n">
         <v>40720543</v>
       </c>
-      <c r="AK8" s="9" t="n">
+      <c r="AO8" s="9" t="n">
         <v>569191.75</v>
       </c>
-      <c r="AL8" s="10" t="n">
+      <c r="AP8" s="10" t="n">
         <v>0.0495</v>
       </c>
-      <c r="AM8" s="11" t="n">
+      <c r="AQ8" s="11" t="n">
         <v>0.02815262499999053</v>
       </c>
-      <c r="AN8" s="8" t="n">
+      <c r="AR8" s="8" t="n">
         <v>39605543</v>
       </c>
-      <c r="AO8" s="9" t="n">
+      <c r="AS8" s="9" t="n">
         <v>586716.51</v>
       </c>
-      <c r="AP8" s="10" t="n">
+      <c r="AT8" s="10" t="n">
         <v>0.0518</v>
       </c>
-      <c r="AQ8" s="11" t="n">
+      <c r="AU8" s="11" t="n">
         <v>0.08540125861519442</v>
       </c>
-      <c r="AR8" s="8" t="n">
+      <c r="AV8" s="8" t="n">
         <v>36489310</v>
       </c>
-      <c r="AS8" s="9" t="n">
+      <c r="AW8" s="9" t="n">
         <v>527562.4399999999</v>
       </c>
-      <c r="AT8" s="10" t="n">
+      <c r="AX8" s="10" t="n">
         <v>0.0478</v>
       </c>
-      <c r="AU8" s="11" t="n">
+      <c r="AY8" s="11" t="n">
         <v>0.04294684214648178</v>
-      </c>
-      <c r="AV8" s="8" t="n">
-        <v>34986740</v>
-      </c>
-      <c r="AW8" s="9" t="n">
-        <v>505838.29</v>
-      </c>
-      <c r="AX8" s="10" t="n">
-        <v>0.0487</v>
-      </c>
-      <c r="AY8" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="AZ8" s="8" t="n">
         <v>34986740</v>
       </c>
       <c r="BA8" s="9" t="n">
-        <v>499260.78</v>
+        <v>505838.29</v>
       </c>
       <c r="BB8" s="10" t="n">
-        <v>0.0507</v>
+        <v>0.0487</v>
       </c>
       <c r="BC8" s="11" t="n">
         <v>0</v>
@@ -2109,10 +2193,10 @@
         <v>34986740</v>
       </c>
       <c r="BE8" s="9" t="n">
-        <v>471743.71</v>
+        <v>499260.78</v>
       </c>
       <c r="BF8" s="10" t="n">
-        <v>0.0505</v>
+        <v>0.0507</v>
       </c>
       <c r="BG8" s="11" t="n">
         <v>0</v>
@@ -2121,10 +2205,10 @@
         <v>34986740</v>
       </c>
       <c r="BI8" s="9" t="n">
-        <v>421275.34</v>
+        <v>471743.71</v>
       </c>
       <c r="BJ8" s="10" t="n">
-        <v>0.0479</v>
+        <v>0.0505</v>
       </c>
       <c r="BK8" s="11" t="n">
         <v>0</v>
@@ -2133,12 +2217,24 @@
         <v>34986740</v>
       </c>
       <c r="BM8" s="9" t="n">
+        <v>421275.34</v>
+      </c>
+      <c r="BN8" s="10" t="n">
+        <v>0.0479</v>
+      </c>
+      <c r="BO8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" s="8" t="n">
+        <v>34986740</v>
+      </c>
+      <c r="BQ8" s="9" t="n">
         <v>438313.88</v>
       </c>
-      <c r="BN8" s="10" t="n">
+      <c r="BR8" s="10" t="n">
         <v>0.0489</v>
       </c>
-      <c r="BO8" s="11" t="n"/>
+      <c r="BS8" s="11" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -2157,73 +2253,73 @@
         </is>
       </c>
       <c r="D9" s="8" t="n">
+        <v>6115824</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>633660.52</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>0.0448</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>0.010087623824352</v>
+      </c>
+      <c r="H9" s="8" t="n">
         <v>6054746</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="I9" s="9" t="n">
         <v>621640.77</v>
       </c>
-      <c r="F9" s="10" t="n">
+      <c r="J9" s="10" t="n">
         <v>0.0441</v>
       </c>
-      <c r="G9" s="11" t="n">
+      <c r="K9" s="11" t="n">
         <v>0.004632287498498381</v>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>6026828</v>
-      </c>
-      <c r="I9" s="9" t="n">
-        <v>527106.38</v>
-      </c>
-      <c r="J9" s="10" t="n">
-        <v>0.0409</v>
-      </c>
-      <c r="K9" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="L9" s="8" t="n">
         <v>6026828</v>
       </c>
       <c r="M9" s="9" t="n">
+        <v>527106.38</v>
+      </c>
+      <c r="N9" s="10" t="n">
+        <v>0.0409</v>
+      </c>
+      <c r="O9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="8" t="n">
+        <v>6026828</v>
+      </c>
+      <c r="Q9" s="9" t="n">
         <v>651138.5</v>
       </c>
-      <c r="N9" s="10" t="n">
+      <c r="R9" s="10" t="n">
         <v>0.0485</v>
       </c>
-      <c r="O9" s="11" t="n">
+      <c r="S9" s="11" t="n">
         <v>0.007956679538397187</v>
       </c>
-      <c r="P9" s="8" t="n">
+      <c r="T9" s="8" t="n">
         <v>5979253</v>
       </c>
-      <c r="Q9" s="9" t="n">
+      <c r="U9" s="9" t="n">
         <v>645759.3199999999</v>
       </c>
-      <c r="R9" s="10" t="n">
+      <c r="V9" s="10" t="n">
         <v>0.0482</v>
       </c>
-      <c r="S9" s="11" t="n">
+      <c r="W9" s="11" t="n">
         <v>0.124148370025633</v>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v>5318918</v>
-      </c>
-      <c r="U9" s="9" t="n">
-        <v>602527.03</v>
-      </c>
-      <c r="V9" s="10" t="n">
-        <v>0.0452</v>
-      </c>
-      <c r="W9" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="X9" s="8" t="n">
         <v>5318918</v>
       </c>
       <c r="Y9" s="9" t="n">
-        <v>611622.38</v>
+        <v>602527.03</v>
       </c>
       <c r="Z9" s="10" t="n">
-        <v>0.0471</v>
+        <v>0.0452</v>
       </c>
       <c r="AA9" s="11" t="n">
         <v>0</v>
@@ -2232,10 +2328,10 @@
         <v>5318918</v>
       </c>
       <c r="AC9" s="9" t="n">
-        <v>654386.48</v>
+        <v>611622.38</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>0.052</v>
+        <v>0.0471</v>
       </c>
       <c r="AE9" s="11" t="n">
         <v>0</v>
@@ -2244,10 +2340,10 @@
         <v>5318918</v>
       </c>
       <c r="AG9" s="9" t="n">
-        <v>651407.89</v>
+        <v>654386.48</v>
       </c>
       <c r="AH9" s="10" t="n">
-        <v>0.0544</v>
+        <v>0.052</v>
       </c>
       <c r="AI9" s="11" t="n">
         <v>0</v>
@@ -2256,10 +2352,10 @@
         <v>5318918</v>
       </c>
       <c r="AK9" s="9" t="n">
-        <v>679225.83</v>
+        <v>651407.89</v>
       </c>
       <c r="AL9" s="10" t="n">
-        <v>0.059</v>
+        <v>0.0544</v>
       </c>
       <c r="AM9" s="11" t="n">
         <v>0</v>
@@ -2268,10 +2364,10 @@
         <v>5318918</v>
       </c>
       <c r="AO9" s="9" t="n">
-        <v>742680.52</v>
+        <v>679225.83</v>
       </c>
       <c r="AP9" s="10" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.059</v>
       </c>
       <c r="AQ9" s="11" t="n">
         <v>0</v>
@@ -2280,10 +2376,10 @@
         <v>5318918</v>
       </c>
       <c r="AS9" s="9" t="n">
-        <v>764807.22</v>
+        <v>742680.52</v>
       </c>
       <c r="AT9" s="10" t="n">
-        <v>0.0693</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="AU9" s="11" t="n">
         <v>0</v>
@@ -2292,10 +2388,10 @@
         <v>5318918</v>
       </c>
       <c r="AW9" s="9" t="n">
-        <v>713479.66</v>
+        <v>764807.22</v>
       </c>
       <c r="AX9" s="10" t="n">
-        <v>0.0687</v>
+        <v>0.0693</v>
       </c>
       <c r="AY9" s="11" t="n">
         <v>0</v>
@@ -2304,10 +2400,10 @@
         <v>5318918</v>
       </c>
       <c r="BA9" s="9" t="n">
-        <v>636834.05</v>
+        <v>713479.66</v>
       </c>
       <c r="BB9" s="10" t="n">
-        <v>0.0646</v>
+        <v>0.0687</v>
       </c>
       <c r="BC9" s="11" t="n">
         <v>0</v>
@@ -2316,10 +2412,10 @@
         <v>5318918</v>
       </c>
       <c r="BE9" s="9" t="n">
-        <v>663431.3</v>
+        <v>636834.05</v>
       </c>
       <c r="BF9" s="10" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.0646</v>
       </c>
       <c r="BG9" s="11" t="n">
         <v>0</v>
@@ -2328,10 +2424,10 @@
         <v>5318918</v>
       </c>
       <c r="BI9" s="9" t="n">
-        <v>615630.1899999999</v>
+        <v>663431.3</v>
       </c>
       <c r="BJ9" s="10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="BK9" s="11" t="n">
         <v>0</v>
@@ -2340,12 +2436,24 @@
         <v>5318918</v>
       </c>
       <c r="BM9" s="9" t="n">
+        <v>615630.1899999999</v>
+      </c>
+      <c r="BN9" s="10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BO9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP9" s="8" t="n">
+        <v>5318918</v>
+      </c>
+      <c r="BQ9" s="9" t="n">
         <v>614850.96</v>
       </c>
-      <c r="BN9" s="10" t="n">
+      <c r="BR9" s="10" t="n">
         <v>0.06850000000000001</v>
       </c>
-      <c r="BO9" s="11" t="n"/>
+      <c r="BS9" s="11" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -2364,57 +2472,65 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
+        <v>151839325</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>583366.6899999999</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>0.0412</v>
+      </c>
+      <c r="G10" s="11" t="n">
+        <v>0.02359455255711862</v>
+      </c>
+      <c r="H10" s="8" t="n">
         <v>148339325</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="I10" s="9" t="n">
         <v>568584.63</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="J10" s="10" t="n">
         <v>0.0403</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="K10" s="11" t="n">
         <v>0.01180948837975782</v>
       </c>
-      <c r="H10" s="8" t="n">
+      <c r="L10" s="8" t="n">
         <v>146607960</v>
       </c>
-      <c r="I10" s="9" t="n">
+      <c r="M10" s="9" t="n">
         <v>518112.53</v>
       </c>
-      <c r="J10" s="10" t="n">
+      <c r="N10" s="10" t="n">
         <v>0.0402</v>
       </c>
-      <c r="K10" s="11" t="n">
+      <c r="O10" s="11" t="n">
         <v>0.1908893624750179</v>
-      </c>
-      <c r="L10" s="8" t="n">
-        <v>123107960</v>
-      </c>
-      <c r="M10" s="9" t="n">
-        <v>511144.25</v>
-      </c>
-      <c r="N10" s="10" t="n">
-        <v>0.0381</v>
-      </c>
-      <c r="O10" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="P10" s="8" t="n">
         <v>123107960</v>
       </c>
       <c r="Q10" s="9" t="n">
+        <v>511144.25</v>
+      </c>
+      <c r="R10" s="10" t="n">
+        <v>0.0381</v>
+      </c>
+      <c r="S10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v>123107960</v>
+      </c>
+      <c r="U10" s="9" t="n">
         <v>502280.48</v>
       </c>
-      <c r="R10" s="10" t="n">
+      <c r="V10" s="10" t="n">
         <v>0.0375</v>
       </c>
-      <c r="S10" s="11" t="n">
+      <c r="W10" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="T10" s="8" t="n"/>
-      <c r="U10" s="9" t="n"/>
-      <c r="V10" s="10" t="n"/>
-      <c r="W10" s="11" t="n"/>
       <c r="X10" s="8" t="n"/>
       <c r="Y10" s="9" t="n"/>
       <c r="Z10" s="10" t="n"/>
@@ -2459,420 +2575,448 @@
       <c r="BM10" s="9" t="n"/>
       <c r="BN10" s="10" t="n"/>
       <c r="BO10" s="11" t="n"/>
+      <c r="BP10" s="8" t="n"/>
+      <c r="BQ10" s="9" t="n"/>
+      <c r="BR10" s="10" t="n"/>
+      <c r="BS10" s="11" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Mahindra &amp; Mahindra Limited</t>
+          <t>HCL Technologies Limited</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>INE101A01026</t>
+          <t>INE860A01027</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Automobiles</t>
+          <t>IT - Software</t>
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>16026000</v>
+        <v>42972063</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>496405.35</v>
+        <v>508703.28</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.0352</v>
+        <v>0.036</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>0.0942516216104385</v>
+        <v>0.0663049542834704</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>14645626</v>
+        <v>40299975</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>432734.31</v>
+        <v>483237</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>0.0336</v>
+        <v>0.0343</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>0.04800817189604804</v>
+        <v>0.3492279063625878</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>13974725</v>
+        <v>29868916</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>474777.31</v>
+        <v>400721.38</v>
       </c>
       <c r="N11" s="10" t="n">
-        <v>0.0354</v>
+        <v>0.0311</v>
       </c>
       <c r="O11" s="11" t="n">
-        <v>0</v>
+        <v>0.07551780932368431</v>
       </c>
       <c r="P11" s="8" t="n">
-        <v>13974725</v>
+        <v>27771661</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>479584.61</v>
+        <v>385776.14</v>
       </c>
       <c r="R11" s="10" t="n">
-        <v>0.0358</v>
+        <v>0.0287</v>
       </c>
       <c r="S11" s="11" t="n">
-        <v>0.07221829643218575</v>
+        <v>0.1837798947287478</v>
       </c>
       <c r="T11" s="8" t="n">
-        <v>13033470</v>
+        <v>23460156</v>
       </c>
       <c r="U11" s="9" t="n">
-        <v>483437.47</v>
+        <v>397790.41</v>
       </c>
       <c r="V11" s="10" t="n">
-        <v>0.0363</v>
+        <v>0.0297</v>
       </c>
       <c r="W11" s="11" t="n">
-        <v>0.0480713103458591</v>
+        <v>0.1005951337129751</v>
       </c>
       <c r="X11" s="8" t="n">
-        <v>12435671</v>
+        <v>21315882</v>
       </c>
       <c r="Y11" s="9" t="n">
-        <v>467245.47</v>
+        <v>346020.71</v>
       </c>
       <c r="Z11" s="10" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="AA11" s="11" t="n">
+        <v>0.07485632112907131</v>
+      </c>
+      <c r="AB11" s="8" t="n">
+        <v>19831378</v>
+      </c>
+      <c r="AC11" s="9" t="n">
+        <v>322101.24</v>
+      </c>
+      <c r="AD11" s="10" t="n">
+        <v>0.0248</v>
+      </c>
+      <c r="AE11" s="11" t="n">
+        <v>0.09330382775845011</v>
+      </c>
+      <c r="AF11" s="8" t="n">
+        <v>18138945</v>
+      </c>
+      <c r="AG11" s="9" t="n">
+        <v>279611.84</v>
+      </c>
+      <c r="AH11" s="10" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="AI11" s="11" t="n">
+        <v>-0.0303656466471499</v>
+      </c>
+      <c r="AJ11" s="8" t="n">
+        <v>18706995</v>
+      </c>
+      <c r="AK11" s="9" t="n">
+        <v>259110.59</v>
+      </c>
+      <c r="AL11" s="10" t="n">
+        <v>0.0216</v>
+      </c>
+      <c r="AM11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" s="8" t="n">
+        <v>18706995</v>
+      </c>
+      <c r="AO11" s="9" t="n">
+        <v>272149.36</v>
+      </c>
+      <c r="AP11" s="10" t="n">
+        <v>0.0237</v>
+      </c>
+      <c r="AQ11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="8" t="n">
+        <v>18706995</v>
+      </c>
+      <c r="AS11" s="9" t="n">
+        <v>274599.98</v>
+      </c>
+      <c r="AT11" s="10" t="n">
+        <v>0.0242</v>
+      </c>
+      <c r="AU11" s="11" t="n">
+        <v>0.00797456974367416</v>
+      </c>
+      <c r="AV11" s="8" t="n">
+        <v>18558995</v>
+      </c>
+      <c r="AW11" s="9" t="n">
+        <v>320810.79</v>
+      </c>
+      <c r="AX11" s="10" t="n">
+        <v>0.0291</v>
+      </c>
+      <c r="AY11" s="11" t="n">
+        <v>0.01185405417517898</v>
+      </c>
+      <c r="AZ11" s="8" t="n">
+        <v>18341573</v>
+      </c>
+      <c r="BA11" s="9" t="n">
+        <v>300178.18</v>
+      </c>
+      <c r="BB11" s="10" t="n">
+        <v>0.0289</v>
+      </c>
+      <c r="BC11" s="11" t="n">
+        <v>-0.01953282340226823</v>
+      </c>
+      <c r="BD11" s="8" t="n">
+        <v>18706973</v>
+      </c>
+      <c r="BE11" s="9" t="n">
+        <v>293231.8</v>
+      </c>
+      <c r="BF11" s="10" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="BG11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH11" s="8" t="n">
+        <v>18706973</v>
+      </c>
+      <c r="BI11" s="9" t="n">
+        <v>297908.55</v>
+      </c>
+      <c r="BJ11" s="10" t="n">
+        <v>0.0319</v>
+      </c>
+      <c r="BK11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL11" s="8" t="n">
+        <v>18706973</v>
+      </c>
+      <c r="BM11" s="9" t="n">
+        <v>294644.18</v>
+      </c>
+      <c r="BN11" s="10" t="n">
+        <v>0.0335</v>
+      </c>
+      <c r="BO11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP11" s="8" t="n">
+        <v>18706973</v>
+      </c>
+      <c r="BQ11" s="9" t="n">
+        <v>322779.47</v>
+      </c>
+      <c r="BR11" s="10" t="n">
         <v>0.036</v>
       </c>
-      <c r="AA11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="8" t="n">
-        <v>12435671</v>
-      </c>
-      <c r="AC11" s="9" t="n">
-        <v>433656.72</v>
-      </c>
-      <c r="AD11" s="10" t="n">
-        <v>0.0345</v>
-      </c>
-      <c r="AE11" s="11" t="n">
-        <v>0.008106571584148119</v>
-      </c>
-      <c r="AF11" s="8" t="n">
-        <v>12335671</v>
-      </c>
-      <c r="AG11" s="9" t="n">
-        <v>422743.45</v>
-      </c>
-      <c r="AH11" s="10" t="n">
-        <v>0.0353</v>
-      </c>
-      <c r="AI11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" s="8" t="n">
-        <v>12335671</v>
-      </c>
-      <c r="AK11" s="9" t="n">
-        <v>394679.79</v>
-      </c>
-      <c r="AL11" s="10" t="n">
-        <v>0.0343</v>
-      </c>
-      <c r="AM11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN11" s="8" t="n">
-        <v>12335671</v>
-      </c>
-      <c r="AO11" s="9" t="n">
-        <v>395123.88</v>
-      </c>
-      <c r="AP11" s="10" t="n">
-        <v>0.0349</v>
-      </c>
-      <c r="AQ11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" s="8" t="n">
-        <v>12335671</v>
-      </c>
-      <c r="AS11" s="9" t="n">
-        <v>392669.08</v>
-      </c>
-      <c r="AT11" s="10" t="n">
-        <v>0.0356</v>
-      </c>
-      <c r="AU11" s="11" t="n">
-        <v>0.00852700604200313</v>
-      </c>
-      <c r="AV11" s="8" t="n">
-        <v>12231374</v>
-      </c>
-      <c r="AW11" s="9" t="n">
-        <v>364103.54</v>
-      </c>
-      <c r="AX11" s="10" t="n">
-        <v>0.0351</v>
-      </c>
-      <c r="AY11" s="11" t="n">
-        <v>0.1078930368366115</v>
-      </c>
-      <c r="AZ11" s="8" t="n">
-        <v>11040212</v>
-      </c>
-      <c r="BA11" s="9" t="n">
-        <v>323345.73</v>
-      </c>
-      <c r="BB11" s="10" t="n">
-        <v>0.0328</v>
-      </c>
-      <c r="BC11" s="11" t="n">
-        <v>0.06163142499453569</v>
-      </c>
-      <c r="BD11" s="8" t="n">
-        <v>10399289</v>
-      </c>
-      <c r="BE11" s="9" t="n">
-        <v>277224.25</v>
-      </c>
-      <c r="BF11" s="10" t="n">
-        <v>0.0297</v>
-      </c>
-      <c r="BG11" s="11" t="n">
-        <v>0.03283692525275198</v>
-      </c>
-      <c r="BH11" s="8" t="n">
-        <v>10068665</v>
-      </c>
-      <c r="BI11" s="9" t="n">
-        <v>260285.06</v>
-      </c>
-      <c r="BJ11" s="10" t="n">
-        <v>0.0296</v>
-      </c>
-      <c r="BK11" s="11" t="n">
-        <v>0.07897007813229198</v>
-      </c>
-      <c r="BL11" s="8" t="n">
-        <v>9331737</v>
-      </c>
-      <c r="BM11" s="9" t="n">
-        <v>279004.94</v>
-      </c>
-      <c r="BN11" s="10" t="n">
-        <v>0.0311</v>
-      </c>
-      <c r="BO11" s="11" t="n"/>
+      <c r="BS11" s="11" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>HCL Technologies Limited</t>
+          <t>Mahindra &amp; Mahindra Limited</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>INE860A01027</t>
+          <t>INE101A01026</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>IT - Software</t>
+          <t>Automobiles</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>40299975</v>
+        <v>16039400</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>483237</v>
+        <v>488495.97</v>
       </c>
       <c r="F12" s="10" t="n">
+        <v>0.0345</v>
+      </c>
+      <c r="G12" s="11" t="n">
+        <v>0.0008361412704355422</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>16026000</v>
+      </c>
+      <c r="I12" s="9" t="n">
+        <v>496405.35</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>0.0352</v>
+      </c>
+      <c r="K12" s="11" t="n">
+        <v>0.0942516216104385</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>14645626</v>
+      </c>
+      <c r="M12" s="9" t="n">
+        <v>432734.31</v>
+      </c>
+      <c r="N12" s="10" t="n">
+        <v>0.0336</v>
+      </c>
+      <c r="O12" s="11" t="n">
+        <v>0.04800817189604804</v>
+      </c>
+      <c r="P12" s="8" t="n">
+        <v>13974725</v>
+      </c>
+      <c r="Q12" s="9" t="n">
+        <v>474777.31</v>
+      </c>
+      <c r="R12" s="10" t="n">
+        <v>0.0354</v>
+      </c>
+      <c r="S12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v>13974725</v>
+      </c>
+      <c r="U12" s="9" t="n">
+        <v>479584.61</v>
+      </c>
+      <c r="V12" s="10" t="n">
+        <v>0.0358</v>
+      </c>
+      <c r="W12" s="11" t="n">
+        <v>0.07221829643218575</v>
+      </c>
+      <c r="X12" s="8" t="n">
+        <v>13033470</v>
+      </c>
+      <c r="Y12" s="9" t="n">
+        <v>483437.47</v>
+      </c>
+      <c r="Z12" s="10" t="n">
+        <v>0.0363</v>
+      </c>
+      <c r="AA12" s="11" t="n">
+        <v>0.0480713103458591</v>
+      </c>
+      <c r="AB12" s="8" t="n">
+        <v>12435671</v>
+      </c>
+      <c r="AC12" s="9" t="n">
+        <v>467245.47</v>
+      </c>
+      <c r="AD12" s="10" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="AE12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="8" t="n">
+        <v>12435671</v>
+      </c>
+      <c r="AG12" s="9" t="n">
+        <v>433656.72</v>
+      </c>
+      <c r="AH12" s="10" t="n">
+        <v>0.0345</v>
+      </c>
+      <c r="AI12" s="11" t="n">
+        <v>0.008106571584148119</v>
+      </c>
+      <c r="AJ12" s="8" t="n">
+        <v>12335671</v>
+      </c>
+      <c r="AK12" s="9" t="n">
+        <v>422743.45</v>
+      </c>
+      <c r="AL12" s="10" t="n">
+        <v>0.0353</v>
+      </c>
+      <c r="AM12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="8" t="n">
+        <v>12335671</v>
+      </c>
+      <c r="AO12" s="9" t="n">
+        <v>394679.79</v>
+      </c>
+      <c r="AP12" s="10" t="n">
         <v>0.0343</v>
       </c>
-      <c r="G12" s="11" t="n">
-        <v>0.3492279063625878</v>
-      </c>
-      <c r="H12" s="8" t="n">
-        <v>29868916</v>
-      </c>
-      <c r="I12" s="9" t="n">
-        <v>400721.38</v>
-      </c>
-      <c r="J12" s="10" t="n">
+      <c r="AQ12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" s="8" t="n">
+        <v>12335671</v>
+      </c>
+      <c r="AS12" s="9" t="n">
+        <v>395123.88</v>
+      </c>
+      <c r="AT12" s="10" t="n">
+        <v>0.0349</v>
+      </c>
+      <c r="AU12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" s="8" t="n">
+        <v>12335671</v>
+      </c>
+      <c r="AW12" s="9" t="n">
+        <v>392669.08</v>
+      </c>
+      <c r="AX12" s="10" t="n">
+        <v>0.0356</v>
+      </c>
+      <c r="AY12" s="11" t="n">
+        <v>0.00852700604200313</v>
+      </c>
+      <c r="AZ12" s="8" t="n">
+        <v>12231374</v>
+      </c>
+      <c r="BA12" s="9" t="n">
+        <v>364103.54</v>
+      </c>
+      <c r="BB12" s="10" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="BC12" s="11" t="n">
+        <v>0.1078930368366115</v>
+      </c>
+      <c r="BD12" s="8" t="n">
+        <v>11040212</v>
+      </c>
+      <c r="BE12" s="9" t="n">
+        <v>323345.73</v>
+      </c>
+      <c r="BF12" s="10" t="n">
+        <v>0.0328</v>
+      </c>
+      <c r="BG12" s="11" t="n">
+        <v>0.06163142499453569</v>
+      </c>
+      <c r="BH12" s="8" t="n">
+        <v>10399289</v>
+      </c>
+      <c r="BI12" s="9" t="n">
+        <v>277224.25</v>
+      </c>
+      <c r="BJ12" s="10" t="n">
+        <v>0.0297</v>
+      </c>
+      <c r="BK12" s="11" t="n">
+        <v>0.03283692525275198</v>
+      </c>
+      <c r="BL12" s="8" t="n">
+        <v>10068665</v>
+      </c>
+      <c r="BM12" s="9" t="n">
+        <v>260285.06</v>
+      </c>
+      <c r="BN12" s="10" t="n">
+        <v>0.0296</v>
+      </c>
+      <c r="BO12" s="11" t="n">
+        <v>0.07897007813229198</v>
+      </c>
+      <c r="BP12" s="8" t="n">
+        <v>9331737</v>
+      </c>
+      <c r="BQ12" s="9" t="n">
+        <v>279004.94</v>
+      </c>
+      <c r="BR12" s="10" t="n">
         <v>0.0311</v>
       </c>
-      <c r="K12" s="11" t="n">
-        <v>0.07551780932368431</v>
-      </c>
-      <c r="L12" s="8" t="n">
-        <v>27771661</v>
-      </c>
-      <c r="M12" s="9" t="n">
-        <v>385776.14</v>
-      </c>
-      <c r="N12" s="10" t="n">
-        <v>0.0287</v>
-      </c>
-      <c r="O12" s="11" t="n">
-        <v>0.1837798947287478</v>
-      </c>
-      <c r="P12" s="8" t="n">
-        <v>23460156</v>
-      </c>
-      <c r="Q12" s="9" t="n">
-        <v>397790.41</v>
-      </c>
-      <c r="R12" s="10" t="n">
-        <v>0.0297</v>
-      </c>
-      <c r="S12" s="11" t="n">
-        <v>0.1005951337129751</v>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v>21315882</v>
-      </c>
-      <c r="U12" s="9" t="n">
-        <v>346020.71</v>
-      </c>
-      <c r="V12" s="10" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="W12" s="11" t="n">
-        <v>0.07485632112907131</v>
-      </c>
-      <c r="X12" s="8" t="n">
-        <v>19831378</v>
-      </c>
-      <c r="Y12" s="9" t="n">
-        <v>322101.24</v>
-      </c>
-      <c r="Z12" s="10" t="n">
-        <v>0.0248</v>
-      </c>
-      <c r="AA12" s="11" t="n">
-        <v>0.09330382775845011</v>
-      </c>
-      <c r="AB12" s="8" t="n">
-        <v>18138945</v>
-      </c>
-      <c r="AC12" s="9" t="n">
-        <v>279611.84</v>
-      </c>
-      <c r="AD12" s="10" t="n">
-        <v>0.0222</v>
-      </c>
-      <c r="AE12" s="11" t="n">
-        <v>-0.0303656466471499</v>
-      </c>
-      <c r="AF12" s="8" t="n">
-        <v>18706995</v>
-      </c>
-      <c r="AG12" s="9" t="n">
-        <v>259110.59</v>
-      </c>
-      <c r="AH12" s="10" t="n">
-        <v>0.0216</v>
-      </c>
-      <c r="AI12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" s="8" t="n">
-        <v>18706995</v>
-      </c>
-      <c r="AK12" s="9" t="n">
-        <v>272149.36</v>
-      </c>
-      <c r="AL12" s="10" t="n">
-        <v>0.0237</v>
-      </c>
-      <c r="AM12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" s="8" t="n">
-        <v>18706995</v>
-      </c>
-      <c r="AO12" s="9" t="n">
-        <v>274599.98</v>
-      </c>
-      <c r="AP12" s="10" t="n">
-        <v>0.0242</v>
-      </c>
-      <c r="AQ12" s="11" t="n">
-        <v>0.00797456974367416</v>
-      </c>
-      <c r="AR12" s="8" t="n">
-        <v>18558995</v>
-      </c>
-      <c r="AS12" s="9" t="n">
-        <v>320810.79</v>
-      </c>
-      <c r="AT12" s="10" t="n">
-        <v>0.0291</v>
-      </c>
-      <c r="AU12" s="11" t="n">
-        <v>0.01185405417517898</v>
-      </c>
-      <c r="AV12" s="8" t="n">
-        <v>18341573</v>
-      </c>
-      <c r="AW12" s="9" t="n">
-        <v>300178.18</v>
-      </c>
-      <c r="AX12" s="10" t="n">
-        <v>0.0289</v>
-      </c>
-      <c r="AY12" s="11" t="n">
-        <v>-0.01953282340226823</v>
-      </c>
-      <c r="AZ12" s="8" t="n">
-        <v>18706973</v>
-      </c>
-      <c r="BA12" s="9" t="n">
-        <v>293231.8</v>
-      </c>
-      <c r="BB12" s="10" t="n">
-        <v>0.0298</v>
-      </c>
-      <c r="BC12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD12" s="8" t="n">
-        <v>18706973</v>
-      </c>
-      <c r="BE12" s="9" t="n">
-        <v>297908.55</v>
-      </c>
-      <c r="BF12" s="10" t="n">
-        <v>0.0319</v>
-      </c>
-      <c r="BG12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH12" s="8" t="n">
-        <v>18706973</v>
-      </c>
-      <c r="BI12" s="9" t="n">
-        <v>294644.18</v>
-      </c>
-      <c r="BJ12" s="10" t="n">
-        <v>0.0335</v>
-      </c>
-      <c r="BK12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL12" s="8" t="n">
-        <v>18706973</v>
-      </c>
-      <c r="BM12" s="9" t="n">
-        <v>322779.47</v>
-      </c>
-      <c r="BN12" s="10" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="BO12" s="11" t="n"/>
+      <c r="BS12" s="11" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -2891,97 +3035,97 @@
         </is>
       </c>
       <c r="D13" s="8" t="n">
+        <v>37339573</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>433475.1</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>0.0306</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>0.03234486242202376</v>
+      </c>
+      <c r="H13" s="8" t="n">
         <v>36169670</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="I13" s="9" t="n">
         <v>427453.16</v>
       </c>
-      <c r="F13" s="10" t="n">
+      <c r="J13" s="10" t="n">
         <v>0.0303</v>
       </c>
-      <c r="G13" s="11" t="n">
+      <c r="K13" s="11" t="n">
         <v>0.342400003741088</v>
       </c>
-      <c r="H13" s="8" t="n">
+      <c r="L13" s="8" t="n">
         <v>26944033</v>
       </c>
-      <c r="I13" s="9" t="n">
+      <c r="M13" s="9" t="n">
         <v>336962.08</v>
       </c>
-      <c r="J13" s="10" t="n">
+      <c r="N13" s="10" t="n">
         <v>0.0261</v>
       </c>
-      <c r="K13" s="11" t="n">
+      <c r="O13" s="11" t="n">
         <v>0.302041511993854</v>
       </c>
-      <c r="L13" s="8" t="n">
+      <c r="P13" s="8" t="n">
         <v>20693682</v>
       </c>
-      <c r="M13" s="9" t="n">
+      <c r="Q13" s="9" t="n">
         <v>269038.56</v>
       </c>
-      <c r="N13" s="10" t="n">
+      <c r="R13" s="10" t="n">
         <v>0.02</v>
       </c>
-      <c r="O13" s="11" t="n">
+      <c r="S13" s="11" t="n">
         <v>0.2534377545687067</v>
       </c>
-      <c r="P13" s="8" t="n">
+      <c r="T13" s="8" t="n">
         <v>16509541</v>
       </c>
-      <c r="Q13" s="9" t="n">
+      <c r="U13" s="9" t="n">
         <v>270921.57</v>
       </c>
-      <c r="R13" s="10" t="n">
+      <c r="V13" s="10" t="n">
         <v>0.0202</v>
       </c>
-      <c r="S13" s="11" t="n">
+      <c r="W13" s="11" t="n">
         <v>0.005579568588889614</v>
       </c>
-      <c r="T13" s="8" t="n">
+      <c r="X13" s="8" t="n">
         <v>16417936</v>
       </c>
-      <c r="U13" s="9" t="n">
+      <c r="Y13" s="9" t="n">
         <v>265215.34</v>
       </c>
-      <c r="V13" s="10" t="n">
+      <c r="Z13" s="10" t="n">
         <v>0.0199</v>
       </c>
-      <c r="W13" s="11" t="n">
+      <c r="AA13" s="11" t="n">
         <v>-0.06831357175852101</v>
       </c>
-      <c r="X13" s="8" t="n">
+      <c r="AB13" s="8" t="n">
         <v>17621740</v>
       </c>
-      <c r="Y13" s="9" t="n">
+      <c r="AC13" s="9" t="n">
         <v>274916.77</v>
       </c>
-      <c r="Z13" s="10" t="n">
+      <c r="AD13" s="10" t="n">
         <v>0.0212</v>
       </c>
-      <c r="AA13" s="11" t="n">
+      <c r="AE13" s="11" t="n">
         <v>0.8934928409505942</v>
-      </c>
-      <c r="AB13" s="8" t="n">
-        <v>9306473</v>
-      </c>
-      <c r="AC13" s="9" t="n">
-        <v>137949.85</v>
-      </c>
-      <c r="AD13" s="10" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="AE13" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="AF13" s="8" t="n">
         <v>9306473</v>
       </c>
       <c r="AG13" s="9" t="n">
-        <v>134180.73</v>
+        <v>137949.85</v>
       </c>
       <c r="AH13" s="10" t="n">
-        <v>0.0112</v>
+        <v>0.011</v>
       </c>
       <c r="AI13" s="11" t="n">
         <v>0</v>
@@ -2990,10 +3134,10 @@
         <v>9306473</v>
       </c>
       <c r="AK13" s="9" t="n">
-        <v>136767.93</v>
+        <v>134180.73</v>
       </c>
       <c r="AL13" s="10" t="n">
-        <v>0.0119</v>
+        <v>0.0112</v>
       </c>
       <c r="AM13" s="11" t="n">
         <v>0</v>
@@ -3002,10 +3146,10 @@
         <v>9306473</v>
       </c>
       <c r="AO13" s="9" t="n">
-        <v>140434.68</v>
+        <v>136767.93</v>
       </c>
       <c r="AP13" s="10" t="n">
-        <v>0.0124</v>
+        <v>0.0119</v>
       </c>
       <c r="AQ13" s="11" t="n">
         <v>0</v>
@@ -3014,10 +3158,10 @@
         <v>9306473</v>
       </c>
       <c r="AS13" s="9" t="n">
-        <v>149071.08</v>
+        <v>140434.68</v>
       </c>
       <c r="AT13" s="10" t="n">
-        <v>0.0135</v>
+        <v>0.0124</v>
       </c>
       <c r="AU13" s="11" t="n">
         <v>0</v>
@@ -3026,10 +3170,10 @@
         <v>9306473</v>
       </c>
       <c r="AW13" s="9" t="n">
-        <v>145432.25</v>
+        <v>149071.08</v>
       </c>
       <c r="AX13" s="10" t="n">
-        <v>0.014</v>
+        <v>0.0135</v>
       </c>
       <c r="AY13" s="11" t="n">
         <v>0</v>
@@ -3038,10 +3182,10 @@
         <v>9306473</v>
       </c>
       <c r="BA13" s="9" t="n">
-        <v>139606.4</v>
+        <v>145432.25</v>
       </c>
       <c r="BB13" s="10" t="n">
-        <v>0.0142</v>
+        <v>0.014</v>
       </c>
       <c r="BC13" s="11" t="n">
         <v>0</v>
@@ -3050,10 +3194,10 @@
         <v>9306473</v>
       </c>
       <c r="BE13" s="9" t="n">
-        <v>146172.12</v>
+        <v>139606.4</v>
       </c>
       <c r="BF13" s="10" t="n">
-        <v>0.0156</v>
+        <v>0.0142</v>
       </c>
       <c r="BG13" s="11" t="n">
         <v>0</v>
@@ -3062,10 +3206,10 @@
         <v>9306473</v>
       </c>
       <c r="BI13" s="9" t="n">
-        <v>157065.34</v>
+        <v>146172.12</v>
       </c>
       <c r="BJ13" s="10" t="n">
-        <v>0.0178</v>
+        <v>0.0156</v>
       </c>
       <c r="BK13" s="11" t="n">
         <v>0</v>
@@ -3074,12 +3218,24 @@
         <v>9306473</v>
       </c>
       <c r="BM13" s="9" t="n">
+        <v>157065.34</v>
+      </c>
+      <c r="BN13" s="10" t="n">
+        <v>0.0178</v>
+      </c>
+      <c r="BO13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP13" s="8" t="n">
+        <v>9306473</v>
+      </c>
+      <c r="BQ13" s="9" t="n">
         <v>174943.08</v>
       </c>
-      <c r="BN13" s="10" t="n">
+      <c r="BR13" s="10" t="n">
         <v>0.0195</v>
       </c>
-      <c r="BO13" s="11" t="n"/>
+      <c r="BS13" s="11" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -3101,10 +3257,10 @@
         <v>33244875</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>421644.75</v>
+        <v>427728.56</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>0.0299</v>
+        <v>0.0302</v>
       </c>
       <c r="G14" s="11" t="n">
         <v>0</v>
@@ -3113,7 +3269,7 @@
         <v>33244875</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>386072.73</v>
+        <v>421644.75</v>
       </c>
       <c r="J14" s="10" t="n">
         <v>0.0299</v>
@@ -3125,10 +3281,10 @@
         <v>33244875</v>
       </c>
       <c r="M14" s="9" t="n">
-        <v>460075.83</v>
+        <v>386072.73</v>
       </c>
       <c r="N14" s="10" t="n">
-        <v>0.0343</v>
+        <v>0.0299</v>
       </c>
       <c r="O14" s="11" t="n">
         <v>0</v>
@@ -3137,10 +3293,10 @@
         <v>33244875</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>455587.77</v>
+        <v>460075.83</v>
       </c>
       <c r="R14" s="10" t="n">
-        <v>0.034</v>
+        <v>0.0343</v>
       </c>
       <c r="S14" s="11" t="n">
         <v>0</v>
@@ -3149,10 +3305,10 @@
         <v>33244875</v>
       </c>
       <c r="U14" s="9" t="n">
-        <v>422010.44</v>
+        <v>455587.77</v>
       </c>
       <c r="V14" s="10" t="n">
-        <v>0.0317</v>
+        <v>0.034</v>
       </c>
       <c r="W14" s="11" t="n">
         <v>0</v>
@@ -3161,10 +3317,10 @@
         <v>33244875</v>
       </c>
       <c r="Y14" s="9" t="n">
-        <v>425434.67</v>
+        <v>422010.44</v>
       </c>
       <c r="Z14" s="10" t="n">
-        <v>0.0328</v>
+        <v>0.0317</v>
       </c>
       <c r="AA14" s="11" t="n">
         <v>0</v>
@@ -3173,10 +3329,10 @@
         <v>33244875</v>
       </c>
       <c r="AC14" s="9" t="n">
-        <v>409842.82</v>
+        <v>425434.67</v>
       </c>
       <c r="AD14" s="10" t="n">
-        <v>0.0326</v>
+        <v>0.0328</v>
       </c>
       <c r="AE14" s="11" t="n">
         <v>0</v>
@@ -3185,58 +3341,58 @@
         <v>33244875</v>
       </c>
       <c r="AG14" s="9" t="n">
+        <v>409842.82</v>
+      </c>
+      <c r="AH14" s="10" t="n">
+        <v>0.0326</v>
+      </c>
+      <c r="AI14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="8" t="n">
+        <v>33244875</v>
+      </c>
+      <c r="AK14" s="9" t="n">
         <v>376199.01</v>
       </c>
-      <c r="AH14" s="10" t="n">
+      <c r="AL14" s="10" t="n">
         <v>0.0314</v>
       </c>
-      <c r="AI14" s="11" t="n">
+      <c r="AM14" s="11" t="n">
         <v>0.01837960782511803</v>
       </c>
-      <c r="AJ14" s="8" t="n">
+      <c r="AN14" s="8" t="n">
         <v>32644875</v>
       </c>
-      <c r="AK14" s="9" t="n">
+      <c r="AO14" s="9" t="n">
         <v>341204.23</v>
       </c>
-      <c r="AL14" s="10" t="n">
+      <c r="AP14" s="10" t="n">
         <v>0.0297</v>
       </c>
-      <c r="AM14" s="11" t="n">
+      <c r="AQ14" s="11" t="n">
         <v>0.0842854566355568</v>
       </c>
-      <c r="AN14" s="8" t="n">
+      <c r="AR14" s="8" t="n">
         <v>30107270</v>
       </c>
-      <c r="AO14" s="9" t="n">
+      <c r="AS14" s="9" t="n">
         <v>321666.07</v>
       </c>
-      <c r="AP14" s="10" t="n">
+      <c r="AT14" s="10" t="n">
         <v>0.0284</v>
       </c>
-      <c r="AQ14" s="11" t="n">
+      <c r="AU14" s="11" t="n">
         <v>0.1045592607036581</v>
-      </c>
-      <c r="AR14" s="8" t="n">
-        <v>27257270</v>
-      </c>
-      <c r="AS14" s="9" t="n">
-        <v>326869.18</v>
-      </c>
-      <c r="AT14" s="10" t="n">
-        <v>0.0296</v>
-      </c>
-      <c r="AU14" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="AV14" s="8" t="n">
         <v>27257270</v>
       </c>
       <c r="AW14" s="9" t="n">
-        <v>324961.17</v>
+        <v>326869.18</v>
       </c>
       <c r="AX14" s="10" t="n">
-        <v>0.0313</v>
+        <v>0.0296</v>
       </c>
       <c r="AY14" s="11" t="n">
         <v>0</v>
@@ -3245,10 +3401,10 @@
         <v>27257270</v>
       </c>
       <c r="BA14" s="9" t="n">
-        <v>322998.65</v>
+        <v>324961.17</v>
       </c>
       <c r="BB14" s="10" t="n">
-        <v>0.0328</v>
+        <v>0.0313</v>
       </c>
       <c r="BC14" s="11" t="n">
         <v>0</v>
@@ -3257,10 +3413,10 @@
         <v>27257270</v>
       </c>
       <c r="BE14" s="9" t="n">
-        <v>300375.12</v>
+        <v>322998.65</v>
       </c>
       <c r="BF14" s="10" t="n">
-        <v>0.0321</v>
+        <v>0.0328</v>
       </c>
       <c r="BG14" s="11" t="n">
         <v>0</v>
@@ -3269,10 +3425,10 @@
         <v>27257270</v>
       </c>
       <c r="BI14" s="9" t="n">
-        <v>276811.21</v>
+        <v>300375.12</v>
       </c>
       <c r="BJ14" s="10" t="n">
-        <v>0.0315</v>
+        <v>0.0321</v>
       </c>
       <c r="BK14" s="11" t="n">
         <v>0</v>
@@ -3281,12 +3437,24 @@
         <v>27257270</v>
       </c>
       <c r="BM14" s="9" t="n">
+        <v>276811.21</v>
+      </c>
+      <c r="BN14" s="10" t="n">
+        <v>0.0315</v>
+      </c>
+      <c r="BO14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP14" s="8" t="n">
+        <v>27257270</v>
+      </c>
+      <c r="BQ14" s="9" t="n">
         <v>268783.94</v>
       </c>
-      <c r="BN14" s="10" t="n">
+      <c r="BR14" s="10" t="n">
         <v>0.03</v>
       </c>
-      <c r="BO14" s="11" t="n"/>
+      <c r="BS14" s="11" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -3308,10 +3476,10 @@
         <v>3039945</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>404738.28</v>
+        <v>399053.58</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.0287</v>
+        <v>0.0282</v>
       </c>
       <c r="G15" s="11" t="n">
         <v>0</v>
@@ -3320,118 +3488,118 @@
         <v>3039945</v>
       </c>
       <c r="I15" s="9" t="n">
+        <v>404738.28</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>0.0287</v>
+      </c>
+      <c r="K15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="8" t="n">
+        <v>3039945</v>
+      </c>
+      <c r="M15" s="9" t="n">
         <v>374095.63</v>
       </c>
-      <c r="J15" s="10" t="n">
+      <c r="N15" s="10" t="n">
         <v>0.029</v>
       </c>
-      <c r="K15" s="11" t="n">
+      <c r="O15" s="11" t="n">
         <v>0.06253145709252579</v>
       </c>
-      <c r="L15" s="8" t="n">
+      <c r="P15" s="8" t="n">
         <v>2861040</v>
       </c>
-      <c r="M15" s="9" t="n">
+      <c r="Q15" s="9" t="n">
         <v>425064.71</v>
       </c>
-      <c r="N15" s="10" t="n">
+      <c r="R15" s="10" t="n">
         <v>0.0317</v>
       </c>
-      <c r="O15" s="11" t="n">
+      <c r="S15" s="11" t="n">
         <v>0.02897415480359852</v>
       </c>
-      <c r="P15" s="8" t="n">
+      <c r="T15" s="8" t="n">
         <v>2780478</v>
       </c>
-      <c r="Q15" s="9" t="n">
+      <c r="U15" s="9" t="n">
         <v>405921.98</v>
       </c>
-      <c r="R15" s="10" t="n">
+      <c r="V15" s="10" t="n">
         <v>0.0303</v>
       </c>
-      <c r="S15" s="11" t="n">
+      <c r="W15" s="11" t="n">
         <v>0.01230872292630713</v>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v>2746670</v>
-      </c>
-      <c r="U15" s="9" t="n">
-        <v>458611.49</v>
-      </c>
-      <c r="V15" s="10" t="n">
-        <v>0.0344</v>
-      </c>
-      <c r="W15" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="X15" s="8" t="n">
         <v>2746670</v>
       </c>
       <c r="Y15" s="9" t="n">
+        <v>458611.49</v>
+      </c>
+      <c r="Z15" s="10" t="n">
+        <v>0.0344</v>
+      </c>
+      <c r="AA15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="8" t="n">
+        <v>2746670</v>
+      </c>
+      <c r="AC15" s="9" t="n">
         <v>436720.53</v>
       </c>
-      <c r="Z15" s="10" t="n">
+      <c r="AD15" s="10" t="n">
         <v>0.0337</v>
       </c>
-      <c r="AA15" s="11" t="n">
+      <c r="AE15" s="11" t="n">
         <v>0.01854138622819997</v>
-      </c>
-      <c r="AB15" s="8" t="n">
-        <v>2696670</v>
-      </c>
-      <c r="AC15" s="9" t="n">
-        <v>436483.01</v>
-      </c>
-      <c r="AD15" s="10" t="n">
-        <v>0.0347</v>
-      </c>
-      <c r="AE15" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="AF15" s="8" t="n">
         <v>2696670</v>
       </c>
       <c r="AG15" s="9" t="n">
+        <v>436483.01</v>
+      </c>
+      <c r="AH15" s="10" t="n">
+        <v>0.0347</v>
+      </c>
+      <c r="AI15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="8" t="n">
+        <v>2696670</v>
+      </c>
+      <c r="AK15" s="9" t="n">
         <v>432249.23</v>
       </c>
-      <c r="AH15" s="10" t="n">
+      <c r="AL15" s="10" t="n">
         <v>0.0361</v>
       </c>
-      <c r="AI15" s="11" t="n">
+      <c r="AM15" s="11" t="n">
         <v>-0.01820386140308082</v>
       </c>
-      <c r="AJ15" s="8" t="n">
+      <c r="AN15" s="8" t="n">
         <v>2746670</v>
       </c>
-      <c r="AK15" s="9" t="n">
+      <c r="AO15" s="9" t="n">
         <v>406259.96</v>
       </c>
-      <c r="AL15" s="10" t="n">
+      <c r="AP15" s="10" t="n">
         <v>0.0353</v>
       </c>
-      <c r="AM15" s="11" t="n">
+      <c r="AQ15" s="11" t="n">
         <v>-0.09100927632732893</v>
-      </c>
-      <c r="AN15" s="8" t="n">
-        <v>3021670</v>
-      </c>
-      <c r="AO15" s="9" t="n">
-        <v>380972.15</v>
-      </c>
-      <c r="AP15" s="10" t="n">
-        <v>0.0336</v>
-      </c>
-      <c r="AQ15" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="AR15" s="8" t="n">
         <v>3021670</v>
       </c>
       <c r="AS15" s="9" t="n">
-        <v>374687.08</v>
+        <v>380972.15</v>
       </c>
       <c r="AT15" s="10" t="n">
-        <v>0.0339</v>
+        <v>0.0336</v>
       </c>
       <c r="AU15" s="11" t="n">
         <v>0</v>
@@ -3440,10 +3608,10 @@
         <v>3021670</v>
       </c>
       <c r="AW15" s="9" t="n">
-        <v>372239.53</v>
+        <v>374687.08</v>
       </c>
       <c r="AX15" s="10" t="n">
-        <v>0.0358</v>
+        <v>0.0339</v>
       </c>
       <c r="AY15" s="11" t="n">
         <v>0</v>
@@ -3452,34 +3620,34 @@
         <v>3021670</v>
       </c>
       <c r="BA15" s="9" t="n">
+        <v>372239.53</v>
+      </c>
+      <c r="BB15" s="10" t="n">
+        <v>0.0358</v>
+      </c>
+      <c r="BC15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" s="8" t="n">
+        <v>3021670</v>
+      </c>
+      <c r="BE15" s="9" t="n">
         <v>370366.09</v>
       </c>
-      <c r="BB15" s="10" t="n">
+      <c r="BF15" s="10" t="n">
         <v>0.0376</v>
       </c>
-      <c r="BC15" s="11" t="n">
+      <c r="BG15" s="11" t="n">
         <v>0.001190161420612721</v>
-      </c>
-      <c r="BD15" s="8" t="n">
-        <v>3018078</v>
-      </c>
-      <c r="BE15" s="9" t="n">
-        <v>347747.47</v>
-      </c>
-      <c r="BF15" s="10" t="n">
-        <v>0.0372</v>
-      </c>
-      <c r="BG15" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="BH15" s="8" t="n">
         <v>3018078</v>
       </c>
       <c r="BI15" s="9" t="n">
-        <v>360535.07</v>
+        <v>347747.47</v>
       </c>
       <c r="BJ15" s="10" t="n">
-        <v>0.041</v>
+        <v>0.0372</v>
       </c>
       <c r="BK15" s="11" t="n">
         <v>0</v>
@@ -3488,12 +3656,24 @@
         <v>3018078</v>
       </c>
       <c r="BM15" s="9" t="n">
+        <v>360535.07</v>
+      </c>
+      <c r="BN15" s="10" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="BO15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP15" s="8" t="n">
+        <v>3018078</v>
+      </c>
+      <c r="BQ15" s="9" t="n">
         <v>371545.02</v>
       </c>
-      <c r="BN15" s="10" t="n">
+      <c r="BR15" s="10" t="n">
         <v>0.0414</v>
       </c>
-      <c r="BO15" s="11" t="n"/>
+      <c r="BS15" s="11" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -3515,10 +3695,10 @@
         <v>21167034</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>399379.6</v>
+        <v>387145.05</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>0.0283</v>
+        <v>0.0274</v>
       </c>
       <c r="G16" s="11" t="n">
         <v>0</v>
@@ -3527,10 +3707,10 @@
         <v>21167034</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>377281.21</v>
+        <v>399379.6</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0.0293</v>
+        <v>0.0283</v>
       </c>
       <c r="K16" s="11" t="n">
         <v>0</v>
@@ -3539,10 +3719,10 @@
         <v>21167034</v>
       </c>
       <c r="M16" s="9" t="n">
-        <v>397792.07</v>
+        <v>377281.21</v>
       </c>
       <c r="N16" s="10" t="n">
-        <v>0.0296</v>
+        <v>0.0293</v>
       </c>
       <c r="O16" s="11" t="n">
         <v>0</v>
@@ -3551,10 +3731,10 @@
         <v>21167034</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>416715.398358</v>
+        <v>397792.07</v>
       </c>
       <c r="R16" s="10" t="n">
-        <v>0.0311051731198606</v>
+        <v>0.0296</v>
       </c>
       <c r="S16" s="11" t="n">
         <v>0</v>
@@ -3563,10 +3743,10 @@
         <v>21167034</v>
       </c>
       <c r="U16" s="9" t="n">
-        <v>445693.07</v>
+        <v>416715.398358</v>
       </c>
       <c r="V16" s="10" t="n">
-        <v>0.0334</v>
+        <v>0.0311051731198606</v>
       </c>
       <c r="W16" s="11" t="n">
         <v>0</v>
@@ -3575,10 +3755,10 @@
         <v>21167034</v>
       </c>
       <c r="Y16" s="9" t="n">
-        <v>444846.39</v>
+        <v>445693.07</v>
       </c>
       <c r="Z16" s="10" t="n">
-        <v>0.0343</v>
+        <v>0.0334</v>
       </c>
       <c r="AA16" s="11" t="n">
         <v>0</v>
@@ -3587,10 +3767,10 @@
         <v>21167034</v>
       </c>
       <c r="AC16" s="9" t="n">
-        <v>434876.71</v>
+        <v>444846.39</v>
       </c>
       <c r="AD16" s="10" t="n">
-        <v>0.0346</v>
+        <v>0.0343</v>
       </c>
       <c r="AE16" s="11" t="n">
         <v>0</v>
@@ -3599,10 +3779,10 @@
         <v>21167034</v>
       </c>
       <c r="AG16" s="9" t="n">
-        <v>397601.57</v>
+        <v>434876.71</v>
       </c>
       <c r="AH16" s="10" t="n">
-        <v>0.0332</v>
+        <v>0.0346</v>
       </c>
       <c r="AI16" s="11" t="n">
         <v>0</v>
@@ -3611,10 +3791,10 @@
         <v>21167034</v>
       </c>
       <c r="AK16" s="9" t="n">
-        <v>399802.94</v>
+        <v>397601.57</v>
       </c>
       <c r="AL16" s="10" t="n">
-        <v>0.0348</v>
+        <v>0.0332</v>
       </c>
       <c r="AM16" s="11" t="n">
         <v>0</v>
@@ -3623,42 +3803,50 @@
         <v>21167034</v>
       </c>
       <c r="AO16" s="9" t="n">
+        <v>399802.94</v>
+      </c>
+      <c r="AP16" s="10" t="n">
+        <v>0.0348</v>
+      </c>
+      <c r="AQ16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" s="8" t="n">
+        <v>21167034</v>
+      </c>
+      <c r="AS16" s="9" t="n">
         <v>405200.53</v>
       </c>
-      <c r="AP16" s="10" t="n">
+      <c r="AT16" s="10" t="n">
         <v>0.0358</v>
       </c>
-      <c r="AQ16" s="11" t="n">
+      <c r="AU16" s="11" t="n">
         <v>0.01098531912399817</v>
       </c>
-      <c r="AR16" s="8" t="n">
+      <c r="AV16" s="8" t="n">
         <v>20937034</v>
       </c>
-      <c r="AS16" s="9" t="n">
+      <c r="AW16" s="9" t="n">
         <v>420750.64</v>
       </c>
-      <c r="AT16" s="10" t="n">
+      <c r="AX16" s="10" t="n">
         <v>0.0381</v>
       </c>
-      <c r="AU16" s="11" t="n">
+      <c r="AY16" s="11" t="n">
         <v>0.7744638647975486</v>
       </c>
-      <c r="AV16" s="8" t="n">
+      <c r="AZ16" s="8" t="n">
         <v>11799076</v>
       </c>
-      <c r="AW16" s="9" t="n">
+      <c r="BA16" s="9" t="n">
         <v>219014.45</v>
       </c>
-      <c r="AX16" s="10" t="n">
+      <c r="BB16" s="10" t="n">
         <v>0.0211</v>
       </c>
-      <c r="AY16" s="11" t="n">
+      <c r="BC16" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="AZ16" s="8" t="n"/>
-      <c r="BA16" s="9" t="n"/>
-      <c r="BB16" s="10" t="n"/>
-      <c r="BC16" s="11" t="n"/>
       <c r="BD16" s="8" t="n"/>
       <c r="BE16" s="9" t="n"/>
       <c r="BF16" s="10" t="n"/>
@@ -3671,6 +3859,10 @@
       <c r="BM16" s="9" t="n"/>
       <c r="BN16" s="10" t="n"/>
       <c r="BO16" s="11" t="n"/>
+      <c r="BP16" s="8" t="n"/>
+      <c r="BQ16" s="9" t="n"/>
+      <c r="BR16" s="10" t="n"/>
+      <c r="BS16" s="11" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -3692,78 +3884,86 @@
         <v>15874545</v>
       </c>
       <c r="E17" s="9" t="n">
+        <v>358590.1</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>0.0254</v>
+      </c>
+      <c r="G17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>15874545</v>
+      </c>
+      <c r="I17" s="9" t="n">
         <v>392720.37</v>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="J17" s="10" t="n">
         <v>0.0279</v>
       </c>
-      <c r="G17" s="11" t="n">
+      <c r="K17" s="11" t="n">
         <v>0.2789485718226543</v>
       </c>
-      <c r="H17" s="8" t="n">
+      <c r="L17" s="8" t="n">
         <v>12412184</v>
       </c>
-      <c r="I17" s="9" t="n">
+      <c r="M17" s="9" t="n">
         <v>292791.01</v>
       </c>
-      <c r="J17" s="10" t="n">
+      <c r="N17" s="10" t="n">
         <v>0.0227</v>
       </c>
-      <c r="K17" s="11" t="n">
+      <c r="O17" s="11" t="n">
         <v>0.1960027966702049</v>
       </c>
-      <c r="L17" s="8" t="n">
+      <c r="P17" s="8" t="n">
         <v>10378056</v>
       </c>
-      <c r="M17" s="9" t="n">
+      <c r="Q17" s="9" t="n">
         <v>273710.85</v>
       </c>
-      <c r="N17" s="10" t="n">
+      <c r="R17" s="10" t="n">
         <v>0.0204</v>
       </c>
-      <c r="O17" s="11" t="n">
+      <c r="S17" s="11" t="n">
         <v>0.2259018504190464</v>
       </c>
-      <c r="P17" s="8" t="n">
+      <c r="T17" s="8" t="n">
         <v>8465650</v>
       </c>
-      <c r="Q17" s="9" t="n">
+      <c r="U17" s="9" t="n">
         <v>264458.44</v>
       </c>
-      <c r="R17" s="10" t="n">
+      <c r="V17" s="10" t="n">
         <v>0.0197</v>
       </c>
-      <c r="S17" s="11" t="n">
+      <c r="W17" s="11" t="n">
         <v>0.8187749766950423</v>
       </c>
-      <c r="T17" s="8" t="n">
+      <c r="X17" s="8" t="n">
         <v>4654589</v>
       </c>
-      <c r="U17" s="9" t="n">
+      <c r="Y17" s="9" t="n">
         <v>149235.43</v>
       </c>
-      <c r="V17" s="10" t="n">
+      <c r="Z17" s="10" t="n">
         <v>0.0112</v>
       </c>
-      <c r="W17" s="11" t="n">
+      <c r="AA17" s="11" t="n">
         <v>0.6557662214497397</v>
       </c>
-      <c r="X17" s="8" t="n">
+      <c r="AB17" s="8" t="n">
         <v>2811139</v>
       </c>
-      <c r="Y17" s="9" t="n">
+      <c r="AC17" s="9" t="n">
         <v>88199.49000000001</v>
       </c>
-      <c r="Z17" s="10" t="n">
+      <c r="AD17" s="10" t="n">
         <v>0.0068</v>
       </c>
-      <c r="AA17" s="11" t="n">
+      <c r="AE17" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="AB17" s="8" t="n"/>
-      <c r="AC17" s="9" t="n"/>
-      <c r="AD17" s="10" t="n"/>
-      <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="8" t="n"/>
       <c r="AG17" s="9" t="n"/>
       <c r="AH17" s="10" t="n"/>
@@ -3800,16 +4000,20 @@
       <c r="BM17" s="9" t="n"/>
       <c r="BN17" s="10" t="n"/>
       <c r="BO17" s="11" t="n"/>
+      <c r="BP17" s="8" t="n"/>
+      <c r="BQ17" s="9" t="n"/>
+      <c r="BR17" s="10" t="n"/>
+      <c r="BS17" s="11" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Laboratories Limited</t>
+          <t>Zydus Lifesciences Limited</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>INE089A01031</t>
+          <t>INE010B01027</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -3818,195 +4022,207 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>14298956</v>
+        <v>19259906</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>189160.89</v>
+        <v>207564.01</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>0.0134</v>
+        <v>0.0147</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.03842089240418815</v>
+        <v>0.003091213049957467</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>13769904</v>
+        <v>19200553</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>172798.53</v>
+        <v>171249.73</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.0134</v>
+        <v>0.0121</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>0</v>
+        <v>0.01839783477883317</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>13769904</v>
+        <v>18853686</v>
       </c>
       <c r="M18" s="9" t="n">
-        <v>177122.28</v>
+        <v>164253.31</v>
       </c>
       <c r="N18" s="10" t="n">
-        <v>0.0132</v>
+        <v>0.0127</v>
       </c>
       <c r="O18" s="11" t="n">
-        <v>-0.02223420828005112</v>
+        <v>0</v>
       </c>
       <c r="P18" s="8" t="n">
-        <v>14083029</v>
+        <v>18853686</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>171545.38</v>
+        <v>173774.42</v>
       </c>
       <c r="R18" s="10" t="n">
-        <v>0.0128</v>
+        <v>0.0129</v>
       </c>
       <c r="S18" s="11" t="n">
-        <v>0.07294813282038955</v>
+        <v>0.00550299933303119</v>
       </c>
       <c r="T18" s="8" t="n">
-        <v>13125545</v>
+        <v>18750502</v>
       </c>
       <c r="U18" s="9" t="n">
-        <v>166878.18</v>
+        <v>165998.19</v>
       </c>
       <c r="V18" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.0124</v>
       </c>
       <c r="W18" s="11" t="n">
-        <v>0</v>
+        <v>0.04733304757267096</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>13125545</v>
+        <v>17903094</v>
       </c>
       <c r="Y18" s="9" t="n">
-        <v>165224.36</v>
+        <v>163696.94</v>
       </c>
       <c r="Z18" s="10" t="n">
-        <v>0.0127</v>
+        <v>0.0123</v>
       </c>
       <c r="AA18" s="11" t="n">
-        <v>0.02739609151703509</v>
+        <v>0.02860906275493533</v>
       </c>
       <c r="AB18" s="8" t="n">
-        <v>12775545</v>
+        <v>17405149</v>
       </c>
       <c r="AC18" s="9" t="n">
-        <v>152999.93</v>
+        <v>164043.53</v>
       </c>
       <c r="AD18" s="10" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="AE18" s="11" t="n">
+        <v>0.1044024130018492</v>
+      </c>
+      <c r="AF18" s="8" t="n">
+        <v>15759789</v>
+      </c>
+      <c r="AG18" s="9" t="n">
+        <v>153571.26</v>
+      </c>
+      <c r="AH18" s="10" t="n">
         <v>0.0122</v>
       </c>
-      <c r="AE18" s="11" t="n">
-        <v>0.05513752418556975</v>
-      </c>
-      <c r="AF18" s="8" t="n">
-        <v>12107943</v>
-      </c>
-      <c r="AG18" s="9" t="n">
-        <v>148164.9</v>
-      </c>
-      <c r="AH18" s="10" t="n">
+      <c r="AI18" s="11" t="n">
+        <v>0.04036608437732761</v>
+      </c>
+      <c r="AJ18" s="8" t="n">
+        <v>15148311</v>
+      </c>
+      <c r="AK18" s="9" t="n">
+        <v>148741.27</v>
+      </c>
+      <c r="AL18" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="AI18" s="11" t="n">
-        <v>0.04083231560577577</v>
-      </c>
-      <c r="AJ18" s="8" t="n">
-        <v>11632943</v>
-      </c>
-      <c r="AK18" s="9" t="n">
-        <v>146586.71</v>
-      </c>
-      <c r="AL18" s="10" t="n">
-        <v>0.0127</v>
-      </c>
       <c r="AM18" s="11" t="n">
-        <v>0.037023978878946</v>
+        <v>0.02447981732333564</v>
       </c>
       <c r="AN18" s="8" t="n">
-        <v>11217622</v>
+        <v>14786344</v>
       </c>
       <c r="AO18" s="9" t="n">
-        <v>142497.45</v>
+        <v>145061.43</v>
       </c>
       <c r="AP18" s="10" t="n">
         <v>0.0126</v>
       </c>
       <c r="AQ18" s="11" t="n">
-        <v>0.08471904462602137</v>
+        <v>0.02183487170521033</v>
       </c>
       <c r="AR18" s="8" t="n">
-        <v>10341500</v>
+        <v>14470385</v>
       </c>
       <c r="AS18" s="9" t="n">
-        <v>132712.47</v>
+        <v>140333.79</v>
       </c>
       <c r="AT18" s="10" t="n">
-        <v>0.012</v>
+        <v>0.0124</v>
       </c>
       <c r="AU18" s="11" t="n">
-        <v>0</v>
+        <v>0.01486488524161312</v>
       </c>
       <c r="AV18" s="8" t="n">
-        <v>10341500</v>
+        <v>14258435</v>
       </c>
       <c r="AW18" s="9" t="n">
-        <v>129392.85</v>
+        <v>141151.38</v>
       </c>
       <c r="AX18" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.0128</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>-0.005975775856020039</v>
+        <v>0</v>
       </c>
       <c r="AZ18" s="8" t="n">
-        <v>10403670</v>
+        <v>14258435</v>
       </c>
       <c r="BA18" s="9" t="n">
-        <v>123169.05</v>
+        <v>132603.45</v>
       </c>
       <c r="BB18" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.0128</v>
       </c>
       <c r="BC18" s="11" t="n">
-        <v>0.02666147990782253</v>
+        <v>0.0231160633003793</v>
       </c>
       <c r="BD18" s="8" t="n">
-        <v>10133496</v>
+        <v>13936283</v>
       </c>
       <c r="BE18" s="9" t="n">
-        <v>115947.46</v>
+        <v>123789.03</v>
       </c>
       <c r="BF18" s="10" t="n">
-        <v>0.0124</v>
+        <v>0.0126</v>
       </c>
       <c r="BG18" s="11" t="n">
-        <v>0.02236244056730923</v>
+        <v>0.07172012123664578</v>
       </c>
       <c r="BH18" s="8" t="n">
-        <v>9911843</v>
+        <v>13003659</v>
       </c>
       <c r="BI18" s="9" t="n">
-        <v>110665.73</v>
+        <v>115264.43</v>
       </c>
       <c r="BJ18" s="10" t="n">
-        <v>0.0126</v>
+        <v>0.0123</v>
       </c>
       <c r="BK18" s="11" t="n">
-        <v>0.3415700706027321</v>
+        <v>0.132761983775747</v>
       </c>
       <c r="BL18" s="8" t="n">
-        <v>7388241</v>
+        <v>11479604</v>
       </c>
       <c r="BM18" s="9" t="n">
-        <v>89940.75</v>
+        <v>100630.21</v>
       </c>
       <c r="BN18" s="10" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="BO18" s="11" t="n"/>
+        <v>0.0114</v>
+      </c>
+      <c r="BO18" s="11" t="n">
+        <v>0.2957940438149267</v>
+      </c>
+      <c r="BP18" s="8" t="n">
+        <v>8859127</v>
+      </c>
+      <c r="BQ18" s="9" t="n">
+        <v>85955.67999999999</v>
+      </c>
+      <c r="BR18" s="10" t="n">
+        <v>0.009599999999999999</v>
+      </c>
+      <c r="BS18" s="11" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -4025,205 +4241,217 @@
         </is>
       </c>
       <c r="D19" s="8" t="n">
+        <v>14020176</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>196422.67</v>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>0.0139</v>
+      </c>
+      <c r="G19" s="11" t="n">
+        <v>-0.02261311629761015</v>
+      </c>
+      <c r="H19" s="8" t="n">
         <v>14344551</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="I19" s="9" t="n">
         <v>187856.24</v>
       </c>
-      <c r="F19" s="10" t="n">
+      <c r="J19" s="10" t="n">
         <v>0.0133</v>
       </c>
-      <c r="G19" s="11" t="n">
+      <c r="K19" s="11" t="n">
         <v>0.08087039879149707</v>
       </c>
-      <c r="H19" s="8" t="n">
+      <c r="L19" s="8" t="n">
         <v>13271296</v>
       </c>
-      <c r="I19" s="9" t="n">
+      <c r="M19" s="9" t="n">
         <v>162467.21</v>
       </c>
-      <c r="J19" s="10" t="n">
+      <c r="N19" s="10" t="n">
         <v>0.0126</v>
       </c>
-      <c r="K19" s="11" t="n">
+      <c r="O19" s="11" t="n">
         <v>0.03027141779062287</v>
       </c>
-      <c r="L19" s="8" t="n">
+      <c r="P19" s="8" t="n">
         <v>12881359</v>
       </c>
-      <c r="M19" s="9" t="n">
+      <c r="Q19" s="9" t="n">
         <v>173666.48</v>
       </c>
-      <c r="N19" s="10" t="n">
+      <c r="R19" s="10" t="n">
         <v>0.0129</v>
       </c>
-      <c r="O19" s="11" t="n">
+      <c r="S19" s="11" t="n">
         <v>0.02043991688728315</v>
       </c>
-      <c r="P19" s="8" t="n">
+      <c r="T19" s="8" t="n">
         <v>12623339</v>
       </c>
-      <c r="Q19" s="9" t="n">
+      <c r="U19" s="9" t="n">
         <v>167133.01</v>
-      </c>
-      <c r="R19" s="10" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="S19" s="11" t="n">
-        <v>0.1486639530668313</v>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v>10989584</v>
-      </c>
-      <c r="U19" s="9" t="n">
-        <v>166085.58</v>
       </c>
       <c r="V19" s="10" t="n">
         <v>0.0125</v>
       </c>
       <c r="W19" s="11" t="n">
+        <v>0.1486639530668313</v>
+      </c>
+      <c r="X19" s="8" t="n">
+        <v>10989584</v>
+      </c>
+      <c r="Y19" s="9" t="n">
+        <v>166085.58</v>
+      </c>
+      <c r="Z19" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AA19" s="11" t="n">
         <v>0.02078030694418823</v>
       </c>
-      <c r="X19" s="8" t="n">
+      <c r="AB19" s="8" t="n">
         <v>10765866</v>
       </c>
-      <c r="Y19" s="9" t="n">
+      <c r="AC19" s="9" t="n">
         <v>164857.71</v>
       </c>
-      <c r="Z19" s="10" t="n">
+      <c r="AD19" s="10" t="n">
         <v>0.0127</v>
       </c>
-      <c r="AA19" s="11" t="n">
+      <c r="AE19" s="11" t="n">
         <v>0.05823053317160534</v>
       </c>
-      <c r="AB19" s="8" t="n">
+      <c r="AF19" s="8" t="n">
         <v>10173460</v>
       </c>
-      <c r="AC19" s="9" t="n">
+      <c r="AG19" s="9" t="n">
         <v>152734.15</v>
       </c>
-      <c r="AD19" s="10" t="n">
+      <c r="AH19" s="10" t="n">
         <v>0.0121</v>
       </c>
-      <c r="AE19" s="11" t="n">
+      <c r="AI19" s="11" t="n">
         <v>0.01848262661129821</v>
       </c>
-      <c r="AF19" s="8" t="n">
+      <c r="AJ19" s="8" t="n">
         <v>9988840</v>
       </c>
-      <c r="AG19" s="9" t="n">
+      <c r="AK19" s="9" t="n">
         <v>150162.23</v>
       </c>
-      <c r="AH19" s="10" t="n">
+      <c r="AL19" s="10" t="n">
         <v>0.0125</v>
       </c>
-      <c r="AI19" s="11" t="n">
+      <c r="AM19" s="11" t="n">
         <v>0.11089473889663</v>
       </c>
-      <c r="AJ19" s="8" t="n">
+      <c r="AN19" s="8" t="n">
         <v>8991707</v>
       </c>
-      <c r="AK19" s="9" t="n">
+      <c r="AO19" s="9" t="n">
         <v>142914.19</v>
       </c>
-      <c r="AL19" s="10" t="n">
+      <c r="AP19" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="AM19" s="11" t="n">
+      <c r="AQ19" s="11" t="n">
         <v>-0.04856779498084111</v>
       </c>
-      <c r="AN19" s="8" t="n">
+      <c r="AR19" s="8" t="n">
         <v>9450707</v>
       </c>
-      <c r="AO19" s="9" t="n">
+      <c r="AS19" s="9" t="n">
         <v>146920.69</v>
       </c>
-      <c r="AP19" s="10" t="n">
+      <c r="AT19" s="10" t="n">
         <v>0.013</v>
       </c>
-      <c r="AQ19" s="11" t="n">
+      <c r="AU19" s="11" t="n">
         <v>0.03318890177940083</v>
       </c>
-      <c r="AR19" s="8" t="n">
+      <c r="AV19" s="8" t="n">
         <v>9147124</v>
       </c>
-      <c r="AS19" s="9" t="n">
+      <c r="AW19" s="9" t="n">
         <v>137746.54</v>
-      </c>
-      <c r="AT19" s="10" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="AU19" s="11" t="n">
-        <v>0.0298589752957666</v>
-      </c>
-      <c r="AV19" s="8" t="n">
-        <v>8881919</v>
-      </c>
-      <c r="AW19" s="9" t="n">
-        <v>130182.29</v>
       </c>
       <c r="AX19" s="10" t="n">
         <v>0.0125</v>
       </c>
       <c r="AY19" s="11" t="n">
+        <v>0.0298589752957666</v>
+      </c>
+      <c r="AZ19" s="8" t="n">
+        <v>8881919</v>
+      </c>
+      <c r="BA19" s="9" t="n">
+        <v>130182.29</v>
+      </c>
+      <c r="BB19" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="BC19" s="11" t="n">
         <v>0.1110462167918367</v>
-      </c>
-      <c r="AZ19" s="8" t="n">
-        <v>7994194</v>
-      </c>
-      <c r="BA19" s="9" t="n">
-        <v>123918</v>
-      </c>
-      <c r="BB19" s="10" t="n">
-        <v>0.0126</v>
-      </c>
-      <c r="BC19" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="BD19" s="8" t="n">
         <v>7994194</v>
       </c>
       <c r="BE19" s="9" t="n">
+        <v>123918</v>
+      </c>
+      <c r="BF19" s="10" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="BG19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" s="8" t="n">
+        <v>7994194</v>
+      </c>
+      <c r="BI19" s="9" t="n">
         <v>115292.27</v>
       </c>
-      <c r="BF19" s="10" t="n">
+      <c r="BJ19" s="10" t="n">
         <v>0.0123</v>
       </c>
-      <c r="BG19" s="11" t="n">
+      <c r="BK19" s="11" t="n">
         <v>0.03077033965211765</v>
       </c>
-      <c r="BH19" s="8" t="n">
+      <c r="BL19" s="8" t="n">
         <v>7755553</v>
       </c>
-      <c r="BI19" s="9" t="n">
+      <c r="BM19" s="9" t="n">
         <v>109159.41</v>
       </c>
-      <c r="BJ19" s="10" t="n">
+      <c r="BN19" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="BK19" s="11" t="n">
+      <c r="BO19" s="11" t="n">
         <v>0.2461624388271065</v>
       </c>
-      <c r="BL19" s="8" t="n">
+      <c r="BP19" s="8" t="n">
         <v>6223549</v>
       </c>
-      <c r="BM19" s="9" t="n">
+      <c r="BQ19" s="9" t="n">
         <v>92071.17999999999</v>
       </c>
-      <c r="BN19" s="10" t="n">
+      <c r="BR19" s="10" t="n">
         <v>0.0103</v>
       </c>
-      <c r="BO19" s="11" t="n"/>
+      <c r="BS19" s="11" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences Limited</t>
+          <t>Dr. Reddy's Laboratories Limited</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>INE010B01027</t>
+          <t>INE089A01031</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -4232,308 +4460,288 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>19200553</v>
+        <v>14298956</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>171249.73</v>
+        <v>186386.89</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>0.0121</v>
+        <v>0.0132</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>0.01839783477883317</v>
+        <v>0</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>18853686</v>
+        <v>14298956</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>164253.31</v>
+        <v>189160.89</v>
       </c>
       <c r="J20" s="10" t="n">
+        <v>0.0134</v>
+      </c>
+      <c r="K20" s="11" t="n">
+        <v>0.03842089240418815</v>
+      </c>
+      <c r="L20" s="8" t="n">
+        <v>13769904</v>
+      </c>
+      <c r="M20" s="9" t="n">
+        <v>172798.53</v>
+      </c>
+      <c r="N20" s="10" t="n">
+        <v>0.0134</v>
+      </c>
+      <c r="O20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="8" t="n">
+        <v>13769904</v>
+      </c>
+      <c r="Q20" s="9" t="n">
+        <v>177122.28</v>
+      </c>
+      <c r="R20" s="10" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="S20" s="11" t="n">
+        <v>-0.02223420828005112</v>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v>14083029</v>
+      </c>
+      <c r="U20" s="9" t="n">
+        <v>171545.38</v>
+      </c>
+      <c r="V20" s="10" t="n">
+        <v>0.0128</v>
+      </c>
+      <c r="W20" s="11" t="n">
+        <v>0.07294813282038955</v>
+      </c>
+      <c r="X20" s="8" t="n">
+        <v>13125545</v>
+      </c>
+      <c r="Y20" s="9" t="n">
+        <v>166878.18</v>
+      </c>
+      <c r="Z20" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AA20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="8" t="n">
+        <v>13125545</v>
+      </c>
+      <c r="AC20" s="9" t="n">
+        <v>165224.36</v>
+      </c>
+      <c r="AD20" s="10" t="n">
         <v>0.0127</v>
       </c>
-      <c r="K20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="8" t="n">
-        <v>18853686</v>
-      </c>
-      <c r="M20" s="9" t="n">
-        <v>173774.42</v>
-      </c>
-      <c r="N20" s="10" t="n">
-        <v>0.0129</v>
-      </c>
-      <c r="O20" s="11" t="n">
-        <v>0.00550299933303119</v>
-      </c>
-      <c r="P20" s="8" t="n">
-        <v>18750502</v>
-      </c>
-      <c r="Q20" s="9" t="n">
-        <v>165998.19</v>
-      </c>
-      <c r="R20" s="10" t="n">
+      <c r="AE20" s="11" t="n">
+        <v>0.02739609151703509</v>
+      </c>
+      <c r="AF20" s="8" t="n">
+        <v>12775545</v>
+      </c>
+      <c r="AG20" s="9" t="n">
+        <v>152999.93</v>
+      </c>
+      <c r="AH20" s="10" t="n">
+        <v>0.0122</v>
+      </c>
+      <c r="AI20" s="11" t="n">
+        <v>0.05513752418556975</v>
+      </c>
+      <c r="AJ20" s="8" t="n">
+        <v>12107943</v>
+      </c>
+      <c r="AK20" s="9" t="n">
+        <v>148164.9</v>
+      </c>
+      <c r="AL20" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="S20" s="11" t="n">
-        <v>0.04733304757267096</v>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v>17903094</v>
-      </c>
-      <c r="U20" s="9" t="n">
-        <v>163696.94</v>
-      </c>
-      <c r="V20" s="10" t="n">
-        <v>0.0123</v>
-      </c>
-      <c r="W20" s="11" t="n">
-        <v>0.02860906275493533</v>
-      </c>
-      <c r="X20" s="8" t="n">
-        <v>17405149</v>
-      </c>
-      <c r="Y20" s="9" t="n">
-        <v>164043.53</v>
-      </c>
-      <c r="Z20" s="10" t="n">
+      <c r="AM20" s="11" t="n">
+        <v>0.04083231560577577</v>
+      </c>
+      <c r="AN20" s="8" t="n">
+        <v>11632943</v>
+      </c>
+      <c r="AO20" s="9" t="n">
+        <v>146586.71</v>
+      </c>
+      <c r="AP20" s="10" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="AQ20" s="11" t="n">
+        <v>0.037023978878946</v>
+      </c>
+      <c r="AR20" s="8" t="n">
+        <v>11217622</v>
+      </c>
+      <c r="AS20" s="9" t="n">
+        <v>142497.45</v>
+      </c>
+      <c r="AT20" s="10" t="n">
         <v>0.0126</v>
       </c>
-      <c r="AA20" s="11" t="n">
-        <v>0.1044024130018492</v>
-      </c>
-      <c r="AB20" s="8" t="n">
-        <v>15759789</v>
-      </c>
-      <c r="AC20" s="9" t="n">
-        <v>153571.26</v>
-      </c>
-      <c r="AD20" s="10" t="n">
-        <v>0.0122</v>
-      </c>
-      <c r="AE20" s="11" t="n">
-        <v>0.04036608437732761</v>
-      </c>
-      <c r="AF20" s="8" t="n">
-        <v>15148311</v>
-      </c>
-      <c r="AG20" s="9" t="n">
-        <v>148741.27</v>
-      </c>
-      <c r="AH20" s="10" t="n">
+      <c r="AU20" s="11" t="n">
+        <v>0.08471904462602137</v>
+      </c>
+      <c r="AV20" s="8" t="n">
+        <v>10341500</v>
+      </c>
+      <c r="AW20" s="9" t="n">
+        <v>132712.47</v>
+      </c>
+      <c r="AX20" s="10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AY20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" s="8" t="n">
+        <v>10341500</v>
+      </c>
+      <c r="BA20" s="9" t="n">
+        <v>129392.85</v>
+      </c>
+      <c r="BB20" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="BC20" s="11" t="n">
+        <v>-0.005975775856020039</v>
+      </c>
+      <c r="BD20" s="8" t="n">
+        <v>10403670</v>
+      </c>
+      <c r="BE20" s="9" t="n">
+        <v>123169.05</v>
+      </c>
+      <c r="BF20" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="BG20" s="11" t="n">
+        <v>0.02666147990782253</v>
+      </c>
+      <c r="BH20" s="8" t="n">
+        <v>10133496</v>
+      </c>
+      <c r="BI20" s="9" t="n">
+        <v>115947.46</v>
+      </c>
+      <c r="BJ20" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="AI20" s="11" t="n">
-        <v>0.02447981732333564</v>
-      </c>
-      <c r="AJ20" s="8" t="n">
-        <v>14786344</v>
-      </c>
-      <c r="AK20" s="9" t="n">
-        <v>145061.43</v>
-      </c>
-      <c r="AL20" s="10" t="n">
+      <c r="BK20" s="11" t="n">
+        <v>0.02236244056730923</v>
+      </c>
+      <c r="BL20" s="8" t="n">
+        <v>9911843</v>
+      </c>
+      <c r="BM20" s="9" t="n">
+        <v>110665.73</v>
+      </c>
+      <c r="BN20" s="10" t="n">
         <v>0.0126</v>
       </c>
-      <c r="AM20" s="11" t="n">
-        <v>0.02183487170521033</v>
-      </c>
-      <c r="AN20" s="8" t="n">
-        <v>14470385</v>
-      </c>
-      <c r="AO20" s="9" t="n">
-        <v>140333.79</v>
-      </c>
-      <c r="AP20" s="10" t="n">
-        <v>0.0124</v>
-      </c>
-      <c r="AQ20" s="11" t="n">
-        <v>0.01486488524161312</v>
-      </c>
-      <c r="AR20" s="8" t="n">
-        <v>14258435</v>
-      </c>
-      <c r="AS20" s="9" t="n">
-        <v>141151.38</v>
-      </c>
-      <c r="AT20" s="10" t="n">
-        <v>0.0128</v>
-      </c>
-      <c r="AU20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" s="8" t="n">
-        <v>14258435</v>
-      </c>
-      <c r="AW20" s="9" t="n">
-        <v>132603.45</v>
-      </c>
-      <c r="AX20" s="10" t="n">
-        <v>0.0128</v>
-      </c>
-      <c r="AY20" s="11" t="n">
-        <v>0.0231160633003793</v>
-      </c>
-      <c r="AZ20" s="8" t="n">
-        <v>13936283</v>
-      </c>
-      <c r="BA20" s="9" t="n">
-        <v>123789.03</v>
-      </c>
-      <c r="BB20" s="10" t="n">
-        <v>0.0126</v>
-      </c>
-      <c r="BC20" s="11" t="n">
-        <v>0.07172012123664578</v>
-      </c>
-      <c r="BD20" s="8" t="n">
-        <v>13003659</v>
-      </c>
-      <c r="BE20" s="9" t="n">
-        <v>115264.43</v>
-      </c>
-      <c r="BF20" s="10" t="n">
-        <v>0.0123</v>
-      </c>
-      <c r="BG20" s="11" t="n">
-        <v>0.132761983775747</v>
-      </c>
-      <c r="BH20" s="8" t="n">
-        <v>11479604</v>
-      </c>
-      <c r="BI20" s="9" t="n">
-        <v>100630.21</v>
-      </c>
-      <c r="BJ20" s="10" t="n">
-        <v>0.0114</v>
-      </c>
-      <c r="BK20" s="11" t="n">
-        <v>0.2957940438149267</v>
-      </c>
-      <c r="BL20" s="8" t="n">
-        <v>8859127</v>
-      </c>
-      <c r="BM20" s="9" t="n">
-        <v>85955.67999999999</v>
-      </c>
-      <c r="BN20" s="10" t="n">
-        <v>0.009599999999999999</v>
-      </c>
-      <c r="BO20" s="11" t="n"/>
+      <c r="BO20" s="11" t="n">
+        <v>0.3415700706027321</v>
+      </c>
+      <c r="BP20" s="8" t="n">
+        <v>7388241</v>
+      </c>
+      <c r="BQ20" s="9" t="n">
+        <v>89940.75</v>
+      </c>
+      <c r="BR20" s="10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BS20" s="11" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited</t>
+          <t>Indraprastha Gas Limited</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>INE768C01028</t>
+          <t>INE203G01027</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Gas</t>
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>22157154</v>
+        <v>87857170</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>112680.21</v>
+        <v>140984.4</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>0</v>
+        <v>1.320032704378069</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>22157154</v>
+        <v>37868936</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>94467.03</v>
+        <v>62870.01</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.0073</v>
+        <v>0.0045</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>0.003718720983944644</v>
+        <v>77.70472532588454</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>22075063</v>
+        <v>481152</v>
       </c>
       <c r="M21" s="9" t="n">
-        <v>84966.92</v>
+        <v>700.65</v>
       </c>
       <c r="N21" s="10" t="n">
-        <v>0.0063</v>
+        <v>0.0001</v>
       </c>
       <c r="O21" s="11" t="n">
-        <v>0.003411954545454545</v>
+        <v>0.6815617857367527</v>
       </c>
       <c r="P21" s="8" t="n">
-        <v>22000000</v>
+        <v>286134</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>98626</v>
+        <v>488.89</v>
       </c>
       <c r="R21" s="10" t="n">
-        <v>0.0074</v>
+        <v>0</v>
       </c>
       <c r="S21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="U21" s="9" t="n">
-        <v>100012</v>
-      </c>
-      <c r="V21" s="10" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="W21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" s="8" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="Y21" s="9" t="n">
-        <v>94699</v>
-      </c>
-      <c r="Z21" s="10" t="n">
-        <v>0.0073</v>
-      </c>
-      <c r="AA21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" s="8" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="AC21" s="9" t="n">
-        <v>104852</v>
-      </c>
-      <c r="AD21" s="10" t="n">
-        <v>0.0083</v>
-      </c>
-      <c r="AE21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" s="8" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="AG21" s="9" t="n">
-        <v>100584</v>
-      </c>
-      <c r="AH21" s="10" t="n">
-        <v>0.008399999999999999</v>
-      </c>
-      <c r="AI21" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="T21" s="8" t="n"/>
+      <c r="U21" s="9" t="n"/>
+      <c r="V21" s="10" t="n"/>
+      <c r="W21" s="11" t="n"/>
+      <c r="X21" s="8" t="n"/>
+      <c r="Y21" s="9" t="n"/>
+      <c r="Z21" s="10" t="n"/>
+      <c r="AA21" s="11" t="n"/>
+      <c r="AB21" s="8" t="n"/>
+      <c r="AC21" s="9" t="n"/>
+      <c r="AD21" s="10" t="n"/>
+      <c r="AE21" s="11" t="n"/>
+      <c r="AF21" s="8" t="n"/>
+      <c r="AG21" s="9" t="n"/>
+      <c r="AH21" s="10" t="n"/>
+      <c r="AI21" s="11" t="n"/>
       <c r="AJ21" s="8" t="n"/>
       <c r="AK21" s="9" t="n"/>
       <c r="AL21" s="10" t="n"/>
@@ -4566,525 +4774,605 @@
       <c r="BM21" s="9" t="n"/>
       <c r="BN21" s="10" t="n"/>
       <c r="BO21" s="11" t="n"/>
+      <c r="BP21" s="8" t="n"/>
+      <c r="BQ21" s="9" t="n"/>
+      <c r="BR21" s="10" t="n"/>
+      <c r="BS21" s="11" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Indian Energy Exchange Limited</t>
+          <t>Zydus Wellness Limited</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>INE022Q01020</t>
+          <t>INE768C01028</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>80755676</v>
+        <v>22157154</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>101098.03</v>
+        <v>112347.85</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>0.0072</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="G22" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>80755676</v>
+        <v>22157154</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>92667.14</v>
+        <v>112680.21</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>0.0072</v>
+        <v>0.008</v>
       </c>
       <c r="K22" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>80755676</v>
+        <v>22157154</v>
       </c>
       <c r="M22" s="9" t="n">
-        <v>101461.43</v>
+        <v>94467.03</v>
       </c>
       <c r="N22" s="10" t="n">
-        <v>0.0076</v>
+        <v>0.0073</v>
       </c>
       <c r="O22" s="11" t="n">
-        <v>0</v>
+        <v>0.003718720983944644</v>
       </c>
       <c r="P22" s="8" t="n">
-        <v>80755676</v>
+        <v>22075063</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>102390.12</v>
+        <v>84966.92</v>
       </c>
       <c r="R22" s="10" t="n">
-        <v>0.0076</v>
+        <v>0.0063</v>
       </c>
       <c r="S22" s="11" t="n">
-        <v>0</v>
+        <v>0.003411954545454545</v>
       </c>
       <c r="T22" s="8" t="n">
-        <v>80755676</v>
+        <v>22000000</v>
       </c>
       <c r="U22" s="9" t="n">
-        <v>108390.27</v>
+        <v>98626</v>
       </c>
       <c r="V22" s="10" t="n">
-        <v>0.0081</v>
+        <v>0.0074</v>
       </c>
       <c r="W22" s="11" t="n">
         <v>0</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>80755676</v>
+        <v>22000000</v>
       </c>
       <c r="Y22" s="9" t="n">
-        <v>112484.58</v>
+        <v>100012</v>
       </c>
       <c r="Z22" s="10" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0075</v>
       </c>
       <c r="AA22" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AB22" s="8" t="n">
-        <v>80755676</v>
+        <v>22000000</v>
       </c>
       <c r="AC22" s="9" t="n">
-        <v>112298.84</v>
+        <v>94699</v>
       </c>
       <c r="AD22" s="10" t="n">
-        <v>0.0089</v>
+        <v>0.0073</v>
       </c>
       <c r="AE22" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AF22" s="8" t="n">
-        <v>80755676</v>
+        <v>22000000</v>
       </c>
       <c r="AG22" s="9" t="n">
-        <v>112403.83</v>
+        <v>104852</v>
       </c>
       <c r="AH22" s="10" t="n">
-        <v>0.0094</v>
+        <v>0.0083</v>
       </c>
       <c r="AI22" s="11" t="n">
-        <v>0.09854178046374168</v>
+        <v>0</v>
       </c>
       <c r="AJ22" s="8" t="n">
-        <v>73511702</v>
+        <v>22000000</v>
       </c>
       <c r="AK22" s="9" t="n">
-        <v>102769.36</v>
+        <v>100584</v>
       </c>
       <c r="AL22" s="10" t="n">
-        <v>0.0089</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="AM22" s="11" t="n">
-        <v>0.6629129724205788</v>
-      </c>
-      <c r="AN22" s="8" t="n">
-        <v>44206584</v>
-      </c>
-      <c r="AO22" s="9" t="n">
-        <v>59811.51</v>
-      </c>
-      <c r="AP22" s="10" t="n">
-        <v>0.0053</v>
-      </c>
-      <c r="AQ22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR22" s="8" t="n">
-        <v>44206584</v>
-      </c>
-      <c r="AS22" s="9" t="n">
-        <v>85367.33</v>
-      </c>
-      <c r="AT22" s="10" t="n">
-        <v>0.0077</v>
-      </c>
-      <c r="AU22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV22" s="8" t="n">
-        <v>44206584</v>
-      </c>
-      <c r="AW22" s="9" t="n">
-        <v>88656.3</v>
-      </c>
-      <c r="AX22" s="10" t="n">
-        <v>0.008500000000000001</v>
-      </c>
-      <c r="AY22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ22" s="8" t="n">
-        <v>44206584</v>
-      </c>
-      <c r="BA22" s="9" t="n">
-        <v>84147.23</v>
-      </c>
-      <c r="BB22" s="10" t="n">
-        <v>0.008500000000000001</v>
-      </c>
-      <c r="BC22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD22" s="8" t="n">
-        <v>44206584</v>
-      </c>
-      <c r="BE22" s="9" t="n">
-        <v>77701.91</v>
-      </c>
-      <c r="BF22" s="10" t="n">
-        <v>0.0083</v>
-      </c>
-      <c r="BG22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH22" s="8" t="n">
-        <v>44206584</v>
-      </c>
-      <c r="BI22" s="9" t="n">
-        <v>68931.33</v>
-      </c>
-      <c r="BJ22" s="10" t="n">
-        <v>0.0078</v>
-      </c>
-      <c r="BK22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL22" s="8" t="n">
-        <v>44206584</v>
-      </c>
-      <c r="BM22" s="9" t="n">
-        <v>77184.7</v>
-      </c>
-      <c r="BN22" s="10" t="n">
-        <v>0.0086</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AN22" s="8" t="n"/>
+      <c r="AO22" s="9" t="n"/>
+      <c r="AP22" s="10" t="n"/>
+      <c r="AQ22" s="11" t="n"/>
+      <c r="AR22" s="8" t="n"/>
+      <c r="AS22" s="9" t="n"/>
+      <c r="AT22" s="10" t="n"/>
+      <c r="AU22" s="11" t="n"/>
+      <c r="AV22" s="8" t="n"/>
+      <c r="AW22" s="9" t="n"/>
+      <c r="AX22" s="10" t="n"/>
+      <c r="AY22" s="11" t="n"/>
+      <c r="AZ22" s="8" t="n"/>
+      <c r="BA22" s="9" t="n"/>
+      <c r="BB22" s="10" t="n"/>
+      <c r="BC22" s="11" t="n"/>
+      <c r="BD22" s="8" t="n"/>
+      <c r="BE22" s="9" t="n"/>
+      <c r="BF22" s="10" t="n"/>
+      <c r="BG22" s="11" t="n"/>
+      <c r="BH22" s="8" t="n"/>
+      <c r="BI22" s="9" t="n"/>
+      <c r="BJ22" s="10" t="n"/>
+      <c r="BK22" s="11" t="n"/>
+      <c r="BL22" s="8" t="n"/>
+      <c r="BM22" s="9" t="n"/>
+      <c r="BN22" s="10" t="n"/>
       <c r="BO22" s="11" t="n"/>
+      <c r="BP22" s="8" t="n"/>
+      <c r="BQ22" s="9" t="n"/>
+      <c r="BR22" s="10" t="n"/>
+      <c r="BS22" s="11" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>EID Parry India Limited</t>
+          <t>Indian Energy Exchange Limited</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>INE126A01031</t>
+          <t>INE022Q01020</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>8256209</v>
+        <v>82840866</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>69682.39999999999</v>
+        <v>106293.12</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>0.0049</v>
+        <v>0.0075</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.1165380029838506</v>
+        <v>0.02582097139524905</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>7394472</v>
+        <v>80755676</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>57344.13</v>
+        <v>101098.03</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>0.0044</v>
+        <v>0.0072</v>
       </c>
       <c r="K23" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>7394472</v>
+        <v>80755676</v>
       </c>
       <c r="M23" s="9" t="n">
-        <v>63976.97</v>
+        <v>92667.14</v>
       </c>
       <c r="N23" s="10" t="n">
-        <v>0.0048</v>
+        <v>0.0072</v>
       </c>
       <c r="O23" s="11" t="n">
-        <v>0.004287575158874156</v>
+        <v>0</v>
       </c>
       <c r="P23" s="8" t="n">
-        <v>7362903</v>
+        <v>80755676</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>67966.96000000001</v>
+        <v>101461.43</v>
       </c>
       <c r="R23" s="10" t="n">
-        <v>0.0051</v>
+        <v>0.0076</v>
       </c>
       <c r="S23" s="11" t="n">
-        <v>0.1913802993295465</v>
+        <v>0</v>
       </c>
       <c r="T23" s="8" t="n">
-        <v>6180145</v>
+        <v>80755676</v>
       </c>
       <c r="U23" s="9" t="n">
-        <v>63945.96</v>
+        <v>102390.12</v>
       </c>
       <c r="V23" s="10" t="n">
-        <v>0.0048</v>
+        <v>0.0076</v>
       </c>
       <c r="W23" s="11" t="n">
-        <v>0.05773144178420389</v>
+        <v>0</v>
       </c>
       <c r="X23" s="8" t="n">
-        <v>5842830</v>
+        <v>80755676</v>
       </c>
       <c r="Y23" s="9" t="n">
-        <v>60233.73</v>
+        <v>108390.27</v>
       </c>
       <c r="Z23" s="10" t="n">
-        <v>0.0046</v>
+        <v>0.0081</v>
       </c>
       <c r="AA23" s="11" t="n">
-        <v>0.05688668625904227</v>
+        <v>0</v>
       </c>
       <c r="AB23" s="8" t="n">
-        <v>5528341</v>
+        <v>80755676</v>
       </c>
       <c r="AC23" s="9" t="n">
-        <v>59285.93</v>
+        <v>112484.58</v>
       </c>
       <c r="AD23" s="10" t="n">
-        <v>0.0047</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="AE23" s="11" t="n">
-        <v>0.1065051605034048</v>
+        <v>0</v>
       </c>
       <c r="AF23" s="8" t="n">
-        <v>4996218</v>
+        <v>80755676</v>
       </c>
       <c r="AG23" s="9" t="n">
-        <v>51236.22</v>
+        <v>112298.84</v>
       </c>
       <c r="AH23" s="10" t="n">
-        <v>0.0043</v>
+        <v>0.0089</v>
       </c>
       <c r="AI23" s="11" t="n">
-        <v>0.1269063080091213</v>
+        <v>0</v>
       </c>
       <c r="AJ23" s="8" t="n">
-        <v>4433570</v>
+        <v>80755676</v>
       </c>
       <c r="AK23" s="9" t="n">
-        <v>49913.13</v>
+        <v>112403.83</v>
       </c>
       <c r="AL23" s="10" t="n">
-        <v>0.0043</v>
+        <v>0.0094</v>
       </c>
       <c r="AM23" s="11" t="n">
-        <v>0.1091786303542636</v>
+        <v>0.09854178046374168</v>
       </c>
       <c r="AN23" s="8" t="n">
-        <v>3997165</v>
+        <v>73511702</v>
       </c>
       <c r="AO23" s="9" t="n">
-        <v>49305.03</v>
+        <v>102769.36</v>
       </c>
       <c r="AP23" s="10" t="n">
-        <v>0.0044</v>
+        <v>0.0089</v>
       </c>
       <c r="AQ23" s="11" t="n">
-        <v>0.136585363079533</v>
+        <v>0.6629129724205788</v>
       </c>
       <c r="AR23" s="8" t="n">
-        <v>3516819</v>
+        <v>44206584</v>
       </c>
       <c r="AS23" s="9" t="n">
-        <v>39036.69</v>
+        <v>59811.51</v>
       </c>
       <c r="AT23" s="10" t="n">
-        <v>0.0035</v>
+        <v>0.0053</v>
       </c>
       <c r="AU23" s="11" t="n">
-        <v>0.08443118240843069</v>
+        <v>0</v>
       </c>
       <c r="AV23" s="8" t="n">
-        <v>3243008</v>
+        <v>44206584</v>
       </c>
       <c r="AW23" s="9" t="n">
-        <v>30813.44</v>
+        <v>85367.33</v>
       </c>
       <c r="AX23" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0077</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.08526813218218672</v>
+        <v>0</v>
       </c>
       <c r="AZ23" s="8" t="n">
-        <v>2988209</v>
+        <v>44206584</v>
       </c>
       <c r="BA23" s="9" t="n">
-        <v>24424.13</v>
+        <v>88656.3</v>
       </c>
       <c r="BB23" s="10" t="n">
-        <v>0.0025</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="BC23" s="11" t="n">
-        <v>0.05097801295341799</v>
+        <v>0</v>
       </c>
       <c r="BD23" s="8" t="n">
-        <v>2843265</v>
+        <v>44206584</v>
       </c>
       <c r="BE23" s="9" t="n">
-        <v>22336.69</v>
+        <v>84147.23</v>
       </c>
       <c r="BF23" s="10" t="n">
-        <v>0.0024</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="BG23" s="11" t="n">
-        <v>0.08976771675272589</v>
+        <v>0</v>
       </c>
       <c r="BH23" s="8" t="n">
-        <v>2609056</v>
+        <v>44206584</v>
       </c>
       <c r="BI23" s="9" t="n">
-        <v>17326.74</v>
+        <v>77701.91</v>
       </c>
       <c r="BJ23" s="10" t="n">
-        <v>0.002</v>
+        <v>0.0083</v>
       </c>
       <c r="BK23" s="11" t="n">
-        <v>0.1546891810734174</v>
+        <v>0</v>
       </c>
       <c r="BL23" s="8" t="n">
-        <v>2259531</v>
+        <v>44206584</v>
       </c>
       <c r="BM23" s="9" t="n">
-        <v>18525.89</v>
+        <v>68931.33</v>
       </c>
       <c r="BN23" s="10" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="BO23" s="11" t="n"/>
+        <v>0.0078</v>
+      </c>
+      <c r="BO23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP23" s="8" t="n">
+        <v>44206584</v>
+      </c>
+      <c r="BQ23" s="9" t="n">
+        <v>77184.7</v>
+      </c>
+      <c r="BR23" s="10" t="n">
+        <v>0.0086</v>
+      </c>
+      <c r="BS23" s="11" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Indraprastha Gas Limited</t>
+          <t>EID Parry India Limited</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>INE203G01027</t>
+          <t>INE126A01031</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>37868936</v>
+        <v>8256209</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>62870.01</v>
+        <v>62367.4</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>0.0045</v>
+        <v>0.0044</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>77.70472532588454</v>
+        <v>0</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>481152</v>
+        <v>8256209</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>700.65</v>
+        <v>69682.39999999999</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0049</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>0.6815617857367527</v>
+        <v>0.1165380029838506</v>
       </c>
       <c r="L24" s="8" t="n">
-        <v>286134</v>
+        <v>7394472</v>
       </c>
       <c r="M24" s="9" t="n">
-        <v>488.89</v>
+        <v>57344.13</v>
       </c>
       <c r="N24" s="10" t="n">
-        <v>0</v>
+        <v>0.0044</v>
       </c>
       <c r="O24" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="P24" s="8" t="n"/>
-      <c r="Q24" s="9" t="n"/>
-      <c r="R24" s="10" t="n"/>
-      <c r="S24" s="11" t="n"/>
-      <c r="T24" s="8" t="n"/>
-      <c r="U24" s="9" t="n"/>
-      <c r="V24" s="10" t="n"/>
-      <c r="W24" s="11" t="n"/>
-      <c r="X24" s="8" t="n"/>
-      <c r="Y24" s="9" t="n"/>
-      <c r="Z24" s="10" t="n"/>
-      <c r="AA24" s="11" t="n"/>
-      <c r="AB24" s="8" t="n"/>
-      <c r="AC24" s="9" t="n"/>
-      <c r="AD24" s="10" t="n"/>
-      <c r="AE24" s="11" t="n"/>
-      <c r="AF24" s="8" t="n"/>
-      <c r="AG24" s="9" t="n"/>
-      <c r="AH24" s="10" t="n"/>
-      <c r="AI24" s="11" t="n"/>
-      <c r="AJ24" s="8" t="n"/>
-      <c r="AK24" s="9" t="n"/>
-      <c r="AL24" s="10" t="n"/>
-      <c r="AM24" s="11" t="n"/>
-      <c r="AN24" s="8" t="n"/>
-      <c r="AO24" s="9" t="n"/>
-      <c r="AP24" s="10" t="n"/>
-      <c r="AQ24" s="11" t="n"/>
-      <c r="AR24" s="8" t="n"/>
-      <c r="AS24" s="9" t="n"/>
-      <c r="AT24" s="10" t="n"/>
-      <c r="AU24" s="11" t="n"/>
-      <c r="AV24" s="8" t="n"/>
-      <c r="AW24" s="9" t="n"/>
-      <c r="AX24" s="10" t="n"/>
-      <c r="AY24" s="11" t="n"/>
-      <c r="AZ24" s="8" t="n"/>
-      <c r="BA24" s="9" t="n"/>
-      <c r="BB24" s="10" t="n"/>
-      <c r="BC24" s="11" t="n"/>
-      <c r="BD24" s="8" t="n"/>
-      <c r="BE24" s="9" t="n"/>
-      <c r="BF24" s="10" t="n"/>
-      <c r="BG24" s="11" t="n"/>
-      <c r="BH24" s="8" t="n"/>
-      <c r="BI24" s="9" t="n"/>
-      <c r="BJ24" s="10" t="n"/>
-      <c r="BK24" s="11" t="n"/>
-      <c r="BL24" s="8" t="n"/>
-      <c r="BM24" s="9" t="n"/>
-      <c r="BN24" s="10" t="n"/>
-      <c r="BO24" s="11" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="P24" s="8" t="n">
+        <v>7394472</v>
+      </c>
+      <c r="Q24" s="9" t="n">
+        <v>63976.97</v>
+      </c>
+      <c r="R24" s="10" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="S24" s="11" t="n">
+        <v>0.004287575158874156</v>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v>7362903</v>
+      </c>
+      <c r="U24" s="9" t="n">
+        <v>67966.96000000001</v>
+      </c>
+      <c r="V24" s="10" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="W24" s="11" t="n">
+        <v>0.1913802993295465</v>
+      </c>
+      <c r="X24" s="8" t="n">
+        <v>6180145</v>
+      </c>
+      <c r="Y24" s="9" t="n">
+        <v>63945.96</v>
+      </c>
+      <c r="Z24" s="10" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="AA24" s="11" t="n">
+        <v>0.05773144178420389</v>
+      </c>
+      <c r="AB24" s="8" t="n">
+        <v>5842830</v>
+      </c>
+      <c r="AC24" s="9" t="n">
+        <v>60233.73</v>
+      </c>
+      <c r="AD24" s="10" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="AE24" s="11" t="n">
+        <v>0.05688668625904227</v>
+      </c>
+      <c r="AF24" s="8" t="n">
+        <v>5528341</v>
+      </c>
+      <c r="AG24" s="9" t="n">
+        <v>59285.93</v>
+      </c>
+      <c r="AH24" s="10" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AI24" s="11" t="n">
+        <v>0.1065051605034048</v>
+      </c>
+      <c r="AJ24" s="8" t="n">
+        <v>4996218</v>
+      </c>
+      <c r="AK24" s="9" t="n">
+        <v>51236.22</v>
+      </c>
+      <c r="AL24" s="10" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="AM24" s="11" t="n">
+        <v>0.1269063080091213</v>
+      </c>
+      <c r="AN24" s="8" t="n">
+        <v>4433570</v>
+      </c>
+      <c r="AO24" s="9" t="n">
+        <v>49913.13</v>
+      </c>
+      <c r="AP24" s="10" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="AQ24" s="11" t="n">
+        <v>0.1091786303542636</v>
+      </c>
+      <c r="AR24" s="8" t="n">
+        <v>3997165</v>
+      </c>
+      <c r="AS24" s="9" t="n">
+        <v>49305.03</v>
+      </c>
+      <c r="AT24" s="10" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="AU24" s="11" t="n">
+        <v>0.136585363079533</v>
+      </c>
+      <c r="AV24" s="8" t="n">
+        <v>3516819</v>
+      </c>
+      <c r="AW24" s="9" t="n">
+        <v>39036.69</v>
+      </c>
+      <c r="AX24" s="10" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="AY24" s="11" t="n">
+        <v>0.08443118240843069</v>
+      </c>
+      <c r="AZ24" s="8" t="n">
+        <v>3243008</v>
+      </c>
+      <c r="BA24" s="9" t="n">
+        <v>30813.44</v>
+      </c>
+      <c r="BB24" s="10" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="BC24" s="11" t="n">
+        <v>0.08526813218218672</v>
+      </c>
+      <c r="BD24" s="8" t="n">
+        <v>2988209</v>
+      </c>
+      <c r="BE24" s="9" t="n">
+        <v>24424.13</v>
+      </c>
+      <c r="BF24" s="10" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="BG24" s="11" t="n">
+        <v>0.05097801295341799</v>
+      </c>
+      <c r="BH24" s="8" t="n">
+        <v>2843265</v>
+      </c>
+      <c r="BI24" s="9" t="n">
+        <v>22336.69</v>
+      </c>
+      <c r="BJ24" s="10" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="BK24" s="11" t="n">
+        <v>0.08976771675272589</v>
+      </c>
+      <c r="BL24" s="8" t="n">
+        <v>2609056</v>
+      </c>
+      <c r="BM24" s="9" t="n">
+        <v>17326.74</v>
+      </c>
+      <c r="BN24" s="10" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="BO24" s="11" t="n">
+        <v>0.1546891810734174</v>
+      </c>
+      <c r="BP24" s="8" t="n">
+        <v>2259531</v>
+      </c>
+      <c r="BQ24" s="9" t="n">
+        <v>18525.89</v>
+      </c>
+      <c r="BR24" s="10" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="BS24" s="11" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -5106,10 +5394,10 @@
         <v>1995914</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>35259.82</v>
+        <v>37802.61</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>0.0025</v>
+        <v>0.0027</v>
       </c>
       <c r="G25" s="11" t="n">
         <v>0</v>
@@ -5118,7 +5406,7 @@
         <v>1995914</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>32040.41</v>
+        <v>35259.82</v>
       </c>
       <c r="J25" s="10" t="n">
         <v>0.0025</v>
@@ -5130,10 +5418,10 @@
         <v>1995914</v>
       </c>
       <c r="M25" s="9" t="n">
-        <v>36543.19</v>
+        <v>32040.41</v>
       </c>
       <c r="N25" s="10" t="n">
-        <v>0.0027</v>
+        <v>0.0025</v>
       </c>
       <c r="O25" s="11" t="n">
         <v>0</v>
@@ -5142,10 +5430,10 @@
         <v>1995914</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>35285.76</v>
+        <v>36543.19</v>
       </c>
       <c r="R25" s="10" t="n">
-        <v>0.0026</v>
+        <v>0.0027</v>
       </c>
       <c r="S25" s="11" t="n">
         <v>0</v>
@@ -5154,10 +5442,10 @@
         <v>1995914</v>
       </c>
       <c r="U25" s="9" t="n">
-        <v>37762.69</v>
+        <v>35285.76</v>
       </c>
       <c r="V25" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.0026</v>
       </c>
       <c r="W25" s="11" t="n">
         <v>0</v>
@@ -5166,10 +5454,10 @@
         <v>1995914</v>
       </c>
       <c r="Y25" s="9" t="n">
-        <v>38830.51</v>
+        <v>37762.69</v>
       </c>
       <c r="Z25" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0028</v>
       </c>
       <c r="AA25" s="11" t="n">
         <v>0</v>
@@ -5178,10 +5466,10 @@
         <v>1995914</v>
       </c>
       <c r="AC25" s="9" t="n">
-        <v>35076.19</v>
+        <v>38830.51</v>
       </c>
       <c r="AD25" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.003</v>
       </c>
       <c r="AE25" s="11" t="n">
         <v>0</v>
@@ -5190,10 +5478,10 @@
         <v>1995914</v>
       </c>
       <c r="AG25" s="9" t="n">
-        <v>34681</v>
+        <v>35076.19</v>
       </c>
       <c r="AH25" s="10" t="n">
-        <v>0.0029</v>
+        <v>0.0028</v>
       </c>
       <c r="AI25" s="11" t="n">
         <v>0</v>
@@ -5202,10 +5490,10 @@
         <v>1995914</v>
       </c>
       <c r="AK25" s="9" t="n">
-        <v>35004.34</v>
+        <v>34681</v>
       </c>
       <c r="AL25" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0029</v>
       </c>
       <c r="AM25" s="11" t="n">
         <v>0</v>
@@ -5214,10 +5502,10 @@
         <v>1995914</v>
       </c>
       <c r="AO25" s="9" t="n">
-        <v>38225.74</v>
+        <v>35004.34</v>
       </c>
       <c r="AP25" s="10" t="n">
-        <v>0.0034</v>
+        <v>0.003</v>
       </c>
       <c r="AQ25" s="11" t="n">
         <v>0</v>
@@ -5226,10 +5514,10 @@
         <v>1995914</v>
       </c>
       <c r="AS25" s="9" t="n">
-        <v>43319.32</v>
+        <v>38225.74</v>
       </c>
       <c r="AT25" s="10" t="n">
-        <v>0.0039</v>
+        <v>0.0034</v>
       </c>
       <c r="AU25" s="11" t="n">
         <v>0</v>
@@ -5238,10 +5526,10 @@
         <v>1995914</v>
       </c>
       <c r="AW25" s="9" t="n">
-        <v>34806.74</v>
+        <v>43319.32</v>
       </c>
       <c r="AX25" s="10" t="n">
-        <v>0.0034</v>
+        <v>0.0039</v>
       </c>
       <c r="AY25" s="11" t="n">
         <v>0</v>
@@ -5250,10 +5538,10 @@
         <v>1995914</v>
       </c>
       <c r="BA25" s="9" t="n">
-        <v>35138.07</v>
+        <v>34806.74</v>
       </c>
       <c r="BB25" s="10" t="n">
-        <v>0.0036</v>
+        <v>0.0034</v>
       </c>
       <c r="BC25" s="11" t="n">
         <v>0</v>
@@ -5262,7 +5550,7 @@
         <v>1995914</v>
       </c>
       <c r="BE25" s="9" t="n">
-        <v>33771.86</v>
+        <v>35138.07</v>
       </c>
       <c r="BF25" s="10" t="n">
         <v>0.0036</v>
@@ -5274,10 +5562,10 @@
         <v>1995914</v>
       </c>
       <c r="BI25" s="9" t="n">
-        <v>28830.98</v>
+        <v>33771.86</v>
       </c>
       <c r="BJ25" s="10" t="n">
-        <v>0.0033</v>
+        <v>0.0036</v>
       </c>
       <c r="BK25" s="11" t="n">
         <v>0</v>
@@ -5286,12 +5574,24 @@
         <v>1995914</v>
       </c>
       <c r="BM25" s="9" t="n">
+        <v>28830.98</v>
+      </c>
+      <c r="BN25" s="10" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="BO25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP25" s="8" t="n">
+        <v>1995914</v>
+      </c>
+      <c r="BQ25" s="9" t="n">
         <v>27686.32</v>
       </c>
-      <c r="BN25" s="10" t="n">
+      <c r="BR25" s="10" t="n">
         <v>0.0031</v>
       </c>
-      <c r="BO25" s="11" t="n"/>
+      <c r="BS25" s="11" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -5313,10 +5613,10 @@
         <v>2205298</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>34773.14</v>
+        <v>31290.97</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>0.0025</v>
+        <v>0.0022</v>
       </c>
       <c r="G26" s="11" t="n">
         <v>0</v>
@@ -5325,10 +5625,10 @@
         <v>2205298</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>31198.35</v>
+        <v>34773.14</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.0024</v>
+        <v>0.0025</v>
       </c>
       <c r="K26" s="11" t="n">
         <v>0</v>
@@ -5337,10 +5637,10 @@
         <v>2205298</v>
       </c>
       <c r="M26" s="9" t="n">
-        <v>29526.73</v>
+        <v>31198.35</v>
       </c>
       <c r="N26" s="10" t="n">
-        <v>0.0022</v>
+        <v>0.0024</v>
       </c>
       <c r="O26" s="11" t="n">
         <v>0</v>
@@ -5349,30 +5649,38 @@
         <v>2205298</v>
       </c>
       <c r="Q26" s="9" t="n">
+        <v>29526.73</v>
+      </c>
+      <c r="R26" s="10" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="S26" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v>2205298</v>
+      </c>
+      <c r="U26" s="9" t="n">
         <v>26516.5</v>
       </c>
-      <c r="R26" s="10" t="n">
+      <c r="V26" s="10" t="n">
         <v>0.002</v>
       </c>
-      <c r="S26" s="11" t="n">
+      <c r="W26" s="11" t="n">
         <v>0.3305575398932319</v>
       </c>
-      <c r="T26" s="8" t="n">
+      <c r="X26" s="8" t="n">
         <v>1657424</v>
       </c>
-      <c r="U26" s="9" t="n">
+      <c r="Y26" s="9" t="n">
         <v>18712.32</v>
       </c>
-      <c r="V26" s="10" t="n">
+      <c r="Z26" s="10" t="n">
         <v>0.0014</v>
       </c>
-      <c r="W26" s="11" t="n">
+      <c r="AA26" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="X26" s="8" t="n"/>
-      <c r="Y26" s="9" t="n"/>
-      <c r="Z26" s="10" t="n"/>
-      <c r="AA26" s="11" t="n"/>
       <c r="AB26" s="8" t="n"/>
       <c r="AC26" s="9" t="n"/>
       <c r="AD26" s="10" t="n"/>
@@ -5413,11 +5721,15 @@
       <c r="BM26" s="9" t="n"/>
       <c r="BN26" s="10" t="n"/>
       <c r="BO26" s="11" t="n"/>
+      <c r="BP26" s="8" t="n"/>
+      <c r="BQ26" s="9" t="n"/>
+      <c r="BR26" s="10" t="n"/>
+      <c r="BS26" s="11" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Central Depository Services (India)</t>
+          <t>Central Depository Services (India) Limited</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -5434,7 +5746,7 @@
         <v>2264603</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>28805.75</v>
+        <v>28185.25</v>
       </c>
       <c r="F27" s="10" t="n">
         <v>0.002</v>
@@ -5446,7 +5758,7 @@
         <v>2264603</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>25349.97</v>
+        <v>28805.75</v>
       </c>
       <c r="J27" s="10" t="n">
         <v>0.002</v>
@@ -5458,10 +5770,10 @@
         <v>2264603</v>
       </c>
       <c r="M27" s="9" t="n">
-        <v>28810.28</v>
+        <v>25349.97</v>
       </c>
       <c r="N27" s="10" t="n">
-        <v>0.0021</v>
+        <v>0.002</v>
       </c>
       <c r="O27" s="11" t="n">
         <v>0</v>
@@ -5470,10 +5782,10 @@
         <v>2264603</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>29897.29</v>
+        <v>28810.28</v>
       </c>
       <c r="R27" s="10" t="n">
-        <v>0.0022</v>
+        <v>0.0021</v>
       </c>
       <c r="S27" s="11" t="n">
         <v>0</v>
@@ -5482,10 +5794,10 @@
         <v>2264603</v>
       </c>
       <c r="U27" s="9" t="n">
-        <v>32691.81</v>
+        <v>29897.29</v>
       </c>
       <c r="V27" s="10" t="n">
-        <v>0.0025</v>
+        <v>0.0022</v>
       </c>
       <c r="W27" s="11" t="n">
         <v>0</v>
@@ -5494,10 +5806,10 @@
         <v>2264603</v>
       </c>
       <c r="Y27" s="9" t="n">
-        <v>36623.16</v>
+        <v>32691.81</v>
       </c>
       <c r="Z27" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.0025</v>
       </c>
       <c r="AA27" s="11" t="n">
         <v>0</v>
@@ -5506,10 +5818,10 @@
         <v>2264603</v>
       </c>
       <c r="AC27" s="9" t="n">
-        <v>35943.78</v>
+        <v>36623.16</v>
       </c>
       <c r="AD27" s="10" t="n">
-        <v>0.0029</v>
+        <v>0.0028</v>
       </c>
       <c r="AE27" s="11" t="n">
         <v>0</v>
@@ -5518,10 +5830,10 @@
         <v>2264603</v>
       </c>
       <c r="AG27" s="9" t="n">
-        <v>33031.5</v>
+        <v>35943.78</v>
       </c>
       <c r="AH27" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.0029</v>
       </c>
       <c r="AI27" s="11" t="n">
         <v>0</v>
@@ -5530,7 +5842,7 @@
         <v>2264603</v>
       </c>
       <c r="AK27" s="9" t="n">
-        <v>32257.01</v>
+        <v>33031.5</v>
       </c>
       <c r="AL27" s="10" t="n">
         <v>0.0028</v>
@@ -5542,10 +5854,10 @@
         <v>2264603</v>
       </c>
       <c r="AO27" s="9" t="n">
-        <v>33534.24</v>
+        <v>32257.01</v>
       </c>
       <c r="AP27" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0028</v>
       </c>
       <c r="AQ27" s="11" t="n">
         <v>0</v>
@@ -5554,10 +5866,10 @@
         <v>2264603</v>
       </c>
       <c r="AS27" s="9" t="n">
-        <v>40626.98</v>
+        <v>33534.24</v>
       </c>
       <c r="AT27" s="10" t="n">
-        <v>0.0037</v>
+        <v>0.003</v>
       </c>
       <c r="AU27" s="11" t="n">
         <v>0</v>
@@ -5566,10 +5878,10 @@
         <v>2264603</v>
       </c>
       <c r="AW27" s="9" t="n">
-        <v>34641.63</v>
+        <v>40626.98</v>
       </c>
       <c r="AX27" s="10" t="n">
-        <v>0.0033</v>
+        <v>0.0037</v>
       </c>
       <c r="AY27" s="11" t="n">
         <v>0</v>
@@ -5578,10 +5890,10 @@
         <v>2264603</v>
       </c>
       <c r="BA27" s="9" t="n">
-        <v>29892.76</v>
+        <v>34641.63</v>
       </c>
       <c r="BB27" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0033</v>
       </c>
       <c r="BC27" s="11" t="n">
         <v>0</v>
@@ -5590,7 +5902,7 @@
         <v>2264603</v>
       </c>
       <c r="BE27" s="9" t="n">
-        <v>27629.29</v>
+        <v>29892.76</v>
       </c>
       <c r="BF27" s="10" t="n">
         <v>0.003</v>
@@ -5602,10 +5914,10 @@
         <v>2264603</v>
       </c>
       <c r="BI27" s="9" t="n">
-        <v>25089.54</v>
+        <v>27629.29</v>
       </c>
       <c r="BJ27" s="10" t="n">
-        <v>0.0029</v>
+        <v>0.003</v>
       </c>
       <c r="BK27" s="11" t="n">
         <v>0</v>
@@ -5614,12 +5926,24 @@
         <v>2264603</v>
       </c>
       <c r="BM27" s="9" t="n">
+        <v>25089.54</v>
+      </c>
+      <c r="BN27" s="10" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="BO27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP27" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="BQ27" s="9" t="n">
         <v>29659.51</v>
       </c>
-      <c r="BN27" s="10" t="n">
+      <c r="BR27" s="10" t="n">
         <v>0.0033</v>
       </c>
-      <c r="BO27" s="11" t="n"/>
+      <c r="BS27" s="11" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -5638,57 +5962,65 @@
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>6957544</v>
+        <v>7626107</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>20201.23</v>
+        <v>23221.5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>0.0014</v>
+        <v>0.0016</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>0</v>
+        <v>0.09609181055843843</v>
       </c>
       <c r="H28" s="8" t="n">
         <v>6957544</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>18479.24</v>
+        <v>20201.23</v>
       </c>
       <c r="J28" s="10" t="n">
         <v>0.0014</v>
       </c>
       <c r="K28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="8" t="n">
+        <v>6957544</v>
+      </c>
+      <c r="M28" s="9" t="n">
+        <v>18479.24</v>
+      </c>
+      <c r="N28" s="10" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="O28" s="11" t="n">
         <v>0.3678192645926667</v>
       </c>
-      <c r="L28" s="8" t="n">
+      <c r="P28" s="8" t="n">
         <v>5086596</v>
       </c>
-      <c r="M28" s="9" t="n">
+      <c r="Q28" s="9" t="n">
         <v>15442.91</v>
       </c>
-      <c r="N28" s="10" t="n">
+      <c r="R28" s="10" t="n">
         <v>0.0012</v>
       </c>
-      <c r="O28" s="11" t="n">
+      <c r="S28" s="11" t="n">
         <v>24.46379118733668</v>
       </c>
-      <c r="P28" s="8" t="n">
+      <c r="T28" s="8" t="n">
         <v>199758</v>
       </c>
-      <c r="Q28" s="9" t="n">
+      <c r="U28" s="9" t="n">
         <v>629.9400000000001</v>
       </c>
-      <c r="R28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" s="11" t="n">
+      <c r="V28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="T28" s="8" t="n"/>
-      <c r="U28" s="9" t="n"/>
-      <c r="V28" s="10" t="n"/>
-      <c r="W28" s="11" t="n"/>
       <c r="X28" s="8" t="n"/>
       <c r="Y28" s="9" t="n"/>
       <c r="Z28" s="10" t="n"/>
@@ -5733,6 +6065,10 @@
       <c r="BM28" s="9" t="n"/>
       <c r="BN28" s="10" t="n"/>
       <c r="BO28" s="11" t="n"/>
+      <c r="BP28" s="8" t="n"/>
+      <c r="BQ28" s="9" t="n"/>
+      <c r="BR28" s="10" t="n"/>
+      <c r="BS28" s="11" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -5754,7 +6090,7 @@
         <v>287393</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>15582.45</v>
+        <v>15447.37</v>
       </c>
       <c r="F29" s="10" t="n">
         <v>0.0011</v>
@@ -5766,7 +6102,7 @@
         <v>287393</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>14378.27</v>
+        <v>15582.45</v>
       </c>
       <c r="J29" s="10" t="n">
         <v>0.0011</v>
@@ -5778,10 +6114,10 @@
         <v>287393</v>
       </c>
       <c r="M29" s="9" t="n">
-        <v>15895.71</v>
+        <v>14378.27</v>
       </c>
       <c r="N29" s="10" t="n">
-        <v>0.0012</v>
+        <v>0.0011</v>
       </c>
       <c r="O29" s="11" t="n">
         <v>0</v>
@@ -5790,10 +6126,10 @@
         <v>287393</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>18124.44</v>
+        <v>15895.71</v>
       </c>
       <c r="R29" s="10" t="n">
-        <v>0.0014</v>
+        <v>0.0012</v>
       </c>
       <c r="S29" s="11" t="n">
         <v>0</v>
@@ -5802,10 +6138,10 @@
         <v>287393</v>
       </c>
       <c r="U29" s="9" t="n">
-        <v>17460.56</v>
+        <v>18124.44</v>
       </c>
       <c r="V29" s="10" t="n">
-        <v>0.0013</v>
+        <v>0.0014</v>
       </c>
       <c r="W29" s="11" t="n">
         <v>0</v>
@@ -5814,10 +6150,10 @@
         <v>287393</v>
       </c>
       <c r="Y29" s="9" t="n">
-        <v>17812.62</v>
+        <v>17460.56</v>
       </c>
       <c r="Z29" s="10" t="n">
-        <v>0.0014</v>
+        <v>0.0013</v>
       </c>
       <c r="AA29" s="11" t="n">
         <v>0</v>
@@ -5826,10 +6162,10 @@
         <v>287393</v>
       </c>
       <c r="AC29" s="9" t="n">
-        <v>18463.56</v>
+        <v>17812.62</v>
       </c>
       <c r="AD29" s="10" t="n">
-        <v>0.0015</v>
+        <v>0.0014</v>
       </c>
       <c r="AE29" s="11" t="n">
         <v>0</v>
@@ -5838,7 +6174,7 @@
         <v>287393</v>
       </c>
       <c r="AG29" s="9" t="n">
-        <v>18243.71</v>
+        <v>18463.56</v>
       </c>
       <c r="AH29" s="10" t="n">
         <v>0.0015</v>
@@ -5850,10 +6186,10 @@
         <v>287393</v>
       </c>
       <c r="AK29" s="9" t="n">
-        <v>17962.06</v>
+        <v>18243.71</v>
       </c>
       <c r="AL29" s="10" t="n">
-        <v>0.0016</v>
+        <v>0.0015</v>
       </c>
       <c r="AM29" s="11" t="n">
         <v>0</v>
@@ -5862,10 +6198,10 @@
         <v>287393</v>
       </c>
       <c r="AO29" s="9" t="n">
-        <v>19048.41</v>
+        <v>17962.06</v>
       </c>
       <c r="AP29" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.0016</v>
       </c>
       <c r="AQ29" s="11" t="n">
         <v>0</v>
@@ -5874,10 +6210,10 @@
         <v>287393</v>
       </c>
       <c r="AS29" s="9" t="n">
-        <v>19453.63</v>
+        <v>19048.41</v>
       </c>
       <c r="AT29" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.0017</v>
       </c>
       <c r="AU29" s="11" t="n">
         <v>0</v>
@@ -5886,10 +6222,10 @@
         <v>287393</v>
       </c>
       <c r="AW29" s="9" t="n">
-        <v>19370.29</v>
+        <v>19453.63</v>
       </c>
       <c r="AX29" s="10" t="n">
-        <v>0.0019</v>
+        <v>0.0018</v>
       </c>
       <c r="AY29" s="11" t="n">
         <v>0</v>
@@ -5898,10 +6234,10 @@
         <v>287393</v>
       </c>
       <c r="BA29" s="9" t="n">
-        <v>15976.18</v>
+        <v>19370.29</v>
       </c>
       <c r="BB29" s="10" t="n">
-        <v>0.0016</v>
+        <v>0.0019</v>
       </c>
       <c r="BC29" s="11" t="n">
         <v>0</v>
@@ -5910,10 +6246,10 @@
         <v>287393</v>
       </c>
       <c r="BE29" s="9" t="n">
-        <v>15821.13</v>
+        <v>15976.18</v>
       </c>
       <c r="BF29" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.0016</v>
       </c>
       <c r="BG29" s="11" t="n">
         <v>0</v>
@@ -5922,24 +6258,36 @@
         <v>287393</v>
       </c>
       <c r="BI29" s="9" t="n">
-        <v>15273.64</v>
+        <v>15821.13</v>
       </c>
       <c r="BJ29" s="10" t="n">
         <v>0.0017</v>
       </c>
       <c r="BK29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL29" s="8" t="n">
+        <v>287393</v>
+      </c>
+      <c r="BM29" s="9" t="n">
+        <v>15273.64</v>
+      </c>
+      <c r="BN29" s="10" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="BO29" s="11" t="n">
         <v>-0.03505968069568721</v>
       </c>
-      <c r="BL29" s="8" t="n">
+      <c r="BP29" s="8" t="n">
         <v>297835</v>
       </c>
-      <c r="BM29" s="9" t="n">
+      <c r="BQ29" s="9" t="n">
         <v>18529.51</v>
       </c>
-      <c r="BN29" s="10" t="n">
+      <c r="BR29" s="10" t="n">
         <v>0.0021</v>
       </c>
-      <c r="BO29" s="11" t="n"/>
+      <c r="BS29" s="11" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -5958,70 +6306,70 @@
         </is>
       </c>
       <c r="D30" s="8" t="n">
+        <v>84295</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>10762.79</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="G30" s="11" t="n">
+        <v>0.04503979569065979</v>
+      </c>
+      <c r="H30" s="8" t="n">
         <v>80662</v>
       </c>
-      <c r="E30" s="9" t="n">
+      <c r="I30" s="9" t="n">
         <v>9876.26</v>
-      </c>
-      <c r="F30" s="10" t="n">
-        <v>0.0007</v>
-      </c>
-      <c r="G30" s="11" t="n">
-        <v>0.001203996772792156</v>
-      </c>
-      <c r="H30" s="8" t="n">
-        <v>80565</v>
-      </c>
-      <c r="I30" s="9" t="n">
-        <v>8949.969999999999</v>
       </c>
       <c r="J30" s="10" t="n">
         <v>0.0007</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>0</v>
+        <v>0.001203996772792156</v>
       </c>
       <c r="L30" s="8" t="n">
         <v>80565</v>
       </c>
       <c r="M30" s="9" t="n">
+        <v>8949.969999999999</v>
+      </c>
+      <c r="N30" s="10" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="O30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="8" t="n">
+        <v>80565</v>
+      </c>
+      <c r="Q30" s="9" t="n">
         <v>10682.11</v>
-      </c>
-      <c r="N30" s="10" t="n">
-        <v>0.0008</v>
-      </c>
-      <c r="O30" s="11" t="n">
-        <v>0.0001613864336081041</v>
-      </c>
-      <c r="P30" s="8" t="n">
-        <v>80552</v>
-      </c>
-      <c r="Q30" s="9" t="n">
-        <v>10825.38</v>
       </c>
       <c r="R30" s="10" t="n">
         <v>0.0008</v>
       </c>
       <c r="S30" s="11" t="n">
+        <v>0.0001613864336081041</v>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v>80552</v>
+      </c>
+      <c r="U30" s="9" t="n">
+        <v>10825.38</v>
+      </c>
+      <c r="V30" s="10" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="W30" s="11" t="n">
         <v>0.004902755772901358</v>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v>80159</v>
-      </c>
-      <c r="U30" s="9" t="n">
-        <v>11401.01</v>
-      </c>
-      <c r="V30" s="10" t="n">
-        <v>0.0009</v>
-      </c>
-      <c r="W30" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="X30" s="8" t="n">
         <v>80159</v>
       </c>
       <c r="Y30" s="9" t="n">
-        <v>11787.38</v>
+        <v>11401.01</v>
       </c>
       <c r="Z30" s="10" t="n">
         <v>0.0009</v>
@@ -6033,10 +6381,10 @@
         <v>80159</v>
       </c>
       <c r="AC30" s="9" t="n">
-        <v>12110.42</v>
+        <v>11787.38</v>
       </c>
       <c r="AD30" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="AE30" s="11" t="n">
         <v>0</v>
@@ -6045,10 +6393,10 @@
         <v>80159</v>
       </c>
       <c r="AG30" s="9" t="n">
-        <v>13825.82</v>
+        <v>12110.42</v>
       </c>
       <c r="AH30" s="10" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="AI30" s="11" t="n">
         <v>0</v>
@@ -6057,10 +6405,10 @@
         <v>80159</v>
       </c>
       <c r="AK30" s="9" t="n">
-        <v>12726.04</v>
+        <v>13825.82</v>
       </c>
       <c r="AL30" s="10" t="n">
-        <v>0.0011</v>
+        <v>0.0012</v>
       </c>
       <c r="AM30" s="11" t="n">
         <v>0</v>
@@ -6069,7 +6417,7 @@
         <v>80159</v>
       </c>
       <c r="AO30" s="9" t="n">
-        <v>12868.73</v>
+        <v>12726.04</v>
       </c>
       <c r="AP30" s="10" t="n">
         <v>0.0011</v>
@@ -6081,7 +6429,7 @@
         <v>80159</v>
       </c>
       <c r="AS30" s="9" t="n">
-        <v>11621.45</v>
+        <v>12868.73</v>
       </c>
       <c r="AT30" s="10" t="n">
         <v>0.0011</v>
@@ -6093,10 +6441,10 @@
         <v>80159</v>
       </c>
       <c r="AW30" s="9" t="n">
-        <v>10722.07</v>
+        <v>11621.45</v>
       </c>
       <c r="AX30" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0011</v>
       </c>
       <c r="AY30" s="11" t="n">
         <v>0</v>
@@ -6105,10 +6453,10 @@
         <v>80159</v>
       </c>
       <c r="BA30" s="9" t="n">
-        <v>9198.25</v>
+        <v>10722.07</v>
       </c>
       <c r="BB30" s="10" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="BC30" s="11" t="n">
         <v>0</v>
@@ -6117,10 +6465,10 @@
         <v>80159</v>
       </c>
       <c r="BE30" s="9" t="n">
-        <v>8997.450000000001</v>
+        <v>9198.25</v>
       </c>
       <c r="BF30" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="BG30" s="11" t="n">
         <v>0</v>
@@ -6129,10 +6477,10 @@
         <v>80159</v>
       </c>
       <c r="BI30" s="9" t="n">
-        <v>7401.52</v>
+        <v>8997.450000000001</v>
       </c>
       <c r="BJ30" s="10" t="n">
-        <v>0.0008</v>
+        <v>0.001</v>
       </c>
       <c r="BK30" s="11" t="n">
         <v>0</v>
@@ -6141,101 +6489,97 @@
         <v>80159</v>
       </c>
       <c r="BM30" s="9" t="n">
-        <v>7463.48</v>
+        <v>7401.52</v>
       </c>
       <c r="BN30" s="10" t="n">
         <v>0.0008</v>
       </c>
-      <c r="BO30" s="11" t="n"/>
+      <c r="BO30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP30" s="8" t="n">
+        <v>80159</v>
+      </c>
+      <c r="BQ30" s="9" t="n">
+        <v>7463.48</v>
+      </c>
+      <c r="BR30" s="10" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="BS30" s="11" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Indus Towers Limited</t>
+          <t>Mahanagar Gas Limited</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>INE121J01017</t>
+          <t>INE002S01010</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Telecom - Services</t>
+          <t>Gas</t>
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>865823</v>
+        <v>898709</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>3549.44</v>
+        <v>9840.860000000001</v>
       </c>
       <c r="F31" s="10" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="G31" s="11" t="n">
+        <v>1.391570112458819</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>375782</v>
+      </c>
+      <c r="I31" s="9" t="n">
+        <v>4267.57</v>
+      </c>
+      <c r="J31" s="10" t="n">
         <v>0.0003</v>
       </c>
-      <c r="G31" s="11" t="n">
-        <v>0.21800226487821</v>
-      </c>
-      <c r="H31" s="8" t="n">
-        <v>710855</v>
-      </c>
-      <c r="I31" s="9" t="n">
-        <v>2972.44</v>
-      </c>
-      <c r="J31" s="10" t="n">
-        <v>0.0002</v>
-      </c>
       <c r="K31" s="11" t="n">
-        <v>0</v>
+        <v>6.08421151852201</v>
       </c>
       <c r="L31" s="8" t="n">
-        <v>710855</v>
+        <v>53045</v>
       </c>
       <c r="M31" s="9" t="n">
-        <v>3234.03</v>
+        <v>492.1</v>
       </c>
       <c r="N31" s="10" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="O31" s="11" t="n">
-        <v>0</v>
+        <v>16.42036124794745</v>
       </c>
       <c r="P31" s="8" t="n">
-        <v>710855</v>
+        <v>3045</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>3158.33</v>
+        <v>37.14</v>
       </c>
       <c r="R31" s="10" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="S31" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v>710855</v>
-      </c>
-      <c r="U31" s="9" t="n">
-        <v>2976.71</v>
-      </c>
-      <c r="V31" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="W31" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" s="8" t="n">
-        <v>710855</v>
-      </c>
-      <c r="Y31" s="9" t="n">
-        <v>2850.8839775</v>
-      </c>
-      <c r="Z31" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AA31" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="T31" s="8" t="n"/>
+      <c r="U31" s="9" t="n"/>
+      <c r="V31" s="10" t="n"/>
+      <c r="W31" s="11" t="n"/>
+      <c r="X31" s="8" t="n"/>
+      <c r="Y31" s="9" t="n"/>
+      <c r="Z31" s="10" t="n"/>
+      <c r="AA31" s="11" t="n"/>
       <c r="AB31" s="8" t="n"/>
       <c r="AC31" s="9" t="n"/>
       <c r="AD31" s="10" t="n"/>
@@ -6276,75 +6620,111 @@
       <c r="BM31" s="9" t="n"/>
       <c r="BN31" s="10" t="n"/>
       <c r="BO31" s="11" t="n"/>
+      <c r="BP31" s="8" t="n"/>
+      <c r="BQ31" s="9" t="n"/>
+      <c r="BR31" s="10" t="n"/>
+      <c r="BS31" s="11" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Mahanagar Gas Limited</t>
+          <t>Indus Towers Limited</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>INE002S01010</t>
+          <t>INE121J01017</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>Telecom - Services</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>375782</v>
+        <v>865823</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>4267.57</v>
+        <v>3827.37</v>
       </c>
       <c r="F32" s="10" t="n">
         <v>0.0003</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>6.08421151852201</v>
+        <v>0</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>53045</v>
+        <v>865823</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>492.1</v>
+        <v>3549.44</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>16.42036124794745</v>
+        <v>0.21800226487821</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>3045</v>
+        <v>710855</v>
       </c>
       <c r="M32" s="9" t="n">
-        <v>37.14</v>
+        <v>2972.44</v>
       </c>
       <c r="N32" s="10" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="O32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="8" t="n">
+        <v>710855</v>
+      </c>
+      <c r="Q32" s="9" t="n">
+        <v>3234.03</v>
+      </c>
+      <c r="R32" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="S32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v>710855</v>
+      </c>
+      <c r="U32" s="9" t="n">
+        <v>3158.33</v>
+      </c>
+      <c r="V32" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="W32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" s="8" t="n">
+        <v>710855</v>
+      </c>
+      <c r="Y32" s="9" t="n">
+        <v>2976.71</v>
+      </c>
+      <c r="Z32" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AA32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="8" t="n">
+        <v>710855</v>
+      </c>
+      <c r="AC32" s="9" t="n">
+        <v>2850.8839775</v>
+      </c>
+      <c r="AD32" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AE32" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="P32" s="8" t="n"/>
-      <c r="Q32" s="9" t="n"/>
-      <c r="R32" s="10" t="n"/>
-      <c r="S32" s="11" t="n"/>
-      <c r="T32" s="8" t="n"/>
-      <c r="U32" s="9" t="n"/>
-      <c r="V32" s="10" t="n"/>
-      <c r="W32" s="11" t="n"/>
-      <c r="X32" s="8" t="n"/>
-      <c r="Y32" s="9" t="n"/>
-      <c r="Z32" s="10" t="n"/>
-      <c r="AA32" s="11" t="n"/>
-      <c r="AB32" s="8" t="n"/>
-      <c r="AC32" s="9" t="n"/>
-      <c r="AD32" s="10" t="n"/>
-      <c r="AE32" s="11" t="n"/>
       <c r="AF32" s="8" t="n"/>
       <c r="AG32" s="9" t="n"/>
       <c r="AH32" s="10" t="n"/>
@@ -6381,6 +6761,10 @@
       <c r="BM32" s="9" t="n"/>
       <c r="BN32" s="10" t="n"/>
       <c r="BO32" s="11" t="n"/>
+      <c r="BP32" s="8" t="n"/>
+      <c r="BQ32" s="9" t="n"/>
+      <c r="BR32" s="10" t="n"/>
+      <c r="BS32" s="11" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -6402,10 +6786,10 @@
         <v>464063</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>2198.5</v>
+        <v>2071.81</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="G33" s="11" t="n">
         <v>0</v>
@@ -6414,7 +6798,7 @@
         <v>464063</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>2065.08</v>
+        <v>2198.5</v>
       </c>
       <c r="J33" s="10" t="n">
         <v>0.0002</v>
@@ -6426,30 +6810,38 @@
         <v>464063</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>2188.75</v>
+        <v>2065.08</v>
       </c>
       <c r="N33" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="O33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="8" t="n">
+        <v>464063</v>
+      </c>
+      <c r="Q33" s="9" t="n">
+        <v>2188.75</v>
+      </c>
+      <c r="R33" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="S33" s="11" t="n">
         <v>0.004302331872531515</v>
       </c>
-      <c r="P33" s="8" t="n">
+      <c r="T33" s="8" t="n">
         <v>462075</v>
       </c>
-      <c r="Q33" s="9" t="n">
+      <c r="U33" s="9" t="n">
         <v>1932.4</v>
       </c>
-      <c r="R33" s="10" t="n">
+      <c r="V33" s="10" t="n">
         <v>0.0001</v>
       </c>
-      <c r="S33" s="11" t="n">
+      <c r="W33" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="T33" s="8" t="n"/>
-      <c r="U33" s="9" t="n"/>
-      <c r="V33" s="10" t="n"/>
-      <c r="W33" s="11" t="n"/>
       <c r="X33" s="8" t="n"/>
       <c r="Y33" s="9" t="n"/>
       <c r="Z33" s="10" t="n"/>
@@ -6494,28 +6886,32 @@
       <c r="BM33" s="9" t="n"/>
       <c r="BN33" s="10" t="n"/>
       <c r="BO33" s="11" t="n"/>
+      <c r="BP33" s="8" t="n"/>
+      <c r="BQ33" s="9" t="n"/>
+      <c r="BR33" s="10" t="n"/>
+      <c r="BS33" s="11" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Nesco Limited</t>
+          <t>Swaraj Engines Limited</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>INE317F01035</t>
+          <t>INE277A01016</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Commercial Services &amp; Supplies</t>
+          <t>Industrial Products</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>1862.26</v>
+        <v>1809.43</v>
       </c>
       <c r="F34" s="10" t="n">
         <v>0.0001</v>
@@ -6524,10 +6920,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>1538.11</v>
+        <v>1871.38</v>
       </c>
       <c r="J34" s="10" t="n">
         <v>0.0001</v>
@@ -6536,10 +6932,10 @@
         <v>0</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="M34" s="9" t="n">
-        <v>1704.36</v>
+        <v>1564.88</v>
       </c>
       <c r="N34" s="10" t="n">
         <v>0.0001</v>
@@ -6548,10 +6944,10 @@
         <v>0</v>
       </c>
       <c r="P34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>1728.63</v>
+        <v>1700.33</v>
       </c>
       <c r="R34" s="10" t="n">
         <v>0.0001</v>
@@ -6560,10 +6956,10 @@
         <v>0</v>
       </c>
       <c r="T34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="U34" s="9" t="n">
-        <v>1858.32</v>
+        <v>1637.61</v>
       </c>
       <c r="V34" s="10" t="n">
         <v>0.0001</v>
@@ -6572,34 +6968,34 @@
         <v>0</v>
       </c>
       <c r="X34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="Y34" s="9" t="n">
-        <v>1947.66</v>
+        <v>1691.91</v>
       </c>
       <c r="Z34" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="AA34" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AB34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AC34" s="9" t="n">
-        <v>2076.6</v>
+        <v>1764.08</v>
       </c>
       <c r="AD34" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="AE34" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AF34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AG34" s="9" t="n">
-        <v>1987.1</v>
+        <v>1892.15</v>
       </c>
       <c r="AH34" s="10" t="n">
         <v>0.0002</v>
@@ -6608,10 +7004,10 @@
         <v>0</v>
       </c>
       <c r="AJ34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AK34" s="9" t="n">
-        <v>2130.6</v>
+        <v>1955.38</v>
       </c>
       <c r="AL34" s="10" t="n">
         <v>0.0002</v>
@@ -6620,10 +7016,10 @@
         <v>0</v>
       </c>
       <c r="AN34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AO34" s="9" t="n">
-        <v>2091.16</v>
+        <v>1897.21</v>
       </c>
       <c r="AP34" s="10" t="n">
         <v>0.0002</v>
@@ -6632,67 +7028,109 @@
         <v>0</v>
       </c>
       <c r="AR34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AS34" s="9" t="n">
-        <v>1766.62</v>
+        <v>1983.66</v>
       </c>
       <c r="AT34" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="AU34" s="11" t="n">
-        <v>0.6954140540298874</v>
+        <v>0</v>
       </c>
       <c r="AV34" s="8" t="n">
-        <v>89469</v>
+        <v>47293</v>
       </c>
       <c r="AW34" s="9" t="n">
-        <v>828.48</v>
+        <v>1867.41</v>
       </c>
       <c r="AX34" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AY34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="BA34" s="9" t="n">
+        <v>1857.76</v>
+      </c>
+      <c r="BB34" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="BC34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD34" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="BE34" s="9" t="n">
+        <v>1925.39</v>
+      </c>
+      <c r="BF34" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="BG34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH34" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="BI34" s="9" t="n">
+        <v>1844.17</v>
+      </c>
+      <c r="BJ34" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="BK34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL34" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="BM34" s="9" t="n">
+        <v>1236.83</v>
+      </c>
+      <c r="BN34" s="10" t="n">
         <v>0.0001</v>
       </c>
-      <c r="AY34" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ34" s="8" t="n"/>
-      <c r="BA34" s="9" t="n"/>
-      <c r="BB34" s="10" t="n"/>
-      <c r="BC34" s="11" t="n"/>
-      <c r="BD34" s="8" t="n"/>
-      <c r="BE34" s="9" t="n"/>
-      <c r="BF34" s="10" t="n"/>
-      <c r="BG34" s="11" t="n"/>
-      <c r="BH34" s="8" t="n"/>
-      <c r="BI34" s="9" t="n"/>
-      <c r="BJ34" s="10" t="n"/>
-      <c r="BK34" s="11" t="n"/>
-      <c r="BL34" s="8" t="n"/>
-      <c r="BM34" s="9" t="n"/>
-      <c r="BN34" s="10" t="n"/>
-      <c r="BO34" s="11" t="n"/>
+      <c r="BO34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP34" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="BQ34" s="9" t="n">
+        <v>1612.64</v>
+      </c>
+      <c r="BR34" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="BS34" s="11" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Swaraj Engines Limited</t>
+          <t>Nesco Limited</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>INE277A01016</t>
+          <t>INE317F01035</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Industrial Products</t>
+          <t>Commercial Services &amp; Supplies</t>
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>1871.38</v>
+        <v>1780.2</v>
       </c>
       <c r="F35" s="10" t="n">
         <v>0.0001</v>
@@ -6701,10 +7139,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>1564.88</v>
+        <v>1862.26</v>
       </c>
       <c r="J35" s="10" t="n">
         <v>0.0001</v>
@@ -6713,10 +7151,10 @@
         <v>0</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>1700.33</v>
+        <v>1538.11</v>
       </c>
       <c r="N35" s="10" t="n">
         <v>0.0001</v>
@@ -6725,10 +7163,10 @@
         <v>0</v>
       </c>
       <c r="P35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>1637.61</v>
+        <v>1704.36</v>
       </c>
       <c r="R35" s="10" t="n">
         <v>0.0001</v>
@@ -6737,10 +7175,10 @@
         <v>0</v>
       </c>
       <c r="T35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="U35" s="9" t="n">
-        <v>1691.91</v>
+        <v>1728.63</v>
       </c>
       <c r="V35" s="10" t="n">
         <v>0.0001</v>
@@ -6749,10 +7187,10 @@
         <v>0</v>
       </c>
       <c r="X35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="Y35" s="9" t="n">
-        <v>1764.08</v>
+        <v>1858.32</v>
       </c>
       <c r="Z35" s="10" t="n">
         <v>0.0001</v>
@@ -6761,10 +7199,10 @@
         <v>0</v>
       </c>
       <c r="AB35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AC35" s="9" t="n">
-        <v>1892.15</v>
+        <v>1947.66</v>
       </c>
       <c r="AD35" s="10" t="n">
         <v>0.0002</v>
@@ -6773,10 +7211,10 @@
         <v>0</v>
       </c>
       <c r="AF35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AG35" s="9" t="n">
-        <v>1955.38</v>
+        <v>2076.6</v>
       </c>
       <c r="AH35" s="10" t="n">
         <v>0.0002</v>
@@ -6785,10 +7223,10 @@
         <v>0</v>
       </c>
       <c r="AJ35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AK35" s="9" t="n">
-        <v>1897.21</v>
+        <v>1987.1</v>
       </c>
       <c r="AL35" s="10" t="n">
         <v>0.0002</v>
@@ -6797,10 +7235,10 @@
         <v>0</v>
       </c>
       <c r="AN35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AO35" s="9" t="n">
-        <v>1983.66</v>
+        <v>2130.6</v>
       </c>
       <c r="AP35" s="10" t="n">
         <v>0.0002</v>
@@ -6809,10 +7247,10 @@
         <v>0</v>
       </c>
       <c r="AR35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AS35" s="9" t="n">
-        <v>1867.41</v>
+        <v>2091.16</v>
       </c>
       <c r="AT35" s="10" t="n">
         <v>0.0002</v>
@@ -6821,63 +7259,45 @@
         <v>0</v>
       </c>
       <c r="AV35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AW35" s="9" t="n">
-        <v>1857.76</v>
+        <v>1766.62</v>
       </c>
       <c r="AX35" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="AY35" s="11" t="n">
-        <v>0</v>
+        <v>0.6954140540298874</v>
       </c>
       <c r="AZ35" s="8" t="n">
-        <v>47293</v>
+        <v>89469</v>
       </c>
       <c r="BA35" s="9" t="n">
-        <v>1925.39</v>
+        <v>828.48</v>
       </c>
       <c r="BB35" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="BC35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD35" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="BE35" s="9" t="n">
-        <v>1844.17</v>
-      </c>
-      <c r="BF35" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="BG35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH35" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="BI35" s="9" t="n">
-        <v>1236.83</v>
-      </c>
-      <c r="BJ35" s="10" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="BK35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL35" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="BM35" s="9" t="n">
-        <v>1612.64</v>
-      </c>
-      <c r="BN35" s="10" t="n">
-        <v>0.0002</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="BD35" s="8" t="n"/>
+      <c r="BE35" s="9" t="n"/>
+      <c r="BF35" s="10" t="n"/>
+      <c r="BG35" s="11" t="n"/>
+      <c r="BH35" s="8" t="n"/>
+      <c r="BI35" s="9" t="n"/>
+      <c r="BJ35" s="10" t="n"/>
+      <c r="BK35" s="11" t="n"/>
+      <c r="BL35" s="8" t="n"/>
+      <c r="BM35" s="9" t="n"/>
+      <c r="BN35" s="10" t="n"/>
       <c r="BO35" s="11" t="n"/>
+      <c r="BP35" s="8" t="n"/>
+      <c r="BQ35" s="9" t="n"/>
+      <c r="BR35" s="10" t="n"/>
+      <c r="BS35" s="11" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -6898,53 +7318,45 @@
       <c r="D36" s="8" t="n"/>
       <c r="E36" s="9" t="n"/>
       <c r="F36" s="10" t="n"/>
-      <c r="G36" s="11" t="n">
+      <c r="G36" s="11" t="n"/>
+      <c r="H36" s="8" t="n"/>
+      <c r="I36" s="9" t="n"/>
+      <c r="J36" s="10" t="n"/>
+      <c r="K36" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="H36" s="8" t="n">
+      <c r="L36" s="8" t="n">
         <v>2274074</v>
       </c>
-      <c r="I36" s="9" t="n">
+      <c r="M36" s="9" t="n">
         <v>47368.96</v>
       </c>
-      <c r="J36" s="10" t="n">
+      <c r="N36" s="10" t="n">
         <v>0.0037</v>
       </c>
-      <c r="K36" s="11" t="n">
+      <c r="O36" s="11" t="n">
         <v>-0.2174731122669314</v>
       </c>
-      <c r="L36" s="8" t="n">
+      <c r="P36" s="8" t="n">
         <v>2906065</v>
       </c>
-      <c r="M36" s="9" t="n">
+      <c r="Q36" s="9" t="n">
         <v>69277.67999999999</v>
       </c>
-      <c r="N36" s="10" t="n">
+      <c r="R36" s="10" t="n">
         <v>0.0052</v>
       </c>
-      <c r="O36" s="11" t="n">
+      <c r="S36" s="11" t="n">
         <v>-0.3062750860930125</v>
-      </c>
-      <c r="P36" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="Q36" s="9" t="n">
-        <v>96591.67</v>
-      </c>
-      <c r="R36" s="10" t="n">
-        <v>0.0072</v>
-      </c>
-      <c r="S36" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="T36" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="U36" s="9" t="n">
-        <v>97173.95</v>
+        <v>96591.67</v>
       </c>
       <c r="V36" s="10" t="n">
-        <v>0.0073</v>
+        <v>0.0072</v>
       </c>
       <c r="W36" s="11" t="n">
         <v>0</v>
@@ -6953,10 +7365,10 @@
         <v>4189074</v>
       </c>
       <c r="Y36" s="9" t="n">
-        <v>96721.53</v>
+        <v>97173.95</v>
       </c>
       <c r="Z36" s="10" t="n">
-        <v>0.0075</v>
+        <v>0.0073</v>
       </c>
       <c r="AA36" s="11" t="n">
         <v>0</v>
@@ -6965,10 +7377,10 @@
         <v>4189074</v>
       </c>
       <c r="AC36" s="9" t="n">
-        <v>95502.50999999999</v>
+        <v>96721.53</v>
       </c>
       <c r="AD36" s="10" t="n">
-        <v>0.0076</v>
+        <v>0.0075</v>
       </c>
       <c r="AE36" s="11" t="n">
         <v>0</v>
@@ -6977,10 +7389,10 @@
         <v>4189074</v>
       </c>
       <c r="AG36" s="9" t="n">
-        <v>96130.87</v>
+        <v>95502.50999999999</v>
       </c>
       <c r="AH36" s="10" t="n">
-        <v>0.008</v>
+        <v>0.0076</v>
       </c>
       <c r="AI36" s="11" t="n">
         <v>0</v>
@@ -6989,10 +7401,10 @@
         <v>4189074</v>
       </c>
       <c r="AK36" s="9" t="n">
-        <v>95904.66</v>
+        <v>96130.87</v>
       </c>
       <c r="AL36" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.008</v>
       </c>
       <c r="AM36" s="11" t="n">
         <v>0</v>
@@ -7001,10 +7413,10 @@
         <v>4189074</v>
       </c>
       <c r="AO36" s="9" t="n">
-        <v>112108</v>
+        <v>95904.66</v>
       </c>
       <c r="AP36" s="10" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0083</v>
       </c>
       <c r="AQ36" s="11" t="n">
         <v>0</v>
@@ -7013,10 +7425,10 @@
         <v>4189074</v>
       </c>
       <c r="AS36" s="9" t="n">
-        <v>102435.43</v>
+        <v>112108</v>
       </c>
       <c r="AT36" s="10" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="AU36" s="11" t="n">
         <v>0</v>
@@ -7025,10 +7437,10 @@
         <v>4189074</v>
       </c>
       <c r="AW36" s="9" t="n">
-        <v>103562.29</v>
+        <v>102435.43</v>
       </c>
       <c r="AX36" s="10" t="n">
-        <v>0.01</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="AY36" s="11" t="n">
         <v>0</v>
@@ -7037,10 +7449,10 @@
         <v>4189074</v>
       </c>
       <c r="BA36" s="9" t="n">
-        <v>112061.92</v>
+        <v>103562.29</v>
       </c>
       <c r="BB36" s="10" t="n">
-        <v>0.0114</v>
+        <v>0.01</v>
       </c>
       <c r="BC36" s="11" t="n">
         <v>0</v>
@@ -7049,10 +7461,10 @@
         <v>4189074</v>
       </c>
       <c r="BE36" s="9" t="n">
-        <v>107022.46</v>
+        <v>112061.92</v>
       </c>
       <c r="BF36" s="10" t="n">
-        <v>0.0115</v>
+        <v>0.0114</v>
       </c>
       <c r="BG36" s="11" t="n">
         <v>0</v>
@@ -7061,10 +7473,10 @@
         <v>4189074</v>
       </c>
       <c r="BI36" s="9" t="n">
-        <v>109571.51</v>
+        <v>107022.46</v>
       </c>
       <c r="BJ36" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.0115</v>
       </c>
       <c r="BK36" s="11" t="n">
         <v>0</v>
@@ -7073,12 +7485,24 @@
         <v>4189074</v>
       </c>
       <c r="BM36" s="9" t="n">
+        <v>109571.51</v>
+      </c>
+      <c r="BN36" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="BO36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP36" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="BQ36" s="9" t="n">
         <v>116089.71</v>
       </c>
-      <c r="BN36" s="10" t="n">
+      <c r="BR36" s="10" t="n">
         <v>0.0129</v>
       </c>
-      <c r="BO36" s="11" t="n"/>
+      <c r="BS36" s="11" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -7107,25 +7531,25 @@
       <c r="L37" s="8" t="n"/>
       <c r="M37" s="9" t="n"/>
       <c r="N37" s="10" t="n"/>
-      <c r="O37" s="11" t="n">
+      <c r="O37" s="11" t="n"/>
+      <c r="P37" s="8" t="n"/>
+      <c r="Q37" s="9" t="n"/>
+      <c r="R37" s="10" t="n"/>
+      <c r="S37" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="P37" s="8" t="n">
+      <c r="T37" s="8" t="n">
         <v>795472</v>
       </c>
-      <c r="Q37" s="9" t="n">
+      <c r="U37" s="9" t="n">
         <v>20109.53</v>
       </c>
-      <c r="R37" s="10" t="n">
+      <c r="V37" s="10" t="n">
         <v>0.0015</v>
       </c>
-      <c r="S37" s="11" t="n">
+      <c r="W37" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="T37" s="8" t="n"/>
-      <c r="U37" s="9" t="n"/>
-      <c r="V37" s="10" t="n"/>
-      <c r="W37" s="11" t="n"/>
       <c r="X37" s="8" t="n"/>
       <c r="Y37" s="9" t="n"/>
       <c r="Z37" s="10" t="n"/>
@@ -7170,6 +7594,10 @@
       <c r="BM37" s="9" t="n"/>
       <c r="BN37" s="10" t="n"/>
       <c r="BO37" s="11" t="n"/>
+      <c r="BP37" s="8" t="n"/>
+      <c r="BQ37" s="9" t="n"/>
+      <c r="BR37" s="10" t="n"/>
+      <c r="BS37" s="11" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -7202,113 +7630,105 @@
       <c r="P38" s="8" t="n"/>
       <c r="Q38" s="9" t="n"/>
       <c r="R38" s="10" t="n"/>
-      <c r="S38" s="11" t="n">
+      <c r="S38" s="11" t="n"/>
+      <c r="T38" s="8" t="n"/>
+      <c r="U38" s="9" t="n"/>
+      <c r="V38" s="10" t="n"/>
+      <c r="W38" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="T38" s="8" t="n">
+      <c r="X38" s="8" t="n">
         <v>24621592</v>
       </c>
-      <c r="U38" s="9" t="n">
+      <c r="Y38" s="9" t="n">
         <v>541945.86</v>
       </c>
-      <c r="V38" s="10" t="n">
+      <c r="Z38" s="10" t="n">
         <v>0.0407</v>
       </c>
-      <c r="W38" s="11" t="n">
+      <c r="AA38" s="11" t="n">
         <v>0.01296144774839237</v>
       </c>
-      <c r="X38" s="8" t="n">
+      <c r="AB38" s="8" t="n">
         <v>24306544</v>
       </c>
-      <c r="Y38" s="9" t="n">
+      <c r="AC38" s="9" t="n">
         <v>516368.22</v>
       </c>
-      <c r="Z38" s="10" t="n">
+      <c r="AD38" s="10" t="n">
         <v>0.0398</v>
       </c>
-      <c r="AA38" s="11" t="n">
+      <c r="AE38" s="11" t="n">
         <v>0.004192884502844551</v>
-      </c>
-      <c r="AB38" s="8" t="n">
-        <v>24205055</v>
-      </c>
-      <c r="AC38" s="9" t="n">
-        <v>508838.67</v>
-      </c>
-      <c r="AD38" s="10" t="n">
-        <v>0.0404</v>
-      </c>
-      <c r="AE38" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="AF38" s="8" t="n">
         <v>24205055</v>
       </c>
       <c r="AG38" s="9" t="n">
+        <v>508838.67</v>
+      </c>
+      <c r="AH38" s="10" t="n">
+        <v>0.0404</v>
+      </c>
+      <c r="AI38" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" s="8" t="n">
+        <v>24205055</v>
+      </c>
+      <c r="AK38" s="9" t="n">
         <v>482334.13</v>
       </c>
-      <c r="AH38" s="10" t="n">
+      <c r="AL38" s="10" t="n">
         <v>0.0403</v>
       </c>
-      <c r="AI38" s="11" t="n">
+      <c r="AM38" s="11" t="n">
         <v>0.03407788338216907</v>
       </c>
-      <c r="AJ38" s="8" t="n">
+      <c r="AN38" s="8" t="n">
         <v>23407381</v>
       </c>
-      <c r="AK38" s="9" t="n">
+      <c r="AO38" s="9" t="n">
         <v>458854.89</v>
       </c>
-      <c r="AL38" s="10" t="n">
+      <c r="AP38" s="10" t="n">
         <v>0.0399</v>
       </c>
-      <c r="AM38" s="11" t="n">
+      <c r="AQ38" s="11" t="n">
         <v>0.06425892329321918</v>
       </c>
-      <c r="AN38" s="8" t="n">
+      <c r="AR38" s="8" t="n">
         <v>21994066</v>
       </c>
-      <c r="AO38" s="9" t="n">
+      <c r="AS38" s="9" t="n">
         <v>435174.59</v>
       </c>
-      <c r="AP38" s="10" t="n">
+      <c r="AT38" s="10" t="n">
         <v>0.0384</v>
       </c>
-      <c r="AQ38" s="11" t="n">
+      <c r="AU38" s="11" t="n">
         <v>0.07428402120388222</v>
       </c>
-      <c r="AR38" s="8" t="n">
+      <c r="AV38" s="8" t="n">
         <v>20473232</v>
       </c>
-      <c r="AS38" s="9" t="n">
+      <c r="AW38" s="9" t="n">
         <v>442938.37</v>
       </c>
-      <c r="AT38" s="10" t="n">
+      <c r="AX38" s="10" t="n">
         <v>0.0401</v>
       </c>
-      <c r="AU38" s="11" t="n">
+      <c r="AY38" s="11" t="n">
         <v>0.03644973136547983</v>
-      </c>
-      <c r="AV38" s="8" t="n">
-        <v>19753232</v>
-      </c>
-      <c r="AW38" s="9" t="n">
-        <v>409820.3</v>
-      </c>
-      <c r="AX38" s="10" t="n">
-        <v>0.0395</v>
-      </c>
-      <c r="AY38" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="AZ38" s="8" t="n">
         <v>19753232</v>
       </c>
       <c r="BA38" s="9" t="n">
-        <v>436171.12</v>
+        <v>409820.3</v>
       </c>
       <c r="BB38" s="10" t="n">
-        <v>0.0443</v>
+        <v>0.0395</v>
       </c>
       <c r="BC38" s="11" t="n">
         <v>0</v>
@@ -7317,10 +7737,10 @@
         <v>19753232</v>
       </c>
       <c r="BE38" s="9" t="n">
-        <v>428882.17</v>
+        <v>436171.12</v>
       </c>
       <c r="BF38" s="10" t="n">
-        <v>0.0459</v>
+        <v>0.0443</v>
       </c>
       <c r="BG38" s="11" t="n">
         <v>0</v>
@@ -7329,10 +7749,10 @@
         <v>19753232</v>
       </c>
       <c r="BI38" s="9" t="n">
-        <v>375894.13</v>
+        <v>428882.17</v>
       </c>
       <c r="BJ38" s="10" t="n">
-        <v>0.0427</v>
+        <v>0.0459</v>
       </c>
       <c r="BK38" s="11" t="n">
         <v>0</v>
@@ -7341,12 +7761,24 @@
         <v>19753232</v>
       </c>
       <c r="BM38" s="9" t="n">
+        <v>375894.13</v>
+      </c>
+      <c r="BN38" s="10" t="n">
+        <v>0.0427</v>
+      </c>
+      <c r="BO38" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP38" s="8" t="n">
+        <v>19753232</v>
+      </c>
+      <c r="BQ38" s="9" t="n">
         <v>375568.2</v>
       </c>
-      <c r="BN38" s="10" t="n">
+      <c r="BR38" s="10" t="n">
         <v>0.0419</v>
       </c>
-      <c r="BO38" s="11" t="n"/>
+      <c r="BS38" s="11" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -7403,79 +7835,83 @@
       <c r="AN39" s="8" t="n"/>
       <c r="AO39" s="9" t="n"/>
       <c r="AP39" s="10" t="n"/>
-      <c r="AQ39" s="11" t="n">
+      <c r="AQ39" s="11" t="n"/>
+      <c r="AR39" s="8" t="n"/>
+      <c r="AS39" s="9" t="n"/>
+      <c r="AT39" s="10" t="n"/>
+      <c r="AU39" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="AR39" s="8" t="n">
+      <c r="AV39" s="8" t="n">
         <v>591805</v>
       </c>
-      <c r="AS39" s="9" t="n">
+      <c r="AW39" s="9" t="n">
         <v>5149</v>
       </c>
-      <c r="AT39" s="10" t="n">
+      <c r="AX39" s="10" t="n">
         <v>0.0005</v>
       </c>
-      <c r="AU39" s="11" t="n">
+      <c r="AY39" s="11" t="n">
         <v>-0.8902567225534253</v>
       </c>
-      <c r="AV39" s="8" t="n">
+      <c r="AZ39" s="8" t="n">
         <v>5392631</v>
       </c>
-      <c r="AW39" s="9" t="n">
+      <c r="BA39" s="9" t="n">
         <v>43674.92</v>
       </c>
-      <c r="AX39" s="10" t="n">
+      <c r="BB39" s="10" t="n">
         <v>0.0042</v>
       </c>
-      <c r="AY39" s="11" t="n">
+      <c r="BC39" s="11" t="n">
         <v>-0.3719237093069153</v>
       </c>
-      <c r="AZ39" s="8" t="n">
+      <c r="BD39" s="8" t="n">
         <v>8585949</v>
       </c>
-      <c r="BA39" s="9" t="n">
+      <c r="BE39" s="9" t="n">
         <v>56044.78</v>
       </c>
-      <c r="BB39" s="10" t="n">
+      <c r="BF39" s="10" t="n">
         <v>0.0057</v>
       </c>
-      <c r="BC39" s="11" t="n">
+      <c r="BG39" s="11" t="n">
         <v>-0.2132577936597328</v>
       </c>
-      <c r="BD39" s="8" t="n">
+      <c r="BH39" s="8" t="n">
         <v>10913294</v>
       </c>
-      <c r="BE39" s="9" t="n">
+      <c r="BI39" s="9" t="n">
         <v>67154.95</v>
       </c>
-      <c r="BF39" s="10" t="n">
+      <c r="BJ39" s="10" t="n">
         <v>0.0072</v>
       </c>
-      <c r="BG39" s="11" t="n">
+      <c r="BK39" s="11" t="n">
         <v>-0.09462389658963724</v>
-      </c>
-      <c r="BH39" s="8" t="n">
-        <v>12053879</v>
-      </c>
-      <c r="BI39" s="9" t="n">
-        <v>70937.08</v>
-      </c>
-      <c r="BJ39" s="10" t="n">
-        <v>0.0081</v>
-      </c>
-      <c r="BK39" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="BL39" s="8" t="n">
         <v>12053879</v>
       </c>
       <c r="BM39" s="9" t="n">
+        <v>70937.08</v>
+      </c>
+      <c r="BN39" s="10" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="BO39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP39" s="8" t="n">
+        <v>12053879</v>
+      </c>
+      <c r="BQ39" s="9" t="n">
         <v>76801.28999999999</v>
       </c>
-      <c r="BN39" s="10" t="n">
+      <c r="BR39" s="10" t="n">
         <v>0.0086</v>
       </c>
-      <c r="BO39" s="11" t="n"/>
+      <c r="BS39" s="11" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -7508,29 +7944,21 @@
       <c r="P40" s="8" t="n"/>
       <c r="Q40" s="9" t="n"/>
       <c r="R40" s="10" t="n"/>
-      <c r="S40" s="11" t="n">
+      <c r="S40" s="11" t="n"/>
+      <c r="T40" s="8" t="n"/>
+      <c r="U40" s="9" t="n"/>
+      <c r="V40" s="10" t="n"/>
+      <c r="W40" s="11" t="n">
         <v>-1</v>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="U40" s="9" t="n">
-        <v>88833.99000000001</v>
-      </c>
-      <c r="V40" s="10" t="n">
-        <v>0.0067</v>
-      </c>
-      <c r="W40" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="X40" s="8" t="n">
         <v>797719</v>
       </c>
       <c r="Y40" s="9" t="n">
-        <v>80358.22</v>
+        <v>88833.99000000001</v>
       </c>
       <c r="Z40" s="10" t="n">
-        <v>0.0062</v>
+        <v>0.0067</v>
       </c>
       <c r="AA40" s="11" t="n">
         <v>0</v>
@@ -7539,10 +7967,10 @@
         <v>797719</v>
       </c>
       <c r="AC40" s="9" t="n">
-        <v>73737.16</v>
+        <v>80358.22</v>
       </c>
       <c r="AD40" s="10" t="n">
-        <v>0.0059</v>
+        <v>0.0062</v>
       </c>
       <c r="AE40" s="11" t="n">
         <v>0</v>
@@ -7551,10 +7979,10 @@
         <v>797719</v>
       </c>
       <c r="AG40" s="9" t="n">
-        <v>62190.17</v>
+        <v>73737.16</v>
       </c>
       <c r="AH40" s="10" t="n">
-        <v>0.0052</v>
+        <v>0.0059</v>
       </c>
       <c r="AI40" s="11" t="n">
         <v>0</v>
@@ -7563,10 +7991,10 @@
         <v>797719</v>
       </c>
       <c r="AK40" s="9" t="n">
-        <v>58951.43</v>
+        <v>62190.17</v>
       </c>
       <c r="AL40" s="10" t="n">
-        <v>0.0051</v>
+        <v>0.0052</v>
       </c>
       <c r="AM40" s="11" t="n">
         <v>0</v>
@@ -7575,10 +8003,10 @@
         <v>797719</v>
       </c>
       <c r="AO40" s="9" t="n">
-        <v>61368.52</v>
+        <v>58951.43</v>
       </c>
       <c r="AP40" s="10" t="n">
-        <v>0.0054</v>
+        <v>0.0051</v>
       </c>
       <c r="AQ40" s="11" t="n">
         <v>0</v>
@@ -7587,10 +8015,10 @@
         <v>797719</v>
       </c>
       <c r="AS40" s="9" t="n">
-        <v>71347.99000000001</v>
+        <v>61368.52</v>
       </c>
       <c r="AT40" s="10" t="n">
-        <v>0.0065</v>
+        <v>0.0054</v>
       </c>
       <c r="AU40" s="11" t="n">
         <v>0</v>
@@ -7599,10 +8027,10 @@
         <v>797719</v>
       </c>
       <c r="AW40" s="9" t="n">
-        <v>52665.41</v>
+        <v>71347.99000000001</v>
       </c>
       <c r="AX40" s="10" t="n">
-        <v>0.0051</v>
+        <v>0.0065</v>
       </c>
       <c r="AY40" s="11" t="n">
         <v>0</v>
@@ -7611,10 +8039,10 @@
         <v>797719</v>
       </c>
       <c r="BA40" s="9" t="n">
-        <v>48884.22</v>
+        <v>52665.41</v>
       </c>
       <c r="BB40" s="10" t="n">
-        <v>0.005</v>
+        <v>0.0051</v>
       </c>
       <c r="BC40" s="11" t="n">
         <v>0</v>
@@ -7623,10 +8051,10 @@
         <v>797719</v>
       </c>
       <c r="BE40" s="9" t="n">
-        <v>42372.84</v>
+        <v>48884.22</v>
       </c>
       <c r="BF40" s="10" t="n">
-        <v>0.0045</v>
+        <v>0.005</v>
       </c>
       <c r="BG40" s="11" t="n">
         <v>0</v>
@@ -7635,24 +8063,36 @@
         <v>797719</v>
       </c>
       <c r="BI40" s="9" t="n">
-        <v>39819.34</v>
+        <v>42372.84</v>
       </c>
       <c r="BJ40" s="10" t="n">
         <v>0.0045</v>
       </c>
       <c r="BK40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL40" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="BM40" s="9" t="n">
+        <v>39819.34</v>
+      </c>
+      <c r="BN40" s="10" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="BO40" s="11" t="n">
         <v>-0.09569612848812428</v>
       </c>
-      <c r="BL40" s="8" t="n">
+      <c r="BP40" s="8" t="n">
         <v>882136</v>
       </c>
-      <c r="BM40" s="9" t="n">
+      <c r="BQ40" s="9" t="n">
         <v>50572.42</v>
       </c>
-      <c r="BN40" s="10" t="n">
+      <c r="BR40" s="10" t="n">
         <v>0.0056</v>
       </c>
-      <c r="BO40" s="11" t="n"/>
+      <c r="BS40" s="11" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -7701,103 +8141,107 @@
       <c r="AF41" s="8" t="n"/>
       <c r="AG41" s="9" t="n"/>
       <c r="AH41" s="10" t="n"/>
-      <c r="AI41" s="11" t="n">
+      <c r="AI41" s="11" t="n"/>
+      <c r="AJ41" s="8" t="n"/>
+      <c r="AK41" s="9" t="n"/>
+      <c r="AL41" s="10" t="n"/>
+      <c r="AM41" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="AJ41" s="8" t="n">
+      <c r="AN41" s="8" t="n">
         <v>218075</v>
       </c>
-      <c r="AK41" s="9" t="n">
+      <c r="AO41" s="9" t="n">
         <v>3019.03</v>
       </c>
-      <c r="AL41" s="10" t="n">
+      <c r="AP41" s="10" t="n">
         <v>0.0003</v>
       </c>
-      <c r="AM41" s="11" t="n">
+      <c r="AQ41" s="11" t="n">
         <v>-0.6148554615199853</v>
       </c>
-      <c r="AN41" s="8" t="n">
+      <c r="AR41" s="8" t="n">
         <v>566216</v>
       </c>
-      <c r="AO41" s="9" t="n">
+      <c r="AS41" s="9" t="n">
         <v>8345.459999999999</v>
       </c>
-      <c r="AP41" s="10" t="n">
+      <c r="AT41" s="10" t="n">
         <v>0.0007</v>
       </c>
-      <c r="AQ41" s="11" t="n">
+      <c r="AU41" s="11" t="n">
         <v>-0.5682871579351869</v>
       </c>
-      <c r="AR41" s="8" t="n">
+      <c r="AV41" s="8" t="n">
         <v>1311557</v>
       </c>
-      <c r="AS41" s="9" t="n">
+      <c r="AW41" s="9" t="n">
         <v>18228.02</v>
       </c>
-      <c r="AT41" s="10" t="n">
+      <c r="AX41" s="10" t="n">
         <v>0.0017</v>
       </c>
-      <c r="AU41" s="11" t="n">
+      <c r="AY41" s="11" t="n">
         <v>-0.2008037316547793</v>
       </c>
-      <c r="AV41" s="8" t="n">
+      <c r="AZ41" s="8" t="n">
         <v>1641095</v>
       </c>
-      <c r="AW41" s="9" t="n">
+      <c r="BA41" s="9" t="n">
         <v>23382.32</v>
       </c>
-      <c r="AX41" s="10" t="n">
+      <c r="BB41" s="10" t="n">
         <v>0.0023</v>
       </c>
-      <c r="AY41" s="11" t="n">
+      <c r="BC41" s="11" t="n">
         <v>-0.1163687388172734</v>
       </c>
-      <c r="AZ41" s="8" t="n">
+      <c r="BD41" s="8" t="n">
         <v>1857217</v>
       </c>
-      <c r="BA41" s="9" t="n">
+      <c r="BE41" s="9" t="n">
         <v>26023.32</v>
       </c>
-      <c r="BB41" s="10" t="n">
+      <c r="BF41" s="10" t="n">
         <v>0.0026</v>
       </c>
-      <c r="BC41" s="11" t="n">
+      <c r="BG41" s="11" t="n">
         <v>-0.03620728307597141</v>
-      </c>
-      <c r="BD41" s="8" t="n">
-        <v>1926988</v>
-      </c>
-      <c r="BE41" s="9" t="n">
-        <v>28941.43</v>
-      </c>
-      <c r="BF41" s="10" t="n">
-        <v>0.0031</v>
-      </c>
-      <c r="BG41" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="BH41" s="8" t="n">
         <v>1926988</v>
       </c>
       <c r="BI41" s="9" t="n">
+        <v>28941.43</v>
+      </c>
+      <c r="BJ41" s="10" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="BK41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL41" s="8" t="n">
+        <v>1926988</v>
+      </c>
+      <c r="BM41" s="9" t="n">
         <v>26117.43</v>
       </c>
-      <c r="BJ41" s="10" t="n">
+      <c r="BN41" s="10" t="n">
         <v>0.003</v>
       </c>
-      <c r="BK41" s="11" t="n">
+      <c r="BO41" s="11" t="n">
         <v>-0.1421734974921662</v>
       </c>
-      <c r="BL41" s="8" t="n">
+      <c r="BP41" s="8" t="n">
         <v>2246361</v>
       </c>
-      <c r="BM41" s="9" t="n">
+      <c r="BQ41" s="9" t="n">
         <v>32421.73</v>
       </c>
-      <c r="BN41" s="10" t="n">
+      <c r="BR41" s="10" t="n">
         <v>0.0036</v>
       </c>
-      <c r="BO41" s="11" t="n"/>
+      <c r="BS41" s="11" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -7866,29 +8310,21 @@
       <c r="AZ42" s="8" t="n"/>
       <c r="BA42" s="9" t="n"/>
       <c r="BB42" s="10" t="n"/>
-      <c r="BC42" s="11" t="n">
+      <c r="BC42" s="11" t="n"/>
+      <c r="BD42" s="8" t="n"/>
+      <c r="BE42" s="9" t="n"/>
+      <c r="BF42" s="10" t="n"/>
+      <c r="BG42" s="11" t="n">
         <v>-1</v>
-      </c>
-      <c r="BD42" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BE42" s="9" t="n">
-        <v>19552.33</v>
-      </c>
-      <c r="BF42" s="10" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="BG42" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="BH42" s="8" t="n">
         <v>9899412</v>
       </c>
       <c r="BI42" s="9" t="n">
-        <v>16216.23</v>
+        <v>19552.33</v>
       </c>
       <c r="BJ42" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.0021</v>
       </c>
       <c r="BK42" s="11" t="n">
         <v>0</v>
@@ -7897,12 +8333,24 @@
         <v>9899412</v>
       </c>
       <c r="BM42" s="9" t="n">
-        <v>16131.09</v>
+        <v>16216.23</v>
       </c>
       <c r="BN42" s="10" t="n">
         <v>0.0018</v>
       </c>
-      <c r="BO42" s="11" t="n"/>
+      <c r="BO42" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP42" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BQ42" s="9" t="n">
+        <v>16131.09</v>
+      </c>
+      <c r="BR42" s="10" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="BS42" s="11" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -7951,29 +8399,21 @@
       <c r="AF43" s="8" t="n"/>
       <c r="AG43" s="9" t="n"/>
       <c r="AH43" s="10" t="n"/>
-      <c r="AI43" s="11" t="n">
+      <c r="AI43" s="11" t="n"/>
+      <c r="AJ43" s="8" t="n"/>
+      <c r="AK43" s="9" t="n"/>
+      <c r="AL43" s="10" t="n"/>
+      <c r="AM43" s="11" t="n">
         <v>-1</v>
-      </c>
-      <c r="AJ43" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="AK43" s="9" t="n">
-        <v>88822.8</v>
-      </c>
-      <c r="AL43" s="10" t="n">
-        <v>0.0077</v>
-      </c>
-      <c r="AM43" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="AN43" s="8" t="n">
         <v>4400000</v>
       </c>
       <c r="AO43" s="9" t="n">
-        <v>89280.39999999999</v>
+        <v>88822.8</v>
       </c>
       <c r="AP43" s="10" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0077</v>
       </c>
       <c r="AQ43" s="11" t="n">
         <v>0</v>
@@ -7982,18 +8422,26 @@
         <v>4400000</v>
       </c>
       <c r="AS43" s="9" t="n">
+        <v>89280.39999999999</v>
+      </c>
+      <c r="AT43" s="10" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="AU43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV43" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AW43" s="9" t="n">
         <v>89020.8</v>
       </c>
-      <c r="AT43" s="10" t="n">
+      <c r="AX43" s="10" t="n">
         <v>0.0081</v>
       </c>
-      <c r="AU43" s="11" t="n">
+      <c r="AY43" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="AV43" s="8" t="n"/>
-      <c r="AW43" s="9" t="n"/>
-      <c r="AX43" s="10" t="n"/>
-      <c r="AY43" s="11" t="n"/>
       <c r="AZ43" s="8" t="n"/>
       <c r="BA43" s="9" t="n"/>
       <c r="BB43" s="10" t="n"/>
@@ -8010,6 +8458,10 @@
       <c r="BM43" s="9" t="n"/>
       <c r="BN43" s="10" t="n"/>
       <c r="BO43" s="11" t="n"/>
+      <c r="BP43" s="8" t="n"/>
+      <c r="BQ43" s="9" t="n"/>
+      <c r="BR43" s="10" t="n"/>
+      <c r="BS43" s="11" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
@@ -8020,171 +8472,181 @@
       <c r="B44" s="12" t="n"/>
       <c r="C44" s="13" t="n"/>
       <c r="D44" s="14" t="n">
-        <v>1459425168</v>
+        <v>1575162378</v>
       </c>
       <c r="E44" s="15" t="n">
-        <v>9669928.740000002</v>
+        <v>9769016.229999995</v>
       </c>
       <c r="F44" s="16" t="n">
-        <v>0.6858999999999997</v>
+        <v>0.6906</v>
       </c>
       <c r="G44" s="17" t="n"/>
       <c r="H44" s="14" t="n">
-        <v>1373201700</v>
+        <v>1459425168</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>8608487.040000001</v>
+        <v>9669928.740000002</v>
       </c>
       <c r="J44" s="16" t="n">
-        <v>0.6675</v>
+        <v>0.6858999999999997</v>
       </c>
       <c r="K44" s="17" t="n"/>
       <c r="L44" s="14" t="n">
-        <v>1285817925</v>
+        <v>1373201700</v>
       </c>
       <c r="M44" s="15" t="n">
-        <v>8857498.140000001</v>
+        <v>8608487.040000001</v>
       </c>
       <c r="N44" s="16" t="n">
-        <v>0.6597999999999998</v>
+        <v>0.6675</v>
       </c>
       <c r="O44" s="17" t="n"/>
       <c r="P44" s="14" t="n">
-        <v>1265994824</v>
+        <v>1285817925</v>
       </c>
       <c r="Q44" s="15" t="n">
-        <v>8789059.288358003</v>
+        <v>8857498.139999999</v>
       </c>
       <c r="R44" s="16" t="n">
-        <v>0.6559051731198605</v>
+        <v>0.6597999999999998</v>
       </c>
       <c r="S44" s="17" t="n"/>
       <c r="T44" s="14" t="n">
-        <v>1079845116</v>
+        <v>1265994824</v>
       </c>
       <c r="U44" s="15" t="n">
-        <v>8588270.84</v>
+        <v>8789059.288358003</v>
       </c>
       <c r="V44" s="16" t="n">
-        <v>0.6443999999999998</v>
+        <v>0.6559051731198605</v>
       </c>
       <c r="W44" s="17" t="n"/>
       <c r="X44" s="14" t="n">
-        <v>1039629309</v>
+        <v>1079845116</v>
       </c>
       <c r="Y44" s="15" t="n">
-        <v>8271351.1939775</v>
+        <v>8588270.84</v>
       </c>
       <c r="Z44" s="16" t="n">
-        <v>0.6374000000000002</v>
+        <v>0.6443999999999998</v>
       </c>
       <c r="AA44" s="17" t="n"/>
       <c r="AB44" s="14" t="n">
-        <v>991416407</v>
+        <v>1039629309</v>
       </c>
       <c r="AC44" s="15" t="n">
-        <v>7865128.239999999</v>
+        <v>8271351.1939775</v>
       </c>
       <c r="AD44" s="16" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.6374</v>
       </c>
       <c r="AE44" s="17" t="n"/>
       <c r="AF44" s="14" t="n">
-        <v>979359723</v>
+        <v>991416407</v>
       </c>
       <c r="AG44" s="15" t="n">
-        <v>7559180.72</v>
+        <v>7865128.239999999</v>
       </c>
       <c r="AH44" s="16" t="n">
-        <v>0.6313999999999996</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="AI44" s="17" t="n"/>
       <c r="AJ44" s="14" t="n">
-        <v>927478800</v>
+        <v>979359723</v>
       </c>
       <c r="AK44" s="15" t="n">
-        <v>7320811.489999998</v>
+        <v>7559180.720000002</v>
       </c>
       <c r="AL44" s="16" t="n">
-        <v>0.6364000000000002</v>
+        <v>0.6313999999999996</v>
       </c>
       <c r="AM44" s="17" t="n"/>
       <c r="AN44" s="14" t="n">
-        <v>819556049</v>
+        <v>927478800</v>
       </c>
       <c r="AO44" s="15" t="n">
-        <v>7290583.900000002</v>
+        <v>7320811.489999998</v>
       </c>
       <c r="AP44" s="16" t="n">
-        <v>0.6436999999999998</v>
+        <v>0.6364000000000001</v>
       </c>
       <c r="AQ44" s="17" t="n"/>
       <c r="AR44" s="14" t="n">
-        <v>799425942</v>
+        <v>819556049</v>
       </c>
       <c r="AS44" s="15" t="n">
-        <v>7347454.07</v>
+        <v>7290583.900000002</v>
       </c>
       <c r="AT44" s="16" t="n">
-        <v>0.6658000000000001</v>
+        <v>0.6436999999999999</v>
       </c>
       <c r="AU44" s="17" t="n"/>
       <c r="AV44" s="14" t="n">
-        <v>756845974</v>
+        <v>799425942</v>
       </c>
       <c r="AW44" s="15" t="n">
-        <v>6714757.130000002</v>
+        <v>7347454.07</v>
       </c>
       <c r="AX44" s="16" t="n">
-        <v>0.6467999999999998</v>
+        <v>0.6658000000000001</v>
       </c>
       <c r="AY44" s="17" t="n"/>
       <c r="AZ44" s="14" t="n">
-        <v>719050337</v>
+        <v>756845974</v>
       </c>
       <c r="BA44" s="15" t="n">
-        <v>6275568.75</v>
+        <v>6714757.130000002</v>
       </c>
       <c r="BB44" s="16" t="n">
-        <v>0.6369999999999999</v>
+        <v>0.6467999999999998</v>
       </c>
       <c r="BC44" s="17" t="n"/>
       <c r="BD44" s="14" t="n">
-        <v>717176528</v>
+        <v>719050337</v>
       </c>
       <c r="BE44" s="15" t="n">
-        <v>6051937.579999999</v>
+        <v>6275568.75</v>
       </c>
       <c r="BF44" s="16" t="n">
-        <v>0.6476999999999998</v>
+        <v>0.6369999999999999</v>
       </c>
       <c r="BG44" s="17" t="n"/>
       <c r="BH44" s="14" t="n">
-        <v>718063829</v>
+        <v>717176528</v>
       </c>
       <c r="BI44" s="15" t="n">
-        <v>5662977.75</v>
+        <v>6051937.579999999</v>
       </c>
       <c r="BJ44" s="16" t="n">
-        <v>0.6437</v>
+        <v>0.6476999999999998</v>
       </c>
       <c r="BK44" s="17" t="n"/>
       <c r="BL44" s="14" t="n">
+        <v>718063829</v>
+      </c>
+      <c r="BM44" s="15" t="n">
+        <v>5662977.75</v>
+      </c>
+      <c r="BN44" s="16" t="n">
+        <v>0.6436999999999999</v>
+      </c>
+      <c r="BO44" s="17" t="n"/>
+      <c r="BP44" s="14" t="n">
         <v>697292654</v>
       </c>
-      <c r="BM44" s="15" t="n">
+      <c r="BQ44" s="15" t="n">
         <v>5868142.6</v>
       </c>
-      <c r="BN44" s="16" t="n">
+      <c r="BR44" s="16" t="n">
         <v>0.6543000000000003</v>
       </c>
-      <c r="BO44" s="17" t="n"/>
+      <c r="BS44" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="18">
     <mergeCell ref="BL2:BO2"/>
     <mergeCell ref="BH2:BK2"/>
-    <mergeCell ref="A1:BO1"/>
+    <mergeCell ref="A1:BS1"/>
     <mergeCell ref="AF2:AI2"/>
     <mergeCell ref="H2:K2"/>
     <mergeCell ref="L2:O2"/>
@@ -8198,6 +8660,7 @@
     <mergeCell ref="P2:S2"/>
     <mergeCell ref="BD2:BG2"/>
     <mergeCell ref="AJ2:AM2"/>
+    <mergeCell ref="BP2:BS2"/>
     <mergeCell ref="AN2:AQ2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -522,7 +522,7 @@
     <col width="22" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="26" customWidth="1" min="29" max="29"/>
-    <col width="14" customWidth="1" min="30" max="30"/>
+    <col width="20" customWidth="1" min="30" max="30"/>
     <col width="22" customWidth="1" min="31" max="31"/>
     <col width="14" customWidth="1" min="32" max="32"/>
     <col width="26" customWidth="1" min="33" max="33"/>
@@ -6769,24 +6769,24 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>CIE Automotive India Limited</t>
+          <t>Nesco Limited</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>INE536H01010</t>
+          <t>INE317F01035</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Auto Components</t>
+          <t>Commercial Services &amp; Supplies</t>
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>464063</v>
+        <v>151687</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>2071.81</v>
+        <v>1780.2</v>
       </c>
       <c r="F33" s="10" t="n">
         <v>0.0001</v>
@@ -6795,85 +6795,149 @@
         <v>0</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>464063</v>
+        <v>151687</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>2198.5</v>
+        <v>1862.26</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="K33" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>464063</v>
+        <v>151687</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>2065.08</v>
+        <v>1538.11</v>
       </c>
       <c r="N33" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="O33" s="11" t="n">
         <v>0</v>
       </c>
       <c r="P33" s="8" t="n">
-        <v>464063</v>
+        <v>151687</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>2188.75</v>
+        <v>1704.36</v>
       </c>
       <c r="R33" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="S33" s="11" t="n">
-        <v>0.004302331872531515</v>
+        <v>0</v>
       </c>
       <c r="T33" s="8" t="n">
-        <v>462075</v>
+        <v>151687</v>
       </c>
       <c r="U33" s="9" t="n">
-        <v>1932.4</v>
+        <v>1728.63</v>
       </c>
       <c r="V33" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="W33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="Y33" s="9" t="n">
+        <v>1858.32</v>
+      </c>
+      <c r="Z33" s="10" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AA33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AC33" s="9" t="n">
+        <v>1947.66</v>
+      </c>
+      <c r="AD33" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AE33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AG33" s="9" t="n">
+        <v>2076.6</v>
+      </c>
+      <c r="AH33" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AI33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AK33" s="9" t="n">
+        <v>1987.1</v>
+      </c>
+      <c r="AL33" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AM33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AO33" s="9" t="n">
+        <v>2130.6</v>
+      </c>
+      <c r="AP33" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AQ33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AS33" s="9" t="n">
+        <v>2091.16</v>
+      </c>
+      <c r="AT33" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AU33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AW33" s="9" t="n">
+        <v>1766.62</v>
+      </c>
+      <c r="AX33" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AY33" s="11" t="n">
+        <v>0.6954140540298874</v>
+      </c>
+      <c r="AZ33" s="8" t="n">
+        <v>89469</v>
+      </c>
+      <c r="BA33" s="9" t="n">
+        <v>828.48</v>
+      </c>
+      <c r="BB33" s="10" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="BC33" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="X33" s="8" t="n"/>
-      <c r="Y33" s="9" t="n"/>
-      <c r="Z33" s="10" t="n"/>
-      <c r="AA33" s="11" t="n"/>
-      <c r="AB33" s="8" t="n"/>
-      <c r="AC33" s="9" t="n"/>
-      <c r="AD33" s="10" t="n"/>
-      <c r="AE33" s="11" t="n"/>
-      <c r="AF33" s="8" t="n"/>
-      <c r="AG33" s="9" t="n"/>
-      <c r="AH33" s="10" t="n"/>
-      <c r="AI33" s="11" t="n"/>
-      <c r="AJ33" s="8" t="n"/>
-      <c r="AK33" s="9" t="n"/>
-      <c r="AL33" s="10" t="n"/>
-      <c r="AM33" s="11" t="n"/>
-      <c r="AN33" s="8" t="n"/>
-      <c r="AO33" s="9" t="n"/>
-      <c r="AP33" s="10" t="n"/>
-      <c r="AQ33" s="11" t="n"/>
-      <c r="AR33" s="8" t="n"/>
-      <c r="AS33" s="9" t="n"/>
-      <c r="AT33" s="10" t="n"/>
-      <c r="AU33" s="11" t="n"/>
-      <c r="AV33" s="8" t="n"/>
-      <c r="AW33" s="9" t="n"/>
-      <c r="AX33" s="10" t="n"/>
-      <c r="AY33" s="11" t="n"/>
-      <c r="AZ33" s="8" t="n"/>
-      <c r="BA33" s="9" t="n"/>
-      <c r="BB33" s="10" t="n"/>
-      <c r="BC33" s="11" t="n"/>
       <c r="BD33" s="8" t="n"/>
       <c r="BE33" s="9" t="n"/>
       <c r="BF33" s="10" t="n"/>
@@ -7113,24 +7177,24 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Nesco Limited</t>
+          <t>CIE Automotive India Limited</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>INE317F01035</t>
+          <t>INE536H01010</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Commercial Services &amp; Supplies</t>
+          <t>Auto Components</t>
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>151687</v>
+        <v>464063</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>1780.2</v>
+        <v>2071.81</v>
       </c>
       <c r="F35" s="10" t="n">
         <v>0.0001</v>
@@ -7139,149 +7203,85 @@
         <v>0</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>151687</v>
+        <v>464063</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>1862.26</v>
+        <v>2198.5</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="K35" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>151687</v>
+        <v>464063</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>1538.11</v>
+        <v>2065.08</v>
       </c>
       <c r="N35" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="O35" s="11" t="n">
         <v>0</v>
       </c>
       <c r="P35" s="8" t="n">
-        <v>151687</v>
+        <v>464063</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>1704.36</v>
+        <v>2188.75</v>
       </c>
       <c r="R35" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="S35" s="11" t="n">
-        <v>0</v>
+        <v>0.004302331872531515</v>
       </c>
       <c r="T35" s="8" t="n">
-        <v>151687</v>
+        <v>462075</v>
       </c>
       <c r="U35" s="9" t="n">
-        <v>1728.63</v>
+        <v>1932.4</v>
       </c>
       <c r="V35" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="W35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="Y35" s="9" t="n">
-        <v>1858.32</v>
-      </c>
-      <c r="Z35" s="10" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="AA35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AC35" s="9" t="n">
-        <v>1947.66</v>
-      </c>
-      <c r="AD35" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AE35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AG35" s="9" t="n">
-        <v>2076.6</v>
-      </c>
-      <c r="AH35" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AI35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AK35" s="9" t="n">
-        <v>1987.1</v>
-      </c>
-      <c r="AL35" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AM35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN35" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AO35" s="9" t="n">
-        <v>2130.6</v>
-      </c>
-      <c r="AP35" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AQ35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR35" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AS35" s="9" t="n">
-        <v>2091.16</v>
-      </c>
-      <c r="AT35" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AU35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV35" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AW35" s="9" t="n">
-        <v>1766.62</v>
-      </c>
-      <c r="AX35" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AY35" s="11" t="n">
-        <v>0.6954140540298874</v>
-      </c>
-      <c r="AZ35" s="8" t="n">
-        <v>89469</v>
-      </c>
-      <c r="BA35" s="9" t="n">
-        <v>828.48</v>
-      </c>
-      <c r="BB35" s="10" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="BC35" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="X35" s="8" t="n"/>
+      <c r="Y35" s="9" t="n"/>
+      <c r="Z35" s="10" t="n"/>
+      <c r="AA35" s="11" t="n"/>
+      <c r="AB35" s="8" t="n"/>
+      <c r="AC35" s="9" t="n"/>
+      <c r="AD35" s="10" t="n"/>
+      <c r="AE35" s="11" t="n"/>
+      <c r="AF35" s="8" t="n"/>
+      <c r="AG35" s="9" t="n"/>
+      <c r="AH35" s="10" t="n"/>
+      <c r="AI35" s="11" t="n"/>
+      <c r="AJ35" s="8" t="n"/>
+      <c r="AK35" s="9" t="n"/>
+      <c r="AL35" s="10" t="n"/>
+      <c r="AM35" s="11" t="n"/>
+      <c r="AN35" s="8" t="n"/>
+      <c r="AO35" s="9" t="n"/>
+      <c r="AP35" s="10" t="n"/>
+      <c r="AQ35" s="11" t="n"/>
+      <c r="AR35" s="8" t="n"/>
+      <c r="AS35" s="9" t="n"/>
+      <c r="AT35" s="10" t="n"/>
+      <c r="AU35" s="11" t="n"/>
+      <c r="AV35" s="8" t="n"/>
+      <c r="AW35" s="9" t="n"/>
+      <c r="AX35" s="10" t="n"/>
+      <c r="AY35" s="11" t="n"/>
+      <c r="AZ35" s="8" t="n"/>
+      <c r="BA35" s="9" t="n"/>
+      <c r="BB35" s="10" t="n"/>
+      <c r="BC35" s="11" t="n"/>
       <c r="BD35" s="8" t="n"/>
       <c r="BE35" s="9" t="n"/>
       <c r="BF35" s="10" t="n"/>
@@ -7302,17 +7302,17 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Balkrishna Industries Limited</t>
+          <t>Kotak Mahindra Bank Limited</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>INE787D01026</t>
+          <t>INE237A01028</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Auto Components</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="D36" s="8" t="n"/>
@@ -7322,202 +7322,178 @@
       <c r="H36" s="8" t="n"/>
       <c r="I36" s="9" t="n"/>
       <c r="J36" s="10" t="n"/>
-      <c r="K36" s="11" t="n">
+      <c r="K36" s="11" t="n"/>
+      <c r="L36" s="8" t="n"/>
+      <c r="M36" s="9" t="n"/>
+      <c r="N36" s="10" t="n"/>
+      <c r="O36" s="11" t="n"/>
+      <c r="P36" s="8" t="n"/>
+      <c r="Q36" s="9" t="n"/>
+      <c r="R36" s="10" t="n"/>
+      <c r="S36" s="11" t="n"/>
+      <c r="T36" s="8" t="n"/>
+      <c r="U36" s="9" t="n"/>
+      <c r="V36" s="10" t="n"/>
+      <c r="W36" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="L36" s="8" t="n">
-        <v>2274074</v>
-      </c>
-      <c r="M36" s="9" t="n">
-        <v>47368.96</v>
-      </c>
-      <c r="N36" s="10" t="n">
-        <v>0.0037</v>
-      </c>
-      <c r="O36" s="11" t="n">
-        <v>-0.2174731122669314</v>
-      </c>
-      <c r="P36" s="8" t="n">
-        <v>2906065</v>
-      </c>
-      <c r="Q36" s="9" t="n">
-        <v>69277.67999999999</v>
-      </c>
-      <c r="R36" s="10" t="n">
-        <v>0.0052</v>
-      </c>
-      <c r="S36" s="11" t="n">
-        <v>-0.3062750860930125</v>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="U36" s="9" t="n">
-        <v>96591.67</v>
-      </c>
-      <c r="V36" s="10" t="n">
-        <v>0.0072</v>
-      </c>
-      <c r="W36" s="11" t="n">
-        <v>0</v>
-      </c>
       <c r="X36" s="8" t="n">
-        <v>4189074</v>
+        <v>24621592</v>
       </c>
       <c r="Y36" s="9" t="n">
-        <v>97173.95</v>
+        <v>541945.86</v>
       </c>
       <c r="Z36" s="10" t="n">
-        <v>0.0073</v>
+        <v>0.0407</v>
       </c>
       <c r="AA36" s="11" t="n">
-        <v>0</v>
+        <v>0.01296144774839237</v>
       </c>
       <c r="AB36" s="8" t="n">
-        <v>4189074</v>
+        <v>24306544</v>
       </c>
       <c r="AC36" s="9" t="n">
-        <v>96721.53</v>
+        <v>516368.22</v>
       </c>
       <c r="AD36" s="10" t="n">
-        <v>0.0075</v>
+        <v>0.0398</v>
       </c>
       <c r="AE36" s="11" t="n">
-        <v>0</v>
+        <v>0.004192884502844551</v>
       </c>
       <c r="AF36" s="8" t="n">
-        <v>4189074</v>
+        <v>24205055</v>
       </c>
       <c r="AG36" s="9" t="n">
-        <v>95502.50999999999</v>
+        <v>508838.67</v>
       </c>
       <c r="AH36" s="10" t="n">
-        <v>0.0076</v>
+        <v>0.0404</v>
       </c>
       <c r="AI36" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AJ36" s="8" t="n">
-        <v>4189074</v>
+        <v>24205055</v>
       </c>
       <c r="AK36" s="9" t="n">
-        <v>96130.87</v>
+        <v>482334.13</v>
       </c>
       <c r="AL36" s="10" t="n">
-        <v>0.008</v>
+        <v>0.0403</v>
       </c>
       <c r="AM36" s="11" t="n">
-        <v>0</v>
+        <v>0.03407788338216907</v>
       </c>
       <c r="AN36" s="8" t="n">
-        <v>4189074</v>
+        <v>23407381</v>
       </c>
       <c r="AO36" s="9" t="n">
-        <v>95904.66</v>
+        <v>458854.89</v>
       </c>
       <c r="AP36" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.0399</v>
       </c>
       <c r="AQ36" s="11" t="n">
-        <v>0</v>
+        <v>0.06425892329321918</v>
       </c>
       <c r="AR36" s="8" t="n">
-        <v>4189074</v>
+        <v>21994066</v>
       </c>
       <c r="AS36" s="9" t="n">
-        <v>112108</v>
+        <v>435174.59</v>
       </c>
       <c r="AT36" s="10" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0384</v>
       </c>
       <c r="AU36" s="11" t="n">
-        <v>0</v>
+        <v>0.07428402120388222</v>
       </c>
       <c r="AV36" s="8" t="n">
-        <v>4189074</v>
+        <v>20473232</v>
       </c>
       <c r="AW36" s="9" t="n">
-        <v>102435.43</v>
+        <v>442938.37</v>
       </c>
       <c r="AX36" s="10" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0401</v>
       </c>
       <c r="AY36" s="11" t="n">
-        <v>0</v>
+        <v>0.03644973136547983</v>
       </c>
       <c r="AZ36" s="8" t="n">
-        <v>4189074</v>
+        <v>19753232</v>
       </c>
       <c r="BA36" s="9" t="n">
-        <v>103562.29</v>
+        <v>409820.3</v>
       </c>
       <c r="BB36" s="10" t="n">
-        <v>0.01</v>
+        <v>0.0395</v>
       </c>
       <c r="BC36" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BD36" s="8" t="n">
-        <v>4189074</v>
+        <v>19753232</v>
       </c>
       <c r="BE36" s="9" t="n">
-        <v>112061.92</v>
+        <v>436171.12</v>
       </c>
       <c r="BF36" s="10" t="n">
-        <v>0.0114</v>
+        <v>0.0443</v>
       </c>
       <c r="BG36" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BH36" s="8" t="n">
-        <v>4189074</v>
+        <v>19753232</v>
       </c>
       <c r="BI36" s="9" t="n">
-        <v>107022.46</v>
+        <v>428882.17</v>
       </c>
       <c r="BJ36" s="10" t="n">
-        <v>0.0115</v>
+        <v>0.0459</v>
       </c>
       <c r="BK36" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BL36" s="8" t="n">
-        <v>4189074</v>
+        <v>19753232</v>
       </c>
       <c r="BM36" s="9" t="n">
-        <v>109571.51</v>
+        <v>375894.13</v>
       </c>
       <c r="BN36" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.0427</v>
       </c>
       <c r="BO36" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BP36" s="8" t="n">
-        <v>4189074</v>
+        <v>19753232</v>
       </c>
       <c r="BQ36" s="9" t="n">
-        <v>116089.71</v>
+        <v>375568.2</v>
       </c>
       <c r="BR36" s="10" t="n">
-        <v>0.0129</v>
+        <v>0.0419</v>
       </c>
       <c r="BS36" s="11" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Multi Commodity Exchange of India Limited</t>
+          <t>Balkrishna Industries Limited</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>INE745G01043</t>
+          <t>INE787D01026</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Auto Components</t>
         </is>
       </c>
       <c r="D37" s="8" t="n"/>
@@ -7527,92 +7503,202 @@
       <c r="H37" s="8" t="n"/>
       <c r="I37" s="9" t="n"/>
       <c r="J37" s="10" t="n"/>
-      <c r="K37" s="11" t="n"/>
-      <c r="L37" s="8" t="n"/>
-      <c r="M37" s="9" t="n"/>
-      <c r="N37" s="10" t="n"/>
-      <c r="O37" s="11" t="n"/>
-      <c r="P37" s="8" t="n"/>
-      <c r="Q37" s="9" t="n"/>
-      <c r="R37" s="10" t="n"/>
+      <c r="K37" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L37" s="8" t="n">
+        <v>2274074</v>
+      </c>
+      <c r="M37" s="9" t="n">
+        <v>47368.96</v>
+      </c>
+      <c r="N37" s="10" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="O37" s="11" t="n">
+        <v>-0.2174731122669314</v>
+      </c>
+      <c r="P37" s="8" t="n">
+        <v>2906065</v>
+      </c>
+      <c r="Q37" s="9" t="n">
+        <v>69277.67999999999</v>
+      </c>
+      <c r="R37" s="10" t="n">
+        <v>0.0052</v>
+      </c>
       <c r="S37" s="11" t="n">
-        <v>-1</v>
+        <v>-0.3062750860930125</v>
       </c>
       <c r="T37" s="8" t="n">
-        <v>795472</v>
+        <v>4189074</v>
       </c>
       <c r="U37" s="9" t="n">
-        <v>20109.53</v>
+        <v>96591.67</v>
       </c>
       <c r="V37" s="10" t="n">
-        <v>0.0015</v>
+        <v>0.0072</v>
       </c>
       <c r="W37" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="X37" s="8" t="n"/>
-      <c r="Y37" s="9" t="n"/>
-      <c r="Z37" s="10" t="n"/>
-      <c r="AA37" s="11" t="n"/>
-      <c r="AB37" s="8" t="n"/>
-      <c r="AC37" s="9" t="n"/>
-      <c r="AD37" s="10" t="n"/>
-      <c r="AE37" s="11" t="n"/>
-      <c r="AF37" s="8" t="n"/>
-      <c r="AG37" s="9" t="n"/>
-      <c r="AH37" s="10" t="n"/>
-      <c r="AI37" s="11" t="n"/>
-      <c r="AJ37" s="8" t="n"/>
-      <c r="AK37" s="9" t="n"/>
-      <c r="AL37" s="10" t="n"/>
-      <c r="AM37" s="11" t="n"/>
-      <c r="AN37" s="8" t="n"/>
-      <c r="AO37" s="9" t="n"/>
-      <c r="AP37" s="10" t="n"/>
-      <c r="AQ37" s="11" t="n"/>
-      <c r="AR37" s="8" t="n"/>
-      <c r="AS37" s="9" t="n"/>
-      <c r="AT37" s="10" t="n"/>
-      <c r="AU37" s="11" t="n"/>
-      <c r="AV37" s="8" t="n"/>
-      <c r="AW37" s="9" t="n"/>
-      <c r="AX37" s="10" t="n"/>
-      <c r="AY37" s="11" t="n"/>
-      <c r="AZ37" s="8" t="n"/>
-      <c r="BA37" s="9" t="n"/>
-      <c r="BB37" s="10" t="n"/>
-      <c r="BC37" s="11" t="n"/>
-      <c r="BD37" s="8" t="n"/>
-      <c r="BE37" s="9" t="n"/>
-      <c r="BF37" s="10" t="n"/>
-      <c r="BG37" s="11" t="n"/>
-      <c r="BH37" s="8" t="n"/>
-      <c r="BI37" s="9" t="n"/>
-      <c r="BJ37" s="10" t="n"/>
-      <c r="BK37" s="11" t="n"/>
-      <c r="BL37" s="8" t="n"/>
-      <c r="BM37" s="9" t="n"/>
-      <c r="BN37" s="10" t="n"/>
-      <c r="BO37" s="11" t="n"/>
-      <c r="BP37" s="8" t="n"/>
-      <c r="BQ37" s="9" t="n"/>
-      <c r="BR37" s="10" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="X37" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="Y37" s="9" t="n">
+        <v>97173.95</v>
+      </c>
+      <c r="Z37" s="10" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="AA37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="AC37" s="9" t="n">
+        <v>96721.53</v>
+      </c>
+      <c r="AD37" s="10" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="AE37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="AG37" s="9" t="n">
+        <v>95502.50999999999</v>
+      </c>
+      <c r="AH37" s="10" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="AI37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="AK37" s="9" t="n">
+        <v>96130.87</v>
+      </c>
+      <c r="AL37" s="10" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="AM37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="AO37" s="9" t="n">
+        <v>95904.66</v>
+      </c>
+      <c r="AP37" s="10" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="AQ37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="AS37" s="9" t="n">
+        <v>112108</v>
+      </c>
+      <c r="AT37" s="10" t="n">
+        <v>0.009900000000000001</v>
+      </c>
+      <c r="AU37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="AW37" s="9" t="n">
+        <v>102435.43</v>
+      </c>
+      <c r="AX37" s="10" t="n">
+        <v>0.009299999999999999</v>
+      </c>
+      <c r="AY37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ37" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="BA37" s="9" t="n">
+        <v>103562.29</v>
+      </c>
+      <c r="BB37" s="10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BC37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD37" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="BE37" s="9" t="n">
+        <v>112061.92</v>
+      </c>
+      <c r="BF37" s="10" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="BG37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH37" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="BI37" s="9" t="n">
+        <v>107022.46</v>
+      </c>
+      <c r="BJ37" s="10" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="BK37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL37" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="BM37" s="9" t="n">
+        <v>109571.51</v>
+      </c>
+      <c r="BN37" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="BO37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP37" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="BQ37" s="9" t="n">
+        <v>116089.71</v>
+      </c>
+      <c r="BR37" s="10" t="n">
+        <v>0.0129</v>
+      </c>
       <c r="BS37" s="11" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Kotak Mahindra Bank Limited</t>
+          <t>Multi Commodity Exchange of India Limited</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>INE237A01028</t>
+          <t>INE745G01035</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D38" s="8" t="n"/>
@@ -7638,157 +7724,157 @@
         <v>-1</v>
       </c>
       <c r="X38" s="8" t="n">
-        <v>24621592</v>
+        <v>797719</v>
       </c>
       <c r="Y38" s="9" t="n">
-        <v>541945.86</v>
+        <v>88833.99000000001</v>
       </c>
       <c r="Z38" s="10" t="n">
-        <v>0.0407</v>
+        <v>0.0067</v>
       </c>
       <c r="AA38" s="11" t="n">
-        <v>0.01296144774839237</v>
+        <v>0</v>
       </c>
       <c r="AB38" s="8" t="n">
-        <v>24306544</v>
+        <v>797719</v>
       </c>
       <c r="AC38" s="9" t="n">
-        <v>516368.22</v>
+        <v>80358.22</v>
       </c>
       <c r="AD38" s="10" t="n">
-        <v>0.0398</v>
+        <v>0.0062</v>
       </c>
       <c r="AE38" s="11" t="n">
-        <v>0.004192884502844551</v>
+        <v>0</v>
       </c>
       <c r="AF38" s="8" t="n">
-        <v>24205055</v>
+        <v>797719</v>
       </c>
       <c r="AG38" s="9" t="n">
-        <v>508838.67</v>
+        <v>73737.16</v>
       </c>
       <c r="AH38" s="10" t="n">
-        <v>0.0404</v>
+        <v>0.0059</v>
       </c>
       <c r="AI38" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AJ38" s="8" t="n">
-        <v>24205055</v>
+        <v>797719</v>
       </c>
       <c r="AK38" s="9" t="n">
-        <v>482334.13</v>
+        <v>62190.17</v>
       </c>
       <c r="AL38" s="10" t="n">
-        <v>0.0403</v>
+        <v>0.0052</v>
       </c>
       <c r="AM38" s="11" t="n">
-        <v>0.03407788338216907</v>
+        <v>0</v>
       </c>
       <c r="AN38" s="8" t="n">
-        <v>23407381</v>
+        <v>797719</v>
       </c>
       <c r="AO38" s="9" t="n">
-        <v>458854.89</v>
+        <v>58951.43</v>
       </c>
       <c r="AP38" s="10" t="n">
-        <v>0.0399</v>
+        <v>0.0051</v>
       </c>
       <c r="AQ38" s="11" t="n">
-        <v>0.06425892329321918</v>
+        <v>0</v>
       </c>
       <c r="AR38" s="8" t="n">
-        <v>21994066</v>
+        <v>797719</v>
       </c>
       <c r="AS38" s="9" t="n">
-        <v>435174.59</v>
+        <v>61368.52</v>
       </c>
       <c r="AT38" s="10" t="n">
-        <v>0.0384</v>
+        <v>0.0054</v>
       </c>
       <c r="AU38" s="11" t="n">
-        <v>0.07428402120388222</v>
+        <v>0</v>
       </c>
       <c r="AV38" s="8" t="n">
-        <v>20473232</v>
+        <v>797719</v>
       </c>
       <c r="AW38" s="9" t="n">
-        <v>442938.37</v>
+        <v>71347.99000000001</v>
       </c>
       <c r="AX38" s="10" t="n">
-        <v>0.0401</v>
+        <v>0.0065</v>
       </c>
       <c r="AY38" s="11" t="n">
-        <v>0.03644973136547983</v>
+        <v>0</v>
       </c>
       <c r="AZ38" s="8" t="n">
-        <v>19753232</v>
+        <v>797719</v>
       </c>
       <c r="BA38" s="9" t="n">
-        <v>409820.3</v>
+        <v>52665.41</v>
       </c>
       <c r="BB38" s="10" t="n">
-        <v>0.0395</v>
+        <v>0.0051</v>
       </c>
       <c r="BC38" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BD38" s="8" t="n">
-        <v>19753232</v>
+        <v>797719</v>
       </c>
       <c r="BE38" s="9" t="n">
-        <v>436171.12</v>
+        <v>48884.22</v>
       </c>
       <c r="BF38" s="10" t="n">
-        <v>0.0443</v>
+        <v>0.005</v>
       </c>
       <c r="BG38" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BH38" s="8" t="n">
-        <v>19753232</v>
+        <v>797719</v>
       </c>
       <c r="BI38" s="9" t="n">
-        <v>428882.17</v>
+        <v>42372.84</v>
       </c>
       <c r="BJ38" s="10" t="n">
-        <v>0.0459</v>
+        <v>0.0045</v>
       </c>
       <c r="BK38" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BL38" s="8" t="n">
-        <v>19753232</v>
+        <v>797719</v>
       </c>
       <c r="BM38" s="9" t="n">
-        <v>375894.13</v>
+        <v>39819.34</v>
       </c>
       <c r="BN38" s="10" t="n">
-        <v>0.0427</v>
+        <v>0.0045</v>
       </c>
       <c r="BO38" s="11" t="n">
-        <v>0</v>
+        <v>-0.09569612848812428</v>
       </c>
       <c r="BP38" s="8" t="n">
-        <v>19753232</v>
+        <v>882136</v>
       </c>
       <c r="BQ38" s="9" t="n">
-        <v>375568.2</v>
+        <v>50572.42</v>
       </c>
       <c r="BR38" s="10" t="n">
-        <v>0.0419</v>
+        <v>0.0056</v>
       </c>
       <c r="BS38" s="11" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Motilal Oswal Financial Services Limited</t>
+          <t>Multi Commodity Exchange of India Limited</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>INE338I01027</t>
+          <t>INE745G01043</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
@@ -7811,11 +7897,21 @@
       <c r="P39" s="8" t="n"/>
       <c r="Q39" s="9" t="n"/>
       <c r="R39" s="10" t="n"/>
-      <c r="S39" s="11" t="n"/>
-      <c r="T39" s="8" t="n"/>
-      <c r="U39" s="9" t="n"/>
-      <c r="V39" s="10" t="n"/>
-      <c r="W39" s="11" t="n"/>
+      <c r="S39" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v>795472</v>
+      </c>
+      <c r="U39" s="9" t="n">
+        <v>20109.53</v>
+      </c>
+      <c r="V39" s="10" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="W39" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="X39" s="8" t="n"/>
       <c r="Y39" s="9" t="n"/>
       <c r="Z39" s="10" t="n"/>
@@ -7839,94 +7935,46 @@
       <c r="AR39" s="8" t="n"/>
       <c r="AS39" s="9" t="n"/>
       <c r="AT39" s="10" t="n"/>
-      <c r="AU39" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AV39" s="8" t="n">
-        <v>591805</v>
-      </c>
-      <c r="AW39" s="9" t="n">
-        <v>5149</v>
-      </c>
-      <c r="AX39" s="10" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="AY39" s="11" t="n">
-        <v>-0.8902567225534253</v>
-      </c>
-      <c r="AZ39" s="8" t="n">
-        <v>5392631</v>
-      </c>
-      <c r="BA39" s="9" t="n">
-        <v>43674.92</v>
-      </c>
-      <c r="BB39" s="10" t="n">
-        <v>0.0042</v>
-      </c>
-      <c r="BC39" s="11" t="n">
-        <v>-0.3719237093069153</v>
-      </c>
-      <c r="BD39" s="8" t="n">
-        <v>8585949</v>
-      </c>
-      <c r="BE39" s="9" t="n">
-        <v>56044.78</v>
-      </c>
-      <c r="BF39" s="10" t="n">
-        <v>0.0057</v>
-      </c>
-      <c r="BG39" s="11" t="n">
-        <v>-0.2132577936597328</v>
-      </c>
-      <c r="BH39" s="8" t="n">
-        <v>10913294</v>
-      </c>
-      <c r="BI39" s="9" t="n">
-        <v>67154.95</v>
-      </c>
-      <c r="BJ39" s="10" t="n">
-        <v>0.0072</v>
-      </c>
-      <c r="BK39" s="11" t="n">
-        <v>-0.09462389658963724</v>
-      </c>
-      <c r="BL39" s="8" t="n">
-        <v>12053879</v>
-      </c>
-      <c r="BM39" s="9" t="n">
-        <v>70937.08</v>
-      </c>
-      <c r="BN39" s="10" t="n">
-        <v>0.0081</v>
-      </c>
-      <c r="BO39" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP39" s="8" t="n">
-        <v>12053879</v>
-      </c>
-      <c r="BQ39" s="9" t="n">
-        <v>76801.28999999999</v>
-      </c>
-      <c r="BR39" s="10" t="n">
-        <v>0.0086</v>
-      </c>
+      <c r="AU39" s="11" t="n"/>
+      <c r="AV39" s="8" t="n"/>
+      <c r="AW39" s="9" t="n"/>
+      <c r="AX39" s="10" t="n"/>
+      <c r="AY39" s="11" t="n"/>
+      <c r="AZ39" s="8" t="n"/>
+      <c r="BA39" s="9" t="n"/>
+      <c r="BB39" s="10" t="n"/>
+      <c r="BC39" s="11" t="n"/>
+      <c r="BD39" s="8" t="n"/>
+      <c r="BE39" s="9" t="n"/>
+      <c r="BF39" s="10" t="n"/>
+      <c r="BG39" s="11" t="n"/>
+      <c r="BH39" s="8" t="n"/>
+      <c r="BI39" s="9" t="n"/>
+      <c r="BJ39" s="10" t="n"/>
+      <c r="BK39" s="11" t="n"/>
+      <c r="BL39" s="8" t="n"/>
+      <c r="BM39" s="9" t="n"/>
+      <c r="BN39" s="10" t="n"/>
+      <c r="BO39" s="11" t="n"/>
+      <c r="BP39" s="8" t="n"/>
+      <c r="BQ39" s="9" t="n"/>
+      <c r="BR39" s="10" t="n"/>
       <c r="BS39" s="11" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Multi Commodity Exchange of India Limited</t>
+          <t>Zydus Wellness Limited</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>INE745G01035</t>
+          <t>INE768C01010</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D40" s="8" t="n"/>
@@ -7948,150 +7996,80 @@
       <c r="T40" s="8" t="n"/>
       <c r="U40" s="9" t="n"/>
       <c r="V40" s="10" t="n"/>
-      <c r="W40" s="11" t="n">
+      <c r="W40" s="11" t="n"/>
+      <c r="X40" s="8" t="n"/>
+      <c r="Y40" s="9" t="n"/>
+      <c r="Z40" s="10" t="n"/>
+      <c r="AA40" s="11" t="n"/>
+      <c r="AB40" s="8" t="n"/>
+      <c r="AC40" s="9" t="n"/>
+      <c r="AD40" s="10" t="n"/>
+      <c r="AE40" s="11" t="n"/>
+      <c r="AF40" s="8" t="n"/>
+      <c r="AG40" s="9" t="n"/>
+      <c r="AH40" s="10" t="n"/>
+      <c r="AI40" s="11" t="n"/>
+      <c r="AJ40" s="8" t="n"/>
+      <c r="AK40" s="9" t="n"/>
+      <c r="AL40" s="10" t="n"/>
+      <c r="AM40" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="X40" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="Y40" s="9" t="n">
-        <v>88833.99000000001</v>
-      </c>
-      <c r="Z40" s="10" t="n">
-        <v>0.0067</v>
-      </c>
-      <c r="AA40" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB40" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="AC40" s="9" t="n">
-        <v>80358.22</v>
-      </c>
-      <c r="AD40" s="10" t="n">
-        <v>0.0062</v>
-      </c>
-      <c r="AE40" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF40" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="AG40" s="9" t="n">
-        <v>73737.16</v>
-      </c>
-      <c r="AH40" s="10" t="n">
-        <v>0.0059</v>
-      </c>
-      <c r="AI40" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ40" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="AK40" s="9" t="n">
-        <v>62190.17</v>
-      </c>
-      <c r="AL40" s="10" t="n">
-        <v>0.0052</v>
-      </c>
-      <c r="AM40" s="11" t="n">
-        <v>0</v>
-      </c>
       <c r="AN40" s="8" t="n">
-        <v>797719</v>
+        <v>4400000</v>
       </c>
       <c r="AO40" s="9" t="n">
-        <v>58951.43</v>
+        <v>88822.8</v>
       </c>
       <c r="AP40" s="10" t="n">
-        <v>0.0051</v>
+        <v>0.0077</v>
       </c>
       <c r="AQ40" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AR40" s="8" t="n">
-        <v>797719</v>
+        <v>4400000</v>
       </c>
       <c r="AS40" s="9" t="n">
-        <v>61368.52</v>
+        <v>89280.39999999999</v>
       </c>
       <c r="AT40" s="10" t="n">
-        <v>0.0054</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="AU40" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AV40" s="8" t="n">
-        <v>797719</v>
+        <v>4400000</v>
       </c>
       <c r="AW40" s="9" t="n">
-        <v>71347.99000000001</v>
+        <v>89020.8</v>
       </c>
       <c r="AX40" s="10" t="n">
-        <v>0.0065</v>
+        <v>0.0081</v>
       </c>
       <c r="AY40" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ40" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="BA40" s="9" t="n">
-        <v>52665.41</v>
-      </c>
-      <c r="BB40" s="10" t="n">
-        <v>0.0051</v>
-      </c>
-      <c r="BC40" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD40" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="BE40" s="9" t="n">
-        <v>48884.22</v>
-      </c>
-      <c r="BF40" s="10" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="BG40" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH40" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="BI40" s="9" t="n">
-        <v>42372.84</v>
-      </c>
-      <c r="BJ40" s="10" t="n">
-        <v>0.0045</v>
-      </c>
-      <c r="BK40" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL40" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="BM40" s="9" t="n">
-        <v>39819.34</v>
-      </c>
-      <c r="BN40" s="10" t="n">
-        <v>0.0045</v>
-      </c>
-      <c r="BO40" s="11" t="n">
-        <v>-0.09569612848812428</v>
-      </c>
-      <c r="BP40" s="8" t="n">
-        <v>882136</v>
-      </c>
-      <c r="BQ40" s="9" t="n">
-        <v>50572.42</v>
-      </c>
-      <c r="BR40" s="10" t="n">
-        <v>0.0056</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AZ40" s="8" t="n"/>
+      <c r="BA40" s="9" t="n"/>
+      <c r="BB40" s="10" t="n"/>
+      <c r="BC40" s="11" t="n"/>
+      <c r="BD40" s="8" t="n"/>
+      <c r="BE40" s="9" t="n"/>
+      <c r="BF40" s="10" t="n"/>
+      <c r="BG40" s="11" t="n"/>
+      <c r="BH40" s="8" t="n"/>
+      <c r="BI40" s="9" t="n"/>
+      <c r="BJ40" s="10" t="n"/>
+      <c r="BK40" s="11" t="n"/>
+      <c r="BL40" s="8" t="n"/>
+      <c r="BM40" s="9" t="n"/>
+      <c r="BN40" s="10" t="n"/>
+      <c r="BO40" s="11" t="n"/>
+      <c r="BP40" s="8" t="n"/>
+      <c r="BQ40" s="9" t="n"/>
+      <c r="BR40" s="10" t="n"/>
       <c r="BS40" s="11" t="n"/>
     </row>
     <row r="41">
@@ -8246,17 +8224,17 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>ITC Hotels Limited</t>
+          <t>Motilal Oswal Financial Services Limited</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>INE379A01028</t>
+          <t>INE338I01027</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Leisure Services</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D42" s="8" t="n"/>
@@ -8302,70 +8280,94 @@
       <c r="AR42" s="8" t="n"/>
       <c r="AS42" s="9" t="n"/>
       <c r="AT42" s="10" t="n"/>
-      <c r="AU42" s="11" t="n"/>
-      <c r="AV42" s="8" t="n"/>
-      <c r="AW42" s="9" t="n"/>
-      <c r="AX42" s="10" t="n"/>
-      <c r="AY42" s="11" t="n"/>
-      <c r="AZ42" s="8" t="n"/>
-      <c r="BA42" s="9" t="n"/>
-      <c r="BB42" s="10" t="n"/>
-      <c r="BC42" s="11" t="n"/>
-      <c r="BD42" s="8" t="n"/>
-      <c r="BE42" s="9" t="n"/>
-      <c r="BF42" s="10" t="n"/>
+      <c r="AU42" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AV42" s="8" t="n">
+        <v>591805</v>
+      </c>
+      <c r="AW42" s="9" t="n">
+        <v>5149</v>
+      </c>
+      <c r="AX42" s="10" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="AY42" s="11" t="n">
+        <v>-0.8902567225534253</v>
+      </c>
+      <c r="AZ42" s="8" t="n">
+        <v>5392631</v>
+      </c>
+      <c r="BA42" s="9" t="n">
+        <v>43674.92</v>
+      </c>
+      <c r="BB42" s="10" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="BC42" s="11" t="n">
+        <v>-0.3719237093069153</v>
+      </c>
+      <c r="BD42" s="8" t="n">
+        <v>8585949</v>
+      </c>
+      <c r="BE42" s="9" t="n">
+        <v>56044.78</v>
+      </c>
+      <c r="BF42" s="10" t="n">
+        <v>0.0057</v>
+      </c>
       <c r="BG42" s="11" t="n">
-        <v>-1</v>
+        <v>-0.2132577936597328</v>
       </c>
       <c r="BH42" s="8" t="n">
-        <v>9899412</v>
+        <v>10913294</v>
       </c>
       <c r="BI42" s="9" t="n">
-        <v>19552.33</v>
+        <v>67154.95</v>
       </c>
       <c r="BJ42" s="10" t="n">
-        <v>0.0021</v>
+        <v>0.0072</v>
       </c>
       <c r="BK42" s="11" t="n">
-        <v>0</v>
+        <v>-0.09462389658963724</v>
       </c>
       <c r="BL42" s="8" t="n">
-        <v>9899412</v>
+        <v>12053879</v>
       </c>
       <c r="BM42" s="9" t="n">
-        <v>16216.23</v>
+        <v>70937.08</v>
       </c>
       <c r="BN42" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.0081</v>
       </c>
       <c r="BO42" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BP42" s="8" t="n">
-        <v>9899412</v>
+        <v>12053879</v>
       </c>
       <c r="BQ42" s="9" t="n">
-        <v>16131.09</v>
+        <v>76801.28999999999</v>
       </c>
       <c r="BR42" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.0086</v>
       </c>
       <c r="BS42" s="11" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited</t>
+          <t>ITC Hotels Limited</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>INE768C01010</t>
+          <t>INE379A01028</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Leisure Services</t>
         </is>
       </c>
       <c r="D43" s="8" t="n"/>
@@ -8403,45 +8405,19 @@
       <c r="AJ43" s="8" t="n"/>
       <c r="AK43" s="9" t="n"/>
       <c r="AL43" s="10" t="n"/>
-      <c r="AM43" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN43" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="AO43" s="9" t="n">
-        <v>88822.8</v>
-      </c>
-      <c r="AP43" s="10" t="n">
-        <v>0.0077</v>
-      </c>
-      <c r="AQ43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR43" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="AS43" s="9" t="n">
-        <v>89280.39999999999</v>
-      </c>
-      <c r="AT43" s="10" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-      <c r="AU43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV43" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="AW43" s="9" t="n">
-        <v>89020.8</v>
-      </c>
-      <c r="AX43" s="10" t="n">
-        <v>0.0081</v>
-      </c>
-      <c r="AY43" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="AM43" s="11" t="n"/>
+      <c r="AN43" s="8" t="n"/>
+      <c r="AO43" s="9" t="n"/>
+      <c r="AP43" s="10" t="n"/>
+      <c r="AQ43" s="11" t="n"/>
+      <c r="AR43" s="8" t="n"/>
+      <c r="AS43" s="9" t="n"/>
+      <c r="AT43" s="10" t="n"/>
+      <c r="AU43" s="11" t="n"/>
+      <c r="AV43" s="8" t="n"/>
+      <c r="AW43" s="9" t="n"/>
+      <c r="AX43" s="10" t="n"/>
+      <c r="AY43" s="11" t="n"/>
       <c r="AZ43" s="8" t="n"/>
       <c r="BA43" s="9" t="n"/>
       <c r="BB43" s="10" t="n"/>
@@ -8449,18 +8425,42 @@
       <c r="BD43" s="8" t="n"/>
       <c r="BE43" s="9" t="n"/>
       <c r="BF43" s="10" t="n"/>
-      <c r="BG43" s="11" t="n"/>
-      <c r="BH43" s="8" t="n"/>
-      <c r="BI43" s="9" t="n"/>
-      <c r="BJ43" s="10" t="n"/>
-      <c r="BK43" s="11" t="n"/>
-      <c r="BL43" s="8" t="n"/>
-      <c r="BM43" s="9" t="n"/>
-      <c r="BN43" s="10" t="n"/>
-      <c r="BO43" s="11" t="n"/>
-      <c r="BP43" s="8" t="n"/>
-      <c r="BQ43" s="9" t="n"/>
-      <c r="BR43" s="10" t="n"/>
+      <c r="BG43" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH43" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BI43" s="9" t="n">
+        <v>19552.33</v>
+      </c>
+      <c r="BJ43" s="10" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="BK43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL43" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BM43" s="9" t="n">
+        <v>16216.23</v>
+      </c>
+      <c r="BN43" s="10" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="BO43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP43" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BQ43" s="9" t="n">
+        <v>16131.09</v>
+      </c>
+      <c r="BR43" s="10" t="n">
+        <v>0.0018</v>
+      </c>
       <c r="BS43" s="11" t="n"/>
     </row>
     <row r="44">
@@ -8525,7 +8525,7 @@
         <v>1079845116</v>
       </c>
       <c r="Y44" s="15" t="n">
-        <v>8588270.84</v>
+        <v>8588270.839999998</v>
       </c>
       <c r="Z44" s="16" t="n">
         <v>0.6443999999999998</v>
@@ -8538,7 +8538,7 @@
         <v>8271351.1939775</v>
       </c>
       <c r="AD44" s="16" t="n">
-        <v>0.6374</v>
+        <v>0.6373999999999999</v>
       </c>
       <c r="AE44" s="17" t="n"/>
       <c r="AF44" s="14" t="n">

--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -522,7 +522,7 @@
     <col width="22" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="26" customWidth="1" min="29" max="29"/>
-    <col width="20" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="30" max="30"/>
     <col width="22" customWidth="1" min="31" max="31"/>
     <col width="14" customWidth="1" min="32" max="32"/>
     <col width="26" customWidth="1" min="33" max="33"/>
@@ -6769,24 +6769,24 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Nesco Limited</t>
+          <t>CIE Automotive India Limited</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>INE317F01035</t>
+          <t>INE536H01010</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Commercial Services &amp; Supplies</t>
+          <t>Auto Components</t>
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>151687</v>
+        <v>464063</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>1780.2</v>
+        <v>2071.81</v>
       </c>
       <c r="F33" s="10" t="n">
         <v>0.0001</v>
@@ -6795,149 +6795,85 @@
         <v>0</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>151687</v>
+        <v>464063</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>1862.26</v>
+        <v>2198.5</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="K33" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>151687</v>
+        <v>464063</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>1538.11</v>
+        <v>2065.08</v>
       </c>
       <c r="N33" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="O33" s="11" t="n">
         <v>0</v>
       </c>
       <c r="P33" s="8" t="n">
-        <v>151687</v>
+        <v>464063</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>1704.36</v>
+        <v>2188.75</v>
       </c>
       <c r="R33" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="S33" s="11" t="n">
-        <v>0</v>
+        <v>0.004302331872531515</v>
       </c>
       <c r="T33" s="8" t="n">
-        <v>151687</v>
+        <v>462075</v>
       </c>
       <c r="U33" s="9" t="n">
-        <v>1728.63</v>
+        <v>1932.4</v>
       </c>
       <c r="V33" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="W33" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="Y33" s="9" t="n">
-        <v>1858.32</v>
-      </c>
-      <c r="Z33" s="10" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="AA33" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AC33" s="9" t="n">
-        <v>1947.66</v>
-      </c>
-      <c r="AD33" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AE33" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AG33" s="9" t="n">
-        <v>2076.6</v>
-      </c>
-      <c r="AH33" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AI33" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ33" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AK33" s="9" t="n">
-        <v>1987.1</v>
-      </c>
-      <c r="AL33" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AM33" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN33" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AO33" s="9" t="n">
-        <v>2130.6</v>
-      </c>
-      <c r="AP33" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AQ33" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR33" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AS33" s="9" t="n">
-        <v>2091.16</v>
-      </c>
-      <c r="AT33" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AU33" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV33" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AW33" s="9" t="n">
-        <v>1766.62</v>
-      </c>
-      <c r="AX33" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AY33" s="11" t="n">
-        <v>0.6954140540298874</v>
-      </c>
-      <c r="AZ33" s="8" t="n">
-        <v>89469</v>
-      </c>
-      <c r="BA33" s="9" t="n">
-        <v>828.48</v>
-      </c>
-      <c r="BB33" s="10" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="BC33" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="X33" s="8" t="n"/>
+      <c r="Y33" s="9" t="n"/>
+      <c r="Z33" s="10" t="n"/>
+      <c r="AA33" s="11" t="n"/>
+      <c r="AB33" s="8" t="n"/>
+      <c r="AC33" s="9" t="n"/>
+      <c r="AD33" s="10" t="n"/>
+      <c r="AE33" s="11" t="n"/>
+      <c r="AF33" s="8" t="n"/>
+      <c r="AG33" s="9" t="n"/>
+      <c r="AH33" s="10" t="n"/>
+      <c r="AI33" s="11" t="n"/>
+      <c r="AJ33" s="8" t="n"/>
+      <c r="AK33" s="9" t="n"/>
+      <c r="AL33" s="10" t="n"/>
+      <c r="AM33" s="11" t="n"/>
+      <c r="AN33" s="8" t="n"/>
+      <c r="AO33" s="9" t="n"/>
+      <c r="AP33" s="10" t="n"/>
+      <c r="AQ33" s="11" t="n"/>
+      <c r="AR33" s="8" t="n"/>
+      <c r="AS33" s="9" t="n"/>
+      <c r="AT33" s="10" t="n"/>
+      <c r="AU33" s="11" t="n"/>
+      <c r="AV33" s="8" t="n"/>
+      <c r="AW33" s="9" t="n"/>
+      <c r="AX33" s="10" t="n"/>
+      <c r="AY33" s="11" t="n"/>
+      <c r="AZ33" s="8" t="n"/>
+      <c r="BA33" s="9" t="n"/>
+      <c r="BB33" s="10" t="n"/>
+      <c r="BC33" s="11" t="n"/>
       <c r="BD33" s="8" t="n"/>
       <c r="BE33" s="9" t="n"/>
       <c r="BF33" s="10" t="n"/>
@@ -7177,24 +7113,24 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>CIE Automotive India Limited</t>
+          <t>Nesco Limited</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>INE536H01010</t>
+          <t>INE317F01035</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Auto Components</t>
+          <t>Commercial Services &amp; Supplies</t>
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>464063</v>
+        <v>151687</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>2071.81</v>
+        <v>1780.2</v>
       </c>
       <c r="F35" s="10" t="n">
         <v>0.0001</v>
@@ -7203,85 +7139,149 @@
         <v>0</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>464063</v>
+        <v>151687</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>2198.5</v>
+        <v>1862.26</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="K35" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>464063</v>
+        <v>151687</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>2065.08</v>
+        <v>1538.11</v>
       </c>
       <c r="N35" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="O35" s="11" t="n">
         <v>0</v>
       </c>
       <c r="P35" s="8" t="n">
-        <v>464063</v>
+        <v>151687</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>2188.75</v>
+        <v>1704.36</v>
       </c>
       <c r="R35" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="S35" s="11" t="n">
-        <v>0.004302331872531515</v>
+        <v>0</v>
       </c>
       <c r="T35" s="8" t="n">
-        <v>462075</v>
+        <v>151687</v>
       </c>
       <c r="U35" s="9" t="n">
-        <v>1932.4</v>
+        <v>1728.63</v>
       </c>
       <c r="V35" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="W35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="Y35" s="9" t="n">
+        <v>1858.32</v>
+      </c>
+      <c r="Z35" s="10" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AA35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AC35" s="9" t="n">
+        <v>1947.66</v>
+      </c>
+      <c r="AD35" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AE35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AG35" s="9" t="n">
+        <v>2076.6</v>
+      </c>
+      <c r="AH35" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AI35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AK35" s="9" t="n">
+        <v>1987.1</v>
+      </c>
+      <c r="AL35" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AM35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AO35" s="9" t="n">
+        <v>2130.6</v>
+      </c>
+      <c r="AP35" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AQ35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AS35" s="9" t="n">
+        <v>2091.16</v>
+      </c>
+      <c r="AT35" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AU35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AW35" s="9" t="n">
+        <v>1766.62</v>
+      </c>
+      <c r="AX35" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AY35" s="11" t="n">
+        <v>0.6954140540298874</v>
+      </c>
+      <c r="AZ35" s="8" t="n">
+        <v>89469</v>
+      </c>
+      <c r="BA35" s="9" t="n">
+        <v>828.48</v>
+      </c>
+      <c r="BB35" s="10" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="BC35" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="X35" s="8" t="n"/>
-      <c r="Y35" s="9" t="n"/>
-      <c r="Z35" s="10" t="n"/>
-      <c r="AA35" s="11" t="n"/>
-      <c r="AB35" s="8" t="n"/>
-      <c r="AC35" s="9" t="n"/>
-      <c r="AD35" s="10" t="n"/>
-      <c r="AE35" s="11" t="n"/>
-      <c r="AF35" s="8" t="n"/>
-      <c r="AG35" s="9" t="n"/>
-      <c r="AH35" s="10" t="n"/>
-      <c r="AI35" s="11" t="n"/>
-      <c r="AJ35" s="8" t="n"/>
-      <c r="AK35" s="9" t="n"/>
-      <c r="AL35" s="10" t="n"/>
-      <c r="AM35" s="11" t="n"/>
-      <c r="AN35" s="8" t="n"/>
-      <c r="AO35" s="9" t="n"/>
-      <c r="AP35" s="10" t="n"/>
-      <c r="AQ35" s="11" t="n"/>
-      <c r="AR35" s="8" t="n"/>
-      <c r="AS35" s="9" t="n"/>
-      <c r="AT35" s="10" t="n"/>
-      <c r="AU35" s="11" t="n"/>
-      <c r="AV35" s="8" t="n"/>
-      <c r="AW35" s="9" t="n"/>
-      <c r="AX35" s="10" t="n"/>
-      <c r="AY35" s="11" t="n"/>
-      <c r="AZ35" s="8" t="n"/>
-      <c r="BA35" s="9" t="n"/>
-      <c r="BB35" s="10" t="n"/>
-      <c r="BC35" s="11" t="n"/>
       <c r="BD35" s="8" t="n"/>
       <c r="BE35" s="9" t="n"/>
       <c r="BF35" s="10" t="n"/>
@@ -7302,17 +7302,17 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Kotak Mahindra Bank Limited</t>
+          <t>Balkrishna Industries Limited</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>INE237A01028</t>
+          <t>INE787D01026</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Auto Components</t>
         </is>
       </c>
       <c r="D36" s="8" t="n"/>
@@ -7322,178 +7322,202 @@
       <c r="H36" s="8" t="n"/>
       <c r="I36" s="9" t="n"/>
       <c r="J36" s="10" t="n"/>
-      <c r="K36" s="11" t="n"/>
-      <c r="L36" s="8" t="n"/>
-      <c r="M36" s="9" t="n"/>
-      <c r="N36" s="10" t="n"/>
-      <c r="O36" s="11" t="n"/>
-      <c r="P36" s="8" t="n"/>
-      <c r="Q36" s="9" t="n"/>
-      <c r="R36" s="10" t="n"/>
-      <c r="S36" s="11" t="n"/>
-      <c r="T36" s="8" t="n"/>
-      <c r="U36" s="9" t="n"/>
-      <c r="V36" s="10" t="n"/>
+      <c r="K36" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L36" s="8" t="n">
+        <v>2274074</v>
+      </c>
+      <c r="M36" s="9" t="n">
+        <v>47368.96</v>
+      </c>
+      <c r="N36" s="10" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="O36" s="11" t="n">
+        <v>-0.2174731122669314</v>
+      </c>
+      <c r="P36" s="8" t="n">
+        <v>2906065</v>
+      </c>
+      <c r="Q36" s="9" t="n">
+        <v>69277.67999999999</v>
+      </c>
+      <c r="R36" s="10" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="S36" s="11" t="n">
+        <v>-0.3062750860930125</v>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="U36" s="9" t="n">
+        <v>96591.67</v>
+      </c>
+      <c r="V36" s="10" t="n">
+        <v>0.0072</v>
+      </c>
       <c r="W36" s="11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X36" s="8" t="n">
-        <v>24621592</v>
+        <v>4189074</v>
       </c>
       <c r="Y36" s="9" t="n">
-        <v>541945.86</v>
+        <v>97173.95</v>
       </c>
       <c r="Z36" s="10" t="n">
-        <v>0.0407</v>
+        <v>0.0073</v>
       </c>
       <c r="AA36" s="11" t="n">
-        <v>0.01296144774839237</v>
+        <v>0</v>
       </c>
       <c r="AB36" s="8" t="n">
-        <v>24306544</v>
+        <v>4189074</v>
       </c>
       <c r="AC36" s="9" t="n">
-        <v>516368.22</v>
+        <v>96721.53</v>
       </c>
       <c r="AD36" s="10" t="n">
-        <v>0.0398</v>
+        <v>0.0075</v>
       </c>
       <c r="AE36" s="11" t="n">
-        <v>0.004192884502844551</v>
+        <v>0</v>
       </c>
       <c r="AF36" s="8" t="n">
-        <v>24205055</v>
+        <v>4189074</v>
       </c>
       <c r="AG36" s="9" t="n">
-        <v>508838.67</v>
+        <v>95502.50999999999</v>
       </c>
       <c r="AH36" s="10" t="n">
-        <v>0.0404</v>
+        <v>0.0076</v>
       </c>
       <c r="AI36" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AJ36" s="8" t="n">
-        <v>24205055</v>
+        <v>4189074</v>
       </c>
       <c r="AK36" s="9" t="n">
-        <v>482334.13</v>
+        <v>96130.87</v>
       </c>
       <c r="AL36" s="10" t="n">
-        <v>0.0403</v>
+        <v>0.008</v>
       </c>
       <c r="AM36" s="11" t="n">
-        <v>0.03407788338216907</v>
+        <v>0</v>
       </c>
       <c r="AN36" s="8" t="n">
-        <v>23407381</v>
+        <v>4189074</v>
       </c>
       <c r="AO36" s="9" t="n">
-        <v>458854.89</v>
+        <v>95904.66</v>
       </c>
       <c r="AP36" s="10" t="n">
-        <v>0.0399</v>
+        <v>0.0083</v>
       </c>
       <c r="AQ36" s="11" t="n">
-        <v>0.06425892329321918</v>
+        <v>0</v>
       </c>
       <c r="AR36" s="8" t="n">
-        <v>21994066</v>
+        <v>4189074</v>
       </c>
       <c r="AS36" s="9" t="n">
-        <v>435174.59</v>
+        <v>112108</v>
       </c>
       <c r="AT36" s="10" t="n">
-        <v>0.0384</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="AU36" s="11" t="n">
-        <v>0.07428402120388222</v>
+        <v>0</v>
       </c>
       <c r="AV36" s="8" t="n">
-        <v>20473232</v>
+        <v>4189074</v>
       </c>
       <c r="AW36" s="9" t="n">
-        <v>442938.37</v>
+        <v>102435.43</v>
       </c>
       <c r="AX36" s="10" t="n">
-        <v>0.0401</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="AY36" s="11" t="n">
-        <v>0.03644973136547983</v>
+        <v>0</v>
       </c>
       <c r="AZ36" s="8" t="n">
-        <v>19753232</v>
+        <v>4189074</v>
       </c>
       <c r="BA36" s="9" t="n">
-        <v>409820.3</v>
+        <v>103562.29</v>
       </c>
       <c r="BB36" s="10" t="n">
-        <v>0.0395</v>
+        <v>0.01</v>
       </c>
       <c r="BC36" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BD36" s="8" t="n">
-        <v>19753232</v>
+        <v>4189074</v>
       </c>
       <c r="BE36" s="9" t="n">
-        <v>436171.12</v>
+        <v>112061.92</v>
       </c>
       <c r="BF36" s="10" t="n">
-        <v>0.0443</v>
+        <v>0.0114</v>
       </c>
       <c r="BG36" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BH36" s="8" t="n">
-        <v>19753232</v>
+        <v>4189074</v>
       </c>
       <c r="BI36" s="9" t="n">
-        <v>428882.17</v>
+        <v>107022.46</v>
       </c>
       <c r="BJ36" s="10" t="n">
-        <v>0.0459</v>
+        <v>0.0115</v>
       </c>
       <c r="BK36" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BL36" s="8" t="n">
-        <v>19753232</v>
+        <v>4189074</v>
       </c>
       <c r="BM36" s="9" t="n">
-        <v>375894.13</v>
+        <v>109571.51</v>
       </c>
       <c r="BN36" s="10" t="n">
-        <v>0.0427</v>
+        <v>0.0125</v>
       </c>
       <c r="BO36" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BP36" s="8" t="n">
-        <v>19753232</v>
+        <v>4189074</v>
       </c>
       <c r="BQ36" s="9" t="n">
-        <v>375568.2</v>
+        <v>116089.71</v>
       </c>
       <c r="BR36" s="10" t="n">
-        <v>0.0419</v>
+        <v>0.0129</v>
       </c>
       <c r="BS36" s="11" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Balkrishna Industries Limited</t>
+          <t>Multi Commodity Exchange of India Limited</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>INE787D01026</t>
+          <t>INE745G01043</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Auto Components</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D37" s="8" t="n"/>
@@ -7503,202 +7527,92 @@
       <c r="H37" s="8" t="n"/>
       <c r="I37" s="9" t="n"/>
       <c r="J37" s="10" t="n"/>
-      <c r="K37" s="11" t="n">
+      <c r="K37" s="11" t="n"/>
+      <c r="L37" s="8" t="n"/>
+      <c r="M37" s="9" t="n"/>
+      <c r="N37" s="10" t="n"/>
+      <c r="O37" s="11" t="n"/>
+      <c r="P37" s="8" t="n"/>
+      <c r="Q37" s="9" t="n"/>
+      <c r="R37" s="10" t="n"/>
+      <c r="S37" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="L37" s="8" t="n">
-        <v>2274074</v>
-      </c>
-      <c r="M37" s="9" t="n">
-        <v>47368.96</v>
-      </c>
-      <c r="N37" s="10" t="n">
-        <v>0.0037</v>
-      </c>
-      <c r="O37" s="11" t="n">
-        <v>-0.2174731122669314</v>
-      </c>
-      <c r="P37" s="8" t="n">
-        <v>2906065</v>
-      </c>
-      <c r="Q37" s="9" t="n">
-        <v>69277.67999999999</v>
-      </c>
-      <c r="R37" s="10" t="n">
-        <v>0.0052</v>
-      </c>
-      <c r="S37" s="11" t="n">
-        <v>-0.3062750860930125</v>
-      </c>
       <c r="T37" s="8" t="n">
-        <v>4189074</v>
+        <v>795472</v>
       </c>
       <c r="U37" s="9" t="n">
-        <v>96591.67</v>
+        <v>20109.53</v>
       </c>
       <c r="V37" s="10" t="n">
-        <v>0.0072</v>
+        <v>0.0015</v>
       </c>
       <c r="W37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="Y37" s="9" t="n">
-        <v>97173.95</v>
-      </c>
-      <c r="Z37" s="10" t="n">
-        <v>0.0073</v>
-      </c>
-      <c r="AA37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="AC37" s="9" t="n">
-        <v>96721.53</v>
-      </c>
-      <c r="AD37" s="10" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="AE37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF37" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="AG37" s="9" t="n">
-        <v>95502.50999999999</v>
-      </c>
-      <c r="AH37" s="10" t="n">
-        <v>0.0076</v>
-      </c>
-      <c r="AI37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ37" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="AK37" s="9" t="n">
-        <v>96130.87</v>
-      </c>
-      <c r="AL37" s="10" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="AM37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN37" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="AO37" s="9" t="n">
-        <v>95904.66</v>
-      </c>
-      <c r="AP37" s="10" t="n">
-        <v>0.0083</v>
-      </c>
-      <c r="AQ37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR37" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="AS37" s="9" t="n">
-        <v>112108</v>
-      </c>
-      <c r="AT37" s="10" t="n">
-        <v>0.009900000000000001</v>
-      </c>
-      <c r="AU37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV37" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="AW37" s="9" t="n">
-        <v>102435.43</v>
-      </c>
-      <c r="AX37" s="10" t="n">
-        <v>0.009299999999999999</v>
-      </c>
-      <c r="AY37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ37" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="BA37" s="9" t="n">
-        <v>103562.29</v>
-      </c>
-      <c r="BB37" s="10" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="BC37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD37" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="BE37" s="9" t="n">
-        <v>112061.92</v>
-      </c>
-      <c r="BF37" s="10" t="n">
-        <v>0.0114</v>
-      </c>
-      <c r="BG37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH37" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="BI37" s="9" t="n">
-        <v>107022.46</v>
-      </c>
-      <c r="BJ37" s="10" t="n">
-        <v>0.0115</v>
-      </c>
-      <c r="BK37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL37" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="BM37" s="9" t="n">
-        <v>109571.51</v>
-      </c>
-      <c r="BN37" s="10" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="BO37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP37" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="BQ37" s="9" t="n">
-        <v>116089.71</v>
-      </c>
-      <c r="BR37" s="10" t="n">
-        <v>0.0129</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="X37" s="8" t="n"/>
+      <c r="Y37" s="9" t="n"/>
+      <c r="Z37" s="10" t="n"/>
+      <c r="AA37" s="11" t="n"/>
+      <c r="AB37" s="8" t="n"/>
+      <c r="AC37" s="9" t="n"/>
+      <c r="AD37" s="10" t="n"/>
+      <c r="AE37" s="11" t="n"/>
+      <c r="AF37" s="8" t="n"/>
+      <c r="AG37" s="9" t="n"/>
+      <c r="AH37" s="10" t="n"/>
+      <c r="AI37" s="11" t="n"/>
+      <c r="AJ37" s="8" t="n"/>
+      <c r="AK37" s="9" t="n"/>
+      <c r="AL37" s="10" t="n"/>
+      <c r="AM37" s="11" t="n"/>
+      <c r="AN37" s="8" t="n"/>
+      <c r="AO37" s="9" t="n"/>
+      <c r="AP37" s="10" t="n"/>
+      <c r="AQ37" s="11" t="n"/>
+      <c r="AR37" s="8" t="n"/>
+      <c r="AS37" s="9" t="n"/>
+      <c r="AT37" s="10" t="n"/>
+      <c r="AU37" s="11" t="n"/>
+      <c r="AV37" s="8" t="n"/>
+      <c r="AW37" s="9" t="n"/>
+      <c r="AX37" s="10" t="n"/>
+      <c r="AY37" s="11" t="n"/>
+      <c r="AZ37" s="8" t="n"/>
+      <c r="BA37" s="9" t="n"/>
+      <c r="BB37" s="10" t="n"/>
+      <c r="BC37" s="11" t="n"/>
+      <c r="BD37" s="8" t="n"/>
+      <c r="BE37" s="9" t="n"/>
+      <c r="BF37" s="10" t="n"/>
+      <c r="BG37" s="11" t="n"/>
+      <c r="BH37" s="8" t="n"/>
+      <c r="BI37" s="9" t="n"/>
+      <c r="BJ37" s="10" t="n"/>
+      <c r="BK37" s="11" t="n"/>
+      <c r="BL37" s="8" t="n"/>
+      <c r="BM37" s="9" t="n"/>
+      <c r="BN37" s="10" t="n"/>
+      <c r="BO37" s="11" t="n"/>
+      <c r="BP37" s="8" t="n"/>
+      <c r="BQ37" s="9" t="n"/>
+      <c r="BR37" s="10" t="n"/>
       <c r="BS37" s="11" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Multi Commodity Exchange of India Limited</t>
+          <t>Kotak Mahindra Bank Limited</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>INE745G01035</t>
+          <t>INE237A01028</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="D38" s="8" t="n"/>
@@ -7724,157 +7638,157 @@
         <v>-1</v>
       </c>
       <c r="X38" s="8" t="n">
-        <v>797719</v>
+        <v>24621592</v>
       </c>
       <c r="Y38" s="9" t="n">
-        <v>88833.99000000001</v>
+        <v>541945.86</v>
       </c>
       <c r="Z38" s="10" t="n">
-        <v>0.0067</v>
+        <v>0.0407</v>
       </c>
       <c r="AA38" s="11" t="n">
-        <v>0</v>
+        <v>0.01296144774839237</v>
       </c>
       <c r="AB38" s="8" t="n">
-        <v>797719</v>
+        <v>24306544</v>
       </c>
       <c r="AC38" s="9" t="n">
-        <v>80358.22</v>
+        <v>516368.22</v>
       </c>
       <c r="AD38" s="10" t="n">
-        <v>0.0062</v>
+        <v>0.0398</v>
       </c>
       <c r="AE38" s="11" t="n">
-        <v>0</v>
+        <v>0.004192884502844551</v>
       </c>
       <c r="AF38" s="8" t="n">
-        <v>797719</v>
+        <v>24205055</v>
       </c>
       <c r="AG38" s="9" t="n">
-        <v>73737.16</v>
+        <v>508838.67</v>
       </c>
       <c r="AH38" s="10" t="n">
-        <v>0.0059</v>
+        <v>0.0404</v>
       </c>
       <c r="AI38" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AJ38" s="8" t="n">
-        <v>797719</v>
+        <v>24205055</v>
       </c>
       <c r="AK38" s="9" t="n">
-        <v>62190.17</v>
+        <v>482334.13</v>
       </c>
       <c r="AL38" s="10" t="n">
-        <v>0.0052</v>
+        <v>0.0403</v>
       </c>
       <c r="AM38" s="11" t="n">
-        <v>0</v>
+        <v>0.03407788338216907</v>
       </c>
       <c r="AN38" s="8" t="n">
-        <v>797719</v>
+        <v>23407381</v>
       </c>
       <c r="AO38" s="9" t="n">
-        <v>58951.43</v>
+        <v>458854.89</v>
       </c>
       <c r="AP38" s="10" t="n">
-        <v>0.0051</v>
+        <v>0.0399</v>
       </c>
       <c r="AQ38" s="11" t="n">
-        <v>0</v>
+        <v>0.06425892329321918</v>
       </c>
       <c r="AR38" s="8" t="n">
-        <v>797719</v>
+        <v>21994066</v>
       </c>
       <c r="AS38" s="9" t="n">
-        <v>61368.52</v>
+        <v>435174.59</v>
       </c>
       <c r="AT38" s="10" t="n">
-        <v>0.0054</v>
+        <v>0.0384</v>
       </c>
       <c r="AU38" s="11" t="n">
-        <v>0</v>
+        <v>0.07428402120388222</v>
       </c>
       <c r="AV38" s="8" t="n">
-        <v>797719</v>
+        <v>20473232</v>
       </c>
       <c r="AW38" s="9" t="n">
-        <v>71347.99000000001</v>
+        <v>442938.37</v>
       </c>
       <c r="AX38" s="10" t="n">
-        <v>0.0065</v>
+        <v>0.0401</v>
       </c>
       <c r="AY38" s="11" t="n">
-        <v>0</v>
+        <v>0.03644973136547983</v>
       </c>
       <c r="AZ38" s="8" t="n">
-        <v>797719</v>
+        <v>19753232</v>
       </c>
       <c r="BA38" s="9" t="n">
-        <v>52665.41</v>
+        <v>409820.3</v>
       </c>
       <c r="BB38" s="10" t="n">
-        <v>0.0051</v>
+        <v>0.0395</v>
       </c>
       <c r="BC38" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BD38" s="8" t="n">
-        <v>797719</v>
+        <v>19753232</v>
       </c>
       <c r="BE38" s="9" t="n">
-        <v>48884.22</v>
+        <v>436171.12</v>
       </c>
       <c r="BF38" s="10" t="n">
-        <v>0.005</v>
+        <v>0.0443</v>
       </c>
       <c r="BG38" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BH38" s="8" t="n">
-        <v>797719</v>
+        <v>19753232</v>
       </c>
       <c r="BI38" s="9" t="n">
-        <v>42372.84</v>
+        <v>428882.17</v>
       </c>
       <c r="BJ38" s="10" t="n">
-        <v>0.0045</v>
+        <v>0.0459</v>
       </c>
       <c r="BK38" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BL38" s="8" t="n">
-        <v>797719</v>
+        <v>19753232</v>
       </c>
       <c r="BM38" s="9" t="n">
-        <v>39819.34</v>
+        <v>375894.13</v>
       </c>
       <c r="BN38" s="10" t="n">
-        <v>0.0045</v>
+        <v>0.0427</v>
       </c>
       <c r="BO38" s="11" t="n">
-        <v>-0.09569612848812428</v>
+        <v>0</v>
       </c>
       <c r="BP38" s="8" t="n">
-        <v>882136</v>
+        <v>19753232</v>
       </c>
       <c r="BQ38" s="9" t="n">
-        <v>50572.42</v>
+        <v>375568.2</v>
       </c>
       <c r="BR38" s="10" t="n">
-        <v>0.0056</v>
+        <v>0.0419</v>
       </c>
       <c r="BS38" s="11" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Multi Commodity Exchange of India Limited</t>
+          <t>Motilal Oswal Financial Services Limited</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>INE745G01043</t>
+          <t>INE338I01027</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
@@ -7897,21 +7811,11 @@
       <c r="P39" s="8" t="n"/>
       <c r="Q39" s="9" t="n"/>
       <c r="R39" s="10" t="n"/>
-      <c r="S39" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v>795472</v>
-      </c>
-      <c r="U39" s="9" t="n">
-        <v>20109.53</v>
-      </c>
-      <c r="V39" s="10" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="W39" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="S39" s="11" t="n"/>
+      <c r="T39" s="8" t="n"/>
+      <c r="U39" s="9" t="n"/>
+      <c r="V39" s="10" t="n"/>
+      <c r="W39" s="11" t="n"/>
       <c r="X39" s="8" t="n"/>
       <c r="Y39" s="9" t="n"/>
       <c r="Z39" s="10" t="n"/>
@@ -7935,46 +7839,94 @@
       <c r="AR39" s="8" t="n"/>
       <c r="AS39" s="9" t="n"/>
       <c r="AT39" s="10" t="n"/>
-      <c r="AU39" s="11" t="n"/>
-      <c r="AV39" s="8" t="n"/>
-      <c r="AW39" s="9" t="n"/>
-      <c r="AX39" s="10" t="n"/>
-      <c r="AY39" s="11" t="n"/>
-      <c r="AZ39" s="8" t="n"/>
-      <c r="BA39" s="9" t="n"/>
-      <c r="BB39" s="10" t="n"/>
-      <c r="BC39" s="11" t="n"/>
-      <c r="BD39" s="8" t="n"/>
-      <c r="BE39" s="9" t="n"/>
-      <c r="BF39" s="10" t="n"/>
-      <c r="BG39" s="11" t="n"/>
-      <c r="BH39" s="8" t="n"/>
-      <c r="BI39" s="9" t="n"/>
-      <c r="BJ39" s="10" t="n"/>
-      <c r="BK39" s="11" t="n"/>
-      <c r="BL39" s="8" t="n"/>
-      <c r="BM39" s="9" t="n"/>
-      <c r="BN39" s="10" t="n"/>
-      <c r="BO39" s="11" t="n"/>
-      <c r="BP39" s="8" t="n"/>
-      <c r="BQ39" s="9" t="n"/>
-      <c r="BR39" s="10" t="n"/>
+      <c r="AU39" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AV39" s="8" t="n">
+        <v>591805</v>
+      </c>
+      <c r="AW39" s="9" t="n">
+        <v>5149</v>
+      </c>
+      <c r="AX39" s="10" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="AY39" s="11" t="n">
+        <v>-0.8902567225534253</v>
+      </c>
+      <c r="AZ39" s="8" t="n">
+        <v>5392631</v>
+      </c>
+      <c r="BA39" s="9" t="n">
+        <v>43674.92</v>
+      </c>
+      <c r="BB39" s="10" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="BC39" s="11" t="n">
+        <v>-0.3719237093069153</v>
+      </c>
+      <c r="BD39" s="8" t="n">
+        <v>8585949</v>
+      </c>
+      <c r="BE39" s="9" t="n">
+        <v>56044.78</v>
+      </c>
+      <c r="BF39" s="10" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="BG39" s="11" t="n">
+        <v>-0.2132577936597328</v>
+      </c>
+      <c r="BH39" s="8" t="n">
+        <v>10913294</v>
+      </c>
+      <c r="BI39" s="9" t="n">
+        <v>67154.95</v>
+      </c>
+      <c r="BJ39" s="10" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="BK39" s="11" t="n">
+        <v>-0.09462389658963724</v>
+      </c>
+      <c r="BL39" s="8" t="n">
+        <v>12053879</v>
+      </c>
+      <c r="BM39" s="9" t="n">
+        <v>70937.08</v>
+      </c>
+      <c r="BN39" s="10" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="BO39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP39" s="8" t="n">
+        <v>12053879</v>
+      </c>
+      <c r="BQ39" s="9" t="n">
+        <v>76801.28999999999</v>
+      </c>
+      <c r="BR39" s="10" t="n">
+        <v>0.0086</v>
+      </c>
       <c r="BS39" s="11" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited</t>
+          <t>Multi Commodity Exchange of India Limited</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>INE768C01010</t>
+          <t>INE745G01035</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D40" s="8" t="n"/>
@@ -7996,80 +7948,150 @@
       <c r="T40" s="8" t="n"/>
       <c r="U40" s="9" t="n"/>
       <c r="V40" s="10" t="n"/>
-      <c r="W40" s="11" t="n"/>
-      <c r="X40" s="8" t="n"/>
-      <c r="Y40" s="9" t="n"/>
-      <c r="Z40" s="10" t="n"/>
-      <c r="AA40" s="11" t="n"/>
-      <c r="AB40" s="8" t="n"/>
-      <c r="AC40" s="9" t="n"/>
-      <c r="AD40" s="10" t="n"/>
-      <c r="AE40" s="11" t="n"/>
-      <c r="AF40" s="8" t="n"/>
-      <c r="AG40" s="9" t="n"/>
-      <c r="AH40" s="10" t="n"/>
-      <c r="AI40" s="11" t="n"/>
-      <c r="AJ40" s="8" t="n"/>
-      <c r="AK40" s="9" t="n"/>
-      <c r="AL40" s="10" t="n"/>
+      <c r="W40" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X40" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="Y40" s="9" t="n">
+        <v>88833.99000000001</v>
+      </c>
+      <c r="Z40" s="10" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="AA40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AC40" s="9" t="n">
+        <v>80358.22</v>
+      </c>
+      <c r="AD40" s="10" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="AE40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AG40" s="9" t="n">
+        <v>73737.16</v>
+      </c>
+      <c r="AH40" s="10" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="AI40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AK40" s="9" t="n">
+        <v>62190.17</v>
+      </c>
+      <c r="AL40" s="10" t="n">
+        <v>0.0052</v>
+      </c>
       <c r="AM40" s="11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN40" s="8" t="n">
-        <v>4400000</v>
+        <v>797719</v>
       </c>
       <c r="AO40" s="9" t="n">
-        <v>88822.8</v>
+        <v>58951.43</v>
       </c>
       <c r="AP40" s="10" t="n">
-        <v>0.0077</v>
+        <v>0.0051</v>
       </c>
       <c r="AQ40" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AR40" s="8" t="n">
-        <v>4400000</v>
+        <v>797719</v>
       </c>
       <c r="AS40" s="9" t="n">
-        <v>89280.39999999999</v>
+        <v>61368.52</v>
       </c>
       <c r="AT40" s="10" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0054</v>
       </c>
       <c r="AU40" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AV40" s="8" t="n">
-        <v>4400000</v>
+        <v>797719</v>
       </c>
       <c r="AW40" s="9" t="n">
-        <v>89020.8</v>
+        <v>71347.99000000001</v>
       </c>
       <c r="AX40" s="10" t="n">
-        <v>0.0081</v>
+        <v>0.0065</v>
       </c>
       <c r="AY40" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ40" s="8" t="n"/>
-      <c r="BA40" s="9" t="n"/>
-      <c r="BB40" s="10" t="n"/>
-      <c r="BC40" s="11" t="n"/>
-      <c r="BD40" s="8" t="n"/>
-      <c r="BE40" s="9" t="n"/>
-      <c r="BF40" s="10" t="n"/>
-      <c r="BG40" s="11" t="n"/>
-      <c r="BH40" s="8" t="n"/>
-      <c r="BI40" s="9" t="n"/>
-      <c r="BJ40" s="10" t="n"/>
-      <c r="BK40" s="11" t="n"/>
-      <c r="BL40" s="8" t="n"/>
-      <c r="BM40" s="9" t="n"/>
-      <c r="BN40" s="10" t="n"/>
-      <c r="BO40" s="11" t="n"/>
-      <c r="BP40" s="8" t="n"/>
-      <c r="BQ40" s="9" t="n"/>
-      <c r="BR40" s="10" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AZ40" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="BA40" s="9" t="n">
+        <v>52665.41</v>
+      </c>
+      <c r="BB40" s="10" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="BC40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD40" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="BE40" s="9" t="n">
+        <v>48884.22</v>
+      </c>
+      <c r="BF40" s="10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="BG40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH40" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="BI40" s="9" t="n">
+        <v>42372.84</v>
+      </c>
+      <c r="BJ40" s="10" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="BK40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL40" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="BM40" s="9" t="n">
+        <v>39819.34</v>
+      </c>
+      <c r="BN40" s="10" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="BO40" s="11" t="n">
+        <v>-0.09569612848812428</v>
+      </c>
+      <c r="BP40" s="8" t="n">
+        <v>882136</v>
+      </c>
+      <c r="BQ40" s="9" t="n">
+        <v>50572.42</v>
+      </c>
+      <c r="BR40" s="10" t="n">
+        <v>0.0056</v>
+      </c>
       <c r="BS40" s="11" t="n"/>
     </row>
     <row r="41">
@@ -8224,17 +8246,17 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Motilal Oswal Financial Services Limited</t>
+          <t>ITC Hotels Limited</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>INE338I01027</t>
+          <t>INE379A01028</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Leisure Services</t>
         </is>
       </c>
       <c r="D42" s="8" t="n"/>
@@ -8280,94 +8302,70 @@
       <c r="AR42" s="8" t="n"/>
       <c r="AS42" s="9" t="n"/>
       <c r="AT42" s="10" t="n"/>
-      <c r="AU42" s="11" t="n">
+      <c r="AU42" s="11" t="n"/>
+      <c r="AV42" s="8" t="n"/>
+      <c r="AW42" s="9" t="n"/>
+      <c r="AX42" s="10" t="n"/>
+      <c r="AY42" s="11" t="n"/>
+      <c r="AZ42" s="8" t="n"/>
+      <c r="BA42" s="9" t="n"/>
+      <c r="BB42" s="10" t="n"/>
+      <c r="BC42" s="11" t="n"/>
+      <c r="BD42" s="8" t="n"/>
+      <c r="BE42" s="9" t="n"/>
+      <c r="BF42" s="10" t="n"/>
+      <c r="BG42" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="AV42" s="8" t="n">
-        <v>591805</v>
-      </c>
-      <c r="AW42" s="9" t="n">
-        <v>5149</v>
-      </c>
-      <c r="AX42" s="10" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="AY42" s="11" t="n">
-        <v>-0.8902567225534253</v>
-      </c>
-      <c r="AZ42" s="8" t="n">
-        <v>5392631</v>
-      </c>
-      <c r="BA42" s="9" t="n">
-        <v>43674.92</v>
-      </c>
-      <c r="BB42" s="10" t="n">
-        <v>0.0042</v>
-      </c>
-      <c r="BC42" s="11" t="n">
-        <v>-0.3719237093069153</v>
-      </c>
-      <c r="BD42" s="8" t="n">
-        <v>8585949</v>
-      </c>
-      <c r="BE42" s="9" t="n">
-        <v>56044.78</v>
-      </c>
-      <c r="BF42" s="10" t="n">
-        <v>0.0057</v>
-      </c>
-      <c r="BG42" s="11" t="n">
-        <v>-0.2132577936597328</v>
-      </c>
       <c r="BH42" s="8" t="n">
-        <v>10913294</v>
+        <v>9899412</v>
       </c>
       <c r="BI42" s="9" t="n">
-        <v>67154.95</v>
+        <v>19552.33</v>
       </c>
       <c r="BJ42" s="10" t="n">
-        <v>0.0072</v>
+        <v>0.0021</v>
       </c>
       <c r="BK42" s="11" t="n">
-        <v>-0.09462389658963724</v>
+        <v>0</v>
       </c>
       <c r="BL42" s="8" t="n">
-        <v>12053879</v>
+        <v>9899412</v>
       </c>
       <c r="BM42" s="9" t="n">
-        <v>70937.08</v>
+        <v>16216.23</v>
       </c>
       <c r="BN42" s="10" t="n">
-        <v>0.0081</v>
+        <v>0.0018</v>
       </c>
       <c r="BO42" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BP42" s="8" t="n">
-        <v>12053879</v>
+        <v>9899412</v>
       </c>
       <c r="BQ42" s="9" t="n">
-        <v>76801.28999999999</v>
+        <v>16131.09</v>
       </c>
       <c r="BR42" s="10" t="n">
-        <v>0.0086</v>
+        <v>0.0018</v>
       </c>
       <c r="BS42" s="11" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>ITC Hotels Limited</t>
+          <t>Zydus Wellness Limited</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>INE379A01028</t>
+          <t>INE768C01010</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Leisure Services</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D43" s="8" t="n"/>
@@ -8405,19 +8403,45 @@
       <c r="AJ43" s="8" t="n"/>
       <c r="AK43" s="9" t="n"/>
       <c r="AL43" s="10" t="n"/>
-      <c r="AM43" s="11" t="n"/>
-      <c r="AN43" s="8" t="n"/>
-      <c r="AO43" s="9" t="n"/>
-      <c r="AP43" s="10" t="n"/>
-      <c r="AQ43" s="11" t="n"/>
-      <c r="AR43" s="8" t="n"/>
-      <c r="AS43" s="9" t="n"/>
-      <c r="AT43" s="10" t="n"/>
-      <c r="AU43" s="11" t="n"/>
-      <c r="AV43" s="8" t="n"/>
-      <c r="AW43" s="9" t="n"/>
-      <c r="AX43" s="10" t="n"/>
-      <c r="AY43" s="11" t="n"/>
+      <c r="AM43" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN43" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AO43" s="9" t="n">
+        <v>88822.8</v>
+      </c>
+      <c r="AP43" s="10" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="AQ43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR43" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AS43" s="9" t="n">
+        <v>89280.39999999999</v>
+      </c>
+      <c r="AT43" s="10" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="AU43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV43" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AW43" s="9" t="n">
+        <v>89020.8</v>
+      </c>
+      <c r="AX43" s="10" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="AY43" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="AZ43" s="8" t="n"/>
       <c r="BA43" s="9" t="n"/>
       <c r="BB43" s="10" t="n"/>
@@ -8425,42 +8449,18 @@
       <c r="BD43" s="8" t="n"/>
       <c r="BE43" s="9" t="n"/>
       <c r="BF43" s="10" t="n"/>
-      <c r="BG43" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BH43" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BI43" s="9" t="n">
-        <v>19552.33</v>
-      </c>
-      <c r="BJ43" s="10" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="BK43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL43" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BM43" s="9" t="n">
-        <v>16216.23</v>
-      </c>
-      <c r="BN43" s="10" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="BO43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP43" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BQ43" s="9" t="n">
-        <v>16131.09</v>
-      </c>
-      <c r="BR43" s="10" t="n">
-        <v>0.0018</v>
-      </c>
+      <c r="BG43" s="11" t="n"/>
+      <c r="BH43" s="8" t="n"/>
+      <c r="BI43" s="9" t="n"/>
+      <c r="BJ43" s="10" t="n"/>
+      <c r="BK43" s="11" t="n"/>
+      <c r="BL43" s="8" t="n"/>
+      <c r="BM43" s="9" t="n"/>
+      <c r="BN43" s="10" t="n"/>
+      <c r="BO43" s="11" t="n"/>
+      <c r="BP43" s="8" t="n"/>
+      <c r="BQ43" s="9" t="n"/>
+      <c r="BR43" s="10" t="n"/>
       <c r="BS43" s="11" t="n"/>
     </row>
     <row r="44">
@@ -8525,7 +8525,7 @@
         <v>1079845116</v>
       </c>
       <c r="Y44" s="15" t="n">
-        <v>8588270.839999998</v>
+        <v>8588270.84</v>
       </c>
       <c r="Z44" s="16" t="n">
         <v>0.6443999999999998</v>
@@ -8538,7 +8538,7 @@
         <v>8271351.1939775</v>
       </c>
       <c r="AD44" s="16" t="n">
-        <v>0.6373999999999999</v>
+        <v>0.6374</v>
       </c>
       <c r="AE44" s="17" t="n"/>
       <c r="AF44" s="14" t="n">

--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -7250,24 +7250,24 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Nesco Limited</t>
+          <t>Swaraj Engines Limited</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>INE317F01035</t>
+          <t>INE277A01016</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Commercial Services &amp; Supplies</t>
+          <t>Industrial Products</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>1635.79</v>
+        <v>1890.58</v>
       </c>
       <c r="F34" s="10" t="n">
         <v>0.0001</v>
@@ -7276,10 +7276,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>1780.2</v>
+        <v>1809.43</v>
       </c>
       <c r="J34" s="10" t="n">
         <v>0.0001</v>
@@ -7288,10 +7288,10 @@
         <v>0</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="M34" s="9" t="n">
-        <v>1862.26</v>
+        <v>1871.38</v>
       </c>
       <c r="N34" s="10" t="n">
         <v>0.0001</v>
@@ -7300,10 +7300,10 @@
         <v>0</v>
       </c>
       <c r="P34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>1538.11</v>
+        <v>1564.88</v>
       </c>
       <c r="R34" s="10" t="n">
         <v>0.0001</v>
@@ -7312,10 +7312,10 @@
         <v>0</v>
       </c>
       <c r="T34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="U34" s="9" t="n">
-        <v>1704.36</v>
+        <v>1700.33</v>
       </c>
       <c r="V34" s="10" t="n">
         <v>0.0001</v>
@@ -7324,10 +7324,10 @@
         <v>0</v>
       </c>
       <c r="X34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="Y34" s="9" t="n">
-        <v>1728.63</v>
+        <v>1637.61</v>
       </c>
       <c r="Z34" s="10" t="n">
         <v>0.0001</v>
@@ -7336,10 +7336,10 @@
         <v>0</v>
       </c>
       <c r="AB34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AC34" s="9" t="n">
-        <v>1858.32</v>
+        <v>1691.91</v>
       </c>
       <c r="AD34" s="10" t="n">
         <v>0.0001</v>
@@ -7348,22 +7348,22 @@
         <v>0</v>
       </c>
       <c r="AF34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AG34" s="9" t="n">
-        <v>1947.66</v>
+        <v>1764.08</v>
       </c>
       <c r="AH34" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="AI34" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AJ34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AK34" s="9" t="n">
-        <v>2076.6</v>
+        <v>1892.15</v>
       </c>
       <c r="AL34" s="10" t="n">
         <v>0.0002</v>
@@ -7372,10 +7372,10 @@
         <v>0</v>
       </c>
       <c r="AN34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AO34" s="9" t="n">
-        <v>1987.1</v>
+        <v>1955.38</v>
       </c>
       <c r="AP34" s="10" t="n">
         <v>0.0002</v>
@@ -7384,10 +7384,10 @@
         <v>0</v>
       </c>
       <c r="AR34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AS34" s="9" t="n">
-        <v>2130.6</v>
+        <v>1897.21</v>
       </c>
       <c r="AT34" s="10" t="n">
         <v>0.0002</v>
@@ -7396,10 +7396,10 @@
         <v>0</v>
       </c>
       <c r="AV34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AW34" s="9" t="n">
-        <v>2091.16</v>
+        <v>1983.66</v>
       </c>
       <c r="AX34" s="10" t="n">
         <v>0.0002</v>
@@ -7408,67 +7408,97 @@
         <v>0</v>
       </c>
       <c r="AZ34" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="BA34" s="9" t="n">
-        <v>1766.62</v>
+        <v>1867.41</v>
       </c>
       <c r="BB34" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="BC34" s="11" t="n">
-        <v>0.6954140540298874</v>
+        <v>0</v>
       </c>
       <c r="BD34" s="8" t="n">
-        <v>89469</v>
+        <v>47293</v>
       </c>
       <c r="BE34" s="9" t="n">
-        <v>828.48</v>
+        <v>1857.76</v>
       </c>
       <c r="BF34" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="BG34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH34" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="BI34" s="9" t="n">
+        <v>1925.39</v>
+      </c>
+      <c r="BJ34" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="BK34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL34" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="BM34" s="9" t="n">
+        <v>1844.17</v>
+      </c>
+      <c r="BN34" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="BO34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP34" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="BQ34" s="9" t="n">
+        <v>1236.83</v>
+      </c>
+      <c r="BR34" s="10" t="n">
         <v>0.0001</v>
       </c>
-      <c r="BG34" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH34" s="8" t="n"/>
-      <c r="BI34" s="9" t="n"/>
-      <c r="BJ34" s="10" t="n"/>
-      <c r="BK34" s="11" t="n"/>
-      <c r="BL34" s="8" t="n"/>
-      <c r="BM34" s="9" t="n"/>
-      <c r="BN34" s="10" t="n"/>
-      <c r="BO34" s="11" t="n"/>
-      <c r="BP34" s="8" t="n"/>
-      <c r="BQ34" s="9" t="n"/>
-      <c r="BR34" s="10" t="n"/>
-      <c r="BS34" s="11" t="n"/>
-      <c r="BT34" s="8" t="n"/>
-      <c r="BU34" s="9" t="n"/>
-      <c r="BV34" s="10" t="n"/>
+      <c r="BS34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT34" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="BU34" s="9" t="n">
+        <v>1612.64</v>
+      </c>
+      <c r="BV34" s="10" t="n">
+        <v>0.0002</v>
+      </c>
       <c r="BW34" s="11" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Swaraj Engines Limited</t>
+          <t>CIE Automotive India Limited</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>INE277A01016</t>
+          <t>INE536H01010</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Industrial Products</t>
+          <t>Auto Components</t>
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>47293</v>
+        <v>464063</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>1890.58</v>
+        <v>2124.48</v>
       </c>
       <c r="F35" s="10" t="n">
         <v>0.0001</v>
@@ -7477,10 +7507,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>47293</v>
+        <v>464063</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>1809.43</v>
+        <v>2071.81</v>
       </c>
       <c r="J35" s="10" t="n">
         <v>0.0001</v>
@@ -7489,217 +7519,123 @@
         <v>0</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>47293</v>
+        <v>464063</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>1871.38</v>
+        <v>2198.5</v>
       </c>
       <c r="N35" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="O35" s="11" t="n">
         <v>0</v>
       </c>
       <c r="P35" s="8" t="n">
-        <v>47293</v>
+        <v>464063</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>1564.88</v>
+        <v>2065.08</v>
       </c>
       <c r="R35" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="S35" s="11" t="n">
         <v>0</v>
       </c>
       <c r="T35" s="8" t="n">
-        <v>47293</v>
+        <v>464063</v>
       </c>
       <c r="U35" s="9" t="n">
-        <v>1700.33</v>
+        <v>2188.75</v>
       </c>
       <c r="V35" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="W35" s="11" t="n">
-        <v>0</v>
+        <v>0.004302331872531515</v>
       </c>
       <c r="X35" s="8" t="n">
-        <v>47293</v>
+        <v>462075</v>
       </c>
       <c r="Y35" s="9" t="n">
-        <v>1637.61</v>
+        <v>1932.4</v>
       </c>
       <c r="Z35" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="AA35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="AC35" s="9" t="n">
-        <v>1691.91</v>
-      </c>
-      <c r="AD35" s="10" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="AE35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="AG35" s="9" t="n">
-        <v>1764.08</v>
-      </c>
-      <c r="AH35" s="10" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="AI35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="AK35" s="9" t="n">
-        <v>1892.15</v>
-      </c>
-      <c r="AL35" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AM35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN35" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="AO35" s="9" t="n">
-        <v>1955.38</v>
-      </c>
-      <c r="AP35" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AQ35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR35" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="AS35" s="9" t="n">
-        <v>1897.21</v>
-      </c>
-      <c r="AT35" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AU35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV35" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="AW35" s="9" t="n">
-        <v>1983.66</v>
-      </c>
-      <c r="AX35" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AY35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ35" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="BA35" s="9" t="n">
-        <v>1867.41</v>
-      </c>
-      <c r="BB35" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="BC35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD35" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="BE35" s="9" t="n">
-        <v>1857.76</v>
-      </c>
-      <c r="BF35" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="BG35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH35" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="BI35" s="9" t="n">
-        <v>1925.39</v>
-      </c>
-      <c r="BJ35" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="BK35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL35" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="BM35" s="9" t="n">
-        <v>1844.17</v>
-      </c>
-      <c r="BN35" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="BO35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP35" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="BQ35" s="9" t="n">
-        <v>1236.83</v>
-      </c>
-      <c r="BR35" s="10" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="BS35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT35" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="BU35" s="9" t="n">
-        <v>1612.64</v>
-      </c>
-      <c r="BV35" s="10" t="n">
-        <v>0.0002</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AB35" s="8" t="n"/>
+      <c r="AC35" s="9" t="n"/>
+      <c r="AD35" s="10" t="n"/>
+      <c r="AE35" s="11" t="n"/>
+      <c r="AF35" s="8" t="n"/>
+      <c r="AG35" s="9" t="n"/>
+      <c r="AH35" s="10" t="n"/>
+      <c r="AI35" s="11" t="n"/>
+      <c r="AJ35" s="8" t="n"/>
+      <c r="AK35" s="9" t="n"/>
+      <c r="AL35" s="10" t="n"/>
+      <c r="AM35" s="11" t="n"/>
+      <c r="AN35" s="8" t="n"/>
+      <c r="AO35" s="9" t="n"/>
+      <c r="AP35" s="10" t="n"/>
+      <c r="AQ35" s="11" t="n"/>
+      <c r="AR35" s="8" t="n"/>
+      <c r="AS35" s="9" t="n"/>
+      <c r="AT35" s="10" t="n"/>
+      <c r="AU35" s="11" t="n"/>
+      <c r="AV35" s="8" t="n"/>
+      <c r="AW35" s="9" t="n"/>
+      <c r="AX35" s="10" t="n"/>
+      <c r="AY35" s="11" t="n"/>
+      <c r="AZ35" s="8" t="n"/>
+      <c r="BA35" s="9" t="n"/>
+      <c r="BB35" s="10" t="n"/>
+      <c r="BC35" s="11" t="n"/>
+      <c r="BD35" s="8" t="n"/>
+      <c r="BE35" s="9" t="n"/>
+      <c r="BF35" s="10" t="n"/>
+      <c r="BG35" s="11" t="n"/>
+      <c r="BH35" s="8" t="n"/>
+      <c r="BI35" s="9" t="n"/>
+      <c r="BJ35" s="10" t="n"/>
+      <c r="BK35" s="11" t="n"/>
+      <c r="BL35" s="8" t="n"/>
+      <c r="BM35" s="9" t="n"/>
+      <c r="BN35" s="10" t="n"/>
+      <c r="BO35" s="11" t="n"/>
+      <c r="BP35" s="8" t="n"/>
+      <c r="BQ35" s="9" t="n"/>
+      <c r="BR35" s="10" t="n"/>
+      <c r="BS35" s="11" t="n"/>
+      <c r="BT35" s="8" t="n"/>
+      <c r="BU35" s="9" t="n"/>
+      <c r="BV35" s="10" t="n"/>
       <c r="BW35" s="11" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>CIE Automotive India Limited</t>
+          <t>Nesco Limited</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>INE536H01010</t>
+          <t>INE317F01035</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Auto Components</t>
+          <t>Commercial Services &amp; Supplies</t>
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>464063</v>
+        <v>151687</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>2124.48</v>
+        <v>1635.79</v>
       </c>
       <c r="F36" s="10" t="n">
         <v>0.0001</v>
@@ -7708,10 +7644,10 @@
         <v>0</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>464063</v>
+        <v>151687</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>2071.81</v>
+        <v>1780.2</v>
       </c>
       <c r="J36" s="10" t="n">
         <v>0.0001</v>
@@ -7720,85 +7656,149 @@
         <v>0</v>
       </c>
       <c r="L36" s="8" t="n">
-        <v>464063</v>
+        <v>151687</v>
       </c>
       <c r="M36" s="9" t="n">
-        <v>2198.5</v>
+        <v>1862.26</v>
       </c>
       <c r="N36" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="O36" s="11" t="n">
         <v>0</v>
       </c>
       <c r="P36" s="8" t="n">
-        <v>464063</v>
+        <v>151687</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>2065.08</v>
+        <v>1538.11</v>
       </c>
       <c r="R36" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="S36" s="11" t="n">
         <v>0</v>
       </c>
       <c r="T36" s="8" t="n">
-        <v>464063</v>
+        <v>151687</v>
       </c>
       <c r="U36" s="9" t="n">
-        <v>2188.75</v>
+        <v>1704.36</v>
       </c>
       <c r="V36" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="W36" s="11" t="n">
-        <v>0.004302331872531515</v>
+        <v>0</v>
       </c>
       <c r="X36" s="8" t="n">
-        <v>462075</v>
+        <v>151687</v>
       </c>
       <c r="Y36" s="9" t="n">
-        <v>1932.4</v>
+        <v>1728.63</v>
       </c>
       <c r="Z36" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="AA36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AC36" s="9" t="n">
+        <v>1858.32</v>
+      </c>
+      <c r="AD36" s="10" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AE36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AG36" s="9" t="n">
+        <v>1947.66</v>
+      </c>
+      <c r="AH36" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AI36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AK36" s="9" t="n">
+        <v>2076.6</v>
+      </c>
+      <c r="AL36" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AM36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AO36" s="9" t="n">
+        <v>1987.1</v>
+      </c>
+      <c r="AP36" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AQ36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AS36" s="9" t="n">
+        <v>2130.6</v>
+      </c>
+      <c r="AT36" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AU36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AW36" s="9" t="n">
+        <v>2091.16</v>
+      </c>
+      <c r="AX36" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AY36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="BA36" s="9" t="n">
+        <v>1766.62</v>
+      </c>
+      <c r="BB36" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="BC36" s="11" t="n">
+        <v>0.6954140540298874</v>
+      </c>
+      <c r="BD36" s="8" t="n">
+        <v>89469</v>
+      </c>
+      <c r="BE36" s="9" t="n">
+        <v>828.48</v>
+      </c>
+      <c r="BF36" s="10" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="BG36" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="AB36" s="8" t="n"/>
-      <c r="AC36" s="9" t="n"/>
-      <c r="AD36" s="10" t="n"/>
-      <c r="AE36" s="11" t="n"/>
-      <c r="AF36" s="8" t="n"/>
-      <c r="AG36" s="9" t="n"/>
-      <c r="AH36" s="10" t="n"/>
-      <c r="AI36" s="11" t="n"/>
-      <c r="AJ36" s="8" t="n"/>
-      <c r="AK36" s="9" t="n"/>
-      <c r="AL36" s="10" t="n"/>
-      <c r="AM36" s="11" t="n"/>
-      <c r="AN36" s="8" t="n"/>
-      <c r="AO36" s="9" t="n"/>
-      <c r="AP36" s="10" t="n"/>
-      <c r="AQ36" s="11" t="n"/>
-      <c r="AR36" s="8" t="n"/>
-      <c r="AS36" s="9" t="n"/>
-      <c r="AT36" s="10" t="n"/>
-      <c r="AU36" s="11" t="n"/>
-      <c r="AV36" s="8" t="n"/>
-      <c r="AW36" s="9" t="n"/>
-      <c r="AX36" s="10" t="n"/>
-      <c r="AY36" s="11" t="n"/>
-      <c r="AZ36" s="8" t="n"/>
-      <c r="BA36" s="9" t="n"/>
-      <c r="BB36" s="10" t="n"/>
-      <c r="BC36" s="11" t="n"/>
-      <c r="BD36" s="8" t="n"/>
-      <c r="BE36" s="9" t="n"/>
-      <c r="BF36" s="10" t="n"/>
-      <c r="BG36" s="11" t="n"/>
       <c r="BH36" s="8" t="n"/>
       <c r="BI36" s="9" t="n"/>
       <c r="BJ36" s="10" t="n"/>
@@ -8213,12 +8213,12 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Multi Commodity Exchange of India Limited</t>
+          <t>Motilal Oswal Financial Services Limited</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>INE745G01035</t>
+          <t>INE338I01027</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
@@ -8249,149 +8249,101 @@
       <c r="X39" s="8" t="n"/>
       <c r="Y39" s="9" t="n"/>
       <c r="Z39" s="10" t="n"/>
-      <c r="AA39" s="11" t="n">
+      <c r="AA39" s="11" t="n"/>
+      <c r="AB39" s="8" t="n"/>
+      <c r="AC39" s="9" t="n"/>
+      <c r="AD39" s="10" t="n"/>
+      <c r="AE39" s="11" t="n"/>
+      <c r="AF39" s="8" t="n"/>
+      <c r="AG39" s="9" t="n"/>
+      <c r="AH39" s="10" t="n"/>
+      <c r="AI39" s="11" t="n"/>
+      <c r="AJ39" s="8" t="n"/>
+      <c r="AK39" s="9" t="n"/>
+      <c r="AL39" s="10" t="n"/>
+      <c r="AM39" s="11" t="n"/>
+      <c r="AN39" s="8" t="n"/>
+      <c r="AO39" s="9" t="n"/>
+      <c r="AP39" s="10" t="n"/>
+      <c r="AQ39" s="11" t="n"/>
+      <c r="AR39" s="8" t="n"/>
+      <c r="AS39" s="9" t="n"/>
+      <c r="AT39" s="10" t="n"/>
+      <c r="AU39" s="11" t="n"/>
+      <c r="AV39" s="8" t="n"/>
+      <c r="AW39" s="9" t="n"/>
+      <c r="AX39" s="10" t="n"/>
+      <c r="AY39" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="AB39" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="AC39" s="9" t="n">
-        <v>88833.99000000001</v>
-      </c>
-      <c r="AD39" s="10" t="n">
-        <v>0.0067</v>
-      </c>
-      <c r="AE39" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="AG39" s="9" t="n">
-        <v>80358.22</v>
-      </c>
-      <c r="AH39" s="10" t="n">
-        <v>0.0062</v>
-      </c>
-      <c r="AI39" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="AK39" s="9" t="n">
-        <v>73737.16</v>
-      </c>
-      <c r="AL39" s="10" t="n">
-        <v>0.0059</v>
-      </c>
-      <c r="AM39" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN39" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="AO39" s="9" t="n">
-        <v>62190.17</v>
-      </c>
-      <c r="AP39" s="10" t="n">
-        <v>0.0052</v>
-      </c>
-      <c r="AQ39" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR39" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="AS39" s="9" t="n">
-        <v>58951.43</v>
-      </c>
-      <c r="AT39" s="10" t="n">
-        <v>0.0051</v>
-      </c>
-      <c r="AU39" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV39" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="AW39" s="9" t="n">
-        <v>61368.52</v>
-      </c>
-      <c r="AX39" s="10" t="n">
-        <v>0.0054</v>
-      </c>
-      <c r="AY39" s="11" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ39" s="8" t="n">
-        <v>797719</v>
+        <v>591805</v>
       </c>
       <c r="BA39" s="9" t="n">
-        <v>71347.99000000001</v>
+        <v>5149</v>
       </c>
       <c r="BB39" s="10" t="n">
-        <v>0.0065</v>
+        <v>0.0005</v>
       </c>
       <c r="BC39" s="11" t="n">
-        <v>0</v>
+        <v>-0.8902567225534253</v>
       </c>
       <c r="BD39" s="8" t="n">
-        <v>797719</v>
+        <v>5392631</v>
       </c>
       <c r="BE39" s="9" t="n">
-        <v>52665.41</v>
+        <v>43674.92</v>
       </c>
       <c r="BF39" s="10" t="n">
-        <v>0.0051</v>
+        <v>0.0042</v>
       </c>
       <c r="BG39" s="11" t="n">
-        <v>0</v>
+        <v>-0.3719237093069153</v>
       </c>
       <c r="BH39" s="8" t="n">
-        <v>797719</v>
+        <v>8585949</v>
       </c>
       <c r="BI39" s="9" t="n">
-        <v>48884.22</v>
+        <v>56044.78</v>
       </c>
       <c r="BJ39" s="10" t="n">
-        <v>0.005</v>
+        <v>0.0057</v>
       </c>
       <c r="BK39" s="11" t="n">
-        <v>0</v>
+        <v>-0.2132577936597328</v>
       </c>
       <c r="BL39" s="8" t="n">
-        <v>797719</v>
+        <v>10913294</v>
       </c>
       <c r="BM39" s="9" t="n">
-        <v>42372.84</v>
+        <v>67154.95</v>
       </c>
       <c r="BN39" s="10" t="n">
-        <v>0.0045</v>
+        <v>0.0072</v>
       </c>
       <c r="BO39" s="11" t="n">
-        <v>0</v>
+        <v>-0.09462389658963724</v>
       </c>
       <c r="BP39" s="8" t="n">
-        <v>797719</v>
+        <v>12053879</v>
       </c>
       <c r="BQ39" s="9" t="n">
-        <v>39819.34</v>
+        <v>70937.08</v>
       </c>
       <c r="BR39" s="10" t="n">
-        <v>0.0045</v>
+        <v>0.0081</v>
       </c>
       <c r="BS39" s="11" t="n">
-        <v>-0.09569612848812428</v>
+        <v>0</v>
       </c>
       <c r="BT39" s="8" t="n">
-        <v>882136</v>
+        <v>12053879</v>
       </c>
       <c r="BU39" s="9" t="n">
-        <v>50572.42</v>
+        <v>76801.28999999999</v>
       </c>
       <c r="BV39" s="10" t="n">
-        <v>0.0056</v>
+        <v>0.0086</v>
       </c>
       <c r="BW39" s="11" t="n"/>
     </row>
@@ -8403,7 +8355,7 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>INE745G01043</t>
+          <t>INE745G01035</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
@@ -8430,84 +8382,170 @@
       <c r="T40" s="8" t="n"/>
       <c r="U40" s="9" t="n"/>
       <c r="V40" s="10" t="n"/>
-      <c r="W40" s="11" t="n">
+      <c r="W40" s="11" t="n"/>
+      <c r="X40" s="8" t="n"/>
+      <c r="Y40" s="9" t="n"/>
+      <c r="Z40" s="10" t="n"/>
+      <c r="AA40" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="X40" s="8" t="n">
-        <v>795472</v>
-      </c>
-      <c r="Y40" s="9" t="n">
-        <v>20109.53</v>
-      </c>
-      <c r="Z40" s="10" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="AA40" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB40" s="8" t="n"/>
-      <c r="AC40" s="9" t="n"/>
-      <c r="AD40" s="10" t="n"/>
-      <c r="AE40" s="11" t="n"/>
-      <c r="AF40" s="8" t="n"/>
-      <c r="AG40" s="9" t="n"/>
-      <c r="AH40" s="10" t="n"/>
-      <c r="AI40" s="11" t="n"/>
-      <c r="AJ40" s="8" t="n"/>
-      <c r="AK40" s="9" t="n"/>
-      <c r="AL40" s="10" t="n"/>
-      <c r="AM40" s="11" t="n"/>
-      <c r="AN40" s="8" t="n"/>
-      <c r="AO40" s="9" t="n"/>
-      <c r="AP40" s="10" t="n"/>
-      <c r="AQ40" s="11" t="n"/>
-      <c r="AR40" s="8" t="n"/>
-      <c r="AS40" s="9" t="n"/>
-      <c r="AT40" s="10" t="n"/>
-      <c r="AU40" s="11" t="n"/>
-      <c r="AV40" s="8" t="n"/>
-      <c r="AW40" s="9" t="n"/>
-      <c r="AX40" s="10" t="n"/>
-      <c r="AY40" s="11" t="n"/>
-      <c r="AZ40" s="8" t="n"/>
-      <c r="BA40" s="9" t="n"/>
-      <c r="BB40" s="10" t="n"/>
-      <c r="BC40" s="11" t="n"/>
-      <c r="BD40" s="8" t="n"/>
-      <c r="BE40" s="9" t="n"/>
-      <c r="BF40" s="10" t="n"/>
-      <c r="BG40" s="11" t="n"/>
-      <c r="BH40" s="8" t="n"/>
-      <c r="BI40" s="9" t="n"/>
-      <c r="BJ40" s="10" t="n"/>
-      <c r="BK40" s="11" t="n"/>
-      <c r="BL40" s="8" t="n"/>
-      <c r="BM40" s="9" t="n"/>
-      <c r="BN40" s="10" t="n"/>
-      <c r="BO40" s="11" t="n"/>
-      <c r="BP40" s="8" t="n"/>
-      <c r="BQ40" s="9" t="n"/>
-      <c r="BR40" s="10" t="n"/>
-      <c r="BS40" s="11" t="n"/>
-      <c r="BT40" s="8" t="n"/>
-      <c r="BU40" s="9" t="n"/>
-      <c r="BV40" s="10" t="n"/>
+      <c r="AB40" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AC40" s="9" t="n">
+        <v>88833.99000000001</v>
+      </c>
+      <c r="AD40" s="10" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="AE40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AG40" s="9" t="n">
+        <v>80358.22</v>
+      </c>
+      <c r="AH40" s="10" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="AI40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AK40" s="9" t="n">
+        <v>73737.16</v>
+      </c>
+      <c r="AL40" s="10" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="AM40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AO40" s="9" t="n">
+        <v>62190.17</v>
+      </c>
+      <c r="AP40" s="10" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="AQ40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AS40" s="9" t="n">
+        <v>58951.43</v>
+      </c>
+      <c r="AT40" s="10" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="AU40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AW40" s="9" t="n">
+        <v>61368.52</v>
+      </c>
+      <c r="AX40" s="10" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="AY40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ40" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="BA40" s="9" t="n">
+        <v>71347.99000000001</v>
+      </c>
+      <c r="BB40" s="10" t="n">
+        <v>0.0065</v>
+      </c>
+      <c r="BC40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD40" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="BE40" s="9" t="n">
+        <v>52665.41</v>
+      </c>
+      <c r="BF40" s="10" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="BG40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH40" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="BI40" s="9" t="n">
+        <v>48884.22</v>
+      </c>
+      <c r="BJ40" s="10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="BK40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL40" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="BM40" s="9" t="n">
+        <v>42372.84</v>
+      </c>
+      <c r="BN40" s="10" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="BO40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP40" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="BQ40" s="9" t="n">
+        <v>39819.34</v>
+      </c>
+      <c r="BR40" s="10" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="BS40" s="11" t="n">
+        <v>-0.09569612848812428</v>
+      </c>
+      <c r="BT40" s="8" t="n">
+        <v>882136</v>
+      </c>
+      <c r="BU40" s="9" t="n">
+        <v>50572.42</v>
+      </c>
+      <c r="BV40" s="10" t="n">
+        <v>0.0056</v>
+      </c>
       <c r="BW40" s="11" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited</t>
+          <t>IPCA Laboratories Limited</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>INE768C01010</t>
+          <t>INE571A01038</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Pharmaceuticals &amp; Biotechnology</t>
         </is>
       </c>
       <c r="D41" s="8" t="n"/>
@@ -8553,76 +8591,114 @@
         <v>-1</v>
       </c>
       <c r="AR41" s="8" t="n">
-        <v>4400000</v>
+        <v>218075</v>
       </c>
       <c r="AS41" s="9" t="n">
-        <v>88822.8</v>
+        <v>3019.03</v>
       </c>
       <c r="AT41" s="10" t="n">
-        <v>0.0077</v>
+        <v>0.0003</v>
       </c>
       <c r="AU41" s="11" t="n">
-        <v>0</v>
+        <v>-0.6148554615199853</v>
       </c>
       <c r="AV41" s="8" t="n">
-        <v>4400000</v>
+        <v>566216</v>
       </c>
       <c r="AW41" s="9" t="n">
-        <v>89280.39999999999</v>
+        <v>8345.459999999999</v>
       </c>
       <c r="AX41" s="10" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0007</v>
       </c>
       <c r="AY41" s="11" t="n">
-        <v>0</v>
+        <v>-0.5682871579351869</v>
       </c>
       <c r="AZ41" s="8" t="n">
-        <v>4400000</v>
+        <v>1311557</v>
       </c>
       <c r="BA41" s="9" t="n">
-        <v>89020.8</v>
+        <v>18228.02</v>
       </c>
       <c r="BB41" s="10" t="n">
-        <v>0.0081</v>
+        <v>0.0017</v>
       </c>
       <c r="BC41" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD41" s="8" t="n"/>
-      <c r="BE41" s="9" t="n"/>
-      <c r="BF41" s="10" t="n"/>
-      <c r="BG41" s="11" t="n"/>
-      <c r="BH41" s="8" t="n"/>
-      <c r="BI41" s="9" t="n"/>
-      <c r="BJ41" s="10" t="n"/>
-      <c r="BK41" s="11" t="n"/>
-      <c r="BL41" s="8" t="n"/>
-      <c r="BM41" s="9" t="n"/>
-      <c r="BN41" s="10" t="n"/>
-      <c r="BO41" s="11" t="n"/>
-      <c r="BP41" s="8" t="n"/>
-      <c r="BQ41" s="9" t="n"/>
-      <c r="BR41" s="10" t="n"/>
-      <c r="BS41" s="11" t="n"/>
-      <c r="BT41" s="8" t="n"/>
-      <c r="BU41" s="9" t="n"/>
-      <c r="BV41" s="10" t="n"/>
+        <v>-0.2008037316547793</v>
+      </c>
+      <c r="BD41" s="8" t="n">
+        <v>1641095</v>
+      </c>
+      <c r="BE41" s="9" t="n">
+        <v>23382.32</v>
+      </c>
+      <c r="BF41" s="10" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="BG41" s="11" t="n">
+        <v>-0.1163687388172734</v>
+      </c>
+      <c r="BH41" s="8" t="n">
+        <v>1857217</v>
+      </c>
+      <c r="BI41" s="9" t="n">
+        <v>26023.32</v>
+      </c>
+      <c r="BJ41" s="10" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="BK41" s="11" t="n">
+        <v>-0.03620728307597141</v>
+      </c>
+      <c r="BL41" s="8" t="n">
+        <v>1926988</v>
+      </c>
+      <c r="BM41" s="9" t="n">
+        <v>28941.43</v>
+      </c>
+      <c r="BN41" s="10" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="BO41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP41" s="8" t="n">
+        <v>1926988</v>
+      </c>
+      <c r="BQ41" s="9" t="n">
+        <v>26117.43</v>
+      </c>
+      <c r="BR41" s="10" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="BS41" s="11" t="n">
+        <v>-0.1421734974921662</v>
+      </c>
+      <c r="BT41" s="8" t="n">
+        <v>2246361</v>
+      </c>
+      <c r="BU41" s="9" t="n">
+        <v>32421.73</v>
+      </c>
+      <c r="BV41" s="10" t="n">
+        <v>0.0036</v>
+      </c>
       <c r="BW41" s="11" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>IPCA Laboratories Limited</t>
+          <t>Zydus Wellness Limited</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>INE571A01038</t>
+          <t>INE768C01010</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Pharmaceuticals &amp; Biotechnology</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D42" s="8" t="n"/>
@@ -8668,114 +8744,76 @@
         <v>-1</v>
       </c>
       <c r="AR42" s="8" t="n">
-        <v>218075</v>
+        <v>4400000</v>
       </c>
       <c r="AS42" s="9" t="n">
-        <v>3019.03</v>
+        <v>88822.8</v>
       </c>
       <c r="AT42" s="10" t="n">
-        <v>0.0003</v>
+        <v>0.0077</v>
       </c>
       <c r="AU42" s="11" t="n">
-        <v>-0.6148554615199853</v>
+        <v>0</v>
       </c>
       <c r="AV42" s="8" t="n">
-        <v>566216</v>
+        <v>4400000</v>
       </c>
       <c r="AW42" s="9" t="n">
-        <v>8345.459999999999</v>
+        <v>89280.39999999999</v>
       </c>
       <c r="AX42" s="10" t="n">
-        <v>0.0007</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="AY42" s="11" t="n">
-        <v>-0.5682871579351869</v>
+        <v>0</v>
       </c>
       <c r="AZ42" s="8" t="n">
-        <v>1311557</v>
+        <v>4400000</v>
       </c>
       <c r="BA42" s="9" t="n">
-        <v>18228.02</v>
+        <v>89020.8</v>
       </c>
       <c r="BB42" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.0081</v>
       </c>
       <c r="BC42" s="11" t="n">
-        <v>-0.2008037316547793</v>
-      </c>
-      <c r="BD42" s="8" t="n">
-        <v>1641095</v>
-      </c>
-      <c r="BE42" s="9" t="n">
-        <v>23382.32</v>
-      </c>
-      <c r="BF42" s="10" t="n">
-        <v>0.0023</v>
-      </c>
-      <c r="BG42" s="11" t="n">
-        <v>-0.1163687388172734</v>
-      </c>
-      <c r="BH42" s="8" t="n">
-        <v>1857217</v>
-      </c>
-      <c r="BI42" s="9" t="n">
-        <v>26023.32</v>
-      </c>
-      <c r="BJ42" s="10" t="n">
-        <v>0.0026</v>
-      </c>
-      <c r="BK42" s="11" t="n">
-        <v>-0.03620728307597141</v>
-      </c>
-      <c r="BL42" s="8" t="n">
-        <v>1926988</v>
-      </c>
-      <c r="BM42" s="9" t="n">
-        <v>28941.43</v>
-      </c>
-      <c r="BN42" s="10" t="n">
-        <v>0.0031</v>
-      </c>
-      <c r="BO42" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP42" s="8" t="n">
-        <v>1926988</v>
-      </c>
-      <c r="BQ42" s="9" t="n">
-        <v>26117.43</v>
-      </c>
-      <c r="BR42" s="10" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="BS42" s="11" t="n">
-        <v>-0.1421734974921662</v>
-      </c>
-      <c r="BT42" s="8" t="n">
-        <v>2246361</v>
-      </c>
-      <c r="BU42" s="9" t="n">
-        <v>32421.73</v>
-      </c>
-      <c r="BV42" s="10" t="n">
-        <v>0.0036</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="BD42" s="8" t="n"/>
+      <c r="BE42" s="9" t="n"/>
+      <c r="BF42" s="10" t="n"/>
+      <c r="BG42" s="11" t="n"/>
+      <c r="BH42" s="8" t="n"/>
+      <c r="BI42" s="9" t="n"/>
+      <c r="BJ42" s="10" t="n"/>
+      <c r="BK42" s="11" t="n"/>
+      <c r="BL42" s="8" t="n"/>
+      <c r="BM42" s="9" t="n"/>
+      <c r="BN42" s="10" t="n"/>
+      <c r="BO42" s="11" t="n"/>
+      <c r="BP42" s="8" t="n"/>
+      <c r="BQ42" s="9" t="n"/>
+      <c r="BR42" s="10" t="n"/>
+      <c r="BS42" s="11" t="n"/>
+      <c r="BT42" s="8" t="n"/>
+      <c r="BU42" s="9" t="n"/>
+      <c r="BV42" s="10" t="n"/>
       <c r="BW42" s="11" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Motilal Oswal Financial Services Limited</t>
+          <t>ITC Hotels Limited</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>INE338I01027</t>
+          <t>INE379A01028</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Leisure Services</t>
         </is>
       </c>
       <c r="D43" s="8" t="n"/>
@@ -8825,94 +8863,70 @@
       <c r="AV43" s="8" t="n"/>
       <c r="AW43" s="9" t="n"/>
       <c r="AX43" s="10" t="n"/>
-      <c r="AY43" s="11" t="n">
+      <c r="AY43" s="11" t="n"/>
+      <c r="AZ43" s="8" t="n"/>
+      <c r="BA43" s="9" t="n"/>
+      <c r="BB43" s="10" t="n"/>
+      <c r="BC43" s="11" t="n"/>
+      <c r="BD43" s="8" t="n"/>
+      <c r="BE43" s="9" t="n"/>
+      <c r="BF43" s="10" t="n"/>
+      <c r="BG43" s="11" t="n"/>
+      <c r="BH43" s="8" t="n"/>
+      <c r="BI43" s="9" t="n"/>
+      <c r="BJ43" s="10" t="n"/>
+      <c r="BK43" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="AZ43" s="8" t="n">
-        <v>591805</v>
-      </c>
-      <c r="BA43" s="9" t="n">
-        <v>5149</v>
-      </c>
-      <c r="BB43" s="10" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="BC43" s="11" t="n">
-        <v>-0.8902567225534253</v>
-      </c>
-      <c r="BD43" s="8" t="n">
-        <v>5392631</v>
-      </c>
-      <c r="BE43" s="9" t="n">
-        <v>43674.92</v>
-      </c>
-      <c r="BF43" s="10" t="n">
-        <v>0.0042</v>
-      </c>
-      <c r="BG43" s="11" t="n">
-        <v>-0.3719237093069153</v>
-      </c>
-      <c r="BH43" s="8" t="n">
-        <v>8585949</v>
-      </c>
-      <c r="BI43" s="9" t="n">
-        <v>56044.78</v>
-      </c>
-      <c r="BJ43" s="10" t="n">
-        <v>0.0057</v>
-      </c>
-      <c r="BK43" s="11" t="n">
-        <v>-0.2132577936597328</v>
-      </c>
       <c r="BL43" s="8" t="n">
-        <v>10913294</v>
+        <v>9899412</v>
       </c>
       <c r="BM43" s="9" t="n">
-        <v>67154.95</v>
+        <v>19552.33</v>
       </c>
       <c r="BN43" s="10" t="n">
-        <v>0.0072</v>
+        <v>0.0021</v>
       </c>
       <c r="BO43" s="11" t="n">
-        <v>-0.09462389658963724</v>
+        <v>0</v>
       </c>
       <c r="BP43" s="8" t="n">
-        <v>12053879</v>
+        <v>9899412</v>
       </c>
       <c r="BQ43" s="9" t="n">
-        <v>70937.08</v>
+        <v>16216.23</v>
       </c>
       <c r="BR43" s="10" t="n">
-        <v>0.0081</v>
+        <v>0.0018</v>
       </c>
       <c r="BS43" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BT43" s="8" t="n">
-        <v>12053879</v>
+        <v>9899412</v>
       </c>
       <c r="BU43" s="9" t="n">
-        <v>76801.28999999999</v>
+        <v>16131.09</v>
       </c>
       <c r="BV43" s="10" t="n">
-        <v>0.0086</v>
+        <v>0.0018</v>
       </c>
       <c r="BW43" s="11" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>ITC Hotels Limited</t>
+          <t>Multi Commodity Exchange of India Limited</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>INE379A01028</t>
+          <t>INE745G01043</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Leisure Services</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D44" s="8" t="n"/>
@@ -8934,11 +8948,21 @@
       <c r="T44" s="8" t="n"/>
       <c r="U44" s="9" t="n"/>
       <c r="V44" s="10" t="n"/>
-      <c r="W44" s="11" t="n"/>
-      <c r="X44" s="8" t="n"/>
-      <c r="Y44" s="9" t="n"/>
-      <c r="Z44" s="10" t="n"/>
-      <c r="AA44" s="11" t="n"/>
+      <c r="W44" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X44" s="8" t="n">
+        <v>795472</v>
+      </c>
+      <c r="Y44" s="9" t="n">
+        <v>20109.53</v>
+      </c>
+      <c r="Z44" s="10" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="AA44" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="AB44" s="8" t="n"/>
       <c r="AC44" s="9" t="n"/>
       <c r="AD44" s="10" t="n"/>
@@ -8974,42 +8998,18 @@
       <c r="BH44" s="8" t="n"/>
       <c r="BI44" s="9" t="n"/>
       <c r="BJ44" s="10" t="n"/>
-      <c r="BK44" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BL44" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BM44" s="9" t="n">
-        <v>19552.33</v>
-      </c>
-      <c r="BN44" s="10" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="BO44" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP44" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BQ44" s="9" t="n">
-        <v>16216.23</v>
-      </c>
-      <c r="BR44" s="10" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="BS44" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT44" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BU44" s="9" t="n">
-        <v>16131.09</v>
-      </c>
-      <c r="BV44" s="10" t="n">
-        <v>0.0018</v>
-      </c>
+      <c r="BK44" s="11" t="n"/>
+      <c r="BL44" s="8" t="n"/>
+      <c r="BM44" s="9" t="n"/>
+      <c r="BN44" s="10" t="n"/>
+      <c r="BO44" s="11" t="n"/>
+      <c r="BP44" s="8" t="n"/>
+      <c r="BQ44" s="9" t="n"/>
+      <c r="BR44" s="10" t="n"/>
+      <c r="BS44" s="11" t="n"/>
+      <c r="BT44" s="8" t="n"/>
+      <c r="BU44" s="9" t="n"/>
+      <c r="BV44" s="10" t="n"/>
       <c r="BW44" s="11" t="n"/>
     </row>
     <row r="45">

--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -7250,24 +7250,24 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Swaraj Engines Limited</t>
+          <t>Nesco Limited</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>INE277A01016</t>
+          <t>INE317F01035</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Industrial Products</t>
+          <t>Commercial Services &amp; Supplies</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>1890.58</v>
+        <v>1635.79</v>
       </c>
       <c r="F34" s="10" t="n">
         <v>0.0001</v>
@@ -7276,10 +7276,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>1809.43</v>
+        <v>1780.2</v>
       </c>
       <c r="J34" s="10" t="n">
         <v>0.0001</v>
@@ -7288,10 +7288,10 @@
         <v>0</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="M34" s="9" t="n">
-        <v>1871.38</v>
+        <v>1862.26</v>
       </c>
       <c r="N34" s="10" t="n">
         <v>0.0001</v>
@@ -7300,10 +7300,10 @@
         <v>0</v>
       </c>
       <c r="P34" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>1564.88</v>
+        <v>1538.11</v>
       </c>
       <c r="R34" s="10" t="n">
         <v>0.0001</v>
@@ -7312,10 +7312,10 @@
         <v>0</v>
       </c>
       <c r="T34" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="U34" s="9" t="n">
-        <v>1700.33</v>
+        <v>1704.36</v>
       </c>
       <c r="V34" s="10" t="n">
         <v>0.0001</v>
@@ -7324,10 +7324,10 @@
         <v>0</v>
       </c>
       <c r="X34" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="Y34" s="9" t="n">
-        <v>1637.61</v>
+        <v>1728.63</v>
       </c>
       <c r="Z34" s="10" t="n">
         <v>0.0001</v>
@@ -7336,10 +7336,10 @@
         <v>0</v>
       </c>
       <c r="AB34" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AC34" s="9" t="n">
-        <v>1691.91</v>
+        <v>1858.32</v>
       </c>
       <c r="AD34" s="10" t="n">
         <v>0.0001</v>
@@ -7348,22 +7348,22 @@
         <v>0</v>
       </c>
       <c r="AF34" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AG34" s="9" t="n">
-        <v>1764.08</v>
+        <v>1947.66</v>
       </c>
       <c r="AH34" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="AI34" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AJ34" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AK34" s="9" t="n">
-        <v>1892.15</v>
+        <v>2076.6</v>
       </c>
       <c r="AL34" s="10" t="n">
         <v>0.0002</v>
@@ -7372,10 +7372,10 @@
         <v>0</v>
       </c>
       <c r="AN34" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AO34" s="9" t="n">
-        <v>1955.38</v>
+        <v>1987.1</v>
       </c>
       <c r="AP34" s="10" t="n">
         <v>0.0002</v>
@@ -7384,10 +7384,10 @@
         <v>0</v>
       </c>
       <c r="AR34" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AS34" s="9" t="n">
-        <v>1897.21</v>
+        <v>2130.6</v>
       </c>
       <c r="AT34" s="10" t="n">
         <v>0.0002</v>
@@ -7396,10 +7396,10 @@
         <v>0</v>
       </c>
       <c r="AV34" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AW34" s="9" t="n">
-        <v>1983.66</v>
+        <v>2091.16</v>
       </c>
       <c r="AX34" s="10" t="n">
         <v>0.0002</v>
@@ -7408,97 +7408,67 @@
         <v>0</v>
       </c>
       <c r="AZ34" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="BA34" s="9" t="n">
-        <v>1867.41</v>
+        <v>1766.62</v>
       </c>
       <c r="BB34" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="BC34" s="11" t="n">
-        <v>0</v>
+        <v>0.6954140540298874</v>
       </c>
       <c r="BD34" s="8" t="n">
-        <v>47293</v>
+        <v>89469</v>
       </c>
       <c r="BE34" s="9" t="n">
-        <v>1857.76</v>
+        <v>828.48</v>
       </c>
       <c r="BF34" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="BG34" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH34" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="BI34" s="9" t="n">
-        <v>1925.39</v>
-      </c>
-      <c r="BJ34" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="BK34" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL34" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="BM34" s="9" t="n">
-        <v>1844.17</v>
-      </c>
-      <c r="BN34" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="BO34" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP34" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="BQ34" s="9" t="n">
-        <v>1236.83</v>
-      </c>
-      <c r="BR34" s="10" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="BS34" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT34" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="BU34" s="9" t="n">
-        <v>1612.64</v>
-      </c>
-      <c r="BV34" s="10" t="n">
-        <v>0.0002</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="BH34" s="8" t="n"/>
+      <c r="BI34" s="9" t="n"/>
+      <c r="BJ34" s="10" t="n"/>
+      <c r="BK34" s="11" t="n"/>
+      <c r="BL34" s="8" t="n"/>
+      <c r="BM34" s="9" t="n"/>
+      <c r="BN34" s="10" t="n"/>
+      <c r="BO34" s="11" t="n"/>
+      <c r="BP34" s="8" t="n"/>
+      <c r="BQ34" s="9" t="n"/>
+      <c r="BR34" s="10" t="n"/>
+      <c r="BS34" s="11" t="n"/>
+      <c r="BT34" s="8" t="n"/>
+      <c r="BU34" s="9" t="n"/>
+      <c r="BV34" s="10" t="n"/>
       <c r="BW34" s="11" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>CIE Automotive India Limited</t>
+          <t>Swaraj Engines Limited</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>INE536H01010</t>
+          <t>INE277A01016</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Auto Components</t>
+          <t>Industrial Products</t>
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>464063</v>
+        <v>47293</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>2124.48</v>
+        <v>1890.58</v>
       </c>
       <c r="F35" s="10" t="n">
         <v>0.0001</v>
@@ -7507,10 +7477,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>464063</v>
+        <v>47293</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>2071.81</v>
+        <v>1809.43</v>
       </c>
       <c r="J35" s="10" t="n">
         <v>0.0001</v>
@@ -7519,123 +7489,217 @@
         <v>0</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>464063</v>
+        <v>47293</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>2198.5</v>
+        <v>1871.38</v>
       </c>
       <c r="N35" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="O35" s="11" t="n">
         <v>0</v>
       </c>
       <c r="P35" s="8" t="n">
-        <v>464063</v>
+        <v>47293</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>2065.08</v>
+        <v>1564.88</v>
       </c>
       <c r="R35" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="S35" s="11" t="n">
         <v>0</v>
       </c>
       <c r="T35" s="8" t="n">
-        <v>464063</v>
+        <v>47293</v>
       </c>
       <c r="U35" s="9" t="n">
-        <v>2188.75</v>
+        <v>1700.33</v>
       </c>
       <c r="V35" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="W35" s="11" t="n">
-        <v>0.004302331872531515</v>
+        <v>0</v>
       </c>
       <c r="X35" s="8" t="n">
-        <v>462075</v>
+        <v>47293</v>
       </c>
       <c r="Y35" s="9" t="n">
-        <v>1932.4</v>
+        <v>1637.61</v>
       </c>
       <c r="Z35" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="AA35" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB35" s="8" t="n"/>
-      <c r="AC35" s="9" t="n"/>
-      <c r="AD35" s="10" t="n"/>
-      <c r="AE35" s="11" t="n"/>
-      <c r="AF35" s="8" t="n"/>
-      <c r="AG35" s="9" t="n"/>
-      <c r="AH35" s="10" t="n"/>
-      <c r="AI35" s="11" t="n"/>
-      <c r="AJ35" s="8" t="n"/>
-      <c r="AK35" s="9" t="n"/>
-      <c r="AL35" s="10" t="n"/>
-      <c r="AM35" s="11" t="n"/>
-      <c r="AN35" s="8" t="n"/>
-      <c r="AO35" s="9" t="n"/>
-      <c r="AP35" s="10" t="n"/>
-      <c r="AQ35" s="11" t="n"/>
-      <c r="AR35" s="8" t="n"/>
-      <c r="AS35" s="9" t="n"/>
-      <c r="AT35" s="10" t="n"/>
-      <c r="AU35" s="11" t="n"/>
-      <c r="AV35" s="8" t="n"/>
-      <c r="AW35" s="9" t="n"/>
-      <c r="AX35" s="10" t="n"/>
-      <c r="AY35" s="11" t="n"/>
-      <c r="AZ35" s="8" t="n"/>
-      <c r="BA35" s="9" t="n"/>
-      <c r="BB35" s="10" t="n"/>
-      <c r="BC35" s="11" t="n"/>
-      <c r="BD35" s="8" t="n"/>
-      <c r="BE35" s="9" t="n"/>
-      <c r="BF35" s="10" t="n"/>
-      <c r="BG35" s="11" t="n"/>
-      <c r="BH35" s="8" t="n"/>
-      <c r="BI35" s="9" t="n"/>
-      <c r="BJ35" s="10" t="n"/>
-      <c r="BK35" s="11" t="n"/>
-      <c r="BL35" s="8" t="n"/>
-      <c r="BM35" s="9" t="n"/>
-      <c r="BN35" s="10" t="n"/>
-      <c r="BO35" s="11" t="n"/>
-      <c r="BP35" s="8" t="n"/>
-      <c r="BQ35" s="9" t="n"/>
-      <c r="BR35" s="10" t="n"/>
-      <c r="BS35" s="11" t="n"/>
-      <c r="BT35" s="8" t="n"/>
-      <c r="BU35" s="9" t="n"/>
-      <c r="BV35" s="10" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AB35" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="AC35" s="9" t="n">
+        <v>1691.91</v>
+      </c>
+      <c r="AD35" s="10" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AE35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="AG35" s="9" t="n">
+        <v>1764.08</v>
+      </c>
+      <c r="AH35" s="10" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AI35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="AK35" s="9" t="n">
+        <v>1892.15</v>
+      </c>
+      <c r="AL35" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AM35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="AO35" s="9" t="n">
+        <v>1955.38</v>
+      </c>
+      <c r="AP35" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AQ35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="AS35" s="9" t="n">
+        <v>1897.21</v>
+      </c>
+      <c r="AT35" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AU35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="AW35" s="9" t="n">
+        <v>1983.66</v>
+      </c>
+      <c r="AX35" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AY35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="BA35" s="9" t="n">
+        <v>1867.41</v>
+      </c>
+      <c r="BB35" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="BC35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD35" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="BE35" s="9" t="n">
+        <v>1857.76</v>
+      </c>
+      <c r="BF35" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="BG35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH35" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="BI35" s="9" t="n">
+        <v>1925.39</v>
+      </c>
+      <c r="BJ35" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="BK35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL35" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="BM35" s="9" t="n">
+        <v>1844.17</v>
+      </c>
+      <c r="BN35" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="BO35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP35" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="BQ35" s="9" t="n">
+        <v>1236.83</v>
+      </c>
+      <c r="BR35" s="10" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="BS35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT35" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="BU35" s="9" t="n">
+        <v>1612.64</v>
+      </c>
+      <c r="BV35" s="10" t="n">
+        <v>0.0002</v>
+      </c>
       <c r="BW35" s="11" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Nesco Limited</t>
+          <t>CIE Automotive India Limited</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>INE317F01035</t>
+          <t>INE536H01010</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Commercial Services &amp; Supplies</t>
+          <t>Auto Components</t>
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>151687</v>
+        <v>464063</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>1635.79</v>
+        <v>2124.48</v>
       </c>
       <c r="F36" s="10" t="n">
         <v>0.0001</v>
@@ -7644,10 +7708,10 @@
         <v>0</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>151687</v>
+        <v>464063</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>1780.2</v>
+        <v>2071.81</v>
       </c>
       <c r="J36" s="10" t="n">
         <v>0.0001</v>
@@ -7656,149 +7720,85 @@
         <v>0</v>
       </c>
       <c r="L36" s="8" t="n">
-        <v>151687</v>
+        <v>464063</v>
       </c>
       <c r="M36" s="9" t="n">
-        <v>1862.26</v>
+        <v>2198.5</v>
       </c>
       <c r="N36" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="O36" s="11" t="n">
         <v>0</v>
       </c>
       <c r="P36" s="8" t="n">
-        <v>151687</v>
+        <v>464063</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>1538.11</v>
+        <v>2065.08</v>
       </c>
       <c r="R36" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="S36" s="11" t="n">
         <v>0</v>
       </c>
       <c r="T36" s="8" t="n">
-        <v>151687</v>
+        <v>464063</v>
       </c>
       <c r="U36" s="9" t="n">
-        <v>1704.36</v>
+        <v>2188.75</v>
       </c>
       <c r="V36" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="W36" s="11" t="n">
-        <v>0</v>
+        <v>0.004302331872531515</v>
       </c>
       <c r="X36" s="8" t="n">
-        <v>151687</v>
+        <v>462075</v>
       </c>
       <c r="Y36" s="9" t="n">
-        <v>1728.63</v>
+        <v>1932.4</v>
       </c>
       <c r="Z36" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="AA36" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AC36" s="9" t="n">
-        <v>1858.32</v>
-      </c>
-      <c r="AD36" s="10" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="AE36" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AG36" s="9" t="n">
-        <v>1947.66</v>
-      </c>
-      <c r="AH36" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AI36" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ36" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AK36" s="9" t="n">
-        <v>2076.6</v>
-      </c>
-      <c r="AL36" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AM36" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN36" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AO36" s="9" t="n">
-        <v>1987.1</v>
-      </c>
-      <c r="AP36" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AQ36" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR36" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AS36" s="9" t="n">
-        <v>2130.6</v>
-      </c>
-      <c r="AT36" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AU36" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV36" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AW36" s="9" t="n">
-        <v>2091.16</v>
-      </c>
-      <c r="AX36" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AY36" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ36" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="BA36" s="9" t="n">
-        <v>1766.62</v>
-      </c>
-      <c r="BB36" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="BC36" s="11" t="n">
-        <v>0.6954140540298874</v>
-      </c>
-      <c r="BD36" s="8" t="n">
-        <v>89469</v>
-      </c>
-      <c r="BE36" s="9" t="n">
-        <v>828.48</v>
-      </c>
-      <c r="BF36" s="10" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="BG36" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="AB36" s="8" t="n"/>
+      <c r="AC36" s="9" t="n"/>
+      <c r="AD36" s="10" t="n"/>
+      <c r="AE36" s="11" t="n"/>
+      <c r="AF36" s="8" t="n"/>
+      <c r="AG36" s="9" t="n"/>
+      <c r="AH36" s="10" t="n"/>
+      <c r="AI36" s="11" t="n"/>
+      <c r="AJ36" s="8" t="n"/>
+      <c r="AK36" s="9" t="n"/>
+      <c r="AL36" s="10" t="n"/>
+      <c r="AM36" s="11" t="n"/>
+      <c r="AN36" s="8" t="n"/>
+      <c r="AO36" s="9" t="n"/>
+      <c r="AP36" s="10" t="n"/>
+      <c r="AQ36" s="11" t="n"/>
+      <c r="AR36" s="8" t="n"/>
+      <c r="AS36" s="9" t="n"/>
+      <c r="AT36" s="10" t="n"/>
+      <c r="AU36" s="11" t="n"/>
+      <c r="AV36" s="8" t="n"/>
+      <c r="AW36" s="9" t="n"/>
+      <c r="AX36" s="10" t="n"/>
+      <c r="AY36" s="11" t="n"/>
+      <c r="AZ36" s="8" t="n"/>
+      <c r="BA36" s="9" t="n"/>
+      <c r="BB36" s="10" t="n"/>
+      <c r="BC36" s="11" t="n"/>
+      <c r="BD36" s="8" t="n"/>
+      <c r="BE36" s="9" t="n"/>
+      <c r="BF36" s="10" t="n"/>
+      <c r="BG36" s="11" t="n"/>
       <c r="BH36" s="8" t="n"/>
       <c r="BI36" s="9" t="n"/>
       <c r="BJ36" s="10" t="n"/>
@@ -8213,12 +8213,12 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Motilal Oswal Financial Services Limited</t>
+          <t>Multi Commodity Exchange of India Limited</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>INE338I01027</t>
+          <t>INE745G01035</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
@@ -8249,101 +8249,149 @@
       <c r="X39" s="8" t="n"/>
       <c r="Y39" s="9" t="n"/>
       <c r="Z39" s="10" t="n"/>
-      <c r="AA39" s="11" t="n"/>
-      <c r="AB39" s="8" t="n"/>
-      <c r="AC39" s="9" t="n"/>
-      <c r="AD39" s="10" t="n"/>
-      <c r="AE39" s="11" t="n"/>
-      <c r="AF39" s="8" t="n"/>
-      <c r="AG39" s="9" t="n"/>
-      <c r="AH39" s="10" t="n"/>
-      <c r="AI39" s="11" t="n"/>
-      <c r="AJ39" s="8" t="n"/>
-      <c r="AK39" s="9" t="n"/>
-      <c r="AL39" s="10" t="n"/>
-      <c r="AM39" s="11" t="n"/>
-      <c r="AN39" s="8" t="n"/>
-      <c r="AO39" s="9" t="n"/>
-      <c r="AP39" s="10" t="n"/>
-      <c r="AQ39" s="11" t="n"/>
-      <c r="AR39" s="8" t="n"/>
-      <c r="AS39" s="9" t="n"/>
-      <c r="AT39" s="10" t="n"/>
-      <c r="AU39" s="11" t="n"/>
-      <c r="AV39" s="8" t="n"/>
-      <c r="AW39" s="9" t="n"/>
-      <c r="AX39" s="10" t="n"/>
+      <c r="AA39" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB39" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AC39" s="9" t="n">
+        <v>88833.99000000001</v>
+      </c>
+      <c r="AD39" s="10" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="AE39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AG39" s="9" t="n">
+        <v>80358.22</v>
+      </c>
+      <c r="AH39" s="10" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="AI39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AK39" s="9" t="n">
+        <v>73737.16</v>
+      </c>
+      <c r="AL39" s="10" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="AM39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AO39" s="9" t="n">
+        <v>62190.17</v>
+      </c>
+      <c r="AP39" s="10" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="AQ39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AS39" s="9" t="n">
+        <v>58951.43</v>
+      </c>
+      <c r="AT39" s="10" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="AU39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AW39" s="9" t="n">
+        <v>61368.52</v>
+      </c>
+      <c r="AX39" s="10" t="n">
+        <v>0.0054</v>
+      </c>
       <c r="AY39" s="11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AZ39" s="8" t="n">
-        <v>591805</v>
+        <v>797719</v>
       </c>
       <c r="BA39" s="9" t="n">
-        <v>5149</v>
+        <v>71347.99000000001</v>
       </c>
       <c r="BB39" s="10" t="n">
-        <v>0.0005</v>
+        <v>0.0065</v>
       </c>
       <c r="BC39" s="11" t="n">
-        <v>-0.8902567225534253</v>
+        <v>0</v>
       </c>
       <c r="BD39" s="8" t="n">
-        <v>5392631</v>
+        <v>797719</v>
       </c>
       <c r="BE39" s="9" t="n">
-        <v>43674.92</v>
+        <v>52665.41</v>
       </c>
       <c r="BF39" s="10" t="n">
-        <v>0.0042</v>
+        <v>0.0051</v>
       </c>
       <c r="BG39" s="11" t="n">
-        <v>-0.3719237093069153</v>
+        <v>0</v>
       </c>
       <c r="BH39" s="8" t="n">
-        <v>8585949</v>
+        <v>797719</v>
       </c>
       <c r="BI39" s="9" t="n">
-        <v>56044.78</v>
+        <v>48884.22</v>
       </c>
       <c r="BJ39" s="10" t="n">
-        <v>0.0057</v>
+        <v>0.005</v>
       </c>
       <c r="BK39" s="11" t="n">
-        <v>-0.2132577936597328</v>
+        <v>0</v>
       </c>
       <c r="BL39" s="8" t="n">
-        <v>10913294</v>
+        <v>797719</v>
       </c>
       <c r="BM39" s="9" t="n">
-        <v>67154.95</v>
+        <v>42372.84</v>
       </c>
       <c r="BN39" s="10" t="n">
-        <v>0.0072</v>
+        <v>0.0045</v>
       </c>
       <c r="BO39" s="11" t="n">
-        <v>-0.09462389658963724</v>
+        <v>0</v>
       </c>
       <c r="BP39" s="8" t="n">
-        <v>12053879</v>
+        <v>797719</v>
       </c>
       <c r="BQ39" s="9" t="n">
-        <v>70937.08</v>
+        <v>39819.34</v>
       </c>
       <c r="BR39" s="10" t="n">
-        <v>0.0081</v>
+        <v>0.0045</v>
       </c>
       <c r="BS39" s="11" t="n">
-        <v>0</v>
+        <v>-0.09569612848812428</v>
       </c>
       <c r="BT39" s="8" t="n">
-        <v>12053879</v>
+        <v>882136</v>
       </c>
       <c r="BU39" s="9" t="n">
-        <v>76801.28999999999</v>
+        <v>50572.42</v>
       </c>
       <c r="BV39" s="10" t="n">
-        <v>0.0086</v>
+        <v>0.0056</v>
       </c>
       <c r="BW39" s="11" t="n"/>
     </row>
@@ -8355,7 +8403,7 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>INE745G01035</t>
+          <t>INE745G01043</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
@@ -8382,170 +8430,84 @@
       <c r="T40" s="8" t="n"/>
       <c r="U40" s="9" t="n"/>
       <c r="V40" s="10" t="n"/>
-      <c r="W40" s="11" t="n"/>
-      <c r="X40" s="8" t="n"/>
-      <c r="Y40" s="9" t="n"/>
-      <c r="Z40" s="10" t="n"/>
+      <c r="W40" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X40" s="8" t="n">
+        <v>795472</v>
+      </c>
+      <c r="Y40" s="9" t="n">
+        <v>20109.53</v>
+      </c>
+      <c r="Z40" s="10" t="n">
+        <v>0.0015</v>
+      </c>
       <c r="AA40" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AB40" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="AC40" s="9" t="n">
-        <v>88833.99000000001</v>
-      </c>
-      <c r="AD40" s="10" t="n">
-        <v>0.0067</v>
-      </c>
-      <c r="AE40" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF40" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="AG40" s="9" t="n">
-        <v>80358.22</v>
-      </c>
-      <c r="AH40" s="10" t="n">
-        <v>0.0062</v>
-      </c>
-      <c r="AI40" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ40" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="AK40" s="9" t="n">
-        <v>73737.16</v>
-      </c>
-      <c r="AL40" s="10" t="n">
-        <v>0.0059</v>
-      </c>
-      <c r="AM40" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN40" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="AO40" s="9" t="n">
-        <v>62190.17</v>
-      </c>
-      <c r="AP40" s="10" t="n">
-        <v>0.0052</v>
-      </c>
-      <c r="AQ40" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR40" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="AS40" s="9" t="n">
-        <v>58951.43</v>
-      </c>
-      <c r="AT40" s="10" t="n">
-        <v>0.0051</v>
-      </c>
-      <c r="AU40" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV40" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="AW40" s="9" t="n">
-        <v>61368.52</v>
-      </c>
-      <c r="AX40" s="10" t="n">
-        <v>0.0054</v>
-      </c>
-      <c r="AY40" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ40" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="BA40" s="9" t="n">
-        <v>71347.99000000001</v>
-      </c>
-      <c r="BB40" s="10" t="n">
-        <v>0.0065</v>
-      </c>
-      <c r="BC40" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD40" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="BE40" s="9" t="n">
-        <v>52665.41</v>
-      </c>
-      <c r="BF40" s="10" t="n">
-        <v>0.0051</v>
-      </c>
-      <c r="BG40" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH40" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="BI40" s="9" t="n">
-        <v>48884.22</v>
-      </c>
-      <c r="BJ40" s="10" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="BK40" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL40" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="BM40" s="9" t="n">
-        <v>42372.84</v>
-      </c>
-      <c r="BN40" s="10" t="n">
-        <v>0.0045</v>
-      </c>
-      <c r="BO40" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP40" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="BQ40" s="9" t="n">
-        <v>39819.34</v>
-      </c>
-      <c r="BR40" s="10" t="n">
-        <v>0.0045</v>
-      </c>
-      <c r="BS40" s="11" t="n">
-        <v>-0.09569612848812428</v>
-      </c>
-      <c r="BT40" s="8" t="n">
-        <v>882136</v>
-      </c>
-      <c r="BU40" s="9" t="n">
-        <v>50572.42</v>
-      </c>
-      <c r="BV40" s="10" t="n">
-        <v>0.0056</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AB40" s="8" t="n"/>
+      <c r="AC40" s="9" t="n"/>
+      <c r="AD40" s="10" t="n"/>
+      <c r="AE40" s="11" t="n"/>
+      <c r="AF40" s="8" t="n"/>
+      <c r="AG40" s="9" t="n"/>
+      <c r="AH40" s="10" t="n"/>
+      <c r="AI40" s="11" t="n"/>
+      <c r="AJ40" s="8" t="n"/>
+      <c r="AK40" s="9" t="n"/>
+      <c r="AL40" s="10" t="n"/>
+      <c r="AM40" s="11" t="n"/>
+      <c r="AN40" s="8" t="n"/>
+      <c r="AO40" s="9" t="n"/>
+      <c r="AP40" s="10" t="n"/>
+      <c r="AQ40" s="11" t="n"/>
+      <c r="AR40" s="8" t="n"/>
+      <c r="AS40" s="9" t="n"/>
+      <c r="AT40" s="10" t="n"/>
+      <c r="AU40" s="11" t="n"/>
+      <c r="AV40" s="8" t="n"/>
+      <c r="AW40" s="9" t="n"/>
+      <c r="AX40" s="10" t="n"/>
+      <c r="AY40" s="11" t="n"/>
+      <c r="AZ40" s="8" t="n"/>
+      <c r="BA40" s="9" t="n"/>
+      <c r="BB40" s="10" t="n"/>
+      <c r="BC40" s="11" t="n"/>
+      <c r="BD40" s="8" t="n"/>
+      <c r="BE40" s="9" t="n"/>
+      <c r="BF40" s="10" t="n"/>
+      <c r="BG40" s="11" t="n"/>
+      <c r="BH40" s="8" t="n"/>
+      <c r="BI40" s="9" t="n"/>
+      <c r="BJ40" s="10" t="n"/>
+      <c r="BK40" s="11" t="n"/>
+      <c r="BL40" s="8" t="n"/>
+      <c r="BM40" s="9" t="n"/>
+      <c r="BN40" s="10" t="n"/>
+      <c r="BO40" s="11" t="n"/>
+      <c r="BP40" s="8" t="n"/>
+      <c r="BQ40" s="9" t="n"/>
+      <c r="BR40" s="10" t="n"/>
+      <c r="BS40" s="11" t="n"/>
+      <c r="BT40" s="8" t="n"/>
+      <c r="BU40" s="9" t="n"/>
+      <c r="BV40" s="10" t="n"/>
       <c r="BW40" s="11" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>IPCA Laboratories Limited</t>
+          <t>Zydus Wellness Limited</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>INE571A01038</t>
+          <t>INE768C01010</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Pharmaceuticals &amp; Biotechnology</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D41" s="8" t="n"/>
@@ -8591,114 +8553,76 @@
         <v>-1</v>
       </c>
       <c r="AR41" s="8" t="n">
-        <v>218075</v>
+        <v>4400000</v>
       </c>
       <c r="AS41" s="9" t="n">
-        <v>3019.03</v>
+        <v>88822.8</v>
       </c>
       <c r="AT41" s="10" t="n">
-        <v>0.0003</v>
+        <v>0.0077</v>
       </c>
       <c r="AU41" s="11" t="n">
-        <v>-0.6148554615199853</v>
+        <v>0</v>
       </c>
       <c r="AV41" s="8" t="n">
-        <v>566216</v>
+        <v>4400000</v>
       </c>
       <c r="AW41" s="9" t="n">
-        <v>8345.459999999999</v>
+        <v>89280.39999999999</v>
       </c>
       <c r="AX41" s="10" t="n">
-        <v>0.0007</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="AY41" s="11" t="n">
-        <v>-0.5682871579351869</v>
+        <v>0</v>
       </c>
       <c r="AZ41" s="8" t="n">
-        <v>1311557</v>
+        <v>4400000</v>
       </c>
       <c r="BA41" s="9" t="n">
-        <v>18228.02</v>
+        <v>89020.8</v>
       </c>
       <c r="BB41" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.0081</v>
       </c>
       <c r="BC41" s="11" t="n">
-        <v>-0.2008037316547793</v>
-      </c>
-      <c r="BD41" s="8" t="n">
-        <v>1641095</v>
-      </c>
-      <c r="BE41" s="9" t="n">
-        <v>23382.32</v>
-      </c>
-      <c r="BF41" s="10" t="n">
-        <v>0.0023</v>
-      </c>
-      <c r="BG41" s="11" t="n">
-        <v>-0.1163687388172734</v>
-      </c>
-      <c r="BH41" s="8" t="n">
-        <v>1857217</v>
-      </c>
-      <c r="BI41" s="9" t="n">
-        <v>26023.32</v>
-      </c>
-      <c r="BJ41" s="10" t="n">
-        <v>0.0026</v>
-      </c>
-      <c r="BK41" s="11" t="n">
-        <v>-0.03620728307597141</v>
-      </c>
-      <c r="BL41" s="8" t="n">
-        <v>1926988</v>
-      </c>
-      <c r="BM41" s="9" t="n">
-        <v>28941.43</v>
-      </c>
-      <c r="BN41" s="10" t="n">
-        <v>0.0031</v>
-      </c>
-      <c r="BO41" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP41" s="8" t="n">
-        <v>1926988</v>
-      </c>
-      <c r="BQ41" s="9" t="n">
-        <v>26117.43</v>
-      </c>
-      <c r="BR41" s="10" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="BS41" s="11" t="n">
-        <v>-0.1421734974921662</v>
-      </c>
-      <c r="BT41" s="8" t="n">
-        <v>2246361</v>
-      </c>
-      <c r="BU41" s="9" t="n">
-        <v>32421.73</v>
-      </c>
-      <c r="BV41" s="10" t="n">
-        <v>0.0036</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="BD41" s="8" t="n"/>
+      <c r="BE41" s="9" t="n"/>
+      <c r="BF41" s="10" t="n"/>
+      <c r="BG41" s="11" t="n"/>
+      <c r="BH41" s="8" t="n"/>
+      <c r="BI41" s="9" t="n"/>
+      <c r="BJ41" s="10" t="n"/>
+      <c r="BK41" s="11" t="n"/>
+      <c r="BL41" s="8" t="n"/>
+      <c r="BM41" s="9" t="n"/>
+      <c r="BN41" s="10" t="n"/>
+      <c r="BO41" s="11" t="n"/>
+      <c r="BP41" s="8" t="n"/>
+      <c r="BQ41" s="9" t="n"/>
+      <c r="BR41" s="10" t="n"/>
+      <c r="BS41" s="11" t="n"/>
+      <c r="BT41" s="8" t="n"/>
+      <c r="BU41" s="9" t="n"/>
+      <c r="BV41" s="10" t="n"/>
       <c r="BW41" s="11" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited</t>
+          <t>IPCA Laboratories Limited</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>INE768C01010</t>
+          <t>INE571A01038</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Pharmaceuticals &amp; Biotechnology</t>
         </is>
       </c>
       <c r="D42" s="8" t="n"/>
@@ -8744,76 +8668,114 @@
         <v>-1</v>
       </c>
       <c r="AR42" s="8" t="n">
-        <v>4400000</v>
+        <v>218075</v>
       </c>
       <c r="AS42" s="9" t="n">
-        <v>88822.8</v>
+        <v>3019.03</v>
       </c>
       <c r="AT42" s="10" t="n">
-        <v>0.0077</v>
+        <v>0.0003</v>
       </c>
       <c r="AU42" s="11" t="n">
-        <v>0</v>
+        <v>-0.6148554615199853</v>
       </c>
       <c r="AV42" s="8" t="n">
-        <v>4400000</v>
+        <v>566216</v>
       </c>
       <c r="AW42" s="9" t="n">
-        <v>89280.39999999999</v>
+        <v>8345.459999999999</v>
       </c>
       <c r="AX42" s="10" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0007</v>
       </c>
       <c r="AY42" s="11" t="n">
-        <v>0</v>
+        <v>-0.5682871579351869</v>
       </c>
       <c r="AZ42" s="8" t="n">
-        <v>4400000</v>
+        <v>1311557</v>
       </c>
       <c r="BA42" s="9" t="n">
-        <v>89020.8</v>
+        <v>18228.02</v>
       </c>
       <c r="BB42" s="10" t="n">
-        <v>0.0081</v>
+        <v>0.0017</v>
       </c>
       <c r="BC42" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD42" s="8" t="n"/>
-      <c r="BE42" s="9" t="n"/>
-      <c r="BF42" s="10" t="n"/>
-      <c r="BG42" s="11" t="n"/>
-      <c r="BH42" s="8" t="n"/>
-      <c r="BI42" s="9" t="n"/>
-      <c r="BJ42" s="10" t="n"/>
-      <c r="BK42" s="11" t="n"/>
-      <c r="BL42" s="8" t="n"/>
-      <c r="BM42" s="9" t="n"/>
-      <c r="BN42" s="10" t="n"/>
-      <c r="BO42" s="11" t="n"/>
-      <c r="BP42" s="8" t="n"/>
-      <c r="BQ42" s="9" t="n"/>
-      <c r="BR42" s="10" t="n"/>
-      <c r="BS42" s="11" t="n"/>
-      <c r="BT42" s="8" t="n"/>
-      <c r="BU42" s="9" t="n"/>
-      <c r="BV42" s="10" t="n"/>
+        <v>-0.2008037316547793</v>
+      </c>
+      <c r="BD42" s="8" t="n">
+        <v>1641095</v>
+      </c>
+      <c r="BE42" s="9" t="n">
+        <v>23382.32</v>
+      </c>
+      <c r="BF42" s="10" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="BG42" s="11" t="n">
+        <v>-0.1163687388172734</v>
+      </c>
+      <c r="BH42" s="8" t="n">
+        <v>1857217</v>
+      </c>
+      <c r="BI42" s="9" t="n">
+        <v>26023.32</v>
+      </c>
+      <c r="BJ42" s="10" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="BK42" s="11" t="n">
+        <v>-0.03620728307597141</v>
+      </c>
+      <c r="BL42" s="8" t="n">
+        <v>1926988</v>
+      </c>
+      <c r="BM42" s="9" t="n">
+        <v>28941.43</v>
+      </c>
+      <c r="BN42" s="10" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="BO42" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP42" s="8" t="n">
+        <v>1926988</v>
+      </c>
+      <c r="BQ42" s="9" t="n">
+        <v>26117.43</v>
+      </c>
+      <c r="BR42" s="10" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="BS42" s="11" t="n">
+        <v>-0.1421734974921662</v>
+      </c>
+      <c r="BT42" s="8" t="n">
+        <v>2246361</v>
+      </c>
+      <c r="BU42" s="9" t="n">
+        <v>32421.73</v>
+      </c>
+      <c r="BV42" s="10" t="n">
+        <v>0.0036</v>
+      </c>
       <c r="BW42" s="11" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>ITC Hotels Limited</t>
+          <t>Motilal Oswal Financial Services Limited</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>INE379A01028</t>
+          <t>INE338I01027</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Leisure Services</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D43" s="8" t="n"/>
@@ -8863,70 +8825,94 @@
       <c r="AV43" s="8" t="n"/>
       <c r="AW43" s="9" t="n"/>
       <c r="AX43" s="10" t="n"/>
-      <c r="AY43" s="11" t="n"/>
-      <c r="AZ43" s="8" t="n"/>
-      <c r="BA43" s="9" t="n"/>
-      <c r="BB43" s="10" t="n"/>
-      <c r="BC43" s="11" t="n"/>
-      <c r="BD43" s="8" t="n"/>
-      <c r="BE43" s="9" t="n"/>
-      <c r="BF43" s="10" t="n"/>
-      <c r="BG43" s="11" t="n"/>
-      <c r="BH43" s="8" t="n"/>
-      <c r="BI43" s="9" t="n"/>
-      <c r="BJ43" s="10" t="n"/>
+      <c r="AY43" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AZ43" s="8" t="n">
+        <v>591805</v>
+      </c>
+      <c r="BA43" s="9" t="n">
+        <v>5149</v>
+      </c>
+      <c r="BB43" s="10" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="BC43" s="11" t="n">
+        <v>-0.8902567225534253</v>
+      </c>
+      <c r="BD43" s="8" t="n">
+        <v>5392631</v>
+      </c>
+      <c r="BE43" s="9" t="n">
+        <v>43674.92</v>
+      </c>
+      <c r="BF43" s="10" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="BG43" s="11" t="n">
+        <v>-0.3719237093069153</v>
+      </c>
+      <c r="BH43" s="8" t="n">
+        <v>8585949</v>
+      </c>
+      <c r="BI43" s="9" t="n">
+        <v>56044.78</v>
+      </c>
+      <c r="BJ43" s="10" t="n">
+        <v>0.0057</v>
+      </c>
       <c r="BK43" s="11" t="n">
-        <v>-1</v>
+        <v>-0.2132577936597328</v>
       </c>
       <c r="BL43" s="8" t="n">
-        <v>9899412</v>
+        <v>10913294</v>
       </c>
       <c r="BM43" s="9" t="n">
-        <v>19552.33</v>
+        <v>67154.95</v>
       </c>
       <c r="BN43" s="10" t="n">
-        <v>0.0021</v>
+        <v>0.0072</v>
       </c>
       <c r="BO43" s="11" t="n">
-        <v>0</v>
+        <v>-0.09462389658963724</v>
       </c>
       <c r="BP43" s="8" t="n">
-        <v>9899412</v>
+        <v>12053879</v>
       </c>
       <c r="BQ43" s="9" t="n">
-        <v>16216.23</v>
+        <v>70937.08</v>
       </c>
       <c r="BR43" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.0081</v>
       </c>
       <c r="BS43" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BT43" s="8" t="n">
-        <v>9899412</v>
+        <v>12053879</v>
       </c>
       <c r="BU43" s="9" t="n">
-        <v>16131.09</v>
+        <v>76801.28999999999</v>
       </c>
       <c r="BV43" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.0086</v>
       </c>
       <c r="BW43" s="11" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Multi Commodity Exchange of India Limited</t>
+          <t>ITC Hotels Limited</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>INE745G01043</t>
+          <t>INE379A01028</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Leisure Services</t>
         </is>
       </c>
       <c r="D44" s="8" t="n"/>
@@ -8948,21 +8934,11 @@
       <c r="T44" s="8" t="n"/>
       <c r="U44" s="9" t="n"/>
       <c r="V44" s="10" t="n"/>
-      <c r="W44" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X44" s="8" t="n">
-        <v>795472</v>
-      </c>
-      <c r="Y44" s="9" t="n">
-        <v>20109.53</v>
-      </c>
-      <c r="Z44" s="10" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="AA44" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="W44" s="11" t="n"/>
+      <c r="X44" s="8" t="n"/>
+      <c r="Y44" s="9" t="n"/>
+      <c r="Z44" s="10" t="n"/>
+      <c r="AA44" s="11" t="n"/>
       <c r="AB44" s="8" t="n"/>
       <c r="AC44" s="9" t="n"/>
       <c r="AD44" s="10" t="n"/>
@@ -8998,18 +8974,42 @@
       <c r="BH44" s="8" t="n"/>
       <c r="BI44" s="9" t="n"/>
       <c r="BJ44" s="10" t="n"/>
-      <c r="BK44" s="11" t="n"/>
-      <c r="BL44" s="8" t="n"/>
-      <c r="BM44" s="9" t="n"/>
-      <c r="BN44" s="10" t="n"/>
-      <c r="BO44" s="11" t="n"/>
-      <c r="BP44" s="8" t="n"/>
-      <c r="BQ44" s="9" t="n"/>
-      <c r="BR44" s="10" t="n"/>
-      <c r="BS44" s="11" t="n"/>
-      <c r="BT44" s="8" t="n"/>
-      <c r="BU44" s="9" t="n"/>
-      <c r="BV44" s="10" t="n"/>
+      <c r="BK44" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL44" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BM44" s="9" t="n">
+        <v>19552.33</v>
+      </c>
+      <c r="BN44" s="10" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="BO44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP44" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BQ44" s="9" t="n">
+        <v>16216.23</v>
+      </c>
+      <c r="BR44" s="10" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="BS44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT44" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BU44" s="9" t="n">
+        <v>16131.09</v>
+      </c>
+      <c r="BV44" s="10" t="n">
+        <v>0.0018</v>
+      </c>
       <c r="BW44" s="11" t="n"/>
     </row>
     <row r="45">

--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -5444,7 +5444,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Fertilizers &amp; Agrochemicals</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -8688,17 +8688,17 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited</t>
+          <t>ITC Hotels Limited</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>INE768C01010</t>
+          <t>INE379A01028</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Leisure Services</t>
         </is>
       </c>
       <c r="D42" s="8" t="n"/>
@@ -8740,45 +8740,19 @@
       <c r="AN42" s="8" t="n"/>
       <c r="AO42" s="9" t="n"/>
       <c r="AP42" s="10" t="n"/>
-      <c r="AQ42" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AR42" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="AS42" s="9" t="n">
-        <v>88822.8</v>
-      </c>
-      <c r="AT42" s="10" t="n">
-        <v>0.0077</v>
-      </c>
-      <c r="AU42" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV42" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="AW42" s="9" t="n">
-        <v>89280.39999999999</v>
-      </c>
-      <c r="AX42" s="10" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-      <c r="AY42" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ42" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="BA42" s="9" t="n">
-        <v>89020.8</v>
-      </c>
-      <c r="BB42" s="10" t="n">
-        <v>0.0081</v>
-      </c>
-      <c r="BC42" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="AQ42" s="11" t="n"/>
+      <c r="AR42" s="8" t="n"/>
+      <c r="AS42" s="9" t="n"/>
+      <c r="AT42" s="10" t="n"/>
+      <c r="AU42" s="11" t="n"/>
+      <c r="AV42" s="8" t="n"/>
+      <c r="AW42" s="9" t="n"/>
+      <c r="AX42" s="10" t="n"/>
+      <c r="AY42" s="11" t="n"/>
+      <c r="AZ42" s="8" t="n"/>
+      <c r="BA42" s="9" t="n"/>
+      <c r="BB42" s="10" t="n"/>
+      <c r="BC42" s="11" t="n"/>
       <c r="BD42" s="8" t="n"/>
       <c r="BE42" s="9" t="n"/>
       <c r="BF42" s="10" t="n"/>
@@ -8786,34 +8760,58 @@
       <c r="BH42" s="8" t="n"/>
       <c r="BI42" s="9" t="n"/>
       <c r="BJ42" s="10" t="n"/>
-      <c r="BK42" s="11" t="n"/>
-      <c r="BL42" s="8" t="n"/>
-      <c r="BM42" s="9" t="n"/>
-      <c r="BN42" s="10" t="n"/>
-      <c r="BO42" s="11" t="n"/>
-      <c r="BP42" s="8" t="n"/>
-      <c r="BQ42" s="9" t="n"/>
-      <c r="BR42" s="10" t="n"/>
-      <c r="BS42" s="11" t="n"/>
-      <c r="BT42" s="8" t="n"/>
-      <c r="BU42" s="9" t="n"/>
-      <c r="BV42" s="10" t="n"/>
+      <c r="BK42" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL42" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BM42" s="9" t="n">
+        <v>19552.33</v>
+      </c>
+      <c r="BN42" s="10" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="BO42" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP42" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BQ42" s="9" t="n">
+        <v>16216.23</v>
+      </c>
+      <c r="BR42" s="10" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="BS42" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT42" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BU42" s="9" t="n">
+        <v>16131.09</v>
+      </c>
+      <c r="BV42" s="10" t="n">
+        <v>0.0018</v>
+      </c>
       <c r="BW42" s="11" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>ITC Hotels Limited</t>
+          <t>Multi Commodity Exchange of India Limited</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>INE379A01028</t>
+          <t>INE745G01043</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Leisure Services</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D43" s="8" t="n"/>
@@ -8835,11 +8833,21 @@
       <c r="T43" s="8" t="n"/>
       <c r="U43" s="9" t="n"/>
       <c r="V43" s="10" t="n"/>
-      <c r="W43" s="11" t="n"/>
-      <c r="X43" s="8" t="n"/>
-      <c r="Y43" s="9" t="n"/>
-      <c r="Z43" s="10" t="n"/>
-      <c r="AA43" s="11" t="n"/>
+      <c r="W43" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X43" s="8" t="n">
+        <v>795472</v>
+      </c>
+      <c r="Y43" s="9" t="n">
+        <v>20109.53</v>
+      </c>
+      <c r="Z43" s="10" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="AA43" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="AB43" s="8" t="n"/>
       <c r="AC43" s="9" t="n"/>
       <c r="AD43" s="10" t="n"/>
@@ -8875,58 +8883,34 @@
       <c r="BH43" s="8" t="n"/>
       <c r="BI43" s="9" t="n"/>
       <c r="BJ43" s="10" t="n"/>
-      <c r="BK43" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BL43" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BM43" s="9" t="n">
-        <v>19552.33</v>
-      </c>
-      <c r="BN43" s="10" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="BO43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP43" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BQ43" s="9" t="n">
-        <v>16216.23</v>
-      </c>
-      <c r="BR43" s="10" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="BS43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT43" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BU43" s="9" t="n">
-        <v>16131.09</v>
-      </c>
-      <c r="BV43" s="10" t="n">
-        <v>0.0018</v>
-      </c>
+      <c r="BK43" s="11" t="n"/>
+      <c r="BL43" s="8" t="n"/>
+      <c r="BM43" s="9" t="n"/>
+      <c r="BN43" s="10" t="n"/>
+      <c r="BO43" s="11" t="n"/>
+      <c r="BP43" s="8" t="n"/>
+      <c r="BQ43" s="9" t="n"/>
+      <c r="BR43" s="10" t="n"/>
+      <c r="BS43" s="11" t="n"/>
+      <c r="BT43" s="8" t="n"/>
+      <c r="BU43" s="9" t="n"/>
+      <c r="BV43" s="10" t="n"/>
       <c r="BW43" s="11" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Multi Commodity Exchange of India Limited</t>
+          <t>Zydus Wellness Limited</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>INE745G01043</t>
+          <t>INE768C01010</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D44" s="8" t="n"/>
@@ -8948,21 +8932,11 @@
       <c r="T44" s="8" t="n"/>
       <c r="U44" s="9" t="n"/>
       <c r="V44" s="10" t="n"/>
-      <c r="W44" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X44" s="8" t="n">
-        <v>795472</v>
-      </c>
-      <c r="Y44" s="9" t="n">
-        <v>20109.53</v>
-      </c>
-      <c r="Z44" s="10" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="AA44" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="W44" s="11" t="n"/>
+      <c r="X44" s="8" t="n"/>
+      <c r="Y44" s="9" t="n"/>
+      <c r="Z44" s="10" t="n"/>
+      <c r="AA44" s="11" t="n"/>
       <c r="AB44" s="8" t="n"/>
       <c r="AC44" s="9" t="n"/>
       <c r="AD44" s="10" t="n"/>
@@ -8978,19 +8952,45 @@
       <c r="AN44" s="8" t="n"/>
       <c r="AO44" s="9" t="n"/>
       <c r="AP44" s="10" t="n"/>
-      <c r="AQ44" s="11" t="n"/>
-      <c r="AR44" s="8" t="n"/>
-      <c r="AS44" s="9" t="n"/>
-      <c r="AT44" s="10" t="n"/>
-      <c r="AU44" s="11" t="n"/>
-      <c r="AV44" s="8" t="n"/>
-      <c r="AW44" s="9" t="n"/>
-      <c r="AX44" s="10" t="n"/>
-      <c r="AY44" s="11" t="n"/>
-      <c r="AZ44" s="8" t="n"/>
-      <c r="BA44" s="9" t="n"/>
-      <c r="BB44" s="10" t="n"/>
-      <c r="BC44" s="11" t="n"/>
+      <c r="AQ44" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AR44" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AS44" s="9" t="n">
+        <v>88822.8</v>
+      </c>
+      <c r="AT44" s="10" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="AU44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV44" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AW44" s="9" t="n">
+        <v>89280.39999999999</v>
+      </c>
+      <c r="AX44" s="10" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="AY44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ44" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="BA44" s="9" t="n">
+        <v>89020.8</v>
+      </c>
+      <c r="BB44" s="10" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="BC44" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="BD44" s="8" t="n"/>
       <c r="BE44" s="9" t="n"/>
       <c r="BF44" s="10" t="n"/>

--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -5444,7 +5444,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Fertilizers &amp; Agrochemicals</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -8688,17 +8688,17 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>ITC Hotels Limited</t>
+          <t>Zydus Wellness Limited</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>INE379A01028</t>
+          <t>INE768C01010</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Leisure Services</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D42" s="8" t="n"/>
@@ -8740,19 +8740,45 @@
       <c r="AN42" s="8" t="n"/>
       <c r="AO42" s="9" t="n"/>
       <c r="AP42" s="10" t="n"/>
-      <c r="AQ42" s="11" t="n"/>
-      <c r="AR42" s="8" t="n"/>
-      <c r="AS42" s="9" t="n"/>
-      <c r="AT42" s="10" t="n"/>
-      <c r="AU42" s="11" t="n"/>
-      <c r="AV42" s="8" t="n"/>
-      <c r="AW42" s="9" t="n"/>
-      <c r="AX42" s="10" t="n"/>
-      <c r="AY42" s="11" t="n"/>
-      <c r="AZ42" s="8" t="n"/>
-      <c r="BA42" s="9" t="n"/>
-      <c r="BB42" s="10" t="n"/>
-      <c r="BC42" s="11" t="n"/>
+      <c r="AQ42" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AR42" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AS42" s="9" t="n">
+        <v>88822.8</v>
+      </c>
+      <c r="AT42" s="10" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="AU42" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV42" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AW42" s="9" t="n">
+        <v>89280.39999999999</v>
+      </c>
+      <c r="AX42" s="10" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="AY42" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ42" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="BA42" s="9" t="n">
+        <v>89020.8</v>
+      </c>
+      <c r="BB42" s="10" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="BC42" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="BD42" s="8" t="n"/>
       <c r="BE42" s="9" t="n"/>
       <c r="BF42" s="10" t="n"/>
@@ -8760,58 +8786,34 @@
       <c r="BH42" s="8" t="n"/>
       <c r="BI42" s="9" t="n"/>
       <c r="BJ42" s="10" t="n"/>
-      <c r="BK42" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BL42" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BM42" s="9" t="n">
-        <v>19552.33</v>
-      </c>
-      <c r="BN42" s="10" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="BO42" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP42" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BQ42" s="9" t="n">
-        <v>16216.23</v>
-      </c>
-      <c r="BR42" s="10" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="BS42" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT42" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BU42" s="9" t="n">
-        <v>16131.09</v>
-      </c>
-      <c r="BV42" s="10" t="n">
-        <v>0.0018</v>
-      </c>
+      <c r="BK42" s="11" t="n"/>
+      <c r="BL42" s="8" t="n"/>
+      <c r="BM42" s="9" t="n"/>
+      <c r="BN42" s="10" t="n"/>
+      <c r="BO42" s="11" t="n"/>
+      <c r="BP42" s="8" t="n"/>
+      <c r="BQ42" s="9" t="n"/>
+      <c r="BR42" s="10" t="n"/>
+      <c r="BS42" s="11" t="n"/>
+      <c r="BT42" s="8" t="n"/>
+      <c r="BU42" s="9" t="n"/>
+      <c r="BV42" s="10" t="n"/>
       <c r="BW42" s="11" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Multi Commodity Exchange of India Limited</t>
+          <t>ITC Hotels Limited</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>INE745G01043</t>
+          <t>INE379A01028</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Leisure Services</t>
         </is>
       </c>
       <c r="D43" s="8" t="n"/>
@@ -8833,21 +8835,11 @@
       <c r="T43" s="8" t="n"/>
       <c r="U43" s="9" t="n"/>
       <c r="V43" s="10" t="n"/>
-      <c r="W43" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X43" s="8" t="n">
-        <v>795472</v>
-      </c>
-      <c r="Y43" s="9" t="n">
-        <v>20109.53</v>
-      </c>
-      <c r="Z43" s="10" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="AA43" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="W43" s="11" t="n"/>
+      <c r="X43" s="8" t="n"/>
+      <c r="Y43" s="9" t="n"/>
+      <c r="Z43" s="10" t="n"/>
+      <c r="AA43" s="11" t="n"/>
       <c r="AB43" s="8" t="n"/>
       <c r="AC43" s="9" t="n"/>
       <c r="AD43" s="10" t="n"/>
@@ -8883,34 +8875,58 @@
       <c r="BH43" s="8" t="n"/>
       <c r="BI43" s="9" t="n"/>
       <c r="BJ43" s="10" t="n"/>
-      <c r="BK43" s="11" t="n"/>
-      <c r="BL43" s="8" t="n"/>
-      <c r="BM43" s="9" t="n"/>
-      <c r="BN43" s="10" t="n"/>
-      <c r="BO43" s="11" t="n"/>
-      <c r="BP43" s="8" t="n"/>
-      <c r="BQ43" s="9" t="n"/>
-      <c r="BR43" s="10" t="n"/>
-      <c r="BS43" s="11" t="n"/>
-      <c r="BT43" s="8" t="n"/>
-      <c r="BU43" s="9" t="n"/>
-      <c r="BV43" s="10" t="n"/>
+      <c r="BK43" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL43" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BM43" s="9" t="n">
+        <v>19552.33</v>
+      </c>
+      <c r="BN43" s="10" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="BO43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP43" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BQ43" s="9" t="n">
+        <v>16216.23</v>
+      </c>
+      <c r="BR43" s="10" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="BS43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT43" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BU43" s="9" t="n">
+        <v>16131.09</v>
+      </c>
+      <c r="BV43" s="10" t="n">
+        <v>0.0018</v>
+      </c>
       <c r="BW43" s="11" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited</t>
+          <t>Multi Commodity Exchange of India Limited</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>INE768C01010</t>
+          <t>INE745G01043</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D44" s="8" t="n"/>
@@ -8932,11 +8948,21 @@
       <c r="T44" s="8" t="n"/>
       <c r="U44" s="9" t="n"/>
       <c r="V44" s="10" t="n"/>
-      <c r="W44" s="11" t="n"/>
-      <c r="X44" s="8" t="n"/>
-      <c r="Y44" s="9" t="n"/>
-      <c r="Z44" s="10" t="n"/>
-      <c r="AA44" s="11" t="n"/>
+      <c r="W44" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X44" s="8" t="n">
+        <v>795472</v>
+      </c>
+      <c r="Y44" s="9" t="n">
+        <v>20109.53</v>
+      </c>
+      <c r="Z44" s="10" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="AA44" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="AB44" s="8" t="n"/>
       <c r="AC44" s="9" t="n"/>
       <c r="AD44" s="10" t="n"/>
@@ -8952,45 +8978,19 @@
       <c r="AN44" s="8" t="n"/>
       <c r="AO44" s="9" t="n"/>
       <c r="AP44" s="10" t="n"/>
-      <c r="AQ44" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AR44" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="AS44" s="9" t="n">
-        <v>88822.8</v>
-      </c>
-      <c r="AT44" s="10" t="n">
-        <v>0.0077</v>
-      </c>
-      <c r="AU44" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV44" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="AW44" s="9" t="n">
-        <v>89280.39999999999</v>
-      </c>
-      <c r="AX44" s="10" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-      <c r="AY44" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ44" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="BA44" s="9" t="n">
-        <v>89020.8</v>
-      </c>
-      <c r="BB44" s="10" t="n">
-        <v>0.0081</v>
-      </c>
-      <c r="BC44" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="AQ44" s="11" t="n"/>
+      <c r="AR44" s="8" t="n"/>
+      <c r="AS44" s="9" t="n"/>
+      <c r="AT44" s="10" t="n"/>
+      <c r="AU44" s="11" t="n"/>
+      <c r="AV44" s="8" t="n"/>
+      <c r="AW44" s="9" t="n"/>
+      <c r="AX44" s="10" t="n"/>
+      <c r="AY44" s="11" t="n"/>
+      <c r="AZ44" s="8" t="n"/>
+      <c r="BA44" s="9" t="n"/>
+      <c r="BB44" s="10" t="n"/>
+      <c r="BC44" s="11" t="n"/>
       <c r="BD44" s="8" t="n"/>
       <c r="BE44" s="9" t="n"/>
       <c r="BF44" s="10" t="n"/>

--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW45"/>
+  <dimension ref="A1:BS45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -524,22 +524,22 @@
     <col width="26" customWidth="1" min="29" max="29"/>
     <col width="20" customWidth="1" min="30" max="30"/>
     <col width="22" customWidth="1" min="31" max="31"/>
-    <col width="15" customWidth="1" min="32" max="32"/>
+    <col width="14" customWidth="1" min="32" max="32"/>
     <col width="26" customWidth="1" min="33" max="33"/>
-    <col width="20" customWidth="1" min="34" max="34"/>
-    <col width="22" customWidth="1" min="35" max="35"/>
-    <col width="14" customWidth="1" min="36" max="36"/>
+    <col width="14" customWidth="1" min="34" max="34"/>
+    <col width="23" customWidth="1" min="35" max="35"/>
+    <col width="16" customWidth="1" min="36" max="36"/>
     <col width="26" customWidth="1" min="37" max="37"/>
-    <col width="14" customWidth="1" min="38" max="38"/>
-    <col width="23" customWidth="1" min="39" max="39"/>
-    <col width="16" customWidth="1" min="40" max="40"/>
+    <col width="20" customWidth="1" min="38" max="38"/>
+    <col width="22" customWidth="1" min="39" max="39"/>
+    <col width="13" customWidth="1" min="40" max="40"/>
     <col width="26" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
-    <col width="22" customWidth="1" min="43" max="43"/>
+    <col width="23" customWidth="1" min="43" max="43"/>
     <col width="13" customWidth="1" min="44" max="44"/>
     <col width="26" customWidth="1" min="45" max="45"/>
     <col width="20" customWidth="1" min="46" max="46"/>
-    <col width="23" customWidth="1" min="47" max="47"/>
+    <col width="22" customWidth="1" min="47" max="47"/>
     <col width="13" customWidth="1" min="48" max="48"/>
     <col width="26" customWidth="1" min="49" max="49"/>
     <col width="20" customWidth="1" min="50" max="50"/>
@@ -547,27 +547,23 @@
     <col width="13" customWidth="1" min="52" max="52"/>
     <col width="26" customWidth="1" min="53" max="53"/>
     <col width="20" customWidth="1" min="54" max="54"/>
-    <col width="22" customWidth="1" min="55" max="55"/>
+    <col width="23" customWidth="1" min="55" max="55"/>
     <col width="13" customWidth="1" min="56" max="56"/>
     <col width="26" customWidth="1" min="57" max="57"/>
     <col width="20" customWidth="1" min="58" max="58"/>
-    <col width="23" customWidth="1" min="59" max="59"/>
+    <col width="22" customWidth="1" min="59" max="59"/>
     <col width="13" customWidth="1" min="60" max="60"/>
     <col width="26" customWidth="1" min="61" max="61"/>
     <col width="20" customWidth="1" min="62" max="62"/>
-    <col width="22" customWidth="1" min="63" max="63"/>
-    <col width="13" customWidth="1" min="64" max="64"/>
+    <col width="23" customWidth="1" min="63" max="63"/>
+    <col width="15" customWidth="1" min="64" max="64"/>
     <col width="26" customWidth="1" min="65" max="65"/>
     <col width="20" customWidth="1" min="66" max="66"/>
-    <col width="23" customWidth="1" min="67" max="67"/>
-    <col width="15" customWidth="1" min="68" max="68"/>
+    <col width="22" customWidth="1" min="67" max="67"/>
+    <col width="14" customWidth="1" min="68" max="68"/>
     <col width="26" customWidth="1" min="69" max="69"/>
     <col width="20" customWidth="1" min="70" max="70"/>
-    <col width="22" customWidth="1" min="71" max="71"/>
-    <col width="14" customWidth="1" min="72" max="72"/>
-    <col width="26" customWidth="1" min="73" max="73"/>
-    <col width="20" customWidth="1" min="74" max="74"/>
-    <col width="17" customWidth="1" min="75" max="75"/>
+    <col width="17" customWidth="1" min="71" max="71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -646,10 +642,6 @@
       <c r="BQ1" s="1" t="n"/>
       <c r="BR1" s="1" t="n"/>
       <c r="BS1" s="1" t="n"/>
-      <c r="BT1" s="1" t="n"/>
-      <c r="BU1" s="1" t="n"/>
-      <c r="BV1" s="1" t="n"/>
-      <c r="BW1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -725,7 +717,7 @@
       <c r="AE2" s="3" t="n"/>
       <c r="AF2" s="2" t="inlineStr">
         <is>
-          <t>November_2025</t>
+          <t>October_2025</t>
         </is>
       </c>
       <c r="AG2" s="2" t="n"/>
@@ -733,7 +725,7 @@
       <c r="AI2" s="3" t="n"/>
       <c r="AJ2" s="2" t="inlineStr">
         <is>
-          <t>October_2025</t>
+          <t>September_2025</t>
         </is>
       </c>
       <c r="AK2" s="2" t="n"/>
@@ -741,7 +733,7 @@
       <c r="AM2" s="3" t="n"/>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>September_2025</t>
+          <t>August_2025</t>
         </is>
       </c>
       <c r="AO2" s="2" t="n"/>
@@ -749,7 +741,7 @@
       <c r="AQ2" s="3" t="n"/>
       <c r="AR2" s="2" t="inlineStr">
         <is>
-          <t>August_2025</t>
+          <t>July_2025</t>
         </is>
       </c>
       <c r="AS2" s="2" t="n"/>
@@ -757,7 +749,7 @@
       <c r="AU2" s="3" t="n"/>
       <c r="AV2" s="2" t="inlineStr">
         <is>
-          <t>July_2025</t>
+          <t>June_2025</t>
         </is>
       </c>
       <c r="AW2" s="2" t="n"/>
@@ -765,7 +757,7 @@
       <c r="AY2" s="3" t="n"/>
       <c r="AZ2" s="2" t="inlineStr">
         <is>
-          <t>June_2025</t>
+          <t>May_2025</t>
         </is>
       </c>
       <c r="BA2" s="2" t="n"/>
@@ -773,7 +765,7 @@
       <c r="BC2" s="3" t="n"/>
       <c r="BD2" s="2" t="inlineStr">
         <is>
-          <t>May_2025</t>
+          <t>April_2025</t>
         </is>
       </c>
       <c r="BE2" s="2" t="n"/>
@@ -781,7 +773,7 @@
       <c r="BG2" s="3" t="n"/>
       <c r="BH2" s="2" t="inlineStr">
         <is>
-          <t>April_2025</t>
+          <t>March_2025</t>
         </is>
       </c>
       <c r="BI2" s="2" t="n"/>
@@ -789,7 +781,7 @@
       <c r="BK2" s="3" t="n"/>
       <c r="BL2" s="2" t="inlineStr">
         <is>
-          <t>March_2025</t>
+          <t>February_2025</t>
         </is>
       </c>
       <c r="BM2" s="2" t="n"/>
@@ -797,20 +789,12 @@
       <c r="BO2" s="3" t="n"/>
       <c r="BP2" s="2" t="inlineStr">
         <is>
-          <t>February_2025</t>
+          <t>January_2025</t>
         </is>
       </c>
       <c r="BQ2" s="2" t="n"/>
       <c r="BR2" s="2" t="n"/>
       <c r="BS2" s="3" t="n"/>
-      <c r="BT2" s="2" t="inlineStr">
-        <is>
-          <t>January_2025</t>
-        </is>
-      </c>
-      <c r="BU2" s="2" t="n"/>
-      <c r="BV2" s="2" t="n"/>
-      <c r="BW2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n"/>
@@ -1156,26 +1140,6 @@
           <t>% Change in Qty</t>
         </is>
       </c>
-      <c r="BT3" s="4" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="BU3" s="4" t="inlineStr">
-        <is>
-          <t>Market Value (Rs. Lakhs)</t>
-        </is>
-      </c>
-      <c r="BV3" s="4" t="inlineStr">
-        <is>
-          <t>% Net Assets</t>
-        </is>
-      </c>
-      <c r="BW3" s="5" t="inlineStr">
-        <is>
-          <t>% Change in Qty</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -1275,100 +1239,100 @@
         <v>0.0809</v>
       </c>
       <c r="AE4" s="11" t="n">
-        <v>0.05075274131724232</v>
+        <v>0.06394013360876992</v>
       </c>
       <c r="AF4" s="8" t="n">
-        <v>103486016</v>
+        <v>102203321</v>
       </c>
       <c r="AG4" s="9" t="n">
-        <v>1042725.1</v>
+        <v>1009053.39</v>
       </c>
       <c r="AH4" s="10" t="n">
-        <v>0.0803</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="AI4" s="11" t="n">
-        <v>0.01255042387516938</v>
+        <v>0.005262209454604842</v>
       </c>
       <c r="AJ4" s="8" t="n">
-        <v>102203321</v>
+        <v>101668321</v>
       </c>
       <c r="AK4" s="9" t="n">
-        <v>1009053.39</v>
+        <v>966865.73</v>
       </c>
       <c r="AL4" s="10" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.0808</v>
       </c>
       <c r="AM4" s="11" t="n">
-        <v>0.005262209454604842</v>
+        <v>0.06097375017638836</v>
       </c>
       <c r="AN4" s="8" t="n">
-        <v>101668321</v>
+        <v>95825482</v>
       </c>
       <c r="AO4" s="9" t="n">
-        <v>966865.73</v>
+        <v>911875.29</v>
       </c>
       <c r="AP4" s="10" t="n">
-        <v>0.0808</v>
+        <v>0.0793</v>
       </c>
       <c r="AQ4" s="11" t="n">
-        <v>0.06097375017638836</v>
+        <v>1.135602796681763</v>
       </c>
       <c r="AR4" s="8" t="n">
-        <v>95825482</v>
+        <v>44870461</v>
       </c>
       <c r="AS4" s="9" t="n">
-        <v>911875.29</v>
+        <v>905575.64</v>
       </c>
       <c r="AT4" s="10" t="n">
-        <v>0.0793</v>
+        <v>0.0799</v>
       </c>
       <c r="AU4" s="11" t="n">
-        <v>1.135602796681763</v>
+        <v>0.009203290657165424</v>
       </c>
       <c r="AV4" s="8" t="n">
-        <v>44870461</v>
+        <v>44461271</v>
       </c>
       <c r="AW4" s="9" t="n">
-        <v>905575.64</v>
+        <v>889892.34</v>
       </c>
       <c r="AX4" s="10" t="n">
-        <v>0.0799</v>
+        <v>0.0806</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.009203290657165424</v>
+        <v>0.026983580212343</v>
       </c>
       <c r="AZ4" s="8" t="n">
-        <v>44461271</v>
+        <v>43293069</v>
       </c>
       <c r="BA4" s="9" t="n">
-        <v>889892.34</v>
+        <v>842006.9</v>
       </c>
       <c r="BB4" s="10" t="n">
-        <v>0.0806</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="BC4" s="11" t="n">
-        <v>0.026983580212343</v>
+        <v>0.01121152982515689</v>
       </c>
       <c r="BD4" s="8" t="n">
-        <v>43293069</v>
+        <v>42813069</v>
       </c>
       <c r="BE4" s="9" t="n">
-        <v>842006.9</v>
+        <v>824151.58</v>
       </c>
       <c r="BF4" s="10" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="BG4" s="11" t="n">
-        <v>0.01121152982515689</v>
+        <v>0</v>
       </c>
       <c r="BH4" s="8" t="n">
         <v>42813069</v>
       </c>
       <c r="BI4" s="9" t="n">
-        <v>824151.58</v>
+        <v>782708.53</v>
       </c>
       <c r="BJ4" s="10" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.0838</v>
       </c>
       <c r="BK4" s="11" t="n">
         <v>0</v>
@@ -1377,10 +1341,10 @@
         <v>42813069</v>
       </c>
       <c r="BM4" s="9" t="n">
-        <v>782708.53</v>
+        <v>741693.61</v>
       </c>
       <c r="BN4" s="10" t="n">
-        <v>0.0838</v>
+        <v>0.0843</v>
       </c>
       <c r="BO4" s="11" t="n">
         <v>0</v>
@@ -1389,24 +1353,12 @@
         <v>42813069</v>
       </c>
       <c r="BQ4" s="9" t="n">
-        <v>741693.61</v>
+        <v>727287.01</v>
       </c>
       <c r="BR4" s="10" t="n">
-        <v>0.0843</v>
-      </c>
-      <c r="BS4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT4" s="8" t="n">
-        <v>42813069</v>
-      </c>
-      <c r="BU4" s="9" t="n">
-        <v>727287.01</v>
-      </c>
-      <c r="BV4" s="10" t="n">
         <v>0.08110000000000001</v>
       </c>
-      <c r="BW4" s="11" t="n"/>
+      <c r="BS4" s="11" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -1506,138 +1458,126 @@
         <v>0.0606</v>
       </c>
       <c r="AE5" s="11" t="n">
-        <v>0.07483622732268541</v>
+        <v>0.1666724875647491</v>
       </c>
       <c r="AF5" s="8" t="n">
-        <v>284154236</v>
+        <v>261786637</v>
       </c>
       <c r="AG5" s="9" t="n">
-        <v>767074.36</v>
+        <v>754338.1899999999</v>
       </c>
       <c r="AH5" s="10" t="n">
-        <v>0.0591</v>
+        <v>0.06</v>
       </c>
       <c r="AI5" s="11" t="n">
-        <v>0.08544209611432535</v>
+        <v>0.02291281861384987</v>
       </c>
       <c r="AJ5" s="8" t="n">
-        <v>261786637</v>
+        <v>255922726</v>
       </c>
       <c r="AK5" s="9" t="n">
-        <v>754338.1899999999</v>
+        <v>717223.4399999999</v>
       </c>
       <c r="AL5" s="10" t="n">
-        <v>0.06</v>
+        <v>0.0599</v>
       </c>
       <c r="AM5" s="11" t="n">
-        <v>0.02291281861384987</v>
+        <v>0.04012490664854439</v>
       </c>
       <c r="AN5" s="8" t="n">
-        <v>255922726</v>
+        <v>246049993</v>
       </c>
       <c r="AO5" s="9" t="n">
-        <v>717223.4399999999</v>
+        <v>677252.61</v>
       </c>
       <c r="AP5" s="10" t="n">
+        <v>0.0589</v>
+      </c>
+      <c r="AQ5" s="11" t="n">
+        <v>0.06613218800272164</v>
+      </c>
+      <c r="AR5" s="8" t="n">
+        <v>230787510</v>
+      </c>
+      <c r="AS5" s="9" t="n">
+        <v>671591.65</v>
+      </c>
+      <c r="AT5" s="10" t="n">
+        <v>0.0593</v>
+      </c>
+      <c r="AU5" s="11" t="n">
+        <v>0.02930647191621902</v>
+      </c>
+      <c r="AV5" s="8" t="n">
+        <v>224216515</v>
+      </c>
+      <c r="AW5" s="9" t="n">
+        <v>672425.33</v>
+      </c>
+      <c r="AX5" s="10" t="n">
+        <v>0.0609</v>
+      </c>
+      <c r="AY5" s="11" t="n">
+        <v>0.07348663585077284</v>
+      </c>
+      <c r="AZ5" s="8" t="n">
+        <v>208867542</v>
+      </c>
+      <c r="BA5" s="9" t="n">
+        <v>605193.7</v>
+      </c>
+      <c r="BB5" s="10" t="n">
+        <v>0.0583</v>
+      </c>
+      <c r="BC5" s="11" t="n">
+        <v>0.0787685054851275</v>
+      </c>
+      <c r="BD5" s="8" t="n">
+        <v>193616648</v>
+      </c>
+      <c r="BE5" s="9" t="n">
+        <v>595274.38</v>
+      </c>
+      <c r="BF5" s="10" t="n">
+        <v>0.0604</v>
+      </c>
+      <c r="BG5" s="11" t="n">
+        <v>0.004416437745811861</v>
+      </c>
+      <c r="BH5" s="8" t="n">
+        <v>192765312</v>
+      </c>
+      <c r="BI5" s="9" t="n">
+        <v>559694.08</v>
+      </c>
+      <c r="BJ5" s="10" t="n">
         <v>0.0599</v>
       </c>
-      <c r="AQ5" s="11" t="n">
-        <v>0.04012490664854439</v>
-      </c>
-      <c r="AR5" s="8" t="n">
-        <v>246049993</v>
-      </c>
-      <c r="AS5" s="9" t="n">
-        <v>677252.61</v>
-      </c>
-      <c r="AT5" s="10" t="n">
-        <v>0.0589</v>
-      </c>
-      <c r="AU5" s="11" t="n">
-        <v>0.06613218800272164</v>
-      </c>
-      <c r="AV5" s="8" t="n">
-        <v>230787510</v>
-      </c>
-      <c r="AW5" s="9" t="n">
-        <v>671591.65</v>
-      </c>
-      <c r="AX5" s="10" t="n">
-        <v>0.0593</v>
-      </c>
-      <c r="AY5" s="11" t="n">
-        <v>0.02930647191621902</v>
-      </c>
-      <c r="AZ5" s="8" t="n">
-        <v>224216515</v>
-      </c>
-      <c r="BA5" s="9" t="n">
-        <v>672425.33</v>
-      </c>
-      <c r="BB5" s="10" t="n">
-        <v>0.0609</v>
-      </c>
-      <c r="BC5" s="11" t="n">
-        <v>0.07348663585077284</v>
-      </c>
-      <c r="BD5" s="8" t="n">
-        <v>208867542</v>
-      </c>
-      <c r="BE5" s="9" t="n">
-        <v>605193.7</v>
-      </c>
-      <c r="BF5" s="10" t="n">
-        <v>0.0583</v>
-      </c>
-      <c r="BG5" s="11" t="n">
-        <v>0.0787685054851275</v>
-      </c>
-      <c r="BH5" s="8" t="n">
-        <v>193616648</v>
-      </c>
-      <c r="BI5" s="9" t="n">
-        <v>595274.38</v>
-      </c>
-      <c r="BJ5" s="10" t="n">
-        <v>0.0604</v>
-      </c>
       <c r="BK5" s="11" t="n">
-        <v>0.004416437745811861</v>
+        <v>-0.003790710650882039</v>
       </c>
       <c r="BL5" s="8" t="n">
-        <v>192765312</v>
+        <v>193498810</v>
       </c>
       <c r="BM5" s="9" t="n">
-        <v>559694.08</v>
+        <v>485391.76</v>
       </c>
       <c r="BN5" s="10" t="n">
-        <v>0.0599</v>
+        <v>0.0552</v>
       </c>
       <c r="BO5" s="11" t="n">
-        <v>-0.003790710650882039</v>
+        <v>0.04268662994371823</v>
       </c>
       <c r="BP5" s="8" t="n">
-        <v>193498810</v>
+        <v>185577147</v>
       </c>
       <c r="BQ5" s="9" t="n">
-        <v>485391.76</v>
+        <v>559793.46</v>
       </c>
       <c r="BR5" s="10" t="n">
-        <v>0.0552</v>
-      </c>
-      <c r="BS5" s="11" t="n">
-        <v>0.04268662994371823</v>
-      </c>
-      <c r="BT5" s="8" t="n">
-        <v>185577147</v>
-      </c>
-      <c r="BU5" s="9" t="n">
-        <v>559793.46</v>
-      </c>
-      <c r="BV5" s="10" t="n">
         <v>0.0624</v>
       </c>
-      <c r="BW5" s="11" t="n"/>
+      <c r="BS5" s="11" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -1737,138 +1677,126 @@
         <v>0.0449</v>
       </c>
       <c r="AE6" s="11" t="n">
-        <v>0.02714259251540287</v>
+        <v>0.07130225543338212</v>
       </c>
       <c r="AF6" s="8" t="n">
-        <v>144737169</v>
+        <v>138771024</v>
       </c>
       <c r="AG6" s="9" t="n">
-        <v>585100.01</v>
+        <v>583324</v>
       </c>
       <c r="AH6" s="10" t="n">
-        <v>0.0451</v>
+        <v>0.0464</v>
       </c>
       <c r="AI6" s="11" t="n">
-        <v>0.04299272879906111</v>
+        <v>0.02247256843567582</v>
       </c>
       <c r="AJ6" s="8" t="n">
-        <v>138771024</v>
+        <v>135721024</v>
       </c>
       <c r="AK6" s="9" t="n">
-        <v>583324</v>
+        <v>544987.77</v>
       </c>
       <c r="AL6" s="10" t="n">
-        <v>0.0464</v>
+        <v>0.0455</v>
       </c>
       <c r="AM6" s="11" t="n">
-        <v>0.02247256843567582</v>
+        <v>0.04867833529118113</v>
       </c>
       <c r="AN6" s="8" t="n">
-        <v>135721024</v>
+        <v>129421024</v>
       </c>
       <c r="AO6" s="9" t="n">
-        <v>544987.77</v>
+        <v>530302.65</v>
       </c>
       <c r="AP6" s="10" t="n">
+        <v>0.0461</v>
+      </c>
+      <c r="AQ6" s="11" t="n">
+        <v>0.05933146465642036</v>
+      </c>
+      <c r="AR6" s="8" t="n">
+        <v>122172359</v>
+      </c>
+      <c r="AS6" s="9" t="n">
+        <v>503289.03</v>
+      </c>
+      <c r="AT6" s="10" t="n">
+        <v>0.0444</v>
+      </c>
+      <c r="AU6" s="11" t="n">
+        <v>0.04045226173662547</v>
+      </c>
+      <c r="AV6" s="8" t="n">
+        <v>117422359</v>
+      </c>
+      <c r="AW6" s="9" t="n">
+        <v>489005.41</v>
+      </c>
+      <c r="AX6" s="10" t="n">
+        <v>0.0443</v>
+      </c>
+      <c r="AY6" s="11" t="n">
+        <v>0.07460089770293252</v>
+      </c>
+      <c r="AZ6" s="8" t="n">
+        <v>109270669</v>
+      </c>
+      <c r="BA6" s="9" t="n">
+        <v>456806.03</v>
+      </c>
+      <c r="BB6" s="10" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="BC6" s="11" t="n">
+        <v>0.03799307836597426</v>
+      </c>
+      <c r="BD6" s="8" t="n">
+        <v>105271096</v>
+      </c>
+      <c r="BE6" s="9" t="n">
+        <v>448244.33</v>
+      </c>
+      <c r="BF6" s="10" t="n">
         <v>0.0455</v>
       </c>
-      <c r="AQ6" s="11" t="n">
-        <v>0.04867833529118113</v>
-      </c>
-      <c r="AR6" s="8" t="n">
-        <v>129421024</v>
-      </c>
-      <c r="AS6" s="9" t="n">
-        <v>530302.65</v>
-      </c>
-      <c r="AT6" s="10" t="n">
-        <v>0.0461</v>
-      </c>
-      <c r="AU6" s="11" t="n">
-        <v>0.05933146465642036</v>
-      </c>
-      <c r="AV6" s="8" t="n">
-        <v>122172359</v>
-      </c>
-      <c r="AW6" s="9" t="n">
-        <v>503289.03</v>
-      </c>
-      <c r="AX6" s="10" t="n">
+      <c r="BG6" s="11" t="n">
+        <v>0.04028866499357868</v>
+      </c>
+      <c r="BH6" s="8" t="n">
+        <v>101194120</v>
+      </c>
+      <c r="BI6" s="9" t="n">
+        <v>414642.91</v>
+      </c>
+      <c r="BJ6" s="10" t="n">
         <v>0.0444</v>
       </c>
-      <c r="AY6" s="11" t="n">
-        <v>0.04045226173662547</v>
-      </c>
-      <c r="AZ6" s="8" t="n">
-        <v>117422359</v>
-      </c>
-      <c r="BA6" s="9" t="n">
-        <v>489005.41</v>
-      </c>
-      <c r="BB6" s="10" t="n">
-        <v>0.0443</v>
-      </c>
-      <c r="BC6" s="11" t="n">
-        <v>0.07460089770293252</v>
-      </c>
-      <c r="BD6" s="8" t="n">
-        <v>109270669</v>
-      </c>
-      <c r="BE6" s="9" t="n">
-        <v>456806.03</v>
-      </c>
-      <c r="BF6" s="10" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="BG6" s="11" t="n">
-        <v>0.03799307836597426</v>
-      </c>
-      <c r="BH6" s="8" t="n">
-        <v>105271096</v>
-      </c>
-      <c r="BI6" s="9" t="n">
-        <v>448244.33</v>
-      </c>
-      <c r="BJ6" s="10" t="n">
-        <v>0.0455</v>
-      </c>
       <c r="BK6" s="11" t="n">
-        <v>0.04028866499357868</v>
+        <v>0</v>
       </c>
       <c r="BL6" s="8" t="n">
         <v>101194120</v>
       </c>
       <c r="BM6" s="9" t="n">
-        <v>414642.91</v>
+        <v>399716.77</v>
       </c>
       <c r="BN6" s="10" t="n">
-        <v>0.0444</v>
+        <v>0.0454</v>
       </c>
       <c r="BO6" s="11" t="n">
-        <v>0</v>
+        <v>0.02222354216593874</v>
       </c>
       <c r="BP6" s="8" t="n">
-        <v>101194120</v>
+        <v>98994120</v>
       </c>
       <c r="BQ6" s="9" t="n">
-        <v>399716.77</v>
+        <v>442998.69</v>
       </c>
       <c r="BR6" s="10" t="n">
-        <v>0.0454</v>
-      </c>
-      <c r="BS6" s="11" t="n">
-        <v>0.02222354216593874</v>
-      </c>
-      <c r="BT6" s="8" t="n">
-        <v>98994120</v>
-      </c>
-      <c r="BU6" s="9" t="n">
-        <v>442998.69</v>
-      </c>
-      <c r="BV6" s="10" t="n">
         <v>0.0494</v>
       </c>
-      <c r="BW6" s="11" t="n"/>
+      <c r="BS6" s="11" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -1968,88 +1896,88 @@
         <v>0.0497</v>
       </c>
       <c r="AE7" s="11" t="n">
-        <v>0.08865063536064391</v>
+        <v>0.1392673796002192</v>
       </c>
       <c r="AF7" s="8" t="n">
-        <v>45308598</v>
+        <v>43295573</v>
       </c>
       <c r="AG7" s="9" t="n">
-        <v>629245.8100000001</v>
+        <v>582455.34</v>
       </c>
       <c r="AH7" s="10" t="n">
-        <v>0.0485</v>
+        <v>0.0463</v>
       </c>
       <c r="AI7" s="11" t="n">
-        <v>0.04649493840859896</v>
+        <v>0.02558297621590971</v>
       </c>
       <c r="AJ7" s="8" t="n">
-        <v>43295573</v>
+        <v>42215573</v>
       </c>
       <c r="AK7" s="9" t="n">
-        <v>582455.34</v>
+        <v>569065.92</v>
       </c>
       <c r="AL7" s="10" t="n">
-        <v>0.0463</v>
+        <v>0.0475</v>
       </c>
       <c r="AM7" s="11" t="n">
-        <v>0.02558297621590971</v>
+        <v>0.03671439253646495</v>
       </c>
       <c r="AN7" s="8" t="n">
-        <v>42215573</v>
+        <v>40720543</v>
       </c>
       <c r="AO7" s="9" t="n">
-        <v>569065.92</v>
+        <v>569191.75</v>
       </c>
       <c r="AP7" s="10" t="n">
-        <v>0.0475</v>
+        <v>0.0495</v>
       </c>
       <c r="AQ7" s="11" t="n">
-        <v>0.03671439253646495</v>
+        <v>0.02815262499999053</v>
       </c>
       <c r="AR7" s="8" t="n">
-        <v>40720543</v>
+        <v>39605543</v>
       </c>
       <c r="AS7" s="9" t="n">
-        <v>569191.75</v>
+        <v>586716.51</v>
       </c>
       <c r="AT7" s="10" t="n">
-        <v>0.0495</v>
+        <v>0.0518</v>
       </c>
       <c r="AU7" s="11" t="n">
-        <v>0.02815262499999053</v>
+        <v>0.08540125861519442</v>
       </c>
       <c r="AV7" s="8" t="n">
-        <v>39605543</v>
+        <v>36489310</v>
       </c>
       <c r="AW7" s="9" t="n">
-        <v>586716.51</v>
+        <v>527562.4399999999</v>
       </c>
       <c r="AX7" s="10" t="n">
-        <v>0.0518</v>
+        <v>0.0478</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>0.08540125861519442</v>
+        <v>0.04294684214648178</v>
       </c>
       <c r="AZ7" s="8" t="n">
-        <v>36489310</v>
+        <v>34986740</v>
       </c>
       <c r="BA7" s="9" t="n">
-        <v>527562.4399999999</v>
+        <v>505838.29</v>
       </c>
       <c r="BB7" s="10" t="n">
-        <v>0.0478</v>
+        <v>0.0487</v>
       </c>
       <c r="BC7" s="11" t="n">
-        <v>0.04294684214648178</v>
+        <v>0</v>
       </c>
       <c r="BD7" s="8" t="n">
         <v>34986740</v>
       </c>
       <c r="BE7" s="9" t="n">
-        <v>505838.29</v>
+        <v>499260.78</v>
       </c>
       <c r="BF7" s="10" t="n">
-        <v>0.0487</v>
+        <v>0.0507</v>
       </c>
       <c r="BG7" s="11" t="n">
         <v>0</v>
@@ -2058,10 +1986,10 @@
         <v>34986740</v>
       </c>
       <c r="BI7" s="9" t="n">
-        <v>499260.78</v>
+        <v>471743.71</v>
       </c>
       <c r="BJ7" s="10" t="n">
-        <v>0.0507</v>
+        <v>0.0505</v>
       </c>
       <c r="BK7" s="11" t="n">
         <v>0</v>
@@ -2070,10 +1998,10 @@
         <v>34986740</v>
       </c>
       <c r="BM7" s="9" t="n">
-        <v>471743.71</v>
+        <v>421275.34</v>
       </c>
       <c r="BN7" s="10" t="n">
-        <v>0.0505</v>
+        <v>0.0479</v>
       </c>
       <c r="BO7" s="11" t="n">
         <v>0</v>
@@ -2082,24 +2010,12 @@
         <v>34986740</v>
       </c>
       <c r="BQ7" s="9" t="n">
-        <v>421275.34</v>
+        <v>438313.88</v>
       </c>
       <c r="BR7" s="10" t="n">
-        <v>0.0479</v>
-      </c>
-      <c r="BS7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT7" s="8" t="n">
-        <v>34986740</v>
-      </c>
-      <c r="BU7" s="9" t="n">
-        <v>438313.88</v>
-      </c>
-      <c r="BV7" s="10" t="n">
         <v>0.0489</v>
       </c>
-      <c r="BW7" s="11" t="n"/>
+      <c r="BS7" s="11" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -2205,10 +2121,10 @@
         <v>162039558</v>
       </c>
       <c r="AG8" s="9" t="n">
-        <v>609511.8</v>
+        <v>629766.74</v>
       </c>
       <c r="AH8" s="10" t="n">
-        <v>0.047</v>
+        <v>0.0501</v>
       </c>
       <c r="AI8" s="11" t="n">
         <v>0</v>
@@ -2217,10 +2133,10 @@
         <v>162039558</v>
       </c>
       <c r="AK8" s="9" t="n">
-        <v>629766.74</v>
+        <v>631873.26</v>
       </c>
       <c r="AL8" s="10" t="n">
-        <v>0.0501</v>
+        <v>0.0528</v>
       </c>
       <c r="AM8" s="11" t="n">
         <v>0</v>
@@ -2229,7 +2145,7 @@
         <v>162039558</v>
       </c>
       <c r="AO8" s="9" t="n">
-        <v>631873.26</v>
+        <v>607324.26</v>
       </c>
       <c r="AP8" s="10" t="n">
         <v>0.0528</v>
@@ -2241,10 +2157,10 @@
         <v>162039558</v>
       </c>
       <c r="AS8" s="9" t="n">
-        <v>607324.26</v>
+        <v>609835.88</v>
       </c>
       <c r="AT8" s="10" t="n">
-        <v>0.0528</v>
+        <v>0.0538</v>
       </c>
       <c r="AU8" s="11" t="n">
         <v>0</v>
@@ -2253,84 +2169,72 @@
         <v>162039558</v>
       </c>
       <c r="AW8" s="9" t="n">
-        <v>609835.88</v>
+        <v>635114.05</v>
       </c>
       <c r="AX8" s="10" t="n">
-        <v>0.0538</v>
+        <v>0.0575</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0</v>
+        <v>0.0408396826825464</v>
       </c>
       <c r="AZ8" s="8" t="n">
-        <v>162039558</v>
+        <v>155681572</v>
       </c>
       <c r="BA8" s="9" t="n">
-        <v>635114.05</v>
+        <v>618522.89</v>
       </c>
       <c r="BB8" s="10" t="n">
-        <v>0.0575</v>
+        <v>0.0595</v>
       </c>
       <c r="BC8" s="11" t="n">
-        <v>0.0408396826825464</v>
+        <v>0.04960632238493121</v>
       </c>
       <c r="BD8" s="8" t="n">
-        <v>155681572</v>
+        <v>148323775</v>
       </c>
       <c r="BE8" s="9" t="n">
-        <v>618522.89</v>
+        <v>571491.51</v>
       </c>
       <c r="BF8" s="10" t="n">
-        <v>0.0595</v>
+        <v>0.058</v>
       </c>
       <c r="BG8" s="11" t="n">
-        <v>0.04960632238493121</v>
+        <v>0.05138982123049783</v>
       </c>
       <c r="BH8" s="8" t="n">
-        <v>148323775</v>
+        <v>141074007</v>
       </c>
       <c r="BI8" s="9" t="n">
-        <v>571491.51</v>
+        <v>561756.7</v>
       </c>
       <c r="BJ8" s="10" t="n">
-        <v>0.058</v>
+        <v>0.0601</v>
       </c>
       <c r="BK8" s="11" t="n">
-        <v>0.05138982123049783</v>
+        <v>-0.01095372515938375</v>
       </c>
       <c r="BL8" s="8" t="n">
-        <v>141074007</v>
+        <v>142636407</v>
       </c>
       <c r="BM8" s="9" t="n">
-        <v>561756.7</v>
+        <v>526827.5699999999</v>
       </c>
       <c r="BN8" s="10" t="n">
-        <v>0.0601</v>
+        <v>0.0599</v>
       </c>
       <c r="BO8" s="11" t="n">
-        <v>-0.01095372515938375</v>
+        <v>0.02369256314048828</v>
       </c>
       <c r="BP8" s="8" t="n">
-        <v>142636407</v>
+        <v>139335199</v>
       </c>
       <c r="BQ8" s="9" t="n">
-        <v>526827.5699999999</v>
+        <v>551628.05</v>
       </c>
       <c r="BR8" s="10" t="n">
-        <v>0.0599</v>
-      </c>
-      <c r="BS8" s="11" t="n">
-        <v>0.02369256314048828</v>
-      </c>
-      <c r="BT8" s="8" t="n">
-        <v>139335199</v>
-      </c>
-      <c r="BU8" s="9" t="n">
-        <v>551628.05</v>
-      </c>
-      <c r="BV8" s="10" t="n">
         <v>0.0615</v>
       </c>
-      <c r="BW8" s="11" t="n"/>
+      <c r="BS8" s="11" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -2436,10 +2340,10 @@
         <v>5318918</v>
       </c>
       <c r="AG9" s="9" t="n">
-        <v>611622.38</v>
+        <v>654386.48</v>
       </c>
       <c r="AH9" s="10" t="n">
-        <v>0.0471</v>
+        <v>0.052</v>
       </c>
       <c r="AI9" s="11" t="n">
         <v>0</v>
@@ -2448,10 +2352,10 @@
         <v>5318918</v>
       </c>
       <c r="AK9" s="9" t="n">
-        <v>654386.48</v>
+        <v>651407.89</v>
       </c>
       <c r="AL9" s="10" t="n">
-        <v>0.052</v>
+        <v>0.0544</v>
       </c>
       <c r="AM9" s="11" t="n">
         <v>0</v>
@@ -2460,10 +2364,10 @@
         <v>5318918</v>
       </c>
       <c r="AO9" s="9" t="n">
-        <v>651407.89</v>
+        <v>679225.83</v>
       </c>
       <c r="AP9" s="10" t="n">
-        <v>0.0544</v>
+        <v>0.059</v>
       </c>
       <c r="AQ9" s="11" t="n">
         <v>0</v>
@@ -2472,10 +2376,10 @@
         <v>5318918</v>
       </c>
       <c r="AS9" s="9" t="n">
-        <v>679225.83</v>
+        <v>742680.52</v>
       </c>
       <c r="AT9" s="10" t="n">
-        <v>0.059</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="AU9" s="11" t="n">
         <v>0</v>
@@ -2484,10 +2388,10 @@
         <v>5318918</v>
       </c>
       <c r="AW9" s="9" t="n">
-        <v>742680.52</v>
+        <v>764807.22</v>
       </c>
       <c r="AX9" s="10" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0693</v>
       </c>
       <c r="AY9" s="11" t="n">
         <v>0</v>
@@ -2496,10 +2400,10 @@
         <v>5318918</v>
       </c>
       <c r="BA9" s="9" t="n">
-        <v>764807.22</v>
+        <v>713479.66</v>
       </c>
       <c r="BB9" s="10" t="n">
-        <v>0.0693</v>
+        <v>0.0687</v>
       </c>
       <c r="BC9" s="11" t="n">
         <v>0</v>
@@ -2508,10 +2412,10 @@
         <v>5318918</v>
       </c>
       <c r="BE9" s="9" t="n">
-        <v>713479.66</v>
+        <v>636834.05</v>
       </c>
       <c r="BF9" s="10" t="n">
-        <v>0.0687</v>
+        <v>0.0646</v>
       </c>
       <c r="BG9" s="11" t="n">
         <v>0</v>
@@ -2520,10 +2424,10 @@
         <v>5318918</v>
       </c>
       <c r="BI9" s="9" t="n">
-        <v>636834.05</v>
+        <v>663431.3</v>
       </c>
       <c r="BJ9" s="10" t="n">
-        <v>0.0646</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="BK9" s="11" t="n">
         <v>0</v>
@@ -2532,10 +2436,10 @@
         <v>5318918</v>
       </c>
       <c r="BM9" s="9" t="n">
-        <v>663431.3</v>
+        <v>615630.1899999999</v>
       </c>
       <c r="BN9" s="10" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BO9" s="11" t="n">
         <v>0</v>
@@ -2544,24 +2448,12 @@
         <v>5318918</v>
       </c>
       <c r="BQ9" s="9" t="n">
-        <v>615630.1899999999</v>
+        <v>614850.96</v>
       </c>
       <c r="BR9" s="10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BS9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT9" s="8" t="n">
-        <v>5318918</v>
-      </c>
-      <c r="BU9" s="9" t="n">
-        <v>614850.96</v>
-      </c>
-      <c r="BV9" s="10" t="n">
         <v>0.06850000000000001</v>
       </c>
-      <c r="BW9" s="11" t="n"/>
+      <c r="BS9" s="11" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -2695,10 +2587,6 @@
       <c r="BQ10" s="9" t="n"/>
       <c r="BR10" s="10" t="n"/>
       <c r="BS10" s="11" t="n"/>
-      <c r="BT10" s="8" t="n"/>
-      <c r="BU10" s="9" t="n"/>
-      <c r="BV10" s="10" t="n"/>
-      <c r="BW10" s="11" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -2804,34 +2692,34 @@
         <v>12435671</v>
       </c>
       <c r="AG11" s="9" t="n">
-        <v>467245.47</v>
+        <v>433656.72</v>
       </c>
       <c r="AH11" s="10" t="n">
-        <v>0.036</v>
+        <v>0.0345</v>
       </c>
       <c r="AI11" s="11" t="n">
-        <v>0</v>
+        <v>0.008106571584148119</v>
       </c>
       <c r="AJ11" s="8" t="n">
-        <v>12435671</v>
+        <v>12335671</v>
       </c>
       <c r="AK11" s="9" t="n">
-        <v>433656.72</v>
+        <v>422743.45</v>
       </c>
       <c r="AL11" s="10" t="n">
-        <v>0.0345</v>
+        <v>0.0353</v>
       </c>
       <c r="AM11" s="11" t="n">
-        <v>0.008106571584148119</v>
+        <v>0</v>
       </c>
       <c r="AN11" s="8" t="n">
         <v>12335671</v>
       </c>
       <c r="AO11" s="9" t="n">
-        <v>422743.45</v>
+        <v>394679.79</v>
       </c>
       <c r="AP11" s="10" t="n">
-        <v>0.0353</v>
+        <v>0.0343</v>
       </c>
       <c r="AQ11" s="11" t="n">
         <v>0</v>
@@ -2840,10 +2728,10 @@
         <v>12335671</v>
       </c>
       <c r="AS11" s="9" t="n">
-        <v>394679.79</v>
+        <v>395123.88</v>
       </c>
       <c r="AT11" s="10" t="n">
-        <v>0.0343</v>
+        <v>0.0349</v>
       </c>
       <c r="AU11" s="11" t="n">
         <v>0</v>
@@ -2852,84 +2740,72 @@
         <v>12335671</v>
       </c>
       <c r="AW11" s="9" t="n">
-        <v>395123.88</v>
+        <v>392669.08</v>
       </c>
       <c r="AX11" s="10" t="n">
-        <v>0.0349</v>
+        <v>0.0356</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0</v>
+        <v>0.00852700604200313</v>
       </c>
       <c r="AZ11" s="8" t="n">
-        <v>12335671</v>
+        <v>12231374</v>
       </c>
       <c r="BA11" s="9" t="n">
-        <v>392669.08</v>
+        <v>364103.54</v>
       </c>
       <c r="BB11" s="10" t="n">
-        <v>0.0356</v>
+        <v>0.0351</v>
       </c>
       <c r="BC11" s="11" t="n">
-        <v>0.00852700604200313</v>
+        <v>0.1078930368366115</v>
       </c>
       <c r="BD11" s="8" t="n">
-        <v>12231374</v>
+        <v>11040212</v>
       </c>
       <c r="BE11" s="9" t="n">
-        <v>364103.54</v>
+        <v>323345.73</v>
       </c>
       <c r="BF11" s="10" t="n">
-        <v>0.0351</v>
+        <v>0.0328</v>
       </c>
       <c r="BG11" s="11" t="n">
-        <v>0.1078930368366115</v>
+        <v>0.06163142499453569</v>
       </c>
       <c r="BH11" s="8" t="n">
-        <v>11040212</v>
+        <v>10399289</v>
       </c>
       <c r="BI11" s="9" t="n">
-        <v>323345.73</v>
+        <v>277224.25</v>
       </c>
       <c r="BJ11" s="10" t="n">
-        <v>0.0328</v>
+        <v>0.0297</v>
       </c>
       <c r="BK11" s="11" t="n">
-        <v>0.06163142499453569</v>
+        <v>0.03283692525275198</v>
       </c>
       <c r="BL11" s="8" t="n">
-        <v>10399289</v>
+        <v>10068665</v>
       </c>
       <c r="BM11" s="9" t="n">
-        <v>277224.25</v>
+        <v>260285.06</v>
       </c>
       <c r="BN11" s="10" t="n">
-        <v>0.0297</v>
+        <v>0.0296</v>
       </c>
       <c r="BO11" s="11" t="n">
-        <v>0.03283692525275198</v>
+        <v>0.07897007813229198</v>
       </c>
       <c r="BP11" s="8" t="n">
-        <v>10068665</v>
+        <v>9331737</v>
       </c>
       <c r="BQ11" s="9" t="n">
-        <v>260285.06</v>
+        <v>279004.94</v>
       </c>
       <c r="BR11" s="10" t="n">
-        <v>0.0296</v>
-      </c>
-      <c r="BS11" s="11" t="n">
-        <v>0.07897007813229198</v>
-      </c>
-      <c r="BT11" s="8" t="n">
-        <v>9331737</v>
-      </c>
-      <c r="BU11" s="9" t="n">
-        <v>279004.94</v>
-      </c>
-      <c r="BV11" s="10" t="n">
         <v>0.0311</v>
       </c>
-      <c r="BW11" s="11" t="n"/>
+      <c r="BS11" s="11" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -3029,40 +2905,40 @@
         <v>0.026</v>
       </c>
       <c r="AE12" s="11" t="n">
-        <v>0.07485632112907131</v>
+        <v>0.1751445301807795</v>
       </c>
       <c r="AF12" s="8" t="n">
-        <v>19831378</v>
+        <v>18138945</v>
       </c>
       <c r="AG12" s="9" t="n">
-        <v>322101.24</v>
+        <v>279611.84</v>
       </c>
       <c r="AH12" s="10" t="n">
-        <v>0.0248</v>
+        <v>0.0222</v>
       </c>
       <c r="AI12" s="11" t="n">
-        <v>0.09330382775845011</v>
+        <v>-0.0303656466471499</v>
       </c>
       <c r="AJ12" s="8" t="n">
-        <v>18138945</v>
+        <v>18706995</v>
       </c>
       <c r="AK12" s="9" t="n">
-        <v>279611.84</v>
+        <v>259110.59</v>
       </c>
       <c r="AL12" s="10" t="n">
-        <v>0.0222</v>
+        <v>0.0216</v>
       </c>
       <c r="AM12" s="11" t="n">
-        <v>-0.0303656466471499</v>
+        <v>0</v>
       </c>
       <c r="AN12" s="8" t="n">
         <v>18706995</v>
       </c>
       <c r="AO12" s="9" t="n">
-        <v>259110.59</v>
+        <v>272149.36</v>
       </c>
       <c r="AP12" s="10" t="n">
-        <v>0.0216</v>
+        <v>0.0237</v>
       </c>
       <c r="AQ12" s="11" t="n">
         <v>0</v>
@@ -3071,58 +2947,58 @@
         <v>18706995</v>
       </c>
       <c r="AS12" s="9" t="n">
-        <v>272149.36</v>
+        <v>274599.98</v>
       </c>
       <c r="AT12" s="10" t="n">
-        <v>0.0237</v>
+        <v>0.0242</v>
       </c>
       <c r="AU12" s="11" t="n">
-        <v>0</v>
+        <v>0.00797456974367416</v>
       </c>
       <c r="AV12" s="8" t="n">
-        <v>18706995</v>
+        <v>18558995</v>
       </c>
       <c r="AW12" s="9" t="n">
-        <v>274599.98</v>
+        <v>320810.79</v>
       </c>
       <c r="AX12" s="10" t="n">
-        <v>0.0242</v>
+        <v>0.0291</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>0.00797456974367416</v>
+        <v>0.01185405417517898</v>
       </c>
       <c r="AZ12" s="8" t="n">
-        <v>18558995</v>
+        <v>18341573</v>
       </c>
       <c r="BA12" s="9" t="n">
-        <v>320810.79</v>
+        <v>300178.18</v>
       </c>
       <c r="BB12" s="10" t="n">
-        <v>0.0291</v>
+        <v>0.0289</v>
       </c>
       <c r="BC12" s="11" t="n">
-        <v>0.01185405417517898</v>
+        <v>-0.01953282340226823</v>
       </c>
       <c r="BD12" s="8" t="n">
-        <v>18341573</v>
+        <v>18706973</v>
       </c>
       <c r="BE12" s="9" t="n">
-        <v>300178.18</v>
+        <v>293231.8</v>
       </c>
       <c r="BF12" s="10" t="n">
-        <v>0.0289</v>
+        <v>0.0298</v>
       </c>
       <c r="BG12" s="11" t="n">
-        <v>-0.01953282340226823</v>
+        <v>0</v>
       </c>
       <c r="BH12" s="8" t="n">
         <v>18706973</v>
       </c>
       <c r="BI12" s="9" t="n">
-        <v>293231.8</v>
+        <v>297908.55</v>
       </c>
       <c r="BJ12" s="10" t="n">
-        <v>0.0298</v>
+        <v>0.0319</v>
       </c>
       <c r="BK12" s="11" t="n">
         <v>0</v>
@@ -3131,10 +3007,10 @@
         <v>18706973</v>
       </c>
       <c r="BM12" s="9" t="n">
-        <v>297908.55</v>
+        <v>294644.18</v>
       </c>
       <c r="BN12" s="10" t="n">
-        <v>0.0319</v>
+        <v>0.0335</v>
       </c>
       <c r="BO12" s="11" t="n">
         <v>0</v>
@@ -3143,24 +3019,12 @@
         <v>18706973</v>
       </c>
       <c r="BQ12" s="9" t="n">
-        <v>294644.18</v>
+        <v>322779.47</v>
       </c>
       <c r="BR12" s="10" t="n">
-        <v>0.0335</v>
-      </c>
-      <c r="BS12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT12" s="8" t="n">
-        <v>18706973</v>
-      </c>
-      <c r="BU12" s="9" t="n">
-        <v>322779.47</v>
-      </c>
-      <c r="BV12" s="10" t="n">
         <v>0.036</v>
       </c>
-      <c r="BW12" s="11" t="n"/>
+      <c r="BS12" s="11" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -3266,10 +3130,10 @@
         <v>33244875</v>
       </c>
       <c r="AG13" s="9" t="n">
-        <v>425434.67</v>
+        <v>409842.82</v>
       </c>
       <c r="AH13" s="10" t="n">
-        <v>0.0328</v>
+        <v>0.0326</v>
       </c>
       <c r="AI13" s="11" t="n">
         <v>0</v>
@@ -3278,58 +3142,58 @@
         <v>33244875</v>
       </c>
       <c r="AK13" s="9" t="n">
-        <v>409842.82</v>
+        <v>376199.01</v>
       </c>
       <c r="AL13" s="10" t="n">
-        <v>0.0326</v>
+        <v>0.0314</v>
       </c>
       <c r="AM13" s="11" t="n">
-        <v>0</v>
+        <v>0.01837960782511803</v>
       </c>
       <c r="AN13" s="8" t="n">
-        <v>33244875</v>
+        <v>32644875</v>
       </c>
       <c r="AO13" s="9" t="n">
-        <v>376199.01</v>
+        <v>341204.23</v>
       </c>
       <c r="AP13" s="10" t="n">
-        <v>0.0314</v>
+        <v>0.0297</v>
       </c>
       <c r="AQ13" s="11" t="n">
-        <v>0.01837960782511803</v>
+        <v>0.0842854566355568</v>
       </c>
       <c r="AR13" s="8" t="n">
-        <v>32644875</v>
+        <v>30107270</v>
       </c>
       <c r="AS13" s="9" t="n">
-        <v>341204.23</v>
+        <v>321666.07</v>
       </c>
       <c r="AT13" s="10" t="n">
-        <v>0.0297</v>
+        <v>0.0284</v>
       </c>
       <c r="AU13" s="11" t="n">
-        <v>0.0842854566355568</v>
+        <v>0.1045592607036581</v>
       </c>
       <c r="AV13" s="8" t="n">
-        <v>30107270</v>
+        <v>27257270</v>
       </c>
       <c r="AW13" s="9" t="n">
-        <v>321666.07</v>
+        <v>326869.18</v>
       </c>
       <c r="AX13" s="10" t="n">
-        <v>0.0284</v>
+        <v>0.0296</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>0.1045592607036581</v>
+        <v>0</v>
       </c>
       <c r="AZ13" s="8" t="n">
         <v>27257270</v>
       </c>
       <c r="BA13" s="9" t="n">
-        <v>326869.18</v>
+        <v>324961.17</v>
       </c>
       <c r="BB13" s="10" t="n">
-        <v>0.0296</v>
+        <v>0.0313</v>
       </c>
       <c r="BC13" s="11" t="n">
         <v>0</v>
@@ -3338,10 +3202,10 @@
         <v>27257270</v>
       </c>
       <c r="BE13" s="9" t="n">
-        <v>324961.17</v>
+        <v>322998.65</v>
       </c>
       <c r="BF13" s="10" t="n">
-        <v>0.0313</v>
+        <v>0.0328</v>
       </c>
       <c r="BG13" s="11" t="n">
         <v>0</v>
@@ -3350,10 +3214,10 @@
         <v>27257270</v>
       </c>
       <c r="BI13" s="9" t="n">
-        <v>322998.65</v>
+        <v>300375.12</v>
       </c>
       <c r="BJ13" s="10" t="n">
-        <v>0.0328</v>
+        <v>0.0321</v>
       </c>
       <c r="BK13" s="11" t="n">
         <v>0</v>
@@ -3362,10 +3226,10 @@
         <v>27257270</v>
       </c>
       <c r="BM13" s="9" t="n">
-        <v>300375.12</v>
+        <v>276811.21</v>
       </c>
       <c r="BN13" s="10" t="n">
-        <v>0.0321</v>
+        <v>0.0315</v>
       </c>
       <c r="BO13" s="11" t="n">
         <v>0</v>
@@ -3374,24 +3238,12 @@
         <v>27257270</v>
       </c>
       <c r="BQ13" s="9" t="n">
-        <v>276811.21</v>
+        <v>268783.94</v>
       </c>
       <c r="BR13" s="10" t="n">
-        <v>0.0315</v>
-      </c>
-      <c r="BS13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT13" s="8" t="n">
-        <v>27257270</v>
-      </c>
-      <c r="BU13" s="9" t="n">
-        <v>268783.94</v>
-      </c>
-      <c r="BV13" s="10" t="n">
         <v>0.03</v>
       </c>
-      <c r="BW13" s="11" t="n"/>
+      <c r="BS13" s="11" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -3491,28 +3343,28 @@
         <v>0.0199</v>
       </c>
       <c r="AE14" s="11" t="n">
-        <v>-0.06831357175852101</v>
+        <v>0.7641415818860701</v>
       </c>
       <c r="AF14" s="8" t="n">
-        <v>17621740</v>
+        <v>9306473</v>
       </c>
       <c r="AG14" s="9" t="n">
-        <v>274916.77</v>
+        <v>137949.85</v>
       </c>
       <c r="AH14" s="10" t="n">
-        <v>0.0212</v>
+        <v>0.011</v>
       </c>
       <c r="AI14" s="11" t="n">
-        <v>0.8934928409505942</v>
+        <v>0</v>
       </c>
       <c r="AJ14" s="8" t="n">
         <v>9306473</v>
       </c>
       <c r="AK14" s="9" t="n">
-        <v>137949.85</v>
+        <v>134180.73</v>
       </c>
       <c r="AL14" s="10" t="n">
-        <v>0.011</v>
+        <v>0.0112</v>
       </c>
       <c r="AM14" s="11" t="n">
         <v>0</v>
@@ -3521,10 +3373,10 @@
         <v>9306473</v>
       </c>
       <c r="AO14" s="9" t="n">
-        <v>134180.73</v>
+        <v>136767.93</v>
       </c>
       <c r="AP14" s="10" t="n">
-        <v>0.0112</v>
+        <v>0.0119</v>
       </c>
       <c r="AQ14" s="11" t="n">
         <v>0</v>
@@ -3533,10 +3385,10 @@
         <v>9306473</v>
       </c>
       <c r="AS14" s="9" t="n">
-        <v>136767.93</v>
+        <v>140434.68</v>
       </c>
       <c r="AT14" s="10" t="n">
-        <v>0.0119</v>
+        <v>0.0124</v>
       </c>
       <c r="AU14" s="11" t="n">
         <v>0</v>
@@ -3545,10 +3397,10 @@
         <v>9306473</v>
       </c>
       <c r="AW14" s="9" t="n">
-        <v>140434.68</v>
+        <v>149071.08</v>
       </c>
       <c r="AX14" s="10" t="n">
-        <v>0.0124</v>
+        <v>0.0135</v>
       </c>
       <c r="AY14" s="11" t="n">
         <v>0</v>
@@ -3557,10 +3409,10 @@
         <v>9306473</v>
       </c>
       <c r="BA14" s="9" t="n">
-        <v>149071.08</v>
+        <v>145432.25</v>
       </c>
       <c r="BB14" s="10" t="n">
-        <v>0.0135</v>
+        <v>0.014</v>
       </c>
       <c r="BC14" s="11" t="n">
         <v>0</v>
@@ -3569,10 +3421,10 @@
         <v>9306473</v>
       </c>
       <c r="BE14" s="9" t="n">
-        <v>145432.25</v>
+        <v>139606.4</v>
       </c>
       <c r="BF14" s="10" t="n">
-        <v>0.014</v>
+        <v>0.0142</v>
       </c>
       <c r="BG14" s="11" t="n">
         <v>0</v>
@@ -3581,10 +3433,10 @@
         <v>9306473</v>
       </c>
       <c r="BI14" s="9" t="n">
-        <v>139606.4</v>
+        <v>146172.12</v>
       </c>
       <c r="BJ14" s="10" t="n">
-        <v>0.0142</v>
+        <v>0.0156</v>
       </c>
       <c r="BK14" s="11" t="n">
         <v>0</v>
@@ -3593,10 +3445,10 @@
         <v>9306473</v>
       </c>
       <c r="BM14" s="9" t="n">
-        <v>146172.12</v>
+        <v>157065.34</v>
       </c>
       <c r="BN14" s="10" t="n">
-        <v>0.0156</v>
+        <v>0.0178</v>
       </c>
       <c r="BO14" s="11" t="n">
         <v>0</v>
@@ -3605,24 +3457,12 @@
         <v>9306473</v>
       </c>
       <c r="BQ14" s="9" t="n">
-        <v>157065.34</v>
+        <v>174943.08</v>
       </c>
       <c r="BR14" s="10" t="n">
-        <v>0.0178</v>
-      </c>
-      <c r="BS14" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT14" s="8" t="n">
-        <v>9306473</v>
-      </c>
-      <c r="BU14" s="9" t="n">
-        <v>174943.08</v>
-      </c>
-      <c r="BV14" s="10" t="n">
         <v>0.0195</v>
       </c>
-      <c r="BW14" s="11" t="n"/>
+      <c r="BS14" s="11" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -3728,10 +3568,10 @@
         <v>21167034</v>
       </c>
       <c r="AG15" s="9" t="n">
-        <v>444846.39</v>
+        <v>434876.71</v>
       </c>
       <c r="AH15" s="10" t="n">
-        <v>0.0343</v>
+        <v>0.0346</v>
       </c>
       <c r="AI15" s="11" t="n">
         <v>0</v>
@@ -3740,10 +3580,10 @@
         <v>21167034</v>
       </c>
       <c r="AK15" s="9" t="n">
-        <v>434876.71</v>
+        <v>397601.57</v>
       </c>
       <c r="AL15" s="10" t="n">
-        <v>0.0346</v>
+        <v>0.0332</v>
       </c>
       <c r="AM15" s="11" t="n">
         <v>0</v>
@@ -3752,10 +3592,10 @@
         <v>21167034</v>
       </c>
       <c r="AO15" s="9" t="n">
-        <v>397601.57</v>
+        <v>399802.94</v>
       </c>
       <c r="AP15" s="10" t="n">
-        <v>0.0332</v>
+        <v>0.0348</v>
       </c>
       <c r="AQ15" s="11" t="n">
         <v>0</v>
@@ -3764,50 +3604,42 @@
         <v>21167034</v>
       </c>
       <c r="AS15" s="9" t="n">
-        <v>399802.94</v>
+        <v>405200.53</v>
       </c>
       <c r="AT15" s="10" t="n">
-        <v>0.0348</v>
+        <v>0.0358</v>
       </c>
       <c r="AU15" s="11" t="n">
-        <v>0</v>
+        <v>0.01098531912399817</v>
       </c>
       <c r="AV15" s="8" t="n">
-        <v>21167034</v>
+        <v>20937034</v>
       </c>
       <c r="AW15" s="9" t="n">
-        <v>405200.53</v>
+        <v>420750.64</v>
       </c>
       <c r="AX15" s="10" t="n">
-        <v>0.0358</v>
+        <v>0.0381</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>0.01098531912399817</v>
+        <v>0.7744638647975486</v>
       </c>
       <c r="AZ15" s="8" t="n">
-        <v>20937034</v>
+        <v>11799076</v>
       </c>
       <c r="BA15" s="9" t="n">
-        <v>420750.64</v>
+        <v>219014.45</v>
       </c>
       <c r="BB15" s="10" t="n">
-        <v>0.0381</v>
+        <v>0.0211</v>
       </c>
       <c r="BC15" s="11" t="n">
-        <v>0.7744638647975486</v>
-      </c>
-      <c r="BD15" s="8" t="n">
-        <v>11799076</v>
-      </c>
-      <c r="BE15" s="9" t="n">
-        <v>219014.45</v>
-      </c>
-      <c r="BF15" s="10" t="n">
-        <v>0.0211</v>
-      </c>
-      <c r="BG15" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="BD15" s="8" t="n"/>
+      <c r="BE15" s="9" t="n"/>
+      <c r="BF15" s="10" t="n"/>
+      <c r="BG15" s="11" t="n"/>
       <c r="BH15" s="8" t="n"/>
       <c r="BI15" s="9" t="n"/>
       <c r="BJ15" s="10" t="n"/>
@@ -3820,10 +3652,6 @@
       <c r="BQ15" s="9" t="n"/>
       <c r="BR15" s="10" t="n"/>
       <c r="BS15" s="11" t="n"/>
-      <c r="BT15" s="8" t="n"/>
-      <c r="BU15" s="9" t="n"/>
-      <c r="BV15" s="10" t="n"/>
-      <c r="BW15" s="11" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -3923,64 +3751,64 @@
         <v>0.0344</v>
       </c>
       <c r="AE16" s="11" t="n">
-        <v>0</v>
+        <v>0.01854138622819997</v>
       </c>
       <c r="AF16" s="8" t="n">
-        <v>2746670</v>
+        <v>2696670</v>
       </c>
       <c r="AG16" s="9" t="n">
-        <v>436720.53</v>
+        <v>436483.01</v>
       </c>
       <c r="AH16" s="10" t="n">
-        <v>0.0337</v>
+        <v>0.0347</v>
       </c>
       <c r="AI16" s="11" t="n">
-        <v>0.01854138622819997</v>
+        <v>0</v>
       </c>
       <c r="AJ16" s="8" t="n">
         <v>2696670</v>
       </c>
       <c r="AK16" s="9" t="n">
-        <v>436483.01</v>
+        <v>432249.23</v>
       </c>
       <c r="AL16" s="10" t="n">
-        <v>0.0347</v>
+        <v>0.0361</v>
       </c>
       <c r="AM16" s="11" t="n">
-        <v>0</v>
+        <v>-0.01820386140308082</v>
       </c>
       <c r="AN16" s="8" t="n">
-        <v>2696670</v>
+        <v>2746670</v>
       </c>
       <c r="AO16" s="9" t="n">
-        <v>432249.23</v>
+        <v>406259.96</v>
       </c>
       <c r="AP16" s="10" t="n">
-        <v>0.0361</v>
+        <v>0.0353</v>
       </c>
       <c r="AQ16" s="11" t="n">
-        <v>-0.01820386140308082</v>
+        <v>-0.09100927632732893</v>
       </c>
       <c r="AR16" s="8" t="n">
-        <v>2746670</v>
+        <v>3021670</v>
       </c>
       <c r="AS16" s="9" t="n">
-        <v>406259.96</v>
+        <v>380972.15</v>
       </c>
       <c r="AT16" s="10" t="n">
-        <v>0.0353</v>
+        <v>0.0336</v>
       </c>
       <c r="AU16" s="11" t="n">
-        <v>-0.09100927632732893</v>
+        <v>0</v>
       </c>
       <c r="AV16" s="8" t="n">
         <v>3021670</v>
       </c>
       <c r="AW16" s="9" t="n">
-        <v>380972.15</v>
+        <v>374687.08</v>
       </c>
       <c r="AX16" s="10" t="n">
-        <v>0.0336</v>
+        <v>0.0339</v>
       </c>
       <c r="AY16" s="11" t="n">
         <v>0</v>
@@ -3989,10 +3817,10 @@
         <v>3021670</v>
       </c>
       <c r="BA16" s="9" t="n">
-        <v>374687.08</v>
+        <v>372239.53</v>
       </c>
       <c r="BB16" s="10" t="n">
-        <v>0.0339</v>
+        <v>0.0358</v>
       </c>
       <c r="BC16" s="11" t="n">
         <v>0</v>
@@ -4001,34 +3829,34 @@
         <v>3021670</v>
       </c>
       <c r="BE16" s="9" t="n">
-        <v>372239.53</v>
+        <v>370366.09</v>
       </c>
       <c r="BF16" s="10" t="n">
-        <v>0.0358</v>
+        <v>0.0376</v>
       </c>
       <c r="BG16" s="11" t="n">
-        <v>0</v>
+        <v>0.001190161420612721</v>
       </c>
       <c r="BH16" s="8" t="n">
-        <v>3021670</v>
+        <v>3018078</v>
       </c>
       <c r="BI16" s="9" t="n">
-        <v>370366.09</v>
+        <v>347747.47</v>
       </c>
       <c r="BJ16" s="10" t="n">
-        <v>0.0376</v>
+        <v>0.0372</v>
       </c>
       <c r="BK16" s="11" t="n">
-        <v>0.001190161420612721</v>
+        <v>0</v>
       </c>
       <c r="BL16" s="8" t="n">
         <v>3018078</v>
       </c>
       <c r="BM16" s="9" t="n">
-        <v>347747.47</v>
+        <v>360535.07</v>
       </c>
       <c r="BN16" s="10" t="n">
-        <v>0.0372</v>
+        <v>0.041</v>
       </c>
       <c r="BO16" s="11" t="n">
         <v>0</v>
@@ -4037,24 +3865,12 @@
         <v>3018078</v>
       </c>
       <c r="BQ16" s="9" t="n">
-        <v>360535.07</v>
+        <v>371545.02</v>
       </c>
       <c r="BR16" s="10" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="BS16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT16" s="8" t="n">
-        <v>3018078</v>
-      </c>
-      <c r="BU16" s="9" t="n">
-        <v>371545.02</v>
-      </c>
-      <c r="BV16" s="10" t="n">
         <v>0.0414</v>
       </c>
-      <c r="BW16" s="11" t="n"/>
+      <c r="BS16" s="11" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -4154,20 +3970,12 @@
         <v>0.0112</v>
       </c>
       <c r="AE17" s="11" t="n">
-        <v>0.6557662214497397</v>
-      </c>
-      <c r="AF17" s="8" t="n">
-        <v>2811139</v>
-      </c>
-      <c r="AG17" s="9" t="n">
-        <v>88199.49000000001</v>
-      </c>
-      <c r="AH17" s="10" t="n">
-        <v>0.0068</v>
-      </c>
-      <c r="AI17" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="AF17" s="8" t="n"/>
+      <c r="AG17" s="9" t="n"/>
+      <c r="AH17" s="10" t="n"/>
+      <c r="AI17" s="11" t="n"/>
       <c r="AJ17" s="8" t="n"/>
       <c r="AK17" s="9" t="n"/>
       <c r="AL17" s="10" t="n"/>
@@ -4204,10 +4012,6 @@
       <c r="BQ17" s="9" t="n"/>
       <c r="BR17" s="10" t="n"/>
       <c r="BS17" s="11" t="n"/>
-      <c r="BT17" s="8" t="n"/>
-      <c r="BU17" s="9" t="n"/>
-      <c r="BV17" s="10" t="n"/>
-      <c r="BW17" s="11" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -4307,138 +4111,126 @@
         <v>0.0123</v>
       </c>
       <c r="AE18" s="11" t="n">
-        <v>0.02860906275493533</v>
+        <v>0.1359983309421211</v>
       </c>
       <c r="AF18" s="8" t="n">
-        <v>17405149</v>
+        <v>15759789</v>
       </c>
       <c r="AG18" s="9" t="n">
-        <v>164043.53</v>
+        <v>153571.26</v>
       </c>
       <c r="AH18" s="10" t="n">
+        <v>0.0122</v>
+      </c>
+      <c r="AI18" s="11" t="n">
+        <v>0.04036608437732761</v>
+      </c>
+      <c r="AJ18" s="8" t="n">
+        <v>15148311</v>
+      </c>
+      <c r="AK18" s="9" t="n">
+        <v>148741.27</v>
+      </c>
+      <c r="AL18" s="10" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="AM18" s="11" t="n">
+        <v>0.02447981732333564</v>
+      </c>
+      <c r="AN18" s="8" t="n">
+        <v>14786344</v>
+      </c>
+      <c r="AO18" s="9" t="n">
+        <v>145061.43</v>
+      </c>
+      <c r="AP18" s="10" t="n">
         <v>0.0126</v>
       </c>
-      <c r="AI18" s="11" t="n">
-        <v>0.1044024130018492</v>
-      </c>
-      <c r="AJ18" s="8" t="n">
-        <v>15759789</v>
-      </c>
-      <c r="AK18" s="9" t="n">
-        <v>153571.26</v>
-      </c>
-      <c r="AL18" s="10" t="n">
-        <v>0.0122</v>
-      </c>
-      <c r="AM18" s="11" t="n">
-        <v>0.04036608437732761</v>
-      </c>
-      <c r="AN18" s="8" t="n">
-        <v>15148311</v>
-      </c>
-      <c r="AO18" s="9" t="n">
-        <v>148741.27</v>
-      </c>
-      <c r="AP18" s="10" t="n">
+      <c r="AQ18" s="11" t="n">
+        <v>0.02183487170521033</v>
+      </c>
+      <c r="AR18" s="8" t="n">
+        <v>14470385</v>
+      </c>
+      <c r="AS18" s="9" t="n">
+        <v>140333.79</v>
+      </c>
+      <c r="AT18" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="AQ18" s="11" t="n">
-        <v>0.02447981732333564</v>
-      </c>
-      <c r="AR18" s="8" t="n">
-        <v>14786344</v>
-      </c>
-      <c r="AS18" s="9" t="n">
-        <v>145061.43</v>
-      </c>
-      <c r="AT18" s="10" t="n">
-        <v>0.0126</v>
-      </c>
       <c r="AU18" s="11" t="n">
-        <v>0.02183487170521033</v>
+        <v>0.01486488524161312</v>
       </c>
       <c r="AV18" s="8" t="n">
-        <v>14470385</v>
+        <v>14258435</v>
       </c>
       <c r="AW18" s="9" t="n">
-        <v>140333.79</v>
+        <v>141151.38</v>
       </c>
       <c r="AX18" s="10" t="n">
-        <v>0.0124</v>
+        <v>0.0128</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.01486488524161312</v>
+        <v>0</v>
       </c>
       <c r="AZ18" s="8" t="n">
         <v>14258435</v>
       </c>
       <c r="BA18" s="9" t="n">
-        <v>141151.38</v>
+        <v>132603.45</v>
       </c>
       <c r="BB18" s="10" t="n">
         <v>0.0128</v>
       </c>
       <c r="BC18" s="11" t="n">
-        <v>0</v>
+        <v>0.0231160633003793</v>
       </c>
       <c r="BD18" s="8" t="n">
-        <v>14258435</v>
+        <v>13936283</v>
       </c>
       <c r="BE18" s="9" t="n">
-        <v>132603.45</v>
+        <v>123789.03</v>
       </c>
       <c r="BF18" s="10" t="n">
-        <v>0.0128</v>
+        <v>0.0126</v>
       </c>
       <c r="BG18" s="11" t="n">
-        <v>0.0231160633003793</v>
+        <v>0.07172012123664578</v>
       </c>
       <c r="BH18" s="8" t="n">
-        <v>13936283</v>
+        <v>13003659</v>
       </c>
       <c r="BI18" s="9" t="n">
-        <v>123789.03</v>
+        <v>115264.43</v>
       </c>
       <c r="BJ18" s="10" t="n">
-        <v>0.0126</v>
+        <v>0.0123</v>
       </c>
       <c r="BK18" s="11" t="n">
-        <v>0.07172012123664578</v>
+        <v>0.132761983775747</v>
       </c>
       <c r="BL18" s="8" t="n">
-        <v>13003659</v>
+        <v>11479604</v>
       </c>
       <c r="BM18" s="9" t="n">
-        <v>115264.43</v>
+        <v>100630.21</v>
       </c>
       <c r="BN18" s="10" t="n">
-        <v>0.0123</v>
+        <v>0.0114</v>
       </c>
       <c r="BO18" s="11" t="n">
-        <v>0.132761983775747</v>
+        <v>0.2957940438149267</v>
       </c>
       <c r="BP18" s="8" t="n">
-        <v>11479604</v>
+        <v>8859127</v>
       </c>
       <c r="BQ18" s="9" t="n">
-        <v>100630.21</v>
+        <v>85955.67999999999</v>
       </c>
       <c r="BR18" s="10" t="n">
-        <v>0.0114</v>
-      </c>
-      <c r="BS18" s="11" t="n">
-        <v>0.2957940438149267</v>
-      </c>
-      <c r="BT18" s="8" t="n">
-        <v>8859127</v>
-      </c>
-      <c r="BU18" s="9" t="n">
-        <v>85955.67999999999</v>
-      </c>
-      <c r="BV18" s="10" t="n">
         <v>0.009599999999999999</v>
       </c>
-      <c r="BW18" s="11" t="n"/>
+      <c r="BS18" s="11" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -4538,138 +4330,126 @@
         <v>0.0125</v>
       </c>
       <c r="AE19" s="11" t="n">
-        <v>0.02078030694418823</v>
+        <v>0.08022088846862326</v>
       </c>
       <c r="AF19" s="8" t="n">
-        <v>10765866</v>
+        <v>10173460</v>
       </c>
       <c r="AG19" s="9" t="n">
-        <v>164857.71</v>
+        <v>152734.15</v>
       </c>
       <c r="AH19" s="10" t="n">
-        <v>0.0127</v>
+        <v>0.0121</v>
       </c>
       <c r="AI19" s="11" t="n">
-        <v>0.05823053317160534</v>
+        <v>0.01848262661129821</v>
       </c>
       <c r="AJ19" s="8" t="n">
-        <v>10173460</v>
+        <v>9988840</v>
       </c>
       <c r="AK19" s="9" t="n">
-        <v>152734.15</v>
+        <v>150162.23</v>
       </c>
       <c r="AL19" s="10" t="n">
-        <v>0.0121</v>
+        <v>0.0125</v>
       </c>
       <c r="AM19" s="11" t="n">
-        <v>0.01848262661129821</v>
+        <v>0.11089473889663</v>
       </c>
       <c r="AN19" s="8" t="n">
-        <v>9988840</v>
+        <v>8991707</v>
       </c>
       <c r="AO19" s="9" t="n">
-        <v>150162.23</v>
+        <v>142914.19</v>
       </c>
       <c r="AP19" s="10" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="AQ19" s="11" t="n">
+        <v>-0.04856779498084111</v>
+      </c>
+      <c r="AR19" s="8" t="n">
+        <v>9450707</v>
+      </c>
+      <c r="AS19" s="9" t="n">
+        <v>146920.69</v>
+      </c>
+      <c r="AT19" s="10" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="AU19" s="11" t="n">
+        <v>0.03318890177940083</v>
+      </c>
+      <c r="AV19" s="8" t="n">
+        <v>9147124</v>
+      </c>
+      <c r="AW19" s="9" t="n">
+        <v>137746.54</v>
+      </c>
+      <c r="AX19" s="10" t="n">
         <v>0.0125</v>
       </c>
-      <c r="AQ19" s="11" t="n">
-        <v>0.11089473889663</v>
-      </c>
-      <c r="AR19" s="8" t="n">
-        <v>8991707</v>
-      </c>
-      <c r="AS19" s="9" t="n">
-        <v>142914.19</v>
-      </c>
-      <c r="AT19" s="10" t="n">
-        <v>0.0124</v>
-      </c>
-      <c r="AU19" s="11" t="n">
-        <v>-0.04856779498084111</v>
-      </c>
-      <c r="AV19" s="8" t="n">
-        <v>9450707</v>
-      </c>
-      <c r="AW19" s="9" t="n">
-        <v>146920.69</v>
-      </c>
-      <c r="AX19" s="10" t="n">
-        <v>0.013</v>
-      </c>
       <c r="AY19" s="11" t="n">
-        <v>0.03318890177940083</v>
+        <v>0.0298589752957666</v>
       </c>
       <c r="AZ19" s="8" t="n">
-        <v>9147124</v>
+        <v>8881919</v>
       </c>
       <c r="BA19" s="9" t="n">
-        <v>137746.54</v>
+        <v>130182.29</v>
       </c>
       <c r="BB19" s="10" t="n">
         <v>0.0125</v>
       </c>
       <c r="BC19" s="11" t="n">
-        <v>0.0298589752957666</v>
+        <v>0.1110462167918367</v>
       </c>
       <c r="BD19" s="8" t="n">
-        <v>8881919</v>
+        <v>7994194</v>
       </c>
       <c r="BE19" s="9" t="n">
-        <v>130182.29</v>
+        <v>123918</v>
       </c>
       <c r="BF19" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.0126</v>
       </c>
       <c r="BG19" s="11" t="n">
-        <v>0.1110462167918367</v>
+        <v>0</v>
       </c>
       <c r="BH19" s="8" t="n">
         <v>7994194</v>
       </c>
       <c r="BI19" s="9" t="n">
-        <v>123918</v>
+        <v>115292.27</v>
       </c>
       <c r="BJ19" s="10" t="n">
-        <v>0.0126</v>
+        <v>0.0123</v>
       </c>
       <c r="BK19" s="11" t="n">
-        <v>0</v>
+        <v>0.03077033965211765</v>
       </c>
       <c r="BL19" s="8" t="n">
-        <v>7994194</v>
+        <v>7755553</v>
       </c>
       <c r="BM19" s="9" t="n">
-        <v>115292.27</v>
+        <v>109159.41</v>
       </c>
       <c r="BN19" s="10" t="n">
-        <v>0.0123</v>
+        <v>0.0124</v>
       </c>
       <c r="BO19" s="11" t="n">
-        <v>0.03077033965211765</v>
+        <v>0.2461624388271065</v>
       </c>
       <c r="BP19" s="8" t="n">
-        <v>7755553</v>
+        <v>6223549</v>
       </c>
       <c r="BQ19" s="9" t="n">
-        <v>109159.41</v>
+        <v>92071.17999999999</v>
       </c>
       <c r="BR19" s="10" t="n">
-        <v>0.0124</v>
-      </c>
-      <c r="BS19" s="11" t="n">
-        <v>0.2461624388271065</v>
-      </c>
-      <c r="BT19" s="8" t="n">
-        <v>6223549</v>
-      </c>
-      <c r="BU19" s="9" t="n">
-        <v>92071.17999999999</v>
-      </c>
-      <c r="BV19" s="10" t="n">
         <v>0.0103</v>
       </c>
-      <c r="BW19" s="11" t="n"/>
+      <c r="BS19" s="11" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -4769,138 +4549,126 @@
         <v>0.0125</v>
       </c>
       <c r="AE20" s="11" t="n">
-        <v>0</v>
+        <v>0.02739609151703509</v>
       </c>
       <c r="AF20" s="8" t="n">
-        <v>13125545</v>
+        <v>12775545</v>
       </c>
       <c r="AG20" s="9" t="n">
-        <v>165224.36</v>
+        <v>152999.93</v>
       </c>
       <c r="AH20" s="10" t="n">
+        <v>0.0122</v>
+      </c>
+      <c r="AI20" s="11" t="n">
+        <v>0.05513752418556975</v>
+      </c>
+      <c r="AJ20" s="8" t="n">
+        <v>12107943</v>
+      </c>
+      <c r="AK20" s="9" t="n">
+        <v>148164.9</v>
+      </c>
+      <c r="AL20" s="10" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="AM20" s="11" t="n">
+        <v>0.04083231560577577</v>
+      </c>
+      <c r="AN20" s="8" t="n">
+        <v>11632943</v>
+      </c>
+      <c r="AO20" s="9" t="n">
+        <v>146586.71</v>
+      </c>
+      <c r="AP20" s="10" t="n">
         <v>0.0127</v>
       </c>
-      <c r="AI20" s="11" t="n">
-        <v>0.02739609151703509</v>
-      </c>
-      <c r="AJ20" s="8" t="n">
-        <v>12775545</v>
-      </c>
-      <c r="AK20" s="9" t="n">
-        <v>152999.93</v>
-      </c>
-      <c r="AL20" s="10" t="n">
-        <v>0.0122</v>
-      </c>
-      <c r="AM20" s="11" t="n">
-        <v>0.05513752418556975</v>
-      </c>
-      <c r="AN20" s="8" t="n">
-        <v>12107943</v>
-      </c>
-      <c r="AO20" s="9" t="n">
-        <v>148164.9</v>
-      </c>
-      <c r="AP20" s="10" t="n">
-        <v>0.0124</v>
-      </c>
       <c r="AQ20" s="11" t="n">
-        <v>0.04083231560577577</v>
+        <v>0.037023978878946</v>
       </c>
       <c r="AR20" s="8" t="n">
-        <v>11632943</v>
+        <v>11217622</v>
       </c>
       <c r="AS20" s="9" t="n">
-        <v>146586.71</v>
+        <v>142497.45</v>
       </c>
       <c r="AT20" s="10" t="n">
-        <v>0.0127</v>
+        <v>0.0126</v>
       </c>
       <c r="AU20" s="11" t="n">
-        <v>0.037023978878946</v>
+        <v>0.08471904462602137</v>
       </c>
       <c r="AV20" s="8" t="n">
-        <v>11217622</v>
+        <v>10341500</v>
       </c>
       <c r="AW20" s="9" t="n">
-        <v>142497.45</v>
+        <v>132712.47</v>
       </c>
       <c r="AX20" s="10" t="n">
-        <v>0.0126</v>
+        <v>0.012</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>0.08471904462602137</v>
+        <v>0</v>
       </c>
       <c r="AZ20" s="8" t="n">
         <v>10341500</v>
       </c>
       <c r="BA20" s="9" t="n">
-        <v>132712.47</v>
+        <v>129392.85</v>
       </c>
       <c r="BB20" s="10" t="n">
-        <v>0.012</v>
+        <v>0.0125</v>
       </c>
       <c r="BC20" s="11" t="n">
-        <v>0</v>
+        <v>-0.005975775856020039</v>
       </c>
       <c r="BD20" s="8" t="n">
-        <v>10341500</v>
+        <v>10403670</v>
       </c>
       <c r="BE20" s="9" t="n">
-        <v>129392.85</v>
+        <v>123169.05</v>
       </c>
       <c r="BF20" s="10" t="n">
         <v>0.0125</v>
       </c>
       <c r="BG20" s="11" t="n">
-        <v>-0.005975775856020039</v>
+        <v>0.02666147990782253</v>
       </c>
       <c r="BH20" s="8" t="n">
-        <v>10403670</v>
+        <v>10133496</v>
       </c>
       <c r="BI20" s="9" t="n">
-        <v>123169.05</v>
+        <v>115947.46</v>
       </c>
       <c r="BJ20" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.0124</v>
       </c>
       <c r="BK20" s="11" t="n">
-        <v>0.02666147990782253</v>
+        <v>0.02236244056730923</v>
       </c>
       <c r="BL20" s="8" t="n">
-        <v>10133496</v>
+        <v>9911843</v>
       </c>
       <c r="BM20" s="9" t="n">
-        <v>115947.46</v>
+        <v>110665.73</v>
       </c>
       <c r="BN20" s="10" t="n">
-        <v>0.0124</v>
+        <v>0.0126</v>
       </c>
       <c r="BO20" s="11" t="n">
-        <v>0.02236244056730923</v>
+        <v>0.3415700706027321</v>
       </c>
       <c r="BP20" s="8" t="n">
-        <v>9911843</v>
+        <v>7388241</v>
       </c>
       <c r="BQ20" s="9" t="n">
-        <v>110665.73</v>
+        <v>89940.75</v>
       </c>
       <c r="BR20" s="10" t="n">
-        <v>0.0126</v>
-      </c>
-      <c r="BS20" s="11" t="n">
-        <v>0.3415700706027321</v>
-      </c>
-      <c r="BT20" s="8" t="n">
-        <v>7388241</v>
-      </c>
-      <c r="BU20" s="9" t="n">
-        <v>89940.75</v>
-      </c>
-      <c r="BV20" s="10" t="n">
         <v>0.01</v>
       </c>
-      <c r="BW20" s="11" t="n"/>
+      <c r="BS20" s="11" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -5026,10 +4794,6 @@
       <c r="BQ21" s="9" t="n"/>
       <c r="BR21" s="10" t="n"/>
       <c r="BS21" s="11" t="n"/>
-      <c r="BT21" s="8" t="n"/>
-      <c r="BU21" s="9" t="n"/>
-      <c r="BV21" s="10" t="n"/>
-      <c r="BW21" s="11" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -5135,10 +4899,10 @@
         <v>22000000</v>
       </c>
       <c r="AG22" s="9" t="n">
-        <v>94699</v>
+        <v>104852</v>
       </c>
       <c r="AH22" s="10" t="n">
-        <v>0.0073</v>
+        <v>0.0083</v>
       </c>
       <c r="AI22" s="11" t="n">
         <v>0</v>
@@ -5147,26 +4911,18 @@
         <v>22000000</v>
       </c>
       <c r="AK22" s="9" t="n">
-        <v>104852</v>
+        <v>100584</v>
       </c>
       <c r="AL22" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="AM22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN22" s="8" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="AO22" s="9" t="n">
-        <v>100584</v>
-      </c>
-      <c r="AP22" s="10" t="n">
-        <v>0.008399999999999999</v>
-      </c>
-      <c r="AQ22" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="AN22" s="8" t="n"/>
+      <c r="AO22" s="9" t="n"/>
+      <c r="AP22" s="10" t="n"/>
+      <c r="AQ22" s="11" t="n"/>
       <c r="AR22" s="8" t="n"/>
       <c r="AS22" s="9" t="n"/>
       <c r="AT22" s="10" t="n"/>
@@ -5195,10 +4951,6 @@
       <c r="BQ22" s="9" t="n"/>
       <c r="BR22" s="10" t="n"/>
       <c r="BS22" s="11" t="n"/>
-      <c r="BT22" s="8" t="n"/>
-      <c r="BU22" s="9" t="n"/>
-      <c r="BV22" s="10" t="n"/>
-      <c r="BW22" s="11" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -5304,10 +5056,10 @@
         <v>80755676</v>
       </c>
       <c r="AG23" s="9" t="n">
-        <v>112484.58</v>
+        <v>112298.84</v>
       </c>
       <c r="AH23" s="10" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0089</v>
       </c>
       <c r="AI23" s="11" t="n">
         <v>0</v>
@@ -5316,46 +5068,46 @@
         <v>80755676</v>
       </c>
       <c r="AK23" s="9" t="n">
-        <v>112298.84</v>
+        <v>112403.83</v>
       </c>
       <c r="AL23" s="10" t="n">
+        <v>0.0094</v>
+      </c>
+      <c r="AM23" s="11" t="n">
+        <v>0.09854178046374168</v>
+      </c>
+      <c r="AN23" s="8" t="n">
+        <v>73511702</v>
+      </c>
+      <c r="AO23" s="9" t="n">
+        <v>102769.36</v>
+      </c>
+      <c r="AP23" s="10" t="n">
         <v>0.0089</v>
       </c>
-      <c r="AM23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN23" s="8" t="n">
-        <v>80755676</v>
-      </c>
-      <c r="AO23" s="9" t="n">
-        <v>112403.83</v>
-      </c>
-      <c r="AP23" s="10" t="n">
-        <v>0.0094</v>
-      </c>
       <c r="AQ23" s="11" t="n">
-        <v>0.09854178046374168</v>
+        <v>0.6629129724205788</v>
       </c>
       <c r="AR23" s="8" t="n">
-        <v>73511702</v>
+        <v>44206584</v>
       </c>
       <c r="AS23" s="9" t="n">
-        <v>102769.36</v>
+        <v>59811.51</v>
       </c>
       <c r="AT23" s="10" t="n">
-        <v>0.0089</v>
+        <v>0.0053</v>
       </c>
       <c r="AU23" s="11" t="n">
-        <v>0.6629129724205788</v>
+        <v>0</v>
       </c>
       <c r="AV23" s="8" t="n">
         <v>44206584</v>
       </c>
       <c r="AW23" s="9" t="n">
-        <v>59811.51</v>
+        <v>85367.33</v>
       </c>
       <c r="AX23" s="10" t="n">
-        <v>0.0053</v>
+        <v>0.0077</v>
       </c>
       <c r="AY23" s="11" t="n">
         <v>0</v>
@@ -5364,10 +5116,10 @@
         <v>44206584</v>
       </c>
       <c r="BA23" s="9" t="n">
-        <v>85367.33</v>
+        <v>88656.3</v>
       </c>
       <c r="BB23" s="10" t="n">
-        <v>0.0077</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="BC23" s="11" t="n">
         <v>0</v>
@@ -5376,7 +5128,7 @@
         <v>44206584</v>
       </c>
       <c r="BE23" s="9" t="n">
-        <v>88656.3</v>
+        <v>84147.23</v>
       </c>
       <c r="BF23" s="10" t="n">
         <v>0.008500000000000001</v>
@@ -5388,10 +5140,10 @@
         <v>44206584</v>
       </c>
       <c r="BI23" s="9" t="n">
-        <v>84147.23</v>
+        <v>77701.91</v>
       </c>
       <c r="BJ23" s="10" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0083</v>
       </c>
       <c r="BK23" s="11" t="n">
         <v>0</v>
@@ -5400,10 +5152,10 @@
         <v>44206584</v>
       </c>
       <c r="BM23" s="9" t="n">
-        <v>77701.91</v>
+        <v>68931.33</v>
       </c>
       <c r="BN23" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.0078</v>
       </c>
       <c r="BO23" s="11" t="n">
         <v>0</v>
@@ -5412,24 +5164,12 @@
         <v>44206584</v>
       </c>
       <c r="BQ23" s="9" t="n">
-        <v>68931.33</v>
+        <v>77184.7</v>
       </c>
       <c r="BR23" s="10" t="n">
-        <v>0.0078</v>
-      </c>
-      <c r="BS23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT23" s="8" t="n">
-        <v>44206584</v>
-      </c>
-      <c r="BU23" s="9" t="n">
-        <v>77184.7</v>
-      </c>
-      <c r="BV23" s="10" t="n">
         <v>0.0086</v>
       </c>
-      <c r="BW23" s="11" t="n"/>
+      <c r="BS23" s="11" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -5529,138 +5269,126 @@
         <v>0.0048</v>
       </c>
       <c r="AE24" s="11" t="n">
-        <v>0.05773144178420389</v>
+        <v>0.1179022784593063</v>
       </c>
       <c r="AF24" s="8" t="n">
-        <v>5842830</v>
+        <v>5528341</v>
       </c>
       <c r="AG24" s="9" t="n">
-        <v>60233.73</v>
+        <v>59285.93</v>
       </c>
       <c r="AH24" s="10" t="n">
-        <v>0.0046</v>
+        <v>0.0047</v>
       </c>
       <c r="AI24" s="11" t="n">
-        <v>0.05688668625904227</v>
+        <v>0.1065051605034048</v>
       </c>
       <c r="AJ24" s="8" t="n">
-        <v>5528341</v>
+        <v>4996218</v>
       </c>
       <c r="AK24" s="9" t="n">
-        <v>59285.93</v>
+        <v>51236.22</v>
       </c>
       <c r="AL24" s="10" t="n">
-        <v>0.0047</v>
+        <v>0.0043</v>
       </c>
       <c r="AM24" s="11" t="n">
-        <v>0.1065051605034048</v>
+        <v>0.1269063080091213</v>
       </c>
       <c r="AN24" s="8" t="n">
-        <v>4996218</v>
+        <v>4433570</v>
       </c>
       <c r="AO24" s="9" t="n">
-        <v>51236.22</v>
+        <v>49913.13</v>
       </c>
       <c r="AP24" s="10" t="n">
         <v>0.0043</v>
       </c>
       <c r="AQ24" s="11" t="n">
-        <v>0.1269063080091213</v>
+        <v>0.1091786303542636</v>
       </c>
       <c r="AR24" s="8" t="n">
-        <v>4433570</v>
+        <v>3997165</v>
       </c>
       <c r="AS24" s="9" t="n">
-        <v>49913.13</v>
+        <v>49305.03</v>
       </c>
       <c r="AT24" s="10" t="n">
-        <v>0.0043</v>
+        <v>0.0044</v>
       </c>
       <c r="AU24" s="11" t="n">
-        <v>0.1091786303542636</v>
+        <v>0.136585363079533</v>
       </c>
       <c r="AV24" s="8" t="n">
-        <v>3997165</v>
+        <v>3516819</v>
       </c>
       <c r="AW24" s="9" t="n">
-        <v>49305.03</v>
+        <v>39036.69</v>
       </c>
       <c r="AX24" s="10" t="n">
-        <v>0.0044</v>
+        <v>0.0035</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.136585363079533</v>
+        <v>0.08443118240843069</v>
       </c>
       <c r="AZ24" s="8" t="n">
-        <v>3516819</v>
+        <v>3243008</v>
       </c>
       <c r="BA24" s="9" t="n">
-        <v>39036.69</v>
+        <v>30813.44</v>
       </c>
       <c r="BB24" s="10" t="n">
-        <v>0.0035</v>
+        <v>0.003</v>
       </c>
       <c r="BC24" s="11" t="n">
-        <v>0.08443118240843069</v>
+        <v>0.08526813218218672</v>
       </c>
       <c r="BD24" s="8" t="n">
-        <v>3243008</v>
+        <v>2988209</v>
       </c>
       <c r="BE24" s="9" t="n">
-        <v>30813.44</v>
+        <v>24424.13</v>
       </c>
       <c r="BF24" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0025</v>
       </c>
       <c r="BG24" s="11" t="n">
-        <v>0.08526813218218672</v>
+        <v>0.05097801295341799</v>
       </c>
       <c r="BH24" s="8" t="n">
-        <v>2988209</v>
+        <v>2843265</v>
       </c>
       <c r="BI24" s="9" t="n">
-        <v>24424.13</v>
+        <v>22336.69</v>
       </c>
       <c r="BJ24" s="10" t="n">
-        <v>0.0025</v>
+        <v>0.0024</v>
       </c>
       <c r="BK24" s="11" t="n">
-        <v>0.05097801295341799</v>
+        <v>0.08976771675272589</v>
       </c>
       <c r="BL24" s="8" t="n">
-        <v>2843265</v>
+        <v>2609056</v>
       </c>
       <c r="BM24" s="9" t="n">
-        <v>22336.69</v>
+        <v>17326.74</v>
       </c>
       <c r="BN24" s="10" t="n">
-        <v>0.0024</v>
+        <v>0.002</v>
       </c>
       <c r="BO24" s="11" t="n">
-        <v>0.08976771675272589</v>
+        <v>0.1546891810734174</v>
       </c>
       <c r="BP24" s="8" t="n">
-        <v>2609056</v>
+        <v>2259531</v>
       </c>
       <c r="BQ24" s="9" t="n">
-        <v>17326.74</v>
+        <v>18525.89</v>
       </c>
       <c r="BR24" s="10" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="BS24" s="11" t="n">
-        <v>0.1546891810734174</v>
-      </c>
-      <c r="BT24" s="8" t="n">
-        <v>2259531</v>
-      </c>
-      <c r="BU24" s="9" t="n">
-        <v>18525.89</v>
-      </c>
-      <c r="BV24" s="10" t="n">
         <v>0.0021</v>
       </c>
-      <c r="BW24" s="11" t="n"/>
+      <c r="BS24" s="11" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -5766,10 +5494,10 @@
         <v>1995914</v>
       </c>
       <c r="AG25" s="9" t="n">
-        <v>38830.51</v>
+        <v>35076.19</v>
       </c>
       <c r="AH25" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0028</v>
       </c>
       <c r="AI25" s="11" t="n">
         <v>0</v>
@@ -5778,10 +5506,10 @@
         <v>1995914</v>
       </c>
       <c r="AK25" s="9" t="n">
-        <v>35076.19</v>
+        <v>34681</v>
       </c>
       <c r="AL25" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.0029</v>
       </c>
       <c r="AM25" s="11" t="n">
         <v>0</v>
@@ -5790,10 +5518,10 @@
         <v>1995914</v>
       </c>
       <c r="AO25" s="9" t="n">
-        <v>34681</v>
+        <v>35004.34</v>
       </c>
       <c r="AP25" s="10" t="n">
-        <v>0.0029</v>
+        <v>0.003</v>
       </c>
       <c r="AQ25" s="11" t="n">
         <v>0</v>
@@ -5802,10 +5530,10 @@
         <v>1995914</v>
       </c>
       <c r="AS25" s="9" t="n">
-        <v>35004.34</v>
+        <v>38225.74</v>
       </c>
       <c r="AT25" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0034</v>
       </c>
       <c r="AU25" s="11" t="n">
         <v>0</v>
@@ -5814,10 +5542,10 @@
         <v>1995914</v>
       </c>
       <c r="AW25" s="9" t="n">
-        <v>38225.74</v>
+        <v>43319.32</v>
       </c>
       <c r="AX25" s="10" t="n">
-        <v>0.0034</v>
+        <v>0.0039</v>
       </c>
       <c r="AY25" s="11" t="n">
         <v>0</v>
@@ -5826,10 +5554,10 @@
         <v>1995914</v>
       </c>
       <c r="BA25" s="9" t="n">
-        <v>43319.32</v>
+        <v>34806.74</v>
       </c>
       <c r="BB25" s="10" t="n">
-        <v>0.0039</v>
+        <v>0.0034</v>
       </c>
       <c r="BC25" s="11" t="n">
         <v>0</v>
@@ -5838,10 +5566,10 @@
         <v>1995914</v>
       </c>
       <c r="BE25" s="9" t="n">
-        <v>34806.74</v>
+        <v>35138.07</v>
       </c>
       <c r="BF25" s="10" t="n">
-        <v>0.0034</v>
+        <v>0.0036</v>
       </c>
       <c r="BG25" s="11" t="n">
         <v>0</v>
@@ -5850,7 +5578,7 @@
         <v>1995914</v>
       </c>
       <c r="BI25" s="9" t="n">
-        <v>35138.07</v>
+        <v>33771.86</v>
       </c>
       <c r="BJ25" s="10" t="n">
         <v>0.0036</v>
@@ -5862,10 +5590,10 @@
         <v>1995914</v>
       </c>
       <c r="BM25" s="9" t="n">
-        <v>33771.86</v>
+        <v>28830.98</v>
       </c>
       <c r="BN25" s="10" t="n">
-        <v>0.0036</v>
+        <v>0.0033</v>
       </c>
       <c r="BO25" s="11" t="n">
         <v>0</v>
@@ -5874,24 +5602,12 @@
         <v>1995914</v>
       </c>
       <c r="BQ25" s="9" t="n">
-        <v>28830.98</v>
+        <v>27686.32</v>
       </c>
       <c r="BR25" s="10" t="n">
-        <v>0.0033</v>
-      </c>
-      <c r="BS25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT25" s="8" t="n">
-        <v>1995914</v>
-      </c>
-      <c r="BU25" s="9" t="n">
-        <v>27686.32</v>
-      </c>
-      <c r="BV25" s="10" t="n">
         <v>0.0031</v>
       </c>
-      <c r="BW25" s="11" t="n"/>
+      <c r="BS25" s="11" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -6033,10 +5749,6 @@
       <c r="BQ26" s="9" t="n"/>
       <c r="BR26" s="10" t="n"/>
       <c r="BS26" s="11" t="n"/>
-      <c r="BT26" s="8" t="n"/>
-      <c r="BU26" s="9" t="n"/>
-      <c r="BV26" s="10" t="n"/>
-      <c r="BW26" s="11" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -6142,10 +5854,10 @@
         <v>2264603</v>
       </c>
       <c r="AG27" s="9" t="n">
-        <v>36623.16</v>
+        <v>35943.78</v>
       </c>
       <c r="AH27" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.0029</v>
       </c>
       <c r="AI27" s="11" t="n">
         <v>0</v>
@@ -6154,10 +5866,10 @@
         <v>2264603</v>
       </c>
       <c r="AK27" s="9" t="n">
-        <v>35943.78</v>
+        <v>33031.5</v>
       </c>
       <c r="AL27" s="10" t="n">
-        <v>0.0029</v>
+        <v>0.0028</v>
       </c>
       <c r="AM27" s="11" t="n">
         <v>0</v>
@@ -6166,7 +5878,7 @@
         <v>2264603</v>
       </c>
       <c r="AO27" s="9" t="n">
-        <v>33031.5</v>
+        <v>32257.01</v>
       </c>
       <c r="AP27" s="10" t="n">
         <v>0.0028</v>
@@ -6178,10 +5890,10 @@
         <v>2264603</v>
       </c>
       <c r="AS27" s="9" t="n">
-        <v>32257.01</v>
+        <v>33534.24</v>
       </c>
       <c r="AT27" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.003</v>
       </c>
       <c r="AU27" s="11" t="n">
         <v>0</v>
@@ -6190,10 +5902,10 @@
         <v>2264603</v>
       </c>
       <c r="AW27" s="9" t="n">
-        <v>33534.24</v>
+        <v>40626.98</v>
       </c>
       <c r="AX27" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0037</v>
       </c>
       <c r="AY27" s="11" t="n">
         <v>0</v>
@@ -6202,10 +5914,10 @@
         <v>2264603</v>
       </c>
       <c r="BA27" s="9" t="n">
-        <v>40626.98</v>
+        <v>34641.63</v>
       </c>
       <c r="BB27" s="10" t="n">
-        <v>0.0037</v>
+        <v>0.0033</v>
       </c>
       <c r="BC27" s="11" t="n">
         <v>0</v>
@@ -6214,10 +5926,10 @@
         <v>2264603</v>
       </c>
       <c r="BE27" s="9" t="n">
-        <v>34641.63</v>
+        <v>29892.76</v>
       </c>
       <c r="BF27" s="10" t="n">
-        <v>0.0033</v>
+        <v>0.003</v>
       </c>
       <c r="BG27" s="11" t="n">
         <v>0</v>
@@ -6226,7 +5938,7 @@
         <v>2264603</v>
       </c>
       <c r="BI27" s="9" t="n">
-        <v>29892.76</v>
+        <v>27629.29</v>
       </c>
       <c r="BJ27" s="10" t="n">
         <v>0.003</v>
@@ -6238,10 +5950,10 @@
         <v>2264603</v>
       </c>
       <c r="BM27" s="9" t="n">
-        <v>27629.29</v>
+        <v>25089.54</v>
       </c>
       <c r="BN27" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0029</v>
       </c>
       <c r="BO27" s="11" t="n">
         <v>0</v>
@@ -6250,24 +5962,12 @@
         <v>2264603</v>
       </c>
       <c r="BQ27" s="9" t="n">
-        <v>25089.54</v>
+        <v>29659.51</v>
       </c>
       <c r="BR27" s="10" t="n">
-        <v>0.0029</v>
-      </c>
-      <c r="BS27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT27" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="BU27" s="9" t="n">
-        <v>29659.51</v>
-      </c>
-      <c r="BV27" s="10" t="n">
         <v>0.0033</v>
       </c>
-      <c r="BW27" s="11" t="n"/>
+      <c r="BS27" s="11" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -6361,10 +6061,6 @@
       <c r="BQ28" s="9" t="n"/>
       <c r="BR28" s="10" t="n"/>
       <c r="BS28" s="11" t="n"/>
-      <c r="BT28" s="8" t="n"/>
-      <c r="BU28" s="9" t="n"/>
-      <c r="BV28" s="10" t="n"/>
-      <c r="BW28" s="11" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -6498,10 +6194,6 @@
       <c r="BQ29" s="9" t="n"/>
       <c r="BR29" s="10" t="n"/>
       <c r="BS29" s="11" t="n"/>
-      <c r="BT29" s="8" t="n"/>
-      <c r="BU29" s="9" t="n"/>
-      <c r="BV29" s="10" t="n"/>
-      <c r="BW29" s="11" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -6627,10 +6319,6 @@
       <c r="BQ30" s="9" t="n"/>
       <c r="BR30" s="10" t="n"/>
       <c r="BS30" s="11" t="n"/>
-      <c r="BT30" s="8" t="n"/>
-      <c r="BU30" s="9" t="n"/>
-      <c r="BV30" s="10" t="n"/>
-      <c r="BW30" s="11" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -6736,10 +6424,10 @@
         <v>287393</v>
       </c>
       <c r="AG31" s="9" t="n">
-        <v>17812.62</v>
+        <v>18463.56</v>
       </c>
       <c r="AH31" s="10" t="n">
-        <v>0.0014</v>
+        <v>0.0015</v>
       </c>
       <c r="AI31" s="11" t="n">
         <v>0</v>
@@ -6748,7 +6436,7 @@
         <v>287393</v>
       </c>
       <c r="AK31" s="9" t="n">
-        <v>18463.56</v>
+        <v>18243.71</v>
       </c>
       <c r="AL31" s="10" t="n">
         <v>0.0015</v>
@@ -6760,10 +6448,10 @@
         <v>287393</v>
       </c>
       <c r="AO31" s="9" t="n">
-        <v>18243.71</v>
+        <v>17962.06</v>
       </c>
       <c r="AP31" s="10" t="n">
-        <v>0.0015</v>
+        <v>0.0016</v>
       </c>
       <c r="AQ31" s="11" t="n">
         <v>0</v>
@@ -6772,10 +6460,10 @@
         <v>287393</v>
       </c>
       <c r="AS31" s="9" t="n">
-        <v>17962.06</v>
+        <v>19048.41</v>
       </c>
       <c r="AT31" s="10" t="n">
-        <v>0.0016</v>
+        <v>0.0017</v>
       </c>
       <c r="AU31" s="11" t="n">
         <v>0</v>
@@ -6784,10 +6472,10 @@
         <v>287393</v>
       </c>
       <c r="AW31" s="9" t="n">
-        <v>19048.41</v>
+        <v>19453.63</v>
       </c>
       <c r="AX31" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.0018</v>
       </c>
       <c r="AY31" s="11" t="n">
         <v>0</v>
@@ -6796,10 +6484,10 @@
         <v>287393</v>
       </c>
       <c r="BA31" s="9" t="n">
-        <v>19453.63</v>
+        <v>19370.29</v>
       </c>
       <c r="BB31" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.0019</v>
       </c>
       <c r="BC31" s="11" t="n">
         <v>0</v>
@@ -6808,10 +6496,10 @@
         <v>287393</v>
       </c>
       <c r="BE31" s="9" t="n">
-        <v>19370.29</v>
+        <v>15976.18</v>
       </c>
       <c r="BF31" s="10" t="n">
-        <v>0.0019</v>
+        <v>0.0016</v>
       </c>
       <c r="BG31" s="11" t="n">
         <v>0</v>
@@ -6820,10 +6508,10 @@
         <v>287393</v>
       </c>
       <c r="BI31" s="9" t="n">
-        <v>15976.18</v>
+        <v>15821.13</v>
       </c>
       <c r="BJ31" s="10" t="n">
-        <v>0.0016</v>
+        <v>0.0017</v>
       </c>
       <c r="BK31" s="11" t="n">
         <v>0</v>
@@ -6832,36 +6520,24 @@
         <v>287393</v>
       </c>
       <c r="BM31" s="9" t="n">
-        <v>15821.13</v>
+        <v>15273.64</v>
       </c>
       <c r="BN31" s="10" t="n">
         <v>0.0017</v>
       </c>
       <c r="BO31" s="11" t="n">
-        <v>0</v>
+        <v>-0.03505968069568721</v>
       </c>
       <c r="BP31" s="8" t="n">
-        <v>287393</v>
+        <v>297835</v>
       </c>
       <c r="BQ31" s="9" t="n">
-        <v>15273.64</v>
+        <v>18529.51</v>
       </c>
       <c r="BR31" s="10" t="n">
-        <v>0.0017</v>
-      </c>
-      <c r="BS31" s="11" t="n">
-        <v>-0.03505968069568721</v>
-      </c>
-      <c r="BT31" s="8" t="n">
-        <v>297835</v>
-      </c>
-      <c r="BU31" s="9" t="n">
-        <v>18529.51</v>
-      </c>
-      <c r="BV31" s="10" t="n">
         <v>0.0021</v>
       </c>
-      <c r="BW31" s="11" t="n"/>
+      <c r="BS31" s="11" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -6967,10 +6643,10 @@
         <v>80159</v>
       </c>
       <c r="AG32" s="9" t="n">
-        <v>11787.38</v>
+        <v>12110.42</v>
       </c>
       <c r="AH32" s="10" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="AI32" s="11" t="n">
         <v>0</v>
@@ -6979,10 +6655,10 @@
         <v>80159</v>
       </c>
       <c r="AK32" s="9" t="n">
-        <v>12110.42</v>
+        <v>13825.82</v>
       </c>
       <c r="AL32" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="AM32" s="11" t="n">
         <v>0</v>
@@ -6991,10 +6667,10 @@
         <v>80159</v>
       </c>
       <c r="AO32" s="9" t="n">
-        <v>13825.82</v>
+        <v>12726.04</v>
       </c>
       <c r="AP32" s="10" t="n">
-        <v>0.0012</v>
+        <v>0.0011</v>
       </c>
       <c r="AQ32" s="11" t="n">
         <v>0</v>
@@ -7003,7 +6679,7 @@
         <v>80159</v>
       </c>
       <c r="AS32" s="9" t="n">
-        <v>12726.04</v>
+        <v>12868.73</v>
       </c>
       <c r="AT32" s="10" t="n">
         <v>0.0011</v>
@@ -7015,7 +6691,7 @@
         <v>80159</v>
       </c>
       <c r="AW32" s="9" t="n">
-        <v>12868.73</v>
+        <v>11621.45</v>
       </c>
       <c r="AX32" s="10" t="n">
         <v>0.0011</v>
@@ -7027,10 +6703,10 @@
         <v>80159</v>
       </c>
       <c r="BA32" s="9" t="n">
-        <v>11621.45</v>
+        <v>10722.07</v>
       </c>
       <c r="BB32" s="10" t="n">
-        <v>0.0011</v>
+        <v>0.001</v>
       </c>
       <c r="BC32" s="11" t="n">
         <v>0</v>
@@ -7039,10 +6715,10 @@
         <v>80159</v>
       </c>
       <c r="BE32" s="9" t="n">
-        <v>10722.07</v>
+        <v>9198.25</v>
       </c>
       <c r="BF32" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="BG32" s="11" t="n">
         <v>0</v>
@@ -7051,10 +6727,10 @@
         <v>80159</v>
       </c>
       <c r="BI32" s="9" t="n">
-        <v>9198.25</v>
+        <v>8997.450000000001</v>
       </c>
       <c r="BJ32" s="10" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="BK32" s="11" t="n">
         <v>0</v>
@@ -7063,10 +6739,10 @@
         <v>80159</v>
       </c>
       <c r="BM32" s="9" t="n">
-        <v>8997.450000000001</v>
+        <v>7401.52</v>
       </c>
       <c r="BN32" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0008</v>
       </c>
       <c r="BO32" s="11" t="n">
         <v>0</v>
@@ -7075,24 +6751,12 @@
         <v>80159</v>
       </c>
       <c r="BQ32" s="9" t="n">
-        <v>7401.52</v>
+        <v>7463.48</v>
       </c>
       <c r="BR32" s="10" t="n">
         <v>0.0008</v>
       </c>
-      <c r="BS32" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT32" s="8" t="n">
-        <v>80159</v>
-      </c>
-      <c r="BU32" s="9" t="n">
-        <v>7463.48</v>
-      </c>
-      <c r="BV32" s="10" t="n">
-        <v>0.0008</v>
-      </c>
-      <c r="BW32" s="11" t="n"/>
+      <c r="BS32" s="11" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -7192,20 +6856,12 @@
         <v>0.0002</v>
       </c>
       <c r="AE33" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" s="8" t="n">
-        <v>710855</v>
-      </c>
-      <c r="AG33" s="9" t="n">
-        <v>2850.8839775</v>
-      </c>
-      <c r="AH33" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AI33" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="AF33" s="8" t="n"/>
+      <c r="AG33" s="9" t="n"/>
+      <c r="AH33" s="10" t="n"/>
+      <c r="AI33" s="11" t="n"/>
       <c r="AJ33" s="8" t="n"/>
       <c r="AK33" s="9" t="n"/>
       <c r="AL33" s="10" t="n"/>
@@ -7242,10 +6898,6 @@
       <c r="BQ33" s="9" t="n"/>
       <c r="BR33" s="10" t="n"/>
       <c r="BS33" s="11" t="n"/>
-      <c r="BT33" s="8" t="n"/>
-      <c r="BU33" s="9" t="n"/>
-      <c r="BV33" s="10" t="n"/>
-      <c r="BW33" s="11" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -7351,10 +7003,10 @@
         <v>47293</v>
       </c>
       <c r="AG34" s="9" t="n">
-        <v>1764.08</v>
+        <v>1892.15</v>
       </c>
       <c r="AH34" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="AI34" s="11" t="n">
         <v>0</v>
@@ -7363,7 +7015,7 @@
         <v>47293</v>
       </c>
       <c r="AK34" s="9" t="n">
-        <v>1892.15</v>
+        <v>1955.38</v>
       </c>
       <c r="AL34" s="10" t="n">
         <v>0.0002</v>
@@ -7375,7 +7027,7 @@
         <v>47293</v>
       </c>
       <c r="AO34" s="9" t="n">
-        <v>1955.38</v>
+        <v>1897.21</v>
       </c>
       <c r="AP34" s="10" t="n">
         <v>0.0002</v>
@@ -7387,7 +7039,7 @@
         <v>47293</v>
       </c>
       <c r="AS34" s="9" t="n">
-        <v>1897.21</v>
+        <v>1983.66</v>
       </c>
       <c r="AT34" s="10" t="n">
         <v>0.0002</v>
@@ -7399,7 +7051,7 @@
         <v>47293</v>
       </c>
       <c r="AW34" s="9" t="n">
-        <v>1983.66</v>
+        <v>1867.41</v>
       </c>
       <c r="AX34" s="10" t="n">
         <v>0.0002</v>
@@ -7411,7 +7063,7 @@
         <v>47293</v>
       </c>
       <c r="BA34" s="9" t="n">
-        <v>1867.41</v>
+        <v>1857.76</v>
       </c>
       <c r="BB34" s="10" t="n">
         <v>0.0002</v>
@@ -7423,7 +7075,7 @@
         <v>47293</v>
       </c>
       <c r="BE34" s="9" t="n">
-        <v>1857.76</v>
+        <v>1925.39</v>
       </c>
       <c r="BF34" s="10" t="n">
         <v>0.0002</v>
@@ -7435,7 +7087,7 @@
         <v>47293</v>
       </c>
       <c r="BI34" s="9" t="n">
-        <v>1925.39</v>
+        <v>1844.17</v>
       </c>
       <c r="BJ34" s="10" t="n">
         <v>0.0002</v>
@@ -7447,10 +7099,10 @@
         <v>47293</v>
       </c>
       <c r="BM34" s="9" t="n">
-        <v>1844.17</v>
+        <v>1236.83</v>
       </c>
       <c r="BN34" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="BO34" s="11" t="n">
         <v>0</v>
@@ -7459,24 +7111,12 @@
         <v>47293</v>
       </c>
       <c r="BQ34" s="9" t="n">
-        <v>1236.83</v>
+        <v>1612.64</v>
       </c>
       <c r="BR34" s="10" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="BS34" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT34" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="BU34" s="9" t="n">
-        <v>1612.64</v>
-      </c>
-      <c r="BV34" s="10" t="n">
         <v>0.0002</v>
       </c>
-      <c r="BW34" s="11" t="n"/>
+      <c r="BS34" s="11" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -7610,10 +7250,6 @@
       <c r="BQ35" s="9" t="n"/>
       <c r="BR35" s="10" t="n"/>
       <c r="BS35" s="11" t="n"/>
-      <c r="BT35" s="8" t="n"/>
-      <c r="BU35" s="9" t="n"/>
-      <c r="BV35" s="10" t="n"/>
-      <c r="BW35" s="11" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -7719,7 +7355,7 @@
         <v>151687</v>
       </c>
       <c r="AG36" s="9" t="n">
-        <v>1947.66</v>
+        <v>2076.6</v>
       </c>
       <c r="AH36" s="10" t="n">
         <v>0.0002</v>
@@ -7731,7 +7367,7 @@
         <v>151687</v>
       </c>
       <c r="AK36" s="9" t="n">
-        <v>2076.6</v>
+        <v>1987.1</v>
       </c>
       <c r="AL36" s="10" t="n">
         <v>0.0002</v>
@@ -7743,7 +7379,7 @@
         <v>151687</v>
       </c>
       <c r="AO36" s="9" t="n">
-        <v>1987.1</v>
+        <v>2130.6</v>
       </c>
       <c r="AP36" s="10" t="n">
         <v>0.0002</v>
@@ -7755,7 +7391,7 @@
         <v>151687</v>
       </c>
       <c r="AS36" s="9" t="n">
-        <v>2130.6</v>
+        <v>2091.16</v>
       </c>
       <c r="AT36" s="10" t="n">
         <v>0.0002</v>
@@ -7767,38 +7403,30 @@
         <v>151687</v>
       </c>
       <c r="AW36" s="9" t="n">
-        <v>2091.16</v>
+        <v>1766.62</v>
       </c>
       <c r="AX36" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="AY36" s="11" t="n">
-        <v>0</v>
+        <v>0.6954140540298874</v>
       </c>
       <c r="AZ36" s="8" t="n">
-        <v>151687</v>
+        <v>89469</v>
       </c>
       <c r="BA36" s="9" t="n">
-        <v>1766.62</v>
+        <v>828.48</v>
       </c>
       <c r="BB36" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="BC36" s="11" t="n">
-        <v>0.6954140540298874</v>
-      </c>
-      <c r="BD36" s="8" t="n">
-        <v>89469</v>
-      </c>
-      <c r="BE36" s="9" t="n">
-        <v>828.48</v>
-      </c>
-      <c r="BF36" s="10" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="BG36" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="BD36" s="8" t="n"/>
+      <c r="BE36" s="9" t="n"/>
+      <c r="BF36" s="10" t="n"/>
+      <c r="BG36" s="11" t="n"/>
       <c r="BH36" s="8" t="n"/>
       <c r="BI36" s="9" t="n"/>
       <c r="BJ36" s="10" t="n"/>
@@ -7811,10 +7439,6 @@
       <c r="BQ36" s="9" t="n"/>
       <c r="BR36" s="10" t="n"/>
       <c r="BS36" s="11" t="n"/>
-      <c r="BT36" s="8" t="n"/>
-      <c r="BU36" s="9" t="n"/>
-      <c r="BV36" s="10" t="n"/>
-      <c r="BW36" s="11" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -7868,88 +7492,88 @@
         <v>0.0407</v>
       </c>
       <c r="AE37" s="11" t="n">
-        <v>0.01296144774839237</v>
+        <v>0.01720867810463558</v>
       </c>
       <c r="AF37" s="8" t="n">
-        <v>24306544</v>
+        <v>24205055</v>
       </c>
       <c r="AG37" s="9" t="n">
-        <v>516368.22</v>
+        <v>508838.67</v>
       </c>
       <c r="AH37" s="10" t="n">
-        <v>0.0398</v>
+        <v>0.0404</v>
       </c>
       <c r="AI37" s="11" t="n">
-        <v>0.004192884502844551</v>
+        <v>0</v>
       </c>
       <c r="AJ37" s="8" t="n">
         <v>24205055</v>
       </c>
       <c r="AK37" s="9" t="n">
-        <v>508838.67</v>
+        <v>482334.13</v>
       </c>
       <c r="AL37" s="10" t="n">
-        <v>0.0404</v>
+        <v>0.0403</v>
       </c>
       <c r="AM37" s="11" t="n">
-        <v>0</v>
+        <v>0.03407788338216907</v>
       </c>
       <c r="AN37" s="8" t="n">
-        <v>24205055</v>
+        <v>23407381</v>
       </c>
       <c r="AO37" s="9" t="n">
-        <v>482334.13</v>
+        <v>458854.89</v>
       </c>
       <c r="AP37" s="10" t="n">
-        <v>0.0403</v>
+        <v>0.0399</v>
       </c>
       <c r="AQ37" s="11" t="n">
-        <v>0.03407788338216907</v>
+        <v>0.06425892329321918</v>
       </c>
       <c r="AR37" s="8" t="n">
-        <v>23407381</v>
+        <v>21994066</v>
       </c>
       <c r="AS37" s="9" t="n">
-        <v>458854.89</v>
+        <v>435174.59</v>
       </c>
       <c r="AT37" s="10" t="n">
-        <v>0.0399</v>
+        <v>0.0384</v>
       </c>
       <c r="AU37" s="11" t="n">
-        <v>0.06425892329321918</v>
+        <v>0.07428402120388222</v>
       </c>
       <c r="AV37" s="8" t="n">
-        <v>21994066</v>
+        <v>20473232</v>
       </c>
       <c r="AW37" s="9" t="n">
-        <v>435174.59</v>
+        <v>442938.37</v>
       </c>
       <c r="AX37" s="10" t="n">
-        <v>0.0384</v>
+        <v>0.0401</v>
       </c>
       <c r="AY37" s="11" t="n">
-        <v>0.07428402120388222</v>
+        <v>0.03644973136547983</v>
       </c>
       <c r="AZ37" s="8" t="n">
-        <v>20473232</v>
+        <v>19753232</v>
       </c>
       <c r="BA37" s="9" t="n">
-        <v>442938.37</v>
+        <v>409820.3</v>
       </c>
       <c r="BB37" s="10" t="n">
-        <v>0.0401</v>
+        <v>0.0395</v>
       </c>
       <c r="BC37" s="11" t="n">
-        <v>0.03644973136547983</v>
+        <v>0</v>
       </c>
       <c r="BD37" s="8" t="n">
         <v>19753232</v>
       </c>
       <c r="BE37" s="9" t="n">
-        <v>409820.3</v>
+        <v>436171.12</v>
       </c>
       <c r="BF37" s="10" t="n">
-        <v>0.0395</v>
+        <v>0.0443</v>
       </c>
       <c r="BG37" s="11" t="n">
         <v>0</v>
@@ -7958,10 +7582,10 @@
         <v>19753232</v>
       </c>
       <c r="BI37" s="9" t="n">
-        <v>436171.12</v>
+        <v>428882.17</v>
       </c>
       <c r="BJ37" s="10" t="n">
-        <v>0.0443</v>
+        <v>0.0459</v>
       </c>
       <c r="BK37" s="11" t="n">
         <v>0</v>
@@ -7970,10 +7594,10 @@
         <v>19753232</v>
       </c>
       <c r="BM37" s="9" t="n">
-        <v>428882.17</v>
+        <v>375894.13</v>
       </c>
       <c r="BN37" s="10" t="n">
-        <v>0.0459</v>
+        <v>0.0427</v>
       </c>
       <c r="BO37" s="11" t="n">
         <v>0</v>
@@ -7982,24 +7606,12 @@
         <v>19753232</v>
       </c>
       <c r="BQ37" s="9" t="n">
-        <v>375894.13</v>
+        <v>375568.2</v>
       </c>
       <c r="BR37" s="10" t="n">
-        <v>0.0427</v>
-      </c>
-      <c r="BS37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT37" s="8" t="n">
-        <v>19753232</v>
-      </c>
-      <c r="BU37" s="9" t="n">
-        <v>375568.2</v>
-      </c>
-      <c r="BV37" s="10" t="n">
         <v>0.0419</v>
       </c>
-      <c r="BW37" s="11" t="n"/>
+      <c r="BS37" s="11" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -8083,10 +7695,10 @@
         <v>4189074</v>
       </c>
       <c r="AG38" s="9" t="n">
-        <v>96721.53</v>
+        <v>95502.50999999999</v>
       </c>
       <c r="AH38" s="10" t="n">
-        <v>0.0075</v>
+        <v>0.0076</v>
       </c>
       <c r="AI38" s="11" t="n">
         <v>0</v>
@@ -8095,10 +7707,10 @@
         <v>4189074</v>
       </c>
       <c r="AK38" s="9" t="n">
-        <v>95502.50999999999</v>
+        <v>96130.87</v>
       </c>
       <c r="AL38" s="10" t="n">
-        <v>0.0076</v>
+        <v>0.008</v>
       </c>
       <c r="AM38" s="11" t="n">
         <v>0</v>
@@ -8107,10 +7719,10 @@
         <v>4189074</v>
       </c>
       <c r="AO38" s="9" t="n">
-        <v>96130.87</v>
+        <v>95904.66</v>
       </c>
       <c r="AP38" s="10" t="n">
-        <v>0.008</v>
+        <v>0.0083</v>
       </c>
       <c r="AQ38" s="11" t="n">
         <v>0</v>
@@ -8119,10 +7731,10 @@
         <v>4189074</v>
       </c>
       <c r="AS38" s="9" t="n">
-        <v>95904.66</v>
+        <v>112108</v>
       </c>
       <c r="AT38" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="AU38" s="11" t="n">
         <v>0</v>
@@ -8131,10 +7743,10 @@
         <v>4189074</v>
       </c>
       <c r="AW38" s="9" t="n">
-        <v>112108</v>
+        <v>102435.43</v>
       </c>
       <c r="AX38" s="10" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="AY38" s="11" t="n">
         <v>0</v>
@@ -8143,10 +7755,10 @@
         <v>4189074</v>
       </c>
       <c r="BA38" s="9" t="n">
-        <v>102435.43</v>
+        <v>103562.29</v>
       </c>
       <c r="BB38" s="10" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="BC38" s="11" t="n">
         <v>0</v>
@@ -8155,10 +7767,10 @@
         <v>4189074</v>
       </c>
       <c r="BE38" s="9" t="n">
-        <v>103562.29</v>
+        <v>112061.92</v>
       </c>
       <c r="BF38" s="10" t="n">
-        <v>0.01</v>
+        <v>0.0114</v>
       </c>
       <c r="BG38" s="11" t="n">
         <v>0</v>
@@ -8167,10 +7779,10 @@
         <v>4189074</v>
       </c>
       <c r="BI38" s="9" t="n">
-        <v>112061.92</v>
+        <v>107022.46</v>
       </c>
       <c r="BJ38" s="10" t="n">
-        <v>0.0114</v>
+        <v>0.0115</v>
       </c>
       <c r="BK38" s="11" t="n">
         <v>0</v>
@@ -8179,10 +7791,10 @@
         <v>4189074</v>
       </c>
       <c r="BM38" s="9" t="n">
-        <v>107022.46</v>
+        <v>109571.51</v>
       </c>
       <c r="BN38" s="10" t="n">
-        <v>0.0115</v>
+        <v>0.0125</v>
       </c>
       <c r="BO38" s="11" t="n">
         <v>0</v>
@@ -8191,24 +7803,12 @@
         <v>4189074</v>
       </c>
       <c r="BQ38" s="9" t="n">
-        <v>109571.51</v>
+        <v>116089.71</v>
       </c>
       <c r="BR38" s="10" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="BS38" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT38" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="BU38" s="9" t="n">
-        <v>116089.71</v>
-      </c>
-      <c r="BV38" s="10" t="n">
         <v>0.0129</v>
       </c>
-      <c r="BW38" s="11" t="n"/>
+      <c r="BS38" s="11" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -8269,83 +7869,79 @@
       <c r="AR39" s="8" t="n"/>
       <c r="AS39" s="9" t="n"/>
       <c r="AT39" s="10" t="n"/>
-      <c r="AU39" s="11" t="n"/>
-      <c r="AV39" s="8" t="n"/>
-      <c r="AW39" s="9" t="n"/>
-      <c r="AX39" s="10" t="n"/>
+      <c r="AU39" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AV39" s="8" t="n">
+        <v>591805</v>
+      </c>
+      <c r="AW39" s="9" t="n">
+        <v>5149</v>
+      </c>
+      <c r="AX39" s="10" t="n">
+        <v>0.0005</v>
+      </c>
       <c r="AY39" s="11" t="n">
-        <v>-1</v>
+        <v>-0.8902567225534253</v>
       </c>
       <c r="AZ39" s="8" t="n">
-        <v>591805</v>
+        <v>5392631</v>
       </c>
       <c r="BA39" s="9" t="n">
-        <v>5149</v>
+        <v>43674.92</v>
       </c>
       <c r="BB39" s="10" t="n">
-        <v>0.0005</v>
+        <v>0.0042</v>
       </c>
       <c r="BC39" s="11" t="n">
-        <v>-0.8902567225534253</v>
+        <v>-0.3719237093069153</v>
       </c>
       <c r="BD39" s="8" t="n">
-        <v>5392631</v>
+        <v>8585949</v>
       </c>
       <c r="BE39" s="9" t="n">
-        <v>43674.92</v>
+        <v>56044.78</v>
       </c>
       <c r="BF39" s="10" t="n">
-        <v>0.0042</v>
+        <v>0.0057</v>
       </c>
       <c r="BG39" s="11" t="n">
-        <v>-0.3719237093069153</v>
+        <v>-0.2132577936597328</v>
       </c>
       <c r="BH39" s="8" t="n">
-        <v>8585949</v>
+        <v>10913294</v>
       </c>
       <c r="BI39" s="9" t="n">
-        <v>56044.78</v>
+        <v>67154.95</v>
       </c>
       <c r="BJ39" s="10" t="n">
-        <v>0.0057</v>
+        <v>0.0072</v>
       </c>
       <c r="BK39" s="11" t="n">
-        <v>-0.2132577936597328</v>
+        <v>-0.09462389658963724</v>
       </c>
       <c r="BL39" s="8" t="n">
-        <v>10913294</v>
+        <v>12053879</v>
       </c>
       <c r="BM39" s="9" t="n">
-        <v>67154.95</v>
+        <v>70937.08</v>
       </c>
       <c r="BN39" s="10" t="n">
-        <v>0.0072</v>
+        <v>0.0081</v>
       </c>
       <c r="BO39" s="11" t="n">
-        <v>-0.09462389658963724</v>
+        <v>0</v>
       </c>
       <c r="BP39" s="8" t="n">
         <v>12053879</v>
       </c>
       <c r="BQ39" s="9" t="n">
-        <v>70937.08</v>
+        <v>76801.28999999999</v>
       </c>
       <c r="BR39" s="10" t="n">
-        <v>0.0081</v>
-      </c>
-      <c r="BS39" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT39" s="8" t="n">
-        <v>12053879</v>
-      </c>
-      <c r="BU39" s="9" t="n">
-        <v>76801.28999999999</v>
-      </c>
-      <c r="BV39" s="10" t="n">
         <v>0.0086</v>
       </c>
-      <c r="BW39" s="11" t="n"/>
+      <c r="BS39" s="11" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -8405,10 +8001,10 @@
         <v>797719</v>
       </c>
       <c r="AG40" s="9" t="n">
-        <v>80358.22</v>
+        <v>73737.16</v>
       </c>
       <c r="AH40" s="10" t="n">
-        <v>0.0062</v>
+        <v>0.0059</v>
       </c>
       <c r="AI40" s="11" t="n">
         <v>0</v>
@@ -8417,10 +8013,10 @@
         <v>797719</v>
       </c>
       <c r="AK40" s="9" t="n">
-        <v>73737.16</v>
+        <v>62190.17</v>
       </c>
       <c r="AL40" s="10" t="n">
-        <v>0.0059</v>
+        <v>0.0052</v>
       </c>
       <c r="AM40" s="11" t="n">
         <v>0</v>
@@ -8429,10 +8025,10 @@
         <v>797719</v>
       </c>
       <c r="AO40" s="9" t="n">
-        <v>62190.17</v>
+        <v>58951.43</v>
       </c>
       <c r="AP40" s="10" t="n">
-        <v>0.0052</v>
+        <v>0.0051</v>
       </c>
       <c r="AQ40" s="11" t="n">
         <v>0</v>
@@ -8441,10 +8037,10 @@
         <v>797719</v>
       </c>
       <c r="AS40" s="9" t="n">
-        <v>58951.43</v>
+        <v>61368.52</v>
       </c>
       <c r="AT40" s="10" t="n">
-        <v>0.0051</v>
+        <v>0.0054</v>
       </c>
       <c r="AU40" s="11" t="n">
         <v>0</v>
@@ -8453,10 +8049,10 @@
         <v>797719</v>
       </c>
       <c r="AW40" s="9" t="n">
-        <v>61368.52</v>
+        <v>71347.99000000001</v>
       </c>
       <c r="AX40" s="10" t="n">
-        <v>0.0054</v>
+        <v>0.0065</v>
       </c>
       <c r="AY40" s="11" t="n">
         <v>0</v>
@@ -8465,10 +8061,10 @@
         <v>797719</v>
       </c>
       <c r="BA40" s="9" t="n">
-        <v>71347.99000000001</v>
+        <v>52665.41</v>
       </c>
       <c r="BB40" s="10" t="n">
-        <v>0.0065</v>
+        <v>0.0051</v>
       </c>
       <c r="BC40" s="11" t="n">
         <v>0</v>
@@ -8477,10 +8073,10 @@
         <v>797719</v>
       </c>
       <c r="BE40" s="9" t="n">
-        <v>52665.41</v>
+        <v>48884.22</v>
       </c>
       <c r="BF40" s="10" t="n">
-        <v>0.0051</v>
+        <v>0.005</v>
       </c>
       <c r="BG40" s="11" t="n">
         <v>0</v>
@@ -8489,10 +8085,10 @@
         <v>797719</v>
       </c>
       <c r="BI40" s="9" t="n">
-        <v>48884.22</v>
+        <v>42372.84</v>
       </c>
       <c r="BJ40" s="10" t="n">
-        <v>0.005</v>
+        <v>0.0045</v>
       </c>
       <c r="BK40" s="11" t="n">
         <v>0</v>
@@ -8501,36 +8097,24 @@
         <v>797719</v>
       </c>
       <c r="BM40" s="9" t="n">
-        <v>42372.84</v>
+        <v>39819.34</v>
       </c>
       <c r="BN40" s="10" t="n">
         <v>0.0045</v>
       </c>
       <c r="BO40" s="11" t="n">
-        <v>0</v>
+        <v>-0.09569612848812428</v>
       </c>
       <c r="BP40" s="8" t="n">
-        <v>797719</v>
+        <v>882136</v>
       </c>
       <c r="BQ40" s="9" t="n">
-        <v>39819.34</v>
+        <v>50572.42</v>
       </c>
       <c r="BR40" s="10" t="n">
-        <v>0.0045</v>
-      </c>
-      <c r="BS40" s="11" t="n">
-        <v>-0.09569612848812428</v>
-      </c>
-      <c r="BT40" s="8" t="n">
-        <v>882136</v>
-      </c>
-      <c r="BU40" s="9" t="n">
-        <v>50572.42</v>
-      </c>
-      <c r="BV40" s="10" t="n">
         <v>0.0056</v>
       </c>
-      <c r="BW40" s="11" t="n"/>
+      <c r="BS40" s="11" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -8583,107 +8167,103 @@
       <c r="AJ41" s="8" t="n"/>
       <c r="AK41" s="9" t="n"/>
       <c r="AL41" s="10" t="n"/>
-      <c r="AM41" s="11" t="n"/>
-      <c r="AN41" s="8" t="n"/>
-      <c r="AO41" s="9" t="n"/>
-      <c r="AP41" s="10" t="n"/>
+      <c r="AM41" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN41" s="8" t="n">
+        <v>218075</v>
+      </c>
+      <c r="AO41" s="9" t="n">
+        <v>3019.03</v>
+      </c>
+      <c r="AP41" s="10" t="n">
+        <v>0.0003</v>
+      </c>
       <c r="AQ41" s="11" t="n">
-        <v>-1</v>
+        <v>-0.6148554615199853</v>
       </c>
       <c r="AR41" s="8" t="n">
-        <v>218075</v>
+        <v>566216</v>
       </c>
       <c r="AS41" s="9" t="n">
-        <v>3019.03</v>
+        <v>8345.459999999999</v>
       </c>
       <c r="AT41" s="10" t="n">
-        <v>0.0003</v>
+        <v>0.0007</v>
       </c>
       <c r="AU41" s="11" t="n">
-        <v>-0.6148554615199853</v>
+        <v>-0.5682871579351869</v>
       </c>
       <c r="AV41" s="8" t="n">
-        <v>566216</v>
+        <v>1311557</v>
       </c>
       <c r="AW41" s="9" t="n">
-        <v>8345.459999999999</v>
+        <v>18228.02</v>
       </c>
       <c r="AX41" s="10" t="n">
-        <v>0.0007</v>
+        <v>0.0017</v>
       </c>
       <c r="AY41" s="11" t="n">
-        <v>-0.5682871579351869</v>
+        <v>-0.2008037316547793</v>
       </c>
       <c r="AZ41" s="8" t="n">
-        <v>1311557</v>
+        <v>1641095</v>
       </c>
       <c r="BA41" s="9" t="n">
-        <v>18228.02</v>
+        <v>23382.32</v>
       </c>
       <c r="BB41" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.0023</v>
       </c>
       <c r="BC41" s="11" t="n">
-        <v>-0.2008037316547793</v>
+        <v>-0.1163687388172734</v>
       </c>
       <c r="BD41" s="8" t="n">
-        <v>1641095</v>
+        <v>1857217</v>
       </c>
       <c r="BE41" s="9" t="n">
-        <v>23382.32</v>
+        <v>26023.32</v>
       </c>
       <c r="BF41" s="10" t="n">
-        <v>0.0023</v>
+        <v>0.0026</v>
       </c>
       <c r="BG41" s="11" t="n">
-        <v>-0.1163687388172734</v>
+        <v>-0.03620728307597141</v>
       </c>
       <c r="BH41" s="8" t="n">
-        <v>1857217</v>
+        <v>1926988</v>
       </c>
       <c r="BI41" s="9" t="n">
-        <v>26023.32</v>
+        <v>28941.43</v>
       </c>
       <c r="BJ41" s="10" t="n">
-        <v>0.0026</v>
+        <v>0.0031</v>
       </c>
       <c r="BK41" s="11" t="n">
-        <v>-0.03620728307597141</v>
+        <v>0</v>
       </c>
       <c r="BL41" s="8" t="n">
         <v>1926988</v>
       </c>
       <c r="BM41" s="9" t="n">
-        <v>28941.43</v>
+        <v>26117.43</v>
       </c>
       <c r="BN41" s="10" t="n">
-        <v>0.0031</v>
+        <v>0.003</v>
       </c>
       <c r="BO41" s="11" t="n">
-        <v>0</v>
+        <v>-0.1421734974921662</v>
       </c>
       <c r="BP41" s="8" t="n">
-        <v>1926988</v>
+        <v>2246361</v>
       </c>
       <c r="BQ41" s="9" t="n">
-        <v>26117.43</v>
+        <v>32421.73</v>
       </c>
       <c r="BR41" s="10" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="BS41" s="11" t="n">
-        <v>-0.1421734974921662</v>
-      </c>
-      <c r="BT41" s="8" t="n">
-        <v>2246361</v>
-      </c>
-      <c r="BU41" s="9" t="n">
-        <v>32421.73</v>
-      </c>
-      <c r="BV41" s="10" t="n">
         <v>0.0036</v>
       </c>
-      <c r="BW41" s="11" t="n"/>
+      <c r="BS41" s="11" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -8756,21 +8336,29 @@
       <c r="BD42" s="8" t="n"/>
       <c r="BE42" s="9" t="n"/>
       <c r="BF42" s="10" t="n"/>
-      <c r="BG42" s="11" t="n"/>
-      <c r="BH42" s="8" t="n"/>
-      <c r="BI42" s="9" t="n"/>
-      <c r="BJ42" s="10" t="n"/>
+      <c r="BG42" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH42" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BI42" s="9" t="n">
+        <v>19552.33</v>
+      </c>
+      <c r="BJ42" s="10" t="n">
+        <v>0.0021</v>
+      </c>
       <c r="BK42" s="11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BL42" s="8" t="n">
         <v>9899412</v>
       </c>
       <c r="BM42" s="9" t="n">
-        <v>19552.33</v>
+        <v>16216.23</v>
       </c>
       <c r="BN42" s="10" t="n">
-        <v>0.0021</v>
+        <v>0.0018</v>
       </c>
       <c r="BO42" s="11" t="n">
         <v>0</v>
@@ -8779,24 +8367,12 @@
         <v>9899412</v>
       </c>
       <c r="BQ42" s="9" t="n">
-        <v>16216.23</v>
+        <v>16131.09</v>
       </c>
       <c r="BR42" s="10" t="n">
         <v>0.0018</v>
       </c>
-      <c r="BS42" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT42" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BU42" s="9" t="n">
-        <v>16131.09</v>
-      </c>
-      <c r="BV42" s="10" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="BW42" s="11" t="n"/>
+      <c r="BS42" s="11" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -8892,10 +8468,6 @@
       <c r="BQ43" s="9" t="n"/>
       <c r="BR43" s="10" t="n"/>
       <c r="BS43" s="11" t="n"/>
-      <c r="BT43" s="8" t="n"/>
-      <c r="BU43" s="9" t="n"/>
-      <c r="BV43" s="10" t="n"/>
-      <c r="BW43" s="11" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -8948,21 +8520,29 @@
       <c r="AJ44" s="8" t="n"/>
       <c r="AK44" s="9" t="n"/>
       <c r="AL44" s="10" t="n"/>
-      <c r="AM44" s="11" t="n"/>
-      <c r="AN44" s="8" t="n"/>
-      <c r="AO44" s="9" t="n"/>
-      <c r="AP44" s="10" t="n"/>
+      <c r="AM44" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN44" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AO44" s="9" t="n">
+        <v>88822.8</v>
+      </c>
+      <c r="AP44" s="10" t="n">
+        <v>0.0077</v>
+      </c>
       <c r="AQ44" s="11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AR44" s="8" t="n">
         <v>4400000</v>
       </c>
       <c r="AS44" s="9" t="n">
-        <v>88822.8</v>
+        <v>89280.39999999999</v>
       </c>
       <c r="AT44" s="10" t="n">
-        <v>0.0077</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="AU44" s="11" t="n">
         <v>0</v>
@@ -8971,26 +8551,18 @@
         <v>4400000</v>
       </c>
       <c r="AW44" s="9" t="n">
-        <v>89280.39999999999</v>
+        <v>89020.8</v>
       </c>
       <c r="AX44" s="10" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0081</v>
       </c>
       <c r="AY44" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ44" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="BA44" s="9" t="n">
-        <v>89020.8</v>
-      </c>
-      <c r="BB44" s="10" t="n">
-        <v>0.0081</v>
-      </c>
-      <c r="BC44" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="AZ44" s="8" t="n"/>
+      <c r="BA44" s="9" t="n"/>
+      <c r="BB44" s="10" t="n"/>
+      <c r="BC44" s="11" t="n"/>
       <c r="BD44" s="8" t="n"/>
       <c r="BE44" s="9" t="n"/>
       <c r="BF44" s="10" t="n"/>
@@ -9007,10 +8579,6 @@
       <c r="BQ44" s="9" t="n"/>
       <c r="BR44" s="10" t="n"/>
       <c r="BS44" s="11" t="n"/>
-      <c r="BT44" s="8" t="n"/>
-      <c r="BU44" s="9" t="n"/>
-      <c r="BV44" s="10" t="n"/>
-      <c r="BW44" s="11" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
@@ -9091,136 +8659,125 @@
       </c>
       <c r="AE45" s="17" t="n"/>
       <c r="AF45" s="14" t="n">
-        <v>1039629309</v>
+        <v>991416407</v>
       </c>
       <c r="AG45" s="15" t="n">
-        <v>8271351.1939775</v>
+        <v>7865128.239999999</v>
       </c>
       <c r="AH45" s="16" t="n">
-        <v>0.6373999999999999</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="AI45" s="17" t="n"/>
       <c r="AJ45" s="14" t="n">
-        <v>991416407</v>
+        <v>979359723</v>
       </c>
       <c r="AK45" s="15" t="n">
-        <v>7865128.239999999</v>
+        <v>7559180.72</v>
       </c>
       <c r="AL45" s="16" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.6313999999999996</v>
       </c>
       <c r="AM45" s="17" t="n"/>
       <c r="AN45" s="14" t="n">
-        <v>979359723</v>
+        <v>927478800</v>
       </c>
       <c r="AO45" s="15" t="n">
-        <v>7559180.72</v>
+        <v>7320811.489999998</v>
       </c>
       <c r="AP45" s="16" t="n">
-        <v>0.6313999999999996</v>
+        <v>0.6364000000000001</v>
       </c>
       <c r="AQ45" s="17" t="n"/>
       <c r="AR45" s="14" t="n">
-        <v>927478800</v>
+        <v>819556049</v>
       </c>
       <c r="AS45" s="15" t="n">
-        <v>7320811.489999998</v>
+        <v>7290583.900000002</v>
       </c>
       <c r="AT45" s="16" t="n">
-        <v>0.6364000000000001</v>
+        <v>0.6436999999999999</v>
       </c>
       <c r="AU45" s="17" t="n"/>
       <c r="AV45" s="14" t="n">
-        <v>819556049</v>
+        <v>799425942</v>
       </c>
       <c r="AW45" s="15" t="n">
-        <v>7290583.900000002</v>
+        <v>7347454.069999999</v>
       </c>
       <c r="AX45" s="16" t="n">
-        <v>0.6436999999999999</v>
+        <v>0.6658000000000001</v>
       </c>
       <c r="AY45" s="17" t="n"/>
       <c r="AZ45" s="14" t="n">
-        <v>799425942</v>
+        <v>756845974</v>
       </c>
       <c r="BA45" s="15" t="n">
-        <v>7347454.069999999</v>
+        <v>6714757.130000002</v>
       </c>
       <c r="BB45" s="16" t="n">
-        <v>0.6658000000000001</v>
+        <v>0.6467999999999997</v>
       </c>
       <c r="BC45" s="17" t="n"/>
       <c r="BD45" s="14" t="n">
-        <v>756845974</v>
+        <v>719050337</v>
       </c>
       <c r="BE45" s="15" t="n">
-        <v>6714757.130000002</v>
+        <v>6275568.75</v>
       </c>
       <c r="BF45" s="16" t="n">
-        <v>0.6467999999999997</v>
+        <v>0.6369999999999999</v>
       </c>
       <c r="BG45" s="17" t="n"/>
       <c r="BH45" s="14" t="n">
-        <v>719050337</v>
+        <v>717176528</v>
       </c>
       <c r="BI45" s="15" t="n">
-        <v>6275568.75</v>
+        <v>6051937.579999999</v>
       </c>
       <c r="BJ45" s="16" t="n">
-        <v>0.6369999999999999</v>
+        <v>0.6476999999999998</v>
       </c>
       <c r="BK45" s="17" t="n"/>
       <c r="BL45" s="14" t="n">
-        <v>717176528</v>
+        <v>718063829</v>
       </c>
       <c r="BM45" s="15" t="n">
-        <v>6051937.579999999</v>
+        <v>5662977.750000001</v>
       </c>
       <c r="BN45" s="16" t="n">
-        <v>0.6476999999999998</v>
+        <v>0.6436999999999999</v>
       </c>
       <c r="BO45" s="17" t="n"/>
       <c r="BP45" s="14" t="n">
-        <v>718063829</v>
+        <v>697292654</v>
       </c>
       <c r="BQ45" s="15" t="n">
-        <v>5662977.750000001</v>
+        <v>5868142.6</v>
       </c>
       <c r="BR45" s="16" t="n">
-        <v>0.6436999999999999</v>
+        <v>0.6543000000000003</v>
       </c>
       <c r="BS45" s="17" t="n"/>
-      <c r="BT45" s="14" t="n">
-        <v>697292654</v>
-      </c>
-      <c r="BU45" s="15" t="n">
-        <v>5868142.6</v>
-      </c>
-      <c r="BV45" s="16" t="n">
-        <v>0.6543000000000003</v>
-      </c>
-      <c r="BW45" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="18">
+    <mergeCell ref="BL2:BO2"/>
+    <mergeCell ref="BH2:BK2"/>
+    <mergeCell ref="A1:BS1"/>
+    <mergeCell ref="AF2:AI2"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="T2:W2"/>
+    <mergeCell ref="X2:AA2"/>
+    <mergeCell ref="AB2:AE2"/>
     <mergeCell ref="AR2:AU2"/>
-    <mergeCell ref="AZ2:BC2"/>
-    <mergeCell ref="BL2:BO2"/>
-    <mergeCell ref="A1:BW1"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="X2:AA2"/>
-    <mergeCell ref="AJ2:AM2"/>
     <mergeCell ref="AV2:AY2"/>
     <mergeCell ref="D2:G2"/>
+    <mergeCell ref="AZ2:BC2"/>
     <mergeCell ref="P2:S2"/>
     <mergeCell ref="BD2:BG2"/>
+    <mergeCell ref="AJ2:AM2"/>
     <mergeCell ref="BP2:BS2"/>
-    <mergeCell ref="BH2:BK2"/>
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="T2:W2"/>
-    <mergeCell ref="AB2:AE2"/>
-    <mergeCell ref="AF2:AI2"/>
-    <mergeCell ref="BT2:BW2"/>
     <mergeCell ref="AN2:AQ2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS45"/>
+  <dimension ref="A1:BW45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -524,22 +524,22 @@
     <col width="26" customWidth="1" min="29" max="29"/>
     <col width="20" customWidth="1" min="30" max="30"/>
     <col width="22" customWidth="1" min="31" max="31"/>
-    <col width="14" customWidth="1" min="32" max="32"/>
+    <col width="15" customWidth="1" min="32" max="32"/>
     <col width="26" customWidth="1" min="33" max="33"/>
-    <col width="14" customWidth="1" min="34" max="34"/>
-    <col width="23" customWidth="1" min="35" max="35"/>
-    <col width="16" customWidth="1" min="36" max="36"/>
+    <col width="20" customWidth="1" min="34" max="34"/>
+    <col width="22" customWidth="1" min="35" max="35"/>
+    <col width="14" customWidth="1" min="36" max="36"/>
     <col width="26" customWidth="1" min="37" max="37"/>
-    <col width="20" customWidth="1" min="38" max="38"/>
-    <col width="22" customWidth="1" min="39" max="39"/>
-    <col width="13" customWidth="1" min="40" max="40"/>
+    <col width="14" customWidth="1" min="38" max="38"/>
+    <col width="23" customWidth="1" min="39" max="39"/>
+    <col width="16" customWidth="1" min="40" max="40"/>
     <col width="26" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
-    <col width="23" customWidth="1" min="43" max="43"/>
+    <col width="22" customWidth="1" min="43" max="43"/>
     <col width="13" customWidth="1" min="44" max="44"/>
     <col width="26" customWidth="1" min="45" max="45"/>
     <col width="20" customWidth="1" min="46" max="46"/>
-    <col width="22" customWidth="1" min="47" max="47"/>
+    <col width="23" customWidth="1" min="47" max="47"/>
     <col width="13" customWidth="1" min="48" max="48"/>
     <col width="26" customWidth="1" min="49" max="49"/>
     <col width="20" customWidth="1" min="50" max="50"/>
@@ -547,23 +547,27 @@
     <col width="13" customWidth="1" min="52" max="52"/>
     <col width="26" customWidth="1" min="53" max="53"/>
     <col width="20" customWidth="1" min="54" max="54"/>
-    <col width="23" customWidth="1" min="55" max="55"/>
+    <col width="22" customWidth="1" min="55" max="55"/>
     <col width="13" customWidth="1" min="56" max="56"/>
     <col width="26" customWidth="1" min="57" max="57"/>
     <col width="20" customWidth="1" min="58" max="58"/>
-    <col width="22" customWidth="1" min="59" max="59"/>
+    <col width="23" customWidth="1" min="59" max="59"/>
     <col width="13" customWidth="1" min="60" max="60"/>
     <col width="26" customWidth="1" min="61" max="61"/>
     <col width="20" customWidth="1" min="62" max="62"/>
-    <col width="23" customWidth="1" min="63" max="63"/>
-    <col width="15" customWidth="1" min="64" max="64"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="13" customWidth="1" min="64" max="64"/>
     <col width="26" customWidth="1" min="65" max="65"/>
     <col width="20" customWidth="1" min="66" max="66"/>
-    <col width="22" customWidth="1" min="67" max="67"/>
-    <col width="14" customWidth="1" min="68" max="68"/>
+    <col width="23" customWidth="1" min="67" max="67"/>
+    <col width="15" customWidth="1" min="68" max="68"/>
     <col width="26" customWidth="1" min="69" max="69"/>
     <col width="20" customWidth="1" min="70" max="70"/>
-    <col width="17" customWidth="1" min="71" max="71"/>
+    <col width="22" customWidth="1" min="71" max="71"/>
+    <col width="14" customWidth="1" min="72" max="72"/>
+    <col width="26" customWidth="1" min="73" max="73"/>
+    <col width="20" customWidth="1" min="74" max="74"/>
+    <col width="17" customWidth="1" min="75" max="75"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -642,6 +646,10 @@
       <c r="BQ1" s="1" t="n"/>
       <c r="BR1" s="1" t="n"/>
       <c r="BS1" s="1" t="n"/>
+      <c r="BT1" s="1" t="n"/>
+      <c r="BU1" s="1" t="n"/>
+      <c r="BV1" s="1" t="n"/>
+      <c r="BW1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -717,7 +725,7 @@
       <c r="AE2" s="3" t="n"/>
       <c r="AF2" s="2" t="inlineStr">
         <is>
-          <t>October_2025</t>
+          <t>November_2025</t>
         </is>
       </c>
       <c r="AG2" s="2" t="n"/>
@@ -725,7 +733,7 @@
       <c r="AI2" s="3" t="n"/>
       <c r="AJ2" s="2" t="inlineStr">
         <is>
-          <t>September_2025</t>
+          <t>October_2025</t>
         </is>
       </c>
       <c r="AK2" s="2" t="n"/>
@@ -733,7 +741,7 @@
       <c r="AM2" s="3" t="n"/>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>August_2025</t>
+          <t>September_2025</t>
         </is>
       </c>
       <c r="AO2" s="2" t="n"/>
@@ -741,7 +749,7 @@
       <c r="AQ2" s="3" t="n"/>
       <c r="AR2" s="2" t="inlineStr">
         <is>
-          <t>July_2025</t>
+          <t>August_2025</t>
         </is>
       </c>
       <c r="AS2" s="2" t="n"/>
@@ -749,7 +757,7 @@
       <c r="AU2" s="3" t="n"/>
       <c r="AV2" s="2" t="inlineStr">
         <is>
-          <t>June_2025</t>
+          <t>July_2025</t>
         </is>
       </c>
       <c r="AW2" s="2" t="n"/>
@@ -757,7 +765,7 @@
       <c r="AY2" s="3" t="n"/>
       <c r="AZ2" s="2" t="inlineStr">
         <is>
-          <t>May_2025</t>
+          <t>June_2025</t>
         </is>
       </c>
       <c r="BA2" s="2" t="n"/>
@@ -765,7 +773,7 @@
       <c r="BC2" s="3" t="n"/>
       <c r="BD2" s="2" t="inlineStr">
         <is>
-          <t>April_2025</t>
+          <t>May_2025</t>
         </is>
       </c>
       <c r="BE2" s="2" t="n"/>
@@ -773,7 +781,7 @@
       <c r="BG2" s="3" t="n"/>
       <c r="BH2" s="2" t="inlineStr">
         <is>
-          <t>March_2025</t>
+          <t>April_2025</t>
         </is>
       </c>
       <c r="BI2" s="2" t="n"/>
@@ -781,7 +789,7 @@
       <c r="BK2" s="3" t="n"/>
       <c r="BL2" s="2" t="inlineStr">
         <is>
-          <t>February_2025</t>
+          <t>March_2025</t>
         </is>
       </c>
       <c r="BM2" s="2" t="n"/>
@@ -789,12 +797,20 @@
       <c r="BO2" s="3" t="n"/>
       <c r="BP2" s="2" t="inlineStr">
         <is>
-          <t>January_2025</t>
+          <t>February_2025</t>
         </is>
       </c>
       <c r="BQ2" s="2" t="n"/>
       <c r="BR2" s="2" t="n"/>
       <c r="BS2" s="3" t="n"/>
+      <c r="BT2" s="2" t="inlineStr">
+        <is>
+          <t>January_2025</t>
+        </is>
+      </c>
+      <c r="BU2" s="2" t="n"/>
+      <c r="BV2" s="2" t="n"/>
+      <c r="BW2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n"/>
@@ -1140,6 +1156,26 @@
           <t>% Change in Qty</t>
         </is>
       </c>
+      <c r="BT3" s="4" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="BU3" s="4" t="inlineStr">
+        <is>
+          <t>Market Value (Rs. Lakhs)</t>
+        </is>
+      </c>
+      <c r="BV3" s="4" t="inlineStr">
+        <is>
+          <t>% Net Assets</t>
+        </is>
+      </c>
+      <c r="BW3" s="5" t="inlineStr">
+        <is>
+          <t>% Change in Qty</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -1239,100 +1275,100 @@
         <v>0.0809</v>
       </c>
       <c r="AE4" s="11" t="n">
-        <v>0.06394013360876992</v>
+        <v>0.05075274131724232</v>
       </c>
       <c r="AF4" s="8" t="n">
+        <v>103486016</v>
+      </c>
+      <c r="AG4" s="9" t="n">
+        <v>1042725.1</v>
+      </c>
+      <c r="AH4" s="10" t="n">
+        <v>0.0803</v>
+      </c>
+      <c r="AI4" s="11" t="n">
+        <v>0.01255042387516938</v>
+      </c>
+      <c r="AJ4" s="8" t="n">
         <v>102203321</v>
       </c>
-      <c r="AG4" s="9" t="n">
+      <c r="AK4" s="9" t="n">
         <v>1009053.39</v>
       </c>
-      <c r="AH4" s="10" t="n">
+      <c r="AL4" s="10" t="n">
         <v>0.08019999999999999</v>
       </c>
-      <c r="AI4" s="11" t="n">
+      <c r="AM4" s="11" t="n">
         <v>0.005262209454604842</v>
       </c>
-      <c r="AJ4" s="8" t="n">
+      <c r="AN4" s="8" t="n">
         <v>101668321</v>
       </c>
-      <c r="AK4" s="9" t="n">
+      <c r="AO4" s="9" t="n">
         <v>966865.73</v>
       </c>
-      <c r="AL4" s="10" t="n">
+      <c r="AP4" s="10" t="n">
         <v>0.0808</v>
       </c>
-      <c r="AM4" s="11" t="n">
+      <c r="AQ4" s="11" t="n">
         <v>0.06097375017638836</v>
       </c>
-      <c r="AN4" s="8" t="n">
+      <c r="AR4" s="8" t="n">
         <v>95825482</v>
       </c>
-      <c r="AO4" s="9" t="n">
+      <c r="AS4" s="9" t="n">
         <v>911875.29</v>
       </c>
-      <c r="AP4" s="10" t="n">
+      <c r="AT4" s="10" t="n">
         <v>0.0793</v>
       </c>
-      <c r="AQ4" s="11" t="n">
+      <c r="AU4" s="11" t="n">
         <v>1.135602796681763</v>
       </c>
-      <c r="AR4" s="8" t="n">
+      <c r="AV4" s="8" t="n">
         <v>44870461</v>
       </c>
-      <c r="AS4" s="9" t="n">
+      <c r="AW4" s="9" t="n">
         <v>905575.64</v>
       </c>
-      <c r="AT4" s="10" t="n">
+      <c r="AX4" s="10" t="n">
         <v>0.0799</v>
       </c>
-      <c r="AU4" s="11" t="n">
+      <c r="AY4" s="11" t="n">
         <v>0.009203290657165424</v>
       </c>
-      <c r="AV4" s="8" t="n">
+      <c r="AZ4" s="8" t="n">
         <v>44461271</v>
       </c>
-      <c r="AW4" s="9" t="n">
+      <c r="BA4" s="9" t="n">
         <v>889892.34</v>
       </c>
-      <c r="AX4" s="10" t="n">
+      <c r="BB4" s="10" t="n">
         <v>0.0806</v>
       </c>
-      <c r="AY4" s="11" t="n">
+      <c r="BC4" s="11" t="n">
         <v>0.026983580212343</v>
       </c>
-      <c r="AZ4" s="8" t="n">
+      <c r="BD4" s="8" t="n">
         <v>43293069</v>
       </c>
-      <c r="BA4" s="9" t="n">
+      <c r="BE4" s="9" t="n">
         <v>842006.9</v>
       </c>
-      <c r="BB4" s="10" t="n">
+      <c r="BF4" s="10" t="n">
         <v>0.08110000000000001</v>
       </c>
-      <c r="BC4" s="11" t="n">
+      <c r="BG4" s="11" t="n">
         <v>0.01121152982515689</v>
-      </c>
-      <c r="BD4" s="8" t="n">
-        <v>42813069</v>
-      </c>
-      <c r="BE4" s="9" t="n">
-        <v>824151.58</v>
-      </c>
-      <c r="BF4" s="10" t="n">
-        <v>0.08359999999999999</v>
-      </c>
-      <c r="BG4" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="BH4" s="8" t="n">
         <v>42813069</v>
       </c>
       <c r="BI4" s="9" t="n">
-        <v>782708.53</v>
+        <v>824151.58</v>
       </c>
       <c r="BJ4" s="10" t="n">
-        <v>0.0838</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="BK4" s="11" t="n">
         <v>0</v>
@@ -1341,10 +1377,10 @@
         <v>42813069</v>
       </c>
       <c r="BM4" s="9" t="n">
-        <v>741693.61</v>
+        <v>782708.53</v>
       </c>
       <c r="BN4" s="10" t="n">
-        <v>0.0843</v>
+        <v>0.0838</v>
       </c>
       <c r="BO4" s="11" t="n">
         <v>0</v>
@@ -1353,12 +1389,24 @@
         <v>42813069</v>
       </c>
       <c r="BQ4" s="9" t="n">
+        <v>741693.61</v>
+      </c>
+      <c r="BR4" s="10" t="n">
+        <v>0.0843</v>
+      </c>
+      <c r="BS4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT4" s="8" t="n">
+        <v>42813069</v>
+      </c>
+      <c r="BU4" s="9" t="n">
         <v>727287.01</v>
       </c>
-      <c r="BR4" s="10" t="n">
+      <c r="BV4" s="10" t="n">
         <v>0.08110000000000001</v>
       </c>
-      <c r="BS4" s="11" t="n"/>
+      <c r="BW4" s="11" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -1458,126 +1506,138 @@
         <v>0.0606</v>
       </c>
       <c r="AE5" s="11" t="n">
-        <v>0.1666724875647491</v>
+        <v>0.07483622732268541</v>
       </c>
       <c r="AF5" s="8" t="n">
+        <v>284154236</v>
+      </c>
+      <c r="AG5" s="9" t="n">
+        <v>767074.36</v>
+      </c>
+      <c r="AH5" s="10" t="n">
+        <v>0.0591</v>
+      </c>
+      <c r="AI5" s="11" t="n">
+        <v>0.08544209611432535</v>
+      </c>
+      <c r="AJ5" s="8" t="n">
         <v>261786637</v>
       </c>
-      <c r="AG5" s="9" t="n">
+      <c r="AK5" s="9" t="n">
         <v>754338.1899999999</v>
       </c>
-      <c r="AH5" s="10" t="n">
+      <c r="AL5" s="10" t="n">
         <v>0.06</v>
       </c>
-      <c r="AI5" s="11" t="n">
+      <c r="AM5" s="11" t="n">
         <v>0.02291281861384987</v>
       </c>
-      <c r="AJ5" s="8" t="n">
+      <c r="AN5" s="8" t="n">
         <v>255922726</v>
       </c>
-      <c r="AK5" s="9" t="n">
+      <c r="AO5" s="9" t="n">
         <v>717223.4399999999</v>
       </c>
-      <c r="AL5" s="10" t="n">
+      <c r="AP5" s="10" t="n">
         <v>0.0599</v>
       </c>
-      <c r="AM5" s="11" t="n">
+      <c r="AQ5" s="11" t="n">
         <v>0.04012490664854439</v>
       </c>
-      <c r="AN5" s="8" t="n">
+      <c r="AR5" s="8" t="n">
         <v>246049993</v>
       </c>
-      <c r="AO5" s="9" t="n">
+      <c r="AS5" s="9" t="n">
         <v>677252.61</v>
       </c>
-      <c r="AP5" s="10" t="n">
+      <c r="AT5" s="10" t="n">
         <v>0.0589</v>
       </c>
-      <c r="AQ5" s="11" t="n">
+      <c r="AU5" s="11" t="n">
         <v>0.06613218800272164</v>
       </c>
-      <c r="AR5" s="8" t="n">
+      <c r="AV5" s="8" t="n">
         <v>230787510</v>
       </c>
-      <c r="AS5" s="9" t="n">
+      <c r="AW5" s="9" t="n">
         <v>671591.65</v>
       </c>
-      <c r="AT5" s="10" t="n">
+      <c r="AX5" s="10" t="n">
         <v>0.0593</v>
       </c>
-      <c r="AU5" s="11" t="n">
+      <c r="AY5" s="11" t="n">
         <v>0.02930647191621902</v>
       </c>
-      <c r="AV5" s="8" t="n">
+      <c r="AZ5" s="8" t="n">
         <v>224216515</v>
       </c>
-      <c r="AW5" s="9" t="n">
+      <c r="BA5" s="9" t="n">
         <v>672425.33</v>
       </c>
-      <c r="AX5" s="10" t="n">
+      <c r="BB5" s="10" t="n">
         <v>0.0609</v>
       </c>
-      <c r="AY5" s="11" t="n">
+      <c r="BC5" s="11" t="n">
         <v>0.07348663585077284</v>
       </c>
-      <c r="AZ5" s="8" t="n">
+      <c r="BD5" s="8" t="n">
         <v>208867542</v>
       </c>
-      <c r="BA5" s="9" t="n">
+      <c r="BE5" s="9" t="n">
         <v>605193.7</v>
       </c>
-      <c r="BB5" s="10" t="n">
+      <c r="BF5" s="10" t="n">
         <v>0.0583</v>
       </c>
-      <c r="BC5" s="11" t="n">
+      <c r="BG5" s="11" t="n">
         <v>0.0787685054851275</v>
       </c>
-      <c r="BD5" s="8" t="n">
+      <c r="BH5" s="8" t="n">
         <v>193616648</v>
       </c>
-      <c r="BE5" s="9" t="n">
+      <c r="BI5" s="9" t="n">
         <v>595274.38</v>
       </c>
-      <c r="BF5" s="10" t="n">
+      <c r="BJ5" s="10" t="n">
         <v>0.0604</v>
       </c>
-      <c r="BG5" s="11" t="n">
+      <c r="BK5" s="11" t="n">
         <v>0.004416437745811861</v>
       </c>
-      <c r="BH5" s="8" t="n">
+      <c r="BL5" s="8" t="n">
         <v>192765312</v>
       </c>
-      <c r="BI5" s="9" t="n">
+      <c r="BM5" s="9" t="n">
         <v>559694.08</v>
       </c>
-      <c r="BJ5" s="10" t="n">
+      <c r="BN5" s="10" t="n">
         <v>0.0599</v>
       </c>
-      <c r="BK5" s="11" t="n">
+      <c r="BO5" s="11" t="n">
         <v>-0.003790710650882039</v>
       </c>
-      <c r="BL5" s="8" t="n">
+      <c r="BP5" s="8" t="n">
         <v>193498810</v>
       </c>
-      <c r="BM5" s="9" t="n">
+      <c r="BQ5" s="9" t="n">
         <v>485391.76</v>
       </c>
-      <c r="BN5" s="10" t="n">
+      <c r="BR5" s="10" t="n">
         <v>0.0552</v>
       </c>
-      <c r="BO5" s="11" t="n">
+      <c r="BS5" s="11" t="n">
         <v>0.04268662994371823</v>
       </c>
-      <c r="BP5" s="8" t="n">
+      <c r="BT5" s="8" t="n">
         <v>185577147</v>
       </c>
-      <c r="BQ5" s="9" t="n">
+      <c r="BU5" s="9" t="n">
         <v>559793.46</v>
       </c>
-      <c r="BR5" s="10" t="n">
+      <c r="BV5" s="10" t="n">
         <v>0.0624</v>
       </c>
-      <c r="BS5" s="11" t="n"/>
+      <c r="BW5" s="11" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -1677,126 +1737,138 @@
         <v>0.0449</v>
       </c>
       <c r="AE6" s="11" t="n">
-        <v>0.07130225543338212</v>
+        <v>0.02714259251540287</v>
       </c>
       <c r="AF6" s="8" t="n">
+        <v>144737169</v>
+      </c>
+      <c r="AG6" s="9" t="n">
+        <v>585100.01</v>
+      </c>
+      <c r="AH6" s="10" t="n">
+        <v>0.0451</v>
+      </c>
+      <c r="AI6" s="11" t="n">
+        <v>0.04299272879906111</v>
+      </c>
+      <c r="AJ6" s="8" t="n">
         <v>138771024</v>
       </c>
-      <c r="AG6" s="9" t="n">
+      <c r="AK6" s="9" t="n">
         <v>583324</v>
       </c>
-      <c r="AH6" s="10" t="n">
+      <c r="AL6" s="10" t="n">
         <v>0.0464</v>
       </c>
-      <c r="AI6" s="11" t="n">
+      <c r="AM6" s="11" t="n">
         <v>0.02247256843567582</v>
       </c>
-      <c r="AJ6" s="8" t="n">
+      <c r="AN6" s="8" t="n">
         <v>135721024</v>
       </c>
-      <c r="AK6" s="9" t="n">
+      <c r="AO6" s="9" t="n">
         <v>544987.77</v>
       </c>
-      <c r="AL6" s="10" t="n">
+      <c r="AP6" s="10" t="n">
         <v>0.0455</v>
       </c>
-      <c r="AM6" s="11" t="n">
+      <c r="AQ6" s="11" t="n">
         <v>0.04867833529118113</v>
       </c>
-      <c r="AN6" s="8" t="n">
+      <c r="AR6" s="8" t="n">
         <v>129421024</v>
       </c>
-      <c r="AO6" s="9" t="n">
+      <c r="AS6" s="9" t="n">
         <v>530302.65</v>
       </c>
-      <c r="AP6" s="10" t="n">
+      <c r="AT6" s="10" t="n">
         <v>0.0461</v>
       </c>
-      <c r="AQ6" s="11" t="n">
+      <c r="AU6" s="11" t="n">
         <v>0.05933146465642036</v>
       </c>
-      <c r="AR6" s="8" t="n">
+      <c r="AV6" s="8" t="n">
         <v>122172359</v>
       </c>
-      <c r="AS6" s="9" t="n">
+      <c r="AW6" s="9" t="n">
         <v>503289.03</v>
       </c>
-      <c r="AT6" s="10" t="n">
+      <c r="AX6" s="10" t="n">
         <v>0.0444</v>
       </c>
-      <c r="AU6" s="11" t="n">
+      <c r="AY6" s="11" t="n">
         <v>0.04045226173662547</v>
       </c>
-      <c r="AV6" s="8" t="n">
+      <c r="AZ6" s="8" t="n">
         <v>117422359</v>
       </c>
-      <c r="AW6" s="9" t="n">
+      <c r="BA6" s="9" t="n">
         <v>489005.41</v>
       </c>
-      <c r="AX6" s="10" t="n">
+      <c r="BB6" s="10" t="n">
         <v>0.0443</v>
       </c>
-      <c r="AY6" s="11" t="n">
+      <c r="BC6" s="11" t="n">
         <v>0.07460089770293252</v>
       </c>
-      <c r="AZ6" s="8" t="n">
+      <c r="BD6" s="8" t="n">
         <v>109270669</v>
       </c>
-      <c r="BA6" s="9" t="n">
+      <c r="BE6" s="9" t="n">
         <v>456806.03</v>
       </c>
-      <c r="BB6" s="10" t="n">
+      <c r="BF6" s="10" t="n">
         <v>0.044</v>
       </c>
-      <c r="BC6" s="11" t="n">
+      <c r="BG6" s="11" t="n">
         <v>0.03799307836597426</v>
       </c>
-      <c r="BD6" s="8" t="n">
+      <c r="BH6" s="8" t="n">
         <v>105271096</v>
       </c>
-      <c r="BE6" s="9" t="n">
+      <c r="BI6" s="9" t="n">
         <v>448244.33</v>
       </c>
-      <c r="BF6" s="10" t="n">
+      <c r="BJ6" s="10" t="n">
         <v>0.0455</v>
       </c>
-      <c r="BG6" s="11" t="n">
+      <c r="BK6" s="11" t="n">
         <v>0.04028866499357868</v>
-      </c>
-      <c r="BH6" s="8" t="n">
-        <v>101194120</v>
-      </c>
-      <c r="BI6" s="9" t="n">
-        <v>414642.91</v>
-      </c>
-      <c r="BJ6" s="10" t="n">
-        <v>0.0444</v>
-      </c>
-      <c r="BK6" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="BL6" s="8" t="n">
         <v>101194120</v>
       </c>
       <c r="BM6" s="9" t="n">
+        <v>414642.91</v>
+      </c>
+      <c r="BN6" s="10" t="n">
+        <v>0.0444</v>
+      </c>
+      <c r="BO6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP6" s="8" t="n">
+        <v>101194120</v>
+      </c>
+      <c r="BQ6" s="9" t="n">
         <v>399716.77</v>
       </c>
-      <c r="BN6" s="10" t="n">
+      <c r="BR6" s="10" t="n">
         <v>0.0454</v>
       </c>
-      <c r="BO6" s="11" t="n">
+      <c r="BS6" s="11" t="n">
         <v>0.02222354216593874</v>
       </c>
-      <c r="BP6" s="8" t="n">
+      <c r="BT6" s="8" t="n">
         <v>98994120</v>
       </c>
-      <c r="BQ6" s="9" t="n">
+      <c r="BU6" s="9" t="n">
         <v>442998.69</v>
       </c>
-      <c r="BR6" s="10" t="n">
+      <c r="BV6" s="10" t="n">
         <v>0.0494</v>
       </c>
-      <c r="BS6" s="11" t="n"/>
+      <c r="BW6" s="11" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -1896,88 +1968,88 @@
         <v>0.0497</v>
       </c>
       <c r="AE7" s="11" t="n">
-        <v>0.1392673796002192</v>
+        <v>0.08865063536064391</v>
       </c>
       <c r="AF7" s="8" t="n">
+        <v>45308598</v>
+      </c>
+      <c r="AG7" s="9" t="n">
+        <v>629245.8100000001</v>
+      </c>
+      <c r="AH7" s="10" t="n">
+        <v>0.0485</v>
+      </c>
+      <c r="AI7" s="11" t="n">
+        <v>0.04649493840859896</v>
+      </c>
+      <c r="AJ7" s="8" t="n">
         <v>43295573</v>
       </c>
-      <c r="AG7" s="9" t="n">
+      <c r="AK7" s="9" t="n">
         <v>582455.34</v>
       </c>
-      <c r="AH7" s="10" t="n">
+      <c r="AL7" s="10" t="n">
         <v>0.0463</v>
       </c>
-      <c r="AI7" s="11" t="n">
+      <c r="AM7" s="11" t="n">
         <v>0.02558297621590971</v>
       </c>
-      <c r="AJ7" s="8" t="n">
+      <c r="AN7" s="8" t="n">
         <v>42215573</v>
       </c>
-      <c r="AK7" s="9" t="n">
+      <c r="AO7" s="9" t="n">
         <v>569065.92</v>
       </c>
-      <c r="AL7" s="10" t="n">
+      <c r="AP7" s="10" t="n">
         <v>0.0475</v>
       </c>
-      <c r="AM7" s="11" t="n">
+      <c r="AQ7" s="11" t="n">
         <v>0.03671439253646495</v>
       </c>
-      <c r="AN7" s="8" t="n">
+      <c r="AR7" s="8" t="n">
         <v>40720543</v>
       </c>
-      <c r="AO7" s="9" t="n">
+      <c r="AS7" s="9" t="n">
         <v>569191.75</v>
       </c>
-      <c r="AP7" s="10" t="n">
+      <c r="AT7" s="10" t="n">
         <v>0.0495</v>
       </c>
-      <c r="AQ7" s="11" t="n">
+      <c r="AU7" s="11" t="n">
         <v>0.02815262499999053</v>
       </c>
-      <c r="AR7" s="8" t="n">
+      <c r="AV7" s="8" t="n">
         <v>39605543</v>
       </c>
-      <c r="AS7" s="9" t="n">
+      <c r="AW7" s="9" t="n">
         <v>586716.51</v>
       </c>
-      <c r="AT7" s="10" t="n">
+      <c r="AX7" s="10" t="n">
         <v>0.0518</v>
       </c>
-      <c r="AU7" s="11" t="n">
+      <c r="AY7" s="11" t="n">
         <v>0.08540125861519442</v>
       </c>
-      <c r="AV7" s="8" t="n">
+      <c r="AZ7" s="8" t="n">
         <v>36489310</v>
       </c>
-      <c r="AW7" s="9" t="n">
+      <c r="BA7" s="9" t="n">
         <v>527562.4399999999</v>
       </c>
-      <c r="AX7" s="10" t="n">
+      <c r="BB7" s="10" t="n">
         <v>0.0478</v>
       </c>
-      <c r="AY7" s="11" t="n">
+      <c r="BC7" s="11" t="n">
         <v>0.04294684214648178</v>
-      </c>
-      <c r="AZ7" s="8" t="n">
-        <v>34986740</v>
-      </c>
-      <c r="BA7" s="9" t="n">
-        <v>505838.29</v>
-      </c>
-      <c r="BB7" s="10" t="n">
-        <v>0.0487</v>
-      </c>
-      <c r="BC7" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="BD7" s="8" t="n">
         <v>34986740</v>
       </c>
       <c r="BE7" s="9" t="n">
-        <v>499260.78</v>
+        <v>505838.29</v>
       </c>
       <c r="BF7" s="10" t="n">
-        <v>0.0507</v>
+        <v>0.0487</v>
       </c>
       <c r="BG7" s="11" t="n">
         <v>0</v>
@@ -1986,10 +2058,10 @@
         <v>34986740</v>
       </c>
       <c r="BI7" s="9" t="n">
-        <v>471743.71</v>
+        <v>499260.78</v>
       </c>
       <c r="BJ7" s="10" t="n">
-        <v>0.0505</v>
+        <v>0.0507</v>
       </c>
       <c r="BK7" s="11" t="n">
         <v>0</v>
@@ -1998,10 +2070,10 @@
         <v>34986740</v>
       </c>
       <c r="BM7" s="9" t="n">
-        <v>421275.34</v>
+        <v>471743.71</v>
       </c>
       <c r="BN7" s="10" t="n">
-        <v>0.0479</v>
+        <v>0.0505</v>
       </c>
       <c r="BO7" s="11" t="n">
         <v>0</v>
@@ -2010,12 +2082,24 @@
         <v>34986740</v>
       </c>
       <c r="BQ7" s="9" t="n">
+        <v>421275.34</v>
+      </c>
+      <c r="BR7" s="10" t="n">
+        <v>0.0479</v>
+      </c>
+      <c r="BS7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" s="8" t="n">
+        <v>34986740</v>
+      </c>
+      <c r="BU7" s="9" t="n">
         <v>438313.88</v>
       </c>
-      <c r="BR7" s="10" t="n">
+      <c r="BV7" s="10" t="n">
         <v>0.0489</v>
       </c>
-      <c r="BS7" s="11" t="n"/>
+      <c r="BW7" s="11" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -2121,10 +2205,10 @@
         <v>162039558</v>
       </c>
       <c r="AG8" s="9" t="n">
-        <v>629766.74</v>
+        <v>609511.8</v>
       </c>
       <c r="AH8" s="10" t="n">
-        <v>0.0501</v>
+        <v>0.047</v>
       </c>
       <c r="AI8" s="11" t="n">
         <v>0</v>
@@ -2133,10 +2217,10 @@
         <v>162039558</v>
       </c>
       <c r="AK8" s="9" t="n">
-        <v>631873.26</v>
+        <v>629766.74</v>
       </c>
       <c r="AL8" s="10" t="n">
-        <v>0.0528</v>
+        <v>0.0501</v>
       </c>
       <c r="AM8" s="11" t="n">
         <v>0</v>
@@ -2145,7 +2229,7 @@
         <v>162039558</v>
       </c>
       <c r="AO8" s="9" t="n">
-        <v>607324.26</v>
+        <v>631873.26</v>
       </c>
       <c r="AP8" s="10" t="n">
         <v>0.0528</v>
@@ -2157,10 +2241,10 @@
         <v>162039558</v>
       </c>
       <c r="AS8" s="9" t="n">
-        <v>609835.88</v>
+        <v>607324.26</v>
       </c>
       <c r="AT8" s="10" t="n">
-        <v>0.0538</v>
+        <v>0.0528</v>
       </c>
       <c r="AU8" s="11" t="n">
         <v>0</v>
@@ -2169,72 +2253,84 @@
         <v>162039558</v>
       </c>
       <c r="AW8" s="9" t="n">
+        <v>609835.88</v>
+      </c>
+      <c r="AX8" s="10" t="n">
+        <v>0.0538</v>
+      </c>
+      <c r="AY8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="8" t="n">
+        <v>162039558</v>
+      </c>
+      <c r="BA8" s="9" t="n">
         <v>635114.05</v>
       </c>
-      <c r="AX8" s="10" t="n">
+      <c r="BB8" s="10" t="n">
         <v>0.0575</v>
       </c>
-      <c r="AY8" s="11" t="n">
+      <c r="BC8" s="11" t="n">
         <v>0.0408396826825464</v>
       </c>
-      <c r="AZ8" s="8" t="n">
+      <c r="BD8" s="8" t="n">
         <v>155681572</v>
       </c>
-      <c r="BA8" s="9" t="n">
+      <c r="BE8" s="9" t="n">
         <v>618522.89</v>
       </c>
-      <c r="BB8" s="10" t="n">
+      <c r="BF8" s="10" t="n">
         <v>0.0595</v>
       </c>
-      <c r="BC8" s="11" t="n">
+      <c r="BG8" s="11" t="n">
         <v>0.04960632238493121</v>
       </c>
-      <c r="BD8" s="8" t="n">
+      <c r="BH8" s="8" t="n">
         <v>148323775</v>
       </c>
-      <c r="BE8" s="9" t="n">
+      <c r="BI8" s="9" t="n">
         <v>571491.51</v>
       </c>
-      <c r="BF8" s="10" t="n">
+      <c r="BJ8" s="10" t="n">
         <v>0.058</v>
       </c>
-      <c r="BG8" s="11" t="n">
+      <c r="BK8" s="11" t="n">
         <v>0.05138982123049783</v>
       </c>
-      <c r="BH8" s="8" t="n">
+      <c r="BL8" s="8" t="n">
         <v>141074007</v>
       </c>
-      <c r="BI8" s="9" t="n">
+      <c r="BM8" s="9" t="n">
         <v>561756.7</v>
       </c>
-      <c r="BJ8" s="10" t="n">
+      <c r="BN8" s="10" t="n">
         <v>0.0601</v>
       </c>
-      <c r="BK8" s="11" t="n">
+      <c r="BO8" s="11" t="n">
         <v>-0.01095372515938375</v>
       </c>
-      <c r="BL8" s="8" t="n">
+      <c r="BP8" s="8" t="n">
         <v>142636407</v>
       </c>
-      <c r="BM8" s="9" t="n">
+      <c r="BQ8" s="9" t="n">
         <v>526827.5699999999</v>
       </c>
-      <c r="BN8" s="10" t="n">
+      <c r="BR8" s="10" t="n">
         <v>0.0599</v>
       </c>
-      <c r="BO8" s="11" t="n">
+      <c r="BS8" s="11" t="n">
         <v>0.02369256314048828</v>
       </c>
-      <c r="BP8" s="8" t="n">
+      <c r="BT8" s="8" t="n">
         <v>139335199</v>
       </c>
-      <c r="BQ8" s="9" t="n">
+      <c r="BU8" s="9" t="n">
         <v>551628.05</v>
       </c>
-      <c r="BR8" s="10" t="n">
+      <c r="BV8" s="10" t="n">
         <v>0.0615</v>
       </c>
-      <c r="BS8" s="11" t="n"/>
+      <c r="BW8" s="11" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -2340,10 +2436,10 @@
         <v>5318918</v>
       </c>
       <c r="AG9" s="9" t="n">
-        <v>654386.48</v>
+        <v>611622.38</v>
       </c>
       <c r="AH9" s="10" t="n">
-        <v>0.052</v>
+        <v>0.0471</v>
       </c>
       <c r="AI9" s="11" t="n">
         <v>0</v>
@@ -2352,10 +2448,10 @@
         <v>5318918</v>
       </c>
       <c r="AK9" s="9" t="n">
-        <v>651407.89</v>
+        <v>654386.48</v>
       </c>
       <c r="AL9" s="10" t="n">
-        <v>0.0544</v>
+        <v>0.052</v>
       </c>
       <c r="AM9" s="11" t="n">
         <v>0</v>
@@ -2364,10 +2460,10 @@
         <v>5318918</v>
       </c>
       <c r="AO9" s="9" t="n">
-        <v>679225.83</v>
+        <v>651407.89</v>
       </c>
       <c r="AP9" s="10" t="n">
-        <v>0.059</v>
+        <v>0.0544</v>
       </c>
       <c r="AQ9" s="11" t="n">
         <v>0</v>
@@ -2376,10 +2472,10 @@
         <v>5318918</v>
       </c>
       <c r="AS9" s="9" t="n">
-        <v>742680.52</v>
+        <v>679225.83</v>
       </c>
       <c r="AT9" s="10" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.059</v>
       </c>
       <c r="AU9" s="11" t="n">
         <v>0</v>
@@ -2388,10 +2484,10 @@
         <v>5318918</v>
       </c>
       <c r="AW9" s="9" t="n">
-        <v>764807.22</v>
+        <v>742680.52</v>
       </c>
       <c r="AX9" s="10" t="n">
-        <v>0.0693</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="AY9" s="11" t="n">
         <v>0</v>
@@ -2400,10 +2496,10 @@
         <v>5318918</v>
       </c>
       <c r="BA9" s="9" t="n">
-        <v>713479.66</v>
+        <v>764807.22</v>
       </c>
       <c r="BB9" s="10" t="n">
-        <v>0.0687</v>
+        <v>0.0693</v>
       </c>
       <c r="BC9" s="11" t="n">
         <v>0</v>
@@ -2412,10 +2508,10 @@
         <v>5318918</v>
       </c>
       <c r="BE9" s="9" t="n">
-        <v>636834.05</v>
+        <v>713479.66</v>
       </c>
       <c r="BF9" s="10" t="n">
-        <v>0.0646</v>
+        <v>0.0687</v>
       </c>
       <c r="BG9" s="11" t="n">
         <v>0</v>
@@ -2424,10 +2520,10 @@
         <v>5318918</v>
       </c>
       <c r="BI9" s="9" t="n">
-        <v>663431.3</v>
+        <v>636834.05</v>
       </c>
       <c r="BJ9" s="10" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.0646</v>
       </c>
       <c r="BK9" s="11" t="n">
         <v>0</v>
@@ -2436,10 +2532,10 @@
         <v>5318918</v>
       </c>
       <c r="BM9" s="9" t="n">
-        <v>615630.1899999999</v>
+        <v>663431.3</v>
       </c>
       <c r="BN9" s="10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="BO9" s="11" t="n">
         <v>0</v>
@@ -2448,12 +2544,24 @@
         <v>5318918</v>
       </c>
       <c r="BQ9" s="9" t="n">
+        <v>615630.1899999999</v>
+      </c>
+      <c r="BR9" s="10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BS9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT9" s="8" t="n">
+        <v>5318918</v>
+      </c>
+      <c r="BU9" s="9" t="n">
         <v>614850.96</v>
       </c>
-      <c r="BR9" s="10" t="n">
+      <c r="BV9" s="10" t="n">
         <v>0.06850000000000001</v>
       </c>
-      <c r="BS9" s="11" t="n"/>
+      <c r="BW9" s="11" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -2587,6 +2695,10 @@
       <c r="BQ10" s="9" t="n"/>
       <c r="BR10" s="10" t="n"/>
       <c r="BS10" s="11" t="n"/>
+      <c r="BT10" s="8" t="n"/>
+      <c r="BU10" s="9" t="n"/>
+      <c r="BV10" s="10" t="n"/>
+      <c r="BW10" s="11" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -2692,34 +2804,34 @@
         <v>12435671</v>
       </c>
       <c r="AG11" s="9" t="n">
+        <v>467245.47</v>
+      </c>
+      <c r="AH11" s="10" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="AI11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="8" t="n">
+        <v>12435671</v>
+      </c>
+      <c r="AK11" s="9" t="n">
         <v>433656.72</v>
       </c>
-      <c r="AH11" s="10" t="n">
+      <c r="AL11" s="10" t="n">
         <v>0.0345</v>
       </c>
-      <c r="AI11" s="11" t="n">
+      <c r="AM11" s="11" t="n">
         <v>0.008106571584148119</v>
-      </c>
-      <c r="AJ11" s="8" t="n">
-        <v>12335671</v>
-      </c>
-      <c r="AK11" s="9" t="n">
-        <v>422743.45</v>
-      </c>
-      <c r="AL11" s="10" t="n">
-        <v>0.0353</v>
-      </c>
-      <c r="AM11" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="AN11" s="8" t="n">
         <v>12335671</v>
       </c>
       <c r="AO11" s="9" t="n">
-        <v>394679.79</v>
+        <v>422743.45</v>
       </c>
       <c r="AP11" s="10" t="n">
-        <v>0.0343</v>
+        <v>0.0353</v>
       </c>
       <c r="AQ11" s="11" t="n">
         <v>0</v>
@@ -2728,10 +2840,10 @@
         <v>12335671</v>
       </c>
       <c r="AS11" s="9" t="n">
-        <v>395123.88</v>
+        <v>394679.79</v>
       </c>
       <c r="AT11" s="10" t="n">
-        <v>0.0349</v>
+        <v>0.0343</v>
       </c>
       <c r="AU11" s="11" t="n">
         <v>0</v>
@@ -2740,72 +2852,84 @@
         <v>12335671</v>
       </c>
       <c r="AW11" s="9" t="n">
+        <v>395123.88</v>
+      </c>
+      <c r="AX11" s="10" t="n">
+        <v>0.0349</v>
+      </c>
+      <c r="AY11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" s="8" t="n">
+        <v>12335671</v>
+      </c>
+      <c r="BA11" s="9" t="n">
         <v>392669.08</v>
       </c>
-      <c r="AX11" s="10" t="n">
+      <c r="BB11" s="10" t="n">
         <v>0.0356</v>
       </c>
-      <c r="AY11" s="11" t="n">
+      <c r="BC11" s="11" t="n">
         <v>0.00852700604200313</v>
       </c>
-      <c r="AZ11" s="8" t="n">
+      <c r="BD11" s="8" t="n">
         <v>12231374</v>
       </c>
-      <c r="BA11" s="9" t="n">
+      <c r="BE11" s="9" t="n">
         <v>364103.54</v>
       </c>
-      <c r="BB11" s="10" t="n">
+      <c r="BF11" s="10" t="n">
         <v>0.0351</v>
       </c>
-      <c r="BC11" s="11" t="n">
+      <c r="BG11" s="11" t="n">
         <v>0.1078930368366115</v>
       </c>
-      <c r="BD11" s="8" t="n">
+      <c r="BH11" s="8" t="n">
         <v>11040212</v>
       </c>
-      <c r="BE11" s="9" t="n">
+      <c r="BI11" s="9" t="n">
         <v>323345.73</v>
       </c>
-      <c r="BF11" s="10" t="n">
+      <c r="BJ11" s="10" t="n">
         <v>0.0328</v>
       </c>
-      <c r="BG11" s="11" t="n">
+      <c r="BK11" s="11" t="n">
         <v>0.06163142499453569</v>
       </c>
-      <c r="BH11" s="8" t="n">
+      <c r="BL11" s="8" t="n">
         <v>10399289</v>
       </c>
-      <c r="BI11" s="9" t="n">
+      <c r="BM11" s="9" t="n">
         <v>277224.25</v>
       </c>
-      <c r="BJ11" s="10" t="n">
+      <c r="BN11" s="10" t="n">
         <v>0.0297</v>
       </c>
-      <c r="BK11" s="11" t="n">
+      <c r="BO11" s="11" t="n">
         <v>0.03283692525275198</v>
       </c>
-      <c r="BL11" s="8" t="n">
+      <c r="BP11" s="8" t="n">
         <v>10068665</v>
       </c>
-      <c r="BM11" s="9" t="n">
+      <c r="BQ11" s="9" t="n">
         <v>260285.06</v>
       </c>
-      <c r="BN11" s="10" t="n">
+      <c r="BR11" s="10" t="n">
         <v>0.0296</v>
       </c>
-      <c r="BO11" s="11" t="n">
+      <c r="BS11" s="11" t="n">
         <v>0.07897007813229198</v>
       </c>
-      <c r="BP11" s="8" t="n">
+      <c r="BT11" s="8" t="n">
         <v>9331737</v>
       </c>
-      <c r="BQ11" s="9" t="n">
+      <c r="BU11" s="9" t="n">
         <v>279004.94</v>
       </c>
-      <c r="BR11" s="10" t="n">
+      <c r="BV11" s="10" t="n">
         <v>0.0311</v>
       </c>
-      <c r="BS11" s="11" t="n"/>
+      <c r="BW11" s="11" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -2905,40 +3029,40 @@
         <v>0.026</v>
       </c>
       <c r="AE12" s="11" t="n">
-        <v>0.1751445301807795</v>
+        <v>0.07485632112907131</v>
       </c>
       <c r="AF12" s="8" t="n">
+        <v>19831378</v>
+      </c>
+      <c r="AG12" s="9" t="n">
+        <v>322101.24</v>
+      </c>
+      <c r="AH12" s="10" t="n">
+        <v>0.0248</v>
+      </c>
+      <c r="AI12" s="11" t="n">
+        <v>0.09330382775845011</v>
+      </c>
+      <c r="AJ12" s="8" t="n">
         <v>18138945</v>
       </c>
-      <c r="AG12" s="9" t="n">
+      <c r="AK12" s="9" t="n">
         <v>279611.84</v>
       </c>
-      <c r="AH12" s="10" t="n">
+      <c r="AL12" s="10" t="n">
         <v>0.0222</v>
       </c>
-      <c r="AI12" s="11" t="n">
+      <c r="AM12" s="11" t="n">
         <v>-0.0303656466471499</v>
-      </c>
-      <c r="AJ12" s="8" t="n">
-        <v>18706995</v>
-      </c>
-      <c r="AK12" s="9" t="n">
-        <v>259110.59</v>
-      </c>
-      <c r="AL12" s="10" t="n">
-        <v>0.0216</v>
-      </c>
-      <c r="AM12" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="AN12" s="8" t="n">
         <v>18706995</v>
       </c>
       <c r="AO12" s="9" t="n">
-        <v>272149.36</v>
+        <v>259110.59</v>
       </c>
       <c r="AP12" s="10" t="n">
-        <v>0.0237</v>
+        <v>0.0216</v>
       </c>
       <c r="AQ12" s="11" t="n">
         <v>0</v>
@@ -2947,58 +3071,58 @@
         <v>18706995</v>
       </c>
       <c r="AS12" s="9" t="n">
+        <v>272149.36</v>
+      </c>
+      <c r="AT12" s="10" t="n">
+        <v>0.0237</v>
+      </c>
+      <c r="AU12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" s="8" t="n">
+        <v>18706995</v>
+      </c>
+      <c r="AW12" s="9" t="n">
         <v>274599.98</v>
       </c>
-      <c r="AT12" s="10" t="n">
+      <c r="AX12" s="10" t="n">
         <v>0.0242</v>
       </c>
-      <c r="AU12" s="11" t="n">
+      <c r="AY12" s="11" t="n">
         <v>0.00797456974367416</v>
       </c>
-      <c r="AV12" s="8" t="n">
+      <c r="AZ12" s="8" t="n">
         <v>18558995</v>
       </c>
-      <c r="AW12" s="9" t="n">
+      <c r="BA12" s="9" t="n">
         <v>320810.79</v>
       </c>
-      <c r="AX12" s="10" t="n">
+      <c r="BB12" s="10" t="n">
         <v>0.0291</v>
       </c>
-      <c r="AY12" s="11" t="n">
+      <c r="BC12" s="11" t="n">
         <v>0.01185405417517898</v>
       </c>
-      <c r="AZ12" s="8" t="n">
+      <c r="BD12" s="8" t="n">
         <v>18341573</v>
       </c>
-      <c r="BA12" s="9" t="n">
+      <c r="BE12" s="9" t="n">
         <v>300178.18</v>
       </c>
-      <c r="BB12" s="10" t="n">
+      <c r="BF12" s="10" t="n">
         <v>0.0289</v>
       </c>
-      <c r="BC12" s="11" t="n">
+      <c r="BG12" s="11" t="n">
         <v>-0.01953282340226823</v>
-      </c>
-      <c r="BD12" s="8" t="n">
-        <v>18706973</v>
-      </c>
-      <c r="BE12" s="9" t="n">
-        <v>293231.8</v>
-      </c>
-      <c r="BF12" s="10" t="n">
-        <v>0.0298</v>
-      </c>
-      <c r="BG12" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="BH12" s="8" t="n">
         <v>18706973</v>
       </c>
       <c r="BI12" s="9" t="n">
-        <v>297908.55</v>
+        <v>293231.8</v>
       </c>
       <c r="BJ12" s="10" t="n">
-        <v>0.0319</v>
+        <v>0.0298</v>
       </c>
       <c r="BK12" s="11" t="n">
         <v>0</v>
@@ -3007,10 +3131,10 @@
         <v>18706973</v>
       </c>
       <c r="BM12" s="9" t="n">
-        <v>294644.18</v>
+        <v>297908.55</v>
       </c>
       <c r="BN12" s="10" t="n">
-        <v>0.0335</v>
+        <v>0.0319</v>
       </c>
       <c r="BO12" s="11" t="n">
         <v>0</v>
@@ -3019,12 +3143,24 @@
         <v>18706973</v>
       </c>
       <c r="BQ12" s="9" t="n">
+        <v>294644.18</v>
+      </c>
+      <c r="BR12" s="10" t="n">
+        <v>0.0335</v>
+      </c>
+      <c r="BS12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT12" s="8" t="n">
+        <v>18706973</v>
+      </c>
+      <c r="BU12" s="9" t="n">
         <v>322779.47</v>
       </c>
-      <c r="BR12" s="10" t="n">
+      <c r="BV12" s="10" t="n">
         <v>0.036</v>
       </c>
-      <c r="BS12" s="11" t="n"/>
+      <c r="BW12" s="11" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -3130,10 +3266,10 @@
         <v>33244875</v>
       </c>
       <c r="AG13" s="9" t="n">
-        <v>409842.82</v>
+        <v>425434.67</v>
       </c>
       <c r="AH13" s="10" t="n">
-        <v>0.0326</v>
+        <v>0.0328</v>
       </c>
       <c r="AI13" s="11" t="n">
         <v>0</v>
@@ -3142,58 +3278,58 @@
         <v>33244875</v>
       </c>
       <c r="AK13" s="9" t="n">
+        <v>409842.82</v>
+      </c>
+      <c r="AL13" s="10" t="n">
+        <v>0.0326</v>
+      </c>
+      <c r="AM13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="8" t="n">
+        <v>33244875</v>
+      </c>
+      <c r="AO13" s="9" t="n">
         <v>376199.01</v>
       </c>
-      <c r="AL13" s="10" t="n">
+      <c r="AP13" s="10" t="n">
         <v>0.0314</v>
       </c>
-      <c r="AM13" s="11" t="n">
+      <c r="AQ13" s="11" t="n">
         <v>0.01837960782511803</v>
       </c>
-      <c r="AN13" s="8" t="n">
+      <c r="AR13" s="8" t="n">
         <v>32644875</v>
       </c>
-      <c r="AO13" s="9" t="n">
+      <c r="AS13" s="9" t="n">
         <v>341204.23</v>
       </c>
-      <c r="AP13" s="10" t="n">
+      <c r="AT13" s="10" t="n">
         <v>0.0297</v>
       </c>
-      <c r="AQ13" s="11" t="n">
+      <c r="AU13" s="11" t="n">
         <v>0.0842854566355568</v>
       </c>
-      <c r="AR13" s="8" t="n">
+      <c r="AV13" s="8" t="n">
         <v>30107270</v>
       </c>
-      <c r="AS13" s="9" t="n">
+      <c r="AW13" s="9" t="n">
         <v>321666.07</v>
       </c>
-      <c r="AT13" s="10" t="n">
+      <c r="AX13" s="10" t="n">
         <v>0.0284</v>
       </c>
-      <c r="AU13" s="11" t="n">
+      <c r="AY13" s="11" t="n">
         <v>0.1045592607036581</v>
-      </c>
-      <c r="AV13" s="8" t="n">
-        <v>27257270</v>
-      </c>
-      <c r="AW13" s="9" t="n">
-        <v>326869.18</v>
-      </c>
-      <c r="AX13" s="10" t="n">
-        <v>0.0296</v>
-      </c>
-      <c r="AY13" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="AZ13" s="8" t="n">
         <v>27257270</v>
       </c>
       <c r="BA13" s="9" t="n">
-        <v>324961.17</v>
+        <v>326869.18</v>
       </c>
       <c r="BB13" s="10" t="n">
-        <v>0.0313</v>
+        <v>0.0296</v>
       </c>
       <c r="BC13" s="11" t="n">
         <v>0</v>
@@ -3202,10 +3338,10 @@
         <v>27257270</v>
       </c>
       <c r="BE13" s="9" t="n">
-        <v>322998.65</v>
+        <v>324961.17</v>
       </c>
       <c r="BF13" s="10" t="n">
-        <v>0.0328</v>
+        <v>0.0313</v>
       </c>
       <c r="BG13" s="11" t="n">
         <v>0</v>
@@ -3214,10 +3350,10 @@
         <v>27257270</v>
       </c>
       <c r="BI13" s="9" t="n">
-        <v>300375.12</v>
+        <v>322998.65</v>
       </c>
       <c r="BJ13" s="10" t="n">
-        <v>0.0321</v>
+        <v>0.0328</v>
       </c>
       <c r="BK13" s="11" t="n">
         <v>0</v>
@@ -3226,10 +3362,10 @@
         <v>27257270</v>
       </c>
       <c r="BM13" s="9" t="n">
-        <v>276811.21</v>
+        <v>300375.12</v>
       </c>
       <c r="BN13" s="10" t="n">
-        <v>0.0315</v>
+        <v>0.0321</v>
       </c>
       <c r="BO13" s="11" t="n">
         <v>0</v>
@@ -3238,12 +3374,24 @@
         <v>27257270</v>
       </c>
       <c r="BQ13" s="9" t="n">
+        <v>276811.21</v>
+      </c>
+      <c r="BR13" s="10" t="n">
+        <v>0.0315</v>
+      </c>
+      <c r="BS13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT13" s="8" t="n">
+        <v>27257270</v>
+      </c>
+      <c r="BU13" s="9" t="n">
         <v>268783.94</v>
       </c>
-      <c r="BR13" s="10" t="n">
+      <c r="BV13" s="10" t="n">
         <v>0.03</v>
       </c>
-      <c r="BS13" s="11" t="n"/>
+      <c r="BW13" s="11" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -3343,28 +3491,28 @@
         <v>0.0199</v>
       </c>
       <c r="AE14" s="11" t="n">
-        <v>0.7641415818860701</v>
+        <v>-0.06831357175852101</v>
       </c>
       <c r="AF14" s="8" t="n">
-        <v>9306473</v>
+        <v>17621740</v>
       </c>
       <c r="AG14" s="9" t="n">
-        <v>137949.85</v>
+        <v>274916.77</v>
       </c>
       <c r="AH14" s="10" t="n">
-        <v>0.011</v>
+        <v>0.0212</v>
       </c>
       <c r="AI14" s="11" t="n">
-        <v>0</v>
+        <v>0.8934928409505942</v>
       </c>
       <c r="AJ14" s="8" t="n">
         <v>9306473</v>
       </c>
       <c r="AK14" s="9" t="n">
-        <v>134180.73</v>
+        <v>137949.85</v>
       </c>
       <c r="AL14" s="10" t="n">
-        <v>0.0112</v>
+        <v>0.011</v>
       </c>
       <c r="AM14" s="11" t="n">
         <v>0</v>
@@ -3373,10 +3521,10 @@
         <v>9306473</v>
       </c>
       <c r="AO14" s="9" t="n">
-        <v>136767.93</v>
+        <v>134180.73</v>
       </c>
       <c r="AP14" s="10" t="n">
-        <v>0.0119</v>
+        <v>0.0112</v>
       </c>
       <c r="AQ14" s="11" t="n">
         <v>0</v>
@@ -3385,10 +3533,10 @@
         <v>9306473</v>
       </c>
       <c r="AS14" s="9" t="n">
-        <v>140434.68</v>
+        <v>136767.93</v>
       </c>
       <c r="AT14" s="10" t="n">
-        <v>0.0124</v>
+        <v>0.0119</v>
       </c>
       <c r="AU14" s="11" t="n">
         <v>0</v>
@@ -3397,10 +3545,10 @@
         <v>9306473</v>
       </c>
       <c r="AW14" s="9" t="n">
-        <v>149071.08</v>
+        <v>140434.68</v>
       </c>
       <c r="AX14" s="10" t="n">
-        <v>0.0135</v>
+        <v>0.0124</v>
       </c>
       <c r="AY14" s="11" t="n">
         <v>0</v>
@@ -3409,10 +3557,10 @@
         <v>9306473</v>
       </c>
       <c r="BA14" s="9" t="n">
-        <v>145432.25</v>
+        <v>149071.08</v>
       </c>
       <c r="BB14" s="10" t="n">
-        <v>0.014</v>
+        <v>0.0135</v>
       </c>
       <c r="BC14" s="11" t="n">
         <v>0</v>
@@ -3421,10 +3569,10 @@
         <v>9306473</v>
       </c>
       <c r="BE14" s="9" t="n">
-        <v>139606.4</v>
+        <v>145432.25</v>
       </c>
       <c r="BF14" s="10" t="n">
-        <v>0.0142</v>
+        <v>0.014</v>
       </c>
       <c r="BG14" s="11" t="n">
         <v>0</v>
@@ -3433,10 +3581,10 @@
         <v>9306473</v>
       </c>
       <c r="BI14" s="9" t="n">
-        <v>146172.12</v>
+        <v>139606.4</v>
       </c>
       <c r="BJ14" s="10" t="n">
-        <v>0.0156</v>
+        <v>0.0142</v>
       </c>
       <c r="BK14" s="11" t="n">
         <v>0</v>
@@ -3445,10 +3593,10 @@
         <v>9306473</v>
       </c>
       <c r="BM14" s="9" t="n">
-        <v>157065.34</v>
+        <v>146172.12</v>
       </c>
       <c r="BN14" s="10" t="n">
-        <v>0.0178</v>
+        <v>0.0156</v>
       </c>
       <c r="BO14" s="11" t="n">
         <v>0</v>
@@ -3457,12 +3605,24 @@
         <v>9306473</v>
       </c>
       <c r="BQ14" s="9" t="n">
+        <v>157065.34</v>
+      </c>
+      <c r="BR14" s="10" t="n">
+        <v>0.0178</v>
+      </c>
+      <c r="BS14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT14" s="8" t="n">
+        <v>9306473</v>
+      </c>
+      <c r="BU14" s="9" t="n">
         <v>174943.08</v>
       </c>
-      <c r="BR14" s="10" t="n">
+      <c r="BV14" s="10" t="n">
         <v>0.0195</v>
       </c>
-      <c r="BS14" s="11" t="n"/>
+      <c r="BW14" s="11" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -3568,10 +3728,10 @@
         <v>21167034</v>
       </c>
       <c r="AG15" s="9" t="n">
-        <v>434876.71</v>
+        <v>444846.39</v>
       </c>
       <c r="AH15" s="10" t="n">
-        <v>0.0346</v>
+        <v>0.0343</v>
       </c>
       <c r="AI15" s="11" t="n">
         <v>0</v>
@@ -3580,10 +3740,10 @@
         <v>21167034</v>
       </c>
       <c r="AK15" s="9" t="n">
-        <v>397601.57</v>
+        <v>434876.71</v>
       </c>
       <c r="AL15" s="10" t="n">
-        <v>0.0332</v>
+        <v>0.0346</v>
       </c>
       <c r="AM15" s="11" t="n">
         <v>0</v>
@@ -3592,10 +3752,10 @@
         <v>21167034</v>
       </c>
       <c r="AO15" s="9" t="n">
-        <v>399802.94</v>
+        <v>397601.57</v>
       </c>
       <c r="AP15" s="10" t="n">
-        <v>0.0348</v>
+        <v>0.0332</v>
       </c>
       <c r="AQ15" s="11" t="n">
         <v>0</v>
@@ -3604,42 +3764,50 @@
         <v>21167034</v>
       </c>
       <c r="AS15" s="9" t="n">
+        <v>399802.94</v>
+      </c>
+      <c r="AT15" s="10" t="n">
+        <v>0.0348</v>
+      </c>
+      <c r="AU15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" s="8" t="n">
+        <v>21167034</v>
+      </c>
+      <c r="AW15" s="9" t="n">
         <v>405200.53</v>
       </c>
-      <c r="AT15" s="10" t="n">
+      <c r="AX15" s="10" t="n">
         <v>0.0358</v>
       </c>
-      <c r="AU15" s="11" t="n">
+      <c r="AY15" s="11" t="n">
         <v>0.01098531912399817</v>
       </c>
-      <c r="AV15" s="8" t="n">
+      <c r="AZ15" s="8" t="n">
         <v>20937034</v>
       </c>
-      <c r="AW15" s="9" t="n">
+      <c r="BA15" s="9" t="n">
         <v>420750.64</v>
       </c>
-      <c r="AX15" s="10" t="n">
+      <c r="BB15" s="10" t="n">
         <v>0.0381</v>
       </c>
-      <c r="AY15" s="11" t="n">
+      <c r="BC15" s="11" t="n">
         <v>0.7744638647975486</v>
       </c>
-      <c r="AZ15" s="8" t="n">
+      <c r="BD15" s="8" t="n">
         <v>11799076</v>
       </c>
-      <c r="BA15" s="9" t="n">
+      <c r="BE15" s="9" t="n">
         <v>219014.45</v>
       </c>
-      <c r="BB15" s="10" t="n">
+      <c r="BF15" s="10" t="n">
         <v>0.0211</v>
       </c>
-      <c r="BC15" s="11" t="n">
+      <c r="BG15" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="BD15" s="8" t="n"/>
-      <c r="BE15" s="9" t="n"/>
-      <c r="BF15" s="10" t="n"/>
-      <c r="BG15" s="11" t="n"/>
       <c r="BH15" s="8" t="n"/>
       <c r="BI15" s="9" t="n"/>
       <c r="BJ15" s="10" t="n"/>
@@ -3652,6 +3820,10 @@
       <c r="BQ15" s="9" t="n"/>
       <c r="BR15" s="10" t="n"/>
       <c r="BS15" s="11" t="n"/>
+      <c r="BT15" s="8" t="n"/>
+      <c r="BU15" s="9" t="n"/>
+      <c r="BV15" s="10" t="n"/>
+      <c r="BW15" s="11" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -3751,64 +3923,64 @@
         <v>0.0344</v>
       </c>
       <c r="AE16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="8" t="n">
+        <v>2746670</v>
+      </c>
+      <c r="AG16" s="9" t="n">
+        <v>436720.53</v>
+      </c>
+      <c r="AH16" s="10" t="n">
+        <v>0.0337</v>
+      </c>
+      <c r="AI16" s="11" t="n">
         <v>0.01854138622819997</v>
-      </c>
-      <c r="AF16" s="8" t="n">
-        <v>2696670</v>
-      </c>
-      <c r="AG16" s="9" t="n">
-        <v>436483.01</v>
-      </c>
-      <c r="AH16" s="10" t="n">
-        <v>0.0347</v>
-      </c>
-      <c r="AI16" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="AJ16" s="8" t="n">
         <v>2696670</v>
       </c>
       <c r="AK16" s="9" t="n">
+        <v>436483.01</v>
+      </c>
+      <c r="AL16" s="10" t="n">
+        <v>0.0347</v>
+      </c>
+      <c r="AM16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" s="8" t="n">
+        <v>2696670</v>
+      </c>
+      <c r="AO16" s="9" t="n">
         <v>432249.23</v>
       </c>
-      <c r="AL16" s="10" t="n">
+      <c r="AP16" s="10" t="n">
         <v>0.0361</v>
       </c>
-      <c r="AM16" s="11" t="n">
+      <c r="AQ16" s="11" t="n">
         <v>-0.01820386140308082</v>
       </c>
-      <c r="AN16" s="8" t="n">
+      <c r="AR16" s="8" t="n">
         <v>2746670</v>
       </c>
-      <c r="AO16" s="9" t="n">
+      <c r="AS16" s="9" t="n">
         <v>406259.96</v>
       </c>
-      <c r="AP16" s="10" t="n">
+      <c r="AT16" s="10" t="n">
         <v>0.0353</v>
       </c>
-      <c r="AQ16" s="11" t="n">
+      <c r="AU16" s="11" t="n">
         <v>-0.09100927632732893</v>
-      </c>
-      <c r="AR16" s="8" t="n">
-        <v>3021670</v>
-      </c>
-      <c r="AS16" s="9" t="n">
-        <v>380972.15</v>
-      </c>
-      <c r="AT16" s="10" t="n">
-        <v>0.0336</v>
-      </c>
-      <c r="AU16" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="AV16" s="8" t="n">
         <v>3021670</v>
       </c>
       <c r="AW16" s="9" t="n">
-        <v>374687.08</v>
+        <v>380972.15</v>
       </c>
       <c r="AX16" s="10" t="n">
-        <v>0.0339</v>
+        <v>0.0336</v>
       </c>
       <c r="AY16" s="11" t="n">
         <v>0</v>
@@ -3817,10 +3989,10 @@
         <v>3021670</v>
       </c>
       <c r="BA16" s="9" t="n">
-        <v>372239.53</v>
+        <v>374687.08</v>
       </c>
       <c r="BB16" s="10" t="n">
-        <v>0.0358</v>
+        <v>0.0339</v>
       </c>
       <c r="BC16" s="11" t="n">
         <v>0</v>
@@ -3829,34 +4001,34 @@
         <v>3021670</v>
       </c>
       <c r="BE16" s="9" t="n">
+        <v>372239.53</v>
+      </c>
+      <c r="BF16" s="10" t="n">
+        <v>0.0358</v>
+      </c>
+      <c r="BG16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" s="8" t="n">
+        <v>3021670</v>
+      </c>
+      <c r="BI16" s="9" t="n">
         <v>370366.09</v>
       </c>
-      <c r="BF16" s="10" t="n">
+      <c r="BJ16" s="10" t="n">
         <v>0.0376</v>
       </c>
-      <c r="BG16" s="11" t="n">
+      <c r="BK16" s="11" t="n">
         <v>0.001190161420612721</v>
-      </c>
-      <c r="BH16" s="8" t="n">
-        <v>3018078</v>
-      </c>
-      <c r="BI16" s="9" t="n">
-        <v>347747.47</v>
-      </c>
-      <c r="BJ16" s="10" t="n">
-        <v>0.0372</v>
-      </c>
-      <c r="BK16" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="BL16" s="8" t="n">
         <v>3018078</v>
       </c>
       <c r="BM16" s="9" t="n">
-        <v>360535.07</v>
+        <v>347747.47</v>
       </c>
       <c r="BN16" s="10" t="n">
-        <v>0.041</v>
+        <v>0.0372</v>
       </c>
       <c r="BO16" s="11" t="n">
         <v>0</v>
@@ -3865,12 +4037,24 @@
         <v>3018078</v>
       </c>
       <c r="BQ16" s="9" t="n">
+        <v>360535.07</v>
+      </c>
+      <c r="BR16" s="10" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="BS16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT16" s="8" t="n">
+        <v>3018078</v>
+      </c>
+      <c r="BU16" s="9" t="n">
         <v>371545.02</v>
       </c>
-      <c r="BR16" s="10" t="n">
+      <c r="BV16" s="10" t="n">
         <v>0.0414</v>
       </c>
-      <c r="BS16" s="11" t="n"/>
+      <c r="BW16" s="11" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -3970,12 +4154,20 @@
         <v>0.0112</v>
       </c>
       <c r="AE17" s="11" t="n">
+        <v>0.6557662214497397</v>
+      </c>
+      <c r="AF17" s="8" t="n">
+        <v>2811139</v>
+      </c>
+      <c r="AG17" s="9" t="n">
+        <v>88199.49000000001</v>
+      </c>
+      <c r="AH17" s="10" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="AI17" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="AF17" s="8" t="n"/>
-      <c r="AG17" s="9" t="n"/>
-      <c r="AH17" s="10" t="n"/>
-      <c r="AI17" s="11" t="n"/>
       <c r="AJ17" s="8" t="n"/>
       <c r="AK17" s="9" t="n"/>
       <c r="AL17" s="10" t="n"/>
@@ -4012,6 +4204,10 @@
       <c r="BQ17" s="9" t="n"/>
       <c r="BR17" s="10" t="n"/>
       <c r="BS17" s="11" t="n"/>
+      <c r="BT17" s="8" t="n"/>
+      <c r="BU17" s="9" t="n"/>
+      <c r="BV17" s="10" t="n"/>
+      <c r="BW17" s="11" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -4111,126 +4307,138 @@
         <v>0.0123</v>
       </c>
       <c r="AE18" s="11" t="n">
-        <v>0.1359983309421211</v>
+        <v>0.02860906275493533</v>
       </c>
       <c r="AF18" s="8" t="n">
+        <v>17405149</v>
+      </c>
+      <c r="AG18" s="9" t="n">
+        <v>164043.53</v>
+      </c>
+      <c r="AH18" s="10" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="AI18" s="11" t="n">
+        <v>0.1044024130018492</v>
+      </c>
+      <c r="AJ18" s="8" t="n">
         <v>15759789</v>
       </c>
-      <c r="AG18" s="9" t="n">
+      <c r="AK18" s="9" t="n">
         <v>153571.26</v>
       </c>
-      <c r="AH18" s="10" t="n">
+      <c r="AL18" s="10" t="n">
         <v>0.0122</v>
       </c>
-      <c r="AI18" s="11" t="n">
+      <c r="AM18" s="11" t="n">
         <v>0.04036608437732761</v>
       </c>
-      <c r="AJ18" s="8" t="n">
+      <c r="AN18" s="8" t="n">
         <v>15148311</v>
       </c>
-      <c r="AK18" s="9" t="n">
+      <c r="AO18" s="9" t="n">
         <v>148741.27</v>
       </c>
-      <c r="AL18" s="10" t="n">
+      <c r="AP18" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="AM18" s="11" t="n">
+      <c r="AQ18" s="11" t="n">
         <v>0.02447981732333564</v>
       </c>
-      <c r="AN18" s="8" t="n">
+      <c r="AR18" s="8" t="n">
         <v>14786344</v>
       </c>
-      <c r="AO18" s="9" t="n">
+      <c r="AS18" s="9" t="n">
         <v>145061.43</v>
       </c>
-      <c r="AP18" s="10" t="n">
+      <c r="AT18" s="10" t="n">
         <v>0.0126</v>
       </c>
-      <c r="AQ18" s="11" t="n">
+      <c r="AU18" s="11" t="n">
         <v>0.02183487170521033</v>
       </c>
-      <c r="AR18" s="8" t="n">
+      <c r="AV18" s="8" t="n">
         <v>14470385</v>
       </c>
-      <c r="AS18" s="9" t="n">
+      <c r="AW18" s="9" t="n">
         <v>140333.79</v>
       </c>
-      <c r="AT18" s="10" t="n">
+      <c r="AX18" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="AU18" s="11" t="n">
+      <c r="AY18" s="11" t="n">
         <v>0.01486488524161312</v>
-      </c>
-      <c r="AV18" s="8" t="n">
-        <v>14258435</v>
-      </c>
-      <c r="AW18" s="9" t="n">
-        <v>141151.38</v>
-      </c>
-      <c r="AX18" s="10" t="n">
-        <v>0.0128</v>
-      </c>
-      <c r="AY18" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="AZ18" s="8" t="n">
         <v>14258435</v>
       </c>
       <c r="BA18" s="9" t="n">
-        <v>132603.45</v>
+        <v>141151.38</v>
       </c>
       <c r="BB18" s="10" t="n">
         <v>0.0128</v>
       </c>
       <c r="BC18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" s="8" t="n">
+        <v>14258435</v>
+      </c>
+      <c r="BE18" s="9" t="n">
+        <v>132603.45</v>
+      </c>
+      <c r="BF18" s="10" t="n">
+        <v>0.0128</v>
+      </c>
+      <c r="BG18" s="11" t="n">
         <v>0.0231160633003793</v>
       </c>
-      <c r="BD18" s="8" t="n">
+      <c r="BH18" s="8" t="n">
         <v>13936283</v>
       </c>
-      <c r="BE18" s="9" t="n">
+      <c r="BI18" s="9" t="n">
         <v>123789.03</v>
       </c>
-      <c r="BF18" s="10" t="n">
+      <c r="BJ18" s="10" t="n">
         <v>0.0126</v>
       </c>
-      <c r="BG18" s="11" t="n">
+      <c r="BK18" s="11" t="n">
         <v>0.07172012123664578</v>
       </c>
-      <c r="BH18" s="8" t="n">
+      <c r="BL18" s="8" t="n">
         <v>13003659</v>
       </c>
-      <c r="BI18" s="9" t="n">
+      <c r="BM18" s="9" t="n">
         <v>115264.43</v>
       </c>
-      <c r="BJ18" s="10" t="n">
+      <c r="BN18" s="10" t="n">
         <v>0.0123</v>
       </c>
-      <c r="BK18" s="11" t="n">
+      <c r="BO18" s="11" t="n">
         <v>0.132761983775747</v>
       </c>
-      <c r="BL18" s="8" t="n">
+      <c r="BP18" s="8" t="n">
         <v>11479604</v>
       </c>
-      <c r="BM18" s="9" t="n">
+      <c r="BQ18" s="9" t="n">
         <v>100630.21</v>
       </c>
-      <c r="BN18" s="10" t="n">
+      <c r="BR18" s="10" t="n">
         <v>0.0114</v>
       </c>
-      <c r="BO18" s="11" t="n">
+      <c r="BS18" s="11" t="n">
         <v>0.2957940438149267</v>
       </c>
-      <c r="BP18" s="8" t="n">
+      <c r="BT18" s="8" t="n">
         <v>8859127</v>
       </c>
-      <c r="BQ18" s="9" t="n">
+      <c r="BU18" s="9" t="n">
         <v>85955.67999999999</v>
       </c>
-      <c r="BR18" s="10" t="n">
+      <c r="BV18" s="10" t="n">
         <v>0.009599999999999999</v>
       </c>
-      <c r="BS18" s="11" t="n"/>
+      <c r="BW18" s="11" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -4330,126 +4538,138 @@
         <v>0.0125</v>
       </c>
       <c r="AE19" s="11" t="n">
-        <v>0.08022088846862326</v>
+        <v>0.02078030694418823</v>
       </c>
       <c r="AF19" s="8" t="n">
+        <v>10765866</v>
+      </c>
+      <c r="AG19" s="9" t="n">
+        <v>164857.71</v>
+      </c>
+      <c r="AH19" s="10" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="AI19" s="11" t="n">
+        <v>0.05823053317160534</v>
+      </c>
+      <c r="AJ19" s="8" t="n">
         <v>10173460</v>
       </c>
-      <c r="AG19" s="9" t="n">
+      <c r="AK19" s="9" t="n">
         <v>152734.15</v>
       </c>
-      <c r="AH19" s="10" t="n">
+      <c r="AL19" s="10" t="n">
         <v>0.0121</v>
       </c>
-      <c r="AI19" s="11" t="n">
+      <c r="AM19" s="11" t="n">
         <v>0.01848262661129821</v>
       </c>
-      <c r="AJ19" s="8" t="n">
+      <c r="AN19" s="8" t="n">
         <v>9988840</v>
       </c>
-      <c r="AK19" s="9" t="n">
+      <c r="AO19" s="9" t="n">
         <v>150162.23</v>
       </c>
-      <c r="AL19" s="10" t="n">
+      <c r="AP19" s="10" t="n">
         <v>0.0125</v>
       </c>
-      <c r="AM19" s="11" t="n">
+      <c r="AQ19" s="11" t="n">
         <v>0.11089473889663</v>
       </c>
-      <c r="AN19" s="8" t="n">
+      <c r="AR19" s="8" t="n">
         <v>8991707</v>
       </c>
-      <c r="AO19" s="9" t="n">
+      <c r="AS19" s="9" t="n">
         <v>142914.19</v>
       </c>
-      <c r="AP19" s="10" t="n">
+      <c r="AT19" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="AQ19" s="11" t="n">
+      <c r="AU19" s="11" t="n">
         <v>-0.04856779498084111</v>
       </c>
-      <c r="AR19" s="8" t="n">
+      <c r="AV19" s="8" t="n">
         <v>9450707</v>
       </c>
-      <c r="AS19" s="9" t="n">
+      <c r="AW19" s="9" t="n">
         <v>146920.69</v>
       </c>
-      <c r="AT19" s="10" t="n">
+      <c r="AX19" s="10" t="n">
         <v>0.013</v>
       </c>
-      <c r="AU19" s="11" t="n">
+      <c r="AY19" s="11" t="n">
         <v>0.03318890177940083</v>
       </c>
-      <c r="AV19" s="8" t="n">
+      <c r="AZ19" s="8" t="n">
         <v>9147124</v>
       </c>
-      <c r="AW19" s="9" t="n">
+      <c r="BA19" s="9" t="n">
         <v>137746.54</v>
-      </c>
-      <c r="AX19" s="10" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="AY19" s="11" t="n">
-        <v>0.0298589752957666</v>
-      </c>
-      <c r="AZ19" s="8" t="n">
-        <v>8881919</v>
-      </c>
-      <c r="BA19" s="9" t="n">
-        <v>130182.29</v>
       </c>
       <c r="BB19" s="10" t="n">
         <v>0.0125</v>
       </c>
       <c r="BC19" s="11" t="n">
+        <v>0.0298589752957666</v>
+      </c>
+      <c r="BD19" s="8" t="n">
+        <v>8881919</v>
+      </c>
+      <c r="BE19" s="9" t="n">
+        <v>130182.29</v>
+      </c>
+      <c r="BF19" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="BG19" s="11" t="n">
         <v>0.1110462167918367</v>
-      </c>
-      <c r="BD19" s="8" t="n">
-        <v>7994194</v>
-      </c>
-      <c r="BE19" s="9" t="n">
-        <v>123918</v>
-      </c>
-      <c r="BF19" s="10" t="n">
-        <v>0.0126</v>
-      </c>
-      <c r="BG19" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="BH19" s="8" t="n">
         <v>7994194</v>
       </c>
       <c r="BI19" s="9" t="n">
+        <v>123918</v>
+      </c>
+      <c r="BJ19" s="10" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="BK19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL19" s="8" t="n">
+        <v>7994194</v>
+      </c>
+      <c r="BM19" s="9" t="n">
         <v>115292.27</v>
       </c>
-      <c r="BJ19" s="10" t="n">
+      <c r="BN19" s="10" t="n">
         <v>0.0123</v>
       </c>
-      <c r="BK19" s="11" t="n">
+      <c r="BO19" s="11" t="n">
         <v>0.03077033965211765</v>
       </c>
-      <c r="BL19" s="8" t="n">
+      <c r="BP19" s="8" t="n">
         <v>7755553</v>
       </c>
-      <c r="BM19" s="9" t="n">
+      <c r="BQ19" s="9" t="n">
         <v>109159.41</v>
       </c>
-      <c r="BN19" s="10" t="n">
+      <c r="BR19" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="BO19" s="11" t="n">
+      <c r="BS19" s="11" t="n">
         <v>0.2461624388271065</v>
       </c>
-      <c r="BP19" s="8" t="n">
+      <c r="BT19" s="8" t="n">
         <v>6223549</v>
       </c>
-      <c r="BQ19" s="9" t="n">
+      <c r="BU19" s="9" t="n">
         <v>92071.17999999999</v>
       </c>
-      <c r="BR19" s="10" t="n">
+      <c r="BV19" s="10" t="n">
         <v>0.0103</v>
       </c>
-      <c r="BS19" s="11" t="n"/>
+      <c r="BW19" s="11" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -4549,126 +4769,138 @@
         <v>0.0125</v>
       </c>
       <c r="AE20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="8" t="n">
+        <v>13125545</v>
+      </c>
+      <c r="AG20" s="9" t="n">
+        <v>165224.36</v>
+      </c>
+      <c r="AH20" s="10" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="AI20" s="11" t="n">
         <v>0.02739609151703509</v>
       </c>
-      <c r="AF20" s="8" t="n">
+      <c r="AJ20" s="8" t="n">
         <v>12775545</v>
       </c>
-      <c r="AG20" s="9" t="n">
+      <c r="AK20" s="9" t="n">
         <v>152999.93</v>
       </c>
-      <c r="AH20" s="10" t="n">
+      <c r="AL20" s="10" t="n">
         <v>0.0122</v>
       </c>
-      <c r="AI20" s="11" t="n">
+      <c r="AM20" s="11" t="n">
         <v>0.05513752418556975</v>
       </c>
-      <c r="AJ20" s="8" t="n">
+      <c r="AN20" s="8" t="n">
         <v>12107943</v>
       </c>
-      <c r="AK20" s="9" t="n">
+      <c r="AO20" s="9" t="n">
         <v>148164.9</v>
       </c>
-      <c r="AL20" s="10" t="n">
+      <c r="AP20" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="AM20" s="11" t="n">
+      <c r="AQ20" s="11" t="n">
         <v>0.04083231560577577</v>
       </c>
-      <c r="AN20" s="8" t="n">
+      <c r="AR20" s="8" t="n">
         <v>11632943</v>
       </c>
-      <c r="AO20" s="9" t="n">
+      <c r="AS20" s="9" t="n">
         <v>146586.71</v>
       </c>
-      <c r="AP20" s="10" t="n">
+      <c r="AT20" s="10" t="n">
         <v>0.0127</v>
       </c>
-      <c r="AQ20" s="11" t="n">
+      <c r="AU20" s="11" t="n">
         <v>0.037023978878946</v>
       </c>
-      <c r="AR20" s="8" t="n">
+      <c r="AV20" s="8" t="n">
         <v>11217622</v>
       </c>
-      <c r="AS20" s="9" t="n">
+      <c r="AW20" s="9" t="n">
         <v>142497.45</v>
       </c>
-      <c r="AT20" s="10" t="n">
+      <c r="AX20" s="10" t="n">
         <v>0.0126</v>
       </c>
-      <c r="AU20" s="11" t="n">
+      <c r="AY20" s="11" t="n">
         <v>0.08471904462602137</v>
-      </c>
-      <c r="AV20" s="8" t="n">
-        <v>10341500</v>
-      </c>
-      <c r="AW20" s="9" t="n">
-        <v>132712.47</v>
-      </c>
-      <c r="AX20" s="10" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="AY20" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="AZ20" s="8" t="n">
         <v>10341500</v>
       </c>
       <c r="BA20" s="9" t="n">
+        <v>132712.47</v>
+      </c>
+      <c r="BB20" s="10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="BC20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" s="8" t="n">
+        <v>10341500</v>
+      </c>
+      <c r="BE20" s="9" t="n">
         <v>129392.85</v>
-      </c>
-      <c r="BB20" s="10" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="BC20" s="11" t="n">
-        <v>-0.005975775856020039</v>
-      </c>
-      <c r="BD20" s="8" t="n">
-        <v>10403670</v>
-      </c>
-      <c r="BE20" s="9" t="n">
-        <v>123169.05</v>
       </c>
       <c r="BF20" s="10" t="n">
         <v>0.0125</v>
       </c>
       <c r="BG20" s="11" t="n">
+        <v>-0.005975775856020039</v>
+      </c>
+      <c r="BH20" s="8" t="n">
+        <v>10403670</v>
+      </c>
+      <c r="BI20" s="9" t="n">
+        <v>123169.05</v>
+      </c>
+      <c r="BJ20" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="BK20" s="11" t="n">
         <v>0.02666147990782253</v>
       </c>
-      <c r="BH20" s="8" t="n">
+      <c r="BL20" s="8" t="n">
         <v>10133496</v>
       </c>
-      <c r="BI20" s="9" t="n">
+      <c r="BM20" s="9" t="n">
         <v>115947.46</v>
       </c>
-      <c r="BJ20" s="10" t="n">
+      <c r="BN20" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="BK20" s="11" t="n">
+      <c r="BO20" s="11" t="n">
         <v>0.02236244056730923</v>
       </c>
-      <c r="BL20" s="8" t="n">
+      <c r="BP20" s="8" t="n">
         <v>9911843</v>
       </c>
-      <c r="BM20" s="9" t="n">
+      <c r="BQ20" s="9" t="n">
         <v>110665.73</v>
       </c>
-      <c r="BN20" s="10" t="n">
+      <c r="BR20" s="10" t="n">
         <v>0.0126</v>
       </c>
-      <c r="BO20" s="11" t="n">
+      <c r="BS20" s="11" t="n">
         <v>0.3415700706027321</v>
       </c>
-      <c r="BP20" s="8" t="n">
+      <c r="BT20" s="8" t="n">
         <v>7388241</v>
       </c>
-      <c r="BQ20" s="9" t="n">
+      <c r="BU20" s="9" t="n">
         <v>89940.75</v>
       </c>
-      <c r="BR20" s="10" t="n">
+      <c r="BV20" s="10" t="n">
         <v>0.01</v>
       </c>
-      <c r="BS20" s="11" t="n"/>
+      <c r="BW20" s="11" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -4794,6 +5026,10 @@
       <c r="BQ21" s="9" t="n"/>
       <c r="BR21" s="10" t="n"/>
       <c r="BS21" s="11" t="n"/>
+      <c r="BT21" s="8" t="n"/>
+      <c r="BU21" s="9" t="n"/>
+      <c r="BV21" s="10" t="n"/>
+      <c r="BW21" s="11" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -4899,10 +5135,10 @@
         <v>22000000</v>
       </c>
       <c r="AG22" s="9" t="n">
-        <v>104852</v>
+        <v>94699</v>
       </c>
       <c r="AH22" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.0073</v>
       </c>
       <c r="AI22" s="11" t="n">
         <v>0</v>
@@ -4911,18 +5147,26 @@
         <v>22000000</v>
       </c>
       <c r="AK22" s="9" t="n">
+        <v>104852</v>
+      </c>
+      <c r="AL22" s="10" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="AM22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" s="8" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="AO22" s="9" t="n">
         <v>100584</v>
       </c>
-      <c r="AL22" s="10" t="n">
+      <c r="AP22" s="10" t="n">
         <v>0.008399999999999999</v>
       </c>
-      <c r="AM22" s="11" t="n">
+      <c r="AQ22" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="AN22" s="8" t="n"/>
-      <c r="AO22" s="9" t="n"/>
-      <c r="AP22" s="10" t="n"/>
-      <c r="AQ22" s="11" t="n"/>
       <c r="AR22" s="8" t="n"/>
       <c r="AS22" s="9" t="n"/>
       <c r="AT22" s="10" t="n"/>
@@ -4951,6 +5195,10 @@
       <c r="BQ22" s="9" t="n"/>
       <c r="BR22" s="10" t="n"/>
       <c r="BS22" s="11" t="n"/>
+      <c r="BT22" s="8" t="n"/>
+      <c r="BU22" s="9" t="n"/>
+      <c r="BV22" s="10" t="n"/>
+      <c r="BW22" s="11" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -5056,10 +5304,10 @@
         <v>80755676</v>
       </c>
       <c r="AG23" s="9" t="n">
-        <v>112298.84</v>
+        <v>112484.58</v>
       </c>
       <c r="AH23" s="10" t="n">
-        <v>0.0089</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="AI23" s="11" t="n">
         <v>0</v>
@@ -5068,46 +5316,46 @@
         <v>80755676</v>
       </c>
       <c r="AK23" s="9" t="n">
+        <v>112298.84</v>
+      </c>
+      <c r="AL23" s="10" t="n">
+        <v>0.0089</v>
+      </c>
+      <c r="AM23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" s="8" t="n">
+        <v>80755676</v>
+      </c>
+      <c r="AO23" s="9" t="n">
         <v>112403.83</v>
       </c>
-      <c r="AL23" s="10" t="n">
+      <c r="AP23" s="10" t="n">
         <v>0.0094</v>
       </c>
-      <c r="AM23" s="11" t="n">
+      <c r="AQ23" s="11" t="n">
         <v>0.09854178046374168</v>
       </c>
-      <c r="AN23" s="8" t="n">
+      <c r="AR23" s="8" t="n">
         <v>73511702</v>
       </c>
-      <c r="AO23" s="9" t="n">
+      <c r="AS23" s="9" t="n">
         <v>102769.36</v>
       </c>
-      <c r="AP23" s="10" t="n">
+      <c r="AT23" s="10" t="n">
         <v>0.0089</v>
       </c>
-      <c r="AQ23" s="11" t="n">
+      <c r="AU23" s="11" t="n">
         <v>0.6629129724205788</v>
-      </c>
-      <c r="AR23" s="8" t="n">
-        <v>44206584</v>
-      </c>
-      <c r="AS23" s="9" t="n">
-        <v>59811.51</v>
-      </c>
-      <c r="AT23" s="10" t="n">
-        <v>0.0053</v>
-      </c>
-      <c r="AU23" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="AV23" s="8" t="n">
         <v>44206584</v>
       </c>
       <c r="AW23" s="9" t="n">
-        <v>85367.33</v>
+        <v>59811.51</v>
       </c>
       <c r="AX23" s="10" t="n">
-        <v>0.0077</v>
+        <v>0.0053</v>
       </c>
       <c r="AY23" s="11" t="n">
         <v>0</v>
@@ -5116,10 +5364,10 @@
         <v>44206584</v>
       </c>
       <c r="BA23" s="9" t="n">
-        <v>88656.3</v>
+        <v>85367.33</v>
       </c>
       <c r="BB23" s="10" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0077</v>
       </c>
       <c r="BC23" s="11" t="n">
         <v>0</v>
@@ -5128,7 +5376,7 @@
         <v>44206584</v>
       </c>
       <c r="BE23" s="9" t="n">
-        <v>84147.23</v>
+        <v>88656.3</v>
       </c>
       <c r="BF23" s="10" t="n">
         <v>0.008500000000000001</v>
@@ -5140,10 +5388,10 @@
         <v>44206584</v>
       </c>
       <c r="BI23" s="9" t="n">
-        <v>77701.91</v>
+        <v>84147.23</v>
       </c>
       <c r="BJ23" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="BK23" s="11" t="n">
         <v>0</v>
@@ -5152,10 +5400,10 @@
         <v>44206584</v>
       </c>
       <c r="BM23" s="9" t="n">
-        <v>68931.33</v>
+        <v>77701.91</v>
       </c>
       <c r="BN23" s="10" t="n">
-        <v>0.0078</v>
+        <v>0.0083</v>
       </c>
       <c r="BO23" s="11" t="n">
         <v>0</v>
@@ -5164,12 +5412,24 @@
         <v>44206584</v>
       </c>
       <c r="BQ23" s="9" t="n">
+        <v>68931.33</v>
+      </c>
+      <c r="BR23" s="10" t="n">
+        <v>0.0078</v>
+      </c>
+      <c r="BS23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT23" s="8" t="n">
+        <v>44206584</v>
+      </c>
+      <c r="BU23" s="9" t="n">
         <v>77184.7</v>
       </c>
-      <c r="BR23" s="10" t="n">
+      <c r="BV23" s="10" t="n">
         <v>0.0086</v>
       </c>
-      <c r="BS23" s="11" t="n"/>
+      <c r="BW23" s="11" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -5269,126 +5529,138 @@
         <v>0.0048</v>
       </c>
       <c r="AE24" s="11" t="n">
-        <v>0.1179022784593063</v>
+        <v>0.05773144178420389</v>
       </c>
       <c r="AF24" s="8" t="n">
+        <v>5842830</v>
+      </c>
+      <c r="AG24" s="9" t="n">
+        <v>60233.73</v>
+      </c>
+      <c r="AH24" s="10" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="AI24" s="11" t="n">
+        <v>0.05688668625904227</v>
+      </c>
+      <c r="AJ24" s="8" t="n">
         <v>5528341</v>
       </c>
-      <c r="AG24" s="9" t="n">
+      <c r="AK24" s="9" t="n">
         <v>59285.93</v>
       </c>
-      <c r="AH24" s="10" t="n">
+      <c r="AL24" s="10" t="n">
         <v>0.0047</v>
       </c>
-      <c r="AI24" s="11" t="n">
+      <c r="AM24" s="11" t="n">
         <v>0.1065051605034048</v>
       </c>
-      <c r="AJ24" s="8" t="n">
+      <c r="AN24" s="8" t="n">
         <v>4996218</v>
       </c>
-      <c r="AK24" s="9" t="n">
+      <c r="AO24" s="9" t="n">
         <v>51236.22</v>
-      </c>
-      <c r="AL24" s="10" t="n">
-        <v>0.0043</v>
-      </c>
-      <c r="AM24" s="11" t="n">
-        <v>0.1269063080091213</v>
-      </c>
-      <c r="AN24" s="8" t="n">
-        <v>4433570</v>
-      </c>
-      <c r="AO24" s="9" t="n">
-        <v>49913.13</v>
       </c>
       <c r="AP24" s="10" t="n">
         <v>0.0043</v>
       </c>
       <c r="AQ24" s="11" t="n">
+        <v>0.1269063080091213</v>
+      </c>
+      <c r="AR24" s="8" t="n">
+        <v>4433570</v>
+      </c>
+      <c r="AS24" s="9" t="n">
+        <v>49913.13</v>
+      </c>
+      <c r="AT24" s="10" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="AU24" s="11" t="n">
         <v>0.1091786303542636</v>
       </c>
-      <c r="AR24" s="8" t="n">
+      <c r="AV24" s="8" t="n">
         <v>3997165</v>
       </c>
-      <c r="AS24" s="9" t="n">
+      <c r="AW24" s="9" t="n">
         <v>49305.03</v>
       </c>
-      <c r="AT24" s="10" t="n">
+      <c r="AX24" s="10" t="n">
         <v>0.0044</v>
       </c>
-      <c r="AU24" s="11" t="n">
+      <c r="AY24" s="11" t="n">
         <v>0.136585363079533</v>
       </c>
-      <c r="AV24" s="8" t="n">
+      <c r="AZ24" s="8" t="n">
         <v>3516819</v>
       </c>
-      <c r="AW24" s="9" t="n">
+      <c r="BA24" s="9" t="n">
         <v>39036.69</v>
       </c>
-      <c r="AX24" s="10" t="n">
+      <c r="BB24" s="10" t="n">
         <v>0.0035</v>
       </c>
-      <c r="AY24" s="11" t="n">
+      <c r="BC24" s="11" t="n">
         <v>0.08443118240843069</v>
       </c>
-      <c r="AZ24" s="8" t="n">
+      <c r="BD24" s="8" t="n">
         <v>3243008</v>
       </c>
-      <c r="BA24" s="9" t="n">
+      <c r="BE24" s="9" t="n">
         <v>30813.44</v>
       </c>
-      <c r="BB24" s="10" t="n">
+      <c r="BF24" s="10" t="n">
         <v>0.003</v>
       </c>
-      <c r="BC24" s="11" t="n">
+      <c r="BG24" s="11" t="n">
         <v>0.08526813218218672</v>
       </c>
-      <c r="BD24" s="8" t="n">
+      <c r="BH24" s="8" t="n">
         <v>2988209</v>
       </c>
-      <c r="BE24" s="9" t="n">
+      <c r="BI24" s="9" t="n">
         <v>24424.13</v>
       </c>
-      <c r="BF24" s="10" t="n">
+      <c r="BJ24" s="10" t="n">
         <v>0.0025</v>
       </c>
-      <c r="BG24" s="11" t="n">
+      <c r="BK24" s="11" t="n">
         <v>0.05097801295341799</v>
       </c>
-      <c r="BH24" s="8" t="n">
+      <c r="BL24" s="8" t="n">
         <v>2843265</v>
       </c>
-      <c r="BI24" s="9" t="n">
+      <c r="BM24" s="9" t="n">
         <v>22336.69</v>
       </c>
-      <c r="BJ24" s="10" t="n">
+      <c r="BN24" s="10" t="n">
         <v>0.0024</v>
       </c>
-      <c r="BK24" s="11" t="n">
+      <c r="BO24" s="11" t="n">
         <v>0.08976771675272589</v>
       </c>
-      <c r="BL24" s="8" t="n">
+      <c r="BP24" s="8" t="n">
         <v>2609056</v>
       </c>
-      <c r="BM24" s="9" t="n">
+      <c r="BQ24" s="9" t="n">
         <v>17326.74</v>
       </c>
-      <c r="BN24" s="10" t="n">
+      <c r="BR24" s="10" t="n">
         <v>0.002</v>
       </c>
-      <c r="BO24" s="11" t="n">
+      <c r="BS24" s="11" t="n">
         <v>0.1546891810734174</v>
       </c>
-      <c r="BP24" s="8" t="n">
+      <c r="BT24" s="8" t="n">
         <v>2259531</v>
       </c>
-      <c r="BQ24" s="9" t="n">
+      <c r="BU24" s="9" t="n">
         <v>18525.89</v>
       </c>
-      <c r="BR24" s="10" t="n">
+      <c r="BV24" s="10" t="n">
         <v>0.0021</v>
       </c>
-      <c r="BS24" s="11" t="n"/>
+      <c r="BW24" s="11" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -5494,10 +5766,10 @@
         <v>1995914</v>
       </c>
       <c r="AG25" s="9" t="n">
-        <v>35076.19</v>
+        <v>38830.51</v>
       </c>
       <c r="AH25" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.003</v>
       </c>
       <c r="AI25" s="11" t="n">
         <v>0</v>
@@ -5506,10 +5778,10 @@
         <v>1995914</v>
       </c>
       <c r="AK25" s="9" t="n">
-        <v>34681</v>
+        <v>35076.19</v>
       </c>
       <c r="AL25" s="10" t="n">
-        <v>0.0029</v>
+        <v>0.0028</v>
       </c>
       <c r="AM25" s="11" t="n">
         <v>0</v>
@@ -5518,10 +5790,10 @@
         <v>1995914</v>
       </c>
       <c r="AO25" s="9" t="n">
-        <v>35004.34</v>
+        <v>34681</v>
       </c>
       <c r="AP25" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0029</v>
       </c>
       <c r="AQ25" s="11" t="n">
         <v>0</v>
@@ -5530,10 +5802,10 @@
         <v>1995914</v>
       </c>
       <c r="AS25" s="9" t="n">
-        <v>38225.74</v>
+        <v>35004.34</v>
       </c>
       <c r="AT25" s="10" t="n">
-        <v>0.0034</v>
+        <v>0.003</v>
       </c>
       <c r="AU25" s="11" t="n">
         <v>0</v>
@@ -5542,10 +5814,10 @@
         <v>1995914</v>
       </c>
       <c r="AW25" s="9" t="n">
-        <v>43319.32</v>
+        <v>38225.74</v>
       </c>
       <c r="AX25" s="10" t="n">
-        <v>0.0039</v>
+        <v>0.0034</v>
       </c>
       <c r="AY25" s="11" t="n">
         <v>0</v>
@@ -5554,10 +5826,10 @@
         <v>1995914</v>
       </c>
       <c r="BA25" s="9" t="n">
-        <v>34806.74</v>
+        <v>43319.32</v>
       </c>
       <c r="BB25" s="10" t="n">
-        <v>0.0034</v>
+        <v>0.0039</v>
       </c>
       <c r="BC25" s="11" t="n">
         <v>0</v>
@@ -5566,10 +5838,10 @@
         <v>1995914</v>
       </c>
       <c r="BE25" s="9" t="n">
-        <v>35138.07</v>
+        <v>34806.74</v>
       </c>
       <c r="BF25" s="10" t="n">
-        <v>0.0036</v>
+        <v>0.0034</v>
       </c>
       <c r="BG25" s="11" t="n">
         <v>0</v>
@@ -5578,7 +5850,7 @@
         <v>1995914</v>
       </c>
       <c r="BI25" s="9" t="n">
-        <v>33771.86</v>
+        <v>35138.07</v>
       </c>
       <c r="BJ25" s="10" t="n">
         <v>0.0036</v>
@@ -5590,10 +5862,10 @@
         <v>1995914</v>
       </c>
       <c r="BM25" s="9" t="n">
-        <v>28830.98</v>
+        <v>33771.86</v>
       </c>
       <c r="BN25" s="10" t="n">
-        <v>0.0033</v>
+        <v>0.0036</v>
       </c>
       <c r="BO25" s="11" t="n">
         <v>0</v>
@@ -5602,12 +5874,24 @@
         <v>1995914</v>
       </c>
       <c r="BQ25" s="9" t="n">
+        <v>28830.98</v>
+      </c>
+      <c r="BR25" s="10" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="BS25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT25" s="8" t="n">
+        <v>1995914</v>
+      </c>
+      <c r="BU25" s="9" t="n">
         <v>27686.32</v>
       </c>
-      <c r="BR25" s="10" t="n">
+      <c r="BV25" s="10" t="n">
         <v>0.0031</v>
       </c>
-      <c r="BS25" s="11" t="n"/>
+      <c r="BW25" s="11" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -5749,6 +6033,10 @@
       <c r="BQ26" s="9" t="n"/>
       <c r="BR26" s="10" t="n"/>
       <c r="BS26" s="11" t="n"/>
+      <c r="BT26" s="8" t="n"/>
+      <c r="BU26" s="9" t="n"/>
+      <c r="BV26" s="10" t="n"/>
+      <c r="BW26" s="11" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -5854,10 +6142,10 @@
         <v>2264603</v>
       </c>
       <c r="AG27" s="9" t="n">
-        <v>35943.78</v>
+        <v>36623.16</v>
       </c>
       <c r="AH27" s="10" t="n">
-        <v>0.0029</v>
+        <v>0.0028</v>
       </c>
       <c r="AI27" s="11" t="n">
         <v>0</v>
@@ -5866,10 +6154,10 @@
         <v>2264603</v>
       </c>
       <c r="AK27" s="9" t="n">
-        <v>33031.5</v>
+        <v>35943.78</v>
       </c>
       <c r="AL27" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.0029</v>
       </c>
       <c r="AM27" s="11" t="n">
         <v>0</v>
@@ -5878,7 +6166,7 @@
         <v>2264603</v>
       </c>
       <c r="AO27" s="9" t="n">
-        <v>32257.01</v>
+        <v>33031.5</v>
       </c>
       <c r="AP27" s="10" t="n">
         <v>0.0028</v>
@@ -5890,10 +6178,10 @@
         <v>2264603</v>
       </c>
       <c r="AS27" s="9" t="n">
-        <v>33534.24</v>
+        <v>32257.01</v>
       </c>
       <c r="AT27" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0028</v>
       </c>
       <c r="AU27" s="11" t="n">
         <v>0</v>
@@ -5902,10 +6190,10 @@
         <v>2264603</v>
       </c>
       <c r="AW27" s="9" t="n">
-        <v>40626.98</v>
+        <v>33534.24</v>
       </c>
       <c r="AX27" s="10" t="n">
-        <v>0.0037</v>
+        <v>0.003</v>
       </c>
       <c r="AY27" s="11" t="n">
         <v>0</v>
@@ -5914,10 +6202,10 @@
         <v>2264603</v>
       </c>
       <c r="BA27" s="9" t="n">
-        <v>34641.63</v>
+        <v>40626.98</v>
       </c>
       <c r="BB27" s="10" t="n">
-        <v>0.0033</v>
+        <v>0.0037</v>
       </c>
       <c r="BC27" s="11" t="n">
         <v>0</v>
@@ -5926,10 +6214,10 @@
         <v>2264603</v>
       </c>
       <c r="BE27" s="9" t="n">
-        <v>29892.76</v>
+        <v>34641.63</v>
       </c>
       <c r="BF27" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0033</v>
       </c>
       <c r="BG27" s="11" t="n">
         <v>0</v>
@@ -5938,7 +6226,7 @@
         <v>2264603</v>
       </c>
       <c r="BI27" s="9" t="n">
-        <v>27629.29</v>
+        <v>29892.76</v>
       </c>
       <c r="BJ27" s="10" t="n">
         <v>0.003</v>
@@ -5950,10 +6238,10 @@
         <v>2264603</v>
       </c>
       <c r="BM27" s="9" t="n">
-        <v>25089.54</v>
+        <v>27629.29</v>
       </c>
       <c r="BN27" s="10" t="n">
-        <v>0.0029</v>
+        <v>0.003</v>
       </c>
       <c r="BO27" s="11" t="n">
         <v>0</v>
@@ -5962,12 +6250,24 @@
         <v>2264603</v>
       </c>
       <c r="BQ27" s="9" t="n">
+        <v>25089.54</v>
+      </c>
+      <c r="BR27" s="10" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="BS27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT27" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="BU27" s="9" t="n">
         <v>29659.51</v>
       </c>
-      <c r="BR27" s="10" t="n">
+      <c r="BV27" s="10" t="n">
         <v>0.0033</v>
       </c>
-      <c r="BS27" s="11" t="n"/>
+      <c r="BW27" s="11" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -6061,6 +6361,10 @@
       <c r="BQ28" s="9" t="n"/>
       <c r="BR28" s="10" t="n"/>
       <c r="BS28" s="11" t="n"/>
+      <c r="BT28" s="8" t="n"/>
+      <c r="BU28" s="9" t="n"/>
+      <c r="BV28" s="10" t="n"/>
+      <c r="BW28" s="11" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -6194,6 +6498,10 @@
       <c r="BQ29" s="9" t="n"/>
       <c r="BR29" s="10" t="n"/>
       <c r="BS29" s="11" t="n"/>
+      <c r="BT29" s="8" t="n"/>
+      <c r="BU29" s="9" t="n"/>
+      <c r="BV29" s="10" t="n"/>
+      <c r="BW29" s="11" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -6319,6 +6627,10 @@
       <c r="BQ30" s="9" t="n"/>
       <c r="BR30" s="10" t="n"/>
       <c r="BS30" s="11" t="n"/>
+      <c r="BT30" s="8" t="n"/>
+      <c r="BU30" s="9" t="n"/>
+      <c r="BV30" s="10" t="n"/>
+      <c r="BW30" s="11" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -6424,10 +6736,10 @@
         <v>287393</v>
       </c>
       <c r="AG31" s="9" t="n">
-        <v>18463.56</v>
+        <v>17812.62</v>
       </c>
       <c r="AH31" s="10" t="n">
-        <v>0.0015</v>
+        <v>0.0014</v>
       </c>
       <c r="AI31" s="11" t="n">
         <v>0</v>
@@ -6436,7 +6748,7 @@
         <v>287393</v>
       </c>
       <c r="AK31" s="9" t="n">
-        <v>18243.71</v>
+        <v>18463.56</v>
       </c>
       <c r="AL31" s="10" t="n">
         <v>0.0015</v>
@@ -6448,10 +6760,10 @@
         <v>287393</v>
       </c>
       <c r="AO31" s="9" t="n">
-        <v>17962.06</v>
+        <v>18243.71</v>
       </c>
       <c r="AP31" s="10" t="n">
-        <v>0.0016</v>
+        <v>0.0015</v>
       </c>
       <c r="AQ31" s="11" t="n">
         <v>0</v>
@@ -6460,10 +6772,10 @@
         <v>287393</v>
       </c>
       <c r="AS31" s="9" t="n">
-        <v>19048.41</v>
+        <v>17962.06</v>
       </c>
       <c r="AT31" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.0016</v>
       </c>
       <c r="AU31" s="11" t="n">
         <v>0</v>
@@ -6472,10 +6784,10 @@
         <v>287393</v>
       </c>
       <c r="AW31" s="9" t="n">
-        <v>19453.63</v>
+        <v>19048.41</v>
       </c>
       <c r="AX31" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.0017</v>
       </c>
       <c r="AY31" s="11" t="n">
         <v>0</v>
@@ -6484,10 +6796,10 @@
         <v>287393</v>
       </c>
       <c r="BA31" s="9" t="n">
-        <v>19370.29</v>
+        <v>19453.63</v>
       </c>
       <c r="BB31" s="10" t="n">
-        <v>0.0019</v>
+        <v>0.0018</v>
       </c>
       <c r="BC31" s="11" t="n">
         <v>0</v>
@@ -6496,10 +6808,10 @@
         <v>287393</v>
       </c>
       <c r="BE31" s="9" t="n">
-        <v>15976.18</v>
+        <v>19370.29</v>
       </c>
       <c r="BF31" s="10" t="n">
-        <v>0.0016</v>
+        <v>0.0019</v>
       </c>
       <c r="BG31" s="11" t="n">
         <v>0</v>
@@ -6508,10 +6820,10 @@
         <v>287393</v>
       </c>
       <c r="BI31" s="9" t="n">
-        <v>15821.13</v>
+        <v>15976.18</v>
       </c>
       <c r="BJ31" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.0016</v>
       </c>
       <c r="BK31" s="11" t="n">
         <v>0</v>
@@ -6520,24 +6832,36 @@
         <v>287393</v>
       </c>
       <c r="BM31" s="9" t="n">
-        <v>15273.64</v>
+        <v>15821.13</v>
       </c>
       <c r="BN31" s="10" t="n">
         <v>0.0017</v>
       </c>
       <c r="BO31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP31" s="8" t="n">
+        <v>287393</v>
+      </c>
+      <c r="BQ31" s="9" t="n">
+        <v>15273.64</v>
+      </c>
+      <c r="BR31" s="10" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="BS31" s="11" t="n">
         <v>-0.03505968069568721</v>
       </c>
-      <c r="BP31" s="8" t="n">
+      <c r="BT31" s="8" t="n">
         <v>297835</v>
       </c>
-      <c r="BQ31" s="9" t="n">
+      <c r="BU31" s="9" t="n">
         <v>18529.51</v>
       </c>
-      <c r="BR31" s="10" t="n">
+      <c r="BV31" s="10" t="n">
         <v>0.0021</v>
       </c>
-      <c r="BS31" s="11" t="n"/>
+      <c r="BW31" s="11" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -6643,10 +6967,10 @@
         <v>80159</v>
       </c>
       <c r="AG32" s="9" t="n">
-        <v>12110.42</v>
+        <v>11787.38</v>
       </c>
       <c r="AH32" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="AI32" s="11" t="n">
         <v>0</v>
@@ -6655,10 +6979,10 @@
         <v>80159</v>
       </c>
       <c r="AK32" s="9" t="n">
-        <v>13825.82</v>
+        <v>12110.42</v>
       </c>
       <c r="AL32" s="10" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="AM32" s="11" t="n">
         <v>0</v>
@@ -6667,10 +6991,10 @@
         <v>80159</v>
       </c>
       <c r="AO32" s="9" t="n">
-        <v>12726.04</v>
+        <v>13825.82</v>
       </c>
       <c r="AP32" s="10" t="n">
-        <v>0.0011</v>
+        <v>0.0012</v>
       </c>
       <c r="AQ32" s="11" t="n">
         <v>0</v>
@@ -6679,7 +7003,7 @@
         <v>80159</v>
       </c>
       <c r="AS32" s="9" t="n">
-        <v>12868.73</v>
+        <v>12726.04</v>
       </c>
       <c r="AT32" s="10" t="n">
         <v>0.0011</v>
@@ -6691,7 +7015,7 @@
         <v>80159</v>
       </c>
       <c r="AW32" s="9" t="n">
-        <v>11621.45</v>
+        <v>12868.73</v>
       </c>
       <c r="AX32" s="10" t="n">
         <v>0.0011</v>
@@ -6703,10 +7027,10 @@
         <v>80159</v>
       </c>
       <c r="BA32" s="9" t="n">
-        <v>10722.07</v>
+        <v>11621.45</v>
       </c>
       <c r="BB32" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0011</v>
       </c>
       <c r="BC32" s="11" t="n">
         <v>0</v>
@@ -6715,10 +7039,10 @@
         <v>80159</v>
       </c>
       <c r="BE32" s="9" t="n">
-        <v>9198.25</v>
+        <v>10722.07</v>
       </c>
       <c r="BF32" s="10" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="BG32" s="11" t="n">
         <v>0</v>
@@ -6727,10 +7051,10 @@
         <v>80159</v>
       </c>
       <c r="BI32" s="9" t="n">
-        <v>8997.450000000001</v>
+        <v>9198.25</v>
       </c>
       <c r="BJ32" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="BK32" s="11" t="n">
         <v>0</v>
@@ -6739,10 +7063,10 @@
         <v>80159</v>
       </c>
       <c r="BM32" s="9" t="n">
-        <v>7401.52</v>
+        <v>8997.450000000001</v>
       </c>
       <c r="BN32" s="10" t="n">
-        <v>0.0008</v>
+        <v>0.001</v>
       </c>
       <c r="BO32" s="11" t="n">
         <v>0</v>
@@ -6751,12 +7075,24 @@
         <v>80159</v>
       </c>
       <c r="BQ32" s="9" t="n">
-        <v>7463.48</v>
+        <v>7401.52</v>
       </c>
       <c r="BR32" s="10" t="n">
         <v>0.0008</v>
       </c>
-      <c r="BS32" s="11" t="n"/>
+      <c r="BS32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT32" s="8" t="n">
+        <v>80159</v>
+      </c>
+      <c r="BU32" s="9" t="n">
+        <v>7463.48</v>
+      </c>
+      <c r="BV32" s="10" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="BW32" s="11" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -6856,12 +7192,20 @@
         <v>0.0002</v>
       </c>
       <c r="AE33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" s="8" t="n">
+        <v>710855</v>
+      </c>
+      <c r="AG33" s="9" t="n">
+        <v>2850.8839775</v>
+      </c>
+      <c r="AH33" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AI33" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="AF33" s="8" t="n"/>
-      <c r="AG33" s="9" t="n"/>
-      <c r="AH33" s="10" t="n"/>
-      <c r="AI33" s="11" t="n"/>
       <c r="AJ33" s="8" t="n"/>
       <c r="AK33" s="9" t="n"/>
       <c r="AL33" s="10" t="n"/>
@@ -6898,6 +7242,10 @@
       <c r="BQ33" s="9" t="n"/>
       <c r="BR33" s="10" t="n"/>
       <c r="BS33" s="11" t="n"/>
+      <c r="BT33" s="8" t="n"/>
+      <c r="BU33" s="9" t="n"/>
+      <c r="BV33" s="10" t="n"/>
+      <c r="BW33" s="11" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -7003,10 +7351,10 @@
         <v>47293</v>
       </c>
       <c r="AG34" s="9" t="n">
-        <v>1892.15</v>
+        <v>1764.08</v>
       </c>
       <c r="AH34" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="AI34" s="11" t="n">
         <v>0</v>
@@ -7015,7 +7363,7 @@
         <v>47293</v>
       </c>
       <c r="AK34" s="9" t="n">
-        <v>1955.38</v>
+        <v>1892.15</v>
       </c>
       <c r="AL34" s="10" t="n">
         <v>0.0002</v>
@@ -7027,7 +7375,7 @@
         <v>47293</v>
       </c>
       <c r="AO34" s="9" t="n">
-        <v>1897.21</v>
+        <v>1955.38</v>
       </c>
       <c r="AP34" s="10" t="n">
         <v>0.0002</v>
@@ -7039,7 +7387,7 @@
         <v>47293</v>
       </c>
       <c r="AS34" s="9" t="n">
-        <v>1983.66</v>
+        <v>1897.21</v>
       </c>
       <c r="AT34" s="10" t="n">
         <v>0.0002</v>
@@ -7051,7 +7399,7 @@
         <v>47293</v>
       </c>
       <c r="AW34" s="9" t="n">
-        <v>1867.41</v>
+        <v>1983.66</v>
       </c>
       <c r="AX34" s="10" t="n">
         <v>0.0002</v>
@@ -7063,7 +7411,7 @@
         <v>47293</v>
       </c>
       <c r="BA34" s="9" t="n">
-        <v>1857.76</v>
+        <v>1867.41</v>
       </c>
       <c r="BB34" s="10" t="n">
         <v>0.0002</v>
@@ -7075,7 +7423,7 @@
         <v>47293</v>
       </c>
       <c r="BE34" s="9" t="n">
-        <v>1925.39</v>
+        <v>1857.76</v>
       </c>
       <c r="BF34" s="10" t="n">
         <v>0.0002</v>
@@ -7087,7 +7435,7 @@
         <v>47293</v>
       </c>
       <c r="BI34" s="9" t="n">
-        <v>1844.17</v>
+        <v>1925.39</v>
       </c>
       <c r="BJ34" s="10" t="n">
         <v>0.0002</v>
@@ -7099,10 +7447,10 @@
         <v>47293</v>
       </c>
       <c r="BM34" s="9" t="n">
-        <v>1236.83</v>
+        <v>1844.17</v>
       </c>
       <c r="BN34" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="BO34" s="11" t="n">
         <v>0</v>
@@ -7111,12 +7459,24 @@
         <v>47293</v>
       </c>
       <c r="BQ34" s="9" t="n">
+        <v>1236.83</v>
+      </c>
+      <c r="BR34" s="10" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="BS34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT34" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="BU34" s="9" t="n">
         <v>1612.64</v>
       </c>
-      <c r="BR34" s="10" t="n">
+      <c r="BV34" s="10" t="n">
         <v>0.0002</v>
       </c>
-      <c r="BS34" s="11" t="n"/>
+      <c r="BW34" s="11" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -7250,6 +7610,10 @@
       <c r="BQ35" s="9" t="n"/>
       <c r="BR35" s="10" t="n"/>
       <c r="BS35" s="11" t="n"/>
+      <c r="BT35" s="8" t="n"/>
+      <c r="BU35" s="9" t="n"/>
+      <c r="BV35" s="10" t="n"/>
+      <c r="BW35" s="11" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -7355,7 +7719,7 @@
         <v>151687</v>
       </c>
       <c r="AG36" s="9" t="n">
-        <v>2076.6</v>
+        <v>1947.66</v>
       </c>
       <c r="AH36" s="10" t="n">
         <v>0.0002</v>
@@ -7367,7 +7731,7 @@
         <v>151687</v>
       </c>
       <c r="AK36" s="9" t="n">
-        <v>1987.1</v>
+        <v>2076.6</v>
       </c>
       <c r="AL36" s="10" t="n">
         <v>0.0002</v>
@@ -7379,7 +7743,7 @@
         <v>151687</v>
       </c>
       <c r="AO36" s="9" t="n">
-        <v>2130.6</v>
+        <v>1987.1</v>
       </c>
       <c r="AP36" s="10" t="n">
         <v>0.0002</v>
@@ -7391,7 +7755,7 @@
         <v>151687</v>
       </c>
       <c r="AS36" s="9" t="n">
-        <v>2091.16</v>
+        <v>2130.6</v>
       </c>
       <c r="AT36" s="10" t="n">
         <v>0.0002</v>
@@ -7403,30 +7767,38 @@
         <v>151687</v>
       </c>
       <c r="AW36" s="9" t="n">
-        <v>1766.62</v>
+        <v>2091.16</v>
       </c>
       <c r="AX36" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="AY36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="BA36" s="9" t="n">
+        <v>1766.62</v>
+      </c>
+      <c r="BB36" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="BC36" s="11" t="n">
         <v>0.6954140540298874</v>
       </c>
-      <c r="AZ36" s="8" t="n">
+      <c r="BD36" s="8" t="n">
         <v>89469</v>
       </c>
-      <c r="BA36" s="9" t="n">
+      <c r="BE36" s="9" t="n">
         <v>828.48</v>
       </c>
-      <c r="BB36" s="10" t="n">
+      <c r="BF36" s="10" t="n">
         <v>0.0001</v>
       </c>
-      <c r="BC36" s="11" t="n">
+      <c r="BG36" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="BD36" s="8" t="n"/>
-      <c r="BE36" s="9" t="n"/>
-      <c r="BF36" s="10" t="n"/>
-      <c r="BG36" s="11" t="n"/>
       <c r="BH36" s="8" t="n"/>
       <c r="BI36" s="9" t="n"/>
       <c r="BJ36" s="10" t="n"/>
@@ -7439,6 +7811,10 @@
       <c r="BQ36" s="9" t="n"/>
       <c r="BR36" s="10" t="n"/>
       <c r="BS36" s="11" t="n"/>
+      <c r="BT36" s="8" t="n"/>
+      <c r="BU36" s="9" t="n"/>
+      <c r="BV36" s="10" t="n"/>
+      <c r="BW36" s="11" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -7492,88 +7868,88 @@
         <v>0.0407</v>
       </c>
       <c r="AE37" s="11" t="n">
-        <v>0.01720867810463558</v>
+        <v>0.01296144774839237</v>
       </c>
       <c r="AF37" s="8" t="n">
-        <v>24205055</v>
+        <v>24306544</v>
       </c>
       <c r="AG37" s="9" t="n">
-        <v>508838.67</v>
+        <v>516368.22</v>
       </c>
       <c r="AH37" s="10" t="n">
-        <v>0.0404</v>
+        <v>0.0398</v>
       </c>
       <c r="AI37" s="11" t="n">
-        <v>0</v>
+        <v>0.004192884502844551</v>
       </c>
       <c r="AJ37" s="8" t="n">
         <v>24205055</v>
       </c>
       <c r="AK37" s="9" t="n">
+        <v>508838.67</v>
+      </c>
+      <c r="AL37" s="10" t="n">
+        <v>0.0404</v>
+      </c>
+      <c r="AM37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" s="8" t="n">
+        <v>24205055</v>
+      </c>
+      <c r="AO37" s="9" t="n">
         <v>482334.13</v>
       </c>
-      <c r="AL37" s="10" t="n">
+      <c r="AP37" s="10" t="n">
         <v>0.0403</v>
       </c>
-      <c r="AM37" s="11" t="n">
+      <c r="AQ37" s="11" t="n">
         <v>0.03407788338216907</v>
       </c>
-      <c r="AN37" s="8" t="n">
+      <c r="AR37" s="8" t="n">
         <v>23407381</v>
       </c>
-      <c r="AO37" s="9" t="n">
+      <c r="AS37" s="9" t="n">
         <v>458854.89</v>
       </c>
-      <c r="AP37" s="10" t="n">
+      <c r="AT37" s="10" t="n">
         <v>0.0399</v>
       </c>
-      <c r="AQ37" s="11" t="n">
+      <c r="AU37" s="11" t="n">
         <v>0.06425892329321918</v>
       </c>
-      <c r="AR37" s="8" t="n">
+      <c r="AV37" s="8" t="n">
         <v>21994066</v>
       </c>
-      <c r="AS37" s="9" t="n">
+      <c r="AW37" s="9" t="n">
         <v>435174.59</v>
       </c>
-      <c r="AT37" s="10" t="n">
+      <c r="AX37" s="10" t="n">
         <v>0.0384</v>
       </c>
-      <c r="AU37" s="11" t="n">
+      <c r="AY37" s="11" t="n">
         <v>0.07428402120388222</v>
       </c>
-      <c r="AV37" s="8" t="n">
+      <c r="AZ37" s="8" t="n">
         <v>20473232</v>
       </c>
-      <c r="AW37" s="9" t="n">
+      <c r="BA37" s="9" t="n">
         <v>442938.37</v>
       </c>
-      <c r="AX37" s="10" t="n">
+      <c r="BB37" s="10" t="n">
         <v>0.0401</v>
       </c>
-      <c r="AY37" s="11" t="n">
+      <c r="BC37" s="11" t="n">
         <v>0.03644973136547983</v>
-      </c>
-      <c r="AZ37" s="8" t="n">
-        <v>19753232</v>
-      </c>
-      <c r="BA37" s="9" t="n">
-        <v>409820.3</v>
-      </c>
-      <c r="BB37" s="10" t="n">
-        <v>0.0395</v>
-      </c>
-      <c r="BC37" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="BD37" s="8" t="n">
         <v>19753232</v>
       </c>
       <c r="BE37" s="9" t="n">
-        <v>436171.12</v>
+        <v>409820.3</v>
       </c>
       <c r="BF37" s="10" t="n">
-        <v>0.0443</v>
+        <v>0.0395</v>
       </c>
       <c r="BG37" s="11" t="n">
         <v>0</v>
@@ -7582,10 +7958,10 @@
         <v>19753232</v>
       </c>
       <c r="BI37" s="9" t="n">
-        <v>428882.17</v>
+        <v>436171.12</v>
       </c>
       <c r="BJ37" s="10" t="n">
-        <v>0.0459</v>
+        <v>0.0443</v>
       </c>
       <c r="BK37" s="11" t="n">
         <v>0</v>
@@ -7594,10 +7970,10 @@
         <v>19753232</v>
       </c>
       <c r="BM37" s="9" t="n">
-        <v>375894.13</v>
+        <v>428882.17</v>
       </c>
       <c r="BN37" s="10" t="n">
-        <v>0.0427</v>
+        <v>0.0459</v>
       </c>
       <c r="BO37" s="11" t="n">
         <v>0</v>
@@ -7606,12 +7982,24 @@
         <v>19753232</v>
       </c>
       <c r="BQ37" s="9" t="n">
+        <v>375894.13</v>
+      </c>
+      <c r="BR37" s="10" t="n">
+        <v>0.0427</v>
+      </c>
+      <c r="BS37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT37" s="8" t="n">
+        <v>19753232</v>
+      </c>
+      <c r="BU37" s="9" t="n">
         <v>375568.2</v>
       </c>
-      <c r="BR37" s="10" t="n">
+      <c r="BV37" s="10" t="n">
         <v>0.0419</v>
       </c>
-      <c r="BS37" s="11" t="n"/>
+      <c r="BW37" s="11" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -7695,10 +8083,10 @@
         <v>4189074</v>
       </c>
       <c r="AG38" s="9" t="n">
-        <v>95502.50999999999</v>
+        <v>96721.53</v>
       </c>
       <c r="AH38" s="10" t="n">
-        <v>0.0076</v>
+        <v>0.0075</v>
       </c>
       <c r="AI38" s="11" t="n">
         <v>0</v>
@@ -7707,10 +8095,10 @@
         <v>4189074</v>
       </c>
       <c r="AK38" s="9" t="n">
-        <v>96130.87</v>
+        <v>95502.50999999999</v>
       </c>
       <c r="AL38" s="10" t="n">
-        <v>0.008</v>
+        <v>0.0076</v>
       </c>
       <c r="AM38" s="11" t="n">
         <v>0</v>
@@ -7719,10 +8107,10 @@
         <v>4189074</v>
       </c>
       <c r="AO38" s="9" t="n">
-        <v>95904.66</v>
+        <v>96130.87</v>
       </c>
       <c r="AP38" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.008</v>
       </c>
       <c r="AQ38" s="11" t="n">
         <v>0</v>
@@ -7731,10 +8119,10 @@
         <v>4189074</v>
       </c>
       <c r="AS38" s="9" t="n">
-        <v>112108</v>
+        <v>95904.66</v>
       </c>
       <c r="AT38" s="10" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0083</v>
       </c>
       <c r="AU38" s="11" t="n">
         <v>0</v>
@@ -7743,10 +8131,10 @@
         <v>4189074</v>
       </c>
       <c r="AW38" s="9" t="n">
-        <v>102435.43</v>
+        <v>112108</v>
       </c>
       <c r="AX38" s="10" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="AY38" s="11" t="n">
         <v>0</v>
@@ -7755,10 +8143,10 @@
         <v>4189074</v>
       </c>
       <c r="BA38" s="9" t="n">
-        <v>103562.29</v>
+        <v>102435.43</v>
       </c>
       <c r="BB38" s="10" t="n">
-        <v>0.01</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="BC38" s="11" t="n">
         <v>0</v>
@@ -7767,10 +8155,10 @@
         <v>4189074</v>
       </c>
       <c r="BE38" s="9" t="n">
-        <v>112061.92</v>
+        <v>103562.29</v>
       </c>
       <c r="BF38" s="10" t="n">
-        <v>0.0114</v>
+        <v>0.01</v>
       </c>
       <c r="BG38" s="11" t="n">
         <v>0</v>
@@ -7779,10 +8167,10 @@
         <v>4189074</v>
       </c>
       <c r="BI38" s="9" t="n">
-        <v>107022.46</v>
+        <v>112061.92</v>
       </c>
       <c r="BJ38" s="10" t="n">
-        <v>0.0115</v>
+        <v>0.0114</v>
       </c>
       <c r="BK38" s="11" t="n">
         <v>0</v>
@@ -7791,10 +8179,10 @@
         <v>4189074</v>
       </c>
       <c r="BM38" s="9" t="n">
-        <v>109571.51</v>
+        <v>107022.46</v>
       </c>
       <c r="BN38" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.0115</v>
       </c>
       <c r="BO38" s="11" t="n">
         <v>0</v>
@@ -7803,12 +8191,24 @@
         <v>4189074</v>
       </c>
       <c r="BQ38" s="9" t="n">
+        <v>109571.51</v>
+      </c>
+      <c r="BR38" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="BS38" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT38" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="BU38" s="9" t="n">
         <v>116089.71</v>
       </c>
-      <c r="BR38" s="10" t="n">
+      <c r="BV38" s="10" t="n">
         <v>0.0129</v>
       </c>
-      <c r="BS38" s="11" t="n"/>
+      <c r="BW38" s="11" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -7869,79 +8269,83 @@
       <c r="AR39" s="8" t="n"/>
       <c r="AS39" s="9" t="n"/>
       <c r="AT39" s="10" t="n"/>
-      <c r="AU39" s="11" t="n">
+      <c r="AU39" s="11" t="n"/>
+      <c r="AV39" s="8" t="n"/>
+      <c r="AW39" s="9" t="n"/>
+      <c r="AX39" s="10" t="n"/>
+      <c r="AY39" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="AV39" s="8" t="n">
+      <c r="AZ39" s="8" t="n">
         <v>591805</v>
       </c>
-      <c r="AW39" s="9" t="n">
+      <c r="BA39" s="9" t="n">
         <v>5149</v>
       </c>
-      <c r="AX39" s="10" t="n">
+      <c r="BB39" s="10" t="n">
         <v>0.0005</v>
       </c>
-      <c r="AY39" s="11" t="n">
+      <c r="BC39" s="11" t="n">
         <v>-0.8902567225534253</v>
       </c>
-      <c r="AZ39" s="8" t="n">
+      <c r="BD39" s="8" t="n">
         <v>5392631</v>
       </c>
-      <c r="BA39" s="9" t="n">
+      <c r="BE39" s="9" t="n">
         <v>43674.92</v>
       </c>
-      <c r="BB39" s="10" t="n">
+      <c r="BF39" s="10" t="n">
         <v>0.0042</v>
       </c>
-      <c r="BC39" s="11" t="n">
+      <c r="BG39" s="11" t="n">
         <v>-0.3719237093069153</v>
       </c>
-      <c r="BD39" s="8" t="n">
+      <c r="BH39" s="8" t="n">
         <v>8585949</v>
       </c>
-      <c r="BE39" s="9" t="n">
+      <c r="BI39" s="9" t="n">
         <v>56044.78</v>
       </c>
-      <c r="BF39" s="10" t="n">
+      <c r="BJ39" s="10" t="n">
         <v>0.0057</v>
       </c>
-      <c r="BG39" s="11" t="n">
+      <c r="BK39" s="11" t="n">
         <v>-0.2132577936597328</v>
       </c>
-      <c r="BH39" s="8" t="n">
+      <c r="BL39" s="8" t="n">
         <v>10913294</v>
       </c>
-      <c r="BI39" s="9" t="n">
+      <c r="BM39" s="9" t="n">
         <v>67154.95</v>
       </c>
-      <c r="BJ39" s="10" t="n">
+      <c r="BN39" s="10" t="n">
         <v>0.0072</v>
       </c>
-      <c r="BK39" s="11" t="n">
+      <c r="BO39" s="11" t="n">
         <v>-0.09462389658963724</v>
-      </c>
-      <c r="BL39" s="8" t="n">
-        <v>12053879</v>
-      </c>
-      <c r="BM39" s="9" t="n">
-        <v>70937.08</v>
-      </c>
-      <c r="BN39" s="10" t="n">
-        <v>0.0081</v>
-      </c>
-      <c r="BO39" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="BP39" s="8" t="n">
         <v>12053879</v>
       </c>
       <c r="BQ39" s="9" t="n">
+        <v>70937.08</v>
+      </c>
+      <c r="BR39" s="10" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="BS39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT39" s="8" t="n">
+        <v>12053879</v>
+      </c>
+      <c r="BU39" s="9" t="n">
         <v>76801.28999999999</v>
       </c>
-      <c r="BR39" s="10" t="n">
+      <c r="BV39" s="10" t="n">
         <v>0.0086</v>
       </c>
-      <c r="BS39" s="11" t="n"/>
+      <c r="BW39" s="11" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -8001,10 +8405,10 @@
         <v>797719</v>
       </c>
       <c r="AG40" s="9" t="n">
-        <v>73737.16</v>
+        <v>80358.22</v>
       </c>
       <c r="AH40" s="10" t="n">
-        <v>0.0059</v>
+        <v>0.0062</v>
       </c>
       <c r="AI40" s="11" t="n">
         <v>0</v>
@@ -8013,10 +8417,10 @@
         <v>797719</v>
       </c>
       <c r="AK40" s="9" t="n">
-        <v>62190.17</v>
+        <v>73737.16</v>
       </c>
       <c r="AL40" s="10" t="n">
-        <v>0.0052</v>
+        <v>0.0059</v>
       </c>
       <c r="AM40" s="11" t="n">
         <v>0</v>
@@ -8025,10 +8429,10 @@
         <v>797719</v>
       </c>
       <c r="AO40" s="9" t="n">
-        <v>58951.43</v>
+        <v>62190.17</v>
       </c>
       <c r="AP40" s="10" t="n">
-        <v>0.0051</v>
+        <v>0.0052</v>
       </c>
       <c r="AQ40" s="11" t="n">
         <v>0</v>
@@ -8037,10 +8441,10 @@
         <v>797719</v>
       </c>
       <c r="AS40" s="9" t="n">
-        <v>61368.52</v>
+        <v>58951.43</v>
       </c>
       <c r="AT40" s="10" t="n">
-        <v>0.0054</v>
+        <v>0.0051</v>
       </c>
       <c r="AU40" s="11" t="n">
         <v>0</v>
@@ -8049,10 +8453,10 @@
         <v>797719</v>
       </c>
       <c r="AW40" s="9" t="n">
-        <v>71347.99000000001</v>
+        <v>61368.52</v>
       </c>
       <c r="AX40" s="10" t="n">
-        <v>0.0065</v>
+        <v>0.0054</v>
       </c>
       <c r="AY40" s="11" t="n">
         <v>0</v>
@@ -8061,10 +8465,10 @@
         <v>797719</v>
       </c>
       <c r="BA40" s="9" t="n">
-        <v>52665.41</v>
+        <v>71347.99000000001</v>
       </c>
       <c r="BB40" s="10" t="n">
-        <v>0.0051</v>
+        <v>0.0065</v>
       </c>
       <c r="BC40" s="11" t="n">
         <v>0</v>
@@ -8073,10 +8477,10 @@
         <v>797719</v>
       </c>
       <c r="BE40" s="9" t="n">
-        <v>48884.22</v>
+        <v>52665.41</v>
       </c>
       <c r="BF40" s="10" t="n">
-        <v>0.005</v>
+        <v>0.0051</v>
       </c>
       <c r="BG40" s="11" t="n">
         <v>0</v>
@@ -8085,10 +8489,10 @@
         <v>797719</v>
       </c>
       <c r="BI40" s="9" t="n">
-        <v>42372.84</v>
+        <v>48884.22</v>
       </c>
       <c r="BJ40" s="10" t="n">
-        <v>0.0045</v>
+        <v>0.005</v>
       </c>
       <c r="BK40" s="11" t="n">
         <v>0</v>
@@ -8097,24 +8501,36 @@
         <v>797719</v>
       </c>
       <c r="BM40" s="9" t="n">
-        <v>39819.34</v>
+        <v>42372.84</v>
       </c>
       <c r="BN40" s="10" t="n">
         <v>0.0045</v>
       </c>
       <c r="BO40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP40" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="BQ40" s="9" t="n">
+        <v>39819.34</v>
+      </c>
+      <c r="BR40" s="10" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="BS40" s="11" t="n">
         <v>-0.09569612848812428</v>
       </c>
-      <c r="BP40" s="8" t="n">
+      <c r="BT40" s="8" t="n">
         <v>882136</v>
       </c>
-      <c r="BQ40" s="9" t="n">
+      <c r="BU40" s="9" t="n">
         <v>50572.42</v>
       </c>
-      <c r="BR40" s="10" t="n">
+      <c r="BV40" s="10" t="n">
         <v>0.0056</v>
       </c>
-      <c r="BS40" s="11" t="n"/>
+      <c r="BW40" s="11" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -8167,103 +8583,107 @@
       <c r="AJ41" s="8" t="n"/>
       <c r="AK41" s="9" t="n"/>
       <c r="AL41" s="10" t="n"/>
-      <c r="AM41" s="11" t="n">
+      <c r="AM41" s="11" t="n"/>
+      <c r="AN41" s="8" t="n"/>
+      <c r="AO41" s="9" t="n"/>
+      <c r="AP41" s="10" t="n"/>
+      <c r="AQ41" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="AN41" s="8" t="n">
+      <c r="AR41" s="8" t="n">
         <v>218075</v>
       </c>
-      <c r="AO41" s="9" t="n">
+      <c r="AS41" s="9" t="n">
         <v>3019.03</v>
       </c>
-      <c r="AP41" s="10" t="n">
+      <c r="AT41" s="10" t="n">
         <v>0.0003</v>
       </c>
-      <c r="AQ41" s="11" t="n">
+      <c r="AU41" s="11" t="n">
         <v>-0.6148554615199853</v>
       </c>
-      <c r="AR41" s="8" t="n">
+      <c r="AV41" s="8" t="n">
         <v>566216</v>
       </c>
-      <c r="AS41" s="9" t="n">
+      <c r="AW41" s="9" t="n">
         <v>8345.459999999999</v>
       </c>
-      <c r="AT41" s="10" t="n">
+      <c r="AX41" s="10" t="n">
         <v>0.0007</v>
       </c>
-      <c r="AU41" s="11" t="n">
+      <c r="AY41" s="11" t="n">
         <v>-0.5682871579351869</v>
       </c>
-      <c r="AV41" s="8" t="n">
+      <c r="AZ41" s="8" t="n">
         <v>1311557</v>
       </c>
-      <c r="AW41" s="9" t="n">
+      <c r="BA41" s="9" t="n">
         <v>18228.02</v>
       </c>
-      <c r="AX41" s="10" t="n">
+      <c r="BB41" s="10" t="n">
         <v>0.0017</v>
       </c>
-      <c r="AY41" s="11" t="n">
+      <c r="BC41" s="11" t="n">
         <v>-0.2008037316547793</v>
       </c>
-      <c r="AZ41" s="8" t="n">
+      <c r="BD41" s="8" t="n">
         <v>1641095</v>
       </c>
-      <c r="BA41" s="9" t="n">
+      <c r="BE41" s="9" t="n">
         <v>23382.32</v>
       </c>
-      <c r="BB41" s="10" t="n">
+      <c r="BF41" s="10" t="n">
         <v>0.0023</v>
       </c>
-      <c r="BC41" s="11" t="n">
+      <c r="BG41" s="11" t="n">
         <v>-0.1163687388172734</v>
       </c>
-      <c r="BD41" s="8" t="n">
+      <c r="BH41" s="8" t="n">
         <v>1857217</v>
       </c>
-      <c r="BE41" s="9" t="n">
+      <c r="BI41" s="9" t="n">
         <v>26023.32</v>
       </c>
-      <c r="BF41" s="10" t="n">
+      <c r="BJ41" s="10" t="n">
         <v>0.0026</v>
       </c>
-      <c r="BG41" s="11" t="n">
+      <c r="BK41" s="11" t="n">
         <v>-0.03620728307597141</v>
-      </c>
-      <c r="BH41" s="8" t="n">
-        <v>1926988</v>
-      </c>
-      <c r="BI41" s="9" t="n">
-        <v>28941.43</v>
-      </c>
-      <c r="BJ41" s="10" t="n">
-        <v>0.0031</v>
-      </c>
-      <c r="BK41" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="BL41" s="8" t="n">
         <v>1926988</v>
       </c>
       <c r="BM41" s="9" t="n">
+        <v>28941.43</v>
+      </c>
+      <c r="BN41" s="10" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="BO41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP41" s="8" t="n">
+        <v>1926988</v>
+      </c>
+      <c r="BQ41" s="9" t="n">
         <v>26117.43</v>
       </c>
-      <c r="BN41" s="10" t="n">
+      <c r="BR41" s="10" t="n">
         <v>0.003</v>
       </c>
-      <c r="BO41" s="11" t="n">
+      <c r="BS41" s="11" t="n">
         <v>-0.1421734974921662</v>
       </c>
-      <c r="BP41" s="8" t="n">
+      <c r="BT41" s="8" t="n">
         <v>2246361</v>
       </c>
-      <c r="BQ41" s="9" t="n">
+      <c r="BU41" s="9" t="n">
         <v>32421.73</v>
       </c>
-      <c r="BR41" s="10" t="n">
+      <c r="BV41" s="10" t="n">
         <v>0.0036</v>
       </c>
-      <c r="BS41" s="11" t="n"/>
+      <c r="BW41" s="11" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -8336,29 +8756,21 @@
       <c r="BD42" s="8" t="n"/>
       <c r="BE42" s="9" t="n"/>
       <c r="BF42" s="10" t="n"/>
-      <c r="BG42" s="11" t="n">
+      <c r="BG42" s="11" t="n"/>
+      <c r="BH42" s="8" t="n"/>
+      <c r="BI42" s="9" t="n"/>
+      <c r="BJ42" s="10" t="n"/>
+      <c r="BK42" s="11" t="n">
         <v>-1</v>
-      </c>
-      <c r="BH42" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BI42" s="9" t="n">
-        <v>19552.33</v>
-      </c>
-      <c r="BJ42" s="10" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="BK42" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="BL42" s="8" t="n">
         <v>9899412</v>
       </c>
       <c r="BM42" s="9" t="n">
-        <v>16216.23</v>
+        <v>19552.33</v>
       </c>
       <c r="BN42" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.0021</v>
       </c>
       <c r="BO42" s="11" t="n">
         <v>0</v>
@@ -8367,12 +8779,24 @@
         <v>9899412</v>
       </c>
       <c r="BQ42" s="9" t="n">
-        <v>16131.09</v>
+        <v>16216.23</v>
       </c>
       <c r="BR42" s="10" t="n">
         <v>0.0018</v>
       </c>
-      <c r="BS42" s="11" t="n"/>
+      <c r="BS42" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT42" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BU42" s="9" t="n">
+        <v>16131.09</v>
+      </c>
+      <c r="BV42" s="10" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="BW42" s="11" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -8468,6 +8892,10 @@
       <c r="BQ43" s="9" t="n"/>
       <c r="BR43" s="10" t="n"/>
       <c r="BS43" s="11" t="n"/>
+      <c r="BT43" s="8" t="n"/>
+      <c r="BU43" s="9" t="n"/>
+      <c r="BV43" s="10" t="n"/>
+      <c r="BW43" s="11" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -8520,29 +8948,21 @@
       <c r="AJ44" s="8" t="n"/>
       <c r="AK44" s="9" t="n"/>
       <c r="AL44" s="10" t="n"/>
-      <c r="AM44" s="11" t="n">
+      <c r="AM44" s="11" t="n"/>
+      <c r="AN44" s="8" t="n"/>
+      <c r="AO44" s="9" t="n"/>
+      <c r="AP44" s="10" t="n"/>
+      <c r="AQ44" s="11" t="n">
         <v>-1</v>
-      </c>
-      <c r="AN44" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="AO44" s="9" t="n">
-        <v>88822.8</v>
-      </c>
-      <c r="AP44" s="10" t="n">
-        <v>0.0077</v>
-      </c>
-      <c r="AQ44" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="AR44" s="8" t="n">
         <v>4400000</v>
       </c>
       <c r="AS44" s="9" t="n">
-        <v>89280.39999999999</v>
+        <v>88822.8</v>
       </c>
       <c r="AT44" s="10" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0077</v>
       </c>
       <c r="AU44" s="11" t="n">
         <v>0</v>
@@ -8551,18 +8971,26 @@
         <v>4400000</v>
       </c>
       <c r="AW44" s="9" t="n">
+        <v>89280.39999999999</v>
+      </c>
+      <c r="AX44" s="10" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="AY44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ44" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="BA44" s="9" t="n">
         <v>89020.8</v>
       </c>
-      <c r="AX44" s="10" t="n">
+      <c r="BB44" s="10" t="n">
         <v>0.0081</v>
       </c>
-      <c r="AY44" s="11" t="n">
+      <c r="BC44" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="AZ44" s="8" t="n"/>
-      <c r="BA44" s="9" t="n"/>
-      <c r="BB44" s="10" t="n"/>
-      <c r="BC44" s="11" t="n"/>
       <c r="BD44" s="8" t="n"/>
       <c r="BE44" s="9" t="n"/>
       <c r="BF44" s="10" t="n"/>
@@ -8579,6 +9007,10 @@
       <c r="BQ44" s="9" t="n"/>
       <c r="BR44" s="10" t="n"/>
       <c r="BS44" s="11" t="n"/>
+      <c r="BT44" s="8" t="n"/>
+      <c r="BU44" s="9" t="n"/>
+      <c r="BV44" s="10" t="n"/>
+      <c r="BW44" s="11" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
@@ -8659,125 +9091,136 @@
       </c>
       <c r="AE45" s="17" t="n"/>
       <c r="AF45" s="14" t="n">
-        <v>991416407</v>
+        <v>1039629309</v>
       </c>
       <c r="AG45" s="15" t="n">
-        <v>7865128.239999999</v>
+        <v>8271351.1939775</v>
       </c>
       <c r="AH45" s="16" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.6373999999999999</v>
       </c>
       <c r="AI45" s="17" t="n"/>
       <c r="AJ45" s="14" t="n">
-        <v>979359723</v>
+        <v>991416407</v>
       </c>
       <c r="AK45" s="15" t="n">
-        <v>7559180.72</v>
+        <v>7865128.239999999</v>
       </c>
       <c r="AL45" s="16" t="n">
-        <v>0.6313999999999996</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="AM45" s="17" t="n"/>
       <c r="AN45" s="14" t="n">
-        <v>927478800</v>
+        <v>979359723</v>
       </c>
       <c r="AO45" s="15" t="n">
-        <v>7320811.489999998</v>
+        <v>7559180.72</v>
       </c>
       <c r="AP45" s="16" t="n">
-        <v>0.6364000000000001</v>
+        <v>0.6313999999999996</v>
       </c>
       <c r="AQ45" s="17" t="n"/>
       <c r="AR45" s="14" t="n">
-        <v>819556049</v>
+        <v>927478800</v>
       </c>
       <c r="AS45" s="15" t="n">
-        <v>7290583.900000002</v>
+        <v>7320811.489999998</v>
       </c>
       <c r="AT45" s="16" t="n">
-        <v>0.6436999999999999</v>
+        <v>0.6364000000000001</v>
       </c>
       <c r="AU45" s="17" t="n"/>
       <c r="AV45" s="14" t="n">
-        <v>799425942</v>
+        <v>819556049</v>
       </c>
       <c r="AW45" s="15" t="n">
-        <v>7347454.069999999</v>
+        <v>7290583.900000002</v>
       </c>
       <c r="AX45" s="16" t="n">
-        <v>0.6658000000000001</v>
+        <v>0.6436999999999999</v>
       </c>
       <c r="AY45" s="17" t="n"/>
       <c r="AZ45" s="14" t="n">
-        <v>756845974</v>
+        <v>799425942</v>
       </c>
       <c r="BA45" s="15" t="n">
-        <v>6714757.130000002</v>
+        <v>7347454.069999999</v>
       </c>
       <c r="BB45" s="16" t="n">
-        <v>0.6467999999999997</v>
+        <v>0.6658000000000001</v>
       </c>
       <c r="BC45" s="17" t="n"/>
       <c r="BD45" s="14" t="n">
-        <v>719050337</v>
+        <v>756845974</v>
       </c>
       <c r="BE45" s="15" t="n">
-        <v>6275568.75</v>
+        <v>6714757.130000002</v>
       </c>
       <c r="BF45" s="16" t="n">
-        <v>0.6369999999999999</v>
+        <v>0.6467999999999997</v>
       </c>
       <c r="BG45" s="17" t="n"/>
       <c r="BH45" s="14" t="n">
-        <v>717176528</v>
+        <v>719050337</v>
       </c>
       <c r="BI45" s="15" t="n">
-        <v>6051937.579999999</v>
+        <v>6275568.75</v>
       </c>
       <c r="BJ45" s="16" t="n">
-        <v>0.6476999999999998</v>
+        <v>0.6369999999999999</v>
       </c>
       <c r="BK45" s="17" t="n"/>
       <c r="BL45" s="14" t="n">
-        <v>718063829</v>
+        <v>717176528</v>
       </c>
       <c r="BM45" s="15" t="n">
-        <v>5662977.750000001</v>
+        <v>6051937.579999999</v>
       </c>
       <c r="BN45" s="16" t="n">
-        <v>0.6436999999999999</v>
+        <v>0.6476999999999998</v>
       </c>
       <c r="BO45" s="17" t="n"/>
       <c r="BP45" s="14" t="n">
+        <v>718063829</v>
+      </c>
+      <c r="BQ45" s="15" t="n">
+        <v>5662977.750000001</v>
+      </c>
+      <c r="BR45" s="16" t="n">
+        <v>0.6436999999999999</v>
+      </c>
+      <c r="BS45" s="17" t="n"/>
+      <c r="BT45" s="14" t="n">
         <v>697292654</v>
       </c>
-      <c r="BQ45" s="15" t="n">
+      <c r="BU45" s="15" t="n">
         <v>5868142.6</v>
       </c>
-      <c r="BR45" s="16" t="n">
+      <c r="BV45" s="16" t="n">
         <v>0.6543000000000003</v>
       </c>
-      <c r="BS45" s="17" t="n"/>
+      <c r="BW45" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="19">
+    <mergeCell ref="AR2:AU2"/>
+    <mergeCell ref="AZ2:BC2"/>
     <mergeCell ref="BL2:BO2"/>
-    <mergeCell ref="BH2:BK2"/>
-    <mergeCell ref="A1:BS1"/>
-    <mergeCell ref="AF2:AI2"/>
-    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="A1:BW1"/>
     <mergeCell ref="L2:O2"/>
-    <mergeCell ref="T2:W2"/>
     <mergeCell ref="X2:AA2"/>
-    <mergeCell ref="AB2:AE2"/>
-    <mergeCell ref="AR2:AU2"/>
+    <mergeCell ref="AJ2:AM2"/>
     <mergeCell ref="AV2:AY2"/>
     <mergeCell ref="D2:G2"/>
-    <mergeCell ref="AZ2:BC2"/>
     <mergeCell ref="P2:S2"/>
     <mergeCell ref="BD2:BG2"/>
-    <mergeCell ref="AJ2:AM2"/>
     <mergeCell ref="BP2:BS2"/>
+    <mergeCell ref="BH2:BK2"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="T2:W2"/>
+    <mergeCell ref="AB2:AE2"/>
+    <mergeCell ref="AF2:AI2"/>
+    <mergeCell ref="BT2:BW2"/>
     <mergeCell ref="AN2:AQ2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -5444,7 +5444,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Fertilizers &amp; Agrochemicals</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -7481,24 +7481,24 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>CIE Automotive India Limited</t>
+          <t>Nesco Limited</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>INE536H01010</t>
+          <t>INE317F01035</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Auto Components</t>
+          <t>Commercial Services &amp; Supplies</t>
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>464063</v>
+        <v>151687</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>2124.48</v>
+        <v>1635.79</v>
       </c>
       <c r="F35" s="10" t="n">
         <v>0.0001</v>
@@ -7507,10 +7507,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>464063</v>
+        <v>151687</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>2071.81</v>
+        <v>1780.2</v>
       </c>
       <c r="J35" s="10" t="n">
         <v>0.0001</v>
@@ -7519,85 +7519,149 @@
         <v>0</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>464063</v>
+        <v>151687</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>2198.5</v>
+        <v>1862.26</v>
       </c>
       <c r="N35" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="O35" s="11" t="n">
         <v>0</v>
       </c>
       <c r="P35" s="8" t="n">
-        <v>464063</v>
+        <v>151687</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>2065.08</v>
+        <v>1538.11</v>
       </c>
       <c r="R35" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="S35" s="11" t="n">
         <v>0</v>
       </c>
       <c r="T35" s="8" t="n">
-        <v>464063</v>
+        <v>151687</v>
       </c>
       <c r="U35" s="9" t="n">
-        <v>2188.75</v>
+        <v>1704.36</v>
       </c>
       <c r="V35" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="W35" s="11" t="n">
-        <v>0.004302331872531515</v>
+        <v>0</v>
       </c>
       <c r="X35" s="8" t="n">
-        <v>462075</v>
+        <v>151687</v>
       </c>
       <c r="Y35" s="9" t="n">
-        <v>1932.4</v>
+        <v>1728.63</v>
       </c>
       <c r="Z35" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="AA35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AC35" s="9" t="n">
+        <v>1858.32</v>
+      </c>
+      <c r="AD35" s="10" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AE35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AG35" s="9" t="n">
+        <v>1947.66</v>
+      </c>
+      <c r="AH35" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AI35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AK35" s="9" t="n">
+        <v>2076.6</v>
+      </c>
+      <c r="AL35" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AM35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AO35" s="9" t="n">
+        <v>1987.1</v>
+      </c>
+      <c r="AP35" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AQ35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AS35" s="9" t="n">
+        <v>2130.6</v>
+      </c>
+      <c r="AT35" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AU35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AW35" s="9" t="n">
+        <v>2091.16</v>
+      </c>
+      <c r="AX35" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AY35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="BA35" s="9" t="n">
+        <v>1766.62</v>
+      </c>
+      <c r="BB35" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="BC35" s="11" t="n">
+        <v>0.6954140540298874</v>
+      </c>
+      <c r="BD35" s="8" t="n">
+        <v>89469</v>
+      </c>
+      <c r="BE35" s="9" t="n">
+        <v>828.48</v>
+      </c>
+      <c r="BF35" s="10" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="BG35" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="AB35" s="8" t="n"/>
-      <c r="AC35" s="9" t="n"/>
-      <c r="AD35" s="10" t="n"/>
-      <c r="AE35" s="11" t="n"/>
-      <c r="AF35" s="8" t="n"/>
-      <c r="AG35" s="9" t="n"/>
-      <c r="AH35" s="10" t="n"/>
-      <c r="AI35" s="11" t="n"/>
-      <c r="AJ35" s="8" t="n"/>
-      <c r="AK35" s="9" t="n"/>
-      <c r="AL35" s="10" t="n"/>
-      <c r="AM35" s="11" t="n"/>
-      <c r="AN35" s="8" t="n"/>
-      <c r="AO35" s="9" t="n"/>
-      <c r="AP35" s="10" t="n"/>
-      <c r="AQ35" s="11" t="n"/>
-      <c r="AR35" s="8" t="n"/>
-      <c r="AS35" s="9" t="n"/>
-      <c r="AT35" s="10" t="n"/>
-      <c r="AU35" s="11" t="n"/>
-      <c r="AV35" s="8" t="n"/>
-      <c r="AW35" s="9" t="n"/>
-      <c r="AX35" s="10" t="n"/>
-      <c r="AY35" s="11" t="n"/>
-      <c r="AZ35" s="8" t="n"/>
-      <c r="BA35" s="9" t="n"/>
-      <c r="BB35" s="10" t="n"/>
-      <c r="BC35" s="11" t="n"/>
-      <c r="BD35" s="8" t="n"/>
-      <c r="BE35" s="9" t="n"/>
-      <c r="BF35" s="10" t="n"/>
-      <c r="BG35" s="11" t="n"/>
       <c r="BH35" s="8" t="n"/>
       <c r="BI35" s="9" t="n"/>
       <c r="BJ35" s="10" t="n"/>
@@ -7618,24 +7682,24 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Nesco Limited</t>
+          <t>CIE Automotive India Limited</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>INE317F01035</t>
+          <t>INE536H01010</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Commercial Services &amp; Supplies</t>
+          <t>Auto Components</t>
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>151687</v>
+        <v>464063</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>1635.79</v>
+        <v>2124.48</v>
       </c>
       <c r="F36" s="10" t="n">
         <v>0.0001</v>
@@ -7644,10 +7708,10 @@
         <v>0</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>151687</v>
+        <v>464063</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>1780.2</v>
+        <v>2071.81</v>
       </c>
       <c r="J36" s="10" t="n">
         <v>0.0001</v>
@@ -7656,149 +7720,85 @@
         <v>0</v>
       </c>
       <c r="L36" s="8" t="n">
-        <v>151687</v>
+        <v>464063</v>
       </c>
       <c r="M36" s="9" t="n">
-        <v>1862.26</v>
+        <v>2198.5</v>
       </c>
       <c r="N36" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="O36" s="11" t="n">
         <v>0</v>
       </c>
       <c r="P36" s="8" t="n">
-        <v>151687</v>
+        <v>464063</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>1538.11</v>
+        <v>2065.08</v>
       </c>
       <c r="R36" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="S36" s="11" t="n">
         <v>0</v>
       </c>
       <c r="T36" s="8" t="n">
-        <v>151687</v>
+        <v>464063</v>
       </c>
       <c r="U36" s="9" t="n">
-        <v>1704.36</v>
+        <v>2188.75</v>
       </c>
       <c r="V36" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="W36" s="11" t="n">
-        <v>0</v>
+        <v>0.004302331872531515</v>
       </c>
       <c r="X36" s="8" t="n">
-        <v>151687</v>
+        <v>462075</v>
       </c>
       <c r="Y36" s="9" t="n">
-        <v>1728.63</v>
+        <v>1932.4</v>
       </c>
       <c r="Z36" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="AA36" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AC36" s="9" t="n">
-        <v>1858.32</v>
-      </c>
-      <c r="AD36" s="10" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="AE36" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AG36" s="9" t="n">
-        <v>1947.66</v>
-      </c>
-      <c r="AH36" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AI36" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ36" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AK36" s="9" t="n">
-        <v>2076.6</v>
-      </c>
-      <c r="AL36" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AM36" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN36" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AO36" s="9" t="n">
-        <v>1987.1</v>
-      </c>
-      <c r="AP36" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AQ36" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR36" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AS36" s="9" t="n">
-        <v>2130.6</v>
-      </c>
-      <c r="AT36" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AU36" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV36" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AW36" s="9" t="n">
-        <v>2091.16</v>
-      </c>
-      <c r="AX36" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AY36" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ36" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="BA36" s="9" t="n">
-        <v>1766.62</v>
-      </c>
-      <c r="BB36" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="BC36" s="11" t="n">
-        <v>0.6954140540298874</v>
-      </c>
-      <c r="BD36" s="8" t="n">
-        <v>89469</v>
-      </c>
-      <c r="BE36" s="9" t="n">
-        <v>828.48</v>
-      </c>
-      <c r="BF36" s="10" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="BG36" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="AB36" s="8" t="n"/>
+      <c r="AC36" s="9" t="n"/>
+      <c r="AD36" s="10" t="n"/>
+      <c r="AE36" s="11" t="n"/>
+      <c r="AF36" s="8" t="n"/>
+      <c r="AG36" s="9" t="n"/>
+      <c r="AH36" s="10" t="n"/>
+      <c r="AI36" s="11" t="n"/>
+      <c r="AJ36" s="8" t="n"/>
+      <c r="AK36" s="9" t="n"/>
+      <c r="AL36" s="10" t="n"/>
+      <c r="AM36" s="11" t="n"/>
+      <c r="AN36" s="8" t="n"/>
+      <c r="AO36" s="9" t="n"/>
+      <c r="AP36" s="10" t="n"/>
+      <c r="AQ36" s="11" t="n"/>
+      <c r="AR36" s="8" t="n"/>
+      <c r="AS36" s="9" t="n"/>
+      <c r="AT36" s="10" t="n"/>
+      <c r="AU36" s="11" t="n"/>
+      <c r="AV36" s="8" t="n"/>
+      <c r="AW36" s="9" t="n"/>
+      <c r="AX36" s="10" t="n"/>
+      <c r="AY36" s="11" t="n"/>
+      <c r="AZ36" s="8" t="n"/>
+      <c r="BA36" s="9" t="n"/>
+      <c r="BB36" s="10" t="n"/>
+      <c r="BC36" s="11" t="n"/>
+      <c r="BD36" s="8" t="n"/>
+      <c r="BE36" s="9" t="n"/>
+      <c r="BF36" s="10" t="n"/>
+      <c r="BG36" s="11" t="n"/>
       <c r="BH36" s="8" t="n"/>
       <c r="BI36" s="9" t="n"/>
       <c r="BJ36" s="10" t="n"/>
@@ -8688,17 +8688,17 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>ITC Hotels Limited</t>
+          <t>Zydus Wellness Limited</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>INE379A01028</t>
+          <t>INE768C01010</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Leisure Services</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D42" s="8" t="n"/>
@@ -8740,19 +8740,45 @@
       <c r="AN42" s="8" t="n"/>
       <c r="AO42" s="9" t="n"/>
       <c r="AP42" s="10" t="n"/>
-      <c r="AQ42" s="11" t="n"/>
-      <c r="AR42" s="8" t="n"/>
-      <c r="AS42" s="9" t="n"/>
-      <c r="AT42" s="10" t="n"/>
-      <c r="AU42" s="11" t="n"/>
-      <c r="AV42" s="8" t="n"/>
-      <c r="AW42" s="9" t="n"/>
-      <c r="AX42" s="10" t="n"/>
-      <c r="AY42" s="11" t="n"/>
-      <c r="AZ42" s="8" t="n"/>
-      <c r="BA42" s="9" t="n"/>
-      <c r="BB42" s="10" t="n"/>
-      <c r="BC42" s="11" t="n"/>
+      <c r="AQ42" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AR42" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AS42" s="9" t="n">
+        <v>88822.8</v>
+      </c>
+      <c r="AT42" s="10" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="AU42" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV42" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AW42" s="9" t="n">
+        <v>89280.39999999999</v>
+      </c>
+      <c r="AX42" s="10" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="AY42" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ42" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="BA42" s="9" t="n">
+        <v>89020.8</v>
+      </c>
+      <c r="BB42" s="10" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="BC42" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="BD42" s="8" t="n"/>
       <c r="BE42" s="9" t="n"/>
       <c r="BF42" s="10" t="n"/>
@@ -8760,58 +8786,34 @@
       <c r="BH42" s="8" t="n"/>
       <c r="BI42" s="9" t="n"/>
       <c r="BJ42" s="10" t="n"/>
-      <c r="BK42" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BL42" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BM42" s="9" t="n">
-        <v>19552.33</v>
-      </c>
-      <c r="BN42" s="10" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="BO42" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP42" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BQ42" s="9" t="n">
-        <v>16216.23</v>
-      </c>
-      <c r="BR42" s="10" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="BS42" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT42" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BU42" s="9" t="n">
-        <v>16131.09</v>
-      </c>
-      <c r="BV42" s="10" t="n">
-        <v>0.0018</v>
-      </c>
+      <c r="BK42" s="11" t="n"/>
+      <c r="BL42" s="8" t="n"/>
+      <c r="BM42" s="9" t="n"/>
+      <c r="BN42" s="10" t="n"/>
+      <c r="BO42" s="11" t="n"/>
+      <c r="BP42" s="8" t="n"/>
+      <c r="BQ42" s="9" t="n"/>
+      <c r="BR42" s="10" t="n"/>
+      <c r="BS42" s="11" t="n"/>
+      <c r="BT42" s="8" t="n"/>
+      <c r="BU42" s="9" t="n"/>
+      <c r="BV42" s="10" t="n"/>
       <c r="BW42" s="11" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Multi Commodity Exchange of India Limited</t>
+          <t>ITC Hotels Limited</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>INE745G01043</t>
+          <t>INE379A01028</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Leisure Services</t>
         </is>
       </c>
       <c r="D43" s="8" t="n"/>
@@ -8833,21 +8835,11 @@
       <c r="T43" s="8" t="n"/>
       <c r="U43" s="9" t="n"/>
       <c r="V43" s="10" t="n"/>
-      <c r="W43" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X43" s="8" t="n">
-        <v>795472</v>
-      </c>
-      <c r="Y43" s="9" t="n">
-        <v>20109.53</v>
-      </c>
-      <c r="Z43" s="10" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="AA43" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="W43" s="11" t="n"/>
+      <c r="X43" s="8" t="n"/>
+      <c r="Y43" s="9" t="n"/>
+      <c r="Z43" s="10" t="n"/>
+      <c r="AA43" s="11" t="n"/>
       <c r="AB43" s="8" t="n"/>
       <c r="AC43" s="9" t="n"/>
       <c r="AD43" s="10" t="n"/>
@@ -8883,34 +8875,58 @@
       <c r="BH43" s="8" t="n"/>
       <c r="BI43" s="9" t="n"/>
       <c r="BJ43" s="10" t="n"/>
-      <c r="BK43" s="11" t="n"/>
-      <c r="BL43" s="8" t="n"/>
-      <c r="BM43" s="9" t="n"/>
-      <c r="BN43" s="10" t="n"/>
-      <c r="BO43" s="11" t="n"/>
-      <c r="BP43" s="8" t="n"/>
-      <c r="BQ43" s="9" t="n"/>
-      <c r="BR43" s="10" t="n"/>
-      <c r="BS43" s="11" t="n"/>
-      <c r="BT43" s="8" t="n"/>
-      <c r="BU43" s="9" t="n"/>
-      <c r="BV43" s="10" t="n"/>
+      <c r="BK43" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL43" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BM43" s="9" t="n">
+        <v>19552.33</v>
+      </c>
+      <c r="BN43" s="10" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="BO43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP43" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BQ43" s="9" t="n">
+        <v>16216.23</v>
+      </c>
+      <c r="BR43" s="10" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="BS43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT43" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BU43" s="9" t="n">
+        <v>16131.09</v>
+      </c>
+      <c r="BV43" s="10" t="n">
+        <v>0.0018</v>
+      </c>
       <c r="BW43" s="11" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited</t>
+          <t>Multi Commodity Exchange of India Limited</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>INE768C01010</t>
+          <t>INE745G01043</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D44" s="8" t="n"/>
@@ -8932,11 +8948,21 @@
       <c r="T44" s="8" t="n"/>
       <c r="U44" s="9" t="n"/>
       <c r="V44" s="10" t="n"/>
-      <c r="W44" s="11" t="n"/>
-      <c r="X44" s="8" t="n"/>
-      <c r="Y44" s="9" t="n"/>
-      <c r="Z44" s="10" t="n"/>
-      <c r="AA44" s="11" t="n"/>
+      <c r="W44" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X44" s="8" t="n">
+        <v>795472</v>
+      </c>
+      <c r="Y44" s="9" t="n">
+        <v>20109.53</v>
+      </c>
+      <c r="Z44" s="10" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="AA44" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="AB44" s="8" t="n"/>
       <c r="AC44" s="9" t="n"/>
       <c r="AD44" s="10" t="n"/>
@@ -8952,45 +8978,19 @@
       <c r="AN44" s="8" t="n"/>
       <c r="AO44" s="9" t="n"/>
       <c r="AP44" s="10" t="n"/>
-      <c r="AQ44" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AR44" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="AS44" s="9" t="n">
-        <v>88822.8</v>
-      </c>
-      <c r="AT44" s="10" t="n">
-        <v>0.0077</v>
-      </c>
-      <c r="AU44" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV44" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="AW44" s="9" t="n">
-        <v>89280.39999999999</v>
-      </c>
-      <c r="AX44" s="10" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-      <c r="AY44" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ44" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="BA44" s="9" t="n">
-        <v>89020.8</v>
-      </c>
-      <c r="BB44" s="10" t="n">
-        <v>0.0081</v>
-      </c>
-      <c r="BC44" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="AQ44" s="11" t="n"/>
+      <c r="AR44" s="8" t="n"/>
+      <c r="AS44" s="9" t="n"/>
+      <c r="AT44" s="10" t="n"/>
+      <c r="AU44" s="11" t="n"/>
+      <c r="AV44" s="8" t="n"/>
+      <c r="AW44" s="9" t="n"/>
+      <c r="AX44" s="10" t="n"/>
+      <c r="AY44" s="11" t="n"/>
+      <c r="AZ44" s="8" t="n"/>
+      <c r="BA44" s="9" t="n"/>
+      <c r="BB44" s="10" t="n"/>
+      <c r="BC44" s="11" t="n"/>
       <c r="BD44" s="8" t="n"/>
       <c r="BE44" s="9" t="n"/>
       <c r="BF44" s="10" t="n"/>

--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -5444,7 +5444,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Fertilizers &amp; Agrochemicals</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -7481,24 +7481,24 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Nesco Limited</t>
+          <t>CIE Automotive India Limited</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>INE317F01035</t>
+          <t>INE536H01010</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Commercial Services &amp; Supplies</t>
+          <t>Auto Components</t>
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>151687</v>
+        <v>464063</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>1635.79</v>
+        <v>2124.48</v>
       </c>
       <c r="F35" s="10" t="n">
         <v>0.0001</v>
@@ -7507,10 +7507,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>151687</v>
+        <v>464063</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>1780.2</v>
+        <v>2071.81</v>
       </c>
       <c r="J35" s="10" t="n">
         <v>0.0001</v>
@@ -7519,149 +7519,85 @@
         <v>0</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>151687</v>
+        <v>464063</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>1862.26</v>
+        <v>2198.5</v>
       </c>
       <c r="N35" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="O35" s="11" t="n">
         <v>0</v>
       </c>
       <c r="P35" s="8" t="n">
-        <v>151687</v>
+        <v>464063</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>1538.11</v>
+        <v>2065.08</v>
       </c>
       <c r="R35" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="S35" s="11" t="n">
         <v>0</v>
       </c>
       <c r="T35" s="8" t="n">
-        <v>151687</v>
+        <v>464063</v>
       </c>
       <c r="U35" s="9" t="n">
-        <v>1704.36</v>
+        <v>2188.75</v>
       </c>
       <c r="V35" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="W35" s="11" t="n">
-        <v>0</v>
+        <v>0.004302331872531515</v>
       </c>
       <c r="X35" s="8" t="n">
-        <v>151687</v>
+        <v>462075</v>
       </c>
       <c r="Y35" s="9" t="n">
-        <v>1728.63</v>
+        <v>1932.4</v>
       </c>
       <c r="Z35" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="AA35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AC35" s="9" t="n">
-        <v>1858.32</v>
-      </c>
-      <c r="AD35" s="10" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="AE35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AG35" s="9" t="n">
-        <v>1947.66</v>
-      </c>
-      <c r="AH35" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AI35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AK35" s="9" t="n">
-        <v>2076.6</v>
-      </c>
-      <c r="AL35" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AM35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN35" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AO35" s="9" t="n">
-        <v>1987.1</v>
-      </c>
-      <c r="AP35" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AQ35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR35" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AS35" s="9" t="n">
-        <v>2130.6</v>
-      </c>
-      <c r="AT35" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AU35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV35" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="AW35" s="9" t="n">
-        <v>2091.16</v>
-      </c>
-      <c r="AX35" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AY35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ35" s="8" t="n">
-        <v>151687</v>
-      </c>
-      <c r="BA35" s="9" t="n">
-        <v>1766.62</v>
-      </c>
-      <c r="BB35" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="BC35" s="11" t="n">
-        <v>0.6954140540298874</v>
-      </c>
-      <c r="BD35" s="8" t="n">
-        <v>89469</v>
-      </c>
-      <c r="BE35" s="9" t="n">
-        <v>828.48</v>
-      </c>
-      <c r="BF35" s="10" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="BG35" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="AB35" s="8" t="n"/>
+      <c r="AC35" s="9" t="n"/>
+      <c r="AD35" s="10" t="n"/>
+      <c r="AE35" s="11" t="n"/>
+      <c r="AF35" s="8" t="n"/>
+      <c r="AG35" s="9" t="n"/>
+      <c r="AH35" s="10" t="n"/>
+      <c r="AI35" s="11" t="n"/>
+      <c r="AJ35" s="8" t="n"/>
+      <c r="AK35" s="9" t="n"/>
+      <c r="AL35" s="10" t="n"/>
+      <c r="AM35" s="11" t="n"/>
+      <c r="AN35" s="8" t="n"/>
+      <c r="AO35" s="9" t="n"/>
+      <c r="AP35" s="10" t="n"/>
+      <c r="AQ35" s="11" t="n"/>
+      <c r="AR35" s="8" t="n"/>
+      <c r="AS35" s="9" t="n"/>
+      <c r="AT35" s="10" t="n"/>
+      <c r="AU35" s="11" t="n"/>
+      <c r="AV35" s="8" t="n"/>
+      <c r="AW35" s="9" t="n"/>
+      <c r="AX35" s="10" t="n"/>
+      <c r="AY35" s="11" t="n"/>
+      <c r="AZ35" s="8" t="n"/>
+      <c r="BA35" s="9" t="n"/>
+      <c r="BB35" s="10" t="n"/>
+      <c r="BC35" s="11" t="n"/>
+      <c r="BD35" s="8" t="n"/>
+      <c r="BE35" s="9" t="n"/>
+      <c r="BF35" s="10" t="n"/>
+      <c r="BG35" s="11" t="n"/>
       <c r="BH35" s="8" t="n"/>
       <c r="BI35" s="9" t="n"/>
       <c r="BJ35" s="10" t="n"/>
@@ -7682,24 +7618,24 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>CIE Automotive India Limited</t>
+          <t>Nesco Limited</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>INE536H01010</t>
+          <t>INE317F01035</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Auto Components</t>
+          <t>Commercial Services &amp; Supplies</t>
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>464063</v>
+        <v>151687</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>2124.48</v>
+        <v>1635.79</v>
       </c>
       <c r="F36" s="10" t="n">
         <v>0.0001</v>
@@ -7708,10 +7644,10 @@
         <v>0</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>464063</v>
+        <v>151687</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>2071.81</v>
+        <v>1780.2</v>
       </c>
       <c r="J36" s="10" t="n">
         <v>0.0001</v>
@@ -7720,85 +7656,149 @@
         <v>0</v>
       </c>
       <c r="L36" s="8" t="n">
-        <v>464063</v>
+        <v>151687</v>
       </c>
       <c r="M36" s="9" t="n">
-        <v>2198.5</v>
+        <v>1862.26</v>
       </c>
       <c r="N36" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="O36" s="11" t="n">
         <v>0</v>
       </c>
       <c r="P36" s="8" t="n">
-        <v>464063</v>
+        <v>151687</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>2065.08</v>
+        <v>1538.11</v>
       </c>
       <c r="R36" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="S36" s="11" t="n">
         <v>0</v>
       </c>
       <c r="T36" s="8" t="n">
-        <v>464063</v>
+        <v>151687</v>
       </c>
       <c r="U36" s="9" t="n">
-        <v>2188.75</v>
+        <v>1704.36</v>
       </c>
       <c r="V36" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="W36" s="11" t="n">
-        <v>0.004302331872531515</v>
+        <v>0</v>
       </c>
       <c r="X36" s="8" t="n">
-        <v>462075</v>
+        <v>151687</v>
       </c>
       <c r="Y36" s="9" t="n">
-        <v>1932.4</v>
+        <v>1728.63</v>
       </c>
       <c r="Z36" s="10" t="n">
         <v>0.0001</v>
       </c>
       <c r="AA36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AC36" s="9" t="n">
+        <v>1858.32</v>
+      </c>
+      <c r="AD36" s="10" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AE36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AG36" s="9" t="n">
+        <v>1947.66</v>
+      </c>
+      <c r="AH36" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AI36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AK36" s="9" t="n">
+        <v>2076.6</v>
+      </c>
+      <c r="AL36" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AM36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AO36" s="9" t="n">
+        <v>1987.1</v>
+      </c>
+      <c r="AP36" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AQ36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AS36" s="9" t="n">
+        <v>2130.6</v>
+      </c>
+      <c r="AT36" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AU36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="AW36" s="9" t="n">
+        <v>2091.16</v>
+      </c>
+      <c r="AX36" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AY36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="BA36" s="9" t="n">
+        <v>1766.62</v>
+      </c>
+      <c r="BB36" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="BC36" s="11" t="n">
+        <v>0.6954140540298874</v>
+      </c>
+      <c r="BD36" s="8" t="n">
+        <v>89469</v>
+      </c>
+      <c r="BE36" s="9" t="n">
+        <v>828.48</v>
+      </c>
+      <c r="BF36" s="10" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="BG36" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="AB36" s="8" t="n"/>
-      <c r="AC36" s="9" t="n"/>
-      <c r="AD36" s="10" t="n"/>
-      <c r="AE36" s="11" t="n"/>
-      <c r="AF36" s="8" t="n"/>
-      <c r="AG36" s="9" t="n"/>
-      <c r="AH36" s="10" t="n"/>
-      <c r="AI36" s="11" t="n"/>
-      <c r="AJ36" s="8" t="n"/>
-      <c r="AK36" s="9" t="n"/>
-      <c r="AL36" s="10" t="n"/>
-      <c r="AM36" s="11" t="n"/>
-      <c r="AN36" s="8" t="n"/>
-      <c r="AO36" s="9" t="n"/>
-      <c r="AP36" s="10" t="n"/>
-      <c r="AQ36" s="11" t="n"/>
-      <c r="AR36" s="8" t="n"/>
-      <c r="AS36" s="9" t="n"/>
-      <c r="AT36" s="10" t="n"/>
-      <c r="AU36" s="11" t="n"/>
-      <c r="AV36" s="8" t="n"/>
-      <c r="AW36" s="9" t="n"/>
-      <c r="AX36" s="10" t="n"/>
-      <c r="AY36" s="11" t="n"/>
-      <c r="AZ36" s="8" t="n"/>
-      <c r="BA36" s="9" t="n"/>
-      <c r="BB36" s="10" t="n"/>
-      <c r="BC36" s="11" t="n"/>
-      <c r="BD36" s="8" t="n"/>
-      <c r="BE36" s="9" t="n"/>
-      <c r="BF36" s="10" t="n"/>
-      <c r="BG36" s="11" t="n"/>
       <c r="BH36" s="8" t="n"/>
       <c r="BI36" s="9" t="n"/>
       <c r="BJ36" s="10" t="n"/>
@@ -8688,17 +8688,17 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited</t>
+          <t>ITC Hotels Limited</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>INE768C01010</t>
+          <t>INE379A01028</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Leisure Services</t>
         </is>
       </c>
       <c r="D42" s="8" t="n"/>
@@ -8740,45 +8740,19 @@
       <c r="AN42" s="8" t="n"/>
       <c r="AO42" s="9" t="n"/>
       <c r="AP42" s="10" t="n"/>
-      <c r="AQ42" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AR42" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="AS42" s="9" t="n">
-        <v>88822.8</v>
-      </c>
-      <c r="AT42" s="10" t="n">
-        <v>0.0077</v>
-      </c>
-      <c r="AU42" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV42" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="AW42" s="9" t="n">
-        <v>89280.39999999999</v>
-      </c>
-      <c r="AX42" s="10" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-      <c r="AY42" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ42" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="BA42" s="9" t="n">
-        <v>89020.8</v>
-      </c>
-      <c r="BB42" s="10" t="n">
-        <v>0.0081</v>
-      </c>
-      <c r="BC42" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="AQ42" s="11" t="n"/>
+      <c r="AR42" s="8" t="n"/>
+      <c r="AS42" s="9" t="n"/>
+      <c r="AT42" s="10" t="n"/>
+      <c r="AU42" s="11" t="n"/>
+      <c r="AV42" s="8" t="n"/>
+      <c r="AW42" s="9" t="n"/>
+      <c r="AX42" s="10" t="n"/>
+      <c r="AY42" s="11" t="n"/>
+      <c r="AZ42" s="8" t="n"/>
+      <c r="BA42" s="9" t="n"/>
+      <c r="BB42" s="10" t="n"/>
+      <c r="BC42" s="11" t="n"/>
       <c r="BD42" s="8" t="n"/>
       <c r="BE42" s="9" t="n"/>
       <c r="BF42" s="10" t="n"/>
@@ -8786,34 +8760,58 @@
       <c r="BH42" s="8" t="n"/>
       <c r="BI42" s="9" t="n"/>
       <c r="BJ42" s="10" t="n"/>
-      <c r="BK42" s="11" t="n"/>
-      <c r="BL42" s="8" t="n"/>
-      <c r="BM42" s="9" t="n"/>
-      <c r="BN42" s="10" t="n"/>
-      <c r="BO42" s="11" t="n"/>
-      <c r="BP42" s="8" t="n"/>
-      <c r="BQ42" s="9" t="n"/>
-      <c r="BR42" s="10" t="n"/>
-      <c r="BS42" s="11" t="n"/>
-      <c r="BT42" s="8" t="n"/>
-      <c r="BU42" s="9" t="n"/>
-      <c r="BV42" s="10" t="n"/>
+      <c r="BK42" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL42" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BM42" s="9" t="n">
+        <v>19552.33</v>
+      </c>
+      <c r="BN42" s="10" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="BO42" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP42" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BQ42" s="9" t="n">
+        <v>16216.23</v>
+      </c>
+      <c r="BR42" s="10" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="BS42" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT42" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BU42" s="9" t="n">
+        <v>16131.09</v>
+      </c>
+      <c r="BV42" s="10" t="n">
+        <v>0.0018</v>
+      </c>
       <c r="BW42" s="11" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>ITC Hotels Limited</t>
+          <t>Multi Commodity Exchange of India Limited</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>INE379A01028</t>
+          <t>INE745G01043</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Leisure Services</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D43" s="8" t="n"/>
@@ -8835,11 +8833,21 @@
       <c r="T43" s="8" t="n"/>
       <c r="U43" s="9" t="n"/>
       <c r="V43" s="10" t="n"/>
-      <c r="W43" s="11" t="n"/>
-      <c r="X43" s="8" t="n"/>
-      <c r="Y43" s="9" t="n"/>
-      <c r="Z43" s="10" t="n"/>
-      <c r="AA43" s="11" t="n"/>
+      <c r="W43" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X43" s="8" t="n">
+        <v>795472</v>
+      </c>
+      <c r="Y43" s="9" t="n">
+        <v>20109.53</v>
+      </c>
+      <c r="Z43" s="10" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="AA43" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="AB43" s="8" t="n"/>
       <c r="AC43" s="9" t="n"/>
       <c r="AD43" s="10" t="n"/>
@@ -8875,58 +8883,34 @@
       <c r="BH43" s="8" t="n"/>
       <c r="BI43" s="9" t="n"/>
       <c r="BJ43" s="10" t="n"/>
-      <c r="BK43" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BL43" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BM43" s="9" t="n">
-        <v>19552.33</v>
-      </c>
-      <c r="BN43" s="10" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="BO43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP43" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BQ43" s="9" t="n">
-        <v>16216.23</v>
-      </c>
-      <c r="BR43" s="10" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="BS43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT43" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BU43" s="9" t="n">
-        <v>16131.09</v>
-      </c>
-      <c r="BV43" s="10" t="n">
-        <v>0.0018</v>
-      </c>
+      <c r="BK43" s="11" t="n"/>
+      <c r="BL43" s="8" t="n"/>
+      <c r="BM43" s="9" t="n"/>
+      <c r="BN43" s="10" t="n"/>
+      <c r="BO43" s="11" t="n"/>
+      <c r="BP43" s="8" t="n"/>
+      <c r="BQ43" s="9" t="n"/>
+      <c r="BR43" s="10" t="n"/>
+      <c r="BS43" s="11" t="n"/>
+      <c r="BT43" s="8" t="n"/>
+      <c r="BU43" s="9" t="n"/>
+      <c r="BV43" s="10" t="n"/>
       <c r="BW43" s="11" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Multi Commodity Exchange of India Limited</t>
+          <t>Zydus Wellness Limited</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>INE745G01043</t>
+          <t>INE768C01010</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D44" s="8" t="n"/>
@@ -8948,21 +8932,11 @@
       <c r="T44" s="8" t="n"/>
       <c r="U44" s="9" t="n"/>
       <c r="V44" s="10" t="n"/>
-      <c r="W44" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X44" s="8" t="n">
-        <v>795472</v>
-      </c>
-      <c r="Y44" s="9" t="n">
-        <v>20109.53</v>
-      </c>
-      <c r="Z44" s="10" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="AA44" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="W44" s="11" t="n"/>
+      <c r="X44" s="8" t="n"/>
+      <c r="Y44" s="9" t="n"/>
+      <c r="Z44" s="10" t="n"/>
+      <c r="AA44" s="11" t="n"/>
       <c r="AB44" s="8" t="n"/>
       <c r="AC44" s="9" t="n"/>
       <c r="AD44" s="10" t="n"/>
@@ -8978,19 +8952,45 @@
       <c r="AN44" s="8" t="n"/>
       <c r="AO44" s="9" t="n"/>
       <c r="AP44" s="10" t="n"/>
-      <c r="AQ44" s="11" t="n"/>
-      <c r="AR44" s="8" t="n"/>
-      <c r="AS44" s="9" t="n"/>
-      <c r="AT44" s="10" t="n"/>
-      <c r="AU44" s="11" t="n"/>
-      <c r="AV44" s="8" t="n"/>
-      <c r="AW44" s="9" t="n"/>
-      <c r="AX44" s="10" t="n"/>
-      <c r="AY44" s="11" t="n"/>
-      <c r="AZ44" s="8" t="n"/>
-      <c r="BA44" s="9" t="n"/>
-      <c r="BB44" s="10" t="n"/>
-      <c r="BC44" s="11" t="n"/>
+      <c r="AQ44" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AR44" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AS44" s="9" t="n">
+        <v>88822.8</v>
+      </c>
+      <c r="AT44" s="10" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="AU44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV44" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AW44" s="9" t="n">
+        <v>89280.39999999999</v>
+      </c>
+      <c r="AX44" s="10" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="AY44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ44" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="BA44" s="9" t="n">
+        <v>89020.8</v>
+      </c>
+      <c r="BB44" s="10" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="BC44" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="BD44" s="8" t="n"/>
       <c r="BE44" s="9" t="n"/>
       <c r="BF44" s="10" t="n"/>

--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -493,7 +493,7 @@
   <dimension ref="A1:CA45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -5720,7 +5720,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Fertilizers &amp; Agrochemicals</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -6305,7 +6305,7 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Central Depository Services (India) Limited</t>
+          <t>Central Depository Services (India)</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -7795,24 +7795,24 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Swaraj Engines Limited</t>
+          <t>Nesco Limited</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>INE277A01016</t>
+          <t>INE317F01035</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Industrial Products</t>
+          <t>Commercial Services &amp; Supplies</t>
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>1716.12</v>
+        <v>1615.16</v>
       </c>
       <c r="F35" s="10" t="n">
         <v>0.0001</v>
@@ -7821,10 +7821,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>1890.58</v>
+        <v>1635.79</v>
       </c>
       <c r="J35" s="10" t="n">
         <v>0.0001</v>
@@ -7833,10 +7833,10 @@
         <v>0</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>1809.43</v>
+        <v>1780.2</v>
       </c>
       <c r="N35" s="10" t="n">
         <v>0.0001</v>
@@ -7845,10 +7845,10 @@
         <v>0</v>
       </c>
       <c r="P35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>1871.38</v>
+        <v>1862.26</v>
       </c>
       <c r="R35" s="10" t="n">
         <v>0.0001</v>
@@ -7857,10 +7857,10 @@
         <v>0</v>
       </c>
       <c r="T35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="U35" s="9" t="n">
-        <v>1564.88</v>
+        <v>1538.11</v>
       </c>
       <c r="V35" s="10" t="n">
         <v>0.0001</v>
@@ -7869,10 +7869,10 @@
         <v>0</v>
       </c>
       <c r="X35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="Y35" s="9" t="n">
-        <v>1700.33</v>
+        <v>1704.36</v>
       </c>
       <c r="Z35" s="10" t="n">
         <v>0.0001</v>
@@ -7881,10 +7881,10 @@
         <v>0</v>
       </c>
       <c r="AB35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AC35" s="9" t="n">
-        <v>1637.61</v>
+        <v>1728.63</v>
       </c>
       <c r="AD35" s="10" t="n">
         <v>0.0001</v>
@@ -7893,10 +7893,10 @@
         <v>0</v>
       </c>
       <c r="AF35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AG35" s="9" t="n">
-        <v>1691.91</v>
+        <v>1858.32</v>
       </c>
       <c r="AH35" s="10" t="n">
         <v>0.0001</v>
@@ -7905,22 +7905,22 @@
         <v>0</v>
       </c>
       <c r="AJ35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AK35" s="9" t="n">
-        <v>1764.08</v>
+        <v>1947.66</v>
       </c>
       <c r="AL35" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="AM35" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AN35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AO35" s="9" t="n">
-        <v>1892.15</v>
+        <v>2076.6</v>
       </c>
       <c r="AP35" s="10" t="n">
         <v>0.0002</v>
@@ -7929,10 +7929,10 @@
         <v>0</v>
       </c>
       <c r="AR35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AS35" s="9" t="n">
-        <v>1955.38</v>
+        <v>1987.1</v>
       </c>
       <c r="AT35" s="10" t="n">
         <v>0.0002</v>
@@ -7941,10 +7941,10 @@
         <v>0</v>
       </c>
       <c r="AV35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AW35" s="9" t="n">
-        <v>1897.21</v>
+        <v>2130.6</v>
       </c>
       <c r="AX35" s="10" t="n">
         <v>0.0002</v>
@@ -7953,10 +7953,10 @@
         <v>0</v>
       </c>
       <c r="AZ35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="BA35" s="9" t="n">
-        <v>1983.66</v>
+        <v>2091.16</v>
       </c>
       <c r="BB35" s="10" t="n">
         <v>0.0002</v>
@@ -7965,97 +7965,67 @@
         <v>0</v>
       </c>
       <c r="BD35" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="BE35" s="9" t="n">
-        <v>1867.41</v>
+        <v>1766.62</v>
       </c>
       <c r="BF35" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="BG35" s="11" t="n">
-        <v>0</v>
+        <v>0.6954140540298874</v>
       </c>
       <c r="BH35" s="8" t="n">
-        <v>47293</v>
+        <v>89469</v>
       </c>
       <c r="BI35" s="9" t="n">
-        <v>1857.76</v>
+        <v>828.48</v>
       </c>
       <c r="BJ35" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="BK35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL35" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="BM35" s="9" t="n">
-        <v>1925.39</v>
-      </c>
-      <c r="BN35" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="BO35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP35" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="BQ35" s="9" t="n">
-        <v>1844.17</v>
-      </c>
-      <c r="BR35" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="BS35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT35" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="BU35" s="9" t="n">
-        <v>1236.83</v>
-      </c>
-      <c r="BV35" s="10" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="BW35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX35" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="BY35" s="9" t="n">
-        <v>1612.64</v>
-      </c>
-      <c r="BZ35" s="10" t="n">
-        <v>0.0002</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="BL35" s="8" t="n"/>
+      <c r="BM35" s="9" t="n"/>
+      <c r="BN35" s="10" t="n"/>
+      <c r="BO35" s="11" t="n"/>
+      <c r="BP35" s="8" t="n"/>
+      <c r="BQ35" s="9" t="n"/>
+      <c r="BR35" s="10" t="n"/>
+      <c r="BS35" s="11" t="n"/>
+      <c r="BT35" s="8" t="n"/>
+      <c r="BU35" s="9" t="n"/>
+      <c r="BV35" s="10" t="n"/>
+      <c r="BW35" s="11" t="n"/>
+      <c r="BX35" s="8" t="n"/>
+      <c r="BY35" s="9" t="n"/>
+      <c r="BZ35" s="10" t="n"/>
       <c r="CA35" s="11" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Nesco Limited</t>
+          <t>Swaraj Engines Limited</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>INE317F01035</t>
+          <t>INE277A01016</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Commercial Services &amp; Supplies</t>
+          <t>Industrial Products</t>
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>1615.16</v>
+        <v>1716.12</v>
       </c>
       <c r="F36" s="10" t="n">
         <v>0.0001</v>
@@ -8064,10 +8034,10 @@
         <v>0</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>1635.79</v>
+        <v>1890.58</v>
       </c>
       <c r="J36" s="10" t="n">
         <v>0.0001</v>
@@ -8076,10 +8046,10 @@
         <v>0</v>
       </c>
       <c r="L36" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="M36" s="9" t="n">
-        <v>1780.2</v>
+        <v>1809.43</v>
       </c>
       <c r="N36" s="10" t="n">
         <v>0.0001</v>
@@ -8088,10 +8058,10 @@
         <v>0</v>
       </c>
       <c r="P36" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>1862.26</v>
+        <v>1871.38</v>
       </c>
       <c r="R36" s="10" t="n">
         <v>0.0001</v>
@@ -8100,10 +8070,10 @@
         <v>0</v>
       </c>
       <c r="T36" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="U36" s="9" t="n">
-        <v>1538.11</v>
+        <v>1564.88</v>
       </c>
       <c r="V36" s="10" t="n">
         <v>0.0001</v>
@@ -8112,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="X36" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="Y36" s="9" t="n">
-        <v>1704.36</v>
+        <v>1700.33</v>
       </c>
       <c r="Z36" s="10" t="n">
         <v>0.0001</v>
@@ -8124,10 +8094,10 @@
         <v>0</v>
       </c>
       <c r="AB36" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AC36" s="9" t="n">
-        <v>1728.63</v>
+        <v>1637.61</v>
       </c>
       <c r="AD36" s="10" t="n">
         <v>0.0001</v>
@@ -8136,10 +8106,10 @@
         <v>0</v>
       </c>
       <c r="AF36" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AG36" s="9" t="n">
-        <v>1858.32</v>
+        <v>1691.91</v>
       </c>
       <c r="AH36" s="10" t="n">
         <v>0.0001</v>
@@ -8148,22 +8118,22 @@
         <v>0</v>
       </c>
       <c r="AJ36" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AK36" s="9" t="n">
-        <v>1947.66</v>
+        <v>1764.08</v>
       </c>
       <c r="AL36" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="AM36" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AN36" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AO36" s="9" t="n">
-        <v>2076.6</v>
+        <v>1892.15</v>
       </c>
       <c r="AP36" s="10" t="n">
         <v>0.0002</v>
@@ -8172,10 +8142,10 @@
         <v>0</v>
       </c>
       <c r="AR36" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AS36" s="9" t="n">
-        <v>1987.1</v>
+        <v>1955.38</v>
       </c>
       <c r="AT36" s="10" t="n">
         <v>0.0002</v>
@@ -8184,10 +8154,10 @@
         <v>0</v>
       </c>
       <c r="AV36" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AW36" s="9" t="n">
-        <v>2130.6</v>
+        <v>1897.21</v>
       </c>
       <c r="AX36" s="10" t="n">
         <v>0.0002</v>
@@ -8196,10 +8166,10 @@
         <v>0</v>
       </c>
       <c r="AZ36" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="BA36" s="9" t="n">
-        <v>2091.16</v>
+        <v>1983.66</v>
       </c>
       <c r="BB36" s="10" t="n">
         <v>0.0002</v>
@@ -8208,44 +8178,74 @@
         <v>0</v>
       </c>
       <c r="BD36" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="BE36" s="9" t="n">
-        <v>1766.62</v>
+        <v>1867.41</v>
       </c>
       <c r="BF36" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="BG36" s="11" t="n">
-        <v>0.6954140540298874</v>
+        <v>0</v>
       </c>
       <c r="BH36" s="8" t="n">
-        <v>89469</v>
+        <v>47293</v>
       </c>
       <c r="BI36" s="9" t="n">
-        <v>828.48</v>
+        <v>1857.76</v>
       </c>
       <c r="BJ36" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="BK36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL36" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="BM36" s="9" t="n">
+        <v>1925.39</v>
+      </c>
+      <c r="BN36" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="BO36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP36" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="BQ36" s="9" t="n">
+        <v>1844.17</v>
+      </c>
+      <c r="BR36" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="BS36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT36" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="BU36" s="9" t="n">
+        <v>1236.83</v>
+      </c>
+      <c r="BV36" s="10" t="n">
         <v>0.0001</v>
       </c>
-      <c r="BK36" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL36" s="8" t="n"/>
-      <c r="BM36" s="9" t="n"/>
-      <c r="BN36" s="10" t="n"/>
-      <c r="BO36" s="11" t="n"/>
-      <c r="BP36" s="8" t="n"/>
-      <c r="BQ36" s="9" t="n"/>
-      <c r="BR36" s="10" t="n"/>
-      <c r="BS36" s="11" t="n"/>
-      <c r="BT36" s="8" t="n"/>
-      <c r="BU36" s="9" t="n"/>
-      <c r="BV36" s="10" t="n"/>
-      <c r="BW36" s="11" t="n"/>
-      <c r="BX36" s="8" t="n"/>
-      <c r="BY36" s="9" t="n"/>
-      <c r="BZ36" s="10" t="n"/>
+      <c r="BW36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX36" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="BY36" s="9" t="n">
+        <v>1612.64</v>
+      </c>
+      <c r="BZ36" s="10" t="n">
+        <v>0.0002</v>
+      </c>
       <c r="CA36" s="11" t="n"/>
     </row>
     <row r="37">
@@ -8653,17 +8653,17 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Motilal Oswal Financial Services Limited</t>
+          <t>Zydus Wellness Limited</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>INE338I01027</t>
+          <t>INE768C01010</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D39" s="8" t="n"/>
@@ -8709,86 +8709,64 @@
       <c r="AR39" s="8" t="n"/>
       <c r="AS39" s="9" t="n"/>
       <c r="AT39" s="10" t="n"/>
-      <c r="AU39" s="11" t="n"/>
-      <c r="AV39" s="8" t="n"/>
-      <c r="AW39" s="9" t="n"/>
-      <c r="AX39" s="10" t="n"/>
-      <c r="AY39" s="11" t="n"/>
-      <c r="AZ39" s="8" t="n"/>
-      <c r="BA39" s="9" t="n"/>
-      <c r="BB39" s="10" t="n"/>
+      <c r="AU39" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AV39" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AW39" s="9" t="n">
+        <v>88822.8</v>
+      </c>
+      <c r="AX39" s="10" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="AY39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ39" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="BA39" s="9" t="n">
+        <v>89280.39999999999</v>
+      </c>
+      <c r="BB39" s="10" t="n">
+        <v>0.007900000000000001</v>
+      </c>
       <c r="BC39" s="11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BD39" s="8" t="n">
-        <v>591805</v>
+        <v>4400000</v>
       </c>
       <c r="BE39" s="9" t="n">
-        <v>5149</v>
+        <v>89020.8</v>
       </c>
       <c r="BF39" s="10" t="n">
-        <v>0.0005</v>
+        <v>0.0081</v>
       </c>
       <c r="BG39" s="11" t="n">
-        <v>-0.8902567225534253</v>
-      </c>
-      <c r="BH39" s="8" t="n">
-        <v>5392631</v>
-      </c>
-      <c r="BI39" s="9" t="n">
-        <v>43674.92</v>
-      </c>
-      <c r="BJ39" s="10" t="n">
-        <v>0.0042</v>
-      </c>
-      <c r="BK39" s="11" t="n">
-        <v>-0.3719237093069153</v>
-      </c>
-      <c r="BL39" s="8" t="n">
-        <v>8585949</v>
-      </c>
-      <c r="BM39" s="9" t="n">
-        <v>56044.78</v>
-      </c>
-      <c r="BN39" s="10" t="n">
-        <v>0.0057</v>
-      </c>
-      <c r="BO39" s="11" t="n">
-        <v>-0.2132577936597328</v>
-      </c>
-      <c r="BP39" s="8" t="n">
-        <v>10913294</v>
-      </c>
-      <c r="BQ39" s="9" t="n">
-        <v>67154.95</v>
-      </c>
-      <c r="BR39" s="10" t="n">
-        <v>0.0072</v>
-      </c>
-      <c r="BS39" s="11" t="n">
-        <v>-0.09462389658963724</v>
-      </c>
-      <c r="BT39" s="8" t="n">
-        <v>12053879</v>
-      </c>
-      <c r="BU39" s="9" t="n">
-        <v>70937.08</v>
-      </c>
-      <c r="BV39" s="10" t="n">
-        <v>0.0081</v>
-      </c>
-      <c r="BW39" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX39" s="8" t="n">
-        <v>12053879</v>
-      </c>
-      <c r="BY39" s="9" t="n">
-        <v>76801.28999999999</v>
-      </c>
-      <c r="BZ39" s="10" t="n">
-        <v>0.0086</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="BH39" s="8" t="n"/>
+      <c r="BI39" s="9" t="n"/>
+      <c r="BJ39" s="10" t="n"/>
+      <c r="BK39" s="11" t="n"/>
+      <c r="BL39" s="8" t="n"/>
+      <c r="BM39" s="9" t="n"/>
+      <c r="BN39" s="10" t="n"/>
+      <c r="BO39" s="11" t="n"/>
+      <c r="BP39" s="8" t="n"/>
+      <c r="BQ39" s="9" t="n"/>
+      <c r="BR39" s="10" t="n"/>
+      <c r="BS39" s="11" t="n"/>
+      <c r="BT39" s="8" t="n"/>
+      <c r="BU39" s="9" t="n"/>
+      <c r="BV39" s="10" t="n"/>
+      <c r="BW39" s="11" t="n"/>
+      <c r="BX39" s="8" t="n"/>
+      <c r="BY39" s="9" t="n"/>
+      <c r="BZ39" s="10" t="n"/>
       <c r="CA39" s="11" t="n"/>
     </row>
     <row r="40">
@@ -9140,17 +9118,17 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>ITC Hotels Limited</t>
+          <t>Motilal Oswal Financial Services Limited</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>INE379A01028</t>
+          <t>INE338I01027</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Leisure Services</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D42" s="8" t="n"/>
@@ -9204,70 +9182,94 @@
       <c r="AZ42" s="8" t="n"/>
       <c r="BA42" s="9" t="n"/>
       <c r="BB42" s="10" t="n"/>
-      <c r="BC42" s="11" t="n"/>
-      <c r="BD42" s="8" t="n"/>
-      <c r="BE42" s="9" t="n"/>
-      <c r="BF42" s="10" t="n"/>
-      <c r="BG42" s="11" t="n"/>
-      <c r="BH42" s="8" t="n"/>
-      <c r="BI42" s="9" t="n"/>
-      <c r="BJ42" s="10" t="n"/>
-      <c r="BK42" s="11" t="n"/>
-      <c r="BL42" s="8" t="n"/>
-      <c r="BM42" s="9" t="n"/>
-      <c r="BN42" s="10" t="n"/>
+      <c r="BC42" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BD42" s="8" t="n">
+        <v>591805</v>
+      </c>
+      <c r="BE42" s="9" t="n">
+        <v>5149</v>
+      </c>
+      <c r="BF42" s="10" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="BG42" s="11" t="n">
+        <v>-0.8902567225534253</v>
+      </c>
+      <c r="BH42" s="8" t="n">
+        <v>5392631</v>
+      </c>
+      <c r="BI42" s="9" t="n">
+        <v>43674.92</v>
+      </c>
+      <c r="BJ42" s="10" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="BK42" s="11" t="n">
+        <v>-0.3719237093069153</v>
+      </c>
+      <c r="BL42" s="8" t="n">
+        <v>8585949</v>
+      </c>
+      <c r="BM42" s="9" t="n">
+        <v>56044.78</v>
+      </c>
+      <c r="BN42" s="10" t="n">
+        <v>0.0057</v>
+      </c>
       <c r="BO42" s="11" t="n">
-        <v>-1</v>
+        <v>-0.2132577936597328</v>
       </c>
       <c r="BP42" s="8" t="n">
-        <v>9899412</v>
+        <v>10913294</v>
       </c>
       <c r="BQ42" s="9" t="n">
-        <v>19552.33</v>
+        <v>67154.95</v>
       </c>
       <c r="BR42" s="10" t="n">
-        <v>0.0021</v>
+        <v>0.0072</v>
       </c>
       <c r="BS42" s="11" t="n">
-        <v>0</v>
+        <v>-0.09462389658963724</v>
       </c>
       <c r="BT42" s="8" t="n">
-        <v>9899412</v>
+        <v>12053879</v>
       </c>
       <c r="BU42" s="9" t="n">
-        <v>16216.23</v>
+        <v>70937.08</v>
       </c>
       <c r="BV42" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.0081</v>
       </c>
       <c r="BW42" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BX42" s="8" t="n">
-        <v>9899412</v>
+        <v>12053879</v>
       </c>
       <c r="BY42" s="9" t="n">
-        <v>16131.09</v>
+        <v>76801.28999999999</v>
       </c>
       <c r="BZ42" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.0086</v>
       </c>
       <c r="CA42" s="11" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Multi Commodity Exchange of India Limited</t>
+          <t>ITC Hotels Limited</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>INE745G01043</t>
+          <t>INE379A01028</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Leisure Services</t>
         </is>
       </c>
       <c r="D43" s="8" t="n"/>
@@ -9293,21 +9295,11 @@
       <c r="X43" s="8" t="n"/>
       <c r="Y43" s="9" t="n"/>
       <c r="Z43" s="10" t="n"/>
-      <c r="AA43" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AB43" s="8" t="n">
-        <v>795472</v>
-      </c>
-      <c r="AC43" s="9" t="n">
-        <v>20109.53</v>
-      </c>
-      <c r="AD43" s="10" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="AE43" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="AA43" s="11" t="n"/>
+      <c r="AB43" s="8" t="n"/>
+      <c r="AC43" s="9" t="n"/>
+      <c r="AD43" s="10" t="n"/>
+      <c r="AE43" s="11" t="n"/>
       <c r="AF43" s="8" t="n"/>
       <c r="AG43" s="9" t="n"/>
       <c r="AH43" s="10" t="n"/>
@@ -9343,34 +9335,58 @@
       <c r="BL43" s="8" t="n"/>
       <c r="BM43" s="9" t="n"/>
       <c r="BN43" s="10" t="n"/>
-      <c r="BO43" s="11" t="n"/>
-      <c r="BP43" s="8" t="n"/>
-      <c r="BQ43" s="9" t="n"/>
-      <c r="BR43" s="10" t="n"/>
-      <c r="BS43" s="11" t="n"/>
-      <c r="BT43" s="8" t="n"/>
-      <c r="BU43" s="9" t="n"/>
-      <c r="BV43" s="10" t="n"/>
-      <c r="BW43" s="11" t="n"/>
-      <c r="BX43" s="8" t="n"/>
-      <c r="BY43" s="9" t="n"/>
-      <c r="BZ43" s="10" t="n"/>
+      <c r="BO43" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BP43" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BQ43" s="9" t="n">
+        <v>19552.33</v>
+      </c>
+      <c r="BR43" s="10" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="BS43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT43" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BU43" s="9" t="n">
+        <v>16216.23</v>
+      </c>
+      <c r="BV43" s="10" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="BW43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX43" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BY43" s="9" t="n">
+        <v>16131.09</v>
+      </c>
+      <c r="BZ43" s="10" t="n">
+        <v>0.0018</v>
+      </c>
       <c r="CA43" s="11" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited</t>
+          <t>Multi Commodity Exchange of India Limited</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>INE768C01010</t>
+          <t>INE745G01043</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D44" s="8" t="n"/>
@@ -9396,11 +9412,21 @@
       <c r="X44" s="8" t="n"/>
       <c r="Y44" s="9" t="n"/>
       <c r="Z44" s="10" t="n"/>
-      <c r="AA44" s="11" t="n"/>
-      <c r="AB44" s="8" t="n"/>
-      <c r="AC44" s="9" t="n"/>
-      <c r="AD44" s="10" t="n"/>
-      <c r="AE44" s="11" t="n"/>
+      <c r="AA44" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB44" s="8" t="n">
+        <v>795472</v>
+      </c>
+      <c r="AC44" s="9" t="n">
+        <v>20109.53</v>
+      </c>
+      <c r="AD44" s="10" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="AE44" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="AF44" s="8" t="n"/>
       <c r="AG44" s="9" t="n"/>
       <c r="AH44" s="10" t="n"/>
@@ -9416,45 +9442,19 @@
       <c r="AR44" s="8" t="n"/>
       <c r="AS44" s="9" t="n"/>
       <c r="AT44" s="10" t="n"/>
-      <c r="AU44" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AV44" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="AW44" s="9" t="n">
-        <v>88822.8</v>
-      </c>
-      <c r="AX44" s="10" t="n">
-        <v>0.0077</v>
-      </c>
-      <c r="AY44" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ44" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="BA44" s="9" t="n">
-        <v>89280.39999999999</v>
-      </c>
-      <c r="BB44" s="10" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-      <c r="BC44" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD44" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="BE44" s="9" t="n">
-        <v>89020.8</v>
-      </c>
-      <c r="BF44" s="10" t="n">
-        <v>0.0081</v>
-      </c>
-      <c r="BG44" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="AU44" s="11" t="n"/>
+      <c r="AV44" s="8" t="n"/>
+      <c r="AW44" s="9" t="n"/>
+      <c r="AX44" s="10" t="n"/>
+      <c r="AY44" s="11" t="n"/>
+      <c r="AZ44" s="8" t="n"/>
+      <c r="BA44" s="9" t="n"/>
+      <c r="BB44" s="10" t="n"/>
+      <c r="BC44" s="11" t="n"/>
+      <c r="BD44" s="8" t="n"/>
+      <c r="BE44" s="9" t="n"/>
+      <c r="BF44" s="10" t="n"/>
+      <c r="BG44" s="11" t="n"/>
       <c r="BH44" s="8" t="n"/>
       <c r="BI44" s="9" t="n"/>
       <c r="BJ44" s="10" t="n"/>

--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -493,7 +493,7 @@
   <dimension ref="A1:CA45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -5720,7 +5720,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Fertilizers &amp; Agrochemicals</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -6305,7 +6305,7 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Central Depository Services (India)</t>
+          <t>Central Depository Services (India) Limited</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -7795,24 +7795,24 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Nesco Limited</t>
+          <t>Swaraj Engines Limited</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>INE317F01035</t>
+          <t>INE277A01016</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Commercial Services &amp; Supplies</t>
+          <t>Industrial Products</t>
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>1615.16</v>
+        <v>1716.12</v>
       </c>
       <c r="F35" s="10" t="n">
         <v>0.0001</v>
@@ -7821,10 +7821,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>1635.79</v>
+        <v>1890.58</v>
       </c>
       <c r="J35" s="10" t="n">
         <v>0.0001</v>
@@ -7833,10 +7833,10 @@
         <v>0</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>1780.2</v>
+        <v>1809.43</v>
       </c>
       <c r="N35" s="10" t="n">
         <v>0.0001</v>
@@ -7845,10 +7845,10 @@
         <v>0</v>
       </c>
       <c r="P35" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>1862.26</v>
+        <v>1871.38</v>
       </c>
       <c r="R35" s="10" t="n">
         <v>0.0001</v>
@@ -7857,10 +7857,10 @@
         <v>0</v>
       </c>
       <c r="T35" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="U35" s="9" t="n">
-        <v>1538.11</v>
+        <v>1564.88</v>
       </c>
       <c r="V35" s="10" t="n">
         <v>0.0001</v>
@@ -7869,10 +7869,10 @@
         <v>0</v>
       </c>
       <c r="X35" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="Y35" s="9" t="n">
-        <v>1704.36</v>
+        <v>1700.33</v>
       </c>
       <c r="Z35" s="10" t="n">
         <v>0.0001</v>
@@ -7881,10 +7881,10 @@
         <v>0</v>
       </c>
       <c r="AB35" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AC35" s="9" t="n">
-        <v>1728.63</v>
+        <v>1637.61</v>
       </c>
       <c r="AD35" s="10" t="n">
         <v>0.0001</v>
@@ -7893,10 +7893,10 @@
         <v>0</v>
       </c>
       <c r="AF35" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AG35" s="9" t="n">
-        <v>1858.32</v>
+        <v>1691.91</v>
       </c>
       <c r="AH35" s="10" t="n">
         <v>0.0001</v>
@@ -7905,22 +7905,22 @@
         <v>0</v>
       </c>
       <c r="AJ35" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AK35" s="9" t="n">
-        <v>1947.66</v>
+        <v>1764.08</v>
       </c>
       <c r="AL35" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="AM35" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AN35" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AO35" s="9" t="n">
-        <v>2076.6</v>
+        <v>1892.15</v>
       </c>
       <c r="AP35" s="10" t="n">
         <v>0.0002</v>
@@ -7929,10 +7929,10 @@
         <v>0</v>
       </c>
       <c r="AR35" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AS35" s="9" t="n">
-        <v>1987.1</v>
+        <v>1955.38</v>
       </c>
       <c r="AT35" s="10" t="n">
         <v>0.0002</v>
@@ -7941,10 +7941,10 @@
         <v>0</v>
       </c>
       <c r="AV35" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="AW35" s="9" t="n">
-        <v>2130.6</v>
+        <v>1897.21</v>
       </c>
       <c r="AX35" s="10" t="n">
         <v>0.0002</v>
@@ -7953,10 +7953,10 @@
         <v>0</v>
       </c>
       <c r="AZ35" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="BA35" s="9" t="n">
-        <v>2091.16</v>
+        <v>1983.66</v>
       </c>
       <c r="BB35" s="10" t="n">
         <v>0.0002</v>
@@ -7965,67 +7965,97 @@
         <v>0</v>
       </c>
       <c r="BD35" s="8" t="n">
-        <v>151687</v>
+        <v>47293</v>
       </c>
       <c r="BE35" s="9" t="n">
-        <v>1766.62</v>
+        <v>1867.41</v>
       </c>
       <c r="BF35" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="BG35" s="11" t="n">
-        <v>0.6954140540298874</v>
+        <v>0</v>
       </c>
       <c r="BH35" s="8" t="n">
-        <v>89469</v>
+        <v>47293</v>
       </c>
       <c r="BI35" s="9" t="n">
-        <v>828.48</v>
+        <v>1857.76</v>
       </c>
       <c r="BJ35" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="BK35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL35" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="BM35" s="9" t="n">
+        <v>1925.39</v>
+      </c>
+      <c r="BN35" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="BO35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP35" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="BQ35" s="9" t="n">
+        <v>1844.17</v>
+      </c>
+      <c r="BR35" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="BS35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT35" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="BU35" s="9" t="n">
+        <v>1236.83</v>
+      </c>
+      <c r="BV35" s="10" t="n">
         <v>0.0001</v>
       </c>
-      <c r="BK35" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL35" s="8" t="n"/>
-      <c r="BM35" s="9" t="n"/>
-      <c r="BN35" s="10" t="n"/>
-      <c r="BO35" s="11" t="n"/>
-      <c r="BP35" s="8" t="n"/>
-      <c r="BQ35" s="9" t="n"/>
-      <c r="BR35" s="10" t="n"/>
-      <c r="BS35" s="11" t="n"/>
-      <c r="BT35" s="8" t="n"/>
-      <c r="BU35" s="9" t="n"/>
-      <c r="BV35" s="10" t="n"/>
-      <c r="BW35" s="11" t="n"/>
-      <c r="BX35" s="8" t="n"/>
-      <c r="BY35" s="9" t="n"/>
-      <c r="BZ35" s="10" t="n"/>
+      <c r="BW35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX35" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="BY35" s="9" t="n">
+        <v>1612.64</v>
+      </c>
+      <c r="BZ35" s="10" t="n">
+        <v>0.0002</v>
+      </c>
       <c r="CA35" s="11" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Swaraj Engines Limited</t>
+          <t>Nesco Limited</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>INE277A01016</t>
+          <t>INE317F01035</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Industrial Products</t>
+          <t>Commercial Services &amp; Supplies</t>
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>1716.12</v>
+        <v>1615.16</v>
       </c>
       <c r="F36" s="10" t="n">
         <v>0.0001</v>
@@ -8034,10 +8064,10 @@
         <v>0</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>1890.58</v>
+        <v>1635.79</v>
       </c>
       <c r="J36" s="10" t="n">
         <v>0.0001</v>
@@ -8046,10 +8076,10 @@
         <v>0</v>
       </c>
       <c r="L36" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="M36" s="9" t="n">
-        <v>1809.43</v>
+        <v>1780.2</v>
       </c>
       <c r="N36" s="10" t="n">
         <v>0.0001</v>
@@ -8058,10 +8088,10 @@
         <v>0</v>
       </c>
       <c r="P36" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>1871.38</v>
+        <v>1862.26</v>
       </c>
       <c r="R36" s="10" t="n">
         <v>0.0001</v>
@@ -8070,10 +8100,10 @@
         <v>0</v>
       </c>
       <c r="T36" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="U36" s="9" t="n">
-        <v>1564.88</v>
+        <v>1538.11</v>
       </c>
       <c r="V36" s="10" t="n">
         <v>0.0001</v>
@@ -8082,10 +8112,10 @@
         <v>0</v>
       </c>
       <c r="X36" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="Y36" s="9" t="n">
-        <v>1700.33</v>
+        <v>1704.36</v>
       </c>
       <c r="Z36" s="10" t="n">
         <v>0.0001</v>
@@ -8094,10 +8124,10 @@
         <v>0</v>
       </c>
       <c r="AB36" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AC36" s="9" t="n">
-        <v>1637.61</v>
+        <v>1728.63</v>
       </c>
       <c r="AD36" s="10" t="n">
         <v>0.0001</v>
@@ -8106,10 +8136,10 @@
         <v>0</v>
       </c>
       <c r="AF36" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AG36" s="9" t="n">
-        <v>1691.91</v>
+        <v>1858.32</v>
       </c>
       <c r="AH36" s="10" t="n">
         <v>0.0001</v>
@@ -8118,22 +8148,22 @@
         <v>0</v>
       </c>
       <c r="AJ36" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AK36" s="9" t="n">
-        <v>1764.08</v>
+        <v>1947.66</v>
       </c>
       <c r="AL36" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="AM36" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AN36" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AO36" s="9" t="n">
-        <v>1892.15</v>
+        <v>2076.6</v>
       </c>
       <c r="AP36" s="10" t="n">
         <v>0.0002</v>
@@ -8142,10 +8172,10 @@
         <v>0</v>
       </c>
       <c r="AR36" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AS36" s="9" t="n">
-        <v>1955.38</v>
+        <v>1987.1</v>
       </c>
       <c r="AT36" s="10" t="n">
         <v>0.0002</v>
@@ -8154,10 +8184,10 @@
         <v>0</v>
       </c>
       <c r="AV36" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="AW36" s="9" t="n">
-        <v>1897.21</v>
+        <v>2130.6</v>
       </c>
       <c r="AX36" s="10" t="n">
         <v>0.0002</v>
@@ -8166,10 +8196,10 @@
         <v>0</v>
       </c>
       <c r="AZ36" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="BA36" s="9" t="n">
-        <v>1983.66</v>
+        <v>2091.16</v>
       </c>
       <c r="BB36" s="10" t="n">
         <v>0.0002</v>
@@ -8178,74 +8208,44 @@
         <v>0</v>
       </c>
       <c r="BD36" s="8" t="n">
-        <v>47293</v>
+        <v>151687</v>
       </c>
       <c r="BE36" s="9" t="n">
-        <v>1867.41</v>
+        <v>1766.62</v>
       </c>
       <c r="BF36" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="BG36" s="11" t="n">
-        <v>0</v>
+        <v>0.6954140540298874</v>
       </c>
       <c r="BH36" s="8" t="n">
-        <v>47293</v>
+        <v>89469</v>
       </c>
       <c r="BI36" s="9" t="n">
-        <v>1857.76</v>
+        <v>828.48</v>
       </c>
       <c r="BJ36" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="BK36" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL36" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="BM36" s="9" t="n">
-        <v>1925.39</v>
-      </c>
-      <c r="BN36" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="BO36" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP36" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="BQ36" s="9" t="n">
-        <v>1844.17</v>
-      </c>
-      <c r="BR36" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="BS36" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT36" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="BU36" s="9" t="n">
-        <v>1236.83</v>
-      </c>
-      <c r="BV36" s="10" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="BW36" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX36" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="BY36" s="9" t="n">
-        <v>1612.64</v>
-      </c>
-      <c r="BZ36" s="10" t="n">
-        <v>0.0002</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="BL36" s="8" t="n"/>
+      <c r="BM36" s="9" t="n"/>
+      <c r="BN36" s="10" t="n"/>
+      <c r="BO36" s="11" t="n"/>
+      <c r="BP36" s="8" t="n"/>
+      <c r="BQ36" s="9" t="n"/>
+      <c r="BR36" s="10" t="n"/>
+      <c r="BS36" s="11" t="n"/>
+      <c r="BT36" s="8" t="n"/>
+      <c r="BU36" s="9" t="n"/>
+      <c r="BV36" s="10" t="n"/>
+      <c r="BW36" s="11" t="n"/>
+      <c r="BX36" s="8" t="n"/>
+      <c r="BY36" s="9" t="n"/>
+      <c r="BZ36" s="10" t="n"/>
       <c r="CA36" s="11" t="n"/>
     </row>
     <row r="37">
@@ -8653,17 +8653,17 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited</t>
+          <t>Motilal Oswal Financial Services Limited</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>INE768C01010</t>
+          <t>INE338I01027</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D39" s="8" t="n"/>
@@ -8709,64 +8709,86 @@
       <c r="AR39" s="8" t="n"/>
       <c r="AS39" s="9" t="n"/>
       <c r="AT39" s="10" t="n"/>
-      <c r="AU39" s="11" t="n">
+      <c r="AU39" s="11" t="n"/>
+      <c r="AV39" s="8" t="n"/>
+      <c r="AW39" s="9" t="n"/>
+      <c r="AX39" s="10" t="n"/>
+      <c r="AY39" s="11" t="n"/>
+      <c r="AZ39" s="8" t="n"/>
+      <c r="BA39" s="9" t="n"/>
+      <c r="BB39" s="10" t="n"/>
+      <c r="BC39" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="AV39" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="AW39" s="9" t="n">
-        <v>88822.8</v>
-      </c>
-      <c r="AX39" s="10" t="n">
-        <v>0.0077</v>
-      </c>
-      <c r="AY39" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ39" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="BA39" s="9" t="n">
-        <v>89280.39999999999</v>
-      </c>
-      <c r="BB39" s="10" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-      <c r="BC39" s="11" t="n">
-        <v>0</v>
-      </c>
       <c r="BD39" s="8" t="n">
-        <v>4400000</v>
+        <v>591805</v>
       </c>
       <c r="BE39" s="9" t="n">
-        <v>89020.8</v>
+        <v>5149</v>
       </c>
       <c r="BF39" s="10" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="BG39" s="11" t="n">
+        <v>-0.8902567225534253</v>
+      </c>
+      <c r="BH39" s="8" t="n">
+        <v>5392631</v>
+      </c>
+      <c r="BI39" s="9" t="n">
+        <v>43674.92</v>
+      </c>
+      <c r="BJ39" s="10" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="BK39" s="11" t="n">
+        <v>-0.3719237093069153</v>
+      </c>
+      <c r="BL39" s="8" t="n">
+        <v>8585949</v>
+      </c>
+      <c r="BM39" s="9" t="n">
+        <v>56044.78</v>
+      </c>
+      <c r="BN39" s="10" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="BO39" s="11" t="n">
+        <v>-0.2132577936597328</v>
+      </c>
+      <c r="BP39" s="8" t="n">
+        <v>10913294</v>
+      </c>
+      <c r="BQ39" s="9" t="n">
+        <v>67154.95</v>
+      </c>
+      <c r="BR39" s="10" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="BS39" s="11" t="n">
+        <v>-0.09462389658963724</v>
+      </c>
+      <c r="BT39" s="8" t="n">
+        <v>12053879</v>
+      </c>
+      <c r="BU39" s="9" t="n">
+        <v>70937.08</v>
+      </c>
+      <c r="BV39" s="10" t="n">
         <v>0.0081</v>
       </c>
-      <c r="BG39" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH39" s="8" t="n"/>
-      <c r="BI39" s="9" t="n"/>
-      <c r="BJ39" s="10" t="n"/>
-      <c r="BK39" s="11" t="n"/>
-      <c r="BL39" s="8" t="n"/>
-      <c r="BM39" s="9" t="n"/>
-      <c r="BN39" s="10" t="n"/>
-      <c r="BO39" s="11" t="n"/>
-      <c r="BP39" s="8" t="n"/>
-      <c r="BQ39" s="9" t="n"/>
-      <c r="BR39" s="10" t="n"/>
-      <c r="BS39" s="11" t="n"/>
-      <c r="BT39" s="8" t="n"/>
-      <c r="BU39" s="9" t="n"/>
-      <c r="BV39" s="10" t="n"/>
-      <c r="BW39" s="11" t="n"/>
-      <c r="BX39" s="8" t="n"/>
-      <c r="BY39" s="9" t="n"/>
-      <c r="BZ39" s="10" t="n"/>
+      <c r="BW39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX39" s="8" t="n">
+        <v>12053879</v>
+      </c>
+      <c r="BY39" s="9" t="n">
+        <v>76801.28999999999</v>
+      </c>
+      <c r="BZ39" s="10" t="n">
+        <v>0.0086</v>
+      </c>
       <c r="CA39" s="11" t="n"/>
     </row>
     <row r="40">
@@ -9118,17 +9140,17 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Motilal Oswal Financial Services Limited</t>
+          <t>ITC Hotels Limited</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>INE338I01027</t>
+          <t>INE379A01028</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Leisure Services</t>
         </is>
       </c>
       <c r="D42" s="8" t="n"/>
@@ -9182,94 +9204,70 @@
       <c r="AZ42" s="8" t="n"/>
       <c r="BA42" s="9" t="n"/>
       <c r="BB42" s="10" t="n"/>
-      <c r="BC42" s="11" t="n">
+      <c r="BC42" s="11" t="n"/>
+      <c r="BD42" s="8" t="n"/>
+      <c r="BE42" s="9" t="n"/>
+      <c r="BF42" s="10" t="n"/>
+      <c r="BG42" s="11" t="n"/>
+      <c r="BH42" s="8" t="n"/>
+      <c r="BI42" s="9" t="n"/>
+      <c r="BJ42" s="10" t="n"/>
+      <c r="BK42" s="11" t="n"/>
+      <c r="BL42" s="8" t="n"/>
+      <c r="BM42" s="9" t="n"/>
+      <c r="BN42" s="10" t="n"/>
+      <c r="BO42" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="BD42" s="8" t="n">
-        <v>591805</v>
-      </c>
-      <c r="BE42" s="9" t="n">
-        <v>5149</v>
-      </c>
-      <c r="BF42" s="10" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="BG42" s="11" t="n">
-        <v>-0.8902567225534253</v>
-      </c>
-      <c r="BH42" s="8" t="n">
-        <v>5392631</v>
-      </c>
-      <c r="BI42" s="9" t="n">
-        <v>43674.92</v>
-      </c>
-      <c r="BJ42" s="10" t="n">
-        <v>0.0042</v>
-      </c>
-      <c r="BK42" s="11" t="n">
-        <v>-0.3719237093069153</v>
-      </c>
-      <c r="BL42" s="8" t="n">
-        <v>8585949</v>
-      </c>
-      <c r="BM42" s="9" t="n">
-        <v>56044.78</v>
-      </c>
-      <c r="BN42" s="10" t="n">
-        <v>0.0057</v>
-      </c>
-      <c r="BO42" s="11" t="n">
-        <v>-0.2132577936597328</v>
-      </c>
       <c r="BP42" s="8" t="n">
-        <v>10913294</v>
+        <v>9899412</v>
       </c>
       <c r="BQ42" s="9" t="n">
-        <v>67154.95</v>
+        <v>19552.33</v>
       </c>
       <c r="BR42" s="10" t="n">
-        <v>0.0072</v>
+        <v>0.0021</v>
       </c>
       <c r="BS42" s="11" t="n">
-        <v>-0.09462389658963724</v>
+        <v>0</v>
       </c>
       <c r="BT42" s="8" t="n">
-        <v>12053879</v>
+        <v>9899412</v>
       </c>
       <c r="BU42" s="9" t="n">
-        <v>70937.08</v>
+        <v>16216.23</v>
       </c>
       <c r="BV42" s="10" t="n">
-        <v>0.0081</v>
+        <v>0.0018</v>
       </c>
       <c r="BW42" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BX42" s="8" t="n">
-        <v>12053879</v>
+        <v>9899412</v>
       </c>
       <c r="BY42" s="9" t="n">
-        <v>76801.28999999999</v>
+        <v>16131.09</v>
       </c>
       <c r="BZ42" s="10" t="n">
-        <v>0.0086</v>
+        <v>0.0018</v>
       </c>
       <c r="CA42" s="11" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>ITC Hotels Limited</t>
+          <t>Multi Commodity Exchange of India Limited</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>INE379A01028</t>
+          <t>INE745G01043</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Leisure Services</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D43" s="8" t="n"/>
@@ -9295,11 +9293,21 @@
       <c r="X43" s="8" t="n"/>
       <c r="Y43" s="9" t="n"/>
       <c r="Z43" s="10" t="n"/>
-      <c r="AA43" s="11" t="n"/>
-      <c r="AB43" s="8" t="n"/>
-      <c r="AC43" s="9" t="n"/>
-      <c r="AD43" s="10" t="n"/>
-      <c r="AE43" s="11" t="n"/>
+      <c r="AA43" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB43" s="8" t="n">
+        <v>795472</v>
+      </c>
+      <c r="AC43" s="9" t="n">
+        <v>20109.53</v>
+      </c>
+      <c r="AD43" s="10" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="AE43" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="AF43" s="8" t="n"/>
       <c r="AG43" s="9" t="n"/>
       <c r="AH43" s="10" t="n"/>
@@ -9335,58 +9343,34 @@
       <c r="BL43" s="8" t="n"/>
       <c r="BM43" s="9" t="n"/>
       <c r="BN43" s="10" t="n"/>
-      <c r="BO43" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BP43" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BQ43" s="9" t="n">
-        <v>19552.33</v>
-      </c>
-      <c r="BR43" s="10" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="BS43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT43" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BU43" s="9" t="n">
-        <v>16216.23</v>
-      </c>
-      <c r="BV43" s="10" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="BW43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX43" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BY43" s="9" t="n">
-        <v>16131.09</v>
-      </c>
-      <c r="BZ43" s="10" t="n">
-        <v>0.0018</v>
-      </c>
+      <c r="BO43" s="11" t="n"/>
+      <c r="BP43" s="8" t="n"/>
+      <c r="BQ43" s="9" t="n"/>
+      <c r="BR43" s="10" t="n"/>
+      <c r="BS43" s="11" t="n"/>
+      <c r="BT43" s="8" t="n"/>
+      <c r="BU43" s="9" t="n"/>
+      <c r="BV43" s="10" t="n"/>
+      <c r="BW43" s="11" t="n"/>
+      <c r="BX43" s="8" t="n"/>
+      <c r="BY43" s="9" t="n"/>
+      <c r="BZ43" s="10" t="n"/>
       <c r="CA43" s="11" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Multi Commodity Exchange of India Limited</t>
+          <t>Zydus Wellness Limited</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>INE745G01043</t>
+          <t>INE768C01010</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D44" s="8" t="n"/>
@@ -9412,21 +9396,11 @@
       <c r="X44" s="8" t="n"/>
       <c r="Y44" s="9" t="n"/>
       <c r="Z44" s="10" t="n"/>
-      <c r="AA44" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AB44" s="8" t="n">
-        <v>795472</v>
-      </c>
-      <c r="AC44" s="9" t="n">
-        <v>20109.53</v>
-      </c>
-      <c r="AD44" s="10" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="AE44" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="AA44" s="11" t="n"/>
+      <c r="AB44" s="8" t="n"/>
+      <c r="AC44" s="9" t="n"/>
+      <c r="AD44" s="10" t="n"/>
+      <c r="AE44" s="11" t="n"/>
       <c r="AF44" s="8" t="n"/>
       <c r="AG44" s="9" t="n"/>
       <c r="AH44" s="10" t="n"/>
@@ -9442,19 +9416,45 @@
       <c r="AR44" s="8" t="n"/>
       <c r="AS44" s="9" t="n"/>
       <c r="AT44" s="10" t="n"/>
-      <c r="AU44" s="11" t="n"/>
-      <c r="AV44" s="8" t="n"/>
-      <c r="AW44" s="9" t="n"/>
-      <c r="AX44" s="10" t="n"/>
-      <c r="AY44" s="11" t="n"/>
-      <c r="AZ44" s="8" t="n"/>
-      <c r="BA44" s="9" t="n"/>
-      <c r="BB44" s="10" t="n"/>
-      <c r="BC44" s="11" t="n"/>
-      <c r="BD44" s="8" t="n"/>
-      <c r="BE44" s="9" t="n"/>
-      <c r="BF44" s="10" t="n"/>
-      <c r="BG44" s="11" t="n"/>
+      <c r="AU44" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AV44" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AW44" s="9" t="n">
+        <v>88822.8</v>
+      </c>
+      <c r="AX44" s="10" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="AY44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ44" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="BA44" s="9" t="n">
+        <v>89280.39999999999</v>
+      </c>
+      <c r="BB44" s="10" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="BC44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD44" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="BE44" s="9" t="n">
+        <v>89020.8</v>
+      </c>
+      <c r="BF44" s="10" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="BG44" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="BH44" s="8" t="n"/>
       <c r="BI44" s="9" t="n"/>
       <c r="BJ44" s="10" t="n"/>

--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -493,7 +493,7 @@
   <dimension ref="A1:CA45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -3930,486 +3930,486 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Maruti Suzuki India Limited</t>
+          <t>Axis Bank Limited</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>INE585B01010</t>
+          <t>INE238A01034</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Automobiles</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>2913495</v>
+        <v>33672018</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>414706.88</v>
+        <v>413997.46</v>
       </c>
       <c r="F16" s="10" t="n">
         <v>0.0279</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>0.008655026233384513</v>
+        <v>0</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>2888495</v>
+        <v>33672018</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>407711.07</v>
+        <v>453124.35</v>
       </c>
       <c r="J16" s="10" t="n">
+        <v>0.0316</v>
+      </c>
+      <c r="K16" s="11" t="n">
+        <v>0.01284838640542339</v>
+      </c>
+      <c r="L16" s="8" t="n">
+        <v>33244875</v>
+      </c>
+      <c r="M16" s="9" t="n">
+        <v>427728.56</v>
+      </c>
+      <c r="N16" s="10" t="n">
+        <v>0.0302</v>
+      </c>
+      <c r="O16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="8" t="n">
+        <v>33244875</v>
+      </c>
+      <c r="Q16" s="9" t="n">
+        <v>421644.75</v>
+      </c>
+      <c r="R16" s="10" t="n">
+        <v>0.0299</v>
+      </c>
+      <c r="S16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v>33244875</v>
+      </c>
+      <c r="U16" s="9" t="n">
+        <v>386072.73</v>
+      </c>
+      <c r="V16" s="10" t="n">
+        <v>0.0299</v>
+      </c>
+      <c r="W16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="8" t="n">
+        <v>33244875</v>
+      </c>
+      <c r="Y16" s="9" t="n">
+        <v>460075.83</v>
+      </c>
+      <c r="Z16" s="10" t="n">
+        <v>0.0343</v>
+      </c>
+      <c r="AA16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="8" t="n">
+        <v>33244875</v>
+      </c>
+      <c r="AC16" s="9" t="n">
+        <v>455587.77</v>
+      </c>
+      <c r="AD16" s="10" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="AE16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="8" t="n">
+        <v>33244875</v>
+      </c>
+      <c r="AG16" s="9" t="n">
+        <v>422010.44</v>
+      </c>
+      <c r="AH16" s="10" t="n">
+        <v>0.0317</v>
+      </c>
+      <c r="AI16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="8" t="n">
+        <v>33244875</v>
+      </c>
+      <c r="AK16" s="9" t="n">
+        <v>425434.67</v>
+      </c>
+      <c r="AL16" s="10" t="n">
+        <v>0.0328</v>
+      </c>
+      <c r="AM16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" s="8" t="n">
+        <v>33244875</v>
+      </c>
+      <c r="AO16" s="9" t="n">
+        <v>409842.82</v>
+      </c>
+      <c r="AP16" s="10" t="n">
+        <v>0.0326</v>
+      </c>
+      <c r="AQ16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" s="8" t="n">
+        <v>33244875</v>
+      </c>
+      <c r="AS16" s="9" t="n">
+        <v>376199.01</v>
+      </c>
+      <c r="AT16" s="10" t="n">
+        <v>0.0314</v>
+      </c>
+      <c r="AU16" s="11" t="n">
+        <v>0.01837960782511803</v>
+      </c>
+      <c r="AV16" s="8" t="n">
+        <v>32644875</v>
+      </c>
+      <c r="AW16" s="9" t="n">
+        <v>341204.23</v>
+      </c>
+      <c r="AX16" s="10" t="n">
+        <v>0.0297</v>
+      </c>
+      <c r="AY16" s="11" t="n">
+        <v>0.0842854566355568</v>
+      </c>
+      <c r="AZ16" s="8" t="n">
+        <v>30107270</v>
+      </c>
+      <c r="BA16" s="9" t="n">
+        <v>321666.07</v>
+      </c>
+      <c r="BB16" s="10" t="n">
         <v>0.0284</v>
       </c>
-      <c r="K16" s="11" t="n">
-        <v>-0.04981998029569614</v>
-      </c>
-      <c r="L16" s="8" t="n">
-        <v>3039945</v>
-      </c>
-      <c r="M16" s="9" t="n">
-        <v>399053.58</v>
-      </c>
-      <c r="N16" s="10" t="n">
-        <v>0.0282</v>
-      </c>
-      <c r="O16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="8" t="n">
-        <v>3039945</v>
-      </c>
-      <c r="Q16" s="9" t="n">
-        <v>404738.28</v>
-      </c>
-      <c r="R16" s="10" t="n">
-        <v>0.0287</v>
-      </c>
-      <c r="S16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v>3039945</v>
-      </c>
-      <c r="U16" s="9" t="n">
-        <v>374095.63</v>
-      </c>
-      <c r="V16" s="10" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="W16" s="11" t="n">
-        <v>0.06253145709252579</v>
-      </c>
-      <c r="X16" s="8" t="n">
-        <v>2861040</v>
-      </c>
-      <c r="Y16" s="9" t="n">
-        <v>425064.71</v>
-      </c>
-      <c r="Z16" s="10" t="n">
-        <v>0.0317</v>
-      </c>
-      <c r="AA16" s="11" t="n">
-        <v>0.02897415480359852</v>
-      </c>
-      <c r="AB16" s="8" t="n">
-        <v>2780478</v>
-      </c>
-      <c r="AC16" s="9" t="n">
-        <v>405921.98</v>
-      </c>
-      <c r="AD16" s="10" t="n">
-        <v>0.0303</v>
-      </c>
-      <c r="AE16" s="11" t="n">
-        <v>0.01230872292630713</v>
-      </c>
-      <c r="AF16" s="8" t="n">
-        <v>2746670</v>
-      </c>
-      <c r="AG16" s="9" t="n">
-        <v>458611.49</v>
-      </c>
-      <c r="AH16" s="10" t="n">
-        <v>0.0344</v>
-      </c>
-      <c r="AI16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" s="8" t="n">
-        <v>2746670</v>
-      </c>
-      <c r="AK16" s="9" t="n">
-        <v>436720.53</v>
-      </c>
-      <c r="AL16" s="10" t="n">
-        <v>0.0337</v>
-      </c>
-      <c r="AM16" s="11" t="n">
-        <v>0.01854138622819997</v>
-      </c>
-      <c r="AN16" s="8" t="n">
-        <v>2696670</v>
-      </c>
-      <c r="AO16" s="9" t="n">
-        <v>436483.01</v>
-      </c>
-      <c r="AP16" s="10" t="n">
-        <v>0.0347</v>
-      </c>
-      <c r="AQ16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" s="8" t="n">
-        <v>2696670</v>
-      </c>
-      <c r="AS16" s="9" t="n">
-        <v>432249.23</v>
-      </c>
-      <c r="AT16" s="10" t="n">
-        <v>0.0361</v>
-      </c>
-      <c r="AU16" s="11" t="n">
-        <v>-0.01820386140308082</v>
-      </c>
-      <c r="AV16" s="8" t="n">
-        <v>2746670</v>
-      </c>
-      <c r="AW16" s="9" t="n">
-        <v>406259.96</v>
-      </c>
-      <c r="AX16" s="10" t="n">
-        <v>0.0353</v>
-      </c>
-      <c r="AY16" s="11" t="n">
-        <v>-0.09100927632732893</v>
-      </c>
-      <c r="AZ16" s="8" t="n">
-        <v>3021670</v>
-      </c>
-      <c r="BA16" s="9" t="n">
-        <v>380972.15</v>
-      </c>
-      <c r="BB16" s="10" t="n">
-        <v>0.0336</v>
-      </c>
       <c r="BC16" s="11" t="n">
-        <v>0</v>
+        <v>0.1045592607036581</v>
       </c>
       <c r="BD16" s="8" t="n">
-        <v>3021670</v>
+        <v>27257270</v>
       </c>
       <c r="BE16" s="9" t="n">
-        <v>374687.08</v>
+        <v>326869.18</v>
       </c>
       <c r="BF16" s="10" t="n">
-        <v>0.0339</v>
+        <v>0.0296</v>
       </c>
       <c r="BG16" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BH16" s="8" t="n">
-        <v>3021670</v>
+        <v>27257270</v>
       </c>
       <c r="BI16" s="9" t="n">
-        <v>372239.53</v>
+        <v>324961.17</v>
       </c>
       <c r="BJ16" s="10" t="n">
-        <v>0.0358</v>
+        <v>0.0313</v>
       </c>
       <c r="BK16" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BL16" s="8" t="n">
-        <v>3021670</v>
+        <v>27257270</v>
       </c>
       <c r="BM16" s="9" t="n">
-        <v>370366.09</v>
+        <v>322998.65</v>
       </c>
       <c r="BN16" s="10" t="n">
-        <v>0.0376</v>
+        <v>0.0328</v>
       </c>
       <c r="BO16" s="11" t="n">
-        <v>0.001190161420612721</v>
+        <v>0</v>
       </c>
       <c r="BP16" s="8" t="n">
-        <v>3018078</v>
+        <v>27257270</v>
       </c>
       <c r="BQ16" s="9" t="n">
-        <v>347747.47</v>
+        <v>300375.12</v>
       </c>
       <c r="BR16" s="10" t="n">
-        <v>0.0372</v>
+        <v>0.0321</v>
       </c>
       <c r="BS16" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BT16" s="8" t="n">
-        <v>3018078</v>
+        <v>27257270</v>
       </c>
       <c r="BU16" s="9" t="n">
-        <v>360535.07</v>
+        <v>276811.21</v>
       </c>
       <c r="BV16" s="10" t="n">
-        <v>0.041</v>
+        <v>0.0315</v>
       </c>
       <c r="BW16" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BX16" s="8" t="n">
-        <v>3018078</v>
+        <v>27257270</v>
       </c>
       <c r="BY16" s="9" t="n">
-        <v>371545.02</v>
+        <v>268783.94</v>
       </c>
       <c r="BZ16" s="10" t="n">
-        <v>0.0414</v>
+        <v>0.03</v>
       </c>
       <c r="CA16" s="11" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Axis Bank Limited</t>
+          <t>Maruti Suzuki India Limited</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>INE238A01034</t>
+          <t>INE585B01010</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Automobiles</t>
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>33672018</v>
+        <v>2913495</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>413997.46</v>
+        <v>414706.88</v>
       </c>
       <c r="F17" s="10" t="n">
         <v>0.0279</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>0</v>
+        <v>0.008655026233384513</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>33672018</v>
+        <v>2888495</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>453124.35</v>
+        <v>407711.07</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.0316</v>
+        <v>0.0284</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>0.01284838640542339</v>
+        <v>-0.04981998029569614</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>33244875</v>
+        <v>3039945</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>427728.56</v>
+        <v>399053.58</v>
       </c>
       <c r="N17" s="10" t="n">
-        <v>0.0302</v>
+        <v>0.0282</v>
       </c>
       <c r="O17" s="11" t="n">
         <v>0</v>
       </c>
       <c r="P17" s="8" t="n">
-        <v>33244875</v>
+        <v>3039945</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>421644.75</v>
+        <v>404738.28</v>
       </c>
       <c r="R17" s="10" t="n">
-        <v>0.0299</v>
+        <v>0.0287</v>
       </c>
       <c r="S17" s="11" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="8" t="n">
-        <v>33244875</v>
+        <v>3039945</v>
       </c>
       <c r="U17" s="9" t="n">
-        <v>386072.73</v>
+        <v>374095.63</v>
       </c>
       <c r="V17" s="10" t="n">
-        <v>0.0299</v>
+        <v>0.029</v>
       </c>
       <c r="W17" s="11" t="n">
-        <v>0</v>
+        <v>0.06253145709252579</v>
       </c>
       <c r="X17" s="8" t="n">
-        <v>33244875</v>
+        <v>2861040</v>
       </c>
       <c r="Y17" s="9" t="n">
-        <v>460075.83</v>
+        <v>425064.71</v>
       </c>
       <c r="Z17" s="10" t="n">
-        <v>0.0343</v>
+        <v>0.0317</v>
       </c>
       <c r="AA17" s="11" t="n">
-        <v>0</v>
+        <v>0.02897415480359852</v>
       </c>
       <c r="AB17" s="8" t="n">
-        <v>33244875</v>
+        <v>2780478</v>
       </c>
       <c r="AC17" s="9" t="n">
-        <v>455587.77</v>
+        <v>405921.98</v>
       </c>
       <c r="AD17" s="10" t="n">
-        <v>0.034</v>
+        <v>0.0303</v>
       </c>
       <c r="AE17" s="11" t="n">
-        <v>0</v>
+        <v>0.01230872292630713</v>
       </c>
       <c r="AF17" s="8" t="n">
-        <v>33244875</v>
+        <v>2746670</v>
       </c>
       <c r="AG17" s="9" t="n">
-        <v>422010.44</v>
+        <v>458611.49</v>
       </c>
       <c r="AH17" s="10" t="n">
-        <v>0.0317</v>
+        <v>0.0344</v>
       </c>
       <c r="AI17" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AJ17" s="8" t="n">
-        <v>33244875</v>
+        <v>2746670</v>
       </c>
       <c r="AK17" s="9" t="n">
-        <v>425434.67</v>
+        <v>436720.53</v>
       </c>
       <c r="AL17" s="10" t="n">
-        <v>0.0328</v>
+        <v>0.0337</v>
       </c>
       <c r="AM17" s="11" t="n">
-        <v>0</v>
+        <v>0.01854138622819997</v>
       </c>
       <c r="AN17" s="8" t="n">
-        <v>33244875</v>
+        <v>2696670</v>
       </c>
       <c r="AO17" s="9" t="n">
-        <v>409842.82</v>
+        <v>436483.01</v>
       </c>
       <c r="AP17" s="10" t="n">
-        <v>0.0326</v>
+        <v>0.0347</v>
       </c>
       <c r="AQ17" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AR17" s="8" t="n">
-        <v>33244875</v>
+        <v>2696670</v>
       </c>
       <c r="AS17" s="9" t="n">
-        <v>376199.01</v>
+        <v>432249.23</v>
       </c>
       <c r="AT17" s="10" t="n">
-        <v>0.0314</v>
+        <v>0.0361</v>
       </c>
       <c r="AU17" s="11" t="n">
-        <v>0.01837960782511803</v>
+        <v>-0.01820386140308082</v>
       </c>
       <c r="AV17" s="8" t="n">
-        <v>32644875</v>
+        <v>2746670</v>
       </c>
       <c r="AW17" s="9" t="n">
-        <v>341204.23</v>
+        <v>406259.96</v>
       </c>
       <c r="AX17" s="10" t="n">
-        <v>0.0297</v>
+        <v>0.0353</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.0842854566355568</v>
+        <v>-0.09100927632732893</v>
       </c>
       <c r="AZ17" s="8" t="n">
-        <v>30107270</v>
+        <v>3021670</v>
       </c>
       <c r="BA17" s="9" t="n">
-        <v>321666.07</v>
+        <v>380972.15</v>
       </c>
       <c r="BB17" s="10" t="n">
-        <v>0.0284</v>
+        <v>0.0336</v>
       </c>
       <c r="BC17" s="11" t="n">
-        <v>0.1045592607036581</v>
+        <v>0</v>
       </c>
       <c r="BD17" s="8" t="n">
-        <v>27257270</v>
+        <v>3021670</v>
       </c>
       <c r="BE17" s="9" t="n">
-        <v>326869.18</v>
+        <v>374687.08</v>
       </c>
       <c r="BF17" s="10" t="n">
-        <v>0.0296</v>
+        <v>0.0339</v>
       </c>
       <c r="BG17" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BH17" s="8" t="n">
-        <v>27257270</v>
+        <v>3021670</v>
       </c>
       <c r="BI17" s="9" t="n">
-        <v>324961.17</v>
+        <v>372239.53</v>
       </c>
       <c r="BJ17" s="10" t="n">
-        <v>0.0313</v>
+        <v>0.0358</v>
       </c>
       <c r="BK17" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BL17" s="8" t="n">
-        <v>27257270</v>
+        <v>3021670</v>
       </c>
       <c r="BM17" s="9" t="n">
-        <v>322998.65</v>
+        <v>370366.09</v>
       </c>
       <c r="BN17" s="10" t="n">
-        <v>0.0328</v>
+        <v>0.0376</v>
       </c>
       <c r="BO17" s="11" t="n">
-        <v>0</v>
+        <v>0.001190161420612721</v>
       </c>
       <c r="BP17" s="8" t="n">
-        <v>27257270</v>
+        <v>3018078</v>
       </c>
       <c r="BQ17" s="9" t="n">
-        <v>300375.12</v>
+        <v>347747.47</v>
       </c>
       <c r="BR17" s="10" t="n">
-        <v>0.0321</v>
+        <v>0.0372</v>
       </c>
       <c r="BS17" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BT17" s="8" t="n">
-        <v>27257270</v>
+        <v>3018078</v>
       </c>
       <c r="BU17" s="9" t="n">
-        <v>276811.21</v>
+        <v>360535.07</v>
       </c>
       <c r="BV17" s="10" t="n">
-        <v>0.0315</v>
+        <v>0.041</v>
       </c>
       <c r="BW17" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BX17" s="8" t="n">
-        <v>27257270</v>
+        <v>3018078</v>
       </c>
       <c r="BY17" s="9" t="n">
-        <v>268783.94</v>
+        <v>371545.02</v>
       </c>
       <c r="BZ17" s="10" t="n">
-        <v>0.03</v>
+        <v>0.0414</v>
       </c>
       <c r="CA17" s="11" t="n"/>
     </row>
@@ -6305,24 +6305,24 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Central Depository Services (India)</t>
+          <t>The Great Eastern Shipping Company Limited</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>INE736A01011</t>
+          <t>INE017A01032</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Transport Services</t>
         </is>
       </c>
       <c r="D27" s="8" t="n">
-        <v>2264603</v>
+        <v>2205298</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>30187.16</v>
+        <v>29780.34</v>
       </c>
       <c r="F27" s="10" t="n">
         <v>0.002</v>
@@ -6331,241 +6331,155 @@
         <v>0</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>2264603</v>
+        <v>2205298</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>29564.39</v>
+        <v>32706.77</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.0021</v>
+        <v>0.0023</v>
       </c>
       <c r="K27" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>2264603</v>
+        <v>2205298</v>
       </c>
       <c r="M27" s="9" t="n">
-        <v>28185.25</v>
+        <v>31290.97</v>
       </c>
       <c r="N27" s="10" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="O27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="8" t="n">
+        <v>2205298</v>
+      </c>
+      <c r="Q27" s="9" t="n">
+        <v>34773.14</v>
+      </c>
+      <c r="R27" s="10" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="S27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v>2205298</v>
+      </c>
+      <c r="U27" s="9" t="n">
+        <v>31198.35</v>
+      </c>
+      <c r="V27" s="10" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="W27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" s="8" t="n">
+        <v>2205298</v>
+      </c>
+      <c r="Y27" s="9" t="n">
+        <v>29526.73</v>
+      </c>
+      <c r="Z27" s="10" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="AA27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="8" t="n">
+        <v>2205298</v>
+      </c>
+      <c r="AC27" s="9" t="n">
+        <v>26516.5</v>
+      </c>
+      <c r="AD27" s="10" t="n">
         <v>0.002</v>
       </c>
-      <c r="O27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="Q27" s="9" t="n">
-        <v>28805.75</v>
-      </c>
-      <c r="R27" s="10" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="S27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="U27" s="9" t="n">
-        <v>25349.97</v>
-      </c>
-      <c r="V27" s="10" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="W27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="Y27" s="9" t="n">
-        <v>28810.28</v>
-      </c>
-      <c r="Z27" s="10" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="AA27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="AC27" s="9" t="n">
-        <v>29897.29</v>
-      </c>
-      <c r="AD27" s="10" t="n">
-        <v>0.0022</v>
-      </c>
       <c r="AE27" s="11" t="n">
-        <v>0</v>
+        <v>0.3305575398932319</v>
       </c>
       <c r="AF27" s="8" t="n">
-        <v>2264603</v>
+        <v>1657424</v>
       </c>
       <c r="AG27" s="9" t="n">
-        <v>32691.81</v>
+        <v>18712.32</v>
       </c>
       <c r="AH27" s="10" t="n">
-        <v>0.0025</v>
+        <v>0.0014</v>
       </c>
       <c r="AI27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ27" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="AK27" s="9" t="n">
-        <v>36623.16</v>
-      </c>
-      <c r="AL27" s="10" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="AM27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN27" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="AO27" s="9" t="n">
-        <v>35943.78</v>
-      </c>
-      <c r="AP27" s="10" t="n">
-        <v>0.0029</v>
-      </c>
-      <c r="AQ27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="AS27" s="9" t="n">
-        <v>33031.5</v>
-      </c>
-      <c r="AT27" s="10" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="AU27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="AW27" s="9" t="n">
-        <v>32257.01</v>
-      </c>
-      <c r="AX27" s="10" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="AY27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ27" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="BA27" s="9" t="n">
-        <v>33534.24</v>
-      </c>
-      <c r="BB27" s="10" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="BC27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD27" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="BE27" s="9" t="n">
-        <v>40626.98</v>
-      </c>
-      <c r="BF27" s="10" t="n">
-        <v>0.0037</v>
-      </c>
-      <c r="BG27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH27" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="BI27" s="9" t="n">
-        <v>34641.63</v>
-      </c>
-      <c r="BJ27" s="10" t="n">
-        <v>0.0033</v>
-      </c>
-      <c r="BK27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL27" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="BM27" s="9" t="n">
-        <v>29892.76</v>
-      </c>
-      <c r="BN27" s="10" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="BO27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP27" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="BQ27" s="9" t="n">
-        <v>27629.29</v>
-      </c>
-      <c r="BR27" s="10" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="BS27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT27" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="BU27" s="9" t="n">
-        <v>25089.54</v>
-      </c>
-      <c r="BV27" s="10" t="n">
-        <v>0.0029</v>
-      </c>
-      <c r="BW27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX27" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="BY27" s="9" t="n">
-        <v>29659.51</v>
-      </c>
-      <c r="BZ27" s="10" t="n">
-        <v>0.0033</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AJ27" s="8" t="n"/>
+      <c r="AK27" s="9" t="n"/>
+      <c r="AL27" s="10" t="n"/>
+      <c r="AM27" s="11" t="n"/>
+      <c r="AN27" s="8" t="n"/>
+      <c r="AO27" s="9" t="n"/>
+      <c r="AP27" s="10" t="n"/>
+      <c r="AQ27" s="11" t="n"/>
+      <c r="AR27" s="8" t="n"/>
+      <c r="AS27" s="9" t="n"/>
+      <c r="AT27" s="10" t="n"/>
+      <c r="AU27" s="11" t="n"/>
+      <c r="AV27" s="8" t="n"/>
+      <c r="AW27" s="9" t="n"/>
+      <c r="AX27" s="10" t="n"/>
+      <c r="AY27" s="11" t="n"/>
+      <c r="AZ27" s="8" t="n"/>
+      <c r="BA27" s="9" t="n"/>
+      <c r="BB27" s="10" t="n"/>
+      <c r="BC27" s="11" t="n"/>
+      <c r="BD27" s="8" t="n"/>
+      <c r="BE27" s="9" t="n"/>
+      <c r="BF27" s="10" t="n"/>
+      <c r="BG27" s="11" t="n"/>
+      <c r="BH27" s="8" t="n"/>
+      <c r="BI27" s="9" t="n"/>
+      <c r="BJ27" s="10" t="n"/>
+      <c r="BK27" s="11" t="n"/>
+      <c r="BL27" s="8" t="n"/>
+      <c r="BM27" s="9" t="n"/>
+      <c r="BN27" s="10" t="n"/>
+      <c r="BO27" s="11" t="n"/>
+      <c r="BP27" s="8" t="n"/>
+      <c r="BQ27" s="9" t="n"/>
+      <c r="BR27" s="10" t="n"/>
+      <c r="BS27" s="11" t="n"/>
+      <c r="BT27" s="8" t="n"/>
+      <c r="BU27" s="9" t="n"/>
+      <c r="BV27" s="10" t="n"/>
+      <c r="BW27" s="11" t="n"/>
+      <c r="BX27" s="8" t="n"/>
+      <c r="BY27" s="9" t="n"/>
+      <c r="BZ27" s="10" t="n"/>
       <c r="CA27" s="11" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>The Great Eastern Shipping Company Limited</t>
+          <t>Central Depository Services (India) Limited</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>INE017A01032</t>
+          <t>INE736A01011</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Transport Services</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>2205298</v>
+        <v>2264603</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>29780.34</v>
+        <v>30187.16</v>
       </c>
       <c r="F28" s="10" t="n">
         <v>0.002</v>
@@ -6574,132 +6488,218 @@
         <v>0</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>2205298</v>
+        <v>2264603</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>32706.77</v>
+        <v>29564.39</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>0.0023</v>
+        <v>0.0021</v>
       </c>
       <c r="K28" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="8" t="n">
-        <v>2205298</v>
+        <v>2264603</v>
       </c>
       <c r="M28" s="9" t="n">
-        <v>31290.97</v>
+        <v>28185.25</v>
       </c>
       <c r="N28" s="10" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="O28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="Q28" s="9" t="n">
+        <v>28805.75</v>
+      </c>
+      <c r="R28" s="10" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="S28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="U28" s="9" t="n">
+        <v>25349.97</v>
+      </c>
+      <c r="V28" s="10" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="W28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="Y28" s="9" t="n">
+        <v>28810.28</v>
+      </c>
+      <c r="Z28" s="10" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="AA28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="AC28" s="9" t="n">
+        <v>29897.29</v>
+      </c>
+      <c r="AD28" s="10" t="n">
         <v>0.0022</v>
       </c>
-      <c r="O28" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" s="8" t="n">
-        <v>2205298</v>
-      </c>
-      <c r="Q28" s="9" t="n">
-        <v>34773.14</v>
-      </c>
-      <c r="R28" s="10" t="n">
+      <c r="AE28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="AG28" s="9" t="n">
+        <v>32691.81</v>
+      </c>
+      <c r="AH28" s="10" t="n">
         <v>0.0025</v>
       </c>
-      <c r="S28" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v>2205298</v>
-      </c>
-      <c r="U28" s="9" t="n">
-        <v>31198.35</v>
-      </c>
-      <c r="V28" s="10" t="n">
-        <v>0.0024</v>
-      </c>
-      <c r="W28" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" s="8" t="n">
-        <v>2205298</v>
-      </c>
-      <c r="Y28" s="9" t="n">
-        <v>29526.73</v>
-      </c>
-      <c r="Z28" s="10" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="AA28" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" s="8" t="n">
-        <v>2205298</v>
-      </c>
-      <c r="AC28" s="9" t="n">
-        <v>26516.5</v>
-      </c>
-      <c r="AD28" s="10" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="AE28" s="11" t="n">
-        <v>0.3305575398932319</v>
-      </c>
-      <c r="AF28" s="8" t="n">
-        <v>1657424</v>
-      </c>
-      <c r="AG28" s="9" t="n">
-        <v>18712.32</v>
-      </c>
-      <c r="AH28" s="10" t="n">
-        <v>0.0014</v>
-      </c>
       <c r="AI28" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ28" s="8" t="n"/>
-      <c r="AK28" s="9" t="n"/>
-      <c r="AL28" s="10" t="n"/>
-      <c r="AM28" s="11" t="n"/>
-      <c r="AN28" s="8" t="n"/>
-      <c r="AO28" s="9" t="n"/>
-      <c r="AP28" s="10" t="n"/>
-      <c r="AQ28" s="11" t="n"/>
-      <c r="AR28" s="8" t="n"/>
-      <c r="AS28" s="9" t="n"/>
-      <c r="AT28" s="10" t="n"/>
-      <c r="AU28" s="11" t="n"/>
-      <c r="AV28" s="8" t="n"/>
-      <c r="AW28" s="9" t="n"/>
-      <c r="AX28" s="10" t="n"/>
-      <c r="AY28" s="11" t="n"/>
-      <c r="AZ28" s="8" t="n"/>
-      <c r="BA28" s="9" t="n"/>
-      <c r="BB28" s="10" t="n"/>
-      <c r="BC28" s="11" t="n"/>
-      <c r="BD28" s="8" t="n"/>
-      <c r="BE28" s="9" t="n"/>
-      <c r="BF28" s="10" t="n"/>
-      <c r="BG28" s="11" t="n"/>
-      <c r="BH28" s="8" t="n"/>
-      <c r="BI28" s="9" t="n"/>
-      <c r="BJ28" s="10" t="n"/>
-      <c r="BK28" s="11" t="n"/>
-      <c r="BL28" s="8" t="n"/>
-      <c r="BM28" s="9" t="n"/>
-      <c r="BN28" s="10" t="n"/>
-      <c r="BO28" s="11" t="n"/>
-      <c r="BP28" s="8" t="n"/>
-      <c r="BQ28" s="9" t="n"/>
-      <c r="BR28" s="10" t="n"/>
-      <c r="BS28" s="11" t="n"/>
-      <c r="BT28" s="8" t="n"/>
-      <c r="BU28" s="9" t="n"/>
-      <c r="BV28" s="10" t="n"/>
-      <c r="BW28" s="11" t="n"/>
-      <c r="BX28" s="8" t="n"/>
-      <c r="BY28" s="9" t="n"/>
-      <c r="BZ28" s="10" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="AK28" s="9" t="n">
+        <v>36623.16</v>
+      </c>
+      <c r="AL28" s="10" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="AM28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="AO28" s="9" t="n">
+        <v>35943.78<